--- a/data/NFLX_data.xlsx
+++ b/data/NFLX_data.xlsx
@@ -469,22 +469,22 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45912</v>
+        <v>45915</v>
       </c>
       <c r="B2" t="n">
-        <v>120.3059997558594</v>
+        <v>118.8399963378906</v>
       </c>
       <c r="C2" t="n">
-        <v>121.1780014038086</v>
+        <v>120.7239990234375</v>
       </c>
       <c r="D2" t="n">
-        <v>118.2399978637695</v>
+        <v>117.3209991455078</v>
       </c>
       <c r="E2" t="n">
-        <v>118.8440017700195</v>
+        <v>120.2259979248047</v>
       </c>
       <c r="F2" t="n">
-        <v>37849000</v>
+        <v>29093000</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -495,22 +495,22 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45915</v>
+        <v>45916</v>
       </c>
       <c r="B3" t="n">
-        <v>118.8399963378906</v>
+        <v>120.5640029907227</v>
       </c>
       <c r="C3" t="n">
-        <v>120.7239990234375</v>
+        <v>120.9000015258789</v>
       </c>
       <c r="D3" t="n">
-        <v>117.3209991455078</v>
+        <v>119.7279968261719</v>
       </c>
       <c r="E3" t="n">
-        <v>120.2259979248047</v>
+        <v>120.0510025024414</v>
       </c>
       <c r="F3" t="n">
-        <v>29093000</v>
+        <v>24047000</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -521,22 +521,22 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>45916</v>
+        <v>45917</v>
       </c>
       <c r="B4" t="n">
-        <v>120.5640029907227</v>
+        <v>122.1019973754883</v>
       </c>
       <c r="C4" t="n">
-        <v>120.9000015258789</v>
+        <v>123.3929977416992</v>
       </c>
       <c r="D4" t="n">
-        <v>119.7279968261719</v>
+        <v>120.661003112793</v>
       </c>
       <c r="E4" t="n">
-        <v>120.0510025024414</v>
+        <v>122.8499984741211</v>
       </c>
       <c r="F4" t="n">
-        <v>24047000</v>
+        <v>34598000</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -547,22 +547,22 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>45917</v>
+        <v>45918</v>
       </c>
       <c r="B5" t="n">
-        <v>122.1019973754883</v>
+        <v>122.0820007324219</v>
       </c>
       <c r="C5" t="n">
-        <v>123.3929977416992</v>
+        <v>123.3000030517578</v>
       </c>
       <c r="D5" t="n">
-        <v>120.661003112793</v>
+        <v>120.5500030517578</v>
       </c>
       <c r="E5" t="n">
-        <v>122.8499984741211</v>
+        <v>120.7779998779297</v>
       </c>
       <c r="F5" t="n">
-        <v>34598000</v>
+        <v>31691000</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -573,22 +573,22 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>45918</v>
+        <v>45919</v>
       </c>
       <c r="B6" t="n">
-        <v>122.0820007324219</v>
+        <v>121.8619995117188</v>
       </c>
       <c r="C6" t="n">
-        <v>123.3000030517578</v>
+        <v>122.995002746582</v>
       </c>
       <c r="D6" t="n">
-        <v>120.5500030517578</v>
+        <v>120.8099975585938</v>
       </c>
       <c r="E6" t="n">
-        <v>120.7779998779297</v>
+        <v>122.6969985961914</v>
       </c>
       <c r="F6" t="n">
-        <v>31691000</v>
+        <v>49476000</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -599,22 +599,22 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>45919</v>
+        <v>45922</v>
       </c>
       <c r="B7" t="n">
-        <v>121.8619995117188</v>
+        <v>122.1900024414062</v>
       </c>
       <c r="C7" t="n">
-        <v>122.995002746582</v>
+        <v>122.9759979248047</v>
       </c>
       <c r="D7" t="n">
-        <v>120.8099975585938</v>
+        <v>121.4240036010742</v>
       </c>
       <c r="E7" t="n">
-        <v>122.6969985961914</v>
+        <v>122.7369995117188</v>
       </c>
       <c r="F7" t="n">
-        <v>49476000</v>
+        <v>25468000</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -625,22 +625,22 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>45922</v>
+        <v>45923</v>
       </c>
       <c r="B8" t="n">
-        <v>122.1900024414062</v>
+        <v>122.7330017089844</v>
       </c>
       <c r="C8" t="n">
-        <v>122.9759979248047</v>
+        <v>122.7789993286133</v>
       </c>
       <c r="D8" t="n">
-        <v>121.4240036010742</v>
+        <v>120.8470001220703</v>
       </c>
       <c r="E8" t="n">
-        <v>122.7369995117188</v>
+        <v>121.8470001220703</v>
       </c>
       <c r="F8" t="n">
-        <v>25468000</v>
+        <v>24991000</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -651,22 +651,22 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>45923</v>
+        <v>45924</v>
       </c>
       <c r="B9" t="n">
-        <v>122.7330017089844</v>
+        <v>121.8610000610352</v>
       </c>
       <c r="C9" t="n">
-        <v>122.7789993286133</v>
+        <v>122.1500015258789</v>
       </c>
       <c r="D9" t="n">
-        <v>120.8470001220703</v>
+        <v>119.4199981689453</v>
       </c>
       <c r="E9" t="n">
-        <v>121.8470001220703</v>
+        <v>120.3949966430664</v>
       </c>
       <c r="F9" t="n">
-        <v>24991000</v>
+        <v>27731000</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -677,22 +677,22 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>45924</v>
+        <v>45925</v>
       </c>
       <c r="B10" t="n">
-        <v>121.8610000610352</v>
+        <v>120.3089981079102</v>
       </c>
       <c r="C10" t="n">
-        <v>122.1500015258789</v>
+        <v>121.6839981079102</v>
       </c>
       <c r="D10" t="n">
-        <v>119.4199981689453</v>
+        <v>119.1510009765625</v>
       </c>
       <c r="E10" t="n">
-        <v>120.3949966430664</v>
+        <v>120.8239974975586</v>
       </c>
       <c r="F10" t="n">
-        <v>27731000</v>
+        <v>19978000</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -703,22 +703,22 @@
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>45925</v>
+        <v>45926</v>
       </c>
       <c r="B11" t="n">
-        <v>120.3089981079102</v>
+        <v>120.5419998168945</v>
       </c>
       <c r="C11" t="n">
-        <v>121.6839981079102</v>
+        <v>121.4000015258789</v>
       </c>
       <c r="D11" t="n">
-        <v>119.1510009765625</v>
+        <v>120</v>
       </c>
       <c r="E11" t="n">
-        <v>120.8239974975586</v>
+        <v>121.0609970092773</v>
       </c>
       <c r="F11" t="n">
-        <v>19978000</v>
+        <v>19450000</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -729,22 +729,22 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>45926</v>
+        <v>45929</v>
       </c>
       <c r="B12" t="n">
-        <v>120.5419998168945</v>
+        <v>120.5</v>
       </c>
       <c r="C12" t="n">
-        <v>121.4000015258789</v>
+        <v>122.4489974975586</v>
       </c>
       <c r="D12" t="n">
-        <v>120</v>
+        <v>118.7539978027344</v>
       </c>
       <c r="E12" t="n">
-        <v>121.0609970092773</v>
+        <v>120.640998840332</v>
       </c>
       <c r="F12" t="n">
-        <v>19450000</v>
+        <v>30332000</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -755,22 +755,22 @@
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="B13" t="n">
-        <v>120.5</v>
+        <v>120.640998840332</v>
       </c>
       <c r="C13" t="n">
-        <v>122.4489974975586</v>
+        <v>120.8499984741211</v>
       </c>
       <c r="D13" t="n">
-        <v>118.7539978027344</v>
+        <v>117.8000030517578</v>
       </c>
       <c r="E13" t="n">
-        <v>120.640998840332</v>
+        <v>119.8919982910156</v>
       </c>
       <c r="F13" t="n">
-        <v>30332000</v>
+        <v>38303000</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -781,22 +781,22 @@
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>45930</v>
+        <v>45931</v>
       </c>
       <c r="B14" t="n">
-        <v>120.640998840332</v>
+        <v>117.5490036010742</v>
       </c>
       <c r="C14" t="n">
-        <v>120.8499984741211</v>
+        <v>117.9140014648438</v>
       </c>
       <c r="D14" t="n">
-        <v>117.8000030517578</v>
+        <v>116.3209991455078</v>
       </c>
       <c r="E14" t="n">
-        <v>119.8919982910156</v>
+        <v>117.0899963378906</v>
       </c>
       <c r="F14" t="n">
-        <v>38303000</v>
+        <v>41102000</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -807,22 +807,22 @@
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>45931</v>
+        <v>45932</v>
       </c>
       <c r="B15" t="n">
-        <v>117.5490036010742</v>
+        <v>116.1500015258789</v>
       </c>
       <c r="C15" t="n">
-        <v>117.9140014648438</v>
+        <v>116.3330001831055</v>
       </c>
       <c r="D15" t="n">
-        <v>116.3209991455078</v>
+        <v>113.4000015258789</v>
       </c>
       <c r="E15" t="n">
-        <v>117.0899963378906</v>
+        <v>116.2529983520508</v>
       </c>
       <c r="F15" t="n">
-        <v>41102000</v>
+        <v>46855000</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -833,22 +833,22 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>45932</v>
+        <v>45933</v>
       </c>
       <c r="B16" t="n">
-        <v>116.1500015258789</v>
+        <v>116.5</v>
       </c>
       <c r="C16" t="n">
-        <v>116.3330001831055</v>
+        <v>116.8000030517578</v>
       </c>
       <c r="D16" t="n">
-        <v>113.4000015258789</v>
+        <v>114.3219985961914</v>
       </c>
       <c r="E16" t="n">
-        <v>116.2529983520508</v>
+        <v>115.3320007324219</v>
       </c>
       <c r="F16" t="n">
-        <v>46855000</v>
+        <v>31374000</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -859,22 +859,22 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>45933</v>
+        <v>45936</v>
       </c>
       <c r="B17" t="n">
-        <v>116.5</v>
+        <v>116.0370025634766</v>
       </c>
       <c r="C17" t="n">
-        <v>116.8000030517578</v>
+        <v>116.3580017089844</v>
       </c>
       <c r="D17" t="n">
-        <v>114.3219985961914</v>
+        <v>114.5449981689453</v>
       </c>
       <c r="E17" t="n">
-        <v>115.3320007324219</v>
+        <v>116.3310012817383</v>
       </c>
       <c r="F17" t="n">
-        <v>31374000</v>
+        <v>29686000</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -885,22 +885,22 @@
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>45936</v>
+        <v>45937</v>
       </c>
       <c r="B18" t="n">
-        <v>116.0370025634766</v>
+        <v>117.7789993286133</v>
       </c>
       <c r="C18" t="n">
-        <v>116.3580017089844</v>
+        <v>120.1370010375977</v>
       </c>
       <c r="D18" t="n">
-        <v>114.5449981689453</v>
+        <v>117.7460021972656</v>
       </c>
       <c r="E18" t="n">
-        <v>116.3310012817383</v>
+        <v>119.1060028076172</v>
       </c>
       <c r="F18" t="n">
-        <v>29686000</v>
+        <v>33091000</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -911,22 +911,22 @@
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>45937</v>
+        <v>45938</v>
       </c>
       <c r="B19" t="n">
-        <v>117.7789993286133</v>
+        <v>119.7109985351562</v>
       </c>
       <c r="C19" t="n">
-        <v>120.1370010375977</v>
+        <v>121.7389984130859</v>
       </c>
       <c r="D19" t="n">
-        <v>117.7460021972656</v>
+        <v>119.1999969482422</v>
       </c>
       <c r="E19" t="n">
-        <v>119.1060028076172</v>
+        <v>121.4250030517578</v>
       </c>
       <c r="F19" t="n">
-        <v>33091000</v>
+        <v>28514000</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -937,22 +937,22 @@
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>45938</v>
+        <v>45939</v>
       </c>
       <c r="B20" t="n">
-        <v>119.7109985351562</v>
+        <v>121.4250030517578</v>
       </c>
       <c r="C20" t="n">
-        <v>121.7389984130859</v>
+        <v>123.75</v>
       </c>
       <c r="D20" t="n">
-        <v>119.1999969482422</v>
+        <v>121.181999206543</v>
       </c>
       <c r="E20" t="n">
-        <v>121.4250030517578</v>
+        <v>123.1070022583008</v>
       </c>
       <c r="F20" t="n">
-        <v>28514000</v>
+        <v>28241000</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -963,22 +963,22 @@
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>45939</v>
+        <v>45940</v>
       </c>
       <c r="B21" t="n">
-        <v>121.4250030517578</v>
+        <v>122.9000015258789</v>
       </c>
       <c r="C21" t="n">
-        <v>123.75</v>
+        <v>124.6999969482422</v>
       </c>
       <c r="D21" t="n">
-        <v>121.181999206543</v>
+        <v>121.9100036621094</v>
       </c>
       <c r="E21" t="n">
-        <v>123.1070022583008</v>
+        <v>122.0080032348633</v>
       </c>
       <c r="F21" t="n">
-        <v>28241000</v>
+        <v>42798000</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -989,22 +989,22 @@
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>45940</v>
+        <v>45943</v>
       </c>
       <c r="B22" t="n">
-        <v>122.9000015258789</v>
+        <v>122.1350021362305</v>
       </c>
       <c r="C22" t="n">
-        <v>124.6999969482422</v>
+        <v>123.1119995117188</v>
       </c>
       <c r="D22" t="n">
-        <v>121.9100036621094</v>
+        <v>120.6809997558594</v>
       </c>
       <c r="E22" t="n">
-        <v>122.0080032348633</v>
+        <v>121.9029998779297</v>
       </c>
       <c r="F22" t="n">
-        <v>42798000</v>
+        <v>24608000</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -1015,22 +1015,22 @@
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>45943</v>
+        <v>45944</v>
       </c>
       <c r="B23" t="n">
-        <v>122.1350021362305</v>
+        <v>121.4749984741211</v>
       </c>
       <c r="C23" t="n">
-        <v>123.1119995117188</v>
+        <v>122.4290008544922</v>
       </c>
       <c r="D23" t="n">
-        <v>120.6809997558594</v>
+        <v>120.3099975585938</v>
       </c>
       <c r="E23" t="n">
-        <v>121.9029998779297</v>
+        <v>121.5350036621094</v>
       </c>
       <c r="F23" t="n">
-        <v>24608000</v>
+        <v>23624000</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -1041,22 +1041,22 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>45944</v>
+        <v>45945</v>
       </c>
       <c r="B24" t="n">
-        <v>121.4749984741211</v>
+        <v>121.3010025024414</v>
       </c>
       <c r="C24" t="n">
-        <v>122.4290008544922</v>
+        <v>121.9619979858398</v>
       </c>
       <c r="D24" t="n">
-        <v>120.3099975585938</v>
+        <v>120.161003112793</v>
       </c>
       <c r="E24" t="n">
-        <v>121.5350036621094</v>
+        <v>120.3290023803711</v>
       </c>
       <c r="F24" t="n">
-        <v>23624000</v>
+        <v>20252000</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -1067,22 +1067,22 @@
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>45945</v>
+        <v>45946</v>
       </c>
       <c r="B25" t="n">
-        <v>121.3010025024414</v>
+        <v>121.2149963378906</v>
       </c>
       <c r="C25" t="n">
-        <v>121.9619979858398</v>
+        <v>121.6709976196289</v>
       </c>
       <c r="D25" t="n">
-        <v>120.161003112793</v>
+        <v>117.5999984741211</v>
       </c>
       <c r="E25" t="n">
-        <v>120.3290023803711</v>
+        <v>118.359001159668</v>
       </c>
       <c r="F25" t="n">
-        <v>20252000</v>
+        <v>28326000</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -1093,22 +1093,22 @@
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>45946</v>
+        <v>45947</v>
       </c>
       <c r="B26" t="n">
-        <v>121.2149963378906</v>
+        <v>118.3600006103516</v>
       </c>
       <c r="C26" t="n">
-        <v>121.6709976196289</v>
+        <v>120.3119964599609</v>
       </c>
       <c r="D26" t="n">
-        <v>117.5999984741211</v>
+        <v>117.8949966430664</v>
       </c>
       <c r="E26" t="n">
-        <v>118.359001159668</v>
+        <v>119.9359970092773</v>
       </c>
       <c r="F26" t="n">
-        <v>28326000</v>
+        <v>29571000</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -1119,22 +1119,22 @@
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>45947</v>
+        <v>45950</v>
       </c>
       <c r="B27" t="n">
-        <v>118.3600006103516</v>
+        <v>120.7880020141602</v>
       </c>
       <c r="C27" t="n">
-        <v>120.3119964599609</v>
+        <v>124.7760009765625</v>
       </c>
       <c r="D27" t="n">
-        <v>117.8949966430664</v>
+        <v>120.6900024414062</v>
       </c>
       <c r="E27" t="n">
-        <v>119.9359970092773</v>
+        <v>123.8560028076172</v>
       </c>
       <c r="F27" t="n">
-        <v>29571000</v>
+        <v>39862000</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -1145,22 +1145,22 @@
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>45950</v>
+        <v>45951</v>
       </c>
       <c r="B28" t="n">
-        <v>120.7880020141602</v>
+        <v>124.2829971313477</v>
       </c>
       <c r="C28" t="n">
-        <v>124.7760009765625</v>
+        <v>124.8600006103516</v>
       </c>
       <c r="D28" t="n">
-        <v>120.6900024414062</v>
+        <v>123.1760025024414</v>
       </c>
       <c r="E28" t="n">
-        <v>123.8560028076172</v>
+        <v>124.1350021362305</v>
       </c>
       <c r="F28" t="n">
-        <v>39862000</v>
+        <v>65082000</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
@@ -1171,22 +1171,22 @@
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>45951</v>
+        <v>45952</v>
       </c>
       <c r="B29" t="n">
-        <v>124.2829971313477</v>
+        <v>114.2900009155273</v>
       </c>
       <c r="C29" t="n">
-        <v>124.8600006103516</v>
+        <v>115.7600021362305</v>
       </c>
       <c r="D29" t="n">
-        <v>123.1760025024414</v>
+        <v>111.2509994506836</v>
       </c>
       <c r="E29" t="n">
-        <v>124.1350021362305</v>
+        <v>111.6370010375977</v>
       </c>
       <c r="F29" t="n">
-        <v>65082000</v>
+        <v>147890000</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -1197,22 +1197,22 @@
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>45952</v>
+        <v>45953</v>
       </c>
       <c r="B30" t="n">
-        <v>114.2900009155273</v>
+        <v>112.6900024414062</v>
       </c>
       <c r="C30" t="n">
-        <v>115.7600021362305</v>
+        <v>112.7829971313477</v>
       </c>
       <c r="D30" t="n">
-        <v>111.2509994506836</v>
+        <v>109.9729995727539</v>
       </c>
       <c r="E30" t="n">
-        <v>111.6370010375977</v>
+        <v>111.359001159668</v>
       </c>
       <c r="F30" t="n">
-        <v>147890000</v>
+        <v>68497000</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -1223,22 +1223,22 @@
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>45953</v>
+        <v>45954</v>
       </c>
       <c r="B31" t="n">
-        <v>112.6900024414062</v>
+        <v>111.0999984741211</v>
       </c>
       <c r="C31" t="n">
-        <v>112.7829971313477</v>
+        <v>111.4509963989258</v>
       </c>
       <c r="D31" t="n">
-        <v>109.9729995727539</v>
+        <v>109.4410018920898</v>
       </c>
       <c r="E31" t="n">
-        <v>111.359001159668</v>
+        <v>109.4690017700195</v>
       </c>
       <c r="F31" t="n">
-        <v>68497000</v>
+        <v>60280000</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -1249,22 +1249,22 @@
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>45954</v>
+        <v>45957</v>
       </c>
       <c r="B32" t="n">
-        <v>111.0999984741211</v>
+        <v>110.0670013427734</v>
       </c>
       <c r="C32" t="n">
-        <v>111.4509963989258</v>
+        <v>110.2279968261719</v>
       </c>
       <c r="D32" t="n">
-        <v>109.4410018920898</v>
+        <v>108.7300033569336</v>
       </c>
       <c r="E32" t="n">
-        <v>109.4690017700195</v>
+        <v>109.4560012817383</v>
       </c>
       <c r="F32" t="n">
-        <v>60280000</v>
+        <v>46911000</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
@@ -1275,22 +1275,22 @@
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>45957</v>
+        <v>45958</v>
       </c>
       <c r="B33" t="n">
-        <v>110.0670013427734</v>
+        <v>109.4000015258789</v>
       </c>
       <c r="C33" t="n">
-        <v>110.2279968261719</v>
+        <v>111.697998046875</v>
       </c>
       <c r="D33" t="n">
-        <v>108.7300033569336</v>
+        <v>109.3010025024414</v>
       </c>
       <c r="E33" t="n">
-        <v>109.4560012817383</v>
+        <v>110.25</v>
       </c>
       <c r="F33" t="n">
-        <v>46911000</v>
+        <v>40209000</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -1301,22 +1301,22 @@
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>45958</v>
+        <v>45959</v>
       </c>
       <c r="B34" t="n">
-        <v>109.4000015258789</v>
+        <v>109.984001159668</v>
       </c>
       <c r="C34" t="n">
-        <v>111.697998046875</v>
+        <v>110.8550033569336</v>
       </c>
       <c r="D34" t="n">
-        <v>109.3010025024414</v>
+        <v>109.5999984741211</v>
       </c>
       <c r="E34" t="n">
-        <v>110.25</v>
+        <v>110.0410003662109</v>
       </c>
       <c r="F34" t="n">
-        <v>40209000</v>
+        <v>33995000</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
@@ -1327,22 +1327,22 @@
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>45959</v>
+        <v>45960</v>
       </c>
       <c r="B35" t="n">
-        <v>109.984001159668</v>
+        <v>109.4400024414062</v>
       </c>
       <c r="C35" t="n">
-        <v>110.8550033569336</v>
+        <v>110.6159973144531</v>
       </c>
       <c r="D35" t="n">
-        <v>109.5999984741211</v>
+        <v>108.8109970092773</v>
       </c>
       <c r="E35" t="n">
-        <v>110.0410003662109</v>
+        <v>108.9000015258789</v>
       </c>
       <c r="F35" t="n">
-        <v>33995000</v>
+        <v>41581000</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
@@ -1353,22 +1353,22 @@
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>45960</v>
+        <v>45961</v>
       </c>
       <c r="B36" t="n">
-        <v>109.4400024414062</v>
+        <v>110.5390014648438</v>
       </c>
       <c r="C36" t="n">
-        <v>110.6159973144531</v>
+        <v>113.4879989624023</v>
       </c>
       <c r="D36" t="n">
-        <v>108.8109970092773</v>
+        <v>110.197998046875</v>
       </c>
       <c r="E36" t="n">
-        <v>108.9000015258789</v>
+        <v>111.8860015869141</v>
       </c>
       <c r="F36" t="n">
-        <v>41581000</v>
+        <v>68665000</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -1379,22 +1379,22 @@
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>45961</v>
+        <v>45964</v>
       </c>
       <c r="B37" t="n">
-        <v>110.5390014648438</v>
+        <v>113.3239974975586</v>
       </c>
       <c r="C37" t="n">
-        <v>113.4879989624023</v>
+        <v>113.3499984741211</v>
       </c>
       <c r="D37" t="n">
-        <v>110.197998046875</v>
+        <v>107.5149993896484</v>
       </c>
       <c r="E37" t="n">
-        <v>111.8860015869141</v>
+        <v>110.0090026855469</v>
       </c>
       <c r="F37" t="n">
-        <v>68665000</v>
+        <v>58634000</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
@@ -1405,22 +1405,22 @@
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>45964</v>
+        <v>45965</v>
       </c>
       <c r="B38" t="n">
-        <v>113.3239974975586</v>
+        <v>109.9990005493164</v>
       </c>
       <c r="C38" t="n">
-        <v>113.3499984741211</v>
+        <v>110.4599990844727</v>
       </c>
       <c r="D38" t="n">
-        <v>107.5149993896484</v>
+        <v>108.6679992675781</v>
       </c>
       <c r="E38" t="n">
-        <v>110.0090026855469</v>
+        <v>109.2959976196289</v>
       </c>
       <c r="F38" t="n">
-        <v>58634000</v>
+        <v>38718000</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
@@ -1431,22 +1431,22 @@
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>45965</v>
+        <v>45966</v>
       </c>
       <c r="B39" t="n">
-        <v>109.9990005493164</v>
+        <v>108.5</v>
       </c>
       <c r="C39" t="n">
-        <v>110.4599990844727</v>
+        <v>110.0849990844727</v>
       </c>
       <c r="D39" t="n">
-        <v>108.6679992675781</v>
+        <v>107.3369979858398</v>
       </c>
       <c r="E39" t="n">
-        <v>109.2959976196289</v>
+        <v>109.8460006713867</v>
       </c>
       <c r="F39" t="n">
-        <v>38718000</v>
+        <v>35539000</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
@@ -1457,22 +1457,22 @@
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>45966</v>
+        <v>45967</v>
       </c>
       <c r="B40" t="n">
-        <v>108.5</v>
+        <v>109.4580001831055</v>
       </c>
       <c r="C40" t="n">
-        <v>110.0849990844727</v>
+        <v>110.370002746582</v>
       </c>
       <c r="D40" t="n">
-        <v>107.3369979858398</v>
+        <v>108.5130004882812</v>
       </c>
       <c r="E40" t="n">
-        <v>109.8460006713867</v>
+        <v>109.7020034790039</v>
       </c>
       <c r="F40" t="n">
-        <v>35539000</v>
+        <v>36532000</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
@@ -1483,22 +1483,22 @@
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>45967</v>
+        <v>45968</v>
       </c>
       <c r="B41" t="n">
-        <v>109.4580001831055</v>
+        <v>109.4179992675781</v>
       </c>
       <c r="C41" t="n">
-        <v>110.370002746582</v>
+        <v>110.8219985961914</v>
       </c>
       <c r="D41" t="n">
-        <v>108.5130004882812</v>
+        <v>108.75</v>
       </c>
       <c r="E41" t="n">
-        <v>109.7020034790039</v>
+        <v>110.3659973144531</v>
       </c>
       <c r="F41" t="n">
-        <v>36532000</v>
+        <v>44125000</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
@@ -1509,22 +1509,22 @@
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>45968</v>
+        <v>45971</v>
       </c>
       <c r="B42" t="n">
-        <v>109.4179992675781</v>
+        <v>110.6719970703125</v>
       </c>
       <c r="C42" t="n">
-        <v>110.8219985961914</v>
+        <v>112.8199996948242</v>
       </c>
       <c r="D42" t="n">
-        <v>108.75</v>
+        <v>110.4049987792969</v>
       </c>
       <c r="E42" t="n">
-        <v>110.3659973144531</v>
+        <v>112.0070037841797</v>
       </c>
       <c r="F42" t="n">
-        <v>44125000</v>
+        <v>36929000</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
@@ -1535,22 +1535,22 @@
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>45971</v>
+        <v>45972</v>
       </c>
       <c r="B43" t="n">
-        <v>110.6719970703125</v>
+        <v>111.7600021362305</v>
       </c>
       <c r="C43" t="n">
-        <v>112.8199996948242</v>
+        <v>113.9219970703125</v>
       </c>
       <c r="D43" t="n">
-        <v>110.4049987792969</v>
+        <v>111.2799987792969</v>
       </c>
       <c r="E43" t="n">
-        <v>112.0070037841797</v>
+        <v>113.6439971923828</v>
       </c>
       <c r="F43" t="n">
-        <v>36929000</v>
+        <v>27966000</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
@@ -1561,22 +1561,22 @@
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
-        <v>45972</v>
+        <v>45973</v>
       </c>
       <c r="B44" t="n">
-        <v>111.7600021362305</v>
+        <v>113.8170013427734</v>
       </c>
       <c r="C44" t="n">
-        <v>113.9219970703125</v>
+        <v>116.4339981079102</v>
       </c>
       <c r="D44" t="n">
-        <v>111.2799987792969</v>
+        <v>112.8259963989258</v>
       </c>
       <c r="E44" t="n">
-        <v>113.6439971923828</v>
+        <v>115.75</v>
       </c>
       <c r="F44" t="n">
-        <v>27966000</v>
+        <v>39221000</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
@@ -1587,22 +1587,22 @@
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
-        <v>45973</v>
+        <v>45974</v>
       </c>
       <c r="B45" t="n">
-        <v>113.8170013427734</v>
+        <v>115.8499984741211</v>
       </c>
       <c r="C45" t="n">
-        <v>116.4339981079102</v>
+        <v>116.7330017089844</v>
       </c>
       <c r="D45" t="n">
-        <v>112.8259963989258</v>
+        <v>114.5690002441406</v>
       </c>
       <c r="E45" t="n">
-        <v>115.75</v>
+        <v>115.4229965209961</v>
       </c>
       <c r="F45" t="n">
-        <v>39221000</v>
+        <v>40144000</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
@@ -1613,22 +1613,22 @@
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
-        <v>45974</v>
+        <v>45975</v>
       </c>
       <c r="B46" t="n">
-        <v>115.8499984741211</v>
+        <v>114.2730026245117</v>
       </c>
       <c r="C46" t="n">
-        <v>116.7330017089844</v>
+        <v>114.2730026245117</v>
       </c>
       <c r="D46" t="n">
-        <v>114.5690002441406</v>
+        <v>110.7210006713867</v>
       </c>
       <c r="E46" t="n">
-        <v>115.4229965209961</v>
+        <v>111.2170028686523</v>
       </c>
       <c r="F46" t="n">
-        <v>40144000</v>
+        <v>47607000</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
@@ -1639,74 +1639,74 @@
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
-        <v>45975</v>
+        <v>45978</v>
       </c>
       <c r="B47" t="n">
-        <v>114.2730026245117</v>
+        <v>110.75</v>
       </c>
       <c r="C47" t="n">
-        <v>114.2730026245117</v>
+        <v>111.8499984741211</v>
       </c>
       <c r="D47" t="n">
-        <v>110.7210006713867</v>
+        <v>109.5500030517578</v>
       </c>
       <c r="E47" t="n">
-        <v>111.2170028686523</v>
+        <v>110.2900009155273</v>
       </c>
       <c r="F47" t="n">
-        <v>47607000</v>
+        <v>26082700</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
-        <v>45978</v>
+        <v>45979</v>
       </c>
       <c r="B48" t="n">
-        <v>110.75</v>
+        <v>110.2900009155273</v>
       </c>
       <c r="C48" t="n">
-        <v>111.8499984741211</v>
+        <v>115.25</v>
       </c>
       <c r="D48" t="n">
-        <v>109.5500030517578</v>
+        <v>109.1999969482422</v>
       </c>
       <c r="E48" t="n">
-        <v>110.2900009155273</v>
+        <v>114.0899963378906</v>
       </c>
       <c r="F48" t="n">
-        <v>26082700</v>
+        <v>43440600</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>45979</v>
+        <v>45980</v>
       </c>
       <c r="B49" t="n">
-        <v>110.2900009155273</v>
+        <v>113</v>
       </c>
       <c r="C49" t="n">
-        <v>115.25</v>
+        <v>113.3399963378906</v>
       </c>
       <c r="D49" t="n">
-        <v>109.1999969482422</v>
+        <v>108.6100006103516</v>
       </c>
       <c r="E49" t="n">
-        <v>114.0899963378906</v>
+        <v>110</v>
       </c>
       <c r="F49" t="n">
-        <v>43440600</v>
+        <v>31868100</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
@@ -1717,22 +1717,22 @@
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>45980</v>
+        <v>45981</v>
       </c>
       <c r="B50" t="n">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C50" t="n">
-        <v>113.3399963378906</v>
+        <v>111.0999984741211</v>
       </c>
       <c r="D50" t="n">
-        <v>108.6100006103516</v>
+        <v>105.3899993896484</v>
       </c>
       <c r="E50" t="n">
-        <v>110</v>
+        <v>105.6699981689453</v>
       </c>
       <c r="F50" t="n">
-        <v>31868100</v>
+        <v>36918500</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
-        <v>45981</v>
+        <v>45982</v>
       </c>
       <c r="B51" t="n">
-        <v>111</v>
+        <v>105.129997253418</v>
       </c>
       <c r="C51" t="n">
-        <v>111.0999984741211</v>
+        <v>106.5299987792969</v>
       </c>
       <c r="D51" t="n">
-        <v>105.3899993896484</v>
+        <v>103.8099975585938</v>
       </c>
       <c r="E51" t="n">
-        <v>105.6699981689453</v>
+        <v>104.3099975585938</v>
       </c>
       <c r="F51" t="n">
-        <v>36918500</v>
+        <v>41232700</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
@@ -1769,22 +1769,22 @@
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
-        <v>45982</v>
+        <v>45985</v>
       </c>
       <c r="B52" t="n">
-        <v>105.129997253418</v>
+        <v>104.25</v>
       </c>
       <c r="C52" t="n">
-        <v>106.5299987792969</v>
+        <v>108.0400009155273</v>
       </c>
       <c r="D52" t="n">
-        <v>103.8099975585938</v>
+        <v>103.3199996948242</v>
       </c>
       <c r="E52" t="n">
-        <v>104.3099975585938</v>
+        <v>106.9700012207031</v>
       </c>
       <c r="F52" t="n">
-        <v>41232700</v>
+        <v>62918300</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
@@ -1795,22 +1795,22 @@
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
-        <v>45985</v>
+        <v>45986</v>
       </c>
       <c r="B53" t="n">
-        <v>104.25</v>
+        <v>106.120002746582</v>
       </c>
       <c r="C53" t="n">
-        <v>108.0400009155273</v>
+        <v>106.3000030517578</v>
       </c>
       <c r="D53" t="n">
-        <v>103.3199996948242</v>
+        <v>103.8199996948242</v>
       </c>
       <c r="E53" t="n">
-        <v>106.9700012207031</v>
+        <v>104.4000015258789</v>
       </c>
       <c r="F53" t="n">
-        <v>62918300</v>
+        <v>35122600</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
@@ -1821,22 +1821,22 @@
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
-        <v>45986</v>
+        <v>45987</v>
       </c>
       <c r="B54" t="n">
-        <v>106.120002746582</v>
+        <v>105.7399978637695</v>
       </c>
       <c r="C54" t="n">
-        <v>106.3000030517578</v>
+        <v>106.9499969482422</v>
       </c>
       <c r="D54" t="n">
-        <v>103.8199996948242</v>
+        <v>105.2200012207031</v>
       </c>
       <c r="E54" t="n">
-        <v>104.4000015258789</v>
+        <v>106.1399993896484</v>
       </c>
       <c r="F54" t="n">
-        <v>35122600</v>
+        <v>27951000</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
@@ -1847,22 +1847,22 @@
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
-        <v>45987</v>
+        <v>45989</v>
       </c>
       <c r="B55" t="n">
-        <v>105.7399978637695</v>
+        <v>106.4400024414062</v>
       </c>
       <c r="C55" t="n">
-        <v>106.9499969482422</v>
+        <v>107.9400024414062</v>
       </c>
       <c r="D55" t="n">
-        <v>105.2200012207031</v>
+        <v>106.2399978637695</v>
       </c>
       <c r="E55" t="n">
-        <v>106.1399993896484</v>
+        <v>107.5800018310547</v>
       </c>
       <c r="F55" t="n">
-        <v>27951000</v>
+        <v>15021600</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
@@ -1873,22 +1873,22 @@
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
-        <v>45989</v>
+        <v>45992</v>
       </c>
       <c r="B56" t="n">
-        <v>106.4400024414062</v>
+        <v>106.5100021362305</v>
       </c>
       <c r="C56" t="n">
-        <v>107.9400024414062</v>
+        <v>109.3399963378906</v>
       </c>
       <c r="D56" t="n">
-        <v>106.2399978637695</v>
+        <v>106.3099975585938</v>
       </c>
       <c r="E56" t="n">
-        <v>107.5800018310547</v>
+        <v>109.129997253418</v>
       </c>
       <c r="F56" t="n">
-        <v>15021600</v>
+        <v>24873400</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
@@ -1899,22 +1899,22 @@
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
-        <v>45992</v>
+        <v>45993</v>
       </c>
       <c r="B57" t="n">
-        <v>106.5100021362305</v>
+        <v>109.2099990844727</v>
       </c>
       <c r="C57" t="n">
-        <v>109.3399963378906</v>
+        <v>109.7300033569336</v>
       </c>
       <c r="D57" t="n">
-        <v>106.3099975585938</v>
+        <v>107.5199966430664</v>
       </c>
       <c r="E57" t="n">
-        <v>109.129997253418</v>
+        <v>109.3499984741211</v>
       </c>
       <c r="F57" t="n">
-        <v>24873400</v>
+        <v>25763000</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
@@ -1925,22 +1925,22 @@
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
-        <v>45993</v>
+        <v>45994</v>
       </c>
       <c r="B58" t="n">
-        <v>109.2099990844727</v>
+        <v>106.5899963378906</v>
       </c>
       <c r="C58" t="n">
-        <v>109.7300033569336</v>
+        <v>106.870002746582</v>
       </c>
       <c r="D58" t="n">
-        <v>107.5199966430664</v>
+        <v>102.0299987792969</v>
       </c>
       <c r="E58" t="n">
-        <v>109.3499984741211</v>
+        <v>103.9599990844727</v>
       </c>
       <c r="F58" t="n">
-        <v>25763000</v>
+        <v>53593400</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
@@ -1951,22 +1951,22 @@
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
-        <v>45994</v>
+        <v>45995</v>
       </c>
       <c r="B59" t="n">
-        <v>106.5899963378906</v>
+        <v>103.5699996948242</v>
       </c>
       <c r="C59" t="n">
-        <v>106.870002746582</v>
+        <v>103.8000030517578</v>
       </c>
       <c r="D59" t="n">
-        <v>102.0299987792969</v>
+        <v>101.7699966430664</v>
       </c>
       <c r="E59" t="n">
-        <v>103.9599990844727</v>
+        <v>103.2200012207031</v>
       </c>
       <c r="F59" t="n">
-        <v>53593400</v>
+        <v>51779100</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
@@ -1977,22 +1977,22 @@
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
-        <v>45995</v>
+        <v>45996</v>
       </c>
       <c r="B60" t="n">
-        <v>103.5699996948242</v>
+        <v>98.77999877929688</v>
       </c>
       <c r="C60" t="n">
-        <v>103.8000030517578</v>
+        <v>104.7900009155273</v>
       </c>
       <c r="D60" t="n">
-        <v>101.7699966430664</v>
+        <v>97.73999786376953</v>
       </c>
       <c r="E60" t="n">
-        <v>103.2200012207031</v>
+        <v>100.2399978637695</v>
       </c>
       <c r="F60" t="n">
-        <v>51779100</v>
+        <v>133363600</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
@@ -2003,22 +2003,22 @@
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
-        <v>45996</v>
+        <v>45999</v>
       </c>
       <c r="B61" t="n">
-        <v>98.77999877929688</v>
+        <v>99.87000274658203</v>
       </c>
       <c r="C61" t="n">
-        <v>104.7900009155273</v>
+        <v>99.88999938964844</v>
       </c>
       <c r="D61" t="n">
-        <v>97.73999786376953</v>
+        <v>95.30000305175781</v>
       </c>
       <c r="E61" t="n">
-        <v>100.2399978637695</v>
+        <v>96.79000091552734</v>
       </c>
       <c r="F61" t="n">
-        <v>133363600</v>
+        <v>100906300</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
@@ -2029,22 +2029,22 @@
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
-        <v>45999</v>
+        <v>46000</v>
       </c>
       <c r="B62" t="n">
-        <v>99.87000274658203</v>
+        <v>97.02999877929688</v>
       </c>
       <c r="C62" t="n">
-        <v>99.88999938964844</v>
+        <v>97.23999786376953</v>
       </c>
       <c r="D62" t="n">
-        <v>95.30000305175781</v>
+        <v>95.44999694824219</v>
       </c>
       <c r="E62" t="n">
-        <v>96.79000091552734</v>
+        <v>96.70999908447266</v>
       </c>
       <c r="F62" t="n">
-        <v>100906300</v>
+        <v>51745600</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
@@ -2055,22 +2055,22 @@
     </row>
     <row r="63">
       <c r="A63" s="1" t="n">
-        <v>46000</v>
+        <v>46001</v>
       </c>
       <c r="B63" t="n">
-        <v>97.02999877929688</v>
+        <v>96.73999786376953</v>
       </c>
       <c r="C63" t="n">
-        <v>97.23999786376953</v>
+        <v>96.97000122070312</v>
       </c>
       <c r="D63" t="n">
-        <v>95.44999694824219</v>
+        <v>92.34999847412109</v>
       </c>
       <c r="E63" t="n">
-        <v>96.70999908447266</v>
+        <v>92.70999908447266</v>
       </c>
       <c r="F63" t="n">
-        <v>51745600</v>
+        <v>74129300</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
@@ -2081,22 +2081,22 @@
     </row>
     <row r="64">
       <c r="A64" s="1" t="n">
-        <v>46001</v>
+        <v>46002</v>
       </c>
       <c r="B64" t="n">
-        <v>96.73999786376953</v>
+        <v>93.90000152587891</v>
       </c>
       <c r="C64" t="n">
-        <v>96.97000122070312</v>
+        <v>94.81999969482422</v>
       </c>
       <c r="D64" t="n">
-        <v>92.34999847412109</v>
+        <v>92.76000213623047</v>
       </c>
       <c r="E64" t="n">
-        <v>92.70999908447266</v>
+        <v>94.08999633789062</v>
       </c>
       <c r="F64" t="n">
-        <v>74129300</v>
+        <v>43949000</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
@@ -2107,22 +2107,22 @@
     </row>
     <row r="65">
       <c r="A65" s="1" t="n">
-        <v>46002</v>
+        <v>46003</v>
       </c>
       <c r="B65" t="n">
-        <v>93.90000152587891</v>
+        <v>95.5</v>
       </c>
       <c r="C65" t="n">
-        <v>94.81999969482422</v>
+        <v>96.91999816894531</v>
       </c>
       <c r="D65" t="n">
-        <v>92.76000213623047</v>
+        <v>94.65000152587891</v>
       </c>
       <c r="E65" t="n">
-        <v>94.08999633789062</v>
+        <v>95.19000244140625</v>
       </c>
       <c r="F65" t="n">
-        <v>43949000</v>
+        <v>49323100</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
@@ -2133,22 +2133,22 @@
     </row>
     <row r="66">
       <c r="A66" s="1" t="n">
-        <v>46003</v>
+        <v>46006</v>
       </c>
       <c r="B66" t="n">
-        <v>95.5</v>
+        <v>96.01999664306641</v>
       </c>
       <c r="C66" t="n">
-        <v>96.91999816894531</v>
+        <v>96.37000274658203</v>
       </c>
       <c r="D66" t="n">
-        <v>94.65000152587891</v>
+        <v>93.52999877929688</v>
       </c>
       <c r="E66" t="n">
-        <v>95.19000244140625</v>
+        <v>93.76999664306641</v>
       </c>
       <c r="F66" t="n">
-        <v>49323100</v>
+        <v>40016500</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
@@ -2159,22 +2159,22 @@
     </row>
     <row r="67">
       <c r="A67" s="1" t="n">
-        <v>46006</v>
+        <v>46007</v>
       </c>
       <c r="B67" t="n">
-        <v>96.01999664306641</v>
+        <v>93.87999725341797</v>
       </c>
       <c r="C67" t="n">
-        <v>96.37000274658203</v>
+        <v>94.93000030517578</v>
       </c>
       <c r="D67" t="n">
-        <v>93.52999877929688</v>
+        <v>93.31999969482422</v>
       </c>
       <c r="E67" t="n">
-        <v>93.76999664306641</v>
+        <v>94.56999969482422</v>
       </c>
       <c r="F67" t="n">
-        <v>40016500</v>
+        <v>34265000</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
@@ -2185,22 +2185,22 @@
     </row>
     <row r="68">
       <c r="A68" s="1" t="n">
-        <v>46007</v>
+        <v>46008</v>
       </c>
       <c r="B68" t="n">
-        <v>93.87999725341797</v>
+        <v>95.98000335693359</v>
       </c>
       <c r="C68" t="n">
-        <v>94.93000030517578</v>
+        <v>97.33000183105469</v>
       </c>
       <c r="D68" t="n">
-        <v>93.31999969482422</v>
+        <v>94.45999908447266</v>
       </c>
       <c r="E68" t="n">
-        <v>94.56999969482422</v>
+        <v>94.79000091552734</v>
       </c>
       <c r="F68" t="n">
-        <v>34265000</v>
+        <v>50472800</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
@@ -2211,22 +2211,22 @@
     </row>
     <row r="69">
       <c r="A69" s="1" t="n">
-        <v>46008</v>
+        <v>46009</v>
       </c>
       <c r="B69" t="n">
-        <v>95.98000335693359</v>
+        <v>95.01999664306641</v>
       </c>
       <c r="C69" t="n">
-        <v>97.33000183105469</v>
+        <v>95.80999755859375</v>
       </c>
       <c r="D69" t="n">
-        <v>94.45999908447266</v>
+        <v>93.58999633789062</v>
       </c>
       <c r="E69" t="n">
-        <v>94.79000091552734</v>
+        <v>94</v>
       </c>
       <c r="F69" t="n">
-        <v>50472800</v>
+        <v>37244700</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
@@ -2237,22 +2237,22 @@
     </row>
     <row r="70">
       <c r="A70" s="1" t="n">
-        <v>46009</v>
+        <v>46010</v>
       </c>
       <c r="B70" t="n">
-        <v>95.01999664306641</v>
+        <v>93.56999969482422</v>
       </c>
       <c r="C70" t="n">
-        <v>95.80999755859375</v>
+        <v>95.54000091552734</v>
       </c>
       <c r="D70" t="n">
-        <v>93.58999633789062</v>
+        <v>93.44999694824219</v>
       </c>
       <c r="E70" t="n">
-        <v>94</v>
+        <v>94.38999938964844</v>
       </c>
       <c r="F70" t="n">
-        <v>37244700</v>
+        <v>78990200</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
@@ -2263,22 +2263,22 @@
     </row>
     <row r="71">
       <c r="A71" s="1" t="n">
-        <v>46010</v>
+        <v>46013</v>
       </c>
       <c r="B71" t="n">
-        <v>93.56999969482422</v>
+        <v>94.70999908447266</v>
       </c>
       <c r="C71" t="n">
-        <v>95.54000091552734</v>
+        <v>94.70999908447266</v>
       </c>
       <c r="D71" t="n">
-        <v>93.44999694824219</v>
+        <v>92.91000366210938</v>
       </c>
       <c r="E71" t="n">
-        <v>94.38999938964844</v>
+        <v>93.23000335693359</v>
       </c>
       <c r="F71" t="n">
-        <v>78990200</v>
+        <v>39484800</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
@@ -2289,22 +2289,22 @@
     </row>
     <row r="72">
       <c r="A72" s="1" t="n">
-        <v>46013</v>
+        <v>46014</v>
       </c>
       <c r="B72" t="n">
-        <v>94.70999908447266</v>
+        <v>93.40000152587891</v>
       </c>
       <c r="C72" t="n">
-        <v>94.70999908447266</v>
+        <v>93.80999755859375</v>
       </c>
       <c r="D72" t="n">
-        <v>92.91000366210938</v>
+        <v>91.33000183105469</v>
       </c>
       <c r="E72" t="n">
-        <v>93.23000335693359</v>
+        <v>93.5</v>
       </c>
       <c r="F72" t="n">
-        <v>39484800</v>
+        <v>25896200</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
@@ -2315,22 +2315,22 @@
     </row>
     <row r="73">
       <c r="A73" s="1" t="n">
-        <v>46014</v>
+        <v>46015</v>
       </c>
       <c r="B73" t="n">
-        <v>93.40000152587891</v>
+        <v>93.11000061035156</v>
       </c>
       <c r="C73" t="n">
-        <v>93.80999755859375</v>
+        <v>93.68000030517578</v>
       </c>
       <c r="D73" t="n">
-        <v>91.33000183105469</v>
+        <v>92.66999816894531</v>
       </c>
       <c r="E73" t="n">
-        <v>93.5</v>
+        <v>93.63999938964844</v>
       </c>
       <c r="F73" t="n">
-        <v>25896200</v>
+        <v>12427900</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
@@ -2341,22 +2341,22 @@
     </row>
     <row r="74">
       <c r="A74" s="1" t="n">
-        <v>46015</v>
+        <v>46017</v>
       </c>
       <c r="B74" t="n">
-        <v>93.11000061035156</v>
+        <v>93.48000335693359</v>
       </c>
       <c r="C74" t="n">
-        <v>93.68000030517578</v>
+        <v>94.69000244140625</v>
       </c>
       <c r="D74" t="n">
-        <v>92.66999816894531</v>
+        <v>93.26999664306641</v>
       </c>
       <c r="E74" t="n">
-        <v>93.63999938964844</v>
+        <v>94.47000122070312</v>
       </c>
       <c r="F74" t="n">
-        <v>12427900</v>
+        <v>22068300</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
@@ -2367,22 +2367,22 @@
     </row>
     <row r="75">
       <c r="A75" s="1" t="n">
-        <v>46017</v>
+        <v>46020</v>
       </c>
       <c r="B75" t="n">
-        <v>93.48000335693359</v>
+        <v>93.98999786376953</v>
       </c>
       <c r="C75" t="n">
-        <v>94.69000244140625</v>
+        <v>94.97000122070312</v>
       </c>
       <c r="D75" t="n">
-        <v>93.26999664306641</v>
+        <v>93.62999725341797</v>
       </c>
       <c r="E75" t="n">
-        <v>94.47000122070312</v>
+        <v>94.15000152587891</v>
       </c>
       <c r="F75" t="n">
-        <v>22068300</v>
+        <v>24493700</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
@@ -2393,22 +2393,22 @@
     </row>
     <row r="76">
       <c r="A76" s="1" t="n">
-        <v>46020</v>
+        <v>46021</v>
       </c>
       <c r="B76" t="n">
+        <v>93.51999664306641</v>
+      </c>
+      <c r="C76" t="n">
         <v>93.98999786376953</v>
       </c>
-      <c r="C76" t="n">
-        <v>94.97000122070312</v>
-      </c>
       <c r="D76" t="n">
-        <v>93.62999725341797</v>
+        <v>93.33999633789062</v>
       </c>
       <c r="E76" t="n">
-        <v>94.15000152587891</v>
+        <v>93.77999877929688</v>
       </c>
       <c r="F76" t="n">
-        <v>24493700</v>
+        <v>23422000</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
@@ -2419,22 +2419,22 @@
     </row>
     <row r="77">
       <c r="A77" s="1" t="n">
-        <v>46021</v>
+        <v>46022</v>
       </c>
       <c r="B77" t="n">
-        <v>93.51999664306641</v>
+        <v>93.59999847412109</v>
       </c>
       <c r="C77" t="n">
-        <v>93.98999786376953</v>
+        <v>94.30999755859375</v>
       </c>
       <c r="D77" t="n">
-        <v>93.33999633789062</v>
+        <v>93.19999694824219</v>
       </c>
       <c r="E77" t="n">
-        <v>93.77999877929688</v>
+        <v>93.76000213623047</v>
       </c>
       <c r="F77" t="n">
-        <v>23422000</v>
+        <v>23495200</v>
       </c>
       <c r="G77" t="n">
         <v>0</v>
@@ -2445,22 +2445,22 @@
     </row>
     <row r="78">
       <c r="A78" s="1" t="n">
-        <v>46022</v>
+        <v>46024</v>
       </c>
       <c r="B78" t="n">
-        <v>93.59999847412109</v>
+        <v>94.12999725341797</v>
       </c>
       <c r="C78" t="n">
-        <v>94.30999755859375</v>
+        <v>94.12999725341797</v>
       </c>
       <c r="D78" t="n">
-        <v>93.19999694824219</v>
+        <v>90.80999755859375</v>
       </c>
       <c r="E78" t="n">
-        <v>93.76000213623047</v>
+        <v>90.98999786376953</v>
       </c>
       <c r="F78" t="n">
-        <v>23495200</v>
+        <v>41155400</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
@@ -2471,22 +2471,22 @@
     </row>
     <row r="79">
       <c r="A79" s="1" t="n">
-        <v>46024</v>
+        <v>46027</v>
       </c>
       <c r="B79" t="n">
-        <v>94.12999725341797</v>
+        <v>90.91999816894531</v>
       </c>
       <c r="C79" t="n">
-        <v>94.12999725341797</v>
+        <v>92.62999725341797</v>
       </c>
       <c r="D79" t="n">
-        <v>90.80999755859375</v>
+        <v>90.83999633789062</v>
       </c>
       <c r="E79" t="n">
-        <v>90.98999786376953</v>
+        <v>91.45999908447266</v>
       </c>
       <c r="F79" t="n">
-        <v>41155400</v>
+        <v>39183300</v>
       </c>
       <c r="G79" t="n">
         <v>0</v>
@@ -2497,22 +2497,22 @@
     </row>
     <row r="80">
       <c r="A80" s="1" t="n">
-        <v>46027</v>
+        <v>46028</v>
       </c>
       <c r="B80" t="n">
-        <v>90.91999816894531</v>
+        <v>91.54000091552734</v>
       </c>
       <c r="C80" t="n">
-        <v>92.62999725341797</v>
+        <v>91.63999938964844</v>
       </c>
       <c r="D80" t="n">
-        <v>90.83999633789062</v>
+        <v>89.73999786376953</v>
       </c>
       <c r="E80" t="n">
-        <v>91.45999908447266</v>
+        <v>90.65000152587891</v>
       </c>
       <c r="F80" t="n">
-        <v>39183300</v>
+        <v>43331000</v>
       </c>
       <c r="G80" t="n">
         <v>0</v>
@@ -2523,22 +2523,22 @@
     </row>
     <row r="81">
       <c r="A81" s="1" t="n">
-        <v>46028</v>
+        <v>46029</v>
       </c>
       <c r="B81" t="n">
-        <v>91.54000091552734</v>
+        <v>91.55999755859375</v>
       </c>
       <c r="C81" t="n">
-        <v>91.63999938964844</v>
+        <v>92.41999816894531</v>
       </c>
       <c r="D81" t="n">
-        <v>89.73999786376953</v>
+        <v>90.05999755859375</v>
       </c>
       <c r="E81" t="n">
-        <v>90.65000152587891</v>
+        <v>90.73000335693359</v>
       </c>
       <c r="F81" t="n">
-        <v>43331000</v>
+        <v>36525700</v>
       </c>
       <c r="G81" t="n">
         <v>0</v>
@@ -2549,22 +2549,22 @@
     </row>
     <row r="82">
       <c r="A82" s="1" t="n">
-        <v>46029</v>
+        <v>46030</v>
       </c>
       <c r="B82" t="n">
-        <v>91.55999755859375</v>
+        <v>90.44999694824219</v>
       </c>
       <c r="C82" t="n">
-        <v>92.41999816894531</v>
+        <v>91.25</v>
       </c>
       <c r="D82" t="n">
-        <v>90.05999755859375</v>
+        <v>89.58000183105469</v>
       </c>
       <c r="E82" t="n">
-        <v>90.73000335693359</v>
+        <v>90.52999877929688</v>
       </c>
       <c r="F82" t="n">
-        <v>36525700</v>
+        <v>40068700</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
@@ -2575,22 +2575,22 @@
     </row>
     <row r="83">
       <c r="A83" s="1" t="n">
-        <v>46030</v>
+        <v>46031</v>
       </c>
       <c r="B83" t="n">
-        <v>90.44999694824219</v>
+        <v>90.02999877929688</v>
       </c>
       <c r="C83" t="n">
-        <v>91.25</v>
+        <v>90.05000305175781</v>
       </c>
       <c r="D83" t="n">
-        <v>89.58000183105469</v>
+        <v>88.31999969482422</v>
       </c>
       <c r="E83" t="n">
-        <v>90.52999877929688</v>
+        <v>89.45999908447266</v>
       </c>
       <c r="F83" t="n">
-        <v>40068700</v>
+        <v>55579500</v>
       </c>
       <c r="G83" t="n">
         <v>0</v>
@@ -2601,22 +2601,22 @@
     </row>
     <row r="84">
       <c r="A84" s="1" t="n">
-        <v>46031</v>
+        <v>46034</v>
       </c>
       <c r="B84" t="n">
-        <v>90.02999877929688</v>
+        <v>89.69000244140625</v>
       </c>
       <c r="C84" t="n">
-        <v>90.05000305175781</v>
+        <v>90.33999633789062</v>
       </c>
       <c r="D84" t="n">
-        <v>88.31999969482422</v>
+        <v>89.33000183105469</v>
       </c>
       <c r="E84" t="n">
-        <v>89.45999908447266</v>
+        <v>89.41000366210938</v>
       </c>
       <c r="F84" t="n">
-        <v>55579500</v>
+        <v>36290600</v>
       </c>
       <c r="G84" t="n">
         <v>0</v>
@@ -2627,22 +2627,22 @@
     </row>
     <row r="85">
       <c r="A85" s="1" t="n">
-        <v>46034</v>
+        <v>46035</v>
       </c>
       <c r="B85" t="n">
-        <v>89.69000244140625</v>
+        <v>89.44000244140625</v>
       </c>
       <c r="C85" t="n">
-        <v>90.33999633789062</v>
+        <v>91.15000152587891</v>
       </c>
       <c r="D85" t="n">
-        <v>89.33000183105469</v>
+        <v>89.06999969482422</v>
       </c>
       <c r="E85" t="n">
-        <v>89.41000366210938</v>
+        <v>90.31999969482422</v>
       </c>
       <c r="F85" t="n">
-        <v>36290600</v>
+        <v>45221100</v>
       </c>
       <c r="G85" t="n">
         <v>0</v>
@@ -2653,22 +2653,22 @@
     </row>
     <row r="86">
       <c r="A86" s="1" t="n">
-        <v>46035</v>
+        <v>46036</v>
       </c>
       <c r="B86" t="n">
-        <v>89.44000244140625</v>
+        <v>91.23999786376953</v>
       </c>
       <c r="C86" t="n">
-        <v>91.15000152587891</v>
+        <v>91.58000183105469</v>
       </c>
       <c r="D86" t="n">
-        <v>89.06999969482422</v>
+        <v>87.94999694824219</v>
       </c>
       <c r="E86" t="n">
-        <v>90.31999969482422</v>
+        <v>88.55000305175781</v>
       </c>
       <c r="F86" t="n">
-        <v>45221100</v>
+        <v>49737700</v>
       </c>
       <c r="G86" t="n">
         <v>0</v>
@@ -2679,22 +2679,22 @@
     </row>
     <row r="87">
       <c r="A87" s="1" t="n">
-        <v>46036</v>
+        <v>46037</v>
       </c>
       <c r="B87" t="n">
-        <v>91.23999786376953</v>
+        <v>89.01999664306641</v>
       </c>
       <c r="C87" t="n">
-        <v>91.58000183105469</v>
+        <v>89.88999938964844</v>
       </c>
       <c r="D87" t="n">
-        <v>87.94999694824219</v>
+        <v>87.81999969482422</v>
       </c>
       <c r="E87" t="n">
-        <v>88.55000305175781</v>
+        <v>88.05000305175781</v>
       </c>
       <c r="F87" t="n">
-        <v>49737700</v>
+        <v>36945100</v>
       </c>
       <c r="G87" t="n">
         <v>0</v>
@@ -2705,22 +2705,22 @@
     </row>
     <row r="88">
       <c r="A88" s="1" t="n">
-        <v>46037</v>
+        <v>46038</v>
       </c>
       <c r="B88" t="n">
-        <v>89.01999664306641</v>
+        <v>88.33999633789062</v>
       </c>
       <c r="C88" t="n">
-        <v>89.88999938964844</v>
+        <v>88.51000213623047</v>
       </c>
       <c r="D88" t="n">
-        <v>87.81999969482422</v>
+        <v>87.77999877929688</v>
       </c>
       <c r="E88" t="n">
-        <v>88.05000305175781</v>
+        <v>88</v>
       </c>
       <c r="F88" t="n">
-        <v>36945100</v>
+        <v>48130500</v>
       </c>
       <c r="G88" t="n">
         <v>0</v>
@@ -2731,22 +2731,22 @@
     </row>
     <row r="89">
       <c r="A89" s="1" t="n">
-        <v>46038</v>
+        <v>46042</v>
       </c>
       <c r="B89" t="n">
-        <v>88.33999633789062</v>
+        <v>88.97000122070312</v>
       </c>
       <c r="C89" t="n">
-        <v>88.51000213623047</v>
+        <v>89.90000152587891</v>
       </c>
       <c r="D89" t="n">
-        <v>87.77999877929688</v>
+        <v>87.01999664306641</v>
       </c>
       <c r="E89" t="n">
-        <v>88</v>
+        <v>87.26000213623047</v>
       </c>
       <c r="F89" t="n">
-        <v>48130500</v>
+        <v>109729700</v>
       </c>
       <c r="G89" t="n">
         <v>0</v>
@@ -2757,22 +2757,22 @@
     </row>
     <row r="90">
       <c r="A90" s="1" t="n">
-        <v>46042</v>
+        <v>46043</v>
       </c>
       <c r="B90" t="n">
-        <v>88.97000122070312</v>
+        <v>82.51999664306641</v>
       </c>
       <c r="C90" t="n">
-        <v>89.90000152587891</v>
+        <v>86</v>
       </c>
       <c r="D90" t="n">
-        <v>87.01999664306641</v>
+        <v>81.93000030517578</v>
       </c>
       <c r="E90" t="n">
-        <v>87.26000213623047</v>
+        <v>85.36000061035156</v>
       </c>
       <c r="F90" t="n">
-        <v>109729700</v>
+        <v>127940700</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
@@ -2783,22 +2783,22 @@
     </row>
     <row r="91">
       <c r="A91" s="1" t="n">
-        <v>46043</v>
+        <v>46044</v>
       </c>
       <c r="B91" t="n">
-        <v>82.51999664306641</v>
+        <v>85.01999664306641</v>
       </c>
       <c r="C91" t="n">
-        <v>86</v>
+        <v>85.09999847412109</v>
       </c>
       <c r="D91" t="n">
-        <v>81.93000030517578</v>
+        <v>82.98000335693359</v>
       </c>
       <c r="E91" t="n">
-        <v>85.36000061035156</v>
+        <v>83.54000091552734</v>
       </c>
       <c r="F91" t="n">
-        <v>127940700</v>
+        <v>69113300</v>
       </c>
       <c r="G91" t="n">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="92">
       <c r="A92" s="1" t="n">
-        <v>46044</v>
+        <v>46045</v>
       </c>
       <c r="B92" t="n">
-        <v>85.01999664306641</v>
+        <v>83.43000030517578</v>
       </c>
       <c r="C92" t="n">
-        <v>85.09999847412109</v>
+        <v>86.30000305175781</v>
       </c>
       <c r="D92" t="n">
-        <v>82.98000335693359</v>
+        <v>83.27999877929688</v>
       </c>
       <c r="E92" t="n">
-        <v>83.54000091552734</v>
+        <v>86.12000274658203</v>
       </c>
       <c r="F92" t="n">
-        <v>69113300</v>
+        <v>64520400</v>
       </c>
       <c r="G92" t="n">
         <v>0</v>
@@ -2835,22 +2835,22 @@
     </row>
     <row r="93">
       <c r="A93" s="1" t="n">
-        <v>46045</v>
+        <v>46048</v>
       </c>
       <c r="B93" t="n">
-        <v>83.43000030517578</v>
+        <v>86.91999816894531</v>
       </c>
       <c r="C93" t="n">
-        <v>86.30000305175781</v>
+        <v>86.94000244140625</v>
       </c>
       <c r="D93" t="n">
-        <v>83.27999877929688</v>
+        <v>85.34999847412109</v>
       </c>
       <c r="E93" t="n">
-        <v>86.12000274658203</v>
+        <v>85.69999694824219</v>
       </c>
       <c r="F93" t="n">
-        <v>64520400</v>
+        <v>40941900</v>
       </c>
       <c r="G93" t="n">
         <v>0</v>
@@ -2861,22 +2861,22 @@
     </row>
     <row r="94">
       <c r="A94" s="1" t="n">
-        <v>46048</v>
+        <v>46049</v>
       </c>
       <c r="B94" t="n">
-        <v>86.91999816894531</v>
+        <v>85.27999877929688</v>
       </c>
       <c r="C94" t="n">
-        <v>86.94000244140625</v>
+        <v>85.59999847412109</v>
       </c>
       <c r="D94" t="n">
-        <v>85.34999847412109</v>
+        <v>83.87999725341797</v>
       </c>
       <c r="E94" t="n">
-        <v>85.69999694824219</v>
+        <v>85.58000183105469</v>
       </c>
       <c r="F94" t="n">
-        <v>40941900</v>
+        <v>37790800</v>
       </c>
       <c r="G94" t="n">
         <v>0</v>
@@ -2887,22 +2887,22 @@
     </row>
     <row r="95">
       <c r="A95" s="1" t="n">
-        <v>46049</v>
+        <v>46050</v>
       </c>
       <c r="B95" t="n">
-        <v>85.27999877929688</v>
+        <v>85.62999725341797</v>
       </c>
       <c r="C95" t="n">
-        <v>85.59999847412109</v>
+        <v>86.47000122070312</v>
       </c>
       <c r="D95" t="n">
-        <v>83.87999725341797</v>
+        <v>84.30000305175781</v>
       </c>
       <c r="E95" t="n">
-        <v>85.58000183105469</v>
+        <v>84.63999938964844</v>
       </c>
       <c r="F95" t="n">
-        <v>37790800</v>
+        <v>37762600</v>
       </c>
       <c r="G95" t="n">
         <v>0</v>
@@ -2913,22 +2913,22 @@
     </row>
     <row r="96">
       <c r="A96" s="1" t="n">
-        <v>46050</v>
+        <v>46051</v>
       </c>
       <c r="B96" t="n">
-        <v>85.62999725341797</v>
+        <v>84.30999755859375</v>
       </c>
       <c r="C96" t="n">
-        <v>86.47000122070312</v>
+        <v>84.37999725341797</v>
       </c>
       <c r="D96" t="n">
-        <v>84.30000305175781</v>
+        <v>82.34999847412109</v>
       </c>
       <c r="E96" t="n">
-        <v>84.63999938964844</v>
+        <v>83.16000366210938</v>
       </c>
       <c r="F96" t="n">
-        <v>37762600</v>
+        <v>42278100</v>
       </c>
       <c r="G96" t="n">
         <v>0</v>
@@ -2939,22 +2939,22 @@
     </row>
     <row r="97">
       <c r="A97" s="1" t="n">
-        <v>46051</v>
+        <v>46052</v>
       </c>
       <c r="B97" t="n">
-        <v>84.30999755859375</v>
+        <v>83.09999847412109</v>
       </c>
       <c r="C97" t="n">
-        <v>84.37999725341797</v>
+        <v>84.05999755859375</v>
       </c>
       <c r="D97" t="n">
-        <v>82.34999847412109</v>
+        <v>82.77999877929688</v>
       </c>
       <c r="E97" t="n">
-        <v>83.16000366210938</v>
+        <v>83.48999786376953</v>
       </c>
       <c r="F97" t="n">
-        <v>42278100</v>
+        <v>45755000</v>
       </c>
       <c r="G97" t="n">
         <v>0</v>
@@ -2965,22 +2965,22 @@
     </row>
     <row r="98">
       <c r="A98" s="1" t="n">
-        <v>46052</v>
+        <v>46055</v>
       </c>
       <c r="B98" t="n">
-        <v>83.09999847412109</v>
+        <v>83.52999877929688</v>
       </c>
       <c r="C98" t="n">
-        <v>84.05999755859375</v>
+        <v>85.26999664306641</v>
       </c>
       <c r="D98" t="n">
-        <v>82.77999877929688</v>
+        <v>82.72000122070312</v>
       </c>
       <c r="E98" t="n">
-        <v>83.48999786376953</v>
+        <v>82.76000213623047</v>
       </c>
       <c r="F98" t="n">
-        <v>45755000</v>
+        <v>41445300</v>
       </c>
       <c r="G98" t="n">
         <v>0</v>
@@ -2991,22 +2991,22 @@
     </row>
     <row r="99">
       <c r="A99" s="1" t="n">
-        <v>46055</v>
+        <v>46056</v>
       </c>
       <c r="B99" t="n">
-        <v>83.52999877929688</v>
+        <v>82.23000335693359</v>
       </c>
       <c r="C99" t="n">
-        <v>85.26999664306641</v>
+        <v>82.44999694824219</v>
       </c>
       <c r="D99" t="n">
-        <v>82.72000122070312</v>
+        <v>79.62000274658203</v>
       </c>
       <c r="E99" t="n">
-        <v>82.76000213623047</v>
+        <v>79.94000244140625</v>
       </c>
       <c r="F99" t="n">
-        <v>41445300</v>
+        <v>49789000</v>
       </c>
       <c r="G99" t="n">
         <v>0</v>
@@ -3017,22 +3017,22 @@
     </row>
     <row r="100">
       <c r="A100" s="1" t="n">
-        <v>46056</v>
+        <v>46057</v>
       </c>
       <c r="B100" t="n">
-        <v>82.23000335693359</v>
+        <v>79.98999786376953</v>
       </c>
       <c r="C100" t="n">
-        <v>82.44999694824219</v>
+        <v>81.44000244140625</v>
       </c>
       <c r="D100" t="n">
-        <v>79.62000274658203</v>
+        <v>79.23000335693359</v>
       </c>
       <c r="E100" t="n">
-        <v>79.94000244140625</v>
+        <v>80.16000366210938</v>
       </c>
       <c r="F100" t="n">
-        <v>49789000</v>
+        <v>48963200</v>
       </c>
       <c r="G100" t="n">
         <v>0</v>
@@ -3043,22 +3043,22 @@
     </row>
     <row r="101">
       <c r="A101" s="1" t="n">
-        <v>46057</v>
+        <v>46058</v>
       </c>
       <c r="B101" t="n">
-        <v>79.98999786376953</v>
+        <v>81.48999786376953</v>
       </c>
       <c r="C101" t="n">
-        <v>81.44000244140625</v>
+        <v>83.30000305175781</v>
       </c>
       <c r="D101" t="n">
-        <v>79.23000335693359</v>
+        <v>80.54000091552734</v>
       </c>
       <c r="E101" t="n">
-        <v>80.16000366210938</v>
+        <v>80.87000274658203</v>
       </c>
       <c r="F101" t="n">
-        <v>48963200</v>
+        <v>54805700</v>
       </c>
       <c r="G101" t="n">
         <v>0</v>
@@ -3069,22 +3069,22 @@
     </row>
     <row r="102">
       <c r="A102" s="1" t="n">
-        <v>46058</v>
+        <v>46059</v>
       </c>
       <c r="B102" t="n">
-        <v>81.48999786376953</v>
+        <v>81.01999664306641</v>
       </c>
       <c r="C102" t="n">
-        <v>83.30000305175781</v>
+        <v>82.48999786376953</v>
       </c>
       <c r="D102" t="n">
-        <v>80.54000091552734</v>
+        <v>80.65000152587891</v>
       </c>
       <c r="E102" t="n">
-        <v>80.87000274658203</v>
+        <v>82.19999694824219</v>
       </c>
       <c r="F102" t="n">
-        <v>54805700</v>
+        <v>46154100</v>
       </c>
       <c r="G102" t="n">
         <v>0</v>
@@ -3095,22 +3095,22 @@
     </row>
     <row r="103">
       <c r="A103" s="1" t="n">
-        <v>46059</v>
+        <v>46062</v>
       </c>
       <c r="B103" t="n">
-        <v>81.01999664306641</v>
+        <v>82.18000030517578</v>
       </c>
       <c r="C103" t="n">
-        <v>82.48999786376953</v>
+        <v>82.20999908447266</v>
       </c>
       <c r="D103" t="n">
-        <v>80.65000152587891</v>
+        <v>79.87000274658203</v>
       </c>
       <c r="E103" t="n">
-        <v>82.19999694824219</v>
+        <v>81.47000122070312</v>
       </c>
       <c r="F103" t="n">
-        <v>46154100</v>
+        <v>42200200</v>
       </c>
       <c r="G103" t="n">
         <v>0</v>
@@ -3121,22 +3121,22 @@
     </row>
     <row r="104">
       <c r="A104" s="1" t="n">
-        <v>46062</v>
+        <v>46063</v>
       </c>
       <c r="B104" t="n">
-        <v>82.18000030517578</v>
+        <v>82.72000122070312</v>
       </c>
       <c r="C104" t="n">
+        <v>84.66000366210938</v>
+      </c>
+      <c r="D104" t="n">
+        <v>82.08999633789062</v>
+      </c>
+      <c r="E104" t="n">
         <v>82.20999908447266</v>
       </c>
-      <c r="D104" t="n">
-        <v>79.87000274658203</v>
-      </c>
-      <c r="E104" t="n">
-        <v>81.47000122070312</v>
-      </c>
       <c r="F104" t="n">
-        <v>42200200</v>
+        <v>43595800</v>
       </c>
       <c r="G104" t="n">
         <v>0</v>
@@ -3147,22 +3147,22 @@
     </row>
     <row r="105">
       <c r="A105" s="1" t="n">
-        <v>46063</v>
+        <v>46064</v>
       </c>
       <c r="B105" t="n">
-        <v>82.72000122070312</v>
+        <v>81.95999908447266</v>
       </c>
       <c r="C105" t="n">
-        <v>84.66000366210938</v>
+        <v>82.48000335693359</v>
       </c>
       <c r="D105" t="n">
-        <v>82.08999633789062</v>
+        <v>79.44999694824219</v>
       </c>
       <c r="E105" t="n">
-        <v>82.20999908447266</v>
+        <v>79.62000274658203</v>
       </c>
       <c r="F105" t="n">
-        <v>43595800</v>
+        <v>40840300</v>
       </c>
       <c r="G105" t="n">
         <v>0</v>
@@ -3173,22 +3173,22 @@
     </row>
     <row r="106">
       <c r="A106" s="1" t="n">
-        <v>46064</v>
+        <v>46065</v>
       </c>
       <c r="B106" t="n">
-        <v>81.95999908447266</v>
+        <v>79.11000061035156</v>
       </c>
       <c r="C106" t="n">
-        <v>82.48000335693359</v>
+        <v>79.15000152587891</v>
       </c>
       <c r="D106" t="n">
-        <v>79.44999694824219</v>
+        <v>75.23000335693359</v>
       </c>
       <c r="E106" t="n">
-        <v>79.62000274658203</v>
+        <v>75.86000061035156</v>
       </c>
       <c r="F106" t="n">
-        <v>40840300</v>
+        <v>73516100</v>
       </c>
       <c r="G106" t="n">
         <v>0</v>
@@ -3199,22 +3199,22 @@
     </row>
     <row r="107">
       <c r="A107" s="1" t="n">
-        <v>46065</v>
+        <v>46066</v>
       </c>
       <c r="B107" t="n">
-        <v>79.11000061035156</v>
+        <v>76.13999938964844</v>
       </c>
       <c r="C107" t="n">
-        <v>79.15000152587891</v>
+        <v>77.18000030517578</v>
       </c>
       <c r="D107" t="n">
-        <v>75.23000335693359</v>
+        <v>75.52999877929688</v>
       </c>
       <c r="E107" t="n">
-        <v>75.86000061035156</v>
+        <v>76.87000274658203</v>
       </c>
       <c r="F107" t="n">
-        <v>73516100</v>
+        <v>42292100</v>
       </c>
       <c r="G107" t="n">
         <v>0</v>
@@ -3225,22 +3225,22 @@
     </row>
     <row r="108">
       <c r="A108" s="1" t="n">
-        <v>46066</v>
+        <v>46070</v>
       </c>
       <c r="B108" t="n">
-        <v>76.13999938964844</v>
+        <v>76.91999816894531</v>
       </c>
       <c r="C108" t="n">
-        <v>77.18000030517578</v>
+        <v>77.87000274658203</v>
       </c>
       <c r="D108" t="n">
-        <v>75.52999877929688</v>
+        <v>75.30000305175781</v>
       </c>
       <c r="E108" t="n">
-        <v>76.87000274658203</v>
+        <v>77</v>
       </c>
       <c r="F108" t="n">
-        <v>42292100</v>
+        <v>35961500</v>
       </c>
       <c r="G108" t="n">
         <v>0</v>
@@ -3251,22 +3251,22 @@
     </row>
     <row r="109">
       <c r="A109" s="1" t="n">
-        <v>46070</v>
+        <v>46071</v>
       </c>
       <c r="B109" t="n">
-        <v>76.91999816894531</v>
+        <v>77.31999969482422</v>
       </c>
       <c r="C109" t="n">
-        <v>77.87000274658203</v>
+        <v>78.31999969482422</v>
       </c>
       <c r="D109" t="n">
-        <v>75.30000305175781</v>
+        <v>76.27999877929688</v>
       </c>
       <c r="E109" t="n">
-        <v>77</v>
+        <v>77.98999786376953</v>
       </c>
       <c r="F109" t="n">
-        <v>35961500</v>
+        <v>29883100</v>
       </c>
       <c r="G109" t="n">
         <v>0</v>
@@ -3277,22 +3277,22 @@
     </row>
     <row r="110">
       <c r="A110" s="1" t="n">
-        <v>46071</v>
+        <v>46072</v>
       </c>
       <c r="B110" t="n">
-        <v>77.31999969482422</v>
+        <v>77.75</v>
       </c>
       <c r="C110" t="n">
-        <v>78.31999969482422</v>
+        <v>78.69999694824219</v>
       </c>
       <c r="D110" t="n">
-        <v>76.27999877929688</v>
+        <v>76.58999633789062</v>
       </c>
       <c r="E110" t="n">
-        <v>77.98999786376953</v>
+        <v>77</v>
       </c>
       <c r="F110" t="n">
-        <v>29883100</v>
+        <v>30139200</v>
       </c>
       <c r="G110" t="n">
         <v>0</v>
@@ -3303,22 +3303,22 @@
     </row>
     <row r="111">
       <c r="A111" s="1" t="n">
-        <v>46072</v>
+        <v>46073</v>
       </c>
       <c r="B111" t="n">
-        <v>77.75</v>
+        <v>76.61000061035156</v>
       </c>
       <c r="C111" t="n">
-        <v>78.69999694824219</v>
+        <v>78.84999847412109</v>
       </c>
       <c r="D111" t="n">
-        <v>76.58999633789062</v>
+        <v>76.40000152587891</v>
       </c>
       <c r="E111" t="n">
-        <v>77</v>
+        <v>78.66999816894531</v>
       </c>
       <c r="F111" t="n">
-        <v>30139200</v>
+        <v>32411300</v>
       </c>
       <c r="G111" t="n">
         <v>0</v>
@@ -3329,22 +3329,22 @@
     </row>
     <row r="112">
       <c r="A112" s="1" t="n">
-        <v>46073</v>
+        <v>46076</v>
       </c>
       <c r="B112" t="n">
-        <v>76.61000061035156</v>
+        <v>77.79000091552734</v>
       </c>
       <c r="C112" t="n">
-        <v>78.84999847412109</v>
+        <v>77.83000183105469</v>
       </c>
       <c r="D112" t="n">
-        <v>76.40000152587891</v>
+        <v>75.01000213623047</v>
       </c>
       <c r="E112" t="n">
-        <v>78.66999816894531</v>
+        <v>76.01999664306641</v>
       </c>
       <c r="F112" t="n">
-        <v>32411300</v>
+        <v>38363000</v>
       </c>
       <c r="G112" t="n">
         <v>0</v>
@@ -3355,22 +3355,22 @@
     </row>
     <row r="113">
       <c r="A113" s="1" t="n">
-        <v>46076</v>
+        <v>46077</v>
       </c>
       <c r="B113" t="n">
-        <v>77.79000091552734</v>
+        <v>75.73000335693359</v>
       </c>
       <c r="C113" t="n">
-        <v>77.83000183105469</v>
+        <v>78.12000274658203</v>
       </c>
       <c r="D113" t="n">
-        <v>75.01000213623047</v>
+        <v>75.20999908447266</v>
       </c>
       <c r="E113" t="n">
-        <v>76.01999664306641</v>
+        <v>78.04000091552734</v>
       </c>
       <c r="F113" t="n">
-        <v>38363000</v>
+        <v>33079100</v>
       </c>
       <c r="G113" t="n">
         <v>0</v>
@@ -3381,22 +3381,22 @@
     </row>
     <row r="114">
       <c r="A114" s="1" t="n">
-        <v>46077</v>
+        <v>46078</v>
       </c>
       <c r="B114" t="n">
-        <v>75.73000335693359</v>
+        <v>79.43000030517578</v>
       </c>
       <c r="C114" t="n">
-        <v>78.12000274658203</v>
+        <v>83.12000274658203</v>
       </c>
       <c r="D114" t="n">
-        <v>75.20999908447266</v>
+        <v>79.25</v>
       </c>
       <c r="E114" t="n">
-        <v>78.04000091552734</v>
+        <v>82.69999694824219</v>
       </c>
       <c r="F114" t="n">
-        <v>33079100</v>
+        <v>69319300</v>
       </c>
       <c r="G114" t="n">
         <v>0</v>
@@ -3407,22 +3407,22 @@
     </row>
     <row r="115">
       <c r="A115" s="1" t="n">
-        <v>46078</v>
+        <v>46079</v>
       </c>
       <c r="B115" t="n">
-        <v>79.43000030517578</v>
+        <v>83.19999694824219</v>
       </c>
       <c r="C115" t="n">
-        <v>83.12000274658203</v>
+        <v>86.5</v>
       </c>
       <c r="D115" t="n">
-        <v>79.25</v>
+        <v>82.80000305175781</v>
       </c>
       <c r="E115" t="n">
-        <v>82.69999694824219</v>
+        <v>84.58999633789062</v>
       </c>
       <c r="F115" t="n">
-        <v>69319300</v>
+        <v>85642500</v>
       </c>
       <c r="G115" t="n">
         <v>0</v>
@@ -3433,22 +3433,22 @@
     </row>
     <row r="116">
       <c r="A116" s="1" t="n">
-        <v>46079</v>
+        <v>46080</v>
       </c>
       <c r="B116" t="n">
-        <v>83.19999694824219</v>
+        <v>94.30000305175781</v>
       </c>
       <c r="C116" t="n">
-        <v>86.5</v>
+        <v>96.75</v>
       </c>
       <c r="D116" t="n">
-        <v>82.80000305175781</v>
+        <v>90.58000183105469</v>
       </c>
       <c r="E116" t="n">
-        <v>84.58999633789062</v>
+        <v>96.23999786376953</v>
       </c>
       <c r="F116" t="n">
-        <v>85642500</v>
+        <v>200767000</v>
       </c>
       <c r="G116" t="n">
         <v>0</v>
@@ -3459,22 +3459,22 @@
     </row>
     <row r="117">
       <c r="A117" s="1" t="n">
-        <v>46080</v>
+        <v>46083</v>
       </c>
       <c r="B117" t="n">
-        <v>94.30000305175781</v>
+        <v>95.26000213623047</v>
       </c>
       <c r="C117" t="n">
-        <v>96.75</v>
+        <v>98.06999969482422</v>
       </c>
       <c r="D117" t="n">
-        <v>90.58000183105469</v>
+        <v>95.19999694824219</v>
       </c>
       <c r="E117" t="n">
-        <v>96.23999786376953</v>
+        <v>97.08999633789062</v>
       </c>
       <c r="F117" t="n">
-        <v>200767000</v>
+        <v>79915400</v>
       </c>
       <c r="G117" t="n">
         <v>0</v>
@@ -3485,22 +3485,22 @@
     </row>
     <row r="118">
       <c r="A118" s="1" t="n">
-        <v>46083</v>
+        <v>46084</v>
       </c>
       <c r="B118" t="n">
-        <v>95.26000213623047</v>
+        <v>96.01000213623047</v>
       </c>
       <c r="C118" t="n">
-        <v>98.06999969482422</v>
+        <v>98.45999908447266</v>
       </c>
       <c r="D118" t="n">
-        <v>95.19999694824219</v>
+        <v>95.33000183105469</v>
       </c>
       <c r="E118" t="n">
-        <v>97.08999633789062</v>
+        <v>97.69999694824219</v>
       </c>
       <c r="F118" t="n">
-        <v>79915400</v>
+        <v>59149000</v>
       </c>
       <c r="G118" t="n">
         <v>0</v>
@@ -3511,22 +3511,22 @@
     </row>
     <row r="119">
       <c r="A119" s="1" t="n">
-        <v>46084</v>
+        <v>46085</v>
       </c>
       <c r="B119" t="n">
-        <v>96.01000213623047</v>
+        <v>97.11000061035156</v>
       </c>
       <c r="C119" t="n">
-        <v>98.45999908447266</v>
+        <v>99.75</v>
       </c>
       <c r="D119" t="n">
-        <v>95.33000183105469</v>
+        <v>96.98999786376953</v>
       </c>
       <c r="E119" t="n">
-        <v>97.69999694824219</v>
+        <v>98.66000366210938</v>
       </c>
       <c r="F119" t="n">
-        <v>59149000</v>
+        <v>52604300</v>
       </c>
       <c r="G119" t="n">
         <v>0</v>
@@ -3537,22 +3537,22 @@
     </row>
     <row r="120">
       <c r="A120" s="1" t="n">
-        <v>46085</v>
+        <v>46086</v>
       </c>
       <c r="B120" t="n">
-        <v>97.11000061035156</v>
+        <v>98.5</v>
       </c>
       <c r="C120" t="n">
-        <v>99.75</v>
+        <v>100.1900024414062</v>
       </c>
       <c r="D120" t="n">
-        <v>96.98999786376953</v>
+        <v>98.09999847412109</v>
       </c>
       <c r="E120" t="n">
-        <v>98.66000366210938</v>
+        <v>99.16999816894531</v>
       </c>
       <c r="F120" t="n">
-        <v>52604300</v>
+        <v>53403000</v>
       </c>
       <c r="G120" t="n">
         <v>0</v>
@@ -3563,22 +3563,22 @@
     </row>
     <row r="121">
       <c r="A121" s="1" t="n">
-        <v>46086</v>
+        <v>46087</v>
       </c>
       <c r="B121" t="n">
-        <v>98.5</v>
+        <v>99.33000183105469</v>
       </c>
       <c r="C121" t="n">
-        <v>100.1900024414062</v>
+        <v>99.87999725341797</v>
       </c>
       <c r="D121" t="n">
-        <v>98.09999847412109</v>
+        <v>97.40000152587891</v>
       </c>
       <c r="E121" t="n">
-        <v>99.16999816894531</v>
+        <v>99.01999664306641</v>
       </c>
       <c r="F121" t="n">
-        <v>53403000</v>
+        <v>41196300</v>
       </c>
       <c r="G121" t="n">
         <v>0</v>
@@ -3589,22 +3589,22 @@
     </row>
     <row r="122">
       <c r="A122" s="1" t="n">
-        <v>46087</v>
+        <v>46090</v>
       </c>
       <c r="B122" t="n">
-        <v>99.33000183105469</v>
+        <v>97.69999694824219</v>
       </c>
       <c r="C122" t="n">
-        <v>99.87999725341797</v>
+        <v>98.94000244140625</v>
       </c>
       <c r="D122" t="n">
-        <v>97.40000152587891</v>
+        <v>96.58000183105469</v>
       </c>
       <c r="E122" t="n">
-        <v>99.01999664306641</v>
+        <v>98.31999969482422</v>
       </c>
       <c r="F122" t="n">
-        <v>41196300</v>
+        <v>48589000</v>
       </c>
       <c r="G122" t="n">
         <v>0</v>
@@ -3615,22 +3615,22 @@
     </row>
     <row r="123">
       <c r="A123" s="1" t="n">
-        <v>46090</v>
+        <v>46091</v>
       </c>
       <c r="B123" t="n">
-        <v>97.69999694824219</v>
+        <v>97.80999755859375</v>
       </c>
       <c r="C123" t="n">
-        <v>98.94000244140625</v>
+        <v>98.48999786376953</v>
       </c>
       <c r="D123" t="n">
-        <v>96.58000183105469</v>
+        <v>96.29000091552734</v>
       </c>
       <c r="E123" t="n">
-        <v>98.31999969482422</v>
+        <v>96.94000244140625</v>
       </c>
       <c r="F123" t="n">
-        <v>48589000</v>
+        <v>41027200</v>
       </c>
       <c r="G123" t="n">
         <v>0</v>
@@ -3641,22 +3641,22 @@
     </row>
     <row r="124">
       <c r="A124" s="1" t="n">
-        <v>46091</v>
+        <v>46092</v>
       </c>
       <c r="B124" t="n">
-        <v>97.80999755859375</v>
+        <v>97.41000366210938</v>
       </c>
       <c r="C124" t="n">
-        <v>98.48999786376953</v>
+        <v>98</v>
       </c>
       <c r="D124" t="n">
-        <v>96.29000091552734</v>
+        <v>94.69000244140625</v>
       </c>
       <c r="E124" t="n">
-        <v>96.94000244140625</v>
+        <v>94.88999938964844</v>
       </c>
       <c r="F124" t="n">
-        <v>41027200</v>
+        <v>33962900</v>
       </c>
       <c r="G124" t="n">
         <v>0</v>
@@ -3667,22 +3667,22 @@
     </row>
     <row r="125">
       <c r="A125" s="1" t="n">
-        <v>46092</v>
+        <v>46093</v>
       </c>
       <c r="B125" t="n">
-        <v>97.41000366210938</v>
+        <v>94.86000061035156</v>
       </c>
       <c r="C125" t="n">
-        <v>98</v>
+        <v>95.40000152587891</v>
       </c>
       <c r="D125" t="n">
-        <v>94.69000244140625</v>
+        <v>93.87000274658203</v>
       </c>
       <c r="E125" t="n">
-        <v>94.88999938964844</v>
+        <v>94.30999755859375</v>
       </c>
       <c r="F125" t="n">
-        <v>33962900</v>
+        <v>34206900</v>
       </c>
       <c r="G125" t="n">
         <v>0</v>
@@ -3693,22 +3693,22 @@
     </row>
     <row r="126">
       <c r="A126" s="1" t="n">
-        <v>46093</v>
+        <v>46094</v>
       </c>
       <c r="B126" t="n">
-        <v>94.86000061035156</v>
+        <v>94.63999938964844</v>
       </c>
       <c r="C126" t="n">
-        <v>95.40000152587891</v>
+        <v>95.68000030517578</v>
       </c>
       <c r="D126" t="n">
-        <v>93.87000274658203</v>
+        <v>94.23999786376953</v>
       </c>
       <c r="E126" t="n">
-        <v>94.30999755859375</v>
+        <v>95.30999755859375</v>
       </c>
       <c r="F126" t="n">
-        <v>34206900</v>
+        <v>29876700</v>
       </c>
       <c r="G126" t="n">
         <v>0</v>
@@ -3719,22 +3719,22 @@
     </row>
     <row r="127">
       <c r="A127" s="1" t="n">
-        <v>46094</v>
+        <v>46097</v>
       </c>
       <c r="B127" t="n">
-        <v>94.63999938964844</v>
+        <v>95.58000183105469</v>
       </c>
       <c r="C127" t="n">
-        <v>95.68000030517578</v>
+        <v>96.09999847412109</v>
       </c>
       <c r="D127" t="n">
-        <v>94.23999786376953</v>
+        <v>94.36000061035156</v>
       </c>
       <c r="E127" t="n">
-        <v>95.30999755859375</v>
+        <v>95.19999694824219</v>
       </c>
       <c r="F127" t="n">
-        <v>29876700</v>
+        <v>34931800</v>
       </c>
       <c r="G127" t="n">
         <v>0</v>
@@ -3745,22 +3745,22 @@
     </row>
     <row r="128">
       <c r="A128" s="1" t="n">
-        <v>46097</v>
+        <v>46098</v>
       </c>
       <c r="B128" t="n">
-        <v>95.58000183105469</v>
+        <v>95.30000305175781</v>
       </c>
       <c r="C128" t="n">
-        <v>96.09999847412109</v>
+        <v>96.33999633789062</v>
       </c>
       <c r="D128" t="n">
+        <v>94.01000213623047</v>
+      </c>
+      <c r="E128" t="n">
         <v>94.36000061035156</v>
       </c>
-      <c r="E128" t="n">
-        <v>95.19999694824219</v>
-      </c>
       <c r="F128" t="n">
-        <v>34931800</v>
+        <v>26434500</v>
       </c>
       <c r="G128" t="n">
         <v>0</v>
@@ -3771,22 +3771,22 @@
     </row>
     <row r="129">
       <c r="A129" s="1" t="n">
-        <v>46098</v>
+        <v>46099</v>
       </c>
       <c r="B129" t="n">
-        <v>95.30000305175781</v>
+        <v>94.44999694824219</v>
       </c>
       <c r="C129" t="n">
-        <v>96.33999633789062</v>
+        <v>95.33999633789062</v>
       </c>
       <c r="D129" t="n">
-        <v>94.01000213623047</v>
+        <v>93.61000061035156</v>
       </c>
       <c r="E129" t="n">
-        <v>94.36000061035156</v>
+        <v>94.69999694824219</v>
       </c>
       <c r="F129" t="n">
-        <v>26434500</v>
+        <v>27878300</v>
       </c>
       <c r="G129" t="n">
         <v>0</v>
@@ -3797,22 +3797,22 @@
     </row>
     <row r="130">
       <c r="A130" s="1" t="n">
-        <v>46099</v>
+        <v>46100</v>
       </c>
       <c r="B130" t="n">
-        <v>94.44999694824219</v>
+        <v>94.30999755859375</v>
       </c>
       <c r="C130" t="n">
-        <v>95.33999633789062</v>
+        <v>95.75</v>
       </c>
       <c r="D130" t="n">
-        <v>93.61000061035156</v>
+        <v>90.77999877929688</v>
       </c>
       <c r="E130" t="n">
-        <v>94.69999694824219</v>
+        <v>91.73999786376953</v>
       </c>
       <c r="F130" t="n">
-        <v>27878300</v>
+        <v>40169300</v>
       </c>
       <c r="G130" t="n">
         <v>0</v>
@@ -3823,22 +3823,22 @@
     </row>
     <row r="131">
       <c r="A131" s="1" t="n">
-        <v>46100</v>
+        <v>46101</v>
       </c>
       <c r="B131" t="n">
-        <v>94.30999755859375</v>
+        <v>91.30999755859375</v>
       </c>
       <c r="C131" t="n">
-        <v>95.75</v>
+        <v>91.87999725341797</v>
       </c>
       <c r="D131" t="n">
-        <v>90.77999877929688</v>
+        <v>90.69000244140625</v>
       </c>
       <c r="E131" t="n">
-        <v>91.73999786376953</v>
+        <v>91.81999969482422</v>
       </c>
       <c r="F131" t="n">
-        <v>40169300</v>
+        <v>61678000</v>
       </c>
       <c r="G131" t="n">
         <v>0</v>
@@ -3849,22 +3849,22 @@
     </row>
     <row r="132">
       <c r="A132" s="1" t="n">
-        <v>46101</v>
+        <v>46104</v>
       </c>
       <c r="B132" t="n">
-        <v>91.30999755859375</v>
+        <v>92.04000091552734</v>
       </c>
       <c r="C132" t="n">
-        <v>91.87999725341797</v>
+        <v>93.98000335693359</v>
       </c>
       <c r="D132" t="n">
-        <v>90.69000244140625</v>
+        <v>91.86000061035156</v>
       </c>
       <c r="E132" t="n">
-        <v>91.81999969482422</v>
+        <v>93.37999725341797</v>
       </c>
       <c r="F132" t="n">
-        <v>61678000</v>
+        <v>34315900</v>
       </c>
       <c r="G132" t="n">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="133">
       <c r="A133" s="1" t="n">
-        <v>46104</v>
+        <v>46105</v>
       </c>
       <c r="B133" t="n">
-        <v>92.04000091552734</v>
+        <v>92.79000091552734</v>
       </c>
       <c r="C133" t="n">
-        <v>93.98000335693359</v>
+        <v>93.73999786376953</v>
       </c>
       <c r="D133" t="n">
-        <v>91.86000061035156</v>
+        <v>90.81999969482422</v>
       </c>
       <c r="E133" t="n">
-        <v>93.37999725341797</v>
+        <v>90.91999816894531</v>
       </c>
       <c r="F133" t="n">
-        <v>34315900</v>
+        <v>28938000</v>
       </c>
       <c r="G133" t="n">
         <v>0</v>
@@ -3901,22 +3901,22 @@
     </row>
     <row r="134">
       <c r="A134" s="1" t="n">
-        <v>46105</v>
+        <v>46106</v>
       </c>
       <c r="B134" t="n">
-        <v>92.79000091552734</v>
+        <v>91.70999908447266</v>
       </c>
       <c r="C134" t="n">
-        <v>93.73999786376953</v>
+        <v>92.51999664306641</v>
       </c>
       <c r="D134" t="n">
-        <v>90.81999969482422</v>
+        <v>91.23999786376953</v>
       </c>
       <c r="E134" t="n">
-        <v>90.91999816894531</v>
+        <v>92.27999877929688</v>
       </c>
       <c r="F134" t="n">
-        <v>28938000</v>
+        <v>29545600</v>
       </c>
       <c r="G134" t="n">
         <v>0</v>
@@ -3927,22 +3927,22 @@
     </row>
     <row r="135">
       <c r="A135" s="1" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B135" t="n">
-        <v>91.70999908447266</v>
+        <v>91.51999664306641</v>
       </c>
       <c r="C135" t="n">
-        <v>92.51999664306641</v>
+        <v>95.86000061035156</v>
       </c>
       <c r="D135" t="n">
-        <v>91.23999786376953</v>
+        <v>91.01000213623047</v>
       </c>
       <c r="E135" t="n">
-        <v>92.27999877929688</v>
+        <v>93.31999969482422</v>
       </c>
       <c r="F135" t="n">
-        <v>29545600</v>
+        <v>59522000</v>
       </c>
       <c r="G135" t="n">
         <v>0</v>
@@ -3953,22 +3953,22 @@
     </row>
     <row r="136">
       <c r="A136" s="1" t="n">
-        <v>46107</v>
+        <v>46108</v>
       </c>
       <c r="B136" t="n">
-        <v>91.51999664306641</v>
+        <v>94.56999969482422</v>
       </c>
       <c r="C136" t="n">
-        <v>95.86000061035156</v>
+        <v>95.58000183105469</v>
       </c>
       <c r="D136" t="n">
-        <v>91.01000213623047</v>
+        <v>92.73999786376953</v>
       </c>
       <c r="E136" t="n">
-        <v>93.31999969482422</v>
+        <v>93.43000030517578</v>
       </c>
       <c r="F136" t="n">
-        <v>59522000</v>
+        <v>44590700</v>
       </c>
       <c r="G136" t="n">
         <v>0</v>
@@ -3979,22 +3979,22 @@
     </row>
     <row r="137">
       <c r="A137" s="1" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B137" t="n">
-        <v>94.56999969482422</v>
+        <v>92.75</v>
       </c>
       <c r="C137" t="n">
-        <v>95.58000183105469</v>
+        <v>94.48999786376953</v>
       </c>
       <c r="D137" t="n">
-        <v>92.73999786376953</v>
+        <v>92.22000122070312</v>
       </c>
       <c r="E137" t="n">
-        <v>93.43000030517578</v>
+        <v>92.97000122070312</v>
       </c>
       <c r="F137" t="n">
-        <v>44590700</v>
+        <v>32375100</v>
       </c>
       <c r="G137" t="n">
         <v>0</v>
@@ -4005,22 +4005,22 @@
     </row>
     <row r="138">
       <c r="A138" s="1" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B138" t="n">
-        <v>92.75</v>
+        <v>93.02999877929688</v>
       </c>
       <c r="C138" t="n">
-        <v>94.48999786376953</v>
+        <v>96.26000213623047</v>
       </c>
       <c r="D138" t="n">
-        <v>92.22000122070312</v>
+        <v>93.02999877929688</v>
       </c>
       <c r="E138" t="n">
-        <v>92.97000122070312</v>
+        <v>96.15000152587891</v>
       </c>
       <c r="F138" t="n">
-        <v>32375100</v>
+        <v>54270000</v>
       </c>
       <c r="G138" t="n">
         <v>0</v>
@@ -4031,22 +4031,22 @@
     </row>
     <row r="139">
       <c r="A139" s="1" t="n">
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="B139" t="n">
-        <v>93.02999877929688</v>
+        <v>96.47000122070312</v>
       </c>
       <c r="C139" t="n">
-        <v>96.26000213623047</v>
+        <v>97.19999694824219</v>
       </c>
       <c r="D139" t="n">
-        <v>93.02999877929688</v>
+        <v>94.26000213623047</v>
       </c>
       <c r="E139" t="n">
-        <v>96.15000152587891</v>
+        <v>95.55000305175781</v>
       </c>
       <c r="F139" t="n">
-        <v>54270000</v>
+        <v>30439300</v>
       </c>
       <c r="G139" t="n">
         <v>0</v>
@@ -4057,22 +4057,22 @@
     </row>
     <row r="140">
       <c r="A140" s="1" t="n">
-        <v>46113</v>
+        <v>46114</v>
       </c>
       <c r="B140" t="n">
-        <v>96.47000122070312</v>
+        <v>95.26999664306641</v>
       </c>
       <c r="C140" t="n">
-        <v>97.19999694824219</v>
+        <v>98.70999908447266</v>
       </c>
       <c r="D140" t="n">
-        <v>94.26000213623047</v>
+        <v>95.16999816894531</v>
       </c>
       <c r="E140" t="n">
-        <v>95.55000305175781</v>
+        <v>98.66000366210938</v>
       </c>
       <c r="F140" t="n">
-        <v>30439300</v>
+        <v>37068000</v>
       </c>
       <c r="G140" t="n">
         <v>0</v>
@@ -4083,22 +4083,22 @@
     </row>
     <row r="141">
       <c r="A141" s="1" t="n">
-        <v>46114</v>
+        <v>46118</v>
       </c>
       <c r="B141" t="n">
-        <v>95.26999664306641</v>
+        <v>100.9599990844727</v>
       </c>
       <c r="C141" t="n">
-        <v>98.70999908447266</v>
+        <v>102.6900024414062</v>
       </c>
       <c r="D141" t="n">
-        <v>95.16999816894531</v>
+        <v>97.97000122070312</v>
       </c>
       <c r="E141" t="n">
-        <v>98.66000366210938</v>
+        <v>98.93000030517578</v>
       </c>
       <c r="F141" t="n">
-        <v>37068000</v>
+        <v>37029300</v>
       </c>
       <c r="G141" t="n">
         <v>0</v>
@@ -4109,22 +4109,22 @@
     </row>
     <row r="142">
       <c r="A142" s="1" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B142" t="n">
-        <v>100.9599990844727</v>
+        <v>98.55000305175781</v>
       </c>
       <c r="C142" t="n">
-        <v>102.6900024414062</v>
+        <v>99.87999725341797</v>
       </c>
       <c r="D142" t="n">
-        <v>97.97000122070312</v>
+        <v>98.25</v>
       </c>
       <c r="E142" t="n">
-        <v>98.93000030517578</v>
+        <v>98.81999969482422</v>
       </c>
       <c r="F142" t="n">
-        <v>37029300</v>
+        <v>25016700</v>
       </c>
       <c r="G142" t="n">
         <v>0</v>
@@ -4135,22 +4135,22 @@
     </row>
     <row r="143">
       <c r="A143" s="1" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B143" t="n">
-        <v>98.55000305175781</v>
+        <v>100.3199996948242</v>
       </c>
       <c r="C143" t="n">
-        <v>99.87999725341797</v>
+        <v>100.4000015258789</v>
       </c>
       <c r="D143" t="n">
-        <v>98.25</v>
+        <v>97.44000244140625</v>
       </c>
       <c r="E143" t="n">
-        <v>98.81999969482422</v>
+        <v>99.38999938964844</v>
       </c>
       <c r="F143" t="n">
-        <v>25016700</v>
+        <v>30957600</v>
       </c>
       <c r="G143" t="n">
         <v>0</v>
@@ -4161,22 +4161,22 @@
     </row>
     <row r="144">
       <c r="A144" s="1" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B144" t="n">
-        <v>100.3199996948242</v>
+        <v>99.62999725341797</v>
       </c>
       <c r="C144" t="n">
-        <v>100.4000015258789</v>
+        <v>102.3399963378906</v>
       </c>
       <c r="D144" t="n">
-        <v>97.44000244140625</v>
+        <v>99.08000183105469</v>
       </c>
       <c r="E144" t="n">
-        <v>99.38999938964844</v>
+        <v>102.0500030517578</v>
       </c>
       <c r="F144" t="n">
-        <v>30957600</v>
+        <v>35087800</v>
       </c>
       <c r="G144" t="n">
         <v>0</v>
@@ -4187,22 +4187,22 @@
     </row>
     <row r="145">
       <c r="A145" s="1" t="n">
-        <v>46121</v>
+        <v>46122</v>
       </c>
       <c r="B145" t="n">
-        <v>99.62999725341797</v>
+        <v>102.4700012207031</v>
       </c>
       <c r="C145" t="n">
-        <v>102.3399963378906</v>
+        <v>103.0800018310547</v>
       </c>
       <c r="D145" t="n">
-        <v>99.08000183105469</v>
+        <v>101.4599990844727</v>
       </c>
       <c r="E145" t="n">
-        <v>102.0500030517578</v>
+        <v>103.0100021362305</v>
       </c>
       <c r="F145" t="n">
-        <v>35087800</v>
+        <v>25769900</v>
       </c>
       <c r="G145" t="n">
         <v>0</v>
@@ -4213,22 +4213,22 @@
     </row>
     <row r="146">
       <c r="A146" s="1" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B146" t="n">
-        <v>102.4700012207031</v>
+        <v>103.0299987792969</v>
       </c>
       <c r="C146" t="n">
-        <v>103.0800018310547</v>
+        <v>103.6699981689453</v>
       </c>
       <c r="D146" t="n">
-        <v>101.4599990844727</v>
+        <v>102.0599975585938</v>
       </c>
       <c r="E146" t="n">
-        <v>103.0100021362305</v>
+        <v>103.1600036621094</v>
       </c>
       <c r="F146" t="n">
-        <v>25769900</v>
+        <v>26042800</v>
       </c>
       <c r="G146" t="n">
         <v>0</v>
@@ -4239,22 +4239,22 @@
     </row>
     <row r="147">
       <c r="A147" s="1" t="n">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="B147" t="n">
-        <v>103.0299987792969</v>
+        <v>103.120002746582</v>
       </c>
       <c r="C147" t="n">
-        <v>103.6699981689453</v>
+        <v>106.5699996948242</v>
       </c>
       <c r="D147" t="n">
-        <v>102.0599975585938</v>
+        <v>103.0400009155273</v>
       </c>
       <c r="E147" t="n">
-        <v>103.1600036621094</v>
+        <v>106.2799987792969</v>
       </c>
       <c r="F147" t="n">
-        <v>26042800</v>
+        <v>40534900</v>
       </c>
       <c r="G147" t="n">
         <v>0</v>
@@ -4265,22 +4265,22 @@
     </row>
     <row r="148">
       <c r="A148" s="1" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B148" t="n">
-        <v>103.120002746582</v>
+        <v>105.9800033569336</v>
       </c>
       <c r="C148" t="n">
-        <v>106.5699996948242</v>
+        <v>107.8499984741211</v>
       </c>
       <c r="D148" t="n">
-        <v>103.0400009155273</v>
+        <v>105.0400009155273</v>
       </c>
       <c r="E148" t="n">
-        <v>106.2799987792969</v>
+        <v>107.7099990844727</v>
       </c>
       <c r="F148" t="n">
-        <v>40534900</v>
+        <v>38023700</v>
       </c>
       <c r="G148" t="n">
         <v>0</v>
@@ -4291,22 +4291,22 @@
     </row>
     <row r="149">
       <c r="A149" s="1" t="n">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c r="B149" t="n">
-        <v>105.9800033569336</v>
+        <v>107.4700012207031</v>
       </c>
       <c r="C149" t="n">
-        <v>107.8499984741211</v>
+        <v>108.9499969482422</v>
       </c>
       <c r="D149" t="n">
-        <v>105.0400009155273</v>
+        <v>106.620002746582</v>
       </c>
       <c r="E149" t="n">
-        <v>107.7099990844727</v>
+        <v>107.7900009155273</v>
       </c>
       <c r="F149" t="n">
-        <v>38023700</v>
+        <v>64928300</v>
       </c>
       <c r="G149" t="n">
         <v>0</v>
@@ -4317,22 +4317,22 @@
     </row>
     <row r="150">
       <c r="A150" s="1" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B150" t="n">
-        <v>107.4700012207031</v>
+        <v>96.37000274658203</v>
       </c>
       <c r="C150" t="n">
-        <v>108.9499969482422</v>
+        <v>98.73999786376953</v>
       </c>
       <c r="D150" t="n">
-        <v>106.620002746582</v>
+        <v>95.09999847412109</v>
       </c>
       <c r="E150" t="n">
-        <v>107.7900009155273</v>
+        <v>97.30999755859375</v>
       </c>
       <c r="F150" t="n">
-        <v>64928300</v>
+        <v>125958700</v>
       </c>
       <c r="G150" t="n">
         <v>0</v>
@@ -4343,22 +4343,22 @@
     </row>
     <row r="151">
       <c r="A151" s="1" t="n">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c r="B151" t="n">
-        <v>96.37000274658203</v>
+        <v>97.13999938964844</v>
       </c>
       <c r="C151" t="n">
-        <v>98.73999786376953</v>
+        <v>97.59999847412109</v>
       </c>
       <c r="D151" t="n">
-        <v>95.09999847412109</v>
+        <v>93.54000091552734</v>
       </c>
       <c r="E151" t="n">
-        <v>97.30999755859375</v>
+        <v>94.83000183105469</v>
       </c>
       <c r="F151" t="n">
-        <v>125958700</v>
+        <v>63298300</v>
       </c>
       <c r="G151" t="n">
         <v>0</v>
@@ -4369,22 +4369,22 @@
     </row>
     <row r="152">
       <c r="A152" s="1" t="n">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="B152" t="n">
-        <v>97.13999938964844</v>
+        <v>94</v>
       </c>
       <c r="C152" t="n">
-        <v>97.59999847412109</v>
+        <v>94.65000152587891</v>
       </c>
       <c r="D152" t="n">
-        <v>93.54000091552734</v>
+        <v>92.37000274658203</v>
       </c>
       <c r="E152" t="n">
-        <v>94.83000183105469</v>
+        <v>92.58000183105469</v>
       </c>
       <c r="F152" t="n">
-        <v>63298300</v>
+        <v>61962300</v>
       </c>
       <c r="G152" t="n">
         <v>0</v>
@@ -4395,22 +4395,22 @@
     </row>
     <row r="153">
       <c r="A153" s="1" t="n">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="B153" t="n">
-        <v>94</v>
+        <v>93.05999755859375</v>
       </c>
       <c r="C153" t="n">
-        <v>94.65000152587891</v>
+        <v>93.84999847412109</v>
       </c>
       <c r="D153" t="n">
-        <v>92.37000274658203</v>
+        <v>92.76999664306641</v>
       </c>
       <c r="E153" t="n">
-        <v>92.58000183105469</v>
+        <v>93.23999786376953</v>
       </c>
       <c r="F153" t="n">
-        <v>61962300</v>
+        <v>33694300</v>
       </c>
       <c r="G153" t="n">
         <v>0</v>
@@ -4421,22 +4421,22 @@
     </row>
     <row r="154">
       <c r="A154" s="1" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B154" t="n">
-        <v>93.05999755859375</v>
+        <v>94.05999755859375</v>
       </c>
       <c r="C154" t="n">
-        <v>93.84999847412109</v>
+        <v>94.63999938964844</v>
       </c>
       <c r="D154" t="n">
-        <v>92.76999664306641</v>
+        <v>92.06999969482422</v>
       </c>
       <c r="E154" t="n">
-        <v>93.23999786376953</v>
+        <v>92.81999969482422</v>
       </c>
       <c r="F154" t="n">
-        <v>33694300</v>
+        <v>36851700</v>
       </c>
       <c r="G154" t="n">
         <v>0</v>
@@ -4447,22 +4447,22 @@
     </row>
     <row r="155">
       <c r="A155" s="1" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B155" t="n">
-        <v>94.05999755859375</v>
+        <v>92.56999969482422</v>
       </c>
       <c r="C155" t="n">
-        <v>94.63999938964844</v>
+        <v>93.27999877929688</v>
       </c>
       <c r="D155" t="n">
-        <v>92.06999969482422</v>
+        <v>91.80000305175781</v>
       </c>
       <c r="E155" t="n">
-        <v>92.81999969482422</v>
+        <v>92.44000244140625</v>
       </c>
       <c r="F155" t="n">
-        <v>36851700</v>
+        <v>32553200</v>
       </c>
       <c r="G155" t="n">
         <v>0</v>
@@ -4473,22 +4473,22 @@
     </row>
     <row r="156">
       <c r="A156" s="1" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B156" t="n">
-        <v>92.56999969482422</v>
+        <v>92.05000305175781</v>
       </c>
       <c r="C156" t="n">
-        <v>93.27999877929688</v>
+        <v>92.83999633789062</v>
       </c>
       <c r="D156" t="n">
-        <v>91.80000305175781</v>
+        <v>91.30000305175781</v>
       </c>
       <c r="E156" t="n">
-        <v>92.44000244140625</v>
+        <v>91.37000274658203</v>
       </c>
       <c r="F156" t="n">
-        <v>32553200</v>
+        <v>29707400</v>
       </c>
       <c r="G156" t="n">
         <v>0</v>
@@ -4499,22 +4499,22 @@
     </row>
     <row r="157">
       <c r="A157" s="1" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B157" t="n">
-        <v>92.05000305175781</v>
+        <v>91.5</v>
       </c>
       <c r="C157" t="n">
-        <v>92.83999633789062</v>
+        <v>92.33999633789062</v>
       </c>
       <c r="D157" t="n">
-        <v>91.30000305175781</v>
+        <v>90.01999664306641</v>
       </c>
       <c r="E157" t="n">
-        <v>91.37000274658203</v>
+        <v>92.26999664306641</v>
       </c>
       <c r="F157" t="n">
-        <v>29707400</v>
+        <v>33418100</v>
       </c>
       <c r="G157" t="n">
         <v>0</v>
@@ -4525,22 +4525,22 @@
     </row>
     <row r="158">
       <c r="A158" s="1" t="n">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="B158" t="n">
-        <v>91.5</v>
+        <v>91.23000335693359</v>
       </c>
       <c r="C158" t="n">
-        <v>92.33999633789062</v>
+        <v>92.86000061035156</v>
       </c>
       <c r="D158" t="n">
-        <v>90.01999664306641</v>
+        <v>90.86000061035156</v>
       </c>
       <c r="E158" t="n">
-        <v>92.26999664306641</v>
+        <v>92.12000274658203</v>
       </c>
       <c r="F158" t="n">
-        <v>33418100</v>
+        <v>26122100</v>
       </c>
       <c r="G158" t="n">
         <v>0</v>
@@ -4551,22 +4551,22 @@
     </row>
     <row r="159">
       <c r="A159" s="1" t="n">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="B159" t="n">
-        <v>91.23000335693359</v>
+        <v>91.34999847412109</v>
       </c>
       <c r="C159" t="n">
-        <v>92.86000061035156</v>
+        <v>94.22000122070312</v>
       </c>
       <c r="D159" t="n">
-        <v>90.86000061035156</v>
+        <v>90.76999664306641</v>
       </c>
       <c r="E159" t="n">
-        <v>92.12000274658203</v>
+        <v>93.61000061035156</v>
       </c>
       <c r="F159" t="n">
-        <v>26122100</v>
+        <v>40923000</v>
       </c>
       <c r="G159" t="n">
         <v>0</v>
@@ -4577,22 +4577,22 @@
     </row>
     <row r="160">
       <c r="A160" s="1" t="n">
-        <v>46142</v>
+        <v>46143</v>
       </c>
       <c r="B160" t="n">
-        <v>91.34999847412109</v>
+        <v>94.41999816894531</v>
       </c>
       <c r="C160" t="n">
-        <v>94.22000122070312</v>
+        <v>94.69999694824219</v>
       </c>
       <c r="D160" t="n">
-        <v>90.76999664306641</v>
+        <v>91.90000152587891</v>
       </c>
       <c r="E160" t="n">
-        <v>93.61000061035156</v>
+        <v>92.05999755859375</v>
       </c>
       <c r="F160" t="n">
-        <v>40923000</v>
+        <v>30406900</v>
       </c>
       <c r="G160" t="n">
         <v>0</v>
@@ -4603,22 +4603,22 @@
     </row>
     <row r="161">
       <c r="A161" s="1" t="n">
-        <v>46143</v>
+        <v>46146</v>
       </c>
       <c r="B161" t="n">
-        <v>94.41999816894531</v>
+        <v>92.09999847412109</v>
       </c>
       <c r="C161" t="n">
-        <v>94.69999694824219</v>
+        <v>92.33000183105469</v>
       </c>
       <c r="D161" t="n">
-        <v>91.90000152587891</v>
+        <v>90.88999938964844</v>
       </c>
       <c r="E161" t="n">
-        <v>92.05999755859375</v>
+        <v>91.01999664306641</v>
       </c>
       <c r="F161" t="n">
-        <v>30406900</v>
+        <v>25928800</v>
       </c>
       <c r="G161" t="n">
         <v>0</v>
@@ -4629,22 +4629,22 @@
     </row>
     <row r="162">
       <c r="A162" s="1" t="n">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="B162" t="n">
-        <v>92.09999847412109</v>
+        <v>91.18000030517578</v>
       </c>
       <c r="C162" t="n">
-        <v>92.33000183105469</v>
+        <v>91.27999877929688</v>
       </c>
       <c r="D162" t="n">
-        <v>90.88999938964844</v>
+        <v>87.56999969482422</v>
       </c>
       <c r="E162" t="n">
-        <v>91.01999664306641</v>
+        <v>87.88999938964844</v>
       </c>
       <c r="F162" t="n">
-        <v>25928800</v>
+        <v>51961300</v>
       </c>
       <c r="G162" t="n">
         <v>0</v>
@@ -4655,22 +4655,22 @@
     </row>
     <row r="163">
       <c r="A163" s="1" t="n">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="B163" t="n">
-        <v>91.18000030517578</v>
+        <v>87.15000152587891</v>
       </c>
       <c r="C163" t="n">
-        <v>91.27999877929688</v>
+        <v>88.55000305175781</v>
       </c>
       <c r="D163" t="n">
-        <v>87.56999969482422</v>
+        <v>86.72000122070312</v>
       </c>
       <c r="E163" t="n">
-        <v>87.88999938964844</v>
+        <v>88.26999664306641</v>
       </c>
       <c r="F163" t="n">
-        <v>51961300</v>
+        <v>41932400</v>
       </c>
       <c r="G163" t="n">
         <v>0</v>
@@ -4681,22 +4681,22 @@
     </row>
     <row r="164">
       <c r="A164" s="1" t="n">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="B164" t="n">
-        <v>87.15000152587891</v>
+        <v>88.19999694824219</v>
       </c>
       <c r="C164" t="n">
-        <v>88.55000305175781</v>
+        <v>89.40000152587891</v>
       </c>
       <c r="D164" t="n">
-        <v>86.72000122070312</v>
+        <v>88.12999725341797</v>
       </c>
       <c r="E164" t="n">
-        <v>88.26999664306641</v>
+        <v>88.25</v>
       </c>
       <c r="F164" t="n">
-        <v>41932400</v>
+        <v>30627600</v>
       </c>
       <c r="G164" t="n">
         <v>0</v>
@@ -4707,22 +4707,22 @@
     </row>
     <row r="165">
       <c r="A165" s="1" t="n">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="B165" t="n">
-        <v>88.19999694824219</v>
+        <v>87.70999908447266</v>
       </c>
       <c r="C165" t="n">
-        <v>89.40000152587891</v>
+        <v>88.04000091552734</v>
       </c>
       <c r="D165" t="n">
-        <v>88.12999725341797</v>
+        <v>87.20999908447266</v>
       </c>
       <c r="E165" t="n">
-        <v>88.25</v>
+        <v>87.48999786376953</v>
       </c>
       <c r="F165" t="n">
-        <v>30627600</v>
+        <v>36215100</v>
       </c>
       <c r="G165" t="n">
         <v>0</v>
@@ -4733,22 +4733,22 @@
     </row>
     <row r="166">
       <c r="A166" s="1" t="n">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="B166" t="n">
-        <v>87.70999908447266</v>
+        <v>86.52999877929688</v>
       </c>
       <c r="C166" t="n">
-        <v>88.04000091552734</v>
+        <v>87.33999633789062</v>
       </c>
       <c r="D166" t="n">
-        <v>87.20999908447266</v>
+        <v>85.09999847412109</v>
       </c>
       <c r="E166" t="n">
-        <v>87.48999786376953</v>
+        <v>85.44999694824219</v>
       </c>
       <c r="F166" t="n">
-        <v>36215100</v>
+        <v>40556500</v>
       </c>
       <c r="G166" t="n">
         <v>0</v>
@@ -4759,22 +4759,22 @@
     </row>
     <row r="167">
       <c r="A167" s="1" t="n">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="B167" t="n">
-        <v>86.52999877929688</v>
+        <v>85.91000366210938</v>
       </c>
       <c r="C167" t="n">
-        <v>87.33999633789062</v>
+        <v>89.16999816894531</v>
       </c>
       <c r="D167" t="n">
-        <v>85.09999847412109</v>
+        <v>85.80999755859375</v>
       </c>
       <c r="E167" t="n">
-        <v>85.44999694824219</v>
+        <v>87.66000366210938</v>
       </c>
       <c r="F167" t="n">
-        <v>40556500</v>
+        <v>43556600</v>
       </c>
       <c r="G167" t="n">
         <v>0</v>
@@ -4785,22 +4785,22 @@
     </row>
     <row r="168">
       <c r="A168" s="1" t="n">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="B168" t="n">
-        <v>85.91000366210938</v>
+        <v>86.56999969482422</v>
       </c>
       <c r="C168" t="n">
-        <v>89.16999816894531</v>
+        <v>88.62000274658203</v>
       </c>
       <c r="D168" t="n">
-        <v>85.80999755859375</v>
+        <v>86.27999877929688</v>
       </c>
       <c r="E168" t="n">
-        <v>87.66000366210938</v>
+        <v>87.55999755859375</v>
       </c>
       <c r="F168" t="n">
-        <v>43556600</v>
+        <v>30823500</v>
       </c>
       <c r="G168" t="n">
         <v>0</v>
@@ -4811,22 +4811,22 @@
     </row>
     <row r="169">
       <c r="A169" s="1" t="n">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="B169" t="n">
-        <v>86.56999969482422</v>
+        <v>87.62000274658203</v>
       </c>
       <c r="C169" t="n">
-        <v>88.62000274658203</v>
+        <v>88.5</v>
       </c>
       <c r="D169" t="n">
-        <v>86.27999877929688</v>
+        <v>86.65000152587891</v>
       </c>
       <c r="E169" t="n">
-        <v>87.55999755859375</v>
+        <v>86.94000244140625</v>
       </c>
       <c r="F169" t="n">
-        <v>30823500</v>
+        <v>29408300</v>
       </c>
       <c r="G169" t="n">
         <v>0</v>
@@ -4837,22 +4837,22 @@
     </row>
     <row r="170">
       <c r="A170" s="1" t="n">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="B170" t="n">
-        <v>87.62000274658203</v>
+        <v>87.69000244140625</v>
       </c>
       <c r="C170" t="n">
-        <v>88.5</v>
+        <v>89.48999786376953</v>
       </c>
       <c r="D170" t="n">
-        <v>86.65000152587891</v>
+        <v>86.69000244140625</v>
       </c>
       <c r="E170" t="n">
-        <v>86.94000244140625</v>
+        <v>87.01999664306641</v>
       </c>
       <c r="F170" t="n">
-        <v>29408300</v>
+        <v>32335700</v>
       </c>
       <c r="G170" t="n">
         <v>0</v>
@@ -4863,22 +4863,22 @@
     </row>
     <row r="171">
       <c r="A171" s="1" t="n">
-        <v>46157</v>
+        <v>46160</v>
       </c>
       <c r="B171" t="n">
-        <v>87.69000244140625</v>
+        <v>86.5</v>
       </c>
       <c r="C171" t="n">
-        <v>89.48999786376953</v>
+        <v>89.81999969482422</v>
       </c>
       <c r="D171" t="n">
-        <v>86.69000244140625</v>
+        <v>86.33000183105469</v>
       </c>
       <c r="E171" t="n">
-        <v>87.01999664306641</v>
+        <v>89.65000152587891</v>
       </c>
       <c r="F171" t="n">
-        <v>32335700</v>
+        <v>35800500</v>
       </c>
       <c r="G171" t="n">
         <v>0</v>
@@ -4889,22 +4889,22 @@
     </row>
     <row r="172">
       <c r="A172" s="1" t="n">
-        <v>46160</v>
+        <v>46161</v>
       </c>
       <c r="B172" t="n">
-        <v>86.5</v>
+        <v>90.13999938964844</v>
       </c>
       <c r="C172" t="n">
-        <v>89.81999969482422</v>
+        <v>91.48000335693359</v>
       </c>
       <c r="D172" t="n">
-        <v>86.33000183105469</v>
+        <v>88.69000244140625</v>
       </c>
       <c r="E172" t="n">
-        <v>89.65000152587891</v>
+        <v>89.33000183105469</v>
       </c>
       <c r="F172" t="n">
-        <v>35800500</v>
+        <v>34545700</v>
       </c>
       <c r="G172" t="n">
         <v>0</v>
@@ -4915,22 +4915,22 @@
     </row>
     <row r="173">
       <c r="A173" s="1" t="n">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="B173" t="n">
-        <v>90.13999938964844</v>
+        <v>88.51999664306641</v>
       </c>
       <c r="C173" t="n">
-        <v>91.48000335693359</v>
+        <v>88.55000305175781</v>
       </c>
       <c r="D173" t="n">
-        <v>88.69000244140625</v>
+        <v>87.5</v>
       </c>
       <c r="E173" t="n">
-        <v>89.33000183105469</v>
+        <v>88.08999633789062</v>
       </c>
       <c r="F173" t="n">
-        <v>34545700</v>
+        <v>23463400</v>
       </c>
       <c r="G173" t="n">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="174">
       <c r="A174" s="1" t="n">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="B174" t="n">
-        <v>88.51999664306641</v>
+        <v>88.02999877929688</v>
       </c>
       <c r="C174" t="n">
-        <v>88.55000305175781</v>
+        <v>90.37000274658203</v>
       </c>
       <c r="D174" t="n">
-        <v>87.5</v>
+        <v>87.51999664306641</v>
       </c>
       <c r="E174" t="n">
-        <v>88.08999633789062</v>
+        <v>89.30000305175781</v>
       </c>
       <c r="F174" t="n">
-        <v>23463400</v>
+        <v>28613900</v>
       </c>
       <c r="G174" t="n">
         <v>0</v>
@@ -4967,22 +4967,22 @@
     </row>
     <row r="175">
       <c r="A175" s="1" t="n">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="B175" t="n">
-        <v>88.02999877929688</v>
+        <v>89.09999847412109</v>
       </c>
       <c r="C175" t="n">
-        <v>90.37000274658203</v>
+        <v>89.97000122070312</v>
       </c>
       <c r="D175" t="n">
-        <v>87.51999664306641</v>
+        <v>88.16999816894531</v>
       </c>
       <c r="E175" t="n">
-        <v>89.30000305175781</v>
+        <v>88.59999847412109</v>
       </c>
       <c r="F175" t="n">
-        <v>28613900</v>
+        <v>23847200</v>
       </c>
       <c r="G175" t="n">
         <v>0</v>
@@ -4993,22 +4993,22 @@
     </row>
     <row r="176">
       <c r="A176" s="1" t="n">
-        <v>46164</v>
+        <v>46168</v>
       </c>
       <c r="B176" t="n">
-        <v>89.09999847412109</v>
+        <v>88.40000152587891</v>
       </c>
       <c r="C176" t="n">
-        <v>89.97000122070312</v>
+        <v>88.73000335693359</v>
       </c>
       <c r="D176" t="n">
-        <v>88.16999816894531</v>
+        <v>87.25</v>
       </c>
       <c r="E176" t="n">
-        <v>88.59999847412109</v>
+        <v>87.68000030517578</v>
       </c>
       <c r="F176" t="n">
-        <v>23847200</v>
+        <v>24014500</v>
       </c>
       <c r="G176" t="n">
         <v>0</v>
@@ -5019,22 +5019,22 @@
     </row>
     <row r="177">
       <c r="A177" s="1" t="n">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="B177" t="n">
-        <v>88.40000152587891</v>
+        <v>87.05000305175781</v>
       </c>
       <c r="C177" t="n">
-        <v>88.73000335693359</v>
+        <v>88.5</v>
       </c>
       <c r="D177" t="n">
-        <v>87.25</v>
+        <v>86.81999969482422</v>
       </c>
       <c r="E177" t="n">
-        <v>87.68000030517578</v>
+        <v>87.34999847412109</v>
       </c>
       <c r="F177" t="n">
-        <v>24014500</v>
+        <v>22569500</v>
       </c>
       <c r="G177" t="n">
         <v>0</v>
@@ -5045,22 +5045,22 @@
     </row>
     <row r="178">
       <c r="A178" s="1" t="n">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="B178" t="n">
-        <v>87.05000305175781</v>
+        <v>86.90000152587891</v>
       </c>
       <c r="C178" t="n">
-        <v>88.5</v>
+        <v>87.04000091552734</v>
       </c>
       <c r="D178" t="n">
-        <v>86.81999969482422</v>
+        <v>85.58999633789062</v>
       </c>
       <c r="E178" t="n">
-        <v>87.34999847412109</v>
+        <v>86.36000061035156</v>
       </c>
       <c r="F178" t="n">
-        <v>22569500</v>
+        <v>38803800</v>
       </c>
       <c r="G178" t="n">
         <v>0</v>
@@ -5071,22 +5071,22 @@
     </row>
     <row r="179">
       <c r="A179" s="1" t="n">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="B179" t="n">
-        <v>86.90000152587891</v>
+        <v>86.19999694824219</v>
       </c>
       <c r="C179" t="n">
-        <v>87.04000091552734</v>
+        <v>86.66999816894531</v>
       </c>
       <c r="D179" t="n">
-        <v>85.58999633789062</v>
+        <v>85.66000366210938</v>
       </c>
       <c r="E179" t="n">
-        <v>86.36000061035156</v>
+        <v>86.01999664306641</v>
       </c>
       <c r="F179" t="n">
-        <v>38803800</v>
+        <v>39793600</v>
       </c>
       <c r="G179" t="n">
         <v>0</v>
@@ -5097,22 +5097,22 @@
     </row>
     <row r="180">
       <c r="A180" s="1" t="n">
-        <v>46171</v>
+        <v>46174</v>
       </c>
       <c r="B180" t="n">
-        <v>86.19999694824219</v>
+        <v>85.73000335693359</v>
       </c>
       <c r="C180" t="n">
-        <v>86.66999816894531</v>
+        <v>87.23000335693359</v>
       </c>
       <c r="D180" t="n">
-        <v>85.66000366210938</v>
+        <v>85.31999969482422</v>
       </c>
       <c r="E180" t="n">
-        <v>86.01999664306641</v>
+        <v>85.84999847412109</v>
       </c>
       <c r="F180" t="n">
-        <v>39793600</v>
+        <v>32747200</v>
       </c>
       <c r="G180" t="n">
         <v>0</v>
@@ -5123,22 +5123,22 @@
     </row>
     <row r="181">
       <c r="A181" s="1" t="n">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="B181" t="n">
-        <v>85.73000335693359</v>
+        <v>85.61000061035156</v>
       </c>
       <c r="C181" t="n">
-        <v>87.23000335693359</v>
+        <v>85.98000335693359</v>
       </c>
       <c r="D181" t="n">
-        <v>85.31999969482422</v>
+        <v>83.29000091552734</v>
       </c>
       <c r="E181" t="n">
-        <v>85.84999847412109</v>
+        <v>83.33000183105469</v>
       </c>
       <c r="F181" t="n">
-        <v>32747200</v>
+        <v>42947200</v>
       </c>
       <c r="G181" t="n">
         <v>0</v>
@@ -5149,22 +5149,22 @@
     </row>
     <row r="182">
       <c r="A182" s="1" t="n">
-        <v>46175</v>
+        <v>46176</v>
       </c>
       <c r="B182" t="n">
-        <v>85.61000061035156</v>
+        <v>82.91000366210938</v>
       </c>
       <c r="C182" t="n">
-        <v>85.98000335693359</v>
+        <v>83.30999755859375</v>
       </c>
       <c r="D182" t="n">
-        <v>83.29000091552734</v>
+        <v>81.09999847412109</v>
       </c>
       <c r="E182" t="n">
-        <v>83.33000183105469</v>
+        <v>81.51999664306641</v>
       </c>
       <c r="F182" t="n">
-        <v>42947200</v>
+        <v>36714700</v>
       </c>
       <c r="G182" t="n">
         <v>0</v>
@@ -5175,22 +5175,22 @@
     </row>
     <row r="183">
       <c r="A183" s="1" t="n">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="B183" t="n">
-        <v>82.91000366210938</v>
+        <v>83.19000244140625</v>
       </c>
       <c r="C183" t="n">
-        <v>83.30999755859375</v>
+        <v>83.69999694824219</v>
       </c>
       <c r="D183" t="n">
-        <v>81.09999847412109</v>
+        <v>81.37000274658203</v>
       </c>
       <c r="E183" t="n">
-        <v>81.51999664306641</v>
+        <v>81.55999755859375</v>
       </c>
       <c r="F183" t="n">
-        <v>36714700</v>
+        <v>39338800</v>
       </c>
       <c r="G183" t="n">
         <v>0</v>
@@ -5201,22 +5201,22 @@
     </row>
     <row r="184">
       <c r="A184" s="1" t="n">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="B184" t="n">
-        <v>83.19000244140625</v>
+        <v>82.33000183105469</v>
       </c>
       <c r="C184" t="n">
-        <v>83.69999694824219</v>
+        <v>82.75</v>
       </c>
       <c r="D184" t="n">
-        <v>81.37000274658203</v>
+        <v>81</v>
       </c>
       <c r="E184" t="n">
-        <v>81.55999755859375</v>
+        <v>82.18000030517578</v>
       </c>
       <c r="F184" t="n">
-        <v>39338800</v>
+        <v>43474100</v>
       </c>
       <c r="G184" t="n">
         <v>0</v>
@@ -5227,22 +5227,22 @@
     </row>
     <row r="185">
       <c r="A185" s="1" t="n">
-        <v>46178</v>
+        <v>46181</v>
       </c>
       <c r="B185" t="n">
-        <v>82.33000183105469</v>
+        <v>81.66000366210938</v>
       </c>
       <c r="C185" t="n">
-        <v>82.75</v>
+        <v>83.08000183105469</v>
       </c>
       <c r="D185" t="n">
-        <v>81</v>
+        <v>81.33999633789062</v>
       </c>
       <c r="E185" t="n">
-        <v>82.18000030517578</v>
+        <v>82.63999938964844</v>
       </c>
       <c r="F185" t="n">
-        <v>43474100</v>
+        <v>33056700</v>
       </c>
       <c r="G185" t="n">
         <v>0</v>
@@ -5253,22 +5253,22 @@
     </row>
     <row r="186">
       <c r="A186" s="1" t="n">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="B186" t="n">
-        <v>81.66000366210938</v>
+        <v>82.12999725341797</v>
       </c>
       <c r="C186" t="n">
-        <v>83.08000183105469</v>
+        <v>82.33999633789062</v>
       </c>
       <c r="D186" t="n">
         <v>81.33999633789062</v>
       </c>
       <c r="E186" t="n">
-        <v>82.63999938964844</v>
+        <v>81.41000366210938</v>
       </c>
       <c r="F186" t="n">
-        <v>33056700</v>
+        <v>34787200</v>
       </c>
       <c r="G186" t="n">
         <v>0</v>
@@ -5279,22 +5279,22 @@
     </row>
     <row r="187">
       <c r="A187" s="1" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="B187" t="n">
-        <v>82.12999725341797</v>
+        <v>81.70999908447266</v>
       </c>
       <c r="C187" t="n">
-        <v>82.33999633789062</v>
+        <v>82.75</v>
       </c>
       <c r="D187" t="n">
-        <v>81.33999633789062</v>
+        <v>80.98000335693359</v>
       </c>
       <c r="E187" t="n">
-        <v>81.41000366210938</v>
+        <v>82</v>
       </c>
       <c r="F187" t="n">
-        <v>34787200</v>
+        <v>36304600</v>
       </c>
       <c r="G187" t="n">
         <v>0</v>
@@ -5305,22 +5305,22 @@
     </row>
     <row r="188">
       <c r="A188" s="1" t="n">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="B188" t="n">
-        <v>81.70999908447266</v>
+        <v>81.87000274658203</v>
       </c>
       <c r="C188" t="n">
-        <v>82.75</v>
+        <v>82.09999847412109</v>
       </c>
       <c r="D188" t="n">
-        <v>80.98000335693359</v>
+        <v>80.08999633789062</v>
       </c>
       <c r="E188" t="n">
-        <v>82</v>
+        <v>81.26999664306641</v>
       </c>
       <c r="F188" t="n">
-        <v>36304600</v>
+        <v>33417600</v>
       </c>
       <c r="G188" t="n">
         <v>0</v>
@@ -5331,22 +5331,22 @@
     </row>
     <row r="189">
       <c r="A189" s="1" t="n">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="B189" t="n">
-        <v>81.87000274658203</v>
+        <v>81.58000183105469</v>
       </c>
       <c r="C189" t="n">
-        <v>82.09999847412109</v>
+        <v>82</v>
       </c>
       <c r="D189" t="n">
-        <v>80.08999633789062</v>
+        <v>79.27999877929688</v>
       </c>
       <c r="E189" t="n">
-        <v>81.26999664306641</v>
+        <v>80.33999633789062</v>
       </c>
       <c r="F189" t="n">
-        <v>33417600</v>
+        <v>35309700</v>
       </c>
       <c r="G189" t="n">
         <v>0</v>
@@ -5357,22 +5357,22 @@
     </row>
     <row r="190">
       <c r="A190" s="1" t="n">
-        <v>46185</v>
+        <v>46188</v>
       </c>
       <c r="B190" t="n">
-        <v>81.58000183105469</v>
+        <v>80.62000274658203</v>
       </c>
       <c r="C190" t="n">
-        <v>82</v>
+        <v>81.70999908447266</v>
       </c>
       <c r="D190" t="n">
-        <v>79.27999877929688</v>
+        <v>80.45999908447266</v>
       </c>
       <c r="E190" t="n">
-        <v>80.33999633789062</v>
+        <v>81.66999816894531</v>
       </c>
       <c r="F190" t="n">
-        <v>35309700</v>
+        <v>36430800</v>
       </c>
       <c r="G190" t="n">
         <v>0</v>
@@ -5383,22 +5383,22 @@
     </row>
     <row r="191">
       <c r="A191" s="1" t="n">
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="B191" t="n">
-        <v>80.62000274658203</v>
+        <v>81.90000152587891</v>
       </c>
       <c r="C191" t="n">
-        <v>81.70999908447266</v>
+        <v>81.93000030517578</v>
       </c>
       <c r="D191" t="n">
-        <v>80.45999908447266</v>
+        <v>77.70999908447266</v>
       </c>
       <c r="E191" t="n">
-        <v>81.66999816894531</v>
+        <v>78.72000122070312</v>
       </c>
       <c r="F191" t="n">
-        <v>36430800</v>
+        <v>65054000</v>
       </c>
       <c r="G191" t="n">
         <v>0</v>
@@ -5409,22 +5409,22 @@
     </row>
     <row r="192">
       <c r="A192" s="1" t="n">
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="B192" t="n">
-        <v>81.90000152587891</v>
+        <v>78.09999847412109</v>
       </c>
       <c r="C192" t="n">
-        <v>81.93000030517578</v>
+        <v>78.44999694824219</v>
       </c>
       <c r="D192" t="n">
-        <v>77.70999908447266</v>
+        <v>76.76000213623047</v>
       </c>
       <c r="E192" t="n">
-        <v>78.72000122070312</v>
+        <v>76.95999908447266</v>
       </c>
       <c r="F192" t="n">
-        <v>65054000</v>
+        <v>50338800</v>
       </c>
       <c r="G192" t="n">
         <v>0</v>
@@ -5435,22 +5435,22 @@
     </row>
     <row r="193">
       <c r="A193" s="1" t="n">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="B193" t="n">
-        <v>78.09999847412109</v>
+        <v>76.93000030517578</v>
       </c>
       <c r="C193" t="n">
-        <v>78.44999694824219</v>
+        <v>78.23999786376953</v>
       </c>
       <c r="D193" t="n">
-        <v>76.76000213623047</v>
+        <v>76.12000274658203</v>
       </c>
       <c r="E193" t="n">
-        <v>76.95999908447266</v>
+        <v>77.37999725341797</v>
       </c>
       <c r="F193" t="n">
-        <v>50338800</v>
+        <v>91920400</v>
       </c>
       <c r="G193" t="n">
         <v>0</v>
@@ -5461,22 +5461,22 @@
     </row>
     <row r="194">
       <c r="A194" s="1" t="n">
-        <v>46191</v>
+        <v>46195</v>
       </c>
       <c r="B194" t="n">
-        <v>76.93000030517578</v>
+        <v>76.13999938964844</v>
       </c>
       <c r="C194" t="n">
-        <v>78.23999786376953</v>
+        <v>77.08999633789062</v>
       </c>
       <c r="D194" t="n">
-        <v>76.12000274658203</v>
+        <v>71.80999755859375</v>
       </c>
       <c r="E194" t="n">
-        <v>77.37999725341797</v>
+        <v>72.87999725341797</v>
       </c>
       <c r="F194" t="n">
-        <v>91920400</v>
+        <v>82203300</v>
       </c>
       <c r="G194" t="n">
         <v>0</v>
@@ -5487,22 +5487,22 @@
     </row>
     <row r="195">
       <c r="A195" s="1" t="n">
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="B195" t="n">
-        <v>76.13999938964844</v>
+        <v>73.26000213623047</v>
       </c>
       <c r="C195" t="n">
-        <v>77.08999633789062</v>
+        <v>73.95999908447266</v>
       </c>
       <c r="D195" t="n">
-        <v>71.80999755859375</v>
+        <v>72.62999725341797</v>
       </c>
       <c r="E195" t="n">
-        <v>72.87999725341797</v>
+        <v>72.81999969482422</v>
       </c>
       <c r="F195" t="n">
-        <v>82203300</v>
+        <v>50806800</v>
       </c>
       <c r="G195" t="n">
         <v>0</v>
@@ -5513,22 +5513,22 @@
     </row>
     <row r="196">
       <c r="A196" s="1" t="n">
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="B196" t="n">
-        <v>73.26000213623047</v>
+        <v>72.69000244140625</v>
       </c>
       <c r="C196" t="n">
-        <v>73.95999908447266</v>
+        <v>73.44999694824219</v>
       </c>
       <c r="D196" t="n">
-        <v>72.62999725341797</v>
+        <v>71.62999725341797</v>
       </c>
       <c r="E196" t="n">
-        <v>72.81999969482422</v>
+        <v>71.83999633789062</v>
       </c>
       <c r="F196" t="n">
-        <v>50806800</v>
+        <v>48001500</v>
       </c>
       <c r="G196" t="n">
         <v>0</v>
@@ -5539,22 +5539,22 @@
     </row>
     <row r="197">
       <c r="A197" s="1" t="n">
-        <v>46197</v>
+        <v>46198</v>
       </c>
       <c r="B197" t="n">
-        <v>72.69000244140625</v>
+        <v>71.33000183105469</v>
       </c>
       <c r="C197" t="n">
-        <v>73.44999694824219</v>
+        <v>72.94000244140625</v>
       </c>
       <c r="D197" t="n">
-        <v>71.62999725341797</v>
+        <v>70.86000061035156</v>
       </c>
       <c r="E197" t="n">
-        <v>71.83999633789062</v>
+        <v>70.90000152587891</v>
       </c>
       <c r="F197" t="n">
-        <v>48001500</v>
+        <v>44446900</v>
       </c>
       <c r="G197" t="n">
         <v>0</v>
@@ -5565,22 +5565,22 @@
     </row>
     <row r="198">
       <c r="A198" s="1" t="n">
-        <v>46198</v>
+        <v>46199</v>
       </c>
       <c r="B198" t="n">
-        <v>71.33000183105469</v>
+        <v>71.69000244140625</v>
       </c>
       <c r="C198" t="n">
-        <v>72.94000244140625</v>
+        <v>75.19999694824219</v>
       </c>
       <c r="D198" t="n">
-        <v>70.86000061035156</v>
+        <v>71.52999877929688</v>
       </c>
       <c r="E198" t="n">
-        <v>70.90000152587891</v>
+        <v>73.80999755859375</v>
       </c>
       <c r="F198" t="n">
-        <v>44446900</v>
+        <v>74990300</v>
       </c>
       <c r="G198" t="n">
         <v>0</v>
@@ -5591,22 +5591,22 @@
     </row>
     <row r="199">
       <c r="A199" s="1" t="n">
-        <v>46199</v>
+        <v>46202</v>
       </c>
       <c r="B199" t="n">
-        <v>71.69000244140625</v>
+        <v>74.62000274658203</v>
       </c>
       <c r="C199" t="n">
-        <v>75.19999694824219</v>
+        <v>76.06999969482422</v>
       </c>
       <c r="D199" t="n">
-        <v>71.52999877929688</v>
+        <v>73.73000335693359</v>
       </c>
       <c r="E199" t="n">
-        <v>73.80999755859375</v>
+        <v>73.77999877929688</v>
       </c>
       <c r="F199" t="n">
-        <v>74990300</v>
+        <v>42429600</v>
       </c>
       <c r="G199" t="n">
         <v>0</v>
@@ -5617,22 +5617,22 @@
     </row>
     <row r="200">
       <c r="A200" s="1" t="n">
-        <v>46202</v>
+        <v>46203</v>
       </c>
       <c r="B200" t="n">
-        <v>74.62000274658203</v>
+        <v>73.58999633789062</v>
       </c>
       <c r="C200" t="n">
-        <v>76.06999969482422</v>
+        <v>73.75</v>
       </c>
       <c r="D200" t="n">
-        <v>73.73000335693359</v>
+        <v>71</v>
       </c>
       <c r="E200" t="n">
-        <v>73.77999877929688</v>
+        <v>71.40000152587891</v>
       </c>
       <c r="F200" t="n">
-        <v>42429600</v>
+        <v>49240900</v>
       </c>
       <c r="G200" t="n">
         <v>0</v>
@@ -5643,22 +5643,22 @@
     </row>
     <row r="201">
       <c r="A201" s="1" t="n">
-        <v>46203</v>
+        <v>46204</v>
       </c>
       <c r="B201" t="n">
-        <v>73.58999633789062</v>
+        <v>72.58999633789062</v>
       </c>
       <c r="C201" t="n">
-        <v>73.75</v>
+        <v>74.36000061035156</v>
       </c>
       <c r="D201" t="n">
-        <v>71</v>
+        <v>72.33000183105469</v>
       </c>
       <c r="E201" t="n">
-        <v>71.40000152587891</v>
+        <v>74.19000244140625</v>
       </c>
       <c r="F201" t="n">
-        <v>49240900</v>
+        <v>43841800</v>
       </c>
       <c r="G201" t="n">
         <v>0</v>
@@ -5669,22 +5669,22 @@
     </row>
     <row r="202">
       <c r="A202" s="1" t="n">
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="B202" t="n">
-        <v>72.58999633789062</v>
+        <v>75.08999633789062</v>
       </c>
       <c r="C202" t="n">
-        <v>74.36000061035156</v>
+        <v>78.44000244140625</v>
       </c>
       <c r="D202" t="n">
-        <v>72.33000183105469</v>
+        <v>74.91000366210938</v>
       </c>
       <c r="E202" t="n">
-        <v>74.19000244140625</v>
+        <v>77.65000152587891</v>
       </c>
       <c r="F202" t="n">
-        <v>43841800</v>
+        <v>55456500</v>
       </c>
       <c r="G202" t="n">
         <v>0</v>
@@ -5695,22 +5695,22 @@
     </row>
     <row r="203">
       <c r="A203" s="1" t="n">
-        <v>46205</v>
+        <v>46209</v>
       </c>
       <c r="B203" t="n">
-        <v>75.08999633789062</v>
+        <v>77.08000183105469</v>
       </c>
       <c r="C203" t="n">
-        <v>78.44000244140625</v>
+        <v>77.83999633789062</v>
       </c>
       <c r="D203" t="n">
-        <v>74.91000366210938</v>
+        <v>75.70999908447266</v>
       </c>
       <c r="E203" t="n">
-        <v>77.65000152587891</v>
+        <v>76.01999664306641</v>
       </c>
       <c r="F203" t="n">
-        <v>55456500</v>
+        <v>45056600</v>
       </c>
       <c r="G203" t="n">
         <v>0</v>
@@ -5721,22 +5721,22 @@
     </row>
     <row r="204">
       <c r="A204" s="1" t="n">
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="B204" t="n">
-        <v>77.08000183105469</v>
+        <v>77.87999725341797</v>
       </c>
       <c r="C204" t="n">
-        <v>77.83999633789062</v>
+        <v>78.19000244140625</v>
       </c>
       <c r="D204" t="n">
-        <v>75.70999908447266</v>
+        <v>76.09999847412109</v>
       </c>
       <c r="E204" t="n">
-        <v>76.01999664306641</v>
+        <v>76.18000030517578</v>
       </c>
       <c r="F204" t="n">
-        <v>45056600</v>
+        <v>33257300</v>
       </c>
       <c r="G204" t="n">
         <v>0</v>
@@ -5747,22 +5747,22 @@
     </row>
     <row r="205">
       <c r="A205" s="1" t="n">
-        <v>46210</v>
+        <v>46211</v>
       </c>
       <c r="B205" t="n">
-        <v>77.87999725341797</v>
+        <v>76.26999664306641</v>
       </c>
       <c r="C205" t="n">
-        <v>78.19000244140625</v>
+        <v>76.63999938964844</v>
       </c>
       <c r="D205" t="n">
-        <v>76.09999847412109</v>
+        <v>74.88999938964844</v>
       </c>
       <c r="E205" t="n">
-        <v>76.18000030517578</v>
+        <v>75.58999633789062</v>
       </c>
       <c r="F205" t="n">
-        <v>33257300</v>
+        <v>34373500</v>
       </c>
       <c r="G205" t="n">
         <v>0</v>
@@ -5773,22 +5773,22 @@
     </row>
     <row r="206">
       <c r="A206" s="1" t="n">
-        <v>46211</v>
+        <v>46212</v>
       </c>
       <c r="B206" t="n">
-        <v>76.26999664306641</v>
+        <v>74.30000305175781</v>
       </c>
       <c r="C206" t="n">
-        <v>76.63999938964844</v>
+        <v>75.55000305175781</v>
       </c>
       <c r="D206" t="n">
-        <v>74.88999938964844</v>
+        <v>74.01999664306641</v>
       </c>
       <c r="E206" t="n">
-        <v>75.58999633789062</v>
+        <v>75.47000122070312</v>
       </c>
       <c r="F206" t="n">
-        <v>34373500</v>
+        <v>36305700</v>
       </c>
       <c r="G206" t="n">
         <v>0</v>
@@ -5799,22 +5799,22 @@
     </row>
     <row r="207">
       <c r="A207" s="1" t="n">
-        <v>46212</v>
+        <v>46213</v>
       </c>
       <c r="B207" t="n">
-        <v>74.30000305175781</v>
+        <v>75.44000244140625</v>
       </c>
       <c r="C207" t="n">
-        <v>75.55000305175781</v>
+        <v>75.69999694824219</v>
       </c>
       <c r="D207" t="n">
-        <v>74.01999664306641</v>
+        <v>72.51000213623047</v>
       </c>
       <c r="E207" t="n">
-        <v>75.47000122070312</v>
+        <v>73.37000274658203</v>
       </c>
       <c r="F207" t="n">
-        <v>36305700</v>
+        <v>46713900</v>
       </c>
       <c r="G207" t="n">
         <v>0</v>
@@ -5825,22 +5825,22 @@
     </row>
     <row r="208">
       <c r="A208" s="1" t="n">
-        <v>46213</v>
+        <v>46216</v>
       </c>
       <c r="B208" t="n">
-        <v>75.44000244140625</v>
+        <v>73.90000152587891</v>
       </c>
       <c r="C208" t="n">
-        <v>75.69999694824219</v>
+        <v>75.44999694824219</v>
       </c>
       <c r="D208" t="n">
-        <v>72.51000213623047</v>
+        <v>73.70999908447266</v>
       </c>
       <c r="E208" t="n">
-        <v>73.37000274658203</v>
+        <v>73.83000183105469</v>
       </c>
       <c r="F208" t="n">
-        <v>46713900</v>
+        <v>35101800</v>
       </c>
       <c r="G208" t="n">
         <v>0</v>
@@ -5851,22 +5851,22 @@
     </row>
     <row r="209">
       <c r="A209" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="B209" t="n">
-        <v>73.90000152587891</v>
+        <v>72.63999938964844</v>
       </c>
       <c r="C209" t="n">
-        <v>75.44999694824219</v>
+        <v>74.01000213623047</v>
       </c>
       <c r="D209" t="n">
-        <v>73.70999908447266</v>
+        <v>72.27999877929688</v>
       </c>
       <c r="E209" t="n">
-        <v>73.83000183105469</v>
+        <v>73.52999877929688</v>
       </c>
       <c r="F209" t="n">
-        <v>35101800</v>
+        <v>33312100</v>
       </c>
       <c r="G209" t="n">
         <v>0</v>
@@ -5877,22 +5877,22 @@
     </row>
     <row r="210">
       <c r="A210" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="B210" t="n">
-        <v>72.63999938964844</v>
+        <v>73.79000091552734</v>
       </c>
       <c r="C210" t="n">
-        <v>74.01000213623047</v>
+        <v>75.05999755859375</v>
       </c>
       <c r="D210" t="n">
-        <v>72.27999877929688</v>
+        <v>73.12999725341797</v>
       </c>
       <c r="E210" t="n">
-        <v>73.52999877929688</v>
+        <v>73.68000030517578</v>
       </c>
       <c r="F210" t="n">
-        <v>33312100</v>
+        <v>32854300</v>
       </c>
       <c r="G210" t="n">
         <v>0</v>
@@ -5903,22 +5903,22 @@
     </row>
     <row r="211">
       <c r="A211" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="B211" t="n">
-        <v>73.79000091552734</v>
+        <v>73.94999694824219</v>
       </c>
       <c r="C211" t="n">
-        <v>75.05999755859375</v>
+        <v>74.68000030517578</v>
       </c>
       <c r="D211" t="n">
-        <v>73.12999725341797</v>
+        <v>72.94000244140625</v>
       </c>
       <c r="E211" t="n">
-        <v>73.68000030517578</v>
+        <v>74.34999847412109</v>
       </c>
       <c r="F211" t="n">
-        <v>32854300</v>
+        <v>77505200</v>
       </c>
       <c r="G211" t="n">
         <v>0</v>
@@ -5929,22 +5929,22 @@
     </row>
     <row r="212">
       <c r="A212" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="B212" t="n">
-        <v>73.94999694824219</v>
+        <v>65.48000335693359</v>
       </c>
       <c r="C212" t="n">
-        <v>74.68000030517578</v>
+        <v>69.48999786376953</v>
       </c>
       <c r="D212" t="n">
-        <v>72.94000244140625</v>
+        <v>65.08000183105469</v>
       </c>
       <c r="E212" t="n">
-        <v>74.34999847412109</v>
+        <v>68.94999694824219</v>
       </c>
       <c r="F212" t="n">
-        <v>77505200</v>
+        <v>142029200</v>
       </c>
       <c r="G212" t="n">
         <v>0</v>
@@ -5955,22 +5955,22 @@
     </row>
     <row r="213">
       <c r="A213" s="1" t="n">
-        <v>46220</v>
+        <v>46223</v>
       </c>
       <c r="B213" t="n">
-        <v>65.48000335693359</v>
+        <v>68.31999969482422</v>
       </c>
       <c r="C213" t="n">
-        <v>69.48999786376953</v>
+        <v>68.37999725341797</v>
       </c>
       <c r="D213" t="n">
-        <v>65.08000183105469</v>
+        <v>66.69000244140625</v>
       </c>
       <c r="E213" t="n">
-        <v>68.94999694824219</v>
+        <v>67.59999847412109</v>
       </c>
       <c r="F213" t="n">
-        <v>142029200</v>
+        <v>60669100</v>
       </c>
       <c r="G213" t="n">
         <v>0</v>
@@ -5981,22 +5981,22 @@
     </row>
     <row r="214">
       <c r="A214" s="1" t="n">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="B214" t="n">
-        <v>68.31999969482422</v>
+        <v>67.41999816894531</v>
       </c>
       <c r="C214" t="n">
-        <v>68.37999725341797</v>
+        <v>68.75</v>
       </c>
       <c r="D214" t="n">
-        <v>66.69000244140625</v>
+        <v>66.73000335693359</v>
       </c>
       <c r="E214" t="n">
-        <v>67.59999847412109</v>
+        <v>68.66999816894531</v>
       </c>
       <c r="F214" t="n">
-        <v>60669100</v>
+        <v>56565800</v>
       </c>
       <c r="G214" t="n">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="215">
       <c r="A215" s="1" t="n">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="B215" t="n">
-        <v>67.41999816894531</v>
+        <v>69.37000274658203</v>
       </c>
       <c r="C215" t="n">
-        <v>68.75</v>
+        <v>70.56999969482422</v>
       </c>
       <c r="D215" t="n">
-        <v>66.73000335693359</v>
+        <v>68.34999847412109</v>
       </c>
       <c r="E215" t="n">
-        <v>68.66999816894531</v>
+        <v>68.52999877929688</v>
       </c>
       <c r="F215" t="n">
-        <v>56565800</v>
+        <v>44947300</v>
       </c>
       <c r="G215" t="n">
         <v>0</v>
@@ -6033,22 +6033,22 @@
     </row>
     <row r="216">
       <c r="A216" s="1" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="B216" t="n">
-        <v>69.37000274658203</v>
+        <v>68.56999969482422</v>
       </c>
       <c r="C216" t="n">
-        <v>70.56999969482422</v>
+        <v>69.36000061035156</v>
       </c>
       <c r="D216" t="n">
-        <v>68.34999847412109</v>
+        <v>67.66999816894531</v>
       </c>
       <c r="E216" t="n">
-        <v>68.52999877929688</v>
+        <v>68.88999938964844</v>
       </c>
       <c r="F216" t="n">
-        <v>44947300</v>
+        <v>45029100</v>
       </c>
       <c r="G216" t="n">
         <v>0</v>
@@ -6059,22 +6059,22 @@
     </row>
     <row r="217">
       <c r="A217" s="1" t="n">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="B217" t="n">
-        <v>68.56999969482422</v>
+        <v>69.29000091552734</v>
       </c>
       <c r="C217" t="n">
-        <v>69.36000061035156</v>
+        <v>70.68000030517578</v>
       </c>
       <c r="D217" t="n">
-        <v>67.66999816894531</v>
+        <v>67.97000122070312</v>
       </c>
       <c r="E217" t="n">
-        <v>68.88999938964844</v>
+        <v>70.08999633789062</v>
       </c>
       <c r="F217" t="n">
-        <v>45029100</v>
+        <v>37593500</v>
       </c>
       <c r="G217" t="n">
         <v>0</v>
@@ -6085,22 +6085,22 @@
     </row>
     <row r="218">
       <c r="A218" s="1" t="n">
-        <v>46227</v>
+        <v>46230</v>
       </c>
       <c r="B218" t="n">
-        <v>69.29000091552734</v>
+        <v>70.58999633789062</v>
       </c>
       <c r="C218" t="n">
-        <v>70.68000030517578</v>
+        <v>71.65000152587891</v>
       </c>
       <c r="D218" t="n">
-        <v>67.97000122070312</v>
+        <v>69.86000061035156</v>
       </c>
       <c r="E218" t="n">
-        <v>70.08999633789062</v>
+        <v>70.40000152587891</v>
       </c>
       <c r="F218" t="n">
-        <v>37593500</v>
+        <v>39090800</v>
       </c>
       <c r="G218" t="n">
         <v>0</v>
@@ -6111,22 +6111,22 @@
     </row>
     <row r="219">
       <c r="A219" s="1" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="B219" t="n">
-        <v>70.58999633789062</v>
+        <v>72.06999969482422</v>
       </c>
       <c r="C219" t="n">
-        <v>71.65000152587891</v>
+        <v>73.76000213623047</v>
       </c>
       <c r="D219" t="n">
-        <v>69.86000061035156</v>
+        <v>71.23000335693359</v>
       </c>
       <c r="E219" t="n">
-        <v>70.40000152587891</v>
+        <v>72.38999938964844</v>
       </c>
       <c r="F219" t="n">
-        <v>39090800</v>
+        <v>47160200</v>
       </c>
       <c r="G219" t="n">
         <v>0</v>
@@ -6137,22 +6137,22 @@
     </row>
     <row r="220">
       <c r="A220" s="1" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="B220" t="n">
-        <v>72.06999969482422</v>
+        <v>72.19000244140625</v>
       </c>
       <c r="C220" t="n">
-        <v>73.76000213623047</v>
+        <v>73.73999786376953</v>
       </c>
       <c r="D220" t="n">
-        <v>71.23000335693359</v>
+        <v>71.75</v>
       </c>
       <c r="E220" t="n">
-        <v>72.38999938964844</v>
+        <v>73.62999725341797</v>
       </c>
       <c r="F220" t="n">
-        <v>47160200</v>
+        <v>43737600</v>
       </c>
       <c r="G220" t="n">
         <v>0</v>
@@ -6163,22 +6163,22 @@
     </row>
     <row r="221">
       <c r="A221" s="1" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="B221" t="n">
-        <v>72.19000244140625</v>
+        <v>71.48000335693359</v>
       </c>
       <c r="C221" t="n">
-        <v>73.73999786376953</v>
+        <v>73.31999969482422</v>
       </c>
       <c r="D221" t="n">
-        <v>71.75</v>
+        <v>70.55000305175781</v>
       </c>
       <c r="E221" t="n">
-        <v>73.62999725341797</v>
+        <v>73.16999816894531</v>
       </c>
       <c r="F221" t="n">
-        <v>43737600</v>
+        <v>54261000</v>
       </c>
       <c r="G221" t="n">
         <v>0</v>
@@ -6189,22 +6189,22 @@
     </row>
     <row r="222">
       <c r="A222" s="1" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="B222" t="n">
-        <v>71.48000335693359</v>
+        <v>71.97000122070312</v>
       </c>
       <c r="C222" t="n">
-        <v>73.31999969482422</v>
+        <v>72.75</v>
       </c>
       <c r="D222" t="n">
-        <v>70.55000305175781</v>
+        <v>71.11000061035156</v>
       </c>
       <c r="E222" t="n">
-        <v>73.16999816894531</v>
+        <v>71.70999908447266</v>
       </c>
       <c r="F222" t="n">
-        <v>54261000</v>
+        <v>35847500</v>
       </c>
       <c r="G222" t="n">
         <v>0</v>
@@ -6215,22 +6215,22 @@
     </row>
     <row r="223">
       <c r="A223" s="1" t="n">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="B223" t="n">
-        <v>71.97000122070312</v>
+        <v>72.76999664306641</v>
       </c>
       <c r="C223" t="n">
-        <v>72.75</v>
+        <v>73.94999694824219</v>
       </c>
       <c r="D223" t="n">
-        <v>71.11000061035156</v>
+        <v>72.18000030517578</v>
       </c>
       <c r="E223" t="n">
-        <v>71.70999908447266</v>
+        <v>73.33000183105469</v>
       </c>
       <c r="F223" t="n">
-        <v>35847500</v>
+        <v>33922300</v>
       </c>
       <c r="G223" t="n">
         <v>0</v>
@@ -6241,22 +6241,22 @@
     </row>
     <row r="224">
       <c r="A224" s="1" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="B224" t="n">
-        <v>72.76999664306641</v>
+        <v>72.51000213623047</v>
       </c>
       <c r="C224" t="n">
-        <v>73.94999694824219</v>
+        <v>73.75</v>
       </c>
       <c r="D224" t="n">
-        <v>72.18000030517578</v>
+        <v>72.30000305175781</v>
       </c>
       <c r="E224" t="n">
-        <v>73.33000183105469</v>
+        <v>73.56999969482422</v>
       </c>
       <c r="F224" t="n">
-        <v>33922300</v>
+        <v>42877900</v>
       </c>
       <c r="G224" t="n">
         <v>0</v>
@@ -6267,22 +6267,22 @@
     </row>
     <row r="225">
       <c r="A225" s="1" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="B225" t="n">
-        <v>72.51000213623047</v>
+        <v>75.11000061035156</v>
       </c>
       <c r="C225" t="n">
-        <v>73.75</v>
+        <v>75.30000305175781</v>
       </c>
       <c r="D225" t="n">
-        <v>72.30000305175781</v>
+        <v>73.16000366210938</v>
       </c>
       <c r="E225" t="n">
-        <v>73.56999969482422</v>
+        <v>74.19999694824219</v>
       </c>
       <c r="F225" t="n">
-        <v>42877900</v>
+        <v>28969400</v>
       </c>
       <c r="G225" t="n">
         <v>0</v>
@@ -6293,22 +6293,22 @@
     </row>
     <row r="226">
       <c r="A226" s="1" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="B226" t="n">
-        <v>75.11000061035156</v>
+        <v>75.13999938964844</v>
       </c>
       <c r="C226" t="n">
-        <v>75.30000305175781</v>
+        <v>75.20999908447266</v>
       </c>
       <c r="D226" t="n">
-        <v>73.16000366210938</v>
+        <v>73.09999847412109</v>
       </c>
       <c r="E226" t="n">
-        <v>74.19999694824219</v>
+        <v>73.69000244140625</v>
       </c>
       <c r="F226" t="n">
-        <v>28969400</v>
+        <v>28892700</v>
       </c>
       <c r="G226" t="n">
         <v>0</v>
@@ -6319,22 +6319,22 @@
     </row>
     <row r="227">
       <c r="A227" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="B227" t="n">
-        <v>75.13999938964844</v>
+        <v>73.12000274658203</v>
       </c>
       <c r="C227" t="n">
-        <v>75.20999908447266</v>
+        <v>74.5</v>
       </c>
       <c r="D227" t="n">
-        <v>73.09999847412109</v>
+        <v>73.08000183105469</v>
       </c>
       <c r="E227" t="n">
-        <v>73.69000244140625</v>
+        <v>74.13999938964844</v>
       </c>
       <c r="F227" t="n">
-        <v>28892700</v>
+        <v>24819000</v>
       </c>
       <c r="G227" t="n">
         <v>0</v>
@@ -6345,22 +6345,22 @@
     </row>
     <row r="228">
       <c r="A228" s="1" t="n">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="B228" t="n">
-        <v>73.12000274658203</v>
+        <v>73.80000305175781</v>
       </c>
       <c r="C228" t="n">
-        <v>74.5</v>
+        <v>76.31999969482422</v>
       </c>
       <c r="D228" t="n">
-        <v>73.08000183105469</v>
+        <v>73.56999969482422</v>
       </c>
       <c r="E228" t="n">
-        <v>74.13999938964844</v>
+        <v>76.29000091552734</v>
       </c>
       <c r="F228" t="n">
-        <v>24819000</v>
+        <v>26959900</v>
       </c>
       <c r="G228" t="n">
         <v>0</v>
@@ -6371,22 +6371,22 @@
     </row>
     <row r="229">
       <c r="A229" s="1" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="B229" t="n">
-        <v>73.80000305175781</v>
+        <v>76.19999694824219</v>
       </c>
       <c r="C229" t="n">
-        <v>76.31999969482422</v>
+        <v>76.90000152587891</v>
       </c>
       <c r="D229" t="n">
-        <v>73.56999969482422</v>
+        <v>74.48000335693359</v>
       </c>
       <c r="E229" t="n">
-        <v>76.29000091552734</v>
+        <v>74.79000091552734</v>
       </c>
       <c r="F229" t="n">
-        <v>26959900</v>
+        <v>27840500</v>
       </c>
       <c r="G229" t="n">
         <v>0</v>
@@ -6397,22 +6397,22 @@
     </row>
     <row r="230">
       <c r="A230" s="1" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="B230" t="n">
-        <v>76.19999694824219</v>
+        <v>74.34999847412109</v>
       </c>
       <c r="C230" t="n">
-        <v>76.90000152587891</v>
+        <v>74.66999816894531</v>
       </c>
       <c r="D230" t="n">
-        <v>74.48000335693359</v>
+        <v>73.56999969482422</v>
       </c>
       <c r="E230" t="n">
-        <v>74.79000091552734</v>
+        <v>74.20999908447266</v>
       </c>
       <c r="F230" t="n">
-        <v>27840500</v>
+        <v>20773100</v>
       </c>
       <c r="G230" t="n">
         <v>0</v>
@@ -6423,22 +6423,22 @@
     </row>
     <row r="231">
       <c r="A231" s="1" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="B231" t="n">
-        <v>74.34999847412109</v>
+        <v>76.01000213623047</v>
       </c>
       <c r="C231" t="n">
-        <v>74.66999816894531</v>
+        <v>78.40000152587891</v>
       </c>
       <c r="D231" t="n">
-        <v>73.56999969482422</v>
+        <v>75.44000244140625</v>
       </c>
       <c r="E231" t="n">
-        <v>74.20999908447266</v>
+        <v>78.23999786376953</v>
       </c>
       <c r="F231" t="n">
-        <v>20773100</v>
+        <v>41452900</v>
       </c>
       <c r="G231" t="n">
         <v>0</v>
@@ -6449,22 +6449,22 @@
     </row>
     <row r="232">
       <c r="A232" s="1" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="B232" t="n">
-        <v>76.01000213623047</v>
+        <v>78.48000335693359</v>
       </c>
       <c r="C232" t="n">
-        <v>78.40000152587891</v>
+        <v>78.73000335693359</v>
       </c>
       <c r="D232" t="n">
-        <v>75.44000244140625</v>
+        <v>77.76000213623047</v>
       </c>
       <c r="E232" t="n">
-        <v>78.23999786376953</v>
+        <v>78.16000366210938</v>
       </c>
       <c r="F232" t="n">
-        <v>41452900</v>
+        <v>26751000</v>
       </c>
       <c r="G232" t="n">
         <v>0</v>
@@ -6475,22 +6475,22 @@
     </row>
     <row r="233">
       <c r="A233" s="1" t="n">
-        <v>46248</v>
+        <v>46251</v>
       </c>
       <c r="B233" t="n">
-        <v>78.48000335693359</v>
+        <v>77.80000305175781</v>
       </c>
       <c r="C233" t="n">
-        <v>78.73000335693359</v>
+        <v>78.52999877929688</v>
       </c>
       <c r="D233" t="n">
-        <v>77.76000213623047</v>
+        <v>75.47000122070312</v>
       </c>
       <c r="E233" t="n">
-        <v>78.16000366210938</v>
+        <v>76.01999664306641</v>
       </c>
       <c r="F233" t="n">
-        <v>26751000</v>
+        <v>30753000</v>
       </c>
       <c r="G233" t="n">
         <v>0</v>
@@ -6501,22 +6501,22 @@
     </row>
     <row r="234">
       <c r="A234" s="1" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="B234" t="n">
-        <v>77.80000305175781</v>
+        <v>77.43000030517578</v>
       </c>
       <c r="C234" t="n">
-        <v>78.52999877929688</v>
+        <v>79.09999847412109</v>
       </c>
       <c r="D234" t="n">
-        <v>75.47000122070312</v>
+        <v>76.33999633789062</v>
       </c>
       <c r="E234" t="n">
-        <v>76.01999664306641</v>
+        <v>77.76999664306641</v>
       </c>
       <c r="F234" t="n">
-        <v>30753000</v>
+        <v>36151300</v>
       </c>
       <c r="G234" t="n">
         <v>0</v>
@@ -6527,22 +6527,22 @@
     </row>
     <row r="235">
       <c r="A235" s="1" t="n">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="B235" t="n">
-        <v>77.43000030517578</v>
+        <v>78.25</v>
       </c>
       <c r="C235" t="n">
-        <v>79.09999847412109</v>
+        <v>81.16000366210938</v>
       </c>
       <c r="D235" t="n">
-        <v>76.33999633789062</v>
+        <v>78.09999847412109</v>
       </c>
       <c r="E235" t="n">
-        <v>77.76999664306641</v>
+        <v>80.22000122070312</v>
       </c>
       <c r="F235" t="n">
-        <v>36151300</v>
+        <v>31461800</v>
       </c>
       <c r="G235" t="n">
         <v>0</v>
@@ -6553,22 +6553,22 @@
     </row>
     <row r="236">
       <c r="A236" s="1" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="B236" t="n">
-        <v>78.25</v>
+        <v>80.13999938964844</v>
       </c>
       <c r="C236" t="n">
-        <v>81.16000366210938</v>
+        <v>81.08000183105469</v>
       </c>
       <c r="D236" t="n">
-        <v>78.09999847412109</v>
+        <v>79.58999633789062</v>
       </c>
       <c r="E236" t="n">
-        <v>80.22000122070312</v>
+        <v>80.13999938964844</v>
       </c>
       <c r="F236" t="n">
-        <v>31461800</v>
+        <v>27118400</v>
       </c>
       <c r="G236" t="n">
         <v>0</v>
@@ -6579,22 +6579,22 @@
     </row>
     <row r="237">
       <c r="A237" s="1" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="B237" t="n">
-        <v>80.13999938964844</v>
+        <v>80.29000091552734</v>
       </c>
       <c r="C237" t="n">
-        <v>81.08000183105469</v>
+        <v>80.48999786376953</v>
       </c>
       <c r="D237" t="n">
+        <v>79.16999816894531</v>
+      </c>
+      <c r="E237" t="n">
         <v>79.58999633789062</v>
       </c>
-      <c r="E237" t="n">
-        <v>80.13999938964844</v>
-      </c>
       <c r="F237" t="n">
-        <v>27118400</v>
+        <v>23773800</v>
       </c>
       <c r="G237" t="n">
         <v>0</v>
@@ -6605,22 +6605,22 @@
     </row>
     <row r="238">
       <c r="A238" s="1" t="n">
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="B238" t="n">
-        <v>80.29000091552734</v>
+        <v>79.94000244140625</v>
       </c>
       <c r="C238" t="n">
-        <v>80.48999786376953</v>
+        <v>80.62000274658203</v>
       </c>
       <c r="D238" t="n">
-        <v>79.16999816894531</v>
+        <v>79.01999664306641</v>
       </c>
       <c r="E238" t="n">
-        <v>79.58999633789062</v>
+        <v>80.01000213623047</v>
       </c>
       <c r="F238" t="n">
-        <v>23773800</v>
+        <v>21085300</v>
       </c>
       <c r="G238" t="n">
         <v>0</v>
@@ -6631,22 +6631,22 @@
     </row>
     <row r="239">
       <c r="A239" s="1" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="B239" t="n">
-        <v>79.94000244140625</v>
+        <v>79.65000152587891</v>
       </c>
       <c r="C239" t="n">
-        <v>80.62000274658203</v>
+        <v>82.45999908447266</v>
       </c>
       <c r="D239" t="n">
-        <v>79.01999664306641</v>
+        <v>79.40000152587891</v>
       </c>
       <c r="E239" t="n">
-        <v>80.01000213623047</v>
+        <v>82.23000335693359</v>
       </c>
       <c r="F239" t="n">
-        <v>21085300</v>
+        <v>29462000</v>
       </c>
       <c r="G239" t="n">
         <v>0</v>
@@ -6657,22 +6657,22 @@
     </row>
     <row r="240">
       <c r="A240" s="1" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="B240" t="n">
-        <v>79.65000152587891</v>
+        <v>82.05000305175781</v>
       </c>
       <c r="C240" t="n">
-        <v>82.45999908447266</v>
+        <v>82.41999816894531</v>
       </c>
       <c r="D240" t="n">
-        <v>79.40000152587891</v>
+        <v>81.30000305175781</v>
       </c>
       <c r="E240" t="n">
-        <v>82.23000335693359</v>
+        <v>81.45999908447266</v>
       </c>
       <c r="F240" t="n">
-        <v>29462000</v>
+        <v>22874900</v>
       </c>
       <c r="G240" t="n">
         <v>0</v>
@@ -6683,22 +6683,22 @@
     </row>
     <row r="241">
       <c r="A241" s="1" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="B241" t="n">
-        <v>82.05000305175781</v>
+        <v>81.06999969482422</v>
       </c>
       <c r="C241" t="n">
-        <v>82.41999816894531</v>
+        <v>81.15000152587891</v>
       </c>
       <c r="D241" t="n">
-        <v>81.30000305175781</v>
+        <v>79.27999877929688</v>
       </c>
       <c r="E241" t="n">
-        <v>81.45999908447266</v>
+        <v>79.83999633789062</v>
       </c>
       <c r="F241" t="n">
-        <v>22874900</v>
+        <v>27174400</v>
       </c>
       <c r="G241" t="n">
         <v>0</v>
@@ -6709,22 +6709,22 @@
     </row>
     <row r="242">
       <c r="A242" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="B242" t="n">
-        <v>81.06999969482422</v>
+        <v>80.36000061035156</v>
       </c>
       <c r="C242" t="n">
-        <v>81.15000152587891</v>
+        <v>82.34999847412109</v>
       </c>
       <c r="D242" t="n">
-        <v>79.27999877929688</v>
+        <v>79.94999694824219</v>
       </c>
       <c r="E242" t="n">
-        <v>79.83999633789062</v>
+        <v>81.72000122070312</v>
       </c>
       <c r="F242" t="n">
-        <v>27174400</v>
+        <v>29092700</v>
       </c>
       <c r="G242" t="n">
         <v>0</v>
@@ -6735,22 +6735,22 @@
     </row>
     <row r="243">
       <c r="A243" s="1" t="n">
-        <v>46262</v>
+        <v>46265</v>
       </c>
       <c r="B243" t="n">
-        <v>80.36000061035156</v>
+        <v>81</v>
       </c>
       <c r="C243" t="n">
-        <v>82.34999847412109</v>
+        <v>81.73000335693359</v>
       </c>
       <c r="D243" t="n">
-        <v>79.94999694824219</v>
+        <v>80.65000152587891</v>
       </c>
       <c r="E243" t="n">
-        <v>81.72000122070312</v>
+        <v>81.05000305175781</v>
       </c>
       <c r="F243" t="n">
-        <v>29092700</v>
+        <v>30740800</v>
       </c>
       <c r="G243" t="n">
         <v>0</v>
@@ -6761,22 +6761,22 @@
     </row>
     <row r="244">
       <c r="A244" s="1" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="B244" t="n">
-        <v>81</v>
+        <v>80.16999816894531</v>
       </c>
       <c r="C244" t="n">
-        <v>81.73000335693359</v>
+        <v>82.12999725341797</v>
       </c>
       <c r="D244" t="n">
-        <v>80.65000152587891</v>
+        <v>79.59999847412109</v>
       </c>
       <c r="E244" t="n">
-        <v>81.05000305175781</v>
+        <v>80.80999755859375</v>
       </c>
       <c r="F244" t="n">
-        <v>30740800</v>
+        <v>21164900</v>
       </c>
       <c r="G244" t="n">
         <v>0</v>
@@ -6787,22 +6787,22 @@
     </row>
     <row r="245">
       <c r="A245" s="1" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="B245" t="n">
-        <v>80.16999816894531</v>
+        <v>80.55000305175781</v>
       </c>
       <c r="C245" t="n">
-        <v>82.12999725341797</v>
+        <v>83.12000274658203</v>
       </c>
       <c r="D245" t="n">
-        <v>79.59999847412109</v>
+        <v>80.30000305175781</v>
       </c>
       <c r="E245" t="n">
-        <v>80.80999755859375</v>
+        <v>82.73000335693359</v>
       </c>
       <c r="F245" t="n">
-        <v>21164900</v>
+        <v>22077800</v>
       </c>
       <c r="G245" t="n">
         <v>0</v>
@@ -6813,22 +6813,22 @@
     </row>
     <row r="246">
       <c r="A246" s="1" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="B246" t="n">
-        <v>80.55000305175781</v>
+        <v>83.18000030517578</v>
       </c>
       <c r="C246" t="n">
-        <v>83.12000274658203</v>
+        <v>83.59999847412109</v>
       </c>
       <c r="D246" t="n">
-        <v>80.30000305175781</v>
+        <v>81.62999725341797</v>
       </c>
       <c r="E246" t="n">
-        <v>82.73000335693359</v>
+        <v>82.66999816894531</v>
       </c>
       <c r="F246" t="n">
-        <v>22077800</v>
+        <v>24006400</v>
       </c>
       <c r="G246" t="n">
         <v>0</v>
@@ -6839,22 +6839,22 @@
     </row>
     <row r="247">
       <c r="A247" s="1" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B247" t="n">
-        <v>83.18000030517578</v>
+        <v>82.16999816894531</v>
       </c>
       <c r="C247" t="n">
-        <v>83.59999847412109</v>
+        <v>82.69000244140625</v>
       </c>
       <c r="D247" t="n">
-        <v>81.62999725341797</v>
+        <v>78.23000335693359</v>
       </c>
       <c r="E247" t="n">
-        <v>82.66999816894531</v>
+        <v>78.25</v>
       </c>
       <c r="F247" t="n">
-        <v>24006400</v>
+        <v>40190000</v>
       </c>
       <c r="G247" t="n">
         <v>0</v>
@@ -6865,22 +6865,22 @@
     </row>
     <row r="248">
       <c r="A248" s="1" t="n">
-        <v>46269</v>
+        <v>46273</v>
       </c>
       <c r="B248" t="n">
-        <v>82.16999816894531</v>
+        <v>77.55000305175781</v>
       </c>
       <c r="C248" t="n">
-        <v>82.69000244140625</v>
+        <v>77.73000335693359</v>
       </c>
       <c r="D248" t="n">
-        <v>78.23000335693359</v>
+        <v>75.91999816894531</v>
       </c>
       <c r="E248" t="n">
-        <v>78.25</v>
+        <v>76.76999664306641</v>
       </c>
       <c r="F248" t="n">
-        <v>40190000</v>
+        <v>33865500</v>
       </c>
       <c r="G248" t="n">
         <v>0</v>
@@ -6891,22 +6891,22 @@
     </row>
     <row r="249">
       <c r="A249" s="1" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B249" t="n">
-        <v>77.55000305175781</v>
+        <v>76.33999633789062</v>
       </c>
       <c r="C249" t="n">
-        <v>77.73000335693359</v>
+        <v>76.72000122070312</v>
       </c>
       <c r="D249" t="n">
-        <v>75.91999816894531</v>
+        <v>75.87000274658203</v>
       </c>
       <c r="E249" t="n">
-        <v>76.76999664306641</v>
+        <v>76.02999877929688</v>
       </c>
       <c r="F249" t="n">
-        <v>33865500</v>
+        <v>22779600</v>
       </c>
       <c r="G249" t="n">
         <v>0</v>
@@ -6917,22 +6917,22 @@
     </row>
     <row r="250">
       <c r="A250" s="1" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="B250" t="n">
-        <v>76.33999633789062</v>
+        <v>75.33000183105469</v>
       </c>
       <c r="C250" t="n">
-        <v>76.72000122070312</v>
+        <v>76.30000305175781</v>
       </c>
       <c r="D250" t="n">
-        <v>75.87000274658203</v>
+        <v>75.02999877929688</v>
       </c>
       <c r="E250" t="n">
-        <v>76.02999877929688</v>
+        <v>76.01000213623047</v>
       </c>
       <c r="F250" t="n">
-        <v>22779600</v>
+        <v>20049000</v>
       </c>
       <c r="G250" t="n">
         <v>0</v>
@@ -6943,22 +6943,22 @@
     </row>
     <row r="251">
       <c r="A251" s="1" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="B251" t="n">
-        <v>75.33000183105469</v>
+        <v>76.63999938964844</v>
       </c>
       <c r="C251" t="n">
-        <v>76.30000305175781</v>
+        <v>77.56999969482422</v>
       </c>
       <c r="D251" t="n">
-        <v>75.02999877929688</v>
+        <v>76.15000152587891</v>
       </c>
       <c r="E251" t="n">
-        <v>76.01000213623047</v>
+        <v>77.40000152587891</v>
       </c>
       <c r="F251" t="n">
-        <v>20049000</v>
+        <v>22237800</v>
       </c>
       <c r="G251" t="n">
         <v>0</v>
@@ -6969,22 +6969,22 @@
     </row>
     <row r="252">
       <c r="A252" s="1" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="B252" t="n">
-        <v>76.63999938964844</v>
+        <v>78.97000122070312</v>
       </c>
       <c r="C252" t="n">
-        <v>77.56999969482422</v>
+        <v>81.01999664306641</v>
       </c>
       <c r="D252" t="n">
-        <v>76.15000152587891</v>
+        <v>78.48999786376953</v>
       </c>
       <c r="E252" t="n">
-        <v>77.40000152587891</v>
+        <v>80.31999969482422</v>
       </c>
       <c r="F252" t="n">
-        <v>22207800</v>
+        <v>30909600</v>
       </c>
       <c r="G252" t="n">
         <v>0</v>
@@ -10414,37 +10414,37 @@
         </is>
       </c>
       <c r="C2" t="n">
+        <v>80.31999999999999</v>
+      </c>
+      <c r="D2" t="n">
         <v>77.40000000000001</v>
       </c>
-      <c r="D2" t="n">
-        <v>76.01000000000001</v>
-      </c>
       <c r="E2" t="n">
-        <v>76.605</v>
+        <v>78.97</v>
       </c>
       <c r="F2" t="n">
-        <v>77.56610000000001</v>
+        <v>81.01000000000001</v>
       </c>
       <c r="G2" t="n">
-        <v>76.15000000000001</v>
+        <v>78.48999999999999</v>
       </c>
       <c r="H2" t="n">
-        <v>22178958</v>
+        <v>30614406</v>
       </c>
       <c r="I2" t="n">
-        <v>40900987</v>
+        <v>40974760</v>
       </c>
       <c r="J2" t="n">
-        <v>322288943104</v>
+        <v>334447640576</v>
       </c>
       <c r="K2" t="n">
-        <v>24.339622</v>
+        <v>25.25786</v>
       </c>
       <c r="L2" t="n">
-        <v>20.256954</v>
+        <v>21.02117</v>
       </c>
       <c r="M2" t="n">
-        <v>3.24</v>
+        <v>3.18</v>
       </c>
       <c r="N2" t="n">
         <v>124.86</v>
@@ -10482,7 +10482,7 @@
         <v>7.241</v>
       </c>
       <c r="Y2" t="n">
-        <v>10.689132</v>
+        <v>11.09239</v>
       </c>
       <c r="Z2" t="n">
         <v>0.111</v>
@@ -10494,7 +10494,7 @@
         <v>48370765824</v>
       </c>
       <c r="AC2" t="n">
-        <v>329815687168</v>
+        <v>341974384640</v>
       </c>
       <c r="AD2" t="n">
         <v>14726931456</v>
@@ -10521,7 +10521,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>2026-09-12 21:47:35</t>
+          <t>2026-09-15 14:14:42</t>
         </is>
       </c>
     </row>

--- a/data/NFLX_data.xlsx
+++ b/data/NFLX_data.xlsx
@@ -469,22 +469,22 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45915</v>
+        <v>45917</v>
       </c>
       <c r="B2" t="n">
-        <v>118.8399963378906</v>
+        <v>122.1019973754883</v>
       </c>
       <c r="C2" t="n">
-        <v>120.7239990234375</v>
+        <v>123.3929977416992</v>
       </c>
       <c r="D2" t="n">
-        <v>117.3209991455078</v>
+        <v>120.661003112793</v>
       </c>
       <c r="E2" t="n">
-        <v>120.2259979248047</v>
+        <v>122.8499984741211</v>
       </c>
       <c r="F2" t="n">
-        <v>29093000</v>
+        <v>34598000</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -495,22 +495,22 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45916</v>
+        <v>45918</v>
       </c>
       <c r="B3" t="n">
-        <v>120.5640029907227</v>
+        <v>122.0820007324219</v>
       </c>
       <c r="C3" t="n">
-        <v>120.9000015258789</v>
+        <v>123.3000030517578</v>
       </c>
       <c r="D3" t="n">
-        <v>119.7279968261719</v>
+        <v>120.5500030517578</v>
       </c>
       <c r="E3" t="n">
-        <v>120.0510025024414</v>
+        <v>120.7779998779297</v>
       </c>
       <c r="F3" t="n">
-        <v>24047000</v>
+        <v>31691000</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -521,22 +521,22 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>45917</v>
+        <v>45919</v>
       </c>
       <c r="B4" t="n">
-        <v>122.1019973754883</v>
+        <v>121.8619995117188</v>
       </c>
       <c r="C4" t="n">
-        <v>123.3929977416992</v>
+        <v>122.995002746582</v>
       </c>
       <c r="D4" t="n">
-        <v>120.661003112793</v>
+        <v>120.8099975585938</v>
       </c>
       <c r="E4" t="n">
-        <v>122.8499984741211</v>
+        <v>122.6969985961914</v>
       </c>
       <c r="F4" t="n">
-        <v>34598000</v>
+        <v>49476000</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -547,22 +547,22 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>45918</v>
+        <v>45922</v>
       </c>
       <c r="B5" t="n">
-        <v>122.0820007324219</v>
+        <v>122.1900024414062</v>
       </c>
       <c r="C5" t="n">
-        <v>123.3000030517578</v>
+        <v>122.9759979248047</v>
       </c>
       <c r="D5" t="n">
-        <v>120.5500030517578</v>
+        <v>121.4240036010742</v>
       </c>
       <c r="E5" t="n">
-        <v>120.7779998779297</v>
+        <v>122.7369995117188</v>
       </c>
       <c r="F5" t="n">
-        <v>31691000</v>
+        <v>25468000</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -573,22 +573,22 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>45919</v>
+        <v>45923</v>
       </c>
       <c r="B6" t="n">
-        <v>121.8619995117188</v>
+        <v>122.7330017089844</v>
       </c>
       <c r="C6" t="n">
-        <v>122.995002746582</v>
+        <v>122.7789993286133</v>
       </c>
       <c r="D6" t="n">
-        <v>120.8099975585938</v>
+        <v>120.8470001220703</v>
       </c>
       <c r="E6" t="n">
-        <v>122.6969985961914</v>
+        <v>121.8470001220703</v>
       </c>
       <c r="F6" t="n">
-        <v>49476000</v>
+        <v>24991000</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -599,22 +599,22 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>45922</v>
+        <v>45924</v>
       </c>
       <c r="B7" t="n">
-        <v>122.1900024414062</v>
+        <v>121.8610000610352</v>
       </c>
       <c r="C7" t="n">
-        <v>122.9759979248047</v>
+        <v>122.1500015258789</v>
       </c>
       <c r="D7" t="n">
-        <v>121.4240036010742</v>
+        <v>119.4199981689453</v>
       </c>
       <c r="E7" t="n">
-        <v>122.7369995117188</v>
+        <v>120.3949966430664</v>
       </c>
       <c r="F7" t="n">
-        <v>25468000</v>
+        <v>27731000</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -625,22 +625,22 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>45923</v>
+        <v>45925</v>
       </c>
       <c r="B8" t="n">
-        <v>122.7330017089844</v>
+        <v>120.3089981079102</v>
       </c>
       <c r="C8" t="n">
-        <v>122.7789993286133</v>
+        <v>121.6839981079102</v>
       </c>
       <c r="D8" t="n">
-        <v>120.8470001220703</v>
+        <v>119.1510009765625</v>
       </c>
       <c r="E8" t="n">
-        <v>121.8470001220703</v>
+        <v>120.8239974975586</v>
       </c>
       <c r="F8" t="n">
-        <v>24991000</v>
+        <v>19978000</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -651,22 +651,22 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>45924</v>
+        <v>45926</v>
       </c>
       <c r="B9" t="n">
-        <v>121.8610000610352</v>
+        <v>120.5419998168945</v>
       </c>
       <c r="C9" t="n">
-        <v>122.1500015258789</v>
+        <v>121.4000015258789</v>
       </c>
       <c r="D9" t="n">
-        <v>119.4199981689453</v>
+        <v>120</v>
       </c>
       <c r="E9" t="n">
-        <v>120.3949966430664</v>
+        <v>121.0609970092773</v>
       </c>
       <c r="F9" t="n">
-        <v>27731000</v>
+        <v>19450000</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -677,22 +677,22 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>45925</v>
+        <v>45929</v>
       </c>
       <c r="B10" t="n">
-        <v>120.3089981079102</v>
+        <v>120.5</v>
       </c>
       <c r="C10" t="n">
-        <v>121.6839981079102</v>
+        <v>122.4489974975586</v>
       </c>
       <c r="D10" t="n">
-        <v>119.1510009765625</v>
+        <v>118.7539978027344</v>
       </c>
       <c r="E10" t="n">
-        <v>120.8239974975586</v>
+        <v>120.640998840332</v>
       </c>
       <c r="F10" t="n">
-        <v>19978000</v>
+        <v>30332000</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -703,22 +703,22 @@
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>45926</v>
+        <v>45930</v>
       </c>
       <c r="B11" t="n">
-        <v>120.5419998168945</v>
+        <v>120.640998840332</v>
       </c>
       <c r="C11" t="n">
-        <v>121.4000015258789</v>
+        <v>120.8499984741211</v>
       </c>
       <c r="D11" t="n">
-        <v>120</v>
+        <v>117.8000030517578</v>
       </c>
       <c r="E11" t="n">
-        <v>121.0609970092773</v>
+        <v>119.8919982910156</v>
       </c>
       <c r="F11" t="n">
-        <v>19450000</v>
+        <v>38303000</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -729,22 +729,22 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>45929</v>
+        <v>45931</v>
       </c>
       <c r="B12" t="n">
-        <v>120.5</v>
+        <v>117.5490036010742</v>
       </c>
       <c r="C12" t="n">
-        <v>122.4489974975586</v>
+        <v>117.9140014648438</v>
       </c>
       <c r="D12" t="n">
-        <v>118.7539978027344</v>
+        <v>116.3209991455078</v>
       </c>
       <c r="E12" t="n">
-        <v>120.640998840332</v>
+        <v>117.0899963378906</v>
       </c>
       <c r="F12" t="n">
-        <v>30332000</v>
+        <v>41102000</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -755,22 +755,22 @@
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>45930</v>
+        <v>45932</v>
       </c>
       <c r="B13" t="n">
-        <v>120.640998840332</v>
+        <v>116.1500015258789</v>
       </c>
       <c r="C13" t="n">
-        <v>120.8499984741211</v>
+        <v>116.3330001831055</v>
       </c>
       <c r="D13" t="n">
-        <v>117.8000030517578</v>
+        <v>113.4000015258789</v>
       </c>
       <c r="E13" t="n">
-        <v>119.8919982910156</v>
+        <v>116.2529983520508</v>
       </c>
       <c r="F13" t="n">
-        <v>38303000</v>
+        <v>46855000</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -781,22 +781,22 @@
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>45931</v>
+        <v>45933</v>
       </c>
       <c r="B14" t="n">
-        <v>117.5490036010742</v>
+        <v>116.5</v>
       </c>
       <c r="C14" t="n">
-        <v>117.9140014648438</v>
+        <v>116.8000030517578</v>
       </c>
       <c r="D14" t="n">
-        <v>116.3209991455078</v>
+        <v>114.3219985961914</v>
       </c>
       <c r="E14" t="n">
-        <v>117.0899963378906</v>
+        <v>115.3320007324219</v>
       </c>
       <c r="F14" t="n">
-        <v>41102000</v>
+        <v>31374000</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -807,22 +807,22 @@
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>45932</v>
+        <v>45936</v>
       </c>
       <c r="B15" t="n">
-        <v>116.1500015258789</v>
+        <v>116.0370025634766</v>
       </c>
       <c r="C15" t="n">
-        <v>116.3330001831055</v>
+        <v>116.3580017089844</v>
       </c>
       <c r="D15" t="n">
-        <v>113.4000015258789</v>
+        <v>114.5449981689453</v>
       </c>
       <c r="E15" t="n">
-        <v>116.2529983520508</v>
+        <v>116.3310012817383</v>
       </c>
       <c r="F15" t="n">
-        <v>46855000</v>
+        <v>29686000</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -833,22 +833,22 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>45933</v>
+        <v>45937</v>
       </c>
       <c r="B16" t="n">
-        <v>116.5</v>
+        <v>117.7789993286133</v>
       </c>
       <c r="C16" t="n">
-        <v>116.8000030517578</v>
+        <v>120.1370010375977</v>
       </c>
       <c r="D16" t="n">
-        <v>114.3219985961914</v>
+        <v>117.7460021972656</v>
       </c>
       <c r="E16" t="n">
-        <v>115.3320007324219</v>
+        <v>119.1060028076172</v>
       </c>
       <c r="F16" t="n">
-        <v>31374000</v>
+        <v>33091000</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -859,22 +859,22 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>45936</v>
+        <v>45938</v>
       </c>
       <c r="B17" t="n">
-        <v>116.0370025634766</v>
+        <v>119.7109985351562</v>
       </c>
       <c r="C17" t="n">
-        <v>116.3580017089844</v>
+        <v>121.7389984130859</v>
       </c>
       <c r="D17" t="n">
-        <v>114.5449981689453</v>
+        <v>119.1999969482422</v>
       </c>
       <c r="E17" t="n">
-        <v>116.3310012817383</v>
+        <v>121.4250030517578</v>
       </c>
       <c r="F17" t="n">
-        <v>29686000</v>
+        <v>28514000</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -885,22 +885,22 @@
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>45937</v>
+        <v>45939</v>
       </c>
       <c r="B18" t="n">
-        <v>117.7789993286133</v>
+        <v>121.4250030517578</v>
       </c>
       <c r="C18" t="n">
-        <v>120.1370010375977</v>
+        <v>123.75</v>
       </c>
       <c r="D18" t="n">
-        <v>117.7460021972656</v>
+        <v>121.181999206543</v>
       </c>
       <c r="E18" t="n">
-        <v>119.1060028076172</v>
+        <v>123.1070022583008</v>
       </c>
       <c r="F18" t="n">
-        <v>33091000</v>
+        <v>28241000</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -911,22 +911,22 @@
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>45938</v>
+        <v>45940</v>
       </c>
       <c r="B19" t="n">
-        <v>119.7109985351562</v>
+        <v>122.9000015258789</v>
       </c>
       <c r="C19" t="n">
-        <v>121.7389984130859</v>
+        <v>124.6999969482422</v>
       </c>
       <c r="D19" t="n">
-        <v>119.1999969482422</v>
+        <v>121.9100036621094</v>
       </c>
       <c r="E19" t="n">
-        <v>121.4250030517578</v>
+        <v>122.0080032348633</v>
       </c>
       <c r="F19" t="n">
-        <v>28514000</v>
+        <v>42798000</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -937,22 +937,22 @@
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>45939</v>
+        <v>45943</v>
       </c>
       <c r="B20" t="n">
-        <v>121.4250030517578</v>
+        <v>122.1350021362305</v>
       </c>
       <c r="C20" t="n">
-        <v>123.75</v>
+        <v>123.1119995117188</v>
       </c>
       <c r="D20" t="n">
-        <v>121.181999206543</v>
+        <v>120.6809997558594</v>
       </c>
       <c r="E20" t="n">
-        <v>123.1070022583008</v>
+        <v>121.9029998779297</v>
       </c>
       <c r="F20" t="n">
-        <v>28241000</v>
+        <v>24608000</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -963,22 +963,22 @@
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>45940</v>
+        <v>45944</v>
       </c>
       <c r="B21" t="n">
-        <v>122.9000015258789</v>
+        <v>121.4749984741211</v>
       </c>
       <c r="C21" t="n">
-        <v>124.6999969482422</v>
+        <v>122.4290008544922</v>
       </c>
       <c r="D21" t="n">
-        <v>121.9100036621094</v>
+        <v>120.3099975585938</v>
       </c>
       <c r="E21" t="n">
-        <v>122.0080032348633</v>
+        <v>121.5350036621094</v>
       </c>
       <c r="F21" t="n">
-        <v>42798000</v>
+        <v>23624000</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -989,22 +989,22 @@
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>45943</v>
+        <v>45945</v>
       </c>
       <c r="B22" t="n">
-        <v>122.1350021362305</v>
+        <v>121.3010025024414</v>
       </c>
       <c r="C22" t="n">
-        <v>123.1119995117188</v>
+        <v>121.9619979858398</v>
       </c>
       <c r="D22" t="n">
-        <v>120.6809997558594</v>
+        <v>120.161003112793</v>
       </c>
       <c r="E22" t="n">
-        <v>121.9029998779297</v>
+        <v>120.3290023803711</v>
       </c>
       <c r="F22" t="n">
-        <v>24608000</v>
+        <v>20252000</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -1015,22 +1015,22 @@
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>45944</v>
+        <v>45946</v>
       </c>
       <c r="B23" t="n">
-        <v>121.4749984741211</v>
+        <v>121.2149963378906</v>
       </c>
       <c r="C23" t="n">
-        <v>122.4290008544922</v>
+        <v>121.6709976196289</v>
       </c>
       <c r="D23" t="n">
-        <v>120.3099975585938</v>
+        <v>117.5999984741211</v>
       </c>
       <c r="E23" t="n">
-        <v>121.5350036621094</v>
+        <v>118.359001159668</v>
       </c>
       <c r="F23" t="n">
-        <v>23624000</v>
+        <v>28326000</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -1041,22 +1041,22 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>45945</v>
+        <v>45947</v>
       </c>
       <c r="B24" t="n">
-        <v>121.3010025024414</v>
+        <v>118.3600006103516</v>
       </c>
       <c r="C24" t="n">
-        <v>121.9619979858398</v>
+        <v>120.3119964599609</v>
       </c>
       <c r="D24" t="n">
-        <v>120.161003112793</v>
+        <v>117.8949966430664</v>
       </c>
       <c r="E24" t="n">
-        <v>120.3290023803711</v>
+        <v>119.9359970092773</v>
       </c>
       <c r="F24" t="n">
-        <v>20252000</v>
+        <v>29571000</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -1067,22 +1067,22 @@
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>45946</v>
+        <v>45950</v>
       </c>
       <c r="B25" t="n">
-        <v>121.2149963378906</v>
+        <v>120.7880020141602</v>
       </c>
       <c r="C25" t="n">
-        <v>121.6709976196289</v>
+        <v>124.7760009765625</v>
       </c>
       <c r="D25" t="n">
-        <v>117.5999984741211</v>
+        <v>120.6900024414062</v>
       </c>
       <c r="E25" t="n">
-        <v>118.359001159668</v>
+        <v>123.8560028076172</v>
       </c>
       <c r="F25" t="n">
-        <v>28326000</v>
+        <v>39862000</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -1093,22 +1093,22 @@
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>45947</v>
+        <v>45951</v>
       </c>
       <c r="B26" t="n">
-        <v>118.3600006103516</v>
+        <v>124.2829971313477</v>
       </c>
       <c r="C26" t="n">
-        <v>120.3119964599609</v>
+        <v>124.8600006103516</v>
       </c>
       <c r="D26" t="n">
-        <v>117.8949966430664</v>
+        <v>123.1760025024414</v>
       </c>
       <c r="E26" t="n">
-        <v>119.9359970092773</v>
+        <v>124.1350021362305</v>
       </c>
       <c r="F26" t="n">
-        <v>29571000</v>
+        <v>65082000</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -1119,22 +1119,22 @@
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>45950</v>
+        <v>45952</v>
       </c>
       <c r="B27" t="n">
-        <v>120.7880020141602</v>
+        <v>114.2900009155273</v>
       </c>
       <c r="C27" t="n">
-        <v>124.7760009765625</v>
+        <v>115.7600021362305</v>
       </c>
       <c r="D27" t="n">
-        <v>120.6900024414062</v>
+        <v>111.2509994506836</v>
       </c>
       <c r="E27" t="n">
-        <v>123.8560028076172</v>
+        <v>111.6370010375977</v>
       </c>
       <c r="F27" t="n">
-        <v>39862000</v>
+        <v>147890000</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -1145,22 +1145,22 @@
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>45951</v>
+        <v>45953</v>
       </c>
       <c r="B28" t="n">
-        <v>124.2829971313477</v>
+        <v>112.6900024414062</v>
       </c>
       <c r="C28" t="n">
-        <v>124.8600006103516</v>
+        <v>112.7829971313477</v>
       </c>
       <c r="D28" t="n">
-        <v>123.1760025024414</v>
+        <v>109.9729995727539</v>
       </c>
       <c r="E28" t="n">
-        <v>124.1350021362305</v>
+        <v>111.359001159668</v>
       </c>
       <c r="F28" t="n">
-        <v>65082000</v>
+        <v>68497000</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
@@ -1171,22 +1171,22 @@
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>45952</v>
+        <v>45954</v>
       </c>
       <c r="B29" t="n">
-        <v>114.2900009155273</v>
+        <v>111.0999984741211</v>
       </c>
       <c r="C29" t="n">
-        <v>115.7600021362305</v>
+        <v>111.4509963989258</v>
       </c>
       <c r="D29" t="n">
-        <v>111.2509994506836</v>
+        <v>109.4410018920898</v>
       </c>
       <c r="E29" t="n">
-        <v>111.6370010375977</v>
+        <v>109.4690017700195</v>
       </c>
       <c r="F29" t="n">
-        <v>147890000</v>
+        <v>60280000</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -1197,22 +1197,22 @@
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>45953</v>
+        <v>45957</v>
       </c>
       <c r="B30" t="n">
-        <v>112.6900024414062</v>
+        <v>110.0670013427734</v>
       </c>
       <c r="C30" t="n">
-        <v>112.7829971313477</v>
+        <v>110.2279968261719</v>
       </c>
       <c r="D30" t="n">
-        <v>109.9729995727539</v>
+        <v>108.7300033569336</v>
       </c>
       <c r="E30" t="n">
-        <v>111.359001159668</v>
+        <v>109.4560012817383</v>
       </c>
       <c r="F30" t="n">
-        <v>68497000</v>
+        <v>46911000</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -1223,22 +1223,22 @@
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>45954</v>
+        <v>45958</v>
       </c>
       <c r="B31" t="n">
-        <v>111.0999984741211</v>
+        <v>109.4000015258789</v>
       </c>
       <c r="C31" t="n">
-        <v>111.4509963989258</v>
+        <v>111.697998046875</v>
       </c>
       <c r="D31" t="n">
-        <v>109.4410018920898</v>
+        <v>109.3010025024414</v>
       </c>
       <c r="E31" t="n">
-        <v>109.4690017700195</v>
+        <v>110.25</v>
       </c>
       <c r="F31" t="n">
-        <v>60280000</v>
+        <v>40209000</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -1249,22 +1249,22 @@
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>45957</v>
+        <v>45959</v>
       </c>
       <c r="B32" t="n">
-        <v>110.0670013427734</v>
+        <v>109.984001159668</v>
       </c>
       <c r="C32" t="n">
-        <v>110.2279968261719</v>
+        <v>110.8550033569336</v>
       </c>
       <c r="D32" t="n">
-        <v>108.7300033569336</v>
+        <v>109.5999984741211</v>
       </c>
       <c r="E32" t="n">
-        <v>109.4560012817383</v>
+        <v>110.0410003662109</v>
       </c>
       <c r="F32" t="n">
-        <v>46911000</v>
+        <v>33995000</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
@@ -1275,22 +1275,22 @@
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>45958</v>
+        <v>45960</v>
       </c>
       <c r="B33" t="n">
-        <v>109.4000015258789</v>
+        <v>109.4400024414062</v>
       </c>
       <c r="C33" t="n">
-        <v>111.697998046875</v>
+        <v>110.6159973144531</v>
       </c>
       <c r="D33" t="n">
-        <v>109.3010025024414</v>
+        <v>108.8109970092773</v>
       </c>
       <c r="E33" t="n">
-        <v>110.25</v>
+        <v>108.9000015258789</v>
       </c>
       <c r="F33" t="n">
-        <v>40209000</v>
+        <v>41581000</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -1301,22 +1301,22 @@
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>45959</v>
+        <v>45961</v>
       </c>
       <c r="B34" t="n">
-        <v>109.984001159668</v>
+        <v>110.5390014648438</v>
       </c>
       <c r="C34" t="n">
-        <v>110.8550033569336</v>
+        <v>113.4879989624023</v>
       </c>
       <c r="D34" t="n">
-        <v>109.5999984741211</v>
+        <v>110.197998046875</v>
       </c>
       <c r="E34" t="n">
-        <v>110.0410003662109</v>
+        <v>111.8860015869141</v>
       </c>
       <c r="F34" t="n">
-        <v>33995000</v>
+        <v>68665000</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
@@ -1327,22 +1327,22 @@
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>45960</v>
+        <v>45964</v>
       </c>
       <c r="B35" t="n">
-        <v>109.4400024414062</v>
+        <v>113.3239974975586</v>
       </c>
       <c r="C35" t="n">
-        <v>110.6159973144531</v>
+        <v>113.3499984741211</v>
       </c>
       <c r="D35" t="n">
-        <v>108.8109970092773</v>
+        <v>107.5149993896484</v>
       </c>
       <c r="E35" t="n">
-        <v>108.9000015258789</v>
+        <v>110.0090026855469</v>
       </c>
       <c r="F35" t="n">
-        <v>41581000</v>
+        <v>58634000</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
@@ -1353,22 +1353,22 @@
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>45961</v>
+        <v>45965</v>
       </c>
       <c r="B36" t="n">
-        <v>110.5390014648438</v>
+        <v>109.9990005493164</v>
       </c>
       <c r="C36" t="n">
-        <v>113.4879989624023</v>
+        <v>110.4599990844727</v>
       </c>
       <c r="D36" t="n">
-        <v>110.197998046875</v>
+        <v>108.6679992675781</v>
       </c>
       <c r="E36" t="n">
-        <v>111.8860015869141</v>
+        <v>109.2959976196289</v>
       </c>
       <c r="F36" t="n">
-        <v>68665000</v>
+        <v>38718000</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -1379,22 +1379,22 @@
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>45964</v>
+        <v>45966</v>
       </c>
       <c r="B37" t="n">
-        <v>113.3239974975586</v>
+        <v>108.5</v>
       </c>
       <c r="C37" t="n">
-        <v>113.3499984741211</v>
+        <v>110.0849990844727</v>
       </c>
       <c r="D37" t="n">
-        <v>107.5149993896484</v>
+        <v>107.3369979858398</v>
       </c>
       <c r="E37" t="n">
-        <v>110.0090026855469</v>
+        <v>109.8460006713867</v>
       </c>
       <c r="F37" t="n">
-        <v>58634000</v>
+        <v>35539000</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
@@ -1405,22 +1405,22 @@
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>45965</v>
+        <v>45967</v>
       </c>
       <c r="B38" t="n">
-        <v>109.9990005493164</v>
+        <v>109.4580001831055</v>
       </c>
       <c r="C38" t="n">
-        <v>110.4599990844727</v>
+        <v>110.370002746582</v>
       </c>
       <c r="D38" t="n">
-        <v>108.6679992675781</v>
+        <v>108.5130004882812</v>
       </c>
       <c r="E38" t="n">
-        <v>109.2959976196289</v>
+        <v>109.7020034790039</v>
       </c>
       <c r="F38" t="n">
-        <v>38718000</v>
+        <v>36532000</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
@@ -1431,22 +1431,22 @@
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>45966</v>
+        <v>45968</v>
       </c>
       <c r="B39" t="n">
-        <v>108.5</v>
+        <v>109.4179992675781</v>
       </c>
       <c r="C39" t="n">
-        <v>110.0849990844727</v>
+        <v>110.8219985961914</v>
       </c>
       <c r="D39" t="n">
-        <v>107.3369979858398</v>
+        <v>108.75</v>
       </c>
       <c r="E39" t="n">
-        <v>109.8460006713867</v>
+        <v>110.3659973144531</v>
       </c>
       <c r="F39" t="n">
-        <v>35539000</v>
+        <v>44125000</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
@@ -1457,22 +1457,22 @@
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>45967</v>
+        <v>45971</v>
       </c>
       <c r="B40" t="n">
-        <v>109.4580001831055</v>
+        <v>110.6719970703125</v>
       </c>
       <c r="C40" t="n">
-        <v>110.370002746582</v>
+        <v>112.8199996948242</v>
       </c>
       <c r="D40" t="n">
-        <v>108.5130004882812</v>
+        <v>110.4049987792969</v>
       </c>
       <c r="E40" t="n">
-        <v>109.7020034790039</v>
+        <v>112.0070037841797</v>
       </c>
       <c r="F40" t="n">
-        <v>36532000</v>
+        <v>36929000</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
@@ -1483,22 +1483,22 @@
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>45968</v>
+        <v>45972</v>
       </c>
       <c r="B41" t="n">
-        <v>109.4179992675781</v>
+        <v>111.7600021362305</v>
       </c>
       <c r="C41" t="n">
-        <v>110.8219985961914</v>
+        <v>113.9219970703125</v>
       </c>
       <c r="D41" t="n">
-        <v>108.75</v>
+        <v>111.2799987792969</v>
       </c>
       <c r="E41" t="n">
-        <v>110.3659973144531</v>
+        <v>113.6439971923828</v>
       </c>
       <c r="F41" t="n">
-        <v>44125000</v>
+        <v>27966000</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
@@ -1509,22 +1509,22 @@
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>45971</v>
+        <v>45973</v>
       </c>
       <c r="B42" t="n">
-        <v>110.6719970703125</v>
+        <v>113.8170013427734</v>
       </c>
       <c r="C42" t="n">
-        <v>112.8199996948242</v>
+        <v>116.4339981079102</v>
       </c>
       <c r="D42" t="n">
-        <v>110.4049987792969</v>
+        <v>112.8259963989258</v>
       </c>
       <c r="E42" t="n">
-        <v>112.0070037841797</v>
+        <v>115.75</v>
       </c>
       <c r="F42" t="n">
-        <v>36929000</v>
+        <v>39221000</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
@@ -1535,22 +1535,22 @@
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>45972</v>
+        <v>45974</v>
       </c>
       <c r="B43" t="n">
-        <v>111.7600021362305</v>
+        <v>115.8499984741211</v>
       </c>
       <c r="C43" t="n">
-        <v>113.9219970703125</v>
+        <v>116.7330017089844</v>
       </c>
       <c r="D43" t="n">
-        <v>111.2799987792969</v>
+        <v>114.5690002441406</v>
       </c>
       <c r="E43" t="n">
-        <v>113.6439971923828</v>
+        <v>115.4229965209961</v>
       </c>
       <c r="F43" t="n">
-        <v>27966000</v>
+        <v>40144000</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
@@ -1561,22 +1561,22 @@
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
-        <v>45973</v>
+        <v>45975</v>
       </c>
       <c r="B44" t="n">
-        <v>113.8170013427734</v>
+        <v>114.2730026245117</v>
       </c>
       <c r="C44" t="n">
-        <v>116.4339981079102</v>
+        <v>114.2730026245117</v>
       </c>
       <c r="D44" t="n">
-        <v>112.8259963989258</v>
+        <v>110.7210006713867</v>
       </c>
       <c r="E44" t="n">
-        <v>115.75</v>
+        <v>111.2170028686523</v>
       </c>
       <c r="F44" t="n">
-        <v>39221000</v>
+        <v>47607000</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
@@ -1587,48 +1587,48 @@
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
-        <v>45974</v>
+        <v>45978</v>
       </c>
       <c r="B45" t="n">
-        <v>115.8499984741211</v>
+        <v>110.75</v>
       </c>
       <c r="C45" t="n">
-        <v>116.7330017089844</v>
+        <v>111.8499984741211</v>
       </c>
       <c r="D45" t="n">
-        <v>114.5690002441406</v>
+        <v>109.5500030517578</v>
       </c>
       <c r="E45" t="n">
-        <v>115.4229965209961</v>
+        <v>110.2900009155273</v>
       </c>
       <c r="F45" t="n">
-        <v>40144000</v>
+        <v>26082700</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
-        <v>45975</v>
+        <v>45979</v>
       </c>
       <c r="B46" t="n">
-        <v>114.2730026245117</v>
+        <v>110.2900009155273</v>
       </c>
       <c r="C46" t="n">
-        <v>114.2730026245117</v>
+        <v>115.25</v>
       </c>
       <c r="D46" t="n">
-        <v>110.7210006713867</v>
+        <v>109.1999969482422</v>
       </c>
       <c r="E46" t="n">
-        <v>111.2170028686523</v>
+        <v>114.0899963378906</v>
       </c>
       <c r="F46" t="n">
-        <v>47607000</v>
+        <v>43440600</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
@@ -1639,48 +1639,48 @@
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
-        <v>45978</v>
+        <v>45980</v>
       </c>
       <c r="B47" t="n">
-        <v>110.75</v>
+        <v>113</v>
       </c>
       <c r="C47" t="n">
-        <v>111.8499984741211</v>
+        <v>113.3399963378906</v>
       </c>
       <c r="D47" t="n">
-        <v>109.5500030517578</v>
+        <v>108.6100006103516</v>
       </c>
       <c r="E47" t="n">
-        <v>110.2900009155273</v>
+        <v>110</v>
       </c>
       <c r="F47" t="n">
-        <v>26082700</v>
+        <v>31868100</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
-        <v>45979</v>
+        <v>45981</v>
       </c>
       <c r="B48" t="n">
-        <v>110.2900009155273</v>
+        <v>111</v>
       </c>
       <c r="C48" t="n">
-        <v>115.25</v>
+        <v>111.0999984741211</v>
       </c>
       <c r="D48" t="n">
-        <v>109.1999969482422</v>
+        <v>105.3899993896484</v>
       </c>
       <c r="E48" t="n">
-        <v>114.0899963378906</v>
+        <v>105.6699981689453</v>
       </c>
       <c r="F48" t="n">
-        <v>43440600</v>
+        <v>36918500</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
@@ -1691,22 +1691,22 @@
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>45980</v>
+        <v>45982</v>
       </c>
       <c r="B49" t="n">
-        <v>113</v>
+        <v>105.129997253418</v>
       </c>
       <c r="C49" t="n">
-        <v>113.3399963378906</v>
+        <v>106.5299987792969</v>
       </c>
       <c r="D49" t="n">
-        <v>108.6100006103516</v>
+        <v>103.8099975585938</v>
       </c>
       <c r="E49" t="n">
-        <v>110</v>
+        <v>104.3099975585938</v>
       </c>
       <c r="F49" t="n">
-        <v>31868100</v>
+        <v>41232700</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
@@ -1717,22 +1717,22 @@
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>45981</v>
+        <v>45985</v>
       </c>
       <c r="B50" t="n">
-        <v>111</v>
+        <v>104.25</v>
       </c>
       <c r="C50" t="n">
-        <v>111.0999984741211</v>
+        <v>108.0400009155273</v>
       </c>
       <c r="D50" t="n">
-        <v>105.3899993896484</v>
+        <v>103.3199996948242</v>
       </c>
       <c r="E50" t="n">
-        <v>105.6699981689453</v>
+        <v>106.9700012207031</v>
       </c>
       <c r="F50" t="n">
-        <v>36918500</v>
+        <v>62918300</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
-        <v>45982</v>
+        <v>45986</v>
       </c>
       <c r="B51" t="n">
-        <v>105.129997253418</v>
+        <v>106.120002746582</v>
       </c>
       <c r="C51" t="n">
-        <v>106.5299987792969</v>
+        <v>106.3000030517578</v>
       </c>
       <c r="D51" t="n">
-        <v>103.8099975585938</v>
+        <v>103.8199996948242</v>
       </c>
       <c r="E51" t="n">
-        <v>104.3099975585938</v>
+        <v>104.4000015258789</v>
       </c>
       <c r="F51" t="n">
-        <v>41232700</v>
+        <v>35122600</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
@@ -1769,22 +1769,22 @@
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
-        <v>45985</v>
+        <v>45987</v>
       </c>
       <c r="B52" t="n">
-        <v>104.25</v>
+        <v>105.7399978637695</v>
       </c>
       <c r="C52" t="n">
-        <v>108.0400009155273</v>
+        <v>106.9499969482422</v>
       </c>
       <c r="D52" t="n">
-        <v>103.3199996948242</v>
+        <v>105.2200012207031</v>
       </c>
       <c r="E52" t="n">
-        <v>106.9700012207031</v>
+        <v>106.1399993896484</v>
       </c>
       <c r="F52" t="n">
-        <v>62918300</v>
+        <v>27951000</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
@@ -1795,22 +1795,22 @@
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
-        <v>45986</v>
+        <v>45989</v>
       </c>
       <c r="B53" t="n">
-        <v>106.120002746582</v>
+        <v>106.4400024414062</v>
       </c>
       <c r="C53" t="n">
-        <v>106.3000030517578</v>
+        <v>107.9400024414062</v>
       </c>
       <c r="D53" t="n">
-        <v>103.8199996948242</v>
+        <v>106.2399978637695</v>
       </c>
       <c r="E53" t="n">
-        <v>104.4000015258789</v>
+        <v>107.5800018310547</v>
       </c>
       <c r="F53" t="n">
-        <v>35122600</v>
+        <v>15021600</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
@@ -1821,22 +1821,22 @@
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
-        <v>45987</v>
+        <v>45992</v>
       </c>
       <c r="B54" t="n">
-        <v>105.7399978637695</v>
+        <v>106.5100021362305</v>
       </c>
       <c r="C54" t="n">
-        <v>106.9499969482422</v>
+        <v>109.3399963378906</v>
       </c>
       <c r="D54" t="n">
-        <v>105.2200012207031</v>
+        <v>106.3099975585938</v>
       </c>
       <c r="E54" t="n">
-        <v>106.1399993896484</v>
+        <v>109.129997253418</v>
       </c>
       <c r="F54" t="n">
-        <v>27951000</v>
+        <v>24873400</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
@@ -1847,22 +1847,22 @@
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
-        <v>45989</v>
+        <v>45993</v>
       </c>
       <c r="B55" t="n">
-        <v>106.4400024414062</v>
+        <v>109.2099990844727</v>
       </c>
       <c r="C55" t="n">
-        <v>107.9400024414062</v>
+        <v>109.7300033569336</v>
       </c>
       <c r="D55" t="n">
-        <v>106.2399978637695</v>
+        <v>107.5199966430664</v>
       </c>
       <c r="E55" t="n">
-        <v>107.5800018310547</v>
+        <v>109.3499984741211</v>
       </c>
       <c r="F55" t="n">
-        <v>15021600</v>
+        <v>25763000</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
@@ -1873,22 +1873,22 @@
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
-        <v>45992</v>
+        <v>45994</v>
       </c>
       <c r="B56" t="n">
-        <v>106.5100021362305</v>
+        <v>106.5899963378906</v>
       </c>
       <c r="C56" t="n">
-        <v>109.3399963378906</v>
+        <v>106.870002746582</v>
       </c>
       <c r="D56" t="n">
-        <v>106.3099975585938</v>
+        <v>102.0299987792969</v>
       </c>
       <c r="E56" t="n">
-        <v>109.129997253418</v>
+        <v>103.9599990844727</v>
       </c>
       <c r="F56" t="n">
-        <v>24873400</v>
+        <v>53593400</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
@@ -1899,22 +1899,22 @@
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
-        <v>45993</v>
+        <v>45995</v>
       </c>
       <c r="B57" t="n">
-        <v>109.2099990844727</v>
+        <v>103.5699996948242</v>
       </c>
       <c r="C57" t="n">
-        <v>109.7300033569336</v>
+        <v>103.8000030517578</v>
       </c>
       <c r="D57" t="n">
-        <v>107.5199966430664</v>
+        <v>101.7699966430664</v>
       </c>
       <c r="E57" t="n">
-        <v>109.3499984741211</v>
+        <v>103.2200012207031</v>
       </c>
       <c r="F57" t="n">
-        <v>25763000</v>
+        <v>51779100</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
@@ -1925,22 +1925,22 @@
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
-        <v>45994</v>
+        <v>45996</v>
       </c>
       <c r="B58" t="n">
-        <v>106.5899963378906</v>
+        <v>98.77999877929688</v>
       </c>
       <c r="C58" t="n">
-        <v>106.870002746582</v>
+        <v>104.7900009155273</v>
       </c>
       <c r="D58" t="n">
-        <v>102.0299987792969</v>
+        <v>97.73999786376953</v>
       </c>
       <c r="E58" t="n">
-        <v>103.9599990844727</v>
+        <v>100.2399978637695</v>
       </c>
       <c r="F58" t="n">
-        <v>53593400</v>
+        <v>133363600</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
@@ -1951,22 +1951,22 @@
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
-        <v>45995</v>
+        <v>45999</v>
       </c>
       <c r="B59" t="n">
-        <v>103.5699996948242</v>
+        <v>99.87000274658203</v>
       </c>
       <c r="C59" t="n">
-        <v>103.8000030517578</v>
+        <v>99.88999938964844</v>
       </c>
       <c r="D59" t="n">
-        <v>101.7699966430664</v>
+        <v>95.30000305175781</v>
       </c>
       <c r="E59" t="n">
-        <v>103.2200012207031</v>
+        <v>96.79000091552734</v>
       </c>
       <c r="F59" t="n">
-        <v>51779100</v>
+        <v>100906300</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
@@ -1977,22 +1977,22 @@
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
-        <v>45996</v>
+        <v>46000</v>
       </c>
       <c r="B60" t="n">
-        <v>98.77999877929688</v>
+        <v>97.02999877929688</v>
       </c>
       <c r="C60" t="n">
-        <v>104.7900009155273</v>
+        <v>97.23999786376953</v>
       </c>
       <c r="D60" t="n">
-        <v>97.73999786376953</v>
+        <v>95.44999694824219</v>
       </c>
       <c r="E60" t="n">
-        <v>100.2399978637695</v>
+        <v>96.70999908447266</v>
       </c>
       <c r="F60" t="n">
-        <v>133363600</v>
+        <v>51745600</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
@@ -2003,22 +2003,22 @@
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
-        <v>45999</v>
+        <v>46001</v>
       </c>
       <c r="B61" t="n">
-        <v>99.87000274658203</v>
+        <v>96.73999786376953</v>
       </c>
       <c r="C61" t="n">
-        <v>99.88999938964844</v>
+        <v>96.97000122070312</v>
       </c>
       <c r="D61" t="n">
-        <v>95.30000305175781</v>
+        <v>92.34999847412109</v>
       </c>
       <c r="E61" t="n">
-        <v>96.79000091552734</v>
+        <v>92.70999908447266</v>
       </c>
       <c r="F61" t="n">
-        <v>100906300</v>
+        <v>74129300</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
@@ -2029,22 +2029,22 @@
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
-        <v>46000</v>
+        <v>46002</v>
       </c>
       <c r="B62" t="n">
-        <v>97.02999877929688</v>
+        <v>93.90000152587891</v>
       </c>
       <c r="C62" t="n">
-        <v>97.23999786376953</v>
+        <v>94.81999969482422</v>
       </c>
       <c r="D62" t="n">
-        <v>95.44999694824219</v>
+        <v>92.76000213623047</v>
       </c>
       <c r="E62" t="n">
-        <v>96.70999908447266</v>
+        <v>94.08999633789062</v>
       </c>
       <c r="F62" t="n">
-        <v>51745600</v>
+        <v>43949000</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
@@ -2055,22 +2055,22 @@
     </row>
     <row r="63">
       <c r="A63" s="1" t="n">
-        <v>46001</v>
+        <v>46003</v>
       </c>
       <c r="B63" t="n">
-        <v>96.73999786376953</v>
+        <v>95.5</v>
       </c>
       <c r="C63" t="n">
-        <v>96.97000122070312</v>
+        <v>96.91999816894531</v>
       </c>
       <c r="D63" t="n">
-        <v>92.34999847412109</v>
+        <v>94.65000152587891</v>
       </c>
       <c r="E63" t="n">
-        <v>92.70999908447266</v>
+        <v>95.19000244140625</v>
       </c>
       <c r="F63" t="n">
-        <v>74129300</v>
+        <v>49323100</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
@@ -2081,22 +2081,22 @@
     </row>
     <row r="64">
       <c r="A64" s="1" t="n">
-        <v>46002</v>
+        <v>46006</v>
       </c>
       <c r="B64" t="n">
-        <v>93.90000152587891</v>
+        <v>96.01999664306641</v>
       </c>
       <c r="C64" t="n">
-        <v>94.81999969482422</v>
+        <v>96.37000274658203</v>
       </c>
       <c r="D64" t="n">
-        <v>92.76000213623047</v>
+        <v>93.52999877929688</v>
       </c>
       <c r="E64" t="n">
-        <v>94.08999633789062</v>
+        <v>93.76999664306641</v>
       </c>
       <c r="F64" t="n">
-        <v>43949000</v>
+        <v>40016500</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
@@ -2107,22 +2107,22 @@
     </row>
     <row r="65">
       <c r="A65" s="1" t="n">
-        <v>46003</v>
+        <v>46007</v>
       </c>
       <c r="B65" t="n">
-        <v>95.5</v>
+        <v>93.87999725341797</v>
       </c>
       <c r="C65" t="n">
-        <v>96.91999816894531</v>
+        <v>94.93000030517578</v>
       </c>
       <c r="D65" t="n">
-        <v>94.65000152587891</v>
+        <v>93.31999969482422</v>
       </c>
       <c r="E65" t="n">
-        <v>95.19000244140625</v>
+        <v>94.56999969482422</v>
       </c>
       <c r="F65" t="n">
-        <v>49323100</v>
+        <v>34265000</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
@@ -2133,22 +2133,22 @@
     </row>
     <row r="66">
       <c r="A66" s="1" t="n">
-        <v>46006</v>
+        <v>46008</v>
       </c>
       <c r="B66" t="n">
-        <v>96.01999664306641</v>
+        <v>95.98000335693359</v>
       </c>
       <c r="C66" t="n">
-        <v>96.37000274658203</v>
+        <v>97.33000183105469</v>
       </c>
       <c r="D66" t="n">
-        <v>93.52999877929688</v>
+        <v>94.45999908447266</v>
       </c>
       <c r="E66" t="n">
-        <v>93.76999664306641</v>
+        <v>94.79000091552734</v>
       </c>
       <c r="F66" t="n">
-        <v>40016500</v>
+        <v>50472800</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
@@ -2159,22 +2159,22 @@
     </row>
     <row r="67">
       <c r="A67" s="1" t="n">
-        <v>46007</v>
+        <v>46009</v>
       </c>
       <c r="B67" t="n">
-        <v>93.87999725341797</v>
+        <v>95.01999664306641</v>
       </c>
       <c r="C67" t="n">
-        <v>94.93000030517578</v>
+        <v>95.80999755859375</v>
       </c>
       <c r="D67" t="n">
-        <v>93.31999969482422</v>
+        <v>93.58999633789062</v>
       </c>
       <c r="E67" t="n">
-        <v>94.56999969482422</v>
+        <v>94</v>
       </c>
       <c r="F67" t="n">
-        <v>34265000</v>
+        <v>37244700</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
@@ -2185,22 +2185,22 @@
     </row>
     <row r="68">
       <c r="A68" s="1" t="n">
-        <v>46008</v>
+        <v>46010</v>
       </c>
       <c r="B68" t="n">
-        <v>95.98000335693359</v>
+        <v>93.56999969482422</v>
       </c>
       <c r="C68" t="n">
-        <v>97.33000183105469</v>
+        <v>95.54000091552734</v>
       </c>
       <c r="D68" t="n">
-        <v>94.45999908447266</v>
+        <v>93.44999694824219</v>
       </c>
       <c r="E68" t="n">
-        <v>94.79000091552734</v>
+        <v>94.38999938964844</v>
       </c>
       <c r="F68" t="n">
-        <v>50472800</v>
+        <v>78990200</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
@@ -2211,22 +2211,22 @@
     </row>
     <row r="69">
       <c r="A69" s="1" t="n">
-        <v>46009</v>
+        <v>46013</v>
       </c>
       <c r="B69" t="n">
-        <v>95.01999664306641</v>
+        <v>94.70999908447266</v>
       </c>
       <c r="C69" t="n">
-        <v>95.80999755859375</v>
+        <v>94.70999908447266</v>
       </c>
       <c r="D69" t="n">
-        <v>93.58999633789062</v>
+        <v>92.91000366210938</v>
       </c>
       <c r="E69" t="n">
-        <v>94</v>
+        <v>93.23000335693359</v>
       </c>
       <c r="F69" t="n">
-        <v>37244700</v>
+        <v>39484800</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
@@ -2237,22 +2237,22 @@
     </row>
     <row r="70">
       <c r="A70" s="1" t="n">
-        <v>46010</v>
+        <v>46014</v>
       </c>
       <c r="B70" t="n">
-        <v>93.56999969482422</v>
+        <v>93.40000152587891</v>
       </c>
       <c r="C70" t="n">
-        <v>95.54000091552734</v>
+        <v>93.80999755859375</v>
       </c>
       <c r="D70" t="n">
-        <v>93.44999694824219</v>
+        <v>91.33000183105469</v>
       </c>
       <c r="E70" t="n">
-        <v>94.38999938964844</v>
+        <v>93.5</v>
       </c>
       <c r="F70" t="n">
-        <v>78990200</v>
+        <v>25896200</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
@@ -2263,22 +2263,22 @@
     </row>
     <row r="71">
       <c r="A71" s="1" t="n">
-        <v>46013</v>
+        <v>46015</v>
       </c>
       <c r="B71" t="n">
-        <v>94.70999908447266</v>
+        <v>93.11000061035156</v>
       </c>
       <c r="C71" t="n">
-        <v>94.70999908447266</v>
+        <v>93.68000030517578</v>
       </c>
       <c r="D71" t="n">
-        <v>92.91000366210938</v>
+        <v>92.66999816894531</v>
       </c>
       <c r="E71" t="n">
-        <v>93.23000335693359</v>
+        <v>93.63999938964844</v>
       </c>
       <c r="F71" t="n">
-        <v>39484800</v>
+        <v>12427900</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
@@ -2289,22 +2289,22 @@
     </row>
     <row r="72">
       <c r="A72" s="1" t="n">
-        <v>46014</v>
+        <v>46017</v>
       </c>
       <c r="B72" t="n">
-        <v>93.40000152587891</v>
+        <v>93.48000335693359</v>
       </c>
       <c r="C72" t="n">
-        <v>93.80999755859375</v>
+        <v>94.69000244140625</v>
       </c>
       <c r="D72" t="n">
-        <v>91.33000183105469</v>
+        <v>93.26999664306641</v>
       </c>
       <c r="E72" t="n">
-        <v>93.5</v>
+        <v>94.47000122070312</v>
       </c>
       <c r="F72" t="n">
-        <v>25896200</v>
+        <v>22068300</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
@@ -2315,22 +2315,22 @@
     </row>
     <row r="73">
       <c r="A73" s="1" t="n">
-        <v>46015</v>
+        <v>46020</v>
       </c>
       <c r="B73" t="n">
-        <v>93.11000061035156</v>
+        <v>93.98999786376953</v>
       </c>
       <c r="C73" t="n">
-        <v>93.68000030517578</v>
+        <v>94.97000122070312</v>
       </c>
       <c r="D73" t="n">
-        <v>92.66999816894531</v>
+        <v>93.62999725341797</v>
       </c>
       <c r="E73" t="n">
-        <v>93.63999938964844</v>
+        <v>94.15000152587891</v>
       </c>
       <c r="F73" t="n">
-        <v>12427900</v>
+        <v>24493700</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
@@ -2341,22 +2341,22 @@
     </row>
     <row r="74">
       <c r="A74" s="1" t="n">
-        <v>46017</v>
+        <v>46021</v>
       </c>
       <c r="B74" t="n">
-        <v>93.48000335693359</v>
+        <v>93.51999664306641</v>
       </c>
       <c r="C74" t="n">
-        <v>94.69000244140625</v>
+        <v>93.98999786376953</v>
       </c>
       <c r="D74" t="n">
-        <v>93.26999664306641</v>
+        <v>93.33999633789062</v>
       </c>
       <c r="E74" t="n">
-        <v>94.47000122070312</v>
+        <v>93.77999877929688</v>
       </c>
       <c r="F74" t="n">
-        <v>22068300</v>
+        <v>23422000</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
@@ -2367,22 +2367,22 @@
     </row>
     <row r="75">
       <c r="A75" s="1" t="n">
-        <v>46020</v>
+        <v>46022</v>
       </c>
       <c r="B75" t="n">
-        <v>93.98999786376953</v>
+        <v>93.59999847412109</v>
       </c>
       <c r="C75" t="n">
-        <v>94.97000122070312</v>
+        <v>94.30999755859375</v>
       </c>
       <c r="D75" t="n">
-        <v>93.62999725341797</v>
+        <v>93.19999694824219</v>
       </c>
       <c r="E75" t="n">
-        <v>94.15000152587891</v>
+        <v>93.76000213623047</v>
       </c>
       <c r="F75" t="n">
-        <v>24493700</v>
+        <v>23495200</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
@@ -2393,22 +2393,22 @@
     </row>
     <row r="76">
       <c r="A76" s="1" t="n">
-        <v>46021</v>
+        <v>46024</v>
       </c>
       <c r="B76" t="n">
-        <v>93.51999664306641</v>
+        <v>94.12999725341797</v>
       </c>
       <c r="C76" t="n">
-        <v>93.98999786376953</v>
+        <v>94.12999725341797</v>
       </c>
       <c r="D76" t="n">
-        <v>93.33999633789062</v>
+        <v>90.80999755859375</v>
       </c>
       <c r="E76" t="n">
-        <v>93.77999877929688</v>
+        <v>90.98999786376953</v>
       </c>
       <c r="F76" t="n">
-        <v>23422000</v>
+        <v>41155400</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
@@ -2419,22 +2419,22 @@
     </row>
     <row r="77">
       <c r="A77" s="1" t="n">
-        <v>46022</v>
+        <v>46027</v>
       </c>
       <c r="B77" t="n">
-        <v>93.59999847412109</v>
+        <v>90.91999816894531</v>
       </c>
       <c r="C77" t="n">
-        <v>94.30999755859375</v>
+        <v>92.62999725341797</v>
       </c>
       <c r="D77" t="n">
-        <v>93.19999694824219</v>
+        <v>90.83999633789062</v>
       </c>
       <c r="E77" t="n">
-        <v>93.76000213623047</v>
+        <v>91.45999908447266</v>
       </c>
       <c r="F77" t="n">
-        <v>23495200</v>
+        <v>39183300</v>
       </c>
       <c r="G77" t="n">
         <v>0</v>
@@ -2445,22 +2445,22 @@
     </row>
     <row r="78">
       <c r="A78" s="1" t="n">
-        <v>46024</v>
+        <v>46028</v>
       </c>
       <c r="B78" t="n">
-        <v>94.12999725341797</v>
+        <v>91.54000091552734</v>
       </c>
       <c r="C78" t="n">
-        <v>94.12999725341797</v>
+        <v>91.63999938964844</v>
       </c>
       <c r="D78" t="n">
-        <v>90.80999755859375</v>
+        <v>89.73999786376953</v>
       </c>
       <c r="E78" t="n">
-        <v>90.98999786376953</v>
+        <v>90.65000152587891</v>
       </c>
       <c r="F78" t="n">
-        <v>41155400</v>
+        <v>43331000</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
@@ -2471,22 +2471,22 @@
     </row>
     <row r="79">
       <c r="A79" s="1" t="n">
-        <v>46027</v>
+        <v>46029</v>
       </c>
       <c r="B79" t="n">
-        <v>90.91999816894531</v>
+        <v>91.55999755859375</v>
       </c>
       <c r="C79" t="n">
-        <v>92.62999725341797</v>
+        <v>92.41999816894531</v>
       </c>
       <c r="D79" t="n">
-        <v>90.83999633789062</v>
+        <v>90.05999755859375</v>
       </c>
       <c r="E79" t="n">
-        <v>91.45999908447266</v>
+        <v>90.73000335693359</v>
       </c>
       <c r="F79" t="n">
-        <v>39183300</v>
+        <v>36525700</v>
       </c>
       <c r="G79" t="n">
         <v>0</v>
@@ -2497,22 +2497,22 @@
     </row>
     <row r="80">
       <c r="A80" s="1" t="n">
-        <v>46028</v>
+        <v>46030</v>
       </c>
       <c r="B80" t="n">
-        <v>91.54000091552734</v>
+        <v>90.44999694824219</v>
       </c>
       <c r="C80" t="n">
-        <v>91.63999938964844</v>
+        <v>91.25</v>
       </c>
       <c r="D80" t="n">
-        <v>89.73999786376953</v>
+        <v>89.58000183105469</v>
       </c>
       <c r="E80" t="n">
-        <v>90.65000152587891</v>
+        <v>90.52999877929688</v>
       </c>
       <c r="F80" t="n">
-        <v>43331000</v>
+        <v>40068700</v>
       </c>
       <c r="G80" t="n">
         <v>0</v>
@@ -2523,22 +2523,22 @@
     </row>
     <row r="81">
       <c r="A81" s="1" t="n">
-        <v>46029</v>
+        <v>46031</v>
       </c>
       <c r="B81" t="n">
-        <v>91.55999755859375</v>
+        <v>90.02999877929688</v>
       </c>
       <c r="C81" t="n">
-        <v>92.41999816894531</v>
+        <v>90.05000305175781</v>
       </c>
       <c r="D81" t="n">
-        <v>90.05999755859375</v>
+        <v>88.31999969482422</v>
       </c>
       <c r="E81" t="n">
-        <v>90.73000335693359</v>
+        <v>89.45999908447266</v>
       </c>
       <c r="F81" t="n">
-        <v>36525700</v>
+        <v>55579500</v>
       </c>
       <c r="G81" t="n">
         <v>0</v>
@@ -2549,22 +2549,22 @@
     </row>
     <row r="82">
       <c r="A82" s="1" t="n">
-        <v>46030</v>
+        <v>46034</v>
       </c>
       <c r="B82" t="n">
-        <v>90.44999694824219</v>
+        <v>89.69000244140625</v>
       </c>
       <c r="C82" t="n">
-        <v>91.25</v>
+        <v>90.33999633789062</v>
       </c>
       <c r="D82" t="n">
-        <v>89.58000183105469</v>
+        <v>89.33000183105469</v>
       </c>
       <c r="E82" t="n">
-        <v>90.52999877929688</v>
+        <v>89.41000366210938</v>
       </c>
       <c r="F82" t="n">
-        <v>40068700</v>
+        <v>36290600</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
@@ -2575,22 +2575,22 @@
     </row>
     <row r="83">
       <c r="A83" s="1" t="n">
-        <v>46031</v>
+        <v>46035</v>
       </c>
       <c r="B83" t="n">
-        <v>90.02999877929688</v>
+        <v>89.44000244140625</v>
       </c>
       <c r="C83" t="n">
-        <v>90.05000305175781</v>
+        <v>91.15000152587891</v>
       </c>
       <c r="D83" t="n">
-        <v>88.31999969482422</v>
+        <v>89.06999969482422</v>
       </c>
       <c r="E83" t="n">
-        <v>89.45999908447266</v>
+        <v>90.31999969482422</v>
       </c>
       <c r="F83" t="n">
-        <v>55579500</v>
+        <v>45221100</v>
       </c>
       <c r="G83" t="n">
         <v>0</v>
@@ -2601,22 +2601,22 @@
     </row>
     <row r="84">
       <c r="A84" s="1" t="n">
-        <v>46034</v>
+        <v>46036</v>
       </c>
       <c r="B84" t="n">
-        <v>89.69000244140625</v>
+        <v>91.23999786376953</v>
       </c>
       <c r="C84" t="n">
-        <v>90.33999633789062</v>
+        <v>91.58000183105469</v>
       </c>
       <c r="D84" t="n">
-        <v>89.33000183105469</v>
+        <v>87.94999694824219</v>
       </c>
       <c r="E84" t="n">
-        <v>89.41000366210938</v>
+        <v>88.55000305175781</v>
       </c>
       <c r="F84" t="n">
-        <v>36290600</v>
+        <v>49737700</v>
       </c>
       <c r="G84" t="n">
         <v>0</v>
@@ -2627,22 +2627,22 @@
     </row>
     <row r="85">
       <c r="A85" s="1" t="n">
-        <v>46035</v>
+        <v>46037</v>
       </c>
       <c r="B85" t="n">
-        <v>89.44000244140625</v>
+        <v>89.01999664306641</v>
       </c>
       <c r="C85" t="n">
-        <v>91.15000152587891</v>
+        <v>89.88999938964844</v>
       </c>
       <c r="D85" t="n">
-        <v>89.06999969482422</v>
+        <v>87.81999969482422</v>
       </c>
       <c r="E85" t="n">
-        <v>90.31999969482422</v>
+        <v>88.05000305175781</v>
       </c>
       <c r="F85" t="n">
-        <v>45221100</v>
+        <v>36945100</v>
       </c>
       <c r="G85" t="n">
         <v>0</v>
@@ -2653,22 +2653,22 @@
     </row>
     <row r="86">
       <c r="A86" s="1" t="n">
-        <v>46036</v>
+        <v>46038</v>
       </c>
       <c r="B86" t="n">
-        <v>91.23999786376953</v>
+        <v>88.33999633789062</v>
       </c>
       <c r="C86" t="n">
-        <v>91.58000183105469</v>
+        <v>88.51000213623047</v>
       </c>
       <c r="D86" t="n">
-        <v>87.94999694824219</v>
+        <v>87.77999877929688</v>
       </c>
       <c r="E86" t="n">
-        <v>88.55000305175781</v>
+        <v>88</v>
       </c>
       <c r="F86" t="n">
-        <v>49737700</v>
+        <v>48130500</v>
       </c>
       <c r="G86" t="n">
         <v>0</v>
@@ -2679,22 +2679,22 @@
     </row>
     <row r="87">
       <c r="A87" s="1" t="n">
-        <v>46037</v>
+        <v>46042</v>
       </c>
       <c r="B87" t="n">
-        <v>89.01999664306641</v>
+        <v>88.97000122070312</v>
       </c>
       <c r="C87" t="n">
-        <v>89.88999938964844</v>
+        <v>89.90000152587891</v>
       </c>
       <c r="D87" t="n">
-        <v>87.81999969482422</v>
+        <v>87.01999664306641</v>
       </c>
       <c r="E87" t="n">
-        <v>88.05000305175781</v>
+        <v>87.26000213623047</v>
       </c>
       <c r="F87" t="n">
-        <v>36945100</v>
+        <v>109729700</v>
       </c>
       <c r="G87" t="n">
         <v>0</v>
@@ -2705,22 +2705,22 @@
     </row>
     <row r="88">
       <c r="A88" s="1" t="n">
-        <v>46038</v>
+        <v>46043</v>
       </c>
       <c r="B88" t="n">
-        <v>88.33999633789062</v>
+        <v>82.51999664306641</v>
       </c>
       <c r="C88" t="n">
-        <v>88.51000213623047</v>
+        <v>86</v>
       </c>
       <c r="D88" t="n">
-        <v>87.77999877929688</v>
+        <v>81.93000030517578</v>
       </c>
       <c r="E88" t="n">
-        <v>88</v>
+        <v>85.36000061035156</v>
       </c>
       <c r="F88" t="n">
-        <v>48130500</v>
+        <v>127940700</v>
       </c>
       <c r="G88" t="n">
         <v>0</v>
@@ -2731,22 +2731,22 @@
     </row>
     <row r="89">
       <c r="A89" s="1" t="n">
-        <v>46042</v>
+        <v>46044</v>
       </c>
       <c r="B89" t="n">
-        <v>88.97000122070312</v>
+        <v>85.01999664306641</v>
       </c>
       <c r="C89" t="n">
-        <v>89.90000152587891</v>
+        <v>85.09999847412109</v>
       </c>
       <c r="D89" t="n">
-        <v>87.01999664306641</v>
+        <v>82.98000335693359</v>
       </c>
       <c r="E89" t="n">
-        <v>87.26000213623047</v>
+        <v>83.54000091552734</v>
       </c>
       <c r="F89" t="n">
-        <v>109729700</v>
+        <v>69113300</v>
       </c>
       <c r="G89" t="n">
         <v>0</v>
@@ -2757,22 +2757,22 @@
     </row>
     <row r="90">
       <c r="A90" s="1" t="n">
-        <v>46043</v>
+        <v>46045</v>
       </c>
       <c r="B90" t="n">
-        <v>82.51999664306641</v>
+        <v>83.43000030517578</v>
       </c>
       <c r="C90" t="n">
-        <v>86</v>
+        <v>86.30000305175781</v>
       </c>
       <c r="D90" t="n">
-        <v>81.93000030517578</v>
+        <v>83.27999877929688</v>
       </c>
       <c r="E90" t="n">
-        <v>85.36000061035156</v>
+        <v>86.12000274658203</v>
       </c>
       <c r="F90" t="n">
-        <v>127940700</v>
+        <v>64520400</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
@@ -2783,22 +2783,22 @@
     </row>
     <row r="91">
       <c r="A91" s="1" t="n">
-        <v>46044</v>
+        <v>46048</v>
       </c>
       <c r="B91" t="n">
-        <v>85.01999664306641</v>
+        <v>86.91999816894531</v>
       </c>
       <c r="C91" t="n">
-        <v>85.09999847412109</v>
+        <v>86.94000244140625</v>
       </c>
       <c r="D91" t="n">
-        <v>82.98000335693359</v>
+        <v>85.34999847412109</v>
       </c>
       <c r="E91" t="n">
-        <v>83.54000091552734</v>
+        <v>85.69999694824219</v>
       </c>
       <c r="F91" t="n">
-        <v>69113300</v>
+        <v>40941900</v>
       </c>
       <c r="G91" t="n">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="92">
       <c r="A92" s="1" t="n">
-        <v>46045</v>
+        <v>46049</v>
       </c>
       <c r="B92" t="n">
-        <v>83.43000030517578</v>
+        <v>85.27999877929688</v>
       </c>
       <c r="C92" t="n">
-        <v>86.30000305175781</v>
+        <v>85.59999847412109</v>
       </c>
       <c r="D92" t="n">
-        <v>83.27999877929688</v>
+        <v>83.87999725341797</v>
       </c>
       <c r="E92" t="n">
-        <v>86.12000274658203</v>
+        <v>85.58000183105469</v>
       </c>
       <c r="F92" t="n">
-        <v>64520400</v>
+        <v>37790800</v>
       </c>
       <c r="G92" t="n">
         <v>0</v>
@@ -2835,22 +2835,22 @@
     </row>
     <row r="93">
       <c r="A93" s="1" t="n">
-        <v>46048</v>
+        <v>46050</v>
       </c>
       <c r="B93" t="n">
-        <v>86.91999816894531</v>
+        <v>85.62999725341797</v>
       </c>
       <c r="C93" t="n">
-        <v>86.94000244140625</v>
+        <v>86.47000122070312</v>
       </c>
       <c r="D93" t="n">
-        <v>85.34999847412109</v>
+        <v>84.30000305175781</v>
       </c>
       <c r="E93" t="n">
-        <v>85.69999694824219</v>
+        <v>84.63999938964844</v>
       </c>
       <c r="F93" t="n">
-        <v>40941900</v>
+        <v>37762600</v>
       </c>
       <c r="G93" t="n">
         <v>0</v>
@@ -2861,22 +2861,22 @@
     </row>
     <row r="94">
       <c r="A94" s="1" t="n">
-        <v>46049</v>
+        <v>46051</v>
       </c>
       <c r="B94" t="n">
-        <v>85.27999877929688</v>
+        <v>84.30999755859375</v>
       </c>
       <c r="C94" t="n">
-        <v>85.59999847412109</v>
+        <v>84.37999725341797</v>
       </c>
       <c r="D94" t="n">
-        <v>83.87999725341797</v>
+        <v>82.34999847412109</v>
       </c>
       <c r="E94" t="n">
-        <v>85.58000183105469</v>
+        <v>83.16000366210938</v>
       </c>
       <c r="F94" t="n">
-        <v>37790800</v>
+        <v>42278100</v>
       </c>
       <c r="G94" t="n">
         <v>0</v>
@@ -2887,22 +2887,22 @@
     </row>
     <row r="95">
       <c r="A95" s="1" t="n">
-        <v>46050</v>
+        <v>46052</v>
       </c>
       <c r="B95" t="n">
-        <v>85.62999725341797</v>
+        <v>83.09999847412109</v>
       </c>
       <c r="C95" t="n">
-        <v>86.47000122070312</v>
+        <v>84.05999755859375</v>
       </c>
       <c r="D95" t="n">
-        <v>84.30000305175781</v>
+        <v>82.77999877929688</v>
       </c>
       <c r="E95" t="n">
-        <v>84.63999938964844</v>
+        <v>83.48999786376953</v>
       </c>
       <c r="F95" t="n">
-        <v>37762600</v>
+        <v>45755000</v>
       </c>
       <c r="G95" t="n">
         <v>0</v>
@@ -2913,22 +2913,22 @@
     </row>
     <row r="96">
       <c r="A96" s="1" t="n">
-        <v>46051</v>
+        <v>46055</v>
       </c>
       <c r="B96" t="n">
-        <v>84.30999755859375</v>
+        <v>83.52999877929688</v>
       </c>
       <c r="C96" t="n">
-        <v>84.37999725341797</v>
+        <v>85.26999664306641</v>
       </c>
       <c r="D96" t="n">
-        <v>82.34999847412109</v>
+        <v>82.72000122070312</v>
       </c>
       <c r="E96" t="n">
-        <v>83.16000366210938</v>
+        <v>82.76000213623047</v>
       </c>
       <c r="F96" t="n">
-        <v>42278100</v>
+        <v>41445300</v>
       </c>
       <c r="G96" t="n">
         <v>0</v>
@@ -2939,22 +2939,22 @@
     </row>
     <row r="97">
       <c r="A97" s="1" t="n">
-        <v>46052</v>
+        <v>46056</v>
       </c>
       <c r="B97" t="n">
-        <v>83.09999847412109</v>
+        <v>82.23000335693359</v>
       </c>
       <c r="C97" t="n">
-        <v>84.05999755859375</v>
+        <v>82.44999694824219</v>
       </c>
       <c r="D97" t="n">
-        <v>82.77999877929688</v>
+        <v>79.62000274658203</v>
       </c>
       <c r="E97" t="n">
-        <v>83.48999786376953</v>
+        <v>79.94000244140625</v>
       </c>
       <c r="F97" t="n">
-        <v>45755000</v>
+        <v>49789000</v>
       </c>
       <c r="G97" t="n">
         <v>0</v>
@@ -2965,22 +2965,22 @@
     </row>
     <row r="98">
       <c r="A98" s="1" t="n">
-        <v>46055</v>
+        <v>46057</v>
       </c>
       <c r="B98" t="n">
-        <v>83.52999877929688</v>
+        <v>79.98999786376953</v>
       </c>
       <c r="C98" t="n">
-        <v>85.26999664306641</v>
+        <v>81.44000244140625</v>
       </c>
       <c r="D98" t="n">
-        <v>82.72000122070312</v>
+        <v>79.23000335693359</v>
       </c>
       <c r="E98" t="n">
-        <v>82.76000213623047</v>
+        <v>80.16000366210938</v>
       </c>
       <c r="F98" t="n">
-        <v>41445300</v>
+        <v>48963200</v>
       </c>
       <c r="G98" t="n">
         <v>0</v>
@@ -2991,22 +2991,22 @@
     </row>
     <row r="99">
       <c r="A99" s="1" t="n">
-        <v>46056</v>
+        <v>46058</v>
       </c>
       <c r="B99" t="n">
-        <v>82.23000335693359</v>
+        <v>81.48999786376953</v>
       </c>
       <c r="C99" t="n">
-        <v>82.44999694824219</v>
+        <v>83.30000305175781</v>
       </c>
       <c r="D99" t="n">
-        <v>79.62000274658203</v>
+        <v>80.54000091552734</v>
       </c>
       <c r="E99" t="n">
-        <v>79.94000244140625</v>
+        <v>80.87000274658203</v>
       </c>
       <c r="F99" t="n">
-        <v>49789000</v>
+        <v>54805700</v>
       </c>
       <c r="G99" t="n">
         <v>0</v>
@@ -3017,22 +3017,22 @@
     </row>
     <row r="100">
       <c r="A100" s="1" t="n">
-        <v>46057</v>
+        <v>46059</v>
       </c>
       <c r="B100" t="n">
-        <v>79.98999786376953</v>
+        <v>81.01999664306641</v>
       </c>
       <c r="C100" t="n">
-        <v>81.44000244140625</v>
+        <v>82.48999786376953</v>
       </c>
       <c r="D100" t="n">
-        <v>79.23000335693359</v>
+        <v>80.65000152587891</v>
       </c>
       <c r="E100" t="n">
-        <v>80.16000366210938</v>
+        <v>82.19999694824219</v>
       </c>
       <c r="F100" t="n">
-        <v>48963200</v>
+        <v>46154100</v>
       </c>
       <c r="G100" t="n">
         <v>0</v>
@@ -3043,22 +3043,22 @@
     </row>
     <row r="101">
       <c r="A101" s="1" t="n">
-        <v>46058</v>
+        <v>46062</v>
       </c>
       <c r="B101" t="n">
-        <v>81.48999786376953</v>
+        <v>82.18000030517578</v>
       </c>
       <c r="C101" t="n">
-        <v>83.30000305175781</v>
+        <v>82.20999908447266</v>
       </c>
       <c r="D101" t="n">
-        <v>80.54000091552734</v>
+        <v>79.87000274658203</v>
       </c>
       <c r="E101" t="n">
-        <v>80.87000274658203</v>
+        <v>81.47000122070312</v>
       </c>
       <c r="F101" t="n">
-        <v>54805700</v>
+        <v>42200200</v>
       </c>
       <c r="G101" t="n">
         <v>0</v>
@@ -3069,22 +3069,22 @@
     </row>
     <row r="102">
       <c r="A102" s="1" t="n">
-        <v>46059</v>
+        <v>46063</v>
       </c>
       <c r="B102" t="n">
-        <v>81.01999664306641</v>
+        <v>82.72000122070312</v>
       </c>
       <c r="C102" t="n">
-        <v>82.48999786376953</v>
+        <v>84.66000366210938</v>
       </c>
       <c r="D102" t="n">
-        <v>80.65000152587891</v>
+        <v>82.08999633789062</v>
       </c>
       <c r="E102" t="n">
-        <v>82.19999694824219</v>
+        <v>82.20999908447266</v>
       </c>
       <c r="F102" t="n">
-        <v>46154100</v>
+        <v>43595800</v>
       </c>
       <c r="G102" t="n">
         <v>0</v>
@@ -3095,22 +3095,22 @@
     </row>
     <row r="103">
       <c r="A103" s="1" t="n">
-        <v>46062</v>
+        <v>46064</v>
       </c>
       <c r="B103" t="n">
-        <v>82.18000030517578</v>
+        <v>81.95999908447266</v>
       </c>
       <c r="C103" t="n">
-        <v>82.20999908447266</v>
+        <v>82.48000335693359</v>
       </c>
       <c r="D103" t="n">
-        <v>79.87000274658203</v>
+        <v>79.44999694824219</v>
       </c>
       <c r="E103" t="n">
-        <v>81.47000122070312</v>
+        <v>79.62000274658203</v>
       </c>
       <c r="F103" t="n">
-        <v>42200200</v>
+        <v>40840300</v>
       </c>
       <c r="G103" t="n">
         <v>0</v>
@@ -3121,22 +3121,22 @@
     </row>
     <row r="104">
       <c r="A104" s="1" t="n">
-        <v>46063</v>
+        <v>46065</v>
       </c>
       <c r="B104" t="n">
-        <v>82.72000122070312</v>
+        <v>79.11000061035156</v>
       </c>
       <c r="C104" t="n">
-        <v>84.66000366210938</v>
+        <v>79.15000152587891</v>
       </c>
       <c r="D104" t="n">
-        <v>82.08999633789062</v>
+        <v>75.23000335693359</v>
       </c>
       <c r="E104" t="n">
-        <v>82.20999908447266</v>
+        <v>75.86000061035156</v>
       </c>
       <c r="F104" t="n">
-        <v>43595800</v>
+        <v>73516100</v>
       </c>
       <c r="G104" t="n">
         <v>0</v>
@@ -3147,22 +3147,22 @@
     </row>
     <row r="105">
       <c r="A105" s="1" t="n">
-        <v>46064</v>
+        <v>46066</v>
       </c>
       <c r="B105" t="n">
-        <v>81.95999908447266</v>
+        <v>76.13999938964844</v>
       </c>
       <c r="C105" t="n">
-        <v>82.48000335693359</v>
+        <v>77.18000030517578</v>
       </c>
       <c r="D105" t="n">
-        <v>79.44999694824219</v>
+        <v>75.52999877929688</v>
       </c>
       <c r="E105" t="n">
-        <v>79.62000274658203</v>
+        <v>76.87000274658203</v>
       </c>
       <c r="F105" t="n">
-        <v>40840300</v>
+        <v>42292100</v>
       </c>
       <c r="G105" t="n">
         <v>0</v>
@@ -3173,22 +3173,22 @@
     </row>
     <row r="106">
       <c r="A106" s="1" t="n">
-        <v>46065</v>
+        <v>46070</v>
       </c>
       <c r="B106" t="n">
-        <v>79.11000061035156</v>
+        <v>76.91999816894531</v>
       </c>
       <c r="C106" t="n">
-        <v>79.15000152587891</v>
+        <v>77.87000274658203</v>
       </c>
       <c r="D106" t="n">
-        <v>75.23000335693359</v>
+        <v>75.30000305175781</v>
       </c>
       <c r="E106" t="n">
-        <v>75.86000061035156</v>
+        <v>77</v>
       </c>
       <c r="F106" t="n">
-        <v>73516100</v>
+        <v>35961500</v>
       </c>
       <c r="G106" t="n">
         <v>0</v>
@@ -3199,22 +3199,22 @@
     </row>
     <row r="107">
       <c r="A107" s="1" t="n">
-        <v>46066</v>
+        <v>46071</v>
       </c>
       <c r="B107" t="n">
-        <v>76.13999938964844</v>
+        <v>77.31999969482422</v>
       </c>
       <c r="C107" t="n">
-        <v>77.18000030517578</v>
+        <v>78.31999969482422</v>
       </c>
       <c r="D107" t="n">
-        <v>75.52999877929688</v>
+        <v>76.27999877929688</v>
       </c>
       <c r="E107" t="n">
-        <v>76.87000274658203</v>
+        <v>77.98999786376953</v>
       </c>
       <c r="F107" t="n">
-        <v>42292100</v>
+        <v>29883100</v>
       </c>
       <c r="G107" t="n">
         <v>0</v>
@@ -3225,22 +3225,22 @@
     </row>
     <row r="108">
       <c r="A108" s="1" t="n">
-        <v>46070</v>
+        <v>46072</v>
       </c>
       <c r="B108" t="n">
-        <v>76.91999816894531</v>
+        <v>77.75</v>
       </c>
       <c r="C108" t="n">
-        <v>77.87000274658203</v>
+        <v>78.69999694824219</v>
       </c>
       <c r="D108" t="n">
-        <v>75.30000305175781</v>
+        <v>76.58999633789062</v>
       </c>
       <c r="E108" t="n">
         <v>77</v>
       </c>
       <c r="F108" t="n">
-        <v>35961500</v>
+        <v>30139200</v>
       </c>
       <c r="G108" t="n">
         <v>0</v>
@@ -3251,22 +3251,22 @@
     </row>
     <row r="109">
       <c r="A109" s="1" t="n">
-        <v>46071</v>
+        <v>46073</v>
       </c>
       <c r="B109" t="n">
-        <v>77.31999969482422</v>
+        <v>76.61000061035156</v>
       </c>
       <c r="C109" t="n">
-        <v>78.31999969482422</v>
+        <v>78.84999847412109</v>
       </c>
       <c r="D109" t="n">
-        <v>76.27999877929688</v>
+        <v>76.40000152587891</v>
       </c>
       <c r="E109" t="n">
-        <v>77.98999786376953</v>
+        <v>78.66999816894531</v>
       </c>
       <c r="F109" t="n">
-        <v>29883100</v>
+        <v>32411300</v>
       </c>
       <c r="G109" t="n">
         <v>0</v>
@@ -3277,22 +3277,22 @@
     </row>
     <row r="110">
       <c r="A110" s="1" t="n">
-        <v>46072</v>
+        <v>46076</v>
       </c>
       <c r="B110" t="n">
-        <v>77.75</v>
+        <v>77.79000091552734</v>
       </c>
       <c r="C110" t="n">
-        <v>78.69999694824219</v>
+        <v>77.83000183105469</v>
       </c>
       <c r="D110" t="n">
-        <v>76.58999633789062</v>
+        <v>75.01000213623047</v>
       </c>
       <c r="E110" t="n">
-        <v>77</v>
+        <v>76.01999664306641</v>
       </c>
       <c r="F110" t="n">
-        <v>30139200</v>
+        <v>38363000</v>
       </c>
       <c r="G110" t="n">
         <v>0</v>
@@ -3303,22 +3303,22 @@
     </row>
     <row r="111">
       <c r="A111" s="1" t="n">
-        <v>46073</v>
+        <v>46077</v>
       </c>
       <c r="B111" t="n">
-        <v>76.61000061035156</v>
+        <v>75.73000335693359</v>
       </c>
       <c r="C111" t="n">
-        <v>78.84999847412109</v>
+        <v>78.12000274658203</v>
       </c>
       <c r="D111" t="n">
-        <v>76.40000152587891</v>
+        <v>75.20999908447266</v>
       </c>
       <c r="E111" t="n">
-        <v>78.66999816894531</v>
+        <v>78.04000091552734</v>
       </c>
       <c r="F111" t="n">
-        <v>32411300</v>
+        <v>33079100</v>
       </c>
       <c r="G111" t="n">
         <v>0</v>
@@ -3329,22 +3329,22 @@
     </row>
     <row r="112">
       <c r="A112" s="1" t="n">
-        <v>46076</v>
+        <v>46078</v>
       </c>
       <c r="B112" t="n">
-        <v>77.79000091552734</v>
+        <v>79.43000030517578</v>
       </c>
       <c r="C112" t="n">
-        <v>77.83000183105469</v>
+        <v>83.12000274658203</v>
       </c>
       <c r="D112" t="n">
-        <v>75.01000213623047</v>
+        <v>79.25</v>
       </c>
       <c r="E112" t="n">
-        <v>76.01999664306641</v>
+        <v>82.69999694824219</v>
       </c>
       <c r="F112" t="n">
-        <v>38363000</v>
+        <v>69319300</v>
       </c>
       <c r="G112" t="n">
         <v>0</v>
@@ -3355,22 +3355,22 @@
     </row>
     <row r="113">
       <c r="A113" s="1" t="n">
-        <v>46077</v>
+        <v>46079</v>
       </c>
       <c r="B113" t="n">
-        <v>75.73000335693359</v>
+        <v>83.19999694824219</v>
       </c>
       <c r="C113" t="n">
-        <v>78.12000274658203</v>
+        <v>86.5</v>
       </c>
       <c r="D113" t="n">
-        <v>75.20999908447266</v>
+        <v>82.80000305175781</v>
       </c>
       <c r="E113" t="n">
-        <v>78.04000091552734</v>
+        <v>84.58999633789062</v>
       </c>
       <c r="F113" t="n">
-        <v>33079100</v>
+        <v>85642500</v>
       </c>
       <c r="G113" t="n">
         <v>0</v>
@@ -3381,22 +3381,22 @@
     </row>
     <row r="114">
       <c r="A114" s="1" t="n">
-        <v>46078</v>
+        <v>46080</v>
       </c>
       <c r="B114" t="n">
-        <v>79.43000030517578</v>
+        <v>94.30000305175781</v>
       </c>
       <c r="C114" t="n">
-        <v>83.12000274658203</v>
+        <v>96.75</v>
       </c>
       <c r="D114" t="n">
-        <v>79.25</v>
+        <v>90.58000183105469</v>
       </c>
       <c r="E114" t="n">
-        <v>82.69999694824219</v>
+        <v>96.23999786376953</v>
       </c>
       <c r="F114" t="n">
-        <v>69319300</v>
+        <v>200767000</v>
       </c>
       <c r="G114" t="n">
         <v>0</v>
@@ -3407,22 +3407,22 @@
     </row>
     <row r="115">
       <c r="A115" s="1" t="n">
-        <v>46079</v>
+        <v>46083</v>
       </c>
       <c r="B115" t="n">
-        <v>83.19999694824219</v>
+        <v>95.26000213623047</v>
       </c>
       <c r="C115" t="n">
-        <v>86.5</v>
+        <v>98.06999969482422</v>
       </c>
       <c r="D115" t="n">
-        <v>82.80000305175781</v>
+        <v>95.19999694824219</v>
       </c>
       <c r="E115" t="n">
-        <v>84.58999633789062</v>
+        <v>97.08999633789062</v>
       </c>
       <c r="F115" t="n">
-        <v>85642500</v>
+        <v>79915400</v>
       </c>
       <c r="G115" t="n">
         <v>0</v>
@@ -3433,22 +3433,22 @@
     </row>
     <row r="116">
       <c r="A116" s="1" t="n">
-        <v>46080</v>
+        <v>46084</v>
       </c>
       <c r="B116" t="n">
-        <v>94.30000305175781</v>
+        <v>96.01000213623047</v>
       </c>
       <c r="C116" t="n">
-        <v>96.75</v>
+        <v>98.45999908447266</v>
       </c>
       <c r="D116" t="n">
-        <v>90.58000183105469</v>
+        <v>95.33000183105469</v>
       </c>
       <c r="E116" t="n">
-        <v>96.23999786376953</v>
+        <v>97.69999694824219</v>
       </c>
       <c r="F116" t="n">
-        <v>200767000</v>
+        <v>59149000</v>
       </c>
       <c r="G116" t="n">
         <v>0</v>
@@ -3459,22 +3459,22 @@
     </row>
     <row r="117">
       <c r="A117" s="1" t="n">
-        <v>46083</v>
+        <v>46085</v>
       </c>
       <c r="B117" t="n">
-        <v>95.26000213623047</v>
+        <v>97.11000061035156</v>
       </c>
       <c r="C117" t="n">
-        <v>98.06999969482422</v>
+        <v>99.75</v>
       </c>
       <c r="D117" t="n">
-        <v>95.19999694824219</v>
+        <v>96.98999786376953</v>
       </c>
       <c r="E117" t="n">
-        <v>97.08999633789062</v>
+        <v>98.66000366210938</v>
       </c>
       <c r="F117" t="n">
-        <v>79915400</v>
+        <v>52604300</v>
       </c>
       <c r="G117" t="n">
         <v>0</v>
@@ -3485,22 +3485,22 @@
     </row>
     <row r="118">
       <c r="A118" s="1" t="n">
-        <v>46084</v>
+        <v>46086</v>
       </c>
       <c r="B118" t="n">
-        <v>96.01000213623047</v>
+        <v>98.5</v>
       </c>
       <c r="C118" t="n">
-        <v>98.45999908447266</v>
+        <v>100.1900024414062</v>
       </c>
       <c r="D118" t="n">
-        <v>95.33000183105469</v>
+        <v>98.09999847412109</v>
       </c>
       <c r="E118" t="n">
-        <v>97.69999694824219</v>
+        <v>99.16999816894531</v>
       </c>
       <c r="F118" t="n">
-        <v>59149000</v>
+        <v>53403000</v>
       </c>
       <c r="G118" t="n">
         <v>0</v>
@@ -3511,22 +3511,22 @@
     </row>
     <row r="119">
       <c r="A119" s="1" t="n">
-        <v>46085</v>
+        <v>46087</v>
       </c>
       <c r="B119" t="n">
-        <v>97.11000061035156</v>
+        <v>99.33000183105469</v>
       </c>
       <c r="C119" t="n">
-        <v>99.75</v>
+        <v>99.87999725341797</v>
       </c>
       <c r="D119" t="n">
-        <v>96.98999786376953</v>
+        <v>97.40000152587891</v>
       </c>
       <c r="E119" t="n">
-        <v>98.66000366210938</v>
+        <v>99.01999664306641</v>
       </c>
       <c r="F119" t="n">
-        <v>52604300</v>
+        <v>41196300</v>
       </c>
       <c r="G119" t="n">
         <v>0</v>
@@ -3537,22 +3537,22 @@
     </row>
     <row r="120">
       <c r="A120" s="1" t="n">
-        <v>46086</v>
+        <v>46090</v>
       </c>
       <c r="B120" t="n">
-        <v>98.5</v>
+        <v>97.69999694824219</v>
       </c>
       <c r="C120" t="n">
-        <v>100.1900024414062</v>
+        <v>98.94000244140625</v>
       </c>
       <c r="D120" t="n">
-        <v>98.09999847412109</v>
+        <v>96.58000183105469</v>
       </c>
       <c r="E120" t="n">
-        <v>99.16999816894531</v>
+        <v>98.31999969482422</v>
       </c>
       <c r="F120" t="n">
-        <v>53403000</v>
+        <v>48589000</v>
       </c>
       <c r="G120" t="n">
         <v>0</v>
@@ -3563,22 +3563,22 @@
     </row>
     <row r="121">
       <c r="A121" s="1" t="n">
-        <v>46087</v>
+        <v>46091</v>
       </c>
       <c r="B121" t="n">
-        <v>99.33000183105469</v>
+        <v>97.80999755859375</v>
       </c>
       <c r="C121" t="n">
-        <v>99.87999725341797</v>
+        <v>98.48999786376953</v>
       </c>
       <c r="D121" t="n">
-        <v>97.40000152587891</v>
+        <v>96.29000091552734</v>
       </c>
       <c r="E121" t="n">
-        <v>99.01999664306641</v>
+        <v>96.94000244140625</v>
       </c>
       <c r="F121" t="n">
-        <v>41196300</v>
+        <v>41027200</v>
       </c>
       <c r="G121" t="n">
         <v>0</v>
@@ -3589,22 +3589,22 @@
     </row>
     <row r="122">
       <c r="A122" s="1" t="n">
-        <v>46090</v>
+        <v>46092</v>
       </c>
       <c r="B122" t="n">
-        <v>97.69999694824219</v>
+        <v>97.41000366210938</v>
       </c>
       <c r="C122" t="n">
-        <v>98.94000244140625</v>
+        <v>98</v>
       </c>
       <c r="D122" t="n">
-        <v>96.58000183105469</v>
+        <v>94.69000244140625</v>
       </c>
       <c r="E122" t="n">
-        <v>98.31999969482422</v>
+        <v>94.88999938964844</v>
       </c>
       <c r="F122" t="n">
-        <v>48589000</v>
+        <v>33962900</v>
       </c>
       <c r="G122" t="n">
         <v>0</v>
@@ -3615,22 +3615,22 @@
     </row>
     <row r="123">
       <c r="A123" s="1" t="n">
-        <v>46091</v>
+        <v>46093</v>
       </c>
       <c r="B123" t="n">
-        <v>97.80999755859375</v>
+        <v>94.86000061035156</v>
       </c>
       <c r="C123" t="n">
-        <v>98.48999786376953</v>
+        <v>95.40000152587891</v>
       </c>
       <c r="D123" t="n">
-        <v>96.29000091552734</v>
+        <v>93.87000274658203</v>
       </c>
       <c r="E123" t="n">
-        <v>96.94000244140625</v>
+        <v>94.30999755859375</v>
       </c>
       <c r="F123" t="n">
-        <v>41027200</v>
+        <v>34206900</v>
       </c>
       <c r="G123" t="n">
         <v>0</v>
@@ -3641,22 +3641,22 @@
     </row>
     <row r="124">
       <c r="A124" s="1" t="n">
-        <v>46092</v>
+        <v>46094</v>
       </c>
       <c r="B124" t="n">
-        <v>97.41000366210938</v>
+        <v>94.63999938964844</v>
       </c>
       <c r="C124" t="n">
-        <v>98</v>
+        <v>95.68000030517578</v>
       </c>
       <c r="D124" t="n">
-        <v>94.69000244140625</v>
+        <v>94.23999786376953</v>
       </c>
       <c r="E124" t="n">
-        <v>94.88999938964844</v>
+        <v>95.30999755859375</v>
       </c>
       <c r="F124" t="n">
-        <v>33962900</v>
+        <v>29876700</v>
       </c>
       <c r="G124" t="n">
         <v>0</v>
@@ -3667,22 +3667,22 @@
     </row>
     <row r="125">
       <c r="A125" s="1" t="n">
-        <v>46093</v>
+        <v>46097</v>
       </c>
       <c r="B125" t="n">
-        <v>94.86000061035156</v>
+        <v>95.58000183105469</v>
       </c>
       <c r="C125" t="n">
-        <v>95.40000152587891</v>
+        <v>96.09999847412109</v>
       </c>
       <c r="D125" t="n">
-        <v>93.87000274658203</v>
+        <v>94.36000061035156</v>
       </c>
       <c r="E125" t="n">
-        <v>94.30999755859375</v>
+        <v>95.19999694824219</v>
       </c>
       <c r="F125" t="n">
-        <v>34206900</v>
+        <v>34931800</v>
       </c>
       <c r="G125" t="n">
         <v>0</v>
@@ -3693,22 +3693,22 @@
     </row>
     <row r="126">
       <c r="A126" s="1" t="n">
-        <v>46094</v>
+        <v>46098</v>
       </c>
       <c r="B126" t="n">
-        <v>94.63999938964844</v>
+        <v>95.30000305175781</v>
       </c>
       <c r="C126" t="n">
-        <v>95.68000030517578</v>
+        <v>96.33999633789062</v>
       </c>
       <c r="D126" t="n">
-        <v>94.23999786376953</v>
+        <v>94.01000213623047</v>
       </c>
       <c r="E126" t="n">
-        <v>95.30999755859375</v>
+        <v>94.36000061035156</v>
       </c>
       <c r="F126" t="n">
-        <v>29876700</v>
+        <v>26434500</v>
       </c>
       <c r="G126" t="n">
         <v>0</v>
@@ -3719,22 +3719,22 @@
     </row>
     <row r="127">
       <c r="A127" s="1" t="n">
-        <v>46097</v>
+        <v>46099</v>
       </c>
       <c r="B127" t="n">
-        <v>95.58000183105469</v>
+        <v>94.44999694824219</v>
       </c>
       <c r="C127" t="n">
-        <v>96.09999847412109</v>
+        <v>95.33999633789062</v>
       </c>
       <c r="D127" t="n">
-        <v>94.36000061035156</v>
+        <v>93.61000061035156</v>
       </c>
       <c r="E127" t="n">
-        <v>95.19999694824219</v>
+        <v>94.69999694824219</v>
       </c>
       <c r="F127" t="n">
-        <v>34931800</v>
+        <v>27878300</v>
       </c>
       <c r="G127" t="n">
         <v>0</v>
@@ -3745,22 +3745,22 @@
     </row>
     <row r="128">
       <c r="A128" s="1" t="n">
-        <v>46098</v>
+        <v>46100</v>
       </c>
       <c r="B128" t="n">
-        <v>95.30000305175781</v>
+        <v>94.30999755859375</v>
       </c>
       <c r="C128" t="n">
-        <v>96.33999633789062</v>
+        <v>95.75</v>
       </c>
       <c r="D128" t="n">
-        <v>94.01000213623047</v>
+        <v>90.77999877929688</v>
       </c>
       <c r="E128" t="n">
-        <v>94.36000061035156</v>
+        <v>91.73999786376953</v>
       </c>
       <c r="F128" t="n">
-        <v>26434500</v>
+        <v>40169300</v>
       </c>
       <c r="G128" t="n">
         <v>0</v>
@@ -3771,22 +3771,22 @@
     </row>
     <row r="129">
       <c r="A129" s="1" t="n">
-        <v>46099</v>
+        <v>46101</v>
       </c>
       <c r="B129" t="n">
-        <v>94.44999694824219</v>
+        <v>91.30999755859375</v>
       </c>
       <c r="C129" t="n">
-        <v>95.33999633789062</v>
+        <v>91.87999725341797</v>
       </c>
       <c r="D129" t="n">
-        <v>93.61000061035156</v>
+        <v>90.69000244140625</v>
       </c>
       <c r="E129" t="n">
-        <v>94.69999694824219</v>
+        <v>91.81999969482422</v>
       </c>
       <c r="F129" t="n">
-        <v>27878300</v>
+        <v>61678000</v>
       </c>
       <c r="G129" t="n">
         <v>0</v>
@@ -3797,22 +3797,22 @@
     </row>
     <row r="130">
       <c r="A130" s="1" t="n">
-        <v>46100</v>
+        <v>46104</v>
       </c>
       <c r="B130" t="n">
-        <v>94.30999755859375</v>
+        <v>92.04000091552734</v>
       </c>
       <c r="C130" t="n">
-        <v>95.75</v>
+        <v>93.98000335693359</v>
       </c>
       <c r="D130" t="n">
-        <v>90.77999877929688</v>
+        <v>91.86000061035156</v>
       </c>
       <c r="E130" t="n">
-        <v>91.73999786376953</v>
+        <v>93.37999725341797</v>
       </c>
       <c r="F130" t="n">
-        <v>40169300</v>
+        <v>34315900</v>
       </c>
       <c r="G130" t="n">
         <v>0</v>
@@ -3823,22 +3823,22 @@
     </row>
     <row r="131">
       <c r="A131" s="1" t="n">
-        <v>46101</v>
+        <v>46105</v>
       </c>
       <c r="B131" t="n">
-        <v>91.30999755859375</v>
+        <v>92.79000091552734</v>
       </c>
       <c r="C131" t="n">
-        <v>91.87999725341797</v>
+        <v>93.73999786376953</v>
       </c>
       <c r="D131" t="n">
-        <v>90.69000244140625</v>
+        <v>90.81999969482422</v>
       </c>
       <c r="E131" t="n">
-        <v>91.81999969482422</v>
+        <v>90.91999816894531</v>
       </c>
       <c r="F131" t="n">
-        <v>61678000</v>
+        <v>28938000</v>
       </c>
       <c r="G131" t="n">
         <v>0</v>
@@ -3849,22 +3849,22 @@
     </row>
     <row r="132">
       <c r="A132" s="1" t="n">
-        <v>46104</v>
+        <v>46106</v>
       </c>
       <c r="B132" t="n">
-        <v>92.04000091552734</v>
+        <v>91.70999908447266</v>
       </c>
       <c r="C132" t="n">
-        <v>93.98000335693359</v>
+        <v>92.51999664306641</v>
       </c>
       <c r="D132" t="n">
-        <v>91.86000061035156</v>
+        <v>91.23999786376953</v>
       </c>
       <c r="E132" t="n">
-        <v>93.37999725341797</v>
+        <v>92.27999877929688</v>
       </c>
       <c r="F132" t="n">
-        <v>34315900</v>
+        <v>29545600</v>
       </c>
       <c r="G132" t="n">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="133">
       <c r="A133" s="1" t="n">
-        <v>46105</v>
+        <v>46107</v>
       </c>
       <c r="B133" t="n">
-        <v>92.79000091552734</v>
+        <v>91.51999664306641</v>
       </c>
       <c r="C133" t="n">
-        <v>93.73999786376953</v>
+        <v>95.86000061035156</v>
       </c>
       <c r="D133" t="n">
-        <v>90.81999969482422</v>
+        <v>91.01000213623047</v>
       </c>
       <c r="E133" t="n">
-        <v>90.91999816894531</v>
+        <v>93.31999969482422</v>
       </c>
       <c r="F133" t="n">
-        <v>28938000</v>
+        <v>59522000</v>
       </c>
       <c r="G133" t="n">
         <v>0</v>
@@ -3901,22 +3901,22 @@
     </row>
     <row r="134">
       <c r="A134" s="1" t="n">
-        <v>46106</v>
+        <v>46108</v>
       </c>
       <c r="B134" t="n">
-        <v>91.70999908447266</v>
+        <v>94.56999969482422</v>
       </c>
       <c r="C134" t="n">
-        <v>92.51999664306641</v>
+        <v>95.58000183105469</v>
       </c>
       <c r="D134" t="n">
-        <v>91.23999786376953</v>
+        <v>92.73999786376953</v>
       </c>
       <c r="E134" t="n">
-        <v>92.27999877929688</v>
+        <v>93.43000030517578</v>
       </c>
       <c r="F134" t="n">
-        <v>29545600</v>
+        <v>44590700</v>
       </c>
       <c r="G134" t="n">
         <v>0</v>
@@ -3927,22 +3927,22 @@
     </row>
     <row r="135">
       <c r="A135" s="1" t="n">
-        <v>46107</v>
+        <v>46111</v>
       </c>
       <c r="B135" t="n">
-        <v>91.51999664306641</v>
+        <v>92.75</v>
       </c>
       <c r="C135" t="n">
-        <v>95.86000061035156</v>
+        <v>94.48999786376953</v>
       </c>
       <c r="D135" t="n">
-        <v>91.01000213623047</v>
+        <v>92.22000122070312</v>
       </c>
       <c r="E135" t="n">
-        <v>93.31999969482422</v>
+        <v>92.97000122070312</v>
       </c>
       <c r="F135" t="n">
-        <v>59522000</v>
+        <v>32375100</v>
       </c>
       <c r="G135" t="n">
         <v>0</v>
@@ -3953,22 +3953,22 @@
     </row>
     <row r="136">
       <c r="A136" s="1" t="n">
-        <v>46108</v>
+        <v>46112</v>
       </c>
       <c r="B136" t="n">
-        <v>94.56999969482422</v>
+        <v>93.02999877929688</v>
       </c>
       <c r="C136" t="n">
-        <v>95.58000183105469</v>
+        <v>96.26000213623047</v>
       </c>
       <c r="D136" t="n">
-        <v>92.73999786376953</v>
+        <v>93.02999877929688</v>
       </c>
       <c r="E136" t="n">
-        <v>93.43000030517578</v>
+        <v>96.15000152587891</v>
       </c>
       <c r="F136" t="n">
-        <v>44590700</v>
+        <v>54270000</v>
       </c>
       <c r="G136" t="n">
         <v>0</v>
@@ -3979,22 +3979,22 @@
     </row>
     <row r="137">
       <c r="A137" s="1" t="n">
-        <v>46111</v>
+        <v>46113</v>
       </c>
       <c r="B137" t="n">
-        <v>92.75</v>
+        <v>96.47000122070312</v>
       </c>
       <c r="C137" t="n">
-        <v>94.48999786376953</v>
+        <v>97.19999694824219</v>
       </c>
       <c r="D137" t="n">
-        <v>92.22000122070312</v>
+        <v>94.26000213623047</v>
       </c>
       <c r="E137" t="n">
-        <v>92.97000122070312</v>
+        <v>95.55000305175781</v>
       </c>
       <c r="F137" t="n">
-        <v>32375100</v>
+        <v>30439300</v>
       </c>
       <c r="G137" t="n">
         <v>0</v>
@@ -4005,22 +4005,22 @@
     </row>
     <row r="138">
       <c r="A138" s="1" t="n">
-        <v>46112</v>
+        <v>46114</v>
       </c>
       <c r="B138" t="n">
-        <v>93.02999877929688</v>
+        <v>95.26999664306641</v>
       </c>
       <c r="C138" t="n">
-        <v>96.26000213623047</v>
+        <v>98.70999908447266</v>
       </c>
       <c r="D138" t="n">
-        <v>93.02999877929688</v>
+        <v>95.16999816894531</v>
       </c>
       <c r="E138" t="n">
-        <v>96.15000152587891</v>
+        <v>98.66000366210938</v>
       </c>
       <c r="F138" t="n">
-        <v>54270000</v>
+        <v>37068000</v>
       </c>
       <c r="G138" t="n">
         <v>0</v>
@@ -4031,22 +4031,22 @@
     </row>
     <row r="139">
       <c r="A139" s="1" t="n">
-        <v>46113</v>
+        <v>46118</v>
       </c>
       <c r="B139" t="n">
-        <v>96.47000122070312</v>
+        <v>100.9599990844727</v>
       </c>
       <c r="C139" t="n">
-        <v>97.19999694824219</v>
+        <v>102.6900024414062</v>
       </c>
       <c r="D139" t="n">
-        <v>94.26000213623047</v>
+        <v>97.97000122070312</v>
       </c>
       <c r="E139" t="n">
-        <v>95.55000305175781</v>
+        <v>98.93000030517578</v>
       </c>
       <c r="F139" t="n">
-        <v>30439300</v>
+        <v>37029300</v>
       </c>
       <c r="G139" t="n">
         <v>0</v>
@@ -4057,22 +4057,22 @@
     </row>
     <row r="140">
       <c r="A140" s="1" t="n">
-        <v>46114</v>
+        <v>46119</v>
       </c>
       <c r="B140" t="n">
-        <v>95.26999664306641</v>
+        <v>98.55000305175781</v>
       </c>
       <c r="C140" t="n">
-        <v>98.70999908447266</v>
+        <v>99.87999725341797</v>
       </c>
       <c r="D140" t="n">
-        <v>95.16999816894531</v>
+        <v>98.25</v>
       </c>
       <c r="E140" t="n">
-        <v>98.66000366210938</v>
+        <v>98.81999969482422</v>
       </c>
       <c r="F140" t="n">
-        <v>37068000</v>
+        <v>25016700</v>
       </c>
       <c r="G140" t="n">
         <v>0</v>
@@ -4083,22 +4083,22 @@
     </row>
     <row r="141">
       <c r="A141" s="1" t="n">
-        <v>46118</v>
+        <v>46120</v>
       </c>
       <c r="B141" t="n">
-        <v>100.9599990844727</v>
+        <v>100.3199996948242</v>
       </c>
       <c r="C141" t="n">
-        <v>102.6900024414062</v>
+        <v>100.4000015258789</v>
       </c>
       <c r="D141" t="n">
-        <v>97.97000122070312</v>
+        <v>97.44000244140625</v>
       </c>
       <c r="E141" t="n">
-        <v>98.93000030517578</v>
+        <v>99.38999938964844</v>
       </c>
       <c r="F141" t="n">
-        <v>37029300</v>
+        <v>30957600</v>
       </c>
       <c r="G141" t="n">
         <v>0</v>
@@ -4109,22 +4109,22 @@
     </row>
     <row r="142">
       <c r="A142" s="1" t="n">
-        <v>46119</v>
+        <v>46121</v>
       </c>
       <c r="B142" t="n">
-        <v>98.55000305175781</v>
+        <v>99.62999725341797</v>
       </c>
       <c r="C142" t="n">
-        <v>99.87999725341797</v>
+        <v>102.3399963378906</v>
       </c>
       <c r="D142" t="n">
-        <v>98.25</v>
+        <v>99.08000183105469</v>
       </c>
       <c r="E142" t="n">
-        <v>98.81999969482422</v>
+        <v>102.0500030517578</v>
       </c>
       <c r="F142" t="n">
-        <v>25016700</v>
+        <v>35087800</v>
       </c>
       <c r="G142" t="n">
         <v>0</v>
@@ -4135,22 +4135,22 @@
     </row>
     <row r="143">
       <c r="A143" s="1" t="n">
-        <v>46120</v>
+        <v>46122</v>
       </c>
       <c r="B143" t="n">
-        <v>100.3199996948242</v>
+        <v>102.4700012207031</v>
       </c>
       <c r="C143" t="n">
-        <v>100.4000015258789</v>
+        <v>103.0800018310547</v>
       </c>
       <c r="D143" t="n">
-        <v>97.44000244140625</v>
+        <v>101.4599990844727</v>
       </c>
       <c r="E143" t="n">
-        <v>99.38999938964844</v>
+        <v>103.0100021362305</v>
       </c>
       <c r="F143" t="n">
-        <v>30957600</v>
+        <v>25769900</v>
       </c>
       <c r="G143" t="n">
         <v>0</v>
@@ -4161,22 +4161,22 @@
     </row>
     <row r="144">
       <c r="A144" s="1" t="n">
-        <v>46121</v>
+        <v>46125</v>
       </c>
       <c r="B144" t="n">
-        <v>99.62999725341797</v>
+        <v>103.0299987792969</v>
       </c>
       <c r="C144" t="n">
-        <v>102.3399963378906</v>
+        <v>103.6699981689453</v>
       </c>
       <c r="D144" t="n">
-        <v>99.08000183105469</v>
+        <v>102.0599975585938</v>
       </c>
       <c r="E144" t="n">
-        <v>102.0500030517578</v>
+        <v>103.1600036621094</v>
       </c>
       <c r="F144" t="n">
-        <v>35087800</v>
+        <v>26042800</v>
       </c>
       <c r="G144" t="n">
         <v>0</v>
@@ -4187,22 +4187,22 @@
     </row>
     <row r="145">
       <c r="A145" s="1" t="n">
-        <v>46122</v>
+        <v>46126</v>
       </c>
       <c r="B145" t="n">
-        <v>102.4700012207031</v>
+        <v>103.120002746582</v>
       </c>
       <c r="C145" t="n">
-        <v>103.0800018310547</v>
+        <v>106.5699996948242</v>
       </c>
       <c r="D145" t="n">
-        <v>101.4599990844727</v>
+        <v>103.0400009155273</v>
       </c>
       <c r="E145" t="n">
-        <v>103.0100021362305</v>
+        <v>106.2799987792969</v>
       </c>
       <c r="F145" t="n">
-        <v>25769900</v>
+        <v>40534900</v>
       </c>
       <c r="G145" t="n">
         <v>0</v>
@@ -4213,22 +4213,22 @@
     </row>
     <row r="146">
       <c r="A146" s="1" t="n">
-        <v>46125</v>
+        <v>46127</v>
       </c>
       <c r="B146" t="n">
-        <v>103.0299987792969</v>
+        <v>105.9800033569336</v>
       </c>
       <c r="C146" t="n">
-        <v>103.6699981689453</v>
+        <v>107.8499984741211</v>
       </c>
       <c r="D146" t="n">
-        <v>102.0599975585938</v>
+        <v>105.0400009155273</v>
       </c>
       <c r="E146" t="n">
-        <v>103.1600036621094</v>
+        <v>107.7099990844727</v>
       </c>
       <c r="F146" t="n">
-        <v>26042800</v>
+        <v>38023700</v>
       </c>
       <c r="G146" t="n">
         <v>0</v>
@@ -4239,22 +4239,22 @@
     </row>
     <row r="147">
       <c r="A147" s="1" t="n">
-        <v>46126</v>
+        <v>46128</v>
       </c>
       <c r="B147" t="n">
-        <v>103.120002746582</v>
+        <v>107.4700012207031</v>
       </c>
       <c r="C147" t="n">
-        <v>106.5699996948242</v>
+        <v>108.9499969482422</v>
       </c>
       <c r="D147" t="n">
-        <v>103.0400009155273</v>
+        <v>106.620002746582</v>
       </c>
       <c r="E147" t="n">
-        <v>106.2799987792969</v>
+        <v>107.7900009155273</v>
       </c>
       <c r="F147" t="n">
-        <v>40534900</v>
+        <v>64928300</v>
       </c>
       <c r="G147" t="n">
         <v>0</v>
@@ -4265,22 +4265,22 @@
     </row>
     <row r="148">
       <c r="A148" s="1" t="n">
-        <v>46127</v>
+        <v>46129</v>
       </c>
       <c r="B148" t="n">
-        <v>105.9800033569336</v>
+        <v>96.37000274658203</v>
       </c>
       <c r="C148" t="n">
-        <v>107.8499984741211</v>
+        <v>98.73999786376953</v>
       </c>
       <c r="D148" t="n">
-        <v>105.0400009155273</v>
+        <v>95.09999847412109</v>
       </c>
       <c r="E148" t="n">
-        <v>107.7099990844727</v>
+        <v>97.30999755859375</v>
       </c>
       <c r="F148" t="n">
-        <v>38023700</v>
+        <v>125958700</v>
       </c>
       <c r="G148" t="n">
         <v>0</v>
@@ -4291,22 +4291,22 @@
     </row>
     <row r="149">
       <c r="A149" s="1" t="n">
-        <v>46128</v>
+        <v>46132</v>
       </c>
       <c r="B149" t="n">
-        <v>107.4700012207031</v>
+        <v>97.13999938964844</v>
       </c>
       <c r="C149" t="n">
-        <v>108.9499969482422</v>
+        <v>97.59999847412109</v>
       </c>
       <c r="D149" t="n">
-        <v>106.620002746582</v>
+        <v>93.54000091552734</v>
       </c>
       <c r="E149" t="n">
-        <v>107.7900009155273</v>
+        <v>94.83000183105469</v>
       </c>
       <c r="F149" t="n">
-        <v>64928300</v>
+        <v>63298300</v>
       </c>
       <c r="G149" t="n">
         <v>0</v>
@@ -4317,22 +4317,22 @@
     </row>
     <row r="150">
       <c r="A150" s="1" t="n">
-        <v>46129</v>
+        <v>46133</v>
       </c>
       <c r="B150" t="n">
-        <v>96.37000274658203</v>
+        <v>94</v>
       </c>
       <c r="C150" t="n">
-        <v>98.73999786376953</v>
+        <v>94.65000152587891</v>
       </c>
       <c r="D150" t="n">
-        <v>95.09999847412109</v>
+        <v>92.37000274658203</v>
       </c>
       <c r="E150" t="n">
-        <v>97.30999755859375</v>
+        <v>92.58000183105469</v>
       </c>
       <c r="F150" t="n">
-        <v>125958700</v>
+        <v>61962300</v>
       </c>
       <c r="G150" t="n">
         <v>0</v>
@@ -4343,22 +4343,22 @@
     </row>
     <row r="151">
       <c r="A151" s="1" t="n">
-        <v>46132</v>
+        <v>46134</v>
       </c>
       <c r="B151" t="n">
-        <v>97.13999938964844</v>
+        <v>93.05999755859375</v>
       </c>
       <c r="C151" t="n">
-        <v>97.59999847412109</v>
+        <v>93.84999847412109</v>
       </c>
       <c r="D151" t="n">
-        <v>93.54000091552734</v>
+        <v>92.76999664306641</v>
       </c>
       <c r="E151" t="n">
-        <v>94.83000183105469</v>
+        <v>93.23999786376953</v>
       </c>
       <c r="F151" t="n">
-        <v>63298300</v>
+        <v>33694300</v>
       </c>
       <c r="G151" t="n">
         <v>0</v>
@@ -4369,22 +4369,22 @@
     </row>
     <row r="152">
       <c r="A152" s="1" t="n">
-        <v>46133</v>
+        <v>46135</v>
       </c>
       <c r="B152" t="n">
-        <v>94</v>
+        <v>94.05999755859375</v>
       </c>
       <c r="C152" t="n">
-        <v>94.65000152587891</v>
+        <v>94.63999938964844</v>
       </c>
       <c r="D152" t="n">
-        <v>92.37000274658203</v>
+        <v>92.06999969482422</v>
       </c>
       <c r="E152" t="n">
-        <v>92.58000183105469</v>
+        <v>92.81999969482422</v>
       </c>
       <c r="F152" t="n">
-        <v>61962300</v>
+        <v>36851700</v>
       </c>
       <c r="G152" t="n">
         <v>0</v>
@@ -4395,22 +4395,22 @@
     </row>
     <row r="153">
       <c r="A153" s="1" t="n">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c r="B153" t="n">
-        <v>93.05999755859375</v>
+        <v>92.56999969482422</v>
       </c>
       <c r="C153" t="n">
-        <v>93.84999847412109</v>
+        <v>93.27999877929688</v>
       </c>
       <c r="D153" t="n">
-        <v>92.76999664306641</v>
+        <v>91.80000305175781</v>
       </c>
       <c r="E153" t="n">
-        <v>93.23999786376953</v>
+        <v>92.44000244140625</v>
       </c>
       <c r="F153" t="n">
-        <v>33694300</v>
+        <v>32553200</v>
       </c>
       <c r="G153" t="n">
         <v>0</v>
@@ -4421,22 +4421,22 @@
     </row>
     <row r="154">
       <c r="A154" s="1" t="n">
-        <v>46135</v>
+        <v>46139</v>
       </c>
       <c r="B154" t="n">
-        <v>94.05999755859375</v>
+        <v>92.05000305175781</v>
       </c>
       <c r="C154" t="n">
-        <v>94.63999938964844</v>
+        <v>92.83999633789062</v>
       </c>
       <c r="D154" t="n">
-        <v>92.06999969482422</v>
+        <v>91.30000305175781</v>
       </c>
       <c r="E154" t="n">
-        <v>92.81999969482422</v>
+        <v>91.37000274658203</v>
       </c>
       <c r="F154" t="n">
-        <v>36851700</v>
+        <v>29707400</v>
       </c>
       <c r="G154" t="n">
         <v>0</v>
@@ -4447,22 +4447,22 @@
     </row>
     <row r="155">
       <c r="A155" s="1" t="n">
-        <v>46136</v>
+        <v>46140</v>
       </c>
       <c r="B155" t="n">
-        <v>92.56999969482422</v>
+        <v>91.5</v>
       </c>
       <c r="C155" t="n">
-        <v>93.27999877929688</v>
+        <v>92.33999633789062</v>
       </c>
       <c r="D155" t="n">
-        <v>91.80000305175781</v>
+        <v>90.01999664306641</v>
       </c>
       <c r="E155" t="n">
-        <v>92.44000244140625</v>
+        <v>92.26999664306641</v>
       </c>
       <c r="F155" t="n">
-        <v>32553200</v>
+        <v>33418100</v>
       </c>
       <c r="G155" t="n">
         <v>0</v>
@@ -4473,22 +4473,22 @@
     </row>
     <row r="156">
       <c r="A156" s="1" t="n">
-        <v>46139</v>
+        <v>46141</v>
       </c>
       <c r="B156" t="n">
-        <v>92.05000305175781</v>
+        <v>91.23000335693359</v>
       </c>
       <c r="C156" t="n">
-        <v>92.83999633789062</v>
+        <v>92.86000061035156</v>
       </c>
       <c r="D156" t="n">
-        <v>91.30000305175781</v>
+        <v>90.86000061035156</v>
       </c>
       <c r="E156" t="n">
-        <v>91.37000274658203</v>
+        <v>92.12000274658203</v>
       </c>
       <c r="F156" t="n">
-        <v>29707400</v>
+        <v>26122100</v>
       </c>
       <c r="G156" t="n">
         <v>0</v>
@@ -4499,22 +4499,22 @@
     </row>
     <row r="157">
       <c r="A157" s="1" t="n">
-        <v>46140</v>
+        <v>46142</v>
       </c>
       <c r="B157" t="n">
-        <v>91.5</v>
+        <v>91.34999847412109</v>
       </c>
       <c r="C157" t="n">
-        <v>92.33999633789062</v>
+        <v>94.22000122070312</v>
       </c>
       <c r="D157" t="n">
-        <v>90.01999664306641</v>
+        <v>90.76999664306641</v>
       </c>
       <c r="E157" t="n">
-        <v>92.26999664306641</v>
+        <v>93.61000061035156</v>
       </c>
       <c r="F157" t="n">
-        <v>33418100</v>
+        <v>40923000</v>
       </c>
       <c r="G157" t="n">
         <v>0</v>
@@ -4525,22 +4525,22 @@
     </row>
     <row r="158">
       <c r="A158" s="1" t="n">
-        <v>46141</v>
+        <v>46143</v>
       </c>
       <c r="B158" t="n">
-        <v>91.23000335693359</v>
+        <v>94.41999816894531</v>
       </c>
       <c r="C158" t="n">
-        <v>92.86000061035156</v>
+        <v>94.69999694824219</v>
       </c>
       <c r="D158" t="n">
-        <v>90.86000061035156</v>
+        <v>91.90000152587891</v>
       </c>
       <c r="E158" t="n">
-        <v>92.12000274658203</v>
+        <v>92.05999755859375</v>
       </c>
       <c r="F158" t="n">
-        <v>26122100</v>
+        <v>30406900</v>
       </c>
       <c r="G158" t="n">
         <v>0</v>
@@ -4551,22 +4551,22 @@
     </row>
     <row r="159">
       <c r="A159" s="1" t="n">
-        <v>46142</v>
+        <v>46146</v>
       </c>
       <c r="B159" t="n">
-        <v>91.34999847412109</v>
+        <v>92.09999847412109</v>
       </c>
       <c r="C159" t="n">
-        <v>94.22000122070312</v>
+        <v>92.33000183105469</v>
       </c>
       <c r="D159" t="n">
-        <v>90.76999664306641</v>
+        <v>90.88999938964844</v>
       </c>
       <c r="E159" t="n">
-        <v>93.61000061035156</v>
+        <v>91.01999664306641</v>
       </c>
       <c r="F159" t="n">
-        <v>40923000</v>
+        <v>25928800</v>
       </c>
       <c r="G159" t="n">
         <v>0</v>
@@ -4577,22 +4577,22 @@
     </row>
     <row r="160">
       <c r="A160" s="1" t="n">
-        <v>46143</v>
+        <v>46147</v>
       </c>
       <c r="B160" t="n">
-        <v>94.41999816894531</v>
+        <v>91.18000030517578</v>
       </c>
       <c r="C160" t="n">
-        <v>94.69999694824219</v>
+        <v>91.27999877929688</v>
       </c>
       <c r="D160" t="n">
-        <v>91.90000152587891</v>
+        <v>87.56999969482422</v>
       </c>
       <c r="E160" t="n">
-        <v>92.05999755859375</v>
+        <v>87.88999938964844</v>
       </c>
       <c r="F160" t="n">
-        <v>30406900</v>
+        <v>51961300</v>
       </c>
       <c r="G160" t="n">
         <v>0</v>
@@ -4603,22 +4603,22 @@
     </row>
     <row r="161">
       <c r="A161" s="1" t="n">
-        <v>46146</v>
+        <v>46148</v>
       </c>
       <c r="B161" t="n">
-        <v>92.09999847412109</v>
+        <v>87.15000152587891</v>
       </c>
       <c r="C161" t="n">
-        <v>92.33000183105469</v>
+        <v>88.55000305175781</v>
       </c>
       <c r="D161" t="n">
-        <v>90.88999938964844</v>
+        <v>86.72000122070312</v>
       </c>
       <c r="E161" t="n">
-        <v>91.01999664306641</v>
+        <v>88.26999664306641</v>
       </c>
       <c r="F161" t="n">
-        <v>25928800</v>
+        <v>41932400</v>
       </c>
       <c r="G161" t="n">
         <v>0</v>
@@ -4629,22 +4629,22 @@
     </row>
     <row r="162">
       <c r="A162" s="1" t="n">
-        <v>46147</v>
+        <v>46149</v>
       </c>
       <c r="B162" t="n">
-        <v>91.18000030517578</v>
+        <v>88.19999694824219</v>
       </c>
       <c r="C162" t="n">
-        <v>91.27999877929688</v>
+        <v>89.40000152587891</v>
       </c>
       <c r="D162" t="n">
-        <v>87.56999969482422</v>
+        <v>88.12999725341797</v>
       </c>
       <c r="E162" t="n">
-        <v>87.88999938964844</v>
+        <v>88.25</v>
       </c>
       <c r="F162" t="n">
-        <v>51961300</v>
+        <v>30627600</v>
       </c>
       <c r="G162" t="n">
         <v>0</v>
@@ -4655,22 +4655,22 @@
     </row>
     <row r="163">
       <c r="A163" s="1" t="n">
-        <v>46148</v>
+        <v>46150</v>
       </c>
       <c r="B163" t="n">
-        <v>87.15000152587891</v>
+        <v>87.70999908447266</v>
       </c>
       <c r="C163" t="n">
-        <v>88.55000305175781</v>
+        <v>88.04000091552734</v>
       </c>
       <c r="D163" t="n">
-        <v>86.72000122070312</v>
+        <v>87.20999908447266</v>
       </c>
       <c r="E163" t="n">
-        <v>88.26999664306641</v>
+        <v>87.48999786376953</v>
       </c>
       <c r="F163" t="n">
-        <v>41932400</v>
+        <v>36215100</v>
       </c>
       <c r="G163" t="n">
         <v>0</v>
@@ -4681,22 +4681,22 @@
     </row>
     <row r="164">
       <c r="A164" s="1" t="n">
-        <v>46149</v>
+        <v>46153</v>
       </c>
       <c r="B164" t="n">
-        <v>88.19999694824219</v>
+        <v>86.52999877929688</v>
       </c>
       <c r="C164" t="n">
-        <v>89.40000152587891</v>
+        <v>87.33999633789062</v>
       </c>
       <c r="D164" t="n">
-        <v>88.12999725341797</v>
+        <v>85.09999847412109</v>
       </c>
       <c r="E164" t="n">
-        <v>88.25</v>
+        <v>85.44999694824219</v>
       </c>
       <c r="F164" t="n">
-        <v>30627600</v>
+        <v>40556500</v>
       </c>
       <c r="G164" t="n">
         <v>0</v>
@@ -4707,22 +4707,22 @@
     </row>
     <row r="165">
       <c r="A165" s="1" t="n">
-        <v>46150</v>
+        <v>46154</v>
       </c>
       <c r="B165" t="n">
-        <v>87.70999908447266</v>
+        <v>85.91000366210938</v>
       </c>
       <c r="C165" t="n">
-        <v>88.04000091552734</v>
+        <v>89.16999816894531</v>
       </c>
       <c r="D165" t="n">
-        <v>87.20999908447266</v>
+        <v>85.80999755859375</v>
       </c>
       <c r="E165" t="n">
-        <v>87.48999786376953</v>
+        <v>87.66000366210938</v>
       </c>
       <c r="F165" t="n">
-        <v>36215100</v>
+        <v>43556600</v>
       </c>
       <c r="G165" t="n">
         <v>0</v>
@@ -4733,22 +4733,22 @@
     </row>
     <row r="166">
       <c r="A166" s="1" t="n">
-        <v>46153</v>
+        <v>46155</v>
       </c>
       <c r="B166" t="n">
-        <v>86.52999877929688</v>
+        <v>86.56999969482422</v>
       </c>
       <c r="C166" t="n">
-        <v>87.33999633789062</v>
+        <v>88.62000274658203</v>
       </c>
       <c r="D166" t="n">
-        <v>85.09999847412109</v>
+        <v>86.27999877929688</v>
       </c>
       <c r="E166" t="n">
-        <v>85.44999694824219</v>
+        <v>87.55999755859375</v>
       </c>
       <c r="F166" t="n">
-        <v>40556500</v>
+        <v>30823500</v>
       </c>
       <c r="G166" t="n">
         <v>0</v>
@@ -4759,22 +4759,22 @@
     </row>
     <row r="167">
       <c r="A167" s="1" t="n">
-        <v>46154</v>
+        <v>46156</v>
       </c>
       <c r="B167" t="n">
-        <v>85.91000366210938</v>
+        <v>87.62000274658203</v>
       </c>
       <c r="C167" t="n">
-        <v>89.16999816894531</v>
+        <v>88.5</v>
       </c>
       <c r="D167" t="n">
-        <v>85.80999755859375</v>
+        <v>86.65000152587891</v>
       </c>
       <c r="E167" t="n">
-        <v>87.66000366210938</v>
+        <v>86.94000244140625</v>
       </c>
       <c r="F167" t="n">
-        <v>43556600</v>
+        <v>29408300</v>
       </c>
       <c r="G167" t="n">
         <v>0</v>
@@ -4785,22 +4785,22 @@
     </row>
     <row r="168">
       <c r="A168" s="1" t="n">
-        <v>46155</v>
+        <v>46157</v>
       </c>
       <c r="B168" t="n">
-        <v>86.56999969482422</v>
+        <v>87.69000244140625</v>
       </c>
       <c r="C168" t="n">
-        <v>88.62000274658203</v>
+        <v>89.48999786376953</v>
       </c>
       <c r="D168" t="n">
-        <v>86.27999877929688</v>
+        <v>86.69000244140625</v>
       </c>
       <c r="E168" t="n">
-        <v>87.55999755859375</v>
+        <v>87.01999664306641</v>
       </c>
       <c r="F168" t="n">
-        <v>30823500</v>
+        <v>32335700</v>
       </c>
       <c r="G168" t="n">
         <v>0</v>
@@ -4811,22 +4811,22 @@
     </row>
     <row r="169">
       <c r="A169" s="1" t="n">
-        <v>46156</v>
+        <v>46160</v>
       </c>
       <c r="B169" t="n">
-        <v>87.62000274658203</v>
+        <v>86.5</v>
       </c>
       <c r="C169" t="n">
-        <v>88.5</v>
+        <v>89.81999969482422</v>
       </c>
       <c r="D169" t="n">
-        <v>86.65000152587891</v>
+        <v>86.33000183105469</v>
       </c>
       <c r="E169" t="n">
-        <v>86.94000244140625</v>
+        <v>89.65000152587891</v>
       </c>
       <c r="F169" t="n">
-        <v>29408300</v>
+        <v>35800500</v>
       </c>
       <c r="G169" t="n">
         <v>0</v>
@@ -4837,22 +4837,22 @@
     </row>
     <row r="170">
       <c r="A170" s="1" t="n">
-        <v>46157</v>
+        <v>46161</v>
       </c>
       <c r="B170" t="n">
-        <v>87.69000244140625</v>
+        <v>90.13999938964844</v>
       </c>
       <c r="C170" t="n">
-        <v>89.48999786376953</v>
+        <v>91.48000335693359</v>
       </c>
       <c r="D170" t="n">
-        <v>86.69000244140625</v>
+        <v>88.69000244140625</v>
       </c>
       <c r="E170" t="n">
-        <v>87.01999664306641</v>
+        <v>89.33000183105469</v>
       </c>
       <c r="F170" t="n">
-        <v>32335700</v>
+        <v>34545700</v>
       </c>
       <c r="G170" t="n">
         <v>0</v>
@@ -4863,22 +4863,22 @@
     </row>
     <row r="171">
       <c r="A171" s="1" t="n">
-        <v>46160</v>
+        <v>46162</v>
       </c>
       <c r="B171" t="n">
-        <v>86.5</v>
+        <v>88.51999664306641</v>
       </c>
       <c r="C171" t="n">
-        <v>89.81999969482422</v>
+        <v>88.55000305175781</v>
       </c>
       <c r="D171" t="n">
-        <v>86.33000183105469</v>
+        <v>87.5</v>
       </c>
       <c r="E171" t="n">
-        <v>89.65000152587891</v>
+        <v>88.08999633789062</v>
       </c>
       <c r="F171" t="n">
-        <v>35800500</v>
+        <v>23463400</v>
       </c>
       <c r="G171" t="n">
         <v>0</v>
@@ -4889,22 +4889,22 @@
     </row>
     <row r="172">
       <c r="A172" s="1" t="n">
-        <v>46161</v>
+        <v>46163</v>
       </c>
       <c r="B172" t="n">
-        <v>90.13999938964844</v>
+        <v>88.02999877929688</v>
       </c>
       <c r="C172" t="n">
-        <v>91.48000335693359</v>
+        <v>90.37000274658203</v>
       </c>
       <c r="D172" t="n">
-        <v>88.69000244140625</v>
+        <v>87.51999664306641</v>
       </c>
       <c r="E172" t="n">
-        <v>89.33000183105469</v>
+        <v>89.30000305175781</v>
       </c>
       <c r="F172" t="n">
-        <v>34545700</v>
+        <v>28613900</v>
       </c>
       <c r="G172" t="n">
         <v>0</v>
@@ -4915,22 +4915,22 @@
     </row>
     <row r="173">
       <c r="A173" s="1" t="n">
-        <v>46162</v>
+        <v>46164</v>
       </c>
       <c r="B173" t="n">
-        <v>88.51999664306641</v>
+        <v>89.09999847412109</v>
       </c>
       <c r="C173" t="n">
-        <v>88.55000305175781</v>
+        <v>89.97000122070312</v>
       </c>
       <c r="D173" t="n">
-        <v>87.5</v>
+        <v>88.16999816894531</v>
       </c>
       <c r="E173" t="n">
-        <v>88.08999633789062</v>
+        <v>88.59999847412109</v>
       </c>
       <c r="F173" t="n">
-        <v>23463400</v>
+        <v>23847200</v>
       </c>
       <c r="G173" t="n">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="174">
       <c r="A174" s="1" t="n">
-        <v>46163</v>
+        <v>46168</v>
       </c>
       <c r="B174" t="n">
-        <v>88.02999877929688</v>
+        <v>88.40000152587891</v>
       </c>
       <c r="C174" t="n">
-        <v>90.37000274658203</v>
+        <v>88.73000335693359</v>
       </c>
       <c r="D174" t="n">
-        <v>87.51999664306641</v>
+        <v>87.25</v>
       </c>
       <c r="E174" t="n">
-        <v>89.30000305175781</v>
+        <v>87.68000030517578</v>
       </c>
       <c r="F174" t="n">
-        <v>28613900</v>
+        <v>24014500</v>
       </c>
       <c r="G174" t="n">
         <v>0</v>
@@ -4967,22 +4967,22 @@
     </row>
     <row r="175">
       <c r="A175" s="1" t="n">
-        <v>46164</v>
+        <v>46169</v>
       </c>
       <c r="B175" t="n">
-        <v>89.09999847412109</v>
+        <v>87.05000305175781</v>
       </c>
       <c r="C175" t="n">
-        <v>89.97000122070312</v>
+        <v>88.5</v>
       </c>
       <c r="D175" t="n">
-        <v>88.16999816894531</v>
+        <v>86.81999969482422</v>
       </c>
       <c r="E175" t="n">
-        <v>88.59999847412109</v>
+        <v>87.34999847412109</v>
       </c>
       <c r="F175" t="n">
-        <v>23847200</v>
+        <v>22569500</v>
       </c>
       <c r="G175" t="n">
         <v>0</v>
@@ -4993,22 +4993,22 @@
     </row>
     <row r="176">
       <c r="A176" s="1" t="n">
-        <v>46168</v>
+        <v>46170</v>
       </c>
       <c r="B176" t="n">
-        <v>88.40000152587891</v>
+        <v>86.90000152587891</v>
       </c>
       <c r="C176" t="n">
-        <v>88.73000335693359</v>
+        <v>87.04000091552734</v>
       </c>
       <c r="D176" t="n">
-        <v>87.25</v>
+        <v>85.58999633789062</v>
       </c>
       <c r="E176" t="n">
-        <v>87.68000030517578</v>
+        <v>86.36000061035156</v>
       </c>
       <c r="F176" t="n">
-        <v>24014500</v>
+        <v>38803800</v>
       </c>
       <c r="G176" t="n">
         <v>0</v>
@@ -5019,22 +5019,22 @@
     </row>
     <row r="177">
       <c r="A177" s="1" t="n">
-        <v>46169</v>
+        <v>46171</v>
       </c>
       <c r="B177" t="n">
-        <v>87.05000305175781</v>
+        <v>86.19999694824219</v>
       </c>
       <c r="C177" t="n">
-        <v>88.5</v>
+        <v>86.66999816894531</v>
       </c>
       <c r="D177" t="n">
-        <v>86.81999969482422</v>
+        <v>85.66000366210938</v>
       </c>
       <c r="E177" t="n">
-        <v>87.34999847412109</v>
+        <v>86.01999664306641</v>
       </c>
       <c r="F177" t="n">
-        <v>22569500</v>
+        <v>39793600</v>
       </c>
       <c r="G177" t="n">
         <v>0</v>
@@ -5045,22 +5045,22 @@
     </row>
     <row r="178">
       <c r="A178" s="1" t="n">
-        <v>46170</v>
+        <v>46174</v>
       </c>
       <c r="B178" t="n">
-        <v>86.90000152587891</v>
+        <v>85.73000335693359</v>
       </c>
       <c r="C178" t="n">
-        <v>87.04000091552734</v>
+        <v>87.23000335693359</v>
       </c>
       <c r="D178" t="n">
-        <v>85.58999633789062</v>
+        <v>85.31999969482422</v>
       </c>
       <c r="E178" t="n">
-        <v>86.36000061035156</v>
+        <v>85.84999847412109</v>
       </c>
       <c r="F178" t="n">
-        <v>38803800</v>
+        <v>32747200</v>
       </c>
       <c r="G178" t="n">
         <v>0</v>
@@ -5071,22 +5071,22 @@
     </row>
     <row r="179">
       <c r="A179" s="1" t="n">
-        <v>46171</v>
+        <v>46175</v>
       </c>
       <c r="B179" t="n">
-        <v>86.19999694824219</v>
+        <v>85.61000061035156</v>
       </c>
       <c r="C179" t="n">
-        <v>86.66999816894531</v>
+        <v>85.98000335693359</v>
       </c>
       <c r="D179" t="n">
-        <v>85.66000366210938</v>
+        <v>83.29000091552734</v>
       </c>
       <c r="E179" t="n">
-        <v>86.01999664306641</v>
+        <v>83.33000183105469</v>
       </c>
       <c r="F179" t="n">
-        <v>39793600</v>
+        <v>42947200</v>
       </c>
       <c r="G179" t="n">
         <v>0</v>
@@ -5097,22 +5097,22 @@
     </row>
     <row r="180">
       <c r="A180" s="1" t="n">
-        <v>46174</v>
+        <v>46176</v>
       </c>
       <c r="B180" t="n">
-        <v>85.73000335693359</v>
+        <v>82.91000366210938</v>
       </c>
       <c r="C180" t="n">
-        <v>87.23000335693359</v>
+        <v>83.30999755859375</v>
       </c>
       <c r="D180" t="n">
-        <v>85.31999969482422</v>
+        <v>81.09999847412109</v>
       </c>
       <c r="E180" t="n">
-        <v>85.84999847412109</v>
+        <v>81.51999664306641</v>
       </c>
       <c r="F180" t="n">
-        <v>32747200</v>
+        <v>36714700</v>
       </c>
       <c r="G180" t="n">
         <v>0</v>
@@ -5123,22 +5123,22 @@
     </row>
     <row r="181">
       <c r="A181" s="1" t="n">
-        <v>46175</v>
+        <v>46177</v>
       </c>
       <c r="B181" t="n">
-        <v>85.61000061035156</v>
+        <v>83.19000244140625</v>
       </c>
       <c r="C181" t="n">
-        <v>85.98000335693359</v>
+        <v>83.69999694824219</v>
       </c>
       <c r="D181" t="n">
-        <v>83.29000091552734</v>
+        <v>81.37000274658203</v>
       </c>
       <c r="E181" t="n">
-        <v>83.33000183105469</v>
+        <v>81.55999755859375</v>
       </c>
       <c r="F181" t="n">
-        <v>42947200</v>
+        <v>39338800</v>
       </c>
       <c r="G181" t="n">
         <v>0</v>
@@ -5149,22 +5149,22 @@
     </row>
     <row r="182">
       <c r="A182" s="1" t="n">
-        <v>46176</v>
+        <v>46178</v>
       </c>
       <c r="B182" t="n">
-        <v>82.91000366210938</v>
+        <v>82.33000183105469</v>
       </c>
       <c r="C182" t="n">
-        <v>83.30999755859375</v>
+        <v>82.75</v>
       </c>
       <c r="D182" t="n">
-        <v>81.09999847412109</v>
+        <v>81</v>
       </c>
       <c r="E182" t="n">
-        <v>81.51999664306641</v>
+        <v>82.18000030517578</v>
       </c>
       <c r="F182" t="n">
-        <v>36714700</v>
+        <v>43474100</v>
       </c>
       <c r="G182" t="n">
         <v>0</v>
@@ -5175,22 +5175,22 @@
     </row>
     <row r="183">
       <c r="A183" s="1" t="n">
-        <v>46177</v>
+        <v>46181</v>
       </c>
       <c r="B183" t="n">
-        <v>83.19000244140625</v>
+        <v>81.66000366210938</v>
       </c>
       <c r="C183" t="n">
-        <v>83.69999694824219</v>
+        <v>83.08000183105469</v>
       </c>
       <c r="D183" t="n">
-        <v>81.37000274658203</v>
+        <v>81.33999633789062</v>
       </c>
       <c r="E183" t="n">
-        <v>81.55999755859375</v>
+        <v>82.63999938964844</v>
       </c>
       <c r="F183" t="n">
-        <v>39338800</v>
+        <v>33056700</v>
       </c>
       <c r="G183" t="n">
         <v>0</v>
@@ -5201,22 +5201,22 @@
     </row>
     <row r="184">
       <c r="A184" s="1" t="n">
-        <v>46178</v>
+        <v>46182</v>
       </c>
       <c r="B184" t="n">
-        <v>82.33000183105469</v>
+        <v>82.12999725341797</v>
       </c>
       <c r="C184" t="n">
-        <v>82.75</v>
+        <v>82.33999633789062</v>
       </c>
       <c r="D184" t="n">
-        <v>81</v>
+        <v>81.33999633789062</v>
       </c>
       <c r="E184" t="n">
-        <v>82.18000030517578</v>
+        <v>81.41000366210938</v>
       </c>
       <c r="F184" t="n">
-        <v>43474100</v>
+        <v>34787200</v>
       </c>
       <c r="G184" t="n">
         <v>0</v>
@@ -5227,22 +5227,22 @@
     </row>
     <row r="185">
       <c r="A185" s="1" t="n">
-        <v>46181</v>
+        <v>46183</v>
       </c>
       <c r="B185" t="n">
-        <v>81.66000366210938</v>
+        <v>81.70999908447266</v>
       </c>
       <c r="C185" t="n">
-        <v>83.08000183105469</v>
+        <v>82.75</v>
       </c>
       <c r="D185" t="n">
-        <v>81.33999633789062</v>
+        <v>80.98000335693359</v>
       </c>
       <c r="E185" t="n">
-        <v>82.63999938964844</v>
+        <v>82</v>
       </c>
       <c r="F185" t="n">
-        <v>33056700</v>
+        <v>36304600</v>
       </c>
       <c r="G185" t="n">
         <v>0</v>
@@ -5253,22 +5253,22 @@
     </row>
     <row r="186">
       <c r="A186" s="1" t="n">
-        <v>46182</v>
+        <v>46184</v>
       </c>
       <c r="B186" t="n">
-        <v>82.12999725341797</v>
+        <v>81.87000274658203</v>
       </c>
       <c r="C186" t="n">
-        <v>82.33999633789062</v>
+        <v>82.09999847412109</v>
       </c>
       <c r="D186" t="n">
-        <v>81.33999633789062</v>
+        <v>80.08999633789062</v>
       </c>
       <c r="E186" t="n">
-        <v>81.41000366210938</v>
+        <v>81.26999664306641</v>
       </c>
       <c r="F186" t="n">
-        <v>34787200</v>
+        <v>33417600</v>
       </c>
       <c r="G186" t="n">
         <v>0</v>
@@ -5279,22 +5279,22 @@
     </row>
     <row r="187">
       <c r="A187" s="1" t="n">
-        <v>46183</v>
+        <v>46185</v>
       </c>
       <c r="B187" t="n">
-        <v>81.70999908447266</v>
+        <v>81.58000183105469</v>
       </c>
       <c r="C187" t="n">
-        <v>82.75</v>
+        <v>82</v>
       </c>
       <c r="D187" t="n">
-        <v>80.98000335693359</v>
+        <v>79.27999877929688</v>
       </c>
       <c r="E187" t="n">
-        <v>82</v>
+        <v>80.33999633789062</v>
       </c>
       <c r="F187" t="n">
-        <v>36304600</v>
+        <v>35309700</v>
       </c>
       <c r="G187" t="n">
         <v>0</v>
@@ -5305,22 +5305,22 @@
     </row>
     <row r="188">
       <c r="A188" s="1" t="n">
-        <v>46184</v>
+        <v>46188</v>
       </c>
       <c r="B188" t="n">
-        <v>81.87000274658203</v>
+        <v>80.62000274658203</v>
       </c>
       <c r="C188" t="n">
-        <v>82.09999847412109</v>
+        <v>81.70999908447266</v>
       </c>
       <c r="D188" t="n">
-        <v>80.08999633789062</v>
+        <v>80.45999908447266</v>
       </c>
       <c r="E188" t="n">
-        <v>81.26999664306641</v>
+        <v>81.66999816894531</v>
       </c>
       <c r="F188" t="n">
-        <v>33417600</v>
+        <v>36430800</v>
       </c>
       <c r="G188" t="n">
         <v>0</v>
@@ -5331,22 +5331,22 @@
     </row>
     <row r="189">
       <c r="A189" s="1" t="n">
-        <v>46185</v>
+        <v>46189</v>
       </c>
       <c r="B189" t="n">
-        <v>81.58000183105469</v>
+        <v>81.90000152587891</v>
       </c>
       <c r="C189" t="n">
-        <v>82</v>
+        <v>81.93000030517578</v>
       </c>
       <c r="D189" t="n">
-        <v>79.27999877929688</v>
+        <v>77.70999908447266</v>
       </c>
       <c r="E189" t="n">
-        <v>80.33999633789062</v>
+        <v>78.72000122070312</v>
       </c>
       <c r="F189" t="n">
-        <v>35309700</v>
+        <v>65054000</v>
       </c>
       <c r="G189" t="n">
         <v>0</v>
@@ -5357,22 +5357,22 @@
     </row>
     <row r="190">
       <c r="A190" s="1" t="n">
-        <v>46188</v>
+        <v>46190</v>
       </c>
       <c r="B190" t="n">
-        <v>80.62000274658203</v>
+        <v>78.09999847412109</v>
       </c>
       <c r="C190" t="n">
-        <v>81.70999908447266</v>
+        <v>78.44999694824219</v>
       </c>
       <c r="D190" t="n">
-        <v>80.45999908447266</v>
+        <v>76.76000213623047</v>
       </c>
       <c r="E190" t="n">
-        <v>81.66999816894531</v>
+        <v>76.95999908447266</v>
       </c>
       <c r="F190" t="n">
-        <v>36430800</v>
+        <v>50338800</v>
       </c>
       <c r="G190" t="n">
         <v>0</v>
@@ -5383,22 +5383,22 @@
     </row>
     <row r="191">
       <c r="A191" s="1" t="n">
-        <v>46189</v>
+        <v>46191</v>
       </c>
       <c r="B191" t="n">
-        <v>81.90000152587891</v>
+        <v>76.93000030517578</v>
       </c>
       <c r="C191" t="n">
-        <v>81.93000030517578</v>
+        <v>78.23999786376953</v>
       </c>
       <c r="D191" t="n">
-        <v>77.70999908447266</v>
+        <v>76.12000274658203</v>
       </c>
       <c r="E191" t="n">
-        <v>78.72000122070312</v>
+        <v>77.37999725341797</v>
       </c>
       <c r="F191" t="n">
-        <v>65054000</v>
+        <v>91920400</v>
       </c>
       <c r="G191" t="n">
         <v>0</v>
@@ -5409,22 +5409,22 @@
     </row>
     <row r="192">
       <c r="A192" s="1" t="n">
-        <v>46190</v>
+        <v>46195</v>
       </c>
       <c r="B192" t="n">
-        <v>78.09999847412109</v>
+        <v>76.13999938964844</v>
       </c>
       <c r="C192" t="n">
-        <v>78.44999694824219</v>
+        <v>77.08999633789062</v>
       </c>
       <c r="D192" t="n">
-        <v>76.76000213623047</v>
+        <v>71.80999755859375</v>
       </c>
       <c r="E192" t="n">
-        <v>76.95999908447266</v>
+        <v>72.87999725341797</v>
       </c>
       <c r="F192" t="n">
-        <v>50338800</v>
+        <v>82203300</v>
       </c>
       <c r="G192" t="n">
         <v>0</v>
@@ -5435,22 +5435,22 @@
     </row>
     <row r="193">
       <c r="A193" s="1" t="n">
-        <v>46191</v>
+        <v>46196</v>
       </c>
       <c r="B193" t="n">
-        <v>76.93000030517578</v>
+        <v>73.26000213623047</v>
       </c>
       <c r="C193" t="n">
-        <v>78.23999786376953</v>
+        <v>73.95999908447266</v>
       </c>
       <c r="D193" t="n">
-        <v>76.12000274658203</v>
+        <v>72.62999725341797</v>
       </c>
       <c r="E193" t="n">
-        <v>77.37999725341797</v>
+        <v>72.81999969482422</v>
       </c>
       <c r="F193" t="n">
-        <v>91920400</v>
+        <v>50806800</v>
       </c>
       <c r="G193" t="n">
         <v>0</v>
@@ -5461,22 +5461,22 @@
     </row>
     <row r="194">
       <c r="A194" s="1" t="n">
-        <v>46195</v>
+        <v>46197</v>
       </c>
       <c r="B194" t="n">
-        <v>76.13999938964844</v>
+        <v>72.69000244140625</v>
       </c>
       <c r="C194" t="n">
-        <v>77.08999633789062</v>
+        <v>73.44999694824219</v>
       </c>
       <c r="D194" t="n">
-        <v>71.80999755859375</v>
+        <v>71.62999725341797</v>
       </c>
       <c r="E194" t="n">
-        <v>72.87999725341797</v>
+        <v>71.83999633789062</v>
       </c>
       <c r="F194" t="n">
-        <v>82203300</v>
+        <v>48001500</v>
       </c>
       <c r="G194" t="n">
         <v>0</v>
@@ -5487,22 +5487,22 @@
     </row>
     <row r="195">
       <c r="A195" s="1" t="n">
-        <v>46196</v>
+        <v>46198</v>
       </c>
       <c r="B195" t="n">
-        <v>73.26000213623047</v>
+        <v>71.33000183105469</v>
       </c>
       <c r="C195" t="n">
-        <v>73.95999908447266</v>
+        <v>72.94000244140625</v>
       </c>
       <c r="D195" t="n">
-        <v>72.62999725341797</v>
+        <v>70.86000061035156</v>
       </c>
       <c r="E195" t="n">
-        <v>72.81999969482422</v>
+        <v>70.90000152587891</v>
       </c>
       <c r="F195" t="n">
-        <v>50806800</v>
+        <v>44446900</v>
       </c>
       <c r="G195" t="n">
         <v>0</v>
@@ -5513,22 +5513,22 @@
     </row>
     <row r="196">
       <c r="A196" s="1" t="n">
-        <v>46197</v>
+        <v>46199</v>
       </c>
       <c r="B196" t="n">
-        <v>72.69000244140625</v>
+        <v>71.69000244140625</v>
       </c>
       <c r="C196" t="n">
-        <v>73.44999694824219</v>
+        <v>75.19999694824219</v>
       </c>
       <c r="D196" t="n">
-        <v>71.62999725341797</v>
+        <v>71.52999877929688</v>
       </c>
       <c r="E196" t="n">
-        <v>71.83999633789062</v>
+        <v>73.80999755859375</v>
       </c>
       <c r="F196" t="n">
-        <v>48001500</v>
+        <v>74990300</v>
       </c>
       <c r="G196" t="n">
         <v>0</v>
@@ -5539,22 +5539,22 @@
     </row>
     <row r="197">
       <c r="A197" s="1" t="n">
-        <v>46198</v>
+        <v>46202</v>
       </c>
       <c r="B197" t="n">
-        <v>71.33000183105469</v>
+        <v>74.62000274658203</v>
       </c>
       <c r="C197" t="n">
-        <v>72.94000244140625</v>
+        <v>76.06999969482422</v>
       </c>
       <c r="D197" t="n">
-        <v>70.86000061035156</v>
+        <v>73.73000335693359</v>
       </c>
       <c r="E197" t="n">
-        <v>70.90000152587891</v>
+        <v>73.77999877929688</v>
       </c>
       <c r="F197" t="n">
-        <v>44446900</v>
+        <v>42429600</v>
       </c>
       <c r="G197" t="n">
         <v>0</v>
@@ -5565,22 +5565,22 @@
     </row>
     <row r="198">
       <c r="A198" s="1" t="n">
-        <v>46199</v>
+        <v>46203</v>
       </c>
       <c r="B198" t="n">
-        <v>71.69000244140625</v>
+        <v>73.58999633789062</v>
       </c>
       <c r="C198" t="n">
-        <v>75.19999694824219</v>
+        <v>73.75</v>
       </c>
       <c r="D198" t="n">
-        <v>71.52999877929688</v>
+        <v>71</v>
       </c>
       <c r="E198" t="n">
-        <v>73.80999755859375</v>
+        <v>71.40000152587891</v>
       </c>
       <c r="F198" t="n">
-        <v>74990300</v>
+        <v>49240900</v>
       </c>
       <c r="G198" t="n">
         <v>0</v>
@@ -5591,22 +5591,22 @@
     </row>
     <row r="199">
       <c r="A199" s="1" t="n">
-        <v>46202</v>
+        <v>46204</v>
       </c>
       <c r="B199" t="n">
-        <v>74.62000274658203</v>
+        <v>72.58999633789062</v>
       </c>
       <c r="C199" t="n">
-        <v>76.06999969482422</v>
+        <v>74.36000061035156</v>
       </c>
       <c r="D199" t="n">
-        <v>73.73000335693359</v>
+        <v>72.33000183105469</v>
       </c>
       <c r="E199" t="n">
-        <v>73.77999877929688</v>
+        <v>74.19000244140625</v>
       </c>
       <c r="F199" t="n">
-        <v>42429600</v>
+        <v>43841800</v>
       </c>
       <c r="G199" t="n">
         <v>0</v>
@@ -5617,22 +5617,22 @@
     </row>
     <row r="200">
       <c r="A200" s="1" t="n">
-        <v>46203</v>
+        <v>46205</v>
       </c>
       <c r="B200" t="n">
-        <v>73.58999633789062</v>
+        <v>75.08999633789062</v>
       </c>
       <c r="C200" t="n">
-        <v>73.75</v>
+        <v>78.44000244140625</v>
       </c>
       <c r="D200" t="n">
-        <v>71</v>
+        <v>74.91000366210938</v>
       </c>
       <c r="E200" t="n">
-        <v>71.40000152587891</v>
+        <v>77.65000152587891</v>
       </c>
       <c r="F200" t="n">
-        <v>49240900</v>
+        <v>55456500</v>
       </c>
       <c r="G200" t="n">
         <v>0</v>
@@ -5643,22 +5643,22 @@
     </row>
     <row r="201">
       <c r="A201" s="1" t="n">
-        <v>46204</v>
+        <v>46209</v>
       </c>
       <c r="B201" t="n">
-        <v>72.58999633789062</v>
+        <v>77.08000183105469</v>
       </c>
       <c r="C201" t="n">
-        <v>74.36000061035156</v>
+        <v>77.83999633789062</v>
       </c>
       <c r="D201" t="n">
-        <v>72.33000183105469</v>
+        <v>75.70999908447266</v>
       </c>
       <c r="E201" t="n">
-        <v>74.19000244140625</v>
+        <v>76.01999664306641</v>
       </c>
       <c r="F201" t="n">
-        <v>43841800</v>
+        <v>45056600</v>
       </c>
       <c r="G201" t="n">
         <v>0</v>
@@ -5669,22 +5669,22 @@
     </row>
     <row r="202">
       <c r="A202" s="1" t="n">
-        <v>46205</v>
+        <v>46210</v>
       </c>
       <c r="B202" t="n">
-        <v>75.08999633789062</v>
+        <v>77.87999725341797</v>
       </c>
       <c r="C202" t="n">
-        <v>78.44000244140625</v>
+        <v>78.19000244140625</v>
       </c>
       <c r="D202" t="n">
-        <v>74.91000366210938</v>
+        <v>76.09999847412109</v>
       </c>
       <c r="E202" t="n">
-        <v>77.65000152587891</v>
+        <v>76.18000030517578</v>
       </c>
       <c r="F202" t="n">
-        <v>55456500</v>
+        <v>33257300</v>
       </c>
       <c r="G202" t="n">
         <v>0</v>
@@ -5695,22 +5695,22 @@
     </row>
     <row r="203">
       <c r="A203" s="1" t="n">
-        <v>46209</v>
+        <v>46211</v>
       </c>
       <c r="B203" t="n">
-        <v>77.08000183105469</v>
+        <v>76.26999664306641</v>
       </c>
       <c r="C203" t="n">
-        <v>77.83999633789062</v>
+        <v>76.63999938964844</v>
       </c>
       <c r="D203" t="n">
-        <v>75.70999908447266</v>
+        <v>74.88999938964844</v>
       </c>
       <c r="E203" t="n">
-        <v>76.01999664306641</v>
+        <v>75.58999633789062</v>
       </c>
       <c r="F203" t="n">
-        <v>45056600</v>
+        <v>34373500</v>
       </c>
       <c r="G203" t="n">
         <v>0</v>
@@ -5721,22 +5721,22 @@
     </row>
     <row r="204">
       <c r="A204" s="1" t="n">
-        <v>46210</v>
+        <v>46212</v>
       </c>
       <c r="B204" t="n">
-        <v>77.87999725341797</v>
+        <v>74.30000305175781</v>
       </c>
       <c r="C204" t="n">
-        <v>78.19000244140625</v>
+        <v>75.55000305175781</v>
       </c>
       <c r="D204" t="n">
-        <v>76.09999847412109</v>
+        <v>74.01999664306641</v>
       </c>
       <c r="E204" t="n">
-        <v>76.18000030517578</v>
+        <v>75.47000122070312</v>
       </c>
       <c r="F204" t="n">
-        <v>33257300</v>
+        <v>36305700</v>
       </c>
       <c r="G204" t="n">
         <v>0</v>
@@ -5747,22 +5747,22 @@
     </row>
     <row r="205">
       <c r="A205" s="1" t="n">
-        <v>46211</v>
+        <v>46213</v>
       </c>
       <c r="B205" t="n">
-        <v>76.26999664306641</v>
+        <v>75.44000244140625</v>
       </c>
       <c r="C205" t="n">
-        <v>76.63999938964844</v>
+        <v>75.69999694824219</v>
       </c>
       <c r="D205" t="n">
-        <v>74.88999938964844</v>
+        <v>72.51000213623047</v>
       </c>
       <c r="E205" t="n">
-        <v>75.58999633789062</v>
+        <v>73.37000274658203</v>
       </c>
       <c r="F205" t="n">
-        <v>34373500</v>
+        <v>46713900</v>
       </c>
       <c r="G205" t="n">
         <v>0</v>
@@ -5773,22 +5773,22 @@
     </row>
     <row r="206">
       <c r="A206" s="1" t="n">
-        <v>46212</v>
+        <v>46216</v>
       </c>
       <c r="B206" t="n">
-        <v>74.30000305175781</v>
+        <v>73.90000152587891</v>
       </c>
       <c r="C206" t="n">
-        <v>75.55000305175781</v>
+        <v>75.44999694824219</v>
       </c>
       <c r="D206" t="n">
-        <v>74.01999664306641</v>
+        <v>73.70999908447266</v>
       </c>
       <c r="E206" t="n">
-        <v>75.47000122070312</v>
+        <v>73.83000183105469</v>
       </c>
       <c r="F206" t="n">
-        <v>36305700</v>
+        <v>35101800</v>
       </c>
       <c r="G206" t="n">
         <v>0</v>
@@ -5799,22 +5799,22 @@
     </row>
     <row r="207">
       <c r="A207" s="1" t="n">
-        <v>46213</v>
+        <v>46217</v>
       </c>
       <c r="B207" t="n">
-        <v>75.44000244140625</v>
+        <v>72.63999938964844</v>
       </c>
       <c r="C207" t="n">
-        <v>75.69999694824219</v>
+        <v>74.01000213623047</v>
       </c>
       <c r="D207" t="n">
-        <v>72.51000213623047</v>
+        <v>72.27999877929688</v>
       </c>
       <c r="E207" t="n">
-        <v>73.37000274658203</v>
+        <v>73.52999877929688</v>
       </c>
       <c r="F207" t="n">
-        <v>46713900</v>
+        <v>33312100</v>
       </c>
       <c r="G207" t="n">
         <v>0</v>
@@ -5825,22 +5825,22 @@
     </row>
     <row r="208">
       <c r="A208" s="1" t="n">
-        <v>46216</v>
+        <v>46218</v>
       </c>
       <c r="B208" t="n">
-        <v>73.90000152587891</v>
+        <v>73.79000091552734</v>
       </c>
       <c r="C208" t="n">
-        <v>75.44999694824219</v>
+        <v>75.05999755859375</v>
       </c>
       <c r="D208" t="n">
-        <v>73.70999908447266</v>
+        <v>73.12999725341797</v>
       </c>
       <c r="E208" t="n">
-        <v>73.83000183105469</v>
+        <v>73.68000030517578</v>
       </c>
       <c r="F208" t="n">
-        <v>35101800</v>
+        <v>32854300</v>
       </c>
       <c r="G208" t="n">
         <v>0</v>
@@ -5851,22 +5851,22 @@
     </row>
     <row r="209">
       <c r="A209" s="1" t="n">
-        <v>46217</v>
+        <v>46219</v>
       </c>
       <c r="B209" t="n">
-        <v>72.63999938964844</v>
+        <v>73.94999694824219</v>
       </c>
       <c r="C209" t="n">
-        <v>74.01000213623047</v>
+        <v>74.68000030517578</v>
       </c>
       <c r="D209" t="n">
-        <v>72.27999877929688</v>
+        <v>72.94000244140625</v>
       </c>
       <c r="E209" t="n">
-        <v>73.52999877929688</v>
+        <v>74.34999847412109</v>
       </c>
       <c r="F209" t="n">
-        <v>33312100</v>
+        <v>77505200</v>
       </c>
       <c r="G209" t="n">
         <v>0</v>
@@ -5877,22 +5877,22 @@
     </row>
     <row r="210">
       <c r="A210" s="1" t="n">
-        <v>46218</v>
+        <v>46220</v>
       </c>
       <c r="B210" t="n">
-        <v>73.79000091552734</v>
+        <v>65.48000335693359</v>
       </c>
       <c r="C210" t="n">
-        <v>75.05999755859375</v>
+        <v>69.48999786376953</v>
       </c>
       <c r="D210" t="n">
-        <v>73.12999725341797</v>
+        <v>65.08000183105469</v>
       </c>
       <c r="E210" t="n">
-        <v>73.68000030517578</v>
+        <v>68.94999694824219</v>
       </c>
       <c r="F210" t="n">
-        <v>32854300</v>
+        <v>142029200</v>
       </c>
       <c r="G210" t="n">
         <v>0</v>
@@ -5903,22 +5903,22 @@
     </row>
     <row r="211">
       <c r="A211" s="1" t="n">
-        <v>46219</v>
+        <v>46223</v>
       </c>
       <c r="B211" t="n">
-        <v>73.94999694824219</v>
+        <v>68.31999969482422</v>
       </c>
       <c r="C211" t="n">
-        <v>74.68000030517578</v>
+        <v>68.37999725341797</v>
       </c>
       <c r="D211" t="n">
-        <v>72.94000244140625</v>
+        <v>66.69000244140625</v>
       </c>
       <c r="E211" t="n">
-        <v>74.34999847412109</v>
+        <v>67.59999847412109</v>
       </c>
       <c r="F211" t="n">
-        <v>77505200</v>
+        <v>60669100</v>
       </c>
       <c r="G211" t="n">
         <v>0</v>
@@ -5929,22 +5929,22 @@
     </row>
     <row r="212">
       <c r="A212" s="1" t="n">
-        <v>46220</v>
+        <v>46224</v>
       </c>
       <c r="B212" t="n">
-        <v>65.48000335693359</v>
+        <v>67.41999816894531</v>
       </c>
       <c r="C212" t="n">
-        <v>69.48999786376953</v>
+        <v>68.75</v>
       </c>
       <c r="D212" t="n">
-        <v>65.08000183105469</v>
+        <v>66.73000335693359</v>
       </c>
       <c r="E212" t="n">
-        <v>68.94999694824219</v>
+        <v>68.66999816894531</v>
       </c>
       <c r="F212" t="n">
-        <v>142029200</v>
+        <v>56565800</v>
       </c>
       <c r="G212" t="n">
         <v>0</v>
@@ -5955,22 +5955,22 @@
     </row>
     <row r="213">
       <c r="A213" s="1" t="n">
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="B213" t="n">
-        <v>68.31999969482422</v>
+        <v>69.37000274658203</v>
       </c>
       <c r="C213" t="n">
-        <v>68.37999725341797</v>
+        <v>70.56999969482422</v>
       </c>
       <c r="D213" t="n">
-        <v>66.69000244140625</v>
+        <v>68.34999847412109</v>
       </c>
       <c r="E213" t="n">
-        <v>67.59999847412109</v>
+        <v>68.52999877929688</v>
       </c>
       <c r="F213" t="n">
-        <v>60669100</v>
+        <v>44947300</v>
       </c>
       <c r="G213" t="n">
         <v>0</v>
@@ -5981,22 +5981,22 @@
     </row>
     <row r="214">
       <c r="A214" s="1" t="n">
-        <v>46224</v>
+        <v>46226</v>
       </c>
       <c r="B214" t="n">
-        <v>67.41999816894531</v>
+        <v>68.56999969482422</v>
       </c>
       <c r="C214" t="n">
-        <v>68.75</v>
+        <v>69.36000061035156</v>
       </c>
       <c r="D214" t="n">
-        <v>66.73000335693359</v>
+        <v>67.66999816894531</v>
       </c>
       <c r="E214" t="n">
-        <v>68.66999816894531</v>
+        <v>68.88999938964844</v>
       </c>
       <c r="F214" t="n">
-        <v>56565800</v>
+        <v>45029100</v>
       </c>
       <c r="G214" t="n">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="215">
       <c r="A215" s="1" t="n">
-        <v>46225</v>
+        <v>46227</v>
       </c>
       <c r="B215" t="n">
-        <v>69.37000274658203</v>
+        <v>69.29000091552734</v>
       </c>
       <c r="C215" t="n">
-        <v>70.56999969482422</v>
+        <v>70.68000030517578</v>
       </c>
       <c r="D215" t="n">
-        <v>68.34999847412109</v>
+        <v>67.97000122070312</v>
       </c>
       <c r="E215" t="n">
-        <v>68.52999877929688</v>
+        <v>70.08999633789062</v>
       </c>
       <c r="F215" t="n">
-        <v>44947300</v>
+        <v>37593500</v>
       </c>
       <c r="G215" t="n">
         <v>0</v>
@@ -6033,22 +6033,22 @@
     </row>
     <row r="216">
       <c r="A216" s="1" t="n">
-        <v>46226</v>
+        <v>46230</v>
       </c>
       <c r="B216" t="n">
-        <v>68.56999969482422</v>
+        <v>70.58999633789062</v>
       </c>
       <c r="C216" t="n">
-        <v>69.36000061035156</v>
+        <v>71.65000152587891</v>
       </c>
       <c r="D216" t="n">
-        <v>67.66999816894531</v>
+        <v>69.86000061035156</v>
       </c>
       <c r="E216" t="n">
-        <v>68.88999938964844</v>
+        <v>70.40000152587891</v>
       </c>
       <c r="F216" t="n">
-        <v>45029100</v>
+        <v>39090800</v>
       </c>
       <c r="G216" t="n">
         <v>0</v>
@@ -6059,22 +6059,22 @@
     </row>
     <row r="217">
       <c r="A217" s="1" t="n">
-        <v>46227</v>
+        <v>46231</v>
       </c>
       <c r="B217" t="n">
-        <v>69.29000091552734</v>
+        <v>72.06999969482422</v>
       </c>
       <c r="C217" t="n">
-        <v>70.68000030517578</v>
+        <v>73.76000213623047</v>
       </c>
       <c r="D217" t="n">
-        <v>67.97000122070312</v>
+        <v>71.23000335693359</v>
       </c>
       <c r="E217" t="n">
-        <v>70.08999633789062</v>
+        <v>72.38999938964844</v>
       </c>
       <c r="F217" t="n">
-        <v>37593500</v>
+        <v>47160200</v>
       </c>
       <c r="G217" t="n">
         <v>0</v>
@@ -6085,22 +6085,22 @@
     </row>
     <row r="218">
       <c r="A218" s="1" t="n">
-        <v>46230</v>
+        <v>46232</v>
       </c>
       <c r="B218" t="n">
-        <v>70.58999633789062</v>
+        <v>72.19000244140625</v>
       </c>
       <c r="C218" t="n">
-        <v>71.65000152587891</v>
+        <v>73.73999786376953</v>
       </c>
       <c r="D218" t="n">
-        <v>69.86000061035156</v>
+        <v>71.75</v>
       </c>
       <c r="E218" t="n">
-        <v>70.40000152587891</v>
+        <v>73.62999725341797</v>
       </c>
       <c r="F218" t="n">
-        <v>39090800</v>
+        <v>43737600</v>
       </c>
       <c r="G218" t="n">
         <v>0</v>
@@ -6111,22 +6111,22 @@
     </row>
     <row r="219">
       <c r="A219" s="1" t="n">
-        <v>46231</v>
+        <v>46233</v>
       </c>
       <c r="B219" t="n">
-        <v>72.06999969482422</v>
+        <v>71.48000335693359</v>
       </c>
       <c r="C219" t="n">
-        <v>73.76000213623047</v>
+        <v>73.31999969482422</v>
       </c>
       <c r="D219" t="n">
-        <v>71.23000335693359</v>
+        <v>70.55000305175781</v>
       </c>
       <c r="E219" t="n">
-        <v>72.38999938964844</v>
+        <v>73.16999816894531</v>
       </c>
       <c r="F219" t="n">
-        <v>47160200</v>
+        <v>54261000</v>
       </c>
       <c r="G219" t="n">
         <v>0</v>
@@ -6137,22 +6137,22 @@
     </row>
     <row r="220">
       <c r="A220" s="1" t="n">
-        <v>46232</v>
+        <v>46234</v>
       </c>
       <c r="B220" t="n">
-        <v>72.19000244140625</v>
+        <v>71.97000122070312</v>
       </c>
       <c r="C220" t="n">
-        <v>73.73999786376953</v>
+        <v>72.75</v>
       </c>
       <c r="D220" t="n">
-        <v>71.75</v>
+        <v>71.11000061035156</v>
       </c>
       <c r="E220" t="n">
-        <v>73.62999725341797</v>
+        <v>71.70999908447266</v>
       </c>
       <c r="F220" t="n">
-        <v>43737600</v>
+        <v>35847500</v>
       </c>
       <c r="G220" t="n">
         <v>0</v>
@@ -6163,22 +6163,22 @@
     </row>
     <row r="221">
       <c r="A221" s="1" t="n">
-        <v>46233</v>
+        <v>46237</v>
       </c>
       <c r="B221" t="n">
-        <v>71.48000335693359</v>
+        <v>72.76999664306641</v>
       </c>
       <c r="C221" t="n">
-        <v>73.31999969482422</v>
+        <v>73.94999694824219</v>
       </c>
       <c r="D221" t="n">
-        <v>70.55000305175781</v>
+        <v>72.18000030517578</v>
       </c>
       <c r="E221" t="n">
-        <v>73.16999816894531</v>
+        <v>73.33000183105469</v>
       </c>
       <c r="F221" t="n">
-        <v>54261000</v>
+        <v>33922300</v>
       </c>
       <c r="G221" t="n">
         <v>0</v>
@@ -6189,22 +6189,22 @@
     </row>
     <row r="222">
       <c r="A222" s="1" t="n">
-        <v>46234</v>
+        <v>46238</v>
       </c>
       <c r="B222" t="n">
-        <v>71.97000122070312</v>
+        <v>72.51000213623047</v>
       </c>
       <c r="C222" t="n">
-        <v>72.75</v>
+        <v>73.75</v>
       </c>
       <c r="D222" t="n">
-        <v>71.11000061035156</v>
+        <v>72.30000305175781</v>
       </c>
       <c r="E222" t="n">
-        <v>71.70999908447266</v>
+        <v>73.56999969482422</v>
       </c>
       <c r="F222" t="n">
-        <v>35847500</v>
+        <v>42877900</v>
       </c>
       <c r="G222" t="n">
         <v>0</v>
@@ -6215,22 +6215,22 @@
     </row>
     <row r="223">
       <c r="A223" s="1" t="n">
-        <v>46237</v>
+        <v>46239</v>
       </c>
       <c r="B223" t="n">
-        <v>72.76999664306641</v>
+        <v>75.11000061035156</v>
       </c>
       <c r="C223" t="n">
-        <v>73.94999694824219</v>
+        <v>75.30000305175781</v>
       </c>
       <c r="D223" t="n">
-        <v>72.18000030517578</v>
+        <v>73.16000366210938</v>
       </c>
       <c r="E223" t="n">
-        <v>73.33000183105469</v>
+        <v>74.19999694824219</v>
       </c>
       <c r="F223" t="n">
-        <v>33922300</v>
+        <v>28969400</v>
       </c>
       <c r="G223" t="n">
         <v>0</v>
@@ -6241,22 +6241,22 @@
     </row>
     <row r="224">
       <c r="A224" s="1" t="n">
-        <v>46238</v>
+        <v>46240</v>
       </c>
       <c r="B224" t="n">
-        <v>72.51000213623047</v>
+        <v>75.13999938964844</v>
       </c>
       <c r="C224" t="n">
-        <v>73.75</v>
+        <v>75.20999908447266</v>
       </c>
       <c r="D224" t="n">
-        <v>72.30000305175781</v>
+        <v>73.09999847412109</v>
       </c>
       <c r="E224" t="n">
-        <v>73.56999969482422</v>
+        <v>73.69000244140625</v>
       </c>
       <c r="F224" t="n">
-        <v>42877900</v>
+        <v>28892700</v>
       </c>
       <c r="G224" t="n">
         <v>0</v>
@@ -6267,22 +6267,22 @@
     </row>
     <row r="225">
       <c r="A225" s="1" t="n">
-        <v>46239</v>
+        <v>46241</v>
       </c>
       <c r="B225" t="n">
-        <v>75.11000061035156</v>
+        <v>73.12000274658203</v>
       </c>
       <c r="C225" t="n">
-        <v>75.30000305175781</v>
+        <v>74.5</v>
       </c>
       <c r="D225" t="n">
-        <v>73.16000366210938</v>
+        <v>73.08000183105469</v>
       </c>
       <c r="E225" t="n">
-        <v>74.19999694824219</v>
+        <v>74.13999938964844</v>
       </c>
       <c r="F225" t="n">
-        <v>28969400</v>
+        <v>24819000</v>
       </c>
       <c r="G225" t="n">
         <v>0</v>
@@ -6293,22 +6293,22 @@
     </row>
     <row r="226">
       <c r="A226" s="1" t="n">
-        <v>46240</v>
+        <v>46244</v>
       </c>
       <c r="B226" t="n">
-        <v>75.13999938964844</v>
+        <v>73.80000305175781</v>
       </c>
       <c r="C226" t="n">
-        <v>75.20999908447266</v>
+        <v>76.31999969482422</v>
       </c>
       <c r="D226" t="n">
-        <v>73.09999847412109</v>
+        <v>73.56999969482422</v>
       </c>
       <c r="E226" t="n">
-        <v>73.69000244140625</v>
+        <v>76.29000091552734</v>
       </c>
       <c r="F226" t="n">
-        <v>28892700</v>
+        <v>26959900</v>
       </c>
       <c r="G226" t="n">
         <v>0</v>
@@ -6319,22 +6319,22 @@
     </row>
     <row r="227">
       <c r="A227" s="1" t="n">
-        <v>46241</v>
+        <v>46245</v>
       </c>
       <c r="B227" t="n">
-        <v>73.12000274658203</v>
+        <v>76.19999694824219</v>
       </c>
       <c r="C227" t="n">
-        <v>74.5</v>
+        <v>76.90000152587891</v>
       </c>
       <c r="D227" t="n">
-        <v>73.08000183105469</v>
+        <v>74.48000335693359</v>
       </c>
       <c r="E227" t="n">
-        <v>74.13999938964844</v>
+        <v>74.79000091552734</v>
       </c>
       <c r="F227" t="n">
-        <v>24819000</v>
+        <v>27840500</v>
       </c>
       <c r="G227" t="n">
         <v>0</v>
@@ -6345,22 +6345,22 @@
     </row>
     <row r="228">
       <c r="A228" s="1" t="n">
-        <v>46244</v>
+        <v>46246</v>
       </c>
       <c r="B228" t="n">
-        <v>73.80000305175781</v>
+        <v>74.34999847412109</v>
       </c>
       <c r="C228" t="n">
-        <v>76.31999969482422</v>
+        <v>74.66999816894531</v>
       </c>
       <c r="D228" t="n">
         <v>73.56999969482422</v>
       </c>
       <c r="E228" t="n">
-        <v>76.29000091552734</v>
+        <v>74.20999908447266</v>
       </c>
       <c r="F228" t="n">
-        <v>26959900</v>
+        <v>20773100</v>
       </c>
       <c r="G228" t="n">
         <v>0</v>
@@ -6371,22 +6371,22 @@
     </row>
     <row r="229">
       <c r="A229" s="1" t="n">
-        <v>46245</v>
+        <v>46247</v>
       </c>
       <c r="B229" t="n">
-        <v>76.19999694824219</v>
+        <v>76.01000213623047</v>
       </c>
       <c r="C229" t="n">
-        <v>76.90000152587891</v>
+        <v>78.40000152587891</v>
       </c>
       <c r="D229" t="n">
-        <v>74.48000335693359</v>
+        <v>75.44000244140625</v>
       </c>
       <c r="E229" t="n">
-        <v>74.79000091552734</v>
+        <v>78.23999786376953</v>
       </c>
       <c r="F229" t="n">
-        <v>27840500</v>
+        <v>41452900</v>
       </c>
       <c r="G229" t="n">
         <v>0</v>
@@ -6397,22 +6397,22 @@
     </row>
     <row r="230">
       <c r="A230" s="1" t="n">
-        <v>46246</v>
+        <v>46248</v>
       </c>
       <c r="B230" t="n">
-        <v>74.34999847412109</v>
+        <v>78.48000335693359</v>
       </c>
       <c r="C230" t="n">
-        <v>74.66999816894531</v>
+        <v>78.73000335693359</v>
       </c>
       <c r="D230" t="n">
-        <v>73.56999969482422</v>
+        <v>77.76000213623047</v>
       </c>
       <c r="E230" t="n">
-        <v>74.20999908447266</v>
+        <v>78.16000366210938</v>
       </c>
       <c r="F230" t="n">
-        <v>20773100</v>
+        <v>26751000</v>
       </c>
       <c r="G230" t="n">
         <v>0</v>
@@ -6423,22 +6423,22 @@
     </row>
     <row r="231">
       <c r="A231" s="1" t="n">
-        <v>46247</v>
+        <v>46251</v>
       </c>
       <c r="B231" t="n">
-        <v>76.01000213623047</v>
+        <v>77.80000305175781</v>
       </c>
       <c r="C231" t="n">
-        <v>78.40000152587891</v>
+        <v>78.52999877929688</v>
       </c>
       <c r="D231" t="n">
-        <v>75.44000244140625</v>
+        <v>75.47000122070312</v>
       </c>
       <c r="E231" t="n">
-        <v>78.23999786376953</v>
+        <v>76.01999664306641</v>
       </c>
       <c r="F231" t="n">
-        <v>41452900</v>
+        <v>30753000</v>
       </c>
       <c r="G231" t="n">
         <v>0</v>
@@ -6449,22 +6449,22 @@
     </row>
     <row r="232">
       <c r="A232" s="1" t="n">
-        <v>46248</v>
+        <v>46252</v>
       </c>
       <c r="B232" t="n">
-        <v>78.48000335693359</v>
+        <v>77.43000030517578</v>
       </c>
       <c r="C232" t="n">
-        <v>78.73000335693359</v>
+        <v>79.09999847412109</v>
       </c>
       <c r="D232" t="n">
-        <v>77.76000213623047</v>
+        <v>76.33999633789062</v>
       </c>
       <c r="E232" t="n">
-        <v>78.16000366210938</v>
+        <v>77.76999664306641</v>
       </c>
       <c r="F232" t="n">
-        <v>26751000</v>
+        <v>36151300</v>
       </c>
       <c r="G232" t="n">
         <v>0</v>
@@ -6475,22 +6475,22 @@
     </row>
     <row r="233">
       <c r="A233" s="1" t="n">
-        <v>46251</v>
+        <v>46253</v>
       </c>
       <c r="B233" t="n">
-        <v>77.80000305175781</v>
+        <v>78.25</v>
       </c>
       <c r="C233" t="n">
-        <v>78.52999877929688</v>
+        <v>81.16000366210938</v>
       </c>
       <c r="D233" t="n">
-        <v>75.47000122070312</v>
+        <v>78.09999847412109</v>
       </c>
       <c r="E233" t="n">
-        <v>76.01999664306641</v>
+        <v>80.22000122070312</v>
       </c>
       <c r="F233" t="n">
-        <v>30753000</v>
+        <v>31461800</v>
       </c>
       <c r="G233" t="n">
         <v>0</v>
@@ -6501,22 +6501,22 @@
     </row>
     <row r="234">
       <c r="A234" s="1" t="n">
-        <v>46252</v>
+        <v>46254</v>
       </c>
       <c r="B234" t="n">
-        <v>77.43000030517578</v>
+        <v>80.13999938964844</v>
       </c>
       <c r="C234" t="n">
-        <v>79.09999847412109</v>
+        <v>81.08000183105469</v>
       </c>
       <c r="D234" t="n">
-        <v>76.33999633789062</v>
+        <v>79.58999633789062</v>
       </c>
       <c r="E234" t="n">
-        <v>77.76999664306641</v>
+        <v>80.13999938964844</v>
       </c>
       <c r="F234" t="n">
-        <v>36151300</v>
+        <v>27118400</v>
       </c>
       <c r="G234" t="n">
         <v>0</v>
@@ -6527,22 +6527,22 @@
     </row>
     <row r="235">
       <c r="A235" s="1" t="n">
-        <v>46253</v>
+        <v>46255</v>
       </c>
       <c r="B235" t="n">
-        <v>78.25</v>
+        <v>80.29000091552734</v>
       </c>
       <c r="C235" t="n">
-        <v>81.16000366210938</v>
+        <v>80.48999786376953</v>
       </c>
       <c r="D235" t="n">
-        <v>78.09999847412109</v>
+        <v>79.16999816894531</v>
       </c>
       <c r="E235" t="n">
-        <v>80.22000122070312</v>
+        <v>79.58999633789062</v>
       </c>
       <c r="F235" t="n">
-        <v>31461800</v>
+        <v>23773800</v>
       </c>
       <c r="G235" t="n">
         <v>0</v>
@@ -6553,22 +6553,22 @@
     </row>
     <row r="236">
       <c r="A236" s="1" t="n">
-        <v>46254</v>
+        <v>46258</v>
       </c>
       <c r="B236" t="n">
-        <v>80.13999938964844</v>
+        <v>79.94000244140625</v>
       </c>
       <c r="C236" t="n">
-        <v>81.08000183105469</v>
+        <v>80.62000274658203</v>
       </c>
       <c r="D236" t="n">
-        <v>79.58999633789062</v>
+        <v>79.01999664306641</v>
       </c>
       <c r="E236" t="n">
-        <v>80.13999938964844</v>
+        <v>80.01000213623047</v>
       </c>
       <c r="F236" t="n">
-        <v>27118400</v>
+        <v>21085300</v>
       </c>
       <c r="G236" t="n">
         <v>0</v>
@@ -6579,22 +6579,22 @@
     </row>
     <row r="237">
       <c r="A237" s="1" t="n">
-        <v>46255</v>
+        <v>46259</v>
       </c>
       <c r="B237" t="n">
-        <v>80.29000091552734</v>
+        <v>79.65000152587891</v>
       </c>
       <c r="C237" t="n">
-        <v>80.48999786376953</v>
+        <v>82.45999908447266</v>
       </c>
       <c r="D237" t="n">
-        <v>79.16999816894531</v>
+        <v>79.40000152587891</v>
       </c>
       <c r="E237" t="n">
-        <v>79.58999633789062</v>
+        <v>82.23000335693359</v>
       </c>
       <c r="F237" t="n">
-        <v>23773800</v>
+        <v>29462000</v>
       </c>
       <c r="G237" t="n">
         <v>0</v>
@@ -6605,22 +6605,22 @@
     </row>
     <row r="238">
       <c r="A238" s="1" t="n">
-        <v>46258</v>
+        <v>46260</v>
       </c>
       <c r="B238" t="n">
-        <v>79.94000244140625</v>
+        <v>82.05000305175781</v>
       </c>
       <c r="C238" t="n">
-        <v>80.62000274658203</v>
+        <v>82.41999816894531</v>
       </c>
       <c r="D238" t="n">
-        <v>79.01999664306641</v>
+        <v>81.30000305175781</v>
       </c>
       <c r="E238" t="n">
-        <v>80.01000213623047</v>
+        <v>81.45999908447266</v>
       </c>
       <c r="F238" t="n">
-        <v>21085300</v>
+        <v>22874900</v>
       </c>
       <c r="G238" t="n">
         <v>0</v>
@@ -6631,22 +6631,22 @@
     </row>
     <row r="239">
       <c r="A239" s="1" t="n">
-        <v>46259</v>
+        <v>46261</v>
       </c>
       <c r="B239" t="n">
-        <v>79.65000152587891</v>
+        <v>81.06999969482422</v>
       </c>
       <c r="C239" t="n">
-        <v>82.45999908447266</v>
+        <v>81.15000152587891</v>
       </c>
       <c r="D239" t="n">
-        <v>79.40000152587891</v>
+        <v>79.27999877929688</v>
       </c>
       <c r="E239" t="n">
-        <v>82.23000335693359</v>
+        <v>79.83999633789062</v>
       </c>
       <c r="F239" t="n">
-        <v>29462000</v>
+        <v>27174400</v>
       </c>
       <c r="G239" t="n">
         <v>0</v>
@@ -6657,22 +6657,22 @@
     </row>
     <row r="240">
       <c r="A240" s="1" t="n">
-        <v>46260</v>
+        <v>46262</v>
       </c>
       <c r="B240" t="n">
-        <v>82.05000305175781</v>
+        <v>80.36000061035156</v>
       </c>
       <c r="C240" t="n">
-        <v>82.41999816894531</v>
+        <v>82.34999847412109</v>
       </c>
       <c r="D240" t="n">
-        <v>81.30000305175781</v>
+        <v>79.94999694824219</v>
       </c>
       <c r="E240" t="n">
-        <v>81.45999908447266</v>
+        <v>81.72000122070312</v>
       </c>
       <c r="F240" t="n">
-        <v>22874900</v>
+        <v>29092700</v>
       </c>
       <c r="G240" t="n">
         <v>0</v>
@@ -6683,22 +6683,22 @@
     </row>
     <row r="241">
       <c r="A241" s="1" t="n">
-        <v>46261</v>
+        <v>46265</v>
       </c>
       <c r="B241" t="n">
-        <v>81.06999969482422</v>
+        <v>81</v>
       </c>
       <c r="C241" t="n">
-        <v>81.15000152587891</v>
+        <v>81.73000335693359</v>
       </c>
       <c r="D241" t="n">
-        <v>79.27999877929688</v>
+        <v>80.65000152587891</v>
       </c>
       <c r="E241" t="n">
-        <v>79.83999633789062</v>
+        <v>81.05000305175781</v>
       </c>
       <c r="F241" t="n">
-        <v>27174400</v>
+        <v>30740800</v>
       </c>
       <c r="G241" t="n">
         <v>0</v>
@@ -6709,22 +6709,22 @@
     </row>
     <row r="242">
       <c r="A242" s="1" t="n">
-        <v>46262</v>
+        <v>46266</v>
       </c>
       <c r="B242" t="n">
-        <v>80.36000061035156</v>
+        <v>80.16999816894531</v>
       </c>
       <c r="C242" t="n">
-        <v>82.34999847412109</v>
+        <v>82.12999725341797</v>
       </c>
       <c r="D242" t="n">
-        <v>79.94999694824219</v>
+        <v>79.59999847412109</v>
       </c>
       <c r="E242" t="n">
-        <v>81.72000122070312</v>
+        <v>80.80999755859375</v>
       </c>
       <c r="F242" t="n">
-        <v>29092700</v>
+        <v>21164900</v>
       </c>
       <c r="G242" t="n">
         <v>0</v>
@@ -6735,22 +6735,22 @@
     </row>
     <row r="243">
       <c r="A243" s="1" t="n">
-        <v>46265</v>
+        <v>46267</v>
       </c>
       <c r="B243" t="n">
-        <v>81</v>
+        <v>80.55000305175781</v>
       </c>
       <c r="C243" t="n">
-        <v>81.73000335693359</v>
+        <v>83.12000274658203</v>
       </c>
       <c r="D243" t="n">
-        <v>80.65000152587891</v>
+        <v>80.30000305175781</v>
       </c>
       <c r="E243" t="n">
-        <v>81.05000305175781</v>
+        <v>82.73000335693359</v>
       </c>
       <c r="F243" t="n">
-        <v>30740800</v>
+        <v>22077800</v>
       </c>
       <c r="G243" t="n">
         <v>0</v>
@@ -6761,22 +6761,22 @@
     </row>
     <row r="244">
       <c r="A244" s="1" t="n">
-        <v>46266</v>
+        <v>46268</v>
       </c>
       <c r="B244" t="n">
-        <v>80.16999816894531</v>
+        <v>83.18000030517578</v>
       </c>
       <c r="C244" t="n">
-        <v>82.12999725341797</v>
+        <v>83.59999847412109</v>
       </c>
       <c r="D244" t="n">
-        <v>79.59999847412109</v>
+        <v>81.62999725341797</v>
       </c>
       <c r="E244" t="n">
-        <v>80.80999755859375</v>
+        <v>82.66999816894531</v>
       </c>
       <c r="F244" t="n">
-        <v>21164900</v>
+        <v>24006400</v>
       </c>
       <c r="G244" t="n">
         <v>0</v>
@@ -6787,22 +6787,22 @@
     </row>
     <row r="245">
       <c r="A245" s="1" t="n">
-        <v>46267</v>
+        <v>46269</v>
       </c>
       <c r="B245" t="n">
-        <v>80.55000305175781</v>
+        <v>82.16999816894531</v>
       </c>
       <c r="C245" t="n">
-        <v>83.12000274658203</v>
+        <v>82.69000244140625</v>
       </c>
       <c r="D245" t="n">
-        <v>80.30000305175781</v>
+        <v>78.23000335693359</v>
       </c>
       <c r="E245" t="n">
-        <v>82.73000335693359</v>
+        <v>78.25</v>
       </c>
       <c r="F245" t="n">
-        <v>22077800</v>
+        <v>40190000</v>
       </c>
       <c r="G245" t="n">
         <v>0</v>
@@ -6813,22 +6813,22 @@
     </row>
     <row r="246">
       <c r="A246" s="1" t="n">
-        <v>46268</v>
+        <v>46273</v>
       </c>
       <c r="B246" t="n">
-        <v>83.18000030517578</v>
+        <v>77.55000305175781</v>
       </c>
       <c r="C246" t="n">
-        <v>83.59999847412109</v>
+        <v>77.73000335693359</v>
       </c>
       <c r="D246" t="n">
-        <v>81.62999725341797</v>
+        <v>75.91999816894531</v>
       </c>
       <c r="E246" t="n">
-        <v>82.66999816894531</v>
+        <v>76.76999664306641</v>
       </c>
       <c r="F246" t="n">
-        <v>24006400</v>
+        <v>33865500</v>
       </c>
       <c r="G246" t="n">
         <v>0</v>
@@ -6839,22 +6839,22 @@
     </row>
     <row r="247">
       <c r="A247" s="1" t="n">
-        <v>46269</v>
+        <v>46274</v>
       </c>
       <c r="B247" t="n">
-        <v>82.16999816894531</v>
+        <v>76.33999633789062</v>
       </c>
       <c r="C247" t="n">
-        <v>82.69000244140625</v>
+        <v>76.72000122070312</v>
       </c>
       <c r="D247" t="n">
-        <v>78.23000335693359</v>
+        <v>75.87000274658203</v>
       </c>
       <c r="E247" t="n">
-        <v>78.25</v>
+        <v>76.02999877929688</v>
       </c>
       <c r="F247" t="n">
-        <v>40190000</v>
+        <v>22779600</v>
       </c>
       <c r="G247" t="n">
         <v>0</v>
@@ -6865,22 +6865,22 @@
     </row>
     <row r="248">
       <c r="A248" s="1" t="n">
-        <v>46273</v>
+        <v>46275</v>
       </c>
       <c r="B248" t="n">
-        <v>77.55000305175781</v>
+        <v>75.33000183105469</v>
       </c>
       <c r="C248" t="n">
-        <v>77.73000335693359</v>
+        <v>76.30000305175781</v>
       </c>
       <c r="D248" t="n">
-        <v>75.91999816894531</v>
+        <v>75.02999877929688</v>
       </c>
       <c r="E248" t="n">
-        <v>76.76999664306641</v>
+        <v>76.01000213623047</v>
       </c>
       <c r="F248" t="n">
-        <v>33865500</v>
+        <v>20049000</v>
       </c>
       <c r="G248" t="n">
         <v>0</v>
@@ -6891,22 +6891,22 @@
     </row>
     <row r="249">
       <c r="A249" s="1" t="n">
-        <v>46274</v>
+        <v>46276</v>
       </c>
       <c r="B249" t="n">
-        <v>76.33999633789062</v>
+        <v>76.63999938964844</v>
       </c>
       <c r="C249" t="n">
-        <v>76.72000122070312</v>
+        <v>77.56999969482422</v>
       </c>
       <c r="D249" t="n">
-        <v>75.87000274658203</v>
+        <v>76.15000152587891</v>
       </c>
       <c r="E249" t="n">
-        <v>76.02999877929688</v>
+        <v>77.40000152587891</v>
       </c>
       <c r="F249" t="n">
-        <v>22779600</v>
+        <v>22237800</v>
       </c>
       <c r="G249" t="n">
         <v>0</v>
@@ -6917,22 +6917,22 @@
     </row>
     <row r="250">
       <c r="A250" s="1" t="n">
-        <v>46275</v>
+        <v>46279</v>
       </c>
       <c r="B250" t="n">
-        <v>75.33000183105469</v>
+        <v>78.97000122070312</v>
       </c>
       <c r="C250" t="n">
-        <v>76.30000305175781</v>
+        <v>81.01999664306641</v>
       </c>
       <c r="D250" t="n">
-        <v>75.02999877929688</v>
+        <v>78.48999786376953</v>
       </c>
       <c r="E250" t="n">
-        <v>76.01000213623047</v>
+        <v>80.31999969482422</v>
       </c>
       <c r="F250" t="n">
-        <v>20049000</v>
+        <v>30945100</v>
       </c>
       <c r="G250" t="n">
         <v>0</v>
@@ -6943,22 +6943,22 @@
     </row>
     <row r="251">
       <c r="A251" s="1" t="n">
-        <v>46276</v>
+        <v>46280</v>
       </c>
       <c r="B251" t="n">
-        <v>76.63999938964844</v>
+        <v>79.37999725341797</v>
       </c>
       <c r="C251" t="n">
-        <v>77.56999969482422</v>
+        <v>79.48000335693359</v>
       </c>
       <c r="D251" t="n">
-        <v>76.15000152587891</v>
+        <v>77.45999908447266</v>
       </c>
       <c r="E251" t="n">
-        <v>77.40000152587891</v>
+        <v>77.90000152587891</v>
       </c>
       <c r="F251" t="n">
-        <v>22237800</v>
+        <v>28027400</v>
       </c>
       <c r="G251" t="n">
         <v>0</v>
@@ -6969,22 +6969,14 @@
     </row>
     <row r="252">
       <c r="A252" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="B252" t="n">
-        <v>78.97000122070312</v>
-      </c>
-      <c r="C252" t="n">
-        <v>81.01999664306641</v>
-      </c>
-      <c r="D252" t="n">
-        <v>78.48999786376953</v>
-      </c>
-      <c r="E252" t="n">
-        <v>80.31999969482422</v>
-      </c>
+        <v>46281</v>
+      </c>
+      <c r="B252" t="inlineStr"/>
+      <c r="C252" t="inlineStr"/>
+      <c r="D252" t="inlineStr"/>
+      <c r="E252" t="inlineStr"/>
       <c r="F252" t="n">
-        <v>30909600</v>
+        <v>25306049</v>
       </c>
       <c r="G252" t="n">
         <v>0</v>
@@ -10414,37 +10406,37 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>80.31999999999999</v>
+        <v>76.41</v>
       </c>
       <c r="D2" t="n">
-        <v>77.40000000000001</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="E2" t="n">
-        <v>78.97</v>
+        <v>77.8</v>
       </c>
       <c r="F2" t="n">
-        <v>81.01000000000001</v>
+        <v>77.8</v>
       </c>
       <c r="G2" t="n">
-        <v>78.48999999999999</v>
+        <v>76.31</v>
       </c>
       <c r="H2" t="n">
-        <v>30614406</v>
+        <v>25306049</v>
       </c>
       <c r="I2" t="n">
-        <v>40974760</v>
+        <v>40215100</v>
       </c>
       <c r="J2" t="n">
-        <v>334447640576</v>
+        <v>318166630400</v>
       </c>
       <c r="K2" t="n">
-        <v>25.25786</v>
+        <v>24.490387</v>
       </c>
       <c r="L2" t="n">
-        <v>21.02117</v>
+        <v>19.997854</v>
       </c>
       <c r="M2" t="n">
-        <v>3.18</v>
+        <v>3.12</v>
       </c>
       <c r="N2" t="n">
         <v>124.86</v>
@@ -10482,7 +10474,7 @@
         <v>7.241</v>
       </c>
       <c r="Y2" t="n">
-        <v>11.09239</v>
+        <v>10.55241</v>
       </c>
       <c r="Z2" t="n">
         <v>0.111</v>
@@ -10494,7 +10486,7 @@
         <v>48370765824</v>
       </c>
       <c r="AC2" t="n">
-        <v>341974384640</v>
+        <v>325693374464</v>
       </c>
       <c r="AD2" t="n">
         <v>14726931456</v>
@@ -10521,7 +10513,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>2026-09-15 14:14:42</t>
+          <t>2026-09-17 08:10:29</t>
         </is>
       </c>
     </row>

--- a/data/NFLX_data.xlsx
+++ b/data/NFLX_data.xlsx
@@ -469,22 +469,22 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45917</v>
+        <v>45918</v>
       </c>
       <c r="B2" t="n">
-        <v>122.1019973754883</v>
+        <v>122.0820007324219</v>
       </c>
       <c r="C2" t="n">
-        <v>123.3929977416992</v>
+        <v>123.3000030517578</v>
       </c>
       <c r="D2" t="n">
-        <v>120.661003112793</v>
+        <v>120.5500030517578</v>
       </c>
       <c r="E2" t="n">
-        <v>122.8499984741211</v>
+        <v>120.7779998779297</v>
       </c>
       <c r="F2" t="n">
-        <v>34598000</v>
+        <v>31691000</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -495,22 +495,22 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45918</v>
+        <v>45919</v>
       </c>
       <c r="B3" t="n">
-        <v>122.0820007324219</v>
+        <v>121.8619995117188</v>
       </c>
       <c r="C3" t="n">
-        <v>123.3000030517578</v>
+        <v>122.995002746582</v>
       </c>
       <c r="D3" t="n">
-        <v>120.5500030517578</v>
+        <v>120.8099975585938</v>
       </c>
       <c r="E3" t="n">
-        <v>120.7779998779297</v>
+        <v>122.6969985961914</v>
       </c>
       <c r="F3" t="n">
-        <v>31691000</v>
+        <v>49476000</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -521,22 +521,22 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>45919</v>
+        <v>45922</v>
       </c>
       <c r="B4" t="n">
-        <v>121.8619995117188</v>
+        <v>122.1900024414062</v>
       </c>
       <c r="C4" t="n">
-        <v>122.995002746582</v>
+        <v>122.9759979248047</v>
       </c>
       <c r="D4" t="n">
-        <v>120.8099975585938</v>
+        <v>121.4240036010742</v>
       </c>
       <c r="E4" t="n">
-        <v>122.6969985961914</v>
+        <v>122.7369995117188</v>
       </c>
       <c r="F4" t="n">
-        <v>49476000</v>
+        <v>25468000</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -547,22 +547,22 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>45922</v>
+        <v>45923</v>
       </c>
       <c r="B5" t="n">
-        <v>122.1900024414062</v>
+        <v>122.7330017089844</v>
       </c>
       <c r="C5" t="n">
-        <v>122.9759979248047</v>
+        <v>122.7789993286133</v>
       </c>
       <c r="D5" t="n">
-        <v>121.4240036010742</v>
+        <v>120.8470001220703</v>
       </c>
       <c r="E5" t="n">
-        <v>122.7369995117188</v>
+        <v>121.8470001220703</v>
       </c>
       <c r="F5" t="n">
-        <v>25468000</v>
+        <v>24991000</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -573,22 +573,22 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>45923</v>
+        <v>45924</v>
       </c>
       <c r="B6" t="n">
-        <v>122.7330017089844</v>
+        <v>121.8610000610352</v>
       </c>
       <c r="C6" t="n">
-        <v>122.7789993286133</v>
+        <v>122.1500015258789</v>
       </c>
       <c r="D6" t="n">
-        <v>120.8470001220703</v>
+        <v>119.4199981689453</v>
       </c>
       <c r="E6" t="n">
-        <v>121.8470001220703</v>
+        <v>120.3949966430664</v>
       </c>
       <c r="F6" t="n">
-        <v>24991000</v>
+        <v>27731000</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -599,22 +599,22 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>45924</v>
+        <v>45925</v>
       </c>
       <c r="B7" t="n">
-        <v>121.8610000610352</v>
+        <v>120.3089981079102</v>
       </c>
       <c r="C7" t="n">
-        <v>122.1500015258789</v>
+        <v>121.6839981079102</v>
       </c>
       <c r="D7" t="n">
-        <v>119.4199981689453</v>
+        <v>119.1510009765625</v>
       </c>
       <c r="E7" t="n">
-        <v>120.3949966430664</v>
+        <v>120.8239974975586</v>
       </c>
       <c r="F7" t="n">
-        <v>27731000</v>
+        <v>19978000</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -625,22 +625,22 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>45925</v>
+        <v>45926</v>
       </c>
       <c r="B8" t="n">
-        <v>120.3089981079102</v>
+        <v>120.5419998168945</v>
       </c>
       <c r="C8" t="n">
-        <v>121.6839981079102</v>
+        <v>121.4000015258789</v>
       </c>
       <c r="D8" t="n">
-        <v>119.1510009765625</v>
+        <v>120</v>
       </c>
       <c r="E8" t="n">
-        <v>120.8239974975586</v>
+        <v>121.0609970092773</v>
       </c>
       <c r="F8" t="n">
-        <v>19978000</v>
+        <v>19450000</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -651,22 +651,22 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>45926</v>
+        <v>45929</v>
       </c>
       <c r="B9" t="n">
-        <v>120.5419998168945</v>
+        <v>120.5</v>
       </c>
       <c r="C9" t="n">
-        <v>121.4000015258789</v>
+        <v>122.4489974975586</v>
       </c>
       <c r="D9" t="n">
-        <v>120</v>
+        <v>118.7539978027344</v>
       </c>
       <c r="E9" t="n">
-        <v>121.0609970092773</v>
+        <v>120.640998840332</v>
       </c>
       <c r="F9" t="n">
-        <v>19450000</v>
+        <v>30332000</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -677,22 +677,22 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="B10" t="n">
-        <v>120.5</v>
+        <v>120.640998840332</v>
       </c>
       <c r="C10" t="n">
-        <v>122.4489974975586</v>
+        <v>120.8499984741211</v>
       </c>
       <c r="D10" t="n">
-        <v>118.7539978027344</v>
+        <v>117.8000030517578</v>
       </c>
       <c r="E10" t="n">
-        <v>120.640998840332</v>
+        <v>119.8919982910156</v>
       </c>
       <c r="F10" t="n">
-        <v>30332000</v>
+        <v>38303000</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -703,22 +703,22 @@
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>45930</v>
+        <v>45931</v>
       </c>
       <c r="B11" t="n">
-        <v>120.640998840332</v>
+        <v>117.5490036010742</v>
       </c>
       <c r="C11" t="n">
-        <v>120.8499984741211</v>
+        <v>117.9140014648438</v>
       </c>
       <c r="D11" t="n">
-        <v>117.8000030517578</v>
+        <v>116.3209991455078</v>
       </c>
       <c r="E11" t="n">
-        <v>119.8919982910156</v>
+        <v>117.0899963378906</v>
       </c>
       <c r="F11" t="n">
-        <v>38303000</v>
+        <v>41102000</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -729,22 +729,22 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>45931</v>
+        <v>45932</v>
       </c>
       <c r="B12" t="n">
-        <v>117.5490036010742</v>
+        <v>116.1500015258789</v>
       </c>
       <c r="C12" t="n">
-        <v>117.9140014648438</v>
+        <v>116.3330001831055</v>
       </c>
       <c r="D12" t="n">
-        <v>116.3209991455078</v>
+        <v>113.4000015258789</v>
       </c>
       <c r="E12" t="n">
-        <v>117.0899963378906</v>
+        <v>116.2529983520508</v>
       </c>
       <c r="F12" t="n">
-        <v>41102000</v>
+        <v>46855000</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -755,22 +755,22 @@
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>45932</v>
+        <v>45933</v>
       </c>
       <c r="B13" t="n">
-        <v>116.1500015258789</v>
+        <v>116.5</v>
       </c>
       <c r="C13" t="n">
-        <v>116.3330001831055</v>
+        <v>116.8000030517578</v>
       </c>
       <c r="D13" t="n">
-        <v>113.4000015258789</v>
+        <v>114.3219985961914</v>
       </c>
       <c r="E13" t="n">
-        <v>116.2529983520508</v>
+        <v>115.3320007324219</v>
       </c>
       <c r="F13" t="n">
-        <v>46855000</v>
+        <v>31374000</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -781,22 +781,22 @@
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>45933</v>
+        <v>45936</v>
       </c>
       <c r="B14" t="n">
-        <v>116.5</v>
+        <v>116.0370025634766</v>
       </c>
       <c r="C14" t="n">
-        <v>116.8000030517578</v>
+        <v>116.3580017089844</v>
       </c>
       <c r="D14" t="n">
-        <v>114.3219985961914</v>
+        <v>114.5449981689453</v>
       </c>
       <c r="E14" t="n">
-        <v>115.3320007324219</v>
+        <v>116.3310012817383</v>
       </c>
       <c r="F14" t="n">
-        <v>31374000</v>
+        <v>29686000</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -807,22 +807,22 @@
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>45936</v>
+        <v>45937</v>
       </c>
       <c r="B15" t="n">
-        <v>116.0370025634766</v>
+        <v>117.7789993286133</v>
       </c>
       <c r="C15" t="n">
-        <v>116.3580017089844</v>
+        <v>120.1370010375977</v>
       </c>
       <c r="D15" t="n">
-        <v>114.5449981689453</v>
+        <v>117.7460021972656</v>
       </c>
       <c r="E15" t="n">
-        <v>116.3310012817383</v>
+        <v>119.1060028076172</v>
       </c>
       <c r="F15" t="n">
-        <v>29686000</v>
+        <v>33091000</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -833,22 +833,22 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>45937</v>
+        <v>45938</v>
       </c>
       <c r="B16" t="n">
-        <v>117.7789993286133</v>
+        <v>119.7109985351562</v>
       </c>
       <c r="C16" t="n">
-        <v>120.1370010375977</v>
+        <v>121.7389984130859</v>
       </c>
       <c r="D16" t="n">
-        <v>117.7460021972656</v>
+        <v>119.1999969482422</v>
       </c>
       <c r="E16" t="n">
-        <v>119.1060028076172</v>
+        <v>121.4250030517578</v>
       </c>
       <c r="F16" t="n">
-        <v>33091000</v>
+        <v>28514000</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -859,22 +859,22 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>45938</v>
+        <v>45939</v>
       </c>
       <c r="B17" t="n">
-        <v>119.7109985351562</v>
+        <v>121.4250030517578</v>
       </c>
       <c r="C17" t="n">
-        <v>121.7389984130859</v>
+        <v>123.75</v>
       </c>
       <c r="D17" t="n">
-        <v>119.1999969482422</v>
+        <v>121.181999206543</v>
       </c>
       <c r="E17" t="n">
-        <v>121.4250030517578</v>
+        <v>123.1070022583008</v>
       </c>
       <c r="F17" t="n">
-        <v>28514000</v>
+        <v>28241000</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -885,22 +885,22 @@
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>45939</v>
+        <v>45940</v>
       </c>
       <c r="B18" t="n">
-        <v>121.4250030517578</v>
+        <v>122.9000015258789</v>
       </c>
       <c r="C18" t="n">
-        <v>123.75</v>
+        <v>124.6999969482422</v>
       </c>
       <c r="D18" t="n">
-        <v>121.181999206543</v>
+        <v>121.9100036621094</v>
       </c>
       <c r="E18" t="n">
-        <v>123.1070022583008</v>
+        <v>122.0080032348633</v>
       </c>
       <c r="F18" t="n">
-        <v>28241000</v>
+        <v>42798000</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -911,22 +911,22 @@
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>45940</v>
+        <v>45943</v>
       </c>
       <c r="B19" t="n">
-        <v>122.9000015258789</v>
+        <v>122.1350021362305</v>
       </c>
       <c r="C19" t="n">
-        <v>124.6999969482422</v>
+        <v>123.1119995117188</v>
       </c>
       <c r="D19" t="n">
-        <v>121.9100036621094</v>
+        <v>120.6809997558594</v>
       </c>
       <c r="E19" t="n">
-        <v>122.0080032348633</v>
+        <v>121.9029998779297</v>
       </c>
       <c r="F19" t="n">
-        <v>42798000</v>
+        <v>24608000</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -937,22 +937,22 @@
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>45943</v>
+        <v>45944</v>
       </c>
       <c r="B20" t="n">
-        <v>122.1350021362305</v>
+        <v>121.4749984741211</v>
       </c>
       <c r="C20" t="n">
-        <v>123.1119995117188</v>
+        <v>122.4290008544922</v>
       </c>
       <c r="D20" t="n">
-        <v>120.6809997558594</v>
+        <v>120.3099975585938</v>
       </c>
       <c r="E20" t="n">
-        <v>121.9029998779297</v>
+        <v>121.5350036621094</v>
       </c>
       <c r="F20" t="n">
-        <v>24608000</v>
+        <v>23624000</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -963,22 +963,22 @@
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>45944</v>
+        <v>45945</v>
       </c>
       <c r="B21" t="n">
-        <v>121.4749984741211</v>
+        <v>121.3010025024414</v>
       </c>
       <c r="C21" t="n">
-        <v>122.4290008544922</v>
+        <v>121.9619979858398</v>
       </c>
       <c r="D21" t="n">
-        <v>120.3099975585938</v>
+        <v>120.161003112793</v>
       </c>
       <c r="E21" t="n">
-        <v>121.5350036621094</v>
+        <v>120.3290023803711</v>
       </c>
       <c r="F21" t="n">
-        <v>23624000</v>
+        <v>20252000</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -989,22 +989,22 @@
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>45945</v>
+        <v>45946</v>
       </c>
       <c r="B22" t="n">
-        <v>121.3010025024414</v>
+        <v>121.2149963378906</v>
       </c>
       <c r="C22" t="n">
-        <v>121.9619979858398</v>
+        <v>121.6709976196289</v>
       </c>
       <c r="D22" t="n">
-        <v>120.161003112793</v>
+        <v>117.5999984741211</v>
       </c>
       <c r="E22" t="n">
-        <v>120.3290023803711</v>
+        <v>118.359001159668</v>
       </c>
       <c r="F22" t="n">
-        <v>20252000</v>
+        <v>28326000</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -1015,22 +1015,22 @@
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>45946</v>
+        <v>45947</v>
       </c>
       <c r="B23" t="n">
-        <v>121.2149963378906</v>
+        <v>118.3600006103516</v>
       </c>
       <c r="C23" t="n">
-        <v>121.6709976196289</v>
+        <v>120.3119964599609</v>
       </c>
       <c r="D23" t="n">
-        <v>117.5999984741211</v>
+        <v>117.8949966430664</v>
       </c>
       <c r="E23" t="n">
-        <v>118.359001159668</v>
+        <v>119.9359970092773</v>
       </c>
       <c r="F23" t="n">
-        <v>28326000</v>
+        <v>29571000</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -1041,22 +1041,22 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>45947</v>
+        <v>45950</v>
       </c>
       <c r="B24" t="n">
-        <v>118.3600006103516</v>
+        <v>120.7880020141602</v>
       </c>
       <c r="C24" t="n">
-        <v>120.3119964599609</v>
+        <v>124.7760009765625</v>
       </c>
       <c r="D24" t="n">
-        <v>117.8949966430664</v>
+        <v>120.6900024414062</v>
       </c>
       <c r="E24" t="n">
-        <v>119.9359970092773</v>
+        <v>123.8560028076172</v>
       </c>
       <c r="F24" t="n">
-        <v>29571000</v>
+        <v>39862000</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -1067,22 +1067,22 @@
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>45950</v>
+        <v>45951</v>
       </c>
       <c r="B25" t="n">
-        <v>120.7880020141602</v>
+        <v>124.2829971313477</v>
       </c>
       <c r="C25" t="n">
-        <v>124.7760009765625</v>
+        <v>124.8600006103516</v>
       </c>
       <c r="D25" t="n">
-        <v>120.6900024414062</v>
+        <v>123.1760025024414</v>
       </c>
       <c r="E25" t="n">
-        <v>123.8560028076172</v>
+        <v>124.1350021362305</v>
       </c>
       <c r="F25" t="n">
-        <v>39862000</v>
+        <v>65082000</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -1093,22 +1093,22 @@
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>45951</v>
+        <v>45952</v>
       </c>
       <c r="B26" t="n">
-        <v>124.2829971313477</v>
+        <v>114.2900009155273</v>
       </c>
       <c r="C26" t="n">
-        <v>124.8600006103516</v>
+        <v>115.7600021362305</v>
       </c>
       <c r="D26" t="n">
-        <v>123.1760025024414</v>
+        <v>111.2509994506836</v>
       </c>
       <c r="E26" t="n">
-        <v>124.1350021362305</v>
+        <v>111.6370010375977</v>
       </c>
       <c r="F26" t="n">
-        <v>65082000</v>
+        <v>147890000</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -1119,22 +1119,22 @@
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>45952</v>
+        <v>45953</v>
       </c>
       <c r="B27" t="n">
-        <v>114.2900009155273</v>
+        <v>112.6900024414062</v>
       </c>
       <c r="C27" t="n">
-        <v>115.7600021362305</v>
+        <v>112.7829971313477</v>
       </c>
       <c r="D27" t="n">
-        <v>111.2509994506836</v>
+        <v>109.9729995727539</v>
       </c>
       <c r="E27" t="n">
-        <v>111.6370010375977</v>
+        <v>111.359001159668</v>
       </c>
       <c r="F27" t="n">
-        <v>147890000</v>
+        <v>68497000</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -1145,22 +1145,22 @@
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>45953</v>
+        <v>45954</v>
       </c>
       <c r="B28" t="n">
-        <v>112.6900024414062</v>
+        <v>111.0999984741211</v>
       </c>
       <c r="C28" t="n">
-        <v>112.7829971313477</v>
+        <v>111.4509963989258</v>
       </c>
       <c r="D28" t="n">
-        <v>109.9729995727539</v>
+        <v>109.4410018920898</v>
       </c>
       <c r="E28" t="n">
-        <v>111.359001159668</v>
+        <v>109.4690017700195</v>
       </c>
       <c r="F28" t="n">
-        <v>68497000</v>
+        <v>60280000</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
@@ -1171,22 +1171,22 @@
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>45954</v>
+        <v>45957</v>
       </c>
       <c r="B29" t="n">
-        <v>111.0999984741211</v>
+        <v>110.0670013427734</v>
       </c>
       <c r="C29" t="n">
-        <v>111.4509963989258</v>
+        <v>110.2279968261719</v>
       </c>
       <c r="D29" t="n">
-        <v>109.4410018920898</v>
+        <v>108.7300033569336</v>
       </c>
       <c r="E29" t="n">
-        <v>109.4690017700195</v>
+        <v>109.4560012817383</v>
       </c>
       <c r="F29" t="n">
-        <v>60280000</v>
+        <v>46911000</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -1197,22 +1197,22 @@
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>45957</v>
+        <v>45958</v>
       </c>
       <c r="B30" t="n">
-        <v>110.0670013427734</v>
+        <v>109.4000015258789</v>
       </c>
       <c r="C30" t="n">
-        <v>110.2279968261719</v>
+        <v>111.697998046875</v>
       </c>
       <c r="D30" t="n">
-        <v>108.7300033569336</v>
+        <v>109.3010025024414</v>
       </c>
       <c r="E30" t="n">
-        <v>109.4560012817383</v>
+        <v>110.25</v>
       </c>
       <c r="F30" t="n">
-        <v>46911000</v>
+        <v>40209000</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -1223,22 +1223,22 @@
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>45958</v>
+        <v>45959</v>
       </c>
       <c r="B31" t="n">
-        <v>109.4000015258789</v>
+        <v>109.984001159668</v>
       </c>
       <c r="C31" t="n">
-        <v>111.697998046875</v>
+        <v>110.8550033569336</v>
       </c>
       <c r="D31" t="n">
-        <v>109.3010025024414</v>
+        <v>109.5999984741211</v>
       </c>
       <c r="E31" t="n">
-        <v>110.25</v>
+        <v>110.0410003662109</v>
       </c>
       <c r="F31" t="n">
-        <v>40209000</v>
+        <v>33995000</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -1249,22 +1249,22 @@
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>45959</v>
+        <v>45960</v>
       </c>
       <c r="B32" t="n">
-        <v>109.984001159668</v>
+        <v>109.4400024414062</v>
       </c>
       <c r="C32" t="n">
-        <v>110.8550033569336</v>
+        <v>110.6159973144531</v>
       </c>
       <c r="D32" t="n">
-        <v>109.5999984741211</v>
+        <v>108.8109970092773</v>
       </c>
       <c r="E32" t="n">
-        <v>110.0410003662109</v>
+        <v>108.9000015258789</v>
       </c>
       <c r="F32" t="n">
-        <v>33995000</v>
+        <v>41581000</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
@@ -1275,22 +1275,22 @@
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>45960</v>
+        <v>45961</v>
       </c>
       <c r="B33" t="n">
-        <v>109.4400024414062</v>
+        <v>110.5390014648438</v>
       </c>
       <c r="C33" t="n">
-        <v>110.6159973144531</v>
+        <v>113.4879989624023</v>
       </c>
       <c r="D33" t="n">
-        <v>108.8109970092773</v>
+        <v>110.197998046875</v>
       </c>
       <c r="E33" t="n">
-        <v>108.9000015258789</v>
+        <v>111.8860015869141</v>
       </c>
       <c r="F33" t="n">
-        <v>41581000</v>
+        <v>68665000</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -1301,22 +1301,22 @@
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>45961</v>
+        <v>45964</v>
       </c>
       <c r="B34" t="n">
-        <v>110.5390014648438</v>
+        <v>113.3239974975586</v>
       </c>
       <c r="C34" t="n">
-        <v>113.4879989624023</v>
+        <v>113.3499984741211</v>
       </c>
       <c r="D34" t="n">
-        <v>110.197998046875</v>
+        <v>107.5149993896484</v>
       </c>
       <c r="E34" t="n">
-        <v>111.8860015869141</v>
+        <v>110.0090026855469</v>
       </c>
       <c r="F34" t="n">
-        <v>68665000</v>
+        <v>58634000</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
@@ -1327,22 +1327,22 @@
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>45964</v>
+        <v>45965</v>
       </c>
       <c r="B35" t="n">
-        <v>113.3239974975586</v>
+        <v>109.9990005493164</v>
       </c>
       <c r="C35" t="n">
-        <v>113.3499984741211</v>
+        <v>110.4599990844727</v>
       </c>
       <c r="D35" t="n">
-        <v>107.5149993896484</v>
+        <v>108.6679992675781</v>
       </c>
       <c r="E35" t="n">
-        <v>110.0090026855469</v>
+        <v>109.2959976196289</v>
       </c>
       <c r="F35" t="n">
-        <v>58634000</v>
+        <v>38718000</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
@@ -1353,22 +1353,22 @@
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>45965</v>
+        <v>45966</v>
       </c>
       <c r="B36" t="n">
-        <v>109.9990005493164</v>
+        <v>108.5</v>
       </c>
       <c r="C36" t="n">
-        <v>110.4599990844727</v>
+        <v>110.0849990844727</v>
       </c>
       <c r="D36" t="n">
-        <v>108.6679992675781</v>
+        <v>107.3369979858398</v>
       </c>
       <c r="E36" t="n">
-        <v>109.2959976196289</v>
+        <v>109.8460006713867</v>
       </c>
       <c r="F36" t="n">
-        <v>38718000</v>
+        <v>35539000</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -1379,22 +1379,22 @@
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>45966</v>
+        <v>45967</v>
       </c>
       <c r="B37" t="n">
-        <v>108.5</v>
+        <v>109.4580001831055</v>
       </c>
       <c r="C37" t="n">
-        <v>110.0849990844727</v>
+        <v>110.370002746582</v>
       </c>
       <c r="D37" t="n">
-        <v>107.3369979858398</v>
+        <v>108.5130004882812</v>
       </c>
       <c r="E37" t="n">
-        <v>109.8460006713867</v>
+        <v>109.7020034790039</v>
       </c>
       <c r="F37" t="n">
-        <v>35539000</v>
+        <v>36532000</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
@@ -1405,22 +1405,22 @@
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>45967</v>
+        <v>45968</v>
       </c>
       <c r="B38" t="n">
-        <v>109.4580001831055</v>
+        <v>109.4179992675781</v>
       </c>
       <c r="C38" t="n">
-        <v>110.370002746582</v>
+        <v>110.8219985961914</v>
       </c>
       <c r="D38" t="n">
-        <v>108.5130004882812</v>
+        <v>108.75</v>
       </c>
       <c r="E38" t="n">
-        <v>109.7020034790039</v>
+        <v>110.3659973144531</v>
       </c>
       <c r="F38" t="n">
-        <v>36532000</v>
+        <v>44125000</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
@@ -1431,22 +1431,22 @@
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>45968</v>
+        <v>45971</v>
       </c>
       <c r="B39" t="n">
-        <v>109.4179992675781</v>
+        <v>110.6719970703125</v>
       </c>
       <c r="C39" t="n">
-        <v>110.8219985961914</v>
+        <v>112.8199996948242</v>
       </c>
       <c r="D39" t="n">
-        <v>108.75</v>
+        <v>110.4049987792969</v>
       </c>
       <c r="E39" t="n">
-        <v>110.3659973144531</v>
+        <v>112.0070037841797</v>
       </c>
       <c r="F39" t="n">
-        <v>44125000</v>
+        <v>36929000</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
@@ -1457,22 +1457,22 @@
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>45971</v>
+        <v>45972</v>
       </c>
       <c r="B40" t="n">
-        <v>110.6719970703125</v>
+        <v>111.7600021362305</v>
       </c>
       <c r="C40" t="n">
-        <v>112.8199996948242</v>
+        <v>113.9219970703125</v>
       </c>
       <c r="D40" t="n">
-        <v>110.4049987792969</v>
+        <v>111.2799987792969</v>
       </c>
       <c r="E40" t="n">
-        <v>112.0070037841797</v>
+        <v>113.6439971923828</v>
       </c>
       <c r="F40" t="n">
-        <v>36929000</v>
+        <v>27966000</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
@@ -1483,22 +1483,22 @@
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>45972</v>
+        <v>45973</v>
       </c>
       <c r="B41" t="n">
-        <v>111.7600021362305</v>
+        <v>113.8170013427734</v>
       </c>
       <c r="C41" t="n">
-        <v>113.9219970703125</v>
+        <v>116.4339981079102</v>
       </c>
       <c r="D41" t="n">
-        <v>111.2799987792969</v>
+        <v>112.8259963989258</v>
       </c>
       <c r="E41" t="n">
-        <v>113.6439971923828</v>
+        <v>115.75</v>
       </c>
       <c r="F41" t="n">
-        <v>27966000</v>
+        <v>39221000</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
@@ -1509,22 +1509,22 @@
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>45973</v>
+        <v>45974</v>
       </c>
       <c r="B42" t="n">
-        <v>113.8170013427734</v>
+        <v>115.8499984741211</v>
       </c>
       <c r="C42" t="n">
-        <v>116.4339981079102</v>
+        <v>116.7330017089844</v>
       </c>
       <c r="D42" t="n">
-        <v>112.8259963989258</v>
+        <v>114.5690002441406</v>
       </c>
       <c r="E42" t="n">
-        <v>115.75</v>
+        <v>115.4229965209961</v>
       </c>
       <c r="F42" t="n">
-        <v>39221000</v>
+        <v>40144000</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
@@ -1535,22 +1535,22 @@
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>45974</v>
+        <v>45975</v>
       </c>
       <c r="B43" t="n">
-        <v>115.8499984741211</v>
+        <v>114.2730026245117</v>
       </c>
       <c r="C43" t="n">
-        <v>116.7330017089844</v>
+        <v>114.2730026245117</v>
       </c>
       <c r="D43" t="n">
-        <v>114.5690002441406</v>
+        <v>110.7210006713867</v>
       </c>
       <c r="E43" t="n">
-        <v>115.4229965209961</v>
+        <v>111.2170028686523</v>
       </c>
       <c r="F43" t="n">
-        <v>40144000</v>
+        <v>47607000</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
@@ -1561,74 +1561,74 @@
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
-        <v>45975</v>
+        <v>45978</v>
       </c>
       <c r="B44" t="n">
-        <v>114.2730026245117</v>
+        <v>110.75</v>
       </c>
       <c r="C44" t="n">
-        <v>114.2730026245117</v>
+        <v>111.8499984741211</v>
       </c>
       <c r="D44" t="n">
-        <v>110.7210006713867</v>
+        <v>109.5500030517578</v>
       </c>
       <c r="E44" t="n">
-        <v>111.2170028686523</v>
+        <v>110.2900009155273</v>
       </c>
       <c r="F44" t="n">
-        <v>47607000</v>
+        <v>26082700</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
-        <v>45978</v>
+        <v>45979</v>
       </c>
       <c r="B45" t="n">
-        <v>110.75</v>
+        <v>110.2900009155273</v>
       </c>
       <c r="C45" t="n">
-        <v>111.8499984741211</v>
+        <v>115.25</v>
       </c>
       <c r="D45" t="n">
-        <v>109.5500030517578</v>
+        <v>109.1999969482422</v>
       </c>
       <c r="E45" t="n">
-        <v>110.2900009155273</v>
+        <v>114.0899963378906</v>
       </c>
       <c r="F45" t="n">
-        <v>26082700</v>
+        <v>43440600</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
-        <v>45979</v>
+        <v>45980</v>
       </c>
       <c r="B46" t="n">
-        <v>110.2900009155273</v>
+        <v>113</v>
       </c>
       <c r="C46" t="n">
-        <v>115.25</v>
+        <v>113.3399963378906</v>
       </c>
       <c r="D46" t="n">
-        <v>109.1999969482422</v>
+        <v>108.6100006103516</v>
       </c>
       <c r="E46" t="n">
-        <v>114.0899963378906</v>
+        <v>110</v>
       </c>
       <c r="F46" t="n">
-        <v>43440600</v>
+        <v>31868100</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
@@ -1639,22 +1639,22 @@
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
-        <v>45980</v>
+        <v>45981</v>
       </c>
       <c r="B47" t="n">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C47" t="n">
-        <v>113.3399963378906</v>
+        <v>111.0999984741211</v>
       </c>
       <c r="D47" t="n">
-        <v>108.6100006103516</v>
+        <v>105.3899993896484</v>
       </c>
       <c r="E47" t="n">
-        <v>110</v>
+        <v>105.6699981689453</v>
       </c>
       <c r="F47" t="n">
-        <v>31868100</v>
+        <v>36918500</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
@@ -1665,22 +1665,22 @@
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
-        <v>45981</v>
+        <v>45982</v>
       </c>
       <c r="B48" t="n">
-        <v>111</v>
+        <v>105.129997253418</v>
       </c>
       <c r="C48" t="n">
-        <v>111.0999984741211</v>
+        <v>106.5299987792969</v>
       </c>
       <c r="D48" t="n">
-        <v>105.3899993896484</v>
+        <v>103.8099975585938</v>
       </c>
       <c r="E48" t="n">
-        <v>105.6699981689453</v>
+        <v>104.3099975585938</v>
       </c>
       <c r="F48" t="n">
-        <v>36918500</v>
+        <v>41232700</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
@@ -1691,22 +1691,22 @@
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>45982</v>
+        <v>45985</v>
       </c>
       <c r="B49" t="n">
-        <v>105.129997253418</v>
+        <v>104.25</v>
       </c>
       <c r="C49" t="n">
-        <v>106.5299987792969</v>
+        <v>108.0400009155273</v>
       </c>
       <c r="D49" t="n">
-        <v>103.8099975585938</v>
+        <v>103.3199996948242</v>
       </c>
       <c r="E49" t="n">
-        <v>104.3099975585938</v>
+        <v>106.9700012207031</v>
       </c>
       <c r="F49" t="n">
-        <v>41232700</v>
+        <v>62918300</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
@@ -1717,22 +1717,22 @@
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>45985</v>
+        <v>45986</v>
       </c>
       <c r="B50" t="n">
-        <v>104.25</v>
+        <v>106.120002746582</v>
       </c>
       <c r="C50" t="n">
-        <v>108.0400009155273</v>
+        <v>106.3000030517578</v>
       </c>
       <c r="D50" t="n">
-        <v>103.3199996948242</v>
+        <v>103.8199996948242</v>
       </c>
       <c r="E50" t="n">
-        <v>106.9700012207031</v>
+        <v>104.4000015258789</v>
       </c>
       <c r="F50" t="n">
-        <v>62918300</v>
+        <v>35122600</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
-        <v>45986</v>
+        <v>45987</v>
       </c>
       <c r="B51" t="n">
-        <v>106.120002746582</v>
+        <v>105.7399978637695</v>
       </c>
       <c r="C51" t="n">
-        <v>106.3000030517578</v>
+        <v>106.9499969482422</v>
       </c>
       <c r="D51" t="n">
-        <v>103.8199996948242</v>
+        <v>105.2200012207031</v>
       </c>
       <c r="E51" t="n">
-        <v>104.4000015258789</v>
+        <v>106.1399993896484</v>
       </c>
       <c r="F51" t="n">
-        <v>35122600</v>
+        <v>27951000</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
@@ -1769,22 +1769,22 @@
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
-        <v>45987</v>
+        <v>45989</v>
       </c>
       <c r="B52" t="n">
-        <v>105.7399978637695</v>
+        <v>106.4400024414062</v>
       </c>
       <c r="C52" t="n">
-        <v>106.9499969482422</v>
+        <v>107.9400024414062</v>
       </c>
       <c r="D52" t="n">
-        <v>105.2200012207031</v>
+        <v>106.2399978637695</v>
       </c>
       <c r="E52" t="n">
-        <v>106.1399993896484</v>
+        <v>107.5800018310547</v>
       </c>
       <c r="F52" t="n">
-        <v>27951000</v>
+        <v>15021600</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
@@ -1795,22 +1795,22 @@
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
-        <v>45989</v>
+        <v>45992</v>
       </c>
       <c r="B53" t="n">
-        <v>106.4400024414062</v>
+        <v>106.5100021362305</v>
       </c>
       <c r="C53" t="n">
-        <v>107.9400024414062</v>
+        <v>109.3399963378906</v>
       </c>
       <c r="D53" t="n">
-        <v>106.2399978637695</v>
+        <v>106.3099975585938</v>
       </c>
       <c r="E53" t="n">
-        <v>107.5800018310547</v>
+        <v>109.129997253418</v>
       </c>
       <c r="F53" t="n">
-        <v>15021600</v>
+        <v>24873400</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
@@ -1821,22 +1821,22 @@
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
-        <v>45992</v>
+        <v>45993</v>
       </c>
       <c r="B54" t="n">
-        <v>106.5100021362305</v>
+        <v>109.2099990844727</v>
       </c>
       <c r="C54" t="n">
-        <v>109.3399963378906</v>
+        <v>109.7300033569336</v>
       </c>
       <c r="D54" t="n">
-        <v>106.3099975585938</v>
+        <v>107.5199966430664</v>
       </c>
       <c r="E54" t="n">
-        <v>109.129997253418</v>
+        <v>109.3499984741211</v>
       </c>
       <c r="F54" t="n">
-        <v>24873400</v>
+        <v>25763000</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
@@ -1847,22 +1847,22 @@
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
-        <v>45993</v>
+        <v>45994</v>
       </c>
       <c r="B55" t="n">
-        <v>109.2099990844727</v>
+        <v>106.5899963378906</v>
       </c>
       <c r="C55" t="n">
-        <v>109.7300033569336</v>
+        <v>106.870002746582</v>
       </c>
       <c r="D55" t="n">
-        <v>107.5199966430664</v>
+        <v>102.0299987792969</v>
       </c>
       <c r="E55" t="n">
-        <v>109.3499984741211</v>
+        <v>103.9599990844727</v>
       </c>
       <c r="F55" t="n">
-        <v>25763000</v>
+        <v>53593400</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
@@ -1873,22 +1873,22 @@
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
-        <v>45994</v>
+        <v>45995</v>
       </c>
       <c r="B56" t="n">
-        <v>106.5899963378906</v>
+        <v>103.5699996948242</v>
       </c>
       <c r="C56" t="n">
-        <v>106.870002746582</v>
+        <v>103.8000030517578</v>
       </c>
       <c r="D56" t="n">
-        <v>102.0299987792969</v>
+        <v>101.7699966430664</v>
       </c>
       <c r="E56" t="n">
-        <v>103.9599990844727</v>
+        <v>103.2200012207031</v>
       </c>
       <c r="F56" t="n">
-        <v>53593400</v>
+        <v>51779100</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
@@ -1899,22 +1899,22 @@
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
-        <v>45995</v>
+        <v>45996</v>
       </c>
       <c r="B57" t="n">
-        <v>103.5699996948242</v>
+        <v>98.77999877929688</v>
       </c>
       <c r="C57" t="n">
-        <v>103.8000030517578</v>
+        <v>104.7900009155273</v>
       </c>
       <c r="D57" t="n">
-        <v>101.7699966430664</v>
+        <v>97.73999786376953</v>
       </c>
       <c r="E57" t="n">
-        <v>103.2200012207031</v>
+        <v>100.2399978637695</v>
       </c>
       <c r="F57" t="n">
-        <v>51779100</v>
+        <v>133363600</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
@@ -1925,22 +1925,22 @@
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
-        <v>45996</v>
+        <v>45999</v>
       </c>
       <c r="B58" t="n">
-        <v>98.77999877929688</v>
+        <v>99.87000274658203</v>
       </c>
       <c r="C58" t="n">
-        <v>104.7900009155273</v>
+        <v>99.88999938964844</v>
       </c>
       <c r="D58" t="n">
-        <v>97.73999786376953</v>
+        <v>95.30000305175781</v>
       </c>
       <c r="E58" t="n">
-        <v>100.2399978637695</v>
+        <v>96.79000091552734</v>
       </c>
       <c r="F58" t="n">
-        <v>133363600</v>
+        <v>100906300</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
@@ -1951,22 +1951,22 @@
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
-        <v>45999</v>
+        <v>46000</v>
       </c>
       <c r="B59" t="n">
-        <v>99.87000274658203</v>
+        <v>97.02999877929688</v>
       </c>
       <c r="C59" t="n">
-        <v>99.88999938964844</v>
+        <v>97.23999786376953</v>
       </c>
       <c r="D59" t="n">
-        <v>95.30000305175781</v>
+        <v>95.44999694824219</v>
       </c>
       <c r="E59" t="n">
-        <v>96.79000091552734</v>
+        <v>96.70999908447266</v>
       </c>
       <c r="F59" t="n">
-        <v>100906300</v>
+        <v>51745600</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
@@ -1977,22 +1977,22 @@
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
-        <v>46000</v>
+        <v>46001</v>
       </c>
       <c r="B60" t="n">
-        <v>97.02999877929688</v>
+        <v>96.73999786376953</v>
       </c>
       <c r="C60" t="n">
-        <v>97.23999786376953</v>
+        <v>96.97000122070312</v>
       </c>
       <c r="D60" t="n">
-        <v>95.44999694824219</v>
+        <v>92.34999847412109</v>
       </c>
       <c r="E60" t="n">
-        <v>96.70999908447266</v>
+        <v>92.70999908447266</v>
       </c>
       <c r="F60" t="n">
-        <v>51745600</v>
+        <v>74129300</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
@@ -2003,22 +2003,22 @@
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
-        <v>46001</v>
+        <v>46002</v>
       </c>
       <c r="B61" t="n">
-        <v>96.73999786376953</v>
+        <v>93.90000152587891</v>
       </c>
       <c r="C61" t="n">
-        <v>96.97000122070312</v>
+        <v>94.81999969482422</v>
       </c>
       <c r="D61" t="n">
-        <v>92.34999847412109</v>
+        <v>92.76000213623047</v>
       </c>
       <c r="E61" t="n">
-        <v>92.70999908447266</v>
+        <v>94.08999633789062</v>
       </c>
       <c r="F61" t="n">
-        <v>74129300</v>
+        <v>43949000</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
@@ -2029,22 +2029,22 @@
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
-        <v>46002</v>
+        <v>46003</v>
       </c>
       <c r="B62" t="n">
-        <v>93.90000152587891</v>
+        <v>95.5</v>
       </c>
       <c r="C62" t="n">
-        <v>94.81999969482422</v>
+        <v>96.91999816894531</v>
       </c>
       <c r="D62" t="n">
-        <v>92.76000213623047</v>
+        <v>94.65000152587891</v>
       </c>
       <c r="E62" t="n">
-        <v>94.08999633789062</v>
+        <v>95.19000244140625</v>
       </c>
       <c r="F62" t="n">
-        <v>43949000</v>
+        <v>49323100</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
@@ -2055,22 +2055,22 @@
     </row>
     <row r="63">
       <c r="A63" s="1" t="n">
-        <v>46003</v>
+        <v>46006</v>
       </c>
       <c r="B63" t="n">
-        <v>95.5</v>
+        <v>96.01999664306641</v>
       </c>
       <c r="C63" t="n">
-        <v>96.91999816894531</v>
+        <v>96.37000274658203</v>
       </c>
       <c r="D63" t="n">
-        <v>94.65000152587891</v>
+        <v>93.52999877929688</v>
       </c>
       <c r="E63" t="n">
-        <v>95.19000244140625</v>
+        <v>93.76999664306641</v>
       </c>
       <c r="F63" t="n">
-        <v>49323100</v>
+        <v>40016500</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
@@ -2081,22 +2081,22 @@
     </row>
     <row r="64">
       <c r="A64" s="1" t="n">
-        <v>46006</v>
+        <v>46007</v>
       </c>
       <c r="B64" t="n">
-        <v>96.01999664306641</v>
+        <v>93.87999725341797</v>
       </c>
       <c r="C64" t="n">
-        <v>96.37000274658203</v>
+        <v>94.93000030517578</v>
       </c>
       <c r="D64" t="n">
-        <v>93.52999877929688</v>
+        <v>93.31999969482422</v>
       </c>
       <c r="E64" t="n">
-        <v>93.76999664306641</v>
+        <v>94.56999969482422</v>
       </c>
       <c r="F64" t="n">
-        <v>40016500</v>
+        <v>34265000</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
@@ -2107,22 +2107,22 @@
     </row>
     <row r="65">
       <c r="A65" s="1" t="n">
-        <v>46007</v>
+        <v>46008</v>
       </c>
       <c r="B65" t="n">
-        <v>93.87999725341797</v>
+        <v>95.98000335693359</v>
       </c>
       <c r="C65" t="n">
-        <v>94.93000030517578</v>
+        <v>97.33000183105469</v>
       </c>
       <c r="D65" t="n">
-        <v>93.31999969482422</v>
+        <v>94.45999908447266</v>
       </c>
       <c r="E65" t="n">
-        <v>94.56999969482422</v>
+        <v>94.79000091552734</v>
       </c>
       <c r="F65" t="n">
-        <v>34265000</v>
+        <v>50472800</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
@@ -2133,22 +2133,22 @@
     </row>
     <row r="66">
       <c r="A66" s="1" t="n">
-        <v>46008</v>
+        <v>46009</v>
       </c>
       <c r="B66" t="n">
-        <v>95.98000335693359</v>
+        <v>95.01999664306641</v>
       </c>
       <c r="C66" t="n">
-        <v>97.33000183105469</v>
+        <v>95.80999755859375</v>
       </c>
       <c r="D66" t="n">
-        <v>94.45999908447266</v>
+        <v>93.58999633789062</v>
       </c>
       <c r="E66" t="n">
-        <v>94.79000091552734</v>
+        <v>94</v>
       </c>
       <c r="F66" t="n">
-        <v>50472800</v>
+        <v>37244700</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
@@ -2159,22 +2159,22 @@
     </row>
     <row r="67">
       <c r="A67" s="1" t="n">
-        <v>46009</v>
+        <v>46010</v>
       </c>
       <c r="B67" t="n">
-        <v>95.01999664306641</v>
+        <v>93.56999969482422</v>
       </c>
       <c r="C67" t="n">
-        <v>95.80999755859375</v>
+        <v>95.54000091552734</v>
       </c>
       <c r="D67" t="n">
-        <v>93.58999633789062</v>
+        <v>93.44999694824219</v>
       </c>
       <c r="E67" t="n">
-        <v>94</v>
+        <v>94.38999938964844</v>
       </c>
       <c r="F67" t="n">
-        <v>37244700</v>
+        <v>78990200</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
@@ -2185,22 +2185,22 @@
     </row>
     <row r="68">
       <c r="A68" s="1" t="n">
-        <v>46010</v>
+        <v>46013</v>
       </c>
       <c r="B68" t="n">
-        <v>93.56999969482422</v>
+        <v>94.70999908447266</v>
       </c>
       <c r="C68" t="n">
-        <v>95.54000091552734</v>
+        <v>94.70999908447266</v>
       </c>
       <c r="D68" t="n">
-        <v>93.44999694824219</v>
+        <v>92.91000366210938</v>
       </c>
       <c r="E68" t="n">
-        <v>94.38999938964844</v>
+        <v>93.23000335693359</v>
       </c>
       <c r="F68" t="n">
-        <v>78990200</v>
+        <v>39484800</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
@@ -2211,22 +2211,22 @@
     </row>
     <row r="69">
       <c r="A69" s="1" t="n">
-        <v>46013</v>
+        <v>46014</v>
       </c>
       <c r="B69" t="n">
-        <v>94.70999908447266</v>
+        <v>93.40000152587891</v>
       </c>
       <c r="C69" t="n">
-        <v>94.70999908447266</v>
+        <v>93.80999755859375</v>
       </c>
       <c r="D69" t="n">
-        <v>92.91000366210938</v>
+        <v>91.33000183105469</v>
       </c>
       <c r="E69" t="n">
-        <v>93.23000335693359</v>
+        <v>93.5</v>
       </c>
       <c r="F69" t="n">
-        <v>39484800</v>
+        <v>25896200</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
@@ -2237,22 +2237,22 @@
     </row>
     <row r="70">
       <c r="A70" s="1" t="n">
-        <v>46014</v>
+        <v>46015</v>
       </c>
       <c r="B70" t="n">
-        <v>93.40000152587891</v>
+        <v>93.11000061035156</v>
       </c>
       <c r="C70" t="n">
-        <v>93.80999755859375</v>
+        <v>93.68000030517578</v>
       </c>
       <c r="D70" t="n">
-        <v>91.33000183105469</v>
+        <v>92.66999816894531</v>
       </c>
       <c r="E70" t="n">
-        <v>93.5</v>
+        <v>93.63999938964844</v>
       </c>
       <c r="F70" t="n">
-        <v>25896200</v>
+        <v>12427900</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
@@ -2263,22 +2263,22 @@
     </row>
     <row r="71">
       <c r="A71" s="1" t="n">
-        <v>46015</v>
+        <v>46017</v>
       </c>
       <c r="B71" t="n">
-        <v>93.11000061035156</v>
+        <v>93.48000335693359</v>
       </c>
       <c r="C71" t="n">
-        <v>93.68000030517578</v>
+        <v>94.69000244140625</v>
       </c>
       <c r="D71" t="n">
-        <v>92.66999816894531</v>
+        <v>93.26999664306641</v>
       </c>
       <c r="E71" t="n">
-        <v>93.63999938964844</v>
+        <v>94.47000122070312</v>
       </c>
       <c r="F71" t="n">
-        <v>12427900</v>
+        <v>22068300</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
@@ -2289,22 +2289,22 @@
     </row>
     <row r="72">
       <c r="A72" s="1" t="n">
-        <v>46017</v>
+        <v>46020</v>
       </c>
       <c r="B72" t="n">
-        <v>93.48000335693359</v>
+        <v>93.98999786376953</v>
       </c>
       <c r="C72" t="n">
-        <v>94.69000244140625</v>
+        <v>94.97000122070312</v>
       </c>
       <c r="D72" t="n">
-        <v>93.26999664306641</v>
+        <v>93.62999725341797</v>
       </c>
       <c r="E72" t="n">
-        <v>94.47000122070312</v>
+        <v>94.15000152587891</v>
       </c>
       <c r="F72" t="n">
-        <v>22068300</v>
+        <v>24493700</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
@@ -2315,22 +2315,22 @@
     </row>
     <row r="73">
       <c r="A73" s="1" t="n">
-        <v>46020</v>
+        <v>46021</v>
       </c>
       <c r="B73" t="n">
+        <v>93.51999664306641</v>
+      </c>
+      <c r="C73" t="n">
         <v>93.98999786376953</v>
       </c>
-      <c r="C73" t="n">
-        <v>94.97000122070312</v>
-      </c>
       <c r="D73" t="n">
-        <v>93.62999725341797</v>
+        <v>93.33999633789062</v>
       </c>
       <c r="E73" t="n">
-        <v>94.15000152587891</v>
+        <v>93.77999877929688</v>
       </c>
       <c r="F73" t="n">
-        <v>24493700</v>
+        <v>23422000</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
@@ -2341,22 +2341,22 @@
     </row>
     <row r="74">
       <c r="A74" s="1" t="n">
-        <v>46021</v>
+        <v>46022</v>
       </c>
       <c r="B74" t="n">
-        <v>93.51999664306641</v>
+        <v>93.59999847412109</v>
       </c>
       <c r="C74" t="n">
-        <v>93.98999786376953</v>
+        <v>94.30999755859375</v>
       </c>
       <c r="D74" t="n">
-        <v>93.33999633789062</v>
+        <v>93.19999694824219</v>
       </c>
       <c r="E74" t="n">
-        <v>93.77999877929688</v>
+        <v>93.76000213623047</v>
       </c>
       <c r="F74" t="n">
-        <v>23422000</v>
+        <v>23495200</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
@@ -2367,22 +2367,22 @@
     </row>
     <row r="75">
       <c r="A75" s="1" t="n">
-        <v>46022</v>
+        <v>46024</v>
       </c>
       <c r="B75" t="n">
-        <v>93.59999847412109</v>
+        <v>94.12999725341797</v>
       </c>
       <c r="C75" t="n">
-        <v>94.30999755859375</v>
+        <v>94.12999725341797</v>
       </c>
       <c r="D75" t="n">
-        <v>93.19999694824219</v>
+        <v>90.80999755859375</v>
       </c>
       <c r="E75" t="n">
-        <v>93.76000213623047</v>
+        <v>90.98999786376953</v>
       </c>
       <c r="F75" t="n">
-        <v>23495200</v>
+        <v>41155400</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
@@ -2393,22 +2393,22 @@
     </row>
     <row r="76">
       <c r="A76" s="1" t="n">
-        <v>46024</v>
+        <v>46027</v>
       </c>
       <c r="B76" t="n">
-        <v>94.12999725341797</v>
+        <v>90.91999816894531</v>
       </c>
       <c r="C76" t="n">
-        <v>94.12999725341797</v>
+        <v>92.62999725341797</v>
       </c>
       <c r="D76" t="n">
-        <v>90.80999755859375</v>
+        <v>90.83999633789062</v>
       </c>
       <c r="E76" t="n">
-        <v>90.98999786376953</v>
+        <v>91.45999908447266</v>
       </c>
       <c r="F76" t="n">
-        <v>41155400</v>
+        <v>39183300</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
@@ -2419,22 +2419,22 @@
     </row>
     <row r="77">
       <c r="A77" s="1" t="n">
-        <v>46027</v>
+        <v>46028</v>
       </c>
       <c r="B77" t="n">
-        <v>90.91999816894531</v>
+        <v>91.54000091552734</v>
       </c>
       <c r="C77" t="n">
-        <v>92.62999725341797</v>
+        <v>91.63999938964844</v>
       </c>
       <c r="D77" t="n">
-        <v>90.83999633789062</v>
+        <v>89.73999786376953</v>
       </c>
       <c r="E77" t="n">
-        <v>91.45999908447266</v>
+        <v>90.65000152587891</v>
       </c>
       <c r="F77" t="n">
-        <v>39183300</v>
+        <v>43331000</v>
       </c>
       <c r="G77" t="n">
         <v>0</v>
@@ -2445,22 +2445,22 @@
     </row>
     <row r="78">
       <c r="A78" s="1" t="n">
-        <v>46028</v>
+        <v>46029</v>
       </c>
       <c r="B78" t="n">
-        <v>91.54000091552734</v>
+        <v>91.55999755859375</v>
       </c>
       <c r="C78" t="n">
-        <v>91.63999938964844</v>
+        <v>92.41999816894531</v>
       </c>
       <c r="D78" t="n">
-        <v>89.73999786376953</v>
+        <v>90.05999755859375</v>
       </c>
       <c r="E78" t="n">
-        <v>90.65000152587891</v>
+        <v>90.73000335693359</v>
       </c>
       <c r="F78" t="n">
-        <v>43331000</v>
+        <v>36525700</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
@@ -2471,22 +2471,22 @@
     </row>
     <row r="79">
       <c r="A79" s="1" t="n">
-        <v>46029</v>
+        <v>46030</v>
       </c>
       <c r="B79" t="n">
-        <v>91.55999755859375</v>
+        <v>90.44999694824219</v>
       </c>
       <c r="C79" t="n">
-        <v>92.41999816894531</v>
+        <v>91.25</v>
       </c>
       <c r="D79" t="n">
-        <v>90.05999755859375</v>
+        <v>89.58000183105469</v>
       </c>
       <c r="E79" t="n">
-        <v>90.73000335693359</v>
+        <v>90.52999877929688</v>
       </c>
       <c r="F79" t="n">
-        <v>36525700</v>
+        <v>40068700</v>
       </c>
       <c r="G79" t="n">
         <v>0</v>
@@ -2497,22 +2497,22 @@
     </row>
     <row r="80">
       <c r="A80" s="1" t="n">
-        <v>46030</v>
+        <v>46031</v>
       </c>
       <c r="B80" t="n">
-        <v>90.44999694824219</v>
+        <v>90.02999877929688</v>
       </c>
       <c r="C80" t="n">
-        <v>91.25</v>
+        <v>90.05000305175781</v>
       </c>
       <c r="D80" t="n">
-        <v>89.58000183105469</v>
+        <v>88.31999969482422</v>
       </c>
       <c r="E80" t="n">
-        <v>90.52999877929688</v>
+        <v>89.45999908447266</v>
       </c>
       <c r="F80" t="n">
-        <v>40068700</v>
+        <v>55579500</v>
       </c>
       <c r="G80" t="n">
         <v>0</v>
@@ -2523,22 +2523,22 @@
     </row>
     <row r="81">
       <c r="A81" s="1" t="n">
-        <v>46031</v>
+        <v>46034</v>
       </c>
       <c r="B81" t="n">
-        <v>90.02999877929688</v>
+        <v>89.69000244140625</v>
       </c>
       <c r="C81" t="n">
-        <v>90.05000305175781</v>
+        <v>90.33999633789062</v>
       </c>
       <c r="D81" t="n">
-        <v>88.31999969482422</v>
+        <v>89.33000183105469</v>
       </c>
       <c r="E81" t="n">
-        <v>89.45999908447266</v>
+        <v>89.41000366210938</v>
       </c>
       <c r="F81" t="n">
-        <v>55579500</v>
+        <v>36290600</v>
       </c>
       <c r="G81" t="n">
         <v>0</v>
@@ -2549,22 +2549,22 @@
     </row>
     <row r="82">
       <c r="A82" s="1" t="n">
-        <v>46034</v>
+        <v>46035</v>
       </c>
       <c r="B82" t="n">
-        <v>89.69000244140625</v>
+        <v>89.44000244140625</v>
       </c>
       <c r="C82" t="n">
-        <v>90.33999633789062</v>
+        <v>91.15000152587891</v>
       </c>
       <c r="D82" t="n">
-        <v>89.33000183105469</v>
+        <v>89.06999969482422</v>
       </c>
       <c r="E82" t="n">
-        <v>89.41000366210938</v>
+        <v>90.31999969482422</v>
       </c>
       <c r="F82" t="n">
-        <v>36290600</v>
+        <v>45221100</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
@@ -2575,22 +2575,22 @@
     </row>
     <row r="83">
       <c r="A83" s="1" t="n">
-        <v>46035</v>
+        <v>46036</v>
       </c>
       <c r="B83" t="n">
-        <v>89.44000244140625</v>
+        <v>91.23999786376953</v>
       </c>
       <c r="C83" t="n">
-        <v>91.15000152587891</v>
+        <v>91.58000183105469</v>
       </c>
       <c r="D83" t="n">
-        <v>89.06999969482422</v>
+        <v>87.94999694824219</v>
       </c>
       <c r="E83" t="n">
-        <v>90.31999969482422</v>
+        <v>88.55000305175781</v>
       </c>
       <c r="F83" t="n">
-        <v>45221100</v>
+        <v>49737700</v>
       </c>
       <c r="G83" t="n">
         <v>0</v>
@@ -2601,22 +2601,22 @@
     </row>
     <row r="84">
       <c r="A84" s="1" t="n">
-        <v>46036</v>
+        <v>46037</v>
       </c>
       <c r="B84" t="n">
-        <v>91.23999786376953</v>
+        <v>89.01999664306641</v>
       </c>
       <c r="C84" t="n">
-        <v>91.58000183105469</v>
+        <v>89.88999938964844</v>
       </c>
       <c r="D84" t="n">
-        <v>87.94999694824219</v>
+        <v>87.81999969482422</v>
       </c>
       <c r="E84" t="n">
-        <v>88.55000305175781</v>
+        <v>88.05000305175781</v>
       </c>
       <c r="F84" t="n">
-        <v>49737700</v>
+        <v>36945100</v>
       </c>
       <c r="G84" t="n">
         <v>0</v>
@@ -2627,22 +2627,22 @@
     </row>
     <row r="85">
       <c r="A85" s="1" t="n">
-        <v>46037</v>
+        <v>46038</v>
       </c>
       <c r="B85" t="n">
-        <v>89.01999664306641</v>
+        <v>88.33999633789062</v>
       </c>
       <c r="C85" t="n">
-        <v>89.88999938964844</v>
+        <v>88.51000213623047</v>
       </c>
       <c r="D85" t="n">
-        <v>87.81999969482422</v>
+        <v>87.77999877929688</v>
       </c>
       <c r="E85" t="n">
-        <v>88.05000305175781</v>
+        <v>88</v>
       </c>
       <c r="F85" t="n">
-        <v>36945100</v>
+        <v>48130500</v>
       </c>
       <c r="G85" t="n">
         <v>0</v>
@@ -2653,22 +2653,22 @@
     </row>
     <row r="86">
       <c r="A86" s="1" t="n">
-        <v>46038</v>
+        <v>46042</v>
       </c>
       <c r="B86" t="n">
-        <v>88.33999633789062</v>
+        <v>88.97000122070312</v>
       </c>
       <c r="C86" t="n">
-        <v>88.51000213623047</v>
+        <v>89.90000152587891</v>
       </c>
       <c r="D86" t="n">
-        <v>87.77999877929688</v>
+        <v>87.01999664306641</v>
       </c>
       <c r="E86" t="n">
-        <v>88</v>
+        <v>87.26000213623047</v>
       </c>
       <c r="F86" t="n">
-        <v>48130500</v>
+        <v>109729700</v>
       </c>
       <c r="G86" t="n">
         <v>0</v>
@@ -2679,22 +2679,22 @@
     </row>
     <row r="87">
       <c r="A87" s="1" t="n">
-        <v>46042</v>
+        <v>46043</v>
       </c>
       <c r="B87" t="n">
-        <v>88.97000122070312</v>
+        <v>82.51999664306641</v>
       </c>
       <c r="C87" t="n">
-        <v>89.90000152587891</v>
+        <v>86</v>
       </c>
       <c r="D87" t="n">
-        <v>87.01999664306641</v>
+        <v>81.93000030517578</v>
       </c>
       <c r="E87" t="n">
-        <v>87.26000213623047</v>
+        <v>85.36000061035156</v>
       </c>
       <c r="F87" t="n">
-        <v>109729700</v>
+        <v>127940700</v>
       </c>
       <c r="G87" t="n">
         <v>0</v>
@@ -2705,22 +2705,22 @@
     </row>
     <row r="88">
       <c r="A88" s="1" t="n">
-        <v>46043</v>
+        <v>46044</v>
       </c>
       <c r="B88" t="n">
-        <v>82.51999664306641</v>
+        <v>85.01999664306641</v>
       </c>
       <c r="C88" t="n">
-        <v>86</v>
+        <v>85.09999847412109</v>
       </c>
       <c r="D88" t="n">
-        <v>81.93000030517578</v>
+        <v>82.98000335693359</v>
       </c>
       <c r="E88" t="n">
-        <v>85.36000061035156</v>
+        <v>83.54000091552734</v>
       </c>
       <c r="F88" t="n">
-        <v>127940700</v>
+        <v>69113300</v>
       </c>
       <c r="G88" t="n">
         <v>0</v>
@@ -2731,22 +2731,22 @@
     </row>
     <row r="89">
       <c r="A89" s="1" t="n">
-        <v>46044</v>
+        <v>46045</v>
       </c>
       <c r="B89" t="n">
-        <v>85.01999664306641</v>
+        <v>83.43000030517578</v>
       </c>
       <c r="C89" t="n">
-        <v>85.09999847412109</v>
+        <v>86.30000305175781</v>
       </c>
       <c r="D89" t="n">
-        <v>82.98000335693359</v>
+        <v>83.27999877929688</v>
       </c>
       <c r="E89" t="n">
-        <v>83.54000091552734</v>
+        <v>86.12000274658203</v>
       </c>
       <c r="F89" t="n">
-        <v>69113300</v>
+        <v>64520400</v>
       </c>
       <c r="G89" t="n">
         <v>0</v>
@@ -2757,22 +2757,22 @@
     </row>
     <row r="90">
       <c r="A90" s="1" t="n">
-        <v>46045</v>
+        <v>46048</v>
       </c>
       <c r="B90" t="n">
-        <v>83.43000030517578</v>
+        <v>86.91999816894531</v>
       </c>
       <c r="C90" t="n">
-        <v>86.30000305175781</v>
+        <v>86.94000244140625</v>
       </c>
       <c r="D90" t="n">
-        <v>83.27999877929688</v>
+        <v>85.34999847412109</v>
       </c>
       <c r="E90" t="n">
-        <v>86.12000274658203</v>
+        <v>85.69999694824219</v>
       </c>
       <c r="F90" t="n">
-        <v>64520400</v>
+        <v>40941900</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
@@ -2783,22 +2783,22 @@
     </row>
     <row r="91">
       <c r="A91" s="1" t="n">
-        <v>46048</v>
+        <v>46049</v>
       </c>
       <c r="B91" t="n">
-        <v>86.91999816894531</v>
+        <v>85.27999877929688</v>
       </c>
       <c r="C91" t="n">
-        <v>86.94000244140625</v>
+        <v>85.59999847412109</v>
       </c>
       <c r="D91" t="n">
-        <v>85.34999847412109</v>
+        <v>83.87999725341797</v>
       </c>
       <c r="E91" t="n">
-        <v>85.69999694824219</v>
+        <v>85.58000183105469</v>
       </c>
       <c r="F91" t="n">
-        <v>40941900</v>
+        <v>37790800</v>
       </c>
       <c r="G91" t="n">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="92">
       <c r="A92" s="1" t="n">
-        <v>46049</v>
+        <v>46050</v>
       </c>
       <c r="B92" t="n">
-        <v>85.27999877929688</v>
+        <v>85.62999725341797</v>
       </c>
       <c r="C92" t="n">
-        <v>85.59999847412109</v>
+        <v>86.47000122070312</v>
       </c>
       <c r="D92" t="n">
-        <v>83.87999725341797</v>
+        <v>84.30000305175781</v>
       </c>
       <c r="E92" t="n">
-        <v>85.58000183105469</v>
+        <v>84.63999938964844</v>
       </c>
       <c r="F92" t="n">
-        <v>37790800</v>
+        <v>37762600</v>
       </c>
       <c r="G92" t="n">
         <v>0</v>
@@ -2835,22 +2835,22 @@
     </row>
     <row r="93">
       <c r="A93" s="1" t="n">
-        <v>46050</v>
+        <v>46051</v>
       </c>
       <c r="B93" t="n">
-        <v>85.62999725341797</v>
+        <v>84.30999755859375</v>
       </c>
       <c r="C93" t="n">
-        <v>86.47000122070312</v>
+        <v>84.37999725341797</v>
       </c>
       <c r="D93" t="n">
-        <v>84.30000305175781</v>
+        <v>82.34999847412109</v>
       </c>
       <c r="E93" t="n">
-        <v>84.63999938964844</v>
+        <v>83.16000366210938</v>
       </c>
       <c r="F93" t="n">
-        <v>37762600</v>
+        <v>42278100</v>
       </c>
       <c r="G93" t="n">
         <v>0</v>
@@ -2861,22 +2861,22 @@
     </row>
     <row r="94">
       <c r="A94" s="1" t="n">
-        <v>46051</v>
+        <v>46052</v>
       </c>
       <c r="B94" t="n">
-        <v>84.30999755859375</v>
+        <v>83.09999847412109</v>
       </c>
       <c r="C94" t="n">
-        <v>84.37999725341797</v>
+        <v>84.05999755859375</v>
       </c>
       <c r="D94" t="n">
-        <v>82.34999847412109</v>
+        <v>82.77999877929688</v>
       </c>
       <c r="E94" t="n">
-        <v>83.16000366210938</v>
+        <v>83.48999786376953</v>
       </c>
       <c r="F94" t="n">
-        <v>42278100</v>
+        <v>45755000</v>
       </c>
       <c r="G94" t="n">
         <v>0</v>
@@ -2887,22 +2887,22 @@
     </row>
     <row r="95">
       <c r="A95" s="1" t="n">
-        <v>46052</v>
+        <v>46055</v>
       </c>
       <c r="B95" t="n">
-        <v>83.09999847412109</v>
+        <v>83.52999877929688</v>
       </c>
       <c r="C95" t="n">
-        <v>84.05999755859375</v>
+        <v>85.26999664306641</v>
       </c>
       <c r="D95" t="n">
-        <v>82.77999877929688</v>
+        <v>82.72000122070312</v>
       </c>
       <c r="E95" t="n">
-        <v>83.48999786376953</v>
+        <v>82.76000213623047</v>
       </c>
       <c r="F95" t="n">
-        <v>45755000</v>
+        <v>41445300</v>
       </c>
       <c r="G95" t="n">
         <v>0</v>
@@ -2913,22 +2913,22 @@
     </row>
     <row r="96">
       <c r="A96" s="1" t="n">
-        <v>46055</v>
+        <v>46056</v>
       </c>
       <c r="B96" t="n">
-        <v>83.52999877929688</v>
+        <v>82.23000335693359</v>
       </c>
       <c r="C96" t="n">
-        <v>85.26999664306641</v>
+        <v>82.44999694824219</v>
       </c>
       <c r="D96" t="n">
-        <v>82.72000122070312</v>
+        <v>79.62000274658203</v>
       </c>
       <c r="E96" t="n">
-        <v>82.76000213623047</v>
+        <v>79.94000244140625</v>
       </c>
       <c r="F96" t="n">
-        <v>41445300</v>
+        <v>49789000</v>
       </c>
       <c r="G96" t="n">
         <v>0</v>
@@ -2939,22 +2939,22 @@
     </row>
     <row r="97">
       <c r="A97" s="1" t="n">
-        <v>46056</v>
+        <v>46057</v>
       </c>
       <c r="B97" t="n">
-        <v>82.23000335693359</v>
+        <v>79.98999786376953</v>
       </c>
       <c r="C97" t="n">
-        <v>82.44999694824219</v>
+        <v>81.44000244140625</v>
       </c>
       <c r="D97" t="n">
-        <v>79.62000274658203</v>
+        <v>79.23000335693359</v>
       </c>
       <c r="E97" t="n">
-        <v>79.94000244140625</v>
+        <v>80.16000366210938</v>
       </c>
       <c r="F97" t="n">
-        <v>49789000</v>
+        <v>48963200</v>
       </c>
       <c r="G97" t="n">
         <v>0</v>
@@ -2965,22 +2965,22 @@
     </row>
     <row r="98">
       <c r="A98" s="1" t="n">
-        <v>46057</v>
+        <v>46058</v>
       </c>
       <c r="B98" t="n">
-        <v>79.98999786376953</v>
+        <v>81.48999786376953</v>
       </c>
       <c r="C98" t="n">
-        <v>81.44000244140625</v>
+        <v>83.30000305175781</v>
       </c>
       <c r="D98" t="n">
-        <v>79.23000335693359</v>
+        <v>80.54000091552734</v>
       </c>
       <c r="E98" t="n">
-        <v>80.16000366210938</v>
+        <v>80.87000274658203</v>
       </c>
       <c r="F98" t="n">
-        <v>48963200</v>
+        <v>54805700</v>
       </c>
       <c r="G98" t="n">
         <v>0</v>
@@ -2991,22 +2991,22 @@
     </row>
     <row r="99">
       <c r="A99" s="1" t="n">
-        <v>46058</v>
+        <v>46059</v>
       </c>
       <c r="B99" t="n">
-        <v>81.48999786376953</v>
+        <v>81.01999664306641</v>
       </c>
       <c r="C99" t="n">
-        <v>83.30000305175781</v>
+        <v>82.48999786376953</v>
       </c>
       <c r="D99" t="n">
-        <v>80.54000091552734</v>
+        <v>80.65000152587891</v>
       </c>
       <c r="E99" t="n">
-        <v>80.87000274658203</v>
+        <v>82.19999694824219</v>
       </c>
       <c r="F99" t="n">
-        <v>54805700</v>
+        <v>46154100</v>
       </c>
       <c r="G99" t="n">
         <v>0</v>
@@ -3017,22 +3017,22 @@
     </row>
     <row r="100">
       <c r="A100" s="1" t="n">
-        <v>46059</v>
+        <v>46062</v>
       </c>
       <c r="B100" t="n">
-        <v>81.01999664306641</v>
+        <v>82.18000030517578</v>
       </c>
       <c r="C100" t="n">
-        <v>82.48999786376953</v>
+        <v>82.20999908447266</v>
       </c>
       <c r="D100" t="n">
-        <v>80.65000152587891</v>
+        <v>79.87000274658203</v>
       </c>
       <c r="E100" t="n">
-        <v>82.19999694824219</v>
+        <v>81.47000122070312</v>
       </c>
       <c r="F100" t="n">
-        <v>46154100</v>
+        <v>42200200</v>
       </c>
       <c r="G100" t="n">
         <v>0</v>
@@ -3043,22 +3043,22 @@
     </row>
     <row r="101">
       <c r="A101" s="1" t="n">
-        <v>46062</v>
+        <v>46063</v>
       </c>
       <c r="B101" t="n">
-        <v>82.18000030517578</v>
+        <v>82.72000122070312</v>
       </c>
       <c r="C101" t="n">
+        <v>84.66000366210938</v>
+      </c>
+      <c r="D101" t="n">
+        <v>82.08999633789062</v>
+      </c>
+      <c r="E101" t="n">
         <v>82.20999908447266</v>
       </c>
-      <c r="D101" t="n">
-        <v>79.87000274658203</v>
-      </c>
-      <c r="E101" t="n">
-        <v>81.47000122070312</v>
-      </c>
       <c r="F101" t="n">
-        <v>42200200</v>
+        <v>43595800</v>
       </c>
       <c r="G101" t="n">
         <v>0</v>
@@ -3069,22 +3069,22 @@
     </row>
     <row r="102">
       <c r="A102" s="1" t="n">
-        <v>46063</v>
+        <v>46064</v>
       </c>
       <c r="B102" t="n">
-        <v>82.72000122070312</v>
+        <v>81.95999908447266</v>
       </c>
       <c r="C102" t="n">
-        <v>84.66000366210938</v>
+        <v>82.48000335693359</v>
       </c>
       <c r="D102" t="n">
-        <v>82.08999633789062</v>
+        <v>79.44999694824219</v>
       </c>
       <c r="E102" t="n">
-        <v>82.20999908447266</v>
+        <v>79.62000274658203</v>
       </c>
       <c r="F102" t="n">
-        <v>43595800</v>
+        <v>40840300</v>
       </c>
       <c r="G102" t="n">
         <v>0</v>
@@ -3095,22 +3095,22 @@
     </row>
     <row r="103">
       <c r="A103" s="1" t="n">
-        <v>46064</v>
+        <v>46065</v>
       </c>
       <c r="B103" t="n">
-        <v>81.95999908447266</v>
+        <v>79.11000061035156</v>
       </c>
       <c r="C103" t="n">
-        <v>82.48000335693359</v>
+        <v>79.15000152587891</v>
       </c>
       <c r="D103" t="n">
-        <v>79.44999694824219</v>
+        <v>75.23000335693359</v>
       </c>
       <c r="E103" t="n">
-        <v>79.62000274658203</v>
+        <v>75.86000061035156</v>
       </c>
       <c r="F103" t="n">
-        <v>40840300</v>
+        <v>73516100</v>
       </c>
       <c r="G103" t="n">
         <v>0</v>
@@ -3121,22 +3121,22 @@
     </row>
     <row r="104">
       <c r="A104" s="1" t="n">
-        <v>46065</v>
+        <v>46066</v>
       </c>
       <c r="B104" t="n">
-        <v>79.11000061035156</v>
+        <v>76.13999938964844</v>
       </c>
       <c r="C104" t="n">
-        <v>79.15000152587891</v>
+        <v>77.18000030517578</v>
       </c>
       <c r="D104" t="n">
-        <v>75.23000335693359</v>
+        <v>75.52999877929688</v>
       </c>
       <c r="E104" t="n">
-        <v>75.86000061035156</v>
+        <v>76.87000274658203</v>
       </c>
       <c r="F104" t="n">
-        <v>73516100</v>
+        <v>42292100</v>
       </c>
       <c r="G104" t="n">
         <v>0</v>
@@ -3147,22 +3147,22 @@
     </row>
     <row r="105">
       <c r="A105" s="1" t="n">
-        <v>46066</v>
+        <v>46070</v>
       </c>
       <c r="B105" t="n">
-        <v>76.13999938964844</v>
+        <v>76.91999816894531</v>
       </c>
       <c r="C105" t="n">
-        <v>77.18000030517578</v>
+        <v>77.87000274658203</v>
       </c>
       <c r="D105" t="n">
-        <v>75.52999877929688</v>
+        <v>75.30000305175781</v>
       </c>
       <c r="E105" t="n">
-        <v>76.87000274658203</v>
+        <v>77</v>
       </c>
       <c r="F105" t="n">
-        <v>42292100</v>
+        <v>35961500</v>
       </c>
       <c r="G105" t="n">
         <v>0</v>
@@ -3173,22 +3173,22 @@
     </row>
     <row r="106">
       <c r="A106" s="1" t="n">
-        <v>46070</v>
+        <v>46071</v>
       </c>
       <c r="B106" t="n">
-        <v>76.91999816894531</v>
+        <v>77.31999969482422</v>
       </c>
       <c r="C106" t="n">
-        <v>77.87000274658203</v>
+        <v>78.31999969482422</v>
       </c>
       <c r="D106" t="n">
-        <v>75.30000305175781</v>
+        <v>76.27999877929688</v>
       </c>
       <c r="E106" t="n">
-        <v>77</v>
+        <v>77.98999786376953</v>
       </c>
       <c r="F106" t="n">
-        <v>35961500</v>
+        <v>29883100</v>
       </c>
       <c r="G106" t="n">
         <v>0</v>
@@ -3199,22 +3199,22 @@
     </row>
     <row r="107">
       <c r="A107" s="1" t="n">
-        <v>46071</v>
+        <v>46072</v>
       </c>
       <c r="B107" t="n">
-        <v>77.31999969482422</v>
+        <v>77.75</v>
       </c>
       <c r="C107" t="n">
-        <v>78.31999969482422</v>
+        <v>78.69999694824219</v>
       </c>
       <c r="D107" t="n">
-        <v>76.27999877929688</v>
+        <v>76.58999633789062</v>
       </c>
       <c r="E107" t="n">
-        <v>77.98999786376953</v>
+        <v>77</v>
       </c>
       <c r="F107" t="n">
-        <v>29883100</v>
+        <v>30139200</v>
       </c>
       <c r="G107" t="n">
         <v>0</v>
@@ -3225,22 +3225,22 @@
     </row>
     <row r="108">
       <c r="A108" s="1" t="n">
-        <v>46072</v>
+        <v>46073</v>
       </c>
       <c r="B108" t="n">
-        <v>77.75</v>
+        <v>76.61000061035156</v>
       </c>
       <c r="C108" t="n">
-        <v>78.69999694824219</v>
+        <v>78.84999847412109</v>
       </c>
       <c r="D108" t="n">
-        <v>76.58999633789062</v>
+        <v>76.40000152587891</v>
       </c>
       <c r="E108" t="n">
-        <v>77</v>
+        <v>78.66999816894531</v>
       </c>
       <c r="F108" t="n">
-        <v>30139200</v>
+        <v>32411300</v>
       </c>
       <c r="G108" t="n">
         <v>0</v>
@@ -3251,22 +3251,22 @@
     </row>
     <row r="109">
       <c r="A109" s="1" t="n">
-        <v>46073</v>
+        <v>46076</v>
       </c>
       <c r="B109" t="n">
-        <v>76.61000061035156</v>
+        <v>77.79000091552734</v>
       </c>
       <c r="C109" t="n">
-        <v>78.84999847412109</v>
+        <v>77.83000183105469</v>
       </c>
       <c r="D109" t="n">
-        <v>76.40000152587891</v>
+        <v>75.01000213623047</v>
       </c>
       <c r="E109" t="n">
-        <v>78.66999816894531</v>
+        <v>76.01999664306641</v>
       </c>
       <c r="F109" t="n">
-        <v>32411300</v>
+        <v>38363000</v>
       </c>
       <c r="G109" t="n">
         <v>0</v>
@@ -3277,22 +3277,22 @@
     </row>
     <row r="110">
       <c r="A110" s="1" t="n">
-        <v>46076</v>
+        <v>46077</v>
       </c>
       <c r="B110" t="n">
-        <v>77.79000091552734</v>
+        <v>75.73000335693359</v>
       </c>
       <c r="C110" t="n">
-        <v>77.83000183105469</v>
+        <v>78.12000274658203</v>
       </c>
       <c r="D110" t="n">
-        <v>75.01000213623047</v>
+        <v>75.20999908447266</v>
       </c>
       <c r="E110" t="n">
-        <v>76.01999664306641</v>
+        <v>78.04000091552734</v>
       </c>
       <c r="F110" t="n">
-        <v>38363000</v>
+        <v>33079100</v>
       </c>
       <c r="G110" t="n">
         <v>0</v>
@@ -3303,22 +3303,22 @@
     </row>
     <row r="111">
       <c r="A111" s="1" t="n">
-        <v>46077</v>
+        <v>46078</v>
       </c>
       <c r="B111" t="n">
-        <v>75.73000335693359</v>
+        <v>79.43000030517578</v>
       </c>
       <c r="C111" t="n">
-        <v>78.12000274658203</v>
+        <v>83.12000274658203</v>
       </c>
       <c r="D111" t="n">
-        <v>75.20999908447266</v>
+        <v>79.25</v>
       </c>
       <c r="E111" t="n">
-        <v>78.04000091552734</v>
+        <v>82.69999694824219</v>
       </c>
       <c r="F111" t="n">
-        <v>33079100</v>
+        <v>69319300</v>
       </c>
       <c r="G111" t="n">
         <v>0</v>
@@ -3329,22 +3329,22 @@
     </row>
     <row r="112">
       <c r="A112" s="1" t="n">
-        <v>46078</v>
+        <v>46079</v>
       </c>
       <c r="B112" t="n">
-        <v>79.43000030517578</v>
+        <v>83.19999694824219</v>
       </c>
       <c r="C112" t="n">
-        <v>83.12000274658203</v>
+        <v>86.5</v>
       </c>
       <c r="D112" t="n">
-        <v>79.25</v>
+        <v>82.80000305175781</v>
       </c>
       <c r="E112" t="n">
-        <v>82.69999694824219</v>
+        <v>84.58999633789062</v>
       </c>
       <c r="F112" t="n">
-        <v>69319300</v>
+        <v>85642500</v>
       </c>
       <c r="G112" t="n">
         <v>0</v>
@@ -3355,22 +3355,22 @@
     </row>
     <row r="113">
       <c r="A113" s="1" t="n">
-        <v>46079</v>
+        <v>46080</v>
       </c>
       <c r="B113" t="n">
-        <v>83.19999694824219</v>
+        <v>94.30000305175781</v>
       </c>
       <c r="C113" t="n">
-        <v>86.5</v>
+        <v>96.75</v>
       </c>
       <c r="D113" t="n">
-        <v>82.80000305175781</v>
+        <v>90.58000183105469</v>
       </c>
       <c r="E113" t="n">
-        <v>84.58999633789062</v>
+        <v>96.23999786376953</v>
       </c>
       <c r="F113" t="n">
-        <v>85642500</v>
+        <v>200767000</v>
       </c>
       <c r="G113" t="n">
         <v>0</v>
@@ -3381,22 +3381,22 @@
     </row>
     <row r="114">
       <c r="A114" s="1" t="n">
-        <v>46080</v>
+        <v>46083</v>
       </c>
       <c r="B114" t="n">
-        <v>94.30000305175781</v>
+        <v>95.26000213623047</v>
       </c>
       <c r="C114" t="n">
-        <v>96.75</v>
+        <v>98.06999969482422</v>
       </c>
       <c r="D114" t="n">
-        <v>90.58000183105469</v>
+        <v>95.19999694824219</v>
       </c>
       <c r="E114" t="n">
-        <v>96.23999786376953</v>
+        <v>97.08999633789062</v>
       </c>
       <c r="F114" t="n">
-        <v>200767000</v>
+        <v>79915400</v>
       </c>
       <c r="G114" t="n">
         <v>0</v>
@@ -3407,22 +3407,22 @@
     </row>
     <row r="115">
       <c r="A115" s="1" t="n">
-        <v>46083</v>
+        <v>46084</v>
       </c>
       <c r="B115" t="n">
-        <v>95.26000213623047</v>
+        <v>96.01000213623047</v>
       </c>
       <c r="C115" t="n">
-        <v>98.06999969482422</v>
+        <v>98.45999908447266</v>
       </c>
       <c r="D115" t="n">
-        <v>95.19999694824219</v>
+        <v>95.33000183105469</v>
       </c>
       <c r="E115" t="n">
-        <v>97.08999633789062</v>
+        <v>97.69999694824219</v>
       </c>
       <c r="F115" t="n">
-        <v>79915400</v>
+        <v>59149000</v>
       </c>
       <c r="G115" t="n">
         <v>0</v>
@@ -3433,22 +3433,22 @@
     </row>
     <row r="116">
       <c r="A116" s="1" t="n">
-        <v>46084</v>
+        <v>46085</v>
       </c>
       <c r="B116" t="n">
-        <v>96.01000213623047</v>
+        <v>97.11000061035156</v>
       </c>
       <c r="C116" t="n">
-        <v>98.45999908447266</v>
+        <v>99.75</v>
       </c>
       <c r="D116" t="n">
-        <v>95.33000183105469</v>
+        <v>96.98999786376953</v>
       </c>
       <c r="E116" t="n">
-        <v>97.69999694824219</v>
+        <v>98.66000366210938</v>
       </c>
       <c r="F116" t="n">
-        <v>59149000</v>
+        <v>52604300</v>
       </c>
       <c r="G116" t="n">
         <v>0</v>
@@ -3459,22 +3459,22 @@
     </row>
     <row r="117">
       <c r="A117" s="1" t="n">
-        <v>46085</v>
+        <v>46086</v>
       </c>
       <c r="B117" t="n">
-        <v>97.11000061035156</v>
+        <v>98.5</v>
       </c>
       <c r="C117" t="n">
-        <v>99.75</v>
+        <v>100.1900024414062</v>
       </c>
       <c r="D117" t="n">
-        <v>96.98999786376953</v>
+        <v>98.09999847412109</v>
       </c>
       <c r="E117" t="n">
-        <v>98.66000366210938</v>
+        <v>99.16999816894531</v>
       </c>
       <c r="F117" t="n">
-        <v>52604300</v>
+        <v>53403000</v>
       </c>
       <c r="G117" t="n">
         <v>0</v>
@@ -3485,22 +3485,22 @@
     </row>
     <row r="118">
       <c r="A118" s="1" t="n">
-        <v>46086</v>
+        <v>46087</v>
       </c>
       <c r="B118" t="n">
-        <v>98.5</v>
+        <v>99.33000183105469</v>
       </c>
       <c r="C118" t="n">
-        <v>100.1900024414062</v>
+        <v>99.87999725341797</v>
       </c>
       <c r="D118" t="n">
-        <v>98.09999847412109</v>
+        <v>97.40000152587891</v>
       </c>
       <c r="E118" t="n">
-        <v>99.16999816894531</v>
+        <v>99.01999664306641</v>
       </c>
       <c r="F118" t="n">
-        <v>53403000</v>
+        <v>41196300</v>
       </c>
       <c r="G118" t="n">
         <v>0</v>
@@ -3511,22 +3511,22 @@
     </row>
     <row r="119">
       <c r="A119" s="1" t="n">
-        <v>46087</v>
+        <v>46090</v>
       </c>
       <c r="B119" t="n">
-        <v>99.33000183105469</v>
+        <v>97.69999694824219</v>
       </c>
       <c r="C119" t="n">
-        <v>99.87999725341797</v>
+        <v>98.94000244140625</v>
       </c>
       <c r="D119" t="n">
-        <v>97.40000152587891</v>
+        <v>96.58000183105469</v>
       </c>
       <c r="E119" t="n">
-        <v>99.01999664306641</v>
+        <v>98.31999969482422</v>
       </c>
       <c r="F119" t="n">
-        <v>41196300</v>
+        <v>48589000</v>
       </c>
       <c r="G119" t="n">
         <v>0</v>
@@ -3537,22 +3537,22 @@
     </row>
     <row r="120">
       <c r="A120" s="1" t="n">
-        <v>46090</v>
+        <v>46091</v>
       </c>
       <c r="B120" t="n">
-        <v>97.69999694824219</v>
+        <v>97.80999755859375</v>
       </c>
       <c r="C120" t="n">
-        <v>98.94000244140625</v>
+        <v>98.48999786376953</v>
       </c>
       <c r="D120" t="n">
-        <v>96.58000183105469</v>
+        <v>96.29000091552734</v>
       </c>
       <c r="E120" t="n">
-        <v>98.31999969482422</v>
+        <v>96.94000244140625</v>
       </c>
       <c r="F120" t="n">
-        <v>48589000</v>
+        <v>41027200</v>
       </c>
       <c r="G120" t="n">
         <v>0</v>
@@ -3563,22 +3563,22 @@
     </row>
     <row r="121">
       <c r="A121" s="1" t="n">
-        <v>46091</v>
+        <v>46092</v>
       </c>
       <c r="B121" t="n">
-        <v>97.80999755859375</v>
+        <v>97.41000366210938</v>
       </c>
       <c r="C121" t="n">
-        <v>98.48999786376953</v>
+        <v>98</v>
       </c>
       <c r="D121" t="n">
-        <v>96.29000091552734</v>
+        <v>94.69000244140625</v>
       </c>
       <c r="E121" t="n">
-        <v>96.94000244140625</v>
+        <v>94.88999938964844</v>
       </c>
       <c r="F121" t="n">
-        <v>41027200</v>
+        <v>33962900</v>
       </c>
       <c r="G121" t="n">
         <v>0</v>
@@ -3589,22 +3589,22 @@
     </row>
     <row r="122">
       <c r="A122" s="1" t="n">
-        <v>46092</v>
+        <v>46093</v>
       </c>
       <c r="B122" t="n">
-        <v>97.41000366210938</v>
+        <v>94.86000061035156</v>
       </c>
       <c r="C122" t="n">
-        <v>98</v>
+        <v>95.40000152587891</v>
       </c>
       <c r="D122" t="n">
-        <v>94.69000244140625</v>
+        <v>93.87000274658203</v>
       </c>
       <c r="E122" t="n">
-        <v>94.88999938964844</v>
+        <v>94.30999755859375</v>
       </c>
       <c r="F122" t="n">
-        <v>33962900</v>
+        <v>34206900</v>
       </c>
       <c r="G122" t="n">
         <v>0</v>
@@ -3615,22 +3615,22 @@
     </row>
     <row r="123">
       <c r="A123" s="1" t="n">
-        <v>46093</v>
+        <v>46094</v>
       </c>
       <c r="B123" t="n">
-        <v>94.86000061035156</v>
+        <v>94.63999938964844</v>
       </c>
       <c r="C123" t="n">
-        <v>95.40000152587891</v>
+        <v>95.68000030517578</v>
       </c>
       <c r="D123" t="n">
-        <v>93.87000274658203</v>
+        <v>94.23999786376953</v>
       </c>
       <c r="E123" t="n">
-        <v>94.30999755859375</v>
+        <v>95.30999755859375</v>
       </c>
       <c r="F123" t="n">
-        <v>34206900</v>
+        <v>29876700</v>
       </c>
       <c r="G123" t="n">
         <v>0</v>
@@ -3641,22 +3641,22 @@
     </row>
     <row r="124">
       <c r="A124" s="1" t="n">
-        <v>46094</v>
+        <v>46097</v>
       </c>
       <c r="B124" t="n">
-        <v>94.63999938964844</v>
+        <v>95.58000183105469</v>
       </c>
       <c r="C124" t="n">
-        <v>95.68000030517578</v>
+        <v>96.09999847412109</v>
       </c>
       <c r="D124" t="n">
-        <v>94.23999786376953</v>
+        <v>94.36000061035156</v>
       </c>
       <c r="E124" t="n">
-        <v>95.30999755859375</v>
+        <v>95.19999694824219</v>
       </c>
       <c r="F124" t="n">
-        <v>29876700</v>
+        <v>34931800</v>
       </c>
       <c r="G124" t="n">
         <v>0</v>
@@ -3667,22 +3667,22 @@
     </row>
     <row r="125">
       <c r="A125" s="1" t="n">
-        <v>46097</v>
+        <v>46098</v>
       </c>
       <c r="B125" t="n">
-        <v>95.58000183105469</v>
+        <v>95.30000305175781</v>
       </c>
       <c r="C125" t="n">
-        <v>96.09999847412109</v>
+        <v>96.33999633789062</v>
       </c>
       <c r="D125" t="n">
+        <v>94.01000213623047</v>
+      </c>
+      <c r="E125" t="n">
         <v>94.36000061035156</v>
       </c>
-      <c r="E125" t="n">
-        <v>95.19999694824219</v>
-      </c>
       <c r="F125" t="n">
-        <v>34931800</v>
+        <v>26434500</v>
       </c>
       <c r="G125" t="n">
         <v>0</v>
@@ -3693,22 +3693,22 @@
     </row>
     <row r="126">
       <c r="A126" s="1" t="n">
-        <v>46098</v>
+        <v>46099</v>
       </c>
       <c r="B126" t="n">
-        <v>95.30000305175781</v>
+        <v>94.44999694824219</v>
       </c>
       <c r="C126" t="n">
-        <v>96.33999633789062</v>
+        <v>95.33999633789062</v>
       </c>
       <c r="D126" t="n">
-        <v>94.01000213623047</v>
+        <v>93.61000061035156</v>
       </c>
       <c r="E126" t="n">
-        <v>94.36000061035156</v>
+        <v>94.69999694824219</v>
       </c>
       <c r="F126" t="n">
-        <v>26434500</v>
+        <v>27878300</v>
       </c>
       <c r="G126" t="n">
         <v>0</v>
@@ -3719,22 +3719,22 @@
     </row>
     <row r="127">
       <c r="A127" s="1" t="n">
-        <v>46099</v>
+        <v>46100</v>
       </c>
       <c r="B127" t="n">
-        <v>94.44999694824219</v>
+        <v>94.30999755859375</v>
       </c>
       <c r="C127" t="n">
-        <v>95.33999633789062</v>
+        <v>95.75</v>
       </c>
       <c r="D127" t="n">
-        <v>93.61000061035156</v>
+        <v>90.77999877929688</v>
       </c>
       <c r="E127" t="n">
-        <v>94.69999694824219</v>
+        <v>91.73999786376953</v>
       </c>
       <c r="F127" t="n">
-        <v>27878300</v>
+        <v>40169300</v>
       </c>
       <c r="G127" t="n">
         <v>0</v>
@@ -3745,22 +3745,22 @@
     </row>
     <row r="128">
       <c r="A128" s="1" t="n">
-        <v>46100</v>
+        <v>46101</v>
       </c>
       <c r="B128" t="n">
-        <v>94.30999755859375</v>
+        <v>91.30999755859375</v>
       </c>
       <c r="C128" t="n">
-        <v>95.75</v>
+        <v>91.87999725341797</v>
       </c>
       <c r="D128" t="n">
-        <v>90.77999877929688</v>
+        <v>90.69000244140625</v>
       </c>
       <c r="E128" t="n">
-        <v>91.73999786376953</v>
+        <v>91.81999969482422</v>
       </c>
       <c r="F128" t="n">
-        <v>40169300</v>
+        <v>61678000</v>
       </c>
       <c r="G128" t="n">
         <v>0</v>
@@ -3771,22 +3771,22 @@
     </row>
     <row r="129">
       <c r="A129" s="1" t="n">
-        <v>46101</v>
+        <v>46104</v>
       </c>
       <c r="B129" t="n">
-        <v>91.30999755859375</v>
+        <v>92.04000091552734</v>
       </c>
       <c r="C129" t="n">
-        <v>91.87999725341797</v>
+        <v>93.98000335693359</v>
       </c>
       <c r="D129" t="n">
-        <v>90.69000244140625</v>
+        <v>91.86000061035156</v>
       </c>
       <c r="E129" t="n">
-        <v>91.81999969482422</v>
+        <v>93.37999725341797</v>
       </c>
       <c r="F129" t="n">
-        <v>61678000</v>
+        <v>34315900</v>
       </c>
       <c r="G129" t="n">
         <v>0</v>
@@ -3797,22 +3797,22 @@
     </row>
     <row r="130">
       <c r="A130" s="1" t="n">
-        <v>46104</v>
+        <v>46105</v>
       </c>
       <c r="B130" t="n">
-        <v>92.04000091552734</v>
+        <v>92.79000091552734</v>
       </c>
       <c r="C130" t="n">
-        <v>93.98000335693359</v>
+        <v>93.73999786376953</v>
       </c>
       <c r="D130" t="n">
-        <v>91.86000061035156</v>
+        <v>90.81999969482422</v>
       </c>
       <c r="E130" t="n">
-        <v>93.37999725341797</v>
+        <v>90.91999816894531</v>
       </c>
       <c r="F130" t="n">
-        <v>34315900</v>
+        <v>28938000</v>
       </c>
       <c r="G130" t="n">
         <v>0</v>
@@ -3823,22 +3823,22 @@
     </row>
     <row r="131">
       <c r="A131" s="1" t="n">
-        <v>46105</v>
+        <v>46106</v>
       </c>
       <c r="B131" t="n">
-        <v>92.79000091552734</v>
+        <v>91.70999908447266</v>
       </c>
       <c r="C131" t="n">
-        <v>93.73999786376953</v>
+        <v>92.51999664306641</v>
       </c>
       <c r="D131" t="n">
-        <v>90.81999969482422</v>
+        <v>91.23999786376953</v>
       </c>
       <c r="E131" t="n">
-        <v>90.91999816894531</v>
+        <v>92.27999877929688</v>
       </c>
       <c r="F131" t="n">
-        <v>28938000</v>
+        <v>29545600</v>
       </c>
       <c r="G131" t="n">
         <v>0</v>
@@ -3849,22 +3849,22 @@
     </row>
     <row r="132">
       <c r="A132" s="1" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B132" t="n">
-        <v>91.70999908447266</v>
+        <v>91.51999664306641</v>
       </c>
       <c r="C132" t="n">
-        <v>92.51999664306641</v>
+        <v>95.86000061035156</v>
       </c>
       <c r="D132" t="n">
-        <v>91.23999786376953</v>
+        <v>91.01000213623047</v>
       </c>
       <c r="E132" t="n">
-        <v>92.27999877929688</v>
+        <v>93.31999969482422</v>
       </c>
       <c r="F132" t="n">
-        <v>29545600</v>
+        <v>59522000</v>
       </c>
       <c r="G132" t="n">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="133">
       <c r="A133" s="1" t="n">
-        <v>46107</v>
+        <v>46108</v>
       </c>
       <c r="B133" t="n">
-        <v>91.51999664306641</v>
+        <v>94.56999969482422</v>
       </c>
       <c r="C133" t="n">
-        <v>95.86000061035156</v>
+        <v>95.58000183105469</v>
       </c>
       <c r="D133" t="n">
-        <v>91.01000213623047</v>
+        <v>92.73999786376953</v>
       </c>
       <c r="E133" t="n">
-        <v>93.31999969482422</v>
+        <v>93.43000030517578</v>
       </c>
       <c r="F133" t="n">
-        <v>59522000</v>
+        <v>44590700</v>
       </c>
       <c r="G133" t="n">
         <v>0</v>
@@ -3901,22 +3901,22 @@
     </row>
     <row r="134">
       <c r="A134" s="1" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B134" t="n">
-        <v>94.56999969482422</v>
+        <v>92.75</v>
       </c>
       <c r="C134" t="n">
-        <v>95.58000183105469</v>
+        <v>94.48999786376953</v>
       </c>
       <c r="D134" t="n">
-        <v>92.73999786376953</v>
+        <v>92.22000122070312</v>
       </c>
       <c r="E134" t="n">
-        <v>93.43000030517578</v>
+        <v>92.97000122070312</v>
       </c>
       <c r="F134" t="n">
-        <v>44590700</v>
+        <v>32375100</v>
       </c>
       <c r="G134" t="n">
         <v>0</v>
@@ -3927,22 +3927,22 @@
     </row>
     <row r="135">
       <c r="A135" s="1" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B135" t="n">
-        <v>92.75</v>
+        <v>93.02999877929688</v>
       </c>
       <c r="C135" t="n">
-        <v>94.48999786376953</v>
+        <v>96.26000213623047</v>
       </c>
       <c r="D135" t="n">
-        <v>92.22000122070312</v>
+        <v>93.02999877929688</v>
       </c>
       <c r="E135" t="n">
-        <v>92.97000122070312</v>
+        <v>96.15000152587891</v>
       </c>
       <c r="F135" t="n">
-        <v>32375100</v>
+        <v>54270000</v>
       </c>
       <c r="G135" t="n">
         <v>0</v>
@@ -3953,22 +3953,22 @@
     </row>
     <row r="136">
       <c r="A136" s="1" t="n">
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="B136" t="n">
-        <v>93.02999877929688</v>
+        <v>96.47000122070312</v>
       </c>
       <c r="C136" t="n">
-        <v>96.26000213623047</v>
+        <v>97.19999694824219</v>
       </c>
       <c r="D136" t="n">
-        <v>93.02999877929688</v>
+        <v>94.26000213623047</v>
       </c>
       <c r="E136" t="n">
-        <v>96.15000152587891</v>
+        <v>95.55000305175781</v>
       </c>
       <c r="F136" t="n">
-        <v>54270000</v>
+        <v>30439300</v>
       </c>
       <c r="G136" t="n">
         <v>0</v>
@@ -3979,22 +3979,22 @@
     </row>
     <row r="137">
       <c r="A137" s="1" t="n">
-        <v>46113</v>
+        <v>46114</v>
       </c>
       <c r="B137" t="n">
-        <v>96.47000122070312</v>
+        <v>95.26999664306641</v>
       </c>
       <c r="C137" t="n">
-        <v>97.19999694824219</v>
+        <v>98.70999908447266</v>
       </c>
       <c r="D137" t="n">
-        <v>94.26000213623047</v>
+        <v>95.16999816894531</v>
       </c>
       <c r="E137" t="n">
-        <v>95.55000305175781</v>
+        <v>98.66000366210938</v>
       </c>
       <c r="F137" t="n">
-        <v>30439300</v>
+        <v>37068000</v>
       </c>
       <c r="G137" t="n">
         <v>0</v>
@@ -4005,22 +4005,22 @@
     </row>
     <row r="138">
       <c r="A138" s="1" t="n">
-        <v>46114</v>
+        <v>46118</v>
       </c>
       <c r="B138" t="n">
-        <v>95.26999664306641</v>
+        <v>100.9599990844727</v>
       </c>
       <c r="C138" t="n">
-        <v>98.70999908447266</v>
+        <v>102.6900024414062</v>
       </c>
       <c r="D138" t="n">
-        <v>95.16999816894531</v>
+        <v>97.97000122070312</v>
       </c>
       <c r="E138" t="n">
-        <v>98.66000366210938</v>
+        <v>98.93000030517578</v>
       </c>
       <c r="F138" t="n">
-        <v>37068000</v>
+        <v>37029300</v>
       </c>
       <c r="G138" t="n">
         <v>0</v>
@@ -4031,22 +4031,22 @@
     </row>
     <row r="139">
       <c r="A139" s="1" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B139" t="n">
-        <v>100.9599990844727</v>
+        <v>98.55000305175781</v>
       </c>
       <c r="C139" t="n">
-        <v>102.6900024414062</v>
+        <v>99.87999725341797</v>
       </c>
       <c r="D139" t="n">
-        <v>97.97000122070312</v>
+        <v>98.25</v>
       </c>
       <c r="E139" t="n">
-        <v>98.93000030517578</v>
+        <v>98.81999969482422</v>
       </c>
       <c r="F139" t="n">
-        <v>37029300</v>
+        <v>25016700</v>
       </c>
       <c r="G139" t="n">
         <v>0</v>
@@ -4057,22 +4057,22 @@
     </row>
     <row r="140">
       <c r="A140" s="1" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B140" t="n">
-        <v>98.55000305175781</v>
+        <v>100.3199996948242</v>
       </c>
       <c r="C140" t="n">
-        <v>99.87999725341797</v>
+        <v>100.4000015258789</v>
       </c>
       <c r="D140" t="n">
-        <v>98.25</v>
+        <v>97.44000244140625</v>
       </c>
       <c r="E140" t="n">
-        <v>98.81999969482422</v>
+        <v>99.38999938964844</v>
       </c>
       <c r="F140" t="n">
-        <v>25016700</v>
+        <v>30957600</v>
       </c>
       <c r="G140" t="n">
         <v>0</v>
@@ -4083,22 +4083,22 @@
     </row>
     <row r="141">
       <c r="A141" s="1" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B141" t="n">
-        <v>100.3199996948242</v>
+        <v>99.62999725341797</v>
       </c>
       <c r="C141" t="n">
-        <v>100.4000015258789</v>
+        <v>102.3399963378906</v>
       </c>
       <c r="D141" t="n">
-        <v>97.44000244140625</v>
+        <v>99.08000183105469</v>
       </c>
       <c r="E141" t="n">
-        <v>99.38999938964844</v>
+        <v>102.0500030517578</v>
       </c>
       <c r="F141" t="n">
-        <v>30957600</v>
+        <v>35087800</v>
       </c>
       <c r="G141" t="n">
         <v>0</v>
@@ -4109,22 +4109,22 @@
     </row>
     <row r="142">
       <c r="A142" s="1" t="n">
-        <v>46121</v>
+        <v>46122</v>
       </c>
       <c r="B142" t="n">
-        <v>99.62999725341797</v>
+        <v>102.4700012207031</v>
       </c>
       <c r="C142" t="n">
-        <v>102.3399963378906</v>
+        <v>103.0800018310547</v>
       </c>
       <c r="D142" t="n">
-        <v>99.08000183105469</v>
+        <v>101.4599990844727</v>
       </c>
       <c r="E142" t="n">
-        <v>102.0500030517578</v>
+        <v>103.0100021362305</v>
       </c>
       <c r="F142" t="n">
-        <v>35087800</v>
+        <v>25769900</v>
       </c>
       <c r="G142" t="n">
         <v>0</v>
@@ -4135,22 +4135,22 @@
     </row>
     <row r="143">
       <c r="A143" s="1" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B143" t="n">
-        <v>102.4700012207031</v>
+        <v>103.0299987792969</v>
       </c>
       <c r="C143" t="n">
-        <v>103.0800018310547</v>
+        <v>103.6699981689453</v>
       </c>
       <c r="D143" t="n">
-        <v>101.4599990844727</v>
+        <v>102.0599975585938</v>
       </c>
       <c r="E143" t="n">
-        <v>103.0100021362305</v>
+        <v>103.1600036621094</v>
       </c>
       <c r="F143" t="n">
-        <v>25769900</v>
+        <v>26042800</v>
       </c>
       <c r="G143" t="n">
         <v>0</v>
@@ -4161,22 +4161,22 @@
     </row>
     <row r="144">
       <c r="A144" s="1" t="n">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="B144" t="n">
-        <v>103.0299987792969</v>
+        <v>103.120002746582</v>
       </c>
       <c r="C144" t="n">
-        <v>103.6699981689453</v>
+        <v>106.5699996948242</v>
       </c>
       <c r="D144" t="n">
-        <v>102.0599975585938</v>
+        <v>103.0400009155273</v>
       </c>
       <c r="E144" t="n">
-        <v>103.1600036621094</v>
+        <v>106.2799987792969</v>
       </c>
       <c r="F144" t="n">
-        <v>26042800</v>
+        <v>40534900</v>
       </c>
       <c r="G144" t="n">
         <v>0</v>
@@ -4187,22 +4187,22 @@
     </row>
     <row r="145">
       <c r="A145" s="1" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B145" t="n">
-        <v>103.120002746582</v>
+        <v>105.9800033569336</v>
       </c>
       <c r="C145" t="n">
-        <v>106.5699996948242</v>
+        <v>107.8499984741211</v>
       </c>
       <c r="D145" t="n">
-        <v>103.0400009155273</v>
+        <v>105.0400009155273</v>
       </c>
       <c r="E145" t="n">
-        <v>106.2799987792969</v>
+        <v>107.7099990844727</v>
       </c>
       <c r="F145" t="n">
-        <v>40534900</v>
+        <v>38023700</v>
       </c>
       <c r="G145" t="n">
         <v>0</v>
@@ -4213,22 +4213,22 @@
     </row>
     <row r="146">
       <c r="A146" s="1" t="n">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c r="B146" t="n">
-        <v>105.9800033569336</v>
+        <v>107.4700012207031</v>
       </c>
       <c r="C146" t="n">
-        <v>107.8499984741211</v>
+        <v>108.9499969482422</v>
       </c>
       <c r="D146" t="n">
-        <v>105.0400009155273</v>
+        <v>106.620002746582</v>
       </c>
       <c r="E146" t="n">
-        <v>107.7099990844727</v>
+        <v>107.7900009155273</v>
       </c>
       <c r="F146" t="n">
-        <v>38023700</v>
+        <v>64928300</v>
       </c>
       <c r="G146" t="n">
         <v>0</v>
@@ -4239,22 +4239,22 @@
     </row>
     <row r="147">
       <c r="A147" s="1" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B147" t="n">
-        <v>107.4700012207031</v>
+        <v>96.37000274658203</v>
       </c>
       <c r="C147" t="n">
-        <v>108.9499969482422</v>
+        <v>98.73999786376953</v>
       </c>
       <c r="D147" t="n">
-        <v>106.620002746582</v>
+        <v>95.09999847412109</v>
       </c>
       <c r="E147" t="n">
-        <v>107.7900009155273</v>
+        <v>97.30999755859375</v>
       </c>
       <c r="F147" t="n">
-        <v>64928300</v>
+        <v>125958700</v>
       </c>
       <c r="G147" t="n">
         <v>0</v>
@@ -4265,22 +4265,22 @@
     </row>
     <row r="148">
       <c r="A148" s="1" t="n">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c r="B148" t="n">
-        <v>96.37000274658203</v>
+        <v>97.13999938964844</v>
       </c>
       <c r="C148" t="n">
-        <v>98.73999786376953</v>
+        <v>97.59999847412109</v>
       </c>
       <c r="D148" t="n">
-        <v>95.09999847412109</v>
+        <v>93.54000091552734</v>
       </c>
       <c r="E148" t="n">
-        <v>97.30999755859375</v>
+        <v>94.83000183105469</v>
       </c>
       <c r="F148" t="n">
-        <v>125958700</v>
+        <v>63298300</v>
       </c>
       <c r="G148" t="n">
         <v>0</v>
@@ -4291,22 +4291,22 @@
     </row>
     <row r="149">
       <c r="A149" s="1" t="n">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="B149" t="n">
-        <v>97.13999938964844</v>
+        <v>94</v>
       </c>
       <c r="C149" t="n">
-        <v>97.59999847412109</v>
+        <v>94.65000152587891</v>
       </c>
       <c r="D149" t="n">
-        <v>93.54000091552734</v>
+        <v>92.37000274658203</v>
       </c>
       <c r="E149" t="n">
-        <v>94.83000183105469</v>
+        <v>92.58000183105469</v>
       </c>
       <c r="F149" t="n">
-        <v>63298300</v>
+        <v>61962300</v>
       </c>
       <c r="G149" t="n">
         <v>0</v>
@@ -4317,22 +4317,22 @@
     </row>
     <row r="150">
       <c r="A150" s="1" t="n">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="B150" t="n">
-        <v>94</v>
+        <v>93.05999755859375</v>
       </c>
       <c r="C150" t="n">
-        <v>94.65000152587891</v>
+        <v>93.84999847412109</v>
       </c>
       <c r="D150" t="n">
-        <v>92.37000274658203</v>
+        <v>92.76999664306641</v>
       </c>
       <c r="E150" t="n">
-        <v>92.58000183105469</v>
+        <v>93.23999786376953</v>
       </c>
       <c r="F150" t="n">
-        <v>61962300</v>
+        <v>33694300</v>
       </c>
       <c r="G150" t="n">
         <v>0</v>
@@ -4343,22 +4343,22 @@
     </row>
     <row r="151">
       <c r="A151" s="1" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B151" t="n">
-        <v>93.05999755859375</v>
+        <v>94.05999755859375</v>
       </c>
       <c r="C151" t="n">
-        <v>93.84999847412109</v>
+        <v>94.63999938964844</v>
       </c>
       <c r="D151" t="n">
-        <v>92.76999664306641</v>
+        <v>92.06999969482422</v>
       </c>
       <c r="E151" t="n">
-        <v>93.23999786376953</v>
+        <v>92.81999969482422</v>
       </c>
       <c r="F151" t="n">
-        <v>33694300</v>
+        <v>36851700</v>
       </c>
       <c r="G151" t="n">
         <v>0</v>
@@ -4369,22 +4369,22 @@
     </row>
     <row r="152">
       <c r="A152" s="1" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B152" t="n">
-        <v>94.05999755859375</v>
+        <v>92.56999969482422</v>
       </c>
       <c r="C152" t="n">
-        <v>94.63999938964844</v>
+        <v>93.27999877929688</v>
       </c>
       <c r="D152" t="n">
-        <v>92.06999969482422</v>
+        <v>91.80000305175781</v>
       </c>
       <c r="E152" t="n">
-        <v>92.81999969482422</v>
+        <v>92.44000244140625</v>
       </c>
       <c r="F152" t="n">
-        <v>36851700</v>
+        <v>32553200</v>
       </c>
       <c r="G152" t="n">
         <v>0</v>
@@ -4395,22 +4395,22 @@
     </row>
     <row r="153">
       <c r="A153" s="1" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B153" t="n">
-        <v>92.56999969482422</v>
+        <v>92.05000305175781</v>
       </c>
       <c r="C153" t="n">
-        <v>93.27999877929688</v>
+        <v>92.83999633789062</v>
       </c>
       <c r="D153" t="n">
-        <v>91.80000305175781</v>
+        <v>91.30000305175781</v>
       </c>
       <c r="E153" t="n">
-        <v>92.44000244140625</v>
+        <v>91.37000274658203</v>
       </c>
       <c r="F153" t="n">
-        <v>32553200</v>
+        <v>29707400</v>
       </c>
       <c r="G153" t="n">
         <v>0</v>
@@ -4421,22 +4421,22 @@
     </row>
     <row r="154">
       <c r="A154" s="1" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B154" t="n">
-        <v>92.05000305175781</v>
+        <v>91.5</v>
       </c>
       <c r="C154" t="n">
-        <v>92.83999633789062</v>
+        <v>92.33999633789062</v>
       </c>
       <c r="D154" t="n">
-        <v>91.30000305175781</v>
+        <v>90.01999664306641</v>
       </c>
       <c r="E154" t="n">
-        <v>91.37000274658203</v>
+        <v>92.26999664306641</v>
       </c>
       <c r="F154" t="n">
-        <v>29707400</v>
+        <v>33418100</v>
       </c>
       <c r="G154" t="n">
         <v>0</v>
@@ -4447,22 +4447,22 @@
     </row>
     <row r="155">
       <c r="A155" s="1" t="n">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="B155" t="n">
-        <v>91.5</v>
+        <v>91.23000335693359</v>
       </c>
       <c r="C155" t="n">
-        <v>92.33999633789062</v>
+        <v>92.86000061035156</v>
       </c>
       <c r="D155" t="n">
-        <v>90.01999664306641</v>
+        <v>90.86000061035156</v>
       </c>
       <c r="E155" t="n">
-        <v>92.26999664306641</v>
+        <v>92.12000274658203</v>
       </c>
       <c r="F155" t="n">
-        <v>33418100</v>
+        <v>26122100</v>
       </c>
       <c r="G155" t="n">
         <v>0</v>
@@ -4473,22 +4473,22 @@
     </row>
     <row r="156">
       <c r="A156" s="1" t="n">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="B156" t="n">
-        <v>91.23000335693359</v>
+        <v>91.34999847412109</v>
       </c>
       <c r="C156" t="n">
-        <v>92.86000061035156</v>
+        <v>94.22000122070312</v>
       </c>
       <c r="D156" t="n">
-        <v>90.86000061035156</v>
+        <v>90.76999664306641</v>
       </c>
       <c r="E156" t="n">
-        <v>92.12000274658203</v>
+        <v>93.61000061035156</v>
       </c>
       <c r="F156" t="n">
-        <v>26122100</v>
+        <v>40923000</v>
       </c>
       <c r="G156" t="n">
         <v>0</v>
@@ -4499,22 +4499,22 @@
     </row>
     <row r="157">
       <c r="A157" s="1" t="n">
-        <v>46142</v>
+        <v>46143</v>
       </c>
       <c r="B157" t="n">
-        <v>91.34999847412109</v>
+        <v>94.41999816894531</v>
       </c>
       <c r="C157" t="n">
-        <v>94.22000122070312</v>
+        <v>94.69999694824219</v>
       </c>
       <c r="D157" t="n">
-        <v>90.76999664306641</v>
+        <v>91.90000152587891</v>
       </c>
       <c r="E157" t="n">
-        <v>93.61000061035156</v>
+        <v>92.05999755859375</v>
       </c>
       <c r="F157" t="n">
-        <v>40923000</v>
+        <v>30406900</v>
       </c>
       <c r="G157" t="n">
         <v>0</v>
@@ -4525,22 +4525,22 @@
     </row>
     <row r="158">
       <c r="A158" s="1" t="n">
-        <v>46143</v>
+        <v>46146</v>
       </c>
       <c r="B158" t="n">
-        <v>94.41999816894531</v>
+        <v>92.09999847412109</v>
       </c>
       <c r="C158" t="n">
-        <v>94.69999694824219</v>
+        <v>92.33000183105469</v>
       </c>
       <c r="D158" t="n">
-        <v>91.90000152587891</v>
+        <v>90.88999938964844</v>
       </c>
       <c r="E158" t="n">
-        <v>92.05999755859375</v>
+        <v>91.01999664306641</v>
       </c>
       <c r="F158" t="n">
-        <v>30406900</v>
+        <v>25928800</v>
       </c>
       <c r="G158" t="n">
         <v>0</v>
@@ -4551,22 +4551,22 @@
     </row>
     <row r="159">
       <c r="A159" s="1" t="n">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="B159" t="n">
-        <v>92.09999847412109</v>
+        <v>91.18000030517578</v>
       </c>
       <c r="C159" t="n">
-        <v>92.33000183105469</v>
+        <v>91.27999877929688</v>
       </c>
       <c r="D159" t="n">
-        <v>90.88999938964844</v>
+        <v>87.56999969482422</v>
       </c>
       <c r="E159" t="n">
-        <v>91.01999664306641</v>
+        <v>87.88999938964844</v>
       </c>
       <c r="F159" t="n">
-        <v>25928800</v>
+        <v>51961300</v>
       </c>
       <c r="G159" t="n">
         <v>0</v>
@@ -4577,22 +4577,22 @@
     </row>
     <row r="160">
       <c r="A160" s="1" t="n">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="B160" t="n">
-        <v>91.18000030517578</v>
+        <v>87.15000152587891</v>
       </c>
       <c r="C160" t="n">
-        <v>91.27999877929688</v>
+        <v>88.55000305175781</v>
       </c>
       <c r="D160" t="n">
-        <v>87.56999969482422</v>
+        <v>86.72000122070312</v>
       </c>
       <c r="E160" t="n">
-        <v>87.88999938964844</v>
+        <v>88.26999664306641</v>
       </c>
       <c r="F160" t="n">
-        <v>51961300</v>
+        <v>41932400</v>
       </c>
       <c r="G160" t="n">
         <v>0</v>
@@ -4603,22 +4603,22 @@
     </row>
     <row r="161">
       <c r="A161" s="1" t="n">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="B161" t="n">
-        <v>87.15000152587891</v>
+        <v>88.19999694824219</v>
       </c>
       <c r="C161" t="n">
-        <v>88.55000305175781</v>
+        <v>89.40000152587891</v>
       </c>
       <c r="D161" t="n">
-        <v>86.72000122070312</v>
+        <v>88.12999725341797</v>
       </c>
       <c r="E161" t="n">
-        <v>88.26999664306641</v>
+        <v>88.25</v>
       </c>
       <c r="F161" t="n">
-        <v>41932400</v>
+        <v>30627600</v>
       </c>
       <c r="G161" t="n">
         <v>0</v>
@@ -4629,22 +4629,22 @@
     </row>
     <row r="162">
       <c r="A162" s="1" t="n">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="B162" t="n">
-        <v>88.19999694824219</v>
+        <v>87.70999908447266</v>
       </c>
       <c r="C162" t="n">
-        <v>89.40000152587891</v>
+        <v>88.04000091552734</v>
       </c>
       <c r="D162" t="n">
-        <v>88.12999725341797</v>
+        <v>87.20999908447266</v>
       </c>
       <c r="E162" t="n">
-        <v>88.25</v>
+        <v>87.48999786376953</v>
       </c>
       <c r="F162" t="n">
-        <v>30627600</v>
+        <v>36215100</v>
       </c>
       <c r="G162" t="n">
         <v>0</v>
@@ -4655,22 +4655,22 @@
     </row>
     <row r="163">
       <c r="A163" s="1" t="n">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="B163" t="n">
-        <v>87.70999908447266</v>
+        <v>86.52999877929688</v>
       </c>
       <c r="C163" t="n">
-        <v>88.04000091552734</v>
+        <v>87.33999633789062</v>
       </c>
       <c r="D163" t="n">
-        <v>87.20999908447266</v>
+        <v>85.09999847412109</v>
       </c>
       <c r="E163" t="n">
-        <v>87.48999786376953</v>
+        <v>85.44999694824219</v>
       </c>
       <c r="F163" t="n">
-        <v>36215100</v>
+        <v>40556500</v>
       </c>
       <c r="G163" t="n">
         <v>0</v>
@@ -4681,22 +4681,22 @@
     </row>
     <row r="164">
       <c r="A164" s="1" t="n">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="B164" t="n">
-        <v>86.52999877929688</v>
+        <v>85.91000366210938</v>
       </c>
       <c r="C164" t="n">
-        <v>87.33999633789062</v>
+        <v>89.16999816894531</v>
       </c>
       <c r="D164" t="n">
-        <v>85.09999847412109</v>
+        <v>85.80999755859375</v>
       </c>
       <c r="E164" t="n">
-        <v>85.44999694824219</v>
+        <v>87.66000366210938</v>
       </c>
       <c r="F164" t="n">
-        <v>40556500</v>
+        <v>43556600</v>
       </c>
       <c r="G164" t="n">
         <v>0</v>
@@ -4707,22 +4707,22 @@
     </row>
     <row r="165">
       <c r="A165" s="1" t="n">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="B165" t="n">
-        <v>85.91000366210938</v>
+        <v>86.56999969482422</v>
       </c>
       <c r="C165" t="n">
-        <v>89.16999816894531</v>
+        <v>88.62000274658203</v>
       </c>
       <c r="D165" t="n">
-        <v>85.80999755859375</v>
+        <v>86.27999877929688</v>
       </c>
       <c r="E165" t="n">
-        <v>87.66000366210938</v>
+        <v>87.55999755859375</v>
       </c>
       <c r="F165" t="n">
-        <v>43556600</v>
+        <v>30823500</v>
       </c>
       <c r="G165" t="n">
         <v>0</v>
@@ -4733,22 +4733,22 @@
     </row>
     <row r="166">
       <c r="A166" s="1" t="n">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="B166" t="n">
-        <v>86.56999969482422</v>
+        <v>87.62000274658203</v>
       </c>
       <c r="C166" t="n">
-        <v>88.62000274658203</v>
+        <v>88.5</v>
       </c>
       <c r="D166" t="n">
-        <v>86.27999877929688</v>
+        <v>86.65000152587891</v>
       </c>
       <c r="E166" t="n">
-        <v>87.55999755859375</v>
+        <v>86.94000244140625</v>
       </c>
       <c r="F166" t="n">
-        <v>30823500</v>
+        <v>29408300</v>
       </c>
       <c r="G166" t="n">
         <v>0</v>
@@ -4759,22 +4759,22 @@
     </row>
     <row r="167">
       <c r="A167" s="1" t="n">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="B167" t="n">
-        <v>87.62000274658203</v>
+        <v>87.69000244140625</v>
       </c>
       <c r="C167" t="n">
-        <v>88.5</v>
+        <v>89.48999786376953</v>
       </c>
       <c r="D167" t="n">
-        <v>86.65000152587891</v>
+        <v>86.69000244140625</v>
       </c>
       <c r="E167" t="n">
-        <v>86.94000244140625</v>
+        <v>87.01999664306641</v>
       </c>
       <c r="F167" t="n">
-        <v>29408300</v>
+        <v>32335700</v>
       </c>
       <c r="G167" t="n">
         <v>0</v>
@@ -4785,22 +4785,22 @@
     </row>
     <row r="168">
       <c r="A168" s="1" t="n">
-        <v>46157</v>
+        <v>46160</v>
       </c>
       <c r="B168" t="n">
-        <v>87.69000244140625</v>
+        <v>86.5</v>
       </c>
       <c r="C168" t="n">
-        <v>89.48999786376953</v>
+        <v>89.81999969482422</v>
       </c>
       <c r="D168" t="n">
-        <v>86.69000244140625</v>
+        <v>86.33000183105469</v>
       </c>
       <c r="E168" t="n">
-        <v>87.01999664306641</v>
+        <v>89.65000152587891</v>
       </c>
       <c r="F168" t="n">
-        <v>32335700</v>
+        <v>35800500</v>
       </c>
       <c r="G168" t="n">
         <v>0</v>
@@ -4811,22 +4811,22 @@
     </row>
     <row r="169">
       <c r="A169" s="1" t="n">
-        <v>46160</v>
+        <v>46161</v>
       </c>
       <c r="B169" t="n">
-        <v>86.5</v>
+        <v>90.13999938964844</v>
       </c>
       <c r="C169" t="n">
-        <v>89.81999969482422</v>
+        <v>91.48000335693359</v>
       </c>
       <c r="D169" t="n">
-        <v>86.33000183105469</v>
+        <v>88.69000244140625</v>
       </c>
       <c r="E169" t="n">
-        <v>89.65000152587891</v>
+        <v>89.33000183105469</v>
       </c>
       <c r="F169" t="n">
-        <v>35800500</v>
+        <v>34545700</v>
       </c>
       <c r="G169" t="n">
         <v>0</v>
@@ -4837,22 +4837,22 @@
     </row>
     <row r="170">
       <c r="A170" s="1" t="n">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="B170" t="n">
-        <v>90.13999938964844</v>
+        <v>88.51999664306641</v>
       </c>
       <c r="C170" t="n">
-        <v>91.48000335693359</v>
+        <v>88.55000305175781</v>
       </c>
       <c r="D170" t="n">
-        <v>88.69000244140625</v>
+        <v>87.5</v>
       </c>
       <c r="E170" t="n">
-        <v>89.33000183105469</v>
+        <v>88.08999633789062</v>
       </c>
       <c r="F170" t="n">
-        <v>34545700</v>
+        <v>23463400</v>
       </c>
       <c r="G170" t="n">
         <v>0</v>
@@ -4863,22 +4863,22 @@
     </row>
     <row r="171">
       <c r="A171" s="1" t="n">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="B171" t="n">
-        <v>88.51999664306641</v>
+        <v>88.02999877929688</v>
       </c>
       <c r="C171" t="n">
-        <v>88.55000305175781</v>
+        <v>90.37000274658203</v>
       </c>
       <c r="D171" t="n">
-        <v>87.5</v>
+        <v>87.51999664306641</v>
       </c>
       <c r="E171" t="n">
-        <v>88.08999633789062</v>
+        <v>89.30000305175781</v>
       </c>
       <c r="F171" t="n">
-        <v>23463400</v>
+        <v>28613900</v>
       </c>
       <c r="G171" t="n">
         <v>0</v>
@@ -4889,22 +4889,22 @@
     </row>
     <row r="172">
       <c r="A172" s="1" t="n">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="B172" t="n">
-        <v>88.02999877929688</v>
+        <v>89.09999847412109</v>
       </c>
       <c r="C172" t="n">
-        <v>90.37000274658203</v>
+        <v>89.97000122070312</v>
       </c>
       <c r="D172" t="n">
-        <v>87.51999664306641</v>
+        <v>88.16999816894531</v>
       </c>
       <c r="E172" t="n">
-        <v>89.30000305175781</v>
+        <v>88.59999847412109</v>
       </c>
       <c r="F172" t="n">
-        <v>28613900</v>
+        <v>23847200</v>
       </c>
       <c r="G172" t="n">
         <v>0</v>
@@ -4915,22 +4915,22 @@
     </row>
     <row r="173">
       <c r="A173" s="1" t="n">
-        <v>46164</v>
+        <v>46168</v>
       </c>
       <c r="B173" t="n">
-        <v>89.09999847412109</v>
+        <v>88.40000152587891</v>
       </c>
       <c r="C173" t="n">
-        <v>89.97000122070312</v>
+        <v>88.73000335693359</v>
       </c>
       <c r="D173" t="n">
-        <v>88.16999816894531</v>
+        <v>87.25</v>
       </c>
       <c r="E173" t="n">
-        <v>88.59999847412109</v>
+        <v>87.68000030517578</v>
       </c>
       <c r="F173" t="n">
-        <v>23847200</v>
+        <v>24014500</v>
       </c>
       <c r="G173" t="n">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="174">
       <c r="A174" s="1" t="n">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="B174" t="n">
-        <v>88.40000152587891</v>
+        <v>87.05000305175781</v>
       </c>
       <c r="C174" t="n">
-        <v>88.73000335693359</v>
+        <v>88.5</v>
       </c>
       <c r="D174" t="n">
-        <v>87.25</v>
+        <v>86.81999969482422</v>
       </c>
       <c r="E174" t="n">
-        <v>87.68000030517578</v>
+        <v>87.34999847412109</v>
       </c>
       <c r="F174" t="n">
-        <v>24014500</v>
+        <v>22569500</v>
       </c>
       <c r="G174" t="n">
         <v>0</v>
@@ -4967,22 +4967,22 @@
     </row>
     <row r="175">
       <c r="A175" s="1" t="n">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="B175" t="n">
-        <v>87.05000305175781</v>
+        <v>86.90000152587891</v>
       </c>
       <c r="C175" t="n">
-        <v>88.5</v>
+        <v>87.04000091552734</v>
       </c>
       <c r="D175" t="n">
-        <v>86.81999969482422</v>
+        <v>85.58999633789062</v>
       </c>
       <c r="E175" t="n">
-        <v>87.34999847412109</v>
+        <v>86.36000061035156</v>
       </c>
       <c r="F175" t="n">
-        <v>22569500</v>
+        <v>38803800</v>
       </c>
       <c r="G175" t="n">
         <v>0</v>
@@ -4993,22 +4993,22 @@
     </row>
     <row r="176">
       <c r="A176" s="1" t="n">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="B176" t="n">
-        <v>86.90000152587891</v>
+        <v>86.19999694824219</v>
       </c>
       <c r="C176" t="n">
-        <v>87.04000091552734</v>
+        <v>86.66999816894531</v>
       </c>
       <c r="D176" t="n">
-        <v>85.58999633789062</v>
+        <v>85.66000366210938</v>
       </c>
       <c r="E176" t="n">
-        <v>86.36000061035156</v>
+        <v>86.01999664306641</v>
       </c>
       <c r="F176" t="n">
-        <v>38803800</v>
+        <v>39793600</v>
       </c>
       <c r="G176" t="n">
         <v>0</v>
@@ -5019,22 +5019,22 @@
     </row>
     <row r="177">
       <c r="A177" s="1" t="n">
-        <v>46171</v>
+        <v>46174</v>
       </c>
       <c r="B177" t="n">
-        <v>86.19999694824219</v>
+        <v>85.73000335693359</v>
       </c>
       <c r="C177" t="n">
-        <v>86.66999816894531</v>
+        <v>87.23000335693359</v>
       </c>
       <c r="D177" t="n">
-        <v>85.66000366210938</v>
+        <v>85.31999969482422</v>
       </c>
       <c r="E177" t="n">
-        <v>86.01999664306641</v>
+        <v>85.84999847412109</v>
       </c>
       <c r="F177" t="n">
-        <v>39793600</v>
+        <v>32747200</v>
       </c>
       <c r="G177" t="n">
         <v>0</v>
@@ -5045,22 +5045,22 @@
     </row>
     <row r="178">
       <c r="A178" s="1" t="n">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="B178" t="n">
-        <v>85.73000335693359</v>
+        <v>85.61000061035156</v>
       </c>
       <c r="C178" t="n">
-        <v>87.23000335693359</v>
+        <v>85.98000335693359</v>
       </c>
       <c r="D178" t="n">
-        <v>85.31999969482422</v>
+        <v>83.29000091552734</v>
       </c>
       <c r="E178" t="n">
-        <v>85.84999847412109</v>
+        <v>83.33000183105469</v>
       </c>
       <c r="F178" t="n">
-        <v>32747200</v>
+        <v>42947200</v>
       </c>
       <c r="G178" t="n">
         <v>0</v>
@@ -5071,22 +5071,22 @@
     </row>
     <row r="179">
       <c r="A179" s="1" t="n">
-        <v>46175</v>
+        <v>46176</v>
       </c>
       <c r="B179" t="n">
-        <v>85.61000061035156</v>
+        <v>82.91000366210938</v>
       </c>
       <c r="C179" t="n">
-        <v>85.98000335693359</v>
+        <v>83.30999755859375</v>
       </c>
       <c r="D179" t="n">
-        <v>83.29000091552734</v>
+        <v>81.09999847412109</v>
       </c>
       <c r="E179" t="n">
-        <v>83.33000183105469</v>
+        <v>81.51999664306641</v>
       </c>
       <c r="F179" t="n">
-        <v>42947200</v>
+        <v>36714700</v>
       </c>
       <c r="G179" t="n">
         <v>0</v>
@@ -5097,22 +5097,22 @@
     </row>
     <row r="180">
       <c r="A180" s="1" t="n">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="B180" t="n">
-        <v>82.91000366210938</v>
+        <v>83.19000244140625</v>
       </c>
       <c r="C180" t="n">
-        <v>83.30999755859375</v>
+        <v>83.69999694824219</v>
       </c>
       <c r="D180" t="n">
-        <v>81.09999847412109</v>
+        <v>81.37000274658203</v>
       </c>
       <c r="E180" t="n">
-        <v>81.51999664306641</v>
+        <v>81.55999755859375</v>
       </c>
       <c r="F180" t="n">
-        <v>36714700</v>
+        <v>39338800</v>
       </c>
       <c r="G180" t="n">
         <v>0</v>
@@ -5123,22 +5123,22 @@
     </row>
     <row r="181">
       <c r="A181" s="1" t="n">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="B181" t="n">
-        <v>83.19000244140625</v>
+        <v>82.33000183105469</v>
       </c>
       <c r="C181" t="n">
-        <v>83.69999694824219</v>
+        <v>82.75</v>
       </c>
       <c r="D181" t="n">
-        <v>81.37000274658203</v>
+        <v>81</v>
       </c>
       <c r="E181" t="n">
-        <v>81.55999755859375</v>
+        <v>82.18000030517578</v>
       </c>
       <c r="F181" t="n">
-        <v>39338800</v>
+        <v>43474100</v>
       </c>
       <c r="G181" t="n">
         <v>0</v>
@@ -5149,22 +5149,22 @@
     </row>
     <row r="182">
       <c r="A182" s="1" t="n">
-        <v>46178</v>
+        <v>46181</v>
       </c>
       <c r="B182" t="n">
-        <v>82.33000183105469</v>
+        <v>81.66000366210938</v>
       </c>
       <c r="C182" t="n">
-        <v>82.75</v>
+        <v>83.08000183105469</v>
       </c>
       <c r="D182" t="n">
-        <v>81</v>
+        <v>81.33999633789062</v>
       </c>
       <c r="E182" t="n">
-        <v>82.18000030517578</v>
+        <v>82.63999938964844</v>
       </c>
       <c r="F182" t="n">
-        <v>43474100</v>
+        <v>33056700</v>
       </c>
       <c r="G182" t="n">
         <v>0</v>
@@ -5175,22 +5175,22 @@
     </row>
     <row r="183">
       <c r="A183" s="1" t="n">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="B183" t="n">
-        <v>81.66000366210938</v>
+        <v>82.12999725341797</v>
       </c>
       <c r="C183" t="n">
-        <v>83.08000183105469</v>
+        <v>82.33999633789062</v>
       </c>
       <c r="D183" t="n">
         <v>81.33999633789062</v>
       </c>
       <c r="E183" t="n">
-        <v>82.63999938964844</v>
+        <v>81.41000366210938</v>
       </c>
       <c r="F183" t="n">
-        <v>33056700</v>
+        <v>34787200</v>
       </c>
       <c r="G183" t="n">
         <v>0</v>
@@ -5201,22 +5201,22 @@
     </row>
     <row r="184">
       <c r="A184" s="1" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="B184" t="n">
-        <v>82.12999725341797</v>
+        <v>81.70999908447266</v>
       </c>
       <c r="C184" t="n">
-        <v>82.33999633789062</v>
+        <v>82.75</v>
       </c>
       <c r="D184" t="n">
-        <v>81.33999633789062</v>
+        <v>80.98000335693359</v>
       </c>
       <c r="E184" t="n">
-        <v>81.41000366210938</v>
+        <v>82</v>
       </c>
       <c r="F184" t="n">
-        <v>34787200</v>
+        <v>36304600</v>
       </c>
       <c r="G184" t="n">
         <v>0</v>
@@ -5227,22 +5227,22 @@
     </row>
     <row r="185">
       <c r="A185" s="1" t="n">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="B185" t="n">
-        <v>81.70999908447266</v>
+        <v>81.87000274658203</v>
       </c>
       <c r="C185" t="n">
-        <v>82.75</v>
+        <v>82.09999847412109</v>
       </c>
       <c r="D185" t="n">
-        <v>80.98000335693359</v>
+        <v>80.08999633789062</v>
       </c>
       <c r="E185" t="n">
-        <v>82</v>
+        <v>81.26999664306641</v>
       </c>
       <c r="F185" t="n">
-        <v>36304600</v>
+        <v>33417600</v>
       </c>
       <c r="G185" t="n">
         <v>0</v>
@@ -5253,22 +5253,22 @@
     </row>
     <row r="186">
       <c r="A186" s="1" t="n">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="B186" t="n">
-        <v>81.87000274658203</v>
+        <v>81.58000183105469</v>
       </c>
       <c r="C186" t="n">
-        <v>82.09999847412109</v>
+        <v>82</v>
       </c>
       <c r="D186" t="n">
-        <v>80.08999633789062</v>
+        <v>79.27999877929688</v>
       </c>
       <c r="E186" t="n">
-        <v>81.26999664306641</v>
+        <v>80.33999633789062</v>
       </c>
       <c r="F186" t="n">
-        <v>33417600</v>
+        <v>35309700</v>
       </c>
       <c r="G186" t="n">
         <v>0</v>
@@ -5279,22 +5279,22 @@
     </row>
     <row r="187">
       <c r="A187" s="1" t="n">
-        <v>46185</v>
+        <v>46188</v>
       </c>
       <c r="B187" t="n">
-        <v>81.58000183105469</v>
+        <v>80.62000274658203</v>
       </c>
       <c r="C187" t="n">
-        <v>82</v>
+        <v>81.70999908447266</v>
       </c>
       <c r="D187" t="n">
-        <v>79.27999877929688</v>
+        <v>80.45999908447266</v>
       </c>
       <c r="E187" t="n">
-        <v>80.33999633789062</v>
+        <v>81.66999816894531</v>
       </c>
       <c r="F187" t="n">
-        <v>35309700</v>
+        <v>36430800</v>
       </c>
       <c r="G187" t="n">
         <v>0</v>
@@ -5305,22 +5305,22 @@
     </row>
     <row r="188">
       <c r="A188" s="1" t="n">
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="B188" t="n">
-        <v>80.62000274658203</v>
+        <v>81.90000152587891</v>
       </c>
       <c r="C188" t="n">
-        <v>81.70999908447266</v>
+        <v>81.93000030517578</v>
       </c>
       <c r="D188" t="n">
-        <v>80.45999908447266</v>
+        <v>77.70999908447266</v>
       </c>
       <c r="E188" t="n">
-        <v>81.66999816894531</v>
+        <v>78.72000122070312</v>
       </c>
       <c r="F188" t="n">
-        <v>36430800</v>
+        <v>65054000</v>
       </c>
       <c r="G188" t="n">
         <v>0</v>
@@ -5331,22 +5331,22 @@
     </row>
     <row r="189">
       <c r="A189" s="1" t="n">
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="B189" t="n">
-        <v>81.90000152587891</v>
+        <v>78.09999847412109</v>
       </c>
       <c r="C189" t="n">
-        <v>81.93000030517578</v>
+        <v>78.44999694824219</v>
       </c>
       <c r="D189" t="n">
-        <v>77.70999908447266</v>
+        <v>76.76000213623047</v>
       </c>
       <c r="E189" t="n">
-        <v>78.72000122070312</v>
+        <v>76.95999908447266</v>
       </c>
       <c r="F189" t="n">
-        <v>65054000</v>
+        <v>50338800</v>
       </c>
       <c r="G189" t="n">
         <v>0</v>
@@ -5357,22 +5357,22 @@
     </row>
     <row r="190">
       <c r="A190" s="1" t="n">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="B190" t="n">
-        <v>78.09999847412109</v>
+        <v>76.93000030517578</v>
       </c>
       <c r="C190" t="n">
-        <v>78.44999694824219</v>
+        <v>78.23999786376953</v>
       </c>
       <c r="D190" t="n">
-        <v>76.76000213623047</v>
+        <v>76.12000274658203</v>
       </c>
       <c r="E190" t="n">
-        <v>76.95999908447266</v>
+        <v>77.37999725341797</v>
       </c>
       <c r="F190" t="n">
-        <v>50338800</v>
+        <v>91920400</v>
       </c>
       <c r="G190" t="n">
         <v>0</v>
@@ -5383,22 +5383,22 @@
     </row>
     <row r="191">
       <c r="A191" s="1" t="n">
-        <v>46191</v>
+        <v>46195</v>
       </c>
       <c r="B191" t="n">
-        <v>76.93000030517578</v>
+        <v>76.13999938964844</v>
       </c>
       <c r="C191" t="n">
-        <v>78.23999786376953</v>
+        <v>77.08999633789062</v>
       </c>
       <c r="D191" t="n">
-        <v>76.12000274658203</v>
+        <v>71.80999755859375</v>
       </c>
       <c r="E191" t="n">
-        <v>77.37999725341797</v>
+        <v>72.87999725341797</v>
       </c>
       <c r="F191" t="n">
-        <v>91920400</v>
+        <v>82203300</v>
       </c>
       <c r="G191" t="n">
         <v>0</v>
@@ -5409,22 +5409,22 @@
     </row>
     <row r="192">
       <c r="A192" s="1" t="n">
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="B192" t="n">
-        <v>76.13999938964844</v>
+        <v>73.26000213623047</v>
       </c>
       <c r="C192" t="n">
-        <v>77.08999633789062</v>
+        <v>73.95999908447266</v>
       </c>
       <c r="D192" t="n">
-        <v>71.80999755859375</v>
+        <v>72.62999725341797</v>
       </c>
       <c r="E192" t="n">
-        <v>72.87999725341797</v>
+        <v>72.81999969482422</v>
       </c>
       <c r="F192" t="n">
-        <v>82203300</v>
+        <v>50806800</v>
       </c>
       <c r="G192" t="n">
         <v>0</v>
@@ -5435,22 +5435,22 @@
     </row>
     <row r="193">
       <c r="A193" s="1" t="n">
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="B193" t="n">
-        <v>73.26000213623047</v>
+        <v>72.69000244140625</v>
       </c>
       <c r="C193" t="n">
-        <v>73.95999908447266</v>
+        <v>73.44999694824219</v>
       </c>
       <c r="D193" t="n">
-        <v>72.62999725341797</v>
+        <v>71.62999725341797</v>
       </c>
       <c r="E193" t="n">
-        <v>72.81999969482422</v>
+        <v>71.83999633789062</v>
       </c>
       <c r="F193" t="n">
-        <v>50806800</v>
+        <v>48001500</v>
       </c>
       <c r="G193" t="n">
         <v>0</v>
@@ -5461,22 +5461,22 @@
     </row>
     <row r="194">
       <c r="A194" s="1" t="n">
-        <v>46197</v>
+        <v>46198</v>
       </c>
       <c r="B194" t="n">
-        <v>72.69000244140625</v>
+        <v>71.33000183105469</v>
       </c>
       <c r="C194" t="n">
-        <v>73.44999694824219</v>
+        <v>72.94000244140625</v>
       </c>
       <c r="D194" t="n">
-        <v>71.62999725341797</v>
+        <v>70.86000061035156</v>
       </c>
       <c r="E194" t="n">
-        <v>71.83999633789062</v>
+        <v>70.90000152587891</v>
       </c>
       <c r="F194" t="n">
-        <v>48001500</v>
+        <v>44446900</v>
       </c>
       <c r="G194" t="n">
         <v>0</v>
@@ -5487,22 +5487,22 @@
     </row>
     <row r="195">
       <c r="A195" s="1" t="n">
-        <v>46198</v>
+        <v>46199</v>
       </c>
       <c r="B195" t="n">
-        <v>71.33000183105469</v>
+        <v>71.69000244140625</v>
       </c>
       <c r="C195" t="n">
-        <v>72.94000244140625</v>
+        <v>75.19999694824219</v>
       </c>
       <c r="D195" t="n">
-        <v>70.86000061035156</v>
+        <v>71.52999877929688</v>
       </c>
       <c r="E195" t="n">
-        <v>70.90000152587891</v>
+        <v>73.80999755859375</v>
       </c>
       <c r="F195" t="n">
-        <v>44446900</v>
+        <v>74990300</v>
       </c>
       <c r="G195" t="n">
         <v>0</v>
@@ -5513,22 +5513,22 @@
     </row>
     <row r="196">
       <c r="A196" s="1" t="n">
-        <v>46199</v>
+        <v>46202</v>
       </c>
       <c r="B196" t="n">
-        <v>71.69000244140625</v>
+        <v>74.62000274658203</v>
       </c>
       <c r="C196" t="n">
-        <v>75.19999694824219</v>
+        <v>76.06999969482422</v>
       </c>
       <c r="D196" t="n">
-        <v>71.52999877929688</v>
+        <v>73.73000335693359</v>
       </c>
       <c r="E196" t="n">
-        <v>73.80999755859375</v>
+        <v>73.77999877929688</v>
       </c>
       <c r="F196" t="n">
-        <v>74990300</v>
+        <v>42429600</v>
       </c>
       <c r="G196" t="n">
         <v>0</v>
@@ -5539,22 +5539,22 @@
     </row>
     <row r="197">
       <c r="A197" s="1" t="n">
-        <v>46202</v>
+        <v>46203</v>
       </c>
       <c r="B197" t="n">
-        <v>74.62000274658203</v>
+        <v>73.58999633789062</v>
       </c>
       <c r="C197" t="n">
-        <v>76.06999969482422</v>
+        <v>73.75</v>
       </c>
       <c r="D197" t="n">
-        <v>73.73000335693359</v>
+        <v>71</v>
       </c>
       <c r="E197" t="n">
-        <v>73.77999877929688</v>
+        <v>71.40000152587891</v>
       </c>
       <c r="F197" t="n">
-        <v>42429600</v>
+        <v>49240900</v>
       </c>
       <c r="G197" t="n">
         <v>0</v>
@@ -5565,22 +5565,22 @@
     </row>
     <row r="198">
       <c r="A198" s="1" t="n">
-        <v>46203</v>
+        <v>46204</v>
       </c>
       <c r="B198" t="n">
-        <v>73.58999633789062</v>
+        <v>72.58999633789062</v>
       </c>
       <c r="C198" t="n">
-        <v>73.75</v>
+        <v>74.36000061035156</v>
       </c>
       <c r="D198" t="n">
-        <v>71</v>
+        <v>72.33000183105469</v>
       </c>
       <c r="E198" t="n">
-        <v>71.40000152587891</v>
+        <v>74.19000244140625</v>
       </c>
       <c r="F198" t="n">
-        <v>49240900</v>
+        <v>43841800</v>
       </c>
       <c r="G198" t="n">
         <v>0</v>
@@ -5591,22 +5591,22 @@
     </row>
     <row r="199">
       <c r="A199" s="1" t="n">
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="B199" t="n">
-        <v>72.58999633789062</v>
+        <v>75.08999633789062</v>
       </c>
       <c r="C199" t="n">
-        <v>74.36000061035156</v>
+        <v>78.44000244140625</v>
       </c>
       <c r="D199" t="n">
-        <v>72.33000183105469</v>
+        <v>74.91000366210938</v>
       </c>
       <c r="E199" t="n">
-        <v>74.19000244140625</v>
+        <v>77.65000152587891</v>
       </c>
       <c r="F199" t="n">
-        <v>43841800</v>
+        <v>55456500</v>
       </c>
       <c r="G199" t="n">
         <v>0</v>
@@ -5617,22 +5617,22 @@
     </row>
     <row r="200">
       <c r="A200" s="1" t="n">
-        <v>46205</v>
+        <v>46209</v>
       </c>
       <c r="B200" t="n">
-        <v>75.08999633789062</v>
+        <v>77.08000183105469</v>
       </c>
       <c r="C200" t="n">
-        <v>78.44000244140625</v>
+        <v>77.83999633789062</v>
       </c>
       <c r="D200" t="n">
-        <v>74.91000366210938</v>
+        <v>75.70999908447266</v>
       </c>
       <c r="E200" t="n">
-        <v>77.65000152587891</v>
+        <v>76.01999664306641</v>
       </c>
       <c r="F200" t="n">
-        <v>55456500</v>
+        <v>45056600</v>
       </c>
       <c r="G200" t="n">
         <v>0</v>
@@ -5643,22 +5643,22 @@
     </row>
     <row r="201">
       <c r="A201" s="1" t="n">
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="B201" t="n">
-        <v>77.08000183105469</v>
+        <v>77.87999725341797</v>
       </c>
       <c r="C201" t="n">
-        <v>77.83999633789062</v>
+        <v>78.19000244140625</v>
       </c>
       <c r="D201" t="n">
-        <v>75.70999908447266</v>
+        <v>76.09999847412109</v>
       </c>
       <c r="E201" t="n">
-        <v>76.01999664306641</v>
+        <v>76.18000030517578</v>
       </c>
       <c r="F201" t="n">
-        <v>45056600</v>
+        <v>33257300</v>
       </c>
       <c r="G201" t="n">
         <v>0</v>
@@ -5669,22 +5669,22 @@
     </row>
     <row r="202">
       <c r="A202" s="1" t="n">
-        <v>46210</v>
+        <v>46211</v>
       </c>
       <c r="B202" t="n">
-        <v>77.87999725341797</v>
+        <v>76.26999664306641</v>
       </c>
       <c r="C202" t="n">
-        <v>78.19000244140625</v>
+        <v>76.63999938964844</v>
       </c>
       <c r="D202" t="n">
-        <v>76.09999847412109</v>
+        <v>74.88999938964844</v>
       </c>
       <c r="E202" t="n">
-        <v>76.18000030517578</v>
+        <v>75.58999633789062</v>
       </c>
       <c r="F202" t="n">
-        <v>33257300</v>
+        <v>34373500</v>
       </c>
       <c r="G202" t="n">
         <v>0</v>
@@ -5695,22 +5695,22 @@
     </row>
     <row r="203">
       <c r="A203" s="1" t="n">
-        <v>46211</v>
+        <v>46212</v>
       </c>
       <c r="B203" t="n">
-        <v>76.26999664306641</v>
+        <v>74.30000305175781</v>
       </c>
       <c r="C203" t="n">
-        <v>76.63999938964844</v>
+        <v>75.55000305175781</v>
       </c>
       <c r="D203" t="n">
-        <v>74.88999938964844</v>
+        <v>74.01999664306641</v>
       </c>
       <c r="E203" t="n">
-        <v>75.58999633789062</v>
+        <v>75.47000122070312</v>
       </c>
       <c r="F203" t="n">
-        <v>34373500</v>
+        <v>36305700</v>
       </c>
       <c r="G203" t="n">
         <v>0</v>
@@ -5721,22 +5721,22 @@
     </row>
     <row r="204">
       <c r="A204" s="1" t="n">
-        <v>46212</v>
+        <v>46213</v>
       </c>
       <c r="B204" t="n">
-        <v>74.30000305175781</v>
+        <v>75.44000244140625</v>
       </c>
       <c r="C204" t="n">
-        <v>75.55000305175781</v>
+        <v>75.69999694824219</v>
       </c>
       <c r="D204" t="n">
-        <v>74.01999664306641</v>
+        <v>72.51000213623047</v>
       </c>
       <c r="E204" t="n">
-        <v>75.47000122070312</v>
+        <v>73.37000274658203</v>
       </c>
       <c r="F204" t="n">
-        <v>36305700</v>
+        <v>46713900</v>
       </c>
       <c r="G204" t="n">
         <v>0</v>
@@ -5747,22 +5747,22 @@
     </row>
     <row r="205">
       <c r="A205" s="1" t="n">
-        <v>46213</v>
+        <v>46216</v>
       </c>
       <c r="B205" t="n">
-        <v>75.44000244140625</v>
+        <v>73.90000152587891</v>
       </c>
       <c r="C205" t="n">
-        <v>75.69999694824219</v>
+        <v>75.44999694824219</v>
       </c>
       <c r="D205" t="n">
-        <v>72.51000213623047</v>
+        <v>73.70999908447266</v>
       </c>
       <c r="E205" t="n">
-        <v>73.37000274658203</v>
+        <v>73.83000183105469</v>
       </c>
       <c r="F205" t="n">
-        <v>46713900</v>
+        <v>35101800</v>
       </c>
       <c r="G205" t="n">
         <v>0</v>
@@ -5773,22 +5773,22 @@
     </row>
     <row r="206">
       <c r="A206" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="B206" t="n">
-        <v>73.90000152587891</v>
+        <v>72.63999938964844</v>
       </c>
       <c r="C206" t="n">
-        <v>75.44999694824219</v>
+        <v>74.01000213623047</v>
       </c>
       <c r="D206" t="n">
-        <v>73.70999908447266</v>
+        <v>72.27999877929688</v>
       </c>
       <c r="E206" t="n">
-        <v>73.83000183105469</v>
+        <v>73.52999877929688</v>
       </c>
       <c r="F206" t="n">
-        <v>35101800</v>
+        <v>33312100</v>
       </c>
       <c r="G206" t="n">
         <v>0</v>
@@ -5799,22 +5799,22 @@
     </row>
     <row r="207">
       <c r="A207" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="B207" t="n">
-        <v>72.63999938964844</v>
+        <v>73.79000091552734</v>
       </c>
       <c r="C207" t="n">
-        <v>74.01000213623047</v>
+        <v>75.05999755859375</v>
       </c>
       <c r="D207" t="n">
-        <v>72.27999877929688</v>
+        <v>73.12999725341797</v>
       </c>
       <c r="E207" t="n">
-        <v>73.52999877929688</v>
+        <v>73.68000030517578</v>
       </c>
       <c r="F207" t="n">
-        <v>33312100</v>
+        <v>32854300</v>
       </c>
       <c r="G207" t="n">
         <v>0</v>
@@ -5825,22 +5825,22 @@
     </row>
     <row r="208">
       <c r="A208" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="B208" t="n">
-        <v>73.79000091552734</v>
+        <v>73.94999694824219</v>
       </c>
       <c r="C208" t="n">
-        <v>75.05999755859375</v>
+        <v>74.68000030517578</v>
       </c>
       <c r="D208" t="n">
-        <v>73.12999725341797</v>
+        <v>72.94000244140625</v>
       </c>
       <c r="E208" t="n">
-        <v>73.68000030517578</v>
+        <v>74.34999847412109</v>
       </c>
       <c r="F208" t="n">
-        <v>32854300</v>
+        <v>77505200</v>
       </c>
       <c r="G208" t="n">
         <v>0</v>
@@ -5851,22 +5851,22 @@
     </row>
     <row r="209">
       <c r="A209" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="B209" t="n">
-        <v>73.94999694824219</v>
+        <v>65.48000335693359</v>
       </c>
       <c r="C209" t="n">
-        <v>74.68000030517578</v>
+        <v>69.48999786376953</v>
       </c>
       <c r="D209" t="n">
-        <v>72.94000244140625</v>
+        <v>65.08000183105469</v>
       </c>
       <c r="E209" t="n">
-        <v>74.34999847412109</v>
+        <v>68.94999694824219</v>
       </c>
       <c r="F209" t="n">
-        <v>77505200</v>
+        <v>142029200</v>
       </c>
       <c r="G209" t="n">
         <v>0</v>
@@ -5877,22 +5877,22 @@
     </row>
     <row r="210">
       <c r="A210" s="1" t="n">
-        <v>46220</v>
+        <v>46223</v>
       </c>
       <c r="B210" t="n">
-        <v>65.48000335693359</v>
+        <v>68.31999969482422</v>
       </c>
       <c r="C210" t="n">
-        <v>69.48999786376953</v>
+        <v>68.37999725341797</v>
       </c>
       <c r="D210" t="n">
-        <v>65.08000183105469</v>
+        <v>66.69000244140625</v>
       </c>
       <c r="E210" t="n">
-        <v>68.94999694824219</v>
+        <v>67.59999847412109</v>
       </c>
       <c r="F210" t="n">
-        <v>142029200</v>
+        <v>60669100</v>
       </c>
       <c r="G210" t="n">
         <v>0</v>
@@ -5903,22 +5903,22 @@
     </row>
     <row r="211">
       <c r="A211" s="1" t="n">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="B211" t="n">
-        <v>68.31999969482422</v>
+        <v>67.41999816894531</v>
       </c>
       <c r="C211" t="n">
-        <v>68.37999725341797</v>
+        <v>68.75</v>
       </c>
       <c r="D211" t="n">
-        <v>66.69000244140625</v>
+        <v>66.73000335693359</v>
       </c>
       <c r="E211" t="n">
-        <v>67.59999847412109</v>
+        <v>68.66999816894531</v>
       </c>
       <c r="F211" t="n">
-        <v>60669100</v>
+        <v>56565800</v>
       </c>
       <c r="G211" t="n">
         <v>0</v>
@@ -5929,22 +5929,22 @@
     </row>
     <row r="212">
       <c r="A212" s="1" t="n">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="B212" t="n">
-        <v>67.41999816894531</v>
+        <v>69.37000274658203</v>
       </c>
       <c r="C212" t="n">
-        <v>68.75</v>
+        <v>70.56999969482422</v>
       </c>
       <c r="D212" t="n">
-        <v>66.73000335693359</v>
+        <v>68.34999847412109</v>
       </c>
       <c r="E212" t="n">
-        <v>68.66999816894531</v>
+        <v>68.52999877929688</v>
       </c>
       <c r="F212" t="n">
-        <v>56565800</v>
+        <v>44947300</v>
       </c>
       <c r="G212" t="n">
         <v>0</v>
@@ -5955,22 +5955,22 @@
     </row>
     <row r="213">
       <c r="A213" s="1" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="B213" t="n">
-        <v>69.37000274658203</v>
+        <v>68.56999969482422</v>
       </c>
       <c r="C213" t="n">
-        <v>70.56999969482422</v>
+        <v>69.36000061035156</v>
       </c>
       <c r="D213" t="n">
-        <v>68.34999847412109</v>
+        <v>67.66999816894531</v>
       </c>
       <c r="E213" t="n">
-        <v>68.52999877929688</v>
+        <v>68.88999938964844</v>
       </c>
       <c r="F213" t="n">
-        <v>44947300</v>
+        <v>45029100</v>
       </c>
       <c r="G213" t="n">
         <v>0</v>
@@ -5981,22 +5981,22 @@
     </row>
     <row r="214">
       <c r="A214" s="1" t="n">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="B214" t="n">
-        <v>68.56999969482422</v>
+        <v>69.29000091552734</v>
       </c>
       <c r="C214" t="n">
-        <v>69.36000061035156</v>
+        <v>70.68000030517578</v>
       </c>
       <c r="D214" t="n">
-        <v>67.66999816894531</v>
+        <v>67.97000122070312</v>
       </c>
       <c r="E214" t="n">
-        <v>68.88999938964844</v>
+        <v>70.08999633789062</v>
       </c>
       <c r="F214" t="n">
-        <v>45029100</v>
+        <v>37593500</v>
       </c>
       <c r="G214" t="n">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="215">
       <c r="A215" s="1" t="n">
-        <v>46227</v>
+        <v>46230</v>
       </c>
       <c r="B215" t="n">
-        <v>69.29000091552734</v>
+        <v>70.58999633789062</v>
       </c>
       <c r="C215" t="n">
-        <v>70.68000030517578</v>
+        <v>71.65000152587891</v>
       </c>
       <c r="D215" t="n">
-        <v>67.97000122070312</v>
+        <v>69.86000061035156</v>
       </c>
       <c r="E215" t="n">
-        <v>70.08999633789062</v>
+        <v>70.40000152587891</v>
       </c>
       <c r="F215" t="n">
-        <v>37593500</v>
+        <v>39090800</v>
       </c>
       <c r="G215" t="n">
         <v>0</v>
@@ -6033,22 +6033,22 @@
     </row>
     <row r="216">
       <c r="A216" s="1" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="B216" t="n">
-        <v>70.58999633789062</v>
+        <v>72.06999969482422</v>
       </c>
       <c r="C216" t="n">
-        <v>71.65000152587891</v>
+        <v>73.76000213623047</v>
       </c>
       <c r="D216" t="n">
-        <v>69.86000061035156</v>
+        <v>71.23000335693359</v>
       </c>
       <c r="E216" t="n">
-        <v>70.40000152587891</v>
+        <v>72.38999938964844</v>
       </c>
       <c r="F216" t="n">
-        <v>39090800</v>
+        <v>47160200</v>
       </c>
       <c r="G216" t="n">
         <v>0</v>
@@ -6059,22 +6059,22 @@
     </row>
     <row r="217">
       <c r="A217" s="1" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="B217" t="n">
-        <v>72.06999969482422</v>
+        <v>72.19000244140625</v>
       </c>
       <c r="C217" t="n">
-        <v>73.76000213623047</v>
+        <v>73.73999786376953</v>
       </c>
       <c r="D217" t="n">
-        <v>71.23000335693359</v>
+        <v>71.75</v>
       </c>
       <c r="E217" t="n">
-        <v>72.38999938964844</v>
+        <v>73.62999725341797</v>
       </c>
       <c r="F217" t="n">
-        <v>47160200</v>
+        <v>43737600</v>
       </c>
       <c r="G217" t="n">
         <v>0</v>
@@ -6085,22 +6085,22 @@
     </row>
     <row r="218">
       <c r="A218" s="1" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="B218" t="n">
-        <v>72.19000244140625</v>
+        <v>71.48000335693359</v>
       </c>
       <c r="C218" t="n">
-        <v>73.73999786376953</v>
+        <v>73.31999969482422</v>
       </c>
       <c r="D218" t="n">
-        <v>71.75</v>
+        <v>70.55000305175781</v>
       </c>
       <c r="E218" t="n">
-        <v>73.62999725341797</v>
+        <v>73.16999816894531</v>
       </c>
       <c r="F218" t="n">
-        <v>43737600</v>
+        <v>54261000</v>
       </c>
       <c r="G218" t="n">
         <v>0</v>
@@ -6111,22 +6111,22 @@
     </row>
     <row r="219">
       <c r="A219" s="1" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="B219" t="n">
-        <v>71.48000335693359</v>
+        <v>71.97000122070312</v>
       </c>
       <c r="C219" t="n">
-        <v>73.31999969482422</v>
+        <v>72.75</v>
       </c>
       <c r="D219" t="n">
-        <v>70.55000305175781</v>
+        <v>71.11000061035156</v>
       </c>
       <c r="E219" t="n">
-        <v>73.16999816894531</v>
+        <v>71.70999908447266</v>
       </c>
       <c r="F219" t="n">
-        <v>54261000</v>
+        <v>35847500</v>
       </c>
       <c r="G219" t="n">
         <v>0</v>
@@ -6137,22 +6137,22 @@
     </row>
     <row r="220">
       <c r="A220" s="1" t="n">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="B220" t="n">
-        <v>71.97000122070312</v>
+        <v>72.76999664306641</v>
       </c>
       <c r="C220" t="n">
-        <v>72.75</v>
+        <v>73.94999694824219</v>
       </c>
       <c r="D220" t="n">
-        <v>71.11000061035156</v>
+        <v>72.18000030517578</v>
       </c>
       <c r="E220" t="n">
-        <v>71.70999908447266</v>
+        <v>73.33000183105469</v>
       </c>
       <c r="F220" t="n">
-        <v>35847500</v>
+        <v>33922300</v>
       </c>
       <c r="G220" t="n">
         <v>0</v>
@@ -6163,22 +6163,22 @@
     </row>
     <row r="221">
       <c r="A221" s="1" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="B221" t="n">
-        <v>72.76999664306641</v>
+        <v>72.51000213623047</v>
       </c>
       <c r="C221" t="n">
-        <v>73.94999694824219</v>
+        <v>73.75</v>
       </c>
       <c r="D221" t="n">
-        <v>72.18000030517578</v>
+        <v>72.30000305175781</v>
       </c>
       <c r="E221" t="n">
-        <v>73.33000183105469</v>
+        <v>73.56999969482422</v>
       </c>
       <c r="F221" t="n">
-        <v>33922300</v>
+        <v>42877900</v>
       </c>
       <c r="G221" t="n">
         <v>0</v>
@@ -6189,22 +6189,22 @@
     </row>
     <row r="222">
       <c r="A222" s="1" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="B222" t="n">
-        <v>72.51000213623047</v>
+        <v>75.11000061035156</v>
       </c>
       <c r="C222" t="n">
-        <v>73.75</v>
+        <v>75.30000305175781</v>
       </c>
       <c r="D222" t="n">
-        <v>72.30000305175781</v>
+        <v>73.16000366210938</v>
       </c>
       <c r="E222" t="n">
-        <v>73.56999969482422</v>
+        <v>74.19999694824219</v>
       </c>
       <c r="F222" t="n">
-        <v>42877900</v>
+        <v>28969400</v>
       </c>
       <c r="G222" t="n">
         <v>0</v>
@@ -6215,22 +6215,22 @@
     </row>
     <row r="223">
       <c r="A223" s="1" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="B223" t="n">
-        <v>75.11000061035156</v>
+        <v>75.13999938964844</v>
       </c>
       <c r="C223" t="n">
-        <v>75.30000305175781</v>
+        <v>75.20999908447266</v>
       </c>
       <c r="D223" t="n">
-        <v>73.16000366210938</v>
+        <v>73.09999847412109</v>
       </c>
       <c r="E223" t="n">
-        <v>74.19999694824219</v>
+        <v>73.69000244140625</v>
       </c>
       <c r="F223" t="n">
-        <v>28969400</v>
+        <v>28892700</v>
       </c>
       <c r="G223" t="n">
         <v>0</v>
@@ -6241,22 +6241,22 @@
     </row>
     <row r="224">
       <c r="A224" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="B224" t="n">
-        <v>75.13999938964844</v>
+        <v>73.12000274658203</v>
       </c>
       <c r="C224" t="n">
-        <v>75.20999908447266</v>
+        <v>74.5</v>
       </c>
       <c r="D224" t="n">
-        <v>73.09999847412109</v>
+        <v>73.08000183105469</v>
       </c>
       <c r="E224" t="n">
-        <v>73.69000244140625</v>
+        <v>74.13999938964844</v>
       </c>
       <c r="F224" t="n">
-        <v>28892700</v>
+        <v>24819000</v>
       </c>
       <c r="G224" t="n">
         <v>0</v>
@@ -6267,22 +6267,22 @@
     </row>
     <row r="225">
       <c r="A225" s="1" t="n">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="B225" t="n">
-        <v>73.12000274658203</v>
+        <v>73.80000305175781</v>
       </c>
       <c r="C225" t="n">
-        <v>74.5</v>
+        <v>76.31999969482422</v>
       </c>
       <c r="D225" t="n">
-        <v>73.08000183105469</v>
+        <v>73.56999969482422</v>
       </c>
       <c r="E225" t="n">
-        <v>74.13999938964844</v>
+        <v>76.29000091552734</v>
       </c>
       <c r="F225" t="n">
-        <v>24819000</v>
+        <v>26959900</v>
       </c>
       <c r="G225" t="n">
         <v>0</v>
@@ -6293,22 +6293,22 @@
     </row>
     <row r="226">
       <c r="A226" s="1" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="B226" t="n">
-        <v>73.80000305175781</v>
+        <v>76.19999694824219</v>
       </c>
       <c r="C226" t="n">
-        <v>76.31999969482422</v>
+        <v>76.90000152587891</v>
       </c>
       <c r="D226" t="n">
-        <v>73.56999969482422</v>
+        <v>74.48000335693359</v>
       </c>
       <c r="E226" t="n">
-        <v>76.29000091552734</v>
+        <v>74.79000091552734</v>
       </c>
       <c r="F226" t="n">
-        <v>26959900</v>
+        <v>27840500</v>
       </c>
       <c r="G226" t="n">
         <v>0</v>
@@ -6319,22 +6319,22 @@
     </row>
     <row r="227">
       <c r="A227" s="1" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="B227" t="n">
-        <v>76.19999694824219</v>
+        <v>74.34999847412109</v>
       </c>
       <c r="C227" t="n">
-        <v>76.90000152587891</v>
+        <v>74.66999816894531</v>
       </c>
       <c r="D227" t="n">
-        <v>74.48000335693359</v>
+        <v>73.56999969482422</v>
       </c>
       <c r="E227" t="n">
-        <v>74.79000091552734</v>
+        <v>74.20999908447266</v>
       </c>
       <c r="F227" t="n">
-        <v>27840500</v>
+        <v>20773100</v>
       </c>
       <c r="G227" t="n">
         <v>0</v>
@@ -6345,22 +6345,22 @@
     </row>
     <row r="228">
       <c r="A228" s="1" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="B228" t="n">
-        <v>74.34999847412109</v>
+        <v>76.01000213623047</v>
       </c>
       <c r="C228" t="n">
-        <v>74.66999816894531</v>
+        <v>78.40000152587891</v>
       </c>
       <c r="D228" t="n">
-        <v>73.56999969482422</v>
+        <v>75.44000244140625</v>
       </c>
       <c r="E228" t="n">
-        <v>74.20999908447266</v>
+        <v>78.23999786376953</v>
       </c>
       <c r="F228" t="n">
-        <v>20773100</v>
+        <v>41452900</v>
       </c>
       <c r="G228" t="n">
         <v>0</v>
@@ -6371,22 +6371,22 @@
     </row>
     <row r="229">
       <c r="A229" s="1" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="B229" t="n">
-        <v>76.01000213623047</v>
+        <v>78.48000335693359</v>
       </c>
       <c r="C229" t="n">
-        <v>78.40000152587891</v>
+        <v>78.73000335693359</v>
       </c>
       <c r="D229" t="n">
-        <v>75.44000244140625</v>
+        <v>77.76000213623047</v>
       </c>
       <c r="E229" t="n">
-        <v>78.23999786376953</v>
+        <v>78.16000366210938</v>
       </c>
       <c r="F229" t="n">
-        <v>41452900</v>
+        <v>26751000</v>
       </c>
       <c r="G229" t="n">
         <v>0</v>
@@ -6397,22 +6397,22 @@
     </row>
     <row r="230">
       <c r="A230" s="1" t="n">
-        <v>46248</v>
+        <v>46251</v>
       </c>
       <c r="B230" t="n">
-        <v>78.48000335693359</v>
+        <v>77.80000305175781</v>
       </c>
       <c r="C230" t="n">
-        <v>78.73000335693359</v>
+        <v>78.52999877929688</v>
       </c>
       <c r="D230" t="n">
-        <v>77.76000213623047</v>
+        <v>75.47000122070312</v>
       </c>
       <c r="E230" t="n">
-        <v>78.16000366210938</v>
+        <v>76.01999664306641</v>
       </c>
       <c r="F230" t="n">
-        <v>26751000</v>
+        <v>30753000</v>
       </c>
       <c r="G230" t="n">
         <v>0</v>
@@ -6423,22 +6423,22 @@
     </row>
     <row r="231">
       <c r="A231" s="1" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="B231" t="n">
-        <v>77.80000305175781</v>
+        <v>77.43000030517578</v>
       </c>
       <c r="C231" t="n">
-        <v>78.52999877929688</v>
+        <v>79.09999847412109</v>
       </c>
       <c r="D231" t="n">
-        <v>75.47000122070312</v>
+        <v>76.33999633789062</v>
       </c>
       <c r="E231" t="n">
-        <v>76.01999664306641</v>
+        <v>77.76999664306641</v>
       </c>
       <c r="F231" t="n">
-        <v>30753000</v>
+        <v>36151300</v>
       </c>
       <c r="G231" t="n">
         <v>0</v>
@@ -6449,22 +6449,22 @@
     </row>
     <row r="232">
       <c r="A232" s="1" t="n">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="B232" t="n">
-        <v>77.43000030517578</v>
+        <v>78.25</v>
       </c>
       <c r="C232" t="n">
-        <v>79.09999847412109</v>
+        <v>81.16000366210938</v>
       </c>
       <c r="D232" t="n">
-        <v>76.33999633789062</v>
+        <v>78.09999847412109</v>
       </c>
       <c r="E232" t="n">
-        <v>77.76999664306641</v>
+        <v>80.22000122070312</v>
       </c>
       <c r="F232" t="n">
-        <v>36151300</v>
+        <v>31461800</v>
       </c>
       <c r="G232" t="n">
         <v>0</v>
@@ -6475,22 +6475,22 @@
     </row>
     <row r="233">
       <c r="A233" s="1" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="B233" t="n">
-        <v>78.25</v>
+        <v>80.13999938964844</v>
       </c>
       <c r="C233" t="n">
-        <v>81.16000366210938</v>
+        <v>81.08000183105469</v>
       </c>
       <c r="D233" t="n">
-        <v>78.09999847412109</v>
+        <v>79.58999633789062</v>
       </c>
       <c r="E233" t="n">
-        <v>80.22000122070312</v>
+        <v>80.13999938964844</v>
       </c>
       <c r="F233" t="n">
-        <v>31461800</v>
+        <v>27118400</v>
       </c>
       <c r="G233" t="n">
         <v>0</v>
@@ -6501,22 +6501,22 @@
     </row>
     <row r="234">
       <c r="A234" s="1" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="B234" t="n">
-        <v>80.13999938964844</v>
+        <v>80.29000091552734</v>
       </c>
       <c r="C234" t="n">
-        <v>81.08000183105469</v>
+        <v>80.48999786376953</v>
       </c>
       <c r="D234" t="n">
+        <v>79.16999816894531</v>
+      </c>
+      <c r="E234" t="n">
         <v>79.58999633789062</v>
       </c>
-      <c r="E234" t="n">
-        <v>80.13999938964844</v>
-      </c>
       <c r="F234" t="n">
-        <v>27118400</v>
+        <v>23773800</v>
       </c>
       <c r="G234" t="n">
         <v>0</v>
@@ -6527,22 +6527,22 @@
     </row>
     <row r="235">
       <c r="A235" s="1" t="n">
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="B235" t="n">
-        <v>80.29000091552734</v>
+        <v>79.94000244140625</v>
       </c>
       <c r="C235" t="n">
-        <v>80.48999786376953</v>
+        <v>80.62000274658203</v>
       </c>
       <c r="D235" t="n">
-        <v>79.16999816894531</v>
+        <v>79.01999664306641</v>
       </c>
       <c r="E235" t="n">
-        <v>79.58999633789062</v>
+        <v>80.01000213623047</v>
       </c>
       <c r="F235" t="n">
-        <v>23773800</v>
+        <v>21085300</v>
       </c>
       <c r="G235" t="n">
         <v>0</v>
@@ -6553,22 +6553,22 @@
     </row>
     <row r="236">
       <c r="A236" s="1" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="B236" t="n">
-        <v>79.94000244140625</v>
+        <v>79.65000152587891</v>
       </c>
       <c r="C236" t="n">
-        <v>80.62000274658203</v>
+        <v>82.45999908447266</v>
       </c>
       <c r="D236" t="n">
-        <v>79.01999664306641</v>
+        <v>79.40000152587891</v>
       </c>
       <c r="E236" t="n">
-        <v>80.01000213623047</v>
+        <v>82.23000335693359</v>
       </c>
       <c r="F236" t="n">
-        <v>21085300</v>
+        <v>29462000</v>
       </c>
       <c r="G236" t="n">
         <v>0</v>
@@ -6579,22 +6579,22 @@
     </row>
     <row r="237">
       <c r="A237" s="1" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="B237" t="n">
-        <v>79.65000152587891</v>
+        <v>82.05000305175781</v>
       </c>
       <c r="C237" t="n">
-        <v>82.45999908447266</v>
+        <v>82.41999816894531</v>
       </c>
       <c r="D237" t="n">
-        <v>79.40000152587891</v>
+        <v>81.30000305175781</v>
       </c>
       <c r="E237" t="n">
-        <v>82.23000335693359</v>
+        <v>81.45999908447266</v>
       </c>
       <c r="F237" t="n">
-        <v>29462000</v>
+        <v>22874900</v>
       </c>
       <c r="G237" t="n">
         <v>0</v>
@@ -6605,22 +6605,22 @@
     </row>
     <row r="238">
       <c r="A238" s="1" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="B238" t="n">
-        <v>82.05000305175781</v>
+        <v>81.06999969482422</v>
       </c>
       <c r="C238" t="n">
-        <v>82.41999816894531</v>
+        <v>81.15000152587891</v>
       </c>
       <c r="D238" t="n">
-        <v>81.30000305175781</v>
+        <v>79.27999877929688</v>
       </c>
       <c r="E238" t="n">
-        <v>81.45999908447266</v>
+        <v>79.83999633789062</v>
       </c>
       <c r="F238" t="n">
-        <v>22874900</v>
+        <v>27174400</v>
       </c>
       <c r="G238" t="n">
         <v>0</v>
@@ -6631,22 +6631,22 @@
     </row>
     <row r="239">
       <c r="A239" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="B239" t="n">
-        <v>81.06999969482422</v>
+        <v>80.36000061035156</v>
       </c>
       <c r="C239" t="n">
-        <v>81.15000152587891</v>
+        <v>82.34999847412109</v>
       </c>
       <c r="D239" t="n">
-        <v>79.27999877929688</v>
+        <v>79.94999694824219</v>
       </c>
       <c r="E239" t="n">
-        <v>79.83999633789062</v>
+        <v>81.72000122070312</v>
       </c>
       <c r="F239" t="n">
-        <v>27174400</v>
+        <v>29092700</v>
       </c>
       <c r="G239" t="n">
         <v>0</v>
@@ -6657,22 +6657,22 @@
     </row>
     <row r="240">
       <c r="A240" s="1" t="n">
-        <v>46262</v>
+        <v>46265</v>
       </c>
       <c r="B240" t="n">
-        <v>80.36000061035156</v>
+        <v>81</v>
       </c>
       <c r="C240" t="n">
-        <v>82.34999847412109</v>
+        <v>81.73000335693359</v>
       </c>
       <c r="D240" t="n">
-        <v>79.94999694824219</v>
+        <v>80.65000152587891</v>
       </c>
       <c r="E240" t="n">
-        <v>81.72000122070312</v>
+        <v>81.05000305175781</v>
       </c>
       <c r="F240" t="n">
-        <v>29092700</v>
+        <v>30740800</v>
       </c>
       <c r="G240" t="n">
         <v>0</v>
@@ -6683,22 +6683,22 @@
     </row>
     <row r="241">
       <c r="A241" s="1" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="B241" t="n">
-        <v>81</v>
+        <v>80.16999816894531</v>
       </c>
       <c r="C241" t="n">
-        <v>81.73000335693359</v>
+        <v>82.12999725341797</v>
       </c>
       <c r="D241" t="n">
-        <v>80.65000152587891</v>
+        <v>79.59999847412109</v>
       </c>
       <c r="E241" t="n">
-        <v>81.05000305175781</v>
+        <v>80.80999755859375</v>
       </c>
       <c r="F241" t="n">
-        <v>30740800</v>
+        <v>21164900</v>
       </c>
       <c r="G241" t="n">
         <v>0</v>
@@ -6709,22 +6709,22 @@
     </row>
     <row r="242">
       <c r="A242" s="1" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="B242" t="n">
-        <v>80.16999816894531</v>
+        <v>80.55000305175781</v>
       </c>
       <c r="C242" t="n">
-        <v>82.12999725341797</v>
+        <v>83.12000274658203</v>
       </c>
       <c r="D242" t="n">
-        <v>79.59999847412109</v>
+        <v>80.30000305175781</v>
       </c>
       <c r="E242" t="n">
-        <v>80.80999755859375</v>
+        <v>82.73000335693359</v>
       </c>
       <c r="F242" t="n">
-        <v>21164900</v>
+        <v>22077800</v>
       </c>
       <c r="G242" t="n">
         <v>0</v>
@@ -6735,22 +6735,22 @@
     </row>
     <row r="243">
       <c r="A243" s="1" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="B243" t="n">
-        <v>80.55000305175781</v>
+        <v>83.18000030517578</v>
       </c>
       <c r="C243" t="n">
-        <v>83.12000274658203</v>
+        <v>83.59999847412109</v>
       </c>
       <c r="D243" t="n">
-        <v>80.30000305175781</v>
+        <v>81.62999725341797</v>
       </c>
       <c r="E243" t="n">
-        <v>82.73000335693359</v>
+        <v>82.66999816894531</v>
       </c>
       <c r="F243" t="n">
-        <v>22077800</v>
+        <v>24006400</v>
       </c>
       <c r="G243" t="n">
         <v>0</v>
@@ -6761,22 +6761,22 @@
     </row>
     <row r="244">
       <c r="A244" s="1" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B244" t="n">
-        <v>83.18000030517578</v>
+        <v>82.16999816894531</v>
       </c>
       <c r="C244" t="n">
-        <v>83.59999847412109</v>
+        <v>82.69000244140625</v>
       </c>
       <c r="D244" t="n">
-        <v>81.62999725341797</v>
+        <v>78.23000335693359</v>
       </c>
       <c r="E244" t="n">
-        <v>82.66999816894531</v>
+        <v>78.25</v>
       </c>
       <c r="F244" t="n">
-        <v>24006400</v>
+        <v>40190000</v>
       </c>
       <c r="G244" t="n">
         <v>0</v>
@@ -6787,22 +6787,22 @@
     </row>
     <row r="245">
       <c r="A245" s="1" t="n">
-        <v>46269</v>
+        <v>46273</v>
       </c>
       <c r="B245" t="n">
-        <v>82.16999816894531</v>
+        <v>77.55000305175781</v>
       </c>
       <c r="C245" t="n">
-        <v>82.69000244140625</v>
+        <v>77.73000335693359</v>
       </c>
       <c r="D245" t="n">
-        <v>78.23000335693359</v>
+        <v>75.91999816894531</v>
       </c>
       <c r="E245" t="n">
-        <v>78.25</v>
+        <v>76.76999664306641</v>
       </c>
       <c r="F245" t="n">
-        <v>40190000</v>
+        <v>33865500</v>
       </c>
       <c r="G245" t="n">
         <v>0</v>
@@ -6813,22 +6813,22 @@
     </row>
     <row r="246">
       <c r="A246" s="1" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B246" t="n">
-        <v>77.55000305175781</v>
+        <v>76.33999633789062</v>
       </c>
       <c r="C246" t="n">
-        <v>77.73000335693359</v>
+        <v>76.72000122070312</v>
       </c>
       <c r="D246" t="n">
-        <v>75.91999816894531</v>
+        <v>75.87000274658203</v>
       </c>
       <c r="E246" t="n">
-        <v>76.76999664306641</v>
+        <v>76.02999877929688</v>
       </c>
       <c r="F246" t="n">
-        <v>33865500</v>
+        <v>22779600</v>
       </c>
       <c r="G246" t="n">
         <v>0</v>
@@ -6839,22 +6839,22 @@
     </row>
     <row r="247">
       <c r="A247" s="1" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="B247" t="n">
-        <v>76.33999633789062</v>
+        <v>75.33000183105469</v>
       </c>
       <c r="C247" t="n">
-        <v>76.72000122070312</v>
+        <v>76.30000305175781</v>
       </c>
       <c r="D247" t="n">
-        <v>75.87000274658203</v>
+        <v>75.02999877929688</v>
       </c>
       <c r="E247" t="n">
-        <v>76.02999877929688</v>
+        <v>76.01000213623047</v>
       </c>
       <c r="F247" t="n">
-        <v>22779600</v>
+        <v>20049000</v>
       </c>
       <c r="G247" t="n">
         <v>0</v>
@@ -6865,22 +6865,22 @@
     </row>
     <row r="248">
       <c r="A248" s="1" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="B248" t="n">
-        <v>75.33000183105469</v>
+        <v>76.63999938964844</v>
       </c>
       <c r="C248" t="n">
-        <v>76.30000305175781</v>
+        <v>77.56999969482422</v>
       </c>
       <c r="D248" t="n">
-        <v>75.02999877929688</v>
+        <v>76.15000152587891</v>
       </c>
       <c r="E248" t="n">
-        <v>76.01000213623047</v>
+        <v>77.40000152587891</v>
       </c>
       <c r="F248" t="n">
-        <v>20049000</v>
+        <v>22237800</v>
       </c>
       <c r="G248" t="n">
         <v>0</v>
@@ -6891,22 +6891,22 @@
     </row>
     <row r="249">
       <c r="A249" s="1" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="B249" t="n">
-        <v>76.63999938964844</v>
+        <v>78.97000122070312</v>
       </c>
       <c r="C249" t="n">
-        <v>77.56999969482422</v>
+        <v>81.01999664306641</v>
       </c>
       <c r="D249" t="n">
-        <v>76.15000152587891</v>
+        <v>78.48999786376953</v>
       </c>
       <c r="E249" t="n">
-        <v>77.40000152587891</v>
+        <v>80.31999969482422</v>
       </c>
       <c r="F249" t="n">
-        <v>22237800</v>
+        <v>30945100</v>
       </c>
       <c r="G249" t="n">
         <v>0</v>
@@ -6917,22 +6917,22 @@
     </row>
     <row r="250">
       <c r="A250" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="B250" t="n">
-        <v>78.97000122070312</v>
+        <v>79.37999725341797</v>
       </c>
       <c r="C250" t="n">
-        <v>81.01999664306641</v>
+        <v>79.48000335693359</v>
       </c>
       <c r="D250" t="n">
-        <v>78.48999786376953</v>
+        <v>77.45999908447266</v>
       </c>
       <c r="E250" t="n">
-        <v>80.31999969482422</v>
+        <v>77.90000152587891</v>
       </c>
       <c r="F250" t="n">
-        <v>30945100</v>
+        <v>28027400</v>
       </c>
       <c r="G250" t="n">
         <v>0</v>
@@ -6943,22 +6943,22 @@
     </row>
     <row r="251">
       <c r="A251" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="B251" t="n">
-        <v>79.37999725341797</v>
+        <v>77.73000335693359</v>
       </c>
       <c r="C251" t="n">
-        <v>79.48000335693359</v>
+        <v>77.80000305175781</v>
       </c>
       <c r="D251" t="n">
-        <v>77.45999908447266</v>
+        <v>76.30999755859375</v>
       </c>
       <c r="E251" t="n">
-        <v>77.90000152587891</v>
+        <v>76.41000366210938</v>
       </c>
       <c r="F251" t="n">
-        <v>28027400</v>
+        <v>25376300</v>
       </c>
       <c r="G251" t="n">
         <v>0</v>
@@ -6969,14 +6969,22 @@
     </row>
     <row r="252">
       <c r="A252" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="B252" t="inlineStr"/>
-      <c r="C252" t="inlineStr"/>
-      <c r="D252" t="inlineStr"/>
-      <c r="E252" t="inlineStr"/>
+        <v>46282</v>
+      </c>
+      <c r="B252" t="n">
+        <v>76.91000366210938</v>
+      </c>
+      <c r="C252" t="n">
+        <v>76.95999908447266</v>
+      </c>
+      <c r="D252" t="n">
+        <v>75.30000305175781</v>
+      </c>
+      <c r="E252" t="n">
+        <v>75.30999755859375</v>
+      </c>
       <c r="F252" t="n">
-        <v>25306049</v>
+        <v>28090300</v>
       </c>
       <c r="G252" t="n">
         <v>0</v>
@@ -9090,7 +9098,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F53"/>
+  <dimension ref="A1:F54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9987,27 +9995,27 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Depreciation Amortization Depletion</t>
+          <t>Deferred Income Tax</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>16755555000</v>
+        <v>-442056000</v>
       </c>
       <c r="C46" t="n">
-        <v>15630431000</v>
+        <v>-590698000</v>
       </c>
       <c r="D46" t="n">
-        <v>14554384000</v>
+        <v>-459359000</v>
       </c>
       <c r="E46" t="n">
-        <v>14362814000</v>
+        <v>-166550000</v>
       </c>
       <c r="F46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Depreciation And Amortization</t>
+          <t>Depreciation Amortization Depletion</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -10027,27 +10035,27 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Amortization Cash Flow</t>
+          <t>Depreciation And Amortization</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>16422166000</v>
+        <v>16755555000</v>
       </c>
       <c r="C48" t="n">
-        <v>15301517000</v>
+        <v>15630431000</v>
       </c>
       <c r="D48" t="n">
-        <v>14197437000</v>
+        <v>14554384000</v>
       </c>
       <c r="E48" t="n">
-        <v>14026132000</v>
+        <v>14362814000</v>
       </c>
       <c r="F48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Amortization Of Intangibles</t>
+          <t>Amortization Cash Flow</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -10067,47 +10075,47 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Depreciation</t>
+          <t>Amortization Of Intangibles</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>333389000</v>
+        <v>16422166000</v>
       </c>
       <c r="C50" t="n">
-        <v>328914000</v>
+        <v>15301517000</v>
       </c>
       <c r="D50" t="n">
-        <v>356947000</v>
+        <v>14197437000</v>
       </c>
       <c r="E50" t="n">
-        <v>336682000</v>
+        <v>14026132000</v>
       </c>
       <c r="F50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Operating Gains Losses</t>
+          <t>Depreciation</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>72348000</v>
+        <v>333389000</v>
       </c>
       <c r="C51" t="n">
-        <v>-121539000</v>
+        <v>328914000</v>
       </c>
       <c r="D51" t="n">
-        <v>176296000</v>
+        <v>356947000</v>
       </c>
       <c r="E51" t="n">
-        <v>-353111000</v>
+        <v>336682000</v>
       </c>
       <c r="F51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Net Foreign Currency Exchange Gain Loss</t>
+          <t>Operating Gains Losses</t>
         </is>
       </c>
       <c r="B52" t="n">
@@ -10127,22 +10135,42 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
+          <t>Net Foreign Currency Exchange Gain Loss</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>72348000</v>
+      </c>
+      <c r="C53" t="n">
+        <v>-121539000</v>
+      </c>
+      <c r="D53" t="n">
+        <v>176296000</v>
+      </c>
+      <c r="E53" t="n">
+        <v>-353111000</v>
+      </c>
+      <c r="F53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
           <t>Net Income From Continuing Operations</t>
         </is>
       </c>
-      <c r="B53" t="n">
+      <c r="B54" t="n">
         <v>10981201000</v>
       </c>
-      <c r="C53" t="n">
+      <c r="C54" t="n">
         <v>8711631000</v>
       </c>
-      <c r="D53" t="n">
+      <c r="D54" t="n">
         <v>5407990000</v>
       </c>
-      <c r="E53" t="n">
+      <c r="E54" t="n">
         <v>4491924000</v>
       </c>
-      <c r="F53" t="inlineStr"/>
+      <c r="F54" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -10406,37 +10434,37 @@
         </is>
       </c>
       <c r="C2" t="n">
+        <v>75.31</v>
+      </c>
+      <c r="D2" t="n">
         <v>76.41</v>
       </c>
-      <c r="D2" t="n">
-        <v>77.90000000000001</v>
-      </c>
       <c r="E2" t="n">
-        <v>77.8</v>
+        <v>76.905</v>
       </c>
       <c r="F2" t="n">
-        <v>77.8</v>
+        <v>76.92310000000001</v>
       </c>
       <c r="G2" t="n">
-        <v>76.31</v>
+        <v>75.3</v>
       </c>
       <c r="H2" t="n">
-        <v>25306049</v>
+        <v>27803406</v>
       </c>
       <c r="I2" t="n">
-        <v>40215100</v>
+        <v>38958950</v>
       </c>
       <c r="J2" t="n">
-        <v>318166630400</v>
+        <v>313586286592</v>
       </c>
       <c r="K2" t="n">
-        <v>24.490387</v>
+        <v>24.060701</v>
       </c>
       <c r="L2" t="n">
-        <v>19.997854</v>
+        <v>19.709965</v>
       </c>
       <c r="M2" t="n">
-        <v>3.12</v>
+        <v>3.13</v>
       </c>
       <c r="N2" t="n">
         <v>124.86</v>
@@ -10474,7 +10502,7 @@
         <v>7.241</v>
       </c>
       <c r="Y2" t="n">
-        <v>10.55241</v>
+        <v>10.4004965</v>
       </c>
       <c r="Z2" t="n">
         <v>0.111</v>
@@ -10486,7 +10514,7 @@
         <v>48370765824</v>
       </c>
       <c r="AC2" t="n">
-        <v>325693374464</v>
+        <v>321113063424</v>
       </c>
       <c r="AD2" t="n">
         <v>14726931456</v>
@@ -10513,7 +10541,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>2026-09-17 08:10:29</t>
+          <t>2026-09-18 13:15:59</t>
         </is>
       </c>
     </row>

--- a/data/NFLX_data.xlsx
+++ b/data/NFLX_data.xlsx
@@ -469,22 +469,22 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45918</v>
+        <v>45919</v>
       </c>
       <c r="B2" t="n">
-        <v>122.0820007324219</v>
+        <v>121.8619995117188</v>
       </c>
       <c r="C2" t="n">
-        <v>123.3000030517578</v>
+        <v>122.995002746582</v>
       </c>
       <c r="D2" t="n">
-        <v>120.5500030517578</v>
+        <v>120.8099975585938</v>
       </c>
       <c r="E2" t="n">
-        <v>120.7779998779297</v>
+        <v>122.6969985961914</v>
       </c>
       <c r="F2" t="n">
-        <v>31691000</v>
+        <v>49476000</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -495,22 +495,22 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45919</v>
+        <v>45922</v>
       </c>
       <c r="B3" t="n">
-        <v>121.8619995117188</v>
+        <v>122.1900024414062</v>
       </c>
       <c r="C3" t="n">
-        <v>122.995002746582</v>
+        <v>122.9759979248047</v>
       </c>
       <c r="D3" t="n">
-        <v>120.8099975585938</v>
+        <v>121.4240036010742</v>
       </c>
       <c r="E3" t="n">
-        <v>122.6969985961914</v>
+        <v>122.7369995117188</v>
       </c>
       <c r="F3" t="n">
-        <v>49476000</v>
+        <v>25468000</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -521,22 +521,22 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>45922</v>
+        <v>45923</v>
       </c>
       <c r="B4" t="n">
-        <v>122.1900024414062</v>
+        <v>122.7330017089844</v>
       </c>
       <c r="C4" t="n">
-        <v>122.9759979248047</v>
+        <v>122.7789993286133</v>
       </c>
       <c r="D4" t="n">
-        <v>121.4240036010742</v>
+        <v>120.8470001220703</v>
       </c>
       <c r="E4" t="n">
-        <v>122.7369995117188</v>
+        <v>121.8470001220703</v>
       </c>
       <c r="F4" t="n">
-        <v>25468000</v>
+        <v>24991000</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -547,22 +547,22 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>45923</v>
+        <v>45924</v>
       </c>
       <c r="B5" t="n">
-        <v>122.7330017089844</v>
+        <v>121.8610000610352</v>
       </c>
       <c r="C5" t="n">
-        <v>122.7789993286133</v>
+        <v>122.1500015258789</v>
       </c>
       <c r="D5" t="n">
-        <v>120.8470001220703</v>
+        <v>119.4199981689453</v>
       </c>
       <c r="E5" t="n">
-        <v>121.8470001220703</v>
+        <v>120.3949966430664</v>
       </c>
       <c r="F5" t="n">
-        <v>24991000</v>
+        <v>27731000</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -573,22 +573,22 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>45924</v>
+        <v>45925</v>
       </c>
       <c r="B6" t="n">
-        <v>121.8610000610352</v>
+        <v>120.3089981079102</v>
       </c>
       <c r="C6" t="n">
-        <v>122.1500015258789</v>
+        <v>121.6839981079102</v>
       </c>
       <c r="D6" t="n">
-        <v>119.4199981689453</v>
+        <v>119.1510009765625</v>
       </c>
       <c r="E6" t="n">
-        <v>120.3949966430664</v>
+        <v>120.8239974975586</v>
       </c>
       <c r="F6" t="n">
-        <v>27731000</v>
+        <v>19978000</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -599,22 +599,22 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>45925</v>
+        <v>45926</v>
       </c>
       <c r="B7" t="n">
-        <v>120.3089981079102</v>
+        <v>120.5419998168945</v>
       </c>
       <c r="C7" t="n">
-        <v>121.6839981079102</v>
+        <v>121.4000015258789</v>
       </c>
       <c r="D7" t="n">
-        <v>119.1510009765625</v>
+        <v>120</v>
       </c>
       <c r="E7" t="n">
-        <v>120.8239974975586</v>
+        <v>121.0609970092773</v>
       </c>
       <c r="F7" t="n">
-        <v>19978000</v>
+        <v>19450000</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -625,22 +625,22 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>45926</v>
+        <v>45929</v>
       </c>
       <c r="B8" t="n">
-        <v>120.5419998168945</v>
+        <v>120.5</v>
       </c>
       <c r="C8" t="n">
-        <v>121.4000015258789</v>
+        <v>122.4489974975586</v>
       </c>
       <c r="D8" t="n">
-        <v>120</v>
+        <v>118.7539978027344</v>
       </c>
       <c r="E8" t="n">
-        <v>121.0609970092773</v>
+        <v>120.640998840332</v>
       </c>
       <c r="F8" t="n">
-        <v>19450000</v>
+        <v>30332000</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -651,22 +651,22 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="B9" t="n">
-        <v>120.5</v>
+        <v>120.640998840332</v>
       </c>
       <c r="C9" t="n">
-        <v>122.4489974975586</v>
+        <v>120.8499984741211</v>
       </c>
       <c r="D9" t="n">
-        <v>118.7539978027344</v>
+        <v>117.8000030517578</v>
       </c>
       <c r="E9" t="n">
-        <v>120.640998840332</v>
+        <v>119.8919982910156</v>
       </c>
       <c r="F9" t="n">
-        <v>30332000</v>
+        <v>38303000</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -677,22 +677,22 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>45930</v>
+        <v>45931</v>
       </c>
       <c r="B10" t="n">
-        <v>120.640998840332</v>
+        <v>117.5490036010742</v>
       </c>
       <c r="C10" t="n">
-        <v>120.8499984741211</v>
+        <v>117.9140014648438</v>
       </c>
       <c r="D10" t="n">
-        <v>117.8000030517578</v>
+        <v>116.3209991455078</v>
       </c>
       <c r="E10" t="n">
-        <v>119.8919982910156</v>
+        <v>117.0899963378906</v>
       </c>
       <c r="F10" t="n">
-        <v>38303000</v>
+        <v>41102000</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -703,22 +703,22 @@
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>45931</v>
+        <v>45932</v>
       </c>
       <c r="B11" t="n">
-        <v>117.5490036010742</v>
+        <v>116.1500015258789</v>
       </c>
       <c r="C11" t="n">
-        <v>117.9140014648438</v>
+        <v>116.3330001831055</v>
       </c>
       <c r="D11" t="n">
-        <v>116.3209991455078</v>
+        <v>113.4000015258789</v>
       </c>
       <c r="E11" t="n">
-        <v>117.0899963378906</v>
+        <v>116.2529983520508</v>
       </c>
       <c r="F11" t="n">
-        <v>41102000</v>
+        <v>46855000</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -729,22 +729,22 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>45932</v>
+        <v>45933</v>
       </c>
       <c r="B12" t="n">
-        <v>116.1500015258789</v>
+        <v>116.5</v>
       </c>
       <c r="C12" t="n">
-        <v>116.3330001831055</v>
+        <v>116.8000030517578</v>
       </c>
       <c r="D12" t="n">
-        <v>113.4000015258789</v>
+        <v>114.3219985961914</v>
       </c>
       <c r="E12" t="n">
-        <v>116.2529983520508</v>
+        <v>115.3320007324219</v>
       </c>
       <c r="F12" t="n">
-        <v>46855000</v>
+        <v>31374000</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -755,22 +755,22 @@
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>45933</v>
+        <v>45936</v>
       </c>
       <c r="B13" t="n">
-        <v>116.5</v>
+        <v>116.0370025634766</v>
       </c>
       <c r="C13" t="n">
-        <v>116.8000030517578</v>
+        <v>116.3580017089844</v>
       </c>
       <c r="D13" t="n">
-        <v>114.3219985961914</v>
+        <v>114.5449981689453</v>
       </c>
       <c r="E13" t="n">
-        <v>115.3320007324219</v>
+        <v>116.3310012817383</v>
       </c>
       <c r="F13" t="n">
-        <v>31374000</v>
+        <v>29686000</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -781,22 +781,22 @@
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>45936</v>
+        <v>45937</v>
       </c>
       <c r="B14" t="n">
-        <v>116.0370025634766</v>
+        <v>117.7789993286133</v>
       </c>
       <c r="C14" t="n">
-        <v>116.3580017089844</v>
+        <v>120.1370010375977</v>
       </c>
       <c r="D14" t="n">
-        <v>114.5449981689453</v>
+        <v>117.7460021972656</v>
       </c>
       <c r="E14" t="n">
-        <v>116.3310012817383</v>
+        <v>119.1060028076172</v>
       </c>
       <c r="F14" t="n">
-        <v>29686000</v>
+        <v>33091000</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -807,22 +807,22 @@
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>45937</v>
+        <v>45938</v>
       </c>
       <c r="B15" t="n">
-        <v>117.7789993286133</v>
+        <v>119.7109985351562</v>
       </c>
       <c r="C15" t="n">
-        <v>120.1370010375977</v>
+        <v>121.7389984130859</v>
       </c>
       <c r="D15" t="n">
-        <v>117.7460021972656</v>
+        <v>119.1999969482422</v>
       </c>
       <c r="E15" t="n">
-        <v>119.1060028076172</v>
+        <v>121.4250030517578</v>
       </c>
       <c r="F15" t="n">
-        <v>33091000</v>
+        <v>28514000</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -833,22 +833,22 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>45938</v>
+        <v>45939</v>
       </c>
       <c r="B16" t="n">
-        <v>119.7109985351562</v>
+        <v>121.4250030517578</v>
       </c>
       <c r="C16" t="n">
-        <v>121.7389984130859</v>
+        <v>123.75</v>
       </c>
       <c r="D16" t="n">
-        <v>119.1999969482422</v>
+        <v>121.181999206543</v>
       </c>
       <c r="E16" t="n">
-        <v>121.4250030517578</v>
+        <v>123.1070022583008</v>
       </c>
       <c r="F16" t="n">
-        <v>28514000</v>
+        <v>28241000</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -859,22 +859,22 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>45939</v>
+        <v>45940</v>
       </c>
       <c r="B17" t="n">
-        <v>121.4250030517578</v>
+        <v>122.9000015258789</v>
       </c>
       <c r="C17" t="n">
-        <v>123.75</v>
+        <v>124.6999969482422</v>
       </c>
       <c r="D17" t="n">
-        <v>121.181999206543</v>
+        <v>121.9100036621094</v>
       </c>
       <c r="E17" t="n">
-        <v>123.1070022583008</v>
+        <v>122.0080032348633</v>
       </c>
       <c r="F17" t="n">
-        <v>28241000</v>
+        <v>42798000</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -885,22 +885,22 @@
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>45940</v>
+        <v>45943</v>
       </c>
       <c r="B18" t="n">
-        <v>122.9000015258789</v>
+        <v>122.1350021362305</v>
       </c>
       <c r="C18" t="n">
-        <v>124.6999969482422</v>
+        <v>123.1119995117188</v>
       </c>
       <c r="D18" t="n">
-        <v>121.9100036621094</v>
+        <v>120.6809997558594</v>
       </c>
       <c r="E18" t="n">
-        <v>122.0080032348633</v>
+        <v>121.9029998779297</v>
       </c>
       <c r="F18" t="n">
-        <v>42798000</v>
+        <v>24608000</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -911,22 +911,22 @@
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>45943</v>
+        <v>45944</v>
       </c>
       <c r="B19" t="n">
-        <v>122.1350021362305</v>
+        <v>121.4749984741211</v>
       </c>
       <c r="C19" t="n">
-        <v>123.1119995117188</v>
+        <v>122.4290008544922</v>
       </c>
       <c r="D19" t="n">
-        <v>120.6809997558594</v>
+        <v>120.3099975585938</v>
       </c>
       <c r="E19" t="n">
-        <v>121.9029998779297</v>
+        <v>121.5350036621094</v>
       </c>
       <c r="F19" t="n">
-        <v>24608000</v>
+        <v>23624000</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -937,22 +937,22 @@
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>45944</v>
+        <v>45945</v>
       </c>
       <c r="B20" t="n">
-        <v>121.4749984741211</v>
+        <v>121.3010025024414</v>
       </c>
       <c r="C20" t="n">
-        <v>122.4290008544922</v>
+        <v>121.9619979858398</v>
       </c>
       <c r="D20" t="n">
-        <v>120.3099975585938</v>
+        <v>120.161003112793</v>
       </c>
       <c r="E20" t="n">
-        <v>121.5350036621094</v>
+        <v>120.3290023803711</v>
       </c>
       <c r="F20" t="n">
-        <v>23624000</v>
+        <v>20252000</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -963,22 +963,22 @@
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>45945</v>
+        <v>45946</v>
       </c>
       <c r="B21" t="n">
-        <v>121.3010025024414</v>
+        <v>121.2149963378906</v>
       </c>
       <c r="C21" t="n">
-        <v>121.9619979858398</v>
+        <v>121.6709976196289</v>
       </c>
       <c r="D21" t="n">
-        <v>120.161003112793</v>
+        <v>117.5999984741211</v>
       </c>
       <c r="E21" t="n">
-        <v>120.3290023803711</v>
+        <v>118.359001159668</v>
       </c>
       <c r="F21" t="n">
-        <v>20252000</v>
+        <v>28326000</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -989,22 +989,22 @@
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>45946</v>
+        <v>45947</v>
       </c>
       <c r="B22" t="n">
-        <v>121.2149963378906</v>
+        <v>118.3600006103516</v>
       </c>
       <c r="C22" t="n">
-        <v>121.6709976196289</v>
+        <v>120.3119964599609</v>
       </c>
       <c r="D22" t="n">
-        <v>117.5999984741211</v>
+        <v>117.8949966430664</v>
       </c>
       <c r="E22" t="n">
-        <v>118.359001159668</v>
+        <v>119.9359970092773</v>
       </c>
       <c r="F22" t="n">
-        <v>28326000</v>
+        <v>29571000</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -1015,22 +1015,22 @@
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>45947</v>
+        <v>45950</v>
       </c>
       <c r="B23" t="n">
-        <v>118.3600006103516</v>
+        <v>120.7880020141602</v>
       </c>
       <c r="C23" t="n">
-        <v>120.3119964599609</v>
+        <v>124.7760009765625</v>
       </c>
       <c r="D23" t="n">
-        <v>117.8949966430664</v>
+        <v>120.6900024414062</v>
       </c>
       <c r="E23" t="n">
-        <v>119.9359970092773</v>
+        <v>123.8560028076172</v>
       </c>
       <c r="F23" t="n">
-        <v>29571000</v>
+        <v>39862000</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -1041,22 +1041,22 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>45950</v>
+        <v>45951</v>
       </c>
       <c r="B24" t="n">
-        <v>120.7880020141602</v>
+        <v>124.2829971313477</v>
       </c>
       <c r="C24" t="n">
-        <v>124.7760009765625</v>
+        <v>124.8600006103516</v>
       </c>
       <c r="D24" t="n">
-        <v>120.6900024414062</v>
+        <v>123.1760025024414</v>
       </c>
       <c r="E24" t="n">
-        <v>123.8560028076172</v>
+        <v>124.1350021362305</v>
       </c>
       <c r="F24" t="n">
-        <v>39862000</v>
+        <v>65082000</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -1067,22 +1067,22 @@
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>45951</v>
+        <v>45952</v>
       </c>
       <c r="B25" t="n">
-        <v>124.2829971313477</v>
+        <v>114.2900009155273</v>
       </c>
       <c r="C25" t="n">
-        <v>124.8600006103516</v>
+        <v>115.7600021362305</v>
       </c>
       <c r="D25" t="n">
-        <v>123.1760025024414</v>
+        <v>111.2509994506836</v>
       </c>
       <c r="E25" t="n">
-        <v>124.1350021362305</v>
+        <v>111.6370010375977</v>
       </c>
       <c r="F25" t="n">
-        <v>65082000</v>
+        <v>147890000</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -1093,22 +1093,22 @@
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>45952</v>
+        <v>45953</v>
       </c>
       <c r="B26" t="n">
-        <v>114.2900009155273</v>
+        <v>112.6900024414062</v>
       </c>
       <c r="C26" t="n">
-        <v>115.7600021362305</v>
+        <v>112.7829971313477</v>
       </c>
       <c r="D26" t="n">
-        <v>111.2509994506836</v>
+        <v>109.9729995727539</v>
       </c>
       <c r="E26" t="n">
-        <v>111.6370010375977</v>
+        <v>111.359001159668</v>
       </c>
       <c r="F26" t="n">
-        <v>147890000</v>
+        <v>68497000</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -1119,22 +1119,22 @@
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>45953</v>
+        <v>45954</v>
       </c>
       <c r="B27" t="n">
-        <v>112.6900024414062</v>
+        <v>111.0999984741211</v>
       </c>
       <c r="C27" t="n">
-        <v>112.7829971313477</v>
+        <v>111.4509963989258</v>
       </c>
       <c r="D27" t="n">
-        <v>109.9729995727539</v>
+        <v>109.4410018920898</v>
       </c>
       <c r="E27" t="n">
-        <v>111.359001159668</v>
+        <v>109.4690017700195</v>
       </c>
       <c r="F27" t="n">
-        <v>68497000</v>
+        <v>60280000</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -1145,22 +1145,22 @@
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>45954</v>
+        <v>45957</v>
       </c>
       <c r="B28" t="n">
-        <v>111.0999984741211</v>
+        <v>110.0670013427734</v>
       </c>
       <c r="C28" t="n">
-        <v>111.4509963989258</v>
+        <v>110.2279968261719</v>
       </c>
       <c r="D28" t="n">
-        <v>109.4410018920898</v>
+        <v>108.7300033569336</v>
       </c>
       <c r="E28" t="n">
-        <v>109.4690017700195</v>
+        <v>109.4560012817383</v>
       </c>
       <c r="F28" t="n">
-        <v>60280000</v>
+        <v>46911000</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
@@ -1171,22 +1171,22 @@
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>45957</v>
+        <v>45958</v>
       </c>
       <c r="B29" t="n">
-        <v>110.0670013427734</v>
+        <v>109.4000015258789</v>
       </c>
       <c r="C29" t="n">
-        <v>110.2279968261719</v>
+        <v>111.697998046875</v>
       </c>
       <c r="D29" t="n">
-        <v>108.7300033569336</v>
+        <v>109.3010025024414</v>
       </c>
       <c r="E29" t="n">
-        <v>109.4560012817383</v>
+        <v>110.25</v>
       </c>
       <c r="F29" t="n">
-        <v>46911000</v>
+        <v>40209000</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -1197,22 +1197,22 @@
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>45958</v>
+        <v>45959</v>
       </c>
       <c r="B30" t="n">
-        <v>109.4000015258789</v>
+        <v>109.984001159668</v>
       </c>
       <c r="C30" t="n">
-        <v>111.697998046875</v>
+        <v>110.8550033569336</v>
       </c>
       <c r="D30" t="n">
-        <v>109.3010025024414</v>
+        <v>109.5999984741211</v>
       </c>
       <c r="E30" t="n">
-        <v>110.25</v>
+        <v>110.0410003662109</v>
       </c>
       <c r="F30" t="n">
-        <v>40209000</v>
+        <v>33995000</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -1223,22 +1223,22 @@
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>45959</v>
+        <v>45960</v>
       </c>
       <c r="B31" t="n">
-        <v>109.984001159668</v>
+        <v>109.4400024414062</v>
       </c>
       <c r="C31" t="n">
-        <v>110.8550033569336</v>
+        <v>110.6159973144531</v>
       </c>
       <c r="D31" t="n">
-        <v>109.5999984741211</v>
+        <v>108.8109970092773</v>
       </c>
       <c r="E31" t="n">
-        <v>110.0410003662109</v>
+        <v>108.9000015258789</v>
       </c>
       <c r="F31" t="n">
-        <v>33995000</v>
+        <v>41581000</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -1249,22 +1249,22 @@
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>45960</v>
+        <v>45961</v>
       </c>
       <c r="B32" t="n">
-        <v>109.4400024414062</v>
+        <v>110.5390014648438</v>
       </c>
       <c r="C32" t="n">
-        <v>110.6159973144531</v>
+        <v>113.4879989624023</v>
       </c>
       <c r="D32" t="n">
-        <v>108.8109970092773</v>
+        <v>110.197998046875</v>
       </c>
       <c r="E32" t="n">
-        <v>108.9000015258789</v>
+        <v>111.8860015869141</v>
       </c>
       <c r="F32" t="n">
-        <v>41581000</v>
+        <v>68665000</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
@@ -1275,22 +1275,22 @@
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>45961</v>
+        <v>45964</v>
       </c>
       <c r="B33" t="n">
-        <v>110.5390014648438</v>
+        <v>113.3239974975586</v>
       </c>
       <c r="C33" t="n">
-        <v>113.4879989624023</v>
+        <v>113.3499984741211</v>
       </c>
       <c r="D33" t="n">
-        <v>110.197998046875</v>
+        <v>107.5149993896484</v>
       </c>
       <c r="E33" t="n">
-        <v>111.8860015869141</v>
+        <v>110.0090026855469</v>
       </c>
       <c r="F33" t="n">
-        <v>68665000</v>
+        <v>58634000</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -1301,22 +1301,22 @@
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>45964</v>
+        <v>45965</v>
       </c>
       <c r="B34" t="n">
-        <v>113.3239974975586</v>
+        <v>109.9990005493164</v>
       </c>
       <c r="C34" t="n">
-        <v>113.3499984741211</v>
+        <v>110.4599990844727</v>
       </c>
       <c r="D34" t="n">
-        <v>107.5149993896484</v>
+        <v>108.6679992675781</v>
       </c>
       <c r="E34" t="n">
-        <v>110.0090026855469</v>
+        <v>109.2959976196289</v>
       </c>
       <c r="F34" t="n">
-        <v>58634000</v>
+        <v>38718000</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
@@ -1327,22 +1327,22 @@
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>45965</v>
+        <v>45966</v>
       </c>
       <c r="B35" t="n">
-        <v>109.9990005493164</v>
+        <v>108.5</v>
       </c>
       <c r="C35" t="n">
-        <v>110.4599990844727</v>
+        <v>110.0849990844727</v>
       </c>
       <c r="D35" t="n">
-        <v>108.6679992675781</v>
+        <v>107.3369979858398</v>
       </c>
       <c r="E35" t="n">
-        <v>109.2959976196289</v>
+        <v>109.8460006713867</v>
       </c>
       <c r="F35" t="n">
-        <v>38718000</v>
+        <v>35539000</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
@@ -1353,22 +1353,22 @@
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>45966</v>
+        <v>45967</v>
       </c>
       <c r="B36" t="n">
-        <v>108.5</v>
+        <v>109.4580001831055</v>
       </c>
       <c r="C36" t="n">
-        <v>110.0849990844727</v>
+        <v>110.370002746582</v>
       </c>
       <c r="D36" t="n">
-        <v>107.3369979858398</v>
+        <v>108.5130004882812</v>
       </c>
       <c r="E36" t="n">
-        <v>109.8460006713867</v>
+        <v>109.7020034790039</v>
       </c>
       <c r="F36" t="n">
-        <v>35539000</v>
+        <v>36532000</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -1379,22 +1379,22 @@
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>45967</v>
+        <v>45968</v>
       </c>
       <c r="B37" t="n">
-        <v>109.4580001831055</v>
+        <v>109.4179992675781</v>
       </c>
       <c r="C37" t="n">
-        <v>110.370002746582</v>
+        <v>110.8219985961914</v>
       </c>
       <c r="D37" t="n">
-        <v>108.5130004882812</v>
+        <v>108.75</v>
       </c>
       <c r="E37" t="n">
-        <v>109.7020034790039</v>
+        <v>110.3659973144531</v>
       </c>
       <c r="F37" t="n">
-        <v>36532000</v>
+        <v>44125000</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
@@ -1405,22 +1405,22 @@
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>45968</v>
+        <v>45971</v>
       </c>
       <c r="B38" t="n">
-        <v>109.4179992675781</v>
+        <v>110.6719970703125</v>
       </c>
       <c r="C38" t="n">
-        <v>110.8219985961914</v>
+        <v>112.8199996948242</v>
       </c>
       <c r="D38" t="n">
-        <v>108.75</v>
+        <v>110.4049987792969</v>
       </c>
       <c r="E38" t="n">
-        <v>110.3659973144531</v>
+        <v>112.0070037841797</v>
       </c>
       <c r="F38" t="n">
-        <v>44125000</v>
+        <v>36929000</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
@@ -1431,22 +1431,22 @@
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>45971</v>
+        <v>45972</v>
       </c>
       <c r="B39" t="n">
-        <v>110.6719970703125</v>
+        <v>111.7600021362305</v>
       </c>
       <c r="C39" t="n">
-        <v>112.8199996948242</v>
+        <v>113.9219970703125</v>
       </c>
       <c r="D39" t="n">
-        <v>110.4049987792969</v>
+        <v>111.2799987792969</v>
       </c>
       <c r="E39" t="n">
-        <v>112.0070037841797</v>
+        <v>113.6439971923828</v>
       </c>
       <c r="F39" t="n">
-        <v>36929000</v>
+        <v>27966000</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
@@ -1457,22 +1457,22 @@
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>45972</v>
+        <v>45973</v>
       </c>
       <c r="B40" t="n">
-        <v>111.7600021362305</v>
+        <v>113.8170013427734</v>
       </c>
       <c r="C40" t="n">
-        <v>113.9219970703125</v>
+        <v>116.4339981079102</v>
       </c>
       <c r="D40" t="n">
-        <v>111.2799987792969</v>
+        <v>112.8259963989258</v>
       </c>
       <c r="E40" t="n">
-        <v>113.6439971923828</v>
+        <v>115.75</v>
       </c>
       <c r="F40" t="n">
-        <v>27966000</v>
+        <v>39221000</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
@@ -1483,22 +1483,22 @@
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>45973</v>
+        <v>45974</v>
       </c>
       <c r="B41" t="n">
-        <v>113.8170013427734</v>
+        <v>115.8499984741211</v>
       </c>
       <c r="C41" t="n">
-        <v>116.4339981079102</v>
+        <v>116.7330017089844</v>
       </c>
       <c r="D41" t="n">
-        <v>112.8259963989258</v>
+        <v>114.5690002441406</v>
       </c>
       <c r="E41" t="n">
-        <v>115.75</v>
+        <v>115.4229965209961</v>
       </c>
       <c r="F41" t="n">
-        <v>39221000</v>
+        <v>40144000</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
@@ -1509,22 +1509,22 @@
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>45974</v>
+        <v>45975</v>
       </c>
       <c r="B42" t="n">
-        <v>115.8499984741211</v>
+        <v>114.2730026245117</v>
       </c>
       <c r="C42" t="n">
-        <v>116.7330017089844</v>
+        <v>114.2730026245117</v>
       </c>
       <c r="D42" t="n">
-        <v>114.5690002441406</v>
+        <v>110.7210006713867</v>
       </c>
       <c r="E42" t="n">
-        <v>115.4229965209961</v>
+        <v>111.2170028686523</v>
       </c>
       <c r="F42" t="n">
-        <v>40144000</v>
+        <v>47607000</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
@@ -1535,74 +1535,74 @@
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>45975</v>
+        <v>45978</v>
       </c>
       <c r="B43" t="n">
-        <v>114.2730026245117</v>
+        <v>110.75</v>
       </c>
       <c r="C43" t="n">
-        <v>114.2730026245117</v>
+        <v>111.8499984741211</v>
       </c>
       <c r="D43" t="n">
-        <v>110.7210006713867</v>
+        <v>109.5500030517578</v>
       </c>
       <c r="E43" t="n">
-        <v>111.2170028686523</v>
+        <v>110.2900009155273</v>
       </c>
       <c r="F43" t="n">
-        <v>47607000</v>
+        <v>26082700</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
-        <v>45978</v>
+        <v>45979</v>
       </c>
       <c r="B44" t="n">
-        <v>110.75</v>
+        <v>110.2900009155273</v>
       </c>
       <c r="C44" t="n">
-        <v>111.8499984741211</v>
+        <v>115.25</v>
       </c>
       <c r="D44" t="n">
-        <v>109.5500030517578</v>
+        <v>109.1999969482422</v>
       </c>
       <c r="E44" t="n">
-        <v>110.2900009155273</v>
+        <v>114.0899963378906</v>
       </c>
       <c r="F44" t="n">
-        <v>26082700</v>
+        <v>43440600</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
-        <v>45979</v>
+        <v>45980</v>
       </c>
       <c r="B45" t="n">
-        <v>110.2900009155273</v>
+        <v>113</v>
       </c>
       <c r="C45" t="n">
-        <v>115.25</v>
+        <v>113.3399963378906</v>
       </c>
       <c r="D45" t="n">
-        <v>109.1999969482422</v>
+        <v>108.6100006103516</v>
       </c>
       <c r="E45" t="n">
-        <v>114.0899963378906</v>
+        <v>110</v>
       </c>
       <c r="F45" t="n">
-        <v>43440600</v>
+        <v>31868100</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
@@ -1613,22 +1613,22 @@
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
-        <v>45980</v>
+        <v>45981</v>
       </c>
       <c r="B46" t="n">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C46" t="n">
-        <v>113.3399963378906</v>
+        <v>111.0999984741211</v>
       </c>
       <c r="D46" t="n">
-        <v>108.6100006103516</v>
+        <v>105.3899993896484</v>
       </c>
       <c r="E46" t="n">
-        <v>110</v>
+        <v>105.6699981689453</v>
       </c>
       <c r="F46" t="n">
-        <v>31868100</v>
+        <v>36918500</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
@@ -1639,22 +1639,22 @@
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
-        <v>45981</v>
+        <v>45982</v>
       </c>
       <c r="B47" t="n">
-        <v>111</v>
+        <v>105.129997253418</v>
       </c>
       <c r="C47" t="n">
-        <v>111.0999984741211</v>
+        <v>106.5299987792969</v>
       </c>
       <c r="D47" t="n">
-        <v>105.3899993896484</v>
+        <v>103.8099975585938</v>
       </c>
       <c r="E47" t="n">
-        <v>105.6699981689453</v>
+        <v>104.3099975585938</v>
       </c>
       <c r="F47" t="n">
-        <v>36918500</v>
+        <v>41232700</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
@@ -1665,22 +1665,22 @@
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
-        <v>45982</v>
+        <v>45985</v>
       </c>
       <c r="B48" t="n">
-        <v>105.129997253418</v>
+        <v>104.25</v>
       </c>
       <c r="C48" t="n">
-        <v>106.5299987792969</v>
+        <v>108.0400009155273</v>
       </c>
       <c r="D48" t="n">
-        <v>103.8099975585938</v>
+        <v>103.3199996948242</v>
       </c>
       <c r="E48" t="n">
-        <v>104.3099975585938</v>
+        <v>106.9700012207031</v>
       </c>
       <c r="F48" t="n">
-        <v>41232700</v>
+        <v>62918300</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
@@ -1691,22 +1691,22 @@
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>45985</v>
+        <v>45986</v>
       </c>
       <c r="B49" t="n">
-        <v>104.25</v>
+        <v>106.120002746582</v>
       </c>
       <c r="C49" t="n">
-        <v>108.0400009155273</v>
+        <v>106.3000030517578</v>
       </c>
       <c r="D49" t="n">
-        <v>103.3199996948242</v>
+        <v>103.8199996948242</v>
       </c>
       <c r="E49" t="n">
-        <v>106.9700012207031</v>
+        <v>104.4000015258789</v>
       </c>
       <c r="F49" t="n">
-        <v>62918300</v>
+        <v>35122600</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
@@ -1717,22 +1717,22 @@
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>45986</v>
+        <v>45987</v>
       </c>
       <c r="B50" t="n">
-        <v>106.120002746582</v>
+        <v>105.7399978637695</v>
       </c>
       <c r="C50" t="n">
-        <v>106.3000030517578</v>
+        <v>106.9499969482422</v>
       </c>
       <c r="D50" t="n">
-        <v>103.8199996948242</v>
+        <v>105.2200012207031</v>
       </c>
       <c r="E50" t="n">
-        <v>104.4000015258789</v>
+        <v>106.1399993896484</v>
       </c>
       <c r="F50" t="n">
-        <v>35122600</v>
+        <v>27951000</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
-        <v>45987</v>
+        <v>45989</v>
       </c>
       <c r="B51" t="n">
-        <v>105.7399978637695</v>
+        <v>106.4400024414062</v>
       </c>
       <c r="C51" t="n">
-        <v>106.9499969482422</v>
+        <v>107.9400024414062</v>
       </c>
       <c r="D51" t="n">
-        <v>105.2200012207031</v>
+        <v>106.2399978637695</v>
       </c>
       <c r="E51" t="n">
-        <v>106.1399993896484</v>
+        <v>107.5800018310547</v>
       </c>
       <c r="F51" t="n">
-        <v>27951000</v>
+        <v>15021600</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
@@ -1769,22 +1769,22 @@
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
-        <v>45989</v>
+        <v>45992</v>
       </c>
       <c r="B52" t="n">
-        <v>106.4400024414062</v>
+        <v>106.5100021362305</v>
       </c>
       <c r="C52" t="n">
-        <v>107.9400024414062</v>
+        <v>109.3399963378906</v>
       </c>
       <c r="D52" t="n">
-        <v>106.2399978637695</v>
+        <v>106.3099975585938</v>
       </c>
       <c r="E52" t="n">
-        <v>107.5800018310547</v>
+        <v>109.129997253418</v>
       </c>
       <c r="F52" t="n">
-        <v>15021600</v>
+        <v>24873400</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
@@ -1795,22 +1795,22 @@
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
-        <v>45992</v>
+        <v>45993</v>
       </c>
       <c r="B53" t="n">
-        <v>106.5100021362305</v>
+        <v>109.2099990844727</v>
       </c>
       <c r="C53" t="n">
-        <v>109.3399963378906</v>
+        <v>109.7300033569336</v>
       </c>
       <c r="D53" t="n">
-        <v>106.3099975585938</v>
+        <v>107.5199966430664</v>
       </c>
       <c r="E53" t="n">
-        <v>109.129997253418</v>
+        <v>109.3499984741211</v>
       </c>
       <c r="F53" t="n">
-        <v>24873400</v>
+        <v>25763000</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
@@ -1821,22 +1821,22 @@
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
-        <v>45993</v>
+        <v>45994</v>
       </c>
       <c r="B54" t="n">
-        <v>109.2099990844727</v>
+        <v>106.5899963378906</v>
       </c>
       <c r="C54" t="n">
-        <v>109.7300033569336</v>
+        <v>106.870002746582</v>
       </c>
       <c r="D54" t="n">
-        <v>107.5199966430664</v>
+        <v>102.0299987792969</v>
       </c>
       <c r="E54" t="n">
-        <v>109.3499984741211</v>
+        <v>103.9599990844727</v>
       </c>
       <c r="F54" t="n">
-        <v>25763000</v>
+        <v>53593400</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
@@ -1847,22 +1847,22 @@
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
-        <v>45994</v>
+        <v>45995</v>
       </c>
       <c r="B55" t="n">
-        <v>106.5899963378906</v>
+        <v>103.5699996948242</v>
       </c>
       <c r="C55" t="n">
-        <v>106.870002746582</v>
+        <v>103.8000030517578</v>
       </c>
       <c r="D55" t="n">
-        <v>102.0299987792969</v>
+        <v>101.7699966430664</v>
       </c>
       <c r="E55" t="n">
-        <v>103.9599990844727</v>
+        <v>103.2200012207031</v>
       </c>
       <c r="F55" t="n">
-        <v>53593400</v>
+        <v>51779100</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
@@ -1873,22 +1873,22 @@
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
-        <v>45995</v>
+        <v>45996</v>
       </c>
       <c r="B56" t="n">
-        <v>103.5699996948242</v>
+        <v>98.77999877929688</v>
       </c>
       <c r="C56" t="n">
-        <v>103.8000030517578</v>
+        <v>104.7900009155273</v>
       </c>
       <c r="D56" t="n">
-        <v>101.7699966430664</v>
+        <v>97.73999786376953</v>
       </c>
       <c r="E56" t="n">
-        <v>103.2200012207031</v>
+        <v>100.2399978637695</v>
       </c>
       <c r="F56" t="n">
-        <v>51779100</v>
+        <v>133363600</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
@@ -1899,22 +1899,22 @@
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
-        <v>45996</v>
+        <v>45999</v>
       </c>
       <c r="B57" t="n">
-        <v>98.77999877929688</v>
+        <v>99.87000274658203</v>
       </c>
       <c r="C57" t="n">
-        <v>104.7900009155273</v>
+        <v>99.88999938964844</v>
       </c>
       <c r="D57" t="n">
-        <v>97.73999786376953</v>
+        <v>95.30000305175781</v>
       </c>
       <c r="E57" t="n">
-        <v>100.2399978637695</v>
+        <v>96.79000091552734</v>
       </c>
       <c r="F57" t="n">
-        <v>133363600</v>
+        <v>100906300</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
@@ -1925,22 +1925,22 @@
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
-        <v>45999</v>
+        <v>46000</v>
       </c>
       <c r="B58" t="n">
-        <v>99.87000274658203</v>
+        <v>97.02999877929688</v>
       </c>
       <c r="C58" t="n">
-        <v>99.88999938964844</v>
+        <v>97.23999786376953</v>
       </c>
       <c r="D58" t="n">
-        <v>95.30000305175781</v>
+        <v>95.44999694824219</v>
       </c>
       <c r="E58" t="n">
-        <v>96.79000091552734</v>
+        <v>96.70999908447266</v>
       </c>
       <c r="F58" t="n">
-        <v>100906300</v>
+        <v>51745600</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
@@ -1951,22 +1951,22 @@
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
-        <v>46000</v>
+        <v>46001</v>
       </c>
       <c r="B59" t="n">
-        <v>97.02999877929688</v>
+        <v>96.73999786376953</v>
       </c>
       <c r="C59" t="n">
-        <v>97.23999786376953</v>
+        <v>96.97000122070312</v>
       </c>
       <c r="D59" t="n">
-        <v>95.44999694824219</v>
+        <v>92.34999847412109</v>
       </c>
       <c r="E59" t="n">
-        <v>96.70999908447266</v>
+        <v>92.70999908447266</v>
       </c>
       <c r="F59" t="n">
-        <v>51745600</v>
+        <v>74129300</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
@@ -1977,22 +1977,22 @@
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
-        <v>46001</v>
+        <v>46002</v>
       </c>
       <c r="B60" t="n">
-        <v>96.73999786376953</v>
+        <v>93.90000152587891</v>
       </c>
       <c r="C60" t="n">
-        <v>96.97000122070312</v>
+        <v>94.81999969482422</v>
       </c>
       <c r="D60" t="n">
-        <v>92.34999847412109</v>
+        <v>92.76000213623047</v>
       </c>
       <c r="E60" t="n">
-        <v>92.70999908447266</v>
+        <v>94.08999633789062</v>
       </c>
       <c r="F60" t="n">
-        <v>74129300</v>
+        <v>43949000</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
@@ -2003,22 +2003,22 @@
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
-        <v>46002</v>
+        <v>46003</v>
       </c>
       <c r="B61" t="n">
-        <v>93.90000152587891</v>
+        <v>95.5</v>
       </c>
       <c r="C61" t="n">
-        <v>94.81999969482422</v>
+        <v>96.91999816894531</v>
       </c>
       <c r="D61" t="n">
-        <v>92.76000213623047</v>
+        <v>94.65000152587891</v>
       </c>
       <c r="E61" t="n">
-        <v>94.08999633789062</v>
+        <v>95.19000244140625</v>
       </c>
       <c r="F61" t="n">
-        <v>43949000</v>
+        <v>49323100</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
@@ -2029,22 +2029,22 @@
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
-        <v>46003</v>
+        <v>46006</v>
       </c>
       <c r="B62" t="n">
-        <v>95.5</v>
+        <v>96.01999664306641</v>
       </c>
       <c r="C62" t="n">
-        <v>96.91999816894531</v>
+        <v>96.37000274658203</v>
       </c>
       <c r="D62" t="n">
-        <v>94.65000152587891</v>
+        <v>93.52999877929688</v>
       </c>
       <c r="E62" t="n">
-        <v>95.19000244140625</v>
+        <v>93.76999664306641</v>
       </c>
       <c r="F62" t="n">
-        <v>49323100</v>
+        <v>40016500</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
@@ -2055,22 +2055,22 @@
     </row>
     <row r="63">
       <c r="A63" s="1" t="n">
-        <v>46006</v>
+        <v>46007</v>
       </c>
       <c r="B63" t="n">
-        <v>96.01999664306641</v>
+        <v>93.87999725341797</v>
       </c>
       <c r="C63" t="n">
-        <v>96.37000274658203</v>
+        <v>94.93000030517578</v>
       </c>
       <c r="D63" t="n">
-        <v>93.52999877929688</v>
+        <v>93.31999969482422</v>
       </c>
       <c r="E63" t="n">
-        <v>93.76999664306641</v>
+        <v>94.56999969482422</v>
       </c>
       <c r="F63" t="n">
-        <v>40016500</v>
+        <v>34265000</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
@@ -2081,22 +2081,22 @@
     </row>
     <row r="64">
       <c r="A64" s="1" t="n">
-        <v>46007</v>
+        <v>46008</v>
       </c>
       <c r="B64" t="n">
-        <v>93.87999725341797</v>
+        <v>95.98000335693359</v>
       </c>
       <c r="C64" t="n">
-        <v>94.93000030517578</v>
+        <v>97.33000183105469</v>
       </c>
       <c r="D64" t="n">
-        <v>93.31999969482422</v>
+        <v>94.45999908447266</v>
       </c>
       <c r="E64" t="n">
-        <v>94.56999969482422</v>
+        <v>94.79000091552734</v>
       </c>
       <c r="F64" t="n">
-        <v>34265000</v>
+        <v>50472800</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
@@ -2107,22 +2107,22 @@
     </row>
     <row r="65">
       <c r="A65" s="1" t="n">
-        <v>46008</v>
+        <v>46009</v>
       </c>
       <c r="B65" t="n">
-        <v>95.98000335693359</v>
+        <v>95.01999664306641</v>
       </c>
       <c r="C65" t="n">
-        <v>97.33000183105469</v>
+        <v>95.80999755859375</v>
       </c>
       <c r="D65" t="n">
-        <v>94.45999908447266</v>
+        <v>93.58999633789062</v>
       </c>
       <c r="E65" t="n">
-        <v>94.79000091552734</v>
+        <v>94</v>
       </c>
       <c r="F65" t="n">
-        <v>50472800</v>
+        <v>37244700</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
@@ -2133,22 +2133,22 @@
     </row>
     <row r="66">
       <c r="A66" s="1" t="n">
-        <v>46009</v>
+        <v>46010</v>
       </c>
       <c r="B66" t="n">
-        <v>95.01999664306641</v>
+        <v>93.56999969482422</v>
       </c>
       <c r="C66" t="n">
-        <v>95.80999755859375</v>
+        <v>95.54000091552734</v>
       </c>
       <c r="D66" t="n">
-        <v>93.58999633789062</v>
+        <v>93.44999694824219</v>
       </c>
       <c r="E66" t="n">
-        <v>94</v>
+        <v>94.38999938964844</v>
       </c>
       <c r="F66" t="n">
-        <v>37244700</v>
+        <v>78990200</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
@@ -2159,22 +2159,22 @@
     </row>
     <row r="67">
       <c r="A67" s="1" t="n">
-        <v>46010</v>
+        <v>46013</v>
       </c>
       <c r="B67" t="n">
-        <v>93.56999969482422</v>
+        <v>94.70999908447266</v>
       </c>
       <c r="C67" t="n">
-        <v>95.54000091552734</v>
+        <v>94.70999908447266</v>
       </c>
       <c r="D67" t="n">
-        <v>93.44999694824219</v>
+        <v>92.91000366210938</v>
       </c>
       <c r="E67" t="n">
-        <v>94.38999938964844</v>
+        <v>93.23000335693359</v>
       </c>
       <c r="F67" t="n">
-        <v>78990200</v>
+        <v>39484800</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
@@ -2185,22 +2185,22 @@
     </row>
     <row r="68">
       <c r="A68" s="1" t="n">
-        <v>46013</v>
+        <v>46014</v>
       </c>
       <c r="B68" t="n">
-        <v>94.70999908447266</v>
+        <v>93.40000152587891</v>
       </c>
       <c r="C68" t="n">
-        <v>94.70999908447266</v>
+        <v>93.80999755859375</v>
       </c>
       <c r="D68" t="n">
-        <v>92.91000366210938</v>
+        <v>91.33000183105469</v>
       </c>
       <c r="E68" t="n">
-        <v>93.23000335693359</v>
+        <v>93.5</v>
       </c>
       <c r="F68" t="n">
-        <v>39484800</v>
+        <v>25896200</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
@@ -2211,22 +2211,22 @@
     </row>
     <row r="69">
       <c r="A69" s="1" t="n">
-        <v>46014</v>
+        <v>46015</v>
       </c>
       <c r="B69" t="n">
-        <v>93.40000152587891</v>
+        <v>93.11000061035156</v>
       </c>
       <c r="C69" t="n">
-        <v>93.80999755859375</v>
+        <v>93.68000030517578</v>
       </c>
       <c r="D69" t="n">
-        <v>91.33000183105469</v>
+        <v>92.66999816894531</v>
       </c>
       <c r="E69" t="n">
-        <v>93.5</v>
+        <v>93.63999938964844</v>
       </c>
       <c r="F69" t="n">
-        <v>25896200</v>
+        <v>12427900</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
@@ -2237,22 +2237,22 @@
     </row>
     <row r="70">
       <c r="A70" s="1" t="n">
-        <v>46015</v>
+        <v>46017</v>
       </c>
       <c r="B70" t="n">
-        <v>93.11000061035156</v>
+        <v>93.48000335693359</v>
       </c>
       <c r="C70" t="n">
-        <v>93.68000030517578</v>
+        <v>94.69000244140625</v>
       </c>
       <c r="D70" t="n">
-        <v>92.66999816894531</v>
+        <v>93.26999664306641</v>
       </c>
       <c r="E70" t="n">
-        <v>93.63999938964844</v>
+        <v>94.47000122070312</v>
       </c>
       <c r="F70" t="n">
-        <v>12427900</v>
+        <v>22068300</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
@@ -2263,22 +2263,22 @@
     </row>
     <row r="71">
       <c r="A71" s="1" t="n">
-        <v>46017</v>
+        <v>46020</v>
       </c>
       <c r="B71" t="n">
-        <v>93.48000335693359</v>
+        <v>93.98999786376953</v>
       </c>
       <c r="C71" t="n">
-        <v>94.69000244140625</v>
+        <v>94.97000122070312</v>
       </c>
       <c r="D71" t="n">
-        <v>93.26999664306641</v>
+        <v>93.62999725341797</v>
       </c>
       <c r="E71" t="n">
-        <v>94.47000122070312</v>
+        <v>94.15000152587891</v>
       </c>
       <c r="F71" t="n">
-        <v>22068300</v>
+        <v>24493700</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
@@ -2289,22 +2289,22 @@
     </row>
     <row r="72">
       <c r="A72" s="1" t="n">
-        <v>46020</v>
+        <v>46021</v>
       </c>
       <c r="B72" t="n">
+        <v>93.51999664306641</v>
+      </c>
+      <c r="C72" t="n">
         <v>93.98999786376953</v>
       </c>
-      <c r="C72" t="n">
-        <v>94.97000122070312</v>
-      </c>
       <c r="D72" t="n">
-        <v>93.62999725341797</v>
+        <v>93.33999633789062</v>
       </c>
       <c r="E72" t="n">
-        <v>94.15000152587891</v>
+        <v>93.77999877929688</v>
       </c>
       <c r="F72" t="n">
-        <v>24493700</v>
+        <v>23422000</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
@@ -2315,22 +2315,22 @@
     </row>
     <row r="73">
       <c r="A73" s="1" t="n">
-        <v>46021</v>
+        <v>46022</v>
       </c>
       <c r="B73" t="n">
-        <v>93.51999664306641</v>
+        <v>93.59999847412109</v>
       </c>
       <c r="C73" t="n">
-        <v>93.98999786376953</v>
+        <v>94.30999755859375</v>
       </c>
       <c r="D73" t="n">
-        <v>93.33999633789062</v>
+        <v>93.19999694824219</v>
       </c>
       <c r="E73" t="n">
-        <v>93.77999877929688</v>
+        <v>93.76000213623047</v>
       </c>
       <c r="F73" t="n">
-        <v>23422000</v>
+        <v>23495200</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
@@ -2341,22 +2341,22 @@
     </row>
     <row r="74">
       <c r="A74" s="1" t="n">
-        <v>46022</v>
+        <v>46024</v>
       </c>
       <c r="B74" t="n">
-        <v>93.59999847412109</v>
+        <v>94.12999725341797</v>
       </c>
       <c r="C74" t="n">
-        <v>94.30999755859375</v>
+        <v>94.12999725341797</v>
       </c>
       <c r="D74" t="n">
-        <v>93.19999694824219</v>
+        <v>90.80999755859375</v>
       </c>
       <c r="E74" t="n">
-        <v>93.76000213623047</v>
+        <v>90.98999786376953</v>
       </c>
       <c r="F74" t="n">
-        <v>23495200</v>
+        <v>41155400</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
@@ -2367,22 +2367,22 @@
     </row>
     <row r="75">
       <c r="A75" s="1" t="n">
-        <v>46024</v>
+        <v>46027</v>
       </c>
       <c r="B75" t="n">
-        <v>94.12999725341797</v>
+        <v>90.91999816894531</v>
       </c>
       <c r="C75" t="n">
-        <v>94.12999725341797</v>
+        <v>92.62999725341797</v>
       </c>
       <c r="D75" t="n">
-        <v>90.80999755859375</v>
+        <v>90.83999633789062</v>
       </c>
       <c r="E75" t="n">
-        <v>90.98999786376953</v>
+        <v>91.45999908447266</v>
       </c>
       <c r="F75" t="n">
-        <v>41155400</v>
+        <v>39183300</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
@@ -2393,22 +2393,22 @@
     </row>
     <row r="76">
       <c r="A76" s="1" t="n">
-        <v>46027</v>
+        <v>46028</v>
       </c>
       <c r="B76" t="n">
-        <v>90.91999816894531</v>
+        <v>91.54000091552734</v>
       </c>
       <c r="C76" t="n">
-        <v>92.62999725341797</v>
+        <v>91.63999938964844</v>
       </c>
       <c r="D76" t="n">
-        <v>90.83999633789062</v>
+        <v>89.73999786376953</v>
       </c>
       <c r="E76" t="n">
-        <v>91.45999908447266</v>
+        <v>90.65000152587891</v>
       </c>
       <c r="F76" t="n">
-        <v>39183300</v>
+        <v>43331000</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
@@ -2419,22 +2419,22 @@
     </row>
     <row r="77">
       <c r="A77" s="1" t="n">
-        <v>46028</v>
+        <v>46029</v>
       </c>
       <c r="B77" t="n">
-        <v>91.54000091552734</v>
+        <v>91.55999755859375</v>
       </c>
       <c r="C77" t="n">
-        <v>91.63999938964844</v>
+        <v>92.41999816894531</v>
       </c>
       <c r="D77" t="n">
-        <v>89.73999786376953</v>
+        <v>90.05999755859375</v>
       </c>
       <c r="E77" t="n">
-        <v>90.65000152587891</v>
+        <v>90.73000335693359</v>
       </c>
       <c r="F77" t="n">
-        <v>43331000</v>
+        <v>36525700</v>
       </c>
       <c r="G77" t="n">
         <v>0</v>
@@ -2445,22 +2445,22 @@
     </row>
     <row r="78">
       <c r="A78" s="1" t="n">
-        <v>46029</v>
+        <v>46030</v>
       </c>
       <c r="B78" t="n">
-        <v>91.55999755859375</v>
+        <v>90.44999694824219</v>
       </c>
       <c r="C78" t="n">
-        <v>92.41999816894531</v>
+        <v>91.25</v>
       </c>
       <c r="D78" t="n">
-        <v>90.05999755859375</v>
+        <v>89.58000183105469</v>
       </c>
       <c r="E78" t="n">
-        <v>90.73000335693359</v>
+        <v>90.52999877929688</v>
       </c>
       <c r="F78" t="n">
-        <v>36525700</v>
+        <v>40068700</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
@@ -2471,22 +2471,22 @@
     </row>
     <row r="79">
       <c r="A79" s="1" t="n">
-        <v>46030</v>
+        <v>46031</v>
       </c>
       <c r="B79" t="n">
-        <v>90.44999694824219</v>
+        <v>90.02999877929688</v>
       </c>
       <c r="C79" t="n">
-        <v>91.25</v>
+        <v>90.05000305175781</v>
       </c>
       <c r="D79" t="n">
-        <v>89.58000183105469</v>
+        <v>88.31999969482422</v>
       </c>
       <c r="E79" t="n">
-        <v>90.52999877929688</v>
+        <v>89.45999908447266</v>
       </c>
       <c r="F79" t="n">
-        <v>40068700</v>
+        <v>55579500</v>
       </c>
       <c r="G79" t="n">
         <v>0</v>
@@ -2497,22 +2497,22 @@
     </row>
     <row r="80">
       <c r="A80" s="1" t="n">
-        <v>46031</v>
+        <v>46034</v>
       </c>
       <c r="B80" t="n">
-        <v>90.02999877929688</v>
+        <v>89.69000244140625</v>
       </c>
       <c r="C80" t="n">
-        <v>90.05000305175781</v>
+        <v>90.33999633789062</v>
       </c>
       <c r="D80" t="n">
-        <v>88.31999969482422</v>
+        <v>89.33000183105469</v>
       </c>
       <c r="E80" t="n">
-        <v>89.45999908447266</v>
+        <v>89.41000366210938</v>
       </c>
       <c r="F80" t="n">
-        <v>55579500</v>
+        <v>36290600</v>
       </c>
       <c r="G80" t="n">
         <v>0</v>
@@ -2523,22 +2523,22 @@
     </row>
     <row r="81">
       <c r="A81" s="1" t="n">
-        <v>46034</v>
+        <v>46035</v>
       </c>
       <c r="B81" t="n">
-        <v>89.69000244140625</v>
+        <v>89.44000244140625</v>
       </c>
       <c r="C81" t="n">
-        <v>90.33999633789062</v>
+        <v>91.15000152587891</v>
       </c>
       <c r="D81" t="n">
-        <v>89.33000183105469</v>
+        <v>89.06999969482422</v>
       </c>
       <c r="E81" t="n">
-        <v>89.41000366210938</v>
+        <v>90.31999969482422</v>
       </c>
       <c r="F81" t="n">
-        <v>36290600</v>
+        <v>45221100</v>
       </c>
       <c r="G81" t="n">
         <v>0</v>
@@ -2549,22 +2549,22 @@
     </row>
     <row r="82">
       <c r="A82" s="1" t="n">
-        <v>46035</v>
+        <v>46036</v>
       </c>
       <c r="B82" t="n">
-        <v>89.44000244140625</v>
+        <v>91.23999786376953</v>
       </c>
       <c r="C82" t="n">
-        <v>91.15000152587891</v>
+        <v>91.58000183105469</v>
       </c>
       <c r="D82" t="n">
-        <v>89.06999969482422</v>
+        <v>87.94999694824219</v>
       </c>
       <c r="E82" t="n">
-        <v>90.31999969482422</v>
+        <v>88.55000305175781</v>
       </c>
       <c r="F82" t="n">
-        <v>45221100</v>
+        <v>49737700</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
@@ -2575,22 +2575,22 @@
     </row>
     <row r="83">
       <c r="A83" s="1" t="n">
-        <v>46036</v>
+        <v>46037</v>
       </c>
       <c r="B83" t="n">
-        <v>91.23999786376953</v>
+        <v>89.01999664306641</v>
       </c>
       <c r="C83" t="n">
-        <v>91.58000183105469</v>
+        <v>89.88999938964844</v>
       </c>
       <c r="D83" t="n">
-        <v>87.94999694824219</v>
+        <v>87.81999969482422</v>
       </c>
       <c r="E83" t="n">
-        <v>88.55000305175781</v>
+        <v>88.05000305175781</v>
       </c>
       <c r="F83" t="n">
-        <v>49737700</v>
+        <v>36945100</v>
       </c>
       <c r="G83" t="n">
         <v>0</v>
@@ -2601,22 +2601,22 @@
     </row>
     <row r="84">
       <c r="A84" s="1" t="n">
-        <v>46037</v>
+        <v>46038</v>
       </c>
       <c r="B84" t="n">
-        <v>89.01999664306641</v>
+        <v>88.33999633789062</v>
       </c>
       <c r="C84" t="n">
-        <v>89.88999938964844</v>
+        <v>88.51000213623047</v>
       </c>
       <c r="D84" t="n">
-        <v>87.81999969482422</v>
+        <v>87.77999877929688</v>
       </c>
       <c r="E84" t="n">
-        <v>88.05000305175781</v>
+        <v>88</v>
       </c>
       <c r="F84" t="n">
-        <v>36945100</v>
+        <v>48130500</v>
       </c>
       <c r="G84" t="n">
         <v>0</v>
@@ -2627,22 +2627,22 @@
     </row>
     <row r="85">
       <c r="A85" s="1" t="n">
-        <v>46038</v>
+        <v>46042</v>
       </c>
       <c r="B85" t="n">
-        <v>88.33999633789062</v>
+        <v>88.97000122070312</v>
       </c>
       <c r="C85" t="n">
-        <v>88.51000213623047</v>
+        <v>89.90000152587891</v>
       </c>
       <c r="D85" t="n">
-        <v>87.77999877929688</v>
+        <v>87.01999664306641</v>
       </c>
       <c r="E85" t="n">
-        <v>88</v>
+        <v>87.26000213623047</v>
       </c>
       <c r="F85" t="n">
-        <v>48130500</v>
+        <v>109729700</v>
       </c>
       <c r="G85" t="n">
         <v>0</v>
@@ -2653,22 +2653,22 @@
     </row>
     <row r="86">
       <c r="A86" s="1" t="n">
-        <v>46042</v>
+        <v>46043</v>
       </c>
       <c r="B86" t="n">
-        <v>88.97000122070312</v>
+        <v>82.51999664306641</v>
       </c>
       <c r="C86" t="n">
-        <v>89.90000152587891</v>
+        <v>86</v>
       </c>
       <c r="D86" t="n">
-        <v>87.01999664306641</v>
+        <v>81.93000030517578</v>
       </c>
       <c r="E86" t="n">
-        <v>87.26000213623047</v>
+        <v>85.36000061035156</v>
       </c>
       <c r="F86" t="n">
-        <v>109729700</v>
+        <v>127940700</v>
       </c>
       <c r="G86" t="n">
         <v>0</v>
@@ -2679,22 +2679,22 @@
     </row>
     <row r="87">
       <c r="A87" s="1" t="n">
-        <v>46043</v>
+        <v>46044</v>
       </c>
       <c r="B87" t="n">
-        <v>82.51999664306641</v>
+        <v>85.01999664306641</v>
       </c>
       <c r="C87" t="n">
-        <v>86</v>
+        <v>85.09999847412109</v>
       </c>
       <c r="D87" t="n">
-        <v>81.93000030517578</v>
+        <v>82.98000335693359</v>
       </c>
       <c r="E87" t="n">
-        <v>85.36000061035156</v>
+        <v>83.54000091552734</v>
       </c>
       <c r="F87" t="n">
-        <v>127940700</v>
+        <v>69113300</v>
       </c>
       <c r="G87" t="n">
         <v>0</v>
@@ -2705,22 +2705,22 @@
     </row>
     <row r="88">
       <c r="A88" s="1" t="n">
-        <v>46044</v>
+        <v>46045</v>
       </c>
       <c r="B88" t="n">
-        <v>85.01999664306641</v>
+        <v>83.43000030517578</v>
       </c>
       <c r="C88" t="n">
-        <v>85.09999847412109</v>
+        <v>86.30000305175781</v>
       </c>
       <c r="D88" t="n">
-        <v>82.98000335693359</v>
+        <v>83.27999877929688</v>
       </c>
       <c r="E88" t="n">
-        <v>83.54000091552734</v>
+        <v>86.12000274658203</v>
       </c>
       <c r="F88" t="n">
-        <v>69113300</v>
+        <v>64520400</v>
       </c>
       <c r="G88" t="n">
         <v>0</v>
@@ -2731,22 +2731,22 @@
     </row>
     <row r="89">
       <c r="A89" s="1" t="n">
-        <v>46045</v>
+        <v>46048</v>
       </c>
       <c r="B89" t="n">
-        <v>83.43000030517578</v>
+        <v>86.91999816894531</v>
       </c>
       <c r="C89" t="n">
-        <v>86.30000305175781</v>
+        <v>86.94000244140625</v>
       </c>
       <c r="D89" t="n">
-        <v>83.27999877929688</v>
+        <v>85.34999847412109</v>
       </c>
       <c r="E89" t="n">
-        <v>86.12000274658203</v>
+        <v>85.69999694824219</v>
       </c>
       <c r="F89" t="n">
-        <v>64520400</v>
+        <v>40941900</v>
       </c>
       <c r="G89" t="n">
         <v>0</v>
@@ -2757,22 +2757,22 @@
     </row>
     <row r="90">
       <c r="A90" s="1" t="n">
-        <v>46048</v>
+        <v>46049</v>
       </c>
       <c r="B90" t="n">
-        <v>86.91999816894531</v>
+        <v>85.27999877929688</v>
       </c>
       <c r="C90" t="n">
-        <v>86.94000244140625</v>
+        <v>85.59999847412109</v>
       </c>
       <c r="D90" t="n">
-        <v>85.34999847412109</v>
+        <v>83.87999725341797</v>
       </c>
       <c r="E90" t="n">
-        <v>85.69999694824219</v>
+        <v>85.58000183105469</v>
       </c>
       <c r="F90" t="n">
-        <v>40941900</v>
+        <v>37790800</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
@@ -2783,22 +2783,22 @@
     </row>
     <row r="91">
       <c r="A91" s="1" t="n">
-        <v>46049</v>
+        <v>46050</v>
       </c>
       <c r="B91" t="n">
-        <v>85.27999877929688</v>
+        <v>85.62999725341797</v>
       </c>
       <c r="C91" t="n">
-        <v>85.59999847412109</v>
+        <v>86.47000122070312</v>
       </c>
       <c r="D91" t="n">
-        <v>83.87999725341797</v>
+        <v>84.30000305175781</v>
       </c>
       <c r="E91" t="n">
-        <v>85.58000183105469</v>
+        <v>84.63999938964844</v>
       </c>
       <c r="F91" t="n">
-        <v>37790800</v>
+        <v>37762600</v>
       </c>
       <c r="G91" t="n">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="92">
       <c r="A92" s="1" t="n">
-        <v>46050</v>
+        <v>46051</v>
       </c>
       <c r="B92" t="n">
-        <v>85.62999725341797</v>
+        <v>84.30999755859375</v>
       </c>
       <c r="C92" t="n">
-        <v>86.47000122070312</v>
+        <v>84.37999725341797</v>
       </c>
       <c r="D92" t="n">
-        <v>84.30000305175781</v>
+        <v>82.34999847412109</v>
       </c>
       <c r="E92" t="n">
-        <v>84.63999938964844</v>
+        <v>83.16000366210938</v>
       </c>
       <c r="F92" t="n">
-        <v>37762600</v>
+        <v>42278100</v>
       </c>
       <c r="G92" t="n">
         <v>0</v>
@@ -2835,22 +2835,22 @@
     </row>
     <row r="93">
       <c r="A93" s="1" t="n">
-        <v>46051</v>
+        <v>46052</v>
       </c>
       <c r="B93" t="n">
-        <v>84.30999755859375</v>
+        <v>83.09999847412109</v>
       </c>
       <c r="C93" t="n">
-        <v>84.37999725341797</v>
+        <v>84.05999755859375</v>
       </c>
       <c r="D93" t="n">
-        <v>82.34999847412109</v>
+        <v>82.77999877929688</v>
       </c>
       <c r="E93" t="n">
-        <v>83.16000366210938</v>
+        <v>83.48999786376953</v>
       </c>
       <c r="F93" t="n">
-        <v>42278100</v>
+        <v>45755000</v>
       </c>
       <c r="G93" t="n">
         <v>0</v>
@@ -2861,22 +2861,22 @@
     </row>
     <row r="94">
       <c r="A94" s="1" t="n">
-        <v>46052</v>
+        <v>46055</v>
       </c>
       <c r="B94" t="n">
-        <v>83.09999847412109</v>
+        <v>83.52999877929688</v>
       </c>
       <c r="C94" t="n">
-        <v>84.05999755859375</v>
+        <v>85.26999664306641</v>
       </c>
       <c r="D94" t="n">
-        <v>82.77999877929688</v>
+        <v>82.72000122070312</v>
       </c>
       <c r="E94" t="n">
-        <v>83.48999786376953</v>
+        <v>82.76000213623047</v>
       </c>
       <c r="F94" t="n">
-        <v>45755000</v>
+        <v>41445300</v>
       </c>
       <c r="G94" t="n">
         <v>0</v>
@@ -2887,22 +2887,22 @@
     </row>
     <row r="95">
       <c r="A95" s="1" t="n">
-        <v>46055</v>
+        <v>46056</v>
       </c>
       <c r="B95" t="n">
-        <v>83.52999877929688</v>
+        <v>82.23000335693359</v>
       </c>
       <c r="C95" t="n">
-        <v>85.26999664306641</v>
+        <v>82.44999694824219</v>
       </c>
       <c r="D95" t="n">
-        <v>82.72000122070312</v>
+        <v>79.62000274658203</v>
       </c>
       <c r="E95" t="n">
-        <v>82.76000213623047</v>
+        <v>79.94000244140625</v>
       </c>
       <c r="F95" t="n">
-        <v>41445300</v>
+        <v>49789000</v>
       </c>
       <c r="G95" t="n">
         <v>0</v>
@@ -2913,22 +2913,22 @@
     </row>
     <row r="96">
       <c r="A96" s="1" t="n">
-        <v>46056</v>
+        <v>46057</v>
       </c>
       <c r="B96" t="n">
-        <v>82.23000335693359</v>
+        <v>79.98999786376953</v>
       </c>
       <c r="C96" t="n">
-        <v>82.44999694824219</v>
+        <v>81.44000244140625</v>
       </c>
       <c r="D96" t="n">
-        <v>79.62000274658203</v>
+        <v>79.23000335693359</v>
       </c>
       <c r="E96" t="n">
-        <v>79.94000244140625</v>
+        <v>80.16000366210938</v>
       </c>
       <c r="F96" t="n">
-        <v>49789000</v>
+        <v>48963200</v>
       </c>
       <c r="G96" t="n">
         <v>0</v>
@@ -2939,22 +2939,22 @@
     </row>
     <row r="97">
       <c r="A97" s="1" t="n">
-        <v>46057</v>
+        <v>46058</v>
       </c>
       <c r="B97" t="n">
-        <v>79.98999786376953</v>
+        <v>81.48999786376953</v>
       </c>
       <c r="C97" t="n">
-        <v>81.44000244140625</v>
+        <v>83.30000305175781</v>
       </c>
       <c r="D97" t="n">
-        <v>79.23000335693359</v>
+        <v>80.54000091552734</v>
       </c>
       <c r="E97" t="n">
-        <v>80.16000366210938</v>
+        <v>80.87000274658203</v>
       </c>
       <c r="F97" t="n">
-        <v>48963200</v>
+        <v>54805700</v>
       </c>
       <c r="G97" t="n">
         <v>0</v>
@@ -2965,22 +2965,22 @@
     </row>
     <row r="98">
       <c r="A98" s="1" t="n">
-        <v>46058</v>
+        <v>46059</v>
       </c>
       <c r="B98" t="n">
-        <v>81.48999786376953</v>
+        <v>81.01999664306641</v>
       </c>
       <c r="C98" t="n">
-        <v>83.30000305175781</v>
+        <v>82.48999786376953</v>
       </c>
       <c r="D98" t="n">
-        <v>80.54000091552734</v>
+        <v>80.65000152587891</v>
       </c>
       <c r="E98" t="n">
-        <v>80.87000274658203</v>
+        <v>82.19999694824219</v>
       </c>
       <c r="F98" t="n">
-        <v>54805700</v>
+        <v>46154100</v>
       </c>
       <c r="G98" t="n">
         <v>0</v>
@@ -2991,22 +2991,22 @@
     </row>
     <row r="99">
       <c r="A99" s="1" t="n">
-        <v>46059</v>
+        <v>46062</v>
       </c>
       <c r="B99" t="n">
-        <v>81.01999664306641</v>
+        <v>82.18000030517578</v>
       </c>
       <c r="C99" t="n">
-        <v>82.48999786376953</v>
+        <v>82.20999908447266</v>
       </c>
       <c r="D99" t="n">
-        <v>80.65000152587891</v>
+        <v>79.87000274658203</v>
       </c>
       <c r="E99" t="n">
-        <v>82.19999694824219</v>
+        <v>81.47000122070312</v>
       </c>
       <c r="F99" t="n">
-        <v>46154100</v>
+        <v>42200200</v>
       </c>
       <c r="G99" t="n">
         <v>0</v>
@@ -3017,22 +3017,22 @@
     </row>
     <row r="100">
       <c r="A100" s="1" t="n">
-        <v>46062</v>
+        <v>46063</v>
       </c>
       <c r="B100" t="n">
-        <v>82.18000030517578</v>
+        <v>82.72000122070312</v>
       </c>
       <c r="C100" t="n">
+        <v>84.66000366210938</v>
+      </c>
+      <c r="D100" t="n">
+        <v>82.08999633789062</v>
+      </c>
+      <c r="E100" t="n">
         <v>82.20999908447266</v>
       </c>
-      <c r="D100" t="n">
-        <v>79.87000274658203</v>
-      </c>
-      <c r="E100" t="n">
-        <v>81.47000122070312</v>
-      </c>
       <c r="F100" t="n">
-        <v>42200200</v>
+        <v>43595800</v>
       </c>
       <c r="G100" t="n">
         <v>0</v>
@@ -3043,22 +3043,22 @@
     </row>
     <row r="101">
       <c r="A101" s="1" t="n">
-        <v>46063</v>
+        <v>46064</v>
       </c>
       <c r="B101" t="n">
-        <v>82.72000122070312</v>
+        <v>81.95999908447266</v>
       </c>
       <c r="C101" t="n">
-        <v>84.66000366210938</v>
+        <v>82.48000335693359</v>
       </c>
       <c r="D101" t="n">
-        <v>82.08999633789062</v>
+        <v>79.44999694824219</v>
       </c>
       <c r="E101" t="n">
-        <v>82.20999908447266</v>
+        <v>79.62000274658203</v>
       </c>
       <c r="F101" t="n">
-        <v>43595800</v>
+        <v>40840300</v>
       </c>
       <c r="G101" t="n">
         <v>0</v>
@@ -3069,22 +3069,22 @@
     </row>
     <row r="102">
       <c r="A102" s="1" t="n">
-        <v>46064</v>
+        <v>46065</v>
       </c>
       <c r="B102" t="n">
-        <v>81.95999908447266</v>
+        <v>79.11000061035156</v>
       </c>
       <c r="C102" t="n">
-        <v>82.48000335693359</v>
+        <v>79.15000152587891</v>
       </c>
       <c r="D102" t="n">
-        <v>79.44999694824219</v>
+        <v>75.23000335693359</v>
       </c>
       <c r="E102" t="n">
-        <v>79.62000274658203</v>
+        <v>75.86000061035156</v>
       </c>
       <c r="F102" t="n">
-        <v>40840300</v>
+        <v>73516100</v>
       </c>
       <c r="G102" t="n">
         <v>0</v>
@@ -3095,22 +3095,22 @@
     </row>
     <row r="103">
       <c r="A103" s="1" t="n">
-        <v>46065</v>
+        <v>46066</v>
       </c>
       <c r="B103" t="n">
-        <v>79.11000061035156</v>
+        <v>76.13999938964844</v>
       </c>
       <c r="C103" t="n">
-        <v>79.15000152587891</v>
+        <v>77.18000030517578</v>
       </c>
       <c r="D103" t="n">
-        <v>75.23000335693359</v>
+        <v>75.52999877929688</v>
       </c>
       <c r="E103" t="n">
-        <v>75.86000061035156</v>
+        <v>76.87000274658203</v>
       </c>
       <c r="F103" t="n">
-        <v>73516100</v>
+        <v>42292100</v>
       </c>
       <c r="G103" t="n">
         <v>0</v>
@@ -3121,22 +3121,22 @@
     </row>
     <row r="104">
       <c r="A104" s="1" t="n">
-        <v>46066</v>
+        <v>46070</v>
       </c>
       <c r="B104" t="n">
-        <v>76.13999938964844</v>
+        <v>76.91999816894531</v>
       </c>
       <c r="C104" t="n">
-        <v>77.18000030517578</v>
+        <v>77.87000274658203</v>
       </c>
       <c r="D104" t="n">
-        <v>75.52999877929688</v>
+        <v>75.30000305175781</v>
       </c>
       <c r="E104" t="n">
-        <v>76.87000274658203</v>
+        <v>77</v>
       </c>
       <c r="F104" t="n">
-        <v>42292100</v>
+        <v>35961500</v>
       </c>
       <c r="G104" t="n">
         <v>0</v>
@@ -3147,22 +3147,22 @@
     </row>
     <row r="105">
       <c r="A105" s="1" t="n">
-        <v>46070</v>
+        <v>46071</v>
       </c>
       <c r="B105" t="n">
-        <v>76.91999816894531</v>
+        <v>77.31999969482422</v>
       </c>
       <c r="C105" t="n">
-        <v>77.87000274658203</v>
+        <v>78.31999969482422</v>
       </c>
       <c r="D105" t="n">
-        <v>75.30000305175781</v>
+        <v>76.27999877929688</v>
       </c>
       <c r="E105" t="n">
-        <v>77</v>
+        <v>77.98999786376953</v>
       </c>
       <c r="F105" t="n">
-        <v>35961500</v>
+        <v>29883100</v>
       </c>
       <c r="G105" t="n">
         <v>0</v>
@@ -3173,22 +3173,22 @@
     </row>
     <row r="106">
       <c r="A106" s="1" t="n">
-        <v>46071</v>
+        <v>46072</v>
       </c>
       <c r="B106" t="n">
-        <v>77.31999969482422</v>
+        <v>77.75</v>
       </c>
       <c r="C106" t="n">
-        <v>78.31999969482422</v>
+        <v>78.69999694824219</v>
       </c>
       <c r="D106" t="n">
-        <v>76.27999877929688</v>
+        <v>76.58999633789062</v>
       </c>
       <c r="E106" t="n">
-        <v>77.98999786376953</v>
+        <v>77</v>
       </c>
       <c r="F106" t="n">
-        <v>29883100</v>
+        <v>30139200</v>
       </c>
       <c r="G106" t="n">
         <v>0</v>
@@ -3199,22 +3199,22 @@
     </row>
     <row r="107">
       <c r="A107" s="1" t="n">
-        <v>46072</v>
+        <v>46073</v>
       </c>
       <c r="B107" t="n">
-        <v>77.75</v>
+        <v>76.61000061035156</v>
       </c>
       <c r="C107" t="n">
-        <v>78.69999694824219</v>
+        <v>78.84999847412109</v>
       </c>
       <c r="D107" t="n">
-        <v>76.58999633789062</v>
+        <v>76.40000152587891</v>
       </c>
       <c r="E107" t="n">
-        <v>77</v>
+        <v>78.66999816894531</v>
       </c>
       <c r="F107" t="n">
-        <v>30139200</v>
+        <v>32411300</v>
       </c>
       <c r="G107" t="n">
         <v>0</v>
@@ -3225,22 +3225,22 @@
     </row>
     <row r="108">
       <c r="A108" s="1" t="n">
-        <v>46073</v>
+        <v>46076</v>
       </c>
       <c r="B108" t="n">
-        <v>76.61000061035156</v>
+        <v>77.79000091552734</v>
       </c>
       <c r="C108" t="n">
-        <v>78.84999847412109</v>
+        <v>77.83000183105469</v>
       </c>
       <c r="D108" t="n">
-        <v>76.40000152587891</v>
+        <v>75.01000213623047</v>
       </c>
       <c r="E108" t="n">
-        <v>78.66999816894531</v>
+        <v>76.01999664306641</v>
       </c>
       <c r="F108" t="n">
-        <v>32411300</v>
+        <v>38363000</v>
       </c>
       <c r="G108" t="n">
         <v>0</v>
@@ -3251,22 +3251,22 @@
     </row>
     <row r="109">
       <c r="A109" s="1" t="n">
-        <v>46076</v>
+        <v>46077</v>
       </c>
       <c r="B109" t="n">
-        <v>77.79000091552734</v>
+        <v>75.73000335693359</v>
       </c>
       <c r="C109" t="n">
-        <v>77.83000183105469</v>
+        <v>78.12000274658203</v>
       </c>
       <c r="D109" t="n">
-        <v>75.01000213623047</v>
+        <v>75.20999908447266</v>
       </c>
       <c r="E109" t="n">
-        <v>76.01999664306641</v>
+        <v>78.04000091552734</v>
       </c>
       <c r="F109" t="n">
-        <v>38363000</v>
+        <v>33079100</v>
       </c>
       <c r="G109" t="n">
         <v>0</v>
@@ -3277,22 +3277,22 @@
     </row>
     <row r="110">
       <c r="A110" s="1" t="n">
-        <v>46077</v>
+        <v>46078</v>
       </c>
       <c r="B110" t="n">
-        <v>75.73000335693359</v>
+        <v>79.43000030517578</v>
       </c>
       <c r="C110" t="n">
-        <v>78.12000274658203</v>
+        <v>83.12000274658203</v>
       </c>
       <c r="D110" t="n">
-        <v>75.20999908447266</v>
+        <v>79.25</v>
       </c>
       <c r="E110" t="n">
-        <v>78.04000091552734</v>
+        <v>82.69999694824219</v>
       </c>
       <c r="F110" t="n">
-        <v>33079100</v>
+        <v>69319300</v>
       </c>
       <c r="G110" t="n">
         <v>0</v>
@@ -3303,22 +3303,22 @@
     </row>
     <row r="111">
       <c r="A111" s="1" t="n">
-        <v>46078</v>
+        <v>46079</v>
       </c>
       <c r="B111" t="n">
-        <v>79.43000030517578</v>
+        <v>83.19999694824219</v>
       </c>
       <c r="C111" t="n">
-        <v>83.12000274658203</v>
+        <v>86.5</v>
       </c>
       <c r="D111" t="n">
-        <v>79.25</v>
+        <v>82.80000305175781</v>
       </c>
       <c r="E111" t="n">
-        <v>82.69999694824219</v>
+        <v>84.58999633789062</v>
       </c>
       <c r="F111" t="n">
-        <v>69319300</v>
+        <v>85642500</v>
       </c>
       <c r="G111" t="n">
         <v>0</v>
@@ -3329,22 +3329,22 @@
     </row>
     <row r="112">
       <c r="A112" s="1" t="n">
-        <v>46079</v>
+        <v>46080</v>
       </c>
       <c r="B112" t="n">
-        <v>83.19999694824219</v>
+        <v>94.30000305175781</v>
       </c>
       <c r="C112" t="n">
-        <v>86.5</v>
+        <v>96.75</v>
       </c>
       <c r="D112" t="n">
-        <v>82.80000305175781</v>
+        <v>90.58000183105469</v>
       </c>
       <c r="E112" t="n">
-        <v>84.58999633789062</v>
+        <v>96.23999786376953</v>
       </c>
       <c r="F112" t="n">
-        <v>85642500</v>
+        <v>200767000</v>
       </c>
       <c r="G112" t="n">
         <v>0</v>
@@ -3355,22 +3355,22 @@
     </row>
     <row r="113">
       <c r="A113" s="1" t="n">
-        <v>46080</v>
+        <v>46083</v>
       </c>
       <c r="B113" t="n">
-        <v>94.30000305175781</v>
+        <v>95.26000213623047</v>
       </c>
       <c r="C113" t="n">
-        <v>96.75</v>
+        <v>98.06999969482422</v>
       </c>
       <c r="D113" t="n">
-        <v>90.58000183105469</v>
+        <v>95.19999694824219</v>
       </c>
       <c r="E113" t="n">
-        <v>96.23999786376953</v>
+        <v>97.08999633789062</v>
       </c>
       <c r="F113" t="n">
-        <v>200767000</v>
+        <v>79915400</v>
       </c>
       <c r="G113" t="n">
         <v>0</v>
@@ -3381,22 +3381,22 @@
     </row>
     <row r="114">
       <c r="A114" s="1" t="n">
-        <v>46083</v>
+        <v>46084</v>
       </c>
       <c r="B114" t="n">
-        <v>95.26000213623047</v>
+        <v>96.01000213623047</v>
       </c>
       <c r="C114" t="n">
-        <v>98.06999969482422</v>
+        <v>98.45999908447266</v>
       </c>
       <c r="D114" t="n">
-        <v>95.19999694824219</v>
+        <v>95.33000183105469</v>
       </c>
       <c r="E114" t="n">
-        <v>97.08999633789062</v>
+        <v>97.69999694824219</v>
       </c>
       <c r="F114" t="n">
-        <v>79915400</v>
+        <v>59149000</v>
       </c>
       <c r="G114" t="n">
         <v>0</v>
@@ -3407,22 +3407,22 @@
     </row>
     <row r="115">
       <c r="A115" s="1" t="n">
-        <v>46084</v>
+        <v>46085</v>
       </c>
       <c r="B115" t="n">
-        <v>96.01000213623047</v>
+        <v>97.11000061035156</v>
       </c>
       <c r="C115" t="n">
-        <v>98.45999908447266</v>
+        <v>99.75</v>
       </c>
       <c r="D115" t="n">
-        <v>95.33000183105469</v>
+        <v>96.98999786376953</v>
       </c>
       <c r="E115" t="n">
-        <v>97.69999694824219</v>
+        <v>98.66000366210938</v>
       </c>
       <c r="F115" t="n">
-        <v>59149000</v>
+        <v>52604300</v>
       </c>
       <c r="G115" t="n">
         <v>0</v>
@@ -3433,22 +3433,22 @@
     </row>
     <row r="116">
       <c r="A116" s="1" t="n">
-        <v>46085</v>
+        <v>46086</v>
       </c>
       <c r="B116" t="n">
-        <v>97.11000061035156</v>
+        <v>98.5</v>
       </c>
       <c r="C116" t="n">
-        <v>99.75</v>
+        <v>100.1900024414062</v>
       </c>
       <c r="D116" t="n">
-        <v>96.98999786376953</v>
+        <v>98.09999847412109</v>
       </c>
       <c r="E116" t="n">
-        <v>98.66000366210938</v>
+        <v>99.16999816894531</v>
       </c>
       <c r="F116" t="n">
-        <v>52604300</v>
+        <v>53403000</v>
       </c>
       <c r="G116" t="n">
         <v>0</v>
@@ -3459,22 +3459,22 @@
     </row>
     <row r="117">
       <c r="A117" s="1" t="n">
-        <v>46086</v>
+        <v>46087</v>
       </c>
       <c r="B117" t="n">
-        <v>98.5</v>
+        <v>99.33000183105469</v>
       </c>
       <c r="C117" t="n">
-        <v>100.1900024414062</v>
+        <v>99.87999725341797</v>
       </c>
       <c r="D117" t="n">
-        <v>98.09999847412109</v>
+        <v>97.40000152587891</v>
       </c>
       <c r="E117" t="n">
-        <v>99.16999816894531</v>
+        <v>99.01999664306641</v>
       </c>
       <c r="F117" t="n">
-        <v>53403000</v>
+        <v>41196300</v>
       </c>
       <c r="G117" t="n">
         <v>0</v>
@@ -3485,22 +3485,22 @@
     </row>
     <row r="118">
       <c r="A118" s="1" t="n">
-        <v>46087</v>
+        <v>46090</v>
       </c>
       <c r="B118" t="n">
-        <v>99.33000183105469</v>
+        <v>97.69999694824219</v>
       </c>
       <c r="C118" t="n">
-        <v>99.87999725341797</v>
+        <v>98.94000244140625</v>
       </c>
       <c r="D118" t="n">
-        <v>97.40000152587891</v>
+        <v>96.58000183105469</v>
       </c>
       <c r="E118" t="n">
-        <v>99.01999664306641</v>
+        <v>98.31999969482422</v>
       </c>
       <c r="F118" t="n">
-        <v>41196300</v>
+        <v>48589000</v>
       </c>
       <c r="G118" t="n">
         <v>0</v>
@@ -3511,22 +3511,22 @@
     </row>
     <row r="119">
       <c r="A119" s="1" t="n">
-        <v>46090</v>
+        <v>46091</v>
       </c>
       <c r="B119" t="n">
-        <v>97.69999694824219</v>
+        <v>97.80999755859375</v>
       </c>
       <c r="C119" t="n">
-        <v>98.94000244140625</v>
+        <v>98.48999786376953</v>
       </c>
       <c r="D119" t="n">
-        <v>96.58000183105469</v>
+        <v>96.29000091552734</v>
       </c>
       <c r="E119" t="n">
-        <v>98.31999969482422</v>
+        <v>96.94000244140625</v>
       </c>
       <c r="F119" t="n">
-        <v>48589000</v>
+        <v>41027200</v>
       </c>
       <c r="G119" t="n">
         <v>0</v>
@@ -3537,22 +3537,22 @@
     </row>
     <row r="120">
       <c r="A120" s="1" t="n">
-        <v>46091</v>
+        <v>46092</v>
       </c>
       <c r="B120" t="n">
-        <v>97.80999755859375</v>
+        <v>97.41000366210938</v>
       </c>
       <c r="C120" t="n">
-        <v>98.48999786376953</v>
+        <v>98</v>
       </c>
       <c r="D120" t="n">
-        <v>96.29000091552734</v>
+        <v>94.69000244140625</v>
       </c>
       <c r="E120" t="n">
-        <v>96.94000244140625</v>
+        <v>94.88999938964844</v>
       </c>
       <c r="F120" t="n">
-        <v>41027200</v>
+        <v>33962900</v>
       </c>
       <c r="G120" t="n">
         <v>0</v>
@@ -3563,22 +3563,22 @@
     </row>
     <row r="121">
       <c r="A121" s="1" t="n">
-        <v>46092</v>
+        <v>46093</v>
       </c>
       <c r="B121" t="n">
-        <v>97.41000366210938</v>
+        <v>94.86000061035156</v>
       </c>
       <c r="C121" t="n">
-        <v>98</v>
+        <v>95.40000152587891</v>
       </c>
       <c r="D121" t="n">
-        <v>94.69000244140625</v>
+        <v>93.87000274658203</v>
       </c>
       <c r="E121" t="n">
-        <v>94.88999938964844</v>
+        <v>94.30999755859375</v>
       </c>
       <c r="F121" t="n">
-        <v>33962900</v>
+        <v>34206900</v>
       </c>
       <c r="G121" t="n">
         <v>0</v>
@@ -3589,22 +3589,22 @@
     </row>
     <row r="122">
       <c r="A122" s="1" t="n">
-        <v>46093</v>
+        <v>46094</v>
       </c>
       <c r="B122" t="n">
-        <v>94.86000061035156</v>
+        <v>94.63999938964844</v>
       </c>
       <c r="C122" t="n">
-        <v>95.40000152587891</v>
+        <v>95.68000030517578</v>
       </c>
       <c r="D122" t="n">
-        <v>93.87000274658203</v>
+        <v>94.23999786376953</v>
       </c>
       <c r="E122" t="n">
-        <v>94.30999755859375</v>
+        <v>95.30999755859375</v>
       </c>
       <c r="F122" t="n">
-        <v>34206900</v>
+        <v>29876700</v>
       </c>
       <c r="G122" t="n">
         <v>0</v>
@@ -3615,22 +3615,22 @@
     </row>
     <row r="123">
       <c r="A123" s="1" t="n">
-        <v>46094</v>
+        <v>46097</v>
       </c>
       <c r="B123" t="n">
-        <v>94.63999938964844</v>
+        <v>95.58000183105469</v>
       </c>
       <c r="C123" t="n">
-        <v>95.68000030517578</v>
+        <v>96.09999847412109</v>
       </c>
       <c r="D123" t="n">
-        <v>94.23999786376953</v>
+        <v>94.36000061035156</v>
       </c>
       <c r="E123" t="n">
-        <v>95.30999755859375</v>
+        <v>95.19999694824219</v>
       </c>
       <c r="F123" t="n">
-        <v>29876700</v>
+        <v>34931800</v>
       </c>
       <c r="G123" t="n">
         <v>0</v>
@@ -3641,22 +3641,22 @@
     </row>
     <row r="124">
       <c r="A124" s="1" t="n">
-        <v>46097</v>
+        <v>46098</v>
       </c>
       <c r="B124" t="n">
-        <v>95.58000183105469</v>
+        <v>95.30000305175781</v>
       </c>
       <c r="C124" t="n">
-        <v>96.09999847412109</v>
+        <v>96.33999633789062</v>
       </c>
       <c r="D124" t="n">
+        <v>94.01000213623047</v>
+      </c>
+      <c r="E124" t="n">
         <v>94.36000061035156</v>
       </c>
-      <c r="E124" t="n">
-        <v>95.19999694824219</v>
-      </c>
       <c r="F124" t="n">
-        <v>34931800</v>
+        <v>26434500</v>
       </c>
       <c r="G124" t="n">
         <v>0</v>
@@ -3667,22 +3667,22 @@
     </row>
     <row r="125">
       <c r="A125" s="1" t="n">
-        <v>46098</v>
+        <v>46099</v>
       </c>
       <c r="B125" t="n">
-        <v>95.30000305175781</v>
+        <v>94.44999694824219</v>
       </c>
       <c r="C125" t="n">
-        <v>96.33999633789062</v>
+        <v>95.33999633789062</v>
       </c>
       <c r="D125" t="n">
-        <v>94.01000213623047</v>
+        <v>93.61000061035156</v>
       </c>
       <c r="E125" t="n">
-        <v>94.36000061035156</v>
+        <v>94.69999694824219</v>
       </c>
       <c r="F125" t="n">
-        <v>26434500</v>
+        <v>27878300</v>
       </c>
       <c r="G125" t="n">
         <v>0</v>
@@ -3693,22 +3693,22 @@
     </row>
     <row r="126">
       <c r="A126" s="1" t="n">
-        <v>46099</v>
+        <v>46100</v>
       </c>
       <c r="B126" t="n">
-        <v>94.44999694824219</v>
+        <v>94.30999755859375</v>
       </c>
       <c r="C126" t="n">
-        <v>95.33999633789062</v>
+        <v>95.75</v>
       </c>
       <c r="D126" t="n">
-        <v>93.61000061035156</v>
+        <v>90.77999877929688</v>
       </c>
       <c r="E126" t="n">
-        <v>94.69999694824219</v>
+        <v>91.73999786376953</v>
       </c>
       <c r="F126" t="n">
-        <v>27878300</v>
+        <v>40169300</v>
       </c>
       <c r="G126" t="n">
         <v>0</v>
@@ -3719,22 +3719,22 @@
     </row>
     <row r="127">
       <c r="A127" s="1" t="n">
-        <v>46100</v>
+        <v>46101</v>
       </c>
       <c r="B127" t="n">
-        <v>94.30999755859375</v>
+        <v>91.30999755859375</v>
       </c>
       <c r="C127" t="n">
-        <v>95.75</v>
+        <v>91.87999725341797</v>
       </c>
       <c r="D127" t="n">
-        <v>90.77999877929688</v>
+        <v>90.69000244140625</v>
       </c>
       <c r="E127" t="n">
-        <v>91.73999786376953</v>
+        <v>91.81999969482422</v>
       </c>
       <c r="F127" t="n">
-        <v>40169300</v>
+        <v>61678000</v>
       </c>
       <c r="G127" t="n">
         <v>0</v>
@@ -3745,22 +3745,22 @@
     </row>
     <row r="128">
       <c r="A128" s="1" t="n">
-        <v>46101</v>
+        <v>46104</v>
       </c>
       <c r="B128" t="n">
-        <v>91.30999755859375</v>
+        <v>92.04000091552734</v>
       </c>
       <c r="C128" t="n">
-        <v>91.87999725341797</v>
+        <v>93.98000335693359</v>
       </c>
       <c r="D128" t="n">
-        <v>90.69000244140625</v>
+        <v>91.86000061035156</v>
       </c>
       <c r="E128" t="n">
-        <v>91.81999969482422</v>
+        <v>93.37999725341797</v>
       </c>
       <c r="F128" t="n">
-        <v>61678000</v>
+        <v>34315900</v>
       </c>
       <c r="G128" t="n">
         <v>0</v>
@@ -3771,22 +3771,22 @@
     </row>
     <row r="129">
       <c r="A129" s="1" t="n">
-        <v>46104</v>
+        <v>46105</v>
       </c>
       <c r="B129" t="n">
-        <v>92.04000091552734</v>
+        <v>92.79000091552734</v>
       </c>
       <c r="C129" t="n">
-        <v>93.98000335693359</v>
+        <v>93.73999786376953</v>
       </c>
       <c r="D129" t="n">
-        <v>91.86000061035156</v>
+        <v>90.81999969482422</v>
       </c>
       <c r="E129" t="n">
-        <v>93.37999725341797</v>
+        <v>90.91999816894531</v>
       </c>
       <c r="F129" t="n">
-        <v>34315900</v>
+        <v>28938000</v>
       </c>
       <c r="G129" t="n">
         <v>0</v>
@@ -3797,22 +3797,22 @@
     </row>
     <row r="130">
       <c r="A130" s="1" t="n">
-        <v>46105</v>
+        <v>46106</v>
       </c>
       <c r="B130" t="n">
-        <v>92.79000091552734</v>
+        <v>91.70999908447266</v>
       </c>
       <c r="C130" t="n">
-        <v>93.73999786376953</v>
+        <v>92.51999664306641</v>
       </c>
       <c r="D130" t="n">
-        <v>90.81999969482422</v>
+        <v>91.23999786376953</v>
       </c>
       <c r="E130" t="n">
-        <v>90.91999816894531</v>
+        <v>92.27999877929688</v>
       </c>
       <c r="F130" t="n">
-        <v>28938000</v>
+        <v>29545600</v>
       </c>
       <c r="G130" t="n">
         <v>0</v>
@@ -3823,22 +3823,22 @@
     </row>
     <row r="131">
       <c r="A131" s="1" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B131" t="n">
-        <v>91.70999908447266</v>
+        <v>91.51999664306641</v>
       </c>
       <c r="C131" t="n">
-        <v>92.51999664306641</v>
+        <v>95.86000061035156</v>
       </c>
       <c r="D131" t="n">
-        <v>91.23999786376953</v>
+        <v>91.01000213623047</v>
       </c>
       <c r="E131" t="n">
-        <v>92.27999877929688</v>
+        <v>93.31999969482422</v>
       </c>
       <c r="F131" t="n">
-        <v>29545600</v>
+        <v>59522000</v>
       </c>
       <c r="G131" t="n">
         <v>0</v>
@@ -3849,22 +3849,22 @@
     </row>
     <row r="132">
       <c r="A132" s="1" t="n">
-        <v>46107</v>
+        <v>46108</v>
       </c>
       <c r="B132" t="n">
-        <v>91.51999664306641</v>
+        <v>94.56999969482422</v>
       </c>
       <c r="C132" t="n">
-        <v>95.86000061035156</v>
+        <v>95.58000183105469</v>
       </c>
       <c r="D132" t="n">
-        <v>91.01000213623047</v>
+        <v>92.73999786376953</v>
       </c>
       <c r="E132" t="n">
-        <v>93.31999969482422</v>
+        <v>93.43000030517578</v>
       </c>
       <c r="F132" t="n">
-        <v>59522000</v>
+        <v>44590700</v>
       </c>
       <c r="G132" t="n">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="133">
       <c r="A133" s="1" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B133" t="n">
-        <v>94.56999969482422</v>
+        <v>92.75</v>
       </c>
       <c r="C133" t="n">
-        <v>95.58000183105469</v>
+        <v>94.48999786376953</v>
       </c>
       <c r="D133" t="n">
-        <v>92.73999786376953</v>
+        <v>92.22000122070312</v>
       </c>
       <c r="E133" t="n">
-        <v>93.43000030517578</v>
+        <v>92.97000122070312</v>
       </c>
       <c r="F133" t="n">
-        <v>44590700</v>
+        <v>32375100</v>
       </c>
       <c r="G133" t="n">
         <v>0</v>
@@ -3901,22 +3901,22 @@
     </row>
     <row r="134">
       <c r="A134" s="1" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B134" t="n">
-        <v>92.75</v>
+        <v>93.02999877929688</v>
       </c>
       <c r="C134" t="n">
-        <v>94.48999786376953</v>
+        <v>96.26000213623047</v>
       </c>
       <c r="D134" t="n">
-        <v>92.22000122070312</v>
+        <v>93.02999877929688</v>
       </c>
       <c r="E134" t="n">
-        <v>92.97000122070312</v>
+        <v>96.15000152587891</v>
       </c>
       <c r="F134" t="n">
-        <v>32375100</v>
+        <v>54270000</v>
       </c>
       <c r="G134" t="n">
         <v>0</v>
@@ -3927,22 +3927,22 @@
     </row>
     <row r="135">
       <c r="A135" s="1" t="n">
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="B135" t="n">
-        <v>93.02999877929688</v>
+        <v>96.47000122070312</v>
       </c>
       <c r="C135" t="n">
-        <v>96.26000213623047</v>
+        <v>97.19999694824219</v>
       </c>
       <c r="D135" t="n">
-        <v>93.02999877929688</v>
+        <v>94.26000213623047</v>
       </c>
       <c r="E135" t="n">
-        <v>96.15000152587891</v>
+        <v>95.55000305175781</v>
       </c>
       <c r="F135" t="n">
-        <v>54270000</v>
+        <v>30439300</v>
       </c>
       <c r="G135" t="n">
         <v>0</v>
@@ -3953,22 +3953,22 @@
     </row>
     <row r="136">
       <c r="A136" s="1" t="n">
-        <v>46113</v>
+        <v>46114</v>
       </c>
       <c r="B136" t="n">
-        <v>96.47000122070312</v>
+        <v>95.26999664306641</v>
       </c>
       <c r="C136" t="n">
-        <v>97.19999694824219</v>
+        <v>98.70999908447266</v>
       </c>
       <c r="D136" t="n">
-        <v>94.26000213623047</v>
+        <v>95.16999816894531</v>
       </c>
       <c r="E136" t="n">
-        <v>95.55000305175781</v>
+        <v>98.66000366210938</v>
       </c>
       <c r="F136" t="n">
-        <v>30439300</v>
+        <v>37068000</v>
       </c>
       <c r="G136" t="n">
         <v>0</v>
@@ -3979,22 +3979,22 @@
     </row>
     <row r="137">
       <c r="A137" s="1" t="n">
-        <v>46114</v>
+        <v>46118</v>
       </c>
       <c r="B137" t="n">
-        <v>95.26999664306641</v>
+        <v>100.9599990844727</v>
       </c>
       <c r="C137" t="n">
-        <v>98.70999908447266</v>
+        <v>102.6900024414062</v>
       </c>
       <c r="D137" t="n">
-        <v>95.16999816894531</v>
+        <v>97.97000122070312</v>
       </c>
       <c r="E137" t="n">
-        <v>98.66000366210938</v>
+        <v>98.93000030517578</v>
       </c>
       <c r="F137" t="n">
-        <v>37068000</v>
+        <v>37029300</v>
       </c>
       <c r="G137" t="n">
         <v>0</v>
@@ -4005,22 +4005,22 @@
     </row>
     <row r="138">
       <c r="A138" s="1" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B138" t="n">
-        <v>100.9599990844727</v>
+        <v>98.55000305175781</v>
       </c>
       <c r="C138" t="n">
-        <v>102.6900024414062</v>
+        <v>99.87999725341797</v>
       </c>
       <c r="D138" t="n">
-        <v>97.97000122070312</v>
+        <v>98.25</v>
       </c>
       <c r="E138" t="n">
-        <v>98.93000030517578</v>
+        <v>98.81999969482422</v>
       </c>
       <c r="F138" t="n">
-        <v>37029300</v>
+        <v>25016700</v>
       </c>
       <c r="G138" t="n">
         <v>0</v>
@@ -4031,22 +4031,22 @@
     </row>
     <row r="139">
       <c r="A139" s="1" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B139" t="n">
-        <v>98.55000305175781</v>
+        <v>100.3199996948242</v>
       </c>
       <c r="C139" t="n">
-        <v>99.87999725341797</v>
+        <v>100.4000015258789</v>
       </c>
       <c r="D139" t="n">
-        <v>98.25</v>
+        <v>97.44000244140625</v>
       </c>
       <c r="E139" t="n">
-        <v>98.81999969482422</v>
+        <v>99.38999938964844</v>
       </c>
       <c r="F139" t="n">
-        <v>25016700</v>
+        <v>30957600</v>
       </c>
       <c r="G139" t="n">
         <v>0</v>
@@ -4057,22 +4057,22 @@
     </row>
     <row r="140">
       <c r="A140" s="1" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B140" t="n">
-        <v>100.3199996948242</v>
+        <v>99.62999725341797</v>
       </c>
       <c r="C140" t="n">
-        <v>100.4000015258789</v>
+        <v>102.3399963378906</v>
       </c>
       <c r="D140" t="n">
-        <v>97.44000244140625</v>
+        <v>99.08000183105469</v>
       </c>
       <c r="E140" t="n">
-        <v>99.38999938964844</v>
+        <v>102.0500030517578</v>
       </c>
       <c r="F140" t="n">
-        <v>30957600</v>
+        <v>35087800</v>
       </c>
       <c r="G140" t="n">
         <v>0</v>
@@ -4083,22 +4083,22 @@
     </row>
     <row r="141">
       <c r="A141" s="1" t="n">
-        <v>46121</v>
+        <v>46122</v>
       </c>
       <c r="B141" t="n">
-        <v>99.62999725341797</v>
+        <v>102.4700012207031</v>
       </c>
       <c r="C141" t="n">
-        <v>102.3399963378906</v>
+        <v>103.0800018310547</v>
       </c>
       <c r="D141" t="n">
-        <v>99.08000183105469</v>
+        <v>101.4599990844727</v>
       </c>
       <c r="E141" t="n">
-        <v>102.0500030517578</v>
+        <v>103.0100021362305</v>
       </c>
       <c r="F141" t="n">
-        <v>35087800</v>
+        <v>25769900</v>
       </c>
       <c r="G141" t="n">
         <v>0</v>
@@ -4109,22 +4109,22 @@
     </row>
     <row r="142">
       <c r="A142" s="1" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B142" t="n">
-        <v>102.4700012207031</v>
+        <v>103.0299987792969</v>
       </c>
       <c r="C142" t="n">
-        <v>103.0800018310547</v>
+        <v>103.6699981689453</v>
       </c>
       <c r="D142" t="n">
-        <v>101.4599990844727</v>
+        <v>102.0599975585938</v>
       </c>
       <c r="E142" t="n">
-        <v>103.0100021362305</v>
+        <v>103.1600036621094</v>
       </c>
       <c r="F142" t="n">
-        <v>25769900</v>
+        <v>26042800</v>
       </c>
       <c r="G142" t="n">
         <v>0</v>
@@ -4135,22 +4135,22 @@
     </row>
     <row r="143">
       <c r="A143" s="1" t="n">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="B143" t="n">
-        <v>103.0299987792969</v>
+        <v>103.120002746582</v>
       </c>
       <c r="C143" t="n">
-        <v>103.6699981689453</v>
+        <v>106.5699996948242</v>
       </c>
       <c r="D143" t="n">
-        <v>102.0599975585938</v>
+        <v>103.0400009155273</v>
       </c>
       <c r="E143" t="n">
-        <v>103.1600036621094</v>
+        <v>106.2799987792969</v>
       </c>
       <c r="F143" t="n">
-        <v>26042800</v>
+        <v>40534900</v>
       </c>
       <c r="G143" t="n">
         <v>0</v>
@@ -4161,22 +4161,22 @@
     </row>
     <row r="144">
       <c r="A144" s="1" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B144" t="n">
-        <v>103.120002746582</v>
+        <v>105.9800033569336</v>
       </c>
       <c r="C144" t="n">
-        <v>106.5699996948242</v>
+        <v>107.8499984741211</v>
       </c>
       <c r="D144" t="n">
-        <v>103.0400009155273</v>
+        <v>105.0400009155273</v>
       </c>
       <c r="E144" t="n">
-        <v>106.2799987792969</v>
+        <v>107.7099990844727</v>
       </c>
       <c r="F144" t="n">
-        <v>40534900</v>
+        <v>38023700</v>
       </c>
       <c r="G144" t="n">
         <v>0</v>
@@ -4187,22 +4187,22 @@
     </row>
     <row r="145">
       <c r="A145" s="1" t="n">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c r="B145" t="n">
-        <v>105.9800033569336</v>
+        <v>107.4700012207031</v>
       </c>
       <c r="C145" t="n">
-        <v>107.8499984741211</v>
+        <v>108.9499969482422</v>
       </c>
       <c r="D145" t="n">
-        <v>105.0400009155273</v>
+        <v>106.620002746582</v>
       </c>
       <c r="E145" t="n">
-        <v>107.7099990844727</v>
+        <v>107.7900009155273</v>
       </c>
       <c r="F145" t="n">
-        <v>38023700</v>
+        <v>64928300</v>
       </c>
       <c r="G145" t="n">
         <v>0</v>
@@ -4213,22 +4213,22 @@
     </row>
     <row r="146">
       <c r="A146" s="1" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B146" t="n">
-        <v>107.4700012207031</v>
+        <v>96.37000274658203</v>
       </c>
       <c r="C146" t="n">
-        <v>108.9499969482422</v>
+        <v>98.73999786376953</v>
       </c>
       <c r="D146" t="n">
-        <v>106.620002746582</v>
+        <v>95.09999847412109</v>
       </c>
       <c r="E146" t="n">
-        <v>107.7900009155273</v>
+        <v>97.30999755859375</v>
       </c>
       <c r="F146" t="n">
-        <v>64928300</v>
+        <v>125958700</v>
       </c>
       <c r="G146" t="n">
         <v>0</v>
@@ -4239,22 +4239,22 @@
     </row>
     <row r="147">
       <c r="A147" s="1" t="n">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c r="B147" t="n">
-        <v>96.37000274658203</v>
+        <v>97.13999938964844</v>
       </c>
       <c r="C147" t="n">
-        <v>98.73999786376953</v>
+        <v>97.59999847412109</v>
       </c>
       <c r="D147" t="n">
-        <v>95.09999847412109</v>
+        <v>93.54000091552734</v>
       </c>
       <c r="E147" t="n">
-        <v>97.30999755859375</v>
+        <v>94.83000183105469</v>
       </c>
       <c r="F147" t="n">
-        <v>125958700</v>
+        <v>63298300</v>
       </c>
       <c r="G147" t="n">
         <v>0</v>
@@ -4265,22 +4265,22 @@
     </row>
     <row r="148">
       <c r="A148" s="1" t="n">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="B148" t="n">
-        <v>97.13999938964844</v>
+        <v>94</v>
       </c>
       <c r="C148" t="n">
-        <v>97.59999847412109</v>
+        <v>94.65000152587891</v>
       </c>
       <c r="D148" t="n">
-        <v>93.54000091552734</v>
+        <v>92.37000274658203</v>
       </c>
       <c r="E148" t="n">
-        <v>94.83000183105469</v>
+        <v>92.58000183105469</v>
       </c>
       <c r="F148" t="n">
-        <v>63298300</v>
+        <v>61962300</v>
       </c>
       <c r="G148" t="n">
         <v>0</v>
@@ -4291,22 +4291,22 @@
     </row>
     <row r="149">
       <c r="A149" s="1" t="n">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="B149" t="n">
-        <v>94</v>
+        <v>93.05999755859375</v>
       </c>
       <c r="C149" t="n">
-        <v>94.65000152587891</v>
+        <v>93.84999847412109</v>
       </c>
       <c r="D149" t="n">
-        <v>92.37000274658203</v>
+        <v>92.76999664306641</v>
       </c>
       <c r="E149" t="n">
-        <v>92.58000183105469</v>
+        <v>93.23999786376953</v>
       </c>
       <c r="F149" t="n">
-        <v>61962300</v>
+        <v>33694300</v>
       </c>
       <c r="G149" t="n">
         <v>0</v>
@@ -4317,22 +4317,22 @@
     </row>
     <row r="150">
       <c r="A150" s="1" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B150" t="n">
-        <v>93.05999755859375</v>
+        <v>94.05999755859375</v>
       </c>
       <c r="C150" t="n">
-        <v>93.84999847412109</v>
+        <v>94.63999938964844</v>
       </c>
       <c r="D150" t="n">
-        <v>92.76999664306641</v>
+        <v>92.06999969482422</v>
       </c>
       <c r="E150" t="n">
-        <v>93.23999786376953</v>
+        <v>92.81999969482422</v>
       </c>
       <c r="F150" t="n">
-        <v>33694300</v>
+        <v>36851700</v>
       </c>
       <c r="G150" t="n">
         <v>0</v>
@@ -4343,22 +4343,22 @@
     </row>
     <row r="151">
       <c r="A151" s="1" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B151" t="n">
-        <v>94.05999755859375</v>
+        <v>92.56999969482422</v>
       </c>
       <c r="C151" t="n">
-        <v>94.63999938964844</v>
+        <v>93.27999877929688</v>
       </c>
       <c r="D151" t="n">
-        <v>92.06999969482422</v>
+        <v>91.80000305175781</v>
       </c>
       <c r="E151" t="n">
-        <v>92.81999969482422</v>
+        <v>92.44000244140625</v>
       </c>
       <c r="F151" t="n">
-        <v>36851700</v>
+        <v>32553200</v>
       </c>
       <c r="G151" t="n">
         <v>0</v>
@@ -4369,22 +4369,22 @@
     </row>
     <row r="152">
       <c r="A152" s="1" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B152" t="n">
-        <v>92.56999969482422</v>
+        <v>92.05000305175781</v>
       </c>
       <c r="C152" t="n">
-        <v>93.27999877929688</v>
+        <v>92.83999633789062</v>
       </c>
       <c r="D152" t="n">
-        <v>91.80000305175781</v>
+        <v>91.30000305175781</v>
       </c>
       <c r="E152" t="n">
-        <v>92.44000244140625</v>
+        <v>91.37000274658203</v>
       </c>
       <c r="F152" t="n">
-        <v>32553200</v>
+        <v>29707400</v>
       </c>
       <c r="G152" t="n">
         <v>0</v>
@@ -4395,22 +4395,22 @@
     </row>
     <row r="153">
       <c r="A153" s="1" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B153" t="n">
-        <v>92.05000305175781</v>
+        <v>91.5</v>
       </c>
       <c r="C153" t="n">
-        <v>92.83999633789062</v>
+        <v>92.33999633789062</v>
       </c>
       <c r="D153" t="n">
-        <v>91.30000305175781</v>
+        <v>90.01999664306641</v>
       </c>
       <c r="E153" t="n">
-        <v>91.37000274658203</v>
+        <v>92.26999664306641</v>
       </c>
       <c r="F153" t="n">
-        <v>29707400</v>
+        <v>33418100</v>
       </c>
       <c r="G153" t="n">
         <v>0</v>
@@ -4421,22 +4421,22 @@
     </row>
     <row r="154">
       <c r="A154" s="1" t="n">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="B154" t="n">
-        <v>91.5</v>
+        <v>91.23000335693359</v>
       </c>
       <c r="C154" t="n">
-        <v>92.33999633789062</v>
+        <v>92.86000061035156</v>
       </c>
       <c r="D154" t="n">
-        <v>90.01999664306641</v>
+        <v>90.86000061035156</v>
       </c>
       <c r="E154" t="n">
-        <v>92.26999664306641</v>
+        <v>92.12000274658203</v>
       </c>
       <c r="F154" t="n">
-        <v>33418100</v>
+        <v>26122100</v>
       </c>
       <c r="G154" t="n">
         <v>0</v>
@@ -4447,22 +4447,22 @@
     </row>
     <row r="155">
       <c r="A155" s="1" t="n">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="B155" t="n">
-        <v>91.23000335693359</v>
+        <v>91.34999847412109</v>
       </c>
       <c r="C155" t="n">
-        <v>92.86000061035156</v>
+        <v>94.22000122070312</v>
       </c>
       <c r="D155" t="n">
-        <v>90.86000061035156</v>
+        <v>90.76999664306641</v>
       </c>
       <c r="E155" t="n">
-        <v>92.12000274658203</v>
+        <v>93.61000061035156</v>
       </c>
       <c r="F155" t="n">
-        <v>26122100</v>
+        <v>40923000</v>
       </c>
       <c r="G155" t="n">
         <v>0</v>
@@ -4473,22 +4473,22 @@
     </row>
     <row r="156">
       <c r="A156" s="1" t="n">
-        <v>46142</v>
+        <v>46143</v>
       </c>
       <c r="B156" t="n">
-        <v>91.34999847412109</v>
+        <v>94.41999816894531</v>
       </c>
       <c r="C156" t="n">
-        <v>94.22000122070312</v>
+        <v>94.69999694824219</v>
       </c>
       <c r="D156" t="n">
-        <v>90.76999664306641</v>
+        <v>91.90000152587891</v>
       </c>
       <c r="E156" t="n">
-        <v>93.61000061035156</v>
+        <v>92.05999755859375</v>
       </c>
       <c r="F156" t="n">
-        <v>40923000</v>
+        <v>30406900</v>
       </c>
       <c r="G156" t="n">
         <v>0</v>
@@ -4499,22 +4499,22 @@
     </row>
     <row r="157">
       <c r="A157" s="1" t="n">
-        <v>46143</v>
+        <v>46146</v>
       </c>
       <c r="B157" t="n">
-        <v>94.41999816894531</v>
+        <v>92.09999847412109</v>
       </c>
       <c r="C157" t="n">
-        <v>94.69999694824219</v>
+        <v>92.33000183105469</v>
       </c>
       <c r="D157" t="n">
-        <v>91.90000152587891</v>
+        <v>90.88999938964844</v>
       </c>
       <c r="E157" t="n">
-        <v>92.05999755859375</v>
+        <v>91.01999664306641</v>
       </c>
       <c r="F157" t="n">
-        <v>30406900</v>
+        <v>25928800</v>
       </c>
       <c r="G157" t="n">
         <v>0</v>
@@ -4525,22 +4525,22 @@
     </row>
     <row r="158">
       <c r="A158" s="1" t="n">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="B158" t="n">
-        <v>92.09999847412109</v>
+        <v>91.18000030517578</v>
       </c>
       <c r="C158" t="n">
-        <v>92.33000183105469</v>
+        <v>91.27999877929688</v>
       </c>
       <c r="D158" t="n">
-        <v>90.88999938964844</v>
+        <v>87.56999969482422</v>
       </c>
       <c r="E158" t="n">
-        <v>91.01999664306641</v>
+        <v>87.88999938964844</v>
       </c>
       <c r="F158" t="n">
-        <v>25928800</v>
+        <v>51961300</v>
       </c>
       <c r="G158" t="n">
         <v>0</v>
@@ -4551,22 +4551,22 @@
     </row>
     <row r="159">
       <c r="A159" s="1" t="n">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="B159" t="n">
-        <v>91.18000030517578</v>
+        <v>87.15000152587891</v>
       </c>
       <c r="C159" t="n">
-        <v>91.27999877929688</v>
+        <v>88.55000305175781</v>
       </c>
       <c r="D159" t="n">
-        <v>87.56999969482422</v>
+        <v>86.72000122070312</v>
       </c>
       <c r="E159" t="n">
-        <v>87.88999938964844</v>
+        <v>88.26999664306641</v>
       </c>
       <c r="F159" t="n">
-        <v>51961300</v>
+        <v>41932400</v>
       </c>
       <c r="G159" t="n">
         <v>0</v>
@@ -4577,22 +4577,22 @@
     </row>
     <row r="160">
       <c r="A160" s="1" t="n">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="B160" t="n">
-        <v>87.15000152587891</v>
+        <v>88.19999694824219</v>
       </c>
       <c r="C160" t="n">
-        <v>88.55000305175781</v>
+        <v>89.40000152587891</v>
       </c>
       <c r="D160" t="n">
-        <v>86.72000122070312</v>
+        <v>88.12999725341797</v>
       </c>
       <c r="E160" t="n">
-        <v>88.26999664306641</v>
+        <v>88.25</v>
       </c>
       <c r="F160" t="n">
-        <v>41932400</v>
+        <v>30627600</v>
       </c>
       <c r="G160" t="n">
         <v>0</v>
@@ -4603,22 +4603,22 @@
     </row>
     <row r="161">
       <c r="A161" s="1" t="n">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="B161" t="n">
-        <v>88.19999694824219</v>
+        <v>87.70999908447266</v>
       </c>
       <c r="C161" t="n">
-        <v>89.40000152587891</v>
+        <v>88.04000091552734</v>
       </c>
       <c r="D161" t="n">
-        <v>88.12999725341797</v>
+        <v>87.20999908447266</v>
       </c>
       <c r="E161" t="n">
-        <v>88.25</v>
+        <v>87.48999786376953</v>
       </c>
       <c r="F161" t="n">
-        <v>30627600</v>
+        <v>36215100</v>
       </c>
       <c r="G161" t="n">
         <v>0</v>
@@ -4629,22 +4629,22 @@
     </row>
     <row r="162">
       <c r="A162" s="1" t="n">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="B162" t="n">
-        <v>87.70999908447266</v>
+        <v>86.52999877929688</v>
       </c>
       <c r="C162" t="n">
-        <v>88.04000091552734</v>
+        <v>87.33999633789062</v>
       </c>
       <c r="D162" t="n">
-        <v>87.20999908447266</v>
+        <v>85.09999847412109</v>
       </c>
       <c r="E162" t="n">
-        <v>87.48999786376953</v>
+        <v>85.44999694824219</v>
       </c>
       <c r="F162" t="n">
-        <v>36215100</v>
+        <v>40556500</v>
       </c>
       <c r="G162" t="n">
         <v>0</v>
@@ -4655,22 +4655,22 @@
     </row>
     <row r="163">
       <c r="A163" s="1" t="n">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="B163" t="n">
-        <v>86.52999877929688</v>
+        <v>85.91000366210938</v>
       </c>
       <c r="C163" t="n">
-        <v>87.33999633789062</v>
+        <v>89.16999816894531</v>
       </c>
       <c r="D163" t="n">
-        <v>85.09999847412109</v>
+        <v>85.80999755859375</v>
       </c>
       <c r="E163" t="n">
-        <v>85.44999694824219</v>
+        <v>87.66000366210938</v>
       </c>
       <c r="F163" t="n">
-        <v>40556500</v>
+        <v>43556600</v>
       </c>
       <c r="G163" t="n">
         <v>0</v>
@@ -4681,22 +4681,22 @@
     </row>
     <row r="164">
       <c r="A164" s="1" t="n">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="B164" t="n">
-        <v>85.91000366210938</v>
+        <v>86.56999969482422</v>
       </c>
       <c r="C164" t="n">
-        <v>89.16999816894531</v>
+        <v>88.62000274658203</v>
       </c>
       <c r="D164" t="n">
-        <v>85.80999755859375</v>
+        <v>86.27999877929688</v>
       </c>
       <c r="E164" t="n">
-        <v>87.66000366210938</v>
+        <v>87.55999755859375</v>
       </c>
       <c r="F164" t="n">
-        <v>43556600</v>
+        <v>30823500</v>
       </c>
       <c r="G164" t="n">
         <v>0</v>
@@ -4707,22 +4707,22 @@
     </row>
     <row r="165">
       <c r="A165" s="1" t="n">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="B165" t="n">
-        <v>86.56999969482422</v>
+        <v>87.62000274658203</v>
       </c>
       <c r="C165" t="n">
-        <v>88.62000274658203</v>
+        <v>88.5</v>
       </c>
       <c r="D165" t="n">
-        <v>86.27999877929688</v>
+        <v>86.65000152587891</v>
       </c>
       <c r="E165" t="n">
-        <v>87.55999755859375</v>
+        <v>86.94000244140625</v>
       </c>
       <c r="F165" t="n">
-        <v>30823500</v>
+        <v>29408300</v>
       </c>
       <c r="G165" t="n">
         <v>0</v>
@@ -4733,22 +4733,22 @@
     </row>
     <row r="166">
       <c r="A166" s="1" t="n">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="B166" t="n">
-        <v>87.62000274658203</v>
+        <v>87.69000244140625</v>
       </c>
       <c r="C166" t="n">
-        <v>88.5</v>
+        <v>89.48999786376953</v>
       </c>
       <c r="D166" t="n">
-        <v>86.65000152587891</v>
+        <v>86.69000244140625</v>
       </c>
       <c r="E166" t="n">
-        <v>86.94000244140625</v>
+        <v>87.01999664306641</v>
       </c>
       <c r="F166" t="n">
-        <v>29408300</v>
+        <v>32335700</v>
       </c>
       <c r="G166" t="n">
         <v>0</v>
@@ -4759,22 +4759,22 @@
     </row>
     <row r="167">
       <c r="A167" s="1" t="n">
-        <v>46157</v>
+        <v>46160</v>
       </c>
       <c r="B167" t="n">
-        <v>87.69000244140625</v>
+        <v>86.5</v>
       </c>
       <c r="C167" t="n">
-        <v>89.48999786376953</v>
+        <v>89.81999969482422</v>
       </c>
       <c r="D167" t="n">
-        <v>86.69000244140625</v>
+        <v>86.33000183105469</v>
       </c>
       <c r="E167" t="n">
-        <v>87.01999664306641</v>
+        <v>89.65000152587891</v>
       </c>
       <c r="F167" t="n">
-        <v>32335700</v>
+        <v>35800500</v>
       </c>
       <c r="G167" t="n">
         <v>0</v>
@@ -4785,22 +4785,22 @@
     </row>
     <row r="168">
       <c r="A168" s="1" t="n">
-        <v>46160</v>
+        <v>46161</v>
       </c>
       <c r="B168" t="n">
-        <v>86.5</v>
+        <v>90.13999938964844</v>
       </c>
       <c r="C168" t="n">
-        <v>89.81999969482422</v>
+        <v>91.48000335693359</v>
       </c>
       <c r="D168" t="n">
-        <v>86.33000183105469</v>
+        <v>88.69000244140625</v>
       </c>
       <c r="E168" t="n">
-        <v>89.65000152587891</v>
+        <v>89.33000183105469</v>
       </c>
       <c r="F168" t="n">
-        <v>35800500</v>
+        <v>34545700</v>
       </c>
       <c r="G168" t="n">
         <v>0</v>
@@ -4811,22 +4811,22 @@
     </row>
     <row r="169">
       <c r="A169" s="1" t="n">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="B169" t="n">
-        <v>90.13999938964844</v>
+        <v>88.51999664306641</v>
       </c>
       <c r="C169" t="n">
-        <v>91.48000335693359</v>
+        <v>88.55000305175781</v>
       </c>
       <c r="D169" t="n">
-        <v>88.69000244140625</v>
+        <v>87.5</v>
       </c>
       <c r="E169" t="n">
-        <v>89.33000183105469</v>
+        <v>88.08999633789062</v>
       </c>
       <c r="F169" t="n">
-        <v>34545700</v>
+        <v>23463400</v>
       </c>
       <c r="G169" t="n">
         <v>0</v>
@@ -4837,22 +4837,22 @@
     </row>
     <row r="170">
       <c r="A170" s="1" t="n">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="B170" t="n">
-        <v>88.51999664306641</v>
+        <v>88.02999877929688</v>
       </c>
       <c r="C170" t="n">
-        <v>88.55000305175781</v>
+        <v>90.37000274658203</v>
       </c>
       <c r="D170" t="n">
-        <v>87.5</v>
+        <v>87.51999664306641</v>
       </c>
       <c r="E170" t="n">
-        <v>88.08999633789062</v>
+        <v>89.30000305175781</v>
       </c>
       <c r="F170" t="n">
-        <v>23463400</v>
+        <v>28613900</v>
       </c>
       <c r="G170" t="n">
         <v>0</v>
@@ -4863,22 +4863,22 @@
     </row>
     <row r="171">
       <c r="A171" s="1" t="n">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="B171" t="n">
-        <v>88.02999877929688</v>
+        <v>89.09999847412109</v>
       </c>
       <c r="C171" t="n">
-        <v>90.37000274658203</v>
+        <v>89.97000122070312</v>
       </c>
       <c r="D171" t="n">
-        <v>87.51999664306641</v>
+        <v>88.16999816894531</v>
       </c>
       <c r="E171" t="n">
-        <v>89.30000305175781</v>
+        <v>88.59999847412109</v>
       </c>
       <c r="F171" t="n">
-        <v>28613900</v>
+        <v>23847200</v>
       </c>
       <c r="G171" t="n">
         <v>0</v>
@@ -4889,22 +4889,22 @@
     </row>
     <row r="172">
       <c r="A172" s="1" t="n">
-        <v>46164</v>
+        <v>46168</v>
       </c>
       <c r="B172" t="n">
-        <v>89.09999847412109</v>
+        <v>88.40000152587891</v>
       </c>
       <c r="C172" t="n">
-        <v>89.97000122070312</v>
+        <v>88.73000335693359</v>
       </c>
       <c r="D172" t="n">
-        <v>88.16999816894531</v>
+        <v>87.25</v>
       </c>
       <c r="E172" t="n">
-        <v>88.59999847412109</v>
+        <v>87.68000030517578</v>
       </c>
       <c r="F172" t="n">
-        <v>23847200</v>
+        <v>24014500</v>
       </c>
       <c r="G172" t="n">
         <v>0</v>
@@ -4915,22 +4915,22 @@
     </row>
     <row r="173">
       <c r="A173" s="1" t="n">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="B173" t="n">
-        <v>88.40000152587891</v>
+        <v>87.05000305175781</v>
       </c>
       <c r="C173" t="n">
-        <v>88.73000335693359</v>
+        <v>88.5</v>
       </c>
       <c r="D173" t="n">
-        <v>87.25</v>
+        <v>86.81999969482422</v>
       </c>
       <c r="E173" t="n">
-        <v>87.68000030517578</v>
+        <v>87.34999847412109</v>
       </c>
       <c r="F173" t="n">
-        <v>24014500</v>
+        <v>22569500</v>
       </c>
       <c r="G173" t="n">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="174">
       <c r="A174" s="1" t="n">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="B174" t="n">
-        <v>87.05000305175781</v>
+        <v>86.90000152587891</v>
       </c>
       <c r="C174" t="n">
-        <v>88.5</v>
+        <v>87.04000091552734</v>
       </c>
       <c r="D174" t="n">
-        <v>86.81999969482422</v>
+        <v>85.58999633789062</v>
       </c>
       <c r="E174" t="n">
-        <v>87.34999847412109</v>
+        <v>86.36000061035156</v>
       </c>
       <c r="F174" t="n">
-        <v>22569500</v>
+        <v>38803800</v>
       </c>
       <c r="G174" t="n">
         <v>0</v>
@@ -4967,22 +4967,22 @@
     </row>
     <row r="175">
       <c r="A175" s="1" t="n">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="B175" t="n">
-        <v>86.90000152587891</v>
+        <v>86.19999694824219</v>
       </c>
       <c r="C175" t="n">
-        <v>87.04000091552734</v>
+        <v>86.66999816894531</v>
       </c>
       <c r="D175" t="n">
-        <v>85.58999633789062</v>
+        <v>85.66000366210938</v>
       </c>
       <c r="E175" t="n">
-        <v>86.36000061035156</v>
+        <v>86.01999664306641</v>
       </c>
       <c r="F175" t="n">
-        <v>38803800</v>
+        <v>39793600</v>
       </c>
       <c r="G175" t="n">
         <v>0</v>
@@ -4993,22 +4993,22 @@
     </row>
     <row r="176">
       <c r="A176" s="1" t="n">
-        <v>46171</v>
+        <v>46174</v>
       </c>
       <c r="B176" t="n">
-        <v>86.19999694824219</v>
+        <v>85.73000335693359</v>
       </c>
       <c r="C176" t="n">
-        <v>86.66999816894531</v>
+        <v>87.23000335693359</v>
       </c>
       <c r="D176" t="n">
-        <v>85.66000366210938</v>
+        <v>85.31999969482422</v>
       </c>
       <c r="E176" t="n">
-        <v>86.01999664306641</v>
+        <v>85.84999847412109</v>
       </c>
       <c r="F176" t="n">
-        <v>39793600</v>
+        <v>32747200</v>
       </c>
       <c r="G176" t="n">
         <v>0</v>
@@ -5019,22 +5019,22 @@
     </row>
     <row r="177">
       <c r="A177" s="1" t="n">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="B177" t="n">
-        <v>85.73000335693359</v>
+        <v>85.61000061035156</v>
       </c>
       <c r="C177" t="n">
-        <v>87.23000335693359</v>
+        <v>85.98000335693359</v>
       </c>
       <c r="D177" t="n">
-        <v>85.31999969482422</v>
+        <v>83.29000091552734</v>
       </c>
       <c r="E177" t="n">
-        <v>85.84999847412109</v>
+        <v>83.33000183105469</v>
       </c>
       <c r="F177" t="n">
-        <v>32747200</v>
+        <v>42947200</v>
       </c>
       <c r="G177" t="n">
         <v>0</v>
@@ -5045,22 +5045,22 @@
     </row>
     <row r="178">
       <c r="A178" s="1" t="n">
-        <v>46175</v>
+        <v>46176</v>
       </c>
       <c r="B178" t="n">
-        <v>85.61000061035156</v>
+        <v>82.91000366210938</v>
       </c>
       <c r="C178" t="n">
-        <v>85.98000335693359</v>
+        <v>83.30999755859375</v>
       </c>
       <c r="D178" t="n">
-        <v>83.29000091552734</v>
+        <v>81.09999847412109</v>
       </c>
       <c r="E178" t="n">
-        <v>83.33000183105469</v>
+        <v>81.51999664306641</v>
       </c>
       <c r="F178" t="n">
-        <v>42947200</v>
+        <v>36714700</v>
       </c>
       <c r="G178" t="n">
         <v>0</v>
@@ -5071,22 +5071,22 @@
     </row>
     <row r="179">
       <c r="A179" s="1" t="n">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="B179" t="n">
-        <v>82.91000366210938</v>
+        <v>83.19000244140625</v>
       </c>
       <c r="C179" t="n">
-        <v>83.30999755859375</v>
+        <v>83.69999694824219</v>
       </c>
       <c r="D179" t="n">
-        <v>81.09999847412109</v>
+        <v>81.37000274658203</v>
       </c>
       <c r="E179" t="n">
-        <v>81.51999664306641</v>
+        <v>81.55999755859375</v>
       </c>
       <c r="F179" t="n">
-        <v>36714700</v>
+        <v>39338800</v>
       </c>
       <c r="G179" t="n">
         <v>0</v>
@@ -5097,22 +5097,22 @@
     </row>
     <row r="180">
       <c r="A180" s="1" t="n">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="B180" t="n">
-        <v>83.19000244140625</v>
+        <v>82.33000183105469</v>
       </c>
       <c r="C180" t="n">
-        <v>83.69999694824219</v>
+        <v>82.75</v>
       </c>
       <c r="D180" t="n">
-        <v>81.37000274658203</v>
+        <v>81</v>
       </c>
       <c r="E180" t="n">
-        <v>81.55999755859375</v>
+        <v>82.18000030517578</v>
       </c>
       <c r="F180" t="n">
-        <v>39338800</v>
+        <v>43474100</v>
       </c>
       <c r="G180" t="n">
         <v>0</v>
@@ -5123,22 +5123,22 @@
     </row>
     <row r="181">
       <c r="A181" s="1" t="n">
-        <v>46178</v>
+        <v>46181</v>
       </c>
       <c r="B181" t="n">
-        <v>82.33000183105469</v>
+        <v>81.66000366210938</v>
       </c>
       <c r="C181" t="n">
-        <v>82.75</v>
+        <v>83.08000183105469</v>
       </c>
       <c r="D181" t="n">
-        <v>81</v>
+        <v>81.33999633789062</v>
       </c>
       <c r="E181" t="n">
-        <v>82.18000030517578</v>
+        <v>82.63999938964844</v>
       </c>
       <c r="F181" t="n">
-        <v>43474100</v>
+        <v>33056700</v>
       </c>
       <c r="G181" t="n">
         <v>0</v>
@@ -5149,22 +5149,22 @@
     </row>
     <row r="182">
       <c r="A182" s="1" t="n">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="B182" t="n">
-        <v>81.66000366210938</v>
+        <v>82.12999725341797</v>
       </c>
       <c r="C182" t="n">
-        <v>83.08000183105469</v>
+        <v>82.33999633789062</v>
       </c>
       <c r="D182" t="n">
         <v>81.33999633789062</v>
       </c>
       <c r="E182" t="n">
-        <v>82.63999938964844</v>
+        <v>81.41000366210938</v>
       </c>
       <c r="F182" t="n">
-        <v>33056700</v>
+        <v>34787200</v>
       </c>
       <c r="G182" t="n">
         <v>0</v>
@@ -5175,22 +5175,22 @@
     </row>
     <row r="183">
       <c r="A183" s="1" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="B183" t="n">
-        <v>82.12999725341797</v>
+        <v>81.70999908447266</v>
       </c>
       <c r="C183" t="n">
-        <v>82.33999633789062</v>
+        <v>82.75</v>
       </c>
       <c r="D183" t="n">
-        <v>81.33999633789062</v>
+        <v>80.98000335693359</v>
       </c>
       <c r="E183" t="n">
-        <v>81.41000366210938</v>
+        <v>82</v>
       </c>
       <c r="F183" t="n">
-        <v>34787200</v>
+        <v>36304600</v>
       </c>
       <c r="G183" t="n">
         <v>0</v>
@@ -5201,22 +5201,22 @@
     </row>
     <row r="184">
       <c r="A184" s="1" t="n">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="B184" t="n">
-        <v>81.70999908447266</v>
+        <v>81.87000274658203</v>
       </c>
       <c r="C184" t="n">
-        <v>82.75</v>
+        <v>82.09999847412109</v>
       </c>
       <c r="D184" t="n">
-        <v>80.98000335693359</v>
+        <v>80.08999633789062</v>
       </c>
       <c r="E184" t="n">
-        <v>82</v>
+        <v>81.26999664306641</v>
       </c>
       <c r="F184" t="n">
-        <v>36304600</v>
+        <v>33417600</v>
       </c>
       <c r="G184" t="n">
         <v>0</v>
@@ -5227,22 +5227,22 @@
     </row>
     <row r="185">
       <c r="A185" s="1" t="n">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="B185" t="n">
-        <v>81.87000274658203</v>
+        <v>81.58000183105469</v>
       </c>
       <c r="C185" t="n">
-        <v>82.09999847412109</v>
+        <v>82</v>
       </c>
       <c r="D185" t="n">
-        <v>80.08999633789062</v>
+        <v>79.27999877929688</v>
       </c>
       <c r="E185" t="n">
-        <v>81.26999664306641</v>
+        <v>80.33999633789062</v>
       </c>
       <c r="F185" t="n">
-        <v>33417600</v>
+        <v>35309700</v>
       </c>
       <c r="G185" t="n">
         <v>0</v>
@@ -5253,22 +5253,22 @@
     </row>
     <row r="186">
       <c r="A186" s="1" t="n">
-        <v>46185</v>
+        <v>46188</v>
       </c>
       <c r="B186" t="n">
-        <v>81.58000183105469</v>
+        <v>80.62000274658203</v>
       </c>
       <c r="C186" t="n">
-        <v>82</v>
+        <v>81.70999908447266</v>
       </c>
       <c r="D186" t="n">
-        <v>79.27999877929688</v>
+        <v>80.45999908447266</v>
       </c>
       <c r="E186" t="n">
-        <v>80.33999633789062</v>
+        <v>81.66999816894531</v>
       </c>
       <c r="F186" t="n">
-        <v>35309700</v>
+        <v>36430800</v>
       </c>
       <c r="G186" t="n">
         <v>0</v>
@@ -5279,22 +5279,22 @@
     </row>
     <row r="187">
       <c r="A187" s="1" t="n">
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="B187" t="n">
-        <v>80.62000274658203</v>
+        <v>81.90000152587891</v>
       </c>
       <c r="C187" t="n">
-        <v>81.70999908447266</v>
+        <v>81.93000030517578</v>
       </c>
       <c r="D187" t="n">
-        <v>80.45999908447266</v>
+        <v>77.70999908447266</v>
       </c>
       <c r="E187" t="n">
-        <v>81.66999816894531</v>
+        <v>78.72000122070312</v>
       </c>
       <c r="F187" t="n">
-        <v>36430800</v>
+        <v>65054000</v>
       </c>
       <c r="G187" t="n">
         <v>0</v>
@@ -5305,22 +5305,22 @@
     </row>
     <row r="188">
       <c r="A188" s="1" t="n">
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="B188" t="n">
-        <v>81.90000152587891</v>
+        <v>78.09999847412109</v>
       </c>
       <c r="C188" t="n">
-        <v>81.93000030517578</v>
+        <v>78.44999694824219</v>
       </c>
       <c r="D188" t="n">
-        <v>77.70999908447266</v>
+        <v>76.76000213623047</v>
       </c>
       <c r="E188" t="n">
-        <v>78.72000122070312</v>
+        <v>76.95999908447266</v>
       </c>
       <c r="F188" t="n">
-        <v>65054000</v>
+        <v>50338800</v>
       </c>
       <c r="G188" t="n">
         <v>0</v>
@@ -5331,22 +5331,22 @@
     </row>
     <row r="189">
       <c r="A189" s="1" t="n">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="B189" t="n">
-        <v>78.09999847412109</v>
+        <v>76.93000030517578</v>
       </c>
       <c r="C189" t="n">
-        <v>78.44999694824219</v>
+        <v>78.23999786376953</v>
       </c>
       <c r="D189" t="n">
-        <v>76.76000213623047</v>
+        <v>76.12000274658203</v>
       </c>
       <c r="E189" t="n">
-        <v>76.95999908447266</v>
+        <v>77.37999725341797</v>
       </c>
       <c r="F189" t="n">
-        <v>50338800</v>
+        <v>91920400</v>
       </c>
       <c r="G189" t="n">
         <v>0</v>
@@ -5357,22 +5357,22 @@
     </row>
     <row r="190">
       <c r="A190" s="1" t="n">
-        <v>46191</v>
+        <v>46195</v>
       </c>
       <c r="B190" t="n">
-        <v>76.93000030517578</v>
+        <v>76.13999938964844</v>
       </c>
       <c r="C190" t="n">
-        <v>78.23999786376953</v>
+        <v>77.08999633789062</v>
       </c>
       <c r="D190" t="n">
-        <v>76.12000274658203</v>
+        <v>71.80999755859375</v>
       </c>
       <c r="E190" t="n">
-        <v>77.37999725341797</v>
+        <v>72.87999725341797</v>
       </c>
       <c r="F190" t="n">
-        <v>91920400</v>
+        <v>82203300</v>
       </c>
       <c r="G190" t="n">
         <v>0</v>
@@ -5383,22 +5383,22 @@
     </row>
     <row r="191">
       <c r="A191" s="1" t="n">
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="B191" t="n">
-        <v>76.13999938964844</v>
+        <v>73.26000213623047</v>
       </c>
       <c r="C191" t="n">
-        <v>77.08999633789062</v>
+        <v>73.95999908447266</v>
       </c>
       <c r="D191" t="n">
-        <v>71.80999755859375</v>
+        <v>72.62999725341797</v>
       </c>
       <c r="E191" t="n">
-        <v>72.87999725341797</v>
+        <v>72.81999969482422</v>
       </c>
       <c r="F191" t="n">
-        <v>82203300</v>
+        <v>50806800</v>
       </c>
       <c r="G191" t="n">
         <v>0</v>
@@ -5409,22 +5409,22 @@
     </row>
     <row r="192">
       <c r="A192" s="1" t="n">
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="B192" t="n">
-        <v>73.26000213623047</v>
+        <v>72.69000244140625</v>
       </c>
       <c r="C192" t="n">
-        <v>73.95999908447266</v>
+        <v>73.44999694824219</v>
       </c>
       <c r="D192" t="n">
-        <v>72.62999725341797</v>
+        <v>71.62999725341797</v>
       </c>
       <c r="E192" t="n">
-        <v>72.81999969482422</v>
+        <v>71.83999633789062</v>
       </c>
       <c r="F192" t="n">
-        <v>50806800</v>
+        <v>48001500</v>
       </c>
       <c r="G192" t="n">
         <v>0</v>
@@ -5435,22 +5435,22 @@
     </row>
     <row r="193">
       <c r="A193" s="1" t="n">
-        <v>46197</v>
+        <v>46198</v>
       </c>
       <c r="B193" t="n">
-        <v>72.69000244140625</v>
+        <v>71.33000183105469</v>
       </c>
       <c r="C193" t="n">
-        <v>73.44999694824219</v>
+        <v>72.94000244140625</v>
       </c>
       <c r="D193" t="n">
-        <v>71.62999725341797</v>
+        <v>70.86000061035156</v>
       </c>
       <c r="E193" t="n">
-        <v>71.83999633789062</v>
+        <v>70.90000152587891</v>
       </c>
       <c r="F193" t="n">
-        <v>48001500</v>
+        <v>44446900</v>
       </c>
       <c r="G193" t="n">
         <v>0</v>
@@ -5461,22 +5461,22 @@
     </row>
     <row r="194">
       <c r="A194" s="1" t="n">
-        <v>46198</v>
+        <v>46199</v>
       </c>
       <c r="B194" t="n">
-        <v>71.33000183105469</v>
+        <v>71.69000244140625</v>
       </c>
       <c r="C194" t="n">
-        <v>72.94000244140625</v>
+        <v>75.19999694824219</v>
       </c>
       <c r="D194" t="n">
-        <v>70.86000061035156</v>
+        <v>71.52999877929688</v>
       </c>
       <c r="E194" t="n">
-        <v>70.90000152587891</v>
+        <v>73.80999755859375</v>
       </c>
       <c r="F194" t="n">
-        <v>44446900</v>
+        <v>74990300</v>
       </c>
       <c r="G194" t="n">
         <v>0</v>
@@ -5487,22 +5487,22 @@
     </row>
     <row r="195">
       <c r="A195" s="1" t="n">
-        <v>46199</v>
+        <v>46202</v>
       </c>
       <c r="B195" t="n">
-        <v>71.69000244140625</v>
+        <v>74.62000274658203</v>
       </c>
       <c r="C195" t="n">
-        <v>75.19999694824219</v>
+        <v>76.06999969482422</v>
       </c>
       <c r="D195" t="n">
-        <v>71.52999877929688</v>
+        <v>73.73000335693359</v>
       </c>
       <c r="E195" t="n">
-        <v>73.80999755859375</v>
+        <v>73.77999877929688</v>
       </c>
       <c r="F195" t="n">
-        <v>74990300</v>
+        <v>42429600</v>
       </c>
       <c r="G195" t="n">
         <v>0</v>
@@ -5513,22 +5513,22 @@
     </row>
     <row r="196">
       <c r="A196" s="1" t="n">
-        <v>46202</v>
+        <v>46203</v>
       </c>
       <c r="B196" t="n">
-        <v>74.62000274658203</v>
+        <v>73.58999633789062</v>
       </c>
       <c r="C196" t="n">
-        <v>76.06999969482422</v>
+        <v>73.75</v>
       </c>
       <c r="D196" t="n">
-        <v>73.73000335693359</v>
+        <v>71</v>
       </c>
       <c r="E196" t="n">
-        <v>73.77999877929688</v>
+        <v>71.40000152587891</v>
       </c>
       <c r="F196" t="n">
-        <v>42429600</v>
+        <v>49240900</v>
       </c>
       <c r="G196" t="n">
         <v>0</v>
@@ -5539,22 +5539,22 @@
     </row>
     <row r="197">
       <c r="A197" s="1" t="n">
-        <v>46203</v>
+        <v>46204</v>
       </c>
       <c r="B197" t="n">
-        <v>73.58999633789062</v>
+        <v>72.58999633789062</v>
       </c>
       <c r="C197" t="n">
-        <v>73.75</v>
+        <v>74.36000061035156</v>
       </c>
       <c r="D197" t="n">
-        <v>71</v>
+        <v>72.33000183105469</v>
       </c>
       <c r="E197" t="n">
-        <v>71.40000152587891</v>
+        <v>74.19000244140625</v>
       </c>
       <c r="F197" t="n">
-        <v>49240900</v>
+        <v>43841800</v>
       </c>
       <c r="G197" t="n">
         <v>0</v>
@@ -5565,22 +5565,22 @@
     </row>
     <row r="198">
       <c r="A198" s="1" t="n">
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="B198" t="n">
-        <v>72.58999633789062</v>
+        <v>75.08999633789062</v>
       </c>
       <c r="C198" t="n">
-        <v>74.36000061035156</v>
+        <v>78.44000244140625</v>
       </c>
       <c r="D198" t="n">
-        <v>72.33000183105469</v>
+        <v>74.91000366210938</v>
       </c>
       <c r="E198" t="n">
-        <v>74.19000244140625</v>
+        <v>77.65000152587891</v>
       </c>
       <c r="F198" t="n">
-        <v>43841800</v>
+        <v>55456500</v>
       </c>
       <c r="G198" t="n">
         <v>0</v>
@@ -5591,22 +5591,22 @@
     </row>
     <row r="199">
       <c r="A199" s="1" t="n">
-        <v>46205</v>
+        <v>46209</v>
       </c>
       <c r="B199" t="n">
-        <v>75.08999633789062</v>
+        <v>77.08000183105469</v>
       </c>
       <c r="C199" t="n">
-        <v>78.44000244140625</v>
+        <v>77.83999633789062</v>
       </c>
       <c r="D199" t="n">
-        <v>74.91000366210938</v>
+        <v>75.70999908447266</v>
       </c>
       <c r="E199" t="n">
-        <v>77.65000152587891</v>
+        <v>76.01999664306641</v>
       </c>
       <c r="F199" t="n">
-        <v>55456500</v>
+        <v>45056600</v>
       </c>
       <c r="G199" t="n">
         <v>0</v>
@@ -5617,22 +5617,22 @@
     </row>
     <row r="200">
       <c r="A200" s="1" t="n">
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="B200" t="n">
-        <v>77.08000183105469</v>
+        <v>77.87999725341797</v>
       </c>
       <c r="C200" t="n">
-        <v>77.83999633789062</v>
+        <v>78.19000244140625</v>
       </c>
       <c r="D200" t="n">
-        <v>75.70999908447266</v>
+        <v>76.09999847412109</v>
       </c>
       <c r="E200" t="n">
-        <v>76.01999664306641</v>
+        <v>76.18000030517578</v>
       </c>
       <c r="F200" t="n">
-        <v>45056600</v>
+        <v>33257300</v>
       </c>
       <c r="G200" t="n">
         <v>0</v>
@@ -5643,22 +5643,22 @@
     </row>
     <row r="201">
       <c r="A201" s="1" t="n">
-        <v>46210</v>
+        <v>46211</v>
       </c>
       <c r="B201" t="n">
-        <v>77.87999725341797</v>
+        <v>76.26999664306641</v>
       </c>
       <c r="C201" t="n">
-        <v>78.19000244140625</v>
+        <v>76.63999938964844</v>
       </c>
       <c r="D201" t="n">
-        <v>76.09999847412109</v>
+        <v>74.88999938964844</v>
       </c>
       <c r="E201" t="n">
-        <v>76.18000030517578</v>
+        <v>75.58999633789062</v>
       </c>
       <c r="F201" t="n">
-        <v>33257300</v>
+        <v>34373500</v>
       </c>
       <c r="G201" t="n">
         <v>0</v>
@@ -5669,22 +5669,22 @@
     </row>
     <row r="202">
       <c r="A202" s="1" t="n">
-        <v>46211</v>
+        <v>46212</v>
       </c>
       <c r="B202" t="n">
-        <v>76.26999664306641</v>
+        <v>74.30000305175781</v>
       </c>
       <c r="C202" t="n">
-        <v>76.63999938964844</v>
+        <v>75.55000305175781</v>
       </c>
       <c r="D202" t="n">
-        <v>74.88999938964844</v>
+        <v>74.01999664306641</v>
       </c>
       <c r="E202" t="n">
-        <v>75.58999633789062</v>
+        <v>75.47000122070312</v>
       </c>
       <c r="F202" t="n">
-        <v>34373500</v>
+        <v>36305700</v>
       </c>
       <c r="G202" t="n">
         <v>0</v>
@@ -5695,22 +5695,22 @@
     </row>
     <row r="203">
       <c r="A203" s="1" t="n">
-        <v>46212</v>
+        <v>46213</v>
       </c>
       <c r="B203" t="n">
-        <v>74.30000305175781</v>
+        <v>75.44000244140625</v>
       </c>
       <c r="C203" t="n">
-        <v>75.55000305175781</v>
+        <v>75.69999694824219</v>
       </c>
       <c r="D203" t="n">
-        <v>74.01999664306641</v>
+        <v>72.51000213623047</v>
       </c>
       <c r="E203" t="n">
-        <v>75.47000122070312</v>
+        <v>73.37000274658203</v>
       </c>
       <c r="F203" t="n">
-        <v>36305700</v>
+        <v>46713900</v>
       </c>
       <c r="G203" t="n">
         <v>0</v>
@@ -5721,22 +5721,22 @@
     </row>
     <row r="204">
       <c r="A204" s="1" t="n">
-        <v>46213</v>
+        <v>46216</v>
       </c>
       <c r="B204" t="n">
-        <v>75.44000244140625</v>
+        <v>73.90000152587891</v>
       </c>
       <c r="C204" t="n">
-        <v>75.69999694824219</v>
+        <v>75.44999694824219</v>
       </c>
       <c r="D204" t="n">
-        <v>72.51000213623047</v>
+        <v>73.70999908447266</v>
       </c>
       <c r="E204" t="n">
-        <v>73.37000274658203</v>
+        <v>73.83000183105469</v>
       </c>
       <c r="F204" t="n">
-        <v>46713900</v>
+        <v>35101800</v>
       </c>
       <c r="G204" t="n">
         <v>0</v>
@@ -5747,22 +5747,22 @@
     </row>
     <row r="205">
       <c r="A205" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="B205" t="n">
-        <v>73.90000152587891</v>
+        <v>72.63999938964844</v>
       </c>
       <c r="C205" t="n">
-        <v>75.44999694824219</v>
+        <v>74.01000213623047</v>
       </c>
       <c r="D205" t="n">
-        <v>73.70999908447266</v>
+        <v>72.27999877929688</v>
       </c>
       <c r="E205" t="n">
-        <v>73.83000183105469</v>
+        <v>73.52999877929688</v>
       </c>
       <c r="F205" t="n">
-        <v>35101800</v>
+        <v>33312100</v>
       </c>
       <c r="G205" t="n">
         <v>0</v>
@@ -5773,22 +5773,22 @@
     </row>
     <row r="206">
       <c r="A206" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="B206" t="n">
-        <v>72.63999938964844</v>
+        <v>73.79000091552734</v>
       </c>
       <c r="C206" t="n">
-        <v>74.01000213623047</v>
+        <v>75.05999755859375</v>
       </c>
       <c r="D206" t="n">
-        <v>72.27999877929688</v>
+        <v>73.12999725341797</v>
       </c>
       <c r="E206" t="n">
-        <v>73.52999877929688</v>
+        <v>73.68000030517578</v>
       </c>
       <c r="F206" t="n">
-        <v>33312100</v>
+        <v>32854300</v>
       </c>
       <c r="G206" t="n">
         <v>0</v>
@@ -5799,22 +5799,22 @@
     </row>
     <row r="207">
       <c r="A207" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="B207" t="n">
-        <v>73.79000091552734</v>
+        <v>73.94999694824219</v>
       </c>
       <c r="C207" t="n">
-        <v>75.05999755859375</v>
+        <v>74.68000030517578</v>
       </c>
       <c r="D207" t="n">
-        <v>73.12999725341797</v>
+        <v>72.94000244140625</v>
       </c>
       <c r="E207" t="n">
-        <v>73.68000030517578</v>
+        <v>74.34999847412109</v>
       </c>
       <c r="F207" t="n">
-        <v>32854300</v>
+        <v>77505200</v>
       </c>
       <c r="G207" t="n">
         <v>0</v>
@@ -5825,22 +5825,22 @@
     </row>
     <row r="208">
       <c r="A208" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="B208" t="n">
-        <v>73.94999694824219</v>
+        <v>65.48000335693359</v>
       </c>
       <c r="C208" t="n">
-        <v>74.68000030517578</v>
+        <v>69.48999786376953</v>
       </c>
       <c r="D208" t="n">
-        <v>72.94000244140625</v>
+        <v>65.08000183105469</v>
       </c>
       <c r="E208" t="n">
-        <v>74.34999847412109</v>
+        <v>68.94999694824219</v>
       </c>
       <c r="F208" t="n">
-        <v>77505200</v>
+        <v>142029200</v>
       </c>
       <c r="G208" t="n">
         <v>0</v>
@@ -5851,22 +5851,22 @@
     </row>
     <row r="209">
       <c r="A209" s="1" t="n">
-        <v>46220</v>
+        <v>46223</v>
       </c>
       <c r="B209" t="n">
-        <v>65.48000335693359</v>
+        <v>68.31999969482422</v>
       </c>
       <c r="C209" t="n">
-        <v>69.48999786376953</v>
+        <v>68.37999725341797</v>
       </c>
       <c r="D209" t="n">
-        <v>65.08000183105469</v>
+        <v>66.69000244140625</v>
       </c>
       <c r="E209" t="n">
-        <v>68.94999694824219</v>
+        <v>67.59999847412109</v>
       </c>
       <c r="F209" t="n">
-        <v>142029200</v>
+        <v>60669100</v>
       </c>
       <c r="G209" t="n">
         <v>0</v>
@@ -5877,22 +5877,22 @@
     </row>
     <row r="210">
       <c r="A210" s="1" t="n">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="B210" t="n">
-        <v>68.31999969482422</v>
+        <v>67.41999816894531</v>
       </c>
       <c r="C210" t="n">
-        <v>68.37999725341797</v>
+        <v>68.75</v>
       </c>
       <c r="D210" t="n">
-        <v>66.69000244140625</v>
+        <v>66.73000335693359</v>
       </c>
       <c r="E210" t="n">
-        <v>67.59999847412109</v>
+        <v>68.66999816894531</v>
       </c>
       <c r="F210" t="n">
-        <v>60669100</v>
+        <v>56565800</v>
       </c>
       <c r="G210" t="n">
         <v>0</v>
@@ -5903,22 +5903,22 @@
     </row>
     <row r="211">
       <c r="A211" s="1" t="n">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="B211" t="n">
-        <v>67.41999816894531</v>
+        <v>69.37000274658203</v>
       </c>
       <c r="C211" t="n">
-        <v>68.75</v>
+        <v>70.56999969482422</v>
       </c>
       <c r="D211" t="n">
-        <v>66.73000335693359</v>
+        <v>68.34999847412109</v>
       </c>
       <c r="E211" t="n">
-        <v>68.66999816894531</v>
+        <v>68.52999877929688</v>
       </c>
       <c r="F211" t="n">
-        <v>56565800</v>
+        <v>44947300</v>
       </c>
       <c r="G211" t="n">
         <v>0</v>
@@ -5929,22 +5929,22 @@
     </row>
     <row r="212">
       <c r="A212" s="1" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="B212" t="n">
-        <v>69.37000274658203</v>
+        <v>68.56999969482422</v>
       </c>
       <c r="C212" t="n">
-        <v>70.56999969482422</v>
+        <v>69.36000061035156</v>
       </c>
       <c r="D212" t="n">
-        <v>68.34999847412109</v>
+        <v>67.66999816894531</v>
       </c>
       <c r="E212" t="n">
-        <v>68.52999877929688</v>
+        <v>68.88999938964844</v>
       </c>
       <c r="F212" t="n">
-        <v>44947300</v>
+        <v>45029100</v>
       </c>
       <c r="G212" t="n">
         <v>0</v>
@@ -5955,22 +5955,22 @@
     </row>
     <row r="213">
       <c r="A213" s="1" t="n">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="B213" t="n">
-        <v>68.56999969482422</v>
+        <v>69.29000091552734</v>
       </c>
       <c r="C213" t="n">
-        <v>69.36000061035156</v>
+        <v>70.68000030517578</v>
       </c>
       <c r="D213" t="n">
-        <v>67.66999816894531</v>
+        <v>67.97000122070312</v>
       </c>
       <c r="E213" t="n">
-        <v>68.88999938964844</v>
+        <v>70.08999633789062</v>
       </c>
       <c r="F213" t="n">
-        <v>45029100</v>
+        <v>37593500</v>
       </c>
       <c r="G213" t="n">
         <v>0</v>
@@ -5981,22 +5981,22 @@
     </row>
     <row r="214">
       <c r="A214" s="1" t="n">
-        <v>46227</v>
+        <v>46230</v>
       </c>
       <c r="B214" t="n">
-        <v>69.29000091552734</v>
+        <v>70.58999633789062</v>
       </c>
       <c r="C214" t="n">
-        <v>70.68000030517578</v>
+        <v>71.65000152587891</v>
       </c>
       <c r="D214" t="n">
-        <v>67.97000122070312</v>
+        <v>69.86000061035156</v>
       </c>
       <c r="E214" t="n">
-        <v>70.08999633789062</v>
+        <v>70.40000152587891</v>
       </c>
       <c r="F214" t="n">
-        <v>37593500</v>
+        <v>39090800</v>
       </c>
       <c r="G214" t="n">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="215">
       <c r="A215" s="1" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="B215" t="n">
-        <v>70.58999633789062</v>
+        <v>72.06999969482422</v>
       </c>
       <c r="C215" t="n">
-        <v>71.65000152587891</v>
+        <v>73.76000213623047</v>
       </c>
       <c r="D215" t="n">
-        <v>69.86000061035156</v>
+        <v>71.23000335693359</v>
       </c>
       <c r="E215" t="n">
-        <v>70.40000152587891</v>
+        <v>72.38999938964844</v>
       </c>
       <c r="F215" t="n">
-        <v>39090800</v>
+        <v>47160200</v>
       </c>
       <c r="G215" t="n">
         <v>0</v>
@@ -6033,22 +6033,22 @@
     </row>
     <row r="216">
       <c r="A216" s="1" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="B216" t="n">
-        <v>72.06999969482422</v>
+        <v>72.19000244140625</v>
       </c>
       <c r="C216" t="n">
-        <v>73.76000213623047</v>
+        <v>73.73999786376953</v>
       </c>
       <c r="D216" t="n">
-        <v>71.23000335693359</v>
+        <v>71.75</v>
       </c>
       <c r="E216" t="n">
-        <v>72.38999938964844</v>
+        <v>73.62999725341797</v>
       </c>
       <c r="F216" t="n">
-        <v>47160200</v>
+        <v>43737600</v>
       </c>
       <c r="G216" t="n">
         <v>0</v>
@@ -6059,22 +6059,22 @@
     </row>
     <row r="217">
       <c r="A217" s="1" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="B217" t="n">
-        <v>72.19000244140625</v>
+        <v>71.48000335693359</v>
       </c>
       <c r="C217" t="n">
-        <v>73.73999786376953</v>
+        <v>73.31999969482422</v>
       </c>
       <c r="D217" t="n">
-        <v>71.75</v>
+        <v>70.55000305175781</v>
       </c>
       <c r="E217" t="n">
-        <v>73.62999725341797</v>
+        <v>73.16999816894531</v>
       </c>
       <c r="F217" t="n">
-        <v>43737600</v>
+        <v>54261000</v>
       </c>
       <c r="G217" t="n">
         <v>0</v>
@@ -6085,22 +6085,22 @@
     </row>
     <row r="218">
       <c r="A218" s="1" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="B218" t="n">
-        <v>71.48000335693359</v>
+        <v>71.97000122070312</v>
       </c>
       <c r="C218" t="n">
-        <v>73.31999969482422</v>
+        <v>72.75</v>
       </c>
       <c r="D218" t="n">
-        <v>70.55000305175781</v>
+        <v>71.11000061035156</v>
       </c>
       <c r="E218" t="n">
-        <v>73.16999816894531</v>
+        <v>71.70999908447266</v>
       </c>
       <c r="F218" t="n">
-        <v>54261000</v>
+        <v>35847500</v>
       </c>
       <c r="G218" t="n">
         <v>0</v>
@@ -6111,22 +6111,22 @@
     </row>
     <row r="219">
       <c r="A219" s="1" t="n">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="B219" t="n">
-        <v>71.97000122070312</v>
+        <v>72.76999664306641</v>
       </c>
       <c r="C219" t="n">
-        <v>72.75</v>
+        <v>73.94999694824219</v>
       </c>
       <c r="D219" t="n">
-        <v>71.11000061035156</v>
+        <v>72.18000030517578</v>
       </c>
       <c r="E219" t="n">
-        <v>71.70999908447266</v>
+        <v>73.33000183105469</v>
       </c>
       <c r="F219" t="n">
-        <v>35847500</v>
+        <v>33922300</v>
       </c>
       <c r="G219" t="n">
         <v>0</v>
@@ -6137,22 +6137,22 @@
     </row>
     <row r="220">
       <c r="A220" s="1" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="B220" t="n">
-        <v>72.76999664306641</v>
+        <v>72.51000213623047</v>
       </c>
       <c r="C220" t="n">
-        <v>73.94999694824219</v>
+        <v>73.75</v>
       </c>
       <c r="D220" t="n">
-        <v>72.18000030517578</v>
+        <v>72.30000305175781</v>
       </c>
       <c r="E220" t="n">
-        <v>73.33000183105469</v>
+        <v>73.56999969482422</v>
       </c>
       <c r="F220" t="n">
-        <v>33922300</v>
+        <v>42877900</v>
       </c>
       <c r="G220" t="n">
         <v>0</v>
@@ -6163,22 +6163,22 @@
     </row>
     <row r="221">
       <c r="A221" s="1" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="B221" t="n">
-        <v>72.51000213623047</v>
+        <v>75.11000061035156</v>
       </c>
       <c r="C221" t="n">
-        <v>73.75</v>
+        <v>75.30000305175781</v>
       </c>
       <c r="D221" t="n">
-        <v>72.30000305175781</v>
+        <v>73.16000366210938</v>
       </c>
       <c r="E221" t="n">
-        <v>73.56999969482422</v>
+        <v>74.19999694824219</v>
       </c>
       <c r="F221" t="n">
-        <v>42877900</v>
+        <v>28969400</v>
       </c>
       <c r="G221" t="n">
         <v>0</v>
@@ -6189,22 +6189,22 @@
     </row>
     <row r="222">
       <c r="A222" s="1" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="B222" t="n">
-        <v>75.11000061035156</v>
+        <v>75.13999938964844</v>
       </c>
       <c r="C222" t="n">
-        <v>75.30000305175781</v>
+        <v>75.20999908447266</v>
       </c>
       <c r="D222" t="n">
-        <v>73.16000366210938</v>
+        <v>73.09999847412109</v>
       </c>
       <c r="E222" t="n">
-        <v>74.19999694824219</v>
+        <v>73.69000244140625</v>
       </c>
       <c r="F222" t="n">
-        <v>28969400</v>
+        <v>28892700</v>
       </c>
       <c r="G222" t="n">
         <v>0</v>
@@ -6215,22 +6215,22 @@
     </row>
     <row r="223">
       <c r="A223" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="B223" t="n">
-        <v>75.13999938964844</v>
+        <v>73.12000274658203</v>
       </c>
       <c r="C223" t="n">
-        <v>75.20999908447266</v>
+        <v>74.5</v>
       </c>
       <c r="D223" t="n">
-        <v>73.09999847412109</v>
+        <v>73.08000183105469</v>
       </c>
       <c r="E223" t="n">
-        <v>73.69000244140625</v>
+        <v>74.13999938964844</v>
       </c>
       <c r="F223" t="n">
-        <v>28892700</v>
+        <v>24819000</v>
       </c>
       <c r="G223" t="n">
         <v>0</v>
@@ -6241,22 +6241,22 @@
     </row>
     <row r="224">
       <c r="A224" s="1" t="n">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="B224" t="n">
-        <v>73.12000274658203</v>
+        <v>73.80000305175781</v>
       </c>
       <c r="C224" t="n">
-        <v>74.5</v>
+        <v>76.31999969482422</v>
       </c>
       <c r="D224" t="n">
-        <v>73.08000183105469</v>
+        <v>73.56999969482422</v>
       </c>
       <c r="E224" t="n">
-        <v>74.13999938964844</v>
+        <v>76.29000091552734</v>
       </c>
       <c r="F224" t="n">
-        <v>24819000</v>
+        <v>26959900</v>
       </c>
       <c r="G224" t="n">
         <v>0</v>
@@ -6267,22 +6267,22 @@
     </row>
     <row r="225">
       <c r="A225" s="1" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="B225" t="n">
-        <v>73.80000305175781</v>
+        <v>76.19999694824219</v>
       </c>
       <c r="C225" t="n">
-        <v>76.31999969482422</v>
+        <v>76.90000152587891</v>
       </c>
       <c r="D225" t="n">
-        <v>73.56999969482422</v>
+        <v>74.48000335693359</v>
       </c>
       <c r="E225" t="n">
-        <v>76.29000091552734</v>
+        <v>74.79000091552734</v>
       </c>
       <c r="F225" t="n">
-        <v>26959900</v>
+        <v>27840500</v>
       </c>
       <c r="G225" t="n">
         <v>0</v>
@@ -6293,22 +6293,22 @@
     </row>
     <row r="226">
       <c r="A226" s="1" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="B226" t="n">
-        <v>76.19999694824219</v>
+        <v>74.34999847412109</v>
       </c>
       <c r="C226" t="n">
-        <v>76.90000152587891</v>
+        <v>74.66999816894531</v>
       </c>
       <c r="D226" t="n">
-        <v>74.48000335693359</v>
+        <v>73.56999969482422</v>
       </c>
       <c r="E226" t="n">
-        <v>74.79000091552734</v>
+        <v>74.20999908447266</v>
       </c>
       <c r="F226" t="n">
-        <v>27840500</v>
+        <v>20773100</v>
       </c>
       <c r="G226" t="n">
         <v>0</v>
@@ -6319,22 +6319,22 @@
     </row>
     <row r="227">
       <c r="A227" s="1" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="B227" t="n">
-        <v>74.34999847412109</v>
+        <v>76.01000213623047</v>
       </c>
       <c r="C227" t="n">
-        <v>74.66999816894531</v>
+        <v>78.40000152587891</v>
       </c>
       <c r="D227" t="n">
-        <v>73.56999969482422</v>
+        <v>75.44000244140625</v>
       </c>
       <c r="E227" t="n">
-        <v>74.20999908447266</v>
+        <v>78.23999786376953</v>
       </c>
       <c r="F227" t="n">
-        <v>20773100</v>
+        <v>41452900</v>
       </c>
       <c r="G227" t="n">
         <v>0</v>
@@ -6345,22 +6345,22 @@
     </row>
     <row r="228">
       <c r="A228" s="1" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="B228" t="n">
-        <v>76.01000213623047</v>
+        <v>78.48000335693359</v>
       </c>
       <c r="C228" t="n">
-        <v>78.40000152587891</v>
+        <v>78.73000335693359</v>
       </c>
       <c r="D228" t="n">
-        <v>75.44000244140625</v>
+        <v>77.76000213623047</v>
       </c>
       <c r="E228" t="n">
-        <v>78.23999786376953</v>
+        <v>78.16000366210938</v>
       </c>
       <c r="F228" t="n">
-        <v>41452900</v>
+        <v>26751000</v>
       </c>
       <c r="G228" t="n">
         <v>0</v>
@@ -6371,22 +6371,22 @@
     </row>
     <row r="229">
       <c r="A229" s="1" t="n">
-        <v>46248</v>
+        <v>46251</v>
       </c>
       <c r="B229" t="n">
-        <v>78.48000335693359</v>
+        <v>77.80000305175781</v>
       </c>
       <c r="C229" t="n">
-        <v>78.73000335693359</v>
+        <v>78.52999877929688</v>
       </c>
       <c r="D229" t="n">
-        <v>77.76000213623047</v>
+        <v>75.47000122070312</v>
       </c>
       <c r="E229" t="n">
-        <v>78.16000366210938</v>
+        <v>76.01999664306641</v>
       </c>
       <c r="F229" t="n">
-        <v>26751000</v>
+        <v>30753000</v>
       </c>
       <c r="G229" t="n">
         <v>0</v>
@@ -6397,22 +6397,22 @@
     </row>
     <row r="230">
       <c r="A230" s="1" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="B230" t="n">
-        <v>77.80000305175781</v>
+        <v>77.43000030517578</v>
       </c>
       <c r="C230" t="n">
-        <v>78.52999877929688</v>
+        <v>79.09999847412109</v>
       </c>
       <c r="D230" t="n">
-        <v>75.47000122070312</v>
+        <v>76.33999633789062</v>
       </c>
       <c r="E230" t="n">
-        <v>76.01999664306641</v>
+        <v>77.76999664306641</v>
       </c>
       <c r="F230" t="n">
-        <v>30753000</v>
+        <v>36151300</v>
       </c>
       <c r="G230" t="n">
         <v>0</v>
@@ -6423,22 +6423,22 @@
     </row>
     <row r="231">
       <c r="A231" s="1" t="n">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="B231" t="n">
-        <v>77.43000030517578</v>
+        <v>78.25</v>
       </c>
       <c r="C231" t="n">
-        <v>79.09999847412109</v>
+        <v>81.16000366210938</v>
       </c>
       <c r="D231" t="n">
-        <v>76.33999633789062</v>
+        <v>78.09999847412109</v>
       </c>
       <c r="E231" t="n">
-        <v>77.76999664306641</v>
+        <v>80.22000122070312</v>
       </c>
       <c r="F231" t="n">
-        <v>36151300</v>
+        <v>31461800</v>
       </c>
       <c r="G231" t="n">
         <v>0</v>
@@ -6449,22 +6449,22 @@
     </row>
     <row r="232">
       <c r="A232" s="1" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="B232" t="n">
-        <v>78.25</v>
+        <v>80.13999938964844</v>
       </c>
       <c r="C232" t="n">
-        <v>81.16000366210938</v>
+        <v>81.08000183105469</v>
       </c>
       <c r="D232" t="n">
-        <v>78.09999847412109</v>
+        <v>79.58999633789062</v>
       </c>
       <c r="E232" t="n">
-        <v>80.22000122070312</v>
+        <v>80.13999938964844</v>
       </c>
       <c r="F232" t="n">
-        <v>31461800</v>
+        <v>27118400</v>
       </c>
       <c r="G232" t="n">
         <v>0</v>
@@ -6475,22 +6475,22 @@
     </row>
     <row r="233">
       <c r="A233" s="1" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="B233" t="n">
-        <v>80.13999938964844</v>
+        <v>80.29000091552734</v>
       </c>
       <c r="C233" t="n">
-        <v>81.08000183105469</v>
+        <v>80.48999786376953</v>
       </c>
       <c r="D233" t="n">
+        <v>79.16999816894531</v>
+      </c>
+      <c r="E233" t="n">
         <v>79.58999633789062</v>
       </c>
-      <c r="E233" t="n">
-        <v>80.13999938964844</v>
-      </c>
       <c r="F233" t="n">
-        <v>27118400</v>
+        <v>23773800</v>
       </c>
       <c r="G233" t="n">
         <v>0</v>
@@ -6501,22 +6501,22 @@
     </row>
     <row r="234">
       <c r="A234" s="1" t="n">
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="B234" t="n">
-        <v>80.29000091552734</v>
+        <v>79.94000244140625</v>
       </c>
       <c r="C234" t="n">
-        <v>80.48999786376953</v>
+        <v>80.62000274658203</v>
       </c>
       <c r="D234" t="n">
-        <v>79.16999816894531</v>
+        <v>79.01999664306641</v>
       </c>
       <c r="E234" t="n">
-        <v>79.58999633789062</v>
+        <v>80.01000213623047</v>
       </c>
       <c r="F234" t="n">
-        <v>23773800</v>
+        <v>21085300</v>
       </c>
       <c r="G234" t="n">
         <v>0</v>
@@ -6527,22 +6527,22 @@
     </row>
     <row r="235">
       <c r="A235" s="1" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="B235" t="n">
-        <v>79.94000244140625</v>
+        <v>79.65000152587891</v>
       </c>
       <c r="C235" t="n">
-        <v>80.62000274658203</v>
+        <v>82.45999908447266</v>
       </c>
       <c r="D235" t="n">
-        <v>79.01999664306641</v>
+        <v>79.40000152587891</v>
       </c>
       <c r="E235" t="n">
-        <v>80.01000213623047</v>
+        <v>82.23000335693359</v>
       </c>
       <c r="F235" t="n">
-        <v>21085300</v>
+        <v>29462000</v>
       </c>
       <c r="G235" t="n">
         <v>0</v>
@@ -6553,22 +6553,22 @@
     </row>
     <row r="236">
       <c r="A236" s="1" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="B236" t="n">
-        <v>79.65000152587891</v>
+        <v>82.05000305175781</v>
       </c>
       <c r="C236" t="n">
-        <v>82.45999908447266</v>
+        <v>82.41999816894531</v>
       </c>
       <c r="D236" t="n">
-        <v>79.40000152587891</v>
+        <v>81.30000305175781</v>
       </c>
       <c r="E236" t="n">
-        <v>82.23000335693359</v>
+        <v>81.45999908447266</v>
       </c>
       <c r="F236" t="n">
-        <v>29462000</v>
+        <v>22874900</v>
       </c>
       <c r="G236" t="n">
         <v>0</v>
@@ -6579,22 +6579,22 @@
     </row>
     <row r="237">
       <c r="A237" s="1" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="B237" t="n">
-        <v>82.05000305175781</v>
+        <v>81.06999969482422</v>
       </c>
       <c r="C237" t="n">
-        <v>82.41999816894531</v>
+        <v>81.15000152587891</v>
       </c>
       <c r="D237" t="n">
-        <v>81.30000305175781</v>
+        <v>79.27999877929688</v>
       </c>
       <c r="E237" t="n">
-        <v>81.45999908447266</v>
+        <v>79.83999633789062</v>
       </c>
       <c r="F237" t="n">
-        <v>22874900</v>
+        <v>27174400</v>
       </c>
       <c r="G237" t="n">
         <v>0</v>
@@ -6605,22 +6605,22 @@
     </row>
     <row r="238">
       <c r="A238" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="B238" t="n">
-        <v>81.06999969482422</v>
+        <v>80.36000061035156</v>
       </c>
       <c r="C238" t="n">
-        <v>81.15000152587891</v>
+        <v>82.34999847412109</v>
       </c>
       <c r="D238" t="n">
-        <v>79.27999877929688</v>
+        <v>79.94999694824219</v>
       </c>
       <c r="E238" t="n">
-        <v>79.83999633789062</v>
+        <v>81.72000122070312</v>
       </c>
       <c r="F238" t="n">
-        <v>27174400</v>
+        <v>29092700</v>
       </c>
       <c r="G238" t="n">
         <v>0</v>
@@ -6631,22 +6631,22 @@
     </row>
     <row r="239">
       <c r="A239" s="1" t="n">
-        <v>46262</v>
+        <v>46265</v>
       </c>
       <c r="B239" t="n">
-        <v>80.36000061035156</v>
+        <v>81</v>
       </c>
       <c r="C239" t="n">
-        <v>82.34999847412109</v>
+        <v>81.73000335693359</v>
       </c>
       <c r="D239" t="n">
-        <v>79.94999694824219</v>
+        <v>80.65000152587891</v>
       </c>
       <c r="E239" t="n">
-        <v>81.72000122070312</v>
+        <v>81.05000305175781</v>
       </c>
       <c r="F239" t="n">
-        <v>29092700</v>
+        <v>30740800</v>
       </c>
       <c r="G239" t="n">
         <v>0</v>
@@ -6657,22 +6657,22 @@
     </row>
     <row r="240">
       <c r="A240" s="1" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="B240" t="n">
-        <v>81</v>
+        <v>80.16999816894531</v>
       </c>
       <c r="C240" t="n">
-        <v>81.73000335693359</v>
+        <v>82.12999725341797</v>
       </c>
       <c r="D240" t="n">
-        <v>80.65000152587891</v>
+        <v>79.59999847412109</v>
       </c>
       <c r="E240" t="n">
-        <v>81.05000305175781</v>
+        <v>80.80999755859375</v>
       </c>
       <c r="F240" t="n">
-        <v>30740800</v>
+        <v>21164900</v>
       </c>
       <c r="G240" t="n">
         <v>0</v>
@@ -6683,22 +6683,22 @@
     </row>
     <row r="241">
       <c r="A241" s="1" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="B241" t="n">
-        <v>80.16999816894531</v>
+        <v>80.55000305175781</v>
       </c>
       <c r="C241" t="n">
-        <v>82.12999725341797</v>
+        <v>83.12000274658203</v>
       </c>
       <c r="D241" t="n">
-        <v>79.59999847412109</v>
+        <v>80.30000305175781</v>
       </c>
       <c r="E241" t="n">
-        <v>80.80999755859375</v>
+        <v>82.73000335693359</v>
       </c>
       <c r="F241" t="n">
-        <v>21164900</v>
+        <v>22077800</v>
       </c>
       <c r="G241" t="n">
         <v>0</v>
@@ -6709,22 +6709,22 @@
     </row>
     <row r="242">
       <c r="A242" s="1" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="B242" t="n">
-        <v>80.55000305175781</v>
+        <v>83.18000030517578</v>
       </c>
       <c r="C242" t="n">
-        <v>83.12000274658203</v>
+        <v>83.59999847412109</v>
       </c>
       <c r="D242" t="n">
-        <v>80.30000305175781</v>
+        <v>81.62999725341797</v>
       </c>
       <c r="E242" t="n">
-        <v>82.73000335693359</v>
+        <v>82.66999816894531</v>
       </c>
       <c r="F242" t="n">
-        <v>22077800</v>
+        <v>24006400</v>
       </c>
       <c r="G242" t="n">
         <v>0</v>
@@ -6735,22 +6735,22 @@
     </row>
     <row r="243">
       <c r="A243" s="1" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B243" t="n">
-        <v>83.18000030517578</v>
+        <v>82.16999816894531</v>
       </c>
       <c r="C243" t="n">
-        <v>83.59999847412109</v>
+        <v>82.69000244140625</v>
       </c>
       <c r="D243" t="n">
-        <v>81.62999725341797</v>
+        <v>78.23000335693359</v>
       </c>
       <c r="E243" t="n">
-        <v>82.66999816894531</v>
+        <v>78.25</v>
       </c>
       <c r="F243" t="n">
-        <v>24006400</v>
+        <v>40190000</v>
       </c>
       <c r="G243" t="n">
         <v>0</v>
@@ -6761,22 +6761,22 @@
     </row>
     <row r="244">
       <c r="A244" s="1" t="n">
-        <v>46269</v>
+        <v>46273</v>
       </c>
       <c r="B244" t="n">
-        <v>82.16999816894531</v>
+        <v>77.55000305175781</v>
       </c>
       <c r="C244" t="n">
-        <v>82.69000244140625</v>
+        <v>77.73000335693359</v>
       </c>
       <c r="D244" t="n">
-        <v>78.23000335693359</v>
+        <v>75.91999816894531</v>
       </c>
       <c r="E244" t="n">
-        <v>78.25</v>
+        <v>76.76999664306641</v>
       </c>
       <c r="F244" t="n">
-        <v>40190000</v>
+        <v>33865500</v>
       </c>
       <c r="G244" t="n">
         <v>0</v>
@@ -6787,22 +6787,22 @@
     </row>
     <row r="245">
       <c r="A245" s="1" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B245" t="n">
-        <v>77.55000305175781</v>
+        <v>76.33999633789062</v>
       </c>
       <c r="C245" t="n">
-        <v>77.73000335693359</v>
+        <v>76.72000122070312</v>
       </c>
       <c r="D245" t="n">
-        <v>75.91999816894531</v>
+        <v>75.87000274658203</v>
       </c>
       <c r="E245" t="n">
-        <v>76.76999664306641</v>
+        <v>76.02999877929688</v>
       </c>
       <c r="F245" t="n">
-        <v>33865500</v>
+        <v>22779600</v>
       </c>
       <c r="G245" t="n">
         <v>0</v>
@@ -6813,22 +6813,22 @@
     </row>
     <row r="246">
       <c r="A246" s="1" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="B246" t="n">
-        <v>76.33999633789062</v>
+        <v>75.33000183105469</v>
       </c>
       <c r="C246" t="n">
-        <v>76.72000122070312</v>
+        <v>76.30000305175781</v>
       </c>
       <c r="D246" t="n">
-        <v>75.87000274658203</v>
+        <v>75.02999877929688</v>
       </c>
       <c r="E246" t="n">
-        <v>76.02999877929688</v>
+        <v>76.01000213623047</v>
       </c>
       <c r="F246" t="n">
-        <v>22779600</v>
+        <v>20049000</v>
       </c>
       <c r="G246" t="n">
         <v>0</v>
@@ -6839,22 +6839,22 @@
     </row>
     <row r="247">
       <c r="A247" s="1" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="B247" t="n">
-        <v>75.33000183105469</v>
+        <v>76.63999938964844</v>
       </c>
       <c r="C247" t="n">
-        <v>76.30000305175781</v>
+        <v>77.56999969482422</v>
       </c>
       <c r="D247" t="n">
-        <v>75.02999877929688</v>
+        <v>76.15000152587891</v>
       </c>
       <c r="E247" t="n">
-        <v>76.01000213623047</v>
+        <v>77.40000152587891</v>
       </c>
       <c r="F247" t="n">
-        <v>20049000</v>
+        <v>22237800</v>
       </c>
       <c r="G247" t="n">
         <v>0</v>
@@ -6865,22 +6865,22 @@
     </row>
     <row r="248">
       <c r="A248" s="1" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="B248" t="n">
-        <v>76.63999938964844</v>
+        <v>78.97000122070312</v>
       </c>
       <c r="C248" t="n">
-        <v>77.56999969482422</v>
+        <v>81.01999664306641</v>
       </c>
       <c r="D248" t="n">
-        <v>76.15000152587891</v>
+        <v>78.48999786376953</v>
       </c>
       <c r="E248" t="n">
-        <v>77.40000152587891</v>
+        <v>80.31999969482422</v>
       </c>
       <c r="F248" t="n">
-        <v>22237800</v>
+        <v>30945100</v>
       </c>
       <c r="G248" t="n">
         <v>0</v>
@@ -6891,22 +6891,22 @@
     </row>
     <row r="249">
       <c r="A249" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="B249" t="n">
-        <v>78.97000122070312</v>
+        <v>79.37999725341797</v>
       </c>
       <c r="C249" t="n">
-        <v>81.01999664306641</v>
+        <v>79.48000335693359</v>
       </c>
       <c r="D249" t="n">
-        <v>78.48999786376953</v>
+        <v>77.45999908447266</v>
       </c>
       <c r="E249" t="n">
-        <v>80.31999969482422</v>
+        <v>77.90000152587891</v>
       </c>
       <c r="F249" t="n">
-        <v>30945100</v>
+        <v>28027400</v>
       </c>
       <c r="G249" t="n">
         <v>0</v>
@@ -6917,22 +6917,22 @@
     </row>
     <row r="250">
       <c r="A250" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="B250" t="n">
-        <v>79.37999725341797</v>
+        <v>77.73000335693359</v>
       </c>
       <c r="C250" t="n">
-        <v>79.48000335693359</v>
+        <v>77.80000305175781</v>
       </c>
       <c r="D250" t="n">
-        <v>77.45999908447266</v>
+        <v>76.30999755859375</v>
       </c>
       <c r="E250" t="n">
-        <v>77.90000152587891</v>
+        <v>76.41000366210938</v>
       </c>
       <c r="F250" t="n">
-        <v>28027400</v>
+        <v>25376300</v>
       </c>
       <c r="G250" t="n">
         <v>0</v>
@@ -6943,22 +6943,22 @@
     </row>
     <row r="251">
       <c r="A251" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="B251" t="n">
-        <v>77.73000335693359</v>
+        <v>76.91000366210938</v>
       </c>
       <c r="C251" t="n">
-        <v>77.80000305175781</v>
+        <v>76.95999908447266</v>
       </c>
       <c r="D251" t="n">
-        <v>76.30999755859375</v>
+        <v>75.30000305175781</v>
       </c>
       <c r="E251" t="n">
-        <v>76.41000366210938</v>
+        <v>75.30999755859375</v>
       </c>
       <c r="F251" t="n">
-        <v>25376300</v>
+        <v>28167600</v>
       </c>
       <c r="G251" t="n">
         <v>0</v>
@@ -6969,22 +6969,22 @@
     </row>
     <row r="252">
       <c r="A252" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="B252" t="n">
-        <v>76.91000366210938</v>
+        <v>71.26999664306641</v>
       </c>
       <c r="C252" t="n">
-        <v>76.95999908447266</v>
+        <v>72.37999725341797</v>
       </c>
       <c r="D252" t="n">
-        <v>75.30000305175781</v>
+        <v>70.11000061035156</v>
       </c>
       <c r="E252" t="n">
-        <v>75.30999755859375</v>
+        <v>71.79000091552734</v>
       </c>
       <c r="F252" t="n">
-        <v>28090300</v>
+        <v>114273800</v>
       </c>
       <c r="G252" t="n">
         <v>0</v>
@@ -10434,37 +10434,37 @@
         </is>
       </c>
       <c r="C2" t="n">
+        <v>71.79000000000001</v>
+      </c>
+      <c r="D2" t="n">
         <v>75.31</v>
       </c>
-      <c r="D2" t="n">
-        <v>76.41</v>
-      </c>
       <c r="E2" t="n">
-        <v>76.905</v>
+        <v>71.27</v>
       </c>
       <c r="F2" t="n">
-        <v>76.92310000000001</v>
+        <v>72.38</v>
       </c>
       <c r="G2" t="n">
-        <v>75.3</v>
+        <v>70.11</v>
       </c>
       <c r="H2" t="n">
-        <v>27803406</v>
+        <v>113606170</v>
       </c>
       <c r="I2" t="n">
-        <v>38958950</v>
+        <v>39983133</v>
       </c>
       <c r="J2" t="n">
-        <v>313586286592</v>
+        <v>298929225728</v>
       </c>
       <c r="K2" t="n">
-        <v>24.060701</v>
+        <v>23.69307</v>
       </c>
       <c r="L2" t="n">
-        <v>19.709965</v>
+        <v>18.799002</v>
       </c>
       <c r="M2" t="n">
-        <v>3.13</v>
+        <v>3.03</v>
       </c>
       <c r="N2" t="n">
         <v>124.86</v>
@@ -10502,7 +10502,7 @@
         <v>7.241</v>
       </c>
       <c r="Y2" t="n">
-        <v>10.4004965</v>
+        <v>9.914376000000001</v>
       </c>
       <c r="Z2" t="n">
         <v>0.111</v>
@@ -10514,7 +10514,7 @@
         <v>48370765824</v>
       </c>
       <c r="AC2" t="n">
-        <v>321113063424</v>
+        <v>306455969792</v>
       </c>
       <c r="AD2" t="n">
         <v>14726931456</v>
@@ -10541,7 +10541,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>2026-09-18 13:15:59</t>
+          <t>2026-09-19 15:21:44</t>
         </is>
       </c>
     </row>

--- a/data/NFLX_data.xlsx
+++ b/data/NFLX_data.xlsx
@@ -469,22 +469,22 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45919</v>
+        <v>45925</v>
       </c>
       <c r="B2" t="n">
-        <v>121.8619995117188</v>
+        <v>120.3089981079102</v>
       </c>
       <c r="C2" t="n">
-        <v>122.995002746582</v>
+        <v>121.6839981079102</v>
       </c>
       <c r="D2" t="n">
-        <v>120.8099975585938</v>
+        <v>119.1510009765625</v>
       </c>
       <c r="E2" t="n">
-        <v>122.6969985961914</v>
+        <v>120.8239974975586</v>
       </c>
       <c r="F2" t="n">
-        <v>49476000</v>
+        <v>19978000</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -495,22 +495,22 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45922</v>
+        <v>45926</v>
       </c>
       <c r="B3" t="n">
-        <v>122.1900024414062</v>
+        <v>120.5419998168945</v>
       </c>
       <c r="C3" t="n">
-        <v>122.9759979248047</v>
+        <v>121.4000015258789</v>
       </c>
       <c r="D3" t="n">
-        <v>121.4240036010742</v>
+        <v>120</v>
       </c>
       <c r="E3" t="n">
-        <v>122.7369995117188</v>
+        <v>121.0609970092773</v>
       </c>
       <c r="F3" t="n">
-        <v>25468000</v>
+        <v>19450000</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -521,22 +521,22 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>45923</v>
+        <v>45929</v>
       </c>
       <c r="B4" t="n">
-        <v>122.7330017089844</v>
+        <v>120.5</v>
       </c>
       <c r="C4" t="n">
-        <v>122.7789993286133</v>
+        <v>122.4489974975586</v>
       </c>
       <c r="D4" t="n">
-        <v>120.8470001220703</v>
+        <v>118.7539978027344</v>
       </c>
       <c r="E4" t="n">
-        <v>121.8470001220703</v>
+        <v>120.640998840332</v>
       </c>
       <c r="F4" t="n">
-        <v>24991000</v>
+        <v>30332000</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -547,22 +547,22 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>45924</v>
+        <v>45930</v>
       </c>
       <c r="B5" t="n">
-        <v>121.8610000610352</v>
+        <v>120.640998840332</v>
       </c>
       <c r="C5" t="n">
-        <v>122.1500015258789</v>
+        <v>120.8499984741211</v>
       </c>
       <c r="D5" t="n">
-        <v>119.4199981689453</v>
+        <v>117.8000030517578</v>
       </c>
       <c r="E5" t="n">
-        <v>120.3949966430664</v>
+        <v>119.8919982910156</v>
       </c>
       <c r="F5" t="n">
-        <v>27731000</v>
+        <v>38303000</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -573,22 +573,22 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>45925</v>
+        <v>45931</v>
       </c>
       <c r="B6" t="n">
-        <v>120.3089981079102</v>
+        <v>117.5490036010742</v>
       </c>
       <c r="C6" t="n">
-        <v>121.6839981079102</v>
+        <v>117.9140014648438</v>
       </c>
       <c r="D6" t="n">
-        <v>119.1510009765625</v>
+        <v>116.3209991455078</v>
       </c>
       <c r="E6" t="n">
-        <v>120.8239974975586</v>
+        <v>117.0899963378906</v>
       </c>
       <c r="F6" t="n">
-        <v>19978000</v>
+        <v>41102000</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -599,22 +599,22 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>45926</v>
+        <v>45932</v>
       </c>
       <c r="B7" t="n">
-        <v>120.5419998168945</v>
+        <v>116.1500015258789</v>
       </c>
       <c r="C7" t="n">
-        <v>121.4000015258789</v>
+        <v>116.3330001831055</v>
       </c>
       <c r="D7" t="n">
-        <v>120</v>
+        <v>113.4000015258789</v>
       </c>
       <c r="E7" t="n">
-        <v>121.0609970092773</v>
+        <v>116.2529983520508</v>
       </c>
       <c r="F7" t="n">
-        <v>19450000</v>
+        <v>46855000</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -625,22 +625,22 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>45929</v>
+        <v>45933</v>
       </c>
       <c r="B8" t="n">
-        <v>120.5</v>
+        <v>116.5</v>
       </c>
       <c r="C8" t="n">
-        <v>122.4489974975586</v>
+        <v>116.8000030517578</v>
       </c>
       <c r="D8" t="n">
-        <v>118.7539978027344</v>
+        <v>114.3219985961914</v>
       </c>
       <c r="E8" t="n">
-        <v>120.640998840332</v>
+        <v>115.3320007324219</v>
       </c>
       <c r="F8" t="n">
-        <v>30332000</v>
+        <v>31374000</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -651,22 +651,22 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>45930</v>
+        <v>45936</v>
       </c>
       <c r="B9" t="n">
-        <v>120.640998840332</v>
+        <v>116.0370025634766</v>
       </c>
       <c r="C9" t="n">
-        <v>120.8499984741211</v>
+        <v>116.3580017089844</v>
       </c>
       <c r="D9" t="n">
-        <v>117.8000030517578</v>
+        <v>114.5449981689453</v>
       </c>
       <c r="E9" t="n">
-        <v>119.8919982910156</v>
+        <v>116.3310012817383</v>
       </c>
       <c r="F9" t="n">
-        <v>38303000</v>
+        <v>29686000</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -677,22 +677,22 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>45931</v>
+        <v>45937</v>
       </c>
       <c r="B10" t="n">
-        <v>117.5490036010742</v>
+        <v>117.7789993286133</v>
       </c>
       <c r="C10" t="n">
-        <v>117.9140014648438</v>
+        <v>120.1370010375977</v>
       </c>
       <c r="D10" t="n">
-        <v>116.3209991455078</v>
+        <v>117.7460021972656</v>
       </c>
       <c r="E10" t="n">
-        <v>117.0899963378906</v>
+        <v>119.1060028076172</v>
       </c>
       <c r="F10" t="n">
-        <v>41102000</v>
+        <v>33091000</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -703,22 +703,22 @@
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>45932</v>
+        <v>45938</v>
       </c>
       <c r="B11" t="n">
-        <v>116.1500015258789</v>
+        <v>119.7109985351562</v>
       </c>
       <c r="C11" t="n">
-        <v>116.3330001831055</v>
+        <v>121.7389984130859</v>
       </c>
       <c r="D11" t="n">
-        <v>113.4000015258789</v>
+        <v>119.1999969482422</v>
       </c>
       <c r="E11" t="n">
-        <v>116.2529983520508</v>
+        <v>121.4250030517578</v>
       </c>
       <c r="F11" t="n">
-        <v>46855000</v>
+        <v>28514000</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -729,22 +729,22 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>45933</v>
+        <v>45939</v>
       </c>
       <c r="B12" t="n">
-        <v>116.5</v>
+        <v>121.4250030517578</v>
       </c>
       <c r="C12" t="n">
-        <v>116.8000030517578</v>
+        <v>123.75</v>
       </c>
       <c r="D12" t="n">
-        <v>114.3219985961914</v>
+        <v>121.181999206543</v>
       </c>
       <c r="E12" t="n">
-        <v>115.3320007324219</v>
+        <v>123.1070022583008</v>
       </c>
       <c r="F12" t="n">
-        <v>31374000</v>
+        <v>28241000</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -755,22 +755,22 @@
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>45936</v>
+        <v>45940</v>
       </c>
       <c r="B13" t="n">
-        <v>116.0370025634766</v>
+        <v>122.9000015258789</v>
       </c>
       <c r="C13" t="n">
-        <v>116.3580017089844</v>
+        <v>124.6999969482422</v>
       </c>
       <c r="D13" t="n">
-        <v>114.5449981689453</v>
+        <v>121.9100036621094</v>
       </c>
       <c r="E13" t="n">
-        <v>116.3310012817383</v>
+        <v>122.0080032348633</v>
       </c>
       <c r="F13" t="n">
-        <v>29686000</v>
+        <v>42798000</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -781,22 +781,22 @@
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>45937</v>
+        <v>45943</v>
       </c>
       <c r="B14" t="n">
-        <v>117.7789993286133</v>
+        <v>122.1350021362305</v>
       </c>
       <c r="C14" t="n">
-        <v>120.1370010375977</v>
+        <v>123.1119995117188</v>
       </c>
       <c r="D14" t="n">
-        <v>117.7460021972656</v>
+        <v>120.6809997558594</v>
       </c>
       <c r="E14" t="n">
-        <v>119.1060028076172</v>
+        <v>121.9029998779297</v>
       </c>
       <c r="F14" t="n">
-        <v>33091000</v>
+        <v>24608000</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -807,22 +807,22 @@
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>45938</v>
+        <v>45944</v>
       </c>
       <c r="B15" t="n">
-        <v>119.7109985351562</v>
+        <v>121.4749984741211</v>
       </c>
       <c r="C15" t="n">
-        <v>121.7389984130859</v>
+        <v>122.4290008544922</v>
       </c>
       <c r="D15" t="n">
-        <v>119.1999969482422</v>
+        <v>120.3099975585938</v>
       </c>
       <c r="E15" t="n">
-        <v>121.4250030517578</v>
+        <v>121.5350036621094</v>
       </c>
       <c r="F15" t="n">
-        <v>28514000</v>
+        <v>23624000</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -833,22 +833,22 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>45939</v>
+        <v>45945</v>
       </c>
       <c r="B16" t="n">
-        <v>121.4250030517578</v>
+        <v>121.3010025024414</v>
       </c>
       <c r="C16" t="n">
-        <v>123.75</v>
+        <v>121.9619979858398</v>
       </c>
       <c r="D16" t="n">
-        <v>121.181999206543</v>
+        <v>120.161003112793</v>
       </c>
       <c r="E16" t="n">
-        <v>123.1070022583008</v>
+        <v>120.3290023803711</v>
       </c>
       <c r="F16" t="n">
-        <v>28241000</v>
+        <v>20252000</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -859,22 +859,22 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>45940</v>
+        <v>45946</v>
       </c>
       <c r="B17" t="n">
-        <v>122.9000015258789</v>
+        <v>121.2149963378906</v>
       </c>
       <c r="C17" t="n">
-        <v>124.6999969482422</v>
+        <v>121.6709976196289</v>
       </c>
       <c r="D17" t="n">
-        <v>121.9100036621094</v>
+        <v>117.5999984741211</v>
       </c>
       <c r="E17" t="n">
-        <v>122.0080032348633</v>
+        <v>118.359001159668</v>
       </c>
       <c r="F17" t="n">
-        <v>42798000</v>
+        <v>28326000</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -885,22 +885,22 @@
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>45943</v>
+        <v>45947</v>
       </c>
       <c r="B18" t="n">
-        <v>122.1350021362305</v>
+        <v>118.3600006103516</v>
       </c>
       <c r="C18" t="n">
-        <v>123.1119995117188</v>
+        <v>120.3119964599609</v>
       </c>
       <c r="D18" t="n">
-        <v>120.6809997558594</v>
+        <v>117.8949966430664</v>
       </c>
       <c r="E18" t="n">
-        <v>121.9029998779297</v>
+        <v>119.9359970092773</v>
       </c>
       <c r="F18" t="n">
-        <v>24608000</v>
+        <v>29571000</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -911,22 +911,22 @@
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>45944</v>
+        <v>45950</v>
       </c>
       <c r="B19" t="n">
-        <v>121.4749984741211</v>
+        <v>120.7880020141602</v>
       </c>
       <c r="C19" t="n">
-        <v>122.4290008544922</v>
+        <v>124.7760009765625</v>
       </c>
       <c r="D19" t="n">
-        <v>120.3099975585938</v>
+        <v>120.6900024414062</v>
       </c>
       <c r="E19" t="n">
-        <v>121.5350036621094</v>
+        <v>123.8560028076172</v>
       </c>
       <c r="F19" t="n">
-        <v>23624000</v>
+        <v>39862000</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -937,22 +937,22 @@
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>45945</v>
+        <v>45951</v>
       </c>
       <c r="B20" t="n">
-        <v>121.3010025024414</v>
+        <v>124.2829971313477</v>
       </c>
       <c r="C20" t="n">
-        <v>121.9619979858398</v>
+        <v>124.8600006103516</v>
       </c>
       <c r="D20" t="n">
-        <v>120.161003112793</v>
+        <v>123.1760025024414</v>
       </c>
       <c r="E20" t="n">
-        <v>120.3290023803711</v>
+        <v>124.1350021362305</v>
       </c>
       <c r="F20" t="n">
-        <v>20252000</v>
+        <v>65082000</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -963,22 +963,22 @@
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>45946</v>
+        <v>45952</v>
       </c>
       <c r="B21" t="n">
-        <v>121.2149963378906</v>
+        <v>114.2900009155273</v>
       </c>
       <c r="C21" t="n">
-        <v>121.6709976196289</v>
+        <v>115.7600021362305</v>
       </c>
       <c r="D21" t="n">
-        <v>117.5999984741211</v>
+        <v>111.2509994506836</v>
       </c>
       <c r="E21" t="n">
-        <v>118.359001159668</v>
+        <v>111.6370010375977</v>
       </c>
       <c r="F21" t="n">
-        <v>28326000</v>
+        <v>147890000</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -989,22 +989,22 @@
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>45947</v>
+        <v>45953</v>
       </c>
       <c r="B22" t="n">
-        <v>118.3600006103516</v>
+        <v>112.6900024414062</v>
       </c>
       <c r="C22" t="n">
-        <v>120.3119964599609</v>
+        <v>112.7829971313477</v>
       </c>
       <c r="D22" t="n">
-        <v>117.8949966430664</v>
+        <v>109.9729995727539</v>
       </c>
       <c r="E22" t="n">
-        <v>119.9359970092773</v>
+        <v>111.359001159668</v>
       </c>
       <c r="F22" t="n">
-        <v>29571000</v>
+        <v>68497000</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -1015,22 +1015,22 @@
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>45950</v>
+        <v>45954</v>
       </c>
       <c r="B23" t="n">
-        <v>120.7880020141602</v>
+        <v>111.0999984741211</v>
       </c>
       <c r="C23" t="n">
-        <v>124.7760009765625</v>
+        <v>111.4509963989258</v>
       </c>
       <c r="D23" t="n">
-        <v>120.6900024414062</v>
+        <v>109.4410018920898</v>
       </c>
       <c r="E23" t="n">
-        <v>123.8560028076172</v>
+        <v>109.4690017700195</v>
       </c>
       <c r="F23" t="n">
-        <v>39862000</v>
+        <v>60280000</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -1041,22 +1041,22 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>45951</v>
+        <v>45957</v>
       </c>
       <c r="B24" t="n">
-        <v>124.2829971313477</v>
+        <v>110.0670013427734</v>
       </c>
       <c r="C24" t="n">
-        <v>124.8600006103516</v>
+        <v>110.2279968261719</v>
       </c>
       <c r="D24" t="n">
-        <v>123.1760025024414</v>
+        <v>108.7300033569336</v>
       </c>
       <c r="E24" t="n">
-        <v>124.1350021362305</v>
+        <v>109.4560012817383</v>
       </c>
       <c r="F24" t="n">
-        <v>65082000</v>
+        <v>46911000</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -1067,22 +1067,22 @@
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>45952</v>
+        <v>45958</v>
       </c>
       <c r="B25" t="n">
-        <v>114.2900009155273</v>
+        <v>109.4000015258789</v>
       </c>
       <c r="C25" t="n">
-        <v>115.7600021362305</v>
+        <v>111.697998046875</v>
       </c>
       <c r="D25" t="n">
-        <v>111.2509994506836</v>
+        <v>109.3010025024414</v>
       </c>
       <c r="E25" t="n">
-        <v>111.6370010375977</v>
+        <v>110.25</v>
       </c>
       <c r="F25" t="n">
-        <v>147890000</v>
+        <v>40209000</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -1093,22 +1093,22 @@
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>45953</v>
+        <v>45959</v>
       </c>
       <c r="B26" t="n">
-        <v>112.6900024414062</v>
+        <v>109.984001159668</v>
       </c>
       <c r="C26" t="n">
-        <v>112.7829971313477</v>
+        <v>110.8550033569336</v>
       </c>
       <c r="D26" t="n">
-        <v>109.9729995727539</v>
+        <v>109.5999984741211</v>
       </c>
       <c r="E26" t="n">
-        <v>111.359001159668</v>
+        <v>110.0410003662109</v>
       </c>
       <c r="F26" t="n">
-        <v>68497000</v>
+        <v>33995000</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -1119,22 +1119,22 @@
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>45954</v>
+        <v>45960</v>
       </c>
       <c r="B27" t="n">
-        <v>111.0999984741211</v>
+        <v>109.4400024414062</v>
       </c>
       <c r="C27" t="n">
-        <v>111.4509963989258</v>
+        <v>110.6159973144531</v>
       </c>
       <c r="D27" t="n">
-        <v>109.4410018920898</v>
+        <v>108.8109970092773</v>
       </c>
       <c r="E27" t="n">
-        <v>109.4690017700195</v>
+        <v>108.9000015258789</v>
       </c>
       <c r="F27" t="n">
-        <v>60280000</v>
+        <v>41581000</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -1145,22 +1145,22 @@
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>45957</v>
+        <v>45961</v>
       </c>
       <c r="B28" t="n">
-        <v>110.0670013427734</v>
+        <v>110.5390014648438</v>
       </c>
       <c r="C28" t="n">
-        <v>110.2279968261719</v>
+        <v>113.4879989624023</v>
       </c>
       <c r="D28" t="n">
-        <v>108.7300033569336</v>
+        <v>110.197998046875</v>
       </c>
       <c r="E28" t="n">
-        <v>109.4560012817383</v>
+        <v>111.8860015869141</v>
       </c>
       <c r="F28" t="n">
-        <v>46911000</v>
+        <v>68665000</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
@@ -1171,22 +1171,22 @@
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>45958</v>
+        <v>45964</v>
       </c>
       <c r="B29" t="n">
-        <v>109.4000015258789</v>
+        <v>113.3239974975586</v>
       </c>
       <c r="C29" t="n">
-        <v>111.697998046875</v>
+        <v>113.3499984741211</v>
       </c>
       <c r="D29" t="n">
-        <v>109.3010025024414</v>
+        <v>107.5149993896484</v>
       </c>
       <c r="E29" t="n">
-        <v>110.25</v>
+        <v>110.0090026855469</v>
       </c>
       <c r="F29" t="n">
-        <v>40209000</v>
+        <v>58634000</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -1197,22 +1197,22 @@
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>45959</v>
+        <v>45965</v>
       </c>
       <c r="B30" t="n">
-        <v>109.984001159668</v>
+        <v>109.9990005493164</v>
       </c>
       <c r="C30" t="n">
-        <v>110.8550033569336</v>
+        <v>110.4599990844727</v>
       </c>
       <c r="D30" t="n">
-        <v>109.5999984741211</v>
+        <v>108.6679992675781</v>
       </c>
       <c r="E30" t="n">
-        <v>110.0410003662109</v>
+        <v>109.2959976196289</v>
       </c>
       <c r="F30" t="n">
-        <v>33995000</v>
+        <v>38718000</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -1223,22 +1223,22 @@
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>45960</v>
+        <v>45966</v>
       </c>
       <c r="B31" t="n">
-        <v>109.4400024414062</v>
+        <v>108.5</v>
       </c>
       <c r="C31" t="n">
-        <v>110.6159973144531</v>
+        <v>110.0849990844727</v>
       </c>
       <c r="D31" t="n">
-        <v>108.8109970092773</v>
+        <v>107.3369979858398</v>
       </c>
       <c r="E31" t="n">
-        <v>108.9000015258789</v>
+        <v>109.8460006713867</v>
       </c>
       <c r="F31" t="n">
-        <v>41581000</v>
+        <v>35539000</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -1249,22 +1249,22 @@
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>45961</v>
+        <v>45967</v>
       </c>
       <c r="B32" t="n">
-        <v>110.5390014648438</v>
+        <v>109.4580001831055</v>
       </c>
       <c r="C32" t="n">
-        <v>113.4879989624023</v>
+        <v>110.370002746582</v>
       </c>
       <c r="D32" t="n">
-        <v>110.197998046875</v>
+        <v>108.5130004882812</v>
       </c>
       <c r="E32" t="n">
-        <v>111.8860015869141</v>
+        <v>109.7020034790039</v>
       </c>
       <c r="F32" t="n">
-        <v>68665000</v>
+        <v>36532000</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
@@ -1275,22 +1275,22 @@
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>45964</v>
+        <v>45968</v>
       </c>
       <c r="B33" t="n">
-        <v>113.3239974975586</v>
+        <v>109.4179992675781</v>
       </c>
       <c r="C33" t="n">
-        <v>113.3499984741211</v>
+        <v>110.8219985961914</v>
       </c>
       <c r="D33" t="n">
-        <v>107.5149993896484</v>
+        <v>108.75</v>
       </c>
       <c r="E33" t="n">
-        <v>110.0090026855469</v>
+        <v>110.3659973144531</v>
       </c>
       <c r="F33" t="n">
-        <v>58634000</v>
+        <v>44125000</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -1301,22 +1301,22 @@
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>45965</v>
+        <v>45971</v>
       </c>
       <c r="B34" t="n">
-        <v>109.9990005493164</v>
+        <v>110.6719970703125</v>
       </c>
       <c r="C34" t="n">
-        <v>110.4599990844727</v>
+        <v>112.8199996948242</v>
       </c>
       <c r="D34" t="n">
-        <v>108.6679992675781</v>
+        <v>110.4049987792969</v>
       </c>
       <c r="E34" t="n">
-        <v>109.2959976196289</v>
+        <v>112.0070037841797</v>
       </c>
       <c r="F34" t="n">
-        <v>38718000</v>
+        <v>36929000</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
@@ -1327,22 +1327,22 @@
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>45966</v>
+        <v>45972</v>
       </c>
       <c r="B35" t="n">
-        <v>108.5</v>
+        <v>111.7600021362305</v>
       </c>
       <c r="C35" t="n">
-        <v>110.0849990844727</v>
+        <v>113.9219970703125</v>
       </c>
       <c r="D35" t="n">
-        <v>107.3369979858398</v>
+        <v>111.2799987792969</v>
       </c>
       <c r="E35" t="n">
-        <v>109.8460006713867</v>
+        <v>113.6439971923828</v>
       </c>
       <c r="F35" t="n">
-        <v>35539000</v>
+        <v>27966000</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
@@ -1353,22 +1353,22 @@
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>45967</v>
+        <v>45973</v>
       </c>
       <c r="B36" t="n">
-        <v>109.4580001831055</v>
+        <v>113.8170013427734</v>
       </c>
       <c r="C36" t="n">
-        <v>110.370002746582</v>
+        <v>116.4339981079102</v>
       </c>
       <c r="D36" t="n">
-        <v>108.5130004882812</v>
+        <v>112.8259963989258</v>
       </c>
       <c r="E36" t="n">
-        <v>109.7020034790039</v>
+        <v>115.75</v>
       </c>
       <c r="F36" t="n">
-        <v>36532000</v>
+        <v>39221000</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -1379,22 +1379,22 @@
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>45968</v>
+        <v>45974</v>
       </c>
       <c r="B37" t="n">
-        <v>109.4179992675781</v>
+        <v>115.8499984741211</v>
       </c>
       <c r="C37" t="n">
-        <v>110.8219985961914</v>
+        <v>116.7330017089844</v>
       </c>
       <c r="D37" t="n">
-        <v>108.75</v>
+        <v>114.5690002441406</v>
       </c>
       <c r="E37" t="n">
-        <v>110.3659973144531</v>
+        <v>115.4229965209961</v>
       </c>
       <c r="F37" t="n">
-        <v>44125000</v>
+        <v>40144000</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
@@ -1405,22 +1405,22 @@
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>45971</v>
+        <v>45975</v>
       </c>
       <c r="B38" t="n">
-        <v>110.6719970703125</v>
+        <v>114.2730026245117</v>
       </c>
       <c r="C38" t="n">
-        <v>112.8199996948242</v>
+        <v>114.2730026245117</v>
       </c>
       <c r="D38" t="n">
-        <v>110.4049987792969</v>
+        <v>110.7210006713867</v>
       </c>
       <c r="E38" t="n">
-        <v>112.0070037841797</v>
+        <v>111.2170028686523</v>
       </c>
       <c r="F38" t="n">
-        <v>36929000</v>
+        <v>47607000</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
@@ -1431,48 +1431,48 @@
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>45972</v>
+        <v>45978</v>
       </c>
       <c r="B39" t="n">
-        <v>111.7600021362305</v>
+        <v>110.75</v>
       </c>
       <c r="C39" t="n">
-        <v>113.9219970703125</v>
+        <v>111.8499984741211</v>
       </c>
       <c r="D39" t="n">
-        <v>111.2799987792969</v>
+        <v>109.5500030517578</v>
       </c>
       <c r="E39" t="n">
-        <v>113.6439971923828</v>
+        <v>110.2900009155273</v>
       </c>
       <c r="F39" t="n">
-        <v>27966000</v>
+        <v>26082700</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>45973</v>
+        <v>45979</v>
       </c>
       <c r="B40" t="n">
-        <v>113.8170013427734</v>
+        <v>110.2900009155273</v>
       </c>
       <c r="C40" t="n">
-        <v>116.4339981079102</v>
+        <v>115.25</v>
       </c>
       <c r="D40" t="n">
-        <v>112.8259963989258</v>
+        <v>109.1999969482422</v>
       </c>
       <c r="E40" t="n">
-        <v>115.75</v>
+        <v>114.0899963378906</v>
       </c>
       <c r="F40" t="n">
-        <v>39221000</v>
+        <v>43440600</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
@@ -1483,22 +1483,22 @@
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>45974</v>
+        <v>45980</v>
       </c>
       <c r="B41" t="n">
-        <v>115.8499984741211</v>
+        <v>113</v>
       </c>
       <c r="C41" t="n">
-        <v>116.7330017089844</v>
+        <v>113.3399963378906</v>
       </c>
       <c r="D41" t="n">
-        <v>114.5690002441406</v>
+        <v>108.6100006103516</v>
       </c>
       <c r="E41" t="n">
-        <v>115.4229965209961</v>
+        <v>110</v>
       </c>
       <c r="F41" t="n">
-        <v>40144000</v>
+        <v>31868100</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
@@ -1509,22 +1509,22 @@
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>45975</v>
+        <v>45981</v>
       </c>
       <c r="B42" t="n">
-        <v>114.2730026245117</v>
+        <v>111</v>
       </c>
       <c r="C42" t="n">
-        <v>114.2730026245117</v>
+        <v>111.0999984741211</v>
       </c>
       <c r="D42" t="n">
-        <v>110.7210006713867</v>
+        <v>105.3899993896484</v>
       </c>
       <c r="E42" t="n">
-        <v>111.2170028686523</v>
+        <v>105.6699981689453</v>
       </c>
       <c r="F42" t="n">
-        <v>47607000</v>
+        <v>36918500</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
@@ -1535,48 +1535,48 @@
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>45978</v>
+        <v>45982</v>
       </c>
       <c r="B43" t="n">
-        <v>110.75</v>
+        <v>105.129997253418</v>
       </c>
       <c r="C43" t="n">
-        <v>111.8499984741211</v>
+        <v>106.5299987792969</v>
       </c>
       <c r="D43" t="n">
-        <v>109.5500030517578</v>
+        <v>103.8099975585938</v>
       </c>
       <c r="E43" t="n">
-        <v>110.2900009155273</v>
+        <v>104.3099975585938</v>
       </c>
       <c r="F43" t="n">
-        <v>26082700</v>
+        <v>41232700</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
-        <v>45979</v>
+        <v>45985</v>
       </c>
       <c r="B44" t="n">
-        <v>110.2900009155273</v>
+        <v>104.25</v>
       </c>
       <c r="C44" t="n">
-        <v>115.25</v>
+        <v>108.0400009155273</v>
       </c>
       <c r="D44" t="n">
-        <v>109.1999969482422</v>
+        <v>103.3199996948242</v>
       </c>
       <c r="E44" t="n">
-        <v>114.0899963378906</v>
+        <v>106.9700012207031</v>
       </c>
       <c r="F44" t="n">
-        <v>43440600</v>
+        <v>62918300</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
@@ -1587,22 +1587,22 @@
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
-        <v>45980</v>
+        <v>45986</v>
       </c>
       <c r="B45" t="n">
-        <v>113</v>
+        <v>106.120002746582</v>
       </c>
       <c r="C45" t="n">
-        <v>113.3399963378906</v>
+        <v>106.3000030517578</v>
       </c>
       <c r="D45" t="n">
-        <v>108.6100006103516</v>
+        <v>103.8199996948242</v>
       </c>
       <c r="E45" t="n">
-        <v>110</v>
+        <v>104.4000015258789</v>
       </c>
       <c r="F45" t="n">
-        <v>31868100</v>
+        <v>35122600</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
@@ -1613,22 +1613,22 @@
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
-        <v>45981</v>
+        <v>45987</v>
       </c>
       <c r="B46" t="n">
-        <v>111</v>
+        <v>105.7399978637695</v>
       </c>
       <c r="C46" t="n">
-        <v>111.0999984741211</v>
+        <v>106.9499969482422</v>
       </c>
       <c r="D46" t="n">
-        <v>105.3899993896484</v>
+        <v>105.2200012207031</v>
       </c>
       <c r="E46" t="n">
-        <v>105.6699981689453</v>
+        <v>106.1399993896484</v>
       </c>
       <c r="F46" t="n">
-        <v>36918500</v>
+        <v>27951000</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
@@ -1639,22 +1639,22 @@
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
-        <v>45982</v>
+        <v>45989</v>
       </c>
       <c r="B47" t="n">
-        <v>105.129997253418</v>
+        <v>106.4400024414062</v>
       </c>
       <c r="C47" t="n">
-        <v>106.5299987792969</v>
+        <v>107.9400024414062</v>
       </c>
       <c r="D47" t="n">
-        <v>103.8099975585938</v>
+        <v>106.2399978637695</v>
       </c>
       <c r="E47" t="n">
-        <v>104.3099975585938</v>
+        <v>107.5800018310547</v>
       </c>
       <c r="F47" t="n">
-        <v>41232700</v>
+        <v>15021600</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
@@ -1665,22 +1665,22 @@
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
-        <v>45985</v>
+        <v>45992</v>
       </c>
       <c r="B48" t="n">
-        <v>104.25</v>
+        <v>106.5100021362305</v>
       </c>
       <c r="C48" t="n">
-        <v>108.0400009155273</v>
+        <v>109.3399963378906</v>
       </c>
       <c r="D48" t="n">
-        <v>103.3199996948242</v>
+        <v>106.3099975585938</v>
       </c>
       <c r="E48" t="n">
-        <v>106.9700012207031</v>
+        <v>109.129997253418</v>
       </c>
       <c r="F48" t="n">
-        <v>62918300</v>
+        <v>24873400</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
@@ -1691,22 +1691,22 @@
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>45986</v>
+        <v>45993</v>
       </c>
       <c r="B49" t="n">
-        <v>106.120002746582</v>
+        <v>109.2099990844727</v>
       </c>
       <c r="C49" t="n">
-        <v>106.3000030517578</v>
+        <v>109.7300033569336</v>
       </c>
       <c r="D49" t="n">
-        <v>103.8199996948242</v>
+        <v>107.5199966430664</v>
       </c>
       <c r="E49" t="n">
-        <v>104.4000015258789</v>
+        <v>109.3499984741211</v>
       </c>
       <c r="F49" t="n">
-        <v>35122600</v>
+        <v>25763000</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
@@ -1717,22 +1717,22 @@
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>45987</v>
+        <v>45994</v>
       </c>
       <c r="B50" t="n">
-        <v>105.7399978637695</v>
+        <v>106.5899963378906</v>
       </c>
       <c r="C50" t="n">
-        <v>106.9499969482422</v>
+        <v>106.870002746582</v>
       </c>
       <c r="D50" t="n">
-        <v>105.2200012207031</v>
+        <v>102.0299987792969</v>
       </c>
       <c r="E50" t="n">
-        <v>106.1399993896484</v>
+        <v>103.9599990844727</v>
       </c>
       <c r="F50" t="n">
-        <v>27951000</v>
+        <v>53593400</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
-        <v>45989</v>
+        <v>45995</v>
       </c>
       <c r="B51" t="n">
-        <v>106.4400024414062</v>
+        <v>103.5699996948242</v>
       </c>
       <c r="C51" t="n">
-        <v>107.9400024414062</v>
+        <v>103.8000030517578</v>
       </c>
       <c r="D51" t="n">
-        <v>106.2399978637695</v>
+        <v>101.7699966430664</v>
       </c>
       <c r="E51" t="n">
-        <v>107.5800018310547</v>
+        <v>103.2200012207031</v>
       </c>
       <c r="F51" t="n">
-        <v>15021600</v>
+        <v>51779100</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
@@ -1769,22 +1769,22 @@
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
-        <v>45992</v>
+        <v>45996</v>
       </c>
       <c r="B52" t="n">
-        <v>106.5100021362305</v>
+        <v>98.77999877929688</v>
       </c>
       <c r="C52" t="n">
-        <v>109.3399963378906</v>
+        <v>104.7900009155273</v>
       </c>
       <c r="D52" t="n">
-        <v>106.3099975585938</v>
+        <v>97.73999786376953</v>
       </c>
       <c r="E52" t="n">
-        <v>109.129997253418</v>
+        <v>100.2399978637695</v>
       </c>
       <c r="F52" t="n">
-        <v>24873400</v>
+        <v>133363600</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
@@ -1795,22 +1795,22 @@
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
-        <v>45993</v>
+        <v>45999</v>
       </c>
       <c r="B53" t="n">
-        <v>109.2099990844727</v>
+        <v>99.87000274658203</v>
       </c>
       <c r="C53" t="n">
-        <v>109.7300033569336</v>
+        <v>99.88999938964844</v>
       </c>
       <c r="D53" t="n">
-        <v>107.5199966430664</v>
+        <v>95.30000305175781</v>
       </c>
       <c r="E53" t="n">
-        <v>109.3499984741211</v>
+        <v>96.79000091552734</v>
       </c>
       <c r="F53" t="n">
-        <v>25763000</v>
+        <v>100906300</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
@@ -1821,22 +1821,22 @@
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
-        <v>45994</v>
+        <v>46000</v>
       </c>
       <c r="B54" t="n">
-        <v>106.5899963378906</v>
+        <v>97.02999877929688</v>
       </c>
       <c r="C54" t="n">
-        <v>106.870002746582</v>
+        <v>97.23999786376953</v>
       </c>
       <c r="D54" t="n">
-        <v>102.0299987792969</v>
+        <v>95.44999694824219</v>
       </c>
       <c r="E54" t="n">
-        <v>103.9599990844727</v>
+        <v>96.70999908447266</v>
       </c>
       <c r="F54" t="n">
-        <v>53593400</v>
+        <v>51745600</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
@@ -1847,22 +1847,22 @@
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
-        <v>45995</v>
+        <v>46001</v>
       </c>
       <c r="B55" t="n">
-        <v>103.5699996948242</v>
+        <v>96.73999786376953</v>
       </c>
       <c r="C55" t="n">
-        <v>103.8000030517578</v>
+        <v>96.97000122070312</v>
       </c>
       <c r="D55" t="n">
-        <v>101.7699966430664</v>
+        <v>92.34999847412109</v>
       </c>
       <c r="E55" t="n">
-        <v>103.2200012207031</v>
+        <v>92.70999908447266</v>
       </c>
       <c r="F55" t="n">
-        <v>51779100</v>
+        <v>74129300</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
@@ -1873,22 +1873,22 @@
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
-        <v>45996</v>
+        <v>46002</v>
       </c>
       <c r="B56" t="n">
-        <v>98.77999877929688</v>
+        <v>93.90000152587891</v>
       </c>
       <c r="C56" t="n">
-        <v>104.7900009155273</v>
+        <v>94.81999969482422</v>
       </c>
       <c r="D56" t="n">
-        <v>97.73999786376953</v>
+        <v>92.76000213623047</v>
       </c>
       <c r="E56" t="n">
-        <v>100.2399978637695</v>
+        <v>94.08999633789062</v>
       </c>
       <c r="F56" t="n">
-        <v>133363600</v>
+        <v>43949000</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
@@ -1899,22 +1899,22 @@
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
-        <v>45999</v>
+        <v>46003</v>
       </c>
       <c r="B57" t="n">
-        <v>99.87000274658203</v>
+        <v>95.5</v>
       </c>
       <c r="C57" t="n">
-        <v>99.88999938964844</v>
+        <v>96.91999816894531</v>
       </c>
       <c r="D57" t="n">
-        <v>95.30000305175781</v>
+        <v>94.65000152587891</v>
       </c>
       <c r="E57" t="n">
-        <v>96.79000091552734</v>
+        <v>95.19000244140625</v>
       </c>
       <c r="F57" t="n">
-        <v>100906300</v>
+        <v>49323100</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
@@ -1925,22 +1925,22 @@
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
-        <v>46000</v>
+        <v>46006</v>
       </c>
       <c r="B58" t="n">
-        <v>97.02999877929688</v>
+        <v>96.01999664306641</v>
       </c>
       <c r="C58" t="n">
-        <v>97.23999786376953</v>
+        <v>96.37000274658203</v>
       </c>
       <c r="D58" t="n">
-        <v>95.44999694824219</v>
+        <v>93.52999877929688</v>
       </c>
       <c r="E58" t="n">
-        <v>96.70999908447266</v>
+        <v>93.76999664306641</v>
       </c>
       <c r="F58" t="n">
-        <v>51745600</v>
+        <v>40016500</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
@@ -1951,22 +1951,22 @@
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
-        <v>46001</v>
+        <v>46007</v>
       </c>
       <c r="B59" t="n">
-        <v>96.73999786376953</v>
+        <v>93.87999725341797</v>
       </c>
       <c r="C59" t="n">
-        <v>96.97000122070312</v>
+        <v>94.93000030517578</v>
       </c>
       <c r="D59" t="n">
-        <v>92.34999847412109</v>
+        <v>93.31999969482422</v>
       </c>
       <c r="E59" t="n">
-        <v>92.70999908447266</v>
+        <v>94.56999969482422</v>
       </c>
       <c r="F59" t="n">
-        <v>74129300</v>
+        <v>34265000</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
@@ -1977,22 +1977,22 @@
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
-        <v>46002</v>
+        <v>46008</v>
       </c>
       <c r="B60" t="n">
-        <v>93.90000152587891</v>
+        <v>95.98000335693359</v>
       </c>
       <c r="C60" t="n">
-        <v>94.81999969482422</v>
+        <v>97.33000183105469</v>
       </c>
       <c r="D60" t="n">
-        <v>92.76000213623047</v>
+        <v>94.45999908447266</v>
       </c>
       <c r="E60" t="n">
-        <v>94.08999633789062</v>
+        <v>94.79000091552734</v>
       </c>
       <c r="F60" t="n">
-        <v>43949000</v>
+        <v>50472800</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
@@ -2003,22 +2003,22 @@
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
-        <v>46003</v>
+        <v>46009</v>
       </c>
       <c r="B61" t="n">
-        <v>95.5</v>
+        <v>95.01999664306641</v>
       </c>
       <c r="C61" t="n">
-        <v>96.91999816894531</v>
+        <v>95.80999755859375</v>
       </c>
       <c r="D61" t="n">
-        <v>94.65000152587891</v>
+        <v>93.58999633789062</v>
       </c>
       <c r="E61" t="n">
-        <v>95.19000244140625</v>
+        <v>94</v>
       </c>
       <c r="F61" t="n">
-        <v>49323100</v>
+        <v>37244700</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
@@ -2029,22 +2029,22 @@
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
-        <v>46006</v>
+        <v>46010</v>
       </c>
       <c r="B62" t="n">
-        <v>96.01999664306641</v>
+        <v>93.56999969482422</v>
       </c>
       <c r="C62" t="n">
-        <v>96.37000274658203</v>
+        <v>95.54000091552734</v>
       </c>
       <c r="D62" t="n">
-        <v>93.52999877929688</v>
+        <v>93.44999694824219</v>
       </c>
       <c r="E62" t="n">
-        <v>93.76999664306641</v>
+        <v>94.38999938964844</v>
       </c>
       <c r="F62" t="n">
-        <v>40016500</v>
+        <v>78990200</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
@@ -2055,22 +2055,22 @@
     </row>
     <row r="63">
       <c r="A63" s="1" t="n">
-        <v>46007</v>
+        <v>46013</v>
       </c>
       <c r="B63" t="n">
-        <v>93.87999725341797</v>
+        <v>94.70999908447266</v>
       </c>
       <c r="C63" t="n">
-        <v>94.93000030517578</v>
+        <v>94.70999908447266</v>
       </c>
       <c r="D63" t="n">
-        <v>93.31999969482422</v>
+        <v>92.91000366210938</v>
       </c>
       <c r="E63" t="n">
-        <v>94.56999969482422</v>
+        <v>93.23000335693359</v>
       </c>
       <c r="F63" t="n">
-        <v>34265000</v>
+        <v>39484800</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
@@ -2081,22 +2081,22 @@
     </row>
     <row r="64">
       <c r="A64" s="1" t="n">
-        <v>46008</v>
+        <v>46014</v>
       </c>
       <c r="B64" t="n">
-        <v>95.98000335693359</v>
+        <v>93.40000152587891</v>
       </c>
       <c r="C64" t="n">
-        <v>97.33000183105469</v>
+        <v>93.80999755859375</v>
       </c>
       <c r="D64" t="n">
-        <v>94.45999908447266</v>
+        <v>91.33000183105469</v>
       </c>
       <c r="E64" t="n">
-        <v>94.79000091552734</v>
+        <v>93.5</v>
       </c>
       <c r="F64" t="n">
-        <v>50472800</v>
+        <v>25896200</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
@@ -2107,22 +2107,22 @@
     </row>
     <row r="65">
       <c r="A65" s="1" t="n">
-        <v>46009</v>
+        <v>46015</v>
       </c>
       <c r="B65" t="n">
-        <v>95.01999664306641</v>
+        <v>93.11000061035156</v>
       </c>
       <c r="C65" t="n">
-        <v>95.80999755859375</v>
+        <v>93.68000030517578</v>
       </c>
       <c r="D65" t="n">
-        <v>93.58999633789062</v>
+        <v>92.66999816894531</v>
       </c>
       <c r="E65" t="n">
-        <v>94</v>
+        <v>93.63999938964844</v>
       </c>
       <c r="F65" t="n">
-        <v>37244700</v>
+        <v>12427900</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
@@ -2133,22 +2133,22 @@
     </row>
     <row r="66">
       <c r="A66" s="1" t="n">
-        <v>46010</v>
+        <v>46017</v>
       </c>
       <c r="B66" t="n">
-        <v>93.56999969482422</v>
+        <v>93.48000335693359</v>
       </c>
       <c r="C66" t="n">
-        <v>95.54000091552734</v>
+        <v>94.69000244140625</v>
       </c>
       <c r="D66" t="n">
-        <v>93.44999694824219</v>
+        <v>93.26999664306641</v>
       </c>
       <c r="E66" t="n">
-        <v>94.38999938964844</v>
+        <v>94.47000122070312</v>
       </c>
       <c r="F66" t="n">
-        <v>78990200</v>
+        <v>22068300</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
@@ -2159,22 +2159,22 @@
     </row>
     <row r="67">
       <c r="A67" s="1" t="n">
-        <v>46013</v>
+        <v>46020</v>
       </c>
       <c r="B67" t="n">
-        <v>94.70999908447266</v>
+        <v>93.98999786376953</v>
       </c>
       <c r="C67" t="n">
-        <v>94.70999908447266</v>
+        <v>94.97000122070312</v>
       </c>
       <c r="D67" t="n">
-        <v>92.91000366210938</v>
+        <v>93.62999725341797</v>
       </c>
       <c r="E67" t="n">
-        <v>93.23000335693359</v>
+        <v>94.15000152587891</v>
       </c>
       <c r="F67" t="n">
-        <v>39484800</v>
+        <v>24493700</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
@@ -2185,22 +2185,22 @@
     </row>
     <row r="68">
       <c r="A68" s="1" t="n">
-        <v>46014</v>
+        <v>46021</v>
       </c>
       <c r="B68" t="n">
-        <v>93.40000152587891</v>
+        <v>93.51999664306641</v>
       </c>
       <c r="C68" t="n">
-        <v>93.80999755859375</v>
+        <v>93.98999786376953</v>
       </c>
       <c r="D68" t="n">
-        <v>91.33000183105469</v>
+        <v>93.33999633789062</v>
       </c>
       <c r="E68" t="n">
-        <v>93.5</v>
+        <v>93.77999877929688</v>
       </c>
       <c r="F68" t="n">
-        <v>25896200</v>
+        <v>23422000</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
@@ -2211,22 +2211,22 @@
     </row>
     <row r="69">
       <c r="A69" s="1" t="n">
-        <v>46015</v>
+        <v>46022</v>
       </c>
       <c r="B69" t="n">
-        <v>93.11000061035156</v>
+        <v>93.59999847412109</v>
       </c>
       <c r="C69" t="n">
-        <v>93.68000030517578</v>
+        <v>94.30999755859375</v>
       </c>
       <c r="D69" t="n">
-        <v>92.66999816894531</v>
+        <v>93.19999694824219</v>
       </c>
       <c r="E69" t="n">
-        <v>93.63999938964844</v>
+        <v>93.76000213623047</v>
       </c>
       <c r="F69" t="n">
-        <v>12427900</v>
+        <v>23495200</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
@@ -2237,22 +2237,22 @@
     </row>
     <row r="70">
       <c r="A70" s="1" t="n">
-        <v>46017</v>
+        <v>46024</v>
       </c>
       <c r="B70" t="n">
-        <v>93.48000335693359</v>
+        <v>94.12999725341797</v>
       </c>
       <c r="C70" t="n">
-        <v>94.69000244140625</v>
+        <v>94.12999725341797</v>
       </c>
       <c r="D70" t="n">
-        <v>93.26999664306641</v>
+        <v>90.80999755859375</v>
       </c>
       <c r="E70" t="n">
-        <v>94.47000122070312</v>
+        <v>90.98999786376953</v>
       </c>
       <c r="F70" t="n">
-        <v>22068300</v>
+        <v>41155400</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
@@ -2263,22 +2263,22 @@
     </row>
     <row r="71">
       <c r="A71" s="1" t="n">
-        <v>46020</v>
+        <v>46027</v>
       </c>
       <c r="B71" t="n">
-        <v>93.98999786376953</v>
+        <v>90.91999816894531</v>
       </c>
       <c r="C71" t="n">
-        <v>94.97000122070312</v>
+        <v>92.62999725341797</v>
       </c>
       <c r="D71" t="n">
-        <v>93.62999725341797</v>
+        <v>90.83999633789062</v>
       </c>
       <c r="E71" t="n">
-        <v>94.15000152587891</v>
+        <v>91.45999908447266</v>
       </c>
       <c r="F71" t="n">
-        <v>24493700</v>
+        <v>39183300</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
@@ -2289,22 +2289,22 @@
     </row>
     <row r="72">
       <c r="A72" s="1" t="n">
-        <v>46021</v>
+        <v>46028</v>
       </c>
       <c r="B72" t="n">
-        <v>93.51999664306641</v>
+        <v>91.54000091552734</v>
       </c>
       <c r="C72" t="n">
-        <v>93.98999786376953</v>
+        <v>91.63999938964844</v>
       </c>
       <c r="D72" t="n">
-        <v>93.33999633789062</v>
+        <v>89.73999786376953</v>
       </c>
       <c r="E72" t="n">
-        <v>93.77999877929688</v>
+        <v>90.65000152587891</v>
       </c>
       <c r="F72" t="n">
-        <v>23422000</v>
+        <v>43331000</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
@@ -2315,22 +2315,22 @@
     </row>
     <row r="73">
       <c r="A73" s="1" t="n">
-        <v>46022</v>
+        <v>46029</v>
       </c>
       <c r="B73" t="n">
-        <v>93.59999847412109</v>
+        <v>91.55999755859375</v>
       </c>
       <c r="C73" t="n">
-        <v>94.30999755859375</v>
+        <v>92.41999816894531</v>
       </c>
       <c r="D73" t="n">
-        <v>93.19999694824219</v>
+        <v>90.05999755859375</v>
       </c>
       <c r="E73" t="n">
-        <v>93.76000213623047</v>
+        <v>90.73000335693359</v>
       </c>
       <c r="F73" t="n">
-        <v>23495200</v>
+        <v>36525700</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
@@ -2341,22 +2341,22 @@
     </row>
     <row r="74">
       <c r="A74" s="1" t="n">
-        <v>46024</v>
+        <v>46030</v>
       </c>
       <c r="B74" t="n">
-        <v>94.12999725341797</v>
+        <v>90.44999694824219</v>
       </c>
       <c r="C74" t="n">
-        <v>94.12999725341797</v>
+        <v>91.25</v>
       </c>
       <c r="D74" t="n">
-        <v>90.80999755859375</v>
+        <v>89.58000183105469</v>
       </c>
       <c r="E74" t="n">
-        <v>90.98999786376953</v>
+        <v>90.52999877929688</v>
       </c>
       <c r="F74" t="n">
-        <v>41155400</v>
+        <v>40068700</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
@@ -2367,22 +2367,22 @@
     </row>
     <row r="75">
       <c r="A75" s="1" t="n">
-        <v>46027</v>
+        <v>46031</v>
       </c>
       <c r="B75" t="n">
-        <v>90.91999816894531</v>
+        <v>90.02999877929688</v>
       </c>
       <c r="C75" t="n">
-        <v>92.62999725341797</v>
+        <v>90.05000305175781</v>
       </c>
       <c r="D75" t="n">
-        <v>90.83999633789062</v>
+        <v>88.31999969482422</v>
       </c>
       <c r="E75" t="n">
-        <v>91.45999908447266</v>
+        <v>89.45999908447266</v>
       </c>
       <c r="F75" t="n">
-        <v>39183300</v>
+        <v>55579500</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
@@ -2393,22 +2393,22 @@
     </row>
     <row r="76">
       <c r="A76" s="1" t="n">
-        <v>46028</v>
+        <v>46034</v>
       </c>
       <c r="B76" t="n">
-        <v>91.54000091552734</v>
+        <v>89.69000244140625</v>
       </c>
       <c r="C76" t="n">
-        <v>91.63999938964844</v>
+        <v>90.33999633789062</v>
       </c>
       <c r="D76" t="n">
-        <v>89.73999786376953</v>
+        <v>89.33000183105469</v>
       </c>
       <c r="E76" t="n">
-        <v>90.65000152587891</v>
+        <v>89.41000366210938</v>
       </c>
       <c r="F76" t="n">
-        <v>43331000</v>
+        <v>36290600</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
@@ -2419,22 +2419,22 @@
     </row>
     <row r="77">
       <c r="A77" s="1" t="n">
-        <v>46029</v>
+        <v>46035</v>
       </c>
       <c r="B77" t="n">
-        <v>91.55999755859375</v>
+        <v>89.44000244140625</v>
       </c>
       <c r="C77" t="n">
-        <v>92.41999816894531</v>
+        <v>91.15000152587891</v>
       </c>
       <c r="D77" t="n">
-        <v>90.05999755859375</v>
+        <v>89.06999969482422</v>
       </c>
       <c r="E77" t="n">
-        <v>90.73000335693359</v>
+        <v>90.31999969482422</v>
       </c>
       <c r="F77" t="n">
-        <v>36525700</v>
+        <v>45221100</v>
       </c>
       <c r="G77" t="n">
         <v>0</v>
@@ -2445,22 +2445,22 @@
     </row>
     <row r="78">
       <c r="A78" s="1" t="n">
-        <v>46030</v>
+        <v>46036</v>
       </c>
       <c r="B78" t="n">
-        <v>90.44999694824219</v>
+        <v>91.23999786376953</v>
       </c>
       <c r="C78" t="n">
-        <v>91.25</v>
+        <v>91.58000183105469</v>
       </c>
       <c r="D78" t="n">
-        <v>89.58000183105469</v>
+        <v>87.94999694824219</v>
       </c>
       <c r="E78" t="n">
-        <v>90.52999877929688</v>
+        <v>88.55000305175781</v>
       </c>
       <c r="F78" t="n">
-        <v>40068700</v>
+        <v>49737700</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
@@ -2471,22 +2471,22 @@
     </row>
     <row r="79">
       <c r="A79" s="1" t="n">
-        <v>46031</v>
+        <v>46037</v>
       </c>
       <c r="B79" t="n">
-        <v>90.02999877929688</v>
+        <v>89.01999664306641</v>
       </c>
       <c r="C79" t="n">
-        <v>90.05000305175781</v>
+        <v>89.88999938964844</v>
       </c>
       <c r="D79" t="n">
-        <v>88.31999969482422</v>
+        <v>87.81999969482422</v>
       </c>
       <c r="E79" t="n">
-        <v>89.45999908447266</v>
+        <v>88.05000305175781</v>
       </c>
       <c r="F79" t="n">
-        <v>55579500</v>
+        <v>36945100</v>
       </c>
       <c r="G79" t="n">
         <v>0</v>
@@ -2497,22 +2497,22 @@
     </row>
     <row r="80">
       <c r="A80" s="1" t="n">
-        <v>46034</v>
+        <v>46038</v>
       </c>
       <c r="B80" t="n">
-        <v>89.69000244140625</v>
+        <v>88.33999633789062</v>
       </c>
       <c r="C80" t="n">
-        <v>90.33999633789062</v>
+        <v>88.51000213623047</v>
       </c>
       <c r="D80" t="n">
-        <v>89.33000183105469</v>
+        <v>87.77999877929688</v>
       </c>
       <c r="E80" t="n">
-        <v>89.41000366210938</v>
+        <v>88</v>
       </c>
       <c r="F80" t="n">
-        <v>36290600</v>
+        <v>48130500</v>
       </c>
       <c r="G80" t="n">
         <v>0</v>
@@ -2523,22 +2523,22 @@
     </row>
     <row r="81">
       <c r="A81" s="1" t="n">
-        <v>46035</v>
+        <v>46042</v>
       </c>
       <c r="B81" t="n">
-        <v>89.44000244140625</v>
+        <v>88.97000122070312</v>
       </c>
       <c r="C81" t="n">
-        <v>91.15000152587891</v>
+        <v>89.90000152587891</v>
       </c>
       <c r="D81" t="n">
-        <v>89.06999969482422</v>
+        <v>87.01999664306641</v>
       </c>
       <c r="E81" t="n">
-        <v>90.31999969482422</v>
+        <v>87.26000213623047</v>
       </c>
       <c r="F81" t="n">
-        <v>45221100</v>
+        <v>109729700</v>
       </c>
       <c r="G81" t="n">
         <v>0</v>
@@ -2549,22 +2549,22 @@
     </row>
     <row r="82">
       <c r="A82" s="1" t="n">
-        <v>46036</v>
+        <v>46043</v>
       </c>
       <c r="B82" t="n">
-        <v>91.23999786376953</v>
+        <v>82.51999664306641</v>
       </c>
       <c r="C82" t="n">
-        <v>91.58000183105469</v>
+        <v>86</v>
       </c>
       <c r="D82" t="n">
-        <v>87.94999694824219</v>
+        <v>81.93000030517578</v>
       </c>
       <c r="E82" t="n">
-        <v>88.55000305175781</v>
+        <v>85.36000061035156</v>
       </c>
       <c r="F82" t="n">
-        <v>49737700</v>
+        <v>127940700</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
@@ -2575,22 +2575,22 @@
     </row>
     <row r="83">
       <c r="A83" s="1" t="n">
-        <v>46037</v>
+        <v>46044</v>
       </c>
       <c r="B83" t="n">
-        <v>89.01999664306641</v>
+        <v>85.01999664306641</v>
       </c>
       <c r="C83" t="n">
-        <v>89.88999938964844</v>
+        <v>85.09999847412109</v>
       </c>
       <c r="D83" t="n">
-        <v>87.81999969482422</v>
+        <v>82.98000335693359</v>
       </c>
       <c r="E83" t="n">
-        <v>88.05000305175781</v>
+        <v>83.54000091552734</v>
       </c>
       <c r="F83" t="n">
-        <v>36945100</v>
+        <v>69113300</v>
       </c>
       <c r="G83" t="n">
         <v>0</v>
@@ -2601,22 +2601,22 @@
     </row>
     <row r="84">
       <c r="A84" s="1" t="n">
-        <v>46038</v>
+        <v>46045</v>
       </c>
       <c r="B84" t="n">
-        <v>88.33999633789062</v>
+        <v>83.43000030517578</v>
       </c>
       <c r="C84" t="n">
-        <v>88.51000213623047</v>
+        <v>86.30000305175781</v>
       </c>
       <c r="D84" t="n">
-        <v>87.77999877929688</v>
+        <v>83.27999877929688</v>
       </c>
       <c r="E84" t="n">
-        <v>88</v>
+        <v>86.12000274658203</v>
       </c>
       <c r="F84" t="n">
-        <v>48130500</v>
+        <v>64520400</v>
       </c>
       <c r="G84" t="n">
         <v>0</v>
@@ -2627,22 +2627,22 @@
     </row>
     <row r="85">
       <c r="A85" s="1" t="n">
-        <v>46042</v>
+        <v>46048</v>
       </c>
       <c r="B85" t="n">
-        <v>88.97000122070312</v>
+        <v>86.91999816894531</v>
       </c>
       <c r="C85" t="n">
-        <v>89.90000152587891</v>
+        <v>86.94000244140625</v>
       </c>
       <c r="D85" t="n">
-        <v>87.01999664306641</v>
+        <v>85.34999847412109</v>
       </c>
       <c r="E85" t="n">
-        <v>87.26000213623047</v>
+        <v>85.69999694824219</v>
       </c>
       <c r="F85" t="n">
-        <v>109729700</v>
+        <v>40941900</v>
       </c>
       <c r="G85" t="n">
         <v>0</v>
@@ -2653,22 +2653,22 @@
     </row>
     <row r="86">
       <c r="A86" s="1" t="n">
-        <v>46043</v>
+        <v>46049</v>
       </c>
       <c r="B86" t="n">
-        <v>82.51999664306641</v>
+        <v>85.27999877929688</v>
       </c>
       <c r="C86" t="n">
-        <v>86</v>
+        <v>85.59999847412109</v>
       </c>
       <c r="D86" t="n">
-        <v>81.93000030517578</v>
+        <v>83.87999725341797</v>
       </c>
       <c r="E86" t="n">
-        <v>85.36000061035156</v>
+        <v>85.58000183105469</v>
       </c>
       <c r="F86" t="n">
-        <v>127940700</v>
+        <v>37790800</v>
       </c>
       <c r="G86" t="n">
         <v>0</v>
@@ -2679,22 +2679,22 @@
     </row>
     <row r="87">
       <c r="A87" s="1" t="n">
-        <v>46044</v>
+        <v>46050</v>
       </c>
       <c r="B87" t="n">
-        <v>85.01999664306641</v>
+        <v>85.62999725341797</v>
       </c>
       <c r="C87" t="n">
-        <v>85.09999847412109</v>
+        <v>86.47000122070312</v>
       </c>
       <c r="D87" t="n">
-        <v>82.98000335693359</v>
+        <v>84.30000305175781</v>
       </c>
       <c r="E87" t="n">
-        <v>83.54000091552734</v>
+        <v>84.63999938964844</v>
       </c>
       <c r="F87" t="n">
-        <v>69113300</v>
+        <v>37762600</v>
       </c>
       <c r="G87" t="n">
         <v>0</v>
@@ -2705,22 +2705,22 @@
     </row>
     <row r="88">
       <c r="A88" s="1" t="n">
-        <v>46045</v>
+        <v>46051</v>
       </c>
       <c r="B88" t="n">
-        <v>83.43000030517578</v>
+        <v>84.30999755859375</v>
       </c>
       <c r="C88" t="n">
-        <v>86.30000305175781</v>
+        <v>84.37999725341797</v>
       </c>
       <c r="D88" t="n">
-        <v>83.27999877929688</v>
+        <v>82.34999847412109</v>
       </c>
       <c r="E88" t="n">
-        <v>86.12000274658203</v>
+        <v>83.16000366210938</v>
       </c>
       <c r="F88" t="n">
-        <v>64520400</v>
+        <v>42278100</v>
       </c>
       <c r="G88" t="n">
         <v>0</v>
@@ -2731,22 +2731,22 @@
     </row>
     <row r="89">
       <c r="A89" s="1" t="n">
-        <v>46048</v>
+        <v>46052</v>
       </c>
       <c r="B89" t="n">
-        <v>86.91999816894531</v>
+        <v>83.09999847412109</v>
       </c>
       <c r="C89" t="n">
-        <v>86.94000244140625</v>
+        <v>84.05999755859375</v>
       </c>
       <c r="D89" t="n">
-        <v>85.34999847412109</v>
+        <v>82.77999877929688</v>
       </c>
       <c r="E89" t="n">
-        <v>85.69999694824219</v>
+        <v>83.48999786376953</v>
       </c>
       <c r="F89" t="n">
-        <v>40941900</v>
+        <v>45755000</v>
       </c>
       <c r="G89" t="n">
         <v>0</v>
@@ -2757,22 +2757,22 @@
     </row>
     <row r="90">
       <c r="A90" s="1" t="n">
-        <v>46049</v>
+        <v>46055</v>
       </c>
       <c r="B90" t="n">
-        <v>85.27999877929688</v>
+        <v>83.52999877929688</v>
       </c>
       <c r="C90" t="n">
-        <v>85.59999847412109</v>
+        <v>85.26999664306641</v>
       </c>
       <c r="D90" t="n">
-        <v>83.87999725341797</v>
+        <v>82.72000122070312</v>
       </c>
       <c r="E90" t="n">
-        <v>85.58000183105469</v>
+        <v>82.76000213623047</v>
       </c>
       <c r="F90" t="n">
-        <v>37790800</v>
+        <v>41445300</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
@@ -2783,22 +2783,22 @@
     </row>
     <row r="91">
       <c r="A91" s="1" t="n">
-        <v>46050</v>
+        <v>46056</v>
       </c>
       <c r="B91" t="n">
-        <v>85.62999725341797</v>
+        <v>82.23000335693359</v>
       </c>
       <c r="C91" t="n">
-        <v>86.47000122070312</v>
+        <v>82.44999694824219</v>
       </c>
       <c r="D91" t="n">
-        <v>84.30000305175781</v>
+        <v>79.62000274658203</v>
       </c>
       <c r="E91" t="n">
-        <v>84.63999938964844</v>
+        <v>79.94000244140625</v>
       </c>
       <c r="F91" t="n">
-        <v>37762600</v>
+        <v>49789000</v>
       </c>
       <c r="G91" t="n">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="92">
       <c r="A92" s="1" t="n">
-        <v>46051</v>
+        <v>46057</v>
       </c>
       <c r="B92" t="n">
-        <v>84.30999755859375</v>
+        <v>79.98999786376953</v>
       </c>
       <c r="C92" t="n">
-        <v>84.37999725341797</v>
+        <v>81.44000244140625</v>
       </c>
       <c r="D92" t="n">
-        <v>82.34999847412109</v>
+        <v>79.23000335693359</v>
       </c>
       <c r="E92" t="n">
-        <v>83.16000366210938</v>
+        <v>80.16000366210938</v>
       </c>
       <c r="F92" t="n">
-        <v>42278100</v>
+        <v>48963200</v>
       </c>
       <c r="G92" t="n">
         <v>0</v>
@@ -2835,22 +2835,22 @@
     </row>
     <row r="93">
       <c r="A93" s="1" t="n">
-        <v>46052</v>
+        <v>46058</v>
       </c>
       <c r="B93" t="n">
-        <v>83.09999847412109</v>
+        <v>81.48999786376953</v>
       </c>
       <c r="C93" t="n">
-        <v>84.05999755859375</v>
+        <v>83.30000305175781</v>
       </c>
       <c r="D93" t="n">
-        <v>82.77999877929688</v>
+        <v>80.54000091552734</v>
       </c>
       <c r="E93" t="n">
-        <v>83.48999786376953</v>
+        <v>80.87000274658203</v>
       </c>
       <c r="F93" t="n">
-        <v>45755000</v>
+        <v>54805700</v>
       </c>
       <c r="G93" t="n">
         <v>0</v>
@@ -2861,22 +2861,22 @@
     </row>
     <row r="94">
       <c r="A94" s="1" t="n">
-        <v>46055</v>
+        <v>46059</v>
       </c>
       <c r="B94" t="n">
-        <v>83.52999877929688</v>
+        <v>81.01999664306641</v>
       </c>
       <c r="C94" t="n">
-        <v>85.26999664306641</v>
+        <v>82.48999786376953</v>
       </c>
       <c r="D94" t="n">
-        <v>82.72000122070312</v>
+        <v>80.65000152587891</v>
       </c>
       <c r="E94" t="n">
-        <v>82.76000213623047</v>
+        <v>82.19999694824219</v>
       </c>
       <c r="F94" t="n">
-        <v>41445300</v>
+        <v>46154100</v>
       </c>
       <c r="G94" t="n">
         <v>0</v>
@@ -2887,22 +2887,22 @@
     </row>
     <row r="95">
       <c r="A95" s="1" t="n">
-        <v>46056</v>
+        <v>46062</v>
       </c>
       <c r="B95" t="n">
-        <v>82.23000335693359</v>
+        <v>82.18000030517578</v>
       </c>
       <c r="C95" t="n">
-        <v>82.44999694824219</v>
+        <v>82.20999908447266</v>
       </c>
       <c r="D95" t="n">
-        <v>79.62000274658203</v>
+        <v>79.87000274658203</v>
       </c>
       <c r="E95" t="n">
-        <v>79.94000244140625</v>
+        <v>81.47000122070312</v>
       </c>
       <c r="F95" t="n">
-        <v>49789000</v>
+        <v>42200200</v>
       </c>
       <c r="G95" t="n">
         <v>0</v>
@@ -2913,22 +2913,22 @@
     </row>
     <row r="96">
       <c r="A96" s="1" t="n">
-        <v>46057</v>
+        <v>46063</v>
       </c>
       <c r="B96" t="n">
-        <v>79.98999786376953</v>
+        <v>82.72000122070312</v>
       </c>
       <c r="C96" t="n">
-        <v>81.44000244140625</v>
+        <v>84.66000366210938</v>
       </c>
       <c r="D96" t="n">
-        <v>79.23000335693359</v>
+        <v>82.08999633789062</v>
       </c>
       <c r="E96" t="n">
-        <v>80.16000366210938</v>
+        <v>82.20999908447266</v>
       </c>
       <c r="F96" t="n">
-        <v>48963200</v>
+        <v>43595800</v>
       </c>
       <c r="G96" t="n">
         <v>0</v>
@@ -2939,22 +2939,22 @@
     </row>
     <row r="97">
       <c r="A97" s="1" t="n">
-        <v>46058</v>
+        <v>46064</v>
       </c>
       <c r="B97" t="n">
-        <v>81.48999786376953</v>
+        <v>81.95999908447266</v>
       </c>
       <c r="C97" t="n">
-        <v>83.30000305175781</v>
+        <v>82.48000335693359</v>
       </c>
       <c r="D97" t="n">
-        <v>80.54000091552734</v>
+        <v>79.44999694824219</v>
       </c>
       <c r="E97" t="n">
-        <v>80.87000274658203</v>
+        <v>79.62000274658203</v>
       </c>
       <c r="F97" t="n">
-        <v>54805700</v>
+        <v>40840300</v>
       </c>
       <c r="G97" t="n">
         <v>0</v>
@@ -2965,22 +2965,22 @@
     </row>
     <row r="98">
       <c r="A98" s="1" t="n">
-        <v>46059</v>
+        <v>46065</v>
       </c>
       <c r="B98" t="n">
-        <v>81.01999664306641</v>
+        <v>79.11000061035156</v>
       </c>
       <c r="C98" t="n">
-        <v>82.48999786376953</v>
+        <v>79.15000152587891</v>
       </c>
       <c r="D98" t="n">
-        <v>80.65000152587891</v>
+        <v>75.23000335693359</v>
       </c>
       <c r="E98" t="n">
-        <v>82.19999694824219</v>
+        <v>75.86000061035156</v>
       </c>
       <c r="F98" t="n">
-        <v>46154100</v>
+        <v>73516100</v>
       </c>
       <c r="G98" t="n">
         <v>0</v>
@@ -2991,22 +2991,22 @@
     </row>
     <row r="99">
       <c r="A99" s="1" t="n">
-        <v>46062</v>
+        <v>46066</v>
       </c>
       <c r="B99" t="n">
-        <v>82.18000030517578</v>
+        <v>76.13999938964844</v>
       </c>
       <c r="C99" t="n">
-        <v>82.20999908447266</v>
+        <v>77.18000030517578</v>
       </c>
       <c r="D99" t="n">
-        <v>79.87000274658203</v>
+        <v>75.52999877929688</v>
       </c>
       <c r="E99" t="n">
-        <v>81.47000122070312</v>
+        <v>76.87000274658203</v>
       </c>
       <c r="F99" t="n">
-        <v>42200200</v>
+        <v>42292100</v>
       </c>
       <c r="G99" t="n">
         <v>0</v>
@@ -3017,22 +3017,22 @@
     </row>
     <row r="100">
       <c r="A100" s="1" t="n">
-        <v>46063</v>
+        <v>46070</v>
       </c>
       <c r="B100" t="n">
-        <v>82.72000122070312</v>
+        <v>76.91999816894531</v>
       </c>
       <c r="C100" t="n">
-        <v>84.66000366210938</v>
+        <v>77.87000274658203</v>
       </c>
       <c r="D100" t="n">
-        <v>82.08999633789062</v>
+        <v>75.30000305175781</v>
       </c>
       <c r="E100" t="n">
-        <v>82.20999908447266</v>
+        <v>77</v>
       </c>
       <c r="F100" t="n">
-        <v>43595800</v>
+        <v>35961500</v>
       </c>
       <c r="G100" t="n">
         <v>0</v>
@@ -3043,22 +3043,22 @@
     </row>
     <row r="101">
       <c r="A101" s="1" t="n">
-        <v>46064</v>
+        <v>46071</v>
       </c>
       <c r="B101" t="n">
-        <v>81.95999908447266</v>
+        <v>77.31999969482422</v>
       </c>
       <c r="C101" t="n">
-        <v>82.48000335693359</v>
+        <v>78.31999969482422</v>
       </c>
       <c r="D101" t="n">
-        <v>79.44999694824219</v>
+        <v>76.27999877929688</v>
       </c>
       <c r="E101" t="n">
-        <v>79.62000274658203</v>
+        <v>77.98999786376953</v>
       </c>
       <c r="F101" t="n">
-        <v>40840300</v>
+        <v>29883100</v>
       </c>
       <c r="G101" t="n">
         <v>0</v>
@@ -3069,22 +3069,22 @@
     </row>
     <row r="102">
       <c r="A102" s="1" t="n">
-        <v>46065</v>
+        <v>46072</v>
       </c>
       <c r="B102" t="n">
-        <v>79.11000061035156</v>
+        <v>77.75</v>
       </c>
       <c r="C102" t="n">
-        <v>79.15000152587891</v>
+        <v>78.69999694824219</v>
       </c>
       <c r="D102" t="n">
-        <v>75.23000335693359</v>
+        <v>76.58999633789062</v>
       </c>
       <c r="E102" t="n">
-        <v>75.86000061035156</v>
+        <v>77</v>
       </c>
       <c r="F102" t="n">
-        <v>73516100</v>
+        <v>30139200</v>
       </c>
       <c r="G102" t="n">
         <v>0</v>
@@ -3095,22 +3095,22 @@
     </row>
     <row r="103">
       <c r="A103" s="1" t="n">
-        <v>46066</v>
+        <v>46073</v>
       </c>
       <c r="B103" t="n">
-        <v>76.13999938964844</v>
+        <v>76.61000061035156</v>
       </c>
       <c r="C103" t="n">
-        <v>77.18000030517578</v>
+        <v>78.84999847412109</v>
       </c>
       <c r="D103" t="n">
-        <v>75.52999877929688</v>
+        <v>76.40000152587891</v>
       </c>
       <c r="E103" t="n">
-        <v>76.87000274658203</v>
+        <v>78.66999816894531</v>
       </c>
       <c r="F103" t="n">
-        <v>42292100</v>
+        <v>32411300</v>
       </c>
       <c r="G103" t="n">
         <v>0</v>
@@ -3121,22 +3121,22 @@
     </row>
     <row r="104">
       <c r="A104" s="1" t="n">
-        <v>46070</v>
+        <v>46076</v>
       </c>
       <c r="B104" t="n">
-        <v>76.91999816894531</v>
+        <v>77.79000091552734</v>
       </c>
       <c r="C104" t="n">
-        <v>77.87000274658203</v>
+        <v>77.83000183105469</v>
       </c>
       <c r="D104" t="n">
-        <v>75.30000305175781</v>
+        <v>75.01000213623047</v>
       </c>
       <c r="E104" t="n">
-        <v>77</v>
+        <v>76.01999664306641</v>
       </c>
       <c r="F104" t="n">
-        <v>35961500</v>
+        <v>38363000</v>
       </c>
       <c r="G104" t="n">
         <v>0</v>
@@ -3147,22 +3147,22 @@
     </row>
     <row r="105">
       <c r="A105" s="1" t="n">
-        <v>46071</v>
+        <v>46077</v>
       </c>
       <c r="B105" t="n">
-        <v>77.31999969482422</v>
+        <v>75.73000335693359</v>
       </c>
       <c r="C105" t="n">
-        <v>78.31999969482422</v>
+        <v>78.12000274658203</v>
       </c>
       <c r="D105" t="n">
-        <v>76.27999877929688</v>
+        <v>75.20999908447266</v>
       </c>
       <c r="E105" t="n">
-        <v>77.98999786376953</v>
+        <v>78.04000091552734</v>
       </c>
       <c r="F105" t="n">
-        <v>29883100</v>
+        <v>33079100</v>
       </c>
       <c r="G105" t="n">
         <v>0</v>
@@ -3173,22 +3173,22 @@
     </row>
     <row r="106">
       <c r="A106" s="1" t="n">
-        <v>46072</v>
+        <v>46078</v>
       </c>
       <c r="B106" t="n">
-        <v>77.75</v>
+        <v>79.43000030517578</v>
       </c>
       <c r="C106" t="n">
-        <v>78.69999694824219</v>
+        <v>83.12000274658203</v>
       </c>
       <c r="D106" t="n">
-        <v>76.58999633789062</v>
+        <v>79.25</v>
       </c>
       <c r="E106" t="n">
-        <v>77</v>
+        <v>82.69999694824219</v>
       </c>
       <c r="F106" t="n">
-        <v>30139200</v>
+        <v>69319300</v>
       </c>
       <c r="G106" t="n">
         <v>0</v>
@@ -3199,22 +3199,22 @@
     </row>
     <row r="107">
       <c r="A107" s="1" t="n">
-        <v>46073</v>
+        <v>46079</v>
       </c>
       <c r="B107" t="n">
-        <v>76.61000061035156</v>
+        <v>83.19999694824219</v>
       </c>
       <c r="C107" t="n">
-        <v>78.84999847412109</v>
+        <v>86.5</v>
       </c>
       <c r="D107" t="n">
-        <v>76.40000152587891</v>
+        <v>82.80000305175781</v>
       </c>
       <c r="E107" t="n">
-        <v>78.66999816894531</v>
+        <v>84.58999633789062</v>
       </c>
       <c r="F107" t="n">
-        <v>32411300</v>
+        <v>85642500</v>
       </c>
       <c r="G107" t="n">
         <v>0</v>
@@ -3225,22 +3225,22 @@
     </row>
     <row r="108">
       <c r="A108" s="1" t="n">
-        <v>46076</v>
+        <v>46080</v>
       </c>
       <c r="B108" t="n">
-        <v>77.79000091552734</v>
+        <v>94.30000305175781</v>
       </c>
       <c r="C108" t="n">
-        <v>77.83000183105469</v>
+        <v>96.75</v>
       </c>
       <c r="D108" t="n">
-        <v>75.01000213623047</v>
+        <v>90.58000183105469</v>
       </c>
       <c r="E108" t="n">
-        <v>76.01999664306641</v>
+        <v>96.23999786376953</v>
       </c>
       <c r="F108" t="n">
-        <v>38363000</v>
+        <v>200767000</v>
       </c>
       <c r="G108" t="n">
         <v>0</v>
@@ -3251,22 +3251,22 @@
     </row>
     <row r="109">
       <c r="A109" s="1" t="n">
-        <v>46077</v>
+        <v>46083</v>
       </c>
       <c r="B109" t="n">
-        <v>75.73000335693359</v>
+        <v>95.26000213623047</v>
       </c>
       <c r="C109" t="n">
-        <v>78.12000274658203</v>
+        <v>98.06999969482422</v>
       </c>
       <c r="D109" t="n">
-        <v>75.20999908447266</v>
+        <v>95.19999694824219</v>
       </c>
       <c r="E109" t="n">
-        <v>78.04000091552734</v>
+        <v>97.08999633789062</v>
       </c>
       <c r="F109" t="n">
-        <v>33079100</v>
+        <v>79915400</v>
       </c>
       <c r="G109" t="n">
         <v>0</v>
@@ -3277,22 +3277,22 @@
     </row>
     <row r="110">
       <c r="A110" s="1" t="n">
-        <v>46078</v>
+        <v>46084</v>
       </c>
       <c r="B110" t="n">
-        <v>79.43000030517578</v>
+        <v>96.01000213623047</v>
       </c>
       <c r="C110" t="n">
-        <v>83.12000274658203</v>
+        <v>98.45999908447266</v>
       </c>
       <c r="D110" t="n">
-        <v>79.25</v>
+        <v>95.33000183105469</v>
       </c>
       <c r="E110" t="n">
-        <v>82.69999694824219</v>
+        <v>97.69999694824219</v>
       </c>
       <c r="F110" t="n">
-        <v>69319300</v>
+        <v>59149000</v>
       </c>
       <c r="G110" t="n">
         <v>0</v>
@@ -3303,22 +3303,22 @@
     </row>
     <row r="111">
       <c r="A111" s="1" t="n">
-        <v>46079</v>
+        <v>46085</v>
       </c>
       <c r="B111" t="n">
-        <v>83.19999694824219</v>
+        <v>97.11000061035156</v>
       </c>
       <c r="C111" t="n">
-        <v>86.5</v>
+        <v>99.75</v>
       </c>
       <c r="D111" t="n">
-        <v>82.80000305175781</v>
+        <v>96.98999786376953</v>
       </c>
       <c r="E111" t="n">
-        <v>84.58999633789062</v>
+        <v>98.66000366210938</v>
       </c>
       <c r="F111" t="n">
-        <v>85642500</v>
+        <v>52604300</v>
       </c>
       <c r="G111" t="n">
         <v>0</v>
@@ -3329,22 +3329,22 @@
     </row>
     <row r="112">
       <c r="A112" s="1" t="n">
-        <v>46080</v>
+        <v>46086</v>
       </c>
       <c r="B112" t="n">
-        <v>94.30000305175781</v>
+        <v>98.5</v>
       </c>
       <c r="C112" t="n">
-        <v>96.75</v>
+        <v>100.1900024414062</v>
       </c>
       <c r="D112" t="n">
-        <v>90.58000183105469</v>
+        <v>98.09999847412109</v>
       </c>
       <c r="E112" t="n">
-        <v>96.23999786376953</v>
+        <v>99.16999816894531</v>
       </c>
       <c r="F112" t="n">
-        <v>200767000</v>
+        <v>53403000</v>
       </c>
       <c r="G112" t="n">
         <v>0</v>
@@ -3355,22 +3355,22 @@
     </row>
     <row r="113">
       <c r="A113" s="1" t="n">
-        <v>46083</v>
+        <v>46087</v>
       </c>
       <c r="B113" t="n">
-        <v>95.26000213623047</v>
+        <v>99.33000183105469</v>
       </c>
       <c r="C113" t="n">
-        <v>98.06999969482422</v>
+        <v>99.87999725341797</v>
       </c>
       <c r="D113" t="n">
-        <v>95.19999694824219</v>
+        <v>97.40000152587891</v>
       </c>
       <c r="E113" t="n">
-        <v>97.08999633789062</v>
+        <v>99.01999664306641</v>
       </c>
       <c r="F113" t="n">
-        <v>79915400</v>
+        <v>41196300</v>
       </c>
       <c r="G113" t="n">
         <v>0</v>
@@ -3381,22 +3381,22 @@
     </row>
     <row r="114">
       <c r="A114" s="1" t="n">
-        <v>46084</v>
+        <v>46090</v>
       </c>
       <c r="B114" t="n">
-        <v>96.01000213623047</v>
+        <v>97.69999694824219</v>
       </c>
       <c r="C114" t="n">
-        <v>98.45999908447266</v>
+        <v>98.94000244140625</v>
       </c>
       <c r="D114" t="n">
-        <v>95.33000183105469</v>
+        <v>96.58000183105469</v>
       </c>
       <c r="E114" t="n">
-        <v>97.69999694824219</v>
+        <v>98.31999969482422</v>
       </c>
       <c r="F114" t="n">
-        <v>59149000</v>
+        <v>48589000</v>
       </c>
       <c r="G114" t="n">
         <v>0</v>
@@ -3407,22 +3407,22 @@
     </row>
     <row r="115">
       <c r="A115" s="1" t="n">
-        <v>46085</v>
+        <v>46091</v>
       </c>
       <c r="B115" t="n">
-        <v>97.11000061035156</v>
+        <v>97.80999755859375</v>
       </c>
       <c r="C115" t="n">
-        <v>99.75</v>
+        <v>98.48999786376953</v>
       </c>
       <c r="D115" t="n">
-        <v>96.98999786376953</v>
+        <v>96.29000091552734</v>
       </c>
       <c r="E115" t="n">
-        <v>98.66000366210938</v>
+        <v>96.94000244140625</v>
       </c>
       <c r="F115" t="n">
-        <v>52604300</v>
+        <v>41027200</v>
       </c>
       <c r="G115" t="n">
         <v>0</v>
@@ -3433,22 +3433,22 @@
     </row>
     <row r="116">
       <c r="A116" s="1" t="n">
-        <v>46086</v>
+        <v>46092</v>
       </c>
       <c r="B116" t="n">
-        <v>98.5</v>
+        <v>97.41000366210938</v>
       </c>
       <c r="C116" t="n">
-        <v>100.1900024414062</v>
+        <v>98</v>
       </c>
       <c r="D116" t="n">
-        <v>98.09999847412109</v>
+        <v>94.69000244140625</v>
       </c>
       <c r="E116" t="n">
-        <v>99.16999816894531</v>
+        <v>94.88999938964844</v>
       </c>
       <c r="F116" t="n">
-        <v>53403000</v>
+        <v>33962900</v>
       </c>
       <c r="G116" t="n">
         <v>0</v>
@@ -3459,22 +3459,22 @@
     </row>
     <row r="117">
       <c r="A117" s="1" t="n">
-        <v>46087</v>
+        <v>46093</v>
       </c>
       <c r="B117" t="n">
-        <v>99.33000183105469</v>
+        <v>94.86000061035156</v>
       </c>
       <c r="C117" t="n">
-        <v>99.87999725341797</v>
+        <v>95.40000152587891</v>
       </c>
       <c r="D117" t="n">
-        <v>97.40000152587891</v>
+        <v>93.87000274658203</v>
       </c>
       <c r="E117" t="n">
-        <v>99.01999664306641</v>
+        <v>94.30999755859375</v>
       </c>
       <c r="F117" t="n">
-        <v>41196300</v>
+        <v>34206900</v>
       </c>
       <c r="G117" t="n">
         <v>0</v>
@@ -3485,22 +3485,22 @@
     </row>
     <row r="118">
       <c r="A118" s="1" t="n">
-        <v>46090</v>
+        <v>46094</v>
       </c>
       <c r="B118" t="n">
-        <v>97.69999694824219</v>
+        <v>94.63999938964844</v>
       </c>
       <c r="C118" t="n">
-        <v>98.94000244140625</v>
+        <v>95.68000030517578</v>
       </c>
       <c r="D118" t="n">
-        <v>96.58000183105469</v>
+        <v>94.23999786376953</v>
       </c>
       <c r="E118" t="n">
-        <v>98.31999969482422</v>
+        <v>95.30999755859375</v>
       </c>
       <c r="F118" t="n">
-        <v>48589000</v>
+        <v>29876700</v>
       </c>
       <c r="G118" t="n">
         <v>0</v>
@@ -3511,22 +3511,22 @@
     </row>
     <row r="119">
       <c r="A119" s="1" t="n">
-        <v>46091</v>
+        <v>46097</v>
       </c>
       <c r="B119" t="n">
-        <v>97.80999755859375</v>
+        <v>95.58000183105469</v>
       </c>
       <c r="C119" t="n">
-        <v>98.48999786376953</v>
+        <v>96.09999847412109</v>
       </c>
       <c r="D119" t="n">
-        <v>96.29000091552734</v>
+        <v>94.36000061035156</v>
       </c>
       <c r="E119" t="n">
-        <v>96.94000244140625</v>
+        <v>95.19999694824219</v>
       </c>
       <c r="F119" t="n">
-        <v>41027200</v>
+        <v>34931800</v>
       </c>
       <c r="G119" t="n">
         <v>0</v>
@@ -3537,22 +3537,22 @@
     </row>
     <row r="120">
       <c r="A120" s="1" t="n">
-        <v>46092</v>
+        <v>46098</v>
       </c>
       <c r="B120" t="n">
-        <v>97.41000366210938</v>
+        <v>95.30000305175781</v>
       </c>
       <c r="C120" t="n">
-        <v>98</v>
+        <v>96.33999633789062</v>
       </c>
       <c r="D120" t="n">
-        <v>94.69000244140625</v>
+        <v>94.01000213623047</v>
       </c>
       <c r="E120" t="n">
-        <v>94.88999938964844</v>
+        <v>94.36000061035156</v>
       </c>
       <c r="F120" t="n">
-        <v>33962900</v>
+        <v>26434500</v>
       </c>
       <c r="G120" t="n">
         <v>0</v>
@@ -3563,22 +3563,22 @@
     </row>
     <row r="121">
       <c r="A121" s="1" t="n">
-        <v>46093</v>
+        <v>46099</v>
       </c>
       <c r="B121" t="n">
-        <v>94.86000061035156</v>
+        <v>94.44999694824219</v>
       </c>
       <c r="C121" t="n">
-        <v>95.40000152587891</v>
+        <v>95.33999633789062</v>
       </c>
       <c r="D121" t="n">
-        <v>93.87000274658203</v>
+        <v>93.61000061035156</v>
       </c>
       <c r="E121" t="n">
-        <v>94.30999755859375</v>
+        <v>94.69999694824219</v>
       </c>
       <c r="F121" t="n">
-        <v>34206900</v>
+        <v>27878300</v>
       </c>
       <c r="G121" t="n">
         <v>0</v>
@@ -3589,22 +3589,22 @@
     </row>
     <row r="122">
       <c r="A122" s="1" t="n">
-        <v>46094</v>
+        <v>46100</v>
       </c>
       <c r="B122" t="n">
-        <v>94.63999938964844</v>
+        <v>94.30999755859375</v>
       </c>
       <c r="C122" t="n">
-        <v>95.68000030517578</v>
+        <v>95.75</v>
       </c>
       <c r="D122" t="n">
-        <v>94.23999786376953</v>
+        <v>90.77999877929688</v>
       </c>
       <c r="E122" t="n">
-        <v>95.30999755859375</v>
+        <v>91.73999786376953</v>
       </c>
       <c r="F122" t="n">
-        <v>29876700</v>
+        <v>40169300</v>
       </c>
       <c r="G122" t="n">
         <v>0</v>
@@ -3615,22 +3615,22 @@
     </row>
     <row r="123">
       <c r="A123" s="1" t="n">
-        <v>46097</v>
+        <v>46101</v>
       </c>
       <c r="B123" t="n">
-        <v>95.58000183105469</v>
+        <v>91.30999755859375</v>
       </c>
       <c r="C123" t="n">
-        <v>96.09999847412109</v>
+        <v>91.87999725341797</v>
       </c>
       <c r="D123" t="n">
-        <v>94.36000061035156</v>
+        <v>90.69000244140625</v>
       </c>
       <c r="E123" t="n">
-        <v>95.19999694824219</v>
+        <v>91.81999969482422</v>
       </c>
       <c r="F123" t="n">
-        <v>34931800</v>
+        <v>61678000</v>
       </c>
       <c r="G123" t="n">
         <v>0</v>
@@ -3641,22 +3641,22 @@
     </row>
     <row r="124">
       <c r="A124" s="1" t="n">
-        <v>46098</v>
+        <v>46104</v>
       </c>
       <c r="B124" t="n">
-        <v>95.30000305175781</v>
+        <v>92.04000091552734</v>
       </c>
       <c r="C124" t="n">
-        <v>96.33999633789062</v>
+        <v>93.98000335693359</v>
       </c>
       <c r="D124" t="n">
-        <v>94.01000213623047</v>
+        <v>91.86000061035156</v>
       </c>
       <c r="E124" t="n">
-        <v>94.36000061035156</v>
+        <v>93.37999725341797</v>
       </c>
       <c r="F124" t="n">
-        <v>26434500</v>
+        <v>34315900</v>
       </c>
       <c r="G124" t="n">
         <v>0</v>
@@ -3667,22 +3667,22 @@
     </row>
     <row r="125">
       <c r="A125" s="1" t="n">
-        <v>46099</v>
+        <v>46105</v>
       </c>
       <c r="B125" t="n">
-        <v>94.44999694824219</v>
+        <v>92.79000091552734</v>
       </c>
       <c r="C125" t="n">
-        <v>95.33999633789062</v>
+        <v>93.73999786376953</v>
       </c>
       <c r="D125" t="n">
-        <v>93.61000061035156</v>
+        <v>90.81999969482422</v>
       </c>
       <c r="E125" t="n">
-        <v>94.69999694824219</v>
+        <v>90.91999816894531</v>
       </c>
       <c r="F125" t="n">
-        <v>27878300</v>
+        <v>28938000</v>
       </c>
       <c r="G125" t="n">
         <v>0</v>
@@ -3693,22 +3693,22 @@
     </row>
     <row r="126">
       <c r="A126" s="1" t="n">
-        <v>46100</v>
+        <v>46106</v>
       </c>
       <c r="B126" t="n">
-        <v>94.30999755859375</v>
+        <v>91.70999908447266</v>
       </c>
       <c r="C126" t="n">
-        <v>95.75</v>
+        <v>92.51999664306641</v>
       </c>
       <c r="D126" t="n">
-        <v>90.77999877929688</v>
+        <v>91.23999786376953</v>
       </c>
       <c r="E126" t="n">
-        <v>91.73999786376953</v>
+        <v>92.27999877929688</v>
       </c>
       <c r="F126" t="n">
-        <v>40169300</v>
+        <v>29545600</v>
       </c>
       <c r="G126" t="n">
         <v>0</v>
@@ -3719,22 +3719,22 @@
     </row>
     <row r="127">
       <c r="A127" s="1" t="n">
-        <v>46101</v>
+        <v>46107</v>
       </c>
       <c r="B127" t="n">
-        <v>91.30999755859375</v>
+        <v>91.51999664306641</v>
       </c>
       <c r="C127" t="n">
-        <v>91.87999725341797</v>
+        <v>95.86000061035156</v>
       </c>
       <c r="D127" t="n">
-        <v>90.69000244140625</v>
+        <v>91.01000213623047</v>
       </c>
       <c r="E127" t="n">
-        <v>91.81999969482422</v>
+        <v>93.31999969482422</v>
       </c>
       <c r="F127" t="n">
-        <v>61678000</v>
+        <v>59522000</v>
       </c>
       <c r="G127" t="n">
         <v>0</v>
@@ -3745,22 +3745,22 @@
     </row>
     <row r="128">
       <c r="A128" s="1" t="n">
-        <v>46104</v>
+        <v>46108</v>
       </c>
       <c r="B128" t="n">
-        <v>92.04000091552734</v>
+        <v>94.56999969482422</v>
       </c>
       <c r="C128" t="n">
-        <v>93.98000335693359</v>
+        <v>95.58000183105469</v>
       </c>
       <c r="D128" t="n">
-        <v>91.86000061035156</v>
+        <v>92.73999786376953</v>
       </c>
       <c r="E128" t="n">
-        <v>93.37999725341797</v>
+        <v>93.43000030517578</v>
       </c>
       <c r="F128" t="n">
-        <v>34315900</v>
+        <v>44590700</v>
       </c>
       <c r="G128" t="n">
         <v>0</v>
@@ -3771,22 +3771,22 @@
     </row>
     <row r="129">
       <c r="A129" s="1" t="n">
-        <v>46105</v>
+        <v>46111</v>
       </c>
       <c r="B129" t="n">
-        <v>92.79000091552734</v>
+        <v>92.75</v>
       </c>
       <c r="C129" t="n">
-        <v>93.73999786376953</v>
+        <v>94.48999786376953</v>
       </c>
       <c r="D129" t="n">
-        <v>90.81999969482422</v>
+        <v>92.22000122070312</v>
       </c>
       <c r="E129" t="n">
-        <v>90.91999816894531</v>
+        <v>92.97000122070312</v>
       </c>
       <c r="F129" t="n">
-        <v>28938000</v>
+        <v>32375100</v>
       </c>
       <c r="G129" t="n">
         <v>0</v>
@@ -3797,22 +3797,22 @@
     </row>
     <row r="130">
       <c r="A130" s="1" t="n">
-        <v>46106</v>
+        <v>46112</v>
       </c>
       <c r="B130" t="n">
-        <v>91.70999908447266</v>
+        <v>93.02999877929688</v>
       </c>
       <c r="C130" t="n">
-        <v>92.51999664306641</v>
+        <v>96.26000213623047</v>
       </c>
       <c r="D130" t="n">
-        <v>91.23999786376953</v>
+        <v>93.02999877929688</v>
       </c>
       <c r="E130" t="n">
-        <v>92.27999877929688</v>
+        <v>96.15000152587891</v>
       </c>
       <c r="F130" t="n">
-        <v>29545600</v>
+        <v>54270000</v>
       </c>
       <c r="G130" t="n">
         <v>0</v>
@@ -3823,22 +3823,22 @@
     </row>
     <row r="131">
       <c r="A131" s="1" t="n">
-        <v>46107</v>
+        <v>46113</v>
       </c>
       <c r="B131" t="n">
-        <v>91.51999664306641</v>
+        <v>96.47000122070312</v>
       </c>
       <c r="C131" t="n">
-        <v>95.86000061035156</v>
+        <v>97.19999694824219</v>
       </c>
       <c r="D131" t="n">
-        <v>91.01000213623047</v>
+        <v>94.26000213623047</v>
       </c>
       <c r="E131" t="n">
-        <v>93.31999969482422</v>
+        <v>95.55000305175781</v>
       </c>
       <c r="F131" t="n">
-        <v>59522000</v>
+        <v>30439300</v>
       </c>
       <c r="G131" t="n">
         <v>0</v>
@@ -3849,22 +3849,22 @@
     </row>
     <row r="132">
       <c r="A132" s="1" t="n">
-        <v>46108</v>
+        <v>46114</v>
       </c>
       <c r="B132" t="n">
-        <v>94.56999969482422</v>
+        <v>95.26999664306641</v>
       </c>
       <c r="C132" t="n">
-        <v>95.58000183105469</v>
+        <v>98.70999908447266</v>
       </c>
       <c r="D132" t="n">
-        <v>92.73999786376953</v>
+        <v>95.16999816894531</v>
       </c>
       <c r="E132" t="n">
-        <v>93.43000030517578</v>
+        <v>98.66000366210938</v>
       </c>
       <c r="F132" t="n">
-        <v>44590700</v>
+        <v>37068000</v>
       </c>
       <c r="G132" t="n">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="133">
       <c r="A133" s="1" t="n">
-        <v>46111</v>
+        <v>46118</v>
       </c>
       <c r="B133" t="n">
-        <v>92.75</v>
+        <v>100.9599990844727</v>
       </c>
       <c r="C133" t="n">
-        <v>94.48999786376953</v>
+        <v>102.6900024414062</v>
       </c>
       <c r="D133" t="n">
-        <v>92.22000122070312</v>
+        <v>97.97000122070312</v>
       </c>
       <c r="E133" t="n">
-        <v>92.97000122070312</v>
+        <v>98.93000030517578</v>
       </c>
       <c r="F133" t="n">
-        <v>32375100</v>
+        <v>37029300</v>
       </c>
       <c r="G133" t="n">
         <v>0</v>
@@ -3901,22 +3901,22 @@
     </row>
     <row r="134">
       <c r="A134" s="1" t="n">
-        <v>46112</v>
+        <v>46119</v>
       </c>
       <c r="B134" t="n">
-        <v>93.02999877929688</v>
+        <v>98.55000305175781</v>
       </c>
       <c r="C134" t="n">
-        <v>96.26000213623047</v>
+        <v>99.87999725341797</v>
       </c>
       <c r="D134" t="n">
-        <v>93.02999877929688</v>
+        <v>98.25</v>
       </c>
       <c r="E134" t="n">
-        <v>96.15000152587891</v>
+        <v>98.81999969482422</v>
       </c>
       <c r="F134" t="n">
-        <v>54270000</v>
+        <v>25016700</v>
       </c>
       <c r="G134" t="n">
         <v>0</v>
@@ -3927,22 +3927,22 @@
     </row>
     <row r="135">
       <c r="A135" s="1" t="n">
-        <v>46113</v>
+        <v>46120</v>
       </c>
       <c r="B135" t="n">
-        <v>96.47000122070312</v>
+        <v>100.3199996948242</v>
       </c>
       <c r="C135" t="n">
-        <v>97.19999694824219</v>
+        <v>100.4000015258789</v>
       </c>
       <c r="D135" t="n">
-        <v>94.26000213623047</v>
+        <v>97.44000244140625</v>
       </c>
       <c r="E135" t="n">
-        <v>95.55000305175781</v>
+        <v>99.38999938964844</v>
       </c>
       <c r="F135" t="n">
-        <v>30439300</v>
+        <v>30957600</v>
       </c>
       <c r="G135" t="n">
         <v>0</v>
@@ -3953,22 +3953,22 @@
     </row>
     <row r="136">
       <c r="A136" s="1" t="n">
-        <v>46114</v>
+        <v>46121</v>
       </c>
       <c r="B136" t="n">
-        <v>95.26999664306641</v>
+        <v>99.62999725341797</v>
       </c>
       <c r="C136" t="n">
-        <v>98.70999908447266</v>
+        <v>102.3399963378906</v>
       </c>
       <c r="D136" t="n">
-        <v>95.16999816894531</v>
+        <v>99.08000183105469</v>
       </c>
       <c r="E136" t="n">
-        <v>98.66000366210938</v>
+        <v>102.0500030517578</v>
       </c>
       <c r="F136" t="n">
-        <v>37068000</v>
+        <v>35087800</v>
       </c>
       <c r="G136" t="n">
         <v>0</v>
@@ -3979,22 +3979,22 @@
     </row>
     <row r="137">
       <c r="A137" s="1" t="n">
-        <v>46118</v>
+        <v>46122</v>
       </c>
       <c r="B137" t="n">
-        <v>100.9599990844727</v>
+        <v>102.4700012207031</v>
       </c>
       <c r="C137" t="n">
-        <v>102.6900024414062</v>
+        <v>103.0800018310547</v>
       </c>
       <c r="D137" t="n">
-        <v>97.97000122070312</v>
+        <v>101.4599990844727</v>
       </c>
       <c r="E137" t="n">
-        <v>98.93000030517578</v>
+        <v>103.0100021362305</v>
       </c>
       <c r="F137" t="n">
-        <v>37029300</v>
+        <v>25769900</v>
       </c>
       <c r="G137" t="n">
         <v>0</v>
@@ -4005,22 +4005,22 @@
     </row>
     <row r="138">
       <c r="A138" s="1" t="n">
-        <v>46119</v>
+        <v>46125</v>
       </c>
       <c r="B138" t="n">
-        <v>98.55000305175781</v>
+        <v>103.0299987792969</v>
       </c>
       <c r="C138" t="n">
-        <v>99.87999725341797</v>
+        <v>103.6699981689453</v>
       </c>
       <c r="D138" t="n">
-        <v>98.25</v>
+        <v>102.0599975585938</v>
       </c>
       <c r="E138" t="n">
-        <v>98.81999969482422</v>
+        <v>103.1600036621094</v>
       </c>
       <c r="F138" t="n">
-        <v>25016700</v>
+        <v>26042800</v>
       </c>
       <c r="G138" t="n">
         <v>0</v>
@@ -4031,22 +4031,22 @@
     </row>
     <row r="139">
       <c r="A139" s="1" t="n">
-        <v>46120</v>
+        <v>46126</v>
       </c>
       <c r="B139" t="n">
-        <v>100.3199996948242</v>
+        <v>103.120002746582</v>
       </c>
       <c r="C139" t="n">
-        <v>100.4000015258789</v>
+        <v>106.5699996948242</v>
       </c>
       <c r="D139" t="n">
-        <v>97.44000244140625</v>
+        <v>103.0400009155273</v>
       </c>
       <c r="E139" t="n">
-        <v>99.38999938964844</v>
+        <v>106.2799987792969</v>
       </c>
       <c r="F139" t="n">
-        <v>30957600</v>
+        <v>40534900</v>
       </c>
       <c r="G139" t="n">
         <v>0</v>
@@ -4057,22 +4057,22 @@
     </row>
     <row r="140">
       <c r="A140" s="1" t="n">
-        <v>46121</v>
+        <v>46127</v>
       </c>
       <c r="B140" t="n">
-        <v>99.62999725341797</v>
+        <v>105.9800033569336</v>
       </c>
       <c r="C140" t="n">
-        <v>102.3399963378906</v>
+        <v>107.8499984741211</v>
       </c>
       <c r="D140" t="n">
-        <v>99.08000183105469</v>
+        <v>105.0400009155273</v>
       </c>
       <c r="E140" t="n">
-        <v>102.0500030517578</v>
+        <v>107.7099990844727</v>
       </c>
       <c r="F140" t="n">
-        <v>35087800</v>
+        <v>38023700</v>
       </c>
       <c r="G140" t="n">
         <v>0</v>
@@ -4083,22 +4083,22 @@
     </row>
     <row r="141">
       <c r="A141" s="1" t="n">
-        <v>46122</v>
+        <v>46128</v>
       </c>
       <c r="B141" t="n">
-        <v>102.4700012207031</v>
+        <v>107.4700012207031</v>
       </c>
       <c r="C141" t="n">
-        <v>103.0800018310547</v>
+        <v>108.9499969482422</v>
       </c>
       <c r="D141" t="n">
-        <v>101.4599990844727</v>
+        <v>106.620002746582</v>
       </c>
       <c r="E141" t="n">
-        <v>103.0100021362305</v>
+        <v>107.7900009155273</v>
       </c>
       <c r="F141" t="n">
-        <v>25769900</v>
+        <v>64928300</v>
       </c>
       <c r="G141" t="n">
         <v>0</v>
@@ -4109,22 +4109,22 @@
     </row>
     <row r="142">
       <c r="A142" s="1" t="n">
-        <v>46125</v>
+        <v>46129</v>
       </c>
       <c r="B142" t="n">
-        <v>103.0299987792969</v>
+        <v>96.37000274658203</v>
       </c>
       <c r="C142" t="n">
-        <v>103.6699981689453</v>
+        <v>98.73999786376953</v>
       </c>
       <c r="D142" t="n">
-        <v>102.0599975585938</v>
+        <v>95.09999847412109</v>
       </c>
       <c r="E142" t="n">
-        <v>103.1600036621094</v>
+        <v>97.30999755859375</v>
       </c>
       <c r="F142" t="n">
-        <v>26042800</v>
+        <v>125958700</v>
       </c>
       <c r="G142" t="n">
         <v>0</v>
@@ -4135,22 +4135,22 @@
     </row>
     <row r="143">
       <c r="A143" s="1" t="n">
-        <v>46126</v>
+        <v>46132</v>
       </c>
       <c r="B143" t="n">
-        <v>103.120002746582</v>
+        <v>97.13999938964844</v>
       </c>
       <c r="C143" t="n">
-        <v>106.5699996948242</v>
+        <v>97.59999847412109</v>
       </c>
       <c r="D143" t="n">
-        <v>103.0400009155273</v>
+        <v>93.54000091552734</v>
       </c>
       <c r="E143" t="n">
-        <v>106.2799987792969</v>
+        <v>94.83000183105469</v>
       </c>
       <c r="F143" t="n">
-        <v>40534900</v>
+        <v>63298300</v>
       </c>
       <c r="G143" t="n">
         <v>0</v>
@@ -4161,22 +4161,22 @@
     </row>
     <row r="144">
       <c r="A144" s="1" t="n">
-        <v>46127</v>
+        <v>46133</v>
       </c>
       <c r="B144" t="n">
-        <v>105.9800033569336</v>
+        <v>94</v>
       </c>
       <c r="C144" t="n">
-        <v>107.8499984741211</v>
+        <v>94.65000152587891</v>
       </c>
       <c r="D144" t="n">
-        <v>105.0400009155273</v>
+        <v>92.37000274658203</v>
       </c>
       <c r="E144" t="n">
-        <v>107.7099990844727</v>
+        <v>92.58000183105469</v>
       </c>
       <c r="F144" t="n">
-        <v>38023700</v>
+        <v>61962300</v>
       </c>
       <c r="G144" t="n">
         <v>0</v>
@@ -4187,22 +4187,22 @@
     </row>
     <row r="145">
       <c r="A145" s="1" t="n">
-        <v>46128</v>
+        <v>46134</v>
       </c>
       <c r="B145" t="n">
-        <v>107.4700012207031</v>
+        <v>93.05999755859375</v>
       </c>
       <c r="C145" t="n">
-        <v>108.9499969482422</v>
+        <v>93.84999847412109</v>
       </c>
       <c r="D145" t="n">
-        <v>106.620002746582</v>
+        <v>92.76999664306641</v>
       </c>
       <c r="E145" t="n">
-        <v>107.7900009155273</v>
+        <v>93.23999786376953</v>
       </c>
       <c r="F145" t="n">
-        <v>64928300</v>
+        <v>33694300</v>
       </c>
       <c r="G145" t="n">
         <v>0</v>
@@ -4213,22 +4213,22 @@
     </row>
     <row r="146">
       <c r="A146" s="1" t="n">
-        <v>46129</v>
+        <v>46135</v>
       </c>
       <c r="B146" t="n">
-        <v>96.37000274658203</v>
+        <v>94.05999755859375</v>
       </c>
       <c r="C146" t="n">
-        <v>98.73999786376953</v>
+        <v>94.63999938964844</v>
       </c>
       <c r="D146" t="n">
-        <v>95.09999847412109</v>
+        <v>92.06999969482422</v>
       </c>
       <c r="E146" t="n">
-        <v>97.30999755859375</v>
+        <v>92.81999969482422</v>
       </c>
       <c r="F146" t="n">
-        <v>125958700</v>
+        <v>36851700</v>
       </c>
       <c r="G146" t="n">
         <v>0</v>
@@ -4239,22 +4239,22 @@
     </row>
     <row r="147">
       <c r="A147" s="1" t="n">
-        <v>46132</v>
+        <v>46136</v>
       </c>
       <c r="B147" t="n">
-        <v>97.13999938964844</v>
+        <v>92.56999969482422</v>
       </c>
       <c r="C147" t="n">
-        <v>97.59999847412109</v>
+        <v>93.27999877929688</v>
       </c>
       <c r="D147" t="n">
-        <v>93.54000091552734</v>
+        <v>91.80000305175781</v>
       </c>
       <c r="E147" t="n">
-        <v>94.83000183105469</v>
+        <v>92.44000244140625</v>
       </c>
       <c r="F147" t="n">
-        <v>63298300</v>
+        <v>32553200</v>
       </c>
       <c r="G147" t="n">
         <v>0</v>
@@ -4265,22 +4265,22 @@
     </row>
     <row r="148">
       <c r="A148" s="1" t="n">
-        <v>46133</v>
+        <v>46139</v>
       </c>
       <c r="B148" t="n">
-        <v>94</v>
+        <v>92.05000305175781</v>
       </c>
       <c r="C148" t="n">
-        <v>94.65000152587891</v>
+        <v>92.83999633789062</v>
       </c>
       <c r="D148" t="n">
-        <v>92.37000274658203</v>
+        <v>91.30000305175781</v>
       </c>
       <c r="E148" t="n">
-        <v>92.58000183105469</v>
+        <v>91.37000274658203</v>
       </c>
       <c r="F148" t="n">
-        <v>61962300</v>
+        <v>29707400</v>
       </c>
       <c r="G148" t="n">
         <v>0</v>
@@ -4291,22 +4291,22 @@
     </row>
     <row r="149">
       <c r="A149" s="1" t="n">
-        <v>46134</v>
+        <v>46140</v>
       </c>
       <c r="B149" t="n">
-        <v>93.05999755859375</v>
+        <v>91.5</v>
       </c>
       <c r="C149" t="n">
-        <v>93.84999847412109</v>
+        <v>92.33999633789062</v>
       </c>
       <c r="D149" t="n">
-        <v>92.76999664306641</v>
+        <v>90.01999664306641</v>
       </c>
       <c r="E149" t="n">
-        <v>93.23999786376953</v>
+        <v>92.26999664306641</v>
       </c>
       <c r="F149" t="n">
-        <v>33694300</v>
+        <v>33418100</v>
       </c>
       <c r="G149" t="n">
         <v>0</v>
@@ -4317,22 +4317,22 @@
     </row>
     <row r="150">
       <c r="A150" s="1" t="n">
-        <v>46135</v>
+        <v>46141</v>
       </c>
       <c r="B150" t="n">
-        <v>94.05999755859375</v>
+        <v>91.23000335693359</v>
       </c>
       <c r="C150" t="n">
-        <v>94.63999938964844</v>
+        <v>92.86000061035156</v>
       </c>
       <c r="D150" t="n">
-        <v>92.06999969482422</v>
+        <v>90.86000061035156</v>
       </c>
       <c r="E150" t="n">
-        <v>92.81999969482422</v>
+        <v>92.12000274658203</v>
       </c>
       <c r="F150" t="n">
-        <v>36851700</v>
+        <v>26122100</v>
       </c>
       <c r="G150" t="n">
         <v>0</v>
@@ -4343,22 +4343,22 @@
     </row>
     <row r="151">
       <c r="A151" s="1" t="n">
-        <v>46136</v>
+        <v>46142</v>
       </c>
       <c r="B151" t="n">
-        <v>92.56999969482422</v>
+        <v>91.34999847412109</v>
       </c>
       <c r="C151" t="n">
-        <v>93.27999877929688</v>
+        <v>94.22000122070312</v>
       </c>
       <c r="D151" t="n">
-        <v>91.80000305175781</v>
+        <v>90.76999664306641</v>
       </c>
       <c r="E151" t="n">
-        <v>92.44000244140625</v>
+        <v>93.61000061035156</v>
       </c>
       <c r="F151" t="n">
-        <v>32553200</v>
+        <v>40923000</v>
       </c>
       <c r="G151" t="n">
         <v>0</v>
@@ -4369,22 +4369,22 @@
     </row>
     <row r="152">
       <c r="A152" s="1" t="n">
-        <v>46139</v>
+        <v>46143</v>
       </c>
       <c r="B152" t="n">
-        <v>92.05000305175781</v>
+        <v>94.41999816894531</v>
       </c>
       <c r="C152" t="n">
-        <v>92.83999633789062</v>
+        <v>94.69999694824219</v>
       </c>
       <c r="D152" t="n">
-        <v>91.30000305175781</v>
+        <v>91.90000152587891</v>
       </c>
       <c r="E152" t="n">
-        <v>91.37000274658203</v>
+        <v>92.05999755859375</v>
       </c>
       <c r="F152" t="n">
-        <v>29707400</v>
+        <v>30406900</v>
       </c>
       <c r="G152" t="n">
         <v>0</v>
@@ -4395,22 +4395,22 @@
     </row>
     <row r="153">
       <c r="A153" s="1" t="n">
-        <v>46140</v>
+        <v>46146</v>
       </c>
       <c r="B153" t="n">
-        <v>91.5</v>
+        <v>92.09999847412109</v>
       </c>
       <c r="C153" t="n">
-        <v>92.33999633789062</v>
+        <v>92.33000183105469</v>
       </c>
       <c r="D153" t="n">
-        <v>90.01999664306641</v>
+        <v>90.88999938964844</v>
       </c>
       <c r="E153" t="n">
-        <v>92.26999664306641</v>
+        <v>91.01999664306641</v>
       </c>
       <c r="F153" t="n">
-        <v>33418100</v>
+        <v>25928800</v>
       </c>
       <c r="G153" t="n">
         <v>0</v>
@@ -4421,22 +4421,22 @@
     </row>
     <row r="154">
       <c r="A154" s="1" t="n">
-        <v>46141</v>
+        <v>46147</v>
       </c>
       <c r="B154" t="n">
-        <v>91.23000335693359</v>
+        <v>91.18000030517578</v>
       </c>
       <c r="C154" t="n">
-        <v>92.86000061035156</v>
+        <v>91.27999877929688</v>
       </c>
       <c r="D154" t="n">
-        <v>90.86000061035156</v>
+        <v>87.56999969482422</v>
       </c>
       <c r="E154" t="n">
-        <v>92.12000274658203</v>
+        <v>87.88999938964844</v>
       </c>
       <c r="F154" t="n">
-        <v>26122100</v>
+        <v>51961300</v>
       </c>
       <c r="G154" t="n">
         <v>0</v>
@@ -4447,22 +4447,22 @@
     </row>
     <row r="155">
       <c r="A155" s="1" t="n">
-        <v>46142</v>
+        <v>46148</v>
       </c>
       <c r="B155" t="n">
-        <v>91.34999847412109</v>
+        <v>87.15000152587891</v>
       </c>
       <c r="C155" t="n">
-        <v>94.22000122070312</v>
+        <v>88.55000305175781</v>
       </c>
       <c r="D155" t="n">
-        <v>90.76999664306641</v>
+        <v>86.72000122070312</v>
       </c>
       <c r="E155" t="n">
-        <v>93.61000061035156</v>
+        <v>88.26999664306641</v>
       </c>
       <c r="F155" t="n">
-        <v>40923000</v>
+        <v>41932400</v>
       </c>
       <c r="G155" t="n">
         <v>0</v>
@@ -4473,22 +4473,22 @@
     </row>
     <row r="156">
       <c r="A156" s="1" t="n">
-        <v>46143</v>
+        <v>46149</v>
       </c>
       <c r="B156" t="n">
-        <v>94.41999816894531</v>
+        <v>88.19999694824219</v>
       </c>
       <c r="C156" t="n">
-        <v>94.69999694824219</v>
+        <v>89.40000152587891</v>
       </c>
       <c r="D156" t="n">
-        <v>91.90000152587891</v>
+        <v>88.12999725341797</v>
       </c>
       <c r="E156" t="n">
-        <v>92.05999755859375</v>
+        <v>88.25</v>
       </c>
       <c r="F156" t="n">
-        <v>30406900</v>
+        <v>30627600</v>
       </c>
       <c r="G156" t="n">
         <v>0</v>
@@ -4499,22 +4499,22 @@
     </row>
     <row r="157">
       <c r="A157" s="1" t="n">
-        <v>46146</v>
+        <v>46150</v>
       </c>
       <c r="B157" t="n">
-        <v>92.09999847412109</v>
+        <v>87.70999908447266</v>
       </c>
       <c r="C157" t="n">
-        <v>92.33000183105469</v>
+        <v>88.04000091552734</v>
       </c>
       <c r="D157" t="n">
-        <v>90.88999938964844</v>
+        <v>87.20999908447266</v>
       </c>
       <c r="E157" t="n">
-        <v>91.01999664306641</v>
+        <v>87.48999786376953</v>
       </c>
       <c r="F157" t="n">
-        <v>25928800</v>
+        <v>36215100</v>
       </c>
       <c r="G157" t="n">
         <v>0</v>
@@ -4525,22 +4525,22 @@
     </row>
     <row r="158">
       <c r="A158" s="1" t="n">
-        <v>46147</v>
+        <v>46153</v>
       </c>
       <c r="B158" t="n">
-        <v>91.18000030517578</v>
+        <v>86.52999877929688</v>
       </c>
       <c r="C158" t="n">
-        <v>91.27999877929688</v>
+        <v>87.33999633789062</v>
       </c>
       <c r="D158" t="n">
-        <v>87.56999969482422</v>
+        <v>85.09999847412109</v>
       </c>
       <c r="E158" t="n">
-        <v>87.88999938964844</v>
+        <v>85.44999694824219</v>
       </c>
       <c r="F158" t="n">
-        <v>51961300</v>
+        <v>40556500</v>
       </c>
       <c r="G158" t="n">
         <v>0</v>
@@ -4551,22 +4551,22 @@
     </row>
     <row r="159">
       <c r="A159" s="1" t="n">
-        <v>46148</v>
+        <v>46154</v>
       </c>
       <c r="B159" t="n">
-        <v>87.15000152587891</v>
+        <v>85.91000366210938</v>
       </c>
       <c r="C159" t="n">
-        <v>88.55000305175781</v>
+        <v>89.16999816894531</v>
       </c>
       <c r="D159" t="n">
-        <v>86.72000122070312</v>
+        <v>85.80999755859375</v>
       </c>
       <c r="E159" t="n">
-        <v>88.26999664306641</v>
+        <v>87.66000366210938</v>
       </c>
       <c r="F159" t="n">
-        <v>41932400</v>
+        <v>43556600</v>
       </c>
       <c r="G159" t="n">
         <v>0</v>
@@ -4577,22 +4577,22 @@
     </row>
     <row r="160">
       <c r="A160" s="1" t="n">
-        <v>46149</v>
+        <v>46155</v>
       </c>
       <c r="B160" t="n">
-        <v>88.19999694824219</v>
+        <v>86.56999969482422</v>
       </c>
       <c r="C160" t="n">
-        <v>89.40000152587891</v>
+        <v>88.62000274658203</v>
       </c>
       <c r="D160" t="n">
-        <v>88.12999725341797</v>
+        <v>86.27999877929688</v>
       </c>
       <c r="E160" t="n">
-        <v>88.25</v>
+        <v>87.55999755859375</v>
       </c>
       <c r="F160" t="n">
-        <v>30627600</v>
+        <v>30823500</v>
       </c>
       <c r="G160" t="n">
         <v>0</v>
@@ -4603,22 +4603,22 @@
     </row>
     <row r="161">
       <c r="A161" s="1" t="n">
-        <v>46150</v>
+        <v>46156</v>
       </c>
       <c r="B161" t="n">
-        <v>87.70999908447266</v>
+        <v>87.62000274658203</v>
       </c>
       <c r="C161" t="n">
-        <v>88.04000091552734</v>
+        <v>88.5</v>
       </c>
       <c r="D161" t="n">
-        <v>87.20999908447266</v>
+        <v>86.65000152587891</v>
       </c>
       <c r="E161" t="n">
-        <v>87.48999786376953</v>
+        <v>86.94000244140625</v>
       </c>
       <c r="F161" t="n">
-        <v>36215100</v>
+        <v>29408300</v>
       </c>
       <c r="G161" t="n">
         <v>0</v>
@@ -4629,22 +4629,22 @@
     </row>
     <row r="162">
       <c r="A162" s="1" t="n">
-        <v>46153</v>
+        <v>46157</v>
       </c>
       <c r="B162" t="n">
-        <v>86.52999877929688</v>
+        <v>87.69000244140625</v>
       </c>
       <c r="C162" t="n">
-        <v>87.33999633789062</v>
+        <v>89.48999786376953</v>
       </c>
       <c r="D162" t="n">
-        <v>85.09999847412109</v>
+        <v>86.69000244140625</v>
       </c>
       <c r="E162" t="n">
-        <v>85.44999694824219</v>
+        <v>87.01999664306641</v>
       </c>
       <c r="F162" t="n">
-        <v>40556500</v>
+        <v>32335700</v>
       </c>
       <c r="G162" t="n">
         <v>0</v>
@@ -4655,22 +4655,22 @@
     </row>
     <row r="163">
       <c r="A163" s="1" t="n">
-        <v>46154</v>
+        <v>46160</v>
       </c>
       <c r="B163" t="n">
-        <v>85.91000366210938</v>
+        <v>86.5</v>
       </c>
       <c r="C163" t="n">
-        <v>89.16999816894531</v>
+        <v>89.81999969482422</v>
       </c>
       <c r="D163" t="n">
-        <v>85.80999755859375</v>
+        <v>86.33000183105469</v>
       </c>
       <c r="E163" t="n">
-        <v>87.66000366210938</v>
+        <v>89.65000152587891</v>
       </c>
       <c r="F163" t="n">
-        <v>43556600</v>
+        <v>35800500</v>
       </c>
       <c r="G163" t="n">
         <v>0</v>
@@ -4681,22 +4681,22 @@
     </row>
     <row r="164">
       <c r="A164" s="1" t="n">
-        <v>46155</v>
+        <v>46161</v>
       </c>
       <c r="B164" t="n">
-        <v>86.56999969482422</v>
+        <v>90.13999938964844</v>
       </c>
       <c r="C164" t="n">
-        <v>88.62000274658203</v>
+        <v>91.48000335693359</v>
       </c>
       <c r="D164" t="n">
-        <v>86.27999877929688</v>
+        <v>88.69000244140625</v>
       </c>
       <c r="E164" t="n">
-        <v>87.55999755859375</v>
+        <v>89.33000183105469</v>
       </c>
       <c r="F164" t="n">
-        <v>30823500</v>
+        <v>34545700</v>
       </c>
       <c r="G164" t="n">
         <v>0</v>
@@ -4707,22 +4707,22 @@
     </row>
     <row r="165">
       <c r="A165" s="1" t="n">
-        <v>46156</v>
+        <v>46162</v>
       </c>
       <c r="B165" t="n">
-        <v>87.62000274658203</v>
+        <v>88.51999664306641</v>
       </c>
       <c r="C165" t="n">
-        <v>88.5</v>
+        <v>88.55000305175781</v>
       </c>
       <c r="D165" t="n">
-        <v>86.65000152587891</v>
+        <v>87.5</v>
       </c>
       <c r="E165" t="n">
-        <v>86.94000244140625</v>
+        <v>88.08999633789062</v>
       </c>
       <c r="F165" t="n">
-        <v>29408300</v>
+        <v>23463400</v>
       </c>
       <c r="G165" t="n">
         <v>0</v>
@@ -4733,22 +4733,22 @@
     </row>
     <row r="166">
       <c r="A166" s="1" t="n">
-        <v>46157</v>
+        <v>46163</v>
       </c>
       <c r="B166" t="n">
-        <v>87.69000244140625</v>
+        <v>88.02999877929688</v>
       </c>
       <c r="C166" t="n">
-        <v>89.48999786376953</v>
+        <v>90.37000274658203</v>
       </c>
       <c r="D166" t="n">
-        <v>86.69000244140625</v>
+        <v>87.51999664306641</v>
       </c>
       <c r="E166" t="n">
-        <v>87.01999664306641</v>
+        <v>89.30000305175781</v>
       </c>
       <c r="F166" t="n">
-        <v>32335700</v>
+        <v>28613900</v>
       </c>
       <c r="G166" t="n">
         <v>0</v>
@@ -4759,22 +4759,22 @@
     </row>
     <row r="167">
       <c r="A167" s="1" t="n">
-        <v>46160</v>
+        <v>46164</v>
       </c>
       <c r="B167" t="n">
-        <v>86.5</v>
+        <v>89.09999847412109</v>
       </c>
       <c r="C167" t="n">
-        <v>89.81999969482422</v>
+        <v>89.97000122070312</v>
       </c>
       <c r="D167" t="n">
-        <v>86.33000183105469</v>
+        <v>88.16999816894531</v>
       </c>
       <c r="E167" t="n">
-        <v>89.65000152587891</v>
+        <v>88.59999847412109</v>
       </c>
       <c r="F167" t="n">
-        <v>35800500</v>
+        <v>23847200</v>
       </c>
       <c r="G167" t="n">
         <v>0</v>
@@ -4785,22 +4785,22 @@
     </row>
     <row r="168">
       <c r="A168" s="1" t="n">
-        <v>46161</v>
+        <v>46168</v>
       </c>
       <c r="B168" t="n">
-        <v>90.13999938964844</v>
+        <v>88.40000152587891</v>
       </c>
       <c r="C168" t="n">
-        <v>91.48000335693359</v>
+        <v>88.73000335693359</v>
       </c>
       <c r="D168" t="n">
-        <v>88.69000244140625</v>
+        <v>87.25</v>
       </c>
       <c r="E168" t="n">
-        <v>89.33000183105469</v>
+        <v>87.68000030517578</v>
       </c>
       <c r="F168" t="n">
-        <v>34545700</v>
+        <v>24014500</v>
       </c>
       <c r="G168" t="n">
         <v>0</v>
@@ -4811,22 +4811,22 @@
     </row>
     <row r="169">
       <c r="A169" s="1" t="n">
-        <v>46162</v>
+        <v>46169</v>
       </c>
       <c r="B169" t="n">
-        <v>88.51999664306641</v>
+        <v>87.05000305175781</v>
       </c>
       <c r="C169" t="n">
-        <v>88.55000305175781</v>
+        <v>88.5</v>
       </c>
       <c r="D169" t="n">
-        <v>87.5</v>
+        <v>86.81999969482422</v>
       </c>
       <c r="E169" t="n">
-        <v>88.08999633789062</v>
+        <v>87.34999847412109</v>
       </c>
       <c r="F169" t="n">
-        <v>23463400</v>
+        <v>22569500</v>
       </c>
       <c r="G169" t="n">
         <v>0</v>
@@ -4837,22 +4837,22 @@
     </row>
     <row r="170">
       <c r="A170" s="1" t="n">
-        <v>46163</v>
+        <v>46170</v>
       </c>
       <c r="B170" t="n">
-        <v>88.02999877929688</v>
+        <v>86.90000152587891</v>
       </c>
       <c r="C170" t="n">
-        <v>90.37000274658203</v>
+        <v>87.04000091552734</v>
       </c>
       <c r="D170" t="n">
-        <v>87.51999664306641</v>
+        <v>85.58999633789062</v>
       </c>
       <c r="E170" t="n">
-        <v>89.30000305175781</v>
+        <v>86.36000061035156</v>
       </c>
       <c r="F170" t="n">
-        <v>28613900</v>
+        <v>38803800</v>
       </c>
       <c r="G170" t="n">
         <v>0</v>
@@ -4863,22 +4863,22 @@
     </row>
     <row r="171">
       <c r="A171" s="1" t="n">
-        <v>46164</v>
+        <v>46171</v>
       </c>
       <c r="B171" t="n">
-        <v>89.09999847412109</v>
+        <v>86.19999694824219</v>
       </c>
       <c r="C171" t="n">
-        <v>89.97000122070312</v>
+        <v>86.66999816894531</v>
       </c>
       <c r="D171" t="n">
-        <v>88.16999816894531</v>
+        <v>85.66000366210938</v>
       </c>
       <c r="E171" t="n">
-        <v>88.59999847412109</v>
+        <v>86.01999664306641</v>
       </c>
       <c r="F171" t="n">
-        <v>23847200</v>
+        <v>39793600</v>
       </c>
       <c r="G171" t="n">
         <v>0</v>
@@ -4889,22 +4889,22 @@
     </row>
     <row r="172">
       <c r="A172" s="1" t="n">
-        <v>46168</v>
+        <v>46174</v>
       </c>
       <c r="B172" t="n">
-        <v>88.40000152587891</v>
+        <v>85.73000335693359</v>
       </c>
       <c r="C172" t="n">
-        <v>88.73000335693359</v>
+        <v>87.23000335693359</v>
       </c>
       <c r="D172" t="n">
-        <v>87.25</v>
+        <v>85.31999969482422</v>
       </c>
       <c r="E172" t="n">
-        <v>87.68000030517578</v>
+        <v>85.84999847412109</v>
       </c>
       <c r="F172" t="n">
-        <v>24014500</v>
+        <v>32747200</v>
       </c>
       <c r="G172" t="n">
         <v>0</v>
@@ -4915,22 +4915,22 @@
     </row>
     <row r="173">
       <c r="A173" s="1" t="n">
-        <v>46169</v>
+        <v>46175</v>
       </c>
       <c r="B173" t="n">
-        <v>87.05000305175781</v>
+        <v>85.61000061035156</v>
       </c>
       <c r="C173" t="n">
-        <v>88.5</v>
+        <v>85.98000335693359</v>
       </c>
       <c r="D173" t="n">
-        <v>86.81999969482422</v>
+        <v>83.29000091552734</v>
       </c>
       <c r="E173" t="n">
-        <v>87.34999847412109</v>
+        <v>83.33000183105469</v>
       </c>
       <c r="F173" t="n">
-        <v>22569500</v>
+        <v>42947200</v>
       </c>
       <c r="G173" t="n">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="174">
       <c r="A174" s="1" t="n">
-        <v>46170</v>
+        <v>46176</v>
       </c>
       <c r="B174" t="n">
-        <v>86.90000152587891</v>
+        <v>82.91000366210938</v>
       </c>
       <c r="C174" t="n">
-        <v>87.04000091552734</v>
+        <v>83.30999755859375</v>
       </c>
       <c r="D174" t="n">
-        <v>85.58999633789062</v>
+        <v>81.09999847412109</v>
       </c>
       <c r="E174" t="n">
-        <v>86.36000061035156</v>
+        <v>81.51999664306641</v>
       </c>
       <c r="F174" t="n">
-        <v>38803800</v>
+        <v>36714700</v>
       </c>
       <c r="G174" t="n">
         <v>0</v>
@@ -4967,22 +4967,22 @@
     </row>
     <row r="175">
       <c r="A175" s="1" t="n">
-        <v>46171</v>
+        <v>46177</v>
       </c>
       <c r="B175" t="n">
-        <v>86.19999694824219</v>
+        <v>83.19000244140625</v>
       </c>
       <c r="C175" t="n">
-        <v>86.66999816894531</v>
+        <v>83.69999694824219</v>
       </c>
       <c r="D175" t="n">
-        <v>85.66000366210938</v>
+        <v>81.37000274658203</v>
       </c>
       <c r="E175" t="n">
-        <v>86.01999664306641</v>
+        <v>81.55999755859375</v>
       </c>
       <c r="F175" t="n">
-        <v>39793600</v>
+        <v>39338800</v>
       </c>
       <c r="G175" t="n">
         <v>0</v>
@@ -4993,22 +4993,22 @@
     </row>
     <row r="176">
       <c r="A176" s="1" t="n">
-        <v>46174</v>
+        <v>46178</v>
       </c>
       <c r="B176" t="n">
-        <v>85.73000335693359</v>
+        <v>82.33000183105469</v>
       </c>
       <c r="C176" t="n">
-        <v>87.23000335693359</v>
+        <v>82.75</v>
       </c>
       <c r="D176" t="n">
-        <v>85.31999969482422</v>
+        <v>81</v>
       </c>
       <c r="E176" t="n">
-        <v>85.84999847412109</v>
+        <v>82.18000030517578</v>
       </c>
       <c r="F176" t="n">
-        <v>32747200</v>
+        <v>43474100</v>
       </c>
       <c r="G176" t="n">
         <v>0</v>
@@ -5019,22 +5019,22 @@
     </row>
     <row r="177">
       <c r="A177" s="1" t="n">
-        <v>46175</v>
+        <v>46181</v>
       </c>
       <c r="B177" t="n">
-        <v>85.61000061035156</v>
+        <v>81.66000366210938</v>
       </c>
       <c r="C177" t="n">
-        <v>85.98000335693359</v>
+        <v>83.08000183105469</v>
       </c>
       <c r="D177" t="n">
-        <v>83.29000091552734</v>
+        <v>81.33999633789062</v>
       </c>
       <c r="E177" t="n">
-        <v>83.33000183105469</v>
+        <v>82.63999938964844</v>
       </c>
       <c r="F177" t="n">
-        <v>42947200</v>
+        <v>33056700</v>
       </c>
       <c r="G177" t="n">
         <v>0</v>
@@ -5045,22 +5045,22 @@
     </row>
     <row r="178">
       <c r="A178" s="1" t="n">
-        <v>46176</v>
+        <v>46182</v>
       </c>
       <c r="B178" t="n">
-        <v>82.91000366210938</v>
+        <v>82.12999725341797</v>
       </c>
       <c r="C178" t="n">
-        <v>83.30999755859375</v>
+        <v>82.33999633789062</v>
       </c>
       <c r="D178" t="n">
-        <v>81.09999847412109</v>
+        <v>81.33999633789062</v>
       </c>
       <c r="E178" t="n">
-        <v>81.51999664306641</v>
+        <v>81.41000366210938</v>
       </c>
       <c r="F178" t="n">
-        <v>36714700</v>
+        <v>34787200</v>
       </c>
       <c r="G178" t="n">
         <v>0</v>
@@ -5071,22 +5071,22 @@
     </row>
     <row r="179">
       <c r="A179" s="1" t="n">
-        <v>46177</v>
+        <v>46183</v>
       </c>
       <c r="B179" t="n">
-        <v>83.19000244140625</v>
+        <v>81.70999908447266</v>
       </c>
       <c r="C179" t="n">
-        <v>83.69999694824219</v>
+        <v>82.75</v>
       </c>
       <c r="D179" t="n">
-        <v>81.37000274658203</v>
+        <v>80.98000335693359</v>
       </c>
       <c r="E179" t="n">
-        <v>81.55999755859375</v>
+        <v>82</v>
       </c>
       <c r="F179" t="n">
-        <v>39338800</v>
+        <v>36304600</v>
       </c>
       <c r="G179" t="n">
         <v>0</v>
@@ -5097,22 +5097,22 @@
     </row>
     <row r="180">
       <c r="A180" s="1" t="n">
-        <v>46178</v>
+        <v>46184</v>
       </c>
       <c r="B180" t="n">
-        <v>82.33000183105469</v>
+        <v>81.87000274658203</v>
       </c>
       <c r="C180" t="n">
-        <v>82.75</v>
+        <v>82.09999847412109</v>
       </c>
       <c r="D180" t="n">
-        <v>81</v>
+        <v>80.08999633789062</v>
       </c>
       <c r="E180" t="n">
-        <v>82.18000030517578</v>
+        <v>81.26999664306641</v>
       </c>
       <c r="F180" t="n">
-        <v>43474100</v>
+        <v>33417600</v>
       </c>
       <c r="G180" t="n">
         <v>0</v>
@@ -5123,22 +5123,22 @@
     </row>
     <row r="181">
       <c r="A181" s="1" t="n">
-        <v>46181</v>
+        <v>46185</v>
       </c>
       <c r="B181" t="n">
-        <v>81.66000366210938</v>
+        <v>81.58000183105469</v>
       </c>
       <c r="C181" t="n">
-        <v>83.08000183105469</v>
+        <v>82</v>
       </c>
       <c r="D181" t="n">
-        <v>81.33999633789062</v>
+        <v>79.27999877929688</v>
       </c>
       <c r="E181" t="n">
-        <v>82.63999938964844</v>
+        <v>80.33999633789062</v>
       </c>
       <c r="F181" t="n">
-        <v>33056700</v>
+        <v>35309700</v>
       </c>
       <c r="G181" t="n">
         <v>0</v>
@@ -5149,22 +5149,22 @@
     </row>
     <row r="182">
       <c r="A182" s="1" t="n">
-        <v>46182</v>
+        <v>46188</v>
       </c>
       <c r="B182" t="n">
-        <v>82.12999725341797</v>
+        <v>80.62000274658203</v>
       </c>
       <c r="C182" t="n">
-        <v>82.33999633789062</v>
+        <v>81.70999908447266</v>
       </c>
       <c r="D182" t="n">
-        <v>81.33999633789062</v>
+        <v>80.45999908447266</v>
       </c>
       <c r="E182" t="n">
-        <v>81.41000366210938</v>
+        <v>81.66999816894531</v>
       </c>
       <c r="F182" t="n">
-        <v>34787200</v>
+        <v>36430800</v>
       </c>
       <c r="G182" t="n">
         <v>0</v>
@@ -5175,22 +5175,22 @@
     </row>
     <row r="183">
       <c r="A183" s="1" t="n">
-        <v>46183</v>
+        <v>46189</v>
       </c>
       <c r="B183" t="n">
-        <v>81.70999908447266</v>
+        <v>81.90000152587891</v>
       </c>
       <c r="C183" t="n">
-        <v>82.75</v>
+        <v>81.93000030517578</v>
       </c>
       <c r="D183" t="n">
-        <v>80.98000335693359</v>
+        <v>77.70999908447266</v>
       </c>
       <c r="E183" t="n">
-        <v>82</v>
+        <v>78.72000122070312</v>
       </c>
       <c r="F183" t="n">
-        <v>36304600</v>
+        <v>65054000</v>
       </c>
       <c r="G183" t="n">
         <v>0</v>
@@ -5201,22 +5201,22 @@
     </row>
     <row r="184">
       <c r="A184" s="1" t="n">
-        <v>46184</v>
+        <v>46190</v>
       </c>
       <c r="B184" t="n">
-        <v>81.87000274658203</v>
+        <v>78.09999847412109</v>
       </c>
       <c r="C184" t="n">
-        <v>82.09999847412109</v>
+        <v>78.44999694824219</v>
       </c>
       <c r="D184" t="n">
-        <v>80.08999633789062</v>
+        <v>76.76000213623047</v>
       </c>
       <c r="E184" t="n">
-        <v>81.26999664306641</v>
+        <v>76.95999908447266</v>
       </c>
       <c r="F184" t="n">
-        <v>33417600</v>
+        <v>50338800</v>
       </c>
       <c r="G184" t="n">
         <v>0</v>
@@ -5227,22 +5227,22 @@
     </row>
     <row r="185">
       <c r="A185" s="1" t="n">
-        <v>46185</v>
+        <v>46191</v>
       </c>
       <c r="B185" t="n">
-        <v>81.58000183105469</v>
+        <v>76.93000030517578</v>
       </c>
       <c r="C185" t="n">
-        <v>82</v>
+        <v>78.23999786376953</v>
       </c>
       <c r="D185" t="n">
-        <v>79.27999877929688</v>
+        <v>76.12000274658203</v>
       </c>
       <c r="E185" t="n">
-        <v>80.33999633789062</v>
+        <v>77.37999725341797</v>
       </c>
       <c r="F185" t="n">
-        <v>35309700</v>
+        <v>91920400</v>
       </c>
       <c r="G185" t="n">
         <v>0</v>
@@ -5253,22 +5253,22 @@
     </row>
     <row r="186">
       <c r="A186" s="1" t="n">
-        <v>46188</v>
+        <v>46195</v>
       </c>
       <c r="B186" t="n">
-        <v>80.62000274658203</v>
+        <v>76.13999938964844</v>
       </c>
       <c r="C186" t="n">
-        <v>81.70999908447266</v>
+        <v>77.08999633789062</v>
       </c>
       <c r="D186" t="n">
-        <v>80.45999908447266</v>
+        <v>71.80999755859375</v>
       </c>
       <c r="E186" t="n">
-        <v>81.66999816894531</v>
+        <v>72.87999725341797</v>
       </c>
       <c r="F186" t="n">
-        <v>36430800</v>
+        <v>82203300</v>
       </c>
       <c r="G186" t="n">
         <v>0</v>
@@ -5279,22 +5279,22 @@
     </row>
     <row r="187">
       <c r="A187" s="1" t="n">
-        <v>46189</v>
+        <v>46196</v>
       </c>
       <c r="B187" t="n">
-        <v>81.90000152587891</v>
+        <v>73.26000213623047</v>
       </c>
       <c r="C187" t="n">
-        <v>81.93000030517578</v>
+        <v>73.95999908447266</v>
       </c>
       <c r="D187" t="n">
-        <v>77.70999908447266</v>
+        <v>72.62999725341797</v>
       </c>
       <c r="E187" t="n">
-        <v>78.72000122070312</v>
+        <v>72.81999969482422</v>
       </c>
       <c r="F187" t="n">
-        <v>65054000</v>
+        <v>50806800</v>
       </c>
       <c r="G187" t="n">
         <v>0</v>
@@ -5305,22 +5305,22 @@
     </row>
     <row r="188">
       <c r="A188" s="1" t="n">
-        <v>46190</v>
+        <v>46197</v>
       </c>
       <c r="B188" t="n">
-        <v>78.09999847412109</v>
+        <v>72.69000244140625</v>
       </c>
       <c r="C188" t="n">
-        <v>78.44999694824219</v>
+        <v>73.44999694824219</v>
       </c>
       <c r="D188" t="n">
-        <v>76.76000213623047</v>
+        <v>71.62999725341797</v>
       </c>
       <c r="E188" t="n">
-        <v>76.95999908447266</v>
+        <v>71.83999633789062</v>
       </c>
       <c r="F188" t="n">
-        <v>50338800</v>
+        <v>48001500</v>
       </c>
       <c r="G188" t="n">
         <v>0</v>
@@ -5331,22 +5331,22 @@
     </row>
     <row r="189">
       <c r="A189" s="1" t="n">
-        <v>46191</v>
+        <v>46198</v>
       </c>
       <c r="B189" t="n">
-        <v>76.93000030517578</v>
+        <v>71.33000183105469</v>
       </c>
       <c r="C189" t="n">
-        <v>78.23999786376953</v>
+        <v>72.94000244140625</v>
       </c>
       <c r="D189" t="n">
-        <v>76.12000274658203</v>
+        <v>70.86000061035156</v>
       </c>
       <c r="E189" t="n">
-        <v>77.37999725341797</v>
+        <v>70.90000152587891</v>
       </c>
       <c r="F189" t="n">
-        <v>91920400</v>
+        <v>44446900</v>
       </c>
       <c r="G189" t="n">
         <v>0</v>
@@ -5357,22 +5357,22 @@
     </row>
     <row r="190">
       <c r="A190" s="1" t="n">
-        <v>46195</v>
+        <v>46199</v>
       </c>
       <c r="B190" t="n">
-        <v>76.13999938964844</v>
+        <v>71.69000244140625</v>
       </c>
       <c r="C190" t="n">
-        <v>77.08999633789062</v>
+        <v>75.19999694824219</v>
       </c>
       <c r="D190" t="n">
-        <v>71.80999755859375</v>
+        <v>71.52999877929688</v>
       </c>
       <c r="E190" t="n">
-        <v>72.87999725341797</v>
+        <v>73.80999755859375</v>
       </c>
       <c r="F190" t="n">
-        <v>82203300</v>
+        <v>74990300</v>
       </c>
       <c r="G190" t="n">
         <v>0</v>
@@ -5383,22 +5383,22 @@
     </row>
     <row r="191">
       <c r="A191" s="1" t="n">
-        <v>46196</v>
+        <v>46202</v>
       </c>
       <c r="B191" t="n">
-        <v>73.26000213623047</v>
+        <v>74.62000274658203</v>
       </c>
       <c r="C191" t="n">
-        <v>73.95999908447266</v>
+        <v>76.06999969482422</v>
       </c>
       <c r="D191" t="n">
-        <v>72.62999725341797</v>
+        <v>73.73000335693359</v>
       </c>
       <c r="E191" t="n">
-        <v>72.81999969482422</v>
+        <v>73.77999877929688</v>
       </c>
       <c r="F191" t="n">
-        <v>50806800</v>
+        <v>42429600</v>
       </c>
       <c r="G191" t="n">
         <v>0</v>
@@ -5409,22 +5409,22 @@
     </row>
     <row r="192">
       <c r="A192" s="1" t="n">
-        <v>46197</v>
+        <v>46203</v>
       </c>
       <c r="B192" t="n">
-        <v>72.69000244140625</v>
+        <v>73.58999633789062</v>
       </c>
       <c r="C192" t="n">
-        <v>73.44999694824219</v>
+        <v>73.75</v>
       </c>
       <c r="D192" t="n">
-        <v>71.62999725341797</v>
+        <v>71</v>
       </c>
       <c r="E192" t="n">
-        <v>71.83999633789062</v>
+        <v>71.40000152587891</v>
       </c>
       <c r="F192" t="n">
-        <v>48001500</v>
+        <v>49240900</v>
       </c>
       <c r="G192" t="n">
         <v>0</v>
@@ -5435,22 +5435,22 @@
     </row>
     <row r="193">
       <c r="A193" s="1" t="n">
-        <v>46198</v>
+        <v>46204</v>
       </c>
       <c r="B193" t="n">
-        <v>71.33000183105469</v>
+        <v>72.58999633789062</v>
       </c>
       <c r="C193" t="n">
-        <v>72.94000244140625</v>
+        <v>74.36000061035156</v>
       </c>
       <c r="D193" t="n">
-        <v>70.86000061035156</v>
+        <v>72.33000183105469</v>
       </c>
       <c r="E193" t="n">
-        <v>70.90000152587891</v>
+        <v>74.19000244140625</v>
       </c>
       <c r="F193" t="n">
-        <v>44446900</v>
+        <v>43841800</v>
       </c>
       <c r="G193" t="n">
         <v>0</v>
@@ -5461,22 +5461,22 @@
     </row>
     <row r="194">
       <c r="A194" s="1" t="n">
-        <v>46199</v>
+        <v>46205</v>
       </c>
       <c r="B194" t="n">
-        <v>71.69000244140625</v>
+        <v>75.08999633789062</v>
       </c>
       <c r="C194" t="n">
-        <v>75.19999694824219</v>
+        <v>78.44000244140625</v>
       </c>
       <c r="D194" t="n">
-        <v>71.52999877929688</v>
+        <v>74.91000366210938</v>
       </c>
       <c r="E194" t="n">
-        <v>73.80999755859375</v>
+        <v>77.65000152587891</v>
       </c>
       <c r="F194" t="n">
-        <v>74990300</v>
+        <v>55456500</v>
       </c>
       <c r="G194" t="n">
         <v>0</v>
@@ -5487,22 +5487,22 @@
     </row>
     <row r="195">
       <c r="A195" s="1" t="n">
-        <v>46202</v>
+        <v>46209</v>
       </c>
       <c r="B195" t="n">
-        <v>74.62000274658203</v>
+        <v>77.08000183105469</v>
       </c>
       <c r="C195" t="n">
-        <v>76.06999969482422</v>
+        <v>77.83999633789062</v>
       </c>
       <c r="D195" t="n">
-        <v>73.73000335693359</v>
+        <v>75.70999908447266</v>
       </c>
       <c r="E195" t="n">
-        <v>73.77999877929688</v>
+        <v>76.01999664306641</v>
       </c>
       <c r="F195" t="n">
-        <v>42429600</v>
+        <v>45056600</v>
       </c>
       <c r="G195" t="n">
         <v>0</v>
@@ -5513,22 +5513,22 @@
     </row>
     <row r="196">
       <c r="A196" s="1" t="n">
-        <v>46203</v>
+        <v>46210</v>
       </c>
       <c r="B196" t="n">
-        <v>73.58999633789062</v>
+        <v>77.87999725341797</v>
       </c>
       <c r="C196" t="n">
-        <v>73.75</v>
+        <v>78.19000244140625</v>
       </c>
       <c r="D196" t="n">
-        <v>71</v>
+        <v>76.09999847412109</v>
       </c>
       <c r="E196" t="n">
-        <v>71.40000152587891</v>
+        <v>76.18000030517578</v>
       </c>
       <c r="F196" t="n">
-        <v>49240900</v>
+        <v>33257300</v>
       </c>
       <c r="G196" t="n">
         <v>0</v>
@@ -5539,22 +5539,22 @@
     </row>
     <row r="197">
       <c r="A197" s="1" t="n">
-        <v>46204</v>
+        <v>46211</v>
       </c>
       <c r="B197" t="n">
-        <v>72.58999633789062</v>
+        <v>76.26999664306641</v>
       </c>
       <c r="C197" t="n">
-        <v>74.36000061035156</v>
+        <v>76.63999938964844</v>
       </c>
       <c r="D197" t="n">
-        <v>72.33000183105469</v>
+        <v>74.88999938964844</v>
       </c>
       <c r="E197" t="n">
-        <v>74.19000244140625</v>
+        <v>75.58999633789062</v>
       </c>
       <c r="F197" t="n">
-        <v>43841800</v>
+        <v>34373500</v>
       </c>
       <c r="G197" t="n">
         <v>0</v>
@@ -5565,22 +5565,22 @@
     </row>
     <row r="198">
       <c r="A198" s="1" t="n">
-        <v>46205</v>
+        <v>46212</v>
       </c>
       <c r="B198" t="n">
-        <v>75.08999633789062</v>
+        <v>74.30000305175781</v>
       </c>
       <c r="C198" t="n">
-        <v>78.44000244140625</v>
+        <v>75.55000305175781</v>
       </c>
       <c r="D198" t="n">
-        <v>74.91000366210938</v>
+        <v>74.01999664306641</v>
       </c>
       <c r="E198" t="n">
-        <v>77.65000152587891</v>
+        <v>75.47000122070312</v>
       </c>
       <c r="F198" t="n">
-        <v>55456500</v>
+        <v>36305700</v>
       </c>
       <c r="G198" t="n">
         <v>0</v>
@@ -5591,22 +5591,22 @@
     </row>
     <row r="199">
       <c r="A199" s="1" t="n">
-        <v>46209</v>
+        <v>46213</v>
       </c>
       <c r="B199" t="n">
-        <v>77.08000183105469</v>
+        <v>75.44000244140625</v>
       </c>
       <c r="C199" t="n">
-        <v>77.83999633789062</v>
+        <v>75.69999694824219</v>
       </c>
       <c r="D199" t="n">
-        <v>75.70999908447266</v>
+        <v>72.51000213623047</v>
       </c>
       <c r="E199" t="n">
-        <v>76.01999664306641</v>
+        <v>73.37000274658203</v>
       </c>
       <c r="F199" t="n">
-        <v>45056600</v>
+        <v>46713900</v>
       </c>
       <c r="G199" t="n">
         <v>0</v>
@@ -5617,22 +5617,22 @@
     </row>
     <row r="200">
       <c r="A200" s="1" t="n">
-        <v>46210</v>
+        <v>46216</v>
       </c>
       <c r="B200" t="n">
-        <v>77.87999725341797</v>
+        <v>73.90000152587891</v>
       </c>
       <c r="C200" t="n">
-        <v>78.19000244140625</v>
+        <v>75.44999694824219</v>
       </c>
       <c r="D200" t="n">
-        <v>76.09999847412109</v>
+        <v>73.70999908447266</v>
       </c>
       <c r="E200" t="n">
-        <v>76.18000030517578</v>
+        <v>73.83000183105469</v>
       </c>
       <c r="F200" t="n">
-        <v>33257300</v>
+        <v>35101800</v>
       </c>
       <c r="G200" t="n">
         <v>0</v>
@@ -5643,22 +5643,22 @@
     </row>
     <row r="201">
       <c r="A201" s="1" t="n">
-        <v>46211</v>
+        <v>46217</v>
       </c>
       <c r="B201" t="n">
-        <v>76.26999664306641</v>
+        <v>72.63999938964844</v>
       </c>
       <c r="C201" t="n">
-        <v>76.63999938964844</v>
+        <v>74.01000213623047</v>
       </c>
       <c r="D201" t="n">
-        <v>74.88999938964844</v>
+        <v>72.27999877929688</v>
       </c>
       <c r="E201" t="n">
-        <v>75.58999633789062</v>
+        <v>73.52999877929688</v>
       </c>
       <c r="F201" t="n">
-        <v>34373500</v>
+        <v>33312100</v>
       </c>
       <c r="G201" t="n">
         <v>0</v>
@@ -5669,22 +5669,22 @@
     </row>
     <row r="202">
       <c r="A202" s="1" t="n">
-        <v>46212</v>
+        <v>46218</v>
       </c>
       <c r="B202" t="n">
-        <v>74.30000305175781</v>
+        <v>73.79000091552734</v>
       </c>
       <c r="C202" t="n">
-        <v>75.55000305175781</v>
+        <v>75.05999755859375</v>
       </c>
       <c r="D202" t="n">
-        <v>74.01999664306641</v>
+        <v>73.12999725341797</v>
       </c>
       <c r="E202" t="n">
-        <v>75.47000122070312</v>
+        <v>73.68000030517578</v>
       </c>
       <c r="F202" t="n">
-        <v>36305700</v>
+        <v>32854300</v>
       </c>
       <c r="G202" t="n">
         <v>0</v>
@@ -5695,22 +5695,22 @@
     </row>
     <row r="203">
       <c r="A203" s="1" t="n">
-        <v>46213</v>
+        <v>46219</v>
       </c>
       <c r="B203" t="n">
-        <v>75.44000244140625</v>
+        <v>73.94999694824219</v>
       </c>
       <c r="C203" t="n">
-        <v>75.69999694824219</v>
+        <v>74.68000030517578</v>
       </c>
       <c r="D203" t="n">
-        <v>72.51000213623047</v>
+        <v>72.94000244140625</v>
       </c>
       <c r="E203" t="n">
-        <v>73.37000274658203</v>
+        <v>74.34999847412109</v>
       </c>
       <c r="F203" t="n">
-        <v>46713900</v>
+        <v>77505200</v>
       </c>
       <c r="G203" t="n">
         <v>0</v>
@@ -5721,22 +5721,22 @@
     </row>
     <row r="204">
       <c r="A204" s="1" t="n">
-        <v>46216</v>
+        <v>46220</v>
       </c>
       <c r="B204" t="n">
-        <v>73.90000152587891</v>
+        <v>65.48000335693359</v>
       </c>
       <c r="C204" t="n">
-        <v>75.44999694824219</v>
+        <v>69.48999786376953</v>
       </c>
       <c r="D204" t="n">
-        <v>73.70999908447266</v>
+        <v>65.08000183105469</v>
       </c>
       <c r="E204" t="n">
-        <v>73.83000183105469</v>
+        <v>68.94999694824219</v>
       </c>
       <c r="F204" t="n">
-        <v>35101800</v>
+        <v>142029200</v>
       </c>
       <c r="G204" t="n">
         <v>0</v>
@@ -5747,22 +5747,22 @@
     </row>
     <row r="205">
       <c r="A205" s="1" t="n">
-        <v>46217</v>
+        <v>46223</v>
       </c>
       <c r="B205" t="n">
-        <v>72.63999938964844</v>
+        <v>68.31999969482422</v>
       </c>
       <c r="C205" t="n">
-        <v>74.01000213623047</v>
+        <v>68.37999725341797</v>
       </c>
       <c r="D205" t="n">
-        <v>72.27999877929688</v>
+        <v>66.69000244140625</v>
       </c>
       <c r="E205" t="n">
-        <v>73.52999877929688</v>
+        <v>67.59999847412109</v>
       </c>
       <c r="F205" t="n">
-        <v>33312100</v>
+        <v>60669100</v>
       </c>
       <c r="G205" t="n">
         <v>0</v>
@@ -5773,22 +5773,22 @@
     </row>
     <row r="206">
       <c r="A206" s="1" t="n">
-        <v>46218</v>
+        <v>46224</v>
       </c>
       <c r="B206" t="n">
-        <v>73.79000091552734</v>
+        <v>67.41999816894531</v>
       </c>
       <c r="C206" t="n">
-        <v>75.05999755859375</v>
+        <v>68.75</v>
       </c>
       <c r="D206" t="n">
-        <v>73.12999725341797</v>
+        <v>66.73000335693359</v>
       </c>
       <c r="E206" t="n">
-        <v>73.68000030517578</v>
+        <v>68.66999816894531</v>
       </c>
       <c r="F206" t="n">
-        <v>32854300</v>
+        <v>56565800</v>
       </c>
       <c r="G206" t="n">
         <v>0</v>
@@ -5799,22 +5799,22 @@
     </row>
     <row r="207">
       <c r="A207" s="1" t="n">
-        <v>46219</v>
+        <v>46225</v>
       </c>
       <c r="B207" t="n">
-        <v>73.94999694824219</v>
+        <v>69.37000274658203</v>
       </c>
       <c r="C207" t="n">
-        <v>74.68000030517578</v>
+        <v>70.56999969482422</v>
       </c>
       <c r="D207" t="n">
-        <v>72.94000244140625</v>
+        <v>68.34999847412109</v>
       </c>
       <c r="E207" t="n">
-        <v>74.34999847412109</v>
+        <v>68.52999877929688</v>
       </c>
       <c r="F207" t="n">
-        <v>77505200</v>
+        <v>44947300</v>
       </c>
       <c r="G207" t="n">
         <v>0</v>
@@ -5825,22 +5825,22 @@
     </row>
     <row r="208">
       <c r="A208" s="1" t="n">
-        <v>46220</v>
+        <v>46226</v>
       </c>
       <c r="B208" t="n">
-        <v>65.48000335693359</v>
+        <v>68.56999969482422</v>
       </c>
       <c r="C208" t="n">
-        <v>69.48999786376953</v>
+        <v>69.36000061035156</v>
       </c>
       <c r="D208" t="n">
-        <v>65.08000183105469</v>
+        <v>67.66999816894531</v>
       </c>
       <c r="E208" t="n">
-        <v>68.94999694824219</v>
+        <v>68.88999938964844</v>
       </c>
       <c r="F208" t="n">
-        <v>142029200</v>
+        <v>45029100</v>
       </c>
       <c r="G208" t="n">
         <v>0</v>
@@ -5851,22 +5851,22 @@
     </row>
     <row r="209">
       <c r="A209" s="1" t="n">
-        <v>46223</v>
+        <v>46227</v>
       </c>
       <c r="B209" t="n">
-        <v>68.31999969482422</v>
+        <v>69.29000091552734</v>
       </c>
       <c r="C209" t="n">
-        <v>68.37999725341797</v>
+        <v>70.68000030517578</v>
       </c>
       <c r="D209" t="n">
-        <v>66.69000244140625</v>
+        <v>67.97000122070312</v>
       </c>
       <c r="E209" t="n">
-        <v>67.59999847412109</v>
+        <v>70.08999633789062</v>
       </c>
       <c r="F209" t="n">
-        <v>60669100</v>
+        <v>37593500</v>
       </c>
       <c r="G209" t="n">
         <v>0</v>
@@ -5877,22 +5877,22 @@
     </row>
     <row r="210">
       <c r="A210" s="1" t="n">
-        <v>46224</v>
+        <v>46230</v>
       </c>
       <c r="B210" t="n">
-        <v>67.41999816894531</v>
+        <v>70.58999633789062</v>
       </c>
       <c r="C210" t="n">
-        <v>68.75</v>
+        <v>71.65000152587891</v>
       </c>
       <c r="D210" t="n">
-        <v>66.73000335693359</v>
+        <v>69.86000061035156</v>
       </c>
       <c r="E210" t="n">
-        <v>68.66999816894531</v>
+        <v>70.40000152587891</v>
       </c>
       <c r="F210" t="n">
-        <v>56565800</v>
+        <v>39090800</v>
       </c>
       <c r="G210" t="n">
         <v>0</v>
@@ -5903,22 +5903,22 @@
     </row>
     <row r="211">
       <c r="A211" s="1" t="n">
-        <v>46225</v>
+        <v>46231</v>
       </c>
       <c r="B211" t="n">
-        <v>69.37000274658203</v>
+        <v>72.06999969482422</v>
       </c>
       <c r="C211" t="n">
-        <v>70.56999969482422</v>
+        <v>73.76000213623047</v>
       </c>
       <c r="D211" t="n">
-        <v>68.34999847412109</v>
+        <v>71.23000335693359</v>
       </c>
       <c r="E211" t="n">
-        <v>68.52999877929688</v>
+        <v>72.38999938964844</v>
       </c>
       <c r="F211" t="n">
-        <v>44947300</v>
+        <v>47160200</v>
       </c>
       <c r="G211" t="n">
         <v>0</v>
@@ -5929,22 +5929,22 @@
     </row>
     <row r="212">
       <c r="A212" s="1" t="n">
-        <v>46226</v>
+        <v>46232</v>
       </c>
       <c r="B212" t="n">
-        <v>68.56999969482422</v>
+        <v>72.19000244140625</v>
       </c>
       <c r="C212" t="n">
-        <v>69.36000061035156</v>
+        <v>73.73999786376953</v>
       </c>
       <c r="D212" t="n">
-        <v>67.66999816894531</v>
+        <v>71.75</v>
       </c>
       <c r="E212" t="n">
-        <v>68.88999938964844</v>
+        <v>73.62999725341797</v>
       </c>
       <c r="F212" t="n">
-        <v>45029100</v>
+        <v>43737600</v>
       </c>
       <c r="G212" t="n">
         <v>0</v>
@@ -5955,22 +5955,22 @@
     </row>
     <row r="213">
       <c r="A213" s="1" t="n">
-        <v>46227</v>
+        <v>46233</v>
       </c>
       <c r="B213" t="n">
-        <v>69.29000091552734</v>
+        <v>71.48000335693359</v>
       </c>
       <c r="C213" t="n">
-        <v>70.68000030517578</v>
+        <v>73.31999969482422</v>
       </c>
       <c r="D213" t="n">
-        <v>67.97000122070312</v>
+        <v>70.55000305175781</v>
       </c>
       <c r="E213" t="n">
-        <v>70.08999633789062</v>
+        <v>73.16999816894531</v>
       </c>
       <c r="F213" t="n">
-        <v>37593500</v>
+        <v>54261000</v>
       </c>
       <c r="G213" t="n">
         <v>0</v>
@@ -5981,22 +5981,22 @@
     </row>
     <row r="214">
       <c r="A214" s="1" t="n">
-        <v>46230</v>
+        <v>46234</v>
       </c>
       <c r="B214" t="n">
-        <v>70.58999633789062</v>
+        <v>71.97000122070312</v>
       </c>
       <c r="C214" t="n">
-        <v>71.65000152587891</v>
+        <v>72.75</v>
       </c>
       <c r="D214" t="n">
-        <v>69.86000061035156</v>
+        <v>71.11000061035156</v>
       </c>
       <c r="E214" t="n">
-        <v>70.40000152587891</v>
+        <v>71.70999908447266</v>
       </c>
       <c r="F214" t="n">
-        <v>39090800</v>
+        <v>35847500</v>
       </c>
       <c r="G214" t="n">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="215">
       <c r="A215" s="1" t="n">
-        <v>46231</v>
+        <v>46237</v>
       </c>
       <c r="B215" t="n">
-        <v>72.06999969482422</v>
+        <v>72.76999664306641</v>
       </c>
       <c r="C215" t="n">
-        <v>73.76000213623047</v>
+        <v>73.94999694824219</v>
       </c>
       <c r="D215" t="n">
-        <v>71.23000335693359</v>
+        <v>72.18000030517578</v>
       </c>
       <c r="E215" t="n">
-        <v>72.38999938964844</v>
+        <v>73.33000183105469</v>
       </c>
       <c r="F215" t="n">
-        <v>47160200</v>
+        <v>33922300</v>
       </c>
       <c r="G215" t="n">
         <v>0</v>
@@ -6033,22 +6033,22 @@
     </row>
     <row r="216">
       <c r="A216" s="1" t="n">
-        <v>46232</v>
+        <v>46238</v>
       </c>
       <c r="B216" t="n">
-        <v>72.19000244140625</v>
+        <v>72.51000213623047</v>
       </c>
       <c r="C216" t="n">
-        <v>73.73999786376953</v>
+        <v>73.75</v>
       </c>
       <c r="D216" t="n">
-        <v>71.75</v>
+        <v>72.30000305175781</v>
       </c>
       <c r="E216" t="n">
-        <v>73.62999725341797</v>
+        <v>73.56999969482422</v>
       </c>
       <c r="F216" t="n">
-        <v>43737600</v>
+        <v>42877900</v>
       </c>
       <c r="G216" t="n">
         <v>0</v>
@@ -6059,22 +6059,22 @@
     </row>
     <row r="217">
       <c r="A217" s="1" t="n">
-        <v>46233</v>
+        <v>46239</v>
       </c>
       <c r="B217" t="n">
-        <v>71.48000335693359</v>
+        <v>75.11000061035156</v>
       </c>
       <c r="C217" t="n">
-        <v>73.31999969482422</v>
+        <v>75.30000305175781</v>
       </c>
       <c r="D217" t="n">
-        <v>70.55000305175781</v>
+        <v>73.16000366210938</v>
       </c>
       <c r="E217" t="n">
-        <v>73.16999816894531</v>
+        <v>74.19999694824219</v>
       </c>
       <c r="F217" t="n">
-        <v>54261000</v>
+        <v>28969400</v>
       </c>
       <c r="G217" t="n">
         <v>0</v>
@@ -6085,22 +6085,22 @@
     </row>
     <row r="218">
       <c r="A218" s="1" t="n">
-        <v>46234</v>
+        <v>46240</v>
       </c>
       <c r="B218" t="n">
-        <v>71.97000122070312</v>
+        <v>75.13999938964844</v>
       </c>
       <c r="C218" t="n">
-        <v>72.75</v>
+        <v>75.20999908447266</v>
       </c>
       <c r="D218" t="n">
-        <v>71.11000061035156</v>
+        <v>73.09999847412109</v>
       </c>
       <c r="E218" t="n">
-        <v>71.70999908447266</v>
+        <v>73.69000244140625</v>
       </c>
       <c r="F218" t="n">
-        <v>35847500</v>
+        <v>28892700</v>
       </c>
       <c r="G218" t="n">
         <v>0</v>
@@ -6111,22 +6111,22 @@
     </row>
     <row r="219">
       <c r="A219" s="1" t="n">
-        <v>46237</v>
+        <v>46241</v>
       </c>
       <c r="B219" t="n">
-        <v>72.76999664306641</v>
+        <v>73.12000274658203</v>
       </c>
       <c r="C219" t="n">
-        <v>73.94999694824219</v>
+        <v>74.5</v>
       </c>
       <c r="D219" t="n">
-        <v>72.18000030517578</v>
+        <v>73.08000183105469</v>
       </c>
       <c r="E219" t="n">
-        <v>73.33000183105469</v>
+        <v>74.13999938964844</v>
       </c>
       <c r="F219" t="n">
-        <v>33922300</v>
+        <v>24819000</v>
       </c>
       <c r="G219" t="n">
         <v>0</v>
@@ -6137,22 +6137,22 @@
     </row>
     <row r="220">
       <c r="A220" s="1" t="n">
-        <v>46238</v>
+        <v>46244</v>
       </c>
       <c r="B220" t="n">
-        <v>72.51000213623047</v>
+        <v>73.80000305175781</v>
       </c>
       <c r="C220" t="n">
-        <v>73.75</v>
+        <v>76.31999969482422</v>
       </c>
       <c r="D220" t="n">
-        <v>72.30000305175781</v>
+        <v>73.56999969482422</v>
       </c>
       <c r="E220" t="n">
-        <v>73.56999969482422</v>
+        <v>76.29000091552734</v>
       </c>
       <c r="F220" t="n">
-        <v>42877900</v>
+        <v>26959900</v>
       </c>
       <c r="G220" t="n">
         <v>0</v>
@@ -6163,22 +6163,22 @@
     </row>
     <row r="221">
       <c r="A221" s="1" t="n">
-        <v>46239</v>
+        <v>46245</v>
       </c>
       <c r="B221" t="n">
-        <v>75.11000061035156</v>
+        <v>76.19999694824219</v>
       </c>
       <c r="C221" t="n">
-        <v>75.30000305175781</v>
+        <v>76.90000152587891</v>
       </c>
       <c r="D221" t="n">
-        <v>73.16000366210938</v>
+        <v>74.48000335693359</v>
       </c>
       <c r="E221" t="n">
-        <v>74.19999694824219</v>
+        <v>74.79000091552734</v>
       </c>
       <c r="F221" t="n">
-        <v>28969400</v>
+        <v>27840500</v>
       </c>
       <c r="G221" t="n">
         <v>0</v>
@@ -6189,22 +6189,22 @@
     </row>
     <row r="222">
       <c r="A222" s="1" t="n">
-        <v>46240</v>
+        <v>46246</v>
       </c>
       <c r="B222" t="n">
-        <v>75.13999938964844</v>
+        <v>74.34999847412109</v>
       </c>
       <c r="C222" t="n">
-        <v>75.20999908447266</v>
+        <v>74.66999816894531</v>
       </c>
       <c r="D222" t="n">
-        <v>73.09999847412109</v>
+        <v>73.56999969482422</v>
       </c>
       <c r="E222" t="n">
-        <v>73.69000244140625</v>
+        <v>74.20999908447266</v>
       </c>
       <c r="F222" t="n">
-        <v>28892700</v>
+        <v>20773100</v>
       </c>
       <c r="G222" t="n">
         <v>0</v>
@@ -6215,22 +6215,22 @@
     </row>
     <row r="223">
       <c r="A223" s="1" t="n">
-        <v>46241</v>
+        <v>46247</v>
       </c>
       <c r="B223" t="n">
-        <v>73.12000274658203</v>
+        <v>76.01000213623047</v>
       </c>
       <c r="C223" t="n">
-        <v>74.5</v>
+        <v>78.40000152587891</v>
       </c>
       <c r="D223" t="n">
-        <v>73.08000183105469</v>
+        <v>75.44000244140625</v>
       </c>
       <c r="E223" t="n">
-        <v>74.13999938964844</v>
+        <v>78.23999786376953</v>
       </c>
       <c r="F223" t="n">
-        <v>24819000</v>
+        <v>41452900</v>
       </c>
       <c r="G223" t="n">
         <v>0</v>
@@ -6241,22 +6241,22 @@
     </row>
     <row r="224">
       <c r="A224" s="1" t="n">
-        <v>46244</v>
+        <v>46248</v>
       </c>
       <c r="B224" t="n">
-        <v>73.80000305175781</v>
+        <v>78.48000335693359</v>
       </c>
       <c r="C224" t="n">
-        <v>76.31999969482422</v>
+        <v>78.73000335693359</v>
       </c>
       <c r="D224" t="n">
-        <v>73.56999969482422</v>
+        <v>77.76000213623047</v>
       </c>
       <c r="E224" t="n">
-        <v>76.29000091552734</v>
+        <v>78.16000366210938</v>
       </c>
       <c r="F224" t="n">
-        <v>26959900</v>
+        <v>26751000</v>
       </c>
       <c r="G224" t="n">
         <v>0</v>
@@ -6267,22 +6267,22 @@
     </row>
     <row r="225">
       <c r="A225" s="1" t="n">
-        <v>46245</v>
+        <v>46251</v>
       </c>
       <c r="B225" t="n">
-        <v>76.19999694824219</v>
+        <v>77.80000305175781</v>
       </c>
       <c r="C225" t="n">
-        <v>76.90000152587891</v>
+        <v>78.52999877929688</v>
       </c>
       <c r="D225" t="n">
-        <v>74.48000335693359</v>
+        <v>75.47000122070312</v>
       </c>
       <c r="E225" t="n">
-        <v>74.79000091552734</v>
+        <v>76.01999664306641</v>
       </c>
       <c r="F225" t="n">
-        <v>27840500</v>
+        <v>30753000</v>
       </c>
       <c r="G225" t="n">
         <v>0</v>
@@ -6293,22 +6293,22 @@
     </row>
     <row r="226">
       <c r="A226" s="1" t="n">
-        <v>46246</v>
+        <v>46252</v>
       </c>
       <c r="B226" t="n">
-        <v>74.34999847412109</v>
+        <v>77.43000030517578</v>
       </c>
       <c r="C226" t="n">
-        <v>74.66999816894531</v>
+        <v>79.09999847412109</v>
       </c>
       <c r="D226" t="n">
-        <v>73.56999969482422</v>
+        <v>76.33999633789062</v>
       </c>
       <c r="E226" t="n">
-        <v>74.20999908447266</v>
+        <v>77.76999664306641</v>
       </c>
       <c r="F226" t="n">
-        <v>20773100</v>
+        <v>36151300</v>
       </c>
       <c r="G226" t="n">
         <v>0</v>
@@ -6319,22 +6319,22 @@
     </row>
     <row r="227">
       <c r="A227" s="1" t="n">
-        <v>46247</v>
+        <v>46253</v>
       </c>
       <c r="B227" t="n">
-        <v>76.01000213623047</v>
+        <v>78.25</v>
       </c>
       <c r="C227" t="n">
-        <v>78.40000152587891</v>
+        <v>81.16000366210938</v>
       </c>
       <c r="D227" t="n">
-        <v>75.44000244140625</v>
+        <v>78.09999847412109</v>
       </c>
       <c r="E227" t="n">
-        <v>78.23999786376953</v>
+        <v>80.22000122070312</v>
       </c>
       <c r="F227" t="n">
-        <v>41452900</v>
+        <v>31461800</v>
       </c>
       <c r="G227" t="n">
         <v>0</v>
@@ -6345,22 +6345,22 @@
     </row>
     <row r="228">
       <c r="A228" s="1" t="n">
-        <v>46248</v>
+        <v>46254</v>
       </c>
       <c r="B228" t="n">
-        <v>78.48000335693359</v>
+        <v>80.13999938964844</v>
       </c>
       <c r="C228" t="n">
-        <v>78.73000335693359</v>
+        <v>81.08000183105469</v>
       </c>
       <c r="D228" t="n">
-        <v>77.76000213623047</v>
+        <v>79.58999633789062</v>
       </c>
       <c r="E228" t="n">
-        <v>78.16000366210938</v>
+        <v>80.13999938964844</v>
       </c>
       <c r="F228" t="n">
-        <v>26751000</v>
+        <v>27118400</v>
       </c>
       <c r="G228" t="n">
         <v>0</v>
@@ -6371,22 +6371,22 @@
     </row>
     <row r="229">
       <c r="A229" s="1" t="n">
-        <v>46251</v>
+        <v>46255</v>
       </c>
       <c r="B229" t="n">
-        <v>77.80000305175781</v>
+        <v>80.29000091552734</v>
       </c>
       <c r="C229" t="n">
-        <v>78.52999877929688</v>
+        <v>80.48999786376953</v>
       </c>
       <c r="D229" t="n">
-        <v>75.47000122070312</v>
+        <v>79.16999816894531</v>
       </c>
       <c r="E229" t="n">
-        <v>76.01999664306641</v>
+        <v>79.58999633789062</v>
       </c>
       <c r="F229" t="n">
-        <v>30753000</v>
+        <v>23773800</v>
       </c>
       <c r="G229" t="n">
         <v>0</v>
@@ -6397,22 +6397,22 @@
     </row>
     <row r="230">
       <c r="A230" s="1" t="n">
-        <v>46252</v>
+        <v>46258</v>
       </c>
       <c r="B230" t="n">
-        <v>77.43000030517578</v>
+        <v>79.94000244140625</v>
       </c>
       <c r="C230" t="n">
-        <v>79.09999847412109</v>
+        <v>80.62000274658203</v>
       </c>
       <c r="D230" t="n">
-        <v>76.33999633789062</v>
+        <v>79.01999664306641</v>
       </c>
       <c r="E230" t="n">
-        <v>77.76999664306641</v>
+        <v>80.01000213623047</v>
       </c>
       <c r="F230" t="n">
-        <v>36151300</v>
+        <v>21085300</v>
       </c>
       <c r="G230" t="n">
         <v>0</v>
@@ -6423,22 +6423,22 @@
     </row>
     <row r="231">
       <c r="A231" s="1" t="n">
-        <v>46253</v>
+        <v>46259</v>
       </c>
       <c r="B231" t="n">
-        <v>78.25</v>
+        <v>79.65000152587891</v>
       </c>
       <c r="C231" t="n">
-        <v>81.16000366210938</v>
+        <v>82.45999908447266</v>
       </c>
       <c r="D231" t="n">
-        <v>78.09999847412109</v>
+        <v>79.40000152587891</v>
       </c>
       <c r="E231" t="n">
-        <v>80.22000122070312</v>
+        <v>82.23000335693359</v>
       </c>
       <c r="F231" t="n">
-        <v>31461800</v>
+        <v>29462000</v>
       </c>
       <c r="G231" t="n">
         <v>0</v>
@@ -6449,22 +6449,22 @@
     </row>
     <row r="232">
       <c r="A232" s="1" t="n">
-        <v>46254</v>
+        <v>46260</v>
       </c>
       <c r="B232" t="n">
-        <v>80.13999938964844</v>
+        <v>82.05000305175781</v>
       </c>
       <c r="C232" t="n">
-        <v>81.08000183105469</v>
+        <v>82.41999816894531</v>
       </c>
       <c r="D232" t="n">
-        <v>79.58999633789062</v>
+        <v>81.30000305175781</v>
       </c>
       <c r="E232" t="n">
-        <v>80.13999938964844</v>
+        <v>81.45999908447266</v>
       </c>
       <c r="F232" t="n">
-        <v>27118400</v>
+        <v>22874900</v>
       </c>
       <c r="G232" t="n">
         <v>0</v>
@@ -6475,22 +6475,22 @@
     </row>
     <row r="233">
       <c r="A233" s="1" t="n">
-        <v>46255</v>
+        <v>46261</v>
       </c>
       <c r="B233" t="n">
-        <v>80.29000091552734</v>
+        <v>81.06999969482422</v>
       </c>
       <c r="C233" t="n">
-        <v>80.48999786376953</v>
+        <v>81.15000152587891</v>
       </c>
       <c r="D233" t="n">
-        <v>79.16999816894531</v>
+        <v>79.27999877929688</v>
       </c>
       <c r="E233" t="n">
-        <v>79.58999633789062</v>
+        <v>79.83999633789062</v>
       </c>
       <c r="F233" t="n">
-        <v>23773800</v>
+        <v>27174400</v>
       </c>
       <c r="G233" t="n">
         <v>0</v>
@@ -6501,22 +6501,22 @@
     </row>
     <row r="234">
       <c r="A234" s="1" t="n">
-        <v>46258</v>
+        <v>46262</v>
       </c>
       <c r="B234" t="n">
-        <v>79.94000244140625</v>
+        <v>80.36000061035156</v>
       </c>
       <c r="C234" t="n">
-        <v>80.62000274658203</v>
+        <v>82.34999847412109</v>
       </c>
       <c r="D234" t="n">
-        <v>79.01999664306641</v>
+        <v>79.94999694824219</v>
       </c>
       <c r="E234" t="n">
-        <v>80.01000213623047</v>
+        <v>81.72000122070312</v>
       </c>
       <c r="F234" t="n">
-        <v>21085300</v>
+        <v>29092700</v>
       </c>
       <c r="G234" t="n">
         <v>0</v>
@@ -6527,22 +6527,22 @@
     </row>
     <row r="235">
       <c r="A235" s="1" t="n">
-        <v>46259</v>
+        <v>46265</v>
       </c>
       <c r="B235" t="n">
-        <v>79.65000152587891</v>
+        <v>81</v>
       </c>
       <c r="C235" t="n">
-        <v>82.45999908447266</v>
+        <v>81.73000335693359</v>
       </c>
       <c r="D235" t="n">
-        <v>79.40000152587891</v>
+        <v>80.65000152587891</v>
       </c>
       <c r="E235" t="n">
-        <v>82.23000335693359</v>
+        <v>81.05000305175781</v>
       </c>
       <c r="F235" t="n">
-        <v>29462000</v>
+        <v>30740800</v>
       </c>
       <c r="G235" t="n">
         <v>0</v>
@@ -6553,22 +6553,22 @@
     </row>
     <row r="236">
       <c r="A236" s="1" t="n">
-        <v>46260</v>
+        <v>46266</v>
       </c>
       <c r="B236" t="n">
-        <v>82.05000305175781</v>
+        <v>80.16999816894531</v>
       </c>
       <c r="C236" t="n">
-        <v>82.41999816894531</v>
+        <v>82.12999725341797</v>
       </c>
       <c r="D236" t="n">
-        <v>81.30000305175781</v>
+        <v>79.59999847412109</v>
       </c>
       <c r="E236" t="n">
-        <v>81.45999908447266</v>
+        <v>80.80999755859375</v>
       </c>
       <c r="F236" t="n">
-        <v>22874900</v>
+        <v>21164900</v>
       </c>
       <c r="G236" t="n">
         <v>0</v>
@@ -6579,22 +6579,22 @@
     </row>
     <row r="237">
       <c r="A237" s="1" t="n">
-        <v>46261</v>
+        <v>46267</v>
       </c>
       <c r="B237" t="n">
-        <v>81.06999969482422</v>
+        <v>80.55000305175781</v>
       </c>
       <c r="C237" t="n">
-        <v>81.15000152587891</v>
+        <v>83.12000274658203</v>
       </c>
       <c r="D237" t="n">
-        <v>79.27999877929688</v>
+        <v>80.30000305175781</v>
       </c>
       <c r="E237" t="n">
-        <v>79.83999633789062</v>
+        <v>82.73000335693359</v>
       </c>
       <c r="F237" t="n">
-        <v>27174400</v>
+        <v>22077800</v>
       </c>
       <c r="G237" t="n">
         <v>0</v>
@@ -6605,22 +6605,22 @@
     </row>
     <row r="238">
       <c r="A238" s="1" t="n">
-        <v>46262</v>
+        <v>46268</v>
       </c>
       <c r="B238" t="n">
-        <v>80.36000061035156</v>
+        <v>83.18000030517578</v>
       </c>
       <c r="C238" t="n">
-        <v>82.34999847412109</v>
+        <v>83.59999847412109</v>
       </c>
       <c r="D238" t="n">
-        <v>79.94999694824219</v>
+        <v>81.62999725341797</v>
       </c>
       <c r="E238" t="n">
-        <v>81.72000122070312</v>
+        <v>82.66999816894531</v>
       </c>
       <c r="F238" t="n">
-        <v>29092700</v>
+        <v>24006400</v>
       </c>
       <c r="G238" t="n">
         <v>0</v>
@@ -6631,22 +6631,22 @@
     </row>
     <row r="239">
       <c r="A239" s="1" t="n">
-        <v>46265</v>
+        <v>46269</v>
       </c>
       <c r="B239" t="n">
-        <v>81</v>
+        <v>82.16999816894531</v>
       </c>
       <c r="C239" t="n">
-        <v>81.73000335693359</v>
+        <v>82.69000244140625</v>
       </c>
       <c r="D239" t="n">
-        <v>80.65000152587891</v>
+        <v>78.23000335693359</v>
       </c>
       <c r="E239" t="n">
-        <v>81.05000305175781</v>
+        <v>78.25</v>
       </c>
       <c r="F239" t="n">
-        <v>30740800</v>
+        <v>40190000</v>
       </c>
       <c r="G239" t="n">
         <v>0</v>
@@ -6657,22 +6657,22 @@
     </row>
     <row r="240">
       <c r="A240" s="1" t="n">
-        <v>46266</v>
+        <v>46273</v>
       </c>
       <c r="B240" t="n">
-        <v>80.16999816894531</v>
+        <v>77.55000305175781</v>
       </c>
       <c r="C240" t="n">
-        <v>82.12999725341797</v>
+        <v>77.73000335693359</v>
       </c>
       <c r="D240" t="n">
-        <v>79.59999847412109</v>
+        <v>75.91999816894531</v>
       </c>
       <c r="E240" t="n">
-        <v>80.80999755859375</v>
+        <v>76.76999664306641</v>
       </c>
       <c r="F240" t="n">
-        <v>21164900</v>
+        <v>33865500</v>
       </c>
       <c r="G240" t="n">
         <v>0</v>
@@ -6683,22 +6683,22 @@
     </row>
     <row r="241">
       <c r="A241" s="1" t="n">
-        <v>46267</v>
+        <v>46274</v>
       </c>
       <c r="B241" t="n">
-        <v>80.55000305175781</v>
+        <v>76.33999633789062</v>
       </c>
       <c r="C241" t="n">
-        <v>83.12000274658203</v>
+        <v>76.72000122070312</v>
       </c>
       <c r="D241" t="n">
-        <v>80.30000305175781</v>
+        <v>75.87000274658203</v>
       </c>
       <c r="E241" t="n">
-        <v>82.73000335693359</v>
+        <v>76.02999877929688</v>
       </c>
       <c r="F241" t="n">
-        <v>22077800</v>
+        <v>22779600</v>
       </c>
       <c r="G241" t="n">
         <v>0</v>
@@ -6709,22 +6709,22 @@
     </row>
     <row r="242">
       <c r="A242" s="1" t="n">
-        <v>46268</v>
+        <v>46275</v>
       </c>
       <c r="B242" t="n">
-        <v>83.18000030517578</v>
+        <v>75.33000183105469</v>
       </c>
       <c r="C242" t="n">
-        <v>83.59999847412109</v>
+        <v>76.30000305175781</v>
       </c>
       <c r="D242" t="n">
-        <v>81.62999725341797</v>
+        <v>75.02999877929688</v>
       </c>
       <c r="E242" t="n">
-        <v>82.66999816894531</v>
+        <v>76.01000213623047</v>
       </c>
       <c r="F242" t="n">
-        <v>24006400</v>
+        <v>20049000</v>
       </c>
       <c r="G242" t="n">
         <v>0</v>
@@ -6735,22 +6735,22 @@
     </row>
     <row r="243">
       <c r="A243" s="1" t="n">
-        <v>46269</v>
+        <v>46276</v>
       </c>
       <c r="B243" t="n">
-        <v>82.16999816894531</v>
+        <v>76.63999938964844</v>
       </c>
       <c r="C243" t="n">
-        <v>82.69000244140625</v>
+        <v>77.56999969482422</v>
       </c>
       <c r="D243" t="n">
-        <v>78.23000335693359</v>
+        <v>76.15000152587891</v>
       </c>
       <c r="E243" t="n">
-        <v>78.25</v>
+        <v>77.40000152587891</v>
       </c>
       <c r="F243" t="n">
-        <v>40190000</v>
+        <v>22237800</v>
       </c>
       <c r="G243" t="n">
         <v>0</v>
@@ -6761,22 +6761,22 @@
     </row>
     <row r="244">
       <c r="A244" s="1" t="n">
-        <v>46273</v>
+        <v>46279</v>
       </c>
       <c r="B244" t="n">
-        <v>77.55000305175781</v>
+        <v>78.97000122070312</v>
       </c>
       <c r="C244" t="n">
-        <v>77.73000335693359</v>
+        <v>81.01999664306641</v>
       </c>
       <c r="D244" t="n">
-        <v>75.91999816894531</v>
+        <v>78.48999786376953</v>
       </c>
       <c r="E244" t="n">
-        <v>76.76999664306641</v>
+        <v>80.31999969482422</v>
       </c>
       <c r="F244" t="n">
-        <v>33865500</v>
+        <v>30945100</v>
       </c>
       <c r="G244" t="n">
         <v>0</v>
@@ -6787,22 +6787,22 @@
     </row>
     <row r="245">
       <c r="A245" s="1" t="n">
-        <v>46274</v>
+        <v>46280</v>
       </c>
       <c r="B245" t="n">
-        <v>76.33999633789062</v>
+        <v>79.37999725341797</v>
       </c>
       <c r="C245" t="n">
-        <v>76.72000122070312</v>
+        <v>79.48000335693359</v>
       </c>
       <c r="D245" t="n">
-        <v>75.87000274658203</v>
+        <v>77.45999908447266</v>
       </c>
       <c r="E245" t="n">
-        <v>76.02999877929688</v>
+        <v>77.90000152587891</v>
       </c>
       <c r="F245" t="n">
-        <v>22779600</v>
+        <v>28027400</v>
       </c>
       <c r="G245" t="n">
         <v>0</v>
@@ -6813,22 +6813,22 @@
     </row>
     <row r="246">
       <c r="A246" s="1" t="n">
-        <v>46275</v>
+        <v>46281</v>
       </c>
       <c r="B246" t="n">
-        <v>75.33000183105469</v>
+        <v>77.73000335693359</v>
       </c>
       <c r="C246" t="n">
-        <v>76.30000305175781</v>
+        <v>77.80000305175781</v>
       </c>
       <c r="D246" t="n">
-        <v>75.02999877929688</v>
+        <v>76.30999755859375</v>
       </c>
       <c r="E246" t="n">
-        <v>76.01000213623047</v>
+        <v>76.41000366210938</v>
       </c>
       <c r="F246" t="n">
-        <v>20049000</v>
+        <v>25376300</v>
       </c>
       <c r="G246" t="n">
         <v>0</v>
@@ -6839,22 +6839,22 @@
     </row>
     <row r="247">
       <c r="A247" s="1" t="n">
-        <v>46276</v>
+        <v>46282</v>
       </c>
       <c r="B247" t="n">
-        <v>76.63999938964844</v>
+        <v>76.91000366210938</v>
       </c>
       <c r="C247" t="n">
-        <v>77.56999969482422</v>
+        <v>76.95999908447266</v>
       </c>
       <c r="D247" t="n">
-        <v>76.15000152587891</v>
+        <v>75.30000305175781</v>
       </c>
       <c r="E247" t="n">
-        <v>77.40000152587891</v>
+        <v>75.30999755859375</v>
       </c>
       <c r="F247" t="n">
-        <v>22237800</v>
+        <v>28167600</v>
       </c>
       <c r="G247" t="n">
         <v>0</v>
@@ -6865,22 +6865,22 @@
     </row>
     <row r="248">
       <c r="A248" s="1" t="n">
-        <v>46279</v>
+        <v>46283</v>
       </c>
       <c r="B248" t="n">
-        <v>78.97000122070312</v>
+        <v>71.26999664306641</v>
       </c>
       <c r="C248" t="n">
-        <v>81.01999664306641</v>
+        <v>72.37999725341797</v>
       </c>
       <c r="D248" t="n">
-        <v>78.48999786376953</v>
+        <v>70.11000061035156</v>
       </c>
       <c r="E248" t="n">
-        <v>80.31999969482422</v>
+        <v>71.79000091552734</v>
       </c>
       <c r="F248" t="n">
-        <v>30945100</v>
+        <v>114413500</v>
       </c>
       <c r="G248" t="n">
         <v>0</v>
@@ -6891,22 +6891,22 @@
     </row>
     <row r="249">
       <c r="A249" s="1" t="n">
-        <v>46280</v>
+        <v>46286</v>
       </c>
       <c r="B249" t="n">
-        <v>79.37999725341797</v>
+        <v>71.81999969482422</v>
       </c>
       <c r="C249" t="n">
-        <v>79.48000335693359</v>
+        <v>73.87000274658203</v>
       </c>
       <c r="D249" t="n">
-        <v>77.45999908447266</v>
+        <v>71.79000091552734</v>
       </c>
       <c r="E249" t="n">
-        <v>77.90000152587891</v>
+        <v>73.36000061035156</v>
       </c>
       <c r="F249" t="n">
-        <v>28027400</v>
+        <v>36948000</v>
       </c>
       <c r="G249" t="n">
         <v>0</v>
@@ -6917,22 +6917,22 @@
     </row>
     <row r="250">
       <c r="A250" s="1" t="n">
-        <v>46281</v>
+        <v>46287</v>
       </c>
       <c r="B250" t="n">
-        <v>77.73000335693359</v>
+        <v>73.69000244140625</v>
       </c>
       <c r="C250" t="n">
-        <v>77.80000305175781</v>
+        <v>73.76000213623047</v>
       </c>
       <c r="D250" t="n">
-        <v>76.30999755859375</v>
+        <v>71.58000183105469</v>
       </c>
       <c r="E250" t="n">
-        <v>76.41000366210938</v>
+        <v>72.16000366210938</v>
       </c>
       <c r="F250" t="n">
-        <v>25376300</v>
+        <v>34372500</v>
       </c>
       <c r="G250" t="n">
         <v>0</v>
@@ -6943,22 +6943,22 @@
     </row>
     <row r="251">
       <c r="A251" s="1" t="n">
-        <v>46282</v>
+        <v>46288</v>
       </c>
       <c r="B251" t="n">
-        <v>76.91000366210938</v>
+        <v>72.08000183105469</v>
       </c>
       <c r="C251" t="n">
-        <v>76.95999908447266</v>
+        <v>72.37000274658203</v>
       </c>
       <c r="D251" t="n">
-        <v>75.30000305175781</v>
+        <v>71.06999969482422</v>
       </c>
       <c r="E251" t="n">
-        <v>75.30999755859375</v>
+        <v>71.36000061035156</v>
       </c>
       <c r="F251" t="n">
-        <v>28167600</v>
+        <v>32807500</v>
       </c>
       <c r="G251" t="n">
         <v>0</v>
@@ -6969,22 +6969,22 @@
     </row>
     <row r="252">
       <c r="A252" s="1" t="n">
-        <v>46283</v>
+        <v>46289</v>
       </c>
       <c r="B252" t="n">
-        <v>71.26999664306641</v>
+        <v>71.62000274658203</v>
       </c>
       <c r="C252" t="n">
-        <v>72.37999725341797</v>
+        <v>72.04000091552734</v>
       </c>
       <c r="D252" t="n">
-        <v>70.11000061035156</v>
+        <v>71.20999908447266</v>
       </c>
       <c r="E252" t="n">
-        <v>71.79000091552734</v>
+        <v>71.72000122070312</v>
       </c>
       <c r="F252" t="n">
-        <v>114273800</v>
+        <v>28189100</v>
       </c>
       <c r="G252" t="n">
         <v>0</v>
@@ -10434,37 +10434,37 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>71.79000000000001</v>
+        <v>71.72</v>
       </c>
       <c r="D2" t="n">
-        <v>75.31</v>
+        <v>71.36</v>
       </c>
       <c r="E2" t="n">
-        <v>71.27</v>
+        <v>71.62</v>
       </c>
       <c r="F2" t="n">
-        <v>72.38</v>
+        <v>72.04000000000001</v>
       </c>
       <c r="G2" t="n">
-        <v>70.11</v>
+        <v>71.20999999999999</v>
       </c>
       <c r="H2" t="n">
-        <v>113606170</v>
+        <v>28121254</v>
       </c>
       <c r="I2" t="n">
-        <v>39983133</v>
+        <v>38506915</v>
       </c>
       <c r="J2" t="n">
-        <v>298929225728</v>
+        <v>298637754368</v>
       </c>
       <c r="K2" t="n">
-        <v>23.69307</v>
+        <v>22.4125</v>
       </c>
       <c r="L2" t="n">
-        <v>18.799002</v>
+        <v>18.808252</v>
       </c>
       <c r="M2" t="n">
-        <v>3.03</v>
+        <v>3.2</v>
       </c>
       <c r="N2" t="n">
         <v>124.86</v>
@@ -10502,7 +10502,7 @@
         <v>7.241</v>
       </c>
       <c r="Y2" t="n">
-        <v>9.914376000000001</v>
+        <v>9.904709</v>
       </c>
       <c r="Z2" t="n">
         <v>0.111</v>
@@ -10514,7 +10514,7 @@
         <v>48370765824</v>
       </c>
       <c r="AC2" t="n">
-        <v>306455969792</v>
+        <v>306164498432</v>
       </c>
       <c r="AD2" t="n">
         <v>14726931456</v>
@@ -10541,7 +10541,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>2026-09-19 15:21:44</t>
+          <t>2026-09-25 14:29:31</t>
         </is>
       </c>
     </row>

--- a/data/NFLX_data.xlsx
+++ b/data/NFLX_data.xlsx
@@ -469,22 +469,22 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45925</v>
+        <v>45926</v>
       </c>
       <c r="B2" t="n">
-        <v>120.3089981079102</v>
+        <v>120.5419998168945</v>
       </c>
       <c r="C2" t="n">
-        <v>121.6839981079102</v>
+        <v>121.4000015258789</v>
       </c>
       <c r="D2" t="n">
-        <v>119.1510009765625</v>
+        <v>120</v>
       </c>
       <c r="E2" t="n">
-        <v>120.8239974975586</v>
+        <v>121.0609970092773</v>
       </c>
       <c r="F2" t="n">
-        <v>19978000</v>
+        <v>19450000</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -495,22 +495,22 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45926</v>
+        <v>45929</v>
       </c>
       <c r="B3" t="n">
-        <v>120.5419998168945</v>
+        <v>120.5</v>
       </c>
       <c r="C3" t="n">
-        <v>121.4000015258789</v>
+        <v>122.4489974975586</v>
       </c>
       <c r="D3" t="n">
-        <v>120</v>
+        <v>118.7539978027344</v>
       </c>
       <c r="E3" t="n">
-        <v>121.0609970092773</v>
+        <v>120.640998840332</v>
       </c>
       <c r="F3" t="n">
-        <v>19450000</v>
+        <v>30332000</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -521,22 +521,22 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="B4" t="n">
-        <v>120.5</v>
+        <v>120.640998840332</v>
       </c>
       <c r="C4" t="n">
-        <v>122.4489974975586</v>
+        <v>120.8499984741211</v>
       </c>
       <c r="D4" t="n">
-        <v>118.7539978027344</v>
+        <v>117.8000030517578</v>
       </c>
       <c r="E4" t="n">
-        <v>120.640998840332</v>
+        <v>119.8919982910156</v>
       </c>
       <c r="F4" t="n">
-        <v>30332000</v>
+        <v>38303000</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -547,22 +547,22 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>45930</v>
+        <v>45931</v>
       </c>
       <c r="B5" t="n">
-        <v>120.640998840332</v>
+        <v>117.5490036010742</v>
       </c>
       <c r="C5" t="n">
-        <v>120.8499984741211</v>
+        <v>117.9140014648438</v>
       </c>
       <c r="D5" t="n">
-        <v>117.8000030517578</v>
+        <v>116.3209991455078</v>
       </c>
       <c r="E5" t="n">
-        <v>119.8919982910156</v>
+        <v>117.0899963378906</v>
       </c>
       <c r="F5" t="n">
-        <v>38303000</v>
+        <v>41102000</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -573,22 +573,22 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>45931</v>
+        <v>45932</v>
       </c>
       <c r="B6" t="n">
-        <v>117.5490036010742</v>
+        <v>116.1500015258789</v>
       </c>
       <c r="C6" t="n">
-        <v>117.9140014648438</v>
+        <v>116.3330001831055</v>
       </c>
       <c r="D6" t="n">
-        <v>116.3209991455078</v>
+        <v>113.4000015258789</v>
       </c>
       <c r="E6" t="n">
-        <v>117.0899963378906</v>
+        <v>116.2529983520508</v>
       </c>
       <c r="F6" t="n">
-        <v>41102000</v>
+        <v>46855000</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -599,22 +599,22 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>45932</v>
+        <v>45933</v>
       </c>
       <c r="B7" t="n">
-        <v>116.1500015258789</v>
+        <v>116.5</v>
       </c>
       <c r="C7" t="n">
-        <v>116.3330001831055</v>
+        <v>116.8000030517578</v>
       </c>
       <c r="D7" t="n">
-        <v>113.4000015258789</v>
+        <v>114.3219985961914</v>
       </c>
       <c r="E7" t="n">
-        <v>116.2529983520508</v>
+        <v>115.3320007324219</v>
       </c>
       <c r="F7" t="n">
-        <v>46855000</v>
+        <v>31374000</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -625,22 +625,22 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>45933</v>
+        <v>45936</v>
       </c>
       <c r="B8" t="n">
-        <v>116.5</v>
+        <v>116.0370025634766</v>
       </c>
       <c r="C8" t="n">
-        <v>116.8000030517578</v>
+        <v>116.3580017089844</v>
       </c>
       <c r="D8" t="n">
-        <v>114.3219985961914</v>
+        <v>114.5449981689453</v>
       </c>
       <c r="E8" t="n">
-        <v>115.3320007324219</v>
+        <v>116.3310012817383</v>
       </c>
       <c r="F8" t="n">
-        <v>31374000</v>
+        <v>29686000</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -651,22 +651,22 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>45936</v>
+        <v>45937</v>
       </c>
       <c r="B9" t="n">
-        <v>116.0370025634766</v>
+        <v>117.7789993286133</v>
       </c>
       <c r="C9" t="n">
-        <v>116.3580017089844</v>
+        <v>120.1370010375977</v>
       </c>
       <c r="D9" t="n">
-        <v>114.5449981689453</v>
+        <v>117.7460021972656</v>
       </c>
       <c r="E9" t="n">
-        <v>116.3310012817383</v>
+        <v>119.1060028076172</v>
       </c>
       <c r="F9" t="n">
-        <v>29686000</v>
+        <v>33091000</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -677,22 +677,22 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>45937</v>
+        <v>45938</v>
       </c>
       <c r="B10" t="n">
-        <v>117.7789993286133</v>
+        <v>119.7109985351562</v>
       </c>
       <c r="C10" t="n">
-        <v>120.1370010375977</v>
+        <v>121.7389984130859</v>
       </c>
       <c r="D10" t="n">
-        <v>117.7460021972656</v>
+        <v>119.1999969482422</v>
       </c>
       <c r="E10" t="n">
-        <v>119.1060028076172</v>
+        <v>121.4250030517578</v>
       </c>
       <c r="F10" t="n">
-        <v>33091000</v>
+        <v>28514000</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -703,22 +703,22 @@
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>45938</v>
+        <v>45939</v>
       </c>
       <c r="B11" t="n">
-        <v>119.7109985351562</v>
+        <v>121.4250030517578</v>
       </c>
       <c r="C11" t="n">
-        <v>121.7389984130859</v>
+        <v>123.75</v>
       </c>
       <c r="D11" t="n">
-        <v>119.1999969482422</v>
+        <v>121.181999206543</v>
       </c>
       <c r="E11" t="n">
-        <v>121.4250030517578</v>
+        <v>123.1070022583008</v>
       </c>
       <c r="F11" t="n">
-        <v>28514000</v>
+        <v>28241000</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -729,22 +729,22 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>45939</v>
+        <v>45940</v>
       </c>
       <c r="B12" t="n">
-        <v>121.4250030517578</v>
+        <v>122.9000015258789</v>
       </c>
       <c r="C12" t="n">
-        <v>123.75</v>
+        <v>124.6999969482422</v>
       </c>
       <c r="D12" t="n">
-        <v>121.181999206543</v>
+        <v>121.9100036621094</v>
       </c>
       <c r="E12" t="n">
-        <v>123.1070022583008</v>
+        <v>122.0080032348633</v>
       </c>
       <c r="F12" t="n">
-        <v>28241000</v>
+        <v>42798000</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -755,22 +755,22 @@
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>45940</v>
+        <v>45943</v>
       </c>
       <c r="B13" t="n">
-        <v>122.9000015258789</v>
+        <v>122.1350021362305</v>
       </c>
       <c r="C13" t="n">
-        <v>124.6999969482422</v>
+        <v>123.1119995117188</v>
       </c>
       <c r="D13" t="n">
-        <v>121.9100036621094</v>
+        <v>120.6809997558594</v>
       </c>
       <c r="E13" t="n">
-        <v>122.0080032348633</v>
+        <v>121.9029998779297</v>
       </c>
       <c r="F13" t="n">
-        <v>42798000</v>
+        <v>24608000</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -781,22 +781,22 @@
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>45943</v>
+        <v>45944</v>
       </c>
       <c r="B14" t="n">
-        <v>122.1350021362305</v>
+        <v>121.4749984741211</v>
       </c>
       <c r="C14" t="n">
-        <v>123.1119995117188</v>
+        <v>122.4290008544922</v>
       </c>
       <c r="D14" t="n">
-        <v>120.6809997558594</v>
+        <v>120.3099975585938</v>
       </c>
       <c r="E14" t="n">
-        <v>121.9029998779297</v>
+        <v>121.5350036621094</v>
       </c>
       <c r="F14" t="n">
-        <v>24608000</v>
+        <v>23624000</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -807,22 +807,22 @@
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>45944</v>
+        <v>45945</v>
       </c>
       <c r="B15" t="n">
-        <v>121.4749984741211</v>
+        <v>121.3010025024414</v>
       </c>
       <c r="C15" t="n">
-        <v>122.4290008544922</v>
+        <v>121.9619979858398</v>
       </c>
       <c r="D15" t="n">
-        <v>120.3099975585938</v>
+        <v>120.161003112793</v>
       </c>
       <c r="E15" t="n">
-        <v>121.5350036621094</v>
+        <v>120.3290023803711</v>
       </c>
       <c r="F15" t="n">
-        <v>23624000</v>
+        <v>20252000</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -833,22 +833,22 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>45945</v>
+        <v>45946</v>
       </c>
       <c r="B16" t="n">
-        <v>121.3010025024414</v>
+        <v>121.2149963378906</v>
       </c>
       <c r="C16" t="n">
-        <v>121.9619979858398</v>
+        <v>121.6709976196289</v>
       </c>
       <c r="D16" t="n">
-        <v>120.161003112793</v>
+        <v>117.5999984741211</v>
       </c>
       <c r="E16" t="n">
-        <v>120.3290023803711</v>
+        <v>118.359001159668</v>
       </c>
       <c r="F16" t="n">
-        <v>20252000</v>
+        <v>28326000</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -859,22 +859,22 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>45946</v>
+        <v>45947</v>
       </c>
       <c r="B17" t="n">
-        <v>121.2149963378906</v>
+        <v>118.3600006103516</v>
       </c>
       <c r="C17" t="n">
-        <v>121.6709976196289</v>
+        <v>120.3119964599609</v>
       </c>
       <c r="D17" t="n">
-        <v>117.5999984741211</v>
+        <v>117.8949966430664</v>
       </c>
       <c r="E17" t="n">
-        <v>118.359001159668</v>
+        <v>119.9359970092773</v>
       </c>
       <c r="F17" t="n">
-        <v>28326000</v>
+        <v>29571000</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -885,22 +885,22 @@
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>45947</v>
+        <v>45950</v>
       </c>
       <c r="B18" t="n">
-        <v>118.3600006103516</v>
+        <v>120.7880020141602</v>
       </c>
       <c r="C18" t="n">
-        <v>120.3119964599609</v>
+        <v>124.7760009765625</v>
       </c>
       <c r="D18" t="n">
-        <v>117.8949966430664</v>
+        <v>120.6900024414062</v>
       </c>
       <c r="E18" t="n">
-        <v>119.9359970092773</v>
+        <v>123.8560028076172</v>
       </c>
       <c r="F18" t="n">
-        <v>29571000</v>
+        <v>39862000</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -911,22 +911,22 @@
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>45950</v>
+        <v>45951</v>
       </c>
       <c r="B19" t="n">
-        <v>120.7880020141602</v>
+        <v>124.2829971313477</v>
       </c>
       <c r="C19" t="n">
-        <v>124.7760009765625</v>
+        <v>124.8600006103516</v>
       </c>
       <c r="D19" t="n">
-        <v>120.6900024414062</v>
+        <v>123.1760025024414</v>
       </c>
       <c r="E19" t="n">
-        <v>123.8560028076172</v>
+        <v>124.1350021362305</v>
       </c>
       <c r="F19" t="n">
-        <v>39862000</v>
+        <v>65082000</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -937,22 +937,22 @@
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>45951</v>
+        <v>45952</v>
       </c>
       <c r="B20" t="n">
-        <v>124.2829971313477</v>
+        <v>114.2900009155273</v>
       </c>
       <c r="C20" t="n">
-        <v>124.8600006103516</v>
+        <v>115.7600021362305</v>
       </c>
       <c r="D20" t="n">
-        <v>123.1760025024414</v>
+        <v>111.2509994506836</v>
       </c>
       <c r="E20" t="n">
-        <v>124.1350021362305</v>
+        <v>111.6370010375977</v>
       </c>
       <c r="F20" t="n">
-        <v>65082000</v>
+        <v>147890000</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -963,22 +963,22 @@
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>45952</v>
+        <v>45953</v>
       </c>
       <c r="B21" t="n">
-        <v>114.2900009155273</v>
+        <v>112.6900024414062</v>
       </c>
       <c r="C21" t="n">
-        <v>115.7600021362305</v>
+        <v>112.7829971313477</v>
       </c>
       <c r="D21" t="n">
-        <v>111.2509994506836</v>
+        <v>109.9729995727539</v>
       </c>
       <c r="E21" t="n">
-        <v>111.6370010375977</v>
+        <v>111.359001159668</v>
       </c>
       <c r="F21" t="n">
-        <v>147890000</v>
+        <v>68497000</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -989,22 +989,22 @@
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>45953</v>
+        <v>45954</v>
       </c>
       <c r="B22" t="n">
-        <v>112.6900024414062</v>
+        <v>111.0999984741211</v>
       </c>
       <c r="C22" t="n">
-        <v>112.7829971313477</v>
+        <v>111.4509963989258</v>
       </c>
       <c r="D22" t="n">
-        <v>109.9729995727539</v>
+        <v>109.4410018920898</v>
       </c>
       <c r="E22" t="n">
-        <v>111.359001159668</v>
+        <v>109.4690017700195</v>
       </c>
       <c r="F22" t="n">
-        <v>68497000</v>
+        <v>60280000</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -1015,22 +1015,22 @@
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>45954</v>
+        <v>45957</v>
       </c>
       <c r="B23" t="n">
-        <v>111.0999984741211</v>
+        <v>110.0670013427734</v>
       </c>
       <c r="C23" t="n">
-        <v>111.4509963989258</v>
+        <v>110.2279968261719</v>
       </c>
       <c r="D23" t="n">
-        <v>109.4410018920898</v>
+        <v>108.7300033569336</v>
       </c>
       <c r="E23" t="n">
-        <v>109.4690017700195</v>
+        <v>109.4560012817383</v>
       </c>
       <c r="F23" t="n">
-        <v>60280000</v>
+        <v>46911000</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -1041,22 +1041,22 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>45957</v>
+        <v>45958</v>
       </c>
       <c r="B24" t="n">
-        <v>110.0670013427734</v>
+        <v>109.4000015258789</v>
       </c>
       <c r="C24" t="n">
-        <v>110.2279968261719</v>
+        <v>111.697998046875</v>
       </c>
       <c r="D24" t="n">
-        <v>108.7300033569336</v>
+        <v>109.3010025024414</v>
       </c>
       <c r="E24" t="n">
-        <v>109.4560012817383</v>
+        <v>110.25</v>
       </c>
       <c r="F24" t="n">
-        <v>46911000</v>
+        <v>40209000</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -1067,22 +1067,22 @@
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>45958</v>
+        <v>45959</v>
       </c>
       <c r="B25" t="n">
-        <v>109.4000015258789</v>
+        <v>109.984001159668</v>
       </c>
       <c r="C25" t="n">
-        <v>111.697998046875</v>
+        <v>110.8550033569336</v>
       </c>
       <c r="D25" t="n">
-        <v>109.3010025024414</v>
+        <v>109.5999984741211</v>
       </c>
       <c r="E25" t="n">
-        <v>110.25</v>
+        <v>110.0410003662109</v>
       </c>
       <c r="F25" t="n">
-        <v>40209000</v>
+        <v>33995000</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -1093,22 +1093,22 @@
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>45959</v>
+        <v>45960</v>
       </c>
       <c r="B26" t="n">
-        <v>109.984001159668</v>
+        <v>109.4400024414062</v>
       </c>
       <c r="C26" t="n">
-        <v>110.8550033569336</v>
+        <v>110.6159973144531</v>
       </c>
       <c r="D26" t="n">
-        <v>109.5999984741211</v>
+        <v>108.8109970092773</v>
       </c>
       <c r="E26" t="n">
-        <v>110.0410003662109</v>
+        <v>108.9000015258789</v>
       </c>
       <c r="F26" t="n">
-        <v>33995000</v>
+        <v>41581000</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -1119,22 +1119,22 @@
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>45960</v>
+        <v>45961</v>
       </c>
       <c r="B27" t="n">
-        <v>109.4400024414062</v>
+        <v>110.5390014648438</v>
       </c>
       <c r="C27" t="n">
-        <v>110.6159973144531</v>
+        <v>113.4879989624023</v>
       </c>
       <c r="D27" t="n">
-        <v>108.8109970092773</v>
+        <v>110.197998046875</v>
       </c>
       <c r="E27" t="n">
-        <v>108.9000015258789</v>
+        <v>111.8860015869141</v>
       </c>
       <c r="F27" t="n">
-        <v>41581000</v>
+        <v>68665000</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -1145,22 +1145,22 @@
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>45961</v>
+        <v>45964</v>
       </c>
       <c r="B28" t="n">
-        <v>110.5390014648438</v>
+        <v>113.3239974975586</v>
       </c>
       <c r="C28" t="n">
-        <v>113.4879989624023</v>
+        <v>113.3499984741211</v>
       </c>
       <c r="D28" t="n">
-        <v>110.197998046875</v>
+        <v>107.5149993896484</v>
       </c>
       <c r="E28" t="n">
-        <v>111.8860015869141</v>
+        <v>110.0090026855469</v>
       </c>
       <c r="F28" t="n">
-        <v>68665000</v>
+        <v>58634000</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
@@ -1171,22 +1171,22 @@
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>45964</v>
+        <v>45965</v>
       </c>
       <c r="B29" t="n">
-        <v>113.3239974975586</v>
+        <v>109.9990005493164</v>
       </c>
       <c r="C29" t="n">
-        <v>113.3499984741211</v>
+        <v>110.4599990844727</v>
       </c>
       <c r="D29" t="n">
-        <v>107.5149993896484</v>
+        <v>108.6679992675781</v>
       </c>
       <c r="E29" t="n">
-        <v>110.0090026855469</v>
+        <v>109.2959976196289</v>
       </c>
       <c r="F29" t="n">
-        <v>58634000</v>
+        <v>38718000</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -1197,22 +1197,22 @@
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>45965</v>
+        <v>45966</v>
       </c>
       <c r="B30" t="n">
-        <v>109.9990005493164</v>
+        <v>108.5</v>
       </c>
       <c r="C30" t="n">
-        <v>110.4599990844727</v>
+        <v>110.0849990844727</v>
       </c>
       <c r="D30" t="n">
-        <v>108.6679992675781</v>
+        <v>107.3369979858398</v>
       </c>
       <c r="E30" t="n">
-        <v>109.2959976196289</v>
+        <v>109.8460006713867</v>
       </c>
       <c r="F30" t="n">
-        <v>38718000</v>
+        <v>35539000</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -1223,22 +1223,22 @@
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>45966</v>
+        <v>45967</v>
       </c>
       <c r="B31" t="n">
-        <v>108.5</v>
+        <v>109.4580001831055</v>
       </c>
       <c r="C31" t="n">
-        <v>110.0849990844727</v>
+        <v>110.370002746582</v>
       </c>
       <c r="D31" t="n">
-        <v>107.3369979858398</v>
+        <v>108.5130004882812</v>
       </c>
       <c r="E31" t="n">
-        <v>109.8460006713867</v>
+        <v>109.7020034790039</v>
       </c>
       <c r="F31" t="n">
-        <v>35539000</v>
+        <v>36532000</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -1249,22 +1249,22 @@
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>45967</v>
+        <v>45968</v>
       </c>
       <c r="B32" t="n">
-        <v>109.4580001831055</v>
+        <v>109.4179992675781</v>
       </c>
       <c r="C32" t="n">
-        <v>110.370002746582</v>
+        <v>110.8219985961914</v>
       </c>
       <c r="D32" t="n">
-        <v>108.5130004882812</v>
+        <v>108.75</v>
       </c>
       <c r="E32" t="n">
-        <v>109.7020034790039</v>
+        <v>110.3659973144531</v>
       </c>
       <c r="F32" t="n">
-        <v>36532000</v>
+        <v>44125000</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
@@ -1275,22 +1275,22 @@
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>45968</v>
+        <v>45971</v>
       </c>
       <c r="B33" t="n">
-        <v>109.4179992675781</v>
+        <v>110.6719970703125</v>
       </c>
       <c r="C33" t="n">
-        <v>110.8219985961914</v>
+        <v>112.8199996948242</v>
       </c>
       <c r="D33" t="n">
-        <v>108.75</v>
+        <v>110.4049987792969</v>
       </c>
       <c r="E33" t="n">
-        <v>110.3659973144531</v>
+        <v>112.0070037841797</v>
       </c>
       <c r="F33" t="n">
-        <v>44125000</v>
+        <v>36929000</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -1301,22 +1301,22 @@
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>45971</v>
+        <v>45972</v>
       </c>
       <c r="B34" t="n">
-        <v>110.6719970703125</v>
+        <v>111.7600021362305</v>
       </c>
       <c r="C34" t="n">
-        <v>112.8199996948242</v>
+        <v>113.9219970703125</v>
       </c>
       <c r="D34" t="n">
-        <v>110.4049987792969</v>
+        <v>111.2799987792969</v>
       </c>
       <c r="E34" t="n">
-        <v>112.0070037841797</v>
+        <v>113.6439971923828</v>
       </c>
       <c r="F34" t="n">
-        <v>36929000</v>
+        <v>27966000</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
@@ -1327,22 +1327,22 @@
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>45972</v>
+        <v>45973</v>
       </c>
       <c r="B35" t="n">
-        <v>111.7600021362305</v>
+        <v>113.8170013427734</v>
       </c>
       <c r="C35" t="n">
-        <v>113.9219970703125</v>
+        <v>116.4339981079102</v>
       </c>
       <c r="D35" t="n">
-        <v>111.2799987792969</v>
+        <v>112.8259963989258</v>
       </c>
       <c r="E35" t="n">
-        <v>113.6439971923828</v>
+        <v>115.75</v>
       </c>
       <c r="F35" t="n">
-        <v>27966000</v>
+        <v>39221000</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
@@ -1353,22 +1353,22 @@
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>45973</v>
+        <v>45974</v>
       </c>
       <c r="B36" t="n">
-        <v>113.8170013427734</v>
+        <v>115.8499984741211</v>
       </c>
       <c r="C36" t="n">
-        <v>116.4339981079102</v>
+        <v>116.7330017089844</v>
       </c>
       <c r="D36" t="n">
-        <v>112.8259963989258</v>
+        <v>114.5690002441406</v>
       </c>
       <c r="E36" t="n">
-        <v>115.75</v>
+        <v>115.4229965209961</v>
       </c>
       <c r="F36" t="n">
-        <v>39221000</v>
+        <v>40144000</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -1379,22 +1379,22 @@
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>45974</v>
+        <v>45975</v>
       </c>
       <c r="B37" t="n">
-        <v>115.8499984741211</v>
+        <v>114.2730026245117</v>
       </c>
       <c r="C37" t="n">
-        <v>116.7330017089844</v>
+        <v>114.2730026245117</v>
       </c>
       <c r="D37" t="n">
-        <v>114.5690002441406</v>
+        <v>110.7210006713867</v>
       </c>
       <c r="E37" t="n">
-        <v>115.4229965209961</v>
+        <v>111.2170028686523</v>
       </c>
       <c r="F37" t="n">
-        <v>40144000</v>
+        <v>47607000</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
@@ -1405,74 +1405,74 @@
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>45975</v>
+        <v>45978</v>
       </c>
       <c r="B38" t="n">
-        <v>114.2730026245117</v>
+        <v>110.75</v>
       </c>
       <c r="C38" t="n">
-        <v>114.2730026245117</v>
+        <v>111.8499984741211</v>
       </c>
       <c r="D38" t="n">
-        <v>110.7210006713867</v>
+        <v>109.5500030517578</v>
       </c>
       <c r="E38" t="n">
-        <v>111.2170028686523</v>
+        <v>110.2900009155273</v>
       </c>
       <c r="F38" t="n">
-        <v>47607000</v>
+        <v>26082700</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>45978</v>
+        <v>45979</v>
       </c>
       <c r="B39" t="n">
-        <v>110.75</v>
+        <v>110.2900009155273</v>
       </c>
       <c r="C39" t="n">
-        <v>111.8499984741211</v>
+        <v>115.25</v>
       </c>
       <c r="D39" t="n">
-        <v>109.5500030517578</v>
+        <v>109.1999969482422</v>
       </c>
       <c r="E39" t="n">
-        <v>110.2900009155273</v>
+        <v>114.0899963378906</v>
       </c>
       <c r="F39" t="n">
-        <v>26082700</v>
+        <v>43440600</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>45979</v>
+        <v>45980</v>
       </c>
       <c r="B40" t="n">
-        <v>110.2900009155273</v>
+        <v>113</v>
       </c>
       <c r="C40" t="n">
-        <v>115.25</v>
+        <v>113.3399963378906</v>
       </c>
       <c r="D40" t="n">
-        <v>109.1999969482422</v>
+        <v>108.6100006103516</v>
       </c>
       <c r="E40" t="n">
-        <v>114.0899963378906</v>
+        <v>110</v>
       </c>
       <c r="F40" t="n">
-        <v>43440600</v>
+        <v>31868100</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
@@ -1483,22 +1483,22 @@
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>45980</v>
+        <v>45981</v>
       </c>
       <c r="B41" t="n">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C41" t="n">
-        <v>113.3399963378906</v>
+        <v>111.0999984741211</v>
       </c>
       <c r="D41" t="n">
-        <v>108.6100006103516</v>
+        <v>105.3899993896484</v>
       </c>
       <c r="E41" t="n">
-        <v>110</v>
+        <v>105.6699981689453</v>
       </c>
       <c r="F41" t="n">
-        <v>31868100</v>
+        <v>36918500</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
@@ -1509,22 +1509,22 @@
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>45981</v>
+        <v>45982</v>
       </c>
       <c r="B42" t="n">
-        <v>111</v>
+        <v>105.129997253418</v>
       </c>
       <c r="C42" t="n">
-        <v>111.0999984741211</v>
+        <v>106.5299987792969</v>
       </c>
       <c r="D42" t="n">
-        <v>105.3899993896484</v>
+        <v>103.8099975585938</v>
       </c>
       <c r="E42" t="n">
-        <v>105.6699981689453</v>
+        <v>104.3099975585938</v>
       </c>
       <c r="F42" t="n">
-        <v>36918500</v>
+        <v>41232700</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
@@ -1535,22 +1535,22 @@
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>45982</v>
+        <v>45985</v>
       </c>
       <c r="B43" t="n">
-        <v>105.129997253418</v>
+        <v>104.25</v>
       </c>
       <c r="C43" t="n">
-        <v>106.5299987792969</v>
+        <v>108.0400009155273</v>
       </c>
       <c r="D43" t="n">
-        <v>103.8099975585938</v>
+        <v>103.3199996948242</v>
       </c>
       <c r="E43" t="n">
-        <v>104.3099975585938</v>
+        <v>106.9700012207031</v>
       </c>
       <c r="F43" t="n">
-        <v>41232700</v>
+        <v>62918300</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
@@ -1561,22 +1561,22 @@
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
-        <v>45985</v>
+        <v>45986</v>
       </c>
       <c r="B44" t="n">
-        <v>104.25</v>
+        <v>106.120002746582</v>
       </c>
       <c r="C44" t="n">
-        <v>108.0400009155273</v>
+        <v>106.3000030517578</v>
       </c>
       <c r="D44" t="n">
-        <v>103.3199996948242</v>
+        <v>103.8199996948242</v>
       </c>
       <c r="E44" t="n">
-        <v>106.9700012207031</v>
+        <v>104.4000015258789</v>
       </c>
       <c r="F44" t="n">
-        <v>62918300</v>
+        <v>35122600</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
@@ -1587,22 +1587,22 @@
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
-        <v>45986</v>
+        <v>45987</v>
       </c>
       <c r="B45" t="n">
-        <v>106.120002746582</v>
+        <v>105.7399978637695</v>
       </c>
       <c r="C45" t="n">
-        <v>106.3000030517578</v>
+        <v>106.9499969482422</v>
       </c>
       <c r="D45" t="n">
-        <v>103.8199996948242</v>
+        <v>105.2200012207031</v>
       </c>
       <c r="E45" t="n">
-        <v>104.4000015258789</v>
+        <v>106.1399993896484</v>
       </c>
       <c r="F45" t="n">
-        <v>35122600</v>
+        <v>27951000</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
@@ -1613,22 +1613,22 @@
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
-        <v>45987</v>
+        <v>45989</v>
       </c>
       <c r="B46" t="n">
-        <v>105.7399978637695</v>
+        <v>106.4400024414062</v>
       </c>
       <c r="C46" t="n">
-        <v>106.9499969482422</v>
+        <v>107.9400024414062</v>
       </c>
       <c r="D46" t="n">
-        <v>105.2200012207031</v>
+        <v>106.2399978637695</v>
       </c>
       <c r="E46" t="n">
-        <v>106.1399993896484</v>
+        <v>107.5800018310547</v>
       </c>
       <c r="F46" t="n">
-        <v>27951000</v>
+        <v>15021600</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
@@ -1639,22 +1639,22 @@
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
-        <v>45989</v>
+        <v>45992</v>
       </c>
       <c r="B47" t="n">
-        <v>106.4400024414062</v>
+        <v>106.5100021362305</v>
       </c>
       <c r="C47" t="n">
-        <v>107.9400024414062</v>
+        <v>109.3399963378906</v>
       </c>
       <c r="D47" t="n">
-        <v>106.2399978637695</v>
+        <v>106.3099975585938</v>
       </c>
       <c r="E47" t="n">
-        <v>107.5800018310547</v>
+        <v>109.129997253418</v>
       </c>
       <c r="F47" t="n">
-        <v>15021600</v>
+        <v>24873400</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
@@ -1665,22 +1665,22 @@
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
-        <v>45992</v>
+        <v>45993</v>
       </c>
       <c r="B48" t="n">
-        <v>106.5100021362305</v>
+        <v>109.2099990844727</v>
       </c>
       <c r="C48" t="n">
-        <v>109.3399963378906</v>
+        <v>109.7300033569336</v>
       </c>
       <c r="D48" t="n">
-        <v>106.3099975585938</v>
+        <v>107.5199966430664</v>
       </c>
       <c r="E48" t="n">
-        <v>109.129997253418</v>
+        <v>109.3499984741211</v>
       </c>
       <c r="F48" t="n">
-        <v>24873400</v>
+        <v>25763000</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
@@ -1691,22 +1691,22 @@
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>45993</v>
+        <v>45994</v>
       </c>
       <c r="B49" t="n">
-        <v>109.2099990844727</v>
+        <v>106.5899963378906</v>
       </c>
       <c r="C49" t="n">
-        <v>109.7300033569336</v>
+        <v>106.870002746582</v>
       </c>
       <c r="D49" t="n">
-        <v>107.5199966430664</v>
+        <v>102.0299987792969</v>
       </c>
       <c r="E49" t="n">
-        <v>109.3499984741211</v>
+        <v>103.9599990844727</v>
       </c>
       <c r="F49" t="n">
-        <v>25763000</v>
+        <v>53593400</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
@@ -1717,22 +1717,22 @@
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>45994</v>
+        <v>45995</v>
       </c>
       <c r="B50" t="n">
-        <v>106.5899963378906</v>
+        <v>103.5699996948242</v>
       </c>
       <c r="C50" t="n">
-        <v>106.870002746582</v>
+        <v>103.8000030517578</v>
       </c>
       <c r="D50" t="n">
-        <v>102.0299987792969</v>
+        <v>101.7699966430664</v>
       </c>
       <c r="E50" t="n">
-        <v>103.9599990844727</v>
+        <v>103.2200012207031</v>
       </c>
       <c r="F50" t="n">
-        <v>53593400</v>
+        <v>51779100</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
-        <v>45995</v>
+        <v>45996</v>
       </c>
       <c r="B51" t="n">
-        <v>103.5699996948242</v>
+        <v>98.77999877929688</v>
       </c>
       <c r="C51" t="n">
-        <v>103.8000030517578</v>
+        <v>104.7900009155273</v>
       </c>
       <c r="D51" t="n">
-        <v>101.7699966430664</v>
+        <v>97.73999786376953</v>
       </c>
       <c r="E51" t="n">
-        <v>103.2200012207031</v>
+        <v>100.2399978637695</v>
       </c>
       <c r="F51" t="n">
-        <v>51779100</v>
+        <v>133363600</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
@@ -1769,22 +1769,22 @@
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
-        <v>45996</v>
+        <v>45999</v>
       </c>
       <c r="B52" t="n">
-        <v>98.77999877929688</v>
+        <v>99.87000274658203</v>
       </c>
       <c r="C52" t="n">
-        <v>104.7900009155273</v>
+        <v>99.88999938964844</v>
       </c>
       <c r="D52" t="n">
-        <v>97.73999786376953</v>
+        <v>95.30000305175781</v>
       </c>
       <c r="E52" t="n">
-        <v>100.2399978637695</v>
+        <v>96.79000091552734</v>
       </c>
       <c r="F52" t="n">
-        <v>133363600</v>
+        <v>100906300</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
@@ -1795,22 +1795,22 @@
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
-        <v>45999</v>
+        <v>46000</v>
       </c>
       <c r="B53" t="n">
-        <v>99.87000274658203</v>
+        <v>97.02999877929688</v>
       </c>
       <c r="C53" t="n">
-        <v>99.88999938964844</v>
+        <v>97.23999786376953</v>
       </c>
       <c r="D53" t="n">
-        <v>95.30000305175781</v>
+        <v>95.44999694824219</v>
       </c>
       <c r="E53" t="n">
-        <v>96.79000091552734</v>
+        <v>96.70999908447266</v>
       </c>
       <c r="F53" t="n">
-        <v>100906300</v>
+        <v>51745600</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
@@ -1821,22 +1821,22 @@
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
-        <v>46000</v>
+        <v>46001</v>
       </c>
       <c r="B54" t="n">
-        <v>97.02999877929688</v>
+        <v>96.73999786376953</v>
       </c>
       <c r="C54" t="n">
-        <v>97.23999786376953</v>
+        <v>96.97000122070312</v>
       </c>
       <c r="D54" t="n">
-        <v>95.44999694824219</v>
+        <v>92.34999847412109</v>
       </c>
       <c r="E54" t="n">
-        <v>96.70999908447266</v>
+        <v>92.70999908447266</v>
       </c>
       <c r="F54" t="n">
-        <v>51745600</v>
+        <v>74129300</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
@@ -1847,22 +1847,22 @@
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
-        <v>46001</v>
+        <v>46002</v>
       </c>
       <c r="B55" t="n">
-        <v>96.73999786376953</v>
+        <v>93.90000152587891</v>
       </c>
       <c r="C55" t="n">
-        <v>96.97000122070312</v>
+        <v>94.81999969482422</v>
       </c>
       <c r="D55" t="n">
-        <v>92.34999847412109</v>
+        <v>92.76000213623047</v>
       </c>
       <c r="E55" t="n">
-        <v>92.70999908447266</v>
+        <v>94.08999633789062</v>
       </c>
       <c r="F55" t="n">
-        <v>74129300</v>
+        <v>43949000</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
@@ -1873,22 +1873,22 @@
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
-        <v>46002</v>
+        <v>46003</v>
       </c>
       <c r="B56" t="n">
-        <v>93.90000152587891</v>
+        <v>95.5</v>
       </c>
       <c r="C56" t="n">
-        <v>94.81999969482422</v>
+        <v>96.91999816894531</v>
       </c>
       <c r="D56" t="n">
-        <v>92.76000213623047</v>
+        <v>94.65000152587891</v>
       </c>
       <c r="E56" t="n">
-        <v>94.08999633789062</v>
+        <v>95.19000244140625</v>
       </c>
       <c r="F56" t="n">
-        <v>43949000</v>
+        <v>49323100</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
@@ -1899,22 +1899,22 @@
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
-        <v>46003</v>
+        <v>46006</v>
       </c>
       <c r="B57" t="n">
-        <v>95.5</v>
+        <v>96.01999664306641</v>
       </c>
       <c r="C57" t="n">
-        <v>96.91999816894531</v>
+        <v>96.37000274658203</v>
       </c>
       <c r="D57" t="n">
-        <v>94.65000152587891</v>
+        <v>93.52999877929688</v>
       </c>
       <c r="E57" t="n">
-        <v>95.19000244140625</v>
+        <v>93.76999664306641</v>
       </c>
       <c r="F57" t="n">
-        <v>49323100</v>
+        <v>40016500</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
@@ -1925,22 +1925,22 @@
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
-        <v>46006</v>
+        <v>46007</v>
       </c>
       <c r="B58" t="n">
-        <v>96.01999664306641</v>
+        <v>93.87999725341797</v>
       </c>
       <c r="C58" t="n">
-        <v>96.37000274658203</v>
+        <v>94.93000030517578</v>
       </c>
       <c r="D58" t="n">
-        <v>93.52999877929688</v>
+        <v>93.31999969482422</v>
       </c>
       <c r="E58" t="n">
-        <v>93.76999664306641</v>
+        <v>94.56999969482422</v>
       </c>
       <c r="F58" t="n">
-        <v>40016500</v>
+        <v>34265000</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
@@ -1951,22 +1951,22 @@
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
-        <v>46007</v>
+        <v>46008</v>
       </c>
       <c r="B59" t="n">
-        <v>93.87999725341797</v>
+        <v>95.98000335693359</v>
       </c>
       <c r="C59" t="n">
-        <v>94.93000030517578</v>
+        <v>97.33000183105469</v>
       </c>
       <c r="D59" t="n">
-        <v>93.31999969482422</v>
+        <v>94.45999908447266</v>
       </c>
       <c r="E59" t="n">
-        <v>94.56999969482422</v>
+        <v>94.79000091552734</v>
       </c>
       <c r="F59" t="n">
-        <v>34265000</v>
+        <v>50472800</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
@@ -1977,22 +1977,22 @@
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
-        <v>46008</v>
+        <v>46009</v>
       </c>
       <c r="B60" t="n">
-        <v>95.98000335693359</v>
+        <v>95.01999664306641</v>
       </c>
       <c r="C60" t="n">
-        <v>97.33000183105469</v>
+        <v>95.80999755859375</v>
       </c>
       <c r="D60" t="n">
-        <v>94.45999908447266</v>
+        <v>93.58999633789062</v>
       </c>
       <c r="E60" t="n">
-        <v>94.79000091552734</v>
+        <v>94</v>
       </c>
       <c r="F60" t="n">
-        <v>50472800</v>
+        <v>37244700</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
@@ -2003,22 +2003,22 @@
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
-        <v>46009</v>
+        <v>46010</v>
       </c>
       <c r="B61" t="n">
-        <v>95.01999664306641</v>
+        <v>93.56999969482422</v>
       </c>
       <c r="C61" t="n">
-        <v>95.80999755859375</v>
+        <v>95.54000091552734</v>
       </c>
       <c r="D61" t="n">
-        <v>93.58999633789062</v>
+        <v>93.44999694824219</v>
       </c>
       <c r="E61" t="n">
-        <v>94</v>
+        <v>94.38999938964844</v>
       </c>
       <c r="F61" t="n">
-        <v>37244700</v>
+        <v>78990200</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
@@ -2029,22 +2029,22 @@
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
-        <v>46010</v>
+        <v>46013</v>
       </c>
       <c r="B62" t="n">
-        <v>93.56999969482422</v>
+        <v>94.70999908447266</v>
       </c>
       <c r="C62" t="n">
-        <v>95.54000091552734</v>
+        <v>94.70999908447266</v>
       </c>
       <c r="D62" t="n">
-        <v>93.44999694824219</v>
+        <v>92.91000366210938</v>
       </c>
       <c r="E62" t="n">
-        <v>94.38999938964844</v>
+        <v>93.23000335693359</v>
       </c>
       <c r="F62" t="n">
-        <v>78990200</v>
+        <v>39484800</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
@@ -2055,22 +2055,22 @@
     </row>
     <row r="63">
       <c r="A63" s="1" t="n">
-        <v>46013</v>
+        <v>46014</v>
       </c>
       <c r="B63" t="n">
-        <v>94.70999908447266</v>
+        <v>93.40000152587891</v>
       </c>
       <c r="C63" t="n">
-        <v>94.70999908447266</v>
+        <v>93.80999755859375</v>
       </c>
       <c r="D63" t="n">
-        <v>92.91000366210938</v>
+        <v>91.33000183105469</v>
       </c>
       <c r="E63" t="n">
-        <v>93.23000335693359</v>
+        <v>93.5</v>
       </c>
       <c r="F63" t="n">
-        <v>39484800</v>
+        <v>25896200</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
@@ -2081,22 +2081,22 @@
     </row>
     <row r="64">
       <c r="A64" s="1" t="n">
-        <v>46014</v>
+        <v>46015</v>
       </c>
       <c r="B64" t="n">
-        <v>93.40000152587891</v>
+        <v>93.11000061035156</v>
       </c>
       <c r="C64" t="n">
-        <v>93.80999755859375</v>
+        <v>93.68000030517578</v>
       </c>
       <c r="D64" t="n">
-        <v>91.33000183105469</v>
+        <v>92.66999816894531</v>
       </c>
       <c r="E64" t="n">
-        <v>93.5</v>
+        <v>93.63999938964844</v>
       </c>
       <c r="F64" t="n">
-        <v>25896200</v>
+        <v>12427900</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
@@ -2107,22 +2107,22 @@
     </row>
     <row r="65">
       <c r="A65" s="1" t="n">
-        <v>46015</v>
+        <v>46017</v>
       </c>
       <c r="B65" t="n">
-        <v>93.11000061035156</v>
+        <v>93.48000335693359</v>
       </c>
       <c r="C65" t="n">
-        <v>93.68000030517578</v>
+        <v>94.69000244140625</v>
       </c>
       <c r="D65" t="n">
-        <v>92.66999816894531</v>
+        <v>93.26999664306641</v>
       </c>
       <c r="E65" t="n">
-        <v>93.63999938964844</v>
+        <v>94.47000122070312</v>
       </c>
       <c r="F65" t="n">
-        <v>12427900</v>
+        <v>22068300</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
@@ -2133,22 +2133,22 @@
     </row>
     <row r="66">
       <c r="A66" s="1" t="n">
-        <v>46017</v>
+        <v>46020</v>
       </c>
       <c r="B66" t="n">
-        <v>93.48000335693359</v>
+        <v>93.98999786376953</v>
       </c>
       <c r="C66" t="n">
-        <v>94.69000244140625</v>
+        <v>94.97000122070312</v>
       </c>
       <c r="D66" t="n">
-        <v>93.26999664306641</v>
+        <v>93.62999725341797</v>
       </c>
       <c r="E66" t="n">
-        <v>94.47000122070312</v>
+        <v>94.15000152587891</v>
       </c>
       <c r="F66" t="n">
-        <v>22068300</v>
+        <v>24493700</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
@@ -2159,22 +2159,22 @@
     </row>
     <row r="67">
       <c r="A67" s="1" t="n">
-        <v>46020</v>
+        <v>46021</v>
       </c>
       <c r="B67" t="n">
+        <v>93.51999664306641</v>
+      </c>
+      <c r="C67" t="n">
         <v>93.98999786376953</v>
       </c>
-      <c r="C67" t="n">
-        <v>94.97000122070312</v>
-      </c>
       <c r="D67" t="n">
-        <v>93.62999725341797</v>
+        <v>93.33999633789062</v>
       </c>
       <c r="E67" t="n">
-        <v>94.15000152587891</v>
+        <v>93.77999877929688</v>
       </c>
       <c r="F67" t="n">
-        <v>24493700</v>
+        <v>23422000</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
@@ -2185,22 +2185,22 @@
     </row>
     <row r="68">
       <c r="A68" s="1" t="n">
-        <v>46021</v>
+        <v>46022</v>
       </c>
       <c r="B68" t="n">
-        <v>93.51999664306641</v>
+        <v>93.59999847412109</v>
       </c>
       <c r="C68" t="n">
-        <v>93.98999786376953</v>
+        <v>94.30999755859375</v>
       </c>
       <c r="D68" t="n">
-        <v>93.33999633789062</v>
+        <v>93.19999694824219</v>
       </c>
       <c r="E68" t="n">
-        <v>93.77999877929688</v>
+        <v>93.76000213623047</v>
       </c>
       <c r="F68" t="n">
-        <v>23422000</v>
+        <v>23495200</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
@@ -2211,22 +2211,22 @@
     </row>
     <row r="69">
       <c r="A69" s="1" t="n">
-        <v>46022</v>
+        <v>46024</v>
       </c>
       <c r="B69" t="n">
-        <v>93.59999847412109</v>
+        <v>94.12999725341797</v>
       </c>
       <c r="C69" t="n">
-        <v>94.30999755859375</v>
+        <v>94.12999725341797</v>
       </c>
       <c r="D69" t="n">
-        <v>93.19999694824219</v>
+        <v>90.80999755859375</v>
       </c>
       <c r="E69" t="n">
-        <v>93.76000213623047</v>
+        <v>90.98999786376953</v>
       </c>
       <c r="F69" t="n">
-        <v>23495200</v>
+        <v>41155400</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
@@ -2237,22 +2237,22 @@
     </row>
     <row r="70">
       <c r="A70" s="1" t="n">
-        <v>46024</v>
+        <v>46027</v>
       </c>
       <c r="B70" t="n">
-        <v>94.12999725341797</v>
+        <v>90.91999816894531</v>
       </c>
       <c r="C70" t="n">
-        <v>94.12999725341797</v>
+        <v>92.62999725341797</v>
       </c>
       <c r="D70" t="n">
-        <v>90.80999755859375</v>
+        <v>90.83999633789062</v>
       </c>
       <c r="E70" t="n">
-        <v>90.98999786376953</v>
+        <v>91.45999908447266</v>
       </c>
       <c r="F70" t="n">
-        <v>41155400</v>
+        <v>39183300</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
@@ -2263,22 +2263,22 @@
     </row>
     <row r="71">
       <c r="A71" s="1" t="n">
-        <v>46027</v>
+        <v>46028</v>
       </c>
       <c r="B71" t="n">
-        <v>90.91999816894531</v>
+        <v>91.54000091552734</v>
       </c>
       <c r="C71" t="n">
-        <v>92.62999725341797</v>
+        <v>91.63999938964844</v>
       </c>
       <c r="D71" t="n">
-        <v>90.83999633789062</v>
+        <v>89.73999786376953</v>
       </c>
       <c r="E71" t="n">
-        <v>91.45999908447266</v>
+        <v>90.65000152587891</v>
       </c>
       <c r="F71" t="n">
-        <v>39183300</v>
+        <v>43331000</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
@@ -2289,22 +2289,22 @@
     </row>
     <row r="72">
       <c r="A72" s="1" t="n">
-        <v>46028</v>
+        <v>46029</v>
       </c>
       <c r="B72" t="n">
-        <v>91.54000091552734</v>
+        <v>91.55999755859375</v>
       </c>
       <c r="C72" t="n">
-        <v>91.63999938964844</v>
+        <v>92.41999816894531</v>
       </c>
       <c r="D72" t="n">
-        <v>89.73999786376953</v>
+        <v>90.05999755859375</v>
       </c>
       <c r="E72" t="n">
-        <v>90.65000152587891</v>
+        <v>90.73000335693359</v>
       </c>
       <c r="F72" t="n">
-        <v>43331000</v>
+        <v>36525700</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
@@ -2315,22 +2315,22 @@
     </row>
     <row r="73">
       <c r="A73" s="1" t="n">
-        <v>46029</v>
+        <v>46030</v>
       </c>
       <c r="B73" t="n">
-        <v>91.55999755859375</v>
+        <v>90.44999694824219</v>
       </c>
       <c r="C73" t="n">
-        <v>92.41999816894531</v>
+        <v>91.25</v>
       </c>
       <c r="D73" t="n">
-        <v>90.05999755859375</v>
+        <v>89.58000183105469</v>
       </c>
       <c r="E73" t="n">
-        <v>90.73000335693359</v>
+        <v>90.52999877929688</v>
       </c>
       <c r="F73" t="n">
-        <v>36525700</v>
+        <v>40068700</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
@@ -2341,22 +2341,22 @@
     </row>
     <row r="74">
       <c r="A74" s="1" t="n">
-        <v>46030</v>
+        <v>46031</v>
       </c>
       <c r="B74" t="n">
-        <v>90.44999694824219</v>
+        <v>90.02999877929688</v>
       </c>
       <c r="C74" t="n">
-        <v>91.25</v>
+        <v>90.05000305175781</v>
       </c>
       <c r="D74" t="n">
-        <v>89.58000183105469</v>
+        <v>88.31999969482422</v>
       </c>
       <c r="E74" t="n">
-        <v>90.52999877929688</v>
+        <v>89.45999908447266</v>
       </c>
       <c r="F74" t="n">
-        <v>40068700</v>
+        <v>55579500</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
@@ -2367,22 +2367,22 @@
     </row>
     <row r="75">
       <c r="A75" s="1" t="n">
-        <v>46031</v>
+        <v>46034</v>
       </c>
       <c r="B75" t="n">
-        <v>90.02999877929688</v>
+        <v>89.69000244140625</v>
       </c>
       <c r="C75" t="n">
-        <v>90.05000305175781</v>
+        <v>90.33999633789062</v>
       </c>
       <c r="D75" t="n">
-        <v>88.31999969482422</v>
+        <v>89.33000183105469</v>
       </c>
       <c r="E75" t="n">
-        <v>89.45999908447266</v>
+        <v>89.41000366210938</v>
       </c>
       <c r="F75" t="n">
-        <v>55579500</v>
+        <v>36290600</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
@@ -2393,22 +2393,22 @@
     </row>
     <row r="76">
       <c r="A76" s="1" t="n">
-        <v>46034</v>
+        <v>46035</v>
       </c>
       <c r="B76" t="n">
-        <v>89.69000244140625</v>
+        <v>89.44000244140625</v>
       </c>
       <c r="C76" t="n">
-        <v>90.33999633789062</v>
+        <v>91.15000152587891</v>
       </c>
       <c r="D76" t="n">
-        <v>89.33000183105469</v>
+        <v>89.06999969482422</v>
       </c>
       <c r="E76" t="n">
-        <v>89.41000366210938</v>
+        <v>90.31999969482422</v>
       </c>
       <c r="F76" t="n">
-        <v>36290600</v>
+        <v>45221100</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
@@ -2419,22 +2419,22 @@
     </row>
     <row r="77">
       <c r="A77" s="1" t="n">
-        <v>46035</v>
+        <v>46036</v>
       </c>
       <c r="B77" t="n">
-        <v>89.44000244140625</v>
+        <v>91.23999786376953</v>
       </c>
       <c r="C77" t="n">
-        <v>91.15000152587891</v>
+        <v>91.58000183105469</v>
       </c>
       <c r="D77" t="n">
-        <v>89.06999969482422</v>
+        <v>87.94999694824219</v>
       </c>
       <c r="E77" t="n">
-        <v>90.31999969482422</v>
+        <v>88.55000305175781</v>
       </c>
       <c r="F77" t="n">
-        <v>45221100</v>
+        <v>49737700</v>
       </c>
       <c r="G77" t="n">
         <v>0</v>
@@ -2445,22 +2445,22 @@
     </row>
     <row r="78">
       <c r="A78" s="1" t="n">
-        <v>46036</v>
+        <v>46037</v>
       </c>
       <c r="B78" t="n">
-        <v>91.23999786376953</v>
+        <v>89.01999664306641</v>
       </c>
       <c r="C78" t="n">
-        <v>91.58000183105469</v>
+        <v>89.88999938964844</v>
       </c>
       <c r="D78" t="n">
-        <v>87.94999694824219</v>
+        <v>87.81999969482422</v>
       </c>
       <c r="E78" t="n">
-        <v>88.55000305175781</v>
+        <v>88.05000305175781</v>
       </c>
       <c r="F78" t="n">
-        <v>49737700</v>
+        <v>36945100</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
@@ -2471,22 +2471,22 @@
     </row>
     <row r="79">
       <c r="A79" s="1" t="n">
-        <v>46037</v>
+        <v>46038</v>
       </c>
       <c r="B79" t="n">
-        <v>89.01999664306641</v>
+        <v>88.33999633789062</v>
       </c>
       <c r="C79" t="n">
-        <v>89.88999938964844</v>
+        <v>88.51000213623047</v>
       </c>
       <c r="D79" t="n">
-        <v>87.81999969482422</v>
+        <v>87.77999877929688</v>
       </c>
       <c r="E79" t="n">
-        <v>88.05000305175781</v>
+        <v>88</v>
       </c>
       <c r="F79" t="n">
-        <v>36945100</v>
+        <v>48130500</v>
       </c>
       <c r="G79" t="n">
         <v>0</v>
@@ -2497,22 +2497,22 @@
     </row>
     <row r="80">
       <c r="A80" s="1" t="n">
-        <v>46038</v>
+        <v>46042</v>
       </c>
       <c r="B80" t="n">
-        <v>88.33999633789062</v>
+        <v>88.97000122070312</v>
       </c>
       <c r="C80" t="n">
-        <v>88.51000213623047</v>
+        <v>89.90000152587891</v>
       </c>
       <c r="D80" t="n">
-        <v>87.77999877929688</v>
+        <v>87.01999664306641</v>
       </c>
       <c r="E80" t="n">
-        <v>88</v>
+        <v>87.26000213623047</v>
       </c>
       <c r="F80" t="n">
-        <v>48130500</v>
+        <v>109729700</v>
       </c>
       <c r="G80" t="n">
         <v>0</v>
@@ -2523,22 +2523,22 @@
     </row>
     <row r="81">
       <c r="A81" s="1" t="n">
-        <v>46042</v>
+        <v>46043</v>
       </c>
       <c r="B81" t="n">
-        <v>88.97000122070312</v>
+        <v>82.51999664306641</v>
       </c>
       <c r="C81" t="n">
-        <v>89.90000152587891</v>
+        <v>86</v>
       </c>
       <c r="D81" t="n">
-        <v>87.01999664306641</v>
+        <v>81.93000030517578</v>
       </c>
       <c r="E81" t="n">
-        <v>87.26000213623047</v>
+        <v>85.36000061035156</v>
       </c>
       <c r="F81" t="n">
-        <v>109729700</v>
+        <v>127940700</v>
       </c>
       <c r="G81" t="n">
         <v>0</v>
@@ -2549,22 +2549,22 @@
     </row>
     <row r="82">
       <c r="A82" s="1" t="n">
-        <v>46043</v>
+        <v>46044</v>
       </c>
       <c r="B82" t="n">
-        <v>82.51999664306641</v>
+        <v>85.01999664306641</v>
       </c>
       <c r="C82" t="n">
-        <v>86</v>
+        <v>85.09999847412109</v>
       </c>
       <c r="D82" t="n">
-        <v>81.93000030517578</v>
+        <v>82.98000335693359</v>
       </c>
       <c r="E82" t="n">
-        <v>85.36000061035156</v>
+        <v>83.54000091552734</v>
       </c>
       <c r="F82" t="n">
-        <v>127940700</v>
+        <v>69113300</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
@@ -2575,22 +2575,22 @@
     </row>
     <row r="83">
       <c r="A83" s="1" t="n">
-        <v>46044</v>
+        <v>46045</v>
       </c>
       <c r="B83" t="n">
-        <v>85.01999664306641</v>
+        <v>83.43000030517578</v>
       </c>
       <c r="C83" t="n">
-        <v>85.09999847412109</v>
+        <v>86.30000305175781</v>
       </c>
       <c r="D83" t="n">
-        <v>82.98000335693359</v>
+        <v>83.27999877929688</v>
       </c>
       <c r="E83" t="n">
-        <v>83.54000091552734</v>
+        <v>86.12000274658203</v>
       </c>
       <c r="F83" t="n">
-        <v>69113300</v>
+        <v>64520400</v>
       </c>
       <c r="G83" t="n">
         <v>0</v>
@@ -2601,22 +2601,22 @@
     </row>
     <row r="84">
       <c r="A84" s="1" t="n">
-        <v>46045</v>
+        <v>46048</v>
       </c>
       <c r="B84" t="n">
-        <v>83.43000030517578</v>
+        <v>86.91999816894531</v>
       </c>
       <c r="C84" t="n">
-        <v>86.30000305175781</v>
+        <v>86.94000244140625</v>
       </c>
       <c r="D84" t="n">
-        <v>83.27999877929688</v>
+        <v>85.34999847412109</v>
       </c>
       <c r="E84" t="n">
-        <v>86.12000274658203</v>
+        <v>85.69999694824219</v>
       </c>
       <c r="F84" t="n">
-        <v>64520400</v>
+        <v>40941900</v>
       </c>
       <c r="G84" t="n">
         <v>0</v>
@@ -2627,22 +2627,22 @@
     </row>
     <row r="85">
       <c r="A85" s="1" t="n">
-        <v>46048</v>
+        <v>46049</v>
       </c>
       <c r="B85" t="n">
-        <v>86.91999816894531</v>
+        <v>85.27999877929688</v>
       </c>
       <c r="C85" t="n">
-        <v>86.94000244140625</v>
+        <v>85.59999847412109</v>
       </c>
       <c r="D85" t="n">
-        <v>85.34999847412109</v>
+        <v>83.87999725341797</v>
       </c>
       <c r="E85" t="n">
-        <v>85.69999694824219</v>
+        <v>85.58000183105469</v>
       </c>
       <c r="F85" t="n">
-        <v>40941900</v>
+        <v>37790800</v>
       </c>
       <c r="G85" t="n">
         <v>0</v>
@@ -2653,22 +2653,22 @@
     </row>
     <row r="86">
       <c r="A86" s="1" t="n">
-        <v>46049</v>
+        <v>46050</v>
       </c>
       <c r="B86" t="n">
-        <v>85.27999877929688</v>
+        <v>85.62999725341797</v>
       </c>
       <c r="C86" t="n">
-        <v>85.59999847412109</v>
+        <v>86.47000122070312</v>
       </c>
       <c r="D86" t="n">
-        <v>83.87999725341797</v>
+        <v>84.30000305175781</v>
       </c>
       <c r="E86" t="n">
-        <v>85.58000183105469</v>
+        <v>84.63999938964844</v>
       </c>
       <c r="F86" t="n">
-        <v>37790800</v>
+        <v>37762600</v>
       </c>
       <c r="G86" t="n">
         <v>0</v>
@@ -2679,22 +2679,22 @@
     </row>
     <row r="87">
       <c r="A87" s="1" t="n">
-        <v>46050</v>
+        <v>46051</v>
       </c>
       <c r="B87" t="n">
-        <v>85.62999725341797</v>
+        <v>84.30999755859375</v>
       </c>
       <c r="C87" t="n">
-        <v>86.47000122070312</v>
+        <v>84.37999725341797</v>
       </c>
       <c r="D87" t="n">
-        <v>84.30000305175781</v>
+        <v>82.34999847412109</v>
       </c>
       <c r="E87" t="n">
-        <v>84.63999938964844</v>
+        <v>83.16000366210938</v>
       </c>
       <c r="F87" t="n">
-        <v>37762600</v>
+        <v>42278100</v>
       </c>
       <c r="G87" t="n">
         <v>0</v>
@@ -2705,22 +2705,22 @@
     </row>
     <row r="88">
       <c r="A88" s="1" t="n">
-        <v>46051</v>
+        <v>46052</v>
       </c>
       <c r="B88" t="n">
-        <v>84.30999755859375</v>
+        <v>83.09999847412109</v>
       </c>
       <c r="C88" t="n">
-        <v>84.37999725341797</v>
+        <v>84.05999755859375</v>
       </c>
       <c r="D88" t="n">
-        <v>82.34999847412109</v>
+        <v>82.77999877929688</v>
       </c>
       <c r="E88" t="n">
-        <v>83.16000366210938</v>
+        <v>83.48999786376953</v>
       </c>
       <c r="F88" t="n">
-        <v>42278100</v>
+        <v>45755000</v>
       </c>
       <c r="G88" t="n">
         <v>0</v>
@@ -2731,22 +2731,22 @@
     </row>
     <row r="89">
       <c r="A89" s="1" t="n">
-        <v>46052</v>
+        <v>46055</v>
       </c>
       <c r="B89" t="n">
-        <v>83.09999847412109</v>
+        <v>83.52999877929688</v>
       </c>
       <c r="C89" t="n">
-        <v>84.05999755859375</v>
+        <v>85.26999664306641</v>
       </c>
       <c r="D89" t="n">
-        <v>82.77999877929688</v>
+        <v>82.72000122070312</v>
       </c>
       <c r="E89" t="n">
-        <v>83.48999786376953</v>
+        <v>82.76000213623047</v>
       </c>
       <c r="F89" t="n">
-        <v>45755000</v>
+        <v>41445300</v>
       </c>
       <c r="G89" t="n">
         <v>0</v>
@@ -2757,22 +2757,22 @@
     </row>
     <row r="90">
       <c r="A90" s="1" t="n">
-        <v>46055</v>
+        <v>46056</v>
       </c>
       <c r="B90" t="n">
-        <v>83.52999877929688</v>
+        <v>82.23000335693359</v>
       </c>
       <c r="C90" t="n">
-        <v>85.26999664306641</v>
+        <v>82.44999694824219</v>
       </c>
       <c r="D90" t="n">
-        <v>82.72000122070312</v>
+        <v>79.62000274658203</v>
       </c>
       <c r="E90" t="n">
-        <v>82.76000213623047</v>
+        <v>79.94000244140625</v>
       </c>
       <c r="F90" t="n">
-        <v>41445300</v>
+        <v>49789000</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
@@ -2783,22 +2783,22 @@
     </row>
     <row r="91">
       <c r="A91" s="1" t="n">
-        <v>46056</v>
+        <v>46057</v>
       </c>
       <c r="B91" t="n">
-        <v>82.23000335693359</v>
+        <v>79.98999786376953</v>
       </c>
       <c r="C91" t="n">
-        <v>82.44999694824219</v>
+        <v>81.44000244140625</v>
       </c>
       <c r="D91" t="n">
-        <v>79.62000274658203</v>
+        <v>79.23000335693359</v>
       </c>
       <c r="E91" t="n">
-        <v>79.94000244140625</v>
+        <v>80.16000366210938</v>
       </c>
       <c r="F91" t="n">
-        <v>49789000</v>
+        <v>48963200</v>
       </c>
       <c r="G91" t="n">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="92">
       <c r="A92" s="1" t="n">
-        <v>46057</v>
+        <v>46058</v>
       </c>
       <c r="B92" t="n">
-        <v>79.98999786376953</v>
+        <v>81.48999786376953</v>
       </c>
       <c r="C92" t="n">
-        <v>81.44000244140625</v>
+        <v>83.30000305175781</v>
       </c>
       <c r="D92" t="n">
-        <v>79.23000335693359</v>
+        <v>80.54000091552734</v>
       </c>
       <c r="E92" t="n">
-        <v>80.16000366210938</v>
+        <v>80.87000274658203</v>
       </c>
       <c r="F92" t="n">
-        <v>48963200</v>
+        <v>54805700</v>
       </c>
       <c r="G92" t="n">
         <v>0</v>
@@ -2835,22 +2835,22 @@
     </row>
     <row r="93">
       <c r="A93" s="1" t="n">
-        <v>46058</v>
+        <v>46059</v>
       </c>
       <c r="B93" t="n">
-        <v>81.48999786376953</v>
+        <v>81.01999664306641</v>
       </c>
       <c r="C93" t="n">
-        <v>83.30000305175781</v>
+        <v>82.48999786376953</v>
       </c>
       <c r="D93" t="n">
-        <v>80.54000091552734</v>
+        <v>80.65000152587891</v>
       </c>
       <c r="E93" t="n">
-        <v>80.87000274658203</v>
+        <v>82.19999694824219</v>
       </c>
       <c r="F93" t="n">
-        <v>54805700</v>
+        <v>46154100</v>
       </c>
       <c r="G93" t="n">
         <v>0</v>
@@ -2861,22 +2861,22 @@
     </row>
     <row r="94">
       <c r="A94" s="1" t="n">
-        <v>46059</v>
+        <v>46062</v>
       </c>
       <c r="B94" t="n">
-        <v>81.01999664306641</v>
+        <v>82.18000030517578</v>
       </c>
       <c r="C94" t="n">
-        <v>82.48999786376953</v>
+        <v>82.20999908447266</v>
       </c>
       <c r="D94" t="n">
-        <v>80.65000152587891</v>
+        <v>79.87000274658203</v>
       </c>
       <c r="E94" t="n">
-        <v>82.19999694824219</v>
+        <v>81.47000122070312</v>
       </c>
       <c r="F94" t="n">
-        <v>46154100</v>
+        <v>42200200</v>
       </c>
       <c r="G94" t="n">
         <v>0</v>
@@ -2887,22 +2887,22 @@
     </row>
     <row r="95">
       <c r="A95" s="1" t="n">
-        <v>46062</v>
+        <v>46063</v>
       </c>
       <c r="B95" t="n">
-        <v>82.18000030517578</v>
+        <v>82.72000122070312</v>
       </c>
       <c r="C95" t="n">
+        <v>84.66000366210938</v>
+      </c>
+      <c r="D95" t="n">
+        <v>82.08999633789062</v>
+      </c>
+      <c r="E95" t="n">
         <v>82.20999908447266</v>
       </c>
-      <c r="D95" t="n">
-        <v>79.87000274658203</v>
-      </c>
-      <c r="E95" t="n">
-        <v>81.47000122070312</v>
-      </c>
       <c r="F95" t="n">
-        <v>42200200</v>
+        <v>43595800</v>
       </c>
       <c r="G95" t="n">
         <v>0</v>
@@ -2913,22 +2913,22 @@
     </row>
     <row r="96">
       <c r="A96" s="1" t="n">
-        <v>46063</v>
+        <v>46064</v>
       </c>
       <c r="B96" t="n">
-        <v>82.72000122070312</v>
+        <v>81.95999908447266</v>
       </c>
       <c r="C96" t="n">
-        <v>84.66000366210938</v>
+        <v>82.48000335693359</v>
       </c>
       <c r="D96" t="n">
-        <v>82.08999633789062</v>
+        <v>79.44999694824219</v>
       </c>
       <c r="E96" t="n">
-        <v>82.20999908447266</v>
+        <v>79.62000274658203</v>
       </c>
       <c r="F96" t="n">
-        <v>43595800</v>
+        <v>40840300</v>
       </c>
       <c r="G96" t="n">
         <v>0</v>
@@ -2939,22 +2939,22 @@
     </row>
     <row r="97">
       <c r="A97" s="1" t="n">
-        <v>46064</v>
+        <v>46065</v>
       </c>
       <c r="B97" t="n">
-        <v>81.95999908447266</v>
+        <v>79.11000061035156</v>
       </c>
       <c r="C97" t="n">
-        <v>82.48000335693359</v>
+        <v>79.15000152587891</v>
       </c>
       <c r="D97" t="n">
-        <v>79.44999694824219</v>
+        <v>75.23000335693359</v>
       </c>
       <c r="E97" t="n">
-        <v>79.62000274658203</v>
+        <v>75.86000061035156</v>
       </c>
       <c r="F97" t="n">
-        <v>40840300</v>
+        <v>73516100</v>
       </c>
       <c r="G97" t="n">
         <v>0</v>
@@ -2965,22 +2965,22 @@
     </row>
     <row r="98">
       <c r="A98" s="1" t="n">
-        <v>46065</v>
+        <v>46066</v>
       </c>
       <c r="B98" t="n">
-        <v>79.11000061035156</v>
+        <v>76.13999938964844</v>
       </c>
       <c r="C98" t="n">
-        <v>79.15000152587891</v>
+        <v>77.18000030517578</v>
       </c>
       <c r="D98" t="n">
-        <v>75.23000335693359</v>
+        <v>75.52999877929688</v>
       </c>
       <c r="E98" t="n">
-        <v>75.86000061035156</v>
+        <v>76.87000274658203</v>
       </c>
       <c r="F98" t="n">
-        <v>73516100</v>
+        <v>42292100</v>
       </c>
       <c r="G98" t="n">
         <v>0</v>
@@ -2991,22 +2991,22 @@
     </row>
     <row r="99">
       <c r="A99" s="1" t="n">
-        <v>46066</v>
+        <v>46070</v>
       </c>
       <c r="B99" t="n">
-        <v>76.13999938964844</v>
+        <v>76.91999816894531</v>
       </c>
       <c r="C99" t="n">
-        <v>77.18000030517578</v>
+        <v>77.87000274658203</v>
       </c>
       <c r="D99" t="n">
-        <v>75.52999877929688</v>
+        <v>75.30000305175781</v>
       </c>
       <c r="E99" t="n">
-        <v>76.87000274658203</v>
+        <v>77</v>
       </c>
       <c r="F99" t="n">
-        <v>42292100</v>
+        <v>35961500</v>
       </c>
       <c r="G99" t="n">
         <v>0</v>
@@ -3017,22 +3017,22 @@
     </row>
     <row r="100">
       <c r="A100" s="1" t="n">
-        <v>46070</v>
+        <v>46071</v>
       </c>
       <c r="B100" t="n">
-        <v>76.91999816894531</v>
+        <v>77.31999969482422</v>
       </c>
       <c r="C100" t="n">
-        <v>77.87000274658203</v>
+        <v>78.31999969482422</v>
       </c>
       <c r="D100" t="n">
-        <v>75.30000305175781</v>
+        <v>76.27999877929688</v>
       </c>
       <c r="E100" t="n">
-        <v>77</v>
+        <v>77.98999786376953</v>
       </c>
       <c r="F100" t="n">
-        <v>35961500</v>
+        <v>29883100</v>
       </c>
       <c r="G100" t="n">
         <v>0</v>
@@ -3043,22 +3043,22 @@
     </row>
     <row r="101">
       <c r="A101" s="1" t="n">
-        <v>46071</v>
+        <v>46072</v>
       </c>
       <c r="B101" t="n">
-        <v>77.31999969482422</v>
+        <v>77.75</v>
       </c>
       <c r="C101" t="n">
-        <v>78.31999969482422</v>
+        <v>78.69999694824219</v>
       </c>
       <c r="D101" t="n">
-        <v>76.27999877929688</v>
+        <v>76.58999633789062</v>
       </c>
       <c r="E101" t="n">
-        <v>77.98999786376953</v>
+        <v>77</v>
       </c>
       <c r="F101" t="n">
-        <v>29883100</v>
+        <v>30139200</v>
       </c>
       <c r="G101" t="n">
         <v>0</v>
@@ -3069,22 +3069,22 @@
     </row>
     <row r="102">
       <c r="A102" s="1" t="n">
-        <v>46072</v>
+        <v>46073</v>
       </c>
       <c r="B102" t="n">
-        <v>77.75</v>
+        <v>76.61000061035156</v>
       </c>
       <c r="C102" t="n">
-        <v>78.69999694824219</v>
+        <v>78.84999847412109</v>
       </c>
       <c r="D102" t="n">
-        <v>76.58999633789062</v>
+        <v>76.40000152587891</v>
       </c>
       <c r="E102" t="n">
-        <v>77</v>
+        <v>78.66999816894531</v>
       </c>
       <c r="F102" t="n">
-        <v>30139200</v>
+        <v>32411300</v>
       </c>
       <c r="G102" t="n">
         <v>0</v>
@@ -3095,22 +3095,22 @@
     </row>
     <row r="103">
       <c r="A103" s="1" t="n">
-        <v>46073</v>
+        <v>46076</v>
       </c>
       <c r="B103" t="n">
-        <v>76.61000061035156</v>
+        <v>77.79000091552734</v>
       </c>
       <c r="C103" t="n">
-        <v>78.84999847412109</v>
+        <v>77.83000183105469</v>
       </c>
       <c r="D103" t="n">
-        <v>76.40000152587891</v>
+        <v>75.01000213623047</v>
       </c>
       <c r="E103" t="n">
-        <v>78.66999816894531</v>
+        <v>76.01999664306641</v>
       </c>
       <c r="F103" t="n">
-        <v>32411300</v>
+        <v>38363000</v>
       </c>
       <c r="G103" t="n">
         <v>0</v>
@@ -3121,22 +3121,22 @@
     </row>
     <row r="104">
       <c r="A104" s="1" t="n">
-        <v>46076</v>
+        <v>46077</v>
       </c>
       <c r="B104" t="n">
-        <v>77.79000091552734</v>
+        <v>75.73000335693359</v>
       </c>
       <c r="C104" t="n">
-        <v>77.83000183105469</v>
+        <v>78.12000274658203</v>
       </c>
       <c r="D104" t="n">
-        <v>75.01000213623047</v>
+        <v>75.20999908447266</v>
       </c>
       <c r="E104" t="n">
-        <v>76.01999664306641</v>
+        <v>78.04000091552734</v>
       </c>
       <c r="F104" t="n">
-        <v>38363000</v>
+        <v>33079100</v>
       </c>
       <c r="G104" t="n">
         <v>0</v>
@@ -3147,22 +3147,22 @@
     </row>
     <row r="105">
       <c r="A105" s="1" t="n">
-        <v>46077</v>
+        <v>46078</v>
       </c>
       <c r="B105" t="n">
-        <v>75.73000335693359</v>
+        <v>79.43000030517578</v>
       </c>
       <c r="C105" t="n">
-        <v>78.12000274658203</v>
+        <v>83.12000274658203</v>
       </c>
       <c r="D105" t="n">
-        <v>75.20999908447266</v>
+        <v>79.25</v>
       </c>
       <c r="E105" t="n">
-        <v>78.04000091552734</v>
+        <v>82.69999694824219</v>
       </c>
       <c r="F105" t="n">
-        <v>33079100</v>
+        <v>69319300</v>
       </c>
       <c r="G105" t="n">
         <v>0</v>
@@ -3173,22 +3173,22 @@
     </row>
     <row r="106">
       <c r="A106" s="1" t="n">
-        <v>46078</v>
+        <v>46079</v>
       </c>
       <c r="B106" t="n">
-        <v>79.43000030517578</v>
+        <v>83.19999694824219</v>
       </c>
       <c r="C106" t="n">
-        <v>83.12000274658203</v>
+        <v>86.5</v>
       </c>
       <c r="D106" t="n">
-        <v>79.25</v>
+        <v>82.80000305175781</v>
       </c>
       <c r="E106" t="n">
-        <v>82.69999694824219</v>
+        <v>84.58999633789062</v>
       </c>
       <c r="F106" t="n">
-        <v>69319300</v>
+        <v>85642500</v>
       </c>
       <c r="G106" t="n">
         <v>0</v>
@@ -3199,22 +3199,22 @@
     </row>
     <row r="107">
       <c r="A107" s="1" t="n">
-        <v>46079</v>
+        <v>46080</v>
       </c>
       <c r="B107" t="n">
-        <v>83.19999694824219</v>
+        <v>94.30000305175781</v>
       </c>
       <c r="C107" t="n">
-        <v>86.5</v>
+        <v>96.75</v>
       </c>
       <c r="D107" t="n">
-        <v>82.80000305175781</v>
+        <v>90.58000183105469</v>
       </c>
       <c r="E107" t="n">
-        <v>84.58999633789062</v>
+        <v>96.23999786376953</v>
       </c>
       <c r="F107" t="n">
-        <v>85642500</v>
+        <v>200767000</v>
       </c>
       <c r="G107" t="n">
         <v>0</v>
@@ -3225,22 +3225,22 @@
     </row>
     <row r="108">
       <c r="A108" s="1" t="n">
-        <v>46080</v>
+        <v>46083</v>
       </c>
       <c r="B108" t="n">
-        <v>94.30000305175781</v>
+        <v>95.26000213623047</v>
       </c>
       <c r="C108" t="n">
-        <v>96.75</v>
+        <v>98.06999969482422</v>
       </c>
       <c r="D108" t="n">
-        <v>90.58000183105469</v>
+        <v>95.19999694824219</v>
       </c>
       <c r="E108" t="n">
-        <v>96.23999786376953</v>
+        <v>97.08999633789062</v>
       </c>
       <c r="F108" t="n">
-        <v>200767000</v>
+        <v>79915400</v>
       </c>
       <c r="G108" t="n">
         <v>0</v>
@@ -3251,22 +3251,22 @@
     </row>
     <row r="109">
       <c r="A109" s="1" t="n">
-        <v>46083</v>
+        <v>46084</v>
       </c>
       <c r="B109" t="n">
-        <v>95.26000213623047</v>
+        <v>96.01000213623047</v>
       </c>
       <c r="C109" t="n">
-        <v>98.06999969482422</v>
+        <v>98.45999908447266</v>
       </c>
       <c r="D109" t="n">
-        <v>95.19999694824219</v>
+        <v>95.33000183105469</v>
       </c>
       <c r="E109" t="n">
-        <v>97.08999633789062</v>
+        <v>97.69999694824219</v>
       </c>
       <c r="F109" t="n">
-        <v>79915400</v>
+        <v>59149000</v>
       </c>
       <c r="G109" t="n">
         <v>0</v>
@@ -3277,22 +3277,22 @@
     </row>
     <row r="110">
       <c r="A110" s="1" t="n">
-        <v>46084</v>
+        <v>46085</v>
       </c>
       <c r="B110" t="n">
-        <v>96.01000213623047</v>
+        <v>97.11000061035156</v>
       </c>
       <c r="C110" t="n">
-        <v>98.45999908447266</v>
+        <v>99.75</v>
       </c>
       <c r="D110" t="n">
-        <v>95.33000183105469</v>
+        <v>96.98999786376953</v>
       </c>
       <c r="E110" t="n">
-        <v>97.69999694824219</v>
+        <v>98.66000366210938</v>
       </c>
       <c r="F110" t="n">
-        <v>59149000</v>
+        <v>52604300</v>
       </c>
       <c r="G110" t="n">
         <v>0</v>
@@ -3303,22 +3303,22 @@
     </row>
     <row r="111">
       <c r="A111" s="1" t="n">
-        <v>46085</v>
+        <v>46086</v>
       </c>
       <c r="B111" t="n">
-        <v>97.11000061035156</v>
+        <v>98.5</v>
       </c>
       <c r="C111" t="n">
-        <v>99.75</v>
+        <v>100.1900024414062</v>
       </c>
       <c r="D111" t="n">
-        <v>96.98999786376953</v>
+        <v>98.09999847412109</v>
       </c>
       <c r="E111" t="n">
-        <v>98.66000366210938</v>
+        <v>99.16999816894531</v>
       </c>
       <c r="F111" t="n">
-        <v>52604300</v>
+        <v>53403000</v>
       </c>
       <c r="G111" t="n">
         <v>0</v>
@@ -3329,22 +3329,22 @@
     </row>
     <row r="112">
       <c r="A112" s="1" t="n">
-        <v>46086</v>
+        <v>46087</v>
       </c>
       <c r="B112" t="n">
-        <v>98.5</v>
+        <v>99.33000183105469</v>
       </c>
       <c r="C112" t="n">
-        <v>100.1900024414062</v>
+        <v>99.87999725341797</v>
       </c>
       <c r="D112" t="n">
-        <v>98.09999847412109</v>
+        <v>97.40000152587891</v>
       </c>
       <c r="E112" t="n">
-        <v>99.16999816894531</v>
+        <v>99.01999664306641</v>
       </c>
       <c r="F112" t="n">
-        <v>53403000</v>
+        <v>41196300</v>
       </c>
       <c r="G112" t="n">
         <v>0</v>
@@ -3355,22 +3355,22 @@
     </row>
     <row r="113">
       <c r="A113" s="1" t="n">
-        <v>46087</v>
+        <v>46090</v>
       </c>
       <c r="B113" t="n">
-        <v>99.33000183105469</v>
+        <v>97.69999694824219</v>
       </c>
       <c r="C113" t="n">
-        <v>99.87999725341797</v>
+        <v>98.94000244140625</v>
       </c>
       <c r="D113" t="n">
-        <v>97.40000152587891</v>
+        <v>96.58000183105469</v>
       </c>
       <c r="E113" t="n">
-        <v>99.01999664306641</v>
+        <v>98.31999969482422</v>
       </c>
       <c r="F113" t="n">
-        <v>41196300</v>
+        <v>48589000</v>
       </c>
       <c r="G113" t="n">
         <v>0</v>
@@ -3381,22 +3381,22 @@
     </row>
     <row r="114">
       <c r="A114" s="1" t="n">
-        <v>46090</v>
+        <v>46091</v>
       </c>
       <c r="B114" t="n">
-        <v>97.69999694824219</v>
+        <v>97.80999755859375</v>
       </c>
       <c r="C114" t="n">
-        <v>98.94000244140625</v>
+        <v>98.48999786376953</v>
       </c>
       <c r="D114" t="n">
-        <v>96.58000183105469</v>
+        <v>96.29000091552734</v>
       </c>
       <c r="E114" t="n">
-        <v>98.31999969482422</v>
+        <v>96.94000244140625</v>
       </c>
       <c r="F114" t="n">
-        <v>48589000</v>
+        <v>41027200</v>
       </c>
       <c r="G114" t="n">
         <v>0</v>
@@ -3407,22 +3407,22 @@
     </row>
     <row r="115">
       <c r="A115" s="1" t="n">
-        <v>46091</v>
+        <v>46092</v>
       </c>
       <c r="B115" t="n">
-        <v>97.80999755859375</v>
+        <v>97.41000366210938</v>
       </c>
       <c r="C115" t="n">
-        <v>98.48999786376953</v>
+        <v>98</v>
       </c>
       <c r="D115" t="n">
-        <v>96.29000091552734</v>
+        <v>94.69000244140625</v>
       </c>
       <c r="E115" t="n">
-        <v>96.94000244140625</v>
+        <v>94.88999938964844</v>
       </c>
       <c r="F115" t="n">
-        <v>41027200</v>
+        <v>33962900</v>
       </c>
       <c r="G115" t="n">
         <v>0</v>
@@ -3433,22 +3433,22 @@
     </row>
     <row r="116">
       <c r="A116" s="1" t="n">
-        <v>46092</v>
+        <v>46093</v>
       </c>
       <c r="B116" t="n">
-        <v>97.41000366210938</v>
+        <v>94.86000061035156</v>
       </c>
       <c r="C116" t="n">
-        <v>98</v>
+        <v>95.40000152587891</v>
       </c>
       <c r="D116" t="n">
-        <v>94.69000244140625</v>
+        <v>93.87000274658203</v>
       </c>
       <c r="E116" t="n">
-        <v>94.88999938964844</v>
+        <v>94.30999755859375</v>
       </c>
       <c r="F116" t="n">
-        <v>33962900</v>
+        <v>34206900</v>
       </c>
       <c r="G116" t="n">
         <v>0</v>
@@ -3459,22 +3459,22 @@
     </row>
     <row r="117">
       <c r="A117" s="1" t="n">
-        <v>46093</v>
+        <v>46094</v>
       </c>
       <c r="B117" t="n">
-        <v>94.86000061035156</v>
+        <v>94.63999938964844</v>
       </c>
       <c r="C117" t="n">
-        <v>95.40000152587891</v>
+        <v>95.68000030517578</v>
       </c>
       <c r="D117" t="n">
-        <v>93.87000274658203</v>
+        <v>94.23999786376953</v>
       </c>
       <c r="E117" t="n">
-        <v>94.30999755859375</v>
+        <v>95.30999755859375</v>
       </c>
       <c r="F117" t="n">
-        <v>34206900</v>
+        <v>29876700</v>
       </c>
       <c r="G117" t="n">
         <v>0</v>
@@ -3485,22 +3485,22 @@
     </row>
     <row r="118">
       <c r="A118" s="1" t="n">
-        <v>46094</v>
+        <v>46097</v>
       </c>
       <c r="B118" t="n">
-        <v>94.63999938964844</v>
+        <v>95.58000183105469</v>
       </c>
       <c r="C118" t="n">
-        <v>95.68000030517578</v>
+        <v>96.09999847412109</v>
       </c>
       <c r="D118" t="n">
-        <v>94.23999786376953</v>
+        <v>94.36000061035156</v>
       </c>
       <c r="E118" t="n">
-        <v>95.30999755859375</v>
+        <v>95.19999694824219</v>
       </c>
       <c r="F118" t="n">
-        <v>29876700</v>
+        <v>34931800</v>
       </c>
       <c r="G118" t="n">
         <v>0</v>
@@ -3511,22 +3511,22 @@
     </row>
     <row r="119">
       <c r="A119" s="1" t="n">
-        <v>46097</v>
+        <v>46098</v>
       </c>
       <c r="B119" t="n">
-        <v>95.58000183105469</v>
+        <v>95.30000305175781</v>
       </c>
       <c r="C119" t="n">
-        <v>96.09999847412109</v>
+        <v>96.33999633789062</v>
       </c>
       <c r="D119" t="n">
+        <v>94.01000213623047</v>
+      </c>
+      <c r="E119" t="n">
         <v>94.36000061035156</v>
       </c>
-      <c r="E119" t="n">
-        <v>95.19999694824219</v>
-      </c>
       <c r="F119" t="n">
-        <v>34931800</v>
+        <v>26434500</v>
       </c>
       <c r="G119" t="n">
         <v>0</v>
@@ -3537,22 +3537,22 @@
     </row>
     <row r="120">
       <c r="A120" s="1" t="n">
-        <v>46098</v>
+        <v>46099</v>
       </c>
       <c r="B120" t="n">
-        <v>95.30000305175781</v>
+        <v>94.44999694824219</v>
       </c>
       <c r="C120" t="n">
-        <v>96.33999633789062</v>
+        <v>95.33999633789062</v>
       </c>
       <c r="D120" t="n">
-        <v>94.01000213623047</v>
+        <v>93.61000061035156</v>
       </c>
       <c r="E120" t="n">
-        <v>94.36000061035156</v>
+        <v>94.69999694824219</v>
       </c>
       <c r="F120" t="n">
-        <v>26434500</v>
+        <v>27878300</v>
       </c>
       <c r="G120" t="n">
         <v>0</v>
@@ -3563,22 +3563,22 @@
     </row>
     <row r="121">
       <c r="A121" s="1" t="n">
-        <v>46099</v>
+        <v>46100</v>
       </c>
       <c r="B121" t="n">
-        <v>94.44999694824219</v>
+        <v>94.30999755859375</v>
       </c>
       <c r="C121" t="n">
-        <v>95.33999633789062</v>
+        <v>95.75</v>
       </c>
       <c r="D121" t="n">
-        <v>93.61000061035156</v>
+        <v>90.77999877929688</v>
       </c>
       <c r="E121" t="n">
-        <v>94.69999694824219</v>
+        <v>91.73999786376953</v>
       </c>
       <c r="F121" t="n">
-        <v>27878300</v>
+        <v>40169300</v>
       </c>
       <c r="G121" t="n">
         <v>0</v>
@@ -3589,22 +3589,22 @@
     </row>
     <row r="122">
       <c r="A122" s="1" t="n">
-        <v>46100</v>
+        <v>46101</v>
       </c>
       <c r="B122" t="n">
-        <v>94.30999755859375</v>
+        <v>91.30999755859375</v>
       </c>
       <c r="C122" t="n">
-        <v>95.75</v>
+        <v>91.87999725341797</v>
       </c>
       <c r="D122" t="n">
-        <v>90.77999877929688</v>
+        <v>90.69000244140625</v>
       </c>
       <c r="E122" t="n">
-        <v>91.73999786376953</v>
+        <v>91.81999969482422</v>
       </c>
       <c r="F122" t="n">
-        <v>40169300</v>
+        <v>61678000</v>
       </c>
       <c r="G122" t="n">
         <v>0</v>
@@ -3615,22 +3615,22 @@
     </row>
     <row r="123">
       <c r="A123" s="1" t="n">
-        <v>46101</v>
+        <v>46104</v>
       </c>
       <c r="B123" t="n">
-        <v>91.30999755859375</v>
+        <v>92.04000091552734</v>
       </c>
       <c r="C123" t="n">
-        <v>91.87999725341797</v>
+        <v>93.98000335693359</v>
       </c>
       <c r="D123" t="n">
-        <v>90.69000244140625</v>
+        <v>91.86000061035156</v>
       </c>
       <c r="E123" t="n">
-        <v>91.81999969482422</v>
+        <v>93.37999725341797</v>
       </c>
       <c r="F123" t="n">
-        <v>61678000</v>
+        <v>34315900</v>
       </c>
       <c r="G123" t="n">
         <v>0</v>
@@ -3641,22 +3641,22 @@
     </row>
     <row r="124">
       <c r="A124" s="1" t="n">
-        <v>46104</v>
+        <v>46105</v>
       </c>
       <c r="B124" t="n">
-        <v>92.04000091552734</v>
+        <v>92.79000091552734</v>
       </c>
       <c r="C124" t="n">
-        <v>93.98000335693359</v>
+        <v>93.73999786376953</v>
       </c>
       <c r="D124" t="n">
-        <v>91.86000061035156</v>
+        <v>90.81999969482422</v>
       </c>
       <c r="E124" t="n">
-        <v>93.37999725341797</v>
+        <v>90.91999816894531</v>
       </c>
       <c r="F124" t="n">
-        <v>34315900</v>
+        <v>28938000</v>
       </c>
       <c r="G124" t="n">
         <v>0</v>
@@ -3667,22 +3667,22 @@
     </row>
     <row r="125">
       <c r="A125" s="1" t="n">
-        <v>46105</v>
+        <v>46106</v>
       </c>
       <c r="B125" t="n">
-        <v>92.79000091552734</v>
+        <v>91.70999908447266</v>
       </c>
       <c r="C125" t="n">
-        <v>93.73999786376953</v>
+        <v>92.51999664306641</v>
       </c>
       <c r="D125" t="n">
-        <v>90.81999969482422</v>
+        <v>91.23999786376953</v>
       </c>
       <c r="E125" t="n">
-        <v>90.91999816894531</v>
+        <v>92.27999877929688</v>
       </c>
       <c r="F125" t="n">
-        <v>28938000</v>
+        <v>29545600</v>
       </c>
       <c r="G125" t="n">
         <v>0</v>
@@ -3693,22 +3693,22 @@
     </row>
     <row r="126">
       <c r="A126" s="1" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B126" t="n">
-        <v>91.70999908447266</v>
+        <v>91.51999664306641</v>
       </c>
       <c r="C126" t="n">
-        <v>92.51999664306641</v>
+        <v>95.86000061035156</v>
       </c>
       <c r="D126" t="n">
-        <v>91.23999786376953</v>
+        <v>91.01000213623047</v>
       </c>
       <c r="E126" t="n">
-        <v>92.27999877929688</v>
+        <v>93.31999969482422</v>
       </c>
       <c r="F126" t="n">
-        <v>29545600</v>
+        <v>59522000</v>
       </c>
       <c r="G126" t="n">
         <v>0</v>
@@ -3719,22 +3719,22 @@
     </row>
     <row r="127">
       <c r="A127" s="1" t="n">
-        <v>46107</v>
+        <v>46108</v>
       </c>
       <c r="B127" t="n">
-        <v>91.51999664306641</v>
+        <v>94.56999969482422</v>
       </c>
       <c r="C127" t="n">
-        <v>95.86000061035156</v>
+        <v>95.58000183105469</v>
       </c>
       <c r="D127" t="n">
-        <v>91.01000213623047</v>
+        <v>92.73999786376953</v>
       </c>
       <c r="E127" t="n">
-        <v>93.31999969482422</v>
+        <v>93.43000030517578</v>
       </c>
       <c r="F127" t="n">
-        <v>59522000</v>
+        <v>44590700</v>
       </c>
       <c r="G127" t="n">
         <v>0</v>
@@ -3745,22 +3745,22 @@
     </row>
     <row r="128">
       <c r="A128" s="1" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B128" t="n">
-        <v>94.56999969482422</v>
+        <v>92.75</v>
       </c>
       <c r="C128" t="n">
-        <v>95.58000183105469</v>
+        <v>94.48999786376953</v>
       </c>
       <c r="D128" t="n">
-        <v>92.73999786376953</v>
+        <v>92.22000122070312</v>
       </c>
       <c r="E128" t="n">
-        <v>93.43000030517578</v>
+        <v>92.97000122070312</v>
       </c>
       <c r="F128" t="n">
-        <v>44590700</v>
+        <v>32375100</v>
       </c>
       <c r="G128" t="n">
         <v>0</v>
@@ -3771,22 +3771,22 @@
     </row>
     <row r="129">
       <c r="A129" s="1" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B129" t="n">
-        <v>92.75</v>
+        <v>93.02999877929688</v>
       </c>
       <c r="C129" t="n">
-        <v>94.48999786376953</v>
+        <v>96.26000213623047</v>
       </c>
       <c r="D129" t="n">
-        <v>92.22000122070312</v>
+        <v>93.02999877929688</v>
       </c>
       <c r="E129" t="n">
-        <v>92.97000122070312</v>
+        <v>96.15000152587891</v>
       </c>
       <c r="F129" t="n">
-        <v>32375100</v>
+        <v>54270000</v>
       </c>
       <c r="G129" t="n">
         <v>0</v>
@@ -3797,22 +3797,22 @@
     </row>
     <row r="130">
       <c r="A130" s="1" t="n">
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="B130" t="n">
-        <v>93.02999877929688</v>
+        <v>96.47000122070312</v>
       </c>
       <c r="C130" t="n">
-        <v>96.26000213623047</v>
+        <v>97.19999694824219</v>
       </c>
       <c r="D130" t="n">
-        <v>93.02999877929688</v>
+        <v>94.26000213623047</v>
       </c>
       <c r="E130" t="n">
-        <v>96.15000152587891</v>
+        <v>95.55000305175781</v>
       </c>
       <c r="F130" t="n">
-        <v>54270000</v>
+        <v>30439300</v>
       </c>
       <c r="G130" t="n">
         <v>0</v>
@@ -3823,22 +3823,22 @@
     </row>
     <row r="131">
       <c r="A131" s="1" t="n">
-        <v>46113</v>
+        <v>46114</v>
       </c>
       <c r="B131" t="n">
-        <v>96.47000122070312</v>
+        <v>95.26999664306641</v>
       </c>
       <c r="C131" t="n">
-        <v>97.19999694824219</v>
+        <v>98.70999908447266</v>
       </c>
       <c r="D131" t="n">
-        <v>94.26000213623047</v>
+        <v>95.16999816894531</v>
       </c>
       <c r="E131" t="n">
-        <v>95.55000305175781</v>
+        <v>98.66000366210938</v>
       </c>
       <c r="F131" t="n">
-        <v>30439300</v>
+        <v>37068000</v>
       </c>
       <c r="G131" t="n">
         <v>0</v>
@@ -3849,22 +3849,22 @@
     </row>
     <row r="132">
       <c r="A132" s="1" t="n">
-        <v>46114</v>
+        <v>46118</v>
       </c>
       <c r="B132" t="n">
-        <v>95.26999664306641</v>
+        <v>100.9599990844727</v>
       </c>
       <c r="C132" t="n">
-        <v>98.70999908447266</v>
+        <v>102.6900024414062</v>
       </c>
       <c r="D132" t="n">
-        <v>95.16999816894531</v>
+        <v>97.97000122070312</v>
       </c>
       <c r="E132" t="n">
-        <v>98.66000366210938</v>
+        <v>98.93000030517578</v>
       </c>
       <c r="F132" t="n">
-        <v>37068000</v>
+        <v>37029300</v>
       </c>
       <c r="G132" t="n">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="133">
       <c r="A133" s="1" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B133" t="n">
-        <v>100.9599990844727</v>
+        <v>98.55000305175781</v>
       </c>
       <c r="C133" t="n">
-        <v>102.6900024414062</v>
+        <v>99.87999725341797</v>
       </c>
       <c r="D133" t="n">
-        <v>97.97000122070312</v>
+        <v>98.25</v>
       </c>
       <c r="E133" t="n">
-        <v>98.93000030517578</v>
+        <v>98.81999969482422</v>
       </c>
       <c r="F133" t="n">
-        <v>37029300</v>
+        <v>25016700</v>
       </c>
       <c r="G133" t="n">
         <v>0</v>
@@ -3901,22 +3901,22 @@
     </row>
     <row r="134">
       <c r="A134" s="1" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B134" t="n">
-        <v>98.55000305175781</v>
+        <v>100.3199996948242</v>
       </c>
       <c r="C134" t="n">
-        <v>99.87999725341797</v>
+        <v>100.4000015258789</v>
       </c>
       <c r="D134" t="n">
-        <v>98.25</v>
+        <v>97.44000244140625</v>
       </c>
       <c r="E134" t="n">
-        <v>98.81999969482422</v>
+        <v>99.38999938964844</v>
       </c>
       <c r="F134" t="n">
-        <v>25016700</v>
+        <v>30957600</v>
       </c>
       <c r="G134" t="n">
         <v>0</v>
@@ -3927,22 +3927,22 @@
     </row>
     <row r="135">
       <c r="A135" s="1" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B135" t="n">
-        <v>100.3199996948242</v>
+        <v>99.62999725341797</v>
       </c>
       <c r="C135" t="n">
-        <v>100.4000015258789</v>
+        <v>102.3399963378906</v>
       </c>
       <c r="D135" t="n">
-        <v>97.44000244140625</v>
+        <v>99.08000183105469</v>
       </c>
       <c r="E135" t="n">
-        <v>99.38999938964844</v>
+        <v>102.0500030517578</v>
       </c>
       <c r="F135" t="n">
-        <v>30957600</v>
+        <v>35087800</v>
       </c>
       <c r="G135" t="n">
         <v>0</v>
@@ -3953,22 +3953,22 @@
     </row>
     <row r="136">
       <c r="A136" s="1" t="n">
-        <v>46121</v>
+        <v>46122</v>
       </c>
       <c r="B136" t="n">
-        <v>99.62999725341797</v>
+        <v>102.4700012207031</v>
       </c>
       <c r="C136" t="n">
-        <v>102.3399963378906</v>
+        <v>103.0800018310547</v>
       </c>
       <c r="D136" t="n">
-        <v>99.08000183105469</v>
+        <v>101.4599990844727</v>
       </c>
       <c r="E136" t="n">
-        <v>102.0500030517578</v>
+        <v>103.0100021362305</v>
       </c>
       <c r="F136" t="n">
-        <v>35087800</v>
+        <v>25769900</v>
       </c>
       <c r="G136" t="n">
         <v>0</v>
@@ -3979,22 +3979,22 @@
     </row>
     <row r="137">
       <c r="A137" s="1" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B137" t="n">
-        <v>102.4700012207031</v>
+        <v>103.0299987792969</v>
       </c>
       <c r="C137" t="n">
-        <v>103.0800018310547</v>
+        <v>103.6699981689453</v>
       </c>
       <c r="D137" t="n">
-        <v>101.4599990844727</v>
+        <v>102.0599975585938</v>
       </c>
       <c r="E137" t="n">
-        <v>103.0100021362305</v>
+        <v>103.1600036621094</v>
       </c>
       <c r="F137" t="n">
-        <v>25769900</v>
+        <v>26042800</v>
       </c>
       <c r="G137" t="n">
         <v>0</v>
@@ -4005,22 +4005,22 @@
     </row>
     <row r="138">
       <c r="A138" s="1" t="n">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="B138" t="n">
-        <v>103.0299987792969</v>
+        <v>103.120002746582</v>
       </c>
       <c r="C138" t="n">
-        <v>103.6699981689453</v>
+        <v>106.5699996948242</v>
       </c>
       <c r="D138" t="n">
-        <v>102.0599975585938</v>
+        <v>103.0400009155273</v>
       </c>
       <c r="E138" t="n">
-        <v>103.1600036621094</v>
+        <v>106.2799987792969</v>
       </c>
       <c r="F138" t="n">
-        <v>26042800</v>
+        <v>40534900</v>
       </c>
       <c r="G138" t="n">
         <v>0</v>
@@ -4031,22 +4031,22 @@
     </row>
     <row r="139">
       <c r="A139" s="1" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B139" t="n">
-        <v>103.120002746582</v>
+        <v>105.9800033569336</v>
       </c>
       <c r="C139" t="n">
-        <v>106.5699996948242</v>
+        <v>107.8499984741211</v>
       </c>
       <c r="D139" t="n">
-        <v>103.0400009155273</v>
+        <v>105.0400009155273</v>
       </c>
       <c r="E139" t="n">
-        <v>106.2799987792969</v>
+        <v>107.7099990844727</v>
       </c>
       <c r="F139" t="n">
-        <v>40534900</v>
+        <v>38023700</v>
       </c>
       <c r="G139" t="n">
         <v>0</v>
@@ -4057,22 +4057,22 @@
     </row>
     <row r="140">
       <c r="A140" s="1" t="n">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c r="B140" t="n">
-        <v>105.9800033569336</v>
+        <v>107.4700012207031</v>
       </c>
       <c r="C140" t="n">
-        <v>107.8499984741211</v>
+        <v>108.9499969482422</v>
       </c>
       <c r="D140" t="n">
-        <v>105.0400009155273</v>
+        <v>106.620002746582</v>
       </c>
       <c r="E140" t="n">
-        <v>107.7099990844727</v>
+        <v>107.7900009155273</v>
       </c>
       <c r="F140" t="n">
-        <v>38023700</v>
+        <v>64928300</v>
       </c>
       <c r="G140" t="n">
         <v>0</v>
@@ -4083,22 +4083,22 @@
     </row>
     <row r="141">
       <c r="A141" s="1" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B141" t="n">
-        <v>107.4700012207031</v>
+        <v>96.37000274658203</v>
       </c>
       <c r="C141" t="n">
-        <v>108.9499969482422</v>
+        <v>98.73999786376953</v>
       </c>
       <c r="D141" t="n">
-        <v>106.620002746582</v>
+        <v>95.09999847412109</v>
       </c>
       <c r="E141" t="n">
-        <v>107.7900009155273</v>
+        <v>97.30999755859375</v>
       </c>
       <c r="F141" t="n">
-        <v>64928300</v>
+        <v>125958700</v>
       </c>
       <c r="G141" t="n">
         <v>0</v>
@@ -4109,22 +4109,22 @@
     </row>
     <row r="142">
       <c r="A142" s="1" t="n">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c r="B142" t="n">
-        <v>96.37000274658203</v>
+        <v>97.13999938964844</v>
       </c>
       <c r="C142" t="n">
-        <v>98.73999786376953</v>
+        <v>97.59999847412109</v>
       </c>
       <c r="D142" t="n">
-        <v>95.09999847412109</v>
+        <v>93.54000091552734</v>
       </c>
       <c r="E142" t="n">
-        <v>97.30999755859375</v>
+        <v>94.83000183105469</v>
       </c>
       <c r="F142" t="n">
-        <v>125958700</v>
+        <v>63298300</v>
       </c>
       <c r="G142" t="n">
         <v>0</v>
@@ -4135,22 +4135,22 @@
     </row>
     <row r="143">
       <c r="A143" s="1" t="n">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="B143" t="n">
-        <v>97.13999938964844</v>
+        <v>94</v>
       </c>
       <c r="C143" t="n">
-        <v>97.59999847412109</v>
+        <v>94.65000152587891</v>
       </c>
       <c r="D143" t="n">
-        <v>93.54000091552734</v>
+        <v>92.37000274658203</v>
       </c>
       <c r="E143" t="n">
-        <v>94.83000183105469</v>
+        <v>92.58000183105469</v>
       </c>
       <c r="F143" t="n">
-        <v>63298300</v>
+        <v>61962300</v>
       </c>
       <c r="G143" t="n">
         <v>0</v>
@@ -4161,22 +4161,22 @@
     </row>
     <row r="144">
       <c r="A144" s="1" t="n">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="B144" t="n">
-        <v>94</v>
+        <v>93.05999755859375</v>
       </c>
       <c r="C144" t="n">
-        <v>94.65000152587891</v>
+        <v>93.84999847412109</v>
       </c>
       <c r="D144" t="n">
-        <v>92.37000274658203</v>
+        <v>92.76999664306641</v>
       </c>
       <c r="E144" t="n">
-        <v>92.58000183105469</v>
+        <v>93.23999786376953</v>
       </c>
       <c r="F144" t="n">
-        <v>61962300</v>
+        <v>33694300</v>
       </c>
       <c r="G144" t="n">
         <v>0</v>
@@ -4187,22 +4187,22 @@
     </row>
     <row r="145">
       <c r="A145" s="1" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B145" t="n">
-        <v>93.05999755859375</v>
+        <v>94.05999755859375</v>
       </c>
       <c r="C145" t="n">
-        <v>93.84999847412109</v>
+        <v>94.63999938964844</v>
       </c>
       <c r="D145" t="n">
-        <v>92.76999664306641</v>
+        <v>92.06999969482422</v>
       </c>
       <c r="E145" t="n">
-        <v>93.23999786376953</v>
+        <v>92.81999969482422</v>
       </c>
       <c r="F145" t="n">
-        <v>33694300</v>
+        <v>36851700</v>
       </c>
       <c r="G145" t="n">
         <v>0</v>
@@ -4213,22 +4213,22 @@
     </row>
     <row r="146">
       <c r="A146" s="1" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B146" t="n">
-        <v>94.05999755859375</v>
+        <v>92.56999969482422</v>
       </c>
       <c r="C146" t="n">
-        <v>94.63999938964844</v>
+        <v>93.27999877929688</v>
       </c>
       <c r="D146" t="n">
-        <v>92.06999969482422</v>
+        <v>91.80000305175781</v>
       </c>
       <c r="E146" t="n">
-        <v>92.81999969482422</v>
+        <v>92.44000244140625</v>
       </c>
       <c r="F146" t="n">
-        <v>36851700</v>
+        <v>32553200</v>
       </c>
       <c r="G146" t="n">
         <v>0</v>
@@ -4239,22 +4239,22 @@
     </row>
     <row r="147">
       <c r="A147" s="1" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B147" t="n">
-        <v>92.56999969482422</v>
+        <v>92.05000305175781</v>
       </c>
       <c r="C147" t="n">
-        <v>93.27999877929688</v>
+        <v>92.83999633789062</v>
       </c>
       <c r="D147" t="n">
-        <v>91.80000305175781</v>
+        <v>91.30000305175781</v>
       </c>
       <c r="E147" t="n">
-        <v>92.44000244140625</v>
+        <v>91.37000274658203</v>
       </c>
       <c r="F147" t="n">
-        <v>32553200</v>
+        <v>29707400</v>
       </c>
       <c r="G147" t="n">
         <v>0</v>
@@ -4265,22 +4265,22 @@
     </row>
     <row r="148">
       <c r="A148" s="1" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B148" t="n">
-        <v>92.05000305175781</v>
+        <v>91.5</v>
       </c>
       <c r="C148" t="n">
-        <v>92.83999633789062</v>
+        <v>92.33999633789062</v>
       </c>
       <c r="D148" t="n">
-        <v>91.30000305175781</v>
+        <v>90.01999664306641</v>
       </c>
       <c r="E148" t="n">
-        <v>91.37000274658203</v>
+        <v>92.26999664306641</v>
       </c>
       <c r="F148" t="n">
-        <v>29707400</v>
+        <v>33418100</v>
       </c>
       <c r="G148" t="n">
         <v>0</v>
@@ -4291,22 +4291,22 @@
     </row>
     <row r="149">
       <c r="A149" s="1" t="n">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="B149" t="n">
-        <v>91.5</v>
+        <v>91.23000335693359</v>
       </c>
       <c r="C149" t="n">
-        <v>92.33999633789062</v>
+        <v>92.86000061035156</v>
       </c>
       <c r="D149" t="n">
-        <v>90.01999664306641</v>
+        <v>90.86000061035156</v>
       </c>
       <c r="E149" t="n">
-        <v>92.26999664306641</v>
+        <v>92.12000274658203</v>
       </c>
       <c r="F149" t="n">
-        <v>33418100</v>
+        <v>26122100</v>
       </c>
       <c r="G149" t="n">
         <v>0</v>
@@ -4317,22 +4317,22 @@
     </row>
     <row r="150">
       <c r="A150" s="1" t="n">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="B150" t="n">
-        <v>91.23000335693359</v>
+        <v>91.34999847412109</v>
       </c>
       <c r="C150" t="n">
-        <v>92.86000061035156</v>
+        <v>94.22000122070312</v>
       </c>
       <c r="D150" t="n">
-        <v>90.86000061035156</v>
+        <v>90.76999664306641</v>
       </c>
       <c r="E150" t="n">
-        <v>92.12000274658203</v>
+        <v>93.61000061035156</v>
       </c>
       <c r="F150" t="n">
-        <v>26122100</v>
+        <v>40923000</v>
       </c>
       <c r="G150" t="n">
         <v>0</v>
@@ -4343,22 +4343,22 @@
     </row>
     <row r="151">
       <c r="A151" s="1" t="n">
-        <v>46142</v>
+        <v>46143</v>
       </c>
       <c r="B151" t="n">
-        <v>91.34999847412109</v>
+        <v>94.41999816894531</v>
       </c>
       <c r="C151" t="n">
-        <v>94.22000122070312</v>
+        <v>94.69999694824219</v>
       </c>
       <c r="D151" t="n">
-        <v>90.76999664306641</v>
+        <v>91.90000152587891</v>
       </c>
       <c r="E151" t="n">
-        <v>93.61000061035156</v>
+        <v>92.05999755859375</v>
       </c>
       <c r="F151" t="n">
-        <v>40923000</v>
+        <v>30406900</v>
       </c>
       <c r="G151" t="n">
         <v>0</v>
@@ -4369,22 +4369,22 @@
     </row>
     <row r="152">
       <c r="A152" s="1" t="n">
-        <v>46143</v>
+        <v>46146</v>
       </c>
       <c r="B152" t="n">
-        <v>94.41999816894531</v>
+        <v>92.09999847412109</v>
       </c>
       <c r="C152" t="n">
-        <v>94.69999694824219</v>
+        <v>92.33000183105469</v>
       </c>
       <c r="D152" t="n">
-        <v>91.90000152587891</v>
+        <v>90.88999938964844</v>
       </c>
       <c r="E152" t="n">
-        <v>92.05999755859375</v>
+        <v>91.01999664306641</v>
       </c>
       <c r="F152" t="n">
-        <v>30406900</v>
+        <v>25928800</v>
       </c>
       <c r="G152" t="n">
         <v>0</v>
@@ -4395,22 +4395,22 @@
     </row>
     <row r="153">
       <c r="A153" s="1" t="n">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="B153" t="n">
-        <v>92.09999847412109</v>
+        <v>91.18000030517578</v>
       </c>
       <c r="C153" t="n">
-        <v>92.33000183105469</v>
+        <v>91.27999877929688</v>
       </c>
       <c r="D153" t="n">
-        <v>90.88999938964844</v>
+        <v>87.56999969482422</v>
       </c>
       <c r="E153" t="n">
-        <v>91.01999664306641</v>
+        <v>87.88999938964844</v>
       </c>
       <c r="F153" t="n">
-        <v>25928800</v>
+        <v>51961300</v>
       </c>
       <c r="G153" t="n">
         <v>0</v>
@@ -4421,22 +4421,22 @@
     </row>
     <row r="154">
       <c r="A154" s="1" t="n">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="B154" t="n">
-        <v>91.18000030517578</v>
+        <v>87.15000152587891</v>
       </c>
       <c r="C154" t="n">
-        <v>91.27999877929688</v>
+        <v>88.55000305175781</v>
       </c>
       <c r="D154" t="n">
-        <v>87.56999969482422</v>
+        <v>86.72000122070312</v>
       </c>
       <c r="E154" t="n">
-        <v>87.88999938964844</v>
+        <v>88.26999664306641</v>
       </c>
       <c r="F154" t="n">
-        <v>51961300</v>
+        <v>41932400</v>
       </c>
       <c r="G154" t="n">
         <v>0</v>
@@ -4447,22 +4447,22 @@
     </row>
     <row r="155">
       <c r="A155" s="1" t="n">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="B155" t="n">
-        <v>87.15000152587891</v>
+        <v>88.19999694824219</v>
       </c>
       <c r="C155" t="n">
-        <v>88.55000305175781</v>
+        <v>89.40000152587891</v>
       </c>
       <c r="D155" t="n">
-        <v>86.72000122070312</v>
+        <v>88.12999725341797</v>
       </c>
       <c r="E155" t="n">
-        <v>88.26999664306641</v>
+        <v>88.25</v>
       </c>
       <c r="F155" t="n">
-        <v>41932400</v>
+        <v>30627600</v>
       </c>
       <c r="G155" t="n">
         <v>0</v>
@@ -4473,22 +4473,22 @@
     </row>
     <row r="156">
       <c r="A156" s="1" t="n">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="B156" t="n">
-        <v>88.19999694824219</v>
+        <v>87.70999908447266</v>
       </c>
       <c r="C156" t="n">
-        <v>89.40000152587891</v>
+        <v>88.04000091552734</v>
       </c>
       <c r="D156" t="n">
-        <v>88.12999725341797</v>
+        <v>87.20999908447266</v>
       </c>
       <c r="E156" t="n">
-        <v>88.25</v>
+        <v>87.48999786376953</v>
       </c>
       <c r="F156" t="n">
-        <v>30627600</v>
+        <v>36215100</v>
       </c>
       <c r="G156" t="n">
         <v>0</v>
@@ -4499,22 +4499,22 @@
     </row>
     <row r="157">
       <c r="A157" s="1" t="n">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="B157" t="n">
-        <v>87.70999908447266</v>
+        <v>86.52999877929688</v>
       </c>
       <c r="C157" t="n">
-        <v>88.04000091552734</v>
+        <v>87.33999633789062</v>
       </c>
       <c r="D157" t="n">
-        <v>87.20999908447266</v>
+        <v>85.09999847412109</v>
       </c>
       <c r="E157" t="n">
-        <v>87.48999786376953</v>
+        <v>85.44999694824219</v>
       </c>
       <c r="F157" t="n">
-        <v>36215100</v>
+        <v>40556500</v>
       </c>
       <c r="G157" t="n">
         <v>0</v>
@@ -4525,22 +4525,22 @@
     </row>
     <row r="158">
       <c r="A158" s="1" t="n">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="B158" t="n">
-        <v>86.52999877929688</v>
+        <v>85.91000366210938</v>
       </c>
       <c r="C158" t="n">
-        <v>87.33999633789062</v>
+        <v>89.16999816894531</v>
       </c>
       <c r="D158" t="n">
-        <v>85.09999847412109</v>
+        <v>85.80999755859375</v>
       </c>
       <c r="E158" t="n">
-        <v>85.44999694824219</v>
+        <v>87.66000366210938</v>
       </c>
       <c r="F158" t="n">
-        <v>40556500</v>
+        <v>43556600</v>
       </c>
       <c r="G158" t="n">
         <v>0</v>
@@ -4551,22 +4551,22 @@
     </row>
     <row r="159">
       <c r="A159" s="1" t="n">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="B159" t="n">
-        <v>85.91000366210938</v>
+        <v>86.56999969482422</v>
       </c>
       <c r="C159" t="n">
-        <v>89.16999816894531</v>
+        <v>88.62000274658203</v>
       </c>
       <c r="D159" t="n">
-        <v>85.80999755859375</v>
+        <v>86.27999877929688</v>
       </c>
       <c r="E159" t="n">
-        <v>87.66000366210938</v>
+        <v>87.55999755859375</v>
       </c>
       <c r="F159" t="n">
-        <v>43556600</v>
+        <v>30823500</v>
       </c>
       <c r="G159" t="n">
         <v>0</v>
@@ -4577,22 +4577,22 @@
     </row>
     <row r="160">
       <c r="A160" s="1" t="n">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="B160" t="n">
-        <v>86.56999969482422</v>
+        <v>87.62000274658203</v>
       </c>
       <c r="C160" t="n">
-        <v>88.62000274658203</v>
+        <v>88.5</v>
       </c>
       <c r="D160" t="n">
-        <v>86.27999877929688</v>
+        <v>86.65000152587891</v>
       </c>
       <c r="E160" t="n">
-        <v>87.55999755859375</v>
+        <v>86.94000244140625</v>
       </c>
       <c r="F160" t="n">
-        <v>30823500</v>
+        <v>29408300</v>
       </c>
       <c r="G160" t="n">
         <v>0</v>
@@ -4603,22 +4603,22 @@
     </row>
     <row r="161">
       <c r="A161" s="1" t="n">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="B161" t="n">
-        <v>87.62000274658203</v>
+        <v>87.69000244140625</v>
       </c>
       <c r="C161" t="n">
-        <v>88.5</v>
+        <v>89.48999786376953</v>
       </c>
       <c r="D161" t="n">
-        <v>86.65000152587891</v>
+        <v>86.69000244140625</v>
       </c>
       <c r="E161" t="n">
-        <v>86.94000244140625</v>
+        <v>87.01999664306641</v>
       </c>
       <c r="F161" t="n">
-        <v>29408300</v>
+        <v>32335700</v>
       </c>
       <c r="G161" t="n">
         <v>0</v>
@@ -4629,22 +4629,22 @@
     </row>
     <row r="162">
       <c r="A162" s="1" t="n">
-        <v>46157</v>
+        <v>46160</v>
       </c>
       <c r="B162" t="n">
-        <v>87.69000244140625</v>
+        <v>86.5</v>
       </c>
       <c r="C162" t="n">
-        <v>89.48999786376953</v>
+        <v>89.81999969482422</v>
       </c>
       <c r="D162" t="n">
-        <v>86.69000244140625</v>
+        <v>86.33000183105469</v>
       </c>
       <c r="E162" t="n">
-        <v>87.01999664306641</v>
+        <v>89.65000152587891</v>
       </c>
       <c r="F162" t="n">
-        <v>32335700</v>
+        <v>35800500</v>
       </c>
       <c r="G162" t="n">
         <v>0</v>
@@ -4655,22 +4655,22 @@
     </row>
     <row r="163">
       <c r="A163" s="1" t="n">
-        <v>46160</v>
+        <v>46161</v>
       </c>
       <c r="B163" t="n">
-        <v>86.5</v>
+        <v>90.13999938964844</v>
       </c>
       <c r="C163" t="n">
-        <v>89.81999969482422</v>
+        <v>91.48000335693359</v>
       </c>
       <c r="D163" t="n">
-        <v>86.33000183105469</v>
+        <v>88.69000244140625</v>
       </c>
       <c r="E163" t="n">
-        <v>89.65000152587891</v>
+        <v>89.33000183105469</v>
       </c>
       <c r="F163" t="n">
-        <v>35800500</v>
+        <v>34545700</v>
       </c>
       <c r="G163" t="n">
         <v>0</v>
@@ -4681,22 +4681,22 @@
     </row>
     <row r="164">
       <c r="A164" s="1" t="n">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="B164" t="n">
-        <v>90.13999938964844</v>
+        <v>88.51999664306641</v>
       </c>
       <c r="C164" t="n">
-        <v>91.48000335693359</v>
+        <v>88.55000305175781</v>
       </c>
       <c r="D164" t="n">
-        <v>88.69000244140625</v>
+        <v>87.5</v>
       </c>
       <c r="E164" t="n">
-        <v>89.33000183105469</v>
+        <v>88.08999633789062</v>
       </c>
       <c r="F164" t="n">
-        <v>34545700</v>
+        <v>23463400</v>
       </c>
       <c r="G164" t="n">
         <v>0</v>
@@ -4707,22 +4707,22 @@
     </row>
     <row r="165">
       <c r="A165" s="1" t="n">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="B165" t="n">
-        <v>88.51999664306641</v>
+        <v>88.02999877929688</v>
       </c>
       <c r="C165" t="n">
-        <v>88.55000305175781</v>
+        <v>90.37000274658203</v>
       </c>
       <c r="D165" t="n">
-        <v>87.5</v>
+        <v>87.51999664306641</v>
       </c>
       <c r="E165" t="n">
-        <v>88.08999633789062</v>
+        <v>89.30000305175781</v>
       </c>
       <c r="F165" t="n">
-        <v>23463400</v>
+        <v>28613900</v>
       </c>
       <c r="G165" t="n">
         <v>0</v>
@@ -4733,22 +4733,22 @@
     </row>
     <row r="166">
       <c r="A166" s="1" t="n">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="B166" t="n">
-        <v>88.02999877929688</v>
+        <v>89.09999847412109</v>
       </c>
       <c r="C166" t="n">
-        <v>90.37000274658203</v>
+        <v>89.97000122070312</v>
       </c>
       <c r="D166" t="n">
-        <v>87.51999664306641</v>
+        <v>88.16999816894531</v>
       </c>
       <c r="E166" t="n">
-        <v>89.30000305175781</v>
+        <v>88.59999847412109</v>
       </c>
       <c r="F166" t="n">
-        <v>28613900</v>
+        <v>23847200</v>
       </c>
       <c r="G166" t="n">
         <v>0</v>
@@ -4759,22 +4759,22 @@
     </row>
     <row r="167">
       <c r="A167" s="1" t="n">
-        <v>46164</v>
+        <v>46168</v>
       </c>
       <c r="B167" t="n">
-        <v>89.09999847412109</v>
+        <v>88.40000152587891</v>
       </c>
       <c r="C167" t="n">
-        <v>89.97000122070312</v>
+        <v>88.73000335693359</v>
       </c>
       <c r="D167" t="n">
-        <v>88.16999816894531</v>
+        <v>87.25</v>
       </c>
       <c r="E167" t="n">
-        <v>88.59999847412109</v>
+        <v>87.68000030517578</v>
       </c>
       <c r="F167" t="n">
-        <v>23847200</v>
+        <v>24014500</v>
       </c>
       <c r="G167" t="n">
         <v>0</v>
@@ -4785,22 +4785,22 @@
     </row>
     <row r="168">
       <c r="A168" s="1" t="n">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="B168" t="n">
-        <v>88.40000152587891</v>
+        <v>87.05000305175781</v>
       </c>
       <c r="C168" t="n">
-        <v>88.73000335693359</v>
+        <v>88.5</v>
       </c>
       <c r="D168" t="n">
-        <v>87.25</v>
+        <v>86.81999969482422</v>
       </c>
       <c r="E168" t="n">
-        <v>87.68000030517578</v>
+        <v>87.34999847412109</v>
       </c>
       <c r="F168" t="n">
-        <v>24014500</v>
+        <v>22569500</v>
       </c>
       <c r="G168" t="n">
         <v>0</v>
@@ -4811,22 +4811,22 @@
     </row>
     <row r="169">
       <c r="A169" s="1" t="n">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="B169" t="n">
-        <v>87.05000305175781</v>
+        <v>86.90000152587891</v>
       </c>
       <c r="C169" t="n">
-        <v>88.5</v>
+        <v>87.04000091552734</v>
       </c>
       <c r="D169" t="n">
-        <v>86.81999969482422</v>
+        <v>85.58999633789062</v>
       </c>
       <c r="E169" t="n">
-        <v>87.34999847412109</v>
+        <v>86.36000061035156</v>
       </c>
       <c r="F169" t="n">
-        <v>22569500</v>
+        <v>38803800</v>
       </c>
       <c r="G169" t="n">
         <v>0</v>
@@ -4837,22 +4837,22 @@
     </row>
     <row r="170">
       <c r="A170" s="1" t="n">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="B170" t="n">
-        <v>86.90000152587891</v>
+        <v>86.19999694824219</v>
       </c>
       <c r="C170" t="n">
-        <v>87.04000091552734</v>
+        <v>86.66999816894531</v>
       </c>
       <c r="D170" t="n">
-        <v>85.58999633789062</v>
+        <v>85.66000366210938</v>
       </c>
       <c r="E170" t="n">
-        <v>86.36000061035156</v>
+        <v>86.01999664306641</v>
       </c>
       <c r="F170" t="n">
-        <v>38803800</v>
+        <v>39793600</v>
       </c>
       <c r="G170" t="n">
         <v>0</v>
@@ -4863,22 +4863,22 @@
     </row>
     <row r="171">
       <c r="A171" s="1" t="n">
-        <v>46171</v>
+        <v>46174</v>
       </c>
       <c r="B171" t="n">
-        <v>86.19999694824219</v>
+        <v>85.73000335693359</v>
       </c>
       <c r="C171" t="n">
-        <v>86.66999816894531</v>
+        <v>87.23000335693359</v>
       </c>
       <c r="D171" t="n">
-        <v>85.66000366210938</v>
+        <v>85.31999969482422</v>
       </c>
       <c r="E171" t="n">
-        <v>86.01999664306641</v>
+        <v>85.84999847412109</v>
       </c>
       <c r="F171" t="n">
-        <v>39793600</v>
+        <v>32747200</v>
       </c>
       <c r="G171" t="n">
         <v>0</v>
@@ -4889,22 +4889,22 @@
     </row>
     <row r="172">
       <c r="A172" s="1" t="n">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="B172" t="n">
-        <v>85.73000335693359</v>
+        <v>85.61000061035156</v>
       </c>
       <c r="C172" t="n">
-        <v>87.23000335693359</v>
+        <v>85.98000335693359</v>
       </c>
       <c r="D172" t="n">
-        <v>85.31999969482422</v>
+        <v>83.29000091552734</v>
       </c>
       <c r="E172" t="n">
-        <v>85.84999847412109</v>
+        <v>83.33000183105469</v>
       </c>
       <c r="F172" t="n">
-        <v>32747200</v>
+        <v>42947200</v>
       </c>
       <c r="G172" t="n">
         <v>0</v>
@@ -4915,22 +4915,22 @@
     </row>
     <row r="173">
       <c r="A173" s="1" t="n">
-        <v>46175</v>
+        <v>46176</v>
       </c>
       <c r="B173" t="n">
-        <v>85.61000061035156</v>
+        <v>82.91000366210938</v>
       </c>
       <c r="C173" t="n">
-        <v>85.98000335693359</v>
+        <v>83.30999755859375</v>
       </c>
       <c r="D173" t="n">
-        <v>83.29000091552734</v>
+        <v>81.09999847412109</v>
       </c>
       <c r="E173" t="n">
-        <v>83.33000183105469</v>
+        <v>81.51999664306641</v>
       </c>
       <c r="F173" t="n">
-        <v>42947200</v>
+        <v>36714700</v>
       </c>
       <c r="G173" t="n">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="174">
       <c r="A174" s="1" t="n">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="B174" t="n">
-        <v>82.91000366210938</v>
+        <v>83.19000244140625</v>
       </c>
       <c r="C174" t="n">
-        <v>83.30999755859375</v>
+        <v>83.69999694824219</v>
       </c>
       <c r="D174" t="n">
-        <v>81.09999847412109</v>
+        <v>81.37000274658203</v>
       </c>
       <c r="E174" t="n">
-        <v>81.51999664306641</v>
+        <v>81.55999755859375</v>
       </c>
       <c r="F174" t="n">
-        <v>36714700</v>
+        <v>39338800</v>
       </c>
       <c r="G174" t="n">
         <v>0</v>
@@ -4967,22 +4967,22 @@
     </row>
     <row r="175">
       <c r="A175" s="1" t="n">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="B175" t="n">
-        <v>83.19000244140625</v>
+        <v>82.33000183105469</v>
       </c>
       <c r="C175" t="n">
-        <v>83.69999694824219</v>
+        <v>82.75</v>
       </c>
       <c r="D175" t="n">
-        <v>81.37000274658203</v>
+        <v>81</v>
       </c>
       <c r="E175" t="n">
-        <v>81.55999755859375</v>
+        <v>82.18000030517578</v>
       </c>
       <c r="F175" t="n">
-        <v>39338800</v>
+        <v>43474100</v>
       </c>
       <c r="G175" t="n">
         <v>0</v>
@@ -4993,22 +4993,22 @@
     </row>
     <row r="176">
       <c r="A176" s="1" t="n">
-        <v>46178</v>
+        <v>46181</v>
       </c>
       <c r="B176" t="n">
-        <v>82.33000183105469</v>
+        <v>81.66000366210938</v>
       </c>
       <c r="C176" t="n">
-        <v>82.75</v>
+        <v>83.08000183105469</v>
       </c>
       <c r="D176" t="n">
-        <v>81</v>
+        <v>81.33999633789062</v>
       </c>
       <c r="E176" t="n">
-        <v>82.18000030517578</v>
+        <v>82.63999938964844</v>
       </c>
       <c r="F176" t="n">
-        <v>43474100</v>
+        <v>33056700</v>
       </c>
       <c r="G176" t="n">
         <v>0</v>
@@ -5019,22 +5019,22 @@
     </row>
     <row r="177">
       <c r="A177" s="1" t="n">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="B177" t="n">
-        <v>81.66000366210938</v>
+        <v>82.12999725341797</v>
       </c>
       <c r="C177" t="n">
-        <v>83.08000183105469</v>
+        <v>82.33999633789062</v>
       </c>
       <c r="D177" t="n">
         <v>81.33999633789062</v>
       </c>
       <c r="E177" t="n">
-        <v>82.63999938964844</v>
+        <v>81.41000366210938</v>
       </c>
       <c r="F177" t="n">
-        <v>33056700</v>
+        <v>34787200</v>
       </c>
       <c r="G177" t="n">
         <v>0</v>
@@ -5045,22 +5045,22 @@
     </row>
     <row r="178">
       <c r="A178" s="1" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="B178" t="n">
-        <v>82.12999725341797</v>
+        <v>81.70999908447266</v>
       </c>
       <c r="C178" t="n">
-        <v>82.33999633789062</v>
+        <v>82.75</v>
       </c>
       <c r="D178" t="n">
-        <v>81.33999633789062</v>
+        <v>80.98000335693359</v>
       </c>
       <c r="E178" t="n">
-        <v>81.41000366210938</v>
+        <v>82</v>
       </c>
       <c r="F178" t="n">
-        <v>34787200</v>
+        <v>36304600</v>
       </c>
       <c r="G178" t="n">
         <v>0</v>
@@ -5071,22 +5071,22 @@
     </row>
     <row r="179">
       <c r="A179" s="1" t="n">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="B179" t="n">
-        <v>81.70999908447266</v>
+        <v>81.87000274658203</v>
       </c>
       <c r="C179" t="n">
-        <v>82.75</v>
+        <v>82.09999847412109</v>
       </c>
       <c r="D179" t="n">
-        <v>80.98000335693359</v>
+        <v>80.08999633789062</v>
       </c>
       <c r="E179" t="n">
-        <v>82</v>
+        <v>81.26999664306641</v>
       </c>
       <c r="F179" t="n">
-        <v>36304600</v>
+        <v>33417600</v>
       </c>
       <c r="G179" t="n">
         <v>0</v>
@@ -5097,22 +5097,22 @@
     </row>
     <row r="180">
       <c r="A180" s="1" t="n">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="B180" t="n">
-        <v>81.87000274658203</v>
+        <v>81.58000183105469</v>
       </c>
       <c r="C180" t="n">
-        <v>82.09999847412109</v>
+        <v>82</v>
       </c>
       <c r="D180" t="n">
-        <v>80.08999633789062</v>
+        <v>79.27999877929688</v>
       </c>
       <c r="E180" t="n">
-        <v>81.26999664306641</v>
+        <v>80.33999633789062</v>
       </c>
       <c r="F180" t="n">
-        <v>33417600</v>
+        <v>35309700</v>
       </c>
       <c r="G180" t="n">
         <v>0</v>
@@ -5123,22 +5123,22 @@
     </row>
     <row r="181">
       <c r="A181" s="1" t="n">
-        <v>46185</v>
+        <v>46188</v>
       </c>
       <c r="B181" t="n">
-        <v>81.58000183105469</v>
+        <v>80.62000274658203</v>
       </c>
       <c r="C181" t="n">
-        <v>82</v>
+        <v>81.70999908447266</v>
       </c>
       <c r="D181" t="n">
-        <v>79.27999877929688</v>
+        <v>80.45999908447266</v>
       </c>
       <c r="E181" t="n">
-        <v>80.33999633789062</v>
+        <v>81.66999816894531</v>
       </c>
       <c r="F181" t="n">
-        <v>35309700</v>
+        <v>36430800</v>
       </c>
       <c r="G181" t="n">
         <v>0</v>
@@ -5149,22 +5149,22 @@
     </row>
     <row r="182">
       <c r="A182" s="1" t="n">
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="B182" t="n">
-        <v>80.62000274658203</v>
+        <v>81.90000152587891</v>
       </c>
       <c r="C182" t="n">
-        <v>81.70999908447266</v>
+        <v>81.93000030517578</v>
       </c>
       <c r="D182" t="n">
-        <v>80.45999908447266</v>
+        <v>77.70999908447266</v>
       </c>
       <c r="E182" t="n">
-        <v>81.66999816894531</v>
+        <v>78.72000122070312</v>
       </c>
       <c r="F182" t="n">
-        <v>36430800</v>
+        <v>65054000</v>
       </c>
       <c r="G182" t="n">
         <v>0</v>
@@ -5175,22 +5175,22 @@
     </row>
     <row r="183">
       <c r="A183" s="1" t="n">
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="B183" t="n">
-        <v>81.90000152587891</v>
+        <v>78.09999847412109</v>
       </c>
       <c r="C183" t="n">
-        <v>81.93000030517578</v>
+        <v>78.44999694824219</v>
       </c>
       <c r="D183" t="n">
-        <v>77.70999908447266</v>
+        <v>76.76000213623047</v>
       </c>
       <c r="E183" t="n">
-        <v>78.72000122070312</v>
+        <v>76.95999908447266</v>
       </c>
       <c r="F183" t="n">
-        <v>65054000</v>
+        <v>50338800</v>
       </c>
       <c r="G183" t="n">
         <v>0</v>
@@ -5201,22 +5201,22 @@
     </row>
     <row r="184">
       <c r="A184" s="1" t="n">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="B184" t="n">
-        <v>78.09999847412109</v>
+        <v>76.93000030517578</v>
       </c>
       <c r="C184" t="n">
-        <v>78.44999694824219</v>
+        <v>78.23999786376953</v>
       </c>
       <c r="D184" t="n">
-        <v>76.76000213623047</v>
+        <v>76.12000274658203</v>
       </c>
       <c r="E184" t="n">
-        <v>76.95999908447266</v>
+        <v>77.37999725341797</v>
       </c>
       <c r="F184" t="n">
-        <v>50338800</v>
+        <v>91920400</v>
       </c>
       <c r="G184" t="n">
         <v>0</v>
@@ -5227,22 +5227,22 @@
     </row>
     <row r="185">
       <c r="A185" s="1" t="n">
-        <v>46191</v>
+        <v>46195</v>
       </c>
       <c r="B185" t="n">
-        <v>76.93000030517578</v>
+        <v>76.13999938964844</v>
       </c>
       <c r="C185" t="n">
-        <v>78.23999786376953</v>
+        <v>77.08999633789062</v>
       </c>
       <c r="D185" t="n">
-        <v>76.12000274658203</v>
+        <v>71.80999755859375</v>
       </c>
       <c r="E185" t="n">
-        <v>77.37999725341797</v>
+        <v>72.87999725341797</v>
       </c>
       <c r="F185" t="n">
-        <v>91920400</v>
+        <v>82203300</v>
       </c>
       <c r="G185" t="n">
         <v>0</v>
@@ -5253,22 +5253,22 @@
     </row>
     <row r="186">
       <c r="A186" s="1" t="n">
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="B186" t="n">
-        <v>76.13999938964844</v>
+        <v>73.26000213623047</v>
       </c>
       <c r="C186" t="n">
-        <v>77.08999633789062</v>
+        <v>73.95999908447266</v>
       </c>
       <c r="D186" t="n">
-        <v>71.80999755859375</v>
+        <v>72.62999725341797</v>
       </c>
       <c r="E186" t="n">
-        <v>72.87999725341797</v>
+        <v>72.81999969482422</v>
       </c>
       <c r="F186" t="n">
-        <v>82203300</v>
+        <v>50806800</v>
       </c>
       <c r="G186" t="n">
         <v>0</v>
@@ -5279,22 +5279,22 @@
     </row>
     <row r="187">
       <c r="A187" s="1" t="n">
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="B187" t="n">
-        <v>73.26000213623047</v>
+        <v>72.69000244140625</v>
       </c>
       <c r="C187" t="n">
-        <v>73.95999908447266</v>
+        <v>73.44999694824219</v>
       </c>
       <c r="D187" t="n">
-        <v>72.62999725341797</v>
+        <v>71.62999725341797</v>
       </c>
       <c r="E187" t="n">
-        <v>72.81999969482422</v>
+        <v>71.83999633789062</v>
       </c>
       <c r="F187" t="n">
-        <v>50806800</v>
+        <v>48001500</v>
       </c>
       <c r="G187" t="n">
         <v>0</v>
@@ -5305,22 +5305,22 @@
     </row>
     <row r="188">
       <c r="A188" s="1" t="n">
-        <v>46197</v>
+        <v>46198</v>
       </c>
       <c r="B188" t="n">
-        <v>72.69000244140625</v>
+        <v>71.33000183105469</v>
       </c>
       <c r="C188" t="n">
-        <v>73.44999694824219</v>
+        <v>72.94000244140625</v>
       </c>
       <c r="D188" t="n">
-        <v>71.62999725341797</v>
+        <v>70.86000061035156</v>
       </c>
       <c r="E188" t="n">
-        <v>71.83999633789062</v>
+        <v>70.90000152587891</v>
       </c>
       <c r="F188" t="n">
-        <v>48001500</v>
+        <v>44446900</v>
       </c>
       <c r="G188" t="n">
         <v>0</v>
@@ -5331,22 +5331,22 @@
     </row>
     <row r="189">
       <c r="A189" s="1" t="n">
-        <v>46198</v>
+        <v>46199</v>
       </c>
       <c r="B189" t="n">
-        <v>71.33000183105469</v>
+        <v>71.69000244140625</v>
       </c>
       <c r="C189" t="n">
-        <v>72.94000244140625</v>
+        <v>75.19999694824219</v>
       </c>
       <c r="D189" t="n">
-        <v>70.86000061035156</v>
+        <v>71.52999877929688</v>
       </c>
       <c r="E189" t="n">
-        <v>70.90000152587891</v>
+        <v>73.80999755859375</v>
       </c>
       <c r="F189" t="n">
-        <v>44446900</v>
+        <v>74990300</v>
       </c>
       <c r="G189" t="n">
         <v>0</v>
@@ -5357,22 +5357,22 @@
     </row>
     <row r="190">
       <c r="A190" s="1" t="n">
-        <v>46199</v>
+        <v>46202</v>
       </c>
       <c r="B190" t="n">
-        <v>71.69000244140625</v>
+        <v>74.62000274658203</v>
       </c>
       <c r="C190" t="n">
-        <v>75.19999694824219</v>
+        <v>76.06999969482422</v>
       </c>
       <c r="D190" t="n">
-        <v>71.52999877929688</v>
+        <v>73.73000335693359</v>
       </c>
       <c r="E190" t="n">
-        <v>73.80999755859375</v>
+        <v>73.77999877929688</v>
       </c>
       <c r="F190" t="n">
-        <v>74990300</v>
+        <v>42429600</v>
       </c>
       <c r="G190" t="n">
         <v>0</v>
@@ -5383,22 +5383,22 @@
     </row>
     <row r="191">
       <c r="A191" s="1" t="n">
-        <v>46202</v>
+        <v>46203</v>
       </c>
       <c r="B191" t="n">
-        <v>74.62000274658203</v>
+        <v>73.58999633789062</v>
       </c>
       <c r="C191" t="n">
-        <v>76.06999969482422</v>
+        <v>73.75</v>
       </c>
       <c r="D191" t="n">
-        <v>73.73000335693359</v>
+        <v>71</v>
       </c>
       <c r="E191" t="n">
-        <v>73.77999877929688</v>
+        <v>71.40000152587891</v>
       </c>
       <c r="F191" t="n">
-        <v>42429600</v>
+        <v>49240900</v>
       </c>
       <c r="G191" t="n">
         <v>0</v>
@@ -5409,22 +5409,22 @@
     </row>
     <row r="192">
       <c r="A192" s="1" t="n">
-        <v>46203</v>
+        <v>46204</v>
       </c>
       <c r="B192" t="n">
-        <v>73.58999633789062</v>
+        <v>72.58999633789062</v>
       </c>
       <c r="C192" t="n">
-        <v>73.75</v>
+        <v>74.36000061035156</v>
       </c>
       <c r="D192" t="n">
-        <v>71</v>
+        <v>72.33000183105469</v>
       </c>
       <c r="E192" t="n">
-        <v>71.40000152587891</v>
+        <v>74.19000244140625</v>
       </c>
       <c r="F192" t="n">
-        <v>49240900</v>
+        <v>43841800</v>
       </c>
       <c r="G192" t="n">
         <v>0</v>
@@ -5435,22 +5435,22 @@
     </row>
     <row r="193">
       <c r="A193" s="1" t="n">
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="B193" t="n">
-        <v>72.58999633789062</v>
+        <v>75.08999633789062</v>
       </c>
       <c r="C193" t="n">
-        <v>74.36000061035156</v>
+        <v>78.44000244140625</v>
       </c>
       <c r="D193" t="n">
-        <v>72.33000183105469</v>
+        <v>74.91000366210938</v>
       </c>
       <c r="E193" t="n">
-        <v>74.19000244140625</v>
+        <v>77.65000152587891</v>
       </c>
       <c r="F193" t="n">
-        <v>43841800</v>
+        <v>55456500</v>
       </c>
       <c r="G193" t="n">
         <v>0</v>
@@ -5461,22 +5461,22 @@
     </row>
     <row r="194">
       <c r="A194" s="1" t="n">
-        <v>46205</v>
+        <v>46209</v>
       </c>
       <c r="B194" t="n">
-        <v>75.08999633789062</v>
+        <v>77.08000183105469</v>
       </c>
       <c r="C194" t="n">
-        <v>78.44000244140625</v>
+        <v>77.83999633789062</v>
       </c>
       <c r="D194" t="n">
-        <v>74.91000366210938</v>
+        <v>75.70999908447266</v>
       </c>
       <c r="E194" t="n">
-        <v>77.65000152587891</v>
+        <v>76.01999664306641</v>
       </c>
       <c r="F194" t="n">
-        <v>55456500</v>
+        <v>45056600</v>
       </c>
       <c r="G194" t="n">
         <v>0</v>
@@ -5487,22 +5487,22 @@
     </row>
     <row r="195">
       <c r="A195" s="1" t="n">
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="B195" t="n">
-        <v>77.08000183105469</v>
+        <v>77.87999725341797</v>
       </c>
       <c r="C195" t="n">
-        <v>77.83999633789062</v>
+        <v>78.19000244140625</v>
       </c>
       <c r="D195" t="n">
-        <v>75.70999908447266</v>
+        <v>76.09999847412109</v>
       </c>
       <c r="E195" t="n">
-        <v>76.01999664306641</v>
+        <v>76.18000030517578</v>
       </c>
       <c r="F195" t="n">
-        <v>45056600</v>
+        <v>33257300</v>
       </c>
       <c r="G195" t="n">
         <v>0</v>
@@ -5513,22 +5513,22 @@
     </row>
     <row r="196">
       <c r="A196" s="1" t="n">
-        <v>46210</v>
+        <v>46211</v>
       </c>
       <c r="B196" t="n">
-        <v>77.87999725341797</v>
+        <v>76.26999664306641</v>
       </c>
       <c r="C196" t="n">
-        <v>78.19000244140625</v>
+        <v>76.63999938964844</v>
       </c>
       <c r="D196" t="n">
-        <v>76.09999847412109</v>
+        <v>74.88999938964844</v>
       </c>
       <c r="E196" t="n">
-        <v>76.18000030517578</v>
+        <v>75.58999633789062</v>
       </c>
       <c r="F196" t="n">
-        <v>33257300</v>
+        <v>34373500</v>
       </c>
       <c r="G196" t="n">
         <v>0</v>
@@ -5539,22 +5539,22 @@
     </row>
     <row r="197">
       <c r="A197" s="1" t="n">
-        <v>46211</v>
+        <v>46212</v>
       </c>
       <c r="B197" t="n">
-        <v>76.26999664306641</v>
+        <v>74.30000305175781</v>
       </c>
       <c r="C197" t="n">
-        <v>76.63999938964844</v>
+        <v>75.55000305175781</v>
       </c>
       <c r="D197" t="n">
-        <v>74.88999938964844</v>
+        <v>74.01999664306641</v>
       </c>
       <c r="E197" t="n">
-        <v>75.58999633789062</v>
+        <v>75.47000122070312</v>
       </c>
       <c r="F197" t="n">
-        <v>34373500</v>
+        <v>36305700</v>
       </c>
       <c r="G197" t="n">
         <v>0</v>
@@ -5565,22 +5565,22 @@
     </row>
     <row r="198">
       <c r="A198" s="1" t="n">
-        <v>46212</v>
+        <v>46213</v>
       </c>
       <c r="B198" t="n">
-        <v>74.30000305175781</v>
+        <v>75.44000244140625</v>
       </c>
       <c r="C198" t="n">
-        <v>75.55000305175781</v>
+        <v>75.69999694824219</v>
       </c>
       <c r="D198" t="n">
-        <v>74.01999664306641</v>
+        <v>72.51000213623047</v>
       </c>
       <c r="E198" t="n">
-        <v>75.47000122070312</v>
+        <v>73.37000274658203</v>
       </c>
       <c r="F198" t="n">
-        <v>36305700</v>
+        <v>46713900</v>
       </c>
       <c r="G198" t="n">
         <v>0</v>
@@ -5591,22 +5591,22 @@
     </row>
     <row r="199">
       <c r="A199" s="1" t="n">
-        <v>46213</v>
+        <v>46216</v>
       </c>
       <c r="B199" t="n">
-        <v>75.44000244140625</v>
+        <v>73.90000152587891</v>
       </c>
       <c r="C199" t="n">
-        <v>75.69999694824219</v>
+        <v>75.44999694824219</v>
       </c>
       <c r="D199" t="n">
-        <v>72.51000213623047</v>
+        <v>73.70999908447266</v>
       </c>
       <c r="E199" t="n">
-        <v>73.37000274658203</v>
+        <v>73.83000183105469</v>
       </c>
       <c r="F199" t="n">
-        <v>46713900</v>
+        <v>35101800</v>
       </c>
       <c r="G199" t="n">
         <v>0</v>
@@ -5617,22 +5617,22 @@
     </row>
     <row r="200">
       <c r="A200" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="B200" t="n">
-        <v>73.90000152587891</v>
+        <v>72.63999938964844</v>
       </c>
       <c r="C200" t="n">
-        <v>75.44999694824219</v>
+        <v>74.01000213623047</v>
       </c>
       <c r="D200" t="n">
-        <v>73.70999908447266</v>
+        <v>72.27999877929688</v>
       </c>
       <c r="E200" t="n">
-        <v>73.83000183105469</v>
+        <v>73.52999877929688</v>
       </c>
       <c r="F200" t="n">
-        <v>35101800</v>
+        <v>33312100</v>
       </c>
       <c r="G200" t="n">
         <v>0</v>
@@ -5643,22 +5643,22 @@
     </row>
     <row r="201">
       <c r="A201" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="B201" t="n">
-        <v>72.63999938964844</v>
+        <v>73.79000091552734</v>
       </c>
       <c r="C201" t="n">
-        <v>74.01000213623047</v>
+        <v>75.05999755859375</v>
       </c>
       <c r="D201" t="n">
-        <v>72.27999877929688</v>
+        <v>73.12999725341797</v>
       </c>
       <c r="E201" t="n">
-        <v>73.52999877929688</v>
+        <v>73.68000030517578</v>
       </c>
       <c r="F201" t="n">
-        <v>33312100</v>
+        <v>32854300</v>
       </c>
       <c r="G201" t="n">
         <v>0</v>
@@ -5669,22 +5669,22 @@
     </row>
     <row r="202">
       <c r="A202" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="B202" t="n">
-        <v>73.79000091552734</v>
+        <v>73.94999694824219</v>
       </c>
       <c r="C202" t="n">
-        <v>75.05999755859375</v>
+        <v>74.68000030517578</v>
       </c>
       <c r="D202" t="n">
-        <v>73.12999725341797</v>
+        <v>72.94000244140625</v>
       </c>
       <c r="E202" t="n">
-        <v>73.68000030517578</v>
+        <v>74.34999847412109</v>
       </c>
       <c r="F202" t="n">
-        <v>32854300</v>
+        <v>77505200</v>
       </c>
       <c r="G202" t="n">
         <v>0</v>
@@ -5695,22 +5695,22 @@
     </row>
     <row r="203">
       <c r="A203" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="B203" t="n">
-        <v>73.94999694824219</v>
+        <v>65.48000335693359</v>
       </c>
       <c r="C203" t="n">
-        <v>74.68000030517578</v>
+        <v>69.48999786376953</v>
       </c>
       <c r="D203" t="n">
-        <v>72.94000244140625</v>
+        <v>65.08000183105469</v>
       </c>
       <c r="E203" t="n">
-        <v>74.34999847412109</v>
+        <v>68.94999694824219</v>
       </c>
       <c r="F203" t="n">
-        <v>77505200</v>
+        <v>142029200</v>
       </c>
       <c r="G203" t="n">
         <v>0</v>
@@ -5721,22 +5721,22 @@
     </row>
     <row r="204">
       <c r="A204" s="1" t="n">
-        <v>46220</v>
+        <v>46223</v>
       </c>
       <c r="B204" t="n">
-        <v>65.48000335693359</v>
+        <v>68.31999969482422</v>
       </c>
       <c r="C204" t="n">
-        <v>69.48999786376953</v>
+        <v>68.37999725341797</v>
       </c>
       <c r="D204" t="n">
-        <v>65.08000183105469</v>
+        <v>66.69000244140625</v>
       </c>
       <c r="E204" t="n">
-        <v>68.94999694824219</v>
+        <v>67.59999847412109</v>
       </c>
       <c r="F204" t="n">
-        <v>142029200</v>
+        <v>60669100</v>
       </c>
       <c r="G204" t="n">
         <v>0</v>
@@ -5747,22 +5747,22 @@
     </row>
     <row r="205">
       <c r="A205" s="1" t="n">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="B205" t="n">
-        <v>68.31999969482422</v>
+        <v>67.41999816894531</v>
       </c>
       <c r="C205" t="n">
-        <v>68.37999725341797</v>
+        <v>68.75</v>
       </c>
       <c r="D205" t="n">
-        <v>66.69000244140625</v>
+        <v>66.73000335693359</v>
       </c>
       <c r="E205" t="n">
-        <v>67.59999847412109</v>
+        <v>68.66999816894531</v>
       </c>
       <c r="F205" t="n">
-        <v>60669100</v>
+        <v>56565800</v>
       </c>
       <c r="G205" t="n">
         <v>0</v>
@@ -5773,22 +5773,22 @@
     </row>
     <row r="206">
       <c r="A206" s="1" t="n">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="B206" t="n">
-        <v>67.41999816894531</v>
+        <v>69.37000274658203</v>
       </c>
       <c r="C206" t="n">
-        <v>68.75</v>
+        <v>70.56999969482422</v>
       </c>
       <c r="D206" t="n">
-        <v>66.73000335693359</v>
+        <v>68.34999847412109</v>
       </c>
       <c r="E206" t="n">
-        <v>68.66999816894531</v>
+        <v>68.52999877929688</v>
       </c>
       <c r="F206" t="n">
-        <v>56565800</v>
+        <v>44947300</v>
       </c>
       <c r="G206" t="n">
         <v>0</v>
@@ -5799,22 +5799,22 @@
     </row>
     <row r="207">
       <c r="A207" s="1" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="B207" t="n">
-        <v>69.37000274658203</v>
+        <v>68.56999969482422</v>
       </c>
       <c r="C207" t="n">
-        <v>70.56999969482422</v>
+        <v>69.36000061035156</v>
       </c>
       <c r="D207" t="n">
-        <v>68.34999847412109</v>
+        <v>67.66999816894531</v>
       </c>
       <c r="E207" t="n">
-        <v>68.52999877929688</v>
+        <v>68.88999938964844</v>
       </c>
       <c r="F207" t="n">
-        <v>44947300</v>
+        <v>45029100</v>
       </c>
       <c r="G207" t="n">
         <v>0</v>
@@ -5825,22 +5825,22 @@
     </row>
     <row r="208">
       <c r="A208" s="1" t="n">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="B208" t="n">
-        <v>68.56999969482422</v>
+        <v>69.29000091552734</v>
       </c>
       <c r="C208" t="n">
-        <v>69.36000061035156</v>
+        <v>70.68000030517578</v>
       </c>
       <c r="D208" t="n">
-        <v>67.66999816894531</v>
+        <v>67.97000122070312</v>
       </c>
       <c r="E208" t="n">
-        <v>68.88999938964844</v>
+        <v>70.08999633789062</v>
       </c>
       <c r="F208" t="n">
-        <v>45029100</v>
+        <v>37593500</v>
       </c>
       <c r="G208" t="n">
         <v>0</v>
@@ -5851,22 +5851,22 @@
     </row>
     <row r="209">
       <c r="A209" s="1" t="n">
-        <v>46227</v>
+        <v>46230</v>
       </c>
       <c r="B209" t="n">
-        <v>69.29000091552734</v>
+        <v>70.58999633789062</v>
       </c>
       <c r="C209" t="n">
-        <v>70.68000030517578</v>
+        <v>71.65000152587891</v>
       </c>
       <c r="D209" t="n">
-        <v>67.97000122070312</v>
+        <v>69.86000061035156</v>
       </c>
       <c r="E209" t="n">
-        <v>70.08999633789062</v>
+        <v>70.40000152587891</v>
       </c>
       <c r="F209" t="n">
-        <v>37593500</v>
+        <v>39090800</v>
       </c>
       <c r="G209" t="n">
         <v>0</v>
@@ -5877,22 +5877,22 @@
     </row>
     <row r="210">
       <c r="A210" s="1" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="B210" t="n">
-        <v>70.58999633789062</v>
+        <v>72.06999969482422</v>
       </c>
       <c r="C210" t="n">
-        <v>71.65000152587891</v>
+        <v>73.76000213623047</v>
       </c>
       <c r="D210" t="n">
-        <v>69.86000061035156</v>
+        <v>71.23000335693359</v>
       </c>
       <c r="E210" t="n">
-        <v>70.40000152587891</v>
+        <v>72.38999938964844</v>
       </c>
       <c r="F210" t="n">
-        <v>39090800</v>
+        <v>47160200</v>
       </c>
       <c r="G210" t="n">
         <v>0</v>
@@ -5903,22 +5903,22 @@
     </row>
     <row r="211">
       <c r="A211" s="1" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="B211" t="n">
-        <v>72.06999969482422</v>
+        <v>72.19000244140625</v>
       </c>
       <c r="C211" t="n">
-        <v>73.76000213623047</v>
+        <v>73.73999786376953</v>
       </c>
       <c r="D211" t="n">
-        <v>71.23000335693359</v>
+        <v>71.75</v>
       </c>
       <c r="E211" t="n">
-        <v>72.38999938964844</v>
+        <v>73.62999725341797</v>
       </c>
       <c r="F211" t="n">
-        <v>47160200</v>
+        <v>43737600</v>
       </c>
       <c r="G211" t="n">
         <v>0</v>
@@ -5929,22 +5929,22 @@
     </row>
     <row r="212">
       <c r="A212" s="1" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="B212" t="n">
-        <v>72.19000244140625</v>
+        <v>71.48000335693359</v>
       </c>
       <c r="C212" t="n">
-        <v>73.73999786376953</v>
+        <v>73.31999969482422</v>
       </c>
       <c r="D212" t="n">
-        <v>71.75</v>
+        <v>70.55000305175781</v>
       </c>
       <c r="E212" t="n">
-        <v>73.62999725341797</v>
+        <v>73.16999816894531</v>
       </c>
       <c r="F212" t="n">
-        <v>43737600</v>
+        <v>54261000</v>
       </c>
       <c r="G212" t="n">
         <v>0</v>
@@ -5955,22 +5955,22 @@
     </row>
     <row r="213">
       <c r="A213" s="1" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="B213" t="n">
-        <v>71.48000335693359</v>
+        <v>71.97000122070312</v>
       </c>
       <c r="C213" t="n">
-        <v>73.31999969482422</v>
+        <v>72.75</v>
       </c>
       <c r="D213" t="n">
-        <v>70.55000305175781</v>
+        <v>71.11000061035156</v>
       </c>
       <c r="E213" t="n">
-        <v>73.16999816894531</v>
+        <v>71.70999908447266</v>
       </c>
       <c r="F213" t="n">
-        <v>54261000</v>
+        <v>35847500</v>
       </c>
       <c r="G213" t="n">
         <v>0</v>
@@ -5981,22 +5981,22 @@
     </row>
     <row r="214">
       <c r="A214" s="1" t="n">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="B214" t="n">
-        <v>71.97000122070312</v>
+        <v>72.76999664306641</v>
       </c>
       <c r="C214" t="n">
-        <v>72.75</v>
+        <v>73.94999694824219</v>
       </c>
       <c r="D214" t="n">
-        <v>71.11000061035156</v>
+        <v>72.18000030517578</v>
       </c>
       <c r="E214" t="n">
-        <v>71.70999908447266</v>
+        <v>73.33000183105469</v>
       </c>
       <c r="F214" t="n">
-        <v>35847500</v>
+        <v>33922300</v>
       </c>
       <c r="G214" t="n">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="215">
       <c r="A215" s="1" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="B215" t="n">
-        <v>72.76999664306641</v>
+        <v>72.51000213623047</v>
       </c>
       <c r="C215" t="n">
-        <v>73.94999694824219</v>
+        <v>73.75</v>
       </c>
       <c r="D215" t="n">
-        <v>72.18000030517578</v>
+        <v>72.30000305175781</v>
       </c>
       <c r="E215" t="n">
-        <v>73.33000183105469</v>
+        <v>73.56999969482422</v>
       </c>
       <c r="F215" t="n">
-        <v>33922300</v>
+        <v>42877900</v>
       </c>
       <c r="G215" t="n">
         <v>0</v>
@@ -6033,22 +6033,22 @@
     </row>
     <row r="216">
       <c r="A216" s="1" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="B216" t="n">
-        <v>72.51000213623047</v>
+        <v>75.11000061035156</v>
       </c>
       <c r="C216" t="n">
-        <v>73.75</v>
+        <v>75.30000305175781</v>
       </c>
       <c r="D216" t="n">
-        <v>72.30000305175781</v>
+        <v>73.16000366210938</v>
       </c>
       <c r="E216" t="n">
-        <v>73.56999969482422</v>
+        <v>74.19999694824219</v>
       </c>
       <c r="F216" t="n">
-        <v>42877900</v>
+        <v>28969400</v>
       </c>
       <c r="G216" t="n">
         <v>0</v>
@@ -6059,22 +6059,22 @@
     </row>
     <row r="217">
       <c r="A217" s="1" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="B217" t="n">
-        <v>75.11000061035156</v>
+        <v>75.13999938964844</v>
       </c>
       <c r="C217" t="n">
-        <v>75.30000305175781</v>
+        <v>75.20999908447266</v>
       </c>
       <c r="D217" t="n">
-        <v>73.16000366210938</v>
+        <v>73.09999847412109</v>
       </c>
       <c r="E217" t="n">
-        <v>74.19999694824219</v>
+        <v>73.69000244140625</v>
       </c>
       <c r="F217" t="n">
-        <v>28969400</v>
+        <v>28892700</v>
       </c>
       <c r="G217" t="n">
         <v>0</v>
@@ -6085,22 +6085,22 @@
     </row>
     <row r="218">
       <c r="A218" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="B218" t="n">
-        <v>75.13999938964844</v>
+        <v>73.12000274658203</v>
       </c>
       <c r="C218" t="n">
-        <v>75.20999908447266</v>
+        <v>74.5</v>
       </c>
       <c r="D218" t="n">
-        <v>73.09999847412109</v>
+        <v>73.08000183105469</v>
       </c>
       <c r="E218" t="n">
-        <v>73.69000244140625</v>
+        <v>74.13999938964844</v>
       </c>
       <c r="F218" t="n">
-        <v>28892700</v>
+        <v>24819000</v>
       </c>
       <c r="G218" t="n">
         <v>0</v>
@@ -6111,22 +6111,22 @@
     </row>
     <row r="219">
       <c r="A219" s="1" t="n">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="B219" t="n">
-        <v>73.12000274658203</v>
+        <v>73.80000305175781</v>
       </c>
       <c r="C219" t="n">
-        <v>74.5</v>
+        <v>76.31999969482422</v>
       </c>
       <c r="D219" t="n">
-        <v>73.08000183105469</v>
+        <v>73.56999969482422</v>
       </c>
       <c r="E219" t="n">
-        <v>74.13999938964844</v>
+        <v>76.29000091552734</v>
       </c>
       <c r="F219" t="n">
-        <v>24819000</v>
+        <v>26959900</v>
       </c>
       <c r="G219" t="n">
         <v>0</v>
@@ -6137,22 +6137,22 @@
     </row>
     <row r="220">
       <c r="A220" s="1" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="B220" t="n">
-        <v>73.80000305175781</v>
+        <v>76.19999694824219</v>
       </c>
       <c r="C220" t="n">
-        <v>76.31999969482422</v>
+        <v>76.90000152587891</v>
       </c>
       <c r="D220" t="n">
-        <v>73.56999969482422</v>
+        <v>74.48000335693359</v>
       </c>
       <c r="E220" t="n">
-        <v>76.29000091552734</v>
+        <v>74.79000091552734</v>
       </c>
       <c r="F220" t="n">
-        <v>26959900</v>
+        <v>27840500</v>
       </c>
       <c r="G220" t="n">
         <v>0</v>
@@ -6163,22 +6163,22 @@
     </row>
     <row r="221">
       <c r="A221" s="1" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="B221" t="n">
-        <v>76.19999694824219</v>
+        <v>74.34999847412109</v>
       </c>
       <c r="C221" t="n">
-        <v>76.90000152587891</v>
+        <v>74.66999816894531</v>
       </c>
       <c r="D221" t="n">
-        <v>74.48000335693359</v>
+        <v>73.56999969482422</v>
       </c>
       <c r="E221" t="n">
-        <v>74.79000091552734</v>
+        <v>74.20999908447266</v>
       </c>
       <c r="F221" t="n">
-        <v>27840500</v>
+        <v>20773100</v>
       </c>
       <c r="G221" t="n">
         <v>0</v>
@@ -6189,22 +6189,22 @@
     </row>
     <row r="222">
       <c r="A222" s="1" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="B222" t="n">
-        <v>74.34999847412109</v>
+        <v>76.01000213623047</v>
       </c>
       <c r="C222" t="n">
-        <v>74.66999816894531</v>
+        <v>78.40000152587891</v>
       </c>
       <c r="D222" t="n">
-        <v>73.56999969482422</v>
+        <v>75.44000244140625</v>
       </c>
       <c r="E222" t="n">
-        <v>74.20999908447266</v>
+        <v>78.23999786376953</v>
       </c>
       <c r="F222" t="n">
-        <v>20773100</v>
+        <v>41452900</v>
       </c>
       <c r="G222" t="n">
         <v>0</v>
@@ -6215,22 +6215,22 @@
     </row>
     <row r="223">
       <c r="A223" s="1" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="B223" t="n">
-        <v>76.01000213623047</v>
+        <v>78.48000335693359</v>
       </c>
       <c r="C223" t="n">
-        <v>78.40000152587891</v>
+        <v>78.73000335693359</v>
       </c>
       <c r="D223" t="n">
-        <v>75.44000244140625</v>
+        <v>77.76000213623047</v>
       </c>
       <c r="E223" t="n">
-        <v>78.23999786376953</v>
+        <v>78.16000366210938</v>
       </c>
       <c r="F223" t="n">
-        <v>41452900</v>
+        <v>26751000</v>
       </c>
       <c r="G223" t="n">
         <v>0</v>
@@ -6241,22 +6241,22 @@
     </row>
     <row r="224">
       <c r="A224" s="1" t="n">
-        <v>46248</v>
+        <v>46251</v>
       </c>
       <c r="B224" t="n">
-        <v>78.48000335693359</v>
+        <v>77.80000305175781</v>
       </c>
       <c r="C224" t="n">
-        <v>78.73000335693359</v>
+        <v>78.52999877929688</v>
       </c>
       <c r="D224" t="n">
-        <v>77.76000213623047</v>
+        <v>75.47000122070312</v>
       </c>
       <c r="E224" t="n">
-        <v>78.16000366210938</v>
+        <v>76.01999664306641</v>
       </c>
       <c r="F224" t="n">
-        <v>26751000</v>
+        <v>30753000</v>
       </c>
       <c r="G224" t="n">
         <v>0</v>
@@ -6267,22 +6267,22 @@
     </row>
     <row r="225">
       <c r="A225" s="1" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="B225" t="n">
-        <v>77.80000305175781</v>
+        <v>77.43000030517578</v>
       </c>
       <c r="C225" t="n">
-        <v>78.52999877929688</v>
+        <v>79.09999847412109</v>
       </c>
       <c r="D225" t="n">
-        <v>75.47000122070312</v>
+        <v>76.33999633789062</v>
       </c>
       <c r="E225" t="n">
-        <v>76.01999664306641</v>
+        <v>77.76999664306641</v>
       </c>
       <c r="F225" t="n">
-        <v>30753000</v>
+        <v>36151300</v>
       </c>
       <c r="G225" t="n">
         <v>0</v>
@@ -6293,22 +6293,22 @@
     </row>
     <row r="226">
       <c r="A226" s="1" t="n">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="B226" t="n">
-        <v>77.43000030517578</v>
+        <v>78.25</v>
       </c>
       <c r="C226" t="n">
-        <v>79.09999847412109</v>
+        <v>81.16000366210938</v>
       </c>
       <c r="D226" t="n">
-        <v>76.33999633789062</v>
+        <v>78.09999847412109</v>
       </c>
       <c r="E226" t="n">
-        <v>77.76999664306641</v>
+        <v>80.22000122070312</v>
       </c>
       <c r="F226" t="n">
-        <v>36151300</v>
+        <v>31461800</v>
       </c>
       <c r="G226" t="n">
         <v>0</v>
@@ -6319,22 +6319,22 @@
     </row>
     <row r="227">
       <c r="A227" s="1" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="B227" t="n">
-        <v>78.25</v>
+        <v>80.13999938964844</v>
       </c>
       <c r="C227" t="n">
-        <v>81.16000366210938</v>
+        <v>81.08000183105469</v>
       </c>
       <c r="D227" t="n">
-        <v>78.09999847412109</v>
+        <v>79.58999633789062</v>
       </c>
       <c r="E227" t="n">
-        <v>80.22000122070312</v>
+        <v>80.13999938964844</v>
       </c>
       <c r="F227" t="n">
-        <v>31461800</v>
+        <v>27118400</v>
       </c>
       <c r="G227" t="n">
         <v>0</v>
@@ -6345,22 +6345,22 @@
     </row>
     <row r="228">
       <c r="A228" s="1" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="B228" t="n">
-        <v>80.13999938964844</v>
+        <v>80.29000091552734</v>
       </c>
       <c r="C228" t="n">
-        <v>81.08000183105469</v>
+        <v>80.48999786376953</v>
       </c>
       <c r="D228" t="n">
+        <v>79.16999816894531</v>
+      </c>
+      <c r="E228" t="n">
         <v>79.58999633789062</v>
       </c>
-      <c r="E228" t="n">
-        <v>80.13999938964844</v>
-      </c>
       <c r="F228" t="n">
-        <v>27118400</v>
+        <v>23773800</v>
       </c>
       <c r="G228" t="n">
         <v>0</v>
@@ -6371,22 +6371,22 @@
     </row>
     <row r="229">
       <c r="A229" s="1" t="n">
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="B229" t="n">
-        <v>80.29000091552734</v>
+        <v>79.94000244140625</v>
       </c>
       <c r="C229" t="n">
-        <v>80.48999786376953</v>
+        <v>80.62000274658203</v>
       </c>
       <c r="D229" t="n">
-        <v>79.16999816894531</v>
+        <v>79.01999664306641</v>
       </c>
       <c r="E229" t="n">
-        <v>79.58999633789062</v>
+        <v>80.01000213623047</v>
       </c>
       <c r="F229" t="n">
-        <v>23773800</v>
+        <v>21085300</v>
       </c>
       <c r="G229" t="n">
         <v>0</v>
@@ -6397,22 +6397,22 @@
     </row>
     <row r="230">
       <c r="A230" s="1" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="B230" t="n">
-        <v>79.94000244140625</v>
+        <v>79.65000152587891</v>
       </c>
       <c r="C230" t="n">
-        <v>80.62000274658203</v>
+        <v>82.45999908447266</v>
       </c>
       <c r="D230" t="n">
-        <v>79.01999664306641</v>
+        <v>79.40000152587891</v>
       </c>
       <c r="E230" t="n">
-        <v>80.01000213623047</v>
+        <v>82.23000335693359</v>
       </c>
       <c r="F230" t="n">
-        <v>21085300</v>
+        <v>29462000</v>
       </c>
       <c r="G230" t="n">
         <v>0</v>
@@ -6423,22 +6423,22 @@
     </row>
     <row r="231">
       <c r="A231" s="1" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="B231" t="n">
-        <v>79.65000152587891</v>
+        <v>82.05000305175781</v>
       </c>
       <c r="C231" t="n">
-        <v>82.45999908447266</v>
+        <v>82.41999816894531</v>
       </c>
       <c r="D231" t="n">
-        <v>79.40000152587891</v>
+        <v>81.30000305175781</v>
       </c>
       <c r="E231" t="n">
-        <v>82.23000335693359</v>
+        <v>81.45999908447266</v>
       </c>
       <c r="F231" t="n">
-        <v>29462000</v>
+        <v>22874900</v>
       </c>
       <c r="G231" t="n">
         <v>0</v>
@@ -6449,22 +6449,22 @@
     </row>
     <row r="232">
       <c r="A232" s="1" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="B232" t="n">
-        <v>82.05000305175781</v>
+        <v>81.06999969482422</v>
       </c>
       <c r="C232" t="n">
-        <v>82.41999816894531</v>
+        <v>81.15000152587891</v>
       </c>
       <c r="D232" t="n">
-        <v>81.30000305175781</v>
+        <v>79.27999877929688</v>
       </c>
       <c r="E232" t="n">
-        <v>81.45999908447266</v>
+        <v>79.83999633789062</v>
       </c>
       <c r="F232" t="n">
-        <v>22874900</v>
+        <v>27174400</v>
       </c>
       <c r="G232" t="n">
         <v>0</v>
@@ -6475,22 +6475,22 @@
     </row>
     <row r="233">
       <c r="A233" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="B233" t="n">
-        <v>81.06999969482422</v>
+        <v>80.36000061035156</v>
       </c>
       <c r="C233" t="n">
-        <v>81.15000152587891</v>
+        <v>82.34999847412109</v>
       </c>
       <c r="D233" t="n">
-        <v>79.27999877929688</v>
+        <v>79.94999694824219</v>
       </c>
       <c r="E233" t="n">
-        <v>79.83999633789062</v>
+        <v>81.72000122070312</v>
       </c>
       <c r="F233" t="n">
-        <v>27174400</v>
+        <v>29092700</v>
       </c>
       <c r="G233" t="n">
         <v>0</v>
@@ -6501,22 +6501,22 @@
     </row>
     <row r="234">
       <c r="A234" s="1" t="n">
-        <v>46262</v>
+        <v>46265</v>
       </c>
       <c r="B234" t="n">
-        <v>80.36000061035156</v>
+        <v>81</v>
       </c>
       <c r="C234" t="n">
-        <v>82.34999847412109</v>
+        <v>81.73000335693359</v>
       </c>
       <c r="D234" t="n">
-        <v>79.94999694824219</v>
+        <v>80.65000152587891</v>
       </c>
       <c r="E234" t="n">
-        <v>81.72000122070312</v>
+        <v>81.05000305175781</v>
       </c>
       <c r="F234" t="n">
-        <v>29092700</v>
+        <v>30740800</v>
       </c>
       <c r="G234" t="n">
         <v>0</v>
@@ -6527,22 +6527,22 @@
     </row>
     <row r="235">
       <c r="A235" s="1" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="B235" t="n">
-        <v>81</v>
+        <v>80.16999816894531</v>
       </c>
       <c r="C235" t="n">
-        <v>81.73000335693359</v>
+        <v>82.12999725341797</v>
       </c>
       <c r="D235" t="n">
-        <v>80.65000152587891</v>
+        <v>79.59999847412109</v>
       </c>
       <c r="E235" t="n">
-        <v>81.05000305175781</v>
+        <v>80.80999755859375</v>
       </c>
       <c r="F235" t="n">
-        <v>30740800</v>
+        <v>21164900</v>
       </c>
       <c r="G235" t="n">
         <v>0</v>
@@ -6553,22 +6553,22 @@
     </row>
     <row r="236">
       <c r="A236" s="1" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="B236" t="n">
-        <v>80.16999816894531</v>
+        <v>80.55000305175781</v>
       </c>
       <c r="C236" t="n">
-        <v>82.12999725341797</v>
+        <v>83.12000274658203</v>
       </c>
       <c r="D236" t="n">
-        <v>79.59999847412109</v>
+        <v>80.30000305175781</v>
       </c>
       <c r="E236" t="n">
-        <v>80.80999755859375</v>
+        <v>82.73000335693359</v>
       </c>
       <c r="F236" t="n">
-        <v>21164900</v>
+        <v>22077800</v>
       </c>
       <c r="G236" t="n">
         <v>0</v>
@@ -6579,22 +6579,22 @@
     </row>
     <row r="237">
       <c r="A237" s="1" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="B237" t="n">
-        <v>80.55000305175781</v>
+        <v>83.18000030517578</v>
       </c>
       <c r="C237" t="n">
-        <v>83.12000274658203</v>
+        <v>83.59999847412109</v>
       </c>
       <c r="D237" t="n">
-        <v>80.30000305175781</v>
+        <v>81.62999725341797</v>
       </c>
       <c r="E237" t="n">
-        <v>82.73000335693359</v>
+        <v>82.66999816894531</v>
       </c>
       <c r="F237" t="n">
-        <v>22077800</v>
+        <v>24006400</v>
       </c>
       <c r="G237" t="n">
         <v>0</v>
@@ -6605,22 +6605,22 @@
     </row>
     <row r="238">
       <c r="A238" s="1" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B238" t="n">
-        <v>83.18000030517578</v>
+        <v>82.16999816894531</v>
       </c>
       <c r="C238" t="n">
-        <v>83.59999847412109</v>
+        <v>82.69000244140625</v>
       </c>
       <c r="D238" t="n">
-        <v>81.62999725341797</v>
+        <v>78.23000335693359</v>
       </c>
       <c r="E238" t="n">
-        <v>82.66999816894531</v>
+        <v>78.25</v>
       </c>
       <c r="F238" t="n">
-        <v>24006400</v>
+        <v>40190000</v>
       </c>
       <c r="G238" t="n">
         <v>0</v>
@@ -6631,22 +6631,22 @@
     </row>
     <row r="239">
       <c r="A239" s="1" t="n">
-        <v>46269</v>
+        <v>46273</v>
       </c>
       <c r="B239" t="n">
-        <v>82.16999816894531</v>
+        <v>77.55000305175781</v>
       </c>
       <c r="C239" t="n">
-        <v>82.69000244140625</v>
+        <v>77.73000335693359</v>
       </c>
       <c r="D239" t="n">
-        <v>78.23000335693359</v>
+        <v>75.91999816894531</v>
       </c>
       <c r="E239" t="n">
-        <v>78.25</v>
+        <v>76.76999664306641</v>
       </c>
       <c r="F239" t="n">
-        <v>40190000</v>
+        <v>33865500</v>
       </c>
       <c r="G239" t="n">
         <v>0</v>
@@ -6657,22 +6657,22 @@
     </row>
     <row r="240">
       <c r="A240" s="1" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B240" t="n">
-        <v>77.55000305175781</v>
+        <v>76.33999633789062</v>
       </c>
       <c r="C240" t="n">
-        <v>77.73000335693359</v>
+        <v>76.72000122070312</v>
       </c>
       <c r="D240" t="n">
-        <v>75.91999816894531</v>
+        <v>75.87000274658203</v>
       </c>
       <c r="E240" t="n">
-        <v>76.76999664306641</v>
+        <v>76.02999877929688</v>
       </c>
       <c r="F240" t="n">
-        <v>33865500</v>
+        <v>22779600</v>
       </c>
       <c r="G240" t="n">
         <v>0</v>
@@ -6683,22 +6683,22 @@
     </row>
     <row r="241">
       <c r="A241" s="1" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="B241" t="n">
-        <v>76.33999633789062</v>
+        <v>75.33000183105469</v>
       </c>
       <c r="C241" t="n">
-        <v>76.72000122070312</v>
+        <v>76.30000305175781</v>
       </c>
       <c r="D241" t="n">
-        <v>75.87000274658203</v>
+        <v>75.02999877929688</v>
       </c>
       <c r="E241" t="n">
-        <v>76.02999877929688</v>
+        <v>76.01000213623047</v>
       </c>
       <c r="F241" t="n">
-        <v>22779600</v>
+        <v>20049000</v>
       </c>
       <c r="G241" t="n">
         <v>0</v>
@@ -6709,22 +6709,22 @@
     </row>
     <row r="242">
       <c r="A242" s="1" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="B242" t="n">
-        <v>75.33000183105469</v>
+        <v>76.63999938964844</v>
       </c>
       <c r="C242" t="n">
-        <v>76.30000305175781</v>
+        <v>77.56999969482422</v>
       </c>
       <c r="D242" t="n">
-        <v>75.02999877929688</v>
+        <v>76.15000152587891</v>
       </c>
       <c r="E242" t="n">
-        <v>76.01000213623047</v>
+        <v>77.40000152587891</v>
       </c>
       <c r="F242" t="n">
-        <v>20049000</v>
+        <v>22237800</v>
       </c>
       <c r="G242" t="n">
         <v>0</v>
@@ -6735,22 +6735,22 @@
     </row>
     <row r="243">
       <c r="A243" s="1" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="B243" t="n">
-        <v>76.63999938964844</v>
+        <v>78.97000122070312</v>
       </c>
       <c r="C243" t="n">
-        <v>77.56999969482422</v>
+        <v>81.01999664306641</v>
       </c>
       <c r="D243" t="n">
-        <v>76.15000152587891</v>
+        <v>78.48999786376953</v>
       </c>
       <c r="E243" t="n">
-        <v>77.40000152587891</v>
+        <v>80.31999969482422</v>
       </c>
       <c r="F243" t="n">
-        <v>22237800</v>
+        <v>30945100</v>
       </c>
       <c r="G243" t="n">
         <v>0</v>
@@ -6761,22 +6761,22 @@
     </row>
     <row r="244">
       <c r="A244" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="B244" t="n">
-        <v>78.97000122070312</v>
+        <v>79.37999725341797</v>
       </c>
       <c r="C244" t="n">
-        <v>81.01999664306641</v>
+        <v>79.48000335693359</v>
       </c>
       <c r="D244" t="n">
-        <v>78.48999786376953</v>
+        <v>77.45999908447266</v>
       </c>
       <c r="E244" t="n">
-        <v>80.31999969482422</v>
+        <v>77.90000152587891</v>
       </c>
       <c r="F244" t="n">
-        <v>30945100</v>
+        <v>28027400</v>
       </c>
       <c r="G244" t="n">
         <v>0</v>
@@ -6787,22 +6787,22 @@
     </row>
     <row r="245">
       <c r="A245" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="B245" t="n">
-        <v>79.37999725341797</v>
+        <v>77.73000335693359</v>
       </c>
       <c r="C245" t="n">
-        <v>79.48000335693359</v>
+        <v>77.80000305175781</v>
       </c>
       <c r="D245" t="n">
-        <v>77.45999908447266</v>
+        <v>76.30999755859375</v>
       </c>
       <c r="E245" t="n">
-        <v>77.90000152587891</v>
+        <v>76.41000366210938</v>
       </c>
       <c r="F245" t="n">
-        <v>28027400</v>
+        <v>25376300</v>
       </c>
       <c r="G245" t="n">
         <v>0</v>
@@ -6813,22 +6813,22 @@
     </row>
     <row r="246">
       <c r="A246" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="B246" t="n">
-        <v>77.73000335693359</v>
+        <v>76.91000366210938</v>
       </c>
       <c r="C246" t="n">
-        <v>77.80000305175781</v>
+        <v>76.95999908447266</v>
       </c>
       <c r="D246" t="n">
-        <v>76.30999755859375</v>
+        <v>75.30000305175781</v>
       </c>
       <c r="E246" t="n">
-        <v>76.41000366210938</v>
+        <v>75.30999755859375</v>
       </c>
       <c r="F246" t="n">
-        <v>25376300</v>
+        <v>28167600</v>
       </c>
       <c r="G246" t="n">
         <v>0</v>
@@ -6839,22 +6839,22 @@
     </row>
     <row r="247">
       <c r="A247" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="B247" t="n">
-        <v>76.91000366210938</v>
+        <v>71.26999664306641</v>
       </c>
       <c r="C247" t="n">
-        <v>76.95999908447266</v>
+        <v>72.37999725341797</v>
       </c>
       <c r="D247" t="n">
-        <v>75.30000305175781</v>
+        <v>70.11000061035156</v>
       </c>
       <c r="E247" t="n">
-        <v>75.30999755859375</v>
+        <v>71.79000091552734</v>
       </c>
       <c r="F247" t="n">
-        <v>28167600</v>
+        <v>114413500</v>
       </c>
       <c r="G247" t="n">
         <v>0</v>
@@ -6865,22 +6865,22 @@
     </row>
     <row r="248">
       <c r="A248" s="1" t="n">
-        <v>46283</v>
+        <v>46286</v>
       </c>
       <c r="B248" t="n">
-        <v>71.26999664306641</v>
+        <v>71.81999969482422</v>
       </c>
       <c r="C248" t="n">
-        <v>72.37999725341797</v>
+        <v>73.87000274658203</v>
       </c>
       <c r="D248" t="n">
-        <v>70.11000061035156</v>
+        <v>71.79000091552734</v>
       </c>
       <c r="E248" t="n">
-        <v>71.79000091552734</v>
+        <v>73.36000061035156</v>
       </c>
       <c r="F248" t="n">
-        <v>114413500</v>
+        <v>36948000</v>
       </c>
       <c r="G248" t="n">
         <v>0</v>
@@ -6891,22 +6891,22 @@
     </row>
     <row r="249">
       <c r="A249" s="1" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="B249" t="n">
-        <v>71.81999969482422</v>
+        <v>73.69000244140625</v>
       </c>
       <c r="C249" t="n">
-        <v>73.87000274658203</v>
+        <v>73.76000213623047</v>
       </c>
       <c r="D249" t="n">
-        <v>71.79000091552734</v>
+        <v>71.58000183105469</v>
       </c>
       <c r="E249" t="n">
-        <v>73.36000061035156</v>
+        <v>72.16000366210938</v>
       </c>
       <c r="F249" t="n">
-        <v>36948000</v>
+        <v>34372500</v>
       </c>
       <c r="G249" t="n">
         <v>0</v>
@@ -6917,22 +6917,22 @@
     </row>
     <row r="250">
       <c r="A250" s="1" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="B250" t="n">
-        <v>73.69000244140625</v>
+        <v>72.08000183105469</v>
       </c>
       <c r="C250" t="n">
-        <v>73.76000213623047</v>
+        <v>72.37000274658203</v>
       </c>
       <c r="D250" t="n">
-        <v>71.58000183105469</v>
+        <v>71.06999969482422</v>
       </c>
       <c r="E250" t="n">
-        <v>72.16000366210938</v>
+        <v>71.36000061035156</v>
       </c>
       <c r="F250" t="n">
-        <v>34372500</v>
+        <v>32807500</v>
       </c>
       <c r="G250" t="n">
         <v>0</v>
@@ -6943,22 +6943,22 @@
     </row>
     <row r="251">
       <c r="A251" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="B251" t="n">
-        <v>72.08000183105469</v>
+        <v>71.62000274658203</v>
       </c>
       <c r="C251" t="n">
-        <v>72.37000274658203</v>
+        <v>72.04000091552734</v>
       </c>
       <c r="D251" t="n">
-        <v>71.06999969482422</v>
+        <v>71.20999908447266</v>
       </c>
       <c r="E251" t="n">
-        <v>71.36000061035156</v>
+        <v>71.72000122070312</v>
       </c>
       <c r="F251" t="n">
-        <v>32807500</v>
+        <v>28223900</v>
       </c>
       <c r="G251" t="n">
         <v>0</v>
@@ -6969,22 +6969,22 @@
     </row>
     <row r="252">
       <c r="A252" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="B252" t="n">
-        <v>71.62000274658203</v>
+        <v>71.62999725341797</v>
       </c>
       <c r="C252" t="n">
-        <v>72.04000091552734</v>
+        <v>71.83999633789062</v>
       </c>
       <c r="D252" t="n">
-        <v>71.20999908447266</v>
+        <v>70.98000335693359</v>
       </c>
       <c r="E252" t="n">
-        <v>71.72000122070312</v>
+        <v>71.15000152587891</v>
       </c>
       <c r="F252" t="n">
-        <v>28189100</v>
+        <v>23175700</v>
       </c>
       <c r="G252" t="n">
         <v>0</v>
@@ -10434,37 +10434,37 @@
         </is>
       </c>
       <c r="C2" t="n">
+        <v>71.145</v>
+      </c>
+      <c r="D2" t="n">
         <v>71.72</v>
       </c>
-      <c r="D2" t="n">
-        <v>71.36</v>
-      </c>
       <c r="E2" t="n">
-        <v>71.62</v>
+        <v>71.575</v>
       </c>
       <c r="F2" t="n">
-        <v>72.04000000000001</v>
+        <v>71.83499999999999</v>
       </c>
       <c r="G2" t="n">
-        <v>71.20999999999999</v>
+        <v>70.98</v>
       </c>
       <c r="H2" t="n">
-        <v>28121254</v>
+        <v>23135069</v>
       </c>
       <c r="I2" t="n">
-        <v>38506915</v>
+        <v>37919035</v>
       </c>
       <c r="J2" t="n">
-        <v>298637754368</v>
+        <v>296243462144</v>
       </c>
       <c r="K2" t="n">
-        <v>22.4125</v>
+        <v>22.37264</v>
       </c>
       <c r="L2" t="n">
-        <v>18.808252</v>
+        <v>18.65746</v>
       </c>
       <c r="M2" t="n">
-        <v>3.2</v>
+        <v>3.18</v>
       </c>
       <c r="N2" t="n">
         <v>124.86</v>
@@ -10502,7 +10502,7 @@
         <v>7.241</v>
       </c>
       <c r="Y2" t="n">
-        <v>9.904709</v>
+        <v>9.825298999999999</v>
       </c>
       <c r="Z2" t="n">
         <v>0.111</v>
@@ -10514,7 +10514,7 @@
         <v>48370765824</v>
       </c>
       <c r="AC2" t="n">
-        <v>306164498432</v>
+        <v>303770238976</v>
       </c>
       <c r="AD2" t="n">
         <v>14726931456</v>
@@ -10541,7 +10541,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>2026-09-25 14:29:31</t>
+          <t>2026-09-26 14:50:04</t>
         </is>
       </c>
     </row>

--- a/data/NFLX_data.xlsx
+++ b/data/NFLX_data.xlsx
@@ -469,22 +469,22 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45926</v>
+        <v>45929</v>
       </c>
       <c r="B2" t="n">
-        <v>120.5419998168945</v>
+        <v>120.5</v>
       </c>
       <c r="C2" t="n">
-        <v>121.4000015258789</v>
+        <v>122.4489974975586</v>
       </c>
       <c r="D2" t="n">
-        <v>120</v>
+        <v>118.7539978027344</v>
       </c>
       <c r="E2" t="n">
-        <v>121.0609970092773</v>
+        <v>120.640998840332</v>
       </c>
       <c r="F2" t="n">
-        <v>19450000</v>
+        <v>30332000</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -495,22 +495,22 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="B3" t="n">
-        <v>120.5</v>
+        <v>120.640998840332</v>
       </c>
       <c r="C3" t="n">
-        <v>122.4489974975586</v>
+        <v>120.8499984741211</v>
       </c>
       <c r="D3" t="n">
-        <v>118.7539978027344</v>
+        <v>117.8000030517578</v>
       </c>
       <c r="E3" t="n">
-        <v>120.640998840332</v>
+        <v>119.8919982910156</v>
       </c>
       <c r="F3" t="n">
-        <v>30332000</v>
+        <v>38303000</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -521,22 +521,22 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>45930</v>
+        <v>45931</v>
       </c>
       <c r="B4" t="n">
-        <v>120.640998840332</v>
+        <v>117.5490036010742</v>
       </c>
       <c r="C4" t="n">
-        <v>120.8499984741211</v>
+        <v>117.9140014648438</v>
       </c>
       <c r="D4" t="n">
-        <v>117.8000030517578</v>
+        <v>116.3209991455078</v>
       </c>
       <c r="E4" t="n">
-        <v>119.8919982910156</v>
+        <v>117.0899963378906</v>
       </c>
       <c r="F4" t="n">
-        <v>38303000</v>
+        <v>41102000</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -547,22 +547,22 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>45931</v>
+        <v>45932</v>
       </c>
       <c r="B5" t="n">
-        <v>117.5490036010742</v>
+        <v>116.1500015258789</v>
       </c>
       <c r="C5" t="n">
-        <v>117.9140014648438</v>
+        <v>116.3330001831055</v>
       </c>
       <c r="D5" t="n">
-        <v>116.3209991455078</v>
+        <v>113.4000015258789</v>
       </c>
       <c r="E5" t="n">
-        <v>117.0899963378906</v>
+        <v>116.2529983520508</v>
       </c>
       <c r="F5" t="n">
-        <v>41102000</v>
+        <v>46855000</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -573,22 +573,22 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>45932</v>
+        <v>45933</v>
       </c>
       <c r="B6" t="n">
-        <v>116.1500015258789</v>
+        <v>116.5</v>
       </c>
       <c r="C6" t="n">
-        <v>116.3330001831055</v>
+        <v>116.8000030517578</v>
       </c>
       <c r="D6" t="n">
-        <v>113.4000015258789</v>
+        <v>114.3219985961914</v>
       </c>
       <c r="E6" t="n">
-        <v>116.2529983520508</v>
+        <v>115.3320007324219</v>
       </c>
       <c r="F6" t="n">
-        <v>46855000</v>
+        <v>31374000</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -599,22 +599,22 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>45933</v>
+        <v>45936</v>
       </c>
       <c r="B7" t="n">
-        <v>116.5</v>
+        <v>116.0370025634766</v>
       </c>
       <c r="C7" t="n">
-        <v>116.8000030517578</v>
+        <v>116.3580017089844</v>
       </c>
       <c r="D7" t="n">
-        <v>114.3219985961914</v>
+        <v>114.5449981689453</v>
       </c>
       <c r="E7" t="n">
-        <v>115.3320007324219</v>
+        <v>116.3310012817383</v>
       </c>
       <c r="F7" t="n">
-        <v>31374000</v>
+        <v>29686000</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -625,22 +625,22 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>45936</v>
+        <v>45937</v>
       </c>
       <c r="B8" t="n">
-        <v>116.0370025634766</v>
+        <v>117.7789993286133</v>
       </c>
       <c r="C8" t="n">
-        <v>116.3580017089844</v>
+        <v>120.1370010375977</v>
       </c>
       <c r="D8" t="n">
-        <v>114.5449981689453</v>
+        <v>117.7460021972656</v>
       </c>
       <c r="E8" t="n">
-        <v>116.3310012817383</v>
+        <v>119.1060028076172</v>
       </c>
       <c r="F8" t="n">
-        <v>29686000</v>
+        <v>33091000</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -651,22 +651,22 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>45937</v>
+        <v>45938</v>
       </c>
       <c r="B9" t="n">
-        <v>117.7789993286133</v>
+        <v>119.7109985351562</v>
       </c>
       <c r="C9" t="n">
-        <v>120.1370010375977</v>
+        <v>121.7389984130859</v>
       </c>
       <c r="D9" t="n">
-        <v>117.7460021972656</v>
+        <v>119.1999969482422</v>
       </c>
       <c r="E9" t="n">
-        <v>119.1060028076172</v>
+        <v>121.4250030517578</v>
       </c>
       <c r="F9" t="n">
-        <v>33091000</v>
+        <v>28514000</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -677,22 +677,22 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>45938</v>
+        <v>45939</v>
       </c>
       <c r="B10" t="n">
-        <v>119.7109985351562</v>
+        <v>121.4250030517578</v>
       </c>
       <c r="C10" t="n">
-        <v>121.7389984130859</v>
+        <v>123.75</v>
       </c>
       <c r="D10" t="n">
-        <v>119.1999969482422</v>
+        <v>121.181999206543</v>
       </c>
       <c r="E10" t="n">
-        <v>121.4250030517578</v>
+        <v>123.1070022583008</v>
       </c>
       <c r="F10" t="n">
-        <v>28514000</v>
+        <v>28241000</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -703,22 +703,22 @@
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>45939</v>
+        <v>45940</v>
       </c>
       <c r="B11" t="n">
-        <v>121.4250030517578</v>
+        <v>122.9000015258789</v>
       </c>
       <c r="C11" t="n">
-        <v>123.75</v>
+        <v>124.6999969482422</v>
       </c>
       <c r="D11" t="n">
-        <v>121.181999206543</v>
+        <v>121.9100036621094</v>
       </c>
       <c r="E11" t="n">
-        <v>123.1070022583008</v>
+        <v>122.0080032348633</v>
       </c>
       <c r="F11" t="n">
-        <v>28241000</v>
+        <v>42798000</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -729,22 +729,22 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>45940</v>
+        <v>45943</v>
       </c>
       <c r="B12" t="n">
-        <v>122.9000015258789</v>
+        <v>122.1350021362305</v>
       </c>
       <c r="C12" t="n">
-        <v>124.6999969482422</v>
+        <v>123.1119995117188</v>
       </c>
       <c r="D12" t="n">
-        <v>121.9100036621094</v>
+        <v>120.6809997558594</v>
       </c>
       <c r="E12" t="n">
-        <v>122.0080032348633</v>
+        <v>121.9029998779297</v>
       </c>
       <c r="F12" t="n">
-        <v>42798000</v>
+        <v>24608000</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -755,22 +755,22 @@
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>45943</v>
+        <v>45944</v>
       </c>
       <c r="B13" t="n">
-        <v>122.1350021362305</v>
+        <v>121.4749984741211</v>
       </c>
       <c r="C13" t="n">
-        <v>123.1119995117188</v>
+        <v>122.4290008544922</v>
       </c>
       <c r="D13" t="n">
-        <v>120.6809997558594</v>
+        <v>120.3099975585938</v>
       </c>
       <c r="E13" t="n">
-        <v>121.9029998779297</v>
+        <v>121.5350036621094</v>
       </c>
       <c r="F13" t="n">
-        <v>24608000</v>
+        <v>23624000</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -781,22 +781,22 @@
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>45944</v>
+        <v>45945</v>
       </c>
       <c r="B14" t="n">
-        <v>121.4749984741211</v>
+        <v>121.3010025024414</v>
       </c>
       <c r="C14" t="n">
-        <v>122.4290008544922</v>
+        <v>121.9619979858398</v>
       </c>
       <c r="D14" t="n">
-        <v>120.3099975585938</v>
+        <v>120.161003112793</v>
       </c>
       <c r="E14" t="n">
-        <v>121.5350036621094</v>
+        <v>120.3290023803711</v>
       </c>
       <c r="F14" t="n">
-        <v>23624000</v>
+        <v>20252000</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -807,22 +807,22 @@
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>45945</v>
+        <v>45946</v>
       </c>
       <c r="B15" t="n">
-        <v>121.3010025024414</v>
+        <v>121.2149963378906</v>
       </c>
       <c r="C15" t="n">
-        <v>121.9619979858398</v>
+        <v>121.6709976196289</v>
       </c>
       <c r="D15" t="n">
-        <v>120.161003112793</v>
+        <v>117.5999984741211</v>
       </c>
       <c r="E15" t="n">
-        <v>120.3290023803711</v>
+        <v>118.359001159668</v>
       </c>
       <c r="F15" t="n">
-        <v>20252000</v>
+        <v>28326000</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -833,22 +833,22 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>45946</v>
+        <v>45947</v>
       </c>
       <c r="B16" t="n">
-        <v>121.2149963378906</v>
+        <v>118.3600006103516</v>
       </c>
       <c r="C16" t="n">
-        <v>121.6709976196289</v>
+        <v>120.3119964599609</v>
       </c>
       <c r="D16" t="n">
-        <v>117.5999984741211</v>
+        <v>117.8949966430664</v>
       </c>
       <c r="E16" t="n">
-        <v>118.359001159668</v>
+        <v>119.9359970092773</v>
       </c>
       <c r="F16" t="n">
-        <v>28326000</v>
+        <v>29571000</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -859,22 +859,22 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>45947</v>
+        <v>45950</v>
       </c>
       <c r="B17" t="n">
-        <v>118.3600006103516</v>
+        <v>120.7880020141602</v>
       </c>
       <c r="C17" t="n">
-        <v>120.3119964599609</v>
+        <v>124.7760009765625</v>
       </c>
       <c r="D17" t="n">
-        <v>117.8949966430664</v>
+        <v>120.6900024414062</v>
       </c>
       <c r="E17" t="n">
-        <v>119.9359970092773</v>
+        <v>123.8560028076172</v>
       </c>
       <c r="F17" t="n">
-        <v>29571000</v>
+        <v>39862000</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -885,22 +885,22 @@
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>45950</v>
+        <v>45951</v>
       </c>
       <c r="B18" t="n">
-        <v>120.7880020141602</v>
+        <v>124.2829971313477</v>
       </c>
       <c r="C18" t="n">
-        <v>124.7760009765625</v>
+        <v>124.8600006103516</v>
       </c>
       <c r="D18" t="n">
-        <v>120.6900024414062</v>
+        <v>123.1760025024414</v>
       </c>
       <c r="E18" t="n">
-        <v>123.8560028076172</v>
+        <v>124.1350021362305</v>
       </c>
       <c r="F18" t="n">
-        <v>39862000</v>
+        <v>65082000</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -911,22 +911,22 @@
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>45951</v>
+        <v>45952</v>
       </c>
       <c r="B19" t="n">
-        <v>124.2829971313477</v>
+        <v>114.2900009155273</v>
       </c>
       <c r="C19" t="n">
-        <v>124.8600006103516</v>
+        <v>115.7600021362305</v>
       </c>
       <c r="D19" t="n">
-        <v>123.1760025024414</v>
+        <v>111.2509994506836</v>
       </c>
       <c r="E19" t="n">
-        <v>124.1350021362305</v>
+        <v>111.6370010375977</v>
       </c>
       <c r="F19" t="n">
-        <v>65082000</v>
+        <v>147890000</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -937,22 +937,22 @@
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>45952</v>
+        <v>45953</v>
       </c>
       <c r="B20" t="n">
-        <v>114.2900009155273</v>
+        <v>112.6900024414062</v>
       </c>
       <c r="C20" t="n">
-        <v>115.7600021362305</v>
+        <v>112.7829971313477</v>
       </c>
       <c r="D20" t="n">
-        <v>111.2509994506836</v>
+        <v>109.9729995727539</v>
       </c>
       <c r="E20" t="n">
-        <v>111.6370010375977</v>
+        <v>111.359001159668</v>
       </c>
       <c r="F20" t="n">
-        <v>147890000</v>
+        <v>68497000</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -963,22 +963,22 @@
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>45953</v>
+        <v>45954</v>
       </c>
       <c r="B21" t="n">
-        <v>112.6900024414062</v>
+        <v>111.0999984741211</v>
       </c>
       <c r="C21" t="n">
-        <v>112.7829971313477</v>
+        <v>111.4509963989258</v>
       </c>
       <c r="D21" t="n">
-        <v>109.9729995727539</v>
+        <v>109.4410018920898</v>
       </c>
       <c r="E21" t="n">
-        <v>111.359001159668</v>
+        <v>109.4690017700195</v>
       </c>
       <c r="F21" t="n">
-        <v>68497000</v>
+        <v>60280000</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -989,22 +989,22 @@
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>45954</v>
+        <v>45957</v>
       </c>
       <c r="B22" t="n">
-        <v>111.0999984741211</v>
+        <v>110.0670013427734</v>
       </c>
       <c r="C22" t="n">
-        <v>111.4509963989258</v>
+        <v>110.2279968261719</v>
       </c>
       <c r="D22" t="n">
-        <v>109.4410018920898</v>
+        <v>108.7300033569336</v>
       </c>
       <c r="E22" t="n">
-        <v>109.4690017700195</v>
+        <v>109.4560012817383</v>
       </c>
       <c r="F22" t="n">
-        <v>60280000</v>
+        <v>46911000</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -1015,22 +1015,22 @@
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>45957</v>
+        <v>45958</v>
       </c>
       <c r="B23" t="n">
-        <v>110.0670013427734</v>
+        <v>109.4000015258789</v>
       </c>
       <c r="C23" t="n">
-        <v>110.2279968261719</v>
+        <v>111.697998046875</v>
       </c>
       <c r="D23" t="n">
-        <v>108.7300033569336</v>
+        <v>109.3010025024414</v>
       </c>
       <c r="E23" t="n">
-        <v>109.4560012817383</v>
+        <v>110.25</v>
       </c>
       <c r="F23" t="n">
-        <v>46911000</v>
+        <v>40209000</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -1041,22 +1041,22 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>45958</v>
+        <v>45959</v>
       </c>
       <c r="B24" t="n">
-        <v>109.4000015258789</v>
+        <v>109.984001159668</v>
       </c>
       <c r="C24" t="n">
-        <v>111.697998046875</v>
+        <v>110.8550033569336</v>
       </c>
       <c r="D24" t="n">
-        <v>109.3010025024414</v>
+        <v>109.5999984741211</v>
       </c>
       <c r="E24" t="n">
-        <v>110.25</v>
+        <v>110.0410003662109</v>
       </c>
       <c r="F24" t="n">
-        <v>40209000</v>
+        <v>33995000</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -1067,22 +1067,22 @@
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>45959</v>
+        <v>45960</v>
       </c>
       <c r="B25" t="n">
-        <v>109.984001159668</v>
+        <v>109.4400024414062</v>
       </c>
       <c r="C25" t="n">
-        <v>110.8550033569336</v>
+        <v>110.6159973144531</v>
       </c>
       <c r="D25" t="n">
-        <v>109.5999984741211</v>
+        <v>108.8109970092773</v>
       </c>
       <c r="E25" t="n">
-        <v>110.0410003662109</v>
+        <v>108.9000015258789</v>
       </c>
       <c r="F25" t="n">
-        <v>33995000</v>
+        <v>41581000</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -1093,22 +1093,22 @@
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>45960</v>
+        <v>45961</v>
       </c>
       <c r="B26" t="n">
-        <v>109.4400024414062</v>
+        <v>110.5390014648438</v>
       </c>
       <c r="C26" t="n">
-        <v>110.6159973144531</v>
+        <v>113.4879989624023</v>
       </c>
       <c r="D26" t="n">
-        <v>108.8109970092773</v>
+        <v>110.197998046875</v>
       </c>
       <c r="E26" t="n">
-        <v>108.9000015258789</v>
+        <v>111.8860015869141</v>
       </c>
       <c r="F26" t="n">
-        <v>41581000</v>
+        <v>68665000</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -1119,22 +1119,22 @@
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>45961</v>
+        <v>45964</v>
       </c>
       <c r="B27" t="n">
-        <v>110.5390014648438</v>
+        <v>113.3239974975586</v>
       </c>
       <c r="C27" t="n">
-        <v>113.4879989624023</v>
+        <v>113.3499984741211</v>
       </c>
       <c r="D27" t="n">
-        <v>110.197998046875</v>
+        <v>107.5149993896484</v>
       </c>
       <c r="E27" t="n">
-        <v>111.8860015869141</v>
+        <v>110.0090026855469</v>
       </c>
       <c r="F27" t="n">
-        <v>68665000</v>
+        <v>58634000</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -1145,22 +1145,22 @@
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>45964</v>
+        <v>45965</v>
       </c>
       <c r="B28" t="n">
-        <v>113.3239974975586</v>
+        <v>109.9990005493164</v>
       </c>
       <c r="C28" t="n">
-        <v>113.3499984741211</v>
+        <v>110.4599990844727</v>
       </c>
       <c r="D28" t="n">
-        <v>107.5149993896484</v>
+        <v>108.6679992675781</v>
       </c>
       <c r="E28" t="n">
-        <v>110.0090026855469</v>
+        <v>109.2959976196289</v>
       </c>
       <c r="F28" t="n">
-        <v>58634000</v>
+        <v>38718000</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
@@ -1171,22 +1171,22 @@
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>45965</v>
+        <v>45966</v>
       </c>
       <c r="B29" t="n">
-        <v>109.9990005493164</v>
+        <v>108.5</v>
       </c>
       <c r="C29" t="n">
-        <v>110.4599990844727</v>
+        <v>110.0849990844727</v>
       </c>
       <c r="D29" t="n">
-        <v>108.6679992675781</v>
+        <v>107.3369979858398</v>
       </c>
       <c r="E29" t="n">
-        <v>109.2959976196289</v>
+        <v>109.8460006713867</v>
       </c>
       <c r="F29" t="n">
-        <v>38718000</v>
+        <v>35539000</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -1197,22 +1197,22 @@
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>45966</v>
+        <v>45967</v>
       </c>
       <c r="B30" t="n">
-        <v>108.5</v>
+        <v>109.4580001831055</v>
       </c>
       <c r="C30" t="n">
-        <v>110.0849990844727</v>
+        <v>110.370002746582</v>
       </c>
       <c r="D30" t="n">
-        <v>107.3369979858398</v>
+        <v>108.5130004882812</v>
       </c>
       <c r="E30" t="n">
-        <v>109.8460006713867</v>
+        <v>109.7020034790039</v>
       </c>
       <c r="F30" t="n">
-        <v>35539000</v>
+        <v>36532000</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -1223,22 +1223,22 @@
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>45967</v>
+        <v>45968</v>
       </c>
       <c r="B31" t="n">
-        <v>109.4580001831055</v>
+        <v>109.4179992675781</v>
       </c>
       <c r="C31" t="n">
-        <v>110.370002746582</v>
+        <v>110.8219985961914</v>
       </c>
       <c r="D31" t="n">
-        <v>108.5130004882812</v>
+        <v>108.75</v>
       </c>
       <c r="E31" t="n">
-        <v>109.7020034790039</v>
+        <v>110.3659973144531</v>
       </c>
       <c r="F31" t="n">
-        <v>36532000</v>
+        <v>44125000</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -1249,22 +1249,22 @@
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>45968</v>
+        <v>45971</v>
       </c>
       <c r="B32" t="n">
-        <v>109.4179992675781</v>
+        <v>110.6719970703125</v>
       </c>
       <c r="C32" t="n">
-        <v>110.8219985961914</v>
+        <v>112.8199996948242</v>
       </c>
       <c r="D32" t="n">
-        <v>108.75</v>
+        <v>110.4049987792969</v>
       </c>
       <c r="E32" t="n">
-        <v>110.3659973144531</v>
+        <v>112.0070037841797</v>
       </c>
       <c r="F32" t="n">
-        <v>44125000</v>
+        <v>36929000</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
@@ -1275,22 +1275,22 @@
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>45971</v>
+        <v>45972</v>
       </c>
       <c r="B33" t="n">
-        <v>110.6719970703125</v>
+        <v>111.7600021362305</v>
       </c>
       <c r="C33" t="n">
-        <v>112.8199996948242</v>
+        <v>113.9219970703125</v>
       </c>
       <c r="D33" t="n">
-        <v>110.4049987792969</v>
+        <v>111.2799987792969</v>
       </c>
       <c r="E33" t="n">
-        <v>112.0070037841797</v>
+        <v>113.6439971923828</v>
       </c>
       <c r="F33" t="n">
-        <v>36929000</v>
+        <v>27966000</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -1301,22 +1301,22 @@
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>45972</v>
+        <v>45973</v>
       </c>
       <c r="B34" t="n">
-        <v>111.7600021362305</v>
+        <v>113.8170013427734</v>
       </c>
       <c r="C34" t="n">
-        <v>113.9219970703125</v>
+        <v>116.4339981079102</v>
       </c>
       <c r="D34" t="n">
-        <v>111.2799987792969</v>
+        <v>112.8259963989258</v>
       </c>
       <c r="E34" t="n">
-        <v>113.6439971923828</v>
+        <v>115.75</v>
       </c>
       <c r="F34" t="n">
-        <v>27966000</v>
+        <v>39221000</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
@@ -1327,22 +1327,22 @@
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>45973</v>
+        <v>45974</v>
       </c>
       <c r="B35" t="n">
-        <v>113.8170013427734</v>
+        <v>115.8499984741211</v>
       </c>
       <c r="C35" t="n">
-        <v>116.4339981079102</v>
+        <v>116.7330017089844</v>
       </c>
       <c r="D35" t="n">
-        <v>112.8259963989258</v>
+        <v>114.5690002441406</v>
       </c>
       <c r="E35" t="n">
-        <v>115.75</v>
+        <v>115.4229965209961</v>
       </c>
       <c r="F35" t="n">
-        <v>39221000</v>
+        <v>40144000</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
@@ -1353,22 +1353,22 @@
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>45974</v>
+        <v>45975</v>
       </c>
       <c r="B36" t="n">
-        <v>115.8499984741211</v>
+        <v>114.2730026245117</v>
       </c>
       <c r="C36" t="n">
-        <v>116.7330017089844</v>
+        <v>114.2730026245117</v>
       </c>
       <c r="D36" t="n">
-        <v>114.5690002441406</v>
+        <v>110.7210006713867</v>
       </c>
       <c r="E36" t="n">
-        <v>115.4229965209961</v>
+        <v>111.2170028686523</v>
       </c>
       <c r="F36" t="n">
-        <v>40144000</v>
+        <v>47607000</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -1379,74 +1379,74 @@
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>45975</v>
+        <v>45978</v>
       </c>
       <c r="B37" t="n">
-        <v>114.2730026245117</v>
+        <v>110.75</v>
       </c>
       <c r="C37" t="n">
-        <v>114.2730026245117</v>
+        <v>111.8499984741211</v>
       </c>
       <c r="D37" t="n">
-        <v>110.7210006713867</v>
+        <v>109.5500030517578</v>
       </c>
       <c r="E37" t="n">
-        <v>111.2170028686523</v>
+        <v>110.2900009155273</v>
       </c>
       <c r="F37" t="n">
-        <v>47607000</v>
+        <v>26082700</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>45978</v>
+        <v>45979</v>
       </c>
       <c r="B38" t="n">
-        <v>110.75</v>
+        <v>110.2900009155273</v>
       </c>
       <c r="C38" t="n">
-        <v>111.8499984741211</v>
+        <v>115.25</v>
       </c>
       <c r="D38" t="n">
-        <v>109.5500030517578</v>
+        <v>109.1999969482422</v>
       </c>
       <c r="E38" t="n">
-        <v>110.2900009155273</v>
+        <v>114.0899963378906</v>
       </c>
       <c r="F38" t="n">
-        <v>26082700</v>
+        <v>43440600</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>45979</v>
+        <v>45980</v>
       </c>
       <c r="B39" t="n">
-        <v>110.2900009155273</v>
+        <v>113</v>
       </c>
       <c r="C39" t="n">
-        <v>115.25</v>
+        <v>113.3399963378906</v>
       </c>
       <c r="D39" t="n">
-        <v>109.1999969482422</v>
+        <v>108.6100006103516</v>
       </c>
       <c r="E39" t="n">
-        <v>114.0899963378906</v>
+        <v>110</v>
       </c>
       <c r="F39" t="n">
-        <v>43440600</v>
+        <v>31868100</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
@@ -1457,22 +1457,22 @@
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>45980</v>
+        <v>45981</v>
       </c>
       <c r="B40" t="n">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C40" t="n">
-        <v>113.3399963378906</v>
+        <v>111.0999984741211</v>
       </c>
       <c r="D40" t="n">
-        <v>108.6100006103516</v>
+        <v>105.3899993896484</v>
       </c>
       <c r="E40" t="n">
-        <v>110</v>
+        <v>105.6699981689453</v>
       </c>
       <c r="F40" t="n">
-        <v>31868100</v>
+        <v>36918500</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
@@ -1483,22 +1483,22 @@
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>45981</v>
+        <v>45982</v>
       </c>
       <c r="B41" t="n">
-        <v>111</v>
+        <v>105.129997253418</v>
       </c>
       <c r="C41" t="n">
-        <v>111.0999984741211</v>
+        <v>106.5299987792969</v>
       </c>
       <c r="D41" t="n">
-        <v>105.3899993896484</v>
+        <v>103.8099975585938</v>
       </c>
       <c r="E41" t="n">
-        <v>105.6699981689453</v>
+        <v>104.3099975585938</v>
       </c>
       <c r="F41" t="n">
-        <v>36918500</v>
+        <v>41232700</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
@@ -1509,22 +1509,22 @@
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>45982</v>
+        <v>45985</v>
       </c>
       <c r="B42" t="n">
-        <v>105.129997253418</v>
+        <v>104.25</v>
       </c>
       <c r="C42" t="n">
-        <v>106.5299987792969</v>
+        <v>108.0400009155273</v>
       </c>
       <c r="D42" t="n">
-        <v>103.8099975585938</v>
+        <v>103.3199996948242</v>
       </c>
       <c r="E42" t="n">
-        <v>104.3099975585938</v>
+        <v>106.9700012207031</v>
       </c>
       <c r="F42" t="n">
-        <v>41232700</v>
+        <v>62918300</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
@@ -1535,22 +1535,22 @@
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>45985</v>
+        <v>45986</v>
       </c>
       <c r="B43" t="n">
-        <v>104.25</v>
+        <v>106.120002746582</v>
       </c>
       <c r="C43" t="n">
-        <v>108.0400009155273</v>
+        <v>106.3000030517578</v>
       </c>
       <c r="D43" t="n">
-        <v>103.3199996948242</v>
+        <v>103.8199996948242</v>
       </c>
       <c r="E43" t="n">
-        <v>106.9700012207031</v>
+        <v>104.4000015258789</v>
       </c>
       <c r="F43" t="n">
-        <v>62918300</v>
+        <v>35122600</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
@@ -1561,22 +1561,22 @@
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
-        <v>45986</v>
+        <v>45987</v>
       </c>
       <c r="B44" t="n">
-        <v>106.120002746582</v>
+        <v>105.7399978637695</v>
       </c>
       <c r="C44" t="n">
-        <v>106.3000030517578</v>
+        <v>106.9499969482422</v>
       </c>
       <c r="D44" t="n">
-        <v>103.8199996948242</v>
+        <v>105.2200012207031</v>
       </c>
       <c r="E44" t="n">
-        <v>104.4000015258789</v>
+        <v>106.1399993896484</v>
       </c>
       <c r="F44" t="n">
-        <v>35122600</v>
+        <v>27951000</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
@@ -1587,22 +1587,22 @@
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
-        <v>45987</v>
+        <v>45989</v>
       </c>
       <c r="B45" t="n">
-        <v>105.7399978637695</v>
+        <v>106.4400024414062</v>
       </c>
       <c r="C45" t="n">
-        <v>106.9499969482422</v>
+        <v>107.9400024414062</v>
       </c>
       <c r="D45" t="n">
-        <v>105.2200012207031</v>
+        <v>106.2399978637695</v>
       </c>
       <c r="E45" t="n">
-        <v>106.1399993896484</v>
+        <v>107.5800018310547</v>
       </c>
       <c r="F45" t="n">
-        <v>27951000</v>
+        <v>15021600</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
@@ -1613,22 +1613,22 @@
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
-        <v>45989</v>
+        <v>45992</v>
       </c>
       <c r="B46" t="n">
-        <v>106.4400024414062</v>
+        <v>106.5100021362305</v>
       </c>
       <c r="C46" t="n">
-        <v>107.9400024414062</v>
+        <v>109.3399963378906</v>
       </c>
       <c r="D46" t="n">
-        <v>106.2399978637695</v>
+        <v>106.3099975585938</v>
       </c>
       <c r="E46" t="n">
-        <v>107.5800018310547</v>
+        <v>109.129997253418</v>
       </c>
       <c r="F46" t="n">
-        <v>15021600</v>
+        <v>24873400</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
@@ -1639,22 +1639,22 @@
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
-        <v>45992</v>
+        <v>45993</v>
       </c>
       <c r="B47" t="n">
-        <v>106.5100021362305</v>
+        <v>109.2099990844727</v>
       </c>
       <c r="C47" t="n">
-        <v>109.3399963378906</v>
+        <v>109.7300033569336</v>
       </c>
       <c r="D47" t="n">
-        <v>106.3099975585938</v>
+        <v>107.5199966430664</v>
       </c>
       <c r="E47" t="n">
-        <v>109.129997253418</v>
+        <v>109.3499984741211</v>
       </c>
       <c r="F47" t="n">
-        <v>24873400</v>
+        <v>25763000</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
@@ -1665,22 +1665,22 @@
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
-        <v>45993</v>
+        <v>45994</v>
       </c>
       <c r="B48" t="n">
-        <v>109.2099990844727</v>
+        <v>106.5899963378906</v>
       </c>
       <c r="C48" t="n">
-        <v>109.7300033569336</v>
+        <v>106.870002746582</v>
       </c>
       <c r="D48" t="n">
-        <v>107.5199966430664</v>
+        <v>102.0299987792969</v>
       </c>
       <c r="E48" t="n">
-        <v>109.3499984741211</v>
+        <v>103.9599990844727</v>
       </c>
       <c r="F48" t="n">
-        <v>25763000</v>
+        <v>53593400</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
@@ -1691,22 +1691,22 @@
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>45994</v>
+        <v>45995</v>
       </c>
       <c r="B49" t="n">
-        <v>106.5899963378906</v>
+        <v>103.5699996948242</v>
       </c>
       <c r="C49" t="n">
-        <v>106.870002746582</v>
+        <v>103.8000030517578</v>
       </c>
       <c r="D49" t="n">
-        <v>102.0299987792969</v>
+        <v>101.7699966430664</v>
       </c>
       <c r="E49" t="n">
-        <v>103.9599990844727</v>
+        <v>103.2200012207031</v>
       </c>
       <c r="F49" t="n">
-        <v>53593400</v>
+        <v>51779100</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
@@ -1717,22 +1717,22 @@
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>45995</v>
+        <v>45996</v>
       </c>
       <c r="B50" t="n">
-        <v>103.5699996948242</v>
+        <v>98.77999877929688</v>
       </c>
       <c r="C50" t="n">
-        <v>103.8000030517578</v>
+        <v>104.7900009155273</v>
       </c>
       <c r="D50" t="n">
-        <v>101.7699966430664</v>
+        <v>97.73999786376953</v>
       </c>
       <c r="E50" t="n">
-        <v>103.2200012207031</v>
+        <v>100.2399978637695</v>
       </c>
       <c r="F50" t="n">
-        <v>51779100</v>
+        <v>133363600</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
-        <v>45996</v>
+        <v>45999</v>
       </c>
       <c r="B51" t="n">
-        <v>98.77999877929688</v>
+        <v>99.87000274658203</v>
       </c>
       <c r="C51" t="n">
-        <v>104.7900009155273</v>
+        <v>99.88999938964844</v>
       </c>
       <c r="D51" t="n">
-        <v>97.73999786376953</v>
+        <v>95.30000305175781</v>
       </c>
       <c r="E51" t="n">
-        <v>100.2399978637695</v>
+        <v>96.79000091552734</v>
       </c>
       <c r="F51" t="n">
-        <v>133363600</v>
+        <v>100906300</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
@@ -1769,22 +1769,22 @@
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
-        <v>45999</v>
+        <v>46000</v>
       </c>
       <c r="B52" t="n">
-        <v>99.87000274658203</v>
+        <v>97.02999877929688</v>
       </c>
       <c r="C52" t="n">
-        <v>99.88999938964844</v>
+        <v>97.23999786376953</v>
       </c>
       <c r="D52" t="n">
-        <v>95.30000305175781</v>
+        <v>95.44999694824219</v>
       </c>
       <c r="E52" t="n">
-        <v>96.79000091552734</v>
+        <v>96.70999908447266</v>
       </c>
       <c r="F52" t="n">
-        <v>100906300</v>
+        <v>51745600</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
@@ -1795,22 +1795,22 @@
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
-        <v>46000</v>
+        <v>46001</v>
       </c>
       <c r="B53" t="n">
-        <v>97.02999877929688</v>
+        <v>96.73999786376953</v>
       </c>
       <c r="C53" t="n">
-        <v>97.23999786376953</v>
+        <v>96.97000122070312</v>
       </c>
       <c r="D53" t="n">
-        <v>95.44999694824219</v>
+        <v>92.34999847412109</v>
       </c>
       <c r="E53" t="n">
-        <v>96.70999908447266</v>
+        <v>92.70999908447266</v>
       </c>
       <c r="F53" t="n">
-        <v>51745600</v>
+        <v>74129300</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
@@ -1821,22 +1821,22 @@
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
-        <v>46001</v>
+        <v>46002</v>
       </c>
       <c r="B54" t="n">
-        <v>96.73999786376953</v>
+        <v>93.90000152587891</v>
       </c>
       <c r="C54" t="n">
-        <v>96.97000122070312</v>
+        <v>94.81999969482422</v>
       </c>
       <c r="D54" t="n">
-        <v>92.34999847412109</v>
+        <v>92.76000213623047</v>
       </c>
       <c r="E54" t="n">
-        <v>92.70999908447266</v>
+        <v>94.08999633789062</v>
       </c>
       <c r="F54" t="n">
-        <v>74129300</v>
+        <v>43949000</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
@@ -1847,22 +1847,22 @@
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
-        <v>46002</v>
+        <v>46003</v>
       </c>
       <c r="B55" t="n">
-        <v>93.90000152587891</v>
+        <v>95.5</v>
       </c>
       <c r="C55" t="n">
-        <v>94.81999969482422</v>
+        <v>96.91999816894531</v>
       </c>
       <c r="D55" t="n">
-        <v>92.76000213623047</v>
+        <v>94.65000152587891</v>
       </c>
       <c r="E55" t="n">
-        <v>94.08999633789062</v>
+        <v>95.19000244140625</v>
       </c>
       <c r="F55" t="n">
-        <v>43949000</v>
+        <v>49323100</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
@@ -1873,22 +1873,22 @@
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
-        <v>46003</v>
+        <v>46006</v>
       </c>
       <c r="B56" t="n">
-        <v>95.5</v>
+        <v>96.01999664306641</v>
       </c>
       <c r="C56" t="n">
-        <v>96.91999816894531</v>
+        <v>96.37000274658203</v>
       </c>
       <c r="D56" t="n">
-        <v>94.65000152587891</v>
+        <v>93.52999877929688</v>
       </c>
       <c r="E56" t="n">
-        <v>95.19000244140625</v>
+        <v>93.76999664306641</v>
       </c>
       <c r="F56" t="n">
-        <v>49323100</v>
+        <v>40016500</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
@@ -1899,22 +1899,22 @@
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
-        <v>46006</v>
+        <v>46007</v>
       </c>
       <c r="B57" t="n">
-        <v>96.01999664306641</v>
+        <v>93.87999725341797</v>
       </c>
       <c r="C57" t="n">
-        <v>96.37000274658203</v>
+        <v>94.93000030517578</v>
       </c>
       <c r="D57" t="n">
-        <v>93.52999877929688</v>
+        <v>93.31999969482422</v>
       </c>
       <c r="E57" t="n">
-        <v>93.76999664306641</v>
+        <v>94.56999969482422</v>
       </c>
       <c r="F57" t="n">
-        <v>40016500</v>
+        <v>34265000</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
@@ -1925,22 +1925,22 @@
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
-        <v>46007</v>
+        <v>46008</v>
       </c>
       <c r="B58" t="n">
-        <v>93.87999725341797</v>
+        <v>95.98000335693359</v>
       </c>
       <c r="C58" t="n">
-        <v>94.93000030517578</v>
+        <v>97.33000183105469</v>
       </c>
       <c r="D58" t="n">
-        <v>93.31999969482422</v>
+        <v>94.45999908447266</v>
       </c>
       <c r="E58" t="n">
-        <v>94.56999969482422</v>
+        <v>94.79000091552734</v>
       </c>
       <c r="F58" t="n">
-        <v>34265000</v>
+        <v>50472800</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
@@ -1951,22 +1951,22 @@
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
-        <v>46008</v>
+        <v>46009</v>
       </c>
       <c r="B59" t="n">
-        <v>95.98000335693359</v>
+        <v>95.01999664306641</v>
       </c>
       <c r="C59" t="n">
-        <v>97.33000183105469</v>
+        <v>95.80999755859375</v>
       </c>
       <c r="D59" t="n">
-        <v>94.45999908447266</v>
+        <v>93.58999633789062</v>
       </c>
       <c r="E59" t="n">
-        <v>94.79000091552734</v>
+        <v>94</v>
       </c>
       <c r="F59" t="n">
-        <v>50472800</v>
+        <v>37244700</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
@@ -1977,22 +1977,22 @@
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
-        <v>46009</v>
+        <v>46010</v>
       </c>
       <c r="B60" t="n">
-        <v>95.01999664306641</v>
+        <v>93.56999969482422</v>
       </c>
       <c r="C60" t="n">
-        <v>95.80999755859375</v>
+        <v>95.54000091552734</v>
       </c>
       <c r="D60" t="n">
-        <v>93.58999633789062</v>
+        <v>93.44999694824219</v>
       </c>
       <c r="E60" t="n">
-        <v>94</v>
+        <v>94.38999938964844</v>
       </c>
       <c r="F60" t="n">
-        <v>37244700</v>
+        <v>78990200</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
@@ -2003,22 +2003,22 @@
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
-        <v>46010</v>
+        <v>46013</v>
       </c>
       <c r="B61" t="n">
-        <v>93.56999969482422</v>
+        <v>94.70999908447266</v>
       </c>
       <c r="C61" t="n">
-        <v>95.54000091552734</v>
+        <v>94.70999908447266</v>
       </c>
       <c r="D61" t="n">
-        <v>93.44999694824219</v>
+        <v>92.91000366210938</v>
       </c>
       <c r="E61" t="n">
-        <v>94.38999938964844</v>
+        <v>93.23000335693359</v>
       </c>
       <c r="F61" t="n">
-        <v>78990200</v>
+        <v>39484800</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
@@ -2029,22 +2029,22 @@
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
-        <v>46013</v>
+        <v>46014</v>
       </c>
       <c r="B62" t="n">
-        <v>94.70999908447266</v>
+        <v>93.40000152587891</v>
       </c>
       <c r="C62" t="n">
-        <v>94.70999908447266</v>
+        <v>93.80999755859375</v>
       </c>
       <c r="D62" t="n">
-        <v>92.91000366210938</v>
+        <v>91.33000183105469</v>
       </c>
       <c r="E62" t="n">
-        <v>93.23000335693359</v>
+        <v>93.5</v>
       </c>
       <c r="F62" t="n">
-        <v>39484800</v>
+        <v>25896200</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
@@ -2055,22 +2055,22 @@
     </row>
     <row r="63">
       <c r="A63" s="1" t="n">
-        <v>46014</v>
+        <v>46015</v>
       </c>
       <c r="B63" t="n">
-        <v>93.40000152587891</v>
+        <v>93.11000061035156</v>
       </c>
       <c r="C63" t="n">
-        <v>93.80999755859375</v>
+        <v>93.68000030517578</v>
       </c>
       <c r="D63" t="n">
-        <v>91.33000183105469</v>
+        <v>92.66999816894531</v>
       </c>
       <c r="E63" t="n">
-        <v>93.5</v>
+        <v>93.63999938964844</v>
       </c>
       <c r="F63" t="n">
-        <v>25896200</v>
+        <v>12427900</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
@@ -2081,22 +2081,22 @@
     </row>
     <row r="64">
       <c r="A64" s="1" t="n">
-        <v>46015</v>
+        <v>46017</v>
       </c>
       <c r="B64" t="n">
-        <v>93.11000061035156</v>
+        <v>93.48000335693359</v>
       </c>
       <c r="C64" t="n">
-        <v>93.68000030517578</v>
+        <v>94.69000244140625</v>
       </c>
       <c r="D64" t="n">
-        <v>92.66999816894531</v>
+        <v>93.26999664306641</v>
       </c>
       <c r="E64" t="n">
-        <v>93.63999938964844</v>
+        <v>94.47000122070312</v>
       </c>
       <c r="F64" t="n">
-        <v>12427900</v>
+        <v>22068300</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
@@ -2107,22 +2107,22 @@
     </row>
     <row r="65">
       <c r="A65" s="1" t="n">
-        <v>46017</v>
+        <v>46020</v>
       </c>
       <c r="B65" t="n">
-        <v>93.48000335693359</v>
+        <v>93.98999786376953</v>
       </c>
       <c r="C65" t="n">
-        <v>94.69000244140625</v>
+        <v>94.97000122070312</v>
       </c>
       <c r="D65" t="n">
-        <v>93.26999664306641</v>
+        <v>93.62999725341797</v>
       </c>
       <c r="E65" t="n">
-        <v>94.47000122070312</v>
+        <v>94.15000152587891</v>
       </c>
       <c r="F65" t="n">
-        <v>22068300</v>
+        <v>24493700</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
@@ -2133,22 +2133,22 @@
     </row>
     <row r="66">
       <c r="A66" s="1" t="n">
-        <v>46020</v>
+        <v>46021</v>
       </c>
       <c r="B66" t="n">
+        <v>93.51999664306641</v>
+      </c>
+      <c r="C66" t="n">
         <v>93.98999786376953</v>
       </c>
-      <c r="C66" t="n">
-        <v>94.97000122070312</v>
-      </c>
       <c r="D66" t="n">
-        <v>93.62999725341797</v>
+        <v>93.33999633789062</v>
       </c>
       <c r="E66" t="n">
-        <v>94.15000152587891</v>
+        <v>93.77999877929688</v>
       </c>
       <c r="F66" t="n">
-        <v>24493700</v>
+        <v>23422000</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
@@ -2159,22 +2159,22 @@
     </row>
     <row r="67">
       <c r="A67" s="1" t="n">
-        <v>46021</v>
+        <v>46022</v>
       </c>
       <c r="B67" t="n">
-        <v>93.51999664306641</v>
+        <v>93.59999847412109</v>
       </c>
       <c r="C67" t="n">
-        <v>93.98999786376953</v>
+        <v>94.30999755859375</v>
       </c>
       <c r="D67" t="n">
-        <v>93.33999633789062</v>
+        <v>93.19999694824219</v>
       </c>
       <c r="E67" t="n">
-        <v>93.77999877929688</v>
+        <v>93.76000213623047</v>
       </c>
       <c r="F67" t="n">
-        <v>23422000</v>
+        <v>23495200</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
@@ -2185,22 +2185,22 @@
     </row>
     <row r="68">
       <c r="A68" s="1" t="n">
-        <v>46022</v>
+        <v>46024</v>
       </c>
       <c r="B68" t="n">
-        <v>93.59999847412109</v>
+        <v>94.12999725341797</v>
       </c>
       <c r="C68" t="n">
-        <v>94.30999755859375</v>
+        <v>94.12999725341797</v>
       </c>
       <c r="D68" t="n">
-        <v>93.19999694824219</v>
+        <v>90.80999755859375</v>
       </c>
       <c r="E68" t="n">
-        <v>93.76000213623047</v>
+        <v>90.98999786376953</v>
       </c>
       <c r="F68" t="n">
-        <v>23495200</v>
+        <v>41155400</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
@@ -2211,22 +2211,22 @@
     </row>
     <row r="69">
       <c r="A69" s="1" t="n">
-        <v>46024</v>
+        <v>46027</v>
       </c>
       <c r="B69" t="n">
-        <v>94.12999725341797</v>
+        <v>90.91999816894531</v>
       </c>
       <c r="C69" t="n">
-        <v>94.12999725341797</v>
+        <v>92.62999725341797</v>
       </c>
       <c r="D69" t="n">
-        <v>90.80999755859375</v>
+        <v>90.83999633789062</v>
       </c>
       <c r="E69" t="n">
-        <v>90.98999786376953</v>
+        <v>91.45999908447266</v>
       </c>
       <c r="F69" t="n">
-        <v>41155400</v>
+        <v>39183300</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
@@ -2237,22 +2237,22 @@
     </row>
     <row r="70">
       <c r="A70" s="1" t="n">
-        <v>46027</v>
+        <v>46028</v>
       </c>
       <c r="B70" t="n">
-        <v>90.91999816894531</v>
+        <v>91.54000091552734</v>
       </c>
       <c r="C70" t="n">
-        <v>92.62999725341797</v>
+        <v>91.63999938964844</v>
       </c>
       <c r="D70" t="n">
-        <v>90.83999633789062</v>
+        <v>89.73999786376953</v>
       </c>
       <c r="E70" t="n">
-        <v>91.45999908447266</v>
+        <v>90.65000152587891</v>
       </c>
       <c r="F70" t="n">
-        <v>39183300</v>
+        <v>43331000</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
@@ -2263,22 +2263,22 @@
     </row>
     <row r="71">
       <c r="A71" s="1" t="n">
-        <v>46028</v>
+        <v>46029</v>
       </c>
       <c r="B71" t="n">
-        <v>91.54000091552734</v>
+        <v>91.55999755859375</v>
       </c>
       <c r="C71" t="n">
-        <v>91.63999938964844</v>
+        <v>92.41999816894531</v>
       </c>
       <c r="D71" t="n">
-        <v>89.73999786376953</v>
+        <v>90.05999755859375</v>
       </c>
       <c r="E71" t="n">
-        <v>90.65000152587891</v>
+        <v>90.73000335693359</v>
       </c>
       <c r="F71" t="n">
-        <v>43331000</v>
+        <v>36525700</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
@@ -2289,22 +2289,22 @@
     </row>
     <row r="72">
       <c r="A72" s="1" t="n">
-        <v>46029</v>
+        <v>46030</v>
       </c>
       <c r="B72" t="n">
-        <v>91.55999755859375</v>
+        <v>90.44999694824219</v>
       </c>
       <c r="C72" t="n">
-        <v>92.41999816894531</v>
+        <v>91.25</v>
       </c>
       <c r="D72" t="n">
-        <v>90.05999755859375</v>
+        <v>89.58000183105469</v>
       </c>
       <c r="E72" t="n">
-        <v>90.73000335693359</v>
+        <v>90.52999877929688</v>
       </c>
       <c r="F72" t="n">
-        <v>36525700</v>
+        <v>40068700</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
@@ -2315,22 +2315,22 @@
     </row>
     <row r="73">
       <c r="A73" s="1" t="n">
-        <v>46030</v>
+        <v>46031</v>
       </c>
       <c r="B73" t="n">
-        <v>90.44999694824219</v>
+        <v>90.02999877929688</v>
       </c>
       <c r="C73" t="n">
-        <v>91.25</v>
+        <v>90.05000305175781</v>
       </c>
       <c r="D73" t="n">
-        <v>89.58000183105469</v>
+        <v>88.31999969482422</v>
       </c>
       <c r="E73" t="n">
-        <v>90.52999877929688</v>
+        <v>89.45999908447266</v>
       </c>
       <c r="F73" t="n">
-        <v>40068700</v>
+        <v>55579500</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
@@ -2341,22 +2341,22 @@
     </row>
     <row r="74">
       <c r="A74" s="1" t="n">
-        <v>46031</v>
+        <v>46034</v>
       </c>
       <c r="B74" t="n">
-        <v>90.02999877929688</v>
+        <v>89.69000244140625</v>
       </c>
       <c r="C74" t="n">
-        <v>90.05000305175781</v>
+        <v>90.33999633789062</v>
       </c>
       <c r="D74" t="n">
-        <v>88.31999969482422</v>
+        <v>89.33000183105469</v>
       </c>
       <c r="E74" t="n">
-        <v>89.45999908447266</v>
+        <v>89.41000366210938</v>
       </c>
       <c r="F74" t="n">
-        <v>55579500</v>
+        <v>36290600</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
@@ -2367,22 +2367,22 @@
     </row>
     <row r="75">
       <c r="A75" s="1" t="n">
-        <v>46034</v>
+        <v>46035</v>
       </c>
       <c r="B75" t="n">
-        <v>89.69000244140625</v>
+        <v>89.44000244140625</v>
       </c>
       <c r="C75" t="n">
-        <v>90.33999633789062</v>
+        <v>91.15000152587891</v>
       </c>
       <c r="D75" t="n">
-        <v>89.33000183105469</v>
+        <v>89.06999969482422</v>
       </c>
       <c r="E75" t="n">
-        <v>89.41000366210938</v>
+        <v>90.31999969482422</v>
       </c>
       <c r="F75" t="n">
-        <v>36290600</v>
+        <v>45221100</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
@@ -2393,22 +2393,22 @@
     </row>
     <row r="76">
       <c r="A76" s="1" t="n">
-        <v>46035</v>
+        <v>46036</v>
       </c>
       <c r="B76" t="n">
-        <v>89.44000244140625</v>
+        <v>91.23999786376953</v>
       </c>
       <c r="C76" t="n">
-        <v>91.15000152587891</v>
+        <v>91.58000183105469</v>
       </c>
       <c r="D76" t="n">
-        <v>89.06999969482422</v>
+        <v>87.94999694824219</v>
       </c>
       <c r="E76" t="n">
-        <v>90.31999969482422</v>
+        <v>88.55000305175781</v>
       </c>
       <c r="F76" t="n">
-        <v>45221100</v>
+        <v>49737700</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
@@ -2419,22 +2419,22 @@
     </row>
     <row r="77">
       <c r="A77" s="1" t="n">
-        <v>46036</v>
+        <v>46037</v>
       </c>
       <c r="B77" t="n">
-        <v>91.23999786376953</v>
+        <v>89.01999664306641</v>
       </c>
       <c r="C77" t="n">
-        <v>91.58000183105469</v>
+        <v>89.88999938964844</v>
       </c>
       <c r="D77" t="n">
-        <v>87.94999694824219</v>
+        <v>87.81999969482422</v>
       </c>
       <c r="E77" t="n">
-        <v>88.55000305175781</v>
+        <v>88.05000305175781</v>
       </c>
       <c r="F77" t="n">
-        <v>49737700</v>
+        <v>36945100</v>
       </c>
       <c r="G77" t="n">
         <v>0</v>
@@ -2445,22 +2445,22 @@
     </row>
     <row r="78">
       <c r="A78" s="1" t="n">
-        <v>46037</v>
+        <v>46038</v>
       </c>
       <c r="B78" t="n">
-        <v>89.01999664306641</v>
+        <v>88.33999633789062</v>
       </c>
       <c r="C78" t="n">
-        <v>89.88999938964844</v>
+        <v>88.51000213623047</v>
       </c>
       <c r="D78" t="n">
-        <v>87.81999969482422</v>
+        <v>87.77999877929688</v>
       </c>
       <c r="E78" t="n">
-        <v>88.05000305175781</v>
+        <v>88</v>
       </c>
       <c r="F78" t="n">
-        <v>36945100</v>
+        <v>48130500</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
@@ -2471,22 +2471,22 @@
     </row>
     <row r="79">
       <c r="A79" s="1" t="n">
-        <v>46038</v>
+        <v>46042</v>
       </c>
       <c r="B79" t="n">
-        <v>88.33999633789062</v>
+        <v>88.97000122070312</v>
       </c>
       <c r="C79" t="n">
-        <v>88.51000213623047</v>
+        <v>89.90000152587891</v>
       </c>
       <c r="D79" t="n">
-        <v>87.77999877929688</v>
+        <v>87.01999664306641</v>
       </c>
       <c r="E79" t="n">
-        <v>88</v>
+        <v>87.26000213623047</v>
       </c>
       <c r="F79" t="n">
-        <v>48130500</v>
+        <v>109729700</v>
       </c>
       <c r="G79" t="n">
         <v>0</v>
@@ -2497,22 +2497,22 @@
     </row>
     <row r="80">
       <c r="A80" s="1" t="n">
-        <v>46042</v>
+        <v>46043</v>
       </c>
       <c r="B80" t="n">
-        <v>88.97000122070312</v>
+        <v>82.51999664306641</v>
       </c>
       <c r="C80" t="n">
-        <v>89.90000152587891</v>
+        <v>86</v>
       </c>
       <c r="D80" t="n">
-        <v>87.01999664306641</v>
+        <v>81.93000030517578</v>
       </c>
       <c r="E80" t="n">
-        <v>87.26000213623047</v>
+        <v>85.36000061035156</v>
       </c>
       <c r="F80" t="n">
-        <v>109729700</v>
+        <v>127940700</v>
       </c>
       <c r="G80" t="n">
         <v>0</v>
@@ -2523,22 +2523,22 @@
     </row>
     <row r="81">
       <c r="A81" s="1" t="n">
-        <v>46043</v>
+        <v>46044</v>
       </c>
       <c r="B81" t="n">
-        <v>82.51999664306641</v>
+        <v>85.01999664306641</v>
       </c>
       <c r="C81" t="n">
-        <v>86</v>
+        <v>85.09999847412109</v>
       </c>
       <c r="D81" t="n">
-        <v>81.93000030517578</v>
+        <v>82.98000335693359</v>
       </c>
       <c r="E81" t="n">
-        <v>85.36000061035156</v>
+        <v>83.54000091552734</v>
       </c>
       <c r="F81" t="n">
-        <v>127940700</v>
+        <v>69113300</v>
       </c>
       <c r="G81" t="n">
         <v>0</v>
@@ -2549,22 +2549,22 @@
     </row>
     <row r="82">
       <c r="A82" s="1" t="n">
-        <v>46044</v>
+        <v>46045</v>
       </c>
       <c r="B82" t="n">
-        <v>85.01999664306641</v>
+        <v>83.43000030517578</v>
       </c>
       <c r="C82" t="n">
-        <v>85.09999847412109</v>
+        <v>86.30000305175781</v>
       </c>
       <c r="D82" t="n">
-        <v>82.98000335693359</v>
+        <v>83.27999877929688</v>
       </c>
       <c r="E82" t="n">
-        <v>83.54000091552734</v>
+        <v>86.12000274658203</v>
       </c>
       <c r="F82" t="n">
-        <v>69113300</v>
+        <v>64520400</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
@@ -2575,22 +2575,22 @@
     </row>
     <row r="83">
       <c r="A83" s="1" t="n">
-        <v>46045</v>
+        <v>46048</v>
       </c>
       <c r="B83" t="n">
-        <v>83.43000030517578</v>
+        <v>86.91999816894531</v>
       </c>
       <c r="C83" t="n">
-        <v>86.30000305175781</v>
+        <v>86.94000244140625</v>
       </c>
       <c r="D83" t="n">
-        <v>83.27999877929688</v>
+        <v>85.34999847412109</v>
       </c>
       <c r="E83" t="n">
-        <v>86.12000274658203</v>
+        <v>85.69999694824219</v>
       </c>
       <c r="F83" t="n">
-        <v>64520400</v>
+        <v>40941900</v>
       </c>
       <c r="G83" t="n">
         <v>0</v>
@@ -2601,22 +2601,22 @@
     </row>
     <row r="84">
       <c r="A84" s="1" t="n">
-        <v>46048</v>
+        <v>46049</v>
       </c>
       <c r="B84" t="n">
-        <v>86.91999816894531</v>
+        <v>85.27999877929688</v>
       </c>
       <c r="C84" t="n">
-        <v>86.94000244140625</v>
+        <v>85.59999847412109</v>
       </c>
       <c r="D84" t="n">
-        <v>85.34999847412109</v>
+        <v>83.87999725341797</v>
       </c>
       <c r="E84" t="n">
-        <v>85.69999694824219</v>
+        <v>85.58000183105469</v>
       </c>
       <c r="F84" t="n">
-        <v>40941900</v>
+        <v>37790800</v>
       </c>
       <c r="G84" t="n">
         <v>0</v>
@@ -2627,22 +2627,22 @@
     </row>
     <row r="85">
       <c r="A85" s="1" t="n">
-        <v>46049</v>
+        <v>46050</v>
       </c>
       <c r="B85" t="n">
-        <v>85.27999877929688</v>
+        <v>85.62999725341797</v>
       </c>
       <c r="C85" t="n">
-        <v>85.59999847412109</v>
+        <v>86.47000122070312</v>
       </c>
       <c r="D85" t="n">
-        <v>83.87999725341797</v>
+        <v>84.30000305175781</v>
       </c>
       <c r="E85" t="n">
-        <v>85.58000183105469</v>
+        <v>84.63999938964844</v>
       </c>
       <c r="F85" t="n">
-        <v>37790800</v>
+        <v>37762600</v>
       </c>
       <c r="G85" t="n">
         <v>0</v>
@@ -2653,22 +2653,22 @@
     </row>
     <row r="86">
       <c r="A86" s="1" t="n">
-        <v>46050</v>
+        <v>46051</v>
       </c>
       <c r="B86" t="n">
-        <v>85.62999725341797</v>
+        <v>84.30999755859375</v>
       </c>
       <c r="C86" t="n">
-        <v>86.47000122070312</v>
+        <v>84.37999725341797</v>
       </c>
       <c r="D86" t="n">
-        <v>84.30000305175781</v>
+        <v>82.34999847412109</v>
       </c>
       <c r="E86" t="n">
-        <v>84.63999938964844</v>
+        <v>83.16000366210938</v>
       </c>
       <c r="F86" t="n">
-        <v>37762600</v>
+        <v>42278100</v>
       </c>
       <c r="G86" t="n">
         <v>0</v>
@@ -2679,22 +2679,22 @@
     </row>
     <row r="87">
       <c r="A87" s="1" t="n">
-        <v>46051</v>
+        <v>46052</v>
       </c>
       <c r="B87" t="n">
-        <v>84.30999755859375</v>
+        <v>83.09999847412109</v>
       </c>
       <c r="C87" t="n">
-        <v>84.37999725341797</v>
+        <v>84.05999755859375</v>
       </c>
       <c r="D87" t="n">
-        <v>82.34999847412109</v>
+        <v>82.77999877929688</v>
       </c>
       <c r="E87" t="n">
-        <v>83.16000366210938</v>
+        <v>83.48999786376953</v>
       </c>
       <c r="F87" t="n">
-        <v>42278100</v>
+        <v>45755000</v>
       </c>
       <c r="G87" t="n">
         <v>0</v>
@@ -2705,22 +2705,22 @@
     </row>
     <row r="88">
       <c r="A88" s="1" t="n">
-        <v>46052</v>
+        <v>46055</v>
       </c>
       <c r="B88" t="n">
-        <v>83.09999847412109</v>
+        <v>83.52999877929688</v>
       </c>
       <c r="C88" t="n">
-        <v>84.05999755859375</v>
+        <v>85.26999664306641</v>
       </c>
       <c r="D88" t="n">
-        <v>82.77999877929688</v>
+        <v>82.72000122070312</v>
       </c>
       <c r="E88" t="n">
-        <v>83.48999786376953</v>
+        <v>82.76000213623047</v>
       </c>
       <c r="F88" t="n">
-        <v>45755000</v>
+        <v>41445300</v>
       </c>
       <c r="G88" t="n">
         <v>0</v>
@@ -2731,22 +2731,22 @@
     </row>
     <row r="89">
       <c r="A89" s="1" t="n">
-        <v>46055</v>
+        <v>46056</v>
       </c>
       <c r="B89" t="n">
-        <v>83.52999877929688</v>
+        <v>82.23000335693359</v>
       </c>
       <c r="C89" t="n">
-        <v>85.26999664306641</v>
+        <v>82.44999694824219</v>
       </c>
       <c r="D89" t="n">
-        <v>82.72000122070312</v>
+        <v>79.62000274658203</v>
       </c>
       <c r="E89" t="n">
-        <v>82.76000213623047</v>
+        <v>79.94000244140625</v>
       </c>
       <c r="F89" t="n">
-        <v>41445300</v>
+        <v>49789000</v>
       </c>
       <c r="G89" t="n">
         <v>0</v>
@@ -2757,22 +2757,22 @@
     </row>
     <row r="90">
       <c r="A90" s="1" t="n">
-        <v>46056</v>
+        <v>46057</v>
       </c>
       <c r="B90" t="n">
-        <v>82.23000335693359</v>
+        <v>79.98999786376953</v>
       </c>
       <c r="C90" t="n">
-        <v>82.44999694824219</v>
+        <v>81.44000244140625</v>
       </c>
       <c r="D90" t="n">
-        <v>79.62000274658203</v>
+        <v>79.23000335693359</v>
       </c>
       <c r="E90" t="n">
-        <v>79.94000244140625</v>
+        <v>80.16000366210938</v>
       </c>
       <c r="F90" t="n">
-        <v>49789000</v>
+        <v>48963200</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
@@ -2783,22 +2783,22 @@
     </row>
     <row r="91">
       <c r="A91" s="1" t="n">
-        <v>46057</v>
+        <v>46058</v>
       </c>
       <c r="B91" t="n">
-        <v>79.98999786376953</v>
+        <v>81.48999786376953</v>
       </c>
       <c r="C91" t="n">
-        <v>81.44000244140625</v>
+        <v>83.30000305175781</v>
       </c>
       <c r="D91" t="n">
-        <v>79.23000335693359</v>
+        <v>80.54000091552734</v>
       </c>
       <c r="E91" t="n">
-        <v>80.16000366210938</v>
+        <v>80.87000274658203</v>
       </c>
       <c r="F91" t="n">
-        <v>48963200</v>
+        <v>54805700</v>
       </c>
       <c r="G91" t="n">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="92">
       <c r="A92" s="1" t="n">
-        <v>46058</v>
+        <v>46059</v>
       </c>
       <c r="B92" t="n">
-        <v>81.48999786376953</v>
+        <v>81.01999664306641</v>
       </c>
       <c r="C92" t="n">
-        <v>83.30000305175781</v>
+        <v>82.48999786376953</v>
       </c>
       <c r="D92" t="n">
-        <v>80.54000091552734</v>
+        <v>80.65000152587891</v>
       </c>
       <c r="E92" t="n">
-        <v>80.87000274658203</v>
+        <v>82.19999694824219</v>
       </c>
       <c r="F92" t="n">
-        <v>54805700</v>
+        <v>46154100</v>
       </c>
       <c r="G92" t="n">
         <v>0</v>
@@ -2835,22 +2835,22 @@
     </row>
     <row r="93">
       <c r="A93" s="1" t="n">
-        <v>46059</v>
+        <v>46062</v>
       </c>
       <c r="B93" t="n">
-        <v>81.01999664306641</v>
+        <v>82.18000030517578</v>
       </c>
       <c r="C93" t="n">
-        <v>82.48999786376953</v>
+        <v>82.20999908447266</v>
       </c>
       <c r="D93" t="n">
-        <v>80.65000152587891</v>
+        <v>79.87000274658203</v>
       </c>
       <c r="E93" t="n">
-        <v>82.19999694824219</v>
+        <v>81.47000122070312</v>
       </c>
       <c r="F93" t="n">
-        <v>46154100</v>
+        <v>42200200</v>
       </c>
       <c r="G93" t="n">
         <v>0</v>
@@ -2861,22 +2861,22 @@
     </row>
     <row r="94">
       <c r="A94" s="1" t="n">
-        <v>46062</v>
+        <v>46063</v>
       </c>
       <c r="B94" t="n">
-        <v>82.18000030517578</v>
+        <v>82.72000122070312</v>
       </c>
       <c r="C94" t="n">
+        <v>84.66000366210938</v>
+      </c>
+      <c r="D94" t="n">
+        <v>82.08999633789062</v>
+      </c>
+      <c r="E94" t="n">
         <v>82.20999908447266</v>
       </c>
-      <c r="D94" t="n">
-        <v>79.87000274658203</v>
-      </c>
-      <c r="E94" t="n">
-        <v>81.47000122070312</v>
-      </c>
       <c r="F94" t="n">
-        <v>42200200</v>
+        <v>43595800</v>
       </c>
       <c r="G94" t="n">
         <v>0</v>
@@ -2887,22 +2887,22 @@
     </row>
     <row r="95">
       <c r="A95" s="1" t="n">
-        <v>46063</v>
+        <v>46064</v>
       </c>
       <c r="B95" t="n">
-        <v>82.72000122070312</v>
+        <v>81.95999908447266</v>
       </c>
       <c r="C95" t="n">
-        <v>84.66000366210938</v>
+        <v>82.48000335693359</v>
       </c>
       <c r="D95" t="n">
-        <v>82.08999633789062</v>
+        <v>79.44999694824219</v>
       </c>
       <c r="E95" t="n">
-        <v>82.20999908447266</v>
+        <v>79.62000274658203</v>
       </c>
       <c r="F95" t="n">
-        <v>43595800</v>
+        <v>40840300</v>
       </c>
       <c r="G95" t="n">
         <v>0</v>
@@ -2913,22 +2913,22 @@
     </row>
     <row r="96">
       <c r="A96" s="1" t="n">
-        <v>46064</v>
+        <v>46065</v>
       </c>
       <c r="B96" t="n">
-        <v>81.95999908447266</v>
+        <v>79.11000061035156</v>
       </c>
       <c r="C96" t="n">
-        <v>82.48000335693359</v>
+        <v>79.15000152587891</v>
       </c>
       <c r="D96" t="n">
-        <v>79.44999694824219</v>
+        <v>75.23000335693359</v>
       </c>
       <c r="E96" t="n">
-        <v>79.62000274658203</v>
+        <v>75.86000061035156</v>
       </c>
       <c r="F96" t="n">
-        <v>40840300</v>
+        <v>73516100</v>
       </c>
       <c r="G96" t="n">
         <v>0</v>
@@ -2939,22 +2939,22 @@
     </row>
     <row r="97">
       <c r="A97" s="1" t="n">
-        <v>46065</v>
+        <v>46066</v>
       </c>
       <c r="B97" t="n">
-        <v>79.11000061035156</v>
+        <v>76.13999938964844</v>
       </c>
       <c r="C97" t="n">
-        <v>79.15000152587891</v>
+        <v>77.18000030517578</v>
       </c>
       <c r="D97" t="n">
-        <v>75.23000335693359</v>
+        <v>75.52999877929688</v>
       </c>
       <c r="E97" t="n">
-        <v>75.86000061035156</v>
+        <v>76.87000274658203</v>
       </c>
       <c r="F97" t="n">
-        <v>73516100</v>
+        <v>42292100</v>
       </c>
       <c r="G97" t="n">
         <v>0</v>
@@ -2965,22 +2965,22 @@
     </row>
     <row r="98">
       <c r="A98" s="1" t="n">
-        <v>46066</v>
+        <v>46070</v>
       </c>
       <c r="B98" t="n">
-        <v>76.13999938964844</v>
+        <v>76.91999816894531</v>
       </c>
       <c r="C98" t="n">
-        <v>77.18000030517578</v>
+        <v>77.87000274658203</v>
       </c>
       <c r="D98" t="n">
-        <v>75.52999877929688</v>
+        <v>75.30000305175781</v>
       </c>
       <c r="E98" t="n">
-        <v>76.87000274658203</v>
+        <v>77</v>
       </c>
       <c r="F98" t="n">
-        <v>42292100</v>
+        <v>35961500</v>
       </c>
       <c r="G98" t="n">
         <v>0</v>
@@ -2991,22 +2991,22 @@
     </row>
     <row r="99">
       <c r="A99" s="1" t="n">
-        <v>46070</v>
+        <v>46071</v>
       </c>
       <c r="B99" t="n">
-        <v>76.91999816894531</v>
+        <v>77.31999969482422</v>
       </c>
       <c r="C99" t="n">
-        <v>77.87000274658203</v>
+        <v>78.31999969482422</v>
       </c>
       <c r="D99" t="n">
-        <v>75.30000305175781</v>
+        <v>76.27999877929688</v>
       </c>
       <c r="E99" t="n">
-        <v>77</v>
+        <v>77.98999786376953</v>
       </c>
       <c r="F99" t="n">
-        <v>35961500</v>
+        <v>29883100</v>
       </c>
       <c r="G99" t="n">
         <v>0</v>
@@ -3017,22 +3017,22 @@
     </row>
     <row r="100">
       <c r="A100" s="1" t="n">
-        <v>46071</v>
+        <v>46072</v>
       </c>
       <c r="B100" t="n">
-        <v>77.31999969482422</v>
+        <v>77.75</v>
       </c>
       <c r="C100" t="n">
-        <v>78.31999969482422</v>
+        <v>78.69999694824219</v>
       </c>
       <c r="D100" t="n">
-        <v>76.27999877929688</v>
+        <v>76.58999633789062</v>
       </c>
       <c r="E100" t="n">
-        <v>77.98999786376953</v>
+        <v>77</v>
       </c>
       <c r="F100" t="n">
-        <v>29883100</v>
+        <v>30139200</v>
       </c>
       <c r="G100" t="n">
         <v>0</v>
@@ -3043,22 +3043,22 @@
     </row>
     <row r="101">
       <c r="A101" s="1" t="n">
-        <v>46072</v>
+        <v>46073</v>
       </c>
       <c r="B101" t="n">
-        <v>77.75</v>
+        <v>76.61000061035156</v>
       </c>
       <c r="C101" t="n">
-        <v>78.69999694824219</v>
+        <v>78.84999847412109</v>
       </c>
       <c r="D101" t="n">
-        <v>76.58999633789062</v>
+        <v>76.40000152587891</v>
       </c>
       <c r="E101" t="n">
-        <v>77</v>
+        <v>78.66999816894531</v>
       </c>
       <c r="F101" t="n">
-        <v>30139200</v>
+        <v>32411300</v>
       </c>
       <c r="G101" t="n">
         <v>0</v>
@@ -3069,22 +3069,22 @@
     </row>
     <row r="102">
       <c r="A102" s="1" t="n">
-        <v>46073</v>
+        <v>46076</v>
       </c>
       <c r="B102" t="n">
-        <v>76.61000061035156</v>
+        <v>77.79000091552734</v>
       </c>
       <c r="C102" t="n">
-        <v>78.84999847412109</v>
+        <v>77.83000183105469</v>
       </c>
       <c r="D102" t="n">
-        <v>76.40000152587891</v>
+        <v>75.01000213623047</v>
       </c>
       <c r="E102" t="n">
-        <v>78.66999816894531</v>
+        <v>76.01999664306641</v>
       </c>
       <c r="F102" t="n">
-        <v>32411300</v>
+        <v>38363000</v>
       </c>
       <c r="G102" t="n">
         <v>0</v>
@@ -3095,22 +3095,22 @@
     </row>
     <row r="103">
       <c r="A103" s="1" t="n">
-        <v>46076</v>
+        <v>46077</v>
       </c>
       <c r="B103" t="n">
-        <v>77.79000091552734</v>
+        <v>75.73000335693359</v>
       </c>
       <c r="C103" t="n">
-        <v>77.83000183105469</v>
+        <v>78.12000274658203</v>
       </c>
       <c r="D103" t="n">
-        <v>75.01000213623047</v>
+        <v>75.20999908447266</v>
       </c>
       <c r="E103" t="n">
-        <v>76.01999664306641</v>
+        <v>78.04000091552734</v>
       </c>
       <c r="F103" t="n">
-        <v>38363000</v>
+        <v>33079100</v>
       </c>
       <c r="G103" t="n">
         <v>0</v>
@@ -3121,22 +3121,22 @@
     </row>
     <row r="104">
       <c r="A104" s="1" t="n">
-        <v>46077</v>
+        <v>46078</v>
       </c>
       <c r="B104" t="n">
-        <v>75.73000335693359</v>
+        <v>79.43000030517578</v>
       </c>
       <c r="C104" t="n">
-        <v>78.12000274658203</v>
+        <v>83.12000274658203</v>
       </c>
       <c r="D104" t="n">
-        <v>75.20999908447266</v>
+        <v>79.25</v>
       </c>
       <c r="E104" t="n">
-        <v>78.04000091552734</v>
+        <v>82.69999694824219</v>
       </c>
       <c r="F104" t="n">
-        <v>33079100</v>
+        <v>69319300</v>
       </c>
       <c r="G104" t="n">
         <v>0</v>
@@ -3147,22 +3147,22 @@
     </row>
     <row r="105">
       <c r="A105" s="1" t="n">
-        <v>46078</v>
+        <v>46079</v>
       </c>
       <c r="B105" t="n">
-        <v>79.43000030517578</v>
+        <v>83.19999694824219</v>
       </c>
       <c r="C105" t="n">
-        <v>83.12000274658203</v>
+        <v>86.5</v>
       </c>
       <c r="D105" t="n">
-        <v>79.25</v>
+        <v>82.80000305175781</v>
       </c>
       <c r="E105" t="n">
-        <v>82.69999694824219</v>
+        <v>84.58999633789062</v>
       </c>
       <c r="F105" t="n">
-        <v>69319300</v>
+        <v>85642500</v>
       </c>
       <c r="G105" t="n">
         <v>0</v>
@@ -3173,22 +3173,22 @@
     </row>
     <row r="106">
       <c r="A106" s="1" t="n">
-        <v>46079</v>
+        <v>46080</v>
       </c>
       <c r="B106" t="n">
-        <v>83.19999694824219</v>
+        <v>94.30000305175781</v>
       </c>
       <c r="C106" t="n">
-        <v>86.5</v>
+        <v>96.75</v>
       </c>
       <c r="D106" t="n">
-        <v>82.80000305175781</v>
+        <v>90.58000183105469</v>
       </c>
       <c r="E106" t="n">
-        <v>84.58999633789062</v>
+        <v>96.23999786376953</v>
       </c>
       <c r="F106" t="n">
-        <v>85642500</v>
+        <v>200767000</v>
       </c>
       <c r="G106" t="n">
         <v>0</v>
@@ -3199,22 +3199,22 @@
     </row>
     <row r="107">
       <c r="A107" s="1" t="n">
-        <v>46080</v>
+        <v>46083</v>
       </c>
       <c r="B107" t="n">
-        <v>94.30000305175781</v>
+        <v>95.26000213623047</v>
       </c>
       <c r="C107" t="n">
-        <v>96.75</v>
+        <v>98.06999969482422</v>
       </c>
       <c r="D107" t="n">
-        <v>90.58000183105469</v>
+        <v>95.19999694824219</v>
       </c>
       <c r="E107" t="n">
-        <v>96.23999786376953</v>
+        <v>97.08999633789062</v>
       </c>
       <c r="F107" t="n">
-        <v>200767000</v>
+        <v>79915400</v>
       </c>
       <c r="G107" t="n">
         <v>0</v>
@@ -3225,22 +3225,22 @@
     </row>
     <row r="108">
       <c r="A108" s="1" t="n">
-        <v>46083</v>
+        <v>46084</v>
       </c>
       <c r="B108" t="n">
-        <v>95.26000213623047</v>
+        <v>96.01000213623047</v>
       </c>
       <c r="C108" t="n">
-        <v>98.06999969482422</v>
+        <v>98.45999908447266</v>
       </c>
       <c r="D108" t="n">
-        <v>95.19999694824219</v>
+        <v>95.33000183105469</v>
       </c>
       <c r="E108" t="n">
-        <v>97.08999633789062</v>
+        <v>97.69999694824219</v>
       </c>
       <c r="F108" t="n">
-        <v>79915400</v>
+        <v>59149000</v>
       </c>
       <c r="G108" t="n">
         <v>0</v>
@@ -3251,22 +3251,22 @@
     </row>
     <row r="109">
       <c r="A109" s="1" t="n">
-        <v>46084</v>
+        <v>46085</v>
       </c>
       <c r="B109" t="n">
-        <v>96.01000213623047</v>
+        <v>97.11000061035156</v>
       </c>
       <c r="C109" t="n">
-        <v>98.45999908447266</v>
+        <v>99.75</v>
       </c>
       <c r="D109" t="n">
-        <v>95.33000183105469</v>
+        <v>96.98999786376953</v>
       </c>
       <c r="E109" t="n">
-        <v>97.69999694824219</v>
+        <v>98.66000366210938</v>
       </c>
       <c r="F109" t="n">
-        <v>59149000</v>
+        <v>52604300</v>
       </c>
       <c r="G109" t="n">
         <v>0</v>
@@ -3277,22 +3277,22 @@
     </row>
     <row r="110">
       <c r="A110" s="1" t="n">
-        <v>46085</v>
+        <v>46086</v>
       </c>
       <c r="B110" t="n">
-        <v>97.11000061035156</v>
+        <v>98.5</v>
       </c>
       <c r="C110" t="n">
-        <v>99.75</v>
+        <v>100.1900024414062</v>
       </c>
       <c r="D110" t="n">
-        <v>96.98999786376953</v>
+        <v>98.09999847412109</v>
       </c>
       <c r="E110" t="n">
-        <v>98.66000366210938</v>
+        <v>99.16999816894531</v>
       </c>
       <c r="F110" t="n">
-        <v>52604300</v>
+        <v>53403000</v>
       </c>
       <c r="G110" t="n">
         <v>0</v>
@@ -3303,22 +3303,22 @@
     </row>
     <row r="111">
       <c r="A111" s="1" t="n">
-        <v>46086</v>
+        <v>46087</v>
       </c>
       <c r="B111" t="n">
-        <v>98.5</v>
+        <v>99.33000183105469</v>
       </c>
       <c r="C111" t="n">
-        <v>100.1900024414062</v>
+        <v>99.87999725341797</v>
       </c>
       <c r="D111" t="n">
-        <v>98.09999847412109</v>
+        <v>97.40000152587891</v>
       </c>
       <c r="E111" t="n">
-        <v>99.16999816894531</v>
+        <v>99.01999664306641</v>
       </c>
       <c r="F111" t="n">
-        <v>53403000</v>
+        <v>41196300</v>
       </c>
       <c r="G111" t="n">
         <v>0</v>
@@ -3329,22 +3329,22 @@
     </row>
     <row r="112">
       <c r="A112" s="1" t="n">
-        <v>46087</v>
+        <v>46090</v>
       </c>
       <c r="B112" t="n">
-        <v>99.33000183105469</v>
+        <v>97.69999694824219</v>
       </c>
       <c r="C112" t="n">
-        <v>99.87999725341797</v>
+        <v>98.94000244140625</v>
       </c>
       <c r="D112" t="n">
-        <v>97.40000152587891</v>
+        <v>96.58000183105469</v>
       </c>
       <c r="E112" t="n">
-        <v>99.01999664306641</v>
+        <v>98.31999969482422</v>
       </c>
       <c r="F112" t="n">
-        <v>41196300</v>
+        <v>48589000</v>
       </c>
       <c r="G112" t="n">
         <v>0</v>
@@ -3355,22 +3355,22 @@
     </row>
     <row r="113">
       <c r="A113" s="1" t="n">
-        <v>46090</v>
+        <v>46091</v>
       </c>
       <c r="B113" t="n">
-        <v>97.69999694824219</v>
+        <v>97.80999755859375</v>
       </c>
       <c r="C113" t="n">
-        <v>98.94000244140625</v>
+        <v>98.48999786376953</v>
       </c>
       <c r="D113" t="n">
-        <v>96.58000183105469</v>
+        <v>96.29000091552734</v>
       </c>
       <c r="E113" t="n">
-        <v>98.31999969482422</v>
+        <v>96.94000244140625</v>
       </c>
       <c r="F113" t="n">
-        <v>48589000</v>
+        <v>41027200</v>
       </c>
       <c r="G113" t="n">
         <v>0</v>
@@ -3381,22 +3381,22 @@
     </row>
     <row r="114">
       <c r="A114" s="1" t="n">
-        <v>46091</v>
+        <v>46092</v>
       </c>
       <c r="B114" t="n">
-        <v>97.80999755859375</v>
+        <v>97.41000366210938</v>
       </c>
       <c r="C114" t="n">
-        <v>98.48999786376953</v>
+        <v>98</v>
       </c>
       <c r="D114" t="n">
-        <v>96.29000091552734</v>
+        <v>94.69000244140625</v>
       </c>
       <c r="E114" t="n">
-        <v>96.94000244140625</v>
+        <v>94.88999938964844</v>
       </c>
       <c r="F114" t="n">
-        <v>41027200</v>
+        <v>33962900</v>
       </c>
       <c r="G114" t="n">
         <v>0</v>
@@ -3407,22 +3407,22 @@
     </row>
     <row r="115">
       <c r="A115" s="1" t="n">
-        <v>46092</v>
+        <v>46093</v>
       </c>
       <c r="B115" t="n">
-        <v>97.41000366210938</v>
+        <v>94.86000061035156</v>
       </c>
       <c r="C115" t="n">
-        <v>98</v>
+        <v>95.40000152587891</v>
       </c>
       <c r="D115" t="n">
-        <v>94.69000244140625</v>
+        <v>93.87000274658203</v>
       </c>
       <c r="E115" t="n">
-        <v>94.88999938964844</v>
+        <v>94.30999755859375</v>
       </c>
       <c r="F115" t="n">
-        <v>33962900</v>
+        <v>34206900</v>
       </c>
       <c r="G115" t="n">
         <v>0</v>
@@ -3433,22 +3433,22 @@
     </row>
     <row r="116">
       <c r="A116" s="1" t="n">
-        <v>46093</v>
+        <v>46094</v>
       </c>
       <c r="B116" t="n">
-        <v>94.86000061035156</v>
+        <v>94.63999938964844</v>
       </c>
       <c r="C116" t="n">
-        <v>95.40000152587891</v>
+        <v>95.68000030517578</v>
       </c>
       <c r="D116" t="n">
-        <v>93.87000274658203</v>
+        <v>94.23999786376953</v>
       </c>
       <c r="E116" t="n">
-        <v>94.30999755859375</v>
+        <v>95.30999755859375</v>
       </c>
       <c r="F116" t="n">
-        <v>34206900</v>
+        <v>29876700</v>
       </c>
       <c r="G116" t="n">
         <v>0</v>
@@ -3459,22 +3459,22 @@
     </row>
     <row r="117">
       <c r="A117" s="1" t="n">
-        <v>46094</v>
+        <v>46097</v>
       </c>
       <c r="B117" t="n">
-        <v>94.63999938964844</v>
+        <v>95.58000183105469</v>
       </c>
       <c r="C117" t="n">
-        <v>95.68000030517578</v>
+        <v>96.09999847412109</v>
       </c>
       <c r="D117" t="n">
-        <v>94.23999786376953</v>
+        <v>94.36000061035156</v>
       </c>
       <c r="E117" t="n">
-        <v>95.30999755859375</v>
+        <v>95.19999694824219</v>
       </c>
       <c r="F117" t="n">
-        <v>29876700</v>
+        <v>34931800</v>
       </c>
       <c r="G117" t="n">
         <v>0</v>
@@ -3485,22 +3485,22 @@
     </row>
     <row r="118">
       <c r="A118" s="1" t="n">
-        <v>46097</v>
+        <v>46098</v>
       </c>
       <c r="B118" t="n">
-        <v>95.58000183105469</v>
+        <v>95.30000305175781</v>
       </c>
       <c r="C118" t="n">
-        <v>96.09999847412109</v>
+        <v>96.33999633789062</v>
       </c>
       <c r="D118" t="n">
+        <v>94.01000213623047</v>
+      </c>
+      <c r="E118" t="n">
         <v>94.36000061035156</v>
       </c>
-      <c r="E118" t="n">
-        <v>95.19999694824219</v>
-      </c>
       <c r="F118" t="n">
-        <v>34931800</v>
+        <v>26434500</v>
       </c>
       <c r="G118" t="n">
         <v>0</v>
@@ -3511,22 +3511,22 @@
     </row>
     <row r="119">
       <c r="A119" s="1" t="n">
-        <v>46098</v>
+        <v>46099</v>
       </c>
       <c r="B119" t="n">
-        <v>95.30000305175781</v>
+        <v>94.44999694824219</v>
       </c>
       <c r="C119" t="n">
-        <v>96.33999633789062</v>
+        <v>95.33999633789062</v>
       </c>
       <c r="D119" t="n">
-        <v>94.01000213623047</v>
+        <v>93.61000061035156</v>
       </c>
       <c r="E119" t="n">
-        <v>94.36000061035156</v>
+        <v>94.69999694824219</v>
       </c>
       <c r="F119" t="n">
-        <v>26434500</v>
+        <v>27878300</v>
       </c>
       <c r="G119" t="n">
         <v>0</v>
@@ -3537,22 +3537,22 @@
     </row>
     <row r="120">
       <c r="A120" s="1" t="n">
-        <v>46099</v>
+        <v>46100</v>
       </c>
       <c r="B120" t="n">
-        <v>94.44999694824219</v>
+        <v>94.30999755859375</v>
       </c>
       <c r="C120" t="n">
-        <v>95.33999633789062</v>
+        <v>95.75</v>
       </c>
       <c r="D120" t="n">
-        <v>93.61000061035156</v>
+        <v>90.77999877929688</v>
       </c>
       <c r="E120" t="n">
-        <v>94.69999694824219</v>
+        <v>91.73999786376953</v>
       </c>
       <c r="F120" t="n">
-        <v>27878300</v>
+        <v>40169300</v>
       </c>
       <c r="G120" t="n">
         <v>0</v>
@@ -3563,22 +3563,22 @@
     </row>
     <row r="121">
       <c r="A121" s="1" t="n">
-        <v>46100</v>
+        <v>46101</v>
       </c>
       <c r="B121" t="n">
-        <v>94.30999755859375</v>
+        <v>91.30999755859375</v>
       </c>
       <c r="C121" t="n">
-        <v>95.75</v>
+        <v>91.87999725341797</v>
       </c>
       <c r="D121" t="n">
-        <v>90.77999877929688</v>
+        <v>90.69000244140625</v>
       </c>
       <c r="E121" t="n">
-        <v>91.73999786376953</v>
+        <v>91.81999969482422</v>
       </c>
       <c r="F121" t="n">
-        <v>40169300</v>
+        <v>61678000</v>
       </c>
       <c r="G121" t="n">
         <v>0</v>
@@ -3589,22 +3589,22 @@
     </row>
     <row r="122">
       <c r="A122" s="1" t="n">
-        <v>46101</v>
+        <v>46104</v>
       </c>
       <c r="B122" t="n">
-        <v>91.30999755859375</v>
+        <v>92.04000091552734</v>
       </c>
       <c r="C122" t="n">
-        <v>91.87999725341797</v>
+        <v>93.98000335693359</v>
       </c>
       <c r="D122" t="n">
-        <v>90.69000244140625</v>
+        <v>91.86000061035156</v>
       </c>
       <c r="E122" t="n">
-        <v>91.81999969482422</v>
+        <v>93.37999725341797</v>
       </c>
       <c r="F122" t="n">
-        <v>61678000</v>
+        <v>34315900</v>
       </c>
       <c r="G122" t="n">
         <v>0</v>
@@ -3615,22 +3615,22 @@
     </row>
     <row r="123">
       <c r="A123" s="1" t="n">
-        <v>46104</v>
+        <v>46105</v>
       </c>
       <c r="B123" t="n">
-        <v>92.04000091552734</v>
+        <v>92.79000091552734</v>
       </c>
       <c r="C123" t="n">
-        <v>93.98000335693359</v>
+        <v>93.73999786376953</v>
       </c>
       <c r="D123" t="n">
-        <v>91.86000061035156</v>
+        <v>90.81999969482422</v>
       </c>
       <c r="E123" t="n">
-        <v>93.37999725341797</v>
+        <v>90.91999816894531</v>
       </c>
       <c r="F123" t="n">
-        <v>34315900</v>
+        <v>28938000</v>
       </c>
       <c r="G123" t="n">
         <v>0</v>
@@ -3641,22 +3641,22 @@
     </row>
     <row r="124">
       <c r="A124" s="1" t="n">
-        <v>46105</v>
+        <v>46106</v>
       </c>
       <c r="B124" t="n">
-        <v>92.79000091552734</v>
+        <v>91.70999908447266</v>
       </c>
       <c r="C124" t="n">
-        <v>93.73999786376953</v>
+        <v>92.51999664306641</v>
       </c>
       <c r="D124" t="n">
-        <v>90.81999969482422</v>
+        <v>91.23999786376953</v>
       </c>
       <c r="E124" t="n">
-        <v>90.91999816894531</v>
+        <v>92.27999877929688</v>
       </c>
       <c r="F124" t="n">
-        <v>28938000</v>
+        <v>29545600</v>
       </c>
       <c r="G124" t="n">
         <v>0</v>
@@ -3667,22 +3667,22 @@
     </row>
     <row r="125">
       <c r="A125" s="1" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B125" t="n">
-        <v>91.70999908447266</v>
+        <v>91.51999664306641</v>
       </c>
       <c r="C125" t="n">
-        <v>92.51999664306641</v>
+        <v>95.86000061035156</v>
       </c>
       <c r="D125" t="n">
-        <v>91.23999786376953</v>
+        <v>91.01000213623047</v>
       </c>
       <c r="E125" t="n">
-        <v>92.27999877929688</v>
+        <v>93.31999969482422</v>
       </c>
       <c r="F125" t="n">
-        <v>29545600</v>
+        <v>59522000</v>
       </c>
       <c r="G125" t="n">
         <v>0</v>
@@ -3693,22 +3693,22 @@
     </row>
     <row r="126">
       <c r="A126" s="1" t="n">
-        <v>46107</v>
+        <v>46108</v>
       </c>
       <c r="B126" t="n">
-        <v>91.51999664306641</v>
+        <v>94.56999969482422</v>
       </c>
       <c r="C126" t="n">
-        <v>95.86000061035156</v>
+        <v>95.58000183105469</v>
       </c>
       <c r="D126" t="n">
-        <v>91.01000213623047</v>
+        <v>92.73999786376953</v>
       </c>
       <c r="E126" t="n">
-        <v>93.31999969482422</v>
+        <v>93.43000030517578</v>
       </c>
       <c r="F126" t="n">
-        <v>59522000</v>
+        <v>44590700</v>
       </c>
       <c r="G126" t="n">
         <v>0</v>
@@ -3719,22 +3719,22 @@
     </row>
     <row r="127">
       <c r="A127" s="1" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B127" t="n">
-        <v>94.56999969482422</v>
+        <v>92.75</v>
       </c>
       <c r="C127" t="n">
-        <v>95.58000183105469</v>
+        <v>94.48999786376953</v>
       </c>
       <c r="D127" t="n">
-        <v>92.73999786376953</v>
+        <v>92.22000122070312</v>
       </c>
       <c r="E127" t="n">
-        <v>93.43000030517578</v>
+        <v>92.97000122070312</v>
       </c>
       <c r="F127" t="n">
-        <v>44590700</v>
+        <v>32375100</v>
       </c>
       <c r="G127" t="n">
         <v>0</v>
@@ -3745,22 +3745,22 @@
     </row>
     <row r="128">
       <c r="A128" s="1" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B128" t="n">
-        <v>92.75</v>
+        <v>93.02999877929688</v>
       </c>
       <c r="C128" t="n">
-        <v>94.48999786376953</v>
+        <v>96.26000213623047</v>
       </c>
       <c r="D128" t="n">
-        <v>92.22000122070312</v>
+        <v>93.02999877929688</v>
       </c>
       <c r="E128" t="n">
-        <v>92.97000122070312</v>
+        <v>96.15000152587891</v>
       </c>
       <c r="F128" t="n">
-        <v>32375100</v>
+        <v>54270000</v>
       </c>
       <c r="G128" t="n">
         <v>0</v>
@@ -3771,22 +3771,22 @@
     </row>
     <row r="129">
       <c r="A129" s="1" t="n">
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="B129" t="n">
-        <v>93.02999877929688</v>
+        <v>96.47000122070312</v>
       </c>
       <c r="C129" t="n">
-        <v>96.26000213623047</v>
+        <v>97.19999694824219</v>
       </c>
       <c r="D129" t="n">
-        <v>93.02999877929688</v>
+        <v>94.26000213623047</v>
       </c>
       <c r="E129" t="n">
-        <v>96.15000152587891</v>
+        <v>95.55000305175781</v>
       </c>
       <c r="F129" t="n">
-        <v>54270000</v>
+        <v>30439300</v>
       </c>
       <c r="G129" t="n">
         <v>0</v>
@@ -3797,22 +3797,22 @@
     </row>
     <row r="130">
       <c r="A130" s="1" t="n">
-        <v>46113</v>
+        <v>46114</v>
       </c>
       <c r="B130" t="n">
-        <v>96.47000122070312</v>
+        <v>95.26999664306641</v>
       </c>
       <c r="C130" t="n">
-        <v>97.19999694824219</v>
+        <v>98.70999908447266</v>
       </c>
       <c r="D130" t="n">
-        <v>94.26000213623047</v>
+        <v>95.16999816894531</v>
       </c>
       <c r="E130" t="n">
-        <v>95.55000305175781</v>
+        <v>98.66000366210938</v>
       </c>
       <c r="F130" t="n">
-        <v>30439300</v>
+        <v>37068000</v>
       </c>
       <c r="G130" t="n">
         <v>0</v>
@@ -3823,22 +3823,22 @@
     </row>
     <row r="131">
       <c r="A131" s="1" t="n">
-        <v>46114</v>
+        <v>46118</v>
       </c>
       <c r="B131" t="n">
-        <v>95.26999664306641</v>
+        <v>100.9599990844727</v>
       </c>
       <c r="C131" t="n">
-        <v>98.70999908447266</v>
+        <v>102.6900024414062</v>
       </c>
       <c r="D131" t="n">
-        <v>95.16999816894531</v>
+        <v>97.97000122070312</v>
       </c>
       <c r="E131" t="n">
-        <v>98.66000366210938</v>
+        <v>98.93000030517578</v>
       </c>
       <c r="F131" t="n">
-        <v>37068000</v>
+        <v>37029300</v>
       </c>
       <c r="G131" t="n">
         <v>0</v>
@@ -3849,22 +3849,22 @@
     </row>
     <row r="132">
       <c r="A132" s="1" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B132" t="n">
-        <v>100.9599990844727</v>
+        <v>98.55000305175781</v>
       </c>
       <c r="C132" t="n">
-        <v>102.6900024414062</v>
+        <v>99.87999725341797</v>
       </c>
       <c r="D132" t="n">
-        <v>97.97000122070312</v>
+        <v>98.25</v>
       </c>
       <c r="E132" t="n">
-        <v>98.93000030517578</v>
+        <v>98.81999969482422</v>
       </c>
       <c r="F132" t="n">
-        <v>37029300</v>
+        <v>25016700</v>
       </c>
       <c r="G132" t="n">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="133">
       <c r="A133" s="1" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B133" t="n">
-        <v>98.55000305175781</v>
+        <v>100.3199996948242</v>
       </c>
       <c r="C133" t="n">
-        <v>99.87999725341797</v>
+        <v>100.4000015258789</v>
       </c>
       <c r="D133" t="n">
-        <v>98.25</v>
+        <v>97.44000244140625</v>
       </c>
       <c r="E133" t="n">
-        <v>98.81999969482422</v>
+        <v>99.38999938964844</v>
       </c>
       <c r="F133" t="n">
-        <v>25016700</v>
+        <v>30957600</v>
       </c>
       <c r="G133" t="n">
         <v>0</v>
@@ -3901,22 +3901,22 @@
     </row>
     <row r="134">
       <c r="A134" s="1" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B134" t="n">
-        <v>100.3199996948242</v>
+        <v>99.62999725341797</v>
       </c>
       <c r="C134" t="n">
-        <v>100.4000015258789</v>
+        <v>102.3399963378906</v>
       </c>
       <c r="D134" t="n">
-        <v>97.44000244140625</v>
+        <v>99.08000183105469</v>
       </c>
       <c r="E134" t="n">
-        <v>99.38999938964844</v>
+        <v>102.0500030517578</v>
       </c>
       <c r="F134" t="n">
-        <v>30957600</v>
+        <v>35087800</v>
       </c>
       <c r="G134" t="n">
         <v>0</v>
@@ -3927,22 +3927,22 @@
     </row>
     <row r="135">
       <c r="A135" s="1" t="n">
-        <v>46121</v>
+        <v>46122</v>
       </c>
       <c r="B135" t="n">
-        <v>99.62999725341797</v>
+        <v>102.4700012207031</v>
       </c>
       <c r="C135" t="n">
-        <v>102.3399963378906</v>
+        <v>103.0800018310547</v>
       </c>
       <c r="D135" t="n">
-        <v>99.08000183105469</v>
+        <v>101.4599990844727</v>
       </c>
       <c r="E135" t="n">
-        <v>102.0500030517578</v>
+        <v>103.0100021362305</v>
       </c>
       <c r="F135" t="n">
-        <v>35087800</v>
+        <v>25769900</v>
       </c>
       <c r="G135" t="n">
         <v>0</v>
@@ -3953,22 +3953,22 @@
     </row>
     <row r="136">
       <c r="A136" s="1" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B136" t="n">
-        <v>102.4700012207031</v>
+        <v>103.0299987792969</v>
       </c>
       <c r="C136" t="n">
-        <v>103.0800018310547</v>
+        <v>103.6699981689453</v>
       </c>
       <c r="D136" t="n">
-        <v>101.4599990844727</v>
+        <v>102.0599975585938</v>
       </c>
       <c r="E136" t="n">
-        <v>103.0100021362305</v>
+        <v>103.1600036621094</v>
       </c>
       <c r="F136" t="n">
-        <v>25769900</v>
+        <v>26042800</v>
       </c>
       <c r="G136" t="n">
         <v>0</v>
@@ -3979,22 +3979,22 @@
     </row>
     <row r="137">
       <c r="A137" s="1" t="n">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="B137" t="n">
-        <v>103.0299987792969</v>
+        <v>103.120002746582</v>
       </c>
       <c r="C137" t="n">
-        <v>103.6699981689453</v>
+        <v>106.5699996948242</v>
       </c>
       <c r="D137" t="n">
-        <v>102.0599975585938</v>
+        <v>103.0400009155273</v>
       </c>
       <c r="E137" t="n">
-        <v>103.1600036621094</v>
+        <v>106.2799987792969</v>
       </c>
       <c r="F137" t="n">
-        <v>26042800</v>
+        <v>40534900</v>
       </c>
       <c r="G137" t="n">
         <v>0</v>
@@ -4005,22 +4005,22 @@
     </row>
     <row r="138">
       <c r="A138" s="1" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B138" t="n">
-        <v>103.120002746582</v>
+        <v>105.9800033569336</v>
       </c>
       <c r="C138" t="n">
-        <v>106.5699996948242</v>
+        <v>107.8499984741211</v>
       </c>
       <c r="D138" t="n">
-        <v>103.0400009155273</v>
+        <v>105.0400009155273</v>
       </c>
       <c r="E138" t="n">
-        <v>106.2799987792969</v>
+        <v>107.7099990844727</v>
       </c>
       <c r="F138" t="n">
-        <v>40534900</v>
+        <v>38023700</v>
       </c>
       <c r="G138" t="n">
         <v>0</v>
@@ -4031,22 +4031,22 @@
     </row>
     <row r="139">
       <c r="A139" s="1" t="n">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c r="B139" t="n">
-        <v>105.9800033569336</v>
+        <v>107.4700012207031</v>
       </c>
       <c r="C139" t="n">
-        <v>107.8499984741211</v>
+        <v>108.9499969482422</v>
       </c>
       <c r="D139" t="n">
-        <v>105.0400009155273</v>
+        <v>106.620002746582</v>
       </c>
       <c r="E139" t="n">
-        <v>107.7099990844727</v>
+        <v>107.7900009155273</v>
       </c>
       <c r="F139" t="n">
-        <v>38023700</v>
+        <v>64928300</v>
       </c>
       <c r="G139" t="n">
         <v>0</v>
@@ -4057,22 +4057,22 @@
     </row>
     <row r="140">
       <c r="A140" s="1" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B140" t="n">
-        <v>107.4700012207031</v>
+        <v>96.37000274658203</v>
       </c>
       <c r="C140" t="n">
-        <v>108.9499969482422</v>
+        <v>98.73999786376953</v>
       </c>
       <c r="D140" t="n">
-        <v>106.620002746582</v>
+        <v>95.09999847412109</v>
       </c>
       <c r="E140" t="n">
-        <v>107.7900009155273</v>
+        <v>97.30999755859375</v>
       </c>
       <c r="F140" t="n">
-        <v>64928300</v>
+        <v>125958700</v>
       </c>
       <c r="G140" t="n">
         <v>0</v>
@@ -4083,22 +4083,22 @@
     </row>
     <row r="141">
       <c r="A141" s="1" t="n">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c r="B141" t="n">
-        <v>96.37000274658203</v>
+        <v>97.13999938964844</v>
       </c>
       <c r="C141" t="n">
-        <v>98.73999786376953</v>
+        <v>97.59999847412109</v>
       </c>
       <c r="D141" t="n">
-        <v>95.09999847412109</v>
+        <v>93.54000091552734</v>
       </c>
       <c r="E141" t="n">
-        <v>97.30999755859375</v>
+        <v>94.83000183105469</v>
       </c>
       <c r="F141" t="n">
-        <v>125958700</v>
+        <v>63298300</v>
       </c>
       <c r="G141" t="n">
         <v>0</v>
@@ -4109,22 +4109,22 @@
     </row>
     <row r="142">
       <c r="A142" s="1" t="n">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="B142" t="n">
-        <v>97.13999938964844</v>
+        <v>94</v>
       </c>
       <c r="C142" t="n">
-        <v>97.59999847412109</v>
+        <v>94.65000152587891</v>
       </c>
       <c r="D142" t="n">
-        <v>93.54000091552734</v>
+        <v>92.37000274658203</v>
       </c>
       <c r="E142" t="n">
-        <v>94.83000183105469</v>
+        <v>92.58000183105469</v>
       </c>
       <c r="F142" t="n">
-        <v>63298300</v>
+        <v>61962300</v>
       </c>
       <c r="G142" t="n">
         <v>0</v>
@@ -4135,22 +4135,22 @@
     </row>
     <row r="143">
       <c r="A143" s="1" t="n">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="B143" t="n">
-        <v>94</v>
+        <v>93.05999755859375</v>
       </c>
       <c r="C143" t="n">
-        <v>94.65000152587891</v>
+        <v>93.84999847412109</v>
       </c>
       <c r="D143" t="n">
-        <v>92.37000274658203</v>
+        <v>92.76999664306641</v>
       </c>
       <c r="E143" t="n">
-        <v>92.58000183105469</v>
+        <v>93.23999786376953</v>
       </c>
       <c r="F143" t="n">
-        <v>61962300</v>
+        <v>33694300</v>
       </c>
       <c r="G143" t="n">
         <v>0</v>
@@ -4161,22 +4161,22 @@
     </row>
     <row r="144">
       <c r="A144" s="1" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B144" t="n">
-        <v>93.05999755859375</v>
+        <v>94.05999755859375</v>
       </c>
       <c r="C144" t="n">
-        <v>93.84999847412109</v>
+        <v>94.63999938964844</v>
       </c>
       <c r="D144" t="n">
-        <v>92.76999664306641</v>
+        <v>92.06999969482422</v>
       </c>
       <c r="E144" t="n">
-        <v>93.23999786376953</v>
+        <v>92.81999969482422</v>
       </c>
       <c r="F144" t="n">
-        <v>33694300</v>
+        <v>36851700</v>
       </c>
       <c r="G144" t="n">
         <v>0</v>
@@ -4187,22 +4187,22 @@
     </row>
     <row r="145">
       <c r="A145" s="1" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B145" t="n">
-        <v>94.05999755859375</v>
+        <v>92.56999969482422</v>
       </c>
       <c r="C145" t="n">
-        <v>94.63999938964844</v>
+        <v>93.27999877929688</v>
       </c>
       <c r="D145" t="n">
-        <v>92.06999969482422</v>
+        <v>91.80000305175781</v>
       </c>
       <c r="E145" t="n">
-        <v>92.81999969482422</v>
+        <v>92.44000244140625</v>
       </c>
       <c r="F145" t="n">
-        <v>36851700</v>
+        <v>32553200</v>
       </c>
       <c r="G145" t="n">
         <v>0</v>
@@ -4213,22 +4213,22 @@
     </row>
     <row r="146">
       <c r="A146" s="1" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B146" t="n">
-        <v>92.56999969482422</v>
+        <v>92.05000305175781</v>
       </c>
       <c r="C146" t="n">
-        <v>93.27999877929688</v>
+        <v>92.83999633789062</v>
       </c>
       <c r="D146" t="n">
-        <v>91.80000305175781</v>
+        <v>91.30000305175781</v>
       </c>
       <c r="E146" t="n">
-        <v>92.44000244140625</v>
+        <v>91.37000274658203</v>
       </c>
       <c r="F146" t="n">
-        <v>32553200</v>
+        <v>29707400</v>
       </c>
       <c r="G146" t="n">
         <v>0</v>
@@ -4239,22 +4239,22 @@
     </row>
     <row r="147">
       <c r="A147" s="1" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B147" t="n">
-        <v>92.05000305175781</v>
+        <v>91.5</v>
       </c>
       <c r="C147" t="n">
-        <v>92.83999633789062</v>
+        <v>92.33999633789062</v>
       </c>
       <c r="D147" t="n">
-        <v>91.30000305175781</v>
+        <v>90.01999664306641</v>
       </c>
       <c r="E147" t="n">
-        <v>91.37000274658203</v>
+        <v>92.26999664306641</v>
       </c>
       <c r="F147" t="n">
-        <v>29707400</v>
+        <v>33418100</v>
       </c>
       <c r="G147" t="n">
         <v>0</v>
@@ -4265,22 +4265,22 @@
     </row>
     <row r="148">
       <c r="A148" s="1" t="n">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="B148" t="n">
-        <v>91.5</v>
+        <v>91.23000335693359</v>
       </c>
       <c r="C148" t="n">
-        <v>92.33999633789062</v>
+        <v>92.86000061035156</v>
       </c>
       <c r="D148" t="n">
-        <v>90.01999664306641</v>
+        <v>90.86000061035156</v>
       </c>
       <c r="E148" t="n">
-        <v>92.26999664306641</v>
+        <v>92.12000274658203</v>
       </c>
       <c r="F148" t="n">
-        <v>33418100</v>
+        <v>26122100</v>
       </c>
       <c r="G148" t="n">
         <v>0</v>
@@ -4291,22 +4291,22 @@
     </row>
     <row r="149">
       <c r="A149" s="1" t="n">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="B149" t="n">
-        <v>91.23000335693359</v>
+        <v>91.34999847412109</v>
       </c>
       <c r="C149" t="n">
-        <v>92.86000061035156</v>
+        <v>94.22000122070312</v>
       </c>
       <c r="D149" t="n">
-        <v>90.86000061035156</v>
+        <v>90.76999664306641</v>
       </c>
       <c r="E149" t="n">
-        <v>92.12000274658203</v>
+        <v>93.61000061035156</v>
       </c>
       <c r="F149" t="n">
-        <v>26122100</v>
+        <v>40923000</v>
       </c>
       <c r="G149" t="n">
         <v>0</v>
@@ -4317,22 +4317,22 @@
     </row>
     <row r="150">
       <c r="A150" s="1" t="n">
-        <v>46142</v>
+        <v>46143</v>
       </c>
       <c r="B150" t="n">
-        <v>91.34999847412109</v>
+        <v>94.41999816894531</v>
       </c>
       <c r="C150" t="n">
-        <v>94.22000122070312</v>
+        <v>94.69999694824219</v>
       </c>
       <c r="D150" t="n">
-        <v>90.76999664306641</v>
+        <v>91.90000152587891</v>
       </c>
       <c r="E150" t="n">
-        <v>93.61000061035156</v>
+        <v>92.05999755859375</v>
       </c>
       <c r="F150" t="n">
-        <v>40923000</v>
+        <v>30406900</v>
       </c>
       <c r="G150" t="n">
         <v>0</v>
@@ -4343,22 +4343,22 @@
     </row>
     <row r="151">
       <c r="A151" s="1" t="n">
-        <v>46143</v>
+        <v>46146</v>
       </c>
       <c r="B151" t="n">
-        <v>94.41999816894531</v>
+        <v>92.09999847412109</v>
       </c>
       <c r="C151" t="n">
-        <v>94.69999694824219</v>
+        <v>92.33000183105469</v>
       </c>
       <c r="D151" t="n">
-        <v>91.90000152587891</v>
+        <v>90.88999938964844</v>
       </c>
       <c r="E151" t="n">
-        <v>92.05999755859375</v>
+        <v>91.01999664306641</v>
       </c>
       <c r="F151" t="n">
-        <v>30406900</v>
+        <v>25928800</v>
       </c>
       <c r="G151" t="n">
         <v>0</v>
@@ -4369,22 +4369,22 @@
     </row>
     <row r="152">
       <c r="A152" s="1" t="n">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="B152" t="n">
-        <v>92.09999847412109</v>
+        <v>91.18000030517578</v>
       </c>
       <c r="C152" t="n">
-        <v>92.33000183105469</v>
+        <v>91.27999877929688</v>
       </c>
       <c r="D152" t="n">
-        <v>90.88999938964844</v>
+        <v>87.56999969482422</v>
       </c>
       <c r="E152" t="n">
-        <v>91.01999664306641</v>
+        <v>87.88999938964844</v>
       </c>
       <c r="F152" t="n">
-        <v>25928800</v>
+        <v>51961300</v>
       </c>
       <c r="G152" t="n">
         <v>0</v>
@@ -4395,22 +4395,22 @@
     </row>
     <row r="153">
       <c r="A153" s="1" t="n">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="B153" t="n">
-        <v>91.18000030517578</v>
+        <v>87.15000152587891</v>
       </c>
       <c r="C153" t="n">
-        <v>91.27999877929688</v>
+        <v>88.55000305175781</v>
       </c>
       <c r="D153" t="n">
-        <v>87.56999969482422</v>
+        <v>86.72000122070312</v>
       </c>
       <c r="E153" t="n">
-        <v>87.88999938964844</v>
+        <v>88.26999664306641</v>
       </c>
       <c r="F153" t="n">
-        <v>51961300</v>
+        <v>41932400</v>
       </c>
       <c r="G153" t="n">
         <v>0</v>
@@ -4421,22 +4421,22 @@
     </row>
     <row r="154">
       <c r="A154" s="1" t="n">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="B154" t="n">
-        <v>87.15000152587891</v>
+        <v>88.19999694824219</v>
       </c>
       <c r="C154" t="n">
-        <v>88.55000305175781</v>
+        <v>89.40000152587891</v>
       </c>
       <c r="D154" t="n">
-        <v>86.72000122070312</v>
+        <v>88.12999725341797</v>
       </c>
       <c r="E154" t="n">
-        <v>88.26999664306641</v>
+        <v>88.25</v>
       </c>
       <c r="F154" t="n">
-        <v>41932400</v>
+        <v>30627600</v>
       </c>
       <c r="G154" t="n">
         <v>0</v>
@@ -4447,22 +4447,22 @@
     </row>
     <row r="155">
       <c r="A155" s="1" t="n">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="B155" t="n">
-        <v>88.19999694824219</v>
+        <v>87.70999908447266</v>
       </c>
       <c r="C155" t="n">
-        <v>89.40000152587891</v>
+        <v>88.04000091552734</v>
       </c>
       <c r="D155" t="n">
-        <v>88.12999725341797</v>
+        <v>87.20999908447266</v>
       </c>
       <c r="E155" t="n">
-        <v>88.25</v>
+        <v>87.48999786376953</v>
       </c>
       <c r="F155" t="n">
-        <v>30627600</v>
+        <v>36215100</v>
       </c>
       <c r="G155" t="n">
         <v>0</v>
@@ -4473,22 +4473,22 @@
     </row>
     <row r="156">
       <c r="A156" s="1" t="n">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="B156" t="n">
-        <v>87.70999908447266</v>
+        <v>86.52999877929688</v>
       </c>
       <c r="C156" t="n">
-        <v>88.04000091552734</v>
+        <v>87.33999633789062</v>
       </c>
       <c r="D156" t="n">
-        <v>87.20999908447266</v>
+        <v>85.09999847412109</v>
       </c>
       <c r="E156" t="n">
-        <v>87.48999786376953</v>
+        <v>85.44999694824219</v>
       </c>
       <c r="F156" t="n">
-        <v>36215100</v>
+        <v>40556500</v>
       </c>
       <c r="G156" t="n">
         <v>0</v>
@@ -4499,22 +4499,22 @@
     </row>
     <row r="157">
       <c r="A157" s="1" t="n">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="B157" t="n">
-        <v>86.52999877929688</v>
+        <v>85.91000366210938</v>
       </c>
       <c r="C157" t="n">
-        <v>87.33999633789062</v>
+        <v>89.16999816894531</v>
       </c>
       <c r="D157" t="n">
-        <v>85.09999847412109</v>
+        <v>85.80999755859375</v>
       </c>
       <c r="E157" t="n">
-        <v>85.44999694824219</v>
+        <v>87.66000366210938</v>
       </c>
       <c r="F157" t="n">
-        <v>40556500</v>
+        <v>43556600</v>
       </c>
       <c r="G157" t="n">
         <v>0</v>
@@ -4525,22 +4525,22 @@
     </row>
     <row r="158">
       <c r="A158" s="1" t="n">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="B158" t="n">
-        <v>85.91000366210938</v>
+        <v>86.56999969482422</v>
       </c>
       <c r="C158" t="n">
-        <v>89.16999816894531</v>
+        <v>88.62000274658203</v>
       </c>
       <c r="D158" t="n">
-        <v>85.80999755859375</v>
+        <v>86.27999877929688</v>
       </c>
       <c r="E158" t="n">
-        <v>87.66000366210938</v>
+        <v>87.55999755859375</v>
       </c>
       <c r="F158" t="n">
-        <v>43556600</v>
+        <v>30823500</v>
       </c>
       <c r="G158" t="n">
         <v>0</v>
@@ -4551,22 +4551,22 @@
     </row>
     <row r="159">
       <c r="A159" s="1" t="n">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="B159" t="n">
-        <v>86.56999969482422</v>
+        <v>87.62000274658203</v>
       </c>
       <c r="C159" t="n">
-        <v>88.62000274658203</v>
+        <v>88.5</v>
       </c>
       <c r="D159" t="n">
-        <v>86.27999877929688</v>
+        <v>86.65000152587891</v>
       </c>
       <c r="E159" t="n">
-        <v>87.55999755859375</v>
+        <v>86.94000244140625</v>
       </c>
       <c r="F159" t="n">
-        <v>30823500</v>
+        <v>29408300</v>
       </c>
       <c r="G159" t="n">
         <v>0</v>
@@ -4577,22 +4577,22 @@
     </row>
     <row r="160">
       <c r="A160" s="1" t="n">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="B160" t="n">
-        <v>87.62000274658203</v>
+        <v>87.69000244140625</v>
       </c>
       <c r="C160" t="n">
-        <v>88.5</v>
+        <v>89.48999786376953</v>
       </c>
       <c r="D160" t="n">
-        <v>86.65000152587891</v>
+        <v>86.69000244140625</v>
       </c>
       <c r="E160" t="n">
-        <v>86.94000244140625</v>
+        <v>87.01999664306641</v>
       </c>
       <c r="F160" t="n">
-        <v>29408300</v>
+        <v>32335700</v>
       </c>
       <c r="G160" t="n">
         <v>0</v>
@@ -4603,22 +4603,22 @@
     </row>
     <row r="161">
       <c r="A161" s="1" t="n">
-        <v>46157</v>
+        <v>46160</v>
       </c>
       <c r="B161" t="n">
-        <v>87.69000244140625</v>
+        <v>86.5</v>
       </c>
       <c r="C161" t="n">
-        <v>89.48999786376953</v>
+        <v>89.81999969482422</v>
       </c>
       <c r="D161" t="n">
-        <v>86.69000244140625</v>
+        <v>86.33000183105469</v>
       </c>
       <c r="E161" t="n">
-        <v>87.01999664306641</v>
+        <v>89.65000152587891</v>
       </c>
       <c r="F161" t="n">
-        <v>32335700</v>
+        <v>35800500</v>
       </c>
       <c r="G161" t="n">
         <v>0</v>
@@ -4629,22 +4629,22 @@
     </row>
     <row r="162">
       <c r="A162" s="1" t="n">
-        <v>46160</v>
+        <v>46161</v>
       </c>
       <c r="B162" t="n">
-        <v>86.5</v>
+        <v>90.13999938964844</v>
       </c>
       <c r="C162" t="n">
-        <v>89.81999969482422</v>
+        <v>91.48000335693359</v>
       </c>
       <c r="D162" t="n">
-        <v>86.33000183105469</v>
+        <v>88.69000244140625</v>
       </c>
       <c r="E162" t="n">
-        <v>89.65000152587891</v>
+        <v>89.33000183105469</v>
       </c>
       <c r="F162" t="n">
-        <v>35800500</v>
+        <v>34545700</v>
       </c>
       <c r="G162" t="n">
         <v>0</v>
@@ -4655,22 +4655,22 @@
     </row>
     <row r="163">
       <c r="A163" s="1" t="n">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="B163" t="n">
-        <v>90.13999938964844</v>
+        <v>88.51999664306641</v>
       </c>
       <c r="C163" t="n">
-        <v>91.48000335693359</v>
+        <v>88.55000305175781</v>
       </c>
       <c r="D163" t="n">
-        <v>88.69000244140625</v>
+        <v>87.5</v>
       </c>
       <c r="E163" t="n">
-        <v>89.33000183105469</v>
+        <v>88.08999633789062</v>
       </c>
       <c r="F163" t="n">
-        <v>34545700</v>
+        <v>23463400</v>
       </c>
       <c r="G163" t="n">
         <v>0</v>
@@ -4681,22 +4681,22 @@
     </row>
     <row r="164">
       <c r="A164" s="1" t="n">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="B164" t="n">
-        <v>88.51999664306641</v>
+        <v>88.02999877929688</v>
       </c>
       <c r="C164" t="n">
-        <v>88.55000305175781</v>
+        <v>90.37000274658203</v>
       </c>
       <c r="D164" t="n">
-        <v>87.5</v>
+        <v>87.51999664306641</v>
       </c>
       <c r="E164" t="n">
-        <v>88.08999633789062</v>
+        <v>89.30000305175781</v>
       </c>
       <c r="F164" t="n">
-        <v>23463400</v>
+        <v>28613900</v>
       </c>
       <c r="G164" t="n">
         <v>0</v>
@@ -4707,22 +4707,22 @@
     </row>
     <row r="165">
       <c r="A165" s="1" t="n">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="B165" t="n">
-        <v>88.02999877929688</v>
+        <v>89.09999847412109</v>
       </c>
       <c r="C165" t="n">
-        <v>90.37000274658203</v>
+        <v>89.97000122070312</v>
       </c>
       <c r="D165" t="n">
-        <v>87.51999664306641</v>
+        <v>88.16999816894531</v>
       </c>
       <c r="E165" t="n">
-        <v>89.30000305175781</v>
+        <v>88.59999847412109</v>
       </c>
       <c r="F165" t="n">
-        <v>28613900</v>
+        <v>23847200</v>
       </c>
       <c r="G165" t="n">
         <v>0</v>
@@ -4733,22 +4733,22 @@
     </row>
     <row r="166">
       <c r="A166" s="1" t="n">
-        <v>46164</v>
+        <v>46168</v>
       </c>
       <c r="B166" t="n">
-        <v>89.09999847412109</v>
+        <v>88.40000152587891</v>
       </c>
       <c r="C166" t="n">
-        <v>89.97000122070312</v>
+        <v>88.73000335693359</v>
       </c>
       <c r="D166" t="n">
-        <v>88.16999816894531</v>
+        <v>87.25</v>
       </c>
       <c r="E166" t="n">
-        <v>88.59999847412109</v>
+        <v>87.68000030517578</v>
       </c>
       <c r="F166" t="n">
-        <v>23847200</v>
+        <v>24014500</v>
       </c>
       <c r="G166" t="n">
         <v>0</v>
@@ -4759,22 +4759,22 @@
     </row>
     <row r="167">
       <c r="A167" s="1" t="n">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="B167" t="n">
-        <v>88.40000152587891</v>
+        <v>87.05000305175781</v>
       </c>
       <c r="C167" t="n">
-        <v>88.73000335693359</v>
+        <v>88.5</v>
       </c>
       <c r="D167" t="n">
-        <v>87.25</v>
+        <v>86.81999969482422</v>
       </c>
       <c r="E167" t="n">
-        <v>87.68000030517578</v>
+        <v>87.34999847412109</v>
       </c>
       <c r="F167" t="n">
-        <v>24014500</v>
+        <v>22569500</v>
       </c>
       <c r="G167" t="n">
         <v>0</v>
@@ -4785,22 +4785,22 @@
     </row>
     <row r="168">
       <c r="A168" s="1" t="n">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="B168" t="n">
-        <v>87.05000305175781</v>
+        <v>86.90000152587891</v>
       </c>
       <c r="C168" t="n">
-        <v>88.5</v>
+        <v>87.04000091552734</v>
       </c>
       <c r="D168" t="n">
-        <v>86.81999969482422</v>
+        <v>85.58999633789062</v>
       </c>
       <c r="E168" t="n">
-        <v>87.34999847412109</v>
+        <v>86.36000061035156</v>
       </c>
       <c r="F168" t="n">
-        <v>22569500</v>
+        <v>38803800</v>
       </c>
       <c r="G168" t="n">
         <v>0</v>
@@ -4811,22 +4811,22 @@
     </row>
     <row r="169">
       <c r="A169" s="1" t="n">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="B169" t="n">
-        <v>86.90000152587891</v>
+        <v>86.19999694824219</v>
       </c>
       <c r="C169" t="n">
-        <v>87.04000091552734</v>
+        <v>86.66999816894531</v>
       </c>
       <c r="D169" t="n">
-        <v>85.58999633789062</v>
+        <v>85.66000366210938</v>
       </c>
       <c r="E169" t="n">
-        <v>86.36000061035156</v>
+        <v>86.01999664306641</v>
       </c>
       <c r="F169" t="n">
-        <v>38803800</v>
+        <v>39793600</v>
       </c>
       <c r="G169" t="n">
         <v>0</v>
@@ -4837,22 +4837,22 @@
     </row>
     <row r="170">
       <c r="A170" s="1" t="n">
-        <v>46171</v>
+        <v>46174</v>
       </c>
       <c r="B170" t="n">
-        <v>86.19999694824219</v>
+        <v>85.73000335693359</v>
       </c>
       <c r="C170" t="n">
-        <v>86.66999816894531</v>
+        <v>87.23000335693359</v>
       </c>
       <c r="D170" t="n">
-        <v>85.66000366210938</v>
+        <v>85.31999969482422</v>
       </c>
       <c r="E170" t="n">
-        <v>86.01999664306641</v>
+        <v>85.84999847412109</v>
       </c>
       <c r="F170" t="n">
-        <v>39793600</v>
+        <v>32747200</v>
       </c>
       <c r="G170" t="n">
         <v>0</v>
@@ -4863,22 +4863,22 @@
     </row>
     <row r="171">
       <c r="A171" s="1" t="n">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="B171" t="n">
-        <v>85.73000335693359</v>
+        <v>85.61000061035156</v>
       </c>
       <c r="C171" t="n">
-        <v>87.23000335693359</v>
+        <v>85.98000335693359</v>
       </c>
       <c r="D171" t="n">
-        <v>85.31999969482422</v>
+        <v>83.29000091552734</v>
       </c>
       <c r="E171" t="n">
-        <v>85.84999847412109</v>
+        <v>83.33000183105469</v>
       </c>
       <c r="F171" t="n">
-        <v>32747200</v>
+        <v>42947200</v>
       </c>
       <c r="G171" t="n">
         <v>0</v>
@@ -4889,22 +4889,22 @@
     </row>
     <row r="172">
       <c r="A172" s="1" t="n">
-        <v>46175</v>
+        <v>46176</v>
       </c>
       <c r="B172" t="n">
-        <v>85.61000061035156</v>
+        <v>82.91000366210938</v>
       </c>
       <c r="C172" t="n">
-        <v>85.98000335693359</v>
+        <v>83.30999755859375</v>
       </c>
       <c r="D172" t="n">
-        <v>83.29000091552734</v>
+        <v>81.09999847412109</v>
       </c>
       <c r="E172" t="n">
-        <v>83.33000183105469</v>
+        <v>81.51999664306641</v>
       </c>
       <c r="F172" t="n">
-        <v>42947200</v>
+        <v>36714700</v>
       </c>
       <c r="G172" t="n">
         <v>0</v>
@@ -4915,22 +4915,22 @@
     </row>
     <row r="173">
       <c r="A173" s="1" t="n">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="B173" t="n">
-        <v>82.91000366210938</v>
+        <v>83.19000244140625</v>
       </c>
       <c r="C173" t="n">
-        <v>83.30999755859375</v>
+        <v>83.69999694824219</v>
       </c>
       <c r="D173" t="n">
-        <v>81.09999847412109</v>
+        <v>81.37000274658203</v>
       </c>
       <c r="E173" t="n">
-        <v>81.51999664306641</v>
+        <v>81.55999755859375</v>
       </c>
       <c r="F173" t="n">
-        <v>36714700</v>
+        <v>39338800</v>
       </c>
       <c r="G173" t="n">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="174">
       <c r="A174" s="1" t="n">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="B174" t="n">
-        <v>83.19000244140625</v>
+        <v>82.33000183105469</v>
       </c>
       <c r="C174" t="n">
-        <v>83.69999694824219</v>
+        <v>82.75</v>
       </c>
       <c r="D174" t="n">
-        <v>81.37000274658203</v>
+        <v>81</v>
       </c>
       <c r="E174" t="n">
-        <v>81.55999755859375</v>
+        <v>82.18000030517578</v>
       </c>
       <c r="F174" t="n">
-        <v>39338800</v>
+        <v>43474100</v>
       </c>
       <c r="G174" t="n">
         <v>0</v>
@@ -4967,22 +4967,22 @@
     </row>
     <row r="175">
       <c r="A175" s="1" t="n">
-        <v>46178</v>
+        <v>46181</v>
       </c>
       <c r="B175" t="n">
-        <v>82.33000183105469</v>
+        <v>81.66000366210938</v>
       </c>
       <c r="C175" t="n">
-        <v>82.75</v>
+        <v>83.08000183105469</v>
       </c>
       <c r="D175" t="n">
-        <v>81</v>
+        <v>81.33999633789062</v>
       </c>
       <c r="E175" t="n">
-        <v>82.18000030517578</v>
+        <v>82.63999938964844</v>
       </c>
       <c r="F175" t="n">
-        <v>43474100</v>
+        <v>33056700</v>
       </c>
       <c r="G175" t="n">
         <v>0</v>
@@ -4993,22 +4993,22 @@
     </row>
     <row r="176">
       <c r="A176" s="1" t="n">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="B176" t="n">
-        <v>81.66000366210938</v>
+        <v>82.12999725341797</v>
       </c>
       <c r="C176" t="n">
-        <v>83.08000183105469</v>
+        <v>82.33999633789062</v>
       </c>
       <c r="D176" t="n">
         <v>81.33999633789062</v>
       </c>
       <c r="E176" t="n">
-        <v>82.63999938964844</v>
+        <v>81.41000366210938</v>
       </c>
       <c r="F176" t="n">
-        <v>33056700</v>
+        <v>34787200</v>
       </c>
       <c r="G176" t="n">
         <v>0</v>
@@ -5019,22 +5019,22 @@
     </row>
     <row r="177">
       <c r="A177" s="1" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="B177" t="n">
-        <v>82.12999725341797</v>
+        <v>81.70999908447266</v>
       </c>
       <c r="C177" t="n">
-        <v>82.33999633789062</v>
+        <v>82.75</v>
       </c>
       <c r="D177" t="n">
-        <v>81.33999633789062</v>
+        <v>80.98000335693359</v>
       </c>
       <c r="E177" t="n">
-        <v>81.41000366210938</v>
+        <v>82</v>
       </c>
       <c r="F177" t="n">
-        <v>34787200</v>
+        <v>36304600</v>
       </c>
       <c r="G177" t="n">
         <v>0</v>
@@ -5045,22 +5045,22 @@
     </row>
     <row r="178">
       <c r="A178" s="1" t="n">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="B178" t="n">
-        <v>81.70999908447266</v>
+        <v>81.87000274658203</v>
       </c>
       <c r="C178" t="n">
-        <v>82.75</v>
+        <v>82.09999847412109</v>
       </c>
       <c r="D178" t="n">
-        <v>80.98000335693359</v>
+        <v>80.08999633789062</v>
       </c>
       <c r="E178" t="n">
-        <v>82</v>
+        <v>81.26999664306641</v>
       </c>
       <c r="F178" t="n">
-        <v>36304600</v>
+        <v>33417600</v>
       </c>
       <c r="G178" t="n">
         <v>0</v>
@@ -5071,22 +5071,22 @@
     </row>
     <row r="179">
       <c r="A179" s="1" t="n">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="B179" t="n">
-        <v>81.87000274658203</v>
+        <v>81.58000183105469</v>
       </c>
       <c r="C179" t="n">
-        <v>82.09999847412109</v>
+        <v>82</v>
       </c>
       <c r="D179" t="n">
-        <v>80.08999633789062</v>
+        <v>79.27999877929688</v>
       </c>
       <c r="E179" t="n">
-        <v>81.26999664306641</v>
+        <v>80.33999633789062</v>
       </c>
       <c r="F179" t="n">
-        <v>33417600</v>
+        <v>35309700</v>
       </c>
       <c r="G179" t="n">
         <v>0</v>
@@ -5097,22 +5097,22 @@
     </row>
     <row r="180">
       <c r="A180" s="1" t="n">
-        <v>46185</v>
+        <v>46188</v>
       </c>
       <c r="B180" t="n">
-        <v>81.58000183105469</v>
+        <v>80.62000274658203</v>
       </c>
       <c r="C180" t="n">
-        <v>82</v>
+        <v>81.70999908447266</v>
       </c>
       <c r="D180" t="n">
-        <v>79.27999877929688</v>
+        <v>80.45999908447266</v>
       </c>
       <c r="E180" t="n">
-        <v>80.33999633789062</v>
+        <v>81.66999816894531</v>
       </c>
       <c r="F180" t="n">
-        <v>35309700</v>
+        <v>36430800</v>
       </c>
       <c r="G180" t="n">
         <v>0</v>
@@ -5123,22 +5123,22 @@
     </row>
     <row r="181">
       <c r="A181" s="1" t="n">
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="B181" t="n">
-        <v>80.62000274658203</v>
+        <v>81.90000152587891</v>
       </c>
       <c r="C181" t="n">
-        <v>81.70999908447266</v>
+        <v>81.93000030517578</v>
       </c>
       <c r="D181" t="n">
-        <v>80.45999908447266</v>
+        <v>77.70999908447266</v>
       </c>
       <c r="E181" t="n">
-        <v>81.66999816894531</v>
+        <v>78.72000122070312</v>
       </c>
       <c r="F181" t="n">
-        <v>36430800</v>
+        <v>65054000</v>
       </c>
       <c r="G181" t="n">
         <v>0</v>
@@ -5149,22 +5149,22 @@
     </row>
     <row r="182">
       <c r="A182" s="1" t="n">
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="B182" t="n">
-        <v>81.90000152587891</v>
+        <v>78.09999847412109</v>
       </c>
       <c r="C182" t="n">
-        <v>81.93000030517578</v>
+        <v>78.44999694824219</v>
       </c>
       <c r="D182" t="n">
-        <v>77.70999908447266</v>
+        <v>76.76000213623047</v>
       </c>
       <c r="E182" t="n">
-        <v>78.72000122070312</v>
+        <v>76.95999908447266</v>
       </c>
       <c r="F182" t="n">
-        <v>65054000</v>
+        <v>50338800</v>
       </c>
       <c r="G182" t="n">
         <v>0</v>
@@ -5175,22 +5175,22 @@
     </row>
     <row r="183">
       <c r="A183" s="1" t="n">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="B183" t="n">
-        <v>78.09999847412109</v>
+        <v>76.93000030517578</v>
       </c>
       <c r="C183" t="n">
-        <v>78.44999694824219</v>
+        <v>78.23999786376953</v>
       </c>
       <c r="D183" t="n">
-        <v>76.76000213623047</v>
+        <v>76.12000274658203</v>
       </c>
       <c r="E183" t="n">
-        <v>76.95999908447266</v>
+        <v>77.37999725341797</v>
       </c>
       <c r="F183" t="n">
-        <v>50338800</v>
+        <v>91920400</v>
       </c>
       <c r="G183" t="n">
         <v>0</v>
@@ -5201,22 +5201,22 @@
     </row>
     <row r="184">
       <c r="A184" s="1" t="n">
-        <v>46191</v>
+        <v>46195</v>
       </c>
       <c r="B184" t="n">
-        <v>76.93000030517578</v>
+        <v>76.13999938964844</v>
       </c>
       <c r="C184" t="n">
-        <v>78.23999786376953</v>
+        <v>77.08999633789062</v>
       </c>
       <c r="D184" t="n">
-        <v>76.12000274658203</v>
+        <v>71.80999755859375</v>
       </c>
       <c r="E184" t="n">
-        <v>77.37999725341797</v>
+        <v>72.87999725341797</v>
       </c>
       <c r="F184" t="n">
-        <v>91920400</v>
+        <v>82203300</v>
       </c>
       <c r="G184" t="n">
         <v>0</v>
@@ -5227,22 +5227,22 @@
     </row>
     <row r="185">
       <c r="A185" s="1" t="n">
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="B185" t="n">
-        <v>76.13999938964844</v>
+        <v>73.26000213623047</v>
       </c>
       <c r="C185" t="n">
-        <v>77.08999633789062</v>
+        <v>73.95999908447266</v>
       </c>
       <c r="D185" t="n">
-        <v>71.80999755859375</v>
+        <v>72.62999725341797</v>
       </c>
       <c r="E185" t="n">
-        <v>72.87999725341797</v>
+        <v>72.81999969482422</v>
       </c>
       <c r="F185" t="n">
-        <v>82203300</v>
+        <v>50806800</v>
       </c>
       <c r="G185" t="n">
         <v>0</v>
@@ -5253,22 +5253,22 @@
     </row>
     <row r="186">
       <c r="A186" s="1" t="n">
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="B186" t="n">
-        <v>73.26000213623047</v>
+        <v>72.69000244140625</v>
       </c>
       <c r="C186" t="n">
-        <v>73.95999908447266</v>
+        <v>73.44999694824219</v>
       </c>
       <c r="D186" t="n">
-        <v>72.62999725341797</v>
+        <v>71.62999725341797</v>
       </c>
       <c r="E186" t="n">
-        <v>72.81999969482422</v>
+        <v>71.83999633789062</v>
       </c>
       <c r="F186" t="n">
-        <v>50806800</v>
+        <v>48001500</v>
       </c>
       <c r="G186" t="n">
         <v>0</v>
@@ -5279,22 +5279,22 @@
     </row>
     <row r="187">
       <c r="A187" s="1" t="n">
-        <v>46197</v>
+        <v>46198</v>
       </c>
       <c r="B187" t="n">
-        <v>72.69000244140625</v>
+        <v>71.33000183105469</v>
       </c>
       <c r="C187" t="n">
-        <v>73.44999694824219</v>
+        <v>72.94000244140625</v>
       </c>
       <c r="D187" t="n">
-        <v>71.62999725341797</v>
+        <v>70.86000061035156</v>
       </c>
       <c r="E187" t="n">
-        <v>71.83999633789062</v>
+        <v>70.90000152587891</v>
       </c>
       <c r="F187" t="n">
-        <v>48001500</v>
+        <v>44446900</v>
       </c>
       <c r="G187" t="n">
         <v>0</v>
@@ -5305,22 +5305,22 @@
     </row>
     <row r="188">
       <c r="A188" s="1" t="n">
-        <v>46198</v>
+        <v>46199</v>
       </c>
       <c r="B188" t="n">
-        <v>71.33000183105469</v>
+        <v>71.69000244140625</v>
       </c>
       <c r="C188" t="n">
-        <v>72.94000244140625</v>
+        <v>75.19999694824219</v>
       </c>
       <c r="D188" t="n">
-        <v>70.86000061035156</v>
+        <v>71.52999877929688</v>
       </c>
       <c r="E188" t="n">
-        <v>70.90000152587891</v>
+        <v>73.80999755859375</v>
       </c>
       <c r="F188" t="n">
-        <v>44446900</v>
+        <v>74990300</v>
       </c>
       <c r="G188" t="n">
         <v>0</v>
@@ -5331,22 +5331,22 @@
     </row>
     <row r="189">
       <c r="A189" s="1" t="n">
-        <v>46199</v>
+        <v>46202</v>
       </c>
       <c r="B189" t="n">
-        <v>71.69000244140625</v>
+        <v>74.62000274658203</v>
       </c>
       <c r="C189" t="n">
-        <v>75.19999694824219</v>
+        <v>76.06999969482422</v>
       </c>
       <c r="D189" t="n">
-        <v>71.52999877929688</v>
+        <v>73.73000335693359</v>
       </c>
       <c r="E189" t="n">
-        <v>73.80999755859375</v>
+        <v>73.77999877929688</v>
       </c>
       <c r="F189" t="n">
-        <v>74990300</v>
+        <v>42429600</v>
       </c>
       <c r="G189" t="n">
         <v>0</v>
@@ -5357,22 +5357,22 @@
     </row>
     <row r="190">
       <c r="A190" s="1" t="n">
-        <v>46202</v>
+        <v>46203</v>
       </c>
       <c r="B190" t="n">
-        <v>74.62000274658203</v>
+        <v>73.58999633789062</v>
       </c>
       <c r="C190" t="n">
-        <v>76.06999969482422</v>
+        <v>73.75</v>
       </c>
       <c r="D190" t="n">
-        <v>73.73000335693359</v>
+        <v>71</v>
       </c>
       <c r="E190" t="n">
-        <v>73.77999877929688</v>
+        <v>71.40000152587891</v>
       </c>
       <c r="F190" t="n">
-        <v>42429600</v>
+        <v>49240900</v>
       </c>
       <c r="G190" t="n">
         <v>0</v>
@@ -5383,22 +5383,22 @@
     </row>
     <row r="191">
       <c r="A191" s="1" t="n">
-        <v>46203</v>
+        <v>46204</v>
       </c>
       <c r="B191" t="n">
-        <v>73.58999633789062</v>
+        <v>72.58999633789062</v>
       </c>
       <c r="C191" t="n">
-        <v>73.75</v>
+        <v>74.36000061035156</v>
       </c>
       <c r="D191" t="n">
-        <v>71</v>
+        <v>72.33000183105469</v>
       </c>
       <c r="E191" t="n">
-        <v>71.40000152587891</v>
+        <v>74.19000244140625</v>
       </c>
       <c r="F191" t="n">
-        <v>49240900</v>
+        <v>43841800</v>
       </c>
       <c r="G191" t="n">
         <v>0</v>
@@ -5409,22 +5409,22 @@
     </row>
     <row r="192">
       <c r="A192" s="1" t="n">
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="B192" t="n">
-        <v>72.58999633789062</v>
+        <v>75.08999633789062</v>
       </c>
       <c r="C192" t="n">
-        <v>74.36000061035156</v>
+        <v>78.44000244140625</v>
       </c>
       <c r="D192" t="n">
-        <v>72.33000183105469</v>
+        <v>74.91000366210938</v>
       </c>
       <c r="E192" t="n">
-        <v>74.19000244140625</v>
+        <v>77.65000152587891</v>
       </c>
       <c r="F192" t="n">
-        <v>43841800</v>
+        <v>55456500</v>
       </c>
       <c r="G192" t="n">
         <v>0</v>
@@ -5435,22 +5435,22 @@
     </row>
     <row r="193">
       <c r="A193" s="1" t="n">
-        <v>46205</v>
+        <v>46209</v>
       </c>
       <c r="B193" t="n">
-        <v>75.08999633789062</v>
+        <v>77.08000183105469</v>
       </c>
       <c r="C193" t="n">
-        <v>78.44000244140625</v>
+        <v>77.83999633789062</v>
       </c>
       <c r="D193" t="n">
-        <v>74.91000366210938</v>
+        <v>75.70999908447266</v>
       </c>
       <c r="E193" t="n">
-        <v>77.65000152587891</v>
+        <v>76.01999664306641</v>
       </c>
       <c r="F193" t="n">
-        <v>55456500</v>
+        <v>45056600</v>
       </c>
       <c r="G193" t="n">
         <v>0</v>
@@ -5461,22 +5461,22 @@
     </row>
     <row r="194">
       <c r="A194" s="1" t="n">
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="B194" t="n">
-        <v>77.08000183105469</v>
+        <v>77.87999725341797</v>
       </c>
       <c r="C194" t="n">
-        <v>77.83999633789062</v>
+        <v>78.19000244140625</v>
       </c>
       <c r="D194" t="n">
-        <v>75.70999908447266</v>
+        <v>76.09999847412109</v>
       </c>
       <c r="E194" t="n">
-        <v>76.01999664306641</v>
+        <v>76.18000030517578</v>
       </c>
       <c r="F194" t="n">
-        <v>45056600</v>
+        <v>33257300</v>
       </c>
       <c r="G194" t="n">
         <v>0</v>
@@ -5487,22 +5487,22 @@
     </row>
     <row r="195">
       <c r="A195" s="1" t="n">
-        <v>46210</v>
+        <v>46211</v>
       </c>
       <c r="B195" t="n">
-        <v>77.87999725341797</v>
+        <v>76.26999664306641</v>
       </c>
       <c r="C195" t="n">
-        <v>78.19000244140625</v>
+        <v>76.63999938964844</v>
       </c>
       <c r="D195" t="n">
-        <v>76.09999847412109</v>
+        <v>74.88999938964844</v>
       </c>
       <c r="E195" t="n">
-        <v>76.18000030517578</v>
+        <v>75.58999633789062</v>
       </c>
       <c r="F195" t="n">
-        <v>33257300</v>
+        <v>34373500</v>
       </c>
       <c r="G195" t="n">
         <v>0</v>
@@ -5513,22 +5513,22 @@
     </row>
     <row r="196">
       <c r="A196" s="1" t="n">
-        <v>46211</v>
+        <v>46212</v>
       </c>
       <c r="B196" t="n">
-        <v>76.26999664306641</v>
+        <v>74.30000305175781</v>
       </c>
       <c r="C196" t="n">
-        <v>76.63999938964844</v>
+        <v>75.55000305175781</v>
       </c>
       <c r="D196" t="n">
-        <v>74.88999938964844</v>
+        <v>74.01999664306641</v>
       </c>
       <c r="E196" t="n">
-        <v>75.58999633789062</v>
+        <v>75.47000122070312</v>
       </c>
       <c r="F196" t="n">
-        <v>34373500</v>
+        <v>36305700</v>
       </c>
       <c r="G196" t="n">
         <v>0</v>
@@ -5539,22 +5539,22 @@
     </row>
     <row r="197">
       <c r="A197" s="1" t="n">
-        <v>46212</v>
+        <v>46213</v>
       </c>
       <c r="B197" t="n">
-        <v>74.30000305175781</v>
+        <v>75.44000244140625</v>
       </c>
       <c r="C197" t="n">
-        <v>75.55000305175781</v>
+        <v>75.69999694824219</v>
       </c>
       <c r="D197" t="n">
-        <v>74.01999664306641</v>
+        <v>72.51000213623047</v>
       </c>
       <c r="E197" t="n">
-        <v>75.47000122070312</v>
+        <v>73.37000274658203</v>
       </c>
       <c r="F197" t="n">
-        <v>36305700</v>
+        <v>46713900</v>
       </c>
       <c r="G197" t="n">
         <v>0</v>
@@ -5565,22 +5565,22 @@
     </row>
     <row r="198">
       <c r="A198" s="1" t="n">
-        <v>46213</v>
+        <v>46216</v>
       </c>
       <c r="B198" t="n">
-        <v>75.44000244140625</v>
+        <v>73.90000152587891</v>
       </c>
       <c r="C198" t="n">
-        <v>75.69999694824219</v>
+        <v>75.44999694824219</v>
       </c>
       <c r="D198" t="n">
-        <v>72.51000213623047</v>
+        <v>73.70999908447266</v>
       </c>
       <c r="E198" t="n">
-        <v>73.37000274658203</v>
+        <v>73.83000183105469</v>
       </c>
       <c r="F198" t="n">
-        <v>46713900</v>
+        <v>35101800</v>
       </c>
       <c r="G198" t="n">
         <v>0</v>
@@ -5591,22 +5591,22 @@
     </row>
     <row r="199">
       <c r="A199" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="B199" t="n">
-        <v>73.90000152587891</v>
+        <v>72.63999938964844</v>
       </c>
       <c r="C199" t="n">
-        <v>75.44999694824219</v>
+        <v>74.01000213623047</v>
       </c>
       <c r="D199" t="n">
-        <v>73.70999908447266</v>
+        <v>72.27999877929688</v>
       </c>
       <c r="E199" t="n">
-        <v>73.83000183105469</v>
+        <v>73.52999877929688</v>
       </c>
       <c r="F199" t="n">
-        <v>35101800</v>
+        <v>33312100</v>
       </c>
       <c r="G199" t="n">
         <v>0</v>
@@ -5617,22 +5617,22 @@
     </row>
     <row r="200">
       <c r="A200" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="B200" t="n">
-        <v>72.63999938964844</v>
+        <v>73.79000091552734</v>
       </c>
       <c r="C200" t="n">
-        <v>74.01000213623047</v>
+        <v>75.05999755859375</v>
       </c>
       <c r="D200" t="n">
-        <v>72.27999877929688</v>
+        <v>73.12999725341797</v>
       </c>
       <c r="E200" t="n">
-        <v>73.52999877929688</v>
+        <v>73.68000030517578</v>
       </c>
       <c r="F200" t="n">
-        <v>33312100</v>
+        <v>32854300</v>
       </c>
       <c r="G200" t="n">
         <v>0</v>
@@ -5643,22 +5643,22 @@
     </row>
     <row r="201">
       <c r="A201" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="B201" t="n">
-        <v>73.79000091552734</v>
+        <v>73.94999694824219</v>
       </c>
       <c r="C201" t="n">
-        <v>75.05999755859375</v>
+        <v>74.68000030517578</v>
       </c>
       <c r="D201" t="n">
-        <v>73.12999725341797</v>
+        <v>72.94000244140625</v>
       </c>
       <c r="E201" t="n">
-        <v>73.68000030517578</v>
+        <v>74.34999847412109</v>
       </c>
       <c r="F201" t="n">
-        <v>32854300</v>
+        <v>77505200</v>
       </c>
       <c r="G201" t="n">
         <v>0</v>
@@ -5669,22 +5669,22 @@
     </row>
     <row r="202">
       <c r="A202" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="B202" t="n">
-        <v>73.94999694824219</v>
+        <v>65.48000335693359</v>
       </c>
       <c r="C202" t="n">
-        <v>74.68000030517578</v>
+        <v>69.48999786376953</v>
       </c>
       <c r="D202" t="n">
-        <v>72.94000244140625</v>
+        <v>65.08000183105469</v>
       </c>
       <c r="E202" t="n">
-        <v>74.34999847412109</v>
+        <v>68.94999694824219</v>
       </c>
       <c r="F202" t="n">
-        <v>77505200</v>
+        <v>142029200</v>
       </c>
       <c r="G202" t="n">
         <v>0</v>
@@ -5695,22 +5695,22 @@
     </row>
     <row r="203">
       <c r="A203" s="1" t="n">
-        <v>46220</v>
+        <v>46223</v>
       </c>
       <c r="B203" t="n">
-        <v>65.48000335693359</v>
+        <v>68.31999969482422</v>
       </c>
       <c r="C203" t="n">
-        <v>69.48999786376953</v>
+        <v>68.37999725341797</v>
       </c>
       <c r="D203" t="n">
-        <v>65.08000183105469</v>
+        <v>66.69000244140625</v>
       </c>
       <c r="E203" t="n">
-        <v>68.94999694824219</v>
+        <v>67.59999847412109</v>
       </c>
       <c r="F203" t="n">
-        <v>142029200</v>
+        <v>60669100</v>
       </c>
       <c r="G203" t="n">
         <v>0</v>
@@ -5721,22 +5721,22 @@
     </row>
     <row r="204">
       <c r="A204" s="1" t="n">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="B204" t="n">
-        <v>68.31999969482422</v>
+        <v>67.41999816894531</v>
       </c>
       <c r="C204" t="n">
-        <v>68.37999725341797</v>
+        <v>68.75</v>
       </c>
       <c r="D204" t="n">
-        <v>66.69000244140625</v>
+        <v>66.73000335693359</v>
       </c>
       <c r="E204" t="n">
-        <v>67.59999847412109</v>
+        <v>68.66999816894531</v>
       </c>
       <c r="F204" t="n">
-        <v>60669100</v>
+        <v>56565800</v>
       </c>
       <c r="G204" t="n">
         <v>0</v>
@@ -5747,22 +5747,22 @@
     </row>
     <row r="205">
       <c r="A205" s="1" t="n">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="B205" t="n">
-        <v>67.41999816894531</v>
+        <v>69.37000274658203</v>
       </c>
       <c r="C205" t="n">
-        <v>68.75</v>
+        <v>70.56999969482422</v>
       </c>
       <c r="D205" t="n">
-        <v>66.73000335693359</v>
+        <v>68.34999847412109</v>
       </c>
       <c r="E205" t="n">
-        <v>68.66999816894531</v>
+        <v>68.52999877929688</v>
       </c>
       <c r="F205" t="n">
-        <v>56565800</v>
+        <v>44947300</v>
       </c>
       <c r="G205" t="n">
         <v>0</v>
@@ -5773,22 +5773,22 @@
     </row>
     <row r="206">
       <c r="A206" s="1" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="B206" t="n">
-        <v>69.37000274658203</v>
+        <v>68.56999969482422</v>
       </c>
       <c r="C206" t="n">
-        <v>70.56999969482422</v>
+        <v>69.36000061035156</v>
       </c>
       <c r="D206" t="n">
-        <v>68.34999847412109</v>
+        <v>67.66999816894531</v>
       </c>
       <c r="E206" t="n">
-        <v>68.52999877929688</v>
+        <v>68.88999938964844</v>
       </c>
       <c r="F206" t="n">
-        <v>44947300</v>
+        <v>45029100</v>
       </c>
       <c r="G206" t="n">
         <v>0</v>
@@ -5799,22 +5799,22 @@
     </row>
     <row r="207">
       <c r="A207" s="1" t="n">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="B207" t="n">
-        <v>68.56999969482422</v>
+        <v>69.29000091552734</v>
       </c>
       <c r="C207" t="n">
-        <v>69.36000061035156</v>
+        <v>70.68000030517578</v>
       </c>
       <c r="D207" t="n">
-        <v>67.66999816894531</v>
+        <v>67.97000122070312</v>
       </c>
       <c r="E207" t="n">
-        <v>68.88999938964844</v>
+        <v>70.08999633789062</v>
       </c>
       <c r="F207" t="n">
-        <v>45029100</v>
+        <v>37593500</v>
       </c>
       <c r="G207" t="n">
         <v>0</v>
@@ -5825,22 +5825,22 @@
     </row>
     <row r="208">
       <c r="A208" s="1" t="n">
-        <v>46227</v>
+        <v>46230</v>
       </c>
       <c r="B208" t="n">
-        <v>69.29000091552734</v>
+        <v>70.58999633789062</v>
       </c>
       <c r="C208" t="n">
-        <v>70.68000030517578</v>
+        <v>71.65000152587891</v>
       </c>
       <c r="D208" t="n">
-        <v>67.97000122070312</v>
+        <v>69.86000061035156</v>
       </c>
       <c r="E208" t="n">
-        <v>70.08999633789062</v>
+        <v>70.40000152587891</v>
       </c>
       <c r="F208" t="n">
-        <v>37593500</v>
+        <v>39090800</v>
       </c>
       <c r="G208" t="n">
         <v>0</v>
@@ -5851,22 +5851,22 @@
     </row>
     <row r="209">
       <c r="A209" s="1" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="B209" t="n">
-        <v>70.58999633789062</v>
+        <v>72.06999969482422</v>
       </c>
       <c r="C209" t="n">
-        <v>71.65000152587891</v>
+        <v>73.76000213623047</v>
       </c>
       <c r="D209" t="n">
-        <v>69.86000061035156</v>
+        <v>71.23000335693359</v>
       </c>
       <c r="E209" t="n">
-        <v>70.40000152587891</v>
+        <v>72.38999938964844</v>
       </c>
       <c r="F209" t="n">
-        <v>39090800</v>
+        <v>47160200</v>
       </c>
       <c r="G209" t="n">
         <v>0</v>
@@ -5877,22 +5877,22 @@
     </row>
     <row r="210">
       <c r="A210" s="1" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="B210" t="n">
-        <v>72.06999969482422</v>
+        <v>72.19000244140625</v>
       </c>
       <c r="C210" t="n">
-        <v>73.76000213623047</v>
+        <v>73.73999786376953</v>
       </c>
       <c r="D210" t="n">
-        <v>71.23000335693359</v>
+        <v>71.75</v>
       </c>
       <c r="E210" t="n">
-        <v>72.38999938964844</v>
+        <v>73.62999725341797</v>
       </c>
       <c r="F210" t="n">
-        <v>47160200</v>
+        <v>43737600</v>
       </c>
       <c r="G210" t="n">
         <v>0</v>
@@ -5903,22 +5903,22 @@
     </row>
     <row r="211">
       <c r="A211" s="1" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="B211" t="n">
-        <v>72.19000244140625</v>
+        <v>71.48000335693359</v>
       </c>
       <c r="C211" t="n">
-        <v>73.73999786376953</v>
+        <v>73.31999969482422</v>
       </c>
       <c r="D211" t="n">
-        <v>71.75</v>
+        <v>70.55000305175781</v>
       </c>
       <c r="E211" t="n">
-        <v>73.62999725341797</v>
+        <v>73.16999816894531</v>
       </c>
       <c r="F211" t="n">
-        <v>43737600</v>
+        <v>54261000</v>
       </c>
       <c r="G211" t="n">
         <v>0</v>
@@ -5929,22 +5929,22 @@
     </row>
     <row r="212">
       <c r="A212" s="1" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="B212" t="n">
-        <v>71.48000335693359</v>
+        <v>71.97000122070312</v>
       </c>
       <c r="C212" t="n">
-        <v>73.31999969482422</v>
+        <v>72.75</v>
       </c>
       <c r="D212" t="n">
-        <v>70.55000305175781</v>
+        <v>71.11000061035156</v>
       </c>
       <c r="E212" t="n">
-        <v>73.16999816894531</v>
+        <v>71.70999908447266</v>
       </c>
       <c r="F212" t="n">
-        <v>54261000</v>
+        <v>35847500</v>
       </c>
       <c r="G212" t="n">
         <v>0</v>
@@ -5955,22 +5955,22 @@
     </row>
     <row r="213">
       <c r="A213" s="1" t="n">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="B213" t="n">
-        <v>71.97000122070312</v>
+        <v>72.76999664306641</v>
       </c>
       <c r="C213" t="n">
-        <v>72.75</v>
+        <v>73.94999694824219</v>
       </c>
       <c r="D213" t="n">
-        <v>71.11000061035156</v>
+        <v>72.18000030517578</v>
       </c>
       <c r="E213" t="n">
-        <v>71.70999908447266</v>
+        <v>73.33000183105469</v>
       </c>
       <c r="F213" t="n">
-        <v>35847500</v>
+        <v>33922300</v>
       </c>
       <c r="G213" t="n">
         <v>0</v>
@@ -5981,22 +5981,22 @@
     </row>
     <row r="214">
       <c r="A214" s="1" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="B214" t="n">
-        <v>72.76999664306641</v>
+        <v>72.51000213623047</v>
       </c>
       <c r="C214" t="n">
-        <v>73.94999694824219</v>
+        <v>73.75</v>
       </c>
       <c r="D214" t="n">
-        <v>72.18000030517578</v>
+        <v>72.30000305175781</v>
       </c>
       <c r="E214" t="n">
-        <v>73.33000183105469</v>
+        <v>73.56999969482422</v>
       </c>
       <c r="F214" t="n">
-        <v>33922300</v>
+        <v>42877900</v>
       </c>
       <c r="G214" t="n">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="215">
       <c r="A215" s="1" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="B215" t="n">
-        <v>72.51000213623047</v>
+        <v>75.11000061035156</v>
       </c>
       <c r="C215" t="n">
-        <v>73.75</v>
+        <v>75.30000305175781</v>
       </c>
       <c r="D215" t="n">
-        <v>72.30000305175781</v>
+        <v>73.16000366210938</v>
       </c>
       <c r="E215" t="n">
-        <v>73.56999969482422</v>
+        <v>74.19999694824219</v>
       </c>
       <c r="F215" t="n">
-        <v>42877900</v>
+        <v>28969400</v>
       </c>
       <c r="G215" t="n">
         <v>0</v>
@@ -6033,22 +6033,22 @@
     </row>
     <row r="216">
       <c r="A216" s="1" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="B216" t="n">
-        <v>75.11000061035156</v>
+        <v>75.13999938964844</v>
       </c>
       <c r="C216" t="n">
-        <v>75.30000305175781</v>
+        <v>75.20999908447266</v>
       </c>
       <c r="D216" t="n">
-        <v>73.16000366210938</v>
+        <v>73.09999847412109</v>
       </c>
       <c r="E216" t="n">
-        <v>74.19999694824219</v>
+        <v>73.69000244140625</v>
       </c>
       <c r="F216" t="n">
-        <v>28969400</v>
+        <v>28892700</v>
       </c>
       <c r="G216" t="n">
         <v>0</v>
@@ -6059,22 +6059,22 @@
     </row>
     <row r="217">
       <c r="A217" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="B217" t="n">
-        <v>75.13999938964844</v>
+        <v>73.12000274658203</v>
       </c>
       <c r="C217" t="n">
-        <v>75.20999908447266</v>
+        <v>74.5</v>
       </c>
       <c r="D217" t="n">
-        <v>73.09999847412109</v>
+        <v>73.08000183105469</v>
       </c>
       <c r="E217" t="n">
-        <v>73.69000244140625</v>
+        <v>74.13999938964844</v>
       </c>
       <c r="F217" t="n">
-        <v>28892700</v>
+        <v>24819000</v>
       </c>
       <c r="G217" t="n">
         <v>0</v>
@@ -6085,22 +6085,22 @@
     </row>
     <row r="218">
       <c r="A218" s="1" t="n">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="B218" t="n">
-        <v>73.12000274658203</v>
+        <v>73.80000305175781</v>
       </c>
       <c r="C218" t="n">
-        <v>74.5</v>
+        <v>76.31999969482422</v>
       </c>
       <c r="D218" t="n">
-        <v>73.08000183105469</v>
+        <v>73.56999969482422</v>
       </c>
       <c r="E218" t="n">
-        <v>74.13999938964844</v>
+        <v>76.29000091552734</v>
       </c>
       <c r="F218" t="n">
-        <v>24819000</v>
+        <v>26959900</v>
       </c>
       <c r="G218" t="n">
         <v>0</v>
@@ -6111,22 +6111,22 @@
     </row>
     <row r="219">
       <c r="A219" s="1" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="B219" t="n">
-        <v>73.80000305175781</v>
+        <v>76.19999694824219</v>
       </c>
       <c r="C219" t="n">
-        <v>76.31999969482422</v>
+        <v>76.90000152587891</v>
       </c>
       <c r="D219" t="n">
-        <v>73.56999969482422</v>
+        <v>74.48000335693359</v>
       </c>
       <c r="E219" t="n">
-        <v>76.29000091552734</v>
+        <v>74.79000091552734</v>
       </c>
       <c r="F219" t="n">
-        <v>26959900</v>
+        <v>27840500</v>
       </c>
       <c r="G219" t="n">
         <v>0</v>
@@ -6137,22 +6137,22 @@
     </row>
     <row r="220">
       <c r="A220" s="1" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="B220" t="n">
-        <v>76.19999694824219</v>
+        <v>74.34999847412109</v>
       </c>
       <c r="C220" t="n">
-        <v>76.90000152587891</v>
+        <v>74.66999816894531</v>
       </c>
       <c r="D220" t="n">
-        <v>74.48000335693359</v>
+        <v>73.56999969482422</v>
       </c>
       <c r="E220" t="n">
-        <v>74.79000091552734</v>
+        <v>74.20999908447266</v>
       </c>
       <c r="F220" t="n">
-        <v>27840500</v>
+        <v>20773100</v>
       </c>
       <c r="G220" t="n">
         <v>0</v>
@@ -6163,22 +6163,22 @@
     </row>
     <row r="221">
       <c r="A221" s="1" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="B221" t="n">
-        <v>74.34999847412109</v>
+        <v>76.01000213623047</v>
       </c>
       <c r="C221" t="n">
-        <v>74.66999816894531</v>
+        <v>78.40000152587891</v>
       </c>
       <c r="D221" t="n">
-        <v>73.56999969482422</v>
+        <v>75.44000244140625</v>
       </c>
       <c r="E221" t="n">
-        <v>74.20999908447266</v>
+        <v>78.23999786376953</v>
       </c>
       <c r="F221" t="n">
-        <v>20773100</v>
+        <v>41452900</v>
       </c>
       <c r="G221" t="n">
         <v>0</v>
@@ -6189,22 +6189,22 @@
     </row>
     <row r="222">
       <c r="A222" s="1" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="B222" t="n">
-        <v>76.01000213623047</v>
+        <v>78.48000335693359</v>
       </c>
       <c r="C222" t="n">
-        <v>78.40000152587891</v>
+        <v>78.73000335693359</v>
       </c>
       <c r="D222" t="n">
-        <v>75.44000244140625</v>
+        <v>77.76000213623047</v>
       </c>
       <c r="E222" t="n">
-        <v>78.23999786376953</v>
+        <v>78.16000366210938</v>
       </c>
       <c r="F222" t="n">
-        <v>41452900</v>
+        <v>26751000</v>
       </c>
       <c r="G222" t="n">
         <v>0</v>
@@ -6215,22 +6215,22 @@
     </row>
     <row r="223">
       <c r="A223" s="1" t="n">
-        <v>46248</v>
+        <v>46251</v>
       </c>
       <c r="B223" t="n">
-        <v>78.48000335693359</v>
+        <v>77.80000305175781</v>
       </c>
       <c r="C223" t="n">
-        <v>78.73000335693359</v>
+        <v>78.52999877929688</v>
       </c>
       <c r="D223" t="n">
-        <v>77.76000213623047</v>
+        <v>75.47000122070312</v>
       </c>
       <c r="E223" t="n">
-        <v>78.16000366210938</v>
+        <v>76.01999664306641</v>
       </c>
       <c r="F223" t="n">
-        <v>26751000</v>
+        <v>30753000</v>
       </c>
       <c r="G223" t="n">
         <v>0</v>
@@ -6241,22 +6241,22 @@
     </row>
     <row r="224">
       <c r="A224" s="1" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="B224" t="n">
-        <v>77.80000305175781</v>
+        <v>77.43000030517578</v>
       </c>
       <c r="C224" t="n">
-        <v>78.52999877929688</v>
+        <v>79.09999847412109</v>
       </c>
       <c r="D224" t="n">
-        <v>75.47000122070312</v>
+        <v>76.33999633789062</v>
       </c>
       <c r="E224" t="n">
-        <v>76.01999664306641</v>
+        <v>77.76999664306641</v>
       </c>
       <c r="F224" t="n">
-        <v>30753000</v>
+        <v>36151300</v>
       </c>
       <c r="G224" t="n">
         <v>0</v>
@@ -6267,22 +6267,22 @@
     </row>
     <row r="225">
       <c r="A225" s="1" t="n">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="B225" t="n">
-        <v>77.43000030517578</v>
+        <v>78.25</v>
       </c>
       <c r="C225" t="n">
-        <v>79.09999847412109</v>
+        <v>81.16000366210938</v>
       </c>
       <c r="D225" t="n">
-        <v>76.33999633789062</v>
+        <v>78.09999847412109</v>
       </c>
       <c r="E225" t="n">
-        <v>77.76999664306641</v>
+        <v>80.22000122070312</v>
       </c>
       <c r="F225" t="n">
-        <v>36151300</v>
+        <v>31461800</v>
       </c>
       <c r="G225" t="n">
         <v>0</v>
@@ -6293,22 +6293,22 @@
     </row>
     <row r="226">
       <c r="A226" s="1" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="B226" t="n">
-        <v>78.25</v>
+        <v>80.13999938964844</v>
       </c>
       <c r="C226" t="n">
-        <v>81.16000366210938</v>
+        <v>81.08000183105469</v>
       </c>
       <c r="D226" t="n">
-        <v>78.09999847412109</v>
+        <v>79.58999633789062</v>
       </c>
       <c r="E226" t="n">
-        <v>80.22000122070312</v>
+        <v>80.13999938964844</v>
       </c>
       <c r="F226" t="n">
-        <v>31461800</v>
+        <v>27118400</v>
       </c>
       <c r="G226" t="n">
         <v>0</v>
@@ -6319,22 +6319,22 @@
     </row>
     <row r="227">
       <c r="A227" s="1" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="B227" t="n">
-        <v>80.13999938964844</v>
+        <v>80.29000091552734</v>
       </c>
       <c r="C227" t="n">
-        <v>81.08000183105469</v>
+        <v>80.48999786376953</v>
       </c>
       <c r="D227" t="n">
+        <v>79.16999816894531</v>
+      </c>
+      <c r="E227" t="n">
         <v>79.58999633789062</v>
       </c>
-      <c r="E227" t="n">
-        <v>80.13999938964844</v>
-      </c>
       <c r="F227" t="n">
-        <v>27118400</v>
+        <v>23773800</v>
       </c>
       <c r="G227" t="n">
         <v>0</v>
@@ -6345,22 +6345,22 @@
     </row>
     <row r="228">
       <c r="A228" s="1" t="n">
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="B228" t="n">
-        <v>80.29000091552734</v>
+        <v>79.94000244140625</v>
       </c>
       <c r="C228" t="n">
-        <v>80.48999786376953</v>
+        <v>80.62000274658203</v>
       </c>
       <c r="D228" t="n">
-        <v>79.16999816894531</v>
+        <v>79.01999664306641</v>
       </c>
       <c r="E228" t="n">
-        <v>79.58999633789062</v>
+        <v>80.01000213623047</v>
       </c>
       <c r="F228" t="n">
-        <v>23773800</v>
+        <v>21085300</v>
       </c>
       <c r="G228" t="n">
         <v>0</v>
@@ -6371,22 +6371,22 @@
     </row>
     <row r="229">
       <c r="A229" s="1" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="B229" t="n">
-        <v>79.94000244140625</v>
+        <v>79.65000152587891</v>
       </c>
       <c r="C229" t="n">
-        <v>80.62000274658203</v>
+        <v>82.45999908447266</v>
       </c>
       <c r="D229" t="n">
-        <v>79.01999664306641</v>
+        <v>79.40000152587891</v>
       </c>
       <c r="E229" t="n">
-        <v>80.01000213623047</v>
+        <v>82.23000335693359</v>
       </c>
       <c r="F229" t="n">
-        <v>21085300</v>
+        <v>29462000</v>
       </c>
       <c r="G229" t="n">
         <v>0</v>
@@ -6397,22 +6397,22 @@
     </row>
     <row r="230">
       <c r="A230" s="1" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="B230" t="n">
-        <v>79.65000152587891</v>
+        <v>82.05000305175781</v>
       </c>
       <c r="C230" t="n">
-        <v>82.45999908447266</v>
+        <v>82.41999816894531</v>
       </c>
       <c r="D230" t="n">
-        <v>79.40000152587891</v>
+        <v>81.30000305175781</v>
       </c>
       <c r="E230" t="n">
-        <v>82.23000335693359</v>
+        <v>81.45999908447266</v>
       </c>
       <c r="F230" t="n">
-        <v>29462000</v>
+        <v>22874900</v>
       </c>
       <c r="G230" t="n">
         <v>0</v>
@@ -6423,22 +6423,22 @@
     </row>
     <row r="231">
       <c r="A231" s="1" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="B231" t="n">
-        <v>82.05000305175781</v>
+        <v>81.06999969482422</v>
       </c>
       <c r="C231" t="n">
-        <v>82.41999816894531</v>
+        <v>81.15000152587891</v>
       </c>
       <c r="D231" t="n">
-        <v>81.30000305175781</v>
+        <v>79.27999877929688</v>
       </c>
       <c r="E231" t="n">
-        <v>81.45999908447266</v>
+        <v>79.83999633789062</v>
       </c>
       <c r="F231" t="n">
-        <v>22874900</v>
+        <v>27174400</v>
       </c>
       <c r="G231" t="n">
         <v>0</v>
@@ -6449,22 +6449,22 @@
     </row>
     <row r="232">
       <c r="A232" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="B232" t="n">
-        <v>81.06999969482422</v>
+        <v>80.36000061035156</v>
       </c>
       <c r="C232" t="n">
-        <v>81.15000152587891</v>
+        <v>82.34999847412109</v>
       </c>
       <c r="D232" t="n">
-        <v>79.27999877929688</v>
+        <v>79.94999694824219</v>
       </c>
       <c r="E232" t="n">
-        <v>79.83999633789062</v>
+        <v>81.72000122070312</v>
       </c>
       <c r="F232" t="n">
-        <v>27174400</v>
+        <v>29092700</v>
       </c>
       <c r="G232" t="n">
         <v>0</v>
@@ -6475,22 +6475,22 @@
     </row>
     <row r="233">
       <c r="A233" s="1" t="n">
-        <v>46262</v>
+        <v>46265</v>
       </c>
       <c r="B233" t="n">
-        <v>80.36000061035156</v>
+        <v>81</v>
       </c>
       <c r="C233" t="n">
-        <v>82.34999847412109</v>
+        <v>81.73000335693359</v>
       </c>
       <c r="D233" t="n">
-        <v>79.94999694824219</v>
+        <v>80.65000152587891</v>
       </c>
       <c r="E233" t="n">
-        <v>81.72000122070312</v>
+        <v>81.05000305175781</v>
       </c>
       <c r="F233" t="n">
-        <v>29092700</v>
+        <v>30740800</v>
       </c>
       <c r="G233" t="n">
         <v>0</v>
@@ -6501,22 +6501,22 @@
     </row>
     <row r="234">
       <c r="A234" s="1" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="B234" t="n">
-        <v>81</v>
+        <v>80.16999816894531</v>
       </c>
       <c r="C234" t="n">
-        <v>81.73000335693359</v>
+        <v>82.12999725341797</v>
       </c>
       <c r="D234" t="n">
-        <v>80.65000152587891</v>
+        <v>79.59999847412109</v>
       </c>
       <c r="E234" t="n">
-        <v>81.05000305175781</v>
+        <v>80.80999755859375</v>
       </c>
       <c r="F234" t="n">
-        <v>30740800</v>
+        <v>21164900</v>
       </c>
       <c r="G234" t="n">
         <v>0</v>
@@ -6527,22 +6527,22 @@
     </row>
     <row r="235">
       <c r="A235" s="1" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="B235" t="n">
-        <v>80.16999816894531</v>
+        <v>80.55000305175781</v>
       </c>
       <c r="C235" t="n">
-        <v>82.12999725341797</v>
+        <v>83.12000274658203</v>
       </c>
       <c r="D235" t="n">
-        <v>79.59999847412109</v>
+        <v>80.30000305175781</v>
       </c>
       <c r="E235" t="n">
-        <v>80.80999755859375</v>
+        <v>82.73000335693359</v>
       </c>
       <c r="F235" t="n">
-        <v>21164900</v>
+        <v>22077800</v>
       </c>
       <c r="G235" t="n">
         <v>0</v>
@@ -6553,22 +6553,22 @@
     </row>
     <row r="236">
       <c r="A236" s="1" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="B236" t="n">
-        <v>80.55000305175781</v>
+        <v>83.18000030517578</v>
       </c>
       <c r="C236" t="n">
-        <v>83.12000274658203</v>
+        <v>83.59999847412109</v>
       </c>
       <c r="D236" t="n">
-        <v>80.30000305175781</v>
+        <v>81.62999725341797</v>
       </c>
       <c r="E236" t="n">
-        <v>82.73000335693359</v>
+        <v>82.66999816894531</v>
       </c>
       <c r="F236" t="n">
-        <v>22077800</v>
+        <v>24006400</v>
       </c>
       <c r="G236" t="n">
         <v>0</v>
@@ -6579,22 +6579,22 @@
     </row>
     <row r="237">
       <c r="A237" s="1" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B237" t="n">
-        <v>83.18000030517578</v>
+        <v>82.16999816894531</v>
       </c>
       <c r="C237" t="n">
-        <v>83.59999847412109</v>
+        <v>82.69000244140625</v>
       </c>
       <c r="D237" t="n">
-        <v>81.62999725341797</v>
+        <v>78.23000335693359</v>
       </c>
       <c r="E237" t="n">
-        <v>82.66999816894531</v>
+        <v>78.25</v>
       </c>
       <c r="F237" t="n">
-        <v>24006400</v>
+        <v>40190000</v>
       </c>
       <c r="G237" t="n">
         <v>0</v>
@@ -6605,22 +6605,22 @@
     </row>
     <row r="238">
       <c r="A238" s="1" t="n">
-        <v>46269</v>
+        <v>46273</v>
       </c>
       <c r="B238" t="n">
-        <v>82.16999816894531</v>
+        <v>77.55000305175781</v>
       </c>
       <c r="C238" t="n">
-        <v>82.69000244140625</v>
+        <v>77.73000335693359</v>
       </c>
       <c r="D238" t="n">
-        <v>78.23000335693359</v>
+        <v>75.91999816894531</v>
       </c>
       <c r="E238" t="n">
-        <v>78.25</v>
+        <v>76.76999664306641</v>
       </c>
       <c r="F238" t="n">
-        <v>40190000</v>
+        <v>33865500</v>
       </c>
       <c r="G238" t="n">
         <v>0</v>
@@ -6631,22 +6631,22 @@
     </row>
     <row r="239">
       <c r="A239" s="1" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B239" t="n">
-        <v>77.55000305175781</v>
+        <v>76.33999633789062</v>
       </c>
       <c r="C239" t="n">
-        <v>77.73000335693359</v>
+        <v>76.72000122070312</v>
       </c>
       <c r="D239" t="n">
-        <v>75.91999816894531</v>
+        <v>75.87000274658203</v>
       </c>
       <c r="E239" t="n">
-        <v>76.76999664306641</v>
+        <v>76.02999877929688</v>
       </c>
       <c r="F239" t="n">
-        <v>33865500</v>
+        <v>22779600</v>
       </c>
       <c r="G239" t="n">
         <v>0</v>
@@ -6657,22 +6657,22 @@
     </row>
     <row r="240">
       <c r="A240" s="1" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="B240" t="n">
-        <v>76.33999633789062</v>
+        <v>75.33000183105469</v>
       </c>
       <c r="C240" t="n">
-        <v>76.72000122070312</v>
+        <v>76.30000305175781</v>
       </c>
       <c r="D240" t="n">
-        <v>75.87000274658203</v>
+        <v>75.02999877929688</v>
       </c>
       <c r="E240" t="n">
-        <v>76.02999877929688</v>
+        <v>76.01000213623047</v>
       </c>
       <c r="F240" t="n">
-        <v>22779600</v>
+        <v>20049000</v>
       </c>
       <c r="G240" t="n">
         <v>0</v>
@@ -6683,22 +6683,22 @@
     </row>
     <row r="241">
       <c r="A241" s="1" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="B241" t="n">
-        <v>75.33000183105469</v>
+        <v>76.63999938964844</v>
       </c>
       <c r="C241" t="n">
-        <v>76.30000305175781</v>
+        <v>77.56999969482422</v>
       </c>
       <c r="D241" t="n">
-        <v>75.02999877929688</v>
+        <v>76.15000152587891</v>
       </c>
       <c r="E241" t="n">
-        <v>76.01000213623047</v>
+        <v>77.40000152587891</v>
       </c>
       <c r="F241" t="n">
-        <v>20049000</v>
+        <v>22237800</v>
       </c>
       <c r="G241" t="n">
         <v>0</v>
@@ -6709,22 +6709,22 @@
     </row>
     <row r="242">
       <c r="A242" s="1" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="B242" t="n">
-        <v>76.63999938964844</v>
+        <v>78.97000122070312</v>
       </c>
       <c r="C242" t="n">
-        <v>77.56999969482422</v>
+        <v>81.01999664306641</v>
       </c>
       <c r="D242" t="n">
-        <v>76.15000152587891</v>
+        <v>78.48999786376953</v>
       </c>
       <c r="E242" t="n">
-        <v>77.40000152587891</v>
+        <v>80.31999969482422</v>
       </c>
       <c r="F242" t="n">
-        <v>22237800</v>
+        <v>30945100</v>
       </c>
       <c r="G242" t="n">
         <v>0</v>
@@ -6735,22 +6735,22 @@
     </row>
     <row r="243">
       <c r="A243" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="B243" t="n">
-        <v>78.97000122070312</v>
+        <v>79.37999725341797</v>
       </c>
       <c r="C243" t="n">
-        <v>81.01999664306641</v>
+        <v>79.48000335693359</v>
       </c>
       <c r="D243" t="n">
-        <v>78.48999786376953</v>
+        <v>77.45999908447266</v>
       </c>
       <c r="E243" t="n">
-        <v>80.31999969482422</v>
+        <v>77.90000152587891</v>
       </c>
       <c r="F243" t="n">
-        <v>30945100</v>
+        <v>28027400</v>
       </c>
       <c r="G243" t="n">
         <v>0</v>
@@ -6761,22 +6761,22 @@
     </row>
     <row r="244">
       <c r="A244" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="B244" t="n">
-        <v>79.37999725341797</v>
+        <v>77.73000335693359</v>
       </c>
       <c r="C244" t="n">
-        <v>79.48000335693359</v>
+        <v>77.80000305175781</v>
       </c>
       <c r="D244" t="n">
-        <v>77.45999908447266</v>
+        <v>76.30999755859375</v>
       </c>
       <c r="E244" t="n">
-        <v>77.90000152587891</v>
+        <v>76.41000366210938</v>
       </c>
       <c r="F244" t="n">
-        <v>28027400</v>
+        <v>25376300</v>
       </c>
       <c r="G244" t="n">
         <v>0</v>
@@ -6787,22 +6787,22 @@
     </row>
     <row r="245">
       <c r="A245" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="B245" t="n">
-        <v>77.73000335693359</v>
+        <v>76.91000366210938</v>
       </c>
       <c r="C245" t="n">
-        <v>77.80000305175781</v>
+        <v>76.95999908447266</v>
       </c>
       <c r="D245" t="n">
-        <v>76.30999755859375</v>
+        <v>75.30000305175781</v>
       </c>
       <c r="E245" t="n">
-        <v>76.41000366210938</v>
+        <v>75.30999755859375</v>
       </c>
       <c r="F245" t="n">
-        <v>25376300</v>
+        <v>28167600</v>
       </c>
       <c r="G245" t="n">
         <v>0</v>
@@ -6813,22 +6813,22 @@
     </row>
     <row r="246">
       <c r="A246" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="B246" t="n">
-        <v>76.91000366210938</v>
+        <v>71.26999664306641</v>
       </c>
       <c r="C246" t="n">
-        <v>76.95999908447266</v>
+        <v>72.37999725341797</v>
       </c>
       <c r="D246" t="n">
-        <v>75.30000305175781</v>
+        <v>70.11000061035156</v>
       </c>
       <c r="E246" t="n">
-        <v>75.30999755859375</v>
+        <v>71.79000091552734</v>
       </c>
       <c r="F246" t="n">
-        <v>28167600</v>
+        <v>114413500</v>
       </c>
       <c r="G246" t="n">
         <v>0</v>
@@ -6839,22 +6839,22 @@
     </row>
     <row r="247">
       <c r="A247" s="1" t="n">
-        <v>46283</v>
+        <v>46286</v>
       </c>
       <c r="B247" t="n">
-        <v>71.26999664306641</v>
+        <v>71.81999969482422</v>
       </c>
       <c r="C247" t="n">
-        <v>72.37999725341797</v>
+        <v>73.87000274658203</v>
       </c>
       <c r="D247" t="n">
-        <v>70.11000061035156</v>
+        <v>71.79000091552734</v>
       </c>
       <c r="E247" t="n">
-        <v>71.79000091552734</v>
+        <v>73.36000061035156</v>
       </c>
       <c r="F247" t="n">
-        <v>114413500</v>
+        <v>36948000</v>
       </c>
       <c r="G247" t="n">
         <v>0</v>
@@ -6865,22 +6865,22 @@
     </row>
     <row r="248">
       <c r="A248" s="1" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="B248" t="n">
-        <v>71.81999969482422</v>
+        <v>73.69000244140625</v>
       </c>
       <c r="C248" t="n">
-        <v>73.87000274658203</v>
+        <v>73.76000213623047</v>
       </c>
       <c r="D248" t="n">
-        <v>71.79000091552734</v>
+        <v>71.58000183105469</v>
       </c>
       <c r="E248" t="n">
-        <v>73.36000061035156</v>
+        <v>72.16000366210938</v>
       </c>
       <c r="F248" t="n">
-        <v>36948000</v>
+        <v>34372500</v>
       </c>
       <c r="G248" t="n">
         <v>0</v>
@@ -6891,22 +6891,22 @@
     </row>
     <row r="249">
       <c r="A249" s="1" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="B249" t="n">
-        <v>73.69000244140625</v>
+        <v>72.08000183105469</v>
       </c>
       <c r="C249" t="n">
-        <v>73.76000213623047</v>
+        <v>72.37000274658203</v>
       </c>
       <c r="D249" t="n">
-        <v>71.58000183105469</v>
+        <v>71.06999969482422</v>
       </c>
       <c r="E249" t="n">
-        <v>72.16000366210938</v>
+        <v>71.36000061035156</v>
       </c>
       <c r="F249" t="n">
-        <v>34372500</v>
+        <v>32807500</v>
       </c>
       <c r="G249" t="n">
         <v>0</v>
@@ -6917,22 +6917,22 @@
     </row>
     <row r="250">
       <c r="A250" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="B250" t="n">
-        <v>72.08000183105469</v>
+        <v>71.62000274658203</v>
       </c>
       <c r="C250" t="n">
-        <v>72.37000274658203</v>
+        <v>72.04000091552734</v>
       </c>
       <c r="D250" t="n">
-        <v>71.06999969482422</v>
+        <v>71.20999908447266</v>
       </c>
       <c r="E250" t="n">
-        <v>71.36000061035156</v>
+        <v>71.72000122070312</v>
       </c>
       <c r="F250" t="n">
-        <v>32807500</v>
+        <v>28223900</v>
       </c>
       <c r="G250" t="n">
         <v>0</v>
@@ -6943,22 +6943,22 @@
     </row>
     <row r="251">
       <c r="A251" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="B251" t="n">
-        <v>71.62000274658203</v>
+        <v>71.62999725341797</v>
       </c>
       <c r="C251" t="n">
-        <v>72.04000091552734</v>
+        <v>71.83999633789062</v>
       </c>
       <c r="D251" t="n">
-        <v>71.20999908447266</v>
+        <v>70.98000335693359</v>
       </c>
       <c r="E251" t="n">
-        <v>71.72000122070312</v>
+        <v>71.15000152587891</v>
       </c>
       <c r="F251" t="n">
-        <v>28223900</v>
+        <v>23203100</v>
       </c>
       <c r="G251" t="n">
         <v>0</v>
@@ -6969,22 +6969,22 @@
     </row>
     <row r="252">
       <c r="A252" s="1" t="n">
-        <v>46290</v>
+        <v>46293</v>
       </c>
       <c r="B252" t="n">
-        <v>71.62999725341797</v>
+        <v>71.55000305175781</v>
       </c>
       <c r="C252" t="n">
-        <v>71.83999633789062</v>
+        <v>71.65000152587891</v>
       </c>
       <c r="D252" t="n">
-        <v>70.98000335693359</v>
+        <v>68.87999725341797</v>
       </c>
       <c r="E252" t="n">
-        <v>71.15000152587891</v>
+        <v>69.23000335693359</v>
       </c>
       <c r="F252" t="n">
-        <v>23175700</v>
+        <v>43145800</v>
       </c>
       <c r="G252" t="n">
         <v>0</v>
@@ -10434,37 +10434,37 @@
         </is>
       </c>
       <c r="C2" t="n">
+        <v>69.23</v>
+      </c>
+      <c r="D2" t="n">
         <v>71.145</v>
       </c>
-      <c r="D2" t="n">
-        <v>71.72</v>
-      </c>
       <c r="E2" t="n">
-        <v>71.575</v>
+        <v>71.55</v>
       </c>
       <c r="F2" t="n">
-        <v>71.83499999999999</v>
+        <v>71.58</v>
       </c>
       <c r="G2" t="n">
-        <v>70.98</v>
+        <v>68.88</v>
       </c>
       <c r="H2" t="n">
-        <v>23135069</v>
+        <v>43070286</v>
       </c>
       <c r="I2" t="n">
-        <v>37919035</v>
+        <v>37696817</v>
       </c>
       <c r="J2" t="n">
-        <v>296243462144</v>
+        <v>288269565952</v>
       </c>
       <c r="K2" t="n">
-        <v>22.37264</v>
+        <v>22.404533</v>
       </c>
       <c r="L2" t="n">
-        <v>18.65746</v>
+        <v>18.15526</v>
       </c>
       <c r="M2" t="n">
-        <v>3.18</v>
+        <v>3.09</v>
       </c>
       <c r="N2" t="n">
         <v>124.86</v>
@@ -10502,7 +10502,7 @@
         <v>7.241</v>
       </c>
       <c r="Y2" t="n">
-        <v>9.825298999999999</v>
+        <v>9.560834</v>
       </c>
       <c r="Z2" t="n">
         <v>0.111</v>
@@ -10514,7 +10514,7 @@
         <v>48370765824</v>
       </c>
       <c r="AC2" t="n">
-        <v>303770238976</v>
+        <v>295796310016</v>
       </c>
       <c r="AD2" t="n">
         <v>14726931456</v>
@@ -10541,7 +10541,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>2026-09-26 14:50:04</t>
+          <t>2026-09-29 13:25:00</t>
         </is>
       </c>
     </row>

--- a/data/NFLX_data.xlsx
+++ b/data/NFLX_data.xlsx
@@ -469,22 +469,22 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="B2" t="n">
-        <v>120.5</v>
+        <v>120.640998840332</v>
       </c>
       <c r="C2" t="n">
-        <v>122.4489974975586</v>
+        <v>120.8499984741211</v>
       </c>
       <c r="D2" t="n">
-        <v>118.7539978027344</v>
+        <v>117.8000030517578</v>
       </c>
       <c r="E2" t="n">
-        <v>120.640998840332</v>
+        <v>119.8919982910156</v>
       </c>
       <c r="F2" t="n">
-        <v>30332000</v>
+        <v>38303000</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -495,22 +495,22 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45930</v>
+        <v>45931</v>
       </c>
       <c r="B3" t="n">
-        <v>120.640998840332</v>
+        <v>117.5490036010742</v>
       </c>
       <c r="C3" t="n">
-        <v>120.8499984741211</v>
+        <v>117.9140014648438</v>
       </c>
       <c r="D3" t="n">
-        <v>117.8000030517578</v>
+        <v>116.3209991455078</v>
       </c>
       <c r="E3" t="n">
-        <v>119.8919982910156</v>
+        <v>117.0899963378906</v>
       </c>
       <c r="F3" t="n">
-        <v>38303000</v>
+        <v>41102000</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -521,22 +521,22 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>45931</v>
+        <v>45932</v>
       </c>
       <c r="B4" t="n">
-        <v>117.5490036010742</v>
+        <v>116.1500015258789</v>
       </c>
       <c r="C4" t="n">
-        <v>117.9140014648438</v>
+        <v>116.3330001831055</v>
       </c>
       <c r="D4" t="n">
-        <v>116.3209991455078</v>
+        <v>113.4000015258789</v>
       </c>
       <c r="E4" t="n">
-        <v>117.0899963378906</v>
+        <v>116.2529983520508</v>
       </c>
       <c r="F4" t="n">
-        <v>41102000</v>
+        <v>46855000</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -547,22 +547,22 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>45932</v>
+        <v>45933</v>
       </c>
       <c r="B5" t="n">
-        <v>116.1500015258789</v>
+        <v>116.5</v>
       </c>
       <c r="C5" t="n">
-        <v>116.3330001831055</v>
+        <v>116.8000030517578</v>
       </c>
       <c r="D5" t="n">
-        <v>113.4000015258789</v>
+        <v>114.3219985961914</v>
       </c>
       <c r="E5" t="n">
-        <v>116.2529983520508</v>
+        <v>115.3320007324219</v>
       </c>
       <c r="F5" t="n">
-        <v>46855000</v>
+        <v>31374000</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -573,22 +573,22 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>45933</v>
+        <v>45936</v>
       </c>
       <c r="B6" t="n">
-        <v>116.5</v>
+        <v>116.0370025634766</v>
       </c>
       <c r="C6" t="n">
-        <v>116.8000030517578</v>
+        <v>116.3580017089844</v>
       </c>
       <c r="D6" t="n">
-        <v>114.3219985961914</v>
+        <v>114.5449981689453</v>
       </c>
       <c r="E6" t="n">
-        <v>115.3320007324219</v>
+        <v>116.3310012817383</v>
       </c>
       <c r="F6" t="n">
-        <v>31374000</v>
+        <v>29686000</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -599,22 +599,22 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>45936</v>
+        <v>45937</v>
       </c>
       <c r="B7" t="n">
-        <v>116.0370025634766</v>
+        <v>117.7789993286133</v>
       </c>
       <c r="C7" t="n">
-        <v>116.3580017089844</v>
+        <v>120.1370010375977</v>
       </c>
       <c r="D7" t="n">
-        <v>114.5449981689453</v>
+        <v>117.7460021972656</v>
       </c>
       <c r="E7" t="n">
-        <v>116.3310012817383</v>
+        <v>119.1060028076172</v>
       </c>
       <c r="F7" t="n">
-        <v>29686000</v>
+        <v>33091000</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -625,22 +625,22 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>45937</v>
+        <v>45938</v>
       </c>
       <c r="B8" t="n">
-        <v>117.7789993286133</v>
+        <v>119.7109985351562</v>
       </c>
       <c r="C8" t="n">
-        <v>120.1370010375977</v>
+        <v>121.7389984130859</v>
       </c>
       <c r="D8" t="n">
-        <v>117.7460021972656</v>
+        <v>119.1999969482422</v>
       </c>
       <c r="E8" t="n">
-        <v>119.1060028076172</v>
+        <v>121.4250030517578</v>
       </c>
       <c r="F8" t="n">
-        <v>33091000</v>
+        <v>28514000</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -651,22 +651,22 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>45938</v>
+        <v>45939</v>
       </c>
       <c r="B9" t="n">
-        <v>119.7109985351562</v>
+        <v>121.4250030517578</v>
       </c>
       <c r="C9" t="n">
-        <v>121.7389984130859</v>
+        <v>123.75</v>
       </c>
       <c r="D9" t="n">
-        <v>119.1999969482422</v>
+        <v>121.181999206543</v>
       </c>
       <c r="E9" t="n">
-        <v>121.4250030517578</v>
+        <v>123.1070022583008</v>
       </c>
       <c r="F9" t="n">
-        <v>28514000</v>
+        <v>28241000</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -677,22 +677,22 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>45939</v>
+        <v>45940</v>
       </c>
       <c r="B10" t="n">
-        <v>121.4250030517578</v>
+        <v>122.9000015258789</v>
       </c>
       <c r="C10" t="n">
-        <v>123.75</v>
+        <v>124.6999969482422</v>
       </c>
       <c r="D10" t="n">
-        <v>121.181999206543</v>
+        <v>121.9100036621094</v>
       </c>
       <c r="E10" t="n">
-        <v>123.1070022583008</v>
+        <v>122.0080032348633</v>
       </c>
       <c r="F10" t="n">
-        <v>28241000</v>
+        <v>42798000</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -703,22 +703,22 @@
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>45940</v>
+        <v>45943</v>
       </c>
       <c r="B11" t="n">
-        <v>122.9000015258789</v>
+        <v>122.1350021362305</v>
       </c>
       <c r="C11" t="n">
-        <v>124.6999969482422</v>
+        <v>123.1119995117188</v>
       </c>
       <c r="D11" t="n">
-        <v>121.9100036621094</v>
+        <v>120.6809997558594</v>
       </c>
       <c r="E11" t="n">
-        <v>122.0080032348633</v>
+        <v>121.9029998779297</v>
       </c>
       <c r="F11" t="n">
-        <v>42798000</v>
+        <v>24608000</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -729,22 +729,22 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>45943</v>
+        <v>45944</v>
       </c>
       <c r="B12" t="n">
-        <v>122.1350021362305</v>
+        <v>121.4749984741211</v>
       </c>
       <c r="C12" t="n">
-        <v>123.1119995117188</v>
+        <v>122.4290008544922</v>
       </c>
       <c r="D12" t="n">
-        <v>120.6809997558594</v>
+        <v>120.3099975585938</v>
       </c>
       <c r="E12" t="n">
-        <v>121.9029998779297</v>
+        <v>121.5350036621094</v>
       </c>
       <c r="F12" t="n">
-        <v>24608000</v>
+        <v>23624000</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -755,22 +755,22 @@
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>45944</v>
+        <v>45945</v>
       </c>
       <c r="B13" t="n">
-        <v>121.4749984741211</v>
+        <v>121.3010025024414</v>
       </c>
       <c r="C13" t="n">
-        <v>122.4290008544922</v>
+        <v>121.9619979858398</v>
       </c>
       <c r="D13" t="n">
-        <v>120.3099975585938</v>
+        <v>120.161003112793</v>
       </c>
       <c r="E13" t="n">
-        <v>121.5350036621094</v>
+        <v>120.3290023803711</v>
       </c>
       <c r="F13" t="n">
-        <v>23624000</v>
+        <v>20252000</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -781,22 +781,22 @@
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>45945</v>
+        <v>45946</v>
       </c>
       <c r="B14" t="n">
-        <v>121.3010025024414</v>
+        <v>121.2149963378906</v>
       </c>
       <c r="C14" t="n">
-        <v>121.9619979858398</v>
+        <v>121.6709976196289</v>
       </c>
       <c r="D14" t="n">
-        <v>120.161003112793</v>
+        <v>117.5999984741211</v>
       </c>
       <c r="E14" t="n">
-        <v>120.3290023803711</v>
+        <v>118.359001159668</v>
       </c>
       <c r="F14" t="n">
-        <v>20252000</v>
+        <v>28326000</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -807,22 +807,22 @@
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>45946</v>
+        <v>45947</v>
       </c>
       <c r="B15" t="n">
-        <v>121.2149963378906</v>
+        <v>118.3600006103516</v>
       </c>
       <c r="C15" t="n">
-        <v>121.6709976196289</v>
+        <v>120.3119964599609</v>
       </c>
       <c r="D15" t="n">
-        <v>117.5999984741211</v>
+        <v>117.8949966430664</v>
       </c>
       <c r="E15" t="n">
-        <v>118.359001159668</v>
+        <v>119.9359970092773</v>
       </c>
       <c r="F15" t="n">
-        <v>28326000</v>
+        <v>29571000</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -833,22 +833,22 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>45947</v>
+        <v>45950</v>
       </c>
       <c r="B16" t="n">
-        <v>118.3600006103516</v>
+        <v>120.7880020141602</v>
       </c>
       <c r="C16" t="n">
-        <v>120.3119964599609</v>
+        <v>124.7760009765625</v>
       </c>
       <c r="D16" t="n">
-        <v>117.8949966430664</v>
+        <v>120.6900024414062</v>
       </c>
       <c r="E16" t="n">
-        <v>119.9359970092773</v>
+        <v>123.8560028076172</v>
       </c>
       <c r="F16" t="n">
-        <v>29571000</v>
+        <v>39862000</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -859,22 +859,22 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>45950</v>
+        <v>45951</v>
       </c>
       <c r="B17" t="n">
-        <v>120.7880020141602</v>
+        <v>124.2829971313477</v>
       </c>
       <c r="C17" t="n">
-        <v>124.7760009765625</v>
+        <v>124.8600006103516</v>
       </c>
       <c r="D17" t="n">
-        <v>120.6900024414062</v>
+        <v>123.1760025024414</v>
       </c>
       <c r="E17" t="n">
-        <v>123.8560028076172</v>
+        <v>124.1350021362305</v>
       </c>
       <c r="F17" t="n">
-        <v>39862000</v>
+        <v>65082000</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -885,22 +885,22 @@
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>45951</v>
+        <v>45952</v>
       </c>
       <c r="B18" t="n">
-        <v>124.2829971313477</v>
+        <v>114.2900009155273</v>
       </c>
       <c r="C18" t="n">
-        <v>124.8600006103516</v>
+        <v>115.7600021362305</v>
       </c>
       <c r="D18" t="n">
-        <v>123.1760025024414</v>
+        <v>111.2509994506836</v>
       </c>
       <c r="E18" t="n">
-        <v>124.1350021362305</v>
+        <v>111.6370010375977</v>
       </c>
       <c r="F18" t="n">
-        <v>65082000</v>
+        <v>147890000</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -911,22 +911,22 @@
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>45952</v>
+        <v>45953</v>
       </c>
       <c r="B19" t="n">
-        <v>114.2900009155273</v>
+        <v>112.6900024414062</v>
       </c>
       <c r="C19" t="n">
-        <v>115.7600021362305</v>
+        <v>112.7829971313477</v>
       </c>
       <c r="D19" t="n">
-        <v>111.2509994506836</v>
+        <v>109.9729995727539</v>
       </c>
       <c r="E19" t="n">
-        <v>111.6370010375977</v>
+        <v>111.359001159668</v>
       </c>
       <c r="F19" t="n">
-        <v>147890000</v>
+        <v>68497000</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -937,22 +937,22 @@
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>45953</v>
+        <v>45954</v>
       </c>
       <c r="B20" t="n">
-        <v>112.6900024414062</v>
+        <v>111.0999984741211</v>
       </c>
       <c r="C20" t="n">
-        <v>112.7829971313477</v>
+        <v>111.4509963989258</v>
       </c>
       <c r="D20" t="n">
-        <v>109.9729995727539</v>
+        <v>109.4410018920898</v>
       </c>
       <c r="E20" t="n">
-        <v>111.359001159668</v>
+        <v>109.4690017700195</v>
       </c>
       <c r="F20" t="n">
-        <v>68497000</v>
+        <v>60280000</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -963,22 +963,22 @@
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>45954</v>
+        <v>45957</v>
       </c>
       <c r="B21" t="n">
-        <v>111.0999984741211</v>
+        <v>110.0670013427734</v>
       </c>
       <c r="C21" t="n">
-        <v>111.4509963989258</v>
+        <v>110.2279968261719</v>
       </c>
       <c r="D21" t="n">
-        <v>109.4410018920898</v>
+        <v>108.7300033569336</v>
       </c>
       <c r="E21" t="n">
-        <v>109.4690017700195</v>
+        <v>109.4560012817383</v>
       </c>
       <c r="F21" t="n">
-        <v>60280000</v>
+        <v>46911000</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -989,22 +989,22 @@
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>45957</v>
+        <v>45958</v>
       </c>
       <c r="B22" t="n">
-        <v>110.0670013427734</v>
+        <v>109.4000015258789</v>
       </c>
       <c r="C22" t="n">
-        <v>110.2279968261719</v>
+        <v>111.697998046875</v>
       </c>
       <c r="D22" t="n">
-        <v>108.7300033569336</v>
+        <v>109.3010025024414</v>
       </c>
       <c r="E22" t="n">
-        <v>109.4560012817383</v>
+        <v>110.25</v>
       </c>
       <c r="F22" t="n">
-        <v>46911000</v>
+        <v>40209000</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -1015,22 +1015,22 @@
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>45958</v>
+        <v>45959</v>
       </c>
       <c r="B23" t="n">
-        <v>109.4000015258789</v>
+        <v>109.984001159668</v>
       </c>
       <c r="C23" t="n">
-        <v>111.697998046875</v>
+        <v>110.8550033569336</v>
       </c>
       <c r="D23" t="n">
-        <v>109.3010025024414</v>
+        <v>109.5999984741211</v>
       </c>
       <c r="E23" t="n">
-        <v>110.25</v>
+        <v>110.0410003662109</v>
       </c>
       <c r="F23" t="n">
-        <v>40209000</v>
+        <v>33995000</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -1041,22 +1041,22 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>45959</v>
+        <v>45960</v>
       </c>
       <c r="B24" t="n">
-        <v>109.984001159668</v>
+        <v>109.4400024414062</v>
       </c>
       <c r="C24" t="n">
-        <v>110.8550033569336</v>
+        <v>110.6159973144531</v>
       </c>
       <c r="D24" t="n">
-        <v>109.5999984741211</v>
+        <v>108.8109970092773</v>
       </c>
       <c r="E24" t="n">
-        <v>110.0410003662109</v>
+        <v>108.9000015258789</v>
       </c>
       <c r="F24" t="n">
-        <v>33995000</v>
+        <v>41581000</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -1067,22 +1067,22 @@
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>45960</v>
+        <v>45961</v>
       </c>
       <c r="B25" t="n">
-        <v>109.4400024414062</v>
+        <v>110.5390014648438</v>
       </c>
       <c r="C25" t="n">
-        <v>110.6159973144531</v>
+        <v>113.4879989624023</v>
       </c>
       <c r="D25" t="n">
-        <v>108.8109970092773</v>
+        <v>110.197998046875</v>
       </c>
       <c r="E25" t="n">
-        <v>108.9000015258789</v>
+        <v>111.8860015869141</v>
       </c>
       <c r="F25" t="n">
-        <v>41581000</v>
+        <v>68665000</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -1093,22 +1093,22 @@
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>45961</v>
+        <v>45964</v>
       </c>
       <c r="B26" t="n">
-        <v>110.5390014648438</v>
+        <v>113.3239974975586</v>
       </c>
       <c r="C26" t="n">
-        <v>113.4879989624023</v>
+        <v>113.3499984741211</v>
       </c>
       <c r="D26" t="n">
-        <v>110.197998046875</v>
+        <v>107.5149993896484</v>
       </c>
       <c r="E26" t="n">
-        <v>111.8860015869141</v>
+        <v>110.0090026855469</v>
       </c>
       <c r="F26" t="n">
-        <v>68665000</v>
+        <v>58634000</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -1119,22 +1119,22 @@
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>45964</v>
+        <v>45965</v>
       </c>
       <c r="B27" t="n">
-        <v>113.3239974975586</v>
+        <v>109.9990005493164</v>
       </c>
       <c r="C27" t="n">
-        <v>113.3499984741211</v>
+        <v>110.4599990844727</v>
       </c>
       <c r="D27" t="n">
-        <v>107.5149993896484</v>
+        <v>108.6679992675781</v>
       </c>
       <c r="E27" t="n">
-        <v>110.0090026855469</v>
+        <v>109.2959976196289</v>
       </c>
       <c r="F27" t="n">
-        <v>58634000</v>
+        <v>38718000</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -1145,22 +1145,22 @@
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>45965</v>
+        <v>45966</v>
       </c>
       <c r="B28" t="n">
-        <v>109.9990005493164</v>
+        <v>108.5</v>
       </c>
       <c r="C28" t="n">
-        <v>110.4599990844727</v>
+        <v>110.0849990844727</v>
       </c>
       <c r="D28" t="n">
-        <v>108.6679992675781</v>
+        <v>107.3369979858398</v>
       </c>
       <c r="E28" t="n">
-        <v>109.2959976196289</v>
+        <v>109.8460006713867</v>
       </c>
       <c r="F28" t="n">
-        <v>38718000</v>
+        <v>35539000</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
@@ -1171,22 +1171,22 @@
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>45966</v>
+        <v>45967</v>
       </c>
       <c r="B29" t="n">
-        <v>108.5</v>
+        <v>109.4580001831055</v>
       </c>
       <c r="C29" t="n">
-        <v>110.0849990844727</v>
+        <v>110.370002746582</v>
       </c>
       <c r="D29" t="n">
-        <v>107.3369979858398</v>
+        <v>108.5130004882812</v>
       </c>
       <c r="E29" t="n">
-        <v>109.8460006713867</v>
+        <v>109.7020034790039</v>
       </c>
       <c r="F29" t="n">
-        <v>35539000</v>
+        <v>36532000</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -1197,22 +1197,22 @@
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>45967</v>
+        <v>45968</v>
       </c>
       <c r="B30" t="n">
-        <v>109.4580001831055</v>
+        <v>109.4179992675781</v>
       </c>
       <c r="C30" t="n">
-        <v>110.370002746582</v>
+        <v>110.8219985961914</v>
       </c>
       <c r="D30" t="n">
-        <v>108.5130004882812</v>
+        <v>108.75</v>
       </c>
       <c r="E30" t="n">
-        <v>109.7020034790039</v>
+        <v>110.3659973144531</v>
       </c>
       <c r="F30" t="n">
-        <v>36532000</v>
+        <v>44125000</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -1223,22 +1223,22 @@
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>45968</v>
+        <v>45971</v>
       </c>
       <c r="B31" t="n">
-        <v>109.4179992675781</v>
+        <v>110.6719970703125</v>
       </c>
       <c r="C31" t="n">
-        <v>110.8219985961914</v>
+        <v>112.8199996948242</v>
       </c>
       <c r="D31" t="n">
-        <v>108.75</v>
+        <v>110.4049987792969</v>
       </c>
       <c r="E31" t="n">
-        <v>110.3659973144531</v>
+        <v>112.0070037841797</v>
       </c>
       <c r="F31" t="n">
-        <v>44125000</v>
+        <v>36929000</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -1249,22 +1249,22 @@
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>45971</v>
+        <v>45972</v>
       </c>
       <c r="B32" t="n">
-        <v>110.6719970703125</v>
+        <v>111.7600021362305</v>
       </c>
       <c r="C32" t="n">
-        <v>112.8199996948242</v>
+        <v>113.9219970703125</v>
       </c>
       <c r="D32" t="n">
-        <v>110.4049987792969</v>
+        <v>111.2799987792969</v>
       </c>
       <c r="E32" t="n">
-        <v>112.0070037841797</v>
+        <v>113.6439971923828</v>
       </c>
       <c r="F32" t="n">
-        <v>36929000</v>
+        <v>27966000</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
@@ -1275,22 +1275,22 @@
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>45972</v>
+        <v>45973</v>
       </c>
       <c r="B33" t="n">
-        <v>111.7600021362305</v>
+        <v>113.8170013427734</v>
       </c>
       <c r="C33" t="n">
-        <v>113.9219970703125</v>
+        <v>116.4339981079102</v>
       </c>
       <c r="D33" t="n">
-        <v>111.2799987792969</v>
+        <v>112.8259963989258</v>
       </c>
       <c r="E33" t="n">
-        <v>113.6439971923828</v>
+        <v>115.75</v>
       </c>
       <c r="F33" t="n">
-        <v>27966000</v>
+        <v>39221000</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -1301,22 +1301,22 @@
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>45973</v>
+        <v>45974</v>
       </c>
       <c r="B34" t="n">
-        <v>113.8170013427734</v>
+        <v>115.8499984741211</v>
       </c>
       <c r="C34" t="n">
-        <v>116.4339981079102</v>
+        <v>116.7330017089844</v>
       </c>
       <c r="D34" t="n">
-        <v>112.8259963989258</v>
+        <v>114.5690002441406</v>
       </c>
       <c r="E34" t="n">
-        <v>115.75</v>
+        <v>115.4229965209961</v>
       </c>
       <c r="F34" t="n">
-        <v>39221000</v>
+        <v>40144000</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
@@ -1327,22 +1327,22 @@
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>45974</v>
+        <v>45975</v>
       </c>
       <c r="B35" t="n">
-        <v>115.8499984741211</v>
+        <v>114.2730026245117</v>
       </c>
       <c r="C35" t="n">
-        <v>116.7330017089844</v>
+        <v>114.2730026245117</v>
       </c>
       <c r="D35" t="n">
-        <v>114.5690002441406</v>
+        <v>110.7210006713867</v>
       </c>
       <c r="E35" t="n">
-        <v>115.4229965209961</v>
+        <v>111.2170028686523</v>
       </c>
       <c r="F35" t="n">
-        <v>40144000</v>
+        <v>47607000</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
@@ -1353,74 +1353,74 @@
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>45975</v>
+        <v>45978</v>
       </c>
       <c r="B36" t="n">
-        <v>114.2730026245117</v>
+        <v>110.75</v>
       </c>
       <c r="C36" t="n">
-        <v>114.2730026245117</v>
+        <v>111.8499984741211</v>
       </c>
       <c r="D36" t="n">
-        <v>110.7210006713867</v>
+        <v>109.5500030517578</v>
       </c>
       <c r="E36" t="n">
-        <v>111.2170028686523</v>
+        <v>110.2900009155273</v>
       </c>
       <c r="F36" t="n">
-        <v>47607000</v>
+        <v>26082700</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>45978</v>
+        <v>45979</v>
       </c>
       <c r="B37" t="n">
-        <v>110.75</v>
+        <v>110.2900009155273</v>
       </c>
       <c r="C37" t="n">
-        <v>111.8499984741211</v>
+        <v>115.25</v>
       </c>
       <c r="D37" t="n">
-        <v>109.5500030517578</v>
+        <v>109.1999969482422</v>
       </c>
       <c r="E37" t="n">
-        <v>110.2900009155273</v>
+        <v>114.0899963378906</v>
       </c>
       <c r="F37" t="n">
-        <v>26082700</v>
+        <v>43440600</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>45979</v>
+        <v>45980</v>
       </c>
       <c r="B38" t="n">
-        <v>110.2900009155273</v>
+        <v>113</v>
       </c>
       <c r="C38" t="n">
-        <v>115.25</v>
+        <v>113.3399963378906</v>
       </c>
       <c r="D38" t="n">
-        <v>109.1999969482422</v>
+        <v>108.6100006103516</v>
       </c>
       <c r="E38" t="n">
-        <v>114.0899963378906</v>
+        <v>110</v>
       </c>
       <c r="F38" t="n">
-        <v>43440600</v>
+        <v>31868100</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
@@ -1431,22 +1431,22 @@
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>45980</v>
+        <v>45981</v>
       </c>
       <c r="B39" t="n">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C39" t="n">
-        <v>113.3399963378906</v>
+        <v>111.0999984741211</v>
       </c>
       <c r="D39" t="n">
-        <v>108.6100006103516</v>
+        <v>105.3899993896484</v>
       </c>
       <c r="E39" t="n">
-        <v>110</v>
+        <v>105.6699981689453</v>
       </c>
       <c r="F39" t="n">
-        <v>31868100</v>
+        <v>36918500</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
@@ -1457,22 +1457,22 @@
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>45981</v>
+        <v>45982</v>
       </c>
       <c r="B40" t="n">
-        <v>111</v>
+        <v>105.129997253418</v>
       </c>
       <c r="C40" t="n">
-        <v>111.0999984741211</v>
+        <v>106.5299987792969</v>
       </c>
       <c r="D40" t="n">
-        <v>105.3899993896484</v>
+        <v>103.8099975585938</v>
       </c>
       <c r="E40" t="n">
-        <v>105.6699981689453</v>
+        <v>104.3099975585938</v>
       </c>
       <c r="F40" t="n">
-        <v>36918500</v>
+        <v>41232700</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
@@ -1483,22 +1483,22 @@
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>45982</v>
+        <v>45985</v>
       </c>
       <c r="B41" t="n">
-        <v>105.129997253418</v>
+        <v>104.25</v>
       </c>
       <c r="C41" t="n">
-        <v>106.5299987792969</v>
+        <v>108.0400009155273</v>
       </c>
       <c r="D41" t="n">
-        <v>103.8099975585938</v>
+        <v>103.3199996948242</v>
       </c>
       <c r="E41" t="n">
-        <v>104.3099975585938</v>
+        <v>106.9700012207031</v>
       </c>
       <c r="F41" t="n">
-        <v>41232700</v>
+        <v>62918300</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
@@ -1509,22 +1509,22 @@
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>45985</v>
+        <v>45986</v>
       </c>
       <c r="B42" t="n">
-        <v>104.25</v>
+        <v>106.120002746582</v>
       </c>
       <c r="C42" t="n">
-        <v>108.0400009155273</v>
+        <v>106.3000030517578</v>
       </c>
       <c r="D42" t="n">
-        <v>103.3199996948242</v>
+        <v>103.8199996948242</v>
       </c>
       <c r="E42" t="n">
-        <v>106.9700012207031</v>
+        <v>104.4000015258789</v>
       </c>
       <c r="F42" t="n">
-        <v>62918300</v>
+        <v>35122600</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
@@ -1535,22 +1535,22 @@
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>45986</v>
+        <v>45987</v>
       </c>
       <c r="B43" t="n">
-        <v>106.120002746582</v>
+        <v>105.7399978637695</v>
       </c>
       <c r="C43" t="n">
-        <v>106.3000030517578</v>
+        <v>106.9499969482422</v>
       </c>
       <c r="D43" t="n">
-        <v>103.8199996948242</v>
+        <v>105.2200012207031</v>
       </c>
       <c r="E43" t="n">
-        <v>104.4000015258789</v>
+        <v>106.1399993896484</v>
       </c>
       <c r="F43" t="n">
-        <v>35122600</v>
+        <v>27951000</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
@@ -1561,22 +1561,22 @@
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
-        <v>45987</v>
+        <v>45989</v>
       </c>
       <c r="B44" t="n">
-        <v>105.7399978637695</v>
+        <v>106.4400024414062</v>
       </c>
       <c r="C44" t="n">
-        <v>106.9499969482422</v>
+        <v>107.9400024414062</v>
       </c>
       <c r="D44" t="n">
-        <v>105.2200012207031</v>
+        <v>106.2399978637695</v>
       </c>
       <c r="E44" t="n">
-        <v>106.1399993896484</v>
+        <v>107.5800018310547</v>
       </c>
       <c r="F44" t="n">
-        <v>27951000</v>
+        <v>15021600</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
@@ -1587,22 +1587,22 @@
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
-        <v>45989</v>
+        <v>45992</v>
       </c>
       <c r="B45" t="n">
-        <v>106.4400024414062</v>
+        <v>106.5100021362305</v>
       </c>
       <c r="C45" t="n">
-        <v>107.9400024414062</v>
+        <v>109.3399963378906</v>
       </c>
       <c r="D45" t="n">
-        <v>106.2399978637695</v>
+        <v>106.3099975585938</v>
       </c>
       <c r="E45" t="n">
-        <v>107.5800018310547</v>
+        <v>109.129997253418</v>
       </c>
       <c r="F45" t="n">
-        <v>15021600</v>
+        <v>24873400</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
@@ -1613,22 +1613,22 @@
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
-        <v>45992</v>
+        <v>45993</v>
       </c>
       <c r="B46" t="n">
-        <v>106.5100021362305</v>
+        <v>109.2099990844727</v>
       </c>
       <c r="C46" t="n">
-        <v>109.3399963378906</v>
+        <v>109.7300033569336</v>
       </c>
       <c r="D46" t="n">
-        <v>106.3099975585938</v>
+        <v>107.5199966430664</v>
       </c>
       <c r="E46" t="n">
-        <v>109.129997253418</v>
+        <v>109.3499984741211</v>
       </c>
       <c r="F46" t="n">
-        <v>24873400</v>
+        <v>25763000</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
@@ -1639,22 +1639,22 @@
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
-        <v>45993</v>
+        <v>45994</v>
       </c>
       <c r="B47" t="n">
-        <v>109.2099990844727</v>
+        <v>106.5899963378906</v>
       </c>
       <c r="C47" t="n">
-        <v>109.7300033569336</v>
+        <v>106.870002746582</v>
       </c>
       <c r="D47" t="n">
-        <v>107.5199966430664</v>
+        <v>102.0299987792969</v>
       </c>
       <c r="E47" t="n">
-        <v>109.3499984741211</v>
+        <v>103.9599990844727</v>
       </c>
       <c r="F47" t="n">
-        <v>25763000</v>
+        <v>53593400</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
@@ -1665,22 +1665,22 @@
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
-        <v>45994</v>
+        <v>45995</v>
       </c>
       <c r="B48" t="n">
-        <v>106.5899963378906</v>
+        <v>103.5699996948242</v>
       </c>
       <c r="C48" t="n">
-        <v>106.870002746582</v>
+        <v>103.8000030517578</v>
       </c>
       <c r="D48" t="n">
-        <v>102.0299987792969</v>
+        <v>101.7699966430664</v>
       </c>
       <c r="E48" t="n">
-        <v>103.9599990844727</v>
+        <v>103.2200012207031</v>
       </c>
       <c r="F48" t="n">
-        <v>53593400</v>
+        <v>51779100</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
@@ -1691,22 +1691,22 @@
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>45995</v>
+        <v>45996</v>
       </c>
       <c r="B49" t="n">
-        <v>103.5699996948242</v>
+        <v>98.77999877929688</v>
       </c>
       <c r="C49" t="n">
-        <v>103.8000030517578</v>
+        <v>104.7900009155273</v>
       </c>
       <c r="D49" t="n">
-        <v>101.7699966430664</v>
+        <v>97.73999786376953</v>
       </c>
       <c r="E49" t="n">
-        <v>103.2200012207031</v>
+        <v>100.2399978637695</v>
       </c>
       <c r="F49" t="n">
-        <v>51779100</v>
+        <v>133363600</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
@@ -1717,22 +1717,22 @@
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>45996</v>
+        <v>45999</v>
       </c>
       <c r="B50" t="n">
-        <v>98.77999877929688</v>
+        <v>99.87000274658203</v>
       </c>
       <c r="C50" t="n">
-        <v>104.7900009155273</v>
+        <v>99.88999938964844</v>
       </c>
       <c r="D50" t="n">
-        <v>97.73999786376953</v>
+        <v>95.30000305175781</v>
       </c>
       <c r="E50" t="n">
-        <v>100.2399978637695</v>
+        <v>96.79000091552734</v>
       </c>
       <c r="F50" t="n">
-        <v>133363600</v>
+        <v>100906300</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
-        <v>45999</v>
+        <v>46000</v>
       </c>
       <c r="B51" t="n">
-        <v>99.87000274658203</v>
+        <v>97.02999877929688</v>
       </c>
       <c r="C51" t="n">
-        <v>99.88999938964844</v>
+        <v>97.23999786376953</v>
       </c>
       <c r="D51" t="n">
-        <v>95.30000305175781</v>
+        <v>95.44999694824219</v>
       </c>
       <c r="E51" t="n">
-        <v>96.79000091552734</v>
+        <v>96.70999908447266</v>
       </c>
       <c r="F51" t="n">
-        <v>100906300</v>
+        <v>51745600</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
@@ -1769,22 +1769,22 @@
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
-        <v>46000</v>
+        <v>46001</v>
       </c>
       <c r="B52" t="n">
-        <v>97.02999877929688</v>
+        <v>96.73999786376953</v>
       </c>
       <c r="C52" t="n">
-        <v>97.23999786376953</v>
+        <v>96.97000122070312</v>
       </c>
       <c r="D52" t="n">
-        <v>95.44999694824219</v>
+        <v>92.34999847412109</v>
       </c>
       <c r="E52" t="n">
-        <v>96.70999908447266</v>
+        <v>92.70999908447266</v>
       </c>
       <c r="F52" t="n">
-        <v>51745600</v>
+        <v>74129300</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
@@ -1795,22 +1795,22 @@
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
-        <v>46001</v>
+        <v>46002</v>
       </c>
       <c r="B53" t="n">
-        <v>96.73999786376953</v>
+        <v>93.90000152587891</v>
       </c>
       <c r="C53" t="n">
-        <v>96.97000122070312</v>
+        <v>94.81999969482422</v>
       </c>
       <c r="D53" t="n">
-        <v>92.34999847412109</v>
+        <v>92.76000213623047</v>
       </c>
       <c r="E53" t="n">
-        <v>92.70999908447266</v>
+        <v>94.08999633789062</v>
       </c>
       <c r="F53" t="n">
-        <v>74129300</v>
+        <v>43949000</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
@@ -1821,22 +1821,22 @@
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
-        <v>46002</v>
+        <v>46003</v>
       </c>
       <c r="B54" t="n">
-        <v>93.90000152587891</v>
+        <v>95.5</v>
       </c>
       <c r="C54" t="n">
-        <v>94.81999969482422</v>
+        <v>96.91999816894531</v>
       </c>
       <c r="D54" t="n">
-        <v>92.76000213623047</v>
+        <v>94.65000152587891</v>
       </c>
       <c r="E54" t="n">
-        <v>94.08999633789062</v>
+        <v>95.19000244140625</v>
       </c>
       <c r="F54" t="n">
-        <v>43949000</v>
+        <v>49323100</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
@@ -1847,22 +1847,22 @@
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
-        <v>46003</v>
+        <v>46006</v>
       </c>
       <c r="B55" t="n">
-        <v>95.5</v>
+        <v>96.01999664306641</v>
       </c>
       <c r="C55" t="n">
-        <v>96.91999816894531</v>
+        <v>96.37000274658203</v>
       </c>
       <c r="D55" t="n">
-        <v>94.65000152587891</v>
+        <v>93.52999877929688</v>
       </c>
       <c r="E55" t="n">
-        <v>95.19000244140625</v>
+        <v>93.76999664306641</v>
       </c>
       <c r="F55" t="n">
-        <v>49323100</v>
+        <v>40016500</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
@@ -1873,22 +1873,22 @@
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
-        <v>46006</v>
+        <v>46007</v>
       </c>
       <c r="B56" t="n">
-        <v>96.01999664306641</v>
+        <v>93.87999725341797</v>
       </c>
       <c r="C56" t="n">
-        <v>96.37000274658203</v>
+        <v>94.93000030517578</v>
       </c>
       <c r="D56" t="n">
-        <v>93.52999877929688</v>
+        <v>93.31999969482422</v>
       </c>
       <c r="E56" t="n">
-        <v>93.76999664306641</v>
+        <v>94.56999969482422</v>
       </c>
       <c r="F56" t="n">
-        <v>40016500</v>
+        <v>34265000</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
@@ -1899,22 +1899,22 @@
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
-        <v>46007</v>
+        <v>46008</v>
       </c>
       <c r="B57" t="n">
-        <v>93.87999725341797</v>
+        <v>95.98000335693359</v>
       </c>
       <c r="C57" t="n">
-        <v>94.93000030517578</v>
+        <v>97.33000183105469</v>
       </c>
       <c r="D57" t="n">
-        <v>93.31999969482422</v>
+        <v>94.45999908447266</v>
       </c>
       <c r="E57" t="n">
-        <v>94.56999969482422</v>
+        <v>94.79000091552734</v>
       </c>
       <c r="F57" t="n">
-        <v>34265000</v>
+        <v>50472800</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
@@ -1925,22 +1925,22 @@
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
-        <v>46008</v>
+        <v>46009</v>
       </c>
       <c r="B58" t="n">
-        <v>95.98000335693359</v>
+        <v>95.01999664306641</v>
       </c>
       <c r="C58" t="n">
-        <v>97.33000183105469</v>
+        <v>95.80999755859375</v>
       </c>
       <c r="D58" t="n">
-        <v>94.45999908447266</v>
+        <v>93.58999633789062</v>
       </c>
       <c r="E58" t="n">
-        <v>94.79000091552734</v>
+        <v>94</v>
       </c>
       <c r="F58" t="n">
-        <v>50472800</v>
+        <v>37244700</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
@@ -1951,22 +1951,22 @@
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
-        <v>46009</v>
+        <v>46010</v>
       </c>
       <c r="B59" t="n">
-        <v>95.01999664306641</v>
+        <v>93.56999969482422</v>
       </c>
       <c r="C59" t="n">
-        <v>95.80999755859375</v>
+        <v>95.54000091552734</v>
       </c>
       <c r="D59" t="n">
-        <v>93.58999633789062</v>
+        <v>93.44999694824219</v>
       </c>
       <c r="E59" t="n">
-        <v>94</v>
+        <v>94.38999938964844</v>
       </c>
       <c r="F59" t="n">
-        <v>37244700</v>
+        <v>78990200</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
@@ -1977,22 +1977,22 @@
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
-        <v>46010</v>
+        <v>46013</v>
       </c>
       <c r="B60" t="n">
-        <v>93.56999969482422</v>
+        <v>94.70999908447266</v>
       </c>
       <c r="C60" t="n">
-        <v>95.54000091552734</v>
+        <v>94.70999908447266</v>
       </c>
       <c r="D60" t="n">
-        <v>93.44999694824219</v>
+        <v>92.91000366210938</v>
       </c>
       <c r="E60" t="n">
-        <v>94.38999938964844</v>
+        <v>93.23000335693359</v>
       </c>
       <c r="F60" t="n">
-        <v>78990200</v>
+        <v>39484800</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
@@ -2003,22 +2003,22 @@
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
-        <v>46013</v>
+        <v>46014</v>
       </c>
       <c r="B61" t="n">
-        <v>94.70999908447266</v>
+        <v>93.40000152587891</v>
       </c>
       <c r="C61" t="n">
-        <v>94.70999908447266</v>
+        <v>93.80999755859375</v>
       </c>
       <c r="D61" t="n">
-        <v>92.91000366210938</v>
+        <v>91.33000183105469</v>
       </c>
       <c r="E61" t="n">
-        <v>93.23000335693359</v>
+        <v>93.5</v>
       </c>
       <c r="F61" t="n">
-        <v>39484800</v>
+        <v>25896200</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
@@ -2029,22 +2029,22 @@
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
-        <v>46014</v>
+        <v>46015</v>
       </c>
       <c r="B62" t="n">
-        <v>93.40000152587891</v>
+        <v>93.11000061035156</v>
       </c>
       <c r="C62" t="n">
-        <v>93.80999755859375</v>
+        <v>93.68000030517578</v>
       </c>
       <c r="D62" t="n">
-        <v>91.33000183105469</v>
+        <v>92.66999816894531</v>
       </c>
       <c r="E62" t="n">
-        <v>93.5</v>
+        <v>93.63999938964844</v>
       </c>
       <c r="F62" t="n">
-        <v>25896200</v>
+        <v>12427900</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
@@ -2055,22 +2055,22 @@
     </row>
     <row r="63">
       <c r="A63" s="1" t="n">
-        <v>46015</v>
+        <v>46017</v>
       </c>
       <c r="B63" t="n">
-        <v>93.11000061035156</v>
+        <v>93.48000335693359</v>
       </c>
       <c r="C63" t="n">
-        <v>93.68000030517578</v>
+        <v>94.69000244140625</v>
       </c>
       <c r="D63" t="n">
-        <v>92.66999816894531</v>
+        <v>93.26999664306641</v>
       </c>
       <c r="E63" t="n">
-        <v>93.63999938964844</v>
+        <v>94.47000122070312</v>
       </c>
       <c r="F63" t="n">
-        <v>12427900</v>
+        <v>22068300</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
@@ -2081,22 +2081,22 @@
     </row>
     <row r="64">
       <c r="A64" s="1" t="n">
-        <v>46017</v>
+        <v>46020</v>
       </c>
       <c r="B64" t="n">
-        <v>93.48000335693359</v>
+        <v>93.98999786376953</v>
       </c>
       <c r="C64" t="n">
-        <v>94.69000244140625</v>
+        <v>94.97000122070312</v>
       </c>
       <c r="D64" t="n">
-        <v>93.26999664306641</v>
+        <v>93.62999725341797</v>
       </c>
       <c r="E64" t="n">
-        <v>94.47000122070312</v>
+        <v>94.15000152587891</v>
       </c>
       <c r="F64" t="n">
-        <v>22068300</v>
+        <v>24493700</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
@@ -2107,22 +2107,22 @@
     </row>
     <row r="65">
       <c r="A65" s="1" t="n">
-        <v>46020</v>
+        <v>46021</v>
       </c>
       <c r="B65" t="n">
+        <v>93.51999664306641</v>
+      </c>
+      <c r="C65" t="n">
         <v>93.98999786376953</v>
       </c>
-      <c r="C65" t="n">
-        <v>94.97000122070312</v>
-      </c>
       <c r="D65" t="n">
-        <v>93.62999725341797</v>
+        <v>93.33999633789062</v>
       </c>
       <c r="E65" t="n">
-        <v>94.15000152587891</v>
+        <v>93.77999877929688</v>
       </c>
       <c r="F65" t="n">
-        <v>24493700</v>
+        <v>23422000</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
@@ -2133,22 +2133,22 @@
     </row>
     <row r="66">
       <c r="A66" s="1" t="n">
-        <v>46021</v>
+        <v>46022</v>
       </c>
       <c r="B66" t="n">
-        <v>93.51999664306641</v>
+        <v>93.59999847412109</v>
       </c>
       <c r="C66" t="n">
-        <v>93.98999786376953</v>
+        <v>94.30999755859375</v>
       </c>
       <c r="D66" t="n">
-        <v>93.33999633789062</v>
+        <v>93.19999694824219</v>
       </c>
       <c r="E66" t="n">
-        <v>93.77999877929688</v>
+        <v>93.76000213623047</v>
       </c>
       <c r="F66" t="n">
-        <v>23422000</v>
+        <v>23495200</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
@@ -2159,22 +2159,22 @@
     </row>
     <row r="67">
       <c r="A67" s="1" t="n">
-        <v>46022</v>
+        <v>46024</v>
       </c>
       <c r="B67" t="n">
-        <v>93.59999847412109</v>
+        <v>94.12999725341797</v>
       </c>
       <c r="C67" t="n">
-        <v>94.30999755859375</v>
+        <v>94.12999725341797</v>
       </c>
       <c r="D67" t="n">
-        <v>93.19999694824219</v>
+        <v>90.80999755859375</v>
       </c>
       <c r="E67" t="n">
-        <v>93.76000213623047</v>
+        <v>90.98999786376953</v>
       </c>
       <c r="F67" t="n">
-        <v>23495200</v>
+        <v>41155400</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
@@ -2185,22 +2185,22 @@
     </row>
     <row r="68">
       <c r="A68" s="1" t="n">
-        <v>46024</v>
+        <v>46027</v>
       </c>
       <c r="B68" t="n">
-        <v>94.12999725341797</v>
+        <v>90.91999816894531</v>
       </c>
       <c r="C68" t="n">
-        <v>94.12999725341797</v>
+        <v>92.62999725341797</v>
       </c>
       <c r="D68" t="n">
-        <v>90.80999755859375</v>
+        <v>90.83999633789062</v>
       </c>
       <c r="E68" t="n">
-        <v>90.98999786376953</v>
+        <v>91.45999908447266</v>
       </c>
       <c r="F68" t="n">
-        <v>41155400</v>
+        <v>39183300</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
@@ -2211,22 +2211,22 @@
     </row>
     <row r="69">
       <c r="A69" s="1" t="n">
-        <v>46027</v>
+        <v>46028</v>
       </c>
       <c r="B69" t="n">
-        <v>90.91999816894531</v>
+        <v>91.54000091552734</v>
       </c>
       <c r="C69" t="n">
-        <v>92.62999725341797</v>
+        <v>91.63999938964844</v>
       </c>
       <c r="D69" t="n">
-        <v>90.83999633789062</v>
+        <v>89.73999786376953</v>
       </c>
       <c r="E69" t="n">
-        <v>91.45999908447266</v>
+        <v>90.65000152587891</v>
       </c>
       <c r="F69" t="n">
-        <v>39183300</v>
+        <v>43331000</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
@@ -2237,22 +2237,22 @@
     </row>
     <row r="70">
       <c r="A70" s="1" t="n">
-        <v>46028</v>
+        <v>46029</v>
       </c>
       <c r="B70" t="n">
-        <v>91.54000091552734</v>
+        <v>91.55999755859375</v>
       </c>
       <c r="C70" t="n">
-        <v>91.63999938964844</v>
+        <v>92.41999816894531</v>
       </c>
       <c r="D70" t="n">
-        <v>89.73999786376953</v>
+        <v>90.05999755859375</v>
       </c>
       <c r="E70" t="n">
-        <v>90.65000152587891</v>
+        <v>90.73000335693359</v>
       </c>
       <c r="F70" t="n">
-        <v>43331000</v>
+        <v>36525700</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
@@ -2263,22 +2263,22 @@
     </row>
     <row r="71">
       <c r="A71" s="1" t="n">
-        <v>46029</v>
+        <v>46030</v>
       </c>
       <c r="B71" t="n">
-        <v>91.55999755859375</v>
+        <v>90.44999694824219</v>
       </c>
       <c r="C71" t="n">
-        <v>92.41999816894531</v>
+        <v>91.25</v>
       </c>
       <c r="D71" t="n">
-        <v>90.05999755859375</v>
+        <v>89.58000183105469</v>
       </c>
       <c r="E71" t="n">
-        <v>90.73000335693359</v>
+        <v>90.52999877929688</v>
       </c>
       <c r="F71" t="n">
-        <v>36525700</v>
+        <v>40068700</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
@@ -2289,22 +2289,22 @@
     </row>
     <row r="72">
       <c r="A72" s="1" t="n">
-        <v>46030</v>
+        <v>46031</v>
       </c>
       <c r="B72" t="n">
-        <v>90.44999694824219</v>
+        <v>90.02999877929688</v>
       </c>
       <c r="C72" t="n">
-        <v>91.25</v>
+        <v>90.05000305175781</v>
       </c>
       <c r="D72" t="n">
-        <v>89.58000183105469</v>
+        <v>88.31999969482422</v>
       </c>
       <c r="E72" t="n">
-        <v>90.52999877929688</v>
+        <v>89.45999908447266</v>
       </c>
       <c r="F72" t="n">
-        <v>40068700</v>
+        <v>55579500</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
@@ -2315,22 +2315,22 @@
     </row>
     <row r="73">
       <c r="A73" s="1" t="n">
-        <v>46031</v>
+        <v>46034</v>
       </c>
       <c r="B73" t="n">
-        <v>90.02999877929688</v>
+        <v>89.69000244140625</v>
       </c>
       <c r="C73" t="n">
-        <v>90.05000305175781</v>
+        <v>90.33999633789062</v>
       </c>
       <c r="D73" t="n">
-        <v>88.31999969482422</v>
+        <v>89.33000183105469</v>
       </c>
       <c r="E73" t="n">
-        <v>89.45999908447266</v>
+        <v>89.41000366210938</v>
       </c>
       <c r="F73" t="n">
-        <v>55579500</v>
+        <v>36290600</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
@@ -2341,22 +2341,22 @@
     </row>
     <row r="74">
       <c r="A74" s="1" t="n">
-        <v>46034</v>
+        <v>46035</v>
       </c>
       <c r="B74" t="n">
-        <v>89.69000244140625</v>
+        <v>89.44000244140625</v>
       </c>
       <c r="C74" t="n">
-        <v>90.33999633789062</v>
+        <v>91.15000152587891</v>
       </c>
       <c r="D74" t="n">
-        <v>89.33000183105469</v>
+        <v>89.06999969482422</v>
       </c>
       <c r="E74" t="n">
-        <v>89.41000366210938</v>
+        <v>90.31999969482422</v>
       </c>
       <c r="F74" t="n">
-        <v>36290600</v>
+        <v>45221100</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
@@ -2367,22 +2367,22 @@
     </row>
     <row r="75">
       <c r="A75" s="1" t="n">
-        <v>46035</v>
+        <v>46036</v>
       </c>
       <c r="B75" t="n">
-        <v>89.44000244140625</v>
+        <v>91.23999786376953</v>
       </c>
       <c r="C75" t="n">
-        <v>91.15000152587891</v>
+        <v>91.58000183105469</v>
       </c>
       <c r="D75" t="n">
-        <v>89.06999969482422</v>
+        <v>87.94999694824219</v>
       </c>
       <c r="E75" t="n">
-        <v>90.31999969482422</v>
+        <v>88.55000305175781</v>
       </c>
       <c r="F75" t="n">
-        <v>45221100</v>
+        <v>49737700</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
@@ -2393,22 +2393,22 @@
     </row>
     <row r="76">
       <c r="A76" s="1" t="n">
-        <v>46036</v>
+        <v>46037</v>
       </c>
       <c r="B76" t="n">
-        <v>91.23999786376953</v>
+        <v>89.01999664306641</v>
       </c>
       <c r="C76" t="n">
-        <v>91.58000183105469</v>
+        <v>89.88999938964844</v>
       </c>
       <c r="D76" t="n">
-        <v>87.94999694824219</v>
+        <v>87.81999969482422</v>
       </c>
       <c r="E76" t="n">
-        <v>88.55000305175781</v>
+        <v>88.05000305175781</v>
       </c>
       <c r="F76" t="n">
-        <v>49737700</v>
+        <v>36945100</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
@@ -2419,22 +2419,22 @@
     </row>
     <row r="77">
       <c r="A77" s="1" t="n">
-        <v>46037</v>
+        <v>46038</v>
       </c>
       <c r="B77" t="n">
-        <v>89.01999664306641</v>
+        <v>88.33999633789062</v>
       </c>
       <c r="C77" t="n">
-        <v>89.88999938964844</v>
+        <v>88.51000213623047</v>
       </c>
       <c r="D77" t="n">
-        <v>87.81999969482422</v>
+        <v>87.77999877929688</v>
       </c>
       <c r="E77" t="n">
-        <v>88.05000305175781</v>
+        <v>88</v>
       </c>
       <c r="F77" t="n">
-        <v>36945100</v>
+        <v>48130500</v>
       </c>
       <c r="G77" t="n">
         <v>0</v>
@@ -2445,22 +2445,22 @@
     </row>
     <row r="78">
       <c r="A78" s="1" t="n">
-        <v>46038</v>
+        <v>46042</v>
       </c>
       <c r="B78" t="n">
-        <v>88.33999633789062</v>
+        <v>88.97000122070312</v>
       </c>
       <c r="C78" t="n">
-        <v>88.51000213623047</v>
+        <v>89.90000152587891</v>
       </c>
       <c r="D78" t="n">
-        <v>87.77999877929688</v>
+        <v>87.01999664306641</v>
       </c>
       <c r="E78" t="n">
-        <v>88</v>
+        <v>87.26000213623047</v>
       </c>
       <c r="F78" t="n">
-        <v>48130500</v>
+        <v>109729700</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
@@ -2471,22 +2471,22 @@
     </row>
     <row r="79">
       <c r="A79" s="1" t="n">
-        <v>46042</v>
+        <v>46043</v>
       </c>
       <c r="B79" t="n">
-        <v>88.97000122070312</v>
+        <v>82.51999664306641</v>
       </c>
       <c r="C79" t="n">
-        <v>89.90000152587891</v>
+        <v>86</v>
       </c>
       <c r="D79" t="n">
-        <v>87.01999664306641</v>
+        <v>81.93000030517578</v>
       </c>
       <c r="E79" t="n">
-        <v>87.26000213623047</v>
+        <v>85.36000061035156</v>
       </c>
       <c r="F79" t="n">
-        <v>109729700</v>
+        <v>127940700</v>
       </c>
       <c r="G79" t="n">
         <v>0</v>
@@ -2497,22 +2497,22 @@
     </row>
     <row r="80">
       <c r="A80" s="1" t="n">
-        <v>46043</v>
+        <v>46044</v>
       </c>
       <c r="B80" t="n">
-        <v>82.51999664306641</v>
+        <v>85.01999664306641</v>
       </c>
       <c r="C80" t="n">
-        <v>86</v>
+        <v>85.09999847412109</v>
       </c>
       <c r="D80" t="n">
-        <v>81.93000030517578</v>
+        <v>82.98000335693359</v>
       </c>
       <c r="E80" t="n">
-        <v>85.36000061035156</v>
+        <v>83.54000091552734</v>
       </c>
       <c r="F80" t="n">
-        <v>127940700</v>
+        <v>69113300</v>
       </c>
       <c r="G80" t="n">
         <v>0</v>
@@ -2523,22 +2523,22 @@
     </row>
     <row r="81">
       <c r="A81" s="1" t="n">
-        <v>46044</v>
+        <v>46045</v>
       </c>
       <c r="B81" t="n">
-        <v>85.01999664306641</v>
+        <v>83.43000030517578</v>
       </c>
       <c r="C81" t="n">
-        <v>85.09999847412109</v>
+        <v>86.30000305175781</v>
       </c>
       <c r="D81" t="n">
-        <v>82.98000335693359</v>
+        <v>83.27999877929688</v>
       </c>
       <c r="E81" t="n">
-        <v>83.54000091552734</v>
+        <v>86.12000274658203</v>
       </c>
       <c r="F81" t="n">
-        <v>69113300</v>
+        <v>64520400</v>
       </c>
       <c r="G81" t="n">
         <v>0</v>
@@ -2549,22 +2549,22 @@
     </row>
     <row r="82">
       <c r="A82" s="1" t="n">
-        <v>46045</v>
+        <v>46048</v>
       </c>
       <c r="B82" t="n">
-        <v>83.43000030517578</v>
+        <v>86.91999816894531</v>
       </c>
       <c r="C82" t="n">
-        <v>86.30000305175781</v>
+        <v>86.94000244140625</v>
       </c>
       <c r="D82" t="n">
-        <v>83.27999877929688</v>
+        <v>85.34999847412109</v>
       </c>
       <c r="E82" t="n">
-        <v>86.12000274658203</v>
+        <v>85.69999694824219</v>
       </c>
       <c r="F82" t="n">
-        <v>64520400</v>
+        <v>40941900</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
@@ -2575,22 +2575,22 @@
     </row>
     <row r="83">
       <c r="A83" s="1" t="n">
-        <v>46048</v>
+        <v>46049</v>
       </c>
       <c r="B83" t="n">
-        <v>86.91999816894531</v>
+        <v>85.27999877929688</v>
       </c>
       <c r="C83" t="n">
-        <v>86.94000244140625</v>
+        <v>85.59999847412109</v>
       </c>
       <c r="D83" t="n">
-        <v>85.34999847412109</v>
+        <v>83.87999725341797</v>
       </c>
       <c r="E83" t="n">
-        <v>85.69999694824219</v>
+        <v>85.58000183105469</v>
       </c>
       <c r="F83" t="n">
-        <v>40941900</v>
+        <v>37790800</v>
       </c>
       <c r="G83" t="n">
         <v>0</v>
@@ -2601,22 +2601,22 @@
     </row>
     <row r="84">
       <c r="A84" s="1" t="n">
-        <v>46049</v>
+        <v>46050</v>
       </c>
       <c r="B84" t="n">
-        <v>85.27999877929688</v>
+        <v>85.62999725341797</v>
       </c>
       <c r="C84" t="n">
-        <v>85.59999847412109</v>
+        <v>86.47000122070312</v>
       </c>
       <c r="D84" t="n">
-        <v>83.87999725341797</v>
+        <v>84.30000305175781</v>
       </c>
       <c r="E84" t="n">
-        <v>85.58000183105469</v>
+        <v>84.63999938964844</v>
       </c>
       <c r="F84" t="n">
-        <v>37790800</v>
+        <v>37762600</v>
       </c>
       <c r="G84" t="n">
         <v>0</v>
@@ -2627,22 +2627,22 @@
     </row>
     <row r="85">
       <c r="A85" s="1" t="n">
-        <v>46050</v>
+        <v>46051</v>
       </c>
       <c r="B85" t="n">
-        <v>85.62999725341797</v>
+        <v>84.30999755859375</v>
       </c>
       <c r="C85" t="n">
-        <v>86.47000122070312</v>
+        <v>84.37999725341797</v>
       </c>
       <c r="D85" t="n">
-        <v>84.30000305175781</v>
+        <v>82.34999847412109</v>
       </c>
       <c r="E85" t="n">
-        <v>84.63999938964844</v>
+        <v>83.16000366210938</v>
       </c>
       <c r="F85" t="n">
-        <v>37762600</v>
+        <v>42278100</v>
       </c>
       <c r="G85" t="n">
         <v>0</v>
@@ -2653,22 +2653,22 @@
     </row>
     <row r="86">
       <c r="A86" s="1" t="n">
-        <v>46051</v>
+        <v>46052</v>
       </c>
       <c r="B86" t="n">
-        <v>84.30999755859375</v>
+        <v>83.09999847412109</v>
       </c>
       <c r="C86" t="n">
-        <v>84.37999725341797</v>
+        <v>84.05999755859375</v>
       </c>
       <c r="D86" t="n">
-        <v>82.34999847412109</v>
+        <v>82.77999877929688</v>
       </c>
       <c r="E86" t="n">
-        <v>83.16000366210938</v>
+        <v>83.48999786376953</v>
       </c>
       <c r="F86" t="n">
-        <v>42278100</v>
+        <v>45755000</v>
       </c>
       <c r="G86" t="n">
         <v>0</v>
@@ -2679,22 +2679,22 @@
     </row>
     <row r="87">
       <c r="A87" s="1" t="n">
-        <v>46052</v>
+        <v>46055</v>
       </c>
       <c r="B87" t="n">
-        <v>83.09999847412109</v>
+        <v>83.52999877929688</v>
       </c>
       <c r="C87" t="n">
-        <v>84.05999755859375</v>
+        <v>85.26999664306641</v>
       </c>
       <c r="D87" t="n">
-        <v>82.77999877929688</v>
+        <v>82.72000122070312</v>
       </c>
       <c r="E87" t="n">
-        <v>83.48999786376953</v>
+        <v>82.76000213623047</v>
       </c>
       <c r="F87" t="n">
-        <v>45755000</v>
+        <v>41445300</v>
       </c>
       <c r="G87" t="n">
         <v>0</v>
@@ -2705,22 +2705,22 @@
     </row>
     <row r="88">
       <c r="A88" s="1" t="n">
-        <v>46055</v>
+        <v>46056</v>
       </c>
       <c r="B88" t="n">
-        <v>83.52999877929688</v>
+        <v>82.23000335693359</v>
       </c>
       <c r="C88" t="n">
-        <v>85.26999664306641</v>
+        <v>82.44999694824219</v>
       </c>
       <c r="D88" t="n">
-        <v>82.72000122070312</v>
+        <v>79.62000274658203</v>
       </c>
       <c r="E88" t="n">
-        <v>82.76000213623047</v>
+        <v>79.94000244140625</v>
       </c>
       <c r="F88" t="n">
-        <v>41445300</v>
+        <v>49789000</v>
       </c>
       <c r="G88" t="n">
         <v>0</v>
@@ -2731,22 +2731,22 @@
     </row>
     <row r="89">
       <c r="A89" s="1" t="n">
-        <v>46056</v>
+        <v>46057</v>
       </c>
       <c r="B89" t="n">
-        <v>82.23000335693359</v>
+        <v>79.98999786376953</v>
       </c>
       <c r="C89" t="n">
-        <v>82.44999694824219</v>
+        <v>81.44000244140625</v>
       </c>
       <c r="D89" t="n">
-        <v>79.62000274658203</v>
+        <v>79.23000335693359</v>
       </c>
       <c r="E89" t="n">
-        <v>79.94000244140625</v>
+        <v>80.16000366210938</v>
       </c>
       <c r="F89" t="n">
-        <v>49789000</v>
+        <v>48963200</v>
       </c>
       <c r="G89" t="n">
         <v>0</v>
@@ -2757,22 +2757,22 @@
     </row>
     <row r="90">
       <c r="A90" s="1" t="n">
-        <v>46057</v>
+        <v>46058</v>
       </c>
       <c r="B90" t="n">
-        <v>79.98999786376953</v>
+        <v>81.48999786376953</v>
       </c>
       <c r="C90" t="n">
-        <v>81.44000244140625</v>
+        <v>83.30000305175781</v>
       </c>
       <c r="D90" t="n">
-        <v>79.23000335693359</v>
+        <v>80.54000091552734</v>
       </c>
       <c r="E90" t="n">
-        <v>80.16000366210938</v>
+        <v>80.87000274658203</v>
       </c>
       <c r="F90" t="n">
-        <v>48963200</v>
+        <v>54805700</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
@@ -2783,22 +2783,22 @@
     </row>
     <row r="91">
       <c r="A91" s="1" t="n">
-        <v>46058</v>
+        <v>46059</v>
       </c>
       <c r="B91" t="n">
-        <v>81.48999786376953</v>
+        <v>81.01999664306641</v>
       </c>
       <c r="C91" t="n">
-        <v>83.30000305175781</v>
+        <v>82.48999786376953</v>
       </c>
       <c r="D91" t="n">
-        <v>80.54000091552734</v>
+        <v>80.65000152587891</v>
       </c>
       <c r="E91" t="n">
-        <v>80.87000274658203</v>
+        <v>82.19999694824219</v>
       </c>
       <c r="F91" t="n">
-        <v>54805700</v>
+        <v>46154100</v>
       </c>
       <c r="G91" t="n">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="92">
       <c r="A92" s="1" t="n">
-        <v>46059</v>
+        <v>46062</v>
       </c>
       <c r="B92" t="n">
-        <v>81.01999664306641</v>
+        <v>82.18000030517578</v>
       </c>
       <c r="C92" t="n">
-        <v>82.48999786376953</v>
+        <v>82.20999908447266</v>
       </c>
       <c r="D92" t="n">
-        <v>80.65000152587891</v>
+        <v>79.87000274658203</v>
       </c>
       <c r="E92" t="n">
-        <v>82.19999694824219</v>
+        <v>81.47000122070312</v>
       </c>
       <c r="F92" t="n">
-        <v>46154100</v>
+        <v>42200200</v>
       </c>
       <c r="G92" t="n">
         <v>0</v>
@@ -2835,22 +2835,22 @@
     </row>
     <row r="93">
       <c r="A93" s="1" t="n">
-        <v>46062</v>
+        <v>46063</v>
       </c>
       <c r="B93" t="n">
-        <v>82.18000030517578</v>
+        <v>82.72000122070312</v>
       </c>
       <c r="C93" t="n">
+        <v>84.66000366210938</v>
+      </c>
+      <c r="D93" t="n">
+        <v>82.08999633789062</v>
+      </c>
+      <c r="E93" t="n">
         <v>82.20999908447266</v>
       </c>
-      <c r="D93" t="n">
-        <v>79.87000274658203</v>
-      </c>
-      <c r="E93" t="n">
-        <v>81.47000122070312</v>
-      </c>
       <c r="F93" t="n">
-        <v>42200200</v>
+        <v>43595800</v>
       </c>
       <c r="G93" t="n">
         <v>0</v>
@@ -2861,22 +2861,22 @@
     </row>
     <row r="94">
       <c r="A94" s="1" t="n">
-        <v>46063</v>
+        <v>46064</v>
       </c>
       <c r="B94" t="n">
-        <v>82.72000122070312</v>
+        <v>81.95999908447266</v>
       </c>
       <c r="C94" t="n">
-        <v>84.66000366210938</v>
+        <v>82.48000335693359</v>
       </c>
       <c r="D94" t="n">
-        <v>82.08999633789062</v>
+        <v>79.44999694824219</v>
       </c>
       <c r="E94" t="n">
-        <v>82.20999908447266</v>
+        <v>79.62000274658203</v>
       </c>
       <c r="F94" t="n">
-        <v>43595800</v>
+        <v>40840300</v>
       </c>
       <c r="G94" t="n">
         <v>0</v>
@@ -2887,22 +2887,22 @@
     </row>
     <row r="95">
       <c r="A95" s="1" t="n">
-        <v>46064</v>
+        <v>46065</v>
       </c>
       <c r="B95" t="n">
-        <v>81.95999908447266</v>
+        <v>79.11000061035156</v>
       </c>
       <c r="C95" t="n">
-        <v>82.48000335693359</v>
+        <v>79.15000152587891</v>
       </c>
       <c r="D95" t="n">
-        <v>79.44999694824219</v>
+        <v>75.23000335693359</v>
       </c>
       <c r="E95" t="n">
-        <v>79.62000274658203</v>
+        <v>75.86000061035156</v>
       </c>
       <c r="F95" t="n">
-        <v>40840300</v>
+        <v>73516100</v>
       </c>
       <c r="G95" t="n">
         <v>0</v>
@@ -2913,22 +2913,22 @@
     </row>
     <row r="96">
       <c r="A96" s="1" t="n">
-        <v>46065</v>
+        <v>46066</v>
       </c>
       <c r="B96" t="n">
-        <v>79.11000061035156</v>
+        <v>76.13999938964844</v>
       </c>
       <c r="C96" t="n">
-        <v>79.15000152587891</v>
+        <v>77.18000030517578</v>
       </c>
       <c r="D96" t="n">
-        <v>75.23000335693359</v>
+        <v>75.52999877929688</v>
       </c>
       <c r="E96" t="n">
-        <v>75.86000061035156</v>
+        <v>76.87000274658203</v>
       </c>
       <c r="F96" t="n">
-        <v>73516100</v>
+        <v>42292100</v>
       </c>
       <c r="G96" t="n">
         <v>0</v>
@@ -2939,22 +2939,22 @@
     </row>
     <row r="97">
       <c r="A97" s="1" t="n">
-        <v>46066</v>
+        <v>46070</v>
       </c>
       <c r="B97" t="n">
-        <v>76.13999938964844</v>
+        <v>76.91999816894531</v>
       </c>
       <c r="C97" t="n">
-        <v>77.18000030517578</v>
+        <v>77.87000274658203</v>
       </c>
       <c r="D97" t="n">
-        <v>75.52999877929688</v>
+        <v>75.30000305175781</v>
       </c>
       <c r="E97" t="n">
-        <v>76.87000274658203</v>
+        <v>77</v>
       </c>
       <c r="F97" t="n">
-        <v>42292100</v>
+        <v>35961500</v>
       </c>
       <c r="G97" t="n">
         <v>0</v>
@@ -2965,22 +2965,22 @@
     </row>
     <row r="98">
       <c r="A98" s="1" t="n">
-        <v>46070</v>
+        <v>46071</v>
       </c>
       <c r="B98" t="n">
-        <v>76.91999816894531</v>
+        <v>77.31999969482422</v>
       </c>
       <c r="C98" t="n">
-        <v>77.87000274658203</v>
+        <v>78.31999969482422</v>
       </c>
       <c r="D98" t="n">
-        <v>75.30000305175781</v>
+        <v>76.27999877929688</v>
       </c>
       <c r="E98" t="n">
-        <v>77</v>
+        <v>77.98999786376953</v>
       </c>
       <c r="F98" t="n">
-        <v>35961500</v>
+        <v>29883100</v>
       </c>
       <c r="G98" t="n">
         <v>0</v>
@@ -2991,22 +2991,22 @@
     </row>
     <row r="99">
       <c r="A99" s="1" t="n">
-        <v>46071</v>
+        <v>46072</v>
       </c>
       <c r="B99" t="n">
-        <v>77.31999969482422</v>
+        <v>77.75</v>
       </c>
       <c r="C99" t="n">
-        <v>78.31999969482422</v>
+        <v>78.69999694824219</v>
       </c>
       <c r="D99" t="n">
-        <v>76.27999877929688</v>
+        <v>76.58999633789062</v>
       </c>
       <c r="E99" t="n">
-        <v>77.98999786376953</v>
+        <v>77</v>
       </c>
       <c r="F99" t="n">
-        <v>29883100</v>
+        <v>30139200</v>
       </c>
       <c r="G99" t="n">
         <v>0</v>
@@ -3017,22 +3017,22 @@
     </row>
     <row r="100">
       <c r="A100" s="1" t="n">
-        <v>46072</v>
+        <v>46073</v>
       </c>
       <c r="B100" t="n">
-        <v>77.75</v>
+        <v>76.61000061035156</v>
       </c>
       <c r="C100" t="n">
-        <v>78.69999694824219</v>
+        <v>78.84999847412109</v>
       </c>
       <c r="D100" t="n">
-        <v>76.58999633789062</v>
+        <v>76.40000152587891</v>
       </c>
       <c r="E100" t="n">
-        <v>77</v>
+        <v>78.66999816894531</v>
       </c>
       <c r="F100" t="n">
-        <v>30139200</v>
+        <v>32411300</v>
       </c>
       <c r="G100" t="n">
         <v>0</v>
@@ -3043,22 +3043,22 @@
     </row>
     <row r="101">
       <c r="A101" s="1" t="n">
-        <v>46073</v>
+        <v>46076</v>
       </c>
       <c r="B101" t="n">
-        <v>76.61000061035156</v>
+        <v>77.79000091552734</v>
       </c>
       <c r="C101" t="n">
-        <v>78.84999847412109</v>
+        <v>77.83000183105469</v>
       </c>
       <c r="D101" t="n">
-        <v>76.40000152587891</v>
+        <v>75.01000213623047</v>
       </c>
       <c r="E101" t="n">
-        <v>78.66999816894531</v>
+        <v>76.01999664306641</v>
       </c>
       <c r="F101" t="n">
-        <v>32411300</v>
+        <v>38363000</v>
       </c>
       <c r="G101" t="n">
         <v>0</v>
@@ -3069,22 +3069,22 @@
     </row>
     <row r="102">
       <c r="A102" s="1" t="n">
-        <v>46076</v>
+        <v>46077</v>
       </c>
       <c r="B102" t="n">
-        <v>77.79000091552734</v>
+        <v>75.73000335693359</v>
       </c>
       <c r="C102" t="n">
-        <v>77.83000183105469</v>
+        <v>78.12000274658203</v>
       </c>
       <c r="D102" t="n">
-        <v>75.01000213623047</v>
+        <v>75.20999908447266</v>
       </c>
       <c r="E102" t="n">
-        <v>76.01999664306641</v>
+        <v>78.04000091552734</v>
       </c>
       <c r="F102" t="n">
-        <v>38363000</v>
+        <v>33079100</v>
       </c>
       <c r="G102" t="n">
         <v>0</v>
@@ -3095,22 +3095,22 @@
     </row>
     <row r="103">
       <c r="A103" s="1" t="n">
-        <v>46077</v>
+        <v>46078</v>
       </c>
       <c r="B103" t="n">
-        <v>75.73000335693359</v>
+        <v>79.43000030517578</v>
       </c>
       <c r="C103" t="n">
-        <v>78.12000274658203</v>
+        <v>83.12000274658203</v>
       </c>
       <c r="D103" t="n">
-        <v>75.20999908447266</v>
+        <v>79.25</v>
       </c>
       <c r="E103" t="n">
-        <v>78.04000091552734</v>
+        <v>82.69999694824219</v>
       </c>
       <c r="F103" t="n">
-        <v>33079100</v>
+        <v>69319300</v>
       </c>
       <c r="G103" t="n">
         <v>0</v>
@@ -3121,22 +3121,22 @@
     </row>
     <row r="104">
       <c r="A104" s="1" t="n">
-        <v>46078</v>
+        <v>46079</v>
       </c>
       <c r="B104" t="n">
-        <v>79.43000030517578</v>
+        <v>83.19999694824219</v>
       </c>
       <c r="C104" t="n">
-        <v>83.12000274658203</v>
+        <v>86.5</v>
       </c>
       <c r="D104" t="n">
-        <v>79.25</v>
+        <v>82.80000305175781</v>
       </c>
       <c r="E104" t="n">
-        <v>82.69999694824219</v>
+        <v>84.58999633789062</v>
       </c>
       <c r="F104" t="n">
-        <v>69319300</v>
+        <v>85642500</v>
       </c>
       <c r="G104" t="n">
         <v>0</v>
@@ -3147,22 +3147,22 @@
     </row>
     <row r="105">
       <c r="A105" s="1" t="n">
-        <v>46079</v>
+        <v>46080</v>
       </c>
       <c r="B105" t="n">
-        <v>83.19999694824219</v>
+        <v>94.30000305175781</v>
       </c>
       <c r="C105" t="n">
-        <v>86.5</v>
+        <v>96.75</v>
       </c>
       <c r="D105" t="n">
-        <v>82.80000305175781</v>
+        <v>90.58000183105469</v>
       </c>
       <c r="E105" t="n">
-        <v>84.58999633789062</v>
+        <v>96.23999786376953</v>
       </c>
       <c r="F105" t="n">
-        <v>85642500</v>
+        <v>200767000</v>
       </c>
       <c r="G105" t="n">
         <v>0</v>
@@ -3173,22 +3173,22 @@
     </row>
     <row r="106">
       <c r="A106" s="1" t="n">
-        <v>46080</v>
+        <v>46083</v>
       </c>
       <c r="B106" t="n">
-        <v>94.30000305175781</v>
+        <v>95.26000213623047</v>
       </c>
       <c r="C106" t="n">
-        <v>96.75</v>
+        <v>98.06999969482422</v>
       </c>
       <c r="D106" t="n">
-        <v>90.58000183105469</v>
+        <v>95.19999694824219</v>
       </c>
       <c r="E106" t="n">
-        <v>96.23999786376953</v>
+        <v>97.08999633789062</v>
       </c>
       <c r="F106" t="n">
-        <v>200767000</v>
+        <v>79915400</v>
       </c>
       <c r="G106" t="n">
         <v>0</v>
@@ -3199,22 +3199,22 @@
     </row>
     <row r="107">
       <c r="A107" s="1" t="n">
-        <v>46083</v>
+        <v>46084</v>
       </c>
       <c r="B107" t="n">
-        <v>95.26000213623047</v>
+        <v>96.01000213623047</v>
       </c>
       <c r="C107" t="n">
-        <v>98.06999969482422</v>
+        <v>98.45999908447266</v>
       </c>
       <c r="D107" t="n">
-        <v>95.19999694824219</v>
+        <v>95.33000183105469</v>
       </c>
       <c r="E107" t="n">
-        <v>97.08999633789062</v>
+        <v>97.69999694824219</v>
       </c>
       <c r="F107" t="n">
-        <v>79915400</v>
+        <v>59149000</v>
       </c>
       <c r="G107" t="n">
         <v>0</v>
@@ -3225,22 +3225,22 @@
     </row>
     <row r="108">
       <c r="A108" s="1" t="n">
-        <v>46084</v>
+        <v>46085</v>
       </c>
       <c r="B108" t="n">
-        <v>96.01000213623047</v>
+        <v>97.11000061035156</v>
       </c>
       <c r="C108" t="n">
-        <v>98.45999908447266</v>
+        <v>99.75</v>
       </c>
       <c r="D108" t="n">
-        <v>95.33000183105469</v>
+        <v>96.98999786376953</v>
       </c>
       <c r="E108" t="n">
-        <v>97.69999694824219</v>
+        <v>98.66000366210938</v>
       </c>
       <c r="F108" t="n">
-        <v>59149000</v>
+        <v>52604300</v>
       </c>
       <c r="G108" t="n">
         <v>0</v>
@@ -3251,22 +3251,22 @@
     </row>
     <row r="109">
       <c r="A109" s="1" t="n">
-        <v>46085</v>
+        <v>46086</v>
       </c>
       <c r="B109" t="n">
-        <v>97.11000061035156</v>
+        <v>98.5</v>
       </c>
       <c r="C109" t="n">
-        <v>99.75</v>
+        <v>100.1900024414062</v>
       </c>
       <c r="D109" t="n">
-        <v>96.98999786376953</v>
+        <v>98.09999847412109</v>
       </c>
       <c r="E109" t="n">
-        <v>98.66000366210938</v>
+        <v>99.16999816894531</v>
       </c>
       <c r="F109" t="n">
-        <v>52604300</v>
+        <v>53403000</v>
       </c>
       <c r="G109" t="n">
         <v>0</v>
@@ -3277,22 +3277,22 @@
     </row>
     <row r="110">
       <c r="A110" s="1" t="n">
-        <v>46086</v>
+        <v>46087</v>
       </c>
       <c r="B110" t="n">
-        <v>98.5</v>
+        <v>99.33000183105469</v>
       </c>
       <c r="C110" t="n">
-        <v>100.1900024414062</v>
+        <v>99.87999725341797</v>
       </c>
       <c r="D110" t="n">
-        <v>98.09999847412109</v>
+        <v>97.40000152587891</v>
       </c>
       <c r="E110" t="n">
-        <v>99.16999816894531</v>
+        <v>99.01999664306641</v>
       </c>
       <c r="F110" t="n">
-        <v>53403000</v>
+        <v>41196300</v>
       </c>
       <c r="G110" t="n">
         <v>0</v>
@@ -3303,22 +3303,22 @@
     </row>
     <row r="111">
       <c r="A111" s="1" t="n">
-        <v>46087</v>
+        <v>46090</v>
       </c>
       <c r="B111" t="n">
-        <v>99.33000183105469</v>
+        <v>97.69999694824219</v>
       </c>
       <c r="C111" t="n">
-        <v>99.87999725341797</v>
+        <v>98.94000244140625</v>
       </c>
       <c r="D111" t="n">
-        <v>97.40000152587891</v>
+        <v>96.58000183105469</v>
       </c>
       <c r="E111" t="n">
-        <v>99.01999664306641</v>
+        <v>98.31999969482422</v>
       </c>
       <c r="F111" t="n">
-        <v>41196300</v>
+        <v>48589000</v>
       </c>
       <c r="G111" t="n">
         <v>0</v>
@@ -3329,22 +3329,22 @@
     </row>
     <row r="112">
       <c r="A112" s="1" t="n">
-        <v>46090</v>
+        <v>46091</v>
       </c>
       <c r="B112" t="n">
-        <v>97.69999694824219</v>
+        <v>97.80999755859375</v>
       </c>
       <c r="C112" t="n">
-        <v>98.94000244140625</v>
+        <v>98.48999786376953</v>
       </c>
       <c r="D112" t="n">
-        <v>96.58000183105469</v>
+        <v>96.29000091552734</v>
       </c>
       <c r="E112" t="n">
-        <v>98.31999969482422</v>
+        <v>96.94000244140625</v>
       </c>
       <c r="F112" t="n">
-        <v>48589000</v>
+        <v>41027200</v>
       </c>
       <c r="G112" t="n">
         <v>0</v>
@@ -3355,22 +3355,22 @@
     </row>
     <row r="113">
       <c r="A113" s="1" t="n">
-        <v>46091</v>
+        <v>46092</v>
       </c>
       <c r="B113" t="n">
-        <v>97.80999755859375</v>
+        <v>97.41000366210938</v>
       </c>
       <c r="C113" t="n">
-        <v>98.48999786376953</v>
+        <v>98</v>
       </c>
       <c r="D113" t="n">
-        <v>96.29000091552734</v>
+        <v>94.69000244140625</v>
       </c>
       <c r="E113" t="n">
-        <v>96.94000244140625</v>
+        <v>94.88999938964844</v>
       </c>
       <c r="F113" t="n">
-        <v>41027200</v>
+        <v>33962900</v>
       </c>
       <c r="G113" t="n">
         <v>0</v>
@@ -3381,22 +3381,22 @@
     </row>
     <row r="114">
       <c r="A114" s="1" t="n">
-        <v>46092</v>
+        <v>46093</v>
       </c>
       <c r="B114" t="n">
-        <v>97.41000366210938</v>
+        <v>94.86000061035156</v>
       </c>
       <c r="C114" t="n">
-        <v>98</v>
+        <v>95.40000152587891</v>
       </c>
       <c r="D114" t="n">
-        <v>94.69000244140625</v>
+        <v>93.87000274658203</v>
       </c>
       <c r="E114" t="n">
-        <v>94.88999938964844</v>
+        <v>94.30999755859375</v>
       </c>
       <c r="F114" t="n">
-        <v>33962900</v>
+        <v>34206900</v>
       </c>
       <c r="G114" t="n">
         <v>0</v>
@@ -3407,22 +3407,22 @@
     </row>
     <row r="115">
       <c r="A115" s="1" t="n">
-        <v>46093</v>
+        <v>46094</v>
       </c>
       <c r="B115" t="n">
-        <v>94.86000061035156</v>
+        <v>94.63999938964844</v>
       </c>
       <c r="C115" t="n">
-        <v>95.40000152587891</v>
+        <v>95.68000030517578</v>
       </c>
       <c r="D115" t="n">
-        <v>93.87000274658203</v>
+        <v>94.23999786376953</v>
       </c>
       <c r="E115" t="n">
-        <v>94.30999755859375</v>
+        <v>95.30999755859375</v>
       </c>
       <c r="F115" t="n">
-        <v>34206900</v>
+        <v>29876700</v>
       </c>
       <c r="G115" t="n">
         <v>0</v>
@@ -3433,22 +3433,22 @@
     </row>
     <row r="116">
       <c r="A116" s="1" t="n">
-        <v>46094</v>
+        <v>46097</v>
       </c>
       <c r="B116" t="n">
-        <v>94.63999938964844</v>
+        <v>95.58000183105469</v>
       </c>
       <c r="C116" t="n">
-        <v>95.68000030517578</v>
+        <v>96.09999847412109</v>
       </c>
       <c r="D116" t="n">
-        <v>94.23999786376953</v>
+        <v>94.36000061035156</v>
       </c>
       <c r="E116" t="n">
-        <v>95.30999755859375</v>
+        <v>95.19999694824219</v>
       </c>
       <c r="F116" t="n">
-        <v>29876700</v>
+        <v>34931800</v>
       </c>
       <c r="G116" t="n">
         <v>0</v>
@@ -3459,22 +3459,22 @@
     </row>
     <row r="117">
       <c r="A117" s="1" t="n">
-        <v>46097</v>
+        <v>46098</v>
       </c>
       <c r="B117" t="n">
-        <v>95.58000183105469</v>
+        <v>95.30000305175781</v>
       </c>
       <c r="C117" t="n">
-        <v>96.09999847412109</v>
+        <v>96.33999633789062</v>
       </c>
       <c r="D117" t="n">
+        <v>94.01000213623047</v>
+      </c>
+      <c r="E117" t="n">
         <v>94.36000061035156</v>
       </c>
-      <c r="E117" t="n">
-        <v>95.19999694824219</v>
-      </c>
       <c r="F117" t="n">
-        <v>34931800</v>
+        <v>26434500</v>
       </c>
       <c r="G117" t="n">
         <v>0</v>
@@ -3485,22 +3485,22 @@
     </row>
     <row r="118">
       <c r="A118" s="1" t="n">
-        <v>46098</v>
+        <v>46099</v>
       </c>
       <c r="B118" t="n">
-        <v>95.30000305175781</v>
+        <v>94.44999694824219</v>
       </c>
       <c r="C118" t="n">
-        <v>96.33999633789062</v>
+        <v>95.33999633789062</v>
       </c>
       <c r="D118" t="n">
-        <v>94.01000213623047</v>
+        <v>93.61000061035156</v>
       </c>
       <c r="E118" t="n">
-        <v>94.36000061035156</v>
+        <v>94.69999694824219</v>
       </c>
       <c r="F118" t="n">
-        <v>26434500</v>
+        <v>27878300</v>
       </c>
       <c r="G118" t="n">
         <v>0</v>
@@ -3511,22 +3511,22 @@
     </row>
     <row r="119">
       <c r="A119" s="1" t="n">
-        <v>46099</v>
+        <v>46100</v>
       </c>
       <c r="B119" t="n">
-        <v>94.44999694824219</v>
+        <v>94.30999755859375</v>
       </c>
       <c r="C119" t="n">
-        <v>95.33999633789062</v>
+        <v>95.75</v>
       </c>
       <c r="D119" t="n">
-        <v>93.61000061035156</v>
+        <v>90.77999877929688</v>
       </c>
       <c r="E119" t="n">
-        <v>94.69999694824219</v>
+        <v>91.73999786376953</v>
       </c>
       <c r="F119" t="n">
-        <v>27878300</v>
+        <v>40169300</v>
       </c>
       <c r="G119" t="n">
         <v>0</v>
@@ -3537,22 +3537,22 @@
     </row>
     <row r="120">
       <c r="A120" s="1" t="n">
-        <v>46100</v>
+        <v>46101</v>
       </c>
       <c r="B120" t="n">
-        <v>94.30999755859375</v>
+        <v>91.30999755859375</v>
       </c>
       <c r="C120" t="n">
-        <v>95.75</v>
+        <v>91.87999725341797</v>
       </c>
       <c r="D120" t="n">
-        <v>90.77999877929688</v>
+        <v>90.69000244140625</v>
       </c>
       <c r="E120" t="n">
-        <v>91.73999786376953</v>
+        <v>91.81999969482422</v>
       </c>
       <c r="F120" t="n">
-        <v>40169300</v>
+        <v>61678000</v>
       </c>
       <c r="G120" t="n">
         <v>0</v>
@@ -3563,22 +3563,22 @@
     </row>
     <row r="121">
       <c r="A121" s="1" t="n">
-        <v>46101</v>
+        <v>46104</v>
       </c>
       <c r="B121" t="n">
-        <v>91.30999755859375</v>
+        <v>92.04000091552734</v>
       </c>
       <c r="C121" t="n">
-        <v>91.87999725341797</v>
+        <v>93.98000335693359</v>
       </c>
       <c r="D121" t="n">
-        <v>90.69000244140625</v>
+        <v>91.86000061035156</v>
       </c>
       <c r="E121" t="n">
-        <v>91.81999969482422</v>
+        <v>93.37999725341797</v>
       </c>
       <c r="F121" t="n">
-        <v>61678000</v>
+        <v>34315900</v>
       </c>
       <c r="G121" t="n">
         <v>0</v>
@@ -3589,22 +3589,22 @@
     </row>
     <row r="122">
       <c r="A122" s="1" t="n">
-        <v>46104</v>
+        <v>46105</v>
       </c>
       <c r="B122" t="n">
-        <v>92.04000091552734</v>
+        <v>92.79000091552734</v>
       </c>
       <c r="C122" t="n">
-        <v>93.98000335693359</v>
+        <v>93.73999786376953</v>
       </c>
       <c r="D122" t="n">
-        <v>91.86000061035156</v>
+        <v>90.81999969482422</v>
       </c>
       <c r="E122" t="n">
-        <v>93.37999725341797</v>
+        <v>90.91999816894531</v>
       </c>
       <c r="F122" t="n">
-        <v>34315900</v>
+        <v>28938000</v>
       </c>
       <c r="G122" t="n">
         <v>0</v>
@@ -3615,22 +3615,22 @@
     </row>
     <row r="123">
       <c r="A123" s="1" t="n">
-        <v>46105</v>
+        <v>46106</v>
       </c>
       <c r="B123" t="n">
-        <v>92.79000091552734</v>
+        <v>91.70999908447266</v>
       </c>
       <c r="C123" t="n">
-        <v>93.73999786376953</v>
+        <v>92.51999664306641</v>
       </c>
       <c r="D123" t="n">
-        <v>90.81999969482422</v>
+        <v>91.23999786376953</v>
       </c>
       <c r="E123" t="n">
-        <v>90.91999816894531</v>
+        <v>92.27999877929688</v>
       </c>
       <c r="F123" t="n">
-        <v>28938000</v>
+        <v>29545600</v>
       </c>
       <c r="G123" t="n">
         <v>0</v>
@@ -3641,22 +3641,22 @@
     </row>
     <row r="124">
       <c r="A124" s="1" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B124" t="n">
-        <v>91.70999908447266</v>
+        <v>91.51999664306641</v>
       </c>
       <c r="C124" t="n">
-        <v>92.51999664306641</v>
+        <v>95.86000061035156</v>
       </c>
       <c r="D124" t="n">
-        <v>91.23999786376953</v>
+        <v>91.01000213623047</v>
       </c>
       <c r="E124" t="n">
-        <v>92.27999877929688</v>
+        <v>93.31999969482422</v>
       </c>
       <c r="F124" t="n">
-        <v>29545600</v>
+        <v>59522000</v>
       </c>
       <c r="G124" t="n">
         <v>0</v>
@@ -3667,22 +3667,22 @@
     </row>
     <row r="125">
       <c r="A125" s="1" t="n">
-        <v>46107</v>
+        <v>46108</v>
       </c>
       <c r="B125" t="n">
-        <v>91.51999664306641</v>
+        <v>94.56999969482422</v>
       </c>
       <c r="C125" t="n">
-        <v>95.86000061035156</v>
+        <v>95.58000183105469</v>
       </c>
       <c r="D125" t="n">
-        <v>91.01000213623047</v>
+        <v>92.73999786376953</v>
       </c>
       <c r="E125" t="n">
-        <v>93.31999969482422</v>
+        <v>93.43000030517578</v>
       </c>
       <c r="F125" t="n">
-        <v>59522000</v>
+        <v>44590700</v>
       </c>
       <c r="G125" t="n">
         <v>0</v>
@@ -3693,22 +3693,22 @@
     </row>
     <row r="126">
       <c r="A126" s="1" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B126" t="n">
-        <v>94.56999969482422</v>
+        <v>92.75</v>
       </c>
       <c r="C126" t="n">
-        <v>95.58000183105469</v>
+        <v>94.48999786376953</v>
       </c>
       <c r="D126" t="n">
-        <v>92.73999786376953</v>
+        <v>92.22000122070312</v>
       </c>
       <c r="E126" t="n">
-        <v>93.43000030517578</v>
+        <v>92.97000122070312</v>
       </c>
       <c r="F126" t="n">
-        <v>44590700</v>
+        <v>32375100</v>
       </c>
       <c r="G126" t="n">
         <v>0</v>
@@ -3719,22 +3719,22 @@
     </row>
     <row r="127">
       <c r="A127" s="1" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B127" t="n">
-        <v>92.75</v>
+        <v>93.02999877929688</v>
       </c>
       <c r="C127" t="n">
-        <v>94.48999786376953</v>
+        <v>96.26000213623047</v>
       </c>
       <c r="D127" t="n">
-        <v>92.22000122070312</v>
+        <v>93.02999877929688</v>
       </c>
       <c r="E127" t="n">
-        <v>92.97000122070312</v>
+        <v>96.15000152587891</v>
       </c>
       <c r="F127" t="n">
-        <v>32375100</v>
+        <v>54270000</v>
       </c>
       <c r="G127" t="n">
         <v>0</v>
@@ -3745,22 +3745,22 @@
     </row>
     <row r="128">
       <c r="A128" s="1" t="n">
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="B128" t="n">
-        <v>93.02999877929688</v>
+        <v>96.47000122070312</v>
       </c>
       <c r="C128" t="n">
-        <v>96.26000213623047</v>
+        <v>97.19999694824219</v>
       </c>
       <c r="D128" t="n">
-        <v>93.02999877929688</v>
+        <v>94.26000213623047</v>
       </c>
       <c r="E128" t="n">
-        <v>96.15000152587891</v>
+        <v>95.55000305175781</v>
       </c>
       <c r="F128" t="n">
-        <v>54270000</v>
+        <v>30439300</v>
       </c>
       <c r="G128" t="n">
         <v>0</v>
@@ -3771,22 +3771,22 @@
     </row>
     <row r="129">
       <c r="A129" s="1" t="n">
-        <v>46113</v>
+        <v>46114</v>
       </c>
       <c r="B129" t="n">
-        <v>96.47000122070312</v>
+        <v>95.26999664306641</v>
       </c>
       <c r="C129" t="n">
-        <v>97.19999694824219</v>
+        <v>98.70999908447266</v>
       </c>
       <c r="D129" t="n">
-        <v>94.26000213623047</v>
+        <v>95.16999816894531</v>
       </c>
       <c r="E129" t="n">
-        <v>95.55000305175781</v>
+        <v>98.66000366210938</v>
       </c>
       <c r="F129" t="n">
-        <v>30439300</v>
+        <v>37068000</v>
       </c>
       <c r="G129" t="n">
         <v>0</v>
@@ -3797,22 +3797,22 @@
     </row>
     <row r="130">
       <c r="A130" s="1" t="n">
-        <v>46114</v>
+        <v>46118</v>
       </c>
       <c r="B130" t="n">
-        <v>95.26999664306641</v>
+        <v>100.9599990844727</v>
       </c>
       <c r="C130" t="n">
-        <v>98.70999908447266</v>
+        <v>102.6900024414062</v>
       </c>
       <c r="D130" t="n">
-        <v>95.16999816894531</v>
+        <v>97.97000122070312</v>
       </c>
       <c r="E130" t="n">
-        <v>98.66000366210938</v>
+        <v>98.93000030517578</v>
       </c>
       <c r="F130" t="n">
-        <v>37068000</v>
+        <v>37029300</v>
       </c>
       <c r="G130" t="n">
         <v>0</v>
@@ -3823,22 +3823,22 @@
     </row>
     <row r="131">
       <c r="A131" s="1" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B131" t="n">
-        <v>100.9599990844727</v>
+        <v>98.55000305175781</v>
       </c>
       <c r="C131" t="n">
-        <v>102.6900024414062</v>
+        <v>99.87999725341797</v>
       </c>
       <c r="D131" t="n">
-        <v>97.97000122070312</v>
+        <v>98.25</v>
       </c>
       <c r="E131" t="n">
-        <v>98.93000030517578</v>
+        <v>98.81999969482422</v>
       </c>
       <c r="F131" t="n">
-        <v>37029300</v>
+        <v>25016700</v>
       </c>
       <c r="G131" t="n">
         <v>0</v>
@@ -3849,22 +3849,22 @@
     </row>
     <row r="132">
       <c r="A132" s="1" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B132" t="n">
-        <v>98.55000305175781</v>
+        <v>100.3199996948242</v>
       </c>
       <c r="C132" t="n">
-        <v>99.87999725341797</v>
+        <v>100.4000015258789</v>
       </c>
       <c r="D132" t="n">
-        <v>98.25</v>
+        <v>97.44000244140625</v>
       </c>
       <c r="E132" t="n">
-        <v>98.81999969482422</v>
+        <v>99.38999938964844</v>
       </c>
       <c r="F132" t="n">
-        <v>25016700</v>
+        <v>30957600</v>
       </c>
       <c r="G132" t="n">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="133">
       <c r="A133" s="1" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B133" t="n">
-        <v>100.3199996948242</v>
+        <v>99.62999725341797</v>
       </c>
       <c r="C133" t="n">
-        <v>100.4000015258789</v>
+        <v>102.3399963378906</v>
       </c>
       <c r="D133" t="n">
-        <v>97.44000244140625</v>
+        <v>99.08000183105469</v>
       </c>
       <c r="E133" t="n">
-        <v>99.38999938964844</v>
+        <v>102.0500030517578</v>
       </c>
       <c r="F133" t="n">
-        <v>30957600</v>
+        <v>35087800</v>
       </c>
       <c r="G133" t="n">
         <v>0</v>
@@ -3901,22 +3901,22 @@
     </row>
     <row r="134">
       <c r="A134" s="1" t="n">
-        <v>46121</v>
+        <v>46122</v>
       </c>
       <c r="B134" t="n">
-        <v>99.62999725341797</v>
+        <v>102.4700012207031</v>
       </c>
       <c r="C134" t="n">
-        <v>102.3399963378906</v>
+        <v>103.0800018310547</v>
       </c>
       <c r="D134" t="n">
-        <v>99.08000183105469</v>
+        <v>101.4599990844727</v>
       </c>
       <c r="E134" t="n">
-        <v>102.0500030517578</v>
+        <v>103.0100021362305</v>
       </c>
       <c r="F134" t="n">
-        <v>35087800</v>
+        <v>25769900</v>
       </c>
       <c r="G134" t="n">
         <v>0</v>
@@ -3927,22 +3927,22 @@
     </row>
     <row r="135">
       <c r="A135" s="1" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B135" t="n">
-        <v>102.4700012207031</v>
+        <v>103.0299987792969</v>
       </c>
       <c r="C135" t="n">
-        <v>103.0800018310547</v>
+        <v>103.6699981689453</v>
       </c>
       <c r="D135" t="n">
-        <v>101.4599990844727</v>
+        <v>102.0599975585938</v>
       </c>
       <c r="E135" t="n">
-        <v>103.0100021362305</v>
+        <v>103.1600036621094</v>
       </c>
       <c r="F135" t="n">
-        <v>25769900</v>
+        <v>26042800</v>
       </c>
       <c r="G135" t="n">
         <v>0</v>
@@ -3953,22 +3953,22 @@
     </row>
     <row r="136">
       <c r="A136" s="1" t="n">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="B136" t="n">
-        <v>103.0299987792969</v>
+        <v>103.120002746582</v>
       </c>
       <c r="C136" t="n">
-        <v>103.6699981689453</v>
+        <v>106.5699996948242</v>
       </c>
       <c r="D136" t="n">
-        <v>102.0599975585938</v>
+        <v>103.0400009155273</v>
       </c>
       <c r="E136" t="n">
-        <v>103.1600036621094</v>
+        <v>106.2799987792969</v>
       </c>
       <c r="F136" t="n">
-        <v>26042800</v>
+        <v>40534900</v>
       </c>
       <c r="G136" t="n">
         <v>0</v>
@@ -3979,22 +3979,22 @@
     </row>
     <row r="137">
       <c r="A137" s="1" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B137" t="n">
-        <v>103.120002746582</v>
+        <v>105.9800033569336</v>
       </c>
       <c r="C137" t="n">
-        <v>106.5699996948242</v>
+        <v>107.8499984741211</v>
       </c>
       <c r="D137" t="n">
-        <v>103.0400009155273</v>
+        <v>105.0400009155273</v>
       </c>
       <c r="E137" t="n">
-        <v>106.2799987792969</v>
+        <v>107.7099990844727</v>
       </c>
       <c r="F137" t="n">
-        <v>40534900</v>
+        <v>38023700</v>
       </c>
       <c r="G137" t="n">
         <v>0</v>
@@ -4005,22 +4005,22 @@
     </row>
     <row r="138">
       <c r="A138" s="1" t="n">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c r="B138" t="n">
-        <v>105.9800033569336</v>
+        <v>107.4700012207031</v>
       </c>
       <c r="C138" t="n">
-        <v>107.8499984741211</v>
+        <v>108.9499969482422</v>
       </c>
       <c r="D138" t="n">
-        <v>105.0400009155273</v>
+        <v>106.620002746582</v>
       </c>
       <c r="E138" t="n">
-        <v>107.7099990844727</v>
+        <v>107.7900009155273</v>
       </c>
       <c r="F138" t="n">
-        <v>38023700</v>
+        <v>64928300</v>
       </c>
       <c r="G138" t="n">
         <v>0</v>
@@ -4031,22 +4031,22 @@
     </row>
     <row r="139">
       <c r="A139" s="1" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B139" t="n">
-        <v>107.4700012207031</v>
+        <v>96.37000274658203</v>
       </c>
       <c r="C139" t="n">
-        <v>108.9499969482422</v>
+        <v>98.73999786376953</v>
       </c>
       <c r="D139" t="n">
-        <v>106.620002746582</v>
+        <v>95.09999847412109</v>
       </c>
       <c r="E139" t="n">
-        <v>107.7900009155273</v>
+        <v>97.30999755859375</v>
       </c>
       <c r="F139" t="n">
-        <v>64928300</v>
+        <v>125958700</v>
       </c>
       <c r="G139" t="n">
         <v>0</v>
@@ -4057,22 +4057,22 @@
     </row>
     <row r="140">
       <c r="A140" s="1" t="n">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c r="B140" t="n">
-        <v>96.37000274658203</v>
+        <v>97.13999938964844</v>
       </c>
       <c r="C140" t="n">
-        <v>98.73999786376953</v>
+        <v>97.59999847412109</v>
       </c>
       <c r="D140" t="n">
-        <v>95.09999847412109</v>
+        <v>93.54000091552734</v>
       </c>
       <c r="E140" t="n">
-        <v>97.30999755859375</v>
+        <v>94.83000183105469</v>
       </c>
       <c r="F140" t="n">
-        <v>125958700</v>
+        <v>63298300</v>
       </c>
       <c r="G140" t="n">
         <v>0</v>
@@ -4083,22 +4083,22 @@
     </row>
     <row r="141">
       <c r="A141" s="1" t="n">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="B141" t="n">
-        <v>97.13999938964844</v>
+        <v>94</v>
       </c>
       <c r="C141" t="n">
-        <v>97.59999847412109</v>
+        <v>94.65000152587891</v>
       </c>
       <c r="D141" t="n">
-        <v>93.54000091552734</v>
+        <v>92.37000274658203</v>
       </c>
       <c r="E141" t="n">
-        <v>94.83000183105469</v>
+        <v>92.58000183105469</v>
       </c>
       <c r="F141" t="n">
-        <v>63298300</v>
+        <v>61962300</v>
       </c>
       <c r="G141" t="n">
         <v>0</v>
@@ -4109,22 +4109,22 @@
     </row>
     <row r="142">
       <c r="A142" s="1" t="n">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="B142" t="n">
-        <v>94</v>
+        <v>93.05999755859375</v>
       </c>
       <c r="C142" t="n">
-        <v>94.65000152587891</v>
+        <v>93.84999847412109</v>
       </c>
       <c r="D142" t="n">
-        <v>92.37000274658203</v>
+        <v>92.76999664306641</v>
       </c>
       <c r="E142" t="n">
-        <v>92.58000183105469</v>
+        <v>93.23999786376953</v>
       </c>
       <c r="F142" t="n">
-        <v>61962300</v>
+        <v>33694300</v>
       </c>
       <c r="G142" t="n">
         <v>0</v>
@@ -4135,22 +4135,22 @@
     </row>
     <row r="143">
       <c r="A143" s="1" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B143" t="n">
-        <v>93.05999755859375</v>
+        <v>94.05999755859375</v>
       </c>
       <c r="C143" t="n">
-        <v>93.84999847412109</v>
+        <v>94.63999938964844</v>
       </c>
       <c r="D143" t="n">
-        <v>92.76999664306641</v>
+        <v>92.06999969482422</v>
       </c>
       <c r="E143" t="n">
-        <v>93.23999786376953</v>
+        <v>92.81999969482422</v>
       </c>
       <c r="F143" t="n">
-        <v>33694300</v>
+        <v>36851700</v>
       </c>
       <c r="G143" t="n">
         <v>0</v>
@@ -4161,22 +4161,22 @@
     </row>
     <row r="144">
       <c r="A144" s="1" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B144" t="n">
-        <v>94.05999755859375</v>
+        <v>92.56999969482422</v>
       </c>
       <c r="C144" t="n">
-        <v>94.63999938964844</v>
+        <v>93.27999877929688</v>
       </c>
       <c r="D144" t="n">
-        <v>92.06999969482422</v>
+        <v>91.80000305175781</v>
       </c>
       <c r="E144" t="n">
-        <v>92.81999969482422</v>
+        <v>92.44000244140625</v>
       </c>
       <c r="F144" t="n">
-        <v>36851700</v>
+        <v>32553200</v>
       </c>
       <c r="G144" t="n">
         <v>0</v>
@@ -4187,22 +4187,22 @@
     </row>
     <row r="145">
       <c r="A145" s="1" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B145" t="n">
-        <v>92.56999969482422</v>
+        <v>92.05000305175781</v>
       </c>
       <c r="C145" t="n">
-        <v>93.27999877929688</v>
+        <v>92.83999633789062</v>
       </c>
       <c r="D145" t="n">
-        <v>91.80000305175781</v>
+        <v>91.30000305175781</v>
       </c>
       <c r="E145" t="n">
-        <v>92.44000244140625</v>
+        <v>91.37000274658203</v>
       </c>
       <c r="F145" t="n">
-        <v>32553200</v>
+        <v>29707400</v>
       </c>
       <c r="G145" t="n">
         <v>0</v>
@@ -4213,22 +4213,22 @@
     </row>
     <row r="146">
       <c r="A146" s="1" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B146" t="n">
-        <v>92.05000305175781</v>
+        <v>91.5</v>
       </c>
       <c r="C146" t="n">
-        <v>92.83999633789062</v>
+        <v>92.33999633789062</v>
       </c>
       <c r="D146" t="n">
-        <v>91.30000305175781</v>
+        <v>90.01999664306641</v>
       </c>
       <c r="E146" t="n">
-        <v>91.37000274658203</v>
+        <v>92.26999664306641</v>
       </c>
       <c r="F146" t="n">
-        <v>29707400</v>
+        <v>33418100</v>
       </c>
       <c r="G146" t="n">
         <v>0</v>
@@ -4239,22 +4239,22 @@
     </row>
     <row r="147">
       <c r="A147" s="1" t="n">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="B147" t="n">
-        <v>91.5</v>
+        <v>91.23000335693359</v>
       </c>
       <c r="C147" t="n">
-        <v>92.33999633789062</v>
+        <v>92.86000061035156</v>
       </c>
       <c r="D147" t="n">
-        <v>90.01999664306641</v>
+        <v>90.86000061035156</v>
       </c>
       <c r="E147" t="n">
-        <v>92.26999664306641</v>
+        <v>92.12000274658203</v>
       </c>
       <c r="F147" t="n">
-        <v>33418100</v>
+        <v>26122100</v>
       </c>
       <c r="G147" t="n">
         <v>0</v>
@@ -4265,22 +4265,22 @@
     </row>
     <row r="148">
       <c r="A148" s="1" t="n">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="B148" t="n">
-        <v>91.23000335693359</v>
+        <v>91.34999847412109</v>
       </c>
       <c r="C148" t="n">
-        <v>92.86000061035156</v>
+        <v>94.22000122070312</v>
       </c>
       <c r="D148" t="n">
-        <v>90.86000061035156</v>
+        <v>90.76999664306641</v>
       </c>
       <c r="E148" t="n">
-        <v>92.12000274658203</v>
+        <v>93.61000061035156</v>
       </c>
       <c r="F148" t="n">
-        <v>26122100</v>
+        <v>40923000</v>
       </c>
       <c r="G148" t="n">
         <v>0</v>
@@ -4291,22 +4291,22 @@
     </row>
     <row r="149">
       <c r="A149" s="1" t="n">
-        <v>46142</v>
+        <v>46143</v>
       </c>
       <c r="B149" t="n">
-        <v>91.34999847412109</v>
+        <v>94.41999816894531</v>
       </c>
       <c r="C149" t="n">
-        <v>94.22000122070312</v>
+        <v>94.69999694824219</v>
       </c>
       <c r="D149" t="n">
-        <v>90.76999664306641</v>
+        <v>91.90000152587891</v>
       </c>
       <c r="E149" t="n">
-        <v>93.61000061035156</v>
+        <v>92.05999755859375</v>
       </c>
       <c r="F149" t="n">
-        <v>40923000</v>
+        <v>30406900</v>
       </c>
       <c r="G149" t="n">
         <v>0</v>
@@ -4317,22 +4317,22 @@
     </row>
     <row r="150">
       <c r="A150" s="1" t="n">
-        <v>46143</v>
+        <v>46146</v>
       </c>
       <c r="B150" t="n">
-        <v>94.41999816894531</v>
+        <v>92.09999847412109</v>
       </c>
       <c r="C150" t="n">
-        <v>94.69999694824219</v>
+        <v>92.33000183105469</v>
       </c>
       <c r="D150" t="n">
-        <v>91.90000152587891</v>
+        <v>90.88999938964844</v>
       </c>
       <c r="E150" t="n">
-        <v>92.05999755859375</v>
+        <v>91.01999664306641</v>
       </c>
       <c r="F150" t="n">
-        <v>30406900</v>
+        <v>25928800</v>
       </c>
       <c r="G150" t="n">
         <v>0</v>
@@ -4343,22 +4343,22 @@
     </row>
     <row r="151">
       <c r="A151" s="1" t="n">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="B151" t="n">
-        <v>92.09999847412109</v>
+        <v>91.18000030517578</v>
       </c>
       <c r="C151" t="n">
-        <v>92.33000183105469</v>
+        <v>91.27999877929688</v>
       </c>
       <c r="D151" t="n">
-        <v>90.88999938964844</v>
+        <v>87.56999969482422</v>
       </c>
       <c r="E151" t="n">
-        <v>91.01999664306641</v>
+        <v>87.88999938964844</v>
       </c>
       <c r="F151" t="n">
-        <v>25928800</v>
+        <v>51961300</v>
       </c>
       <c r="G151" t="n">
         <v>0</v>
@@ -4369,22 +4369,22 @@
     </row>
     <row r="152">
       <c r="A152" s="1" t="n">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="B152" t="n">
-        <v>91.18000030517578</v>
+        <v>87.15000152587891</v>
       </c>
       <c r="C152" t="n">
-        <v>91.27999877929688</v>
+        <v>88.55000305175781</v>
       </c>
       <c r="D152" t="n">
-        <v>87.56999969482422</v>
+        <v>86.72000122070312</v>
       </c>
       <c r="E152" t="n">
-        <v>87.88999938964844</v>
+        <v>88.26999664306641</v>
       </c>
       <c r="F152" t="n">
-        <v>51961300</v>
+        <v>41932400</v>
       </c>
       <c r="G152" t="n">
         <v>0</v>
@@ -4395,22 +4395,22 @@
     </row>
     <row r="153">
       <c r="A153" s="1" t="n">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="B153" t="n">
-        <v>87.15000152587891</v>
+        <v>88.19999694824219</v>
       </c>
       <c r="C153" t="n">
-        <v>88.55000305175781</v>
+        <v>89.40000152587891</v>
       </c>
       <c r="D153" t="n">
-        <v>86.72000122070312</v>
+        <v>88.12999725341797</v>
       </c>
       <c r="E153" t="n">
-        <v>88.26999664306641</v>
+        <v>88.25</v>
       </c>
       <c r="F153" t="n">
-        <v>41932400</v>
+        <v>30627600</v>
       </c>
       <c r="G153" t="n">
         <v>0</v>
@@ -4421,22 +4421,22 @@
     </row>
     <row r="154">
       <c r="A154" s="1" t="n">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="B154" t="n">
-        <v>88.19999694824219</v>
+        <v>87.70999908447266</v>
       </c>
       <c r="C154" t="n">
-        <v>89.40000152587891</v>
+        <v>88.04000091552734</v>
       </c>
       <c r="D154" t="n">
-        <v>88.12999725341797</v>
+        <v>87.20999908447266</v>
       </c>
       <c r="E154" t="n">
-        <v>88.25</v>
+        <v>87.48999786376953</v>
       </c>
       <c r="F154" t="n">
-        <v>30627600</v>
+        <v>36215100</v>
       </c>
       <c r="G154" t="n">
         <v>0</v>
@@ -4447,22 +4447,22 @@
     </row>
     <row r="155">
       <c r="A155" s="1" t="n">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="B155" t="n">
-        <v>87.70999908447266</v>
+        <v>86.52999877929688</v>
       </c>
       <c r="C155" t="n">
-        <v>88.04000091552734</v>
+        <v>87.33999633789062</v>
       </c>
       <c r="D155" t="n">
-        <v>87.20999908447266</v>
+        <v>85.09999847412109</v>
       </c>
       <c r="E155" t="n">
-        <v>87.48999786376953</v>
+        <v>85.44999694824219</v>
       </c>
       <c r="F155" t="n">
-        <v>36215100</v>
+        <v>40556500</v>
       </c>
       <c r="G155" t="n">
         <v>0</v>
@@ -4473,22 +4473,22 @@
     </row>
     <row r="156">
       <c r="A156" s="1" t="n">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="B156" t="n">
-        <v>86.52999877929688</v>
+        <v>85.91000366210938</v>
       </c>
       <c r="C156" t="n">
-        <v>87.33999633789062</v>
+        <v>89.16999816894531</v>
       </c>
       <c r="D156" t="n">
-        <v>85.09999847412109</v>
+        <v>85.80999755859375</v>
       </c>
       <c r="E156" t="n">
-        <v>85.44999694824219</v>
+        <v>87.66000366210938</v>
       </c>
       <c r="F156" t="n">
-        <v>40556500</v>
+        <v>43556600</v>
       </c>
       <c r="G156" t="n">
         <v>0</v>
@@ -4499,22 +4499,22 @@
     </row>
     <row r="157">
       <c r="A157" s="1" t="n">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="B157" t="n">
-        <v>85.91000366210938</v>
+        <v>86.56999969482422</v>
       </c>
       <c r="C157" t="n">
-        <v>89.16999816894531</v>
+        <v>88.62000274658203</v>
       </c>
       <c r="D157" t="n">
-        <v>85.80999755859375</v>
+        <v>86.27999877929688</v>
       </c>
       <c r="E157" t="n">
-        <v>87.66000366210938</v>
+        <v>87.55999755859375</v>
       </c>
       <c r="F157" t="n">
-        <v>43556600</v>
+        <v>30823500</v>
       </c>
       <c r="G157" t="n">
         <v>0</v>
@@ -4525,22 +4525,22 @@
     </row>
     <row r="158">
       <c r="A158" s="1" t="n">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="B158" t="n">
-        <v>86.56999969482422</v>
+        <v>87.62000274658203</v>
       </c>
       <c r="C158" t="n">
-        <v>88.62000274658203</v>
+        <v>88.5</v>
       </c>
       <c r="D158" t="n">
-        <v>86.27999877929688</v>
+        <v>86.65000152587891</v>
       </c>
       <c r="E158" t="n">
-        <v>87.55999755859375</v>
+        <v>86.94000244140625</v>
       </c>
       <c r="F158" t="n">
-        <v>30823500</v>
+        <v>29408300</v>
       </c>
       <c r="G158" t="n">
         <v>0</v>
@@ -4551,22 +4551,22 @@
     </row>
     <row r="159">
       <c r="A159" s="1" t="n">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="B159" t="n">
-        <v>87.62000274658203</v>
+        <v>87.69000244140625</v>
       </c>
       <c r="C159" t="n">
-        <v>88.5</v>
+        <v>89.48999786376953</v>
       </c>
       <c r="D159" t="n">
-        <v>86.65000152587891</v>
+        <v>86.69000244140625</v>
       </c>
       <c r="E159" t="n">
-        <v>86.94000244140625</v>
+        <v>87.01999664306641</v>
       </c>
       <c r="F159" t="n">
-        <v>29408300</v>
+        <v>32335700</v>
       </c>
       <c r="G159" t="n">
         <v>0</v>
@@ -4577,22 +4577,22 @@
     </row>
     <row r="160">
       <c r="A160" s="1" t="n">
-        <v>46157</v>
+        <v>46160</v>
       </c>
       <c r="B160" t="n">
-        <v>87.69000244140625</v>
+        <v>86.5</v>
       </c>
       <c r="C160" t="n">
-        <v>89.48999786376953</v>
+        <v>89.81999969482422</v>
       </c>
       <c r="D160" t="n">
-        <v>86.69000244140625</v>
+        <v>86.33000183105469</v>
       </c>
       <c r="E160" t="n">
-        <v>87.01999664306641</v>
+        <v>89.65000152587891</v>
       </c>
       <c r="F160" t="n">
-        <v>32335700</v>
+        <v>35800500</v>
       </c>
       <c r="G160" t="n">
         <v>0</v>
@@ -4603,22 +4603,22 @@
     </row>
     <row r="161">
       <c r="A161" s="1" t="n">
-        <v>46160</v>
+        <v>46161</v>
       </c>
       <c r="B161" t="n">
-        <v>86.5</v>
+        <v>90.13999938964844</v>
       </c>
       <c r="C161" t="n">
-        <v>89.81999969482422</v>
+        <v>91.48000335693359</v>
       </c>
       <c r="D161" t="n">
-        <v>86.33000183105469</v>
+        <v>88.69000244140625</v>
       </c>
       <c r="E161" t="n">
-        <v>89.65000152587891</v>
+        <v>89.33000183105469</v>
       </c>
       <c r="F161" t="n">
-        <v>35800500</v>
+        <v>34545700</v>
       </c>
       <c r="G161" t="n">
         <v>0</v>
@@ -4629,22 +4629,22 @@
     </row>
     <row r="162">
       <c r="A162" s="1" t="n">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="B162" t="n">
-        <v>90.13999938964844</v>
+        <v>88.51999664306641</v>
       </c>
       <c r="C162" t="n">
-        <v>91.48000335693359</v>
+        <v>88.55000305175781</v>
       </c>
       <c r="D162" t="n">
-        <v>88.69000244140625</v>
+        <v>87.5</v>
       </c>
       <c r="E162" t="n">
-        <v>89.33000183105469</v>
+        <v>88.08999633789062</v>
       </c>
       <c r="F162" t="n">
-        <v>34545700</v>
+        <v>23463400</v>
       </c>
       <c r="G162" t="n">
         <v>0</v>
@@ -4655,22 +4655,22 @@
     </row>
     <row r="163">
       <c r="A163" s="1" t="n">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="B163" t="n">
-        <v>88.51999664306641</v>
+        <v>88.02999877929688</v>
       </c>
       <c r="C163" t="n">
-        <v>88.55000305175781</v>
+        <v>90.37000274658203</v>
       </c>
       <c r="D163" t="n">
-        <v>87.5</v>
+        <v>87.51999664306641</v>
       </c>
       <c r="E163" t="n">
-        <v>88.08999633789062</v>
+        <v>89.30000305175781</v>
       </c>
       <c r="F163" t="n">
-        <v>23463400</v>
+        <v>28613900</v>
       </c>
       <c r="G163" t="n">
         <v>0</v>
@@ -4681,22 +4681,22 @@
     </row>
     <row r="164">
       <c r="A164" s="1" t="n">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="B164" t="n">
-        <v>88.02999877929688</v>
+        <v>89.09999847412109</v>
       </c>
       <c r="C164" t="n">
-        <v>90.37000274658203</v>
+        <v>89.97000122070312</v>
       </c>
       <c r="D164" t="n">
-        <v>87.51999664306641</v>
+        <v>88.16999816894531</v>
       </c>
       <c r="E164" t="n">
-        <v>89.30000305175781</v>
+        <v>88.59999847412109</v>
       </c>
       <c r="F164" t="n">
-        <v>28613900</v>
+        <v>23847200</v>
       </c>
       <c r="G164" t="n">
         <v>0</v>
@@ -4707,22 +4707,22 @@
     </row>
     <row r="165">
       <c r="A165" s="1" t="n">
-        <v>46164</v>
+        <v>46168</v>
       </c>
       <c r="B165" t="n">
-        <v>89.09999847412109</v>
+        <v>88.40000152587891</v>
       </c>
       <c r="C165" t="n">
-        <v>89.97000122070312</v>
+        <v>88.73000335693359</v>
       </c>
       <c r="D165" t="n">
-        <v>88.16999816894531</v>
+        <v>87.25</v>
       </c>
       <c r="E165" t="n">
-        <v>88.59999847412109</v>
+        <v>87.68000030517578</v>
       </c>
       <c r="F165" t="n">
-        <v>23847200</v>
+        <v>24014500</v>
       </c>
       <c r="G165" t="n">
         <v>0</v>
@@ -4733,22 +4733,22 @@
     </row>
     <row r="166">
       <c r="A166" s="1" t="n">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="B166" t="n">
-        <v>88.40000152587891</v>
+        <v>87.05000305175781</v>
       </c>
       <c r="C166" t="n">
-        <v>88.73000335693359</v>
+        <v>88.5</v>
       </c>
       <c r="D166" t="n">
-        <v>87.25</v>
+        <v>86.81999969482422</v>
       </c>
       <c r="E166" t="n">
-        <v>87.68000030517578</v>
+        <v>87.34999847412109</v>
       </c>
       <c r="F166" t="n">
-        <v>24014500</v>
+        <v>22569500</v>
       </c>
       <c r="G166" t="n">
         <v>0</v>
@@ -4759,22 +4759,22 @@
     </row>
     <row r="167">
       <c r="A167" s="1" t="n">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="B167" t="n">
-        <v>87.05000305175781</v>
+        <v>86.90000152587891</v>
       </c>
       <c r="C167" t="n">
-        <v>88.5</v>
+        <v>87.04000091552734</v>
       </c>
       <c r="D167" t="n">
-        <v>86.81999969482422</v>
+        <v>85.58999633789062</v>
       </c>
       <c r="E167" t="n">
-        <v>87.34999847412109</v>
+        <v>86.36000061035156</v>
       </c>
       <c r="F167" t="n">
-        <v>22569500</v>
+        <v>38803800</v>
       </c>
       <c r="G167" t="n">
         <v>0</v>
@@ -4785,22 +4785,22 @@
     </row>
     <row r="168">
       <c r="A168" s="1" t="n">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="B168" t="n">
-        <v>86.90000152587891</v>
+        <v>86.19999694824219</v>
       </c>
       <c r="C168" t="n">
-        <v>87.04000091552734</v>
+        <v>86.66999816894531</v>
       </c>
       <c r="D168" t="n">
-        <v>85.58999633789062</v>
+        <v>85.66000366210938</v>
       </c>
       <c r="E168" t="n">
-        <v>86.36000061035156</v>
+        <v>86.01999664306641</v>
       </c>
       <c r="F168" t="n">
-        <v>38803800</v>
+        <v>39793600</v>
       </c>
       <c r="G168" t="n">
         <v>0</v>
@@ -4811,22 +4811,22 @@
     </row>
     <row r="169">
       <c r="A169" s="1" t="n">
-        <v>46171</v>
+        <v>46174</v>
       </c>
       <c r="B169" t="n">
-        <v>86.19999694824219</v>
+        <v>85.73000335693359</v>
       </c>
       <c r="C169" t="n">
-        <v>86.66999816894531</v>
+        <v>87.23000335693359</v>
       </c>
       <c r="D169" t="n">
-        <v>85.66000366210938</v>
+        <v>85.31999969482422</v>
       </c>
       <c r="E169" t="n">
-        <v>86.01999664306641</v>
+        <v>85.84999847412109</v>
       </c>
       <c r="F169" t="n">
-        <v>39793600</v>
+        <v>32747200</v>
       </c>
       <c r="G169" t="n">
         <v>0</v>
@@ -4837,22 +4837,22 @@
     </row>
     <row r="170">
       <c r="A170" s="1" t="n">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="B170" t="n">
-        <v>85.73000335693359</v>
+        <v>85.61000061035156</v>
       </c>
       <c r="C170" t="n">
-        <v>87.23000335693359</v>
+        <v>85.98000335693359</v>
       </c>
       <c r="D170" t="n">
-        <v>85.31999969482422</v>
+        <v>83.29000091552734</v>
       </c>
       <c r="E170" t="n">
-        <v>85.84999847412109</v>
+        <v>83.33000183105469</v>
       </c>
       <c r="F170" t="n">
-        <v>32747200</v>
+        <v>42947200</v>
       </c>
       <c r="G170" t="n">
         <v>0</v>
@@ -4863,22 +4863,22 @@
     </row>
     <row r="171">
       <c r="A171" s="1" t="n">
-        <v>46175</v>
+        <v>46176</v>
       </c>
       <c r="B171" t="n">
-        <v>85.61000061035156</v>
+        <v>82.91000366210938</v>
       </c>
       <c r="C171" t="n">
-        <v>85.98000335693359</v>
+        <v>83.30999755859375</v>
       </c>
       <c r="D171" t="n">
-        <v>83.29000091552734</v>
+        <v>81.09999847412109</v>
       </c>
       <c r="E171" t="n">
-        <v>83.33000183105469</v>
+        <v>81.51999664306641</v>
       </c>
       <c r="F171" t="n">
-        <v>42947200</v>
+        <v>36714700</v>
       </c>
       <c r="G171" t="n">
         <v>0</v>
@@ -4889,22 +4889,22 @@
     </row>
     <row r="172">
       <c r="A172" s="1" t="n">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="B172" t="n">
-        <v>82.91000366210938</v>
+        <v>83.19000244140625</v>
       </c>
       <c r="C172" t="n">
-        <v>83.30999755859375</v>
+        <v>83.69999694824219</v>
       </c>
       <c r="D172" t="n">
-        <v>81.09999847412109</v>
+        <v>81.37000274658203</v>
       </c>
       <c r="E172" t="n">
-        <v>81.51999664306641</v>
+        <v>81.55999755859375</v>
       </c>
       <c r="F172" t="n">
-        <v>36714700</v>
+        <v>39338800</v>
       </c>
       <c r="G172" t="n">
         <v>0</v>
@@ -4915,22 +4915,22 @@
     </row>
     <row r="173">
       <c r="A173" s="1" t="n">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="B173" t="n">
-        <v>83.19000244140625</v>
+        <v>82.33000183105469</v>
       </c>
       <c r="C173" t="n">
-        <v>83.69999694824219</v>
+        <v>82.75</v>
       </c>
       <c r="D173" t="n">
-        <v>81.37000274658203</v>
+        <v>81</v>
       </c>
       <c r="E173" t="n">
-        <v>81.55999755859375</v>
+        <v>82.18000030517578</v>
       </c>
       <c r="F173" t="n">
-        <v>39338800</v>
+        <v>43474100</v>
       </c>
       <c r="G173" t="n">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="174">
       <c r="A174" s="1" t="n">
-        <v>46178</v>
+        <v>46181</v>
       </c>
       <c r="B174" t="n">
-        <v>82.33000183105469</v>
+        <v>81.66000366210938</v>
       </c>
       <c r="C174" t="n">
-        <v>82.75</v>
+        <v>83.08000183105469</v>
       </c>
       <c r="D174" t="n">
-        <v>81</v>
+        <v>81.33999633789062</v>
       </c>
       <c r="E174" t="n">
-        <v>82.18000030517578</v>
+        <v>82.63999938964844</v>
       </c>
       <c r="F174" t="n">
-        <v>43474100</v>
+        <v>33056700</v>
       </c>
       <c r="G174" t="n">
         <v>0</v>
@@ -4967,22 +4967,22 @@
     </row>
     <row r="175">
       <c r="A175" s="1" t="n">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="B175" t="n">
-        <v>81.66000366210938</v>
+        <v>82.12999725341797</v>
       </c>
       <c r="C175" t="n">
-        <v>83.08000183105469</v>
+        <v>82.33999633789062</v>
       </c>
       <c r="D175" t="n">
         <v>81.33999633789062</v>
       </c>
       <c r="E175" t="n">
-        <v>82.63999938964844</v>
+        <v>81.41000366210938</v>
       </c>
       <c r="F175" t="n">
-        <v>33056700</v>
+        <v>34787200</v>
       </c>
       <c r="G175" t="n">
         <v>0</v>
@@ -4993,22 +4993,22 @@
     </row>
     <row r="176">
       <c r="A176" s="1" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="B176" t="n">
-        <v>82.12999725341797</v>
+        <v>81.70999908447266</v>
       </c>
       <c r="C176" t="n">
-        <v>82.33999633789062</v>
+        <v>82.75</v>
       </c>
       <c r="D176" t="n">
-        <v>81.33999633789062</v>
+        <v>80.98000335693359</v>
       </c>
       <c r="E176" t="n">
-        <v>81.41000366210938</v>
+        <v>82</v>
       </c>
       <c r="F176" t="n">
-        <v>34787200</v>
+        <v>36304600</v>
       </c>
       <c r="G176" t="n">
         <v>0</v>
@@ -5019,22 +5019,22 @@
     </row>
     <row r="177">
       <c r="A177" s="1" t="n">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="B177" t="n">
-        <v>81.70999908447266</v>
+        <v>81.87000274658203</v>
       </c>
       <c r="C177" t="n">
-        <v>82.75</v>
+        <v>82.09999847412109</v>
       </c>
       <c r="D177" t="n">
-        <v>80.98000335693359</v>
+        <v>80.08999633789062</v>
       </c>
       <c r="E177" t="n">
-        <v>82</v>
+        <v>81.26999664306641</v>
       </c>
       <c r="F177" t="n">
-        <v>36304600</v>
+        <v>33417600</v>
       </c>
       <c r="G177" t="n">
         <v>0</v>
@@ -5045,22 +5045,22 @@
     </row>
     <row r="178">
       <c r="A178" s="1" t="n">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="B178" t="n">
-        <v>81.87000274658203</v>
+        <v>81.58000183105469</v>
       </c>
       <c r="C178" t="n">
-        <v>82.09999847412109</v>
+        <v>82</v>
       </c>
       <c r="D178" t="n">
-        <v>80.08999633789062</v>
+        <v>79.27999877929688</v>
       </c>
       <c r="E178" t="n">
-        <v>81.26999664306641</v>
+        <v>80.33999633789062</v>
       </c>
       <c r="F178" t="n">
-        <v>33417600</v>
+        <v>35309700</v>
       </c>
       <c r="G178" t="n">
         <v>0</v>
@@ -5071,22 +5071,22 @@
     </row>
     <row r="179">
       <c r="A179" s="1" t="n">
-        <v>46185</v>
+        <v>46188</v>
       </c>
       <c r="B179" t="n">
-        <v>81.58000183105469</v>
+        <v>80.62000274658203</v>
       </c>
       <c r="C179" t="n">
-        <v>82</v>
+        <v>81.70999908447266</v>
       </c>
       <c r="D179" t="n">
-        <v>79.27999877929688</v>
+        <v>80.45999908447266</v>
       </c>
       <c r="E179" t="n">
-        <v>80.33999633789062</v>
+        <v>81.66999816894531</v>
       </c>
       <c r="F179" t="n">
-        <v>35309700</v>
+        <v>36430800</v>
       </c>
       <c r="G179" t="n">
         <v>0</v>
@@ -5097,22 +5097,22 @@
     </row>
     <row r="180">
       <c r="A180" s="1" t="n">
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="B180" t="n">
-        <v>80.62000274658203</v>
+        <v>81.90000152587891</v>
       </c>
       <c r="C180" t="n">
-        <v>81.70999908447266</v>
+        <v>81.93000030517578</v>
       </c>
       <c r="D180" t="n">
-        <v>80.45999908447266</v>
+        <v>77.70999908447266</v>
       </c>
       <c r="E180" t="n">
-        <v>81.66999816894531</v>
+        <v>78.72000122070312</v>
       </c>
       <c r="F180" t="n">
-        <v>36430800</v>
+        <v>65054000</v>
       </c>
       <c r="G180" t="n">
         <v>0</v>
@@ -5123,22 +5123,22 @@
     </row>
     <row r="181">
       <c r="A181" s="1" t="n">
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="B181" t="n">
-        <v>81.90000152587891</v>
+        <v>78.09999847412109</v>
       </c>
       <c r="C181" t="n">
-        <v>81.93000030517578</v>
+        <v>78.44999694824219</v>
       </c>
       <c r="D181" t="n">
-        <v>77.70999908447266</v>
+        <v>76.76000213623047</v>
       </c>
       <c r="E181" t="n">
-        <v>78.72000122070312</v>
+        <v>76.95999908447266</v>
       </c>
       <c r="F181" t="n">
-        <v>65054000</v>
+        <v>50338800</v>
       </c>
       <c r="G181" t="n">
         <v>0</v>
@@ -5149,22 +5149,22 @@
     </row>
     <row r="182">
       <c r="A182" s="1" t="n">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="B182" t="n">
-        <v>78.09999847412109</v>
+        <v>76.93000030517578</v>
       </c>
       <c r="C182" t="n">
-        <v>78.44999694824219</v>
+        <v>78.23999786376953</v>
       </c>
       <c r="D182" t="n">
-        <v>76.76000213623047</v>
+        <v>76.12000274658203</v>
       </c>
       <c r="E182" t="n">
-        <v>76.95999908447266</v>
+        <v>77.37999725341797</v>
       </c>
       <c r="F182" t="n">
-        <v>50338800</v>
+        <v>91920400</v>
       </c>
       <c r="G182" t="n">
         <v>0</v>
@@ -5175,22 +5175,22 @@
     </row>
     <row r="183">
       <c r="A183" s="1" t="n">
-        <v>46191</v>
+        <v>46195</v>
       </c>
       <c r="B183" t="n">
-        <v>76.93000030517578</v>
+        <v>76.13999938964844</v>
       </c>
       <c r="C183" t="n">
-        <v>78.23999786376953</v>
+        <v>77.08999633789062</v>
       </c>
       <c r="D183" t="n">
-        <v>76.12000274658203</v>
+        <v>71.80999755859375</v>
       </c>
       <c r="E183" t="n">
-        <v>77.37999725341797</v>
+        <v>72.87999725341797</v>
       </c>
       <c r="F183" t="n">
-        <v>91920400</v>
+        <v>82203300</v>
       </c>
       <c r="G183" t="n">
         <v>0</v>
@@ -5201,22 +5201,22 @@
     </row>
     <row r="184">
       <c r="A184" s="1" t="n">
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="B184" t="n">
-        <v>76.13999938964844</v>
+        <v>73.26000213623047</v>
       </c>
       <c r="C184" t="n">
-        <v>77.08999633789062</v>
+        <v>73.95999908447266</v>
       </c>
       <c r="D184" t="n">
-        <v>71.80999755859375</v>
+        <v>72.62999725341797</v>
       </c>
       <c r="E184" t="n">
-        <v>72.87999725341797</v>
+        <v>72.81999969482422</v>
       </c>
       <c r="F184" t="n">
-        <v>82203300</v>
+        <v>50806800</v>
       </c>
       <c r="G184" t="n">
         <v>0</v>
@@ -5227,22 +5227,22 @@
     </row>
     <row r="185">
       <c r="A185" s="1" t="n">
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="B185" t="n">
-        <v>73.26000213623047</v>
+        <v>72.69000244140625</v>
       </c>
       <c r="C185" t="n">
-        <v>73.95999908447266</v>
+        <v>73.44999694824219</v>
       </c>
       <c r="D185" t="n">
-        <v>72.62999725341797</v>
+        <v>71.62999725341797</v>
       </c>
       <c r="E185" t="n">
-        <v>72.81999969482422</v>
+        <v>71.83999633789062</v>
       </c>
       <c r="F185" t="n">
-        <v>50806800</v>
+        <v>48001500</v>
       </c>
       <c r="G185" t="n">
         <v>0</v>
@@ -5253,22 +5253,22 @@
     </row>
     <row r="186">
       <c r="A186" s="1" t="n">
-        <v>46197</v>
+        <v>46198</v>
       </c>
       <c r="B186" t="n">
-        <v>72.69000244140625</v>
+        <v>71.33000183105469</v>
       </c>
       <c r="C186" t="n">
-        <v>73.44999694824219</v>
+        <v>72.94000244140625</v>
       </c>
       <c r="D186" t="n">
-        <v>71.62999725341797</v>
+        <v>70.86000061035156</v>
       </c>
       <c r="E186" t="n">
-        <v>71.83999633789062</v>
+        <v>70.90000152587891</v>
       </c>
       <c r="F186" t="n">
-        <v>48001500</v>
+        <v>44446900</v>
       </c>
       <c r="G186" t="n">
         <v>0</v>
@@ -5279,22 +5279,22 @@
     </row>
     <row r="187">
       <c r="A187" s="1" t="n">
-        <v>46198</v>
+        <v>46199</v>
       </c>
       <c r="B187" t="n">
-        <v>71.33000183105469</v>
+        <v>71.69000244140625</v>
       </c>
       <c r="C187" t="n">
-        <v>72.94000244140625</v>
+        <v>75.19999694824219</v>
       </c>
       <c r="D187" t="n">
-        <v>70.86000061035156</v>
+        <v>71.52999877929688</v>
       </c>
       <c r="E187" t="n">
-        <v>70.90000152587891</v>
+        <v>73.80999755859375</v>
       </c>
       <c r="F187" t="n">
-        <v>44446900</v>
+        <v>74990300</v>
       </c>
       <c r="G187" t="n">
         <v>0</v>
@@ -5305,22 +5305,22 @@
     </row>
     <row r="188">
       <c r="A188" s="1" t="n">
-        <v>46199</v>
+        <v>46202</v>
       </c>
       <c r="B188" t="n">
-        <v>71.69000244140625</v>
+        <v>74.62000274658203</v>
       </c>
       <c r="C188" t="n">
-        <v>75.19999694824219</v>
+        <v>76.06999969482422</v>
       </c>
       <c r="D188" t="n">
-        <v>71.52999877929688</v>
+        <v>73.73000335693359</v>
       </c>
       <c r="E188" t="n">
-        <v>73.80999755859375</v>
+        <v>73.77999877929688</v>
       </c>
       <c r="F188" t="n">
-        <v>74990300</v>
+        <v>42429600</v>
       </c>
       <c r="G188" t="n">
         <v>0</v>
@@ -5331,22 +5331,22 @@
     </row>
     <row r="189">
       <c r="A189" s="1" t="n">
-        <v>46202</v>
+        <v>46203</v>
       </c>
       <c r="B189" t="n">
-        <v>74.62000274658203</v>
+        <v>73.58999633789062</v>
       </c>
       <c r="C189" t="n">
-        <v>76.06999969482422</v>
+        <v>73.75</v>
       </c>
       <c r="D189" t="n">
-        <v>73.73000335693359</v>
+        <v>71</v>
       </c>
       <c r="E189" t="n">
-        <v>73.77999877929688</v>
+        <v>71.40000152587891</v>
       </c>
       <c r="F189" t="n">
-        <v>42429600</v>
+        <v>49240900</v>
       </c>
       <c r="G189" t="n">
         <v>0</v>
@@ -5357,22 +5357,22 @@
     </row>
     <row r="190">
       <c r="A190" s="1" t="n">
-        <v>46203</v>
+        <v>46204</v>
       </c>
       <c r="B190" t="n">
-        <v>73.58999633789062</v>
+        <v>72.58999633789062</v>
       </c>
       <c r="C190" t="n">
-        <v>73.75</v>
+        <v>74.36000061035156</v>
       </c>
       <c r="D190" t="n">
-        <v>71</v>
+        <v>72.33000183105469</v>
       </c>
       <c r="E190" t="n">
-        <v>71.40000152587891</v>
+        <v>74.19000244140625</v>
       </c>
       <c r="F190" t="n">
-        <v>49240900</v>
+        <v>43841800</v>
       </c>
       <c r="G190" t="n">
         <v>0</v>
@@ -5383,22 +5383,22 @@
     </row>
     <row r="191">
       <c r="A191" s="1" t="n">
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="B191" t="n">
-        <v>72.58999633789062</v>
+        <v>75.08999633789062</v>
       </c>
       <c r="C191" t="n">
-        <v>74.36000061035156</v>
+        <v>78.44000244140625</v>
       </c>
       <c r="D191" t="n">
-        <v>72.33000183105469</v>
+        <v>74.91000366210938</v>
       </c>
       <c r="E191" t="n">
-        <v>74.19000244140625</v>
+        <v>77.65000152587891</v>
       </c>
       <c r="F191" t="n">
-        <v>43841800</v>
+        <v>55456500</v>
       </c>
       <c r="G191" t="n">
         <v>0</v>
@@ -5409,22 +5409,22 @@
     </row>
     <row r="192">
       <c r="A192" s="1" t="n">
-        <v>46205</v>
+        <v>46209</v>
       </c>
       <c r="B192" t="n">
-        <v>75.08999633789062</v>
+        <v>77.08000183105469</v>
       </c>
       <c r="C192" t="n">
-        <v>78.44000244140625</v>
+        <v>77.83999633789062</v>
       </c>
       <c r="D192" t="n">
-        <v>74.91000366210938</v>
+        <v>75.70999908447266</v>
       </c>
       <c r="E192" t="n">
-        <v>77.65000152587891</v>
+        <v>76.01999664306641</v>
       </c>
       <c r="F192" t="n">
-        <v>55456500</v>
+        <v>45056600</v>
       </c>
       <c r="G192" t="n">
         <v>0</v>
@@ -5435,22 +5435,22 @@
     </row>
     <row r="193">
       <c r="A193" s="1" t="n">
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="B193" t="n">
-        <v>77.08000183105469</v>
+        <v>77.87999725341797</v>
       </c>
       <c r="C193" t="n">
-        <v>77.83999633789062</v>
+        <v>78.19000244140625</v>
       </c>
       <c r="D193" t="n">
-        <v>75.70999908447266</v>
+        <v>76.09999847412109</v>
       </c>
       <c r="E193" t="n">
-        <v>76.01999664306641</v>
+        <v>76.18000030517578</v>
       </c>
       <c r="F193" t="n">
-        <v>45056600</v>
+        <v>33257300</v>
       </c>
       <c r="G193" t="n">
         <v>0</v>
@@ -5461,22 +5461,22 @@
     </row>
     <row r="194">
       <c r="A194" s="1" t="n">
-        <v>46210</v>
+        <v>46211</v>
       </c>
       <c r="B194" t="n">
-        <v>77.87999725341797</v>
+        <v>76.26999664306641</v>
       </c>
       <c r="C194" t="n">
-        <v>78.19000244140625</v>
+        <v>76.63999938964844</v>
       </c>
       <c r="D194" t="n">
-        <v>76.09999847412109</v>
+        <v>74.88999938964844</v>
       </c>
       <c r="E194" t="n">
-        <v>76.18000030517578</v>
+        <v>75.58999633789062</v>
       </c>
       <c r="F194" t="n">
-        <v>33257300</v>
+        <v>34373500</v>
       </c>
       <c r="G194" t="n">
         <v>0</v>
@@ -5487,22 +5487,22 @@
     </row>
     <row r="195">
       <c r="A195" s="1" t="n">
-        <v>46211</v>
+        <v>46212</v>
       </c>
       <c r="B195" t="n">
-        <v>76.26999664306641</v>
+        <v>74.30000305175781</v>
       </c>
       <c r="C195" t="n">
-        <v>76.63999938964844</v>
+        <v>75.55000305175781</v>
       </c>
       <c r="D195" t="n">
-        <v>74.88999938964844</v>
+        <v>74.01999664306641</v>
       </c>
       <c r="E195" t="n">
-        <v>75.58999633789062</v>
+        <v>75.47000122070312</v>
       </c>
       <c r="F195" t="n">
-        <v>34373500</v>
+        <v>36305700</v>
       </c>
       <c r="G195" t="n">
         <v>0</v>
@@ -5513,22 +5513,22 @@
     </row>
     <row r="196">
       <c r="A196" s="1" t="n">
-        <v>46212</v>
+        <v>46213</v>
       </c>
       <c r="B196" t="n">
-        <v>74.30000305175781</v>
+        <v>75.44000244140625</v>
       </c>
       <c r="C196" t="n">
-        <v>75.55000305175781</v>
+        <v>75.69999694824219</v>
       </c>
       <c r="D196" t="n">
-        <v>74.01999664306641</v>
+        <v>72.51000213623047</v>
       </c>
       <c r="E196" t="n">
-        <v>75.47000122070312</v>
+        <v>73.37000274658203</v>
       </c>
       <c r="F196" t="n">
-        <v>36305700</v>
+        <v>46713900</v>
       </c>
       <c r="G196" t="n">
         <v>0</v>
@@ -5539,22 +5539,22 @@
     </row>
     <row r="197">
       <c r="A197" s="1" t="n">
-        <v>46213</v>
+        <v>46216</v>
       </c>
       <c r="B197" t="n">
-        <v>75.44000244140625</v>
+        <v>73.90000152587891</v>
       </c>
       <c r="C197" t="n">
-        <v>75.69999694824219</v>
+        <v>75.44999694824219</v>
       </c>
       <c r="D197" t="n">
-        <v>72.51000213623047</v>
+        <v>73.70999908447266</v>
       </c>
       <c r="E197" t="n">
-        <v>73.37000274658203</v>
+        <v>73.83000183105469</v>
       </c>
       <c r="F197" t="n">
-        <v>46713900</v>
+        <v>35101800</v>
       </c>
       <c r="G197" t="n">
         <v>0</v>
@@ -5565,22 +5565,22 @@
     </row>
     <row r="198">
       <c r="A198" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="B198" t="n">
-        <v>73.90000152587891</v>
+        <v>72.63999938964844</v>
       </c>
       <c r="C198" t="n">
-        <v>75.44999694824219</v>
+        <v>74.01000213623047</v>
       </c>
       <c r="D198" t="n">
-        <v>73.70999908447266</v>
+        <v>72.27999877929688</v>
       </c>
       <c r="E198" t="n">
-        <v>73.83000183105469</v>
+        <v>73.52999877929688</v>
       </c>
       <c r="F198" t="n">
-        <v>35101800</v>
+        <v>33312100</v>
       </c>
       <c r="G198" t="n">
         <v>0</v>
@@ -5591,22 +5591,22 @@
     </row>
     <row r="199">
       <c r="A199" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="B199" t="n">
-        <v>72.63999938964844</v>
+        <v>73.79000091552734</v>
       </c>
       <c r="C199" t="n">
-        <v>74.01000213623047</v>
+        <v>75.05999755859375</v>
       </c>
       <c r="D199" t="n">
-        <v>72.27999877929688</v>
+        <v>73.12999725341797</v>
       </c>
       <c r="E199" t="n">
-        <v>73.52999877929688</v>
+        <v>73.68000030517578</v>
       </c>
       <c r="F199" t="n">
-        <v>33312100</v>
+        <v>32854300</v>
       </c>
       <c r="G199" t="n">
         <v>0</v>
@@ -5617,22 +5617,22 @@
     </row>
     <row r="200">
       <c r="A200" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="B200" t="n">
-        <v>73.79000091552734</v>
+        <v>73.94999694824219</v>
       </c>
       <c r="C200" t="n">
-        <v>75.05999755859375</v>
+        <v>74.68000030517578</v>
       </c>
       <c r="D200" t="n">
-        <v>73.12999725341797</v>
+        <v>72.94000244140625</v>
       </c>
       <c r="E200" t="n">
-        <v>73.68000030517578</v>
+        <v>74.34999847412109</v>
       </c>
       <c r="F200" t="n">
-        <v>32854300</v>
+        <v>77505200</v>
       </c>
       <c r="G200" t="n">
         <v>0</v>
@@ -5643,22 +5643,22 @@
     </row>
     <row r="201">
       <c r="A201" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="B201" t="n">
-        <v>73.94999694824219</v>
+        <v>65.48000335693359</v>
       </c>
       <c r="C201" t="n">
-        <v>74.68000030517578</v>
+        <v>69.48999786376953</v>
       </c>
       <c r="D201" t="n">
-        <v>72.94000244140625</v>
+        <v>65.08000183105469</v>
       </c>
       <c r="E201" t="n">
-        <v>74.34999847412109</v>
+        <v>68.94999694824219</v>
       </c>
       <c r="F201" t="n">
-        <v>77505200</v>
+        <v>142029200</v>
       </c>
       <c r="G201" t="n">
         <v>0</v>
@@ -5669,22 +5669,22 @@
     </row>
     <row r="202">
       <c r="A202" s="1" t="n">
-        <v>46220</v>
+        <v>46223</v>
       </c>
       <c r="B202" t="n">
-        <v>65.48000335693359</v>
+        <v>68.31999969482422</v>
       </c>
       <c r="C202" t="n">
-        <v>69.48999786376953</v>
+        <v>68.37999725341797</v>
       </c>
       <c r="D202" t="n">
-        <v>65.08000183105469</v>
+        <v>66.69000244140625</v>
       </c>
       <c r="E202" t="n">
-        <v>68.94999694824219</v>
+        <v>67.59999847412109</v>
       </c>
       <c r="F202" t="n">
-        <v>142029200</v>
+        <v>60669100</v>
       </c>
       <c r="G202" t="n">
         <v>0</v>
@@ -5695,22 +5695,22 @@
     </row>
     <row r="203">
       <c r="A203" s="1" t="n">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="B203" t="n">
-        <v>68.31999969482422</v>
+        <v>67.41999816894531</v>
       </c>
       <c r="C203" t="n">
-        <v>68.37999725341797</v>
+        <v>68.75</v>
       </c>
       <c r="D203" t="n">
-        <v>66.69000244140625</v>
+        <v>66.73000335693359</v>
       </c>
       <c r="E203" t="n">
-        <v>67.59999847412109</v>
+        <v>68.66999816894531</v>
       </c>
       <c r="F203" t="n">
-        <v>60669100</v>
+        <v>56565800</v>
       </c>
       <c r="G203" t="n">
         <v>0</v>
@@ -5721,22 +5721,22 @@
     </row>
     <row r="204">
       <c r="A204" s="1" t="n">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="B204" t="n">
-        <v>67.41999816894531</v>
+        <v>69.37000274658203</v>
       </c>
       <c r="C204" t="n">
-        <v>68.75</v>
+        <v>70.56999969482422</v>
       </c>
       <c r="D204" t="n">
-        <v>66.73000335693359</v>
+        <v>68.34999847412109</v>
       </c>
       <c r="E204" t="n">
-        <v>68.66999816894531</v>
+        <v>68.52999877929688</v>
       </c>
       <c r="F204" t="n">
-        <v>56565800</v>
+        <v>44947300</v>
       </c>
       <c r="G204" t="n">
         <v>0</v>
@@ -5747,22 +5747,22 @@
     </row>
     <row r="205">
       <c r="A205" s="1" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="B205" t="n">
-        <v>69.37000274658203</v>
+        <v>68.56999969482422</v>
       </c>
       <c r="C205" t="n">
-        <v>70.56999969482422</v>
+        <v>69.36000061035156</v>
       </c>
       <c r="D205" t="n">
-        <v>68.34999847412109</v>
+        <v>67.66999816894531</v>
       </c>
       <c r="E205" t="n">
-        <v>68.52999877929688</v>
+        <v>68.88999938964844</v>
       </c>
       <c r="F205" t="n">
-        <v>44947300</v>
+        <v>45029100</v>
       </c>
       <c r="G205" t="n">
         <v>0</v>
@@ -5773,22 +5773,22 @@
     </row>
     <row r="206">
       <c r="A206" s="1" t="n">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="B206" t="n">
-        <v>68.56999969482422</v>
+        <v>69.29000091552734</v>
       </c>
       <c r="C206" t="n">
-        <v>69.36000061035156</v>
+        <v>70.68000030517578</v>
       </c>
       <c r="D206" t="n">
-        <v>67.66999816894531</v>
+        <v>67.97000122070312</v>
       </c>
       <c r="E206" t="n">
-        <v>68.88999938964844</v>
+        <v>70.08999633789062</v>
       </c>
       <c r="F206" t="n">
-        <v>45029100</v>
+        <v>37593500</v>
       </c>
       <c r="G206" t="n">
         <v>0</v>
@@ -5799,22 +5799,22 @@
     </row>
     <row r="207">
       <c r="A207" s="1" t="n">
-        <v>46227</v>
+        <v>46230</v>
       </c>
       <c r="B207" t="n">
-        <v>69.29000091552734</v>
+        <v>70.58999633789062</v>
       </c>
       <c r="C207" t="n">
-        <v>70.68000030517578</v>
+        <v>71.65000152587891</v>
       </c>
       <c r="D207" t="n">
-        <v>67.97000122070312</v>
+        <v>69.86000061035156</v>
       </c>
       <c r="E207" t="n">
-        <v>70.08999633789062</v>
+        <v>70.40000152587891</v>
       </c>
       <c r="F207" t="n">
-        <v>37593500</v>
+        <v>39090800</v>
       </c>
       <c r="G207" t="n">
         <v>0</v>
@@ -5825,22 +5825,22 @@
     </row>
     <row r="208">
       <c r="A208" s="1" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="B208" t="n">
-        <v>70.58999633789062</v>
+        <v>72.06999969482422</v>
       </c>
       <c r="C208" t="n">
-        <v>71.65000152587891</v>
+        <v>73.76000213623047</v>
       </c>
       <c r="D208" t="n">
-        <v>69.86000061035156</v>
+        <v>71.23000335693359</v>
       </c>
       <c r="E208" t="n">
-        <v>70.40000152587891</v>
+        <v>72.38999938964844</v>
       </c>
       <c r="F208" t="n">
-        <v>39090800</v>
+        <v>47160200</v>
       </c>
       <c r="G208" t="n">
         <v>0</v>
@@ -5851,22 +5851,22 @@
     </row>
     <row r="209">
       <c r="A209" s="1" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="B209" t="n">
-        <v>72.06999969482422</v>
+        <v>72.19000244140625</v>
       </c>
       <c r="C209" t="n">
-        <v>73.76000213623047</v>
+        <v>73.73999786376953</v>
       </c>
       <c r="D209" t="n">
-        <v>71.23000335693359</v>
+        <v>71.75</v>
       </c>
       <c r="E209" t="n">
-        <v>72.38999938964844</v>
+        <v>73.62999725341797</v>
       </c>
       <c r="F209" t="n">
-        <v>47160200</v>
+        <v>43737600</v>
       </c>
       <c r="G209" t="n">
         <v>0</v>
@@ -5877,22 +5877,22 @@
     </row>
     <row r="210">
       <c r="A210" s="1" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="B210" t="n">
-        <v>72.19000244140625</v>
+        <v>71.48000335693359</v>
       </c>
       <c r="C210" t="n">
-        <v>73.73999786376953</v>
+        <v>73.31999969482422</v>
       </c>
       <c r="D210" t="n">
-        <v>71.75</v>
+        <v>70.55000305175781</v>
       </c>
       <c r="E210" t="n">
-        <v>73.62999725341797</v>
+        <v>73.16999816894531</v>
       </c>
       <c r="F210" t="n">
-        <v>43737600</v>
+        <v>54261000</v>
       </c>
       <c r="G210" t="n">
         <v>0</v>
@@ -5903,22 +5903,22 @@
     </row>
     <row r="211">
       <c r="A211" s="1" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="B211" t="n">
-        <v>71.48000335693359</v>
+        <v>71.97000122070312</v>
       </c>
       <c r="C211" t="n">
-        <v>73.31999969482422</v>
+        <v>72.75</v>
       </c>
       <c r="D211" t="n">
-        <v>70.55000305175781</v>
+        <v>71.11000061035156</v>
       </c>
       <c r="E211" t="n">
-        <v>73.16999816894531</v>
+        <v>71.70999908447266</v>
       </c>
       <c r="F211" t="n">
-        <v>54261000</v>
+        <v>35847500</v>
       </c>
       <c r="G211" t="n">
         <v>0</v>
@@ -5929,22 +5929,22 @@
     </row>
     <row r="212">
       <c r="A212" s="1" t="n">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="B212" t="n">
-        <v>71.97000122070312</v>
+        <v>72.76999664306641</v>
       </c>
       <c r="C212" t="n">
-        <v>72.75</v>
+        <v>73.94999694824219</v>
       </c>
       <c r="D212" t="n">
-        <v>71.11000061035156</v>
+        <v>72.18000030517578</v>
       </c>
       <c r="E212" t="n">
-        <v>71.70999908447266</v>
+        <v>73.33000183105469</v>
       </c>
       <c r="F212" t="n">
-        <v>35847500</v>
+        <v>33922300</v>
       </c>
       <c r="G212" t="n">
         <v>0</v>
@@ -5955,22 +5955,22 @@
     </row>
     <row r="213">
       <c r="A213" s="1" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="B213" t="n">
-        <v>72.76999664306641</v>
+        <v>72.51000213623047</v>
       </c>
       <c r="C213" t="n">
-        <v>73.94999694824219</v>
+        <v>73.75</v>
       </c>
       <c r="D213" t="n">
-        <v>72.18000030517578</v>
+        <v>72.30000305175781</v>
       </c>
       <c r="E213" t="n">
-        <v>73.33000183105469</v>
+        <v>73.56999969482422</v>
       </c>
       <c r="F213" t="n">
-        <v>33922300</v>
+        <v>42877900</v>
       </c>
       <c r="G213" t="n">
         <v>0</v>
@@ -5981,22 +5981,22 @@
     </row>
     <row r="214">
       <c r="A214" s="1" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="B214" t="n">
-        <v>72.51000213623047</v>
+        <v>75.11000061035156</v>
       </c>
       <c r="C214" t="n">
-        <v>73.75</v>
+        <v>75.30000305175781</v>
       </c>
       <c r="D214" t="n">
-        <v>72.30000305175781</v>
+        <v>73.16000366210938</v>
       </c>
       <c r="E214" t="n">
-        <v>73.56999969482422</v>
+        <v>74.19999694824219</v>
       </c>
       <c r="F214" t="n">
-        <v>42877900</v>
+        <v>28969400</v>
       </c>
       <c r="G214" t="n">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="215">
       <c r="A215" s="1" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="B215" t="n">
-        <v>75.11000061035156</v>
+        <v>75.13999938964844</v>
       </c>
       <c r="C215" t="n">
-        <v>75.30000305175781</v>
+        <v>75.20999908447266</v>
       </c>
       <c r="D215" t="n">
-        <v>73.16000366210938</v>
+        <v>73.09999847412109</v>
       </c>
       <c r="E215" t="n">
-        <v>74.19999694824219</v>
+        <v>73.69000244140625</v>
       </c>
       <c r="F215" t="n">
-        <v>28969400</v>
+        <v>28892700</v>
       </c>
       <c r="G215" t="n">
         <v>0</v>
@@ -6033,22 +6033,22 @@
     </row>
     <row r="216">
       <c r="A216" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="B216" t="n">
-        <v>75.13999938964844</v>
+        <v>73.12000274658203</v>
       </c>
       <c r="C216" t="n">
-        <v>75.20999908447266</v>
+        <v>74.5</v>
       </c>
       <c r="D216" t="n">
-        <v>73.09999847412109</v>
+        <v>73.08000183105469</v>
       </c>
       <c r="E216" t="n">
-        <v>73.69000244140625</v>
+        <v>74.13999938964844</v>
       </c>
       <c r="F216" t="n">
-        <v>28892700</v>
+        <v>24819000</v>
       </c>
       <c r="G216" t="n">
         <v>0</v>
@@ -6059,22 +6059,22 @@
     </row>
     <row r="217">
       <c r="A217" s="1" t="n">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="B217" t="n">
-        <v>73.12000274658203</v>
+        <v>73.80000305175781</v>
       </c>
       <c r="C217" t="n">
-        <v>74.5</v>
+        <v>76.31999969482422</v>
       </c>
       <c r="D217" t="n">
-        <v>73.08000183105469</v>
+        <v>73.56999969482422</v>
       </c>
       <c r="E217" t="n">
-        <v>74.13999938964844</v>
+        <v>76.29000091552734</v>
       </c>
       <c r="F217" t="n">
-        <v>24819000</v>
+        <v>26959900</v>
       </c>
       <c r="G217" t="n">
         <v>0</v>
@@ -6085,22 +6085,22 @@
     </row>
     <row r="218">
       <c r="A218" s="1" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="B218" t="n">
-        <v>73.80000305175781</v>
+        <v>76.19999694824219</v>
       </c>
       <c r="C218" t="n">
-        <v>76.31999969482422</v>
+        <v>76.90000152587891</v>
       </c>
       <c r="D218" t="n">
-        <v>73.56999969482422</v>
+        <v>74.48000335693359</v>
       </c>
       <c r="E218" t="n">
-        <v>76.29000091552734</v>
+        <v>74.79000091552734</v>
       </c>
       <c r="F218" t="n">
-        <v>26959900</v>
+        <v>27840500</v>
       </c>
       <c r="G218" t="n">
         <v>0</v>
@@ -6111,22 +6111,22 @@
     </row>
     <row r="219">
       <c r="A219" s="1" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="B219" t="n">
-        <v>76.19999694824219</v>
+        <v>74.34999847412109</v>
       </c>
       <c r="C219" t="n">
-        <v>76.90000152587891</v>
+        <v>74.66999816894531</v>
       </c>
       <c r="D219" t="n">
-        <v>74.48000335693359</v>
+        <v>73.56999969482422</v>
       </c>
       <c r="E219" t="n">
-        <v>74.79000091552734</v>
+        <v>74.20999908447266</v>
       </c>
       <c r="F219" t="n">
-        <v>27840500</v>
+        <v>20773100</v>
       </c>
       <c r="G219" t="n">
         <v>0</v>
@@ -6137,22 +6137,22 @@
     </row>
     <row r="220">
       <c r="A220" s="1" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="B220" t="n">
-        <v>74.34999847412109</v>
+        <v>76.01000213623047</v>
       </c>
       <c r="C220" t="n">
-        <v>74.66999816894531</v>
+        <v>78.40000152587891</v>
       </c>
       <c r="D220" t="n">
-        <v>73.56999969482422</v>
+        <v>75.44000244140625</v>
       </c>
       <c r="E220" t="n">
-        <v>74.20999908447266</v>
+        <v>78.23999786376953</v>
       </c>
       <c r="F220" t="n">
-        <v>20773100</v>
+        <v>41452900</v>
       </c>
       <c r="G220" t="n">
         <v>0</v>
@@ -6163,22 +6163,22 @@
     </row>
     <row r="221">
       <c r="A221" s="1" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="B221" t="n">
-        <v>76.01000213623047</v>
+        <v>78.48000335693359</v>
       </c>
       <c r="C221" t="n">
-        <v>78.40000152587891</v>
+        <v>78.73000335693359</v>
       </c>
       <c r="D221" t="n">
-        <v>75.44000244140625</v>
+        <v>77.76000213623047</v>
       </c>
       <c r="E221" t="n">
-        <v>78.23999786376953</v>
+        <v>78.16000366210938</v>
       </c>
       <c r="F221" t="n">
-        <v>41452900</v>
+        <v>26751000</v>
       </c>
       <c r="G221" t="n">
         <v>0</v>
@@ -6189,22 +6189,22 @@
     </row>
     <row r="222">
       <c r="A222" s="1" t="n">
-        <v>46248</v>
+        <v>46251</v>
       </c>
       <c r="B222" t="n">
-        <v>78.48000335693359</v>
+        <v>77.80000305175781</v>
       </c>
       <c r="C222" t="n">
-        <v>78.73000335693359</v>
+        <v>78.52999877929688</v>
       </c>
       <c r="D222" t="n">
-        <v>77.76000213623047</v>
+        <v>75.47000122070312</v>
       </c>
       <c r="E222" t="n">
-        <v>78.16000366210938</v>
+        <v>76.01999664306641</v>
       </c>
       <c r="F222" t="n">
-        <v>26751000</v>
+        <v>30753000</v>
       </c>
       <c r="G222" t="n">
         <v>0</v>
@@ -6215,22 +6215,22 @@
     </row>
     <row r="223">
       <c r="A223" s="1" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="B223" t="n">
-        <v>77.80000305175781</v>
+        <v>77.43000030517578</v>
       </c>
       <c r="C223" t="n">
-        <v>78.52999877929688</v>
+        <v>79.09999847412109</v>
       </c>
       <c r="D223" t="n">
-        <v>75.47000122070312</v>
+        <v>76.33999633789062</v>
       </c>
       <c r="E223" t="n">
-        <v>76.01999664306641</v>
+        <v>77.76999664306641</v>
       </c>
       <c r="F223" t="n">
-        <v>30753000</v>
+        <v>36151300</v>
       </c>
       <c r="G223" t="n">
         <v>0</v>
@@ -6241,22 +6241,22 @@
     </row>
     <row r="224">
       <c r="A224" s="1" t="n">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="B224" t="n">
-        <v>77.43000030517578</v>
+        <v>78.25</v>
       </c>
       <c r="C224" t="n">
-        <v>79.09999847412109</v>
+        <v>81.16000366210938</v>
       </c>
       <c r="D224" t="n">
-        <v>76.33999633789062</v>
+        <v>78.09999847412109</v>
       </c>
       <c r="E224" t="n">
-        <v>77.76999664306641</v>
+        <v>80.22000122070312</v>
       </c>
       <c r="F224" t="n">
-        <v>36151300</v>
+        <v>31461800</v>
       </c>
       <c r="G224" t="n">
         <v>0</v>
@@ -6267,22 +6267,22 @@
     </row>
     <row r="225">
       <c r="A225" s="1" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="B225" t="n">
-        <v>78.25</v>
+        <v>80.13999938964844</v>
       </c>
       <c r="C225" t="n">
-        <v>81.16000366210938</v>
+        <v>81.08000183105469</v>
       </c>
       <c r="D225" t="n">
-        <v>78.09999847412109</v>
+        <v>79.58999633789062</v>
       </c>
       <c r="E225" t="n">
-        <v>80.22000122070312</v>
+        <v>80.13999938964844</v>
       </c>
       <c r="F225" t="n">
-        <v>31461800</v>
+        <v>27118400</v>
       </c>
       <c r="G225" t="n">
         <v>0</v>
@@ -6293,22 +6293,22 @@
     </row>
     <row r="226">
       <c r="A226" s="1" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="B226" t="n">
-        <v>80.13999938964844</v>
+        <v>80.29000091552734</v>
       </c>
       <c r="C226" t="n">
-        <v>81.08000183105469</v>
+        <v>80.48999786376953</v>
       </c>
       <c r="D226" t="n">
+        <v>79.16999816894531</v>
+      </c>
+      <c r="E226" t="n">
         <v>79.58999633789062</v>
       </c>
-      <c r="E226" t="n">
-        <v>80.13999938964844</v>
-      </c>
       <c r="F226" t="n">
-        <v>27118400</v>
+        <v>23773800</v>
       </c>
       <c r="G226" t="n">
         <v>0</v>
@@ -6319,22 +6319,22 @@
     </row>
     <row r="227">
       <c r="A227" s="1" t="n">
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="B227" t="n">
-        <v>80.29000091552734</v>
+        <v>79.94000244140625</v>
       </c>
       <c r="C227" t="n">
-        <v>80.48999786376953</v>
+        <v>80.62000274658203</v>
       </c>
       <c r="D227" t="n">
-        <v>79.16999816894531</v>
+        <v>79.01999664306641</v>
       </c>
       <c r="E227" t="n">
-        <v>79.58999633789062</v>
+        <v>80.01000213623047</v>
       </c>
       <c r="F227" t="n">
-        <v>23773800</v>
+        <v>21085300</v>
       </c>
       <c r="G227" t="n">
         <v>0</v>
@@ -6345,22 +6345,22 @@
     </row>
     <row r="228">
       <c r="A228" s="1" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="B228" t="n">
-        <v>79.94000244140625</v>
+        <v>79.65000152587891</v>
       </c>
       <c r="C228" t="n">
-        <v>80.62000274658203</v>
+        <v>82.45999908447266</v>
       </c>
       <c r="D228" t="n">
-        <v>79.01999664306641</v>
+        <v>79.40000152587891</v>
       </c>
       <c r="E228" t="n">
-        <v>80.01000213623047</v>
+        <v>82.23000335693359</v>
       </c>
       <c r="F228" t="n">
-        <v>21085300</v>
+        <v>29462000</v>
       </c>
       <c r="G228" t="n">
         <v>0</v>
@@ -6371,22 +6371,22 @@
     </row>
     <row r="229">
       <c r="A229" s="1" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="B229" t="n">
-        <v>79.65000152587891</v>
+        <v>82.05000305175781</v>
       </c>
       <c r="C229" t="n">
-        <v>82.45999908447266</v>
+        <v>82.41999816894531</v>
       </c>
       <c r="D229" t="n">
-        <v>79.40000152587891</v>
+        <v>81.30000305175781</v>
       </c>
       <c r="E229" t="n">
-        <v>82.23000335693359</v>
+        <v>81.45999908447266</v>
       </c>
       <c r="F229" t="n">
-        <v>29462000</v>
+        <v>22874900</v>
       </c>
       <c r="G229" t="n">
         <v>0</v>
@@ -6397,22 +6397,22 @@
     </row>
     <row r="230">
       <c r="A230" s="1" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="B230" t="n">
-        <v>82.05000305175781</v>
+        <v>81.06999969482422</v>
       </c>
       <c r="C230" t="n">
-        <v>82.41999816894531</v>
+        <v>81.15000152587891</v>
       </c>
       <c r="D230" t="n">
-        <v>81.30000305175781</v>
+        <v>79.27999877929688</v>
       </c>
       <c r="E230" t="n">
-        <v>81.45999908447266</v>
+        <v>79.83999633789062</v>
       </c>
       <c r="F230" t="n">
-        <v>22874900</v>
+        <v>27174400</v>
       </c>
       <c r="G230" t="n">
         <v>0</v>
@@ -6423,22 +6423,22 @@
     </row>
     <row r="231">
       <c r="A231" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="B231" t="n">
-        <v>81.06999969482422</v>
+        <v>80.36000061035156</v>
       </c>
       <c r="C231" t="n">
-        <v>81.15000152587891</v>
+        <v>82.34999847412109</v>
       </c>
       <c r="D231" t="n">
-        <v>79.27999877929688</v>
+        <v>79.94999694824219</v>
       </c>
       <c r="E231" t="n">
-        <v>79.83999633789062</v>
+        <v>81.72000122070312</v>
       </c>
       <c r="F231" t="n">
-        <v>27174400</v>
+        <v>29092700</v>
       </c>
       <c r="G231" t="n">
         <v>0</v>
@@ -6449,22 +6449,22 @@
     </row>
     <row r="232">
       <c r="A232" s="1" t="n">
-        <v>46262</v>
+        <v>46265</v>
       </c>
       <c r="B232" t="n">
-        <v>80.36000061035156</v>
+        <v>81</v>
       </c>
       <c r="C232" t="n">
-        <v>82.34999847412109</v>
+        <v>81.73000335693359</v>
       </c>
       <c r="D232" t="n">
-        <v>79.94999694824219</v>
+        <v>80.65000152587891</v>
       </c>
       <c r="E232" t="n">
-        <v>81.72000122070312</v>
+        <v>81.05000305175781</v>
       </c>
       <c r="F232" t="n">
-        <v>29092700</v>
+        <v>30740800</v>
       </c>
       <c r="G232" t="n">
         <v>0</v>
@@ -6475,22 +6475,22 @@
     </row>
     <row r="233">
       <c r="A233" s="1" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="B233" t="n">
-        <v>81</v>
+        <v>80.16999816894531</v>
       </c>
       <c r="C233" t="n">
-        <v>81.73000335693359</v>
+        <v>82.12999725341797</v>
       </c>
       <c r="D233" t="n">
-        <v>80.65000152587891</v>
+        <v>79.59999847412109</v>
       </c>
       <c r="E233" t="n">
-        <v>81.05000305175781</v>
+        <v>80.80999755859375</v>
       </c>
       <c r="F233" t="n">
-        <v>30740800</v>
+        <v>21164900</v>
       </c>
       <c r="G233" t="n">
         <v>0</v>
@@ -6501,22 +6501,22 @@
     </row>
     <row r="234">
       <c r="A234" s="1" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="B234" t="n">
-        <v>80.16999816894531</v>
+        <v>80.55000305175781</v>
       </c>
       <c r="C234" t="n">
-        <v>82.12999725341797</v>
+        <v>83.12000274658203</v>
       </c>
       <c r="D234" t="n">
-        <v>79.59999847412109</v>
+        <v>80.30000305175781</v>
       </c>
       <c r="E234" t="n">
-        <v>80.80999755859375</v>
+        <v>82.73000335693359</v>
       </c>
       <c r="F234" t="n">
-        <v>21164900</v>
+        <v>22077800</v>
       </c>
       <c r="G234" t="n">
         <v>0</v>
@@ -6527,22 +6527,22 @@
     </row>
     <row r="235">
       <c r="A235" s="1" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="B235" t="n">
-        <v>80.55000305175781</v>
+        <v>83.18000030517578</v>
       </c>
       <c r="C235" t="n">
-        <v>83.12000274658203</v>
+        <v>83.59999847412109</v>
       </c>
       <c r="D235" t="n">
-        <v>80.30000305175781</v>
+        <v>81.62999725341797</v>
       </c>
       <c r="E235" t="n">
-        <v>82.73000335693359</v>
+        <v>82.66999816894531</v>
       </c>
       <c r="F235" t="n">
-        <v>22077800</v>
+        <v>24006400</v>
       </c>
       <c r="G235" t="n">
         <v>0</v>
@@ -6553,22 +6553,22 @@
     </row>
     <row r="236">
       <c r="A236" s="1" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B236" t="n">
-        <v>83.18000030517578</v>
+        <v>82.16999816894531</v>
       </c>
       <c r="C236" t="n">
-        <v>83.59999847412109</v>
+        <v>82.69000244140625</v>
       </c>
       <c r="D236" t="n">
-        <v>81.62999725341797</v>
+        <v>78.23000335693359</v>
       </c>
       <c r="E236" t="n">
-        <v>82.66999816894531</v>
+        <v>78.25</v>
       </c>
       <c r="F236" t="n">
-        <v>24006400</v>
+        <v>40190000</v>
       </c>
       <c r="G236" t="n">
         <v>0</v>
@@ -6579,22 +6579,22 @@
     </row>
     <row r="237">
       <c r="A237" s="1" t="n">
-        <v>46269</v>
+        <v>46273</v>
       </c>
       <c r="B237" t="n">
-        <v>82.16999816894531</v>
+        <v>77.55000305175781</v>
       </c>
       <c r="C237" t="n">
-        <v>82.69000244140625</v>
+        <v>77.73000335693359</v>
       </c>
       <c r="D237" t="n">
-        <v>78.23000335693359</v>
+        <v>75.91999816894531</v>
       </c>
       <c r="E237" t="n">
-        <v>78.25</v>
+        <v>76.76999664306641</v>
       </c>
       <c r="F237" t="n">
-        <v>40190000</v>
+        <v>33865500</v>
       </c>
       <c r="G237" t="n">
         <v>0</v>
@@ -6605,22 +6605,22 @@
     </row>
     <row r="238">
       <c r="A238" s="1" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B238" t="n">
-        <v>77.55000305175781</v>
+        <v>76.33999633789062</v>
       </c>
       <c r="C238" t="n">
-        <v>77.73000335693359</v>
+        <v>76.72000122070312</v>
       </c>
       <c r="D238" t="n">
-        <v>75.91999816894531</v>
+        <v>75.87000274658203</v>
       </c>
       <c r="E238" t="n">
-        <v>76.76999664306641</v>
+        <v>76.02999877929688</v>
       </c>
       <c r="F238" t="n">
-        <v>33865500</v>
+        <v>22779600</v>
       </c>
       <c r="G238" t="n">
         <v>0</v>
@@ -6631,22 +6631,22 @@
     </row>
     <row r="239">
       <c r="A239" s="1" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="B239" t="n">
-        <v>76.33999633789062</v>
+        <v>75.33000183105469</v>
       </c>
       <c r="C239" t="n">
-        <v>76.72000122070312</v>
+        <v>76.30000305175781</v>
       </c>
       <c r="D239" t="n">
-        <v>75.87000274658203</v>
+        <v>75.02999877929688</v>
       </c>
       <c r="E239" t="n">
-        <v>76.02999877929688</v>
+        <v>76.01000213623047</v>
       </c>
       <c r="F239" t="n">
-        <v>22779600</v>
+        <v>20049000</v>
       </c>
       <c r="G239" t="n">
         <v>0</v>
@@ -6657,22 +6657,22 @@
     </row>
     <row r="240">
       <c r="A240" s="1" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="B240" t="n">
-        <v>75.33000183105469</v>
+        <v>76.63999938964844</v>
       </c>
       <c r="C240" t="n">
-        <v>76.30000305175781</v>
+        <v>77.56999969482422</v>
       </c>
       <c r="D240" t="n">
-        <v>75.02999877929688</v>
+        <v>76.15000152587891</v>
       </c>
       <c r="E240" t="n">
-        <v>76.01000213623047</v>
+        <v>77.40000152587891</v>
       </c>
       <c r="F240" t="n">
-        <v>20049000</v>
+        <v>22237800</v>
       </c>
       <c r="G240" t="n">
         <v>0</v>
@@ -6683,22 +6683,22 @@
     </row>
     <row r="241">
       <c r="A241" s="1" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="B241" t="n">
-        <v>76.63999938964844</v>
+        <v>78.97000122070312</v>
       </c>
       <c r="C241" t="n">
-        <v>77.56999969482422</v>
+        <v>81.01999664306641</v>
       </c>
       <c r="D241" t="n">
-        <v>76.15000152587891</v>
+        <v>78.48999786376953</v>
       </c>
       <c r="E241" t="n">
-        <v>77.40000152587891</v>
+        <v>80.31999969482422</v>
       </c>
       <c r="F241" t="n">
-        <v>22237800</v>
+        <v>30945100</v>
       </c>
       <c r="G241" t="n">
         <v>0</v>
@@ -6709,22 +6709,22 @@
     </row>
     <row r="242">
       <c r="A242" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="B242" t="n">
-        <v>78.97000122070312</v>
+        <v>79.37999725341797</v>
       </c>
       <c r="C242" t="n">
-        <v>81.01999664306641</v>
+        <v>79.48000335693359</v>
       </c>
       <c r="D242" t="n">
-        <v>78.48999786376953</v>
+        <v>77.45999908447266</v>
       </c>
       <c r="E242" t="n">
-        <v>80.31999969482422</v>
+        <v>77.90000152587891</v>
       </c>
       <c r="F242" t="n">
-        <v>30945100</v>
+        <v>28027400</v>
       </c>
       <c r="G242" t="n">
         <v>0</v>
@@ -6735,22 +6735,22 @@
     </row>
     <row r="243">
       <c r="A243" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="B243" t="n">
-        <v>79.37999725341797</v>
+        <v>77.73000335693359</v>
       </c>
       <c r="C243" t="n">
-        <v>79.48000335693359</v>
+        <v>77.80000305175781</v>
       </c>
       <c r="D243" t="n">
-        <v>77.45999908447266</v>
+        <v>76.30999755859375</v>
       </c>
       <c r="E243" t="n">
-        <v>77.90000152587891</v>
+        <v>76.41000366210938</v>
       </c>
       <c r="F243" t="n">
-        <v>28027400</v>
+        <v>25376300</v>
       </c>
       <c r="G243" t="n">
         <v>0</v>
@@ -6761,22 +6761,22 @@
     </row>
     <row r="244">
       <c r="A244" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="B244" t="n">
-        <v>77.73000335693359</v>
+        <v>76.91000366210938</v>
       </c>
       <c r="C244" t="n">
-        <v>77.80000305175781</v>
+        <v>76.95999908447266</v>
       </c>
       <c r="D244" t="n">
-        <v>76.30999755859375</v>
+        <v>75.30000305175781</v>
       </c>
       <c r="E244" t="n">
-        <v>76.41000366210938</v>
+        <v>75.30999755859375</v>
       </c>
       <c r="F244" t="n">
-        <v>25376300</v>
+        <v>28167600</v>
       </c>
       <c r="G244" t="n">
         <v>0</v>
@@ -6787,22 +6787,22 @@
     </row>
     <row r="245">
       <c r="A245" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="B245" t="n">
-        <v>76.91000366210938</v>
+        <v>71.26999664306641</v>
       </c>
       <c r="C245" t="n">
-        <v>76.95999908447266</v>
+        <v>72.37999725341797</v>
       </c>
       <c r="D245" t="n">
-        <v>75.30000305175781</v>
+        <v>70.11000061035156</v>
       </c>
       <c r="E245" t="n">
-        <v>75.30999755859375</v>
+        <v>71.79000091552734</v>
       </c>
       <c r="F245" t="n">
-        <v>28167600</v>
+        <v>114413500</v>
       </c>
       <c r="G245" t="n">
         <v>0</v>
@@ -6813,22 +6813,22 @@
     </row>
     <row r="246">
       <c r="A246" s="1" t="n">
-        <v>46283</v>
+        <v>46286</v>
       </c>
       <c r="B246" t="n">
-        <v>71.26999664306641</v>
+        <v>71.81999969482422</v>
       </c>
       <c r="C246" t="n">
-        <v>72.37999725341797</v>
+        <v>73.87000274658203</v>
       </c>
       <c r="D246" t="n">
-        <v>70.11000061035156</v>
+        <v>71.79000091552734</v>
       </c>
       <c r="E246" t="n">
-        <v>71.79000091552734</v>
+        <v>73.36000061035156</v>
       </c>
       <c r="F246" t="n">
-        <v>114413500</v>
+        <v>36948000</v>
       </c>
       <c r="G246" t="n">
         <v>0</v>
@@ -6839,22 +6839,22 @@
     </row>
     <row r="247">
       <c r="A247" s="1" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="B247" t="n">
-        <v>71.81999969482422</v>
+        <v>73.69000244140625</v>
       </c>
       <c r="C247" t="n">
-        <v>73.87000274658203</v>
+        <v>73.76000213623047</v>
       </c>
       <c r="D247" t="n">
-        <v>71.79000091552734</v>
+        <v>71.58000183105469</v>
       </c>
       <c r="E247" t="n">
-        <v>73.36000061035156</v>
+        <v>72.16000366210938</v>
       </c>
       <c r="F247" t="n">
-        <v>36948000</v>
+        <v>34372500</v>
       </c>
       <c r="G247" t="n">
         <v>0</v>
@@ -6865,22 +6865,22 @@
     </row>
     <row r="248">
       <c r="A248" s="1" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="B248" t="n">
-        <v>73.69000244140625</v>
+        <v>72.08000183105469</v>
       </c>
       <c r="C248" t="n">
-        <v>73.76000213623047</v>
+        <v>72.37000274658203</v>
       </c>
       <c r="D248" t="n">
-        <v>71.58000183105469</v>
+        <v>71.06999969482422</v>
       </c>
       <c r="E248" t="n">
-        <v>72.16000366210938</v>
+        <v>71.36000061035156</v>
       </c>
       <c r="F248" t="n">
-        <v>34372500</v>
+        <v>32807500</v>
       </c>
       <c r="G248" t="n">
         <v>0</v>
@@ -6891,22 +6891,22 @@
     </row>
     <row r="249">
       <c r="A249" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="B249" t="n">
-        <v>72.08000183105469</v>
+        <v>71.62000274658203</v>
       </c>
       <c r="C249" t="n">
-        <v>72.37000274658203</v>
+        <v>72.04000091552734</v>
       </c>
       <c r="D249" t="n">
-        <v>71.06999969482422</v>
+        <v>71.20999908447266</v>
       </c>
       <c r="E249" t="n">
-        <v>71.36000061035156</v>
+        <v>71.72000122070312</v>
       </c>
       <c r="F249" t="n">
-        <v>32807500</v>
+        <v>28223900</v>
       </c>
       <c r="G249" t="n">
         <v>0</v>
@@ -6917,22 +6917,22 @@
     </row>
     <row r="250">
       <c r="A250" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="B250" t="n">
-        <v>71.62000274658203</v>
+        <v>71.62999725341797</v>
       </c>
       <c r="C250" t="n">
-        <v>72.04000091552734</v>
+        <v>71.83999633789062</v>
       </c>
       <c r="D250" t="n">
-        <v>71.20999908447266</v>
+        <v>70.98000335693359</v>
       </c>
       <c r="E250" t="n">
-        <v>71.72000122070312</v>
+        <v>71.15000152587891</v>
       </c>
       <c r="F250" t="n">
-        <v>28223900</v>
+        <v>23203100</v>
       </c>
       <c r="G250" t="n">
         <v>0</v>
@@ -6943,22 +6943,22 @@
     </row>
     <row r="251">
       <c r="A251" s="1" t="n">
-        <v>46290</v>
+        <v>46293</v>
       </c>
       <c r="B251" t="n">
-        <v>71.62999725341797</v>
+        <v>71.55000305175781</v>
       </c>
       <c r="C251" t="n">
-        <v>71.83999633789062</v>
+        <v>71.65000152587891</v>
       </c>
       <c r="D251" t="n">
-        <v>70.98000335693359</v>
+        <v>68.87999725341797</v>
       </c>
       <c r="E251" t="n">
-        <v>71.15000152587891</v>
+        <v>69.23000335693359</v>
       </c>
       <c r="F251" t="n">
-        <v>23203100</v>
+        <v>43366300</v>
       </c>
       <c r="G251" t="n">
         <v>0</v>
@@ -6969,22 +6969,22 @@
     </row>
     <row r="252">
       <c r="A252" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="B252" t="n">
-        <v>71.55000305175781</v>
+        <v>70.33000183105469</v>
       </c>
       <c r="C252" t="n">
-        <v>71.65000152587891</v>
+        <v>71.36000061035156</v>
       </c>
       <c r="D252" t="n">
-        <v>68.87999725341797</v>
+        <v>70.15000152587891</v>
       </c>
       <c r="E252" t="n">
-        <v>69.23000335693359</v>
+        <v>70.30000305175781</v>
       </c>
       <c r="F252" t="n">
-        <v>43145800</v>
+        <v>34497700</v>
       </c>
       <c r="G252" t="n">
         <v>0</v>
@@ -10434,37 +10434,37 @@
         </is>
       </c>
       <c r="C2" t="n">
+        <v>70.3</v>
+      </c>
+      <c r="D2" t="n">
         <v>69.23</v>
       </c>
-      <c r="D2" t="n">
-        <v>71.145</v>
-      </c>
       <c r="E2" t="n">
-        <v>71.55</v>
+        <v>70.39</v>
       </c>
       <c r="F2" t="n">
-        <v>71.58</v>
+        <v>71.34</v>
       </c>
       <c r="G2" t="n">
-        <v>68.88</v>
+        <v>70.15000000000001</v>
       </c>
       <c r="H2" t="n">
-        <v>43070286</v>
+        <v>33202113</v>
       </c>
       <c r="I2" t="n">
-        <v>37696817</v>
+        <v>37466298</v>
       </c>
       <c r="J2" t="n">
-        <v>288269565952</v>
+        <v>292724965376</v>
       </c>
       <c r="K2" t="n">
-        <v>22.404533</v>
+        <v>21.764708</v>
       </c>
       <c r="L2" t="n">
-        <v>18.15526</v>
+        <v>18.439152</v>
       </c>
       <c r="M2" t="n">
-        <v>3.09</v>
+        <v>3.23</v>
       </c>
       <c r="N2" t="n">
         <v>124.86</v>
@@ -10502,7 +10502,7 @@
         <v>7.241</v>
       </c>
       <c r="Y2" t="n">
-        <v>9.560834</v>
+        <v>9.708603999999999</v>
       </c>
       <c r="Z2" t="n">
         <v>0.111</v>
@@ -10514,7 +10514,7 @@
         <v>48370765824</v>
       </c>
       <c r="AC2" t="n">
-        <v>295796310016</v>
+        <v>300251709440</v>
       </c>
       <c r="AD2" t="n">
         <v>14726931456</v>
@@ -10541,7 +10541,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>2026-09-29 13:25:00</t>
+          <t>2026-09-30 16:07:29</t>
         </is>
       </c>
     </row>

--- a/data/NFLX_data.xlsx
+++ b/data/NFLX_data.xlsx
@@ -469,22 +469,22 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45930</v>
+        <v>45931</v>
       </c>
       <c r="B2" t="n">
-        <v>120.640998840332</v>
+        <v>117.5490036010742</v>
       </c>
       <c r="C2" t="n">
-        <v>120.8499984741211</v>
+        <v>117.9140014648438</v>
       </c>
       <c r="D2" t="n">
-        <v>117.8000030517578</v>
+        <v>116.3209991455078</v>
       </c>
       <c r="E2" t="n">
-        <v>119.8919982910156</v>
+        <v>117.0899963378906</v>
       </c>
       <c r="F2" t="n">
-        <v>38303000</v>
+        <v>41102000</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -495,22 +495,22 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45931</v>
+        <v>45932</v>
       </c>
       <c r="B3" t="n">
-        <v>117.5490036010742</v>
+        <v>116.1500015258789</v>
       </c>
       <c r="C3" t="n">
-        <v>117.9140014648438</v>
+        <v>116.3330001831055</v>
       </c>
       <c r="D3" t="n">
-        <v>116.3209991455078</v>
+        <v>113.4000015258789</v>
       </c>
       <c r="E3" t="n">
-        <v>117.0899963378906</v>
+        <v>116.2529983520508</v>
       </c>
       <c r="F3" t="n">
-        <v>41102000</v>
+        <v>46855000</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -521,22 +521,22 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>45932</v>
+        <v>45933</v>
       </c>
       <c r="B4" t="n">
-        <v>116.1500015258789</v>
+        <v>116.5</v>
       </c>
       <c r="C4" t="n">
-        <v>116.3330001831055</v>
+        <v>116.8000030517578</v>
       </c>
       <c r="D4" t="n">
-        <v>113.4000015258789</v>
+        <v>114.3219985961914</v>
       </c>
       <c r="E4" t="n">
-        <v>116.2529983520508</v>
+        <v>115.3320007324219</v>
       </c>
       <c r="F4" t="n">
-        <v>46855000</v>
+        <v>31374000</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -547,22 +547,22 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>45933</v>
+        <v>45936</v>
       </c>
       <c r="B5" t="n">
-        <v>116.5</v>
+        <v>116.0370025634766</v>
       </c>
       <c r="C5" t="n">
-        <v>116.8000030517578</v>
+        <v>116.3580017089844</v>
       </c>
       <c r="D5" t="n">
-        <v>114.3219985961914</v>
+        <v>114.5449981689453</v>
       </c>
       <c r="E5" t="n">
-        <v>115.3320007324219</v>
+        <v>116.3310012817383</v>
       </c>
       <c r="F5" t="n">
-        <v>31374000</v>
+        <v>29686000</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -573,22 +573,22 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>45936</v>
+        <v>45937</v>
       </c>
       <c r="B6" t="n">
-        <v>116.0370025634766</v>
+        <v>117.7789993286133</v>
       </c>
       <c r="C6" t="n">
-        <v>116.3580017089844</v>
+        <v>120.1370010375977</v>
       </c>
       <c r="D6" t="n">
-        <v>114.5449981689453</v>
+        <v>117.7460021972656</v>
       </c>
       <c r="E6" t="n">
-        <v>116.3310012817383</v>
+        <v>119.1060028076172</v>
       </c>
       <c r="F6" t="n">
-        <v>29686000</v>
+        <v>33091000</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -599,22 +599,22 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>45937</v>
+        <v>45938</v>
       </c>
       <c r="B7" t="n">
-        <v>117.7789993286133</v>
+        <v>119.7109985351562</v>
       </c>
       <c r="C7" t="n">
-        <v>120.1370010375977</v>
+        <v>121.7389984130859</v>
       </c>
       <c r="D7" t="n">
-        <v>117.7460021972656</v>
+        <v>119.1999969482422</v>
       </c>
       <c r="E7" t="n">
-        <v>119.1060028076172</v>
+        <v>121.4250030517578</v>
       </c>
       <c r="F7" t="n">
-        <v>33091000</v>
+        <v>28514000</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -625,22 +625,22 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>45938</v>
+        <v>45939</v>
       </c>
       <c r="B8" t="n">
-        <v>119.7109985351562</v>
+        <v>121.4250030517578</v>
       </c>
       <c r="C8" t="n">
-        <v>121.7389984130859</v>
+        <v>123.75</v>
       </c>
       <c r="D8" t="n">
-        <v>119.1999969482422</v>
+        <v>121.181999206543</v>
       </c>
       <c r="E8" t="n">
-        <v>121.4250030517578</v>
+        <v>123.1070022583008</v>
       </c>
       <c r="F8" t="n">
-        <v>28514000</v>
+        <v>28241000</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -651,22 +651,22 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>45939</v>
+        <v>45940</v>
       </c>
       <c r="B9" t="n">
-        <v>121.4250030517578</v>
+        <v>122.9000015258789</v>
       </c>
       <c r="C9" t="n">
-        <v>123.75</v>
+        <v>124.6999969482422</v>
       </c>
       <c r="D9" t="n">
-        <v>121.181999206543</v>
+        <v>121.9100036621094</v>
       </c>
       <c r="E9" t="n">
-        <v>123.1070022583008</v>
+        <v>122.0080032348633</v>
       </c>
       <c r="F9" t="n">
-        <v>28241000</v>
+        <v>42798000</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -677,22 +677,22 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>45940</v>
+        <v>45943</v>
       </c>
       <c r="B10" t="n">
-        <v>122.9000015258789</v>
+        <v>122.1350021362305</v>
       </c>
       <c r="C10" t="n">
-        <v>124.6999969482422</v>
+        <v>123.1119995117188</v>
       </c>
       <c r="D10" t="n">
-        <v>121.9100036621094</v>
+        <v>120.6809997558594</v>
       </c>
       <c r="E10" t="n">
-        <v>122.0080032348633</v>
+        <v>121.9029998779297</v>
       </c>
       <c r="F10" t="n">
-        <v>42798000</v>
+        <v>24608000</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -703,22 +703,22 @@
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>45943</v>
+        <v>45944</v>
       </c>
       <c r="B11" t="n">
-        <v>122.1350021362305</v>
+        <v>121.4749984741211</v>
       </c>
       <c r="C11" t="n">
-        <v>123.1119995117188</v>
+        <v>122.4290008544922</v>
       </c>
       <c r="D11" t="n">
-        <v>120.6809997558594</v>
+        <v>120.3099975585938</v>
       </c>
       <c r="E11" t="n">
-        <v>121.9029998779297</v>
+        <v>121.5350036621094</v>
       </c>
       <c r="F11" t="n">
-        <v>24608000</v>
+        <v>23624000</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -729,22 +729,22 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>45944</v>
+        <v>45945</v>
       </c>
       <c r="B12" t="n">
-        <v>121.4749984741211</v>
+        <v>121.3010025024414</v>
       </c>
       <c r="C12" t="n">
-        <v>122.4290008544922</v>
+        <v>121.9619979858398</v>
       </c>
       <c r="D12" t="n">
-        <v>120.3099975585938</v>
+        <v>120.161003112793</v>
       </c>
       <c r="E12" t="n">
-        <v>121.5350036621094</v>
+        <v>120.3290023803711</v>
       </c>
       <c r="F12" t="n">
-        <v>23624000</v>
+        <v>20252000</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -755,22 +755,22 @@
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>45945</v>
+        <v>45946</v>
       </c>
       <c r="B13" t="n">
-        <v>121.3010025024414</v>
+        <v>121.2149963378906</v>
       </c>
       <c r="C13" t="n">
-        <v>121.9619979858398</v>
+        <v>121.6709976196289</v>
       </c>
       <c r="D13" t="n">
-        <v>120.161003112793</v>
+        <v>117.5999984741211</v>
       </c>
       <c r="E13" t="n">
-        <v>120.3290023803711</v>
+        <v>118.359001159668</v>
       </c>
       <c r="F13" t="n">
-        <v>20252000</v>
+        <v>28326000</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -781,22 +781,22 @@
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>45946</v>
+        <v>45947</v>
       </c>
       <c r="B14" t="n">
-        <v>121.2149963378906</v>
+        <v>118.3600006103516</v>
       </c>
       <c r="C14" t="n">
-        <v>121.6709976196289</v>
+        <v>120.3119964599609</v>
       </c>
       <c r="D14" t="n">
-        <v>117.5999984741211</v>
+        <v>117.8949966430664</v>
       </c>
       <c r="E14" t="n">
-        <v>118.359001159668</v>
+        <v>119.9359970092773</v>
       </c>
       <c r="F14" t="n">
-        <v>28326000</v>
+        <v>29571000</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -807,22 +807,22 @@
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>45947</v>
+        <v>45950</v>
       </c>
       <c r="B15" t="n">
-        <v>118.3600006103516</v>
+        <v>120.7880020141602</v>
       </c>
       <c r="C15" t="n">
-        <v>120.3119964599609</v>
+        <v>124.7760009765625</v>
       </c>
       <c r="D15" t="n">
-        <v>117.8949966430664</v>
+        <v>120.6900024414062</v>
       </c>
       <c r="E15" t="n">
-        <v>119.9359970092773</v>
+        <v>123.8560028076172</v>
       </c>
       <c r="F15" t="n">
-        <v>29571000</v>
+        <v>39862000</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -833,22 +833,22 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>45950</v>
+        <v>45951</v>
       </c>
       <c r="B16" t="n">
-        <v>120.7880020141602</v>
+        <v>124.2829971313477</v>
       </c>
       <c r="C16" t="n">
-        <v>124.7760009765625</v>
+        <v>124.8600006103516</v>
       </c>
       <c r="D16" t="n">
-        <v>120.6900024414062</v>
+        <v>123.1760025024414</v>
       </c>
       <c r="E16" t="n">
-        <v>123.8560028076172</v>
+        <v>124.1350021362305</v>
       </c>
       <c r="F16" t="n">
-        <v>39862000</v>
+        <v>65082000</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -859,22 +859,22 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>45951</v>
+        <v>45952</v>
       </c>
       <c r="B17" t="n">
-        <v>124.2829971313477</v>
+        <v>114.2900009155273</v>
       </c>
       <c r="C17" t="n">
-        <v>124.8600006103516</v>
+        <v>115.7600021362305</v>
       </c>
       <c r="D17" t="n">
-        <v>123.1760025024414</v>
+        <v>111.2509994506836</v>
       </c>
       <c r="E17" t="n">
-        <v>124.1350021362305</v>
+        <v>111.6370010375977</v>
       </c>
       <c r="F17" t="n">
-        <v>65082000</v>
+        <v>147890000</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -885,22 +885,22 @@
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>45952</v>
+        <v>45953</v>
       </c>
       <c r="B18" t="n">
-        <v>114.2900009155273</v>
+        <v>112.6900024414062</v>
       </c>
       <c r="C18" t="n">
-        <v>115.7600021362305</v>
+        <v>112.7829971313477</v>
       </c>
       <c r="D18" t="n">
-        <v>111.2509994506836</v>
+        <v>109.9729995727539</v>
       </c>
       <c r="E18" t="n">
-        <v>111.6370010375977</v>
+        <v>111.359001159668</v>
       </c>
       <c r="F18" t="n">
-        <v>147890000</v>
+        <v>68497000</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -911,22 +911,22 @@
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>45953</v>
+        <v>45954</v>
       </c>
       <c r="B19" t="n">
-        <v>112.6900024414062</v>
+        <v>111.0999984741211</v>
       </c>
       <c r="C19" t="n">
-        <v>112.7829971313477</v>
+        <v>111.4509963989258</v>
       </c>
       <c r="D19" t="n">
-        <v>109.9729995727539</v>
+        <v>109.4410018920898</v>
       </c>
       <c r="E19" t="n">
-        <v>111.359001159668</v>
+        <v>109.4690017700195</v>
       </c>
       <c r="F19" t="n">
-        <v>68497000</v>
+        <v>60280000</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -937,22 +937,22 @@
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>45954</v>
+        <v>45957</v>
       </c>
       <c r="B20" t="n">
-        <v>111.0999984741211</v>
+        <v>110.0670013427734</v>
       </c>
       <c r="C20" t="n">
-        <v>111.4509963989258</v>
+        <v>110.2279968261719</v>
       </c>
       <c r="D20" t="n">
-        <v>109.4410018920898</v>
+        <v>108.7300033569336</v>
       </c>
       <c r="E20" t="n">
-        <v>109.4690017700195</v>
+        <v>109.4560012817383</v>
       </c>
       <c r="F20" t="n">
-        <v>60280000</v>
+        <v>46911000</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -963,22 +963,22 @@
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>45957</v>
+        <v>45958</v>
       </c>
       <c r="B21" t="n">
-        <v>110.0670013427734</v>
+        <v>109.4000015258789</v>
       </c>
       <c r="C21" t="n">
-        <v>110.2279968261719</v>
+        <v>111.697998046875</v>
       </c>
       <c r="D21" t="n">
-        <v>108.7300033569336</v>
+        <v>109.3010025024414</v>
       </c>
       <c r="E21" t="n">
-        <v>109.4560012817383</v>
+        <v>110.25</v>
       </c>
       <c r="F21" t="n">
-        <v>46911000</v>
+        <v>40209000</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -989,22 +989,22 @@
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>45958</v>
+        <v>45959</v>
       </c>
       <c r="B22" t="n">
-        <v>109.4000015258789</v>
+        <v>109.984001159668</v>
       </c>
       <c r="C22" t="n">
-        <v>111.697998046875</v>
+        <v>110.8550033569336</v>
       </c>
       <c r="D22" t="n">
-        <v>109.3010025024414</v>
+        <v>109.5999984741211</v>
       </c>
       <c r="E22" t="n">
-        <v>110.25</v>
+        <v>110.0410003662109</v>
       </c>
       <c r="F22" t="n">
-        <v>40209000</v>
+        <v>33995000</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -1015,22 +1015,22 @@
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>45959</v>
+        <v>45960</v>
       </c>
       <c r="B23" t="n">
-        <v>109.984001159668</v>
+        <v>109.4400024414062</v>
       </c>
       <c r="C23" t="n">
-        <v>110.8550033569336</v>
+        <v>110.6159973144531</v>
       </c>
       <c r="D23" t="n">
-        <v>109.5999984741211</v>
+        <v>108.8109970092773</v>
       </c>
       <c r="E23" t="n">
-        <v>110.0410003662109</v>
+        <v>108.9000015258789</v>
       </c>
       <c r="F23" t="n">
-        <v>33995000</v>
+        <v>41581000</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -1041,22 +1041,22 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>45960</v>
+        <v>45961</v>
       </c>
       <c r="B24" t="n">
-        <v>109.4400024414062</v>
+        <v>110.5390014648438</v>
       </c>
       <c r="C24" t="n">
-        <v>110.6159973144531</v>
+        <v>113.4879989624023</v>
       </c>
       <c r="D24" t="n">
-        <v>108.8109970092773</v>
+        <v>110.197998046875</v>
       </c>
       <c r="E24" t="n">
-        <v>108.9000015258789</v>
+        <v>111.8860015869141</v>
       </c>
       <c r="F24" t="n">
-        <v>41581000</v>
+        <v>68665000</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -1067,22 +1067,22 @@
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>45961</v>
+        <v>45964</v>
       </c>
       <c r="B25" t="n">
-        <v>110.5390014648438</v>
+        <v>113.3239974975586</v>
       </c>
       <c r="C25" t="n">
-        <v>113.4879989624023</v>
+        <v>113.3499984741211</v>
       </c>
       <c r="D25" t="n">
-        <v>110.197998046875</v>
+        <v>107.5149993896484</v>
       </c>
       <c r="E25" t="n">
-        <v>111.8860015869141</v>
+        <v>110.0090026855469</v>
       </c>
       <c r="F25" t="n">
-        <v>68665000</v>
+        <v>58634000</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -1093,22 +1093,22 @@
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>45964</v>
+        <v>45965</v>
       </c>
       <c r="B26" t="n">
-        <v>113.3239974975586</v>
+        <v>109.9990005493164</v>
       </c>
       <c r="C26" t="n">
-        <v>113.3499984741211</v>
+        <v>110.4599990844727</v>
       </c>
       <c r="D26" t="n">
-        <v>107.5149993896484</v>
+        <v>108.6679992675781</v>
       </c>
       <c r="E26" t="n">
-        <v>110.0090026855469</v>
+        <v>109.2959976196289</v>
       </c>
       <c r="F26" t="n">
-        <v>58634000</v>
+        <v>38718000</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -1119,22 +1119,22 @@
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>45965</v>
+        <v>45966</v>
       </c>
       <c r="B27" t="n">
-        <v>109.9990005493164</v>
+        <v>108.5</v>
       </c>
       <c r="C27" t="n">
-        <v>110.4599990844727</v>
+        <v>110.0849990844727</v>
       </c>
       <c r="D27" t="n">
-        <v>108.6679992675781</v>
+        <v>107.3369979858398</v>
       </c>
       <c r="E27" t="n">
-        <v>109.2959976196289</v>
+        <v>109.8460006713867</v>
       </c>
       <c r="F27" t="n">
-        <v>38718000</v>
+        <v>35539000</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -1145,22 +1145,22 @@
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>45966</v>
+        <v>45967</v>
       </c>
       <c r="B28" t="n">
-        <v>108.5</v>
+        <v>109.4580001831055</v>
       </c>
       <c r="C28" t="n">
-        <v>110.0849990844727</v>
+        <v>110.370002746582</v>
       </c>
       <c r="D28" t="n">
-        <v>107.3369979858398</v>
+        <v>108.5130004882812</v>
       </c>
       <c r="E28" t="n">
-        <v>109.8460006713867</v>
+        <v>109.7020034790039</v>
       </c>
       <c r="F28" t="n">
-        <v>35539000</v>
+        <v>36532000</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
@@ -1171,22 +1171,22 @@
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>45967</v>
+        <v>45968</v>
       </c>
       <c r="B29" t="n">
-        <v>109.4580001831055</v>
+        <v>109.4179992675781</v>
       </c>
       <c r="C29" t="n">
-        <v>110.370002746582</v>
+        <v>110.8219985961914</v>
       </c>
       <c r="D29" t="n">
-        <v>108.5130004882812</v>
+        <v>108.75</v>
       </c>
       <c r="E29" t="n">
-        <v>109.7020034790039</v>
+        <v>110.3659973144531</v>
       </c>
       <c r="F29" t="n">
-        <v>36532000</v>
+        <v>44125000</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -1197,22 +1197,22 @@
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>45968</v>
+        <v>45971</v>
       </c>
       <c r="B30" t="n">
-        <v>109.4179992675781</v>
+        <v>110.6719970703125</v>
       </c>
       <c r="C30" t="n">
-        <v>110.8219985961914</v>
+        <v>112.8199996948242</v>
       </c>
       <c r="D30" t="n">
-        <v>108.75</v>
+        <v>110.4049987792969</v>
       </c>
       <c r="E30" t="n">
-        <v>110.3659973144531</v>
+        <v>112.0070037841797</v>
       </c>
       <c r="F30" t="n">
-        <v>44125000</v>
+        <v>36929000</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -1223,22 +1223,22 @@
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>45971</v>
+        <v>45972</v>
       </c>
       <c r="B31" t="n">
-        <v>110.6719970703125</v>
+        <v>111.7600021362305</v>
       </c>
       <c r="C31" t="n">
-        <v>112.8199996948242</v>
+        <v>113.9219970703125</v>
       </c>
       <c r="D31" t="n">
-        <v>110.4049987792969</v>
+        <v>111.2799987792969</v>
       </c>
       <c r="E31" t="n">
-        <v>112.0070037841797</v>
+        <v>113.6439971923828</v>
       </c>
       <c r="F31" t="n">
-        <v>36929000</v>
+        <v>27966000</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -1249,22 +1249,22 @@
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>45972</v>
+        <v>45973</v>
       </c>
       <c r="B32" t="n">
-        <v>111.7600021362305</v>
+        <v>113.8170013427734</v>
       </c>
       <c r="C32" t="n">
-        <v>113.9219970703125</v>
+        <v>116.4339981079102</v>
       </c>
       <c r="D32" t="n">
-        <v>111.2799987792969</v>
+        <v>112.8259963989258</v>
       </c>
       <c r="E32" t="n">
-        <v>113.6439971923828</v>
+        <v>115.75</v>
       </c>
       <c r="F32" t="n">
-        <v>27966000</v>
+        <v>39221000</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
@@ -1275,22 +1275,22 @@
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>45973</v>
+        <v>45974</v>
       </c>
       <c r="B33" t="n">
-        <v>113.8170013427734</v>
+        <v>115.8499984741211</v>
       </c>
       <c r="C33" t="n">
-        <v>116.4339981079102</v>
+        <v>116.7330017089844</v>
       </c>
       <c r="D33" t="n">
-        <v>112.8259963989258</v>
+        <v>114.5690002441406</v>
       </c>
       <c r="E33" t="n">
-        <v>115.75</v>
+        <v>115.4229965209961</v>
       </c>
       <c r="F33" t="n">
-        <v>39221000</v>
+        <v>40144000</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -1301,22 +1301,22 @@
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>45974</v>
+        <v>45975</v>
       </c>
       <c r="B34" t="n">
-        <v>115.8499984741211</v>
+        <v>114.2730026245117</v>
       </c>
       <c r="C34" t="n">
-        <v>116.7330017089844</v>
+        <v>114.2730026245117</v>
       </c>
       <c r="D34" t="n">
-        <v>114.5690002441406</v>
+        <v>110.7210006713867</v>
       </c>
       <c r="E34" t="n">
-        <v>115.4229965209961</v>
+        <v>111.2170028686523</v>
       </c>
       <c r="F34" t="n">
-        <v>40144000</v>
+        <v>47607000</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
@@ -1327,74 +1327,74 @@
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>45975</v>
+        <v>45978</v>
       </c>
       <c r="B35" t="n">
-        <v>114.2730026245117</v>
+        <v>110.75</v>
       </c>
       <c r="C35" t="n">
-        <v>114.2730026245117</v>
+        <v>111.8499984741211</v>
       </c>
       <c r="D35" t="n">
-        <v>110.7210006713867</v>
+        <v>109.5500030517578</v>
       </c>
       <c r="E35" t="n">
-        <v>111.2170028686523</v>
+        <v>110.2900009155273</v>
       </c>
       <c r="F35" t="n">
-        <v>47607000</v>
+        <v>26082700</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>45978</v>
+        <v>45979</v>
       </c>
       <c r="B36" t="n">
-        <v>110.75</v>
+        <v>110.2900009155273</v>
       </c>
       <c r="C36" t="n">
-        <v>111.8499984741211</v>
+        <v>115.25</v>
       </c>
       <c r="D36" t="n">
-        <v>109.5500030517578</v>
+        <v>109.1999969482422</v>
       </c>
       <c r="E36" t="n">
-        <v>110.2900009155273</v>
+        <v>114.0899963378906</v>
       </c>
       <c r="F36" t="n">
-        <v>26082700</v>
+        <v>43440600</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>45979</v>
+        <v>45980</v>
       </c>
       <c r="B37" t="n">
-        <v>110.2900009155273</v>
+        <v>113</v>
       </c>
       <c r="C37" t="n">
-        <v>115.25</v>
+        <v>113.3399963378906</v>
       </c>
       <c r="D37" t="n">
-        <v>109.1999969482422</v>
+        <v>108.6100006103516</v>
       </c>
       <c r="E37" t="n">
-        <v>114.0899963378906</v>
+        <v>110</v>
       </c>
       <c r="F37" t="n">
-        <v>43440600</v>
+        <v>31868100</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
@@ -1405,22 +1405,22 @@
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>45980</v>
+        <v>45981</v>
       </c>
       <c r="B38" t="n">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C38" t="n">
-        <v>113.3399963378906</v>
+        <v>111.0999984741211</v>
       </c>
       <c r="D38" t="n">
-        <v>108.6100006103516</v>
+        <v>105.3899993896484</v>
       </c>
       <c r="E38" t="n">
-        <v>110</v>
+        <v>105.6699981689453</v>
       </c>
       <c r="F38" t="n">
-        <v>31868100</v>
+        <v>36918500</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
@@ -1431,22 +1431,22 @@
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>45981</v>
+        <v>45982</v>
       </c>
       <c r="B39" t="n">
-        <v>111</v>
+        <v>105.129997253418</v>
       </c>
       <c r="C39" t="n">
-        <v>111.0999984741211</v>
+        <v>106.5299987792969</v>
       </c>
       <c r="D39" t="n">
-        <v>105.3899993896484</v>
+        <v>103.8099975585938</v>
       </c>
       <c r="E39" t="n">
-        <v>105.6699981689453</v>
+        <v>104.3099975585938</v>
       </c>
       <c r="F39" t="n">
-        <v>36918500</v>
+        <v>41232700</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
@@ -1457,22 +1457,22 @@
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>45982</v>
+        <v>45985</v>
       </c>
       <c r="B40" t="n">
-        <v>105.129997253418</v>
+        <v>104.25</v>
       </c>
       <c r="C40" t="n">
-        <v>106.5299987792969</v>
+        <v>108.0400009155273</v>
       </c>
       <c r="D40" t="n">
-        <v>103.8099975585938</v>
+        <v>103.3199996948242</v>
       </c>
       <c r="E40" t="n">
-        <v>104.3099975585938</v>
+        <v>106.9700012207031</v>
       </c>
       <c r="F40" t="n">
-        <v>41232700</v>
+        <v>62918300</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
@@ -1483,22 +1483,22 @@
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>45985</v>
+        <v>45986</v>
       </c>
       <c r="B41" t="n">
-        <v>104.25</v>
+        <v>106.120002746582</v>
       </c>
       <c r="C41" t="n">
-        <v>108.0400009155273</v>
+        <v>106.3000030517578</v>
       </c>
       <c r="D41" t="n">
-        <v>103.3199996948242</v>
+        <v>103.8199996948242</v>
       </c>
       <c r="E41" t="n">
-        <v>106.9700012207031</v>
+        <v>104.4000015258789</v>
       </c>
       <c r="F41" t="n">
-        <v>62918300</v>
+        <v>35122600</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
@@ -1509,22 +1509,22 @@
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>45986</v>
+        <v>45987</v>
       </c>
       <c r="B42" t="n">
-        <v>106.120002746582</v>
+        <v>105.7399978637695</v>
       </c>
       <c r="C42" t="n">
-        <v>106.3000030517578</v>
+        <v>106.9499969482422</v>
       </c>
       <c r="D42" t="n">
-        <v>103.8199996948242</v>
+        <v>105.2200012207031</v>
       </c>
       <c r="E42" t="n">
-        <v>104.4000015258789</v>
+        <v>106.1399993896484</v>
       </c>
       <c r="F42" t="n">
-        <v>35122600</v>
+        <v>27951000</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
@@ -1535,22 +1535,22 @@
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>45987</v>
+        <v>45989</v>
       </c>
       <c r="B43" t="n">
-        <v>105.7399978637695</v>
+        <v>106.4400024414062</v>
       </c>
       <c r="C43" t="n">
-        <v>106.9499969482422</v>
+        <v>107.9400024414062</v>
       </c>
       <c r="D43" t="n">
-        <v>105.2200012207031</v>
+        <v>106.2399978637695</v>
       </c>
       <c r="E43" t="n">
-        <v>106.1399993896484</v>
+        <v>107.5800018310547</v>
       </c>
       <c r="F43" t="n">
-        <v>27951000</v>
+        <v>15021600</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
@@ -1561,22 +1561,22 @@
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
-        <v>45989</v>
+        <v>45992</v>
       </c>
       <c r="B44" t="n">
-        <v>106.4400024414062</v>
+        <v>106.5100021362305</v>
       </c>
       <c r="C44" t="n">
-        <v>107.9400024414062</v>
+        <v>109.3399963378906</v>
       </c>
       <c r="D44" t="n">
-        <v>106.2399978637695</v>
+        <v>106.3099975585938</v>
       </c>
       <c r="E44" t="n">
-        <v>107.5800018310547</v>
+        <v>109.129997253418</v>
       </c>
       <c r="F44" t="n">
-        <v>15021600</v>
+        <v>24873400</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
@@ -1587,22 +1587,22 @@
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
-        <v>45992</v>
+        <v>45993</v>
       </c>
       <c r="B45" t="n">
-        <v>106.5100021362305</v>
+        <v>109.2099990844727</v>
       </c>
       <c r="C45" t="n">
-        <v>109.3399963378906</v>
+        <v>109.7300033569336</v>
       </c>
       <c r="D45" t="n">
-        <v>106.3099975585938</v>
+        <v>107.5199966430664</v>
       </c>
       <c r="E45" t="n">
-        <v>109.129997253418</v>
+        <v>109.3499984741211</v>
       </c>
       <c r="F45" t="n">
-        <v>24873400</v>
+        <v>25763000</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
@@ -1613,22 +1613,22 @@
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
-        <v>45993</v>
+        <v>45994</v>
       </c>
       <c r="B46" t="n">
-        <v>109.2099990844727</v>
+        <v>106.5899963378906</v>
       </c>
       <c r="C46" t="n">
-        <v>109.7300033569336</v>
+        <v>106.870002746582</v>
       </c>
       <c r="D46" t="n">
-        <v>107.5199966430664</v>
+        <v>102.0299987792969</v>
       </c>
       <c r="E46" t="n">
-        <v>109.3499984741211</v>
+        <v>103.9599990844727</v>
       </c>
       <c r="F46" t="n">
-        <v>25763000</v>
+        <v>53593400</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
@@ -1639,22 +1639,22 @@
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
-        <v>45994</v>
+        <v>45995</v>
       </c>
       <c r="B47" t="n">
-        <v>106.5899963378906</v>
+        <v>103.5699996948242</v>
       </c>
       <c r="C47" t="n">
-        <v>106.870002746582</v>
+        <v>103.8000030517578</v>
       </c>
       <c r="D47" t="n">
-        <v>102.0299987792969</v>
+        <v>101.7699966430664</v>
       </c>
       <c r="E47" t="n">
-        <v>103.9599990844727</v>
+        <v>103.2200012207031</v>
       </c>
       <c r="F47" t="n">
-        <v>53593400</v>
+        <v>51779100</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
@@ -1665,22 +1665,22 @@
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
-        <v>45995</v>
+        <v>45996</v>
       </c>
       <c r="B48" t="n">
-        <v>103.5699996948242</v>
+        <v>98.77999877929688</v>
       </c>
       <c r="C48" t="n">
-        <v>103.8000030517578</v>
+        <v>104.7900009155273</v>
       </c>
       <c r="D48" t="n">
-        <v>101.7699966430664</v>
+        <v>97.73999786376953</v>
       </c>
       <c r="E48" t="n">
-        <v>103.2200012207031</v>
+        <v>100.2399978637695</v>
       </c>
       <c r="F48" t="n">
-        <v>51779100</v>
+        <v>133363600</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
@@ -1691,22 +1691,22 @@
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>45996</v>
+        <v>45999</v>
       </c>
       <c r="B49" t="n">
-        <v>98.77999877929688</v>
+        <v>99.87000274658203</v>
       </c>
       <c r="C49" t="n">
-        <v>104.7900009155273</v>
+        <v>99.88999938964844</v>
       </c>
       <c r="D49" t="n">
-        <v>97.73999786376953</v>
+        <v>95.30000305175781</v>
       </c>
       <c r="E49" t="n">
-        <v>100.2399978637695</v>
+        <v>96.79000091552734</v>
       </c>
       <c r="F49" t="n">
-        <v>133363600</v>
+        <v>100906300</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
@@ -1717,22 +1717,22 @@
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>45999</v>
+        <v>46000</v>
       </c>
       <c r="B50" t="n">
-        <v>99.87000274658203</v>
+        <v>97.02999877929688</v>
       </c>
       <c r="C50" t="n">
-        <v>99.88999938964844</v>
+        <v>97.23999786376953</v>
       </c>
       <c r="D50" t="n">
-        <v>95.30000305175781</v>
+        <v>95.44999694824219</v>
       </c>
       <c r="E50" t="n">
-        <v>96.79000091552734</v>
+        <v>96.70999908447266</v>
       </c>
       <c r="F50" t="n">
-        <v>100906300</v>
+        <v>51745600</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
-        <v>46000</v>
+        <v>46001</v>
       </c>
       <c r="B51" t="n">
-        <v>97.02999877929688</v>
+        <v>96.73999786376953</v>
       </c>
       <c r="C51" t="n">
-        <v>97.23999786376953</v>
+        <v>96.97000122070312</v>
       </c>
       <c r="D51" t="n">
-        <v>95.44999694824219</v>
+        <v>92.34999847412109</v>
       </c>
       <c r="E51" t="n">
-        <v>96.70999908447266</v>
+        <v>92.70999908447266</v>
       </c>
       <c r="F51" t="n">
-        <v>51745600</v>
+        <v>74129300</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
@@ -1769,22 +1769,22 @@
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
-        <v>46001</v>
+        <v>46002</v>
       </c>
       <c r="B52" t="n">
-        <v>96.73999786376953</v>
+        <v>93.90000152587891</v>
       </c>
       <c r="C52" t="n">
-        <v>96.97000122070312</v>
+        <v>94.81999969482422</v>
       </c>
       <c r="D52" t="n">
-        <v>92.34999847412109</v>
+        <v>92.76000213623047</v>
       </c>
       <c r="E52" t="n">
-        <v>92.70999908447266</v>
+        <v>94.08999633789062</v>
       </c>
       <c r="F52" t="n">
-        <v>74129300</v>
+        <v>43949000</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
@@ -1795,22 +1795,22 @@
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
-        <v>46002</v>
+        <v>46003</v>
       </c>
       <c r="B53" t="n">
-        <v>93.90000152587891</v>
+        <v>95.5</v>
       </c>
       <c r="C53" t="n">
-        <v>94.81999969482422</v>
+        <v>96.91999816894531</v>
       </c>
       <c r="D53" t="n">
-        <v>92.76000213623047</v>
+        <v>94.65000152587891</v>
       </c>
       <c r="E53" t="n">
-        <v>94.08999633789062</v>
+        <v>95.19000244140625</v>
       </c>
       <c r="F53" t="n">
-        <v>43949000</v>
+        <v>49323100</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
@@ -1821,22 +1821,22 @@
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
-        <v>46003</v>
+        <v>46006</v>
       </c>
       <c r="B54" t="n">
-        <v>95.5</v>
+        <v>96.01999664306641</v>
       </c>
       <c r="C54" t="n">
-        <v>96.91999816894531</v>
+        <v>96.37000274658203</v>
       </c>
       <c r="D54" t="n">
-        <v>94.65000152587891</v>
+        <v>93.52999877929688</v>
       </c>
       <c r="E54" t="n">
-        <v>95.19000244140625</v>
+        <v>93.76999664306641</v>
       </c>
       <c r="F54" t="n">
-        <v>49323100</v>
+        <v>40016500</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
@@ -1847,22 +1847,22 @@
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
-        <v>46006</v>
+        <v>46007</v>
       </c>
       <c r="B55" t="n">
-        <v>96.01999664306641</v>
+        <v>93.87999725341797</v>
       </c>
       <c r="C55" t="n">
-        <v>96.37000274658203</v>
+        <v>94.93000030517578</v>
       </c>
       <c r="D55" t="n">
-        <v>93.52999877929688</v>
+        <v>93.31999969482422</v>
       </c>
       <c r="E55" t="n">
-        <v>93.76999664306641</v>
+        <v>94.56999969482422</v>
       </c>
       <c r="F55" t="n">
-        <v>40016500</v>
+        <v>34265000</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
@@ -1873,22 +1873,22 @@
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
-        <v>46007</v>
+        <v>46008</v>
       </c>
       <c r="B56" t="n">
-        <v>93.87999725341797</v>
+        <v>95.98000335693359</v>
       </c>
       <c r="C56" t="n">
-        <v>94.93000030517578</v>
+        <v>97.33000183105469</v>
       </c>
       <c r="D56" t="n">
-        <v>93.31999969482422</v>
+        <v>94.45999908447266</v>
       </c>
       <c r="E56" t="n">
-        <v>94.56999969482422</v>
+        <v>94.79000091552734</v>
       </c>
       <c r="F56" t="n">
-        <v>34265000</v>
+        <v>50472800</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
@@ -1899,22 +1899,22 @@
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
-        <v>46008</v>
+        <v>46009</v>
       </c>
       <c r="B57" t="n">
-        <v>95.98000335693359</v>
+        <v>95.01999664306641</v>
       </c>
       <c r="C57" t="n">
-        <v>97.33000183105469</v>
+        <v>95.80999755859375</v>
       </c>
       <c r="D57" t="n">
-        <v>94.45999908447266</v>
+        <v>93.58999633789062</v>
       </c>
       <c r="E57" t="n">
-        <v>94.79000091552734</v>
+        <v>94</v>
       </c>
       <c r="F57" t="n">
-        <v>50472800</v>
+        <v>37244700</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
@@ -1925,22 +1925,22 @@
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
-        <v>46009</v>
+        <v>46010</v>
       </c>
       <c r="B58" t="n">
-        <v>95.01999664306641</v>
+        <v>93.56999969482422</v>
       </c>
       <c r="C58" t="n">
-        <v>95.80999755859375</v>
+        <v>95.54000091552734</v>
       </c>
       <c r="D58" t="n">
-        <v>93.58999633789062</v>
+        <v>93.44999694824219</v>
       </c>
       <c r="E58" t="n">
-        <v>94</v>
+        <v>94.38999938964844</v>
       </c>
       <c r="F58" t="n">
-        <v>37244700</v>
+        <v>78990200</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
@@ -1951,22 +1951,22 @@
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
-        <v>46010</v>
+        <v>46013</v>
       </c>
       <c r="B59" t="n">
-        <v>93.56999969482422</v>
+        <v>94.70999908447266</v>
       </c>
       <c r="C59" t="n">
-        <v>95.54000091552734</v>
+        <v>94.70999908447266</v>
       </c>
       <c r="D59" t="n">
-        <v>93.44999694824219</v>
+        <v>92.91000366210938</v>
       </c>
       <c r="E59" t="n">
-        <v>94.38999938964844</v>
+        <v>93.23000335693359</v>
       </c>
       <c r="F59" t="n">
-        <v>78990200</v>
+        <v>39484800</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
@@ -1977,22 +1977,22 @@
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
-        <v>46013</v>
+        <v>46014</v>
       </c>
       <c r="B60" t="n">
-        <v>94.70999908447266</v>
+        <v>93.40000152587891</v>
       </c>
       <c r="C60" t="n">
-        <v>94.70999908447266</v>
+        <v>93.80999755859375</v>
       </c>
       <c r="D60" t="n">
-        <v>92.91000366210938</v>
+        <v>91.33000183105469</v>
       </c>
       <c r="E60" t="n">
-        <v>93.23000335693359</v>
+        <v>93.5</v>
       </c>
       <c r="F60" t="n">
-        <v>39484800</v>
+        <v>25896200</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
@@ -2003,22 +2003,22 @@
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
-        <v>46014</v>
+        <v>46015</v>
       </c>
       <c r="B61" t="n">
-        <v>93.40000152587891</v>
+        <v>93.11000061035156</v>
       </c>
       <c r="C61" t="n">
-        <v>93.80999755859375</v>
+        <v>93.68000030517578</v>
       </c>
       <c r="D61" t="n">
-        <v>91.33000183105469</v>
+        <v>92.66999816894531</v>
       </c>
       <c r="E61" t="n">
-        <v>93.5</v>
+        <v>93.63999938964844</v>
       </c>
       <c r="F61" t="n">
-        <v>25896200</v>
+        <v>12427900</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
@@ -2029,22 +2029,22 @@
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
-        <v>46015</v>
+        <v>46017</v>
       </c>
       <c r="B62" t="n">
-        <v>93.11000061035156</v>
+        <v>93.48000335693359</v>
       </c>
       <c r="C62" t="n">
-        <v>93.68000030517578</v>
+        <v>94.69000244140625</v>
       </c>
       <c r="D62" t="n">
-        <v>92.66999816894531</v>
+        <v>93.26999664306641</v>
       </c>
       <c r="E62" t="n">
-        <v>93.63999938964844</v>
+        <v>94.47000122070312</v>
       </c>
       <c r="F62" t="n">
-        <v>12427900</v>
+        <v>22068300</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
@@ -2055,22 +2055,22 @@
     </row>
     <row r="63">
       <c r="A63" s="1" t="n">
-        <v>46017</v>
+        <v>46020</v>
       </c>
       <c r="B63" t="n">
-        <v>93.48000335693359</v>
+        <v>93.98999786376953</v>
       </c>
       <c r="C63" t="n">
-        <v>94.69000244140625</v>
+        <v>94.97000122070312</v>
       </c>
       <c r="D63" t="n">
-        <v>93.26999664306641</v>
+        <v>93.62999725341797</v>
       </c>
       <c r="E63" t="n">
-        <v>94.47000122070312</v>
+        <v>94.15000152587891</v>
       </c>
       <c r="F63" t="n">
-        <v>22068300</v>
+        <v>24493700</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
@@ -2081,22 +2081,22 @@
     </row>
     <row r="64">
       <c r="A64" s="1" t="n">
-        <v>46020</v>
+        <v>46021</v>
       </c>
       <c r="B64" t="n">
+        <v>93.51999664306641</v>
+      </c>
+      <c r="C64" t="n">
         <v>93.98999786376953</v>
       </c>
-      <c r="C64" t="n">
-        <v>94.97000122070312</v>
-      </c>
       <c r="D64" t="n">
-        <v>93.62999725341797</v>
+        <v>93.33999633789062</v>
       </c>
       <c r="E64" t="n">
-        <v>94.15000152587891</v>
+        <v>93.77999877929688</v>
       </c>
       <c r="F64" t="n">
-        <v>24493700</v>
+        <v>23422000</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
@@ -2107,22 +2107,22 @@
     </row>
     <row r="65">
       <c r="A65" s="1" t="n">
-        <v>46021</v>
+        <v>46022</v>
       </c>
       <c r="B65" t="n">
-        <v>93.51999664306641</v>
+        <v>93.59999847412109</v>
       </c>
       <c r="C65" t="n">
-        <v>93.98999786376953</v>
+        <v>94.30999755859375</v>
       </c>
       <c r="D65" t="n">
-        <v>93.33999633789062</v>
+        <v>93.19999694824219</v>
       </c>
       <c r="E65" t="n">
-        <v>93.77999877929688</v>
+        <v>93.76000213623047</v>
       </c>
       <c r="F65" t="n">
-        <v>23422000</v>
+        <v>23495200</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
@@ -2133,22 +2133,22 @@
     </row>
     <row r="66">
       <c r="A66" s="1" t="n">
-        <v>46022</v>
+        <v>46024</v>
       </c>
       <c r="B66" t="n">
-        <v>93.59999847412109</v>
+        <v>94.12999725341797</v>
       </c>
       <c r="C66" t="n">
-        <v>94.30999755859375</v>
+        <v>94.12999725341797</v>
       </c>
       <c r="D66" t="n">
-        <v>93.19999694824219</v>
+        <v>90.80999755859375</v>
       </c>
       <c r="E66" t="n">
-        <v>93.76000213623047</v>
+        <v>90.98999786376953</v>
       </c>
       <c r="F66" t="n">
-        <v>23495200</v>
+        <v>41155400</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
@@ -2159,22 +2159,22 @@
     </row>
     <row r="67">
       <c r="A67" s="1" t="n">
-        <v>46024</v>
+        <v>46027</v>
       </c>
       <c r="B67" t="n">
-        <v>94.12999725341797</v>
+        <v>90.91999816894531</v>
       </c>
       <c r="C67" t="n">
-        <v>94.12999725341797</v>
+        <v>92.62999725341797</v>
       </c>
       <c r="D67" t="n">
-        <v>90.80999755859375</v>
+        <v>90.83999633789062</v>
       </c>
       <c r="E67" t="n">
-        <v>90.98999786376953</v>
+        <v>91.45999908447266</v>
       </c>
       <c r="F67" t="n">
-        <v>41155400</v>
+        <v>39183300</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
@@ -2185,22 +2185,22 @@
     </row>
     <row r="68">
       <c r="A68" s="1" t="n">
-        <v>46027</v>
+        <v>46028</v>
       </c>
       <c r="B68" t="n">
-        <v>90.91999816894531</v>
+        <v>91.54000091552734</v>
       </c>
       <c r="C68" t="n">
-        <v>92.62999725341797</v>
+        <v>91.63999938964844</v>
       </c>
       <c r="D68" t="n">
-        <v>90.83999633789062</v>
+        <v>89.73999786376953</v>
       </c>
       <c r="E68" t="n">
-        <v>91.45999908447266</v>
+        <v>90.65000152587891</v>
       </c>
       <c r="F68" t="n">
-        <v>39183300</v>
+        <v>43331000</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
@@ -2211,22 +2211,22 @@
     </row>
     <row r="69">
       <c r="A69" s="1" t="n">
-        <v>46028</v>
+        <v>46029</v>
       </c>
       <c r="B69" t="n">
-        <v>91.54000091552734</v>
+        <v>91.55999755859375</v>
       </c>
       <c r="C69" t="n">
-        <v>91.63999938964844</v>
+        <v>92.41999816894531</v>
       </c>
       <c r="D69" t="n">
-        <v>89.73999786376953</v>
+        <v>90.05999755859375</v>
       </c>
       <c r="E69" t="n">
-        <v>90.65000152587891</v>
+        <v>90.73000335693359</v>
       </c>
       <c r="F69" t="n">
-        <v>43331000</v>
+        <v>36525700</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
@@ -2237,22 +2237,22 @@
     </row>
     <row r="70">
       <c r="A70" s="1" t="n">
-        <v>46029</v>
+        <v>46030</v>
       </c>
       <c r="B70" t="n">
-        <v>91.55999755859375</v>
+        <v>90.44999694824219</v>
       </c>
       <c r="C70" t="n">
-        <v>92.41999816894531</v>
+        <v>91.25</v>
       </c>
       <c r="D70" t="n">
-        <v>90.05999755859375</v>
+        <v>89.58000183105469</v>
       </c>
       <c r="E70" t="n">
-        <v>90.73000335693359</v>
+        <v>90.52999877929688</v>
       </c>
       <c r="F70" t="n">
-        <v>36525700</v>
+        <v>40068700</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
@@ -2263,22 +2263,22 @@
     </row>
     <row r="71">
       <c r="A71" s="1" t="n">
-        <v>46030</v>
+        <v>46031</v>
       </c>
       <c r="B71" t="n">
-        <v>90.44999694824219</v>
+        <v>90.02999877929688</v>
       </c>
       <c r="C71" t="n">
-        <v>91.25</v>
+        <v>90.05000305175781</v>
       </c>
       <c r="D71" t="n">
-        <v>89.58000183105469</v>
+        <v>88.31999969482422</v>
       </c>
       <c r="E71" t="n">
-        <v>90.52999877929688</v>
+        <v>89.45999908447266</v>
       </c>
       <c r="F71" t="n">
-        <v>40068700</v>
+        <v>55579500</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
@@ -2289,22 +2289,22 @@
     </row>
     <row r="72">
       <c r="A72" s="1" t="n">
-        <v>46031</v>
+        <v>46034</v>
       </c>
       <c r="B72" t="n">
-        <v>90.02999877929688</v>
+        <v>89.69000244140625</v>
       </c>
       <c r="C72" t="n">
-        <v>90.05000305175781</v>
+        <v>90.33999633789062</v>
       </c>
       <c r="D72" t="n">
-        <v>88.31999969482422</v>
+        <v>89.33000183105469</v>
       </c>
       <c r="E72" t="n">
-        <v>89.45999908447266</v>
+        <v>89.41000366210938</v>
       </c>
       <c r="F72" t="n">
-        <v>55579500</v>
+        <v>36290600</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
@@ -2315,22 +2315,22 @@
     </row>
     <row r="73">
       <c r="A73" s="1" t="n">
-        <v>46034</v>
+        <v>46035</v>
       </c>
       <c r="B73" t="n">
-        <v>89.69000244140625</v>
+        <v>89.44000244140625</v>
       </c>
       <c r="C73" t="n">
-        <v>90.33999633789062</v>
+        <v>91.15000152587891</v>
       </c>
       <c r="D73" t="n">
-        <v>89.33000183105469</v>
+        <v>89.06999969482422</v>
       </c>
       <c r="E73" t="n">
-        <v>89.41000366210938</v>
+        <v>90.31999969482422</v>
       </c>
       <c r="F73" t="n">
-        <v>36290600</v>
+        <v>45221100</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
@@ -2341,22 +2341,22 @@
     </row>
     <row r="74">
       <c r="A74" s="1" t="n">
-        <v>46035</v>
+        <v>46036</v>
       </c>
       <c r="B74" t="n">
-        <v>89.44000244140625</v>
+        <v>91.23999786376953</v>
       </c>
       <c r="C74" t="n">
-        <v>91.15000152587891</v>
+        <v>91.58000183105469</v>
       </c>
       <c r="D74" t="n">
-        <v>89.06999969482422</v>
+        <v>87.94999694824219</v>
       </c>
       <c r="E74" t="n">
-        <v>90.31999969482422</v>
+        <v>88.55000305175781</v>
       </c>
       <c r="F74" t="n">
-        <v>45221100</v>
+        <v>49737700</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
@@ -2367,22 +2367,22 @@
     </row>
     <row r="75">
       <c r="A75" s="1" t="n">
-        <v>46036</v>
+        <v>46037</v>
       </c>
       <c r="B75" t="n">
-        <v>91.23999786376953</v>
+        <v>89.01999664306641</v>
       </c>
       <c r="C75" t="n">
-        <v>91.58000183105469</v>
+        <v>89.88999938964844</v>
       </c>
       <c r="D75" t="n">
-        <v>87.94999694824219</v>
+        <v>87.81999969482422</v>
       </c>
       <c r="E75" t="n">
-        <v>88.55000305175781</v>
+        <v>88.05000305175781</v>
       </c>
       <c r="F75" t="n">
-        <v>49737700</v>
+        <v>36945100</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
@@ -2393,22 +2393,22 @@
     </row>
     <row r="76">
       <c r="A76" s="1" t="n">
-        <v>46037</v>
+        <v>46038</v>
       </c>
       <c r="B76" t="n">
-        <v>89.01999664306641</v>
+        <v>88.33999633789062</v>
       </c>
       <c r="C76" t="n">
-        <v>89.88999938964844</v>
+        <v>88.51000213623047</v>
       </c>
       <c r="D76" t="n">
-        <v>87.81999969482422</v>
+        <v>87.77999877929688</v>
       </c>
       <c r="E76" t="n">
-        <v>88.05000305175781</v>
+        <v>88</v>
       </c>
       <c r="F76" t="n">
-        <v>36945100</v>
+        <v>48130500</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
@@ -2419,22 +2419,22 @@
     </row>
     <row r="77">
       <c r="A77" s="1" t="n">
-        <v>46038</v>
+        <v>46042</v>
       </c>
       <c r="B77" t="n">
-        <v>88.33999633789062</v>
+        <v>88.97000122070312</v>
       </c>
       <c r="C77" t="n">
-        <v>88.51000213623047</v>
+        <v>89.90000152587891</v>
       </c>
       <c r="D77" t="n">
-        <v>87.77999877929688</v>
+        <v>87.01999664306641</v>
       </c>
       <c r="E77" t="n">
-        <v>88</v>
+        <v>87.26000213623047</v>
       </c>
       <c r="F77" t="n">
-        <v>48130500</v>
+        <v>109729700</v>
       </c>
       <c r="G77" t="n">
         <v>0</v>
@@ -2445,22 +2445,22 @@
     </row>
     <row r="78">
       <c r="A78" s="1" t="n">
-        <v>46042</v>
+        <v>46043</v>
       </c>
       <c r="B78" t="n">
-        <v>88.97000122070312</v>
+        <v>82.51999664306641</v>
       </c>
       <c r="C78" t="n">
-        <v>89.90000152587891</v>
+        <v>86</v>
       </c>
       <c r="D78" t="n">
-        <v>87.01999664306641</v>
+        <v>81.93000030517578</v>
       </c>
       <c r="E78" t="n">
-        <v>87.26000213623047</v>
+        <v>85.36000061035156</v>
       </c>
       <c r="F78" t="n">
-        <v>109729700</v>
+        <v>127940700</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
@@ -2471,22 +2471,22 @@
     </row>
     <row r="79">
       <c r="A79" s="1" t="n">
-        <v>46043</v>
+        <v>46044</v>
       </c>
       <c r="B79" t="n">
-        <v>82.51999664306641</v>
+        <v>85.01999664306641</v>
       </c>
       <c r="C79" t="n">
-        <v>86</v>
+        <v>85.09999847412109</v>
       </c>
       <c r="D79" t="n">
-        <v>81.93000030517578</v>
+        <v>82.98000335693359</v>
       </c>
       <c r="E79" t="n">
-        <v>85.36000061035156</v>
+        <v>83.54000091552734</v>
       </c>
       <c r="F79" t="n">
-        <v>127940700</v>
+        <v>69113300</v>
       </c>
       <c r="G79" t="n">
         <v>0</v>
@@ -2497,22 +2497,22 @@
     </row>
     <row r="80">
       <c r="A80" s="1" t="n">
-        <v>46044</v>
+        <v>46045</v>
       </c>
       <c r="B80" t="n">
-        <v>85.01999664306641</v>
+        <v>83.43000030517578</v>
       </c>
       <c r="C80" t="n">
-        <v>85.09999847412109</v>
+        <v>86.30000305175781</v>
       </c>
       <c r="D80" t="n">
-        <v>82.98000335693359</v>
+        <v>83.27999877929688</v>
       </c>
       <c r="E80" t="n">
-        <v>83.54000091552734</v>
+        <v>86.12000274658203</v>
       </c>
       <c r="F80" t="n">
-        <v>69113300</v>
+        <v>64520400</v>
       </c>
       <c r="G80" t="n">
         <v>0</v>
@@ -2523,22 +2523,22 @@
     </row>
     <row r="81">
       <c r="A81" s="1" t="n">
-        <v>46045</v>
+        <v>46048</v>
       </c>
       <c r="B81" t="n">
-        <v>83.43000030517578</v>
+        <v>86.91999816894531</v>
       </c>
       <c r="C81" t="n">
-        <v>86.30000305175781</v>
+        <v>86.94000244140625</v>
       </c>
       <c r="D81" t="n">
-        <v>83.27999877929688</v>
+        <v>85.34999847412109</v>
       </c>
       <c r="E81" t="n">
-        <v>86.12000274658203</v>
+        <v>85.69999694824219</v>
       </c>
       <c r="F81" t="n">
-        <v>64520400</v>
+        <v>40941900</v>
       </c>
       <c r="G81" t="n">
         <v>0</v>
@@ -2549,22 +2549,22 @@
     </row>
     <row r="82">
       <c r="A82" s="1" t="n">
-        <v>46048</v>
+        <v>46049</v>
       </c>
       <c r="B82" t="n">
-        <v>86.91999816894531</v>
+        <v>85.27999877929688</v>
       </c>
       <c r="C82" t="n">
-        <v>86.94000244140625</v>
+        <v>85.59999847412109</v>
       </c>
       <c r="D82" t="n">
-        <v>85.34999847412109</v>
+        <v>83.87999725341797</v>
       </c>
       <c r="E82" t="n">
-        <v>85.69999694824219</v>
+        <v>85.58000183105469</v>
       </c>
       <c r="F82" t="n">
-        <v>40941900</v>
+        <v>37790800</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
@@ -2575,22 +2575,22 @@
     </row>
     <row r="83">
       <c r="A83" s="1" t="n">
-        <v>46049</v>
+        <v>46050</v>
       </c>
       <c r="B83" t="n">
-        <v>85.27999877929688</v>
+        <v>85.62999725341797</v>
       </c>
       <c r="C83" t="n">
-        <v>85.59999847412109</v>
+        <v>86.47000122070312</v>
       </c>
       <c r="D83" t="n">
-        <v>83.87999725341797</v>
+        <v>84.30000305175781</v>
       </c>
       <c r="E83" t="n">
-        <v>85.58000183105469</v>
+        <v>84.63999938964844</v>
       </c>
       <c r="F83" t="n">
-        <v>37790800</v>
+        <v>37762600</v>
       </c>
       <c r="G83" t="n">
         <v>0</v>
@@ -2601,22 +2601,22 @@
     </row>
     <row r="84">
       <c r="A84" s="1" t="n">
-        <v>46050</v>
+        <v>46051</v>
       </c>
       <c r="B84" t="n">
-        <v>85.62999725341797</v>
+        <v>84.30999755859375</v>
       </c>
       <c r="C84" t="n">
-        <v>86.47000122070312</v>
+        <v>84.37999725341797</v>
       </c>
       <c r="D84" t="n">
-        <v>84.30000305175781</v>
+        <v>82.34999847412109</v>
       </c>
       <c r="E84" t="n">
-        <v>84.63999938964844</v>
+        <v>83.16000366210938</v>
       </c>
       <c r="F84" t="n">
-        <v>37762600</v>
+        <v>42278100</v>
       </c>
       <c r="G84" t="n">
         <v>0</v>
@@ -2627,22 +2627,22 @@
     </row>
     <row r="85">
       <c r="A85" s="1" t="n">
-        <v>46051</v>
+        <v>46052</v>
       </c>
       <c r="B85" t="n">
-        <v>84.30999755859375</v>
+        <v>83.09999847412109</v>
       </c>
       <c r="C85" t="n">
-        <v>84.37999725341797</v>
+        <v>84.05999755859375</v>
       </c>
       <c r="D85" t="n">
-        <v>82.34999847412109</v>
+        <v>82.77999877929688</v>
       </c>
       <c r="E85" t="n">
-        <v>83.16000366210938</v>
+        <v>83.48999786376953</v>
       </c>
       <c r="F85" t="n">
-        <v>42278100</v>
+        <v>45755000</v>
       </c>
       <c r="G85" t="n">
         <v>0</v>
@@ -2653,22 +2653,22 @@
     </row>
     <row r="86">
       <c r="A86" s="1" t="n">
-        <v>46052</v>
+        <v>46055</v>
       </c>
       <c r="B86" t="n">
-        <v>83.09999847412109</v>
+        <v>83.52999877929688</v>
       </c>
       <c r="C86" t="n">
-        <v>84.05999755859375</v>
+        <v>85.26999664306641</v>
       </c>
       <c r="D86" t="n">
-        <v>82.77999877929688</v>
+        <v>82.72000122070312</v>
       </c>
       <c r="E86" t="n">
-        <v>83.48999786376953</v>
+        <v>82.76000213623047</v>
       </c>
       <c r="F86" t="n">
-        <v>45755000</v>
+        <v>41445300</v>
       </c>
       <c r="G86" t="n">
         <v>0</v>
@@ -2679,22 +2679,22 @@
     </row>
     <row r="87">
       <c r="A87" s="1" t="n">
-        <v>46055</v>
+        <v>46056</v>
       </c>
       <c r="B87" t="n">
-        <v>83.52999877929688</v>
+        <v>82.23000335693359</v>
       </c>
       <c r="C87" t="n">
-        <v>85.26999664306641</v>
+        <v>82.44999694824219</v>
       </c>
       <c r="D87" t="n">
-        <v>82.72000122070312</v>
+        <v>79.62000274658203</v>
       </c>
       <c r="E87" t="n">
-        <v>82.76000213623047</v>
+        <v>79.94000244140625</v>
       </c>
       <c r="F87" t="n">
-        <v>41445300</v>
+        <v>49789000</v>
       </c>
       <c r="G87" t="n">
         <v>0</v>
@@ -2705,22 +2705,22 @@
     </row>
     <row r="88">
       <c r="A88" s="1" t="n">
-        <v>46056</v>
+        <v>46057</v>
       </c>
       <c r="B88" t="n">
-        <v>82.23000335693359</v>
+        <v>79.98999786376953</v>
       </c>
       <c r="C88" t="n">
-        <v>82.44999694824219</v>
+        <v>81.44000244140625</v>
       </c>
       <c r="D88" t="n">
-        <v>79.62000274658203</v>
+        <v>79.23000335693359</v>
       </c>
       <c r="E88" t="n">
-        <v>79.94000244140625</v>
+        <v>80.16000366210938</v>
       </c>
       <c r="F88" t="n">
-        <v>49789000</v>
+        <v>48963200</v>
       </c>
       <c r="G88" t="n">
         <v>0</v>
@@ -2731,22 +2731,22 @@
     </row>
     <row r="89">
       <c r="A89" s="1" t="n">
-        <v>46057</v>
+        <v>46058</v>
       </c>
       <c r="B89" t="n">
-        <v>79.98999786376953</v>
+        <v>81.48999786376953</v>
       </c>
       <c r="C89" t="n">
-        <v>81.44000244140625</v>
+        <v>83.30000305175781</v>
       </c>
       <c r="D89" t="n">
-        <v>79.23000335693359</v>
+        <v>80.54000091552734</v>
       </c>
       <c r="E89" t="n">
-        <v>80.16000366210938</v>
+        <v>80.87000274658203</v>
       </c>
       <c r="F89" t="n">
-        <v>48963200</v>
+        <v>54805700</v>
       </c>
       <c r="G89" t="n">
         <v>0</v>
@@ -2757,22 +2757,22 @@
     </row>
     <row r="90">
       <c r="A90" s="1" t="n">
-        <v>46058</v>
+        <v>46059</v>
       </c>
       <c r="B90" t="n">
-        <v>81.48999786376953</v>
+        <v>81.01999664306641</v>
       </c>
       <c r="C90" t="n">
-        <v>83.30000305175781</v>
+        <v>82.48999786376953</v>
       </c>
       <c r="D90" t="n">
-        <v>80.54000091552734</v>
+        <v>80.65000152587891</v>
       </c>
       <c r="E90" t="n">
-        <v>80.87000274658203</v>
+        <v>82.19999694824219</v>
       </c>
       <c r="F90" t="n">
-        <v>54805700</v>
+        <v>46154100</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
@@ -2783,22 +2783,22 @@
     </row>
     <row r="91">
       <c r="A91" s="1" t="n">
-        <v>46059</v>
+        <v>46062</v>
       </c>
       <c r="B91" t="n">
-        <v>81.01999664306641</v>
+        <v>82.18000030517578</v>
       </c>
       <c r="C91" t="n">
-        <v>82.48999786376953</v>
+        <v>82.20999908447266</v>
       </c>
       <c r="D91" t="n">
-        <v>80.65000152587891</v>
+        <v>79.87000274658203</v>
       </c>
       <c r="E91" t="n">
-        <v>82.19999694824219</v>
+        <v>81.47000122070312</v>
       </c>
       <c r="F91" t="n">
-        <v>46154100</v>
+        <v>42200200</v>
       </c>
       <c r="G91" t="n">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="92">
       <c r="A92" s="1" t="n">
-        <v>46062</v>
+        <v>46063</v>
       </c>
       <c r="B92" t="n">
-        <v>82.18000030517578</v>
+        <v>82.72000122070312</v>
       </c>
       <c r="C92" t="n">
+        <v>84.66000366210938</v>
+      </c>
+      <c r="D92" t="n">
+        <v>82.08999633789062</v>
+      </c>
+      <c r="E92" t="n">
         <v>82.20999908447266</v>
       </c>
-      <c r="D92" t="n">
-        <v>79.87000274658203</v>
-      </c>
-      <c r="E92" t="n">
-        <v>81.47000122070312</v>
-      </c>
       <c r="F92" t="n">
-        <v>42200200</v>
+        <v>43595800</v>
       </c>
       <c r="G92" t="n">
         <v>0</v>
@@ -2835,22 +2835,22 @@
     </row>
     <row r="93">
       <c r="A93" s="1" t="n">
-        <v>46063</v>
+        <v>46064</v>
       </c>
       <c r="B93" t="n">
-        <v>82.72000122070312</v>
+        <v>81.95999908447266</v>
       </c>
       <c r="C93" t="n">
-        <v>84.66000366210938</v>
+        <v>82.48000335693359</v>
       </c>
       <c r="D93" t="n">
-        <v>82.08999633789062</v>
+        <v>79.44999694824219</v>
       </c>
       <c r="E93" t="n">
-        <v>82.20999908447266</v>
+        <v>79.62000274658203</v>
       </c>
       <c r="F93" t="n">
-        <v>43595800</v>
+        <v>40840300</v>
       </c>
       <c r="G93" t="n">
         <v>0</v>
@@ -2861,22 +2861,22 @@
     </row>
     <row r="94">
       <c r="A94" s="1" t="n">
-        <v>46064</v>
+        <v>46065</v>
       </c>
       <c r="B94" t="n">
-        <v>81.95999908447266</v>
+        <v>79.11000061035156</v>
       </c>
       <c r="C94" t="n">
-        <v>82.48000335693359</v>
+        <v>79.15000152587891</v>
       </c>
       <c r="D94" t="n">
-        <v>79.44999694824219</v>
+        <v>75.23000335693359</v>
       </c>
       <c r="E94" t="n">
-        <v>79.62000274658203</v>
+        <v>75.86000061035156</v>
       </c>
       <c r="F94" t="n">
-        <v>40840300</v>
+        <v>73516100</v>
       </c>
       <c r="G94" t="n">
         <v>0</v>
@@ -2887,22 +2887,22 @@
     </row>
     <row r="95">
       <c r="A95" s="1" t="n">
-        <v>46065</v>
+        <v>46066</v>
       </c>
       <c r="B95" t="n">
-        <v>79.11000061035156</v>
+        <v>76.13999938964844</v>
       </c>
       <c r="C95" t="n">
-        <v>79.15000152587891</v>
+        <v>77.18000030517578</v>
       </c>
       <c r="D95" t="n">
-        <v>75.23000335693359</v>
+        <v>75.52999877929688</v>
       </c>
       <c r="E95" t="n">
-        <v>75.86000061035156</v>
+        <v>76.87000274658203</v>
       </c>
       <c r="F95" t="n">
-        <v>73516100</v>
+        <v>42292100</v>
       </c>
       <c r="G95" t="n">
         <v>0</v>
@@ -2913,22 +2913,22 @@
     </row>
     <row r="96">
       <c r="A96" s="1" t="n">
-        <v>46066</v>
+        <v>46070</v>
       </c>
       <c r="B96" t="n">
-        <v>76.13999938964844</v>
+        <v>76.91999816894531</v>
       </c>
       <c r="C96" t="n">
-        <v>77.18000030517578</v>
+        <v>77.87000274658203</v>
       </c>
       <c r="D96" t="n">
-        <v>75.52999877929688</v>
+        <v>75.30000305175781</v>
       </c>
       <c r="E96" t="n">
-        <v>76.87000274658203</v>
+        <v>77</v>
       </c>
       <c r="F96" t="n">
-        <v>42292100</v>
+        <v>35961500</v>
       </c>
       <c r="G96" t="n">
         <v>0</v>
@@ -2939,22 +2939,22 @@
     </row>
     <row r="97">
       <c r="A97" s="1" t="n">
-        <v>46070</v>
+        <v>46071</v>
       </c>
       <c r="B97" t="n">
-        <v>76.91999816894531</v>
+        <v>77.31999969482422</v>
       </c>
       <c r="C97" t="n">
-        <v>77.87000274658203</v>
+        <v>78.31999969482422</v>
       </c>
       <c r="D97" t="n">
-        <v>75.30000305175781</v>
+        <v>76.27999877929688</v>
       </c>
       <c r="E97" t="n">
-        <v>77</v>
+        <v>77.98999786376953</v>
       </c>
       <c r="F97" t="n">
-        <v>35961500</v>
+        <v>29883100</v>
       </c>
       <c r="G97" t="n">
         <v>0</v>
@@ -2965,22 +2965,22 @@
     </row>
     <row r="98">
       <c r="A98" s="1" t="n">
-        <v>46071</v>
+        <v>46072</v>
       </c>
       <c r="B98" t="n">
-        <v>77.31999969482422</v>
+        <v>77.75</v>
       </c>
       <c r="C98" t="n">
-        <v>78.31999969482422</v>
+        <v>78.69999694824219</v>
       </c>
       <c r="D98" t="n">
-        <v>76.27999877929688</v>
+        <v>76.58999633789062</v>
       </c>
       <c r="E98" t="n">
-        <v>77.98999786376953</v>
+        <v>77</v>
       </c>
       <c r="F98" t="n">
-        <v>29883100</v>
+        <v>30139200</v>
       </c>
       <c r="G98" t="n">
         <v>0</v>
@@ -2991,22 +2991,22 @@
     </row>
     <row r="99">
       <c r="A99" s="1" t="n">
-        <v>46072</v>
+        <v>46073</v>
       </c>
       <c r="B99" t="n">
-        <v>77.75</v>
+        <v>76.61000061035156</v>
       </c>
       <c r="C99" t="n">
-        <v>78.69999694824219</v>
+        <v>78.84999847412109</v>
       </c>
       <c r="D99" t="n">
-        <v>76.58999633789062</v>
+        <v>76.40000152587891</v>
       </c>
       <c r="E99" t="n">
-        <v>77</v>
+        <v>78.66999816894531</v>
       </c>
       <c r="F99" t="n">
-        <v>30139200</v>
+        <v>32411300</v>
       </c>
       <c r="G99" t="n">
         <v>0</v>
@@ -3017,22 +3017,22 @@
     </row>
     <row r="100">
       <c r="A100" s="1" t="n">
-        <v>46073</v>
+        <v>46076</v>
       </c>
       <c r="B100" t="n">
-        <v>76.61000061035156</v>
+        <v>77.79000091552734</v>
       </c>
       <c r="C100" t="n">
-        <v>78.84999847412109</v>
+        <v>77.83000183105469</v>
       </c>
       <c r="D100" t="n">
-        <v>76.40000152587891</v>
+        <v>75.01000213623047</v>
       </c>
       <c r="E100" t="n">
-        <v>78.66999816894531</v>
+        <v>76.01999664306641</v>
       </c>
       <c r="F100" t="n">
-        <v>32411300</v>
+        <v>38363000</v>
       </c>
       <c r="G100" t="n">
         <v>0</v>
@@ -3043,22 +3043,22 @@
     </row>
     <row r="101">
       <c r="A101" s="1" t="n">
-        <v>46076</v>
+        <v>46077</v>
       </c>
       <c r="B101" t="n">
-        <v>77.79000091552734</v>
+        <v>75.73000335693359</v>
       </c>
       <c r="C101" t="n">
-        <v>77.83000183105469</v>
+        <v>78.12000274658203</v>
       </c>
       <c r="D101" t="n">
-        <v>75.01000213623047</v>
+        <v>75.20999908447266</v>
       </c>
       <c r="E101" t="n">
-        <v>76.01999664306641</v>
+        <v>78.04000091552734</v>
       </c>
       <c r="F101" t="n">
-        <v>38363000</v>
+        <v>33079100</v>
       </c>
       <c r="G101" t="n">
         <v>0</v>
@@ -3069,22 +3069,22 @@
     </row>
     <row r="102">
       <c r="A102" s="1" t="n">
-        <v>46077</v>
+        <v>46078</v>
       </c>
       <c r="B102" t="n">
-        <v>75.73000335693359</v>
+        <v>79.43000030517578</v>
       </c>
       <c r="C102" t="n">
-        <v>78.12000274658203</v>
+        <v>83.12000274658203</v>
       </c>
       <c r="D102" t="n">
-        <v>75.20999908447266</v>
+        <v>79.25</v>
       </c>
       <c r="E102" t="n">
-        <v>78.04000091552734</v>
+        <v>82.69999694824219</v>
       </c>
       <c r="F102" t="n">
-        <v>33079100</v>
+        <v>69319300</v>
       </c>
       <c r="G102" t="n">
         <v>0</v>
@@ -3095,22 +3095,22 @@
     </row>
     <row r="103">
       <c r="A103" s="1" t="n">
-        <v>46078</v>
+        <v>46079</v>
       </c>
       <c r="B103" t="n">
-        <v>79.43000030517578</v>
+        <v>83.19999694824219</v>
       </c>
       <c r="C103" t="n">
-        <v>83.12000274658203</v>
+        <v>86.5</v>
       </c>
       <c r="D103" t="n">
-        <v>79.25</v>
+        <v>82.80000305175781</v>
       </c>
       <c r="E103" t="n">
-        <v>82.69999694824219</v>
+        <v>84.58999633789062</v>
       </c>
       <c r="F103" t="n">
-        <v>69319300</v>
+        <v>85642500</v>
       </c>
       <c r="G103" t="n">
         <v>0</v>
@@ -3121,22 +3121,22 @@
     </row>
     <row r="104">
       <c r="A104" s="1" t="n">
-        <v>46079</v>
+        <v>46080</v>
       </c>
       <c r="B104" t="n">
-        <v>83.19999694824219</v>
+        <v>94.30000305175781</v>
       </c>
       <c r="C104" t="n">
-        <v>86.5</v>
+        <v>96.75</v>
       </c>
       <c r="D104" t="n">
-        <v>82.80000305175781</v>
+        <v>90.58000183105469</v>
       </c>
       <c r="E104" t="n">
-        <v>84.58999633789062</v>
+        <v>96.23999786376953</v>
       </c>
       <c r="F104" t="n">
-        <v>85642500</v>
+        <v>200767000</v>
       </c>
       <c r="G104" t="n">
         <v>0</v>
@@ -3147,22 +3147,22 @@
     </row>
     <row r="105">
       <c r="A105" s="1" t="n">
-        <v>46080</v>
+        <v>46083</v>
       </c>
       <c r="B105" t="n">
-        <v>94.30000305175781</v>
+        <v>95.26000213623047</v>
       </c>
       <c r="C105" t="n">
-        <v>96.75</v>
+        <v>98.06999969482422</v>
       </c>
       <c r="D105" t="n">
-        <v>90.58000183105469</v>
+        <v>95.19999694824219</v>
       </c>
       <c r="E105" t="n">
-        <v>96.23999786376953</v>
+        <v>97.08999633789062</v>
       </c>
       <c r="F105" t="n">
-        <v>200767000</v>
+        <v>79915400</v>
       </c>
       <c r="G105" t="n">
         <v>0</v>
@@ -3173,22 +3173,22 @@
     </row>
     <row r="106">
       <c r="A106" s="1" t="n">
-        <v>46083</v>
+        <v>46084</v>
       </c>
       <c r="B106" t="n">
-        <v>95.26000213623047</v>
+        <v>96.01000213623047</v>
       </c>
       <c r="C106" t="n">
-        <v>98.06999969482422</v>
+        <v>98.45999908447266</v>
       </c>
       <c r="D106" t="n">
-        <v>95.19999694824219</v>
+        <v>95.33000183105469</v>
       </c>
       <c r="E106" t="n">
-        <v>97.08999633789062</v>
+        <v>97.69999694824219</v>
       </c>
       <c r="F106" t="n">
-        <v>79915400</v>
+        <v>59149000</v>
       </c>
       <c r="G106" t="n">
         <v>0</v>
@@ -3199,22 +3199,22 @@
     </row>
     <row r="107">
       <c r="A107" s="1" t="n">
-        <v>46084</v>
+        <v>46085</v>
       </c>
       <c r="B107" t="n">
-        <v>96.01000213623047</v>
+        <v>97.11000061035156</v>
       </c>
       <c r="C107" t="n">
-        <v>98.45999908447266</v>
+        <v>99.75</v>
       </c>
       <c r="D107" t="n">
-        <v>95.33000183105469</v>
+        <v>96.98999786376953</v>
       </c>
       <c r="E107" t="n">
-        <v>97.69999694824219</v>
+        <v>98.66000366210938</v>
       </c>
       <c r="F107" t="n">
-        <v>59149000</v>
+        <v>52604300</v>
       </c>
       <c r="G107" t="n">
         <v>0</v>
@@ -3225,22 +3225,22 @@
     </row>
     <row r="108">
       <c r="A108" s="1" t="n">
-        <v>46085</v>
+        <v>46086</v>
       </c>
       <c r="B108" t="n">
-        <v>97.11000061035156</v>
+        <v>98.5</v>
       </c>
       <c r="C108" t="n">
-        <v>99.75</v>
+        <v>100.1900024414062</v>
       </c>
       <c r="D108" t="n">
-        <v>96.98999786376953</v>
+        <v>98.09999847412109</v>
       </c>
       <c r="E108" t="n">
-        <v>98.66000366210938</v>
+        <v>99.16999816894531</v>
       </c>
       <c r="F108" t="n">
-        <v>52604300</v>
+        <v>53403000</v>
       </c>
       <c r="G108" t="n">
         <v>0</v>
@@ -3251,22 +3251,22 @@
     </row>
     <row r="109">
       <c r="A109" s="1" t="n">
-        <v>46086</v>
+        <v>46087</v>
       </c>
       <c r="B109" t="n">
-        <v>98.5</v>
+        <v>99.33000183105469</v>
       </c>
       <c r="C109" t="n">
-        <v>100.1900024414062</v>
+        <v>99.87999725341797</v>
       </c>
       <c r="D109" t="n">
-        <v>98.09999847412109</v>
+        <v>97.40000152587891</v>
       </c>
       <c r="E109" t="n">
-        <v>99.16999816894531</v>
+        <v>99.01999664306641</v>
       </c>
       <c r="F109" t="n">
-        <v>53403000</v>
+        <v>41196300</v>
       </c>
       <c r="G109" t="n">
         <v>0</v>
@@ -3277,22 +3277,22 @@
     </row>
     <row r="110">
       <c r="A110" s="1" t="n">
-        <v>46087</v>
+        <v>46090</v>
       </c>
       <c r="B110" t="n">
-        <v>99.33000183105469</v>
+        <v>97.69999694824219</v>
       </c>
       <c r="C110" t="n">
-        <v>99.87999725341797</v>
+        <v>98.94000244140625</v>
       </c>
       <c r="D110" t="n">
-        <v>97.40000152587891</v>
+        <v>96.58000183105469</v>
       </c>
       <c r="E110" t="n">
-        <v>99.01999664306641</v>
+        <v>98.31999969482422</v>
       </c>
       <c r="F110" t="n">
-        <v>41196300</v>
+        <v>48589000</v>
       </c>
       <c r="G110" t="n">
         <v>0</v>
@@ -3303,22 +3303,22 @@
     </row>
     <row r="111">
       <c r="A111" s="1" t="n">
-        <v>46090</v>
+        <v>46091</v>
       </c>
       <c r="B111" t="n">
-        <v>97.69999694824219</v>
+        <v>97.80999755859375</v>
       </c>
       <c r="C111" t="n">
-        <v>98.94000244140625</v>
+        <v>98.48999786376953</v>
       </c>
       <c r="D111" t="n">
-        <v>96.58000183105469</v>
+        <v>96.29000091552734</v>
       </c>
       <c r="E111" t="n">
-        <v>98.31999969482422</v>
+        <v>96.94000244140625</v>
       </c>
       <c r="F111" t="n">
-        <v>48589000</v>
+        <v>41027200</v>
       </c>
       <c r="G111" t="n">
         <v>0</v>
@@ -3329,22 +3329,22 @@
     </row>
     <row r="112">
       <c r="A112" s="1" t="n">
-        <v>46091</v>
+        <v>46092</v>
       </c>
       <c r="B112" t="n">
-        <v>97.80999755859375</v>
+        <v>97.41000366210938</v>
       </c>
       <c r="C112" t="n">
-        <v>98.48999786376953</v>
+        <v>98</v>
       </c>
       <c r="D112" t="n">
-        <v>96.29000091552734</v>
+        <v>94.69000244140625</v>
       </c>
       <c r="E112" t="n">
-        <v>96.94000244140625</v>
+        <v>94.88999938964844</v>
       </c>
       <c r="F112" t="n">
-        <v>41027200</v>
+        <v>33962900</v>
       </c>
       <c r="G112" t="n">
         <v>0</v>
@@ -3355,22 +3355,22 @@
     </row>
     <row r="113">
       <c r="A113" s="1" t="n">
-        <v>46092</v>
+        <v>46093</v>
       </c>
       <c r="B113" t="n">
-        <v>97.41000366210938</v>
+        <v>94.86000061035156</v>
       </c>
       <c r="C113" t="n">
-        <v>98</v>
+        <v>95.40000152587891</v>
       </c>
       <c r="D113" t="n">
-        <v>94.69000244140625</v>
+        <v>93.87000274658203</v>
       </c>
       <c r="E113" t="n">
-        <v>94.88999938964844</v>
+        <v>94.30999755859375</v>
       </c>
       <c r="F113" t="n">
-        <v>33962900</v>
+        <v>34206900</v>
       </c>
       <c r="G113" t="n">
         <v>0</v>
@@ -3381,22 +3381,22 @@
     </row>
     <row r="114">
       <c r="A114" s="1" t="n">
-        <v>46093</v>
+        <v>46094</v>
       </c>
       <c r="B114" t="n">
-        <v>94.86000061035156</v>
+        <v>94.63999938964844</v>
       </c>
       <c r="C114" t="n">
-        <v>95.40000152587891</v>
+        <v>95.68000030517578</v>
       </c>
       <c r="D114" t="n">
-        <v>93.87000274658203</v>
+        <v>94.23999786376953</v>
       </c>
       <c r="E114" t="n">
-        <v>94.30999755859375</v>
+        <v>95.30999755859375</v>
       </c>
       <c r="F114" t="n">
-        <v>34206900</v>
+        <v>29876700</v>
       </c>
       <c r="G114" t="n">
         <v>0</v>
@@ -3407,22 +3407,22 @@
     </row>
     <row r="115">
       <c r="A115" s="1" t="n">
-        <v>46094</v>
+        <v>46097</v>
       </c>
       <c r="B115" t="n">
-        <v>94.63999938964844</v>
+        <v>95.58000183105469</v>
       </c>
       <c r="C115" t="n">
-        <v>95.68000030517578</v>
+        <v>96.09999847412109</v>
       </c>
       <c r="D115" t="n">
-        <v>94.23999786376953</v>
+        <v>94.36000061035156</v>
       </c>
       <c r="E115" t="n">
-        <v>95.30999755859375</v>
+        <v>95.19999694824219</v>
       </c>
       <c r="F115" t="n">
-        <v>29876700</v>
+        <v>34931800</v>
       </c>
       <c r="G115" t="n">
         <v>0</v>
@@ -3433,22 +3433,22 @@
     </row>
     <row r="116">
       <c r="A116" s="1" t="n">
-        <v>46097</v>
+        <v>46098</v>
       </c>
       <c r="B116" t="n">
-        <v>95.58000183105469</v>
+        <v>95.30000305175781</v>
       </c>
       <c r="C116" t="n">
-        <v>96.09999847412109</v>
+        <v>96.33999633789062</v>
       </c>
       <c r="D116" t="n">
+        <v>94.01000213623047</v>
+      </c>
+      <c r="E116" t="n">
         <v>94.36000061035156</v>
       </c>
-      <c r="E116" t="n">
-        <v>95.19999694824219</v>
-      </c>
       <c r="F116" t="n">
-        <v>34931800</v>
+        <v>26434500</v>
       </c>
       <c r="G116" t="n">
         <v>0</v>
@@ -3459,22 +3459,22 @@
     </row>
     <row r="117">
       <c r="A117" s="1" t="n">
-        <v>46098</v>
+        <v>46099</v>
       </c>
       <c r="B117" t="n">
-        <v>95.30000305175781</v>
+        <v>94.44999694824219</v>
       </c>
       <c r="C117" t="n">
-        <v>96.33999633789062</v>
+        <v>95.33999633789062</v>
       </c>
       <c r="D117" t="n">
-        <v>94.01000213623047</v>
+        <v>93.61000061035156</v>
       </c>
       <c r="E117" t="n">
-        <v>94.36000061035156</v>
+        <v>94.69999694824219</v>
       </c>
       <c r="F117" t="n">
-        <v>26434500</v>
+        <v>27878300</v>
       </c>
       <c r="G117" t="n">
         <v>0</v>
@@ -3485,22 +3485,22 @@
     </row>
     <row r="118">
       <c r="A118" s="1" t="n">
-        <v>46099</v>
+        <v>46100</v>
       </c>
       <c r="B118" t="n">
-        <v>94.44999694824219</v>
+        <v>94.30999755859375</v>
       </c>
       <c r="C118" t="n">
-        <v>95.33999633789062</v>
+        <v>95.75</v>
       </c>
       <c r="D118" t="n">
-        <v>93.61000061035156</v>
+        <v>90.77999877929688</v>
       </c>
       <c r="E118" t="n">
-        <v>94.69999694824219</v>
+        <v>91.73999786376953</v>
       </c>
       <c r="F118" t="n">
-        <v>27878300</v>
+        <v>40169300</v>
       </c>
       <c r="G118" t="n">
         <v>0</v>
@@ -3511,22 +3511,22 @@
     </row>
     <row r="119">
       <c r="A119" s="1" t="n">
-        <v>46100</v>
+        <v>46101</v>
       </c>
       <c r="B119" t="n">
-        <v>94.30999755859375</v>
+        <v>91.30999755859375</v>
       </c>
       <c r="C119" t="n">
-        <v>95.75</v>
+        <v>91.87999725341797</v>
       </c>
       <c r="D119" t="n">
-        <v>90.77999877929688</v>
+        <v>90.69000244140625</v>
       </c>
       <c r="E119" t="n">
-        <v>91.73999786376953</v>
+        <v>91.81999969482422</v>
       </c>
       <c r="F119" t="n">
-        <v>40169300</v>
+        <v>61678000</v>
       </c>
       <c r="G119" t="n">
         <v>0</v>
@@ -3537,22 +3537,22 @@
     </row>
     <row r="120">
       <c r="A120" s="1" t="n">
-        <v>46101</v>
+        <v>46104</v>
       </c>
       <c r="B120" t="n">
-        <v>91.30999755859375</v>
+        <v>92.04000091552734</v>
       </c>
       <c r="C120" t="n">
-        <v>91.87999725341797</v>
+        <v>93.98000335693359</v>
       </c>
       <c r="D120" t="n">
-        <v>90.69000244140625</v>
+        <v>91.86000061035156</v>
       </c>
       <c r="E120" t="n">
-        <v>91.81999969482422</v>
+        <v>93.37999725341797</v>
       </c>
       <c r="F120" t="n">
-        <v>61678000</v>
+        <v>34315900</v>
       </c>
       <c r="G120" t="n">
         <v>0</v>
@@ -3563,22 +3563,22 @@
     </row>
     <row r="121">
       <c r="A121" s="1" t="n">
-        <v>46104</v>
+        <v>46105</v>
       </c>
       <c r="B121" t="n">
-        <v>92.04000091552734</v>
+        <v>92.79000091552734</v>
       </c>
       <c r="C121" t="n">
-        <v>93.98000335693359</v>
+        <v>93.73999786376953</v>
       </c>
       <c r="D121" t="n">
-        <v>91.86000061035156</v>
+        <v>90.81999969482422</v>
       </c>
       <c r="E121" t="n">
-        <v>93.37999725341797</v>
+        <v>90.91999816894531</v>
       </c>
       <c r="F121" t="n">
-        <v>34315900</v>
+        <v>28938000</v>
       </c>
       <c r="G121" t="n">
         <v>0</v>
@@ -3589,22 +3589,22 @@
     </row>
     <row r="122">
       <c r="A122" s="1" t="n">
-        <v>46105</v>
+        <v>46106</v>
       </c>
       <c r="B122" t="n">
-        <v>92.79000091552734</v>
+        <v>91.70999908447266</v>
       </c>
       <c r="C122" t="n">
-        <v>93.73999786376953</v>
+        <v>92.51999664306641</v>
       </c>
       <c r="D122" t="n">
-        <v>90.81999969482422</v>
+        <v>91.23999786376953</v>
       </c>
       <c r="E122" t="n">
-        <v>90.91999816894531</v>
+        <v>92.27999877929688</v>
       </c>
       <c r="F122" t="n">
-        <v>28938000</v>
+        <v>29545600</v>
       </c>
       <c r="G122" t="n">
         <v>0</v>
@@ -3615,22 +3615,22 @@
     </row>
     <row r="123">
       <c r="A123" s="1" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B123" t="n">
-        <v>91.70999908447266</v>
+        <v>91.51999664306641</v>
       </c>
       <c r="C123" t="n">
-        <v>92.51999664306641</v>
+        <v>95.86000061035156</v>
       </c>
       <c r="D123" t="n">
-        <v>91.23999786376953</v>
+        <v>91.01000213623047</v>
       </c>
       <c r="E123" t="n">
-        <v>92.27999877929688</v>
+        <v>93.31999969482422</v>
       </c>
       <c r="F123" t="n">
-        <v>29545600</v>
+        <v>59522000</v>
       </c>
       <c r="G123" t="n">
         <v>0</v>
@@ -3641,22 +3641,22 @@
     </row>
     <row r="124">
       <c r="A124" s="1" t="n">
-        <v>46107</v>
+        <v>46108</v>
       </c>
       <c r="B124" t="n">
-        <v>91.51999664306641</v>
+        <v>94.56999969482422</v>
       </c>
       <c r="C124" t="n">
-        <v>95.86000061035156</v>
+        <v>95.58000183105469</v>
       </c>
       <c r="D124" t="n">
-        <v>91.01000213623047</v>
+        <v>92.73999786376953</v>
       </c>
       <c r="E124" t="n">
-        <v>93.31999969482422</v>
+        <v>93.43000030517578</v>
       </c>
       <c r="F124" t="n">
-        <v>59522000</v>
+        <v>44590700</v>
       </c>
       <c r="G124" t="n">
         <v>0</v>
@@ -3667,22 +3667,22 @@
     </row>
     <row r="125">
       <c r="A125" s="1" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B125" t="n">
-        <v>94.56999969482422</v>
+        <v>92.75</v>
       </c>
       <c r="C125" t="n">
-        <v>95.58000183105469</v>
+        <v>94.48999786376953</v>
       </c>
       <c r="D125" t="n">
-        <v>92.73999786376953</v>
+        <v>92.22000122070312</v>
       </c>
       <c r="E125" t="n">
-        <v>93.43000030517578</v>
+        <v>92.97000122070312</v>
       </c>
       <c r="F125" t="n">
-        <v>44590700</v>
+        <v>32375100</v>
       </c>
       <c r="G125" t="n">
         <v>0</v>
@@ -3693,22 +3693,22 @@
     </row>
     <row r="126">
       <c r="A126" s="1" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B126" t="n">
-        <v>92.75</v>
+        <v>93.02999877929688</v>
       </c>
       <c r="C126" t="n">
-        <v>94.48999786376953</v>
+        <v>96.26000213623047</v>
       </c>
       <c r="D126" t="n">
-        <v>92.22000122070312</v>
+        <v>93.02999877929688</v>
       </c>
       <c r="E126" t="n">
-        <v>92.97000122070312</v>
+        <v>96.15000152587891</v>
       </c>
       <c r="F126" t="n">
-        <v>32375100</v>
+        <v>54270000</v>
       </c>
       <c r="G126" t="n">
         <v>0</v>
@@ -3719,22 +3719,22 @@
     </row>
     <row r="127">
       <c r="A127" s="1" t="n">
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="B127" t="n">
-        <v>93.02999877929688</v>
+        <v>96.47000122070312</v>
       </c>
       <c r="C127" t="n">
-        <v>96.26000213623047</v>
+        <v>97.19999694824219</v>
       </c>
       <c r="D127" t="n">
-        <v>93.02999877929688</v>
+        <v>94.26000213623047</v>
       </c>
       <c r="E127" t="n">
-        <v>96.15000152587891</v>
+        <v>95.55000305175781</v>
       </c>
       <c r="F127" t="n">
-        <v>54270000</v>
+        <v>30439300</v>
       </c>
       <c r="G127" t="n">
         <v>0</v>
@@ -3745,22 +3745,22 @@
     </row>
     <row r="128">
       <c r="A128" s="1" t="n">
-        <v>46113</v>
+        <v>46114</v>
       </c>
       <c r="B128" t="n">
-        <v>96.47000122070312</v>
+        <v>95.26999664306641</v>
       </c>
       <c r="C128" t="n">
-        <v>97.19999694824219</v>
+        <v>98.70999908447266</v>
       </c>
       <c r="D128" t="n">
-        <v>94.26000213623047</v>
+        <v>95.16999816894531</v>
       </c>
       <c r="E128" t="n">
-        <v>95.55000305175781</v>
+        <v>98.66000366210938</v>
       </c>
       <c r="F128" t="n">
-        <v>30439300</v>
+        <v>37068000</v>
       </c>
       <c r="G128" t="n">
         <v>0</v>
@@ -3771,22 +3771,22 @@
     </row>
     <row r="129">
       <c r="A129" s="1" t="n">
-        <v>46114</v>
+        <v>46118</v>
       </c>
       <c r="B129" t="n">
-        <v>95.26999664306641</v>
+        <v>100.9599990844727</v>
       </c>
       <c r="C129" t="n">
-        <v>98.70999908447266</v>
+        <v>102.6900024414062</v>
       </c>
       <c r="D129" t="n">
-        <v>95.16999816894531</v>
+        <v>97.97000122070312</v>
       </c>
       <c r="E129" t="n">
-        <v>98.66000366210938</v>
+        <v>98.93000030517578</v>
       </c>
       <c r="F129" t="n">
-        <v>37068000</v>
+        <v>37029300</v>
       </c>
       <c r="G129" t="n">
         <v>0</v>
@@ -3797,22 +3797,22 @@
     </row>
     <row r="130">
       <c r="A130" s="1" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B130" t="n">
-        <v>100.9599990844727</v>
+        <v>98.55000305175781</v>
       </c>
       <c r="C130" t="n">
-        <v>102.6900024414062</v>
+        <v>99.87999725341797</v>
       </c>
       <c r="D130" t="n">
-        <v>97.97000122070312</v>
+        <v>98.25</v>
       </c>
       <c r="E130" t="n">
-        <v>98.93000030517578</v>
+        <v>98.81999969482422</v>
       </c>
       <c r="F130" t="n">
-        <v>37029300</v>
+        <v>25016700</v>
       </c>
       <c r="G130" t="n">
         <v>0</v>
@@ -3823,22 +3823,22 @@
     </row>
     <row r="131">
       <c r="A131" s="1" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B131" t="n">
-        <v>98.55000305175781</v>
+        <v>100.3199996948242</v>
       </c>
       <c r="C131" t="n">
-        <v>99.87999725341797</v>
+        <v>100.4000015258789</v>
       </c>
       <c r="D131" t="n">
-        <v>98.25</v>
+        <v>97.44000244140625</v>
       </c>
       <c r="E131" t="n">
-        <v>98.81999969482422</v>
+        <v>99.38999938964844</v>
       </c>
       <c r="F131" t="n">
-        <v>25016700</v>
+        <v>30957600</v>
       </c>
       <c r="G131" t="n">
         <v>0</v>
@@ -3849,22 +3849,22 @@
     </row>
     <row r="132">
       <c r="A132" s="1" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B132" t="n">
-        <v>100.3199996948242</v>
+        <v>99.62999725341797</v>
       </c>
       <c r="C132" t="n">
-        <v>100.4000015258789</v>
+        <v>102.3399963378906</v>
       </c>
       <c r="D132" t="n">
-        <v>97.44000244140625</v>
+        <v>99.08000183105469</v>
       </c>
       <c r="E132" t="n">
-        <v>99.38999938964844</v>
+        <v>102.0500030517578</v>
       </c>
       <c r="F132" t="n">
-        <v>30957600</v>
+        <v>35087800</v>
       </c>
       <c r="G132" t="n">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="133">
       <c r="A133" s="1" t="n">
-        <v>46121</v>
+        <v>46122</v>
       </c>
       <c r="B133" t="n">
-        <v>99.62999725341797</v>
+        <v>102.4700012207031</v>
       </c>
       <c r="C133" t="n">
-        <v>102.3399963378906</v>
+        <v>103.0800018310547</v>
       </c>
       <c r="D133" t="n">
-        <v>99.08000183105469</v>
+        <v>101.4599990844727</v>
       </c>
       <c r="E133" t="n">
-        <v>102.0500030517578</v>
+        <v>103.0100021362305</v>
       </c>
       <c r="F133" t="n">
-        <v>35087800</v>
+        <v>25769900</v>
       </c>
       <c r="G133" t="n">
         <v>0</v>
@@ -3901,22 +3901,22 @@
     </row>
     <row r="134">
       <c r="A134" s="1" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B134" t="n">
-        <v>102.4700012207031</v>
+        <v>103.0299987792969</v>
       </c>
       <c r="C134" t="n">
-        <v>103.0800018310547</v>
+        <v>103.6699981689453</v>
       </c>
       <c r="D134" t="n">
-        <v>101.4599990844727</v>
+        <v>102.0599975585938</v>
       </c>
       <c r="E134" t="n">
-        <v>103.0100021362305</v>
+        <v>103.1600036621094</v>
       </c>
       <c r="F134" t="n">
-        <v>25769900</v>
+        <v>26042800</v>
       </c>
       <c r="G134" t="n">
         <v>0</v>
@@ -3927,22 +3927,22 @@
     </row>
     <row r="135">
       <c r="A135" s="1" t="n">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="B135" t="n">
-        <v>103.0299987792969</v>
+        <v>103.120002746582</v>
       </c>
       <c r="C135" t="n">
-        <v>103.6699981689453</v>
+        <v>106.5699996948242</v>
       </c>
       <c r="D135" t="n">
-        <v>102.0599975585938</v>
+        <v>103.0400009155273</v>
       </c>
       <c r="E135" t="n">
-        <v>103.1600036621094</v>
+        <v>106.2799987792969</v>
       </c>
       <c r="F135" t="n">
-        <v>26042800</v>
+        <v>40534900</v>
       </c>
       <c r="G135" t="n">
         <v>0</v>
@@ -3953,22 +3953,22 @@
     </row>
     <row r="136">
       <c r="A136" s="1" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B136" t="n">
-        <v>103.120002746582</v>
+        <v>105.9800033569336</v>
       </c>
       <c r="C136" t="n">
-        <v>106.5699996948242</v>
+        <v>107.8499984741211</v>
       </c>
       <c r="D136" t="n">
-        <v>103.0400009155273</v>
+        <v>105.0400009155273</v>
       </c>
       <c r="E136" t="n">
-        <v>106.2799987792969</v>
+        <v>107.7099990844727</v>
       </c>
       <c r="F136" t="n">
-        <v>40534900</v>
+        <v>38023700</v>
       </c>
       <c r="G136" t="n">
         <v>0</v>
@@ -3979,22 +3979,22 @@
     </row>
     <row r="137">
       <c r="A137" s="1" t="n">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c r="B137" t="n">
-        <v>105.9800033569336</v>
+        <v>107.4700012207031</v>
       </c>
       <c r="C137" t="n">
-        <v>107.8499984741211</v>
+        <v>108.9499969482422</v>
       </c>
       <c r="D137" t="n">
-        <v>105.0400009155273</v>
+        <v>106.620002746582</v>
       </c>
       <c r="E137" t="n">
-        <v>107.7099990844727</v>
+        <v>107.7900009155273</v>
       </c>
       <c r="F137" t="n">
-        <v>38023700</v>
+        <v>64928300</v>
       </c>
       <c r="G137" t="n">
         <v>0</v>
@@ -4005,22 +4005,22 @@
     </row>
     <row r="138">
       <c r="A138" s="1" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B138" t="n">
-        <v>107.4700012207031</v>
+        <v>96.37000274658203</v>
       </c>
       <c r="C138" t="n">
-        <v>108.9499969482422</v>
+        <v>98.73999786376953</v>
       </c>
       <c r="D138" t="n">
-        <v>106.620002746582</v>
+        <v>95.09999847412109</v>
       </c>
       <c r="E138" t="n">
-        <v>107.7900009155273</v>
+        <v>97.30999755859375</v>
       </c>
       <c r="F138" t="n">
-        <v>64928300</v>
+        <v>125958700</v>
       </c>
       <c r="G138" t="n">
         <v>0</v>
@@ -4031,22 +4031,22 @@
     </row>
     <row r="139">
       <c r="A139" s="1" t="n">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c r="B139" t="n">
-        <v>96.37000274658203</v>
+        <v>97.13999938964844</v>
       </c>
       <c r="C139" t="n">
-        <v>98.73999786376953</v>
+        <v>97.59999847412109</v>
       </c>
       <c r="D139" t="n">
-        <v>95.09999847412109</v>
+        <v>93.54000091552734</v>
       </c>
       <c r="E139" t="n">
-        <v>97.30999755859375</v>
+        <v>94.83000183105469</v>
       </c>
       <c r="F139" t="n">
-        <v>125958700</v>
+        <v>63298300</v>
       </c>
       <c r="G139" t="n">
         <v>0</v>
@@ -4057,22 +4057,22 @@
     </row>
     <row r="140">
       <c r="A140" s="1" t="n">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="B140" t="n">
-        <v>97.13999938964844</v>
+        <v>94</v>
       </c>
       <c r="C140" t="n">
-        <v>97.59999847412109</v>
+        <v>94.65000152587891</v>
       </c>
       <c r="D140" t="n">
-        <v>93.54000091552734</v>
+        <v>92.37000274658203</v>
       </c>
       <c r="E140" t="n">
-        <v>94.83000183105469</v>
+        <v>92.58000183105469</v>
       </c>
       <c r="F140" t="n">
-        <v>63298300</v>
+        <v>61962300</v>
       </c>
       <c r="G140" t="n">
         <v>0</v>
@@ -4083,22 +4083,22 @@
     </row>
     <row r="141">
       <c r="A141" s="1" t="n">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="B141" t="n">
-        <v>94</v>
+        <v>93.05999755859375</v>
       </c>
       <c r="C141" t="n">
-        <v>94.65000152587891</v>
+        <v>93.84999847412109</v>
       </c>
       <c r="D141" t="n">
-        <v>92.37000274658203</v>
+        <v>92.76999664306641</v>
       </c>
       <c r="E141" t="n">
-        <v>92.58000183105469</v>
+        <v>93.23999786376953</v>
       </c>
       <c r="F141" t="n">
-        <v>61962300</v>
+        <v>33694300</v>
       </c>
       <c r="G141" t="n">
         <v>0</v>
@@ -4109,22 +4109,22 @@
     </row>
     <row r="142">
       <c r="A142" s="1" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B142" t="n">
-        <v>93.05999755859375</v>
+        <v>94.05999755859375</v>
       </c>
       <c r="C142" t="n">
-        <v>93.84999847412109</v>
+        <v>94.63999938964844</v>
       </c>
       <c r="D142" t="n">
-        <v>92.76999664306641</v>
+        <v>92.06999969482422</v>
       </c>
       <c r="E142" t="n">
-        <v>93.23999786376953</v>
+        <v>92.81999969482422</v>
       </c>
       <c r="F142" t="n">
-        <v>33694300</v>
+        <v>36851700</v>
       </c>
       <c r="G142" t="n">
         <v>0</v>
@@ -4135,22 +4135,22 @@
     </row>
     <row r="143">
       <c r="A143" s="1" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B143" t="n">
-        <v>94.05999755859375</v>
+        <v>92.56999969482422</v>
       </c>
       <c r="C143" t="n">
-        <v>94.63999938964844</v>
+        <v>93.27999877929688</v>
       </c>
       <c r="D143" t="n">
-        <v>92.06999969482422</v>
+        <v>91.80000305175781</v>
       </c>
       <c r="E143" t="n">
-        <v>92.81999969482422</v>
+        <v>92.44000244140625</v>
       </c>
       <c r="F143" t="n">
-        <v>36851700</v>
+        <v>32553200</v>
       </c>
       <c r="G143" t="n">
         <v>0</v>
@@ -4161,22 +4161,22 @@
     </row>
     <row r="144">
       <c r="A144" s="1" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B144" t="n">
-        <v>92.56999969482422</v>
+        <v>92.05000305175781</v>
       </c>
       <c r="C144" t="n">
-        <v>93.27999877929688</v>
+        <v>92.83999633789062</v>
       </c>
       <c r="D144" t="n">
-        <v>91.80000305175781</v>
+        <v>91.30000305175781</v>
       </c>
       <c r="E144" t="n">
-        <v>92.44000244140625</v>
+        <v>91.37000274658203</v>
       </c>
       <c r="F144" t="n">
-        <v>32553200</v>
+        <v>29707400</v>
       </c>
       <c r="G144" t="n">
         <v>0</v>
@@ -4187,22 +4187,22 @@
     </row>
     <row r="145">
       <c r="A145" s="1" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B145" t="n">
-        <v>92.05000305175781</v>
+        <v>91.5</v>
       </c>
       <c r="C145" t="n">
-        <v>92.83999633789062</v>
+        <v>92.33999633789062</v>
       </c>
       <c r="D145" t="n">
-        <v>91.30000305175781</v>
+        <v>90.01999664306641</v>
       </c>
       <c r="E145" t="n">
-        <v>91.37000274658203</v>
+        <v>92.26999664306641</v>
       </c>
       <c r="F145" t="n">
-        <v>29707400</v>
+        <v>33418100</v>
       </c>
       <c r="G145" t="n">
         <v>0</v>
@@ -4213,22 +4213,22 @@
     </row>
     <row r="146">
       <c r="A146" s="1" t="n">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="B146" t="n">
-        <v>91.5</v>
+        <v>91.23000335693359</v>
       </c>
       <c r="C146" t="n">
-        <v>92.33999633789062</v>
+        <v>92.86000061035156</v>
       </c>
       <c r="D146" t="n">
-        <v>90.01999664306641</v>
+        <v>90.86000061035156</v>
       </c>
       <c r="E146" t="n">
-        <v>92.26999664306641</v>
+        <v>92.12000274658203</v>
       </c>
       <c r="F146" t="n">
-        <v>33418100</v>
+        <v>26122100</v>
       </c>
       <c r="G146" t="n">
         <v>0</v>
@@ -4239,22 +4239,22 @@
     </row>
     <row r="147">
       <c r="A147" s="1" t="n">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="B147" t="n">
-        <v>91.23000335693359</v>
+        <v>91.34999847412109</v>
       </c>
       <c r="C147" t="n">
-        <v>92.86000061035156</v>
+        <v>94.22000122070312</v>
       </c>
       <c r="D147" t="n">
-        <v>90.86000061035156</v>
+        <v>90.76999664306641</v>
       </c>
       <c r="E147" t="n">
-        <v>92.12000274658203</v>
+        <v>93.61000061035156</v>
       </c>
       <c r="F147" t="n">
-        <v>26122100</v>
+        <v>40923000</v>
       </c>
       <c r="G147" t="n">
         <v>0</v>
@@ -4265,22 +4265,22 @@
     </row>
     <row r="148">
       <c r="A148" s="1" t="n">
-        <v>46142</v>
+        <v>46143</v>
       </c>
       <c r="B148" t="n">
-        <v>91.34999847412109</v>
+        <v>94.41999816894531</v>
       </c>
       <c r="C148" t="n">
-        <v>94.22000122070312</v>
+        <v>94.69999694824219</v>
       </c>
       <c r="D148" t="n">
-        <v>90.76999664306641</v>
+        <v>91.90000152587891</v>
       </c>
       <c r="E148" t="n">
-        <v>93.61000061035156</v>
+        <v>92.05999755859375</v>
       </c>
       <c r="F148" t="n">
-        <v>40923000</v>
+        <v>30406900</v>
       </c>
       <c r="G148" t="n">
         <v>0</v>
@@ -4291,22 +4291,22 @@
     </row>
     <row r="149">
       <c r="A149" s="1" t="n">
-        <v>46143</v>
+        <v>46146</v>
       </c>
       <c r="B149" t="n">
-        <v>94.41999816894531</v>
+        <v>92.09999847412109</v>
       </c>
       <c r="C149" t="n">
-        <v>94.69999694824219</v>
+        <v>92.33000183105469</v>
       </c>
       <c r="D149" t="n">
-        <v>91.90000152587891</v>
+        <v>90.88999938964844</v>
       </c>
       <c r="E149" t="n">
-        <v>92.05999755859375</v>
+        <v>91.01999664306641</v>
       </c>
       <c r="F149" t="n">
-        <v>30406900</v>
+        <v>25928800</v>
       </c>
       <c r="G149" t="n">
         <v>0</v>
@@ -4317,22 +4317,22 @@
     </row>
     <row r="150">
       <c r="A150" s="1" t="n">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="B150" t="n">
-        <v>92.09999847412109</v>
+        <v>91.18000030517578</v>
       </c>
       <c r="C150" t="n">
-        <v>92.33000183105469</v>
+        <v>91.27999877929688</v>
       </c>
       <c r="D150" t="n">
-        <v>90.88999938964844</v>
+        <v>87.56999969482422</v>
       </c>
       <c r="E150" t="n">
-        <v>91.01999664306641</v>
+        <v>87.88999938964844</v>
       </c>
       <c r="F150" t="n">
-        <v>25928800</v>
+        <v>51961300</v>
       </c>
       <c r="G150" t="n">
         <v>0</v>
@@ -4343,22 +4343,22 @@
     </row>
     <row r="151">
       <c r="A151" s="1" t="n">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="B151" t="n">
-        <v>91.18000030517578</v>
+        <v>87.15000152587891</v>
       </c>
       <c r="C151" t="n">
-        <v>91.27999877929688</v>
+        <v>88.55000305175781</v>
       </c>
       <c r="D151" t="n">
-        <v>87.56999969482422</v>
+        <v>86.72000122070312</v>
       </c>
       <c r="E151" t="n">
-        <v>87.88999938964844</v>
+        <v>88.26999664306641</v>
       </c>
       <c r="F151" t="n">
-        <v>51961300</v>
+        <v>41932400</v>
       </c>
       <c r="G151" t="n">
         <v>0</v>
@@ -4369,22 +4369,22 @@
     </row>
     <row r="152">
       <c r="A152" s="1" t="n">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="B152" t="n">
-        <v>87.15000152587891</v>
+        <v>88.19999694824219</v>
       </c>
       <c r="C152" t="n">
-        <v>88.55000305175781</v>
+        <v>89.40000152587891</v>
       </c>
       <c r="D152" t="n">
-        <v>86.72000122070312</v>
+        <v>88.12999725341797</v>
       </c>
       <c r="E152" t="n">
-        <v>88.26999664306641</v>
+        <v>88.25</v>
       </c>
       <c r="F152" t="n">
-        <v>41932400</v>
+        <v>30627600</v>
       </c>
       <c r="G152" t="n">
         <v>0</v>
@@ -4395,22 +4395,22 @@
     </row>
     <row r="153">
       <c r="A153" s="1" t="n">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="B153" t="n">
-        <v>88.19999694824219</v>
+        <v>87.70999908447266</v>
       </c>
       <c r="C153" t="n">
-        <v>89.40000152587891</v>
+        <v>88.04000091552734</v>
       </c>
       <c r="D153" t="n">
-        <v>88.12999725341797</v>
+        <v>87.20999908447266</v>
       </c>
       <c r="E153" t="n">
-        <v>88.25</v>
+        <v>87.48999786376953</v>
       </c>
       <c r="F153" t="n">
-        <v>30627600</v>
+        <v>36215100</v>
       </c>
       <c r="G153" t="n">
         <v>0</v>
@@ -4421,22 +4421,22 @@
     </row>
     <row r="154">
       <c r="A154" s="1" t="n">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="B154" t="n">
-        <v>87.70999908447266</v>
+        <v>86.52999877929688</v>
       </c>
       <c r="C154" t="n">
-        <v>88.04000091552734</v>
+        <v>87.33999633789062</v>
       </c>
       <c r="D154" t="n">
-        <v>87.20999908447266</v>
+        <v>85.09999847412109</v>
       </c>
       <c r="E154" t="n">
-        <v>87.48999786376953</v>
+        <v>85.44999694824219</v>
       </c>
       <c r="F154" t="n">
-        <v>36215100</v>
+        <v>40556500</v>
       </c>
       <c r="G154" t="n">
         <v>0</v>
@@ -4447,22 +4447,22 @@
     </row>
     <row r="155">
       <c r="A155" s="1" t="n">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="B155" t="n">
-        <v>86.52999877929688</v>
+        <v>85.91000366210938</v>
       </c>
       <c r="C155" t="n">
-        <v>87.33999633789062</v>
+        <v>89.16999816894531</v>
       </c>
       <c r="D155" t="n">
-        <v>85.09999847412109</v>
+        <v>85.80999755859375</v>
       </c>
       <c r="E155" t="n">
-        <v>85.44999694824219</v>
+        <v>87.66000366210938</v>
       </c>
       <c r="F155" t="n">
-        <v>40556500</v>
+        <v>43556600</v>
       </c>
       <c r="G155" t="n">
         <v>0</v>
@@ -4473,22 +4473,22 @@
     </row>
     <row r="156">
       <c r="A156" s="1" t="n">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="B156" t="n">
-        <v>85.91000366210938</v>
+        <v>86.56999969482422</v>
       </c>
       <c r="C156" t="n">
-        <v>89.16999816894531</v>
+        <v>88.62000274658203</v>
       </c>
       <c r="D156" t="n">
-        <v>85.80999755859375</v>
+        <v>86.27999877929688</v>
       </c>
       <c r="E156" t="n">
-        <v>87.66000366210938</v>
+        <v>87.55999755859375</v>
       </c>
       <c r="F156" t="n">
-        <v>43556600</v>
+        <v>30823500</v>
       </c>
       <c r="G156" t="n">
         <v>0</v>
@@ -4499,22 +4499,22 @@
     </row>
     <row r="157">
       <c r="A157" s="1" t="n">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="B157" t="n">
-        <v>86.56999969482422</v>
+        <v>87.62000274658203</v>
       </c>
       <c r="C157" t="n">
-        <v>88.62000274658203</v>
+        <v>88.5</v>
       </c>
       <c r="D157" t="n">
-        <v>86.27999877929688</v>
+        <v>86.65000152587891</v>
       </c>
       <c r="E157" t="n">
-        <v>87.55999755859375</v>
+        <v>86.94000244140625</v>
       </c>
       <c r="F157" t="n">
-        <v>30823500</v>
+        <v>29408300</v>
       </c>
       <c r="G157" t="n">
         <v>0</v>
@@ -4525,22 +4525,22 @@
     </row>
     <row r="158">
       <c r="A158" s="1" t="n">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="B158" t="n">
-        <v>87.62000274658203</v>
+        <v>87.69000244140625</v>
       </c>
       <c r="C158" t="n">
-        <v>88.5</v>
+        <v>89.48999786376953</v>
       </c>
       <c r="D158" t="n">
-        <v>86.65000152587891</v>
+        <v>86.69000244140625</v>
       </c>
       <c r="E158" t="n">
-        <v>86.94000244140625</v>
+        <v>87.01999664306641</v>
       </c>
       <c r="F158" t="n">
-        <v>29408300</v>
+        <v>32335700</v>
       </c>
       <c r="G158" t="n">
         <v>0</v>
@@ -4551,22 +4551,22 @@
     </row>
     <row r="159">
       <c r="A159" s="1" t="n">
-        <v>46157</v>
+        <v>46160</v>
       </c>
       <c r="B159" t="n">
-        <v>87.69000244140625</v>
+        <v>86.5</v>
       </c>
       <c r="C159" t="n">
-        <v>89.48999786376953</v>
+        <v>89.81999969482422</v>
       </c>
       <c r="D159" t="n">
-        <v>86.69000244140625</v>
+        <v>86.33000183105469</v>
       </c>
       <c r="E159" t="n">
-        <v>87.01999664306641</v>
+        <v>89.65000152587891</v>
       </c>
       <c r="F159" t="n">
-        <v>32335700</v>
+        <v>35800500</v>
       </c>
       <c r="G159" t="n">
         <v>0</v>
@@ -4577,22 +4577,22 @@
     </row>
     <row r="160">
       <c r="A160" s="1" t="n">
-        <v>46160</v>
+        <v>46161</v>
       </c>
       <c r="B160" t="n">
-        <v>86.5</v>
+        <v>90.13999938964844</v>
       </c>
       <c r="C160" t="n">
-        <v>89.81999969482422</v>
+        <v>91.48000335693359</v>
       </c>
       <c r="D160" t="n">
-        <v>86.33000183105469</v>
+        <v>88.69000244140625</v>
       </c>
       <c r="E160" t="n">
-        <v>89.65000152587891</v>
+        <v>89.33000183105469</v>
       </c>
       <c r="F160" t="n">
-        <v>35800500</v>
+        <v>34545700</v>
       </c>
       <c r="G160" t="n">
         <v>0</v>
@@ -4603,22 +4603,22 @@
     </row>
     <row r="161">
       <c r="A161" s="1" t="n">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="B161" t="n">
-        <v>90.13999938964844</v>
+        <v>88.51999664306641</v>
       </c>
       <c r="C161" t="n">
-        <v>91.48000335693359</v>
+        <v>88.55000305175781</v>
       </c>
       <c r="D161" t="n">
-        <v>88.69000244140625</v>
+        <v>87.5</v>
       </c>
       <c r="E161" t="n">
-        <v>89.33000183105469</v>
+        <v>88.08999633789062</v>
       </c>
       <c r="F161" t="n">
-        <v>34545700</v>
+        <v>23463400</v>
       </c>
       <c r="G161" t="n">
         <v>0</v>
@@ -4629,22 +4629,22 @@
     </row>
     <row r="162">
       <c r="A162" s="1" t="n">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="B162" t="n">
-        <v>88.51999664306641</v>
+        <v>88.02999877929688</v>
       </c>
       <c r="C162" t="n">
-        <v>88.55000305175781</v>
+        <v>90.37000274658203</v>
       </c>
       <c r="D162" t="n">
-        <v>87.5</v>
+        <v>87.51999664306641</v>
       </c>
       <c r="E162" t="n">
-        <v>88.08999633789062</v>
+        <v>89.30000305175781</v>
       </c>
       <c r="F162" t="n">
-        <v>23463400</v>
+        <v>28613900</v>
       </c>
       <c r="G162" t="n">
         <v>0</v>
@@ -4655,22 +4655,22 @@
     </row>
     <row r="163">
       <c r="A163" s="1" t="n">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="B163" t="n">
-        <v>88.02999877929688</v>
+        <v>89.09999847412109</v>
       </c>
       <c r="C163" t="n">
-        <v>90.37000274658203</v>
+        <v>89.97000122070312</v>
       </c>
       <c r="D163" t="n">
-        <v>87.51999664306641</v>
+        <v>88.16999816894531</v>
       </c>
       <c r="E163" t="n">
-        <v>89.30000305175781</v>
+        <v>88.59999847412109</v>
       </c>
       <c r="F163" t="n">
-        <v>28613900</v>
+        <v>23847200</v>
       </c>
       <c r="G163" t="n">
         <v>0</v>
@@ -4681,22 +4681,22 @@
     </row>
     <row r="164">
       <c r="A164" s="1" t="n">
-        <v>46164</v>
+        <v>46168</v>
       </c>
       <c r="B164" t="n">
-        <v>89.09999847412109</v>
+        <v>88.40000152587891</v>
       </c>
       <c r="C164" t="n">
-        <v>89.97000122070312</v>
+        <v>88.73000335693359</v>
       </c>
       <c r="D164" t="n">
-        <v>88.16999816894531</v>
+        <v>87.25</v>
       </c>
       <c r="E164" t="n">
-        <v>88.59999847412109</v>
+        <v>87.68000030517578</v>
       </c>
       <c r="F164" t="n">
-        <v>23847200</v>
+        <v>24014500</v>
       </c>
       <c r="G164" t="n">
         <v>0</v>
@@ -4707,22 +4707,22 @@
     </row>
     <row r="165">
       <c r="A165" s="1" t="n">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="B165" t="n">
-        <v>88.40000152587891</v>
+        <v>87.05000305175781</v>
       </c>
       <c r="C165" t="n">
-        <v>88.73000335693359</v>
+        <v>88.5</v>
       </c>
       <c r="D165" t="n">
-        <v>87.25</v>
+        <v>86.81999969482422</v>
       </c>
       <c r="E165" t="n">
-        <v>87.68000030517578</v>
+        <v>87.34999847412109</v>
       </c>
       <c r="F165" t="n">
-        <v>24014500</v>
+        <v>22569500</v>
       </c>
       <c r="G165" t="n">
         <v>0</v>
@@ -4733,22 +4733,22 @@
     </row>
     <row r="166">
       <c r="A166" s="1" t="n">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="B166" t="n">
-        <v>87.05000305175781</v>
+        <v>86.90000152587891</v>
       </c>
       <c r="C166" t="n">
-        <v>88.5</v>
+        <v>87.04000091552734</v>
       </c>
       <c r="D166" t="n">
-        <v>86.81999969482422</v>
+        <v>85.58999633789062</v>
       </c>
       <c r="E166" t="n">
-        <v>87.34999847412109</v>
+        <v>86.36000061035156</v>
       </c>
       <c r="F166" t="n">
-        <v>22569500</v>
+        <v>38803800</v>
       </c>
       <c r="G166" t="n">
         <v>0</v>
@@ -4759,22 +4759,22 @@
     </row>
     <row r="167">
       <c r="A167" s="1" t="n">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="B167" t="n">
-        <v>86.90000152587891</v>
+        <v>86.19999694824219</v>
       </c>
       <c r="C167" t="n">
-        <v>87.04000091552734</v>
+        <v>86.66999816894531</v>
       </c>
       <c r="D167" t="n">
-        <v>85.58999633789062</v>
+        <v>85.66000366210938</v>
       </c>
       <c r="E167" t="n">
-        <v>86.36000061035156</v>
+        <v>86.01999664306641</v>
       </c>
       <c r="F167" t="n">
-        <v>38803800</v>
+        <v>39793600</v>
       </c>
       <c r="G167" t="n">
         <v>0</v>
@@ -4785,22 +4785,22 @@
     </row>
     <row r="168">
       <c r="A168" s="1" t="n">
-        <v>46171</v>
+        <v>46174</v>
       </c>
       <c r="B168" t="n">
-        <v>86.19999694824219</v>
+        <v>85.73000335693359</v>
       </c>
       <c r="C168" t="n">
-        <v>86.66999816894531</v>
+        <v>87.23000335693359</v>
       </c>
       <c r="D168" t="n">
-        <v>85.66000366210938</v>
+        <v>85.31999969482422</v>
       </c>
       <c r="E168" t="n">
-        <v>86.01999664306641</v>
+        <v>85.84999847412109</v>
       </c>
       <c r="F168" t="n">
-        <v>39793600</v>
+        <v>32747200</v>
       </c>
       <c r="G168" t="n">
         <v>0</v>
@@ -4811,22 +4811,22 @@
     </row>
     <row r="169">
       <c r="A169" s="1" t="n">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="B169" t="n">
-        <v>85.73000335693359</v>
+        <v>85.61000061035156</v>
       </c>
       <c r="C169" t="n">
-        <v>87.23000335693359</v>
+        <v>85.98000335693359</v>
       </c>
       <c r="D169" t="n">
-        <v>85.31999969482422</v>
+        <v>83.29000091552734</v>
       </c>
       <c r="E169" t="n">
-        <v>85.84999847412109</v>
+        <v>83.33000183105469</v>
       </c>
       <c r="F169" t="n">
-        <v>32747200</v>
+        <v>42947200</v>
       </c>
       <c r="G169" t="n">
         <v>0</v>
@@ -4837,22 +4837,22 @@
     </row>
     <row r="170">
       <c r="A170" s="1" t="n">
-        <v>46175</v>
+        <v>46176</v>
       </c>
       <c r="B170" t="n">
-        <v>85.61000061035156</v>
+        <v>82.91000366210938</v>
       </c>
       <c r="C170" t="n">
-        <v>85.98000335693359</v>
+        <v>83.30999755859375</v>
       </c>
       <c r="D170" t="n">
-        <v>83.29000091552734</v>
+        <v>81.09999847412109</v>
       </c>
       <c r="E170" t="n">
-        <v>83.33000183105469</v>
+        <v>81.51999664306641</v>
       </c>
       <c r="F170" t="n">
-        <v>42947200</v>
+        <v>36714700</v>
       </c>
       <c r="G170" t="n">
         <v>0</v>
@@ -4863,22 +4863,22 @@
     </row>
     <row r="171">
       <c r="A171" s="1" t="n">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="B171" t="n">
-        <v>82.91000366210938</v>
+        <v>83.19000244140625</v>
       </c>
       <c r="C171" t="n">
-        <v>83.30999755859375</v>
+        <v>83.69999694824219</v>
       </c>
       <c r="D171" t="n">
-        <v>81.09999847412109</v>
+        <v>81.37000274658203</v>
       </c>
       <c r="E171" t="n">
-        <v>81.51999664306641</v>
+        <v>81.55999755859375</v>
       </c>
       <c r="F171" t="n">
-        <v>36714700</v>
+        <v>39338800</v>
       </c>
       <c r="G171" t="n">
         <v>0</v>
@@ -4889,22 +4889,22 @@
     </row>
     <row r="172">
       <c r="A172" s="1" t="n">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="B172" t="n">
-        <v>83.19000244140625</v>
+        <v>82.33000183105469</v>
       </c>
       <c r="C172" t="n">
-        <v>83.69999694824219</v>
+        <v>82.75</v>
       </c>
       <c r="D172" t="n">
-        <v>81.37000274658203</v>
+        <v>81</v>
       </c>
       <c r="E172" t="n">
-        <v>81.55999755859375</v>
+        <v>82.18000030517578</v>
       </c>
       <c r="F172" t="n">
-        <v>39338800</v>
+        <v>43474100</v>
       </c>
       <c r="G172" t="n">
         <v>0</v>
@@ -4915,22 +4915,22 @@
     </row>
     <row r="173">
       <c r="A173" s="1" t="n">
-        <v>46178</v>
+        <v>46181</v>
       </c>
       <c r="B173" t="n">
-        <v>82.33000183105469</v>
+        <v>81.66000366210938</v>
       </c>
       <c r="C173" t="n">
-        <v>82.75</v>
+        <v>83.08000183105469</v>
       </c>
       <c r="D173" t="n">
-        <v>81</v>
+        <v>81.33999633789062</v>
       </c>
       <c r="E173" t="n">
-        <v>82.18000030517578</v>
+        <v>82.63999938964844</v>
       </c>
       <c r="F173" t="n">
-        <v>43474100</v>
+        <v>33056700</v>
       </c>
       <c r="G173" t="n">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="174">
       <c r="A174" s="1" t="n">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="B174" t="n">
-        <v>81.66000366210938</v>
+        <v>82.12999725341797</v>
       </c>
       <c r="C174" t="n">
-        <v>83.08000183105469</v>
+        <v>82.33999633789062</v>
       </c>
       <c r="D174" t="n">
         <v>81.33999633789062</v>
       </c>
       <c r="E174" t="n">
-        <v>82.63999938964844</v>
+        <v>81.41000366210938</v>
       </c>
       <c r="F174" t="n">
-        <v>33056700</v>
+        <v>34787200</v>
       </c>
       <c r="G174" t="n">
         <v>0</v>
@@ -4967,22 +4967,22 @@
     </row>
     <row r="175">
       <c r="A175" s="1" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="B175" t="n">
-        <v>82.12999725341797</v>
+        <v>81.70999908447266</v>
       </c>
       <c r="C175" t="n">
-        <v>82.33999633789062</v>
+        <v>82.75</v>
       </c>
       <c r="D175" t="n">
-        <v>81.33999633789062</v>
+        <v>80.98000335693359</v>
       </c>
       <c r="E175" t="n">
-        <v>81.41000366210938</v>
+        <v>82</v>
       </c>
       <c r="F175" t="n">
-        <v>34787200</v>
+        <v>36304600</v>
       </c>
       <c r="G175" t="n">
         <v>0</v>
@@ -4993,22 +4993,22 @@
     </row>
     <row r="176">
       <c r="A176" s="1" t="n">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="B176" t="n">
-        <v>81.70999908447266</v>
+        <v>81.87000274658203</v>
       </c>
       <c r="C176" t="n">
-        <v>82.75</v>
+        <v>82.09999847412109</v>
       </c>
       <c r="D176" t="n">
-        <v>80.98000335693359</v>
+        <v>80.08999633789062</v>
       </c>
       <c r="E176" t="n">
-        <v>82</v>
+        <v>81.26999664306641</v>
       </c>
       <c r="F176" t="n">
-        <v>36304600</v>
+        <v>33417600</v>
       </c>
       <c r="G176" t="n">
         <v>0</v>
@@ -5019,22 +5019,22 @@
     </row>
     <row r="177">
       <c r="A177" s="1" t="n">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="B177" t="n">
-        <v>81.87000274658203</v>
+        <v>81.58000183105469</v>
       </c>
       <c r="C177" t="n">
-        <v>82.09999847412109</v>
+        <v>82</v>
       </c>
       <c r="D177" t="n">
-        <v>80.08999633789062</v>
+        <v>79.27999877929688</v>
       </c>
       <c r="E177" t="n">
-        <v>81.26999664306641</v>
+        <v>80.33999633789062</v>
       </c>
       <c r="F177" t="n">
-        <v>33417600</v>
+        <v>35309700</v>
       </c>
       <c r="G177" t="n">
         <v>0</v>
@@ -5045,22 +5045,22 @@
     </row>
     <row r="178">
       <c r="A178" s="1" t="n">
-        <v>46185</v>
+        <v>46188</v>
       </c>
       <c r="B178" t="n">
-        <v>81.58000183105469</v>
+        <v>80.62000274658203</v>
       </c>
       <c r="C178" t="n">
-        <v>82</v>
+        <v>81.70999908447266</v>
       </c>
       <c r="D178" t="n">
-        <v>79.27999877929688</v>
+        <v>80.45999908447266</v>
       </c>
       <c r="E178" t="n">
-        <v>80.33999633789062</v>
+        <v>81.66999816894531</v>
       </c>
       <c r="F178" t="n">
-        <v>35309700</v>
+        <v>36430800</v>
       </c>
       <c r="G178" t="n">
         <v>0</v>
@@ -5071,22 +5071,22 @@
     </row>
     <row r="179">
       <c r="A179" s="1" t="n">
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="B179" t="n">
-        <v>80.62000274658203</v>
+        <v>81.90000152587891</v>
       </c>
       <c r="C179" t="n">
-        <v>81.70999908447266</v>
+        <v>81.93000030517578</v>
       </c>
       <c r="D179" t="n">
-        <v>80.45999908447266</v>
+        <v>77.70999908447266</v>
       </c>
       <c r="E179" t="n">
-        <v>81.66999816894531</v>
+        <v>78.72000122070312</v>
       </c>
       <c r="F179" t="n">
-        <v>36430800</v>
+        <v>65054000</v>
       </c>
       <c r="G179" t="n">
         <v>0</v>
@@ -5097,22 +5097,22 @@
     </row>
     <row r="180">
       <c r="A180" s="1" t="n">
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="B180" t="n">
-        <v>81.90000152587891</v>
+        <v>78.09999847412109</v>
       </c>
       <c r="C180" t="n">
-        <v>81.93000030517578</v>
+        <v>78.44999694824219</v>
       </c>
       <c r="D180" t="n">
-        <v>77.70999908447266</v>
+        <v>76.76000213623047</v>
       </c>
       <c r="E180" t="n">
-        <v>78.72000122070312</v>
+        <v>76.95999908447266</v>
       </c>
       <c r="F180" t="n">
-        <v>65054000</v>
+        <v>50338800</v>
       </c>
       <c r="G180" t="n">
         <v>0</v>
@@ -5123,22 +5123,22 @@
     </row>
     <row r="181">
       <c r="A181" s="1" t="n">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="B181" t="n">
-        <v>78.09999847412109</v>
+        <v>76.93000030517578</v>
       </c>
       <c r="C181" t="n">
-        <v>78.44999694824219</v>
+        <v>78.23999786376953</v>
       </c>
       <c r="D181" t="n">
-        <v>76.76000213623047</v>
+        <v>76.12000274658203</v>
       </c>
       <c r="E181" t="n">
-        <v>76.95999908447266</v>
+        <v>77.37999725341797</v>
       </c>
       <c r="F181" t="n">
-        <v>50338800</v>
+        <v>91920400</v>
       </c>
       <c r="G181" t="n">
         <v>0</v>
@@ -5149,22 +5149,22 @@
     </row>
     <row r="182">
       <c r="A182" s="1" t="n">
-        <v>46191</v>
+        <v>46195</v>
       </c>
       <c r="B182" t="n">
-        <v>76.93000030517578</v>
+        <v>76.13999938964844</v>
       </c>
       <c r="C182" t="n">
-        <v>78.23999786376953</v>
+        <v>77.08999633789062</v>
       </c>
       <c r="D182" t="n">
-        <v>76.12000274658203</v>
+        <v>71.80999755859375</v>
       </c>
       <c r="E182" t="n">
-        <v>77.37999725341797</v>
+        <v>72.87999725341797</v>
       </c>
       <c r="F182" t="n">
-        <v>91920400</v>
+        <v>82203300</v>
       </c>
       <c r="G182" t="n">
         <v>0</v>
@@ -5175,22 +5175,22 @@
     </row>
     <row r="183">
       <c r="A183" s="1" t="n">
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="B183" t="n">
-        <v>76.13999938964844</v>
+        <v>73.26000213623047</v>
       </c>
       <c r="C183" t="n">
-        <v>77.08999633789062</v>
+        <v>73.95999908447266</v>
       </c>
       <c r="D183" t="n">
-        <v>71.80999755859375</v>
+        <v>72.62999725341797</v>
       </c>
       <c r="E183" t="n">
-        <v>72.87999725341797</v>
+        <v>72.81999969482422</v>
       </c>
       <c r="F183" t="n">
-        <v>82203300</v>
+        <v>50806800</v>
       </c>
       <c r="G183" t="n">
         <v>0</v>
@@ -5201,22 +5201,22 @@
     </row>
     <row r="184">
       <c r="A184" s="1" t="n">
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="B184" t="n">
-        <v>73.26000213623047</v>
+        <v>72.69000244140625</v>
       </c>
       <c r="C184" t="n">
-        <v>73.95999908447266</v>
+        <v>73.44999694824219</v>
       </c>
       <c r="D184" t="n">
-        <v>72.62999725341797</v>
+        <v>71.62999725341797</v>
       </c>
       <c r="E184" t="n">
-        <v>72.81999969482422</v>
+        <v>71.83999633789062</v>
       </c>
       <c r="F184" t="n">
-        <v>50806800</v>
+        <v>48001500</v>
       </c>
       <c r="G184" t="n">
         <v>0</v>
@@ -5227,22 +5227,22 @@
     </row>
     <row r="185">
       <c r="A185" s="1" t="n">
-        <v>46197</v>
+        <v>46198</v>
       </c>
       <c r="B185" t="n">
-        <v>72.69000244140625</v>
+        <v>71.33000183105469</v>
       </c>
       <c r="C185" t="n">
-        <v>73.44999694824219</v>
+        <v>72.94000244140625</v>
       </c>
       <c r="D185" t="n">
-        <v>71.62999725341797</v>
+        <v>70.86000061035156</v>
       </c>
       <c r="E185" t="n">
-        <v>71.83999633789062</v>
+        <v>70.90000152587891</v>
       </c>
       <c r="F185" t="n">
-        <v>48001500</v>
+        <v>44446900</v>
       </c>
       <c r="G185" t="n">
         <v>0</v>
@@ -5253,22 +5253,22 @@
     </row>
     <row r="186">
       <c r="A186" s="1" t="n">
-        <v>46198</v>
+        <v>46199</v>
       </c>
       <c r="B186" t="n">
-        <v>71.33000183105469</v>
+        <v>71.69000244140625</v>
       </c>
       <c r="C186" t="n">
-        <v>72.94000244140625</v>
+        <v>75.19999694824219</v>
       </c>
       <c r="D186" t="n">
-        <v>70.86000061035156</v>
+        <v>71.52999877929688</v>
       </c>
       <c r="E186" t="n">
-        <v>70.90000152587891</v>
+        <v>73.80999755859375</v>
       </c>
       <c r="F186" t="n">
-        <v>44446900</v>
+        <v>74990300</v>
       </c>
       <c r="G186" t="n">
         <v>0</v>
@@ -5279,22 +5279,22 @@
     </row>
     <row r="187">
       <c r="A187" s="1" t="n">
-        <v>46199</v>
+        <v>46202</v>
       </c>
       <c r="B187" t="n">
-        <v>71.69000244140625</v>
+        <v>74.62000274658203</v>
       </c>
       <c r="C187" t="n">
-        <v>75.19999694824219</v>
+        <v>76.06999969482422</v>
       </c>
       <c r="D187" t="n">
-        <v>71.52999877929688</v>
+        <v>73.73000335693359</v>
       </c>
       <c r="E187" t="n">
-        <v>73.80999755859375</v>
+        <v>73.77999877929688</v>
       </c>
       <c r="F187" t="n">
-        <v>74990300</v>
+        <v>42429600</v>
       </c>
       <c r="G187" t="n">
         <v>0</v>
@@ -5305,22 +5305,22 @@
     </row>
     <row r="188">
       <c r="A188" s="1" t="n">
-        <v>46202</v>
+        <v>46203</v>
       </c>
       <c r="B188" t="n">
-        <v>74.62000274658203</v>
+        <v>73.58999633789062</v>
       </c>
       <c r="C188" t="n">
-        <v>76.06999969482422</v>
+        <v>73.75</v>
       </c>
       <c r="D188" t="n">
-        <v>73.73000335693359</v>
+        <v>71</v>
       </c>
       <c r="E188" t="n">
-        <v>73.77999877929688</v>
+        <v>71.40000152587891</v>
       </c>
       <c r="F188" t="n">
-        <v>42429600</v>
+        <v>49240900</v>
       </c>
       <c r="G188" t="n">
         <v>0</v>
@@ -5331,22 +5331,22 @@
     </row>
     <row r="189">
       <c r="A189" s="1" t="n">
-        <v>46203</v>
+        <v>46204</v>
       </c>
       <c r="B189" t="n">
-        <v>73.58999633789062</v>
+        <v>72.58999633789062</v>
       </c>
       <c r="C189" t="n">
-        <v>73.75</v>
+        <v>74.36000061035156</v>
       </c>
       <c r="D189" t="n">
-        <v>71</v>
+        <v>72.33000183105469</v>
       </c>
       <c r="E189" t="n">
-        <v>71.40000152587891</v>
+        <v>74.19000244140625</v>
       </c>
       <c r="F189" t="n">
-        <v>49240900</v>
+        <v>43841800</v>
       </c>
       <c r="G189" t="n">
         <v>0</v>
@@ -5357,22 +5357,22 @@
     </row>
     <row r="190">
       <c r="A190" s="1" t="n">
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="B190" t="n">
-        <v>72.58999633789062</v>
+        <v>75.08999633789062</v>
       </c>
       <c r="C190" t="n">
-        <v>74.36000061035156</v>
+        <v>78.44000244140625</v>
       </c>
       <c r="D190" t="n">
-        <v>72.33000183105469</v>
+        <v>74.91000366210938</v>
       </c>
       <c r="E190" t="n">
-        <v>74.19000244140625</v>
+        <v>77.65000152587891</v>
       </c>
       <c r="F190" t="n">
-        <v>43841800</v>
+        <v>55456500</v>
       </c>
       <c r="G190" t="n">
         <v>0</v>
@@ -5383,22 +5383,22 @@
     </row>
     <row r="191">
       <c r="A191" s="1" t="n">
-        <v>46205</v>
+        <v>46209</v>
       </c>
       <c r="B191" t="n">
-        <v>75.08999633789062</v>
+        <v>77.08000183105469</v>
       </c>
       <c r="C191" t="n">
-        <v>78.44000244140625</v>
+        <v>77.83999633789062</v>
       </c>
       <c r="D191" t="n">
-        <v>74.91000366210938</v>
+        <v>75.70999908447266</v>
       </c>
       <c r="E191" t="n">
-        <v>77.65000152587891</v>
+        <v>76.01999664306641</v>
       </c>
       <c r="F191" t="n">
-        <v>55456500</v>
+        <v>45056600</v>
       </c>
       <c r="G191" t="n">
         <v>0</v>
@@ -5409,22 +5409,22 @@
     </row>
     <row r="192">
       <c r="A192" s="1" t="n">
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="B192" t="n">
-        <v>77.08000183105469</v>
+        <v>77.87999725341797</v>
       </c>
       <c r="C192" t="n">
-        <v>77.83999633789062</v>
+        <v>78.19000244140625</v>
       </c>
       <c r="D192" t="n">
-        <v>75.70999908447266</v>
+        <v>76.09999847412109</v>
       </c>
       <c r="E192" t="n">
-        <v>76.01999664306641</v>
+        <v>76.18000030517578</v>
       </c>
       <c r="F192" t="n">
-        <v>45056600</v>
+        <v>33257300</v>
       </c>
       <c r="G192" t="n">
         <v>0</v>
@@ -5435,22 +5435,22 @@
     </row>
     <row r="193">
       <c r="A193" s="1" t="n">
-        <v>46210</v>
+        <v>46211</v>
       </c>
       <c r="B193" t="n">
-        <v>77.87999725341797</v>
+        <v>76.26999664306641</v>
       </c>
       <c r="C193" t="n">
-        <v>78.19000244140625</v>
+        <v>76.63999938964844</v>
       </c>
       <c r="D193" t="n">
-        <v>76.09999847412109</v>
+        <v>74.88999938964844</v>
       </c>
       <c r="E193" t="n">
-        <v>76.18000030517578</v>
+        <v>75.58999633789062</v>
       </c>
       <c r="F193" t="n">
-        <v>33257300</v>
+        <v>34373500</v>
       </c>
       <c r="G193" t="n">
         <v>0</v>
@@ -5461,22 +5461,22 @@
     </row>
     <row r="194">
       <c r="A194" s="1" t="n">
-        <v>46211</v>
+        <v>46212</v>
       </c>
       <c r="B194" t="n">
-        <v>76.26999664306641</v>
+        <v>74.30000305175781</v>
       </c>
       <c r="C194" t="n">
-        <v>76.63999938964844</v>
+        <v>75.55000305175781</v>
       </c>
       <c r="D194" t="n">
-        <v>74.88999938964844</v>
+        <v>74.01999664306641</v>
       </c>
       <c r="E194" t="n">
-        <v>75.58999633789062</v>
+        <v>75.47000122070312</v>
       </c>
       <c r="F194" t="n">
-        <v>34373500</v>
+        <v>36305700</v>
       </c>
       <c r="G194" t="n">
         <v>0</v>
@@ -5487,22 +5487,22 @@
     </row>
     <row r="195">
       <c r="A195" s="1" t="n">
-        <v>46212</v>
+        <v>46213</v>
       </c>
       <c r="B195" t="n">
-        <v>74.30000305175781</v>
+        <v>75.44000244140625</v>
       </c>
       <c r="C195" t="n">
-        <v>75.55000305175781</v>
+        <v>75.69999694824219</v>
       </c>
       <c r="D195" t="n">
-        <v>74.01999664306641</v>
+        <v>72.51000213623047</v>
       </c>
       <c r="E195" t="n">
-        <v>75.47000122070312</v>
+        <v>73.37000274658203</v>
       </c>
       <c r="F195" t="n">
-        <v>36305700</v>
+        <v>46713900</v>
       </c>
       <c r="G195" t="n">
         <v>0</v>
@@ -5513,22 +5513,22 @@
     </row>
     <row r="196">
       <c r="A196" s="1" t="n">
-        <v>46213</v>
+        <v>46216</v>
       </c>
       <c r="B196" t="n">
-        <v>75.44000244140625</v>
+        <v>73.90000152587891</v>
       </c>
       <c r="C196" t="n">
-        <v>75.69999694824219</v>
+        <v>75.44999694824219</v>
       </c>
       <c r="D196" t="n">
-        <v>72.51000213623047</v>
+        <v>73.70999908447266</v>
       </c>
       <c r="E196" t="n">
-        <v>73.37000274658203</v>
+        <v>73.83000183105469</v>
       </c>
       <c r="F196" t="n">
-        <v>46713900</v>
+        <v>35101800</v>
       </c>
       <c r="G196" t="n">
         <v>0</v>
@@ -5539,22 +5539,22 @@
     </row>
     <row r="197">
       <c r="A197" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="B197" t="n">
-        <v>73.90000152587891</v>
+        <v>72.63999938964844</v>
       </c>
       <c r="C197" t="n">
-        <v>75.44999694824219</v>
+        <v>74.01000213623047</v>
       </c>
       <c r="D197" t="n">
-        <v>73.70999908447266</v>
+        <v>72.27999877929688</v>
       </c>
       <c r="E197" t="n">
-        <v>73.83000183105469</v>
+        <v>73.52999877929688</v>
       </c>
       <c r="F197" t="n">
-        <v>35101800</v>
+        <v>33312100</v>
       </c>
       <c r="G197" t="n">
         <v>0</v>
@@ -5565,22 +5565,22 @@
     </row>
     <row r="198">
       <c r="A198" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="B198" t="n">
-        <v>72.63999938964844</v>
+        <v>73.79000091552734</v>
       </c>
       <c r="C198" t="n">
-        <v>74.01000213623047</v>
+        <v>75.05999755859375</v>
       </c>
       <c r="D198" t="n">
-        <v>72.27999877929688</v>
+        <v>73.12999725341797</v>
       </c>
       <c r="E198" t="n">
-        <v>73.52999877929688</v>
+        <v>73.68000030517578</v>
       </c>
       <c r="F198" t="n">
-        <v>33312100</v>
+        <v>32854300</v>
       </c>
       <c r="G198" t="n">
         <v>0</v>
@@ -5591,22 +5591,22 @@
     </row>
     <row r="199">
       <c r="A199" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="B199" t="n">
-        <v>73.79000091552734</v>
+        <v>73.94999694824219</v>
       </c>
       <c r="C199" t="n">
-        <v>75.05999755859375</v>
+        <v>74.68000030517578</v>
       </c>
       <c r="D199" t="n">
-        <v>73.12999725341797</v>
+        <v>72.94000244140625</v>
       </c>
       <c r="E199" t="n">
-        <v>73.68000030517578</v>
+        <v>74.34999847412109</v>
       </c>
       <c r="F199" t="n">
-        <v>32854300</v>
+        <v>77505200</v>
       </c>
       <c r="G199" t="n">
         <v>0</v>
@@ -5617,22 +5617,22 @@
     </row>
     <row r="200">
       <c r="A200" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="B200" t="n">
-        <v>73.94999694824219</v>
+        <v>65.48000335693359</v>
       </c>
       <c r="C200" t="n">
-        <v>74.68000030517578</v>
+        <v>69.48999786376953</v>
       </c>
       <c r="D200" t="n">
-        <v>72.94000244140625</v>
+        <v>65.08000183105469</v>
       </c>
       <c r="E200" t="n">
-        <v>74.34999847412109</v>
+        <v>68.94999694824219</v>
       </c>
       <c r="F200" t="n">
-        <v>77505200</v>
+        <v>142029200</v>
       </c>
       <c r="G200" t="n">
         <v>0</v>
@@ -5643,22 +5643,22 @@
     </row>
     <row r="201">
       <c r="A201" s="1" t="n">
-        <v>46220</v>
+        <v>46223</v>
       </c>
       <c r="B201" t="n">
-        <v>65.48000335693359</v>
+        <v>68.31999969482422</v>
       </c>
       <c r="C201" t="n">
-        <v>69.48999786376953</v>
+        <v>68.37999725341797</v>
       </c>
       <c r="D201" t="n">
-        <v>65.08000183105469</v>
+        <v>66.69000244140625</v>
       </c>
       <c r="E201" t="n">
-        <v>68.94999694824219</v>
+        <v>67.59999847412109</v>
       </c>
       <c r="F201" t="n">
-        <v>142029200</v>
+        <v>60669100</v>
       </c>
       <c r="G201" t="n">
         <v>0</v>
@@ -5669,22 +5669,22 @@
     </row>
     <row r="202">
       <c r="A202" s="1" t="n">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="B202" t="n">
-        <v>68.31999969482422</v>
+        <v>67.41999816894531</v>
       </c>
       <c r="C202" t="n">
-        <v>68.37999725341797</v>
+        <v>68.75</v>
       </c>
       <c r="D202" t="n">
-        <v>66.69000244140625</v>
+        <v>66.73000335693359</v>
       </c>
       <c r="E202" t="n">
-        <v>67.59999847412109</v>
+        <v>68.66999816894531</v>
       </c>
       <c r="F202" t="n">
-        <v>60669100</v>
+        <v>56565800</v>
       </c>
       <c r="G202" t="n">
         <v>0</v>
@@ -5695,22 +5695,22 @@
     </row>
     <row r="203">
       <c r="A203" s="1" t="n">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="B203" t="n">
-        <v>67.41999816894531</v>
+        <v>69.37000274658203</v>
       </c>
       <c r="C203" t="n">
-        <v>68.75</v>
+        <v>70.56999969482422</v>
       </c>
       <c r="D203" t="n">
-        <v>66.73000335693359</v>
+        <v>68.34999847412109</v>
       </c>
       <c r="E203" t="n">
-        <v>68.66999816894531</v>
+        <v>68.52999877929688</v>
       </c>
       <c r="F203" t="n">
-        <v>56565800</v>
+        <v>44947300</v>
       </c>
       <c r="G203" t="n">
         <v>0</v>
@@ -5721,22 +5721,22 @@
     </row>
     <row r="204">
       <c r="A204" s="1" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="B204" t="n">
-        <v>69.37000274658203</v>
+        <v>68.56999969482422</v>
       </c>
       <c r="C204" t="n">
-        <v>70.56999969482422</v>
+        <v>69.36000061035156</v>
       </c>
       <c r="D204" t="n">
-        <v>68.34999847412109</v>
+        <v>67.66999816894531</v>
       </c>
       <c r="E204" t="n">
-        <v>68.52999877929688</v>
+        <v>68.88999938964844</v>
       </c>
       <c r="F204" t="n">
-        <v>44947300</v>
+        <v>45029100</v>
       </c>
       <c r="G204" t="n">
         <v>0</v>
@@ -5747,22 +5747,22 @@
     </row>
     <row r="205">
       <c r="A205" s="1" t="n">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="B205" t="n">
-        <v>68.56999969482422</v>
+        <v>69.29000091552734</v>
       </c>
       <c r="C205" t="n">
-        <v>69.36000061035156</v>
+        <v>70.68000030517578</v>
       </c>
       <c r="D205" t="n">
-        <v>67.66999816894531</v>
+        <v>67.97000122070312</v>
       </c>
       <c r="E205" t="n">
-        <v>68.88999938964844</v>
+        <v>70.08999633789062</v>
       </c>
       <c r="F205" t="n">
-        <v>45029100</v>
+        <v>37593500</v>
       </c>
       <c r="G205" t="n">
         <v>0</v>
@@ -5773,22 +5773,22 @@
     </row>
     <row r="206">
       <c r="A206" s="1" t="n">
-        <v>46227</v>
+        <v>46230</v>
       </c>
       <c r="B206" t="n">
-        <v>69.29000091552734</v>
+        <v>70.58999633789062</v>
       </c>
       <c r="C206" t="n">
-        <v>70.68000030517578</v>
+        <v>71.65000152587891</v>
       </c>
       <c r="D206" t="n">
-        <v>67.97000122070312</v>
+        <v>69.86000061035156</v>
       </c>
       <c r="E206" t="n">
-        <v>70.08999633789062</v>
+        <v>70.40000152587891</v>
       </c>
       <c r="F206" t="n">
-        <v>37593500</v>
+        <v>39090800</v>
       </c>
       <c r="G206" t="n">
         <v>0</v>
@@ -5799,22 +5799,22 @@
     </row>
     <row r="207">
       <c r="A207" s="1" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="B207" t="n">
-        <v>70.58999633789062</v>
+        <v>72.06999969482422</v>
       </c>
       <c r="C207" t="n">
-        <v>71.65000152587891</v>
+        <v>73.76000213623047</v>
       </c>
       <c r="D207" t="n">
-        <v>69.86000061035156</v>
+        <v>71.23000335693359</v>
       </c>
       <c r="E207" t="n">
-        <v>70.40000152587891</v>
+        <v>72.38999938964844</v>
       </c>
       <c r="F207" t="n">
-        <v>39090800</v>
+        <v>47160200</v>
       </c>
       <c r="G207" t="n">
         <v>0</v>
@@ -5825,22 +5825,22 @@
     </row>
     <row r="208">
       <c r="A208" s="1" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="B208" t="n">
-        <v>72.06999969482422</v>
+        <v>72.19000244140625</v>
       </c>
       <c r="C208" t="n">
-        <v>73.76000213623047</v>
+        <v>73.73999786376953</v>
       </c>
       <c r="D208" t="n">
-        <v>71.23000335693359</v>
+        <v>71.75</v>
       </c>
       <c r="E208" t="n">
-        <v>72.38999938964844</v>
+        <v>73.62999725341797</v>
       </c>
       <c r="F208" t="n">
-        <v>47160200</v>
+        <v>43737600</v>
       </c>
       <c r="G208" t="n">
         <v>0</v>
@@ -5851,22 +5851,22 @@
     </row>
     <row r="209">
       <c r="A209" s="1" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="B209" t="n">
-        <v>72.19000244140625</v>
+        <v>71.48000335693359</v>
       </c>
       <c r="C209" t="n">
-        <v>73.73999786376953</v>
+        <v>73.31999969482422</v>
       </c>
       <c r="D209" t="n">
-        <v>71.75</v>
+        <v>70.55000305175781</v>
       </c>
       <c r="E209" t="n">
-        <v>73.62999725341797</v>
+        <v>73.16999816894531</v>
       </c>
       <c r="F209" t="n">
-        <v>43737600</v>
+        <v>54261000</v>
       </c>
       <c r="G209" t="n">
         <v>0</v>
@@ -5877,22 +5877,22 @@
     </row>
     <row r="210">
       <c r="A210" s="1" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="B210" t="n">
-        <v>71.48000335693359</v>
+        <v>71.97000122070312</v>
       </c>
       <c r="C210" t="n">
-        <v>73.31999969482422</v>
+        <v>72.75</v>
       </c>
       <c r="D210" t="n">
-        <v>70.55000305175781</v>
+        <v>71.11000061035156</v>
       </c>
       <c r="E210" t="n">
-        <v>73.16999816894531</v>
+        <v>71.70999908447266</v>
       </c>
       <c r="F210" t="n">
-        <v>54261000</v>
+        <v>35847500</v>
       </c>
       <c r="G210" t="n">
         <v>0</v>
@@ -5903,22 +5903,22 @@
     </row>
     <row r="211">
       <c r="A211" s="1" t="n">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="B211" t="n">
-        <v>71.97000122070312</v>
+        <v>72.76999664306641</v>
       </c>
       <c r="C211" t="n">
-        <v>72.75</v>
+        <v>73.94999694824219</v>
       </c>
       <c r="D211" t="n">
-        <v>71.11000061035156</v>
+        <v>72.18000030517578</v>
       </c>
       <c r="E211" t="n">
-        <v>71.70999908447266</v>
+        <v>73.33000183105469</v>
       </c>
       <c r="F211" t="n">
-        <v>35847500</v>
+        <v>33922300</v>
       </c>
       <c r="G211" t="n">
         <v>0</v>
@@ -5929,22 +5929,22 @@
     </row>
     <row r="212">
       <c r="A212" s="1" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="B212" t="n">
-        <v>72.76999664306641</v>
+        <v>72.51000213623047</v>
       </c>
       <c r="C212" t="n">
-        <v>73.94999694824219</v>
+        <v>73.75</v>
       </c>
       <c r="D212" t="n">
-        <v>72.18000030517578</v>
+        <v>72.30000305175781</v>
       </c>
       <c r="E212" t="n">
-        <v>73.33000183105469</v>
+        <v>73.56999969482422</v>
       </c>
       <c r="F212" t="n">
-        <v>33922300</v>
+        <v>42877900</v>
       </c>
       <c r="G212" t="n">
         <v>0</v>
@@ -5955,22 +5955,22 @@
     </row>
     <row r="213">
       <c r="A213" s="1" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="B213" t="n">
-        <v>72.51000213623047</v>
+        <v>75.11000061035156</v>
       </c>
       <c r="C213" t="n">
-        <v>73.75</v>
+        <v>75.30000305175781</v>
       </c>
       <c r="D213" t="n">
-        <v>72.30000305175781</v>
+        <v>73.16000366210938</v>
       </c>
       <c r="E213" t="n">
-        <v>73.56999969482422</v>
+        <v>74.19999694824219</v>
       </c>
       <c r="F213" t="n">
-        <v>42877900</v>
+        <v>28969400</v>
       </c>
       <c r="G213" t="n">
         <v>0</v>
@@ -5981,22 +5981,22 @@
     </row>
     <row r="214">
       <c r="A214" s="1" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="B214" t="n">
-        <v>75.11000061035156</v>
+        <v>75.13999938964844</v>
       </c>
       <c r="C214" t="n">
-        <v>75.30000305175781</v>
+        <v>75.20999908447266</v>
       </c>
       <c r="D214" t="n">
-        <v>73.16000366210938</v>
+        <v>73.09999847412109</v>
       </c>
       <c r="E214" t="n">
-        <v>74.19999694824219</v>
+        <v>73.69000244140625</v>
       </c>
       <c r="F214" t="n">
-        <v>28969400</v>
+        <v>28892700</v>
       </c>
       <c r="G214" t="n">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="215">
       <c r="A215" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="B215" t="n">
-        <v>75.13999938964844</v>
+        <v>73.12000274658203</v>
       </c>
       <c r="C215" t="n">
-        <v>75.20999908447266</v>
+        <v>74.5</v>
       </c>
       <c r="D215" t="n">
-        <v>73.09999847412109</v>
+        <v>73.08000183105469</v>
       </c>
       <c r="E215" t="n">
-        <v>73.69000244140625</v>
+        <v>74.13999938964844</v>
       </c>
       <c r="F215" t="n">
-        <v>28892700</v>
+        <v>24819000</v>
       </c>
       <c r="G215" t="n">
         <v>0</v>
@@ -6033,22 +6033,22 @@
     </row>
     <row r="216">
       <c r="A216" s="1" t="n">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="B216" t="n">
-        <v>73.12000274658203</v>
+        <v>73.80000305175781</v>
       </c>
       <c r="C216" t="n">
-        <v>74.5</v>
+        <v>76.31999969482422</v>
       </c>
       <c r="D216" t="n">
-        <v>73.08000183105469</v>
+        <v>73.56999969482422</v>
       </c>
       <c r="E216" t="n">
-        <v>74.13999938964844</v>
+        <v>76.29000091552734</v>
       </c>
       <c r="F216" t="n">
-        <v>24819000</v>
+        <v>26959900</v>
       </c>
       <c r="G216" t="n">
         <v>0</v>
@@ -6059,22 +6059,22 @@
     </row>
     <row r="217">
       <c r="A217" s="1" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="B217" t="n">
-        <v>73.80000305175781</v>
+        <v>76.19999694824219</v>
       </c>
       <c r="C217" t="n">
-        <v>76.31999969482422</v>
+        <v>76.90000152587891</v>
       </c>
       <c r="D217" t="n">
-        <v>73.56999969482422</v>
+        <v>74.48000335693359</v>
       </c>
       <c r="E217" t="n">
-        <v>76.29000091552734</v>
+        <v>74.79000091552734</v>
       </c>
       <c r="F217" t="n">
-        <v>26959900</v>
+        <v>27840500</v>
       </c>
       <c r="G217" t="n">
         <v>0</v>
@@ -6085,22 +6085,22 @@
     </row>
     <row r="218">
       <c r="A218" s="1" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="B218" t="n">
-        <v>76.19999694824219</v>
+        <v>74.34999847412109</v>
       </c>
       <c r="C218" t="n">
-        <v>76.90000152587891</v>
+        <v>74.66999816894531</v>
       </c>
       <c r="D218" t="n">
-        <v>74.48000335693359</v>
+        <v>73.56999969482422</v>
       </c>
       <c r="E218" t="n">
-        <v>74.79000091552734</v>
+        <v>74.20999908447266</v>
       </c>
       <c r="F218" t="n">
-        <v>27840500</v>
+        <v>20773100</v>
       </c>
       <c r="G218" t="n">
         <v>0</v>
@@ -6111,22 +6111,22 @@
     </row>
     <row r="219">
       <c r="A219" s="1" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="B219" t="n">
-        <v>74.34999847412109</v>
+        <v>76.01000213623047</v>
       </c>
       <c r="C219" t="n">
-        <v>74.66999816894531</v>
+        <v>78.40000152587891</v>
       </c>
       <c r="D219" t="n">
-        <v>73.56999969482422</v>
+        <v>75.44000244140625</v>
       </c>
       <c r="E219" t="n">
-        <v>74.20999908447266</v>
+        <v>78.23999786376953</v>
       </c>
       <c r="F219" t="n">
-        <v>20773100</v>
+        <v>41452900</v>
       </c>
       <c r="G219" t="n">
         <v>0</v>
@@ -6137,22 +6137,22 @@
     </row>
     <row r="220">
       <c r="A220" s="1" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="B220" t="n">
-        <v>76.01000213623047</v>
+        <v>78.48000335693359</v>
       </c>
       <c r="C220" t="n">
-        <v>78.40000152587891</v>
+        <v>78.73000335693359</v>
       </c>
       <c r="D220" t="n">
-        <v>75.44000244140625</v>
+        <v>77.76000213623047</v>
       </c>
       <c r="E220" t="n">
-        <v>78.23999786376953</v>
+        <v>78.16000366210938</v>
       </c>
       <c r="F220" t="n">
-        <v>41452900</v>
+        <v>26751000</v>
       </c>
       <c r="G220" t="n">
         <v>0</v>
@@ -6163,22 +6163,22 @@
     </row>
     <row r="221">
       <c r="A221" s="1" t="n">
-        <v>46248</v>
+        <v>46251</v>
       </c>
       <c r="B221" t="n">
-        <v>78.48000335693359</v>
+        <v>77.80000305175781</v>
       </c>
       <c r="C221" t="n">
-        <v>78.73000335693359</v>
+        <v>78.52999877929688</v>
       </c>
       <c r="D221" t="n">
-        <v>77.76000213623047</v>
+        <v>75.47000122070312</v>
       </c>
       <c r="E221" t="n">
-        <v>78.16000366210938</v>
+        <v>76.01999664306641</v>
       </c>
       <c r="F221" t="n">
-        <v>26751000</v>
+        <v>30753000</v>
       </c>
       <c r="G221" t="n">
         <v>0</v>
@@ -6189,22 +6189,22 @@
     </row>
     <row r="222">
       <c r="A222" s="1" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="B222" t="n">
-        <v>77.80000305175781</v>
+        <v>77.43000030517578</v>
       </c>
       <c r="C222" t="n">
-        <v>78.52999877929688</v>
+        <v>79.09999847412109</v>
       </c>
       <c r="D222" t="n">
-        <v>75.47000122070312</v>
+        <v>76.33999633789062</v>
       </c>
       <c r="E222" t="n">
-        <v>76.01999664306641</v>
+        <v>77.76999664306641</v>
       </c>
       <c r="F222" t="n">
-        <v>30753000</v>
+        <v>36151300</v>
       </c>
       <c r="G222" t="n">
         <v>0</v>
@@ -6215,22 +6215,22 @@
     </row>
     <row r="223">
       <c r="A223" s="1" t="n">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="B223" t="n">
-        <v>77.43000030517578</v>
+        <v>78.25</v>
       </c>
       <c r="C223" t="n">
-        <v>79.09999847412109</v>
+        <v>81.16000366210938</v>
       </c>
       <c r="D223" t="n">
-        <v>76.33999633789062</v>
+        <v>78.09999847412109</v>
       </c>
       <c r="E223" t="n">
-        <v>77.76999664306641</v>
+        <v>80.22000122070312</v>
       </c>
       <c r="F223" t="n">
-        <v>36151300</v>
+        <v>31461800</v>
       </c>
       <c r="G223" t="n">
         <v>0</v>
@@ -6241,22 +6241,22 @@
     </row>
     <row r="224">
       <c r="A224" s="1" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="B224" t="n">
-        <v>78.25</v>
+        <v>80.13999938964844</v>
       </c>
       <c r="C224" t="n">
-        <v>81.16000366210938</v>
+        <v>81.08000183105469</v>
       </c>
       <c r="D224" t="n">
-        <v>78.09999847412109</v>
+        <v>79.58999633789062</v>
       </c>
       <c r="E224" t="n">
-        <v>80.22000122070312</v>
+        <v>80.13999938964844</v>
       </c>
       <c r="F224" t="n">
-        <v>31461800</v>
+        <v>27118400</v>
       </c>
       <c r="G224" t="n">
         <v>0</v>
@@ -6267,22 +6267,22 @@
     </row>
     <row r="225">
       <c r="A225" s="1" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="B225" t="n">
-        <v>80.13999938964844</v>
+        <v>80.29000091552734</v>
       </c>
       <c r="C225" t="n">
-        <v>81.08000183105469</v>
+        <v>80.48999786376953</v>
       </c>
       <c r="D225" t="n">
+        <v>79.16999816894531</v>
+      </c>
+      <c r="E225" t="n">
         <v>79.58999633789062</v>
       </c>
-      <c r="E225" t="n">
-        <v>80.13999938964844</v>
-      </c>
       <c r="F225" t="n">
-        <v>27118400</v>
+        <v>23773800</v>
       </c>
       <c r="G225" t="n">
         <v>0</v>
@@ -6293,22 +6293,22 @@
     </row>
     <row r="226">
       <c r="A226" s="1" t="n">
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="B226" t="n">
-        <v>80.29000091552734</v>
+        <v>79.94000244140625</v>
       </c>
       <c r="C226" t="n">
-        <v>80.48999786376953</v>
+        <v>80.62000274658203</v>
       </c>
       <c r="D226" t="n">
-        <v>79.16999816894531</v>
+        <v>79.01999664306641</v>
       </c>
       <c r="E226" t="n">
-        <v>79.58999633789062</v>
+        <v>80.01000213623047</v>
       </c>
       <c r="F226" t="n">
-        <v>23773800</v>
+        <v>21085300</v>
       </c>
       <c r="G226" t="n">
         <v>0</v>
@@ -6319,22 +6319,22 @@
     </row>
     <row r="227">
       <c r="A227" s="1" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="B227" t="n">
-        <v>79.94000244140625</v>
+        <v>79.65000152587891</v>
       </c>
       <c r="C227" t="n">
-        <v>80.62000274658203</v>
+        <v>82.45999908447266</v>
       </c>
       <c r="D227" t="n">
-        <v>79.01999664306641</v>
+        <v>79.40000152587891</v>
       </c>
       <c r="E227" t="n">
-        <v>80.01000213623047</v>
+        <v>82.23000335693359</v>
       </c>
       <c r="F227" t="n">
-        <v>21085300</v>
+        <v>29462000</v>
       </c>
       <c r="G227" t="n">
         <v>0</v>
@@ -6345,22 +6345,22 @@
     </row>
     <row r="228">
       <c r="A228" s="1" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="B228" t="n">
-        <v>79.65000152587891</v>
+        <v>82.05000305175781</v>
       </c>
       <c r="C228" t="n">
-        <v>82.45999908447266</v>
+        <v>82.41999816894531</v>
       </c>
       <c r="D228" t="n">
-        <v>79.40000152587891</v>
+        <v>81.30000305175781</v>
       </c>
       <c r="E228" t="n">
-        <v>82.23000335693359</v>
+        <v>81.45999908447266</v>
       </c>
       <c r="F228" t="n">
-        <v>29462000</v>
+        <v>22874900</v>
       </c>
       <c r="G228" t="n">
         <v>0</v>
@@ -6371,22 +6371,22 @@
     </row>
     <row r="229">
       <c r="A229" s="1" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="B229" t="n">
-        <v>82.05000305175781</v>
+        <v>81.06999969482422</v>
       </c>
       <c r="C229" t="n">
-        <v>82.41999816894531</v>
+        <v>81.15000152587891</v>
       </c>
       <c r="D229" t="n">
-        <v>81.30000305175781</v>
+        <v>79.27999877929688</v>
       </c>
       <c r="E229" t="n">
-        <v>81.45999908447266</v>
+        <v>79.83999633789062</v>
       </c>
       <c r="F229" t="n">
-        <v>22874900</v>
+        <v>27174400</v>
       </c>
       <c r="G229" t="n">
         <v>0</v>
@@ -6397,22 +6397,22 @@
     </row>
     <row r="230">
       <c r="A230" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="B230" t="n">
-        <v>81.06999969482422</v>
+        <v>80.36000061035156</v>
       </c>
       <c r="C230" t="n">
-        <v>81.15000152587891</v>
+        <v>82.34999847412109</v>
       </c>
       <c r="D230" t="n">
-        <v>79.27999877929688</v>
+        <v>79.94999694824219</v>
       </c>
       <c r="E230" t="n">
-        <v>79.83999633789062</v>
+        <v>81.72000122070312</v>
       </c>
       <c r="F230" t="n">
-        <v>27174400</v>
+        <v>29092700</v>
       </c>
       <c r="G230" t="n">
         <v>0</v>
@@ -6423,22 +6423,22 @@
     </row>
     <row r="231">
       <c r="A231" s="1" t="n">
-        <v>46262</v>
+        <v>46265</v>
       </c>
       <c r="B231" t="n">
-        <v>80.36000061035156</v>
+        <v>81</v>
       </c>
       <c r="C231" t="n">
-        <v>82.34999847412109</v>
+        <v>81.73000335693359</v>
       </c>
       <c r="D231" t="n">
-        <v>79.94999694824219</v>
+        <v>80.65000152587891</v>
       </c>
       <c r="E231" t="n">
-        <v>81.72000122070312</v>
+        <v>81.05000305175781</v>
       </c>
       <c r="F231" t="n">
-        <v>29092700</v>
+        <v>30740800</v>
       </c>
       <c r="G231" t="n">
         <v>0</v>
@@ -6449,22 +6449,22 @@
     </row>
     <row r="232">
       <c r="A232" s="1" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="B232" t="n">
-        <v>81</v>
+        <v>80.16999816894531</v>
       </c>
       <c r="C232" t="n">
-        <v>81.73000335693359</v>
+        <v>82.12999725341797</v>
       </c>
       <c r="D232" t="n">
-        <v>80.65000152587891</v>
+        <v>79.59999847412109</v>
       </c>
       <c r="E232" t="n">
-        <v>81.05000305175781</v>
+        <v>80.80999755859375</v>
       </c>
       <c r="F232" t="n">
-        <v>30740800</v>
+        <v>21164900</v>
       </c>
       <c r="G232" t="n">
         <v>0</v>
@@ -6475,22 +6475,22 @@
     </row>
     <row r="233">
       <c r="A233" s="1" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="B233" t="n">
-        <v>80.16999816894531</v>
+        <v>80.55000305175781</v>
       </c>
       <c r="C233" t="n">
-        <v>82.12999725341797</v>
+        <v>83.12000274658203</v>
       </c>
       <c r="D233" t="n">
-        <v>79.59999847412109</v>
+        <v>80.30000305175781</v>
       </c>
       <c r="E233" t="n">
-        <v>80.80999755859375</v>
+        <v>82.73000335693359</v>
       </c>
       <c r="F233" t="n">
-        <v>21164900</v>
+        <v>22077800</v>
       </c>
       <c r="G233" t="n">
         <v>0</v>
@@ -6501,22 +6501,22 @@
     </row>
     <row r="234">
       <c r="A234" s="1" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="B234" t="n">
-        <v>80.55000305175781</v>
+        <v>83.18000030517578</v>
       </c>
       <c r="C234" t="n">
-        <v>83.12000274658203</v>
+        <v>83.59999847412109</v>
       </c>
       <c r="D234" t="n">
-        <v>80.30000305175781</v>
+        <v>81.62999725341797</v>
       </c>
       <c r="E234" t="n">
-        <v>82.73000335693359</v>
+        <v>82.66999816894531</v>
       </c>
       <c r="F234" t="n">
-        <v>22077800</v>
+        <v>24006400</v>
       </c>
       <c r="G234" t="n">
         <v>0</v>
@@ -6527,22 +6527,22 @@
     </row>
     <row r="235">
       <c r="A235" s="1" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B235" t="n">
-        <v>83.18000030517578</v>
+        <v>82.16999816894531</v>
       </c>
       <c r="C235" t="n">
-        <v>83.59999847412109</v>
+        <v>82.69000244140625</v>
       </c>
       <c r="D235" t="n">
-        <v>81.62999725341797</v>
+        <v>78.23000335693359</v>
       </c>
       <c r="E235" t="n">
-        <v>82.66999816894531</v>
+        <v>78.25</v>
       </c>
       <c r="F235" t="n">
-        <v>24006400</v>
+        <v>40190000</v>
       </c>
       <c r="G235" t="n">
         <v>0</v>
@@ -6553,22 +6553,22 @@
     </row>
     <row r="236">
       <c r="A236" s="1" t="n">
-        <v>46269</v>
+        <v>46273</v>
       </c>
       <c r="B236" t="n">
-        <v>82.16999816894531</v>
+        <v>77.55000305175781</v>
       </c>
       <c r="C236" t="n">
-        <v>82.69000244140625</v>
+        <v>77.73000335693359</v>
       </c>
       <c r="D236" t="n">
-        <v>78.23000335693359</v>
+        <v>75.91999816894531</v>
       </c>
       <c r="E236" t="n">
-        <v>78.25</v>
+        <v>76.76999664306641</v>
       </c>
       <c r="F236" t="n">
-        <v>40190000</v>
+        <v>33865500</v>
       </c>
       <c r="G236" t="n">
         <v>0</v>
@@ -6579,22 +6579,22 @@
     </row>
     <row r="237">
       <c r="A237" s="1" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B237" t="n">
-        <v>77.55000305175781</v>
+        <v>76.33999633789062</v>
       </c>
       <c r="C237" t="n">
-        <v>77.73000335693359</v>
+        <v>76.72000122070312</v>
       </c>
       <c r="D237" t="n">
-        <v>75.91999816894531</v>
+        <v>75.87000274658203</v>
       </c>
       <c r="E237" t="n">
-        <v>76.76999664306641</v>
+        <v>76.02999877929688</v>
       </c>
       <c r="F237" t="n">
-        <v>33865500</v>
+        <v>22779600</v>
       </c>
       <c r="G237" t="n">
         <v>0</v>
@@ -6605,22 +6605,22 @@
     </row>
     <row r="238">
       <c r="A238" s="1" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="B238" t="n">
-        <v>76.33999633789062</v>
+        <v>75.33000183105469</v>
       </c>
       <c r="C238" t="n">
-        <v>76.72000122070312</v>
+        <v>76.30000305175781</v>
       </c>
       <c r="D238" t="n">
-        <v>75.87000274658203</v>
+        <v>75.02999877929688</v>
       </c>
       <c r="E238" t="n">
-        <v>76.02999877929688</v>
+        <v>76.01000213623047</v>
       </c>
       <c r="F238" t="n">
-        <v>22779600</v>
+        <v>20049000</v>
       </c>
       <c r="G238" t="n">
         <v>0</v>
@@ -6631,22 +6631,22 @@
     </row>
     <row r="239">
       <c r="A239" s="1" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="B239" t="n">
-        <v>75.33000183105469</v>
+        <v>76.63999938964844</v>
       </c>
       <c r="C239" t="n">
-        <v>76.30000305175781</v>
+        <v>77.56999969482422</v>
       </c>
       <c r="D239" t="n">
-        <v>75.02999877929688</v>
+        <v>76.15000152587891</v>
       </c>
       <c r="E239" t="n">
-        <v>76.01000213623047</v>
+        <v>77.40000152587891</v>
       </c>
       <c r="F239" t="n">
-        <v>20049000</v>
+        <v>22237800</v>
       </c>
       <c r="G239" t="n">
         <v>0</v>
@@ -6657,22 +6657,22 @@
     </row>
     <row r="240">
       <c r="A240" s="1" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="B240" t="n">
-        <v>76.63999938964844</v>
+        <v>78.97000122070312</v>
       </c>
       <c r="C240" t="n">
-        <v>77.56999969482422</v>
+        <v>81.01999664306641</v>
       </c>
       <c r="D240" t="n">
-        <v>76.15000152587891</v>
+        <v>78.48999786376953</v>
       </c>
       <c r="E240" t="n">
-        <v>77.40000152587891</v>
+        <v>80.31999969482422</v>
       </c>
       <c r="F240" t="n">
-        <v>22237800</v>
+        <v>30945100</v>
       </c>
       <c r="G240" t="n">
         <v>0</v>
@@ -6683,22 +6683,22 @@
     </row>
     <row r="241">
       <c r="A241" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="B241" t="n">
-        <v>78.97000122070312</v>
+        <v>79.37999725341797</v>
       </c>
       <c r="C241" t="n">
-        <v>81.01999664306641</v>
+        <v>79.48000335693359</v>
       </c>
       <c r="D241" t="n">
-        <v>78.48999786376953</v>
+        <v>77.45999908447266</v>
       </c>
       <c r="E241" t="n">
-        <v>80.31999969482422</v>
+        <v>77.90000152587891</v>
       </c>
       <c r="F241" t="n">
-        <v>30945100</v>
+        <v>28027400</v>
       </c>
       <c r="G241" t="n">
         <v>0</v>
@@ -6709,22 +6709,22 @@
     </row>
     <row r="242">
       <c r="A242" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="B242" t="n">
-        <v>79.37999725341797</v>
+        <v>77.73000335693359</v>
       </c>
       <c r="C242" t="n">
-        <v>79.48000335693359</v>
+        <v>77.80000305175781</v>
       </c>
       <c r="D242" t="n">
-        <v>77.45999908447266</v>
+        <v>76.30999755859375</v>
       </c>
       <c r="E242" t="n">
-        <v>77.90000152587891</v>
+        <v>76.41000366210938</v>
       </c>
       <c r="F242" t="n">
-        <v>28027400</v>
+        <v>25376300</v>
       </c>
       <c r="G242" t="n">
         <v>0</v>
@@ -6735,22 +6735,22 @@
     </row>
     <row r="243">
       <c r="A243" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="B243" t="n">
-        <v>77.73000335693359</v>
+        <v>76.91000366210938</v>
       </c>
       <c r="C243" t="n">
-        <v>77.80000305175781</v>
+        <v>76.95999908447266</v>
       </c>
       <c r="D243" t="n">
-        <v>76.30999755859375</v>
+        <v>75.30000305175781</v>
       </c>
       <c r="E243" t="n">
-        <v>76.41000366210938</v>
+        <v>75.30999755859375</v>
       </c>
       <c r="F243" t="n">
-        <v>25376300</v>
+        <v>28167600</v>
       </c>
       <c r="G243" t="n">
         <v>0</v>
@@ -6761,22 +6761,22 @@
     </row>
     <row r="244">
       <c r="A244" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="B244" t="n">
-        <v>76.91000366210938</v>
+        <v>71.26999664306641</v>
       </c>
       <c r="C244" t="n">
-        <v>76.95999908447266</v>
+        <v>72.37999725341797</v>
       </c>
       <c r="D244" t="n">
-        <v>75.30000305175781</v>
+        <v>70.11000061035156</v>
       </c>
       <c r="E244" t="n">
-        <v>75.30999755859375</v>
+        <v>71.79000091552734</v>
       </c>
       <c r="F244" t="n">
-        <v>28167600</v>
+        <v>114413500</v>
       </c>
       <c r="G244" t="n">
         <v>0</v>
@@ -6787,22 +6787,22 @@
     </row>
     <row r="245">
       <c r="A245" s="1" t="n">
-        <v>46283</v>
+        <v>46286</v>
       </c>
       <c r="B245" t="n">
-        <v>71.26999664306641</v>
+        <v>71.81999969482422</v>
       </c>
       <c r="C245" t="n">
-        <v>72.37999725341797</v>
+        <v>73.87000274658203</v>
       </c>
       <c r="D245" t="n">
-        <v>70.11000061035156</v>
+        <v>71.79000091552734</v>
       </c>
       <c r="E245" t="n">
-        <v>71.79000091552734</v>
+        <v>73.36000061035156</v>
       </c>
       <c r="F245" t="n">
-        <v>114413500</v>
+        <v>36948000</v>
       </c>
       <c r="G245" t="n">
         <v>0</v>
@@ -6813,22 +6813,22 @@
     </row>
     <row r="246">
       <c r="A246" s="1" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="B246" t="n">
-        <v>71.81999969482422</v>
+        <v>73.69000244140625</v>
       </c>
       <c r="C246" t="n">
-        <v>73.87000274658203</v>
+        <v>73.76000213623047</v>
       </c>
       <c r="D246" t="n">
-        <v>71.79000091552734</v>
+        <v>71.58000183105469</v>
       </c>
       <c r="E246" t="n">
-        <v>73.36000061035156</v>
+        <v>72.16000366210938</v>
       </c>
       <c r="F246" t="n">
-        <v>36948000</v>
+        <v>34372500</v>
       </c>
       <c r="G246" t="n">
         <v>0</v>
@@ -6839,22 +6839,22 @@
     </row>
     <row r="247">
       <c r="A247" s="1" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="B247" t="n">
-        <v>73.69000244140625</v>
+        <v>72.08000183105469</v>
       </c>
       <c r="C247" t="n">
-        <v>73.76000213623047</v>
+        <v>72.37000274658203</v>
       </c>
       <c r="D247" t="n">
-        <v>71.58000183105469</v>
+        <v>71.06999969482422</v>
       </c>
       <c r="E247" t="n">
-        <v>72.16000366210938</v>
+        <v>71.36000061035156</v>
       </c>
       <c r="F247" t="n">
-        <v>34372500</v>
+        <v>32807500</v>
       </c>
       <c r="G247" t="n">
         <v>0</v>
@@ -6865,22 +6865,22 @@
     </row>
     <row r="248">
       <c r="A248" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="B248" t="n">
-        <v>72.08000183105469</v>
+        <v>71.62000274658203</v>
       </c>
       <c r="C248" t="n">
-        <v>72.37000274658203</v>
+        <v>72.04000091552734</v>
       </c>
       <c r="D248" t="n">
-        <v>71.06999969482422</v>
+        <v>71.20999908447266</v>
       </c>
       <c r="E248" t="n">
-        <v>71.36000061035156</v>
+        <v>71.72000122070312</v>
       </c>
       <c r="F248" t="n">
-        <v>32807500</v>
+        <v>28223900</v>
       </c>
       <c r="G248" t="n">
         <v>0</v>
@@ -6891,22 +6891,22 @@
     </row>
     <row r="249">
       <c r="A249" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="B249" t="n">
-        <v>71.62000274658203</v>
+        <v>71.62999725341797</v>
       </c>
       <c r="C249" t="n">
-        <v>72.04000091552734</v>
+        <v>71.83999633789062</v>
       </c>
       <c r="D249" t="n">
-        <v>71.20999908447266</v>
+        <v>70.98000335693359</v>
       </c>
       <c r="E249" t="n">
-        <v>71.72000122070312</v>
+        <v>71.15000152587891</v>
       </c>
       <c r="F249" t="n">
-        <v>28223900</v>
+        <v>23203100</v>
       </c>
       <c r="G249" t="n">
         <v>0</v>
@@ -6917,22 +6917,22 @@
     </row>
     <row r="250">
       <c r="A250" s="1" t="n">
-        <v>46290</v>
+        <v>46293</v>
       </c>
       <c r="B250" t="n">
-        <v>71.62999725341797</v>
+        <v>71.55000305175781</v>
       </c>
       <c r="C250" t="n">
-        <v>71.83999633789062</v>
+        <v>71.65000152587891</v>
       </c>
       <c r="D250" t="n">
-        <v>70.98000335693359</v>
+        <v>68.87999725341797</v>
       </c>
       <c r="E250" t="n">
-        <v>71.15000152587891</v>
+        <v>69.23000335693359</v>
       </c>
       <c r="F250" t="n">
-        <v>23203100</v>
+        <v>43366300</v>
       </c>
       <c r="G250" t="n">
         <v>0</v>
@@ -6943,22 +6943,22 @@
     </row>
     <row r="251">
       <c r="A251" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="B251" t="n">
-        <v>71.55000305175781</v>
+        <v>70.33000183105469</v>
       </c>
       <c r="C251" t="n">
-        <v>71.65000152587891</v>
+        <v>71.36000061035156</v>
       </c>
       <c r="D251" t="n">
-        <v>68.87999725341797</v>
+        <v>70.15000152587891</v>
       </c>
       <c r="E251" t="n">
-        <v>69.23000335693359</v>
+        <v>70.30000305175781</v>
       </c>
       <c r="F251" t="n">
-        <v>43366300</v>
+        <v>34550800</v>
       </c>
       <c r="G251" t="n">
         <v>0</v>
@@ -6969,22 +6969,22 @@
     </row>
     <row r="252">
       <c r="A252" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="B252" t="n">
-        <v>70.33000183105469</v>
+        <v>70.19999694824219</v>
       </c>
       <c r="C252" t="n">
-        <v>71.36000061035156</v>
+        <v>70.30000305175781</v>
       </c>
       <c r="D252" t="n">
-        <v>70.15000152587891</v>
+        <v>69.51000213623047</v>
       </c>
       <c r="E252" t="n">
-        <v>70.30000305175781</v>
+        <v>69.58000183105469</v>
       </c>
       <c r="F252" t="n">
-        <v>34497700</v>
+        <v>36350700</v>
       </c>
       <c r="G252" t="n">
         <v>0</v>
@@ -10434,37 +10434,37 @@
         </is>
       </c>
       <c r="C2" t="n">
+        <v>69.58</v>
+      </c>
+      <c r="D2" t="n">
         <v>70.3</v>
       </c>
-      <c r="D2" t="n">
-        <v>69.23</v>
-      </c>
       <c r="E2" t="n">
-        <v>70.39</v>
+        <v>70.13500000000001</v>
       </c>
       <c r="F2" t="n">
-        <v>71.34</v>
+        <v>70.3</v>
       </c>
       <c r="G2" t="n">
-        <v>70.15000000000001</v>
+        <v>69.51000000000001</v>
       </c>
       <c r="H2" t="n">
-        <v>33202113</v>
+        <v>34574416</v>
       </c>
       <c r="I2" t="n">
-        <v>37466298</v>
+        <v>37364324</v>
       </c>
       <c r="J2" t="n">
-        <v>292724965376</v>
+        <v>289726922752</v>
       </c>
       <c r="K2" t="n">
-        <v>21.764708</v>
+        <v>21.880503</v>
       </c>
       <c r="L2" t="n">
-        <v>18.439152</v>
+        <v>18.250301</v>
       </c>
       <c r="M2" t="n">
-        <v>3.23</v>
+        <v>3.18</v>
       </c>
       <c r="N2" t="n">
         <v>124.86</v>
@@ -10502,7 +10502,7 @@
         <v>7.241</v>
       </c>
       <c r="Y2" t="n">
-        <v>9.708603999999999</v>
+        <v>9.609170000000001</v>
       </c>
       <c r="Z2" t="n">
         <v>0.111</v>
@@ -10514,7 +10514,7 @@
         <v>48370765824</v>
       </c>
       <c r="AC2" t="n">
-        <v>300251709440</v>
+        <v>297253666816</v>
       </c>
       <c r="AD2" t="n">
         <v>14726931456</v>
@@ -10541,7 +10541,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>2026-09-30 16:07:29</t>
+          <t>2026-10-01 17:03:07</t>
         </is>
       </c>
     </row>

--- a/data/NFLX_data.xlsx
+++ b/data/NFLX_data.xlsx
@@ -469,22 +469,22 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45931</v>
+        <v>45932</v>
       </c>
       <c r="B2" t="n">
-        <v>117.5490036010742</v>
+        <v>116.1500015258789</v>
       </c>
       <c r="C2" t="n">
-        <v>117.9140014648438</v>
+        <v>116.3330001831055</v>
       </c>
       <c r="D2" t="n">
-        <v>116.3209991455078</v>
+        <v>113.4000015258789</v>
       </c>
       <c r="E2" t="n">
-        <v>117.0899963378906</v>
+        <v>116.2529983520508</v>
       </c>
       <c r="F2" t="n">
-        <v>41102000</v>
+        <v>46855000</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -495,22 +495,22 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45932</v>
+        <v>45933</v>
       </c>
       <c r="B3" t="n">
-        <v>116.1500015258789</v>
+        <v>116.5</v>
       </c>
       <c r="C3" t="n">
-        <v>116.3330001831055</v>
+        <v>116.8000030517578</v>
       </c>
       <c r="D3" t="n">
-        <v>113.4000015258789</v>
+        <v>114.3219985961914</v>
       </c>
       <c r="E3" t="n">
-        <v>116.2529983520508</v>
+        <v>115.3320007324219</v>
       </c>
       <c r="F3" t="n">
-        <v>46855000</v>
+        <v>31374000</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -521,22 +521,22 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>45933</v>
+        <v>45936</v>
       </c>
       <c r="B4" t="n">
-        <v>116.5</v>
+        <v>116.0370025634766</v>
       </c>
       <c r="C4" t="n">
-        <v>116.8000030517578</v>
+        <v>116.3580017089844</v>
       </c>
       <c r="D4" t="n">
-        <v>114.3219985961914</v>
+        <v>114.5449981689453</v>
       </c>
       <c r="E4" t="n">
-        <v>115.3320007324219</v>
+        <v>116.3310012817383</v>
       </c>
       <c r="F4" t="n">
-        <v>31374000</v>
+        <v>29686000</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -547,22 +547,22 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>45936</v>
+        <v>45937</v>
       </c>
       <c r="B5" t="n">
-        <v>116.0370025634766</v>
+        <v>117.7789993286133</v>
       </c>
       <c r="C5" t="n">
-        <v>116.3580017089844</v>
+        <v>120.1370010375977</v>
       </c>
       <c r="D5" t="n">
-        <v>114.5449981689453</v>
+        <v>117.7460021972656</v>
       </c>
       <c r="E5" t="n">
-        <v>116.3310012817383</v>
+        <v>119.1060028076172</v>
       </c>
       <c r="F5" t="n">
-        <v>29686000</v>
+        <v>33091000</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -573,22 +573,22 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>45937</v>
+        <v>45938</v>
       </c>
       <c r="B6" t="n">
-        <v>117.7789993286133</v>
+        <v>119.7109985351562</v>
       </c>
       <c r="C6" t="n">
-        <v>120.1370010375977</v>
+        <v>121.7389984130859</v>
       </c>
       <c r="D6" t="n">
-        <v>117.7460021972656</v>
+        <v>119.1999969482422</v>
       </c>
       <c r="E6" t="n">
-        <v>119.1060028076172</v>
+        <v>121.4250030517578</v>
       </c>
       <c r="F6" t="n">
-        <v>33091000</v>
+        <v>28514000</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -599,22 +599,22 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>45938</v>
+        <v>45939</v>
       </c>
       <c r="B7" t="n">
-        <v>119.7109985351562</v>
+        <v>121.4250030517578</v>
       </c>
       <c r="C7" t="n">
-        <v>121.7389984130859</v>
+        <v>123.75</v>
       </c>
       <c r="D7" t="n">
-        <v>119.1999969482422</v>
+        <v>121.181999206543</v>
       </c>
       <c r="E7" t="n">
-        <v>121.4250030517578</v>
+        <v>123.1070022583008</v>
       </c>
       <c r="F7" t="n">
-        <v>28514000</v>
+        <v>28241000</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -625,22 +625,22 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>45939</v>
+        <v>45940</v>
       </c>
       <c r="B8" t="n">
-        <v>121.4250030517578</v>
+        <v>122.9000015258789</v>
       </c>
       <c r="C8" t="n">
-        <v>123.75</v>
+        <v>124.6999969482422</v>
       </c>
       <c r="D8" t="n">
-        <v>121.181999206543</v>
+        <v>121.9100036621094</v>
       </c>
       <c r="E8" t="n">
-        <v>123.1070022583008</v>
+        <v>122.0080032348633</v>
       </c>
       <c r="F8" t="n">
-        <v>28241000</v>
+        <v>42798000</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -651,22 +651,22 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>45940</v>
+        <v>45943</v>
       </c>
       <c r="B9" t="n">
-        <v>122.9000015258789</v>
+        <v>122.1350021362305</v>
       </c>
       <c r="C9" t="n">
-        <v>124.6999969482422</v>
+        <v>123.1119995117188</v>
       </c>
       <c r="D9" t="n">
-        <v>121.9100036621094</v>
+        <v>120.6809997558594</v>
       </c>
       <c r="E9" t="n">
-        <v>122.0080032348633</v>
+        <v>121.9029998779297</v>
       </c>
       <c r="F9" t="n">
-        <v>42798000</v>
+        <v>24608000</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -677,22 +677,22 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>45943</v>
+        <v>45944</v>
       </c>
       <c r="B10" t="n">
-        <v>122.1350021362305</v>
+        <v>121.4749984741211</v>
       </c>
       <c r="C10" t="n">
-        <v>123.1119995117188</v>
+        <v>122.4290008544922</v>
       </c>
       <c r="D10" t="n">
-        <v>120.6809997558594</v>
+        <v>120.3099975585938</v>
       </c>
       <c r="E10" t="n">
-        <v>121.9029998779297</v>
+        <v>121.5350036621094</v>
       </c>
       <c r="F10" t="n">
-        <v>24608000</v>
+        <v>23624000</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -703,22 +703,22 @@
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>45944</v>
+        <v>45945</v>
       </c>
       <c r="B11" t="n">
-        <v>121.4749984741211</v>
+        <v>121.3010025024414</v>
       </c>
       <c r="C11" t="n">
-        <v>122.4290008544922</v>
+        <v>121.9619979858398</v>
       </c>
       <c r="D11" t="n">
-        <v>120.3099975585938</v>
+        <v>120.161003112793</v>
       </c>
       <c r="E11" t="n">
-        <v>121.5350036621094</v>
+        <v>120.3290023803711</v>
       </c>
       <c r="F11" t="n">
-        <v>23624000</v>
+        <v>20252000</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -729,22 +729,22 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>45945</v>
+        <v>45946</v>
       </c>
       <c r="B12" t="n">
-        <v>121.3010025024414</v>
+        <v>121.2149963378906</v>
       </c>
       <c r="C12" t="n">
-        <v>121.9619979858398</v>
+        <v>121.6709976196289</v>
       </c>
       <c r="D12" t="n">
-        <v>120.161003112793</v>
+        <v>117.5999984741211</v>
       </c>
       <c r="E12" t="n">
-        <v>120.3290023803711</v>
+        <v>118.359001159668</v>
       </c>
       <c r="F12" t="n">
-        <v>20252000</v>
+        <v>28326000</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -755,22 +755,22 @@
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>45946</v>
+        <v>45947</v>
       </c>
       <c r="B13" t="n">
-        <v>121.2149963378906</v>
+        <v>118.3600006103516</v>
       </c>
       <c r="C13" t="n">
-        <v>121.6709976196289</v>
+        <v>120.3119964599609</v>
       </c>
       <c r="D13" t="n">
-        <v>117.5999984741211</v>
+        <v>117.8949966430664</v>
       </c>
       <c r="E13" t="n">
-        <v>118.359001159668</v>
+        <v>119.9359970092773</v>
       </c>
       <c r="F13" t="n">
-        <v>28326000</v>
+        <v>29571000</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -781,22 +781,22 @@
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>45947</v>
+        <v>45950</v>
       </c>
       <c r="B14" t="n">
-        <v>118.3600006103516</v>
+        <v>120.7880020141602</v>
       </c>
       <c r="C14" t="n">
-        <v>120.3119964599609</v>
+        <v>124.7760009765625</v>
       </c>
       <c r="D14" t="n">
-        <v>117.8949966430664</v>
+        <v>120.6900024414062</v>
       </c>
       <c r="E14" t="n">
-        <v>119.9359970092773</v>
+        <v>123.8560028076172</v>
       </c>
       <c r="F14" t="n">
-        <v>29571000</v>
+        <v>39862000</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -807,22 +807,22 @@
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>45950</v>
+        <v>45951</v>
       </c>
       <c r="B15" t="n">
-        <v>120.7880020141602</v>
+        <v>124.2829971313477</v>
       </c>
       <c r="C15" t="n">
-        <v>124.7760009765625</v>
+        <v>124.8600006103516</v>
       </c>
       <c r="D15" t="n">
-        <v>120.6900024414062</v>
+        <v>123.1760025024414</v>
       </c>
       <c r="E15" t="n">
-        <v>123.8560028076172</v>
+        <v>124.1350021362305</v>
       </c>
       <c r="F15" t="n">
-        <v>39862000</v>
+        <v>65082000</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -833,22 +833,22 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>45951</v>
+        <v>45952</v>
       </c>
       <c r="B16" t="n">
-        <v>124.2829971313477</v>
+        <v>114.2900009155273</v>
       </c>
       <c r="C16" t="n">
-        <v>124.8600006103516</v>
+        <v>115.7600021362305</v>
       </c>
       <c r="D16" t="n">
-        <v>123.1760025024414</v>
+        <v>111.2509994506836</v>
       </c>
       <c r="E16" t="n">
-        <v>124.1350021362305</v>
+        <v>111.6370010375977</v>
       </c>
       <c r="F16" t="n">
-        <v>65082000</v>
+        <v>147890000</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -859,22 +859,22 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>45952</v>
+        <v>45953</v>
       </c>
       <c r="B17" t="n">
-        <v>114.2900009155273</v>
+        <v>112.6900024414062</v>
       </c>
       <c r="C17" t="n">
-        <v>115.7600021362305</v>
+        <v>112.7829971313477</v>
       </c>
       <c r="D17" t="n">
-        <v>111.2509994506836</v>
+        <v>109.9729995727539</v>
       </c>
       <c r="E17" t="n">
-        <v>111.6370010375977</v>
+        <v>111.359001159668</v>
       </c>
       <c r="F17" t="n">
-        <v>147890000</v>
+        <v>68497000</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -885,22 +885,22 @@
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>45953</v>
+        <v>45954</v>
       </c>
       <c r="B18" t="n">
-        <v>112.6900024414062</v>
+        <v>111.0999984741211</v>
       </c>
       <c r="C18" t="n">
-        <v>112.7829971313477</v>
+        <v>111.4509963989258</v>
       </c>
       <c r="D18" t="n">
-        <v>109.9729995727539</v>
+        <v>109.4410018920898</v>
       </c>
       <c r="E18" t="n">
-        <v>111.359001159668</v>
+        <v>109.4690017700195</v>
       </c>
       <c r="F18" t="n">
-        <v>68497000</v>
+        <v>60280000</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -911,22 +911,22 @@
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>45954</v>
+        <v>45957</v>
       </c>
       <c r="B19" t="n">
-        <v>111.0999984741211</v>
+        <v>110.0670013427734</v>
       </c>
       <c r="C19" t="n">
-        <v>111.4509963989258</v>
+        <v>110.2279968261719</v>
       </c>
       <c r="D19" t="n">
-        <v>109.4410018920898</v>
+        <v>108.7300033569336</v>
       </c>
       <c r="E19" t="n">
-        <v>109.4690017700195</v>
+        <v>109.4560012817383</v>
       </c>
       <c r="F19" t="n">
-        <v>60280000</v>
+        <v>46911000</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -937,22 +937,22 @@
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>45957</v>
+        <v>45958</v>
       </c>
       <c r="B20" t="n">
-        <v>110.0670013427734</v>
+        <v>109.4000015258789</v>
       </c>
       <c r="C20" t="n">
-        <v>110.2279968261719</v>
+        <v>111.697998046875</v>
       </c>
       <c r="D20" t="n">
-        <v>108.7300033569336</v>
+        <v>109.3010025024414</v>
       </c>
       <c r="E20" t="n">
-        <v>109.4560012817383</v>
+        <v>110.25</v>
       </c>
       <c r="F20" t="n">
-        <v>46911000</v>
+        <v>40209000</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -963,22 +963,22 @@
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>45958</v>
+        <v>45959</v>
       </c>
       <c r="B21" t="n">
-        <v>109.4000015258789</v>
+        <v>109.984001159668</v>
       </c>
       <c r="C21" t="n">
-        <v>111.697998046875</v>
+        <v>110.8550033569336</v>
       </c>
       <c r="D21" t="n">
-        <v>109.3010025024414</v>
+        <v>109.5999984741211</v>
       </c>
       <c r="E21" t="n">
-        <v>110.25</v>
+        <v>110.0410003662109</v>
       </c>
       <c r="F21" t="n">
-        <v>40209000</v>
+        <v>33995000</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -989,22 +989,22 @@
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>45959</v>
+        <v>45960</v>
       </c>
       <c r="B22" t="n">
-        <v>109.984001159668</v>
+        <v>109.4400024414062</v>
       </c>
       <c r="C22" t="n">
-        <v>110.8550033569336</v>
+        <v>110.6159973144531</v>
       </c>
       <c r="D22" t="n">
-        <v>109.5999984741211</v>
+        <v>108.8109970092773</v>
       </c>
       <c r="E22" t="n">
-        <v>110.0410003662109</v>
+        <v>108.9000015258789</v>
       </c>
       <c r="F22" t="n">
-        <v>33995000</v>
+        <v>41581000</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -1015,22 +1015,22 @@
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>45960</v>
+        <v>45961</v>
       </c>
       <c r="B23" t="n">
-        <v>109.4400024414062</v>
+        <v>110.5390014648438</v>
       </c>
       <c r="C23" t="n">
-        <v>110.6159973144531</v>
+        <v>113.4879989624023</v>
       </c>
       <c r="D23" t="n">
-        <v>108.8109970092773</v>
+        <v>110.197998046875</v>
       </c>
       <c r="E23" t="n">
-        <v>108.9000015258789</v>
+        <v>111.8860015869141</v>
       </c>
       <c r="F23" t="n">
-        <v>41581000</v>
+        <v>68665000</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -1041,22 +1041,22 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>45961</v>
+        <v>45964</v>
       </c>
       <c r="B24" t="n">
-        <v>110.5390014648438</v>
+        <v>113.3239974975586</v>
       </c>
       <c r="C24" t="n">
-        <v>113.4879989624023</v>
+        <v>113.3499984741211</v>
       </c>
       <c r="D24" t="n">
-        <v>110.197998046875</v>
+        <v>107.5149993896484</v>
       </c>
       <c r="E24" t="n">
-        <v>111.8860015869141</v>
+        <v>110.0090026855469</v>
       </c>
       <c r="F24" t="n">
-        <v>68665000</v>
+        <v>58634000</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -1067,22 +1067,22 @@
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>45964</v>
+        <v>45965</v>
       </c>
       <c r="B25" t="n">
-        <v>113.3239974975586</v>
+        <v>109.9990005493164</v>
       </c>
       <c r="C25" t="n">
-        <v>113.3499984741211</v>
+        <v>110.4599990844727</v>
       </c>
       <c r="D25" t="n">
-        <v>107.5149993896484</v>
+        <v>108.6679992675781</v>
       </c>
       <c r="E25" t="n">
-        <v>110.0090026855469</v>
+        <v>109.2959976196289</v>
       </c>
       <c r="F25" t="n">
-        <v>58634000</v>
+        <v>38718000</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -1093,22 +1093,22 @@
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>45965</v>
+        <v>45966</v>
       </c>
       <c r="B26" t="n">
-        <v>109.9990005493164</v>
+        <v>108.5</v>
       </c>
       <c r="C26" t="n">
-        <v>110.4599990844727</v>
+        <v>110.0849990844727</v>
       </c>
       <c r="D26" t="n">
-        <v>108.6679992675781</v>
+        <v>107.3369979858398</v>
       </c>
       <c r="E26" t="n">
-        <v>109.2959976196289</v>
+        <v>109.8460006713867</v>
       </c>
       <c r="F26" t="n">
-        <v>38718000</v>
+        <v>35539000</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -1119,22 +1119,22 @@
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>45966</v>
+        <v>45967</v>
       </c>
       <c r="B27" t="n">
-        <v>108.5</v>
+        <v>109.4580001831055</v>
       </c>
       <c r="C27" t="n">
-        <v>110.0849990844727</v>
+        <v>110.370002746582</v>
       </c>
       <c r="D27" t="n">
-        <v>107.3369979858398</v>
+        <v>108.5130004882812</v>
       </c>
       <c r="E27" t="n">
-        <v>109.8460006713867</v>
+        <v>109.7020034790039</v>
       </c>
       <c r="F27" t="n">
-        <v>35539000</v>
+        <v>36532000</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -1145,22 +1145,22 @@
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>45967</v>
+        <v>45968</v>
       </c>
       <c r="B28" t="n">
-        <v>109.4580001831055</v>
+        <v>109.4179992675781</v>
       </c>
       <c r="C28" t="n">
-        <v>110.370002746582</v>
+        <v>110.8219985961914</v>
       </c>
       <c r="D28" t="n">
-        <v>108.5130004882812</v>
+        <v>108.75</v>
       </c>
       <c r="E28" t="n">
-        <v>109.7020034790039</v>
+        <v>110.3659973144531</v>
       </c>
       <c r="F28" t="n">
-        <v>36532000</v>
+        <v>44125000</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
@@ -1171,22 +1171,22 @@
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>45968</v>
+        <v>45971</v>
       </c>
       <c r="B29" t="n">
-        <v>109.4179992675781</v>
+        <v>110.6719970703125</v>
       </c>
       <c r="C29" t="n">
-        <v>110.8219985961914</v>
+        <v>112.8199996948242</v>
       </c>
       <c r="D29" t="n">
-        <v>108.75</v>
+        <v>110.4049987792969</v>
       </c>
       <c r="E29" t="n">
-        <v>110.3659973144531</v>
+        <v>112.0070037841797</v>
       </c>
       <c r="F29" t="n">
-        <v>44125000</v>
+        <v>36929000</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -1197,22 +1197,22 @@
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>45971</v>
+        <v>45972</v>
       </c>
       <c r="B30" t="n">
-        <v>110.6719970703125</v>
+        <v>111.7600021362305</v>
       </c>
       <c r="C30" t="n">
-        <v>112.8199996948242</v>
+        <v>113.9219970703125</v>
       </c>
       <c r="D30" t="n">
-        <v>110.4049987792969</v>
+        <v>111.2799987792969</v>
       </c>
       <c r="E30" t="n">
-        <v>112.0070037841797</v>
+        <v>113.6439971923828</v>
       </c>
       <c r="F30" t="n">
-        <v>36929000</v>
+        <v>27966000</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -1223,22 +1223,22 @@
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>45972</v>
+        <v>45973</v>
       </c>
       <c r="B31" t="n">
-        <v>111.7600021362305</v>
+        <v>113.8170013427734</v>
       </c>
       <c r="C31" t="n">
-        <v>113.9219970703125</v>
+        <v>116.4339981079102</v>
       </c>
       <c r="D31" t="n">
-        <v>111.2799987792969</v>
+        <v>112.8259963989258</v>
       </c>
       <c r="E31" t="n">
-        <v>113.6439971923828</v>
+        <v>115.75</v>
       </c>
       <c r="F31" t="n">
-        <v>27966000</v>
+        <v>39221000</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -1249,22 +1249,22 @@
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>45973</v>
+        <v>45974</v>
       </c>
       <c r="B32" t="n">
-        <v>113.8170013427734</v>
+        <v>115.8499984741211</v>
       </c>
       <c r="C32" t="n">
-        <v>116.4339981079102</v>
+        <v>116.7330017089844</v>
       </c>
       <c r="D32" t="n">
-        <v>112.8259963989258</v>
+        <v>114.5690002441406</v>
       </c>
       <c r="E32" t="n">
-        <v>115.75</v>
+        <v>115.4229965209961</v>
       </c>
       <c r="F32" t="n">
-        <v>39221000</v>
+        <v>40144000</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
@@ -1275,22 +1275,22 @@
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>45974</v>
+        <v>45975</v>
       </c>
       <c r="B33" t="n">
-        <v>115.8499984741211</v>
+        <v>114.2730026245117</v>
       </c>
       <c r="C33" t="n">
-        <v>116.7330017089844</v>
+        <v>114.2730026245117</v>
       </c>
       <c r="D33" t="n">
-        <v>114.5690002441406</v>
+        <v>110.7210006713867</v>
       </c>
       <c r="E33" t="n">
-        <v>115.4229965209961</v>
+        <v>111.2170028686523</v>
       </c>
       <c r="F33" t="n">
-        <v>40144000</v>
+        <v>47607000</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -1301,74 +1301,74 @@
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>45975</v>
+        <v>45978</v>
       </c>
       <c r="B34" t="n">
-        <v>114.2730026245117</v>
+        <v>110.75</v>
       </c>
       <c r="C34" t="n">
-        <v>114.2730026245117</v>
+        <v>111.8499984741211</v>
       </c>
       <c r="D34" t="n">
-        <v>110.7210006713867</v>
+        <v>109.5500030517578</v>
       </c>
       <c r="E34" t="n">
-        <v>111.2170028686523</v>
+        <v>110.2900009155273</v>
       </c>
       <c r="F34" t="n">
-        <v>47607000</v>
+        <v>26082700</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>45978</v>
+        <v>45979</v>
       </c>
       <c r="B35" t="n">
-        <v>110.75</v>
+        <v>110.2900009155273</v>
       </c>
       <c r="C35" t="n">
-        <v>111.8499984741211</v>
+        <v>115.25</v>
       </c>
       <c r="D35" t="n">
-        <v>109.5500030517578</v>
+        <v>109.1999969482422</v>
       </c>
       <c r="E35" t="n">
-        <v>110.2900009155273</v>
+        <v>114.0899963378906</v>
       </c>
       <c r="F35" t="n">
-        <v>26082700</v>
+        <v>43440600</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>45979</v>
+        <v>45980</v>
       </c>
       <c r="B36" t="n">
-        <v>110.2900009155273</v>
+        <v>113</v>
       </c>
       <c r="C36" t="n">
-        <v>115.25</v>
+        <v>113.3399963378906</v>
       </c>
       <c r="D36" t="n">
-        <v>109.1999969482422</v>
+        <v>108.6100006103516</v>
       </c>
       <c r="E36" t="n">
-        <v>114.0899963378906</v>
+        <v>110</v>
       </c>
       <c r="F36" t="n">
-        <v>43440600</v>
+        <v>31868100</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -1379,22 +1379,22 @@
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>45980</v>
+        <v>45981</v>
       </c>
       <c r="B37" t="n">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C37" t="n">
-        <v>113.3399963378906</v>
+        <v>111.0999984741211</v>
       </c>
       <c r="D37" t="n">
-        <v>108.6100006103516</v>
+        <v>105.3899993896484</v>
       </c>
       <c r="E37" t="n">
-        <v>110</v>
+        <v>105.6699981689453</v>
       </c>
       <c r="F37" t="n">
-        <v>31868100</v>
+        <v>36918500</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
@@ -1405,22 +1405,22 @@
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>45981</v>
+        <v>45982</v>
       </c>
       <c r="B38" t="n">
-        <v>111</v>
+        <v>105.129997253418</v>
       </c>
       <c r="C38" t="n">
-        <v>111.0999984741211</v>
+        <v>106.5299987792969</v>
       </c>
       <c r="D38" t="n">
-        <v>105.3899993896484</v>
+        <v>103.8099975585938</v>
       </c>
       <c r="E38" t="n">
-        <v>105.6699981689453</v>
+        <v>104.3099975585938</v>
       </c>
       <c r="F38" t="n">
-        <v>36918500</v>
+        <v>41232700</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
@@ -1431,22 +1431,22 @@
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>45982</v>
+        <v>45985</v>
       </c>
       <c r="B39" t="n">
-        <v>105.129997253418</v>
+        <v>104.25</v>
       </c>
       <c r="C39" t="n">
-        <v>106.5299987792969</v>
+        <v>108.0400009155273</v>
       </c>
       <c r="D39" t="n">
-        <v>103.8099975585938</v>
+        <v>103.3199996948242</v>
       </c>
       <c r="E39" t="n">
-        <v>104.3099975585938</v>
+        <v>106.9700012207031</v>
       </c>
       <c r="F39" t="n">
-        <v>41232700</v>
+        <v>62918300</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
@@ -1457,22 +1457,22 @@
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>45985</v>
+        <v>45986</v>
       </c>
       <c r="B40" t="n">
-        <v>104.25</v>
+        <v>106.120002746582</v>
       </c>
       <c r="C40" t="n">
-        <v>108.0400009155273</v>
+        <v>106.3000030517578</v>
       </c>
       <c r="D40" t="n">
-        <v>103.3199996948242</v>
+        <v>103.8199996948242</v>
       </c>
       <c r="E40" t="n">
-        <v>106.9700012207031</v>
+        <v>104.4000015258789</v>
       </c>
       <c r="F40" t="n">
-        <v>62918300</v>
+        <v>35122600</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
@@ -1483,22 +1483,22 @@
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>45986</v>
+        <v>45987</v>
       </c>
       <c r="B41" t="n">
-        <v>106.120002746582</v>
+        <v>105.7399978637695</v>
       </c>
       <c r="C41" t="n">
-        <v>106.3000030517578</v>
+        <v>106.9499969482422</v>
       </c>
       <c r="D41" t="n">
-        <v>103.8199996948242</v>
+        <v>105.2200012207031</v>
       </c>
       <c r="E41" t="n">
-        <v>104.4000015258789</v>
+        <v>106.1399993896484</v>
       </c>
       <c r="F41" t="n">
-        <v>35122600</v>
+        <v>27951000</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
@@ -1509,22 +1509,22 @@
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>45987</v>
+        <v>45989</v>
       </c>
       <c r="B42" t="n">
-        <v>105.7399978637695</v>
+        <v>106.4400024414062</v>
       </c>
       <c r="C42" t="n">
-        <v>106.9499969482422</v>
+        <v>107.9400024414062</v>
       </c>
       <c r="D42" t="n">
-        <v>105.2200012207031</v>
+        <v>106.2399978637695</v>
       </c>
       <c r="E42" t="n">
-        <v>106.1399993896484</v>
+        <v>107.5800018310547</v>
       </c>
       <c r="F42" t="n">
-        <v>27951000</v>
+        <v>15021600</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
@@ -1535,22 +1535,22 @@
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>45989</v>
+        <v>45992</v>
       </c>
       <c r="B43" t="n">
-        <v>106.4400024414062</v>
+        <v>106.5100021362305</v>
       </c>
       <c r="C43" t="n">
-        <v>107.9400024414062</v>
+        <v>109.3399963378906</v>
       </c>
       <c r="D43" t="n">
-        <v>106.2399978637695</v>
+        <v>106.3099975585938</v>
       </c>
       <c r="E43" t="n">
-        <v>107.5800018310547</v>
+        <v>109.129997253418</v>
       </c>
       <c r="F43" t="n">
-        <v>15021600</v>
+        <v>24873400</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
@@ -1561,22 +1561,22 @@
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
-        <v>45992</v>
+        <v>45993</v>
       </c>
       <c r="B44" t="n">
-        <v>106.5100021362305</v>
+        <v>109.2099990844727</v>
       </c>
       <c r="C44" t="n">
-        <v>109.3399963378906</v>
+        <v>109.7300033569336</v>
       </c>
       <c r="D44" t="n">
-        <v>106.3099975585938</v>
+        <v>107.5199966430664</v>
       </c>
       <c r="E44" t="n">
-        <v>109.129997253418</v>
+        <v>109.3499984741211</v>
       </c>
       <c r="F44" t="n">
-        <v>24873400</v>
+        <v>25763000</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
@@ -1587,22 +1587,22 @@
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
-        <v>45993</v>
+        <v>45994</v>
       </c>
       <c r="B45" t="n">
-        <v>109.2099990844727</v>
+        <v>106.5899963378906</v>
       </c>
       <c r="C45" t="n">
-        <v>109.7300033569336</v>
+        <v>106.870002746582</v>
       </c>
       <c r="D45" t="n">
-        <v>107.5199966430664</v>
+        <v>102.0299987792969</v>
       </c>
       <c r="E45" t="n">
-        <v>109.3499984741211</v>
+        <v>103.9599990844727</v>
       </c>
       <c r="F45" t="n">
-        <v>25763000</v>
+        <v>53593400</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
@@ -1613,22 +1613,22 @@
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
-        <v>45994</v>
+        <v>45995</v>
       </c>
       <c r="B46" t="n">
-        <v>106.5899963378906</v>
+        <v>103.5699996948242</v>
       </c>
       <c r="C46" t="n">
-        <v>106.870002746582</v>
+        <v>103.8000030517578</v>
       </c>
       <c r="D46" t="n">
-        <v>102.0299987792969</v>
+        <v>101.7699966430664</v>
       </c>
       <c r="E46" t="n">
-        <v>103.9599990844727</v>
+        <v>103.2200012207031</v>
       </c>
       <c r="F46" t="n">
-        <v>53593400</v>
+        <v>51779100</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
@@ -1639,22 +1639,22 @@
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
-        <v>45995</v>
+        <v>45996</v>
       </c>
       <c r="B47" t="n">
-        <v>103.5699996948242</v>
+        <v>98.77999877929688</v>
       </c>
       <c r="C47" t="n">
-        <v>103.8000030517578</v>
+        <v>104.7900009155273</v>
       </c>
       <c r="D47" t="n">
-        <v>101.7699966430664</v>
+        <v>97.73999786376953</v>
       </c>
       <c r="E47" t="n">
-        <v>103.2200012207031</v>
+        <v>100.2399978637695</v>
       </c>
       <c r="F47" t="n">
-        <v>51779100</v>
+        <v>133363600</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
@@ -1665,22 +1665,22 @@
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
-        <v>45996</v>
+        <v>45999</v>
       </c>
       <c r="B48" t="n">
-        <v>98.77999877929688</v>
+        <v>99.87000274658203</v>
       </c>
       <c r="C48" t="n">
-        <v>104.7900009155273</v>
+        <v>99.88999938964844</v>
       </c>
       <c r="D48" t="n">
-        <v>97.73999786376953</v>
+        <v>95.30000305175781</v>
       </c>
       <c r="E48" t="n">
-        <v>100.2399978637695</v>
+        <v>96.79000091552734</v>
       </c>
       <c r="F48" t="n">
-        <v>133363600</v>
+        <v>100906300</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
@@ -1691,22 +1691,22 @@
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>45999</v>
+        <v>46000</v>
       </c>
       <c r="B49" t="n">
-        <v>99.87000274658203</v>
+        <v>97.02999877929688</v>
       </c>
       <c r="C49" t="n">
-        <v>99.88999938964844</v>
+        <v>97.23999786376953</v>
       </c>
       <c r="D49" t="n">
-        <v>95.30000305175781</v>
+        <v>95.44999694824219</v>
       </c>
       <c r="E49" t="n">
-        <v>96.79000091552734</v>
+        <v>96.70999908447266</v>
       </c>
       <c r="F49" t="n">
-        <v>100906300</v>
+        <v>51745600</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
@@ -1717,22 +1717,22 @@
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>46000</v>
+        <v>46001</v>
       </c>
       <c r="B50" t="n">
-        <v>97.02999877929688</v>
+        <v>96.73999786376953</v>
       </c>
       <c r="C50" t="n">
-        <v>97.23999786376953</v>
+        <v>96.97000122070312</v>
       </c>
       <c r="D50" t="n">
-        <v>95.44999694824219</v>
+        <v>92.34999847412109</v>
       </c>
       <c r="E50" t="n">
-        <v>96.70999908447266</v>
+        <v>92.70999908447266</v>
       </c>
       <c r="F50" t="n">
-        <v>51745600</v>
+        <v>74129300</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
-        <v>46001</v>
+        <v>46002</v>
       </c>
       <c r="B51" t="n">
-        <v>96.73999786376953</v>
+        <v>93.90000152587891</v>
       </c>
       <c r="C51" t="n">
-        <v>96.97000122070312</v>
+        <v>94.81999969482422</v>
       </c>
       <c r="D51" t="n">
-        <v>92.34999847412109</v>
+        <v>92.76000213623047</v>
       </c>
       <c r="E51" t="n">
-        <v>92.70999908447266</v>
+        <v>94.08999633789062</v>
       </c>
       <c r="F51" t="n">
-        <v>74129300</v>
+        <v>43949000</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
@@ -1769,22 +1769,22 @@
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
-        <v>46002</v>
+        <v>46003</v>
       </c>
       <c r="B52" t="n">
-        <v>93.90000152587891</v>
+        <v>95.5</v>
       </c>
       <c r="C52" t="n">
-        <v>94.81999969482422</v>
+        <v>96.91999816894531</v>
       </c>
       <c r="D52" t="n">
-        <v>92.76000213623047</v>
+        <v>94.65000152587891</v>
       </c>
       <c r="E52" t="n">
-        <v>94.08999633789062</v>
+        <v>95.19000244140625</v>
       </c>
       <c r="F52" t="n">
-        <v>43949000</v>
+        <v>49323100</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
@@ -1795,22 +1795,22 @@
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
-        <v>46003</v>
+        <v>46006</v>
       </c>
       <c r="B53" t="n">
-        <v>95.5</v>
+        <v>96.01999664306641</v>
       </c>
       <c r="C53" t="n">
-        <v>96.91999816894531</v>
+        <v>96.37000274658203</v>
       </c>
       <c r="D53" t="n">
-        <v>94.65000152587891</v>
+        <v>93.52999877929688</v>
       </c>
       <c r="E53" t="n">
-        <v>95.19000244140625</v>
+        <v>93.76999664306641</v>
       </c>
       <c r="F53" t="n">
-        <v>49323100</v>
+        <v>40016500</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
@@ -1821,22 +1821,22 @@
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
-        <v>46006</v>
+        <v>46007</v>
       </c>
       <c r="B54" t="n">
-        <v>96.01999664306641</v>
+        <v>93.87999725341797</v>
       </c>
       <c r="C54" t="n">
-        <v>96.37000274658203</v>
+        <v>94.93000030517578</v>
       </c>
       <c r="D54" t="n">
-        <v>93.52999877929688</v>
+        <v>93.31999969482422</v>
       </c>
       <c r="E54" t="n">
-        <v>93.76999664306641</v>
+        <v>94.56999969482422</v>
       </c>
       <c r="F54" t="n">
-        <v>40016500</v>
+        <v>34265000</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
@@ -1847,22 +1847,22 @@
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
-        <v>46007</v>
+        <v>46008</v>
       </c>
       <c r="B55" t="n">
-        <v>93.87999725341797</v>
+        <v>95.98000335693359</v>
       </c>
       <c r="C55" t="n">
-        <v>94.93000030517578</v>
+        <v>97.33000183105469</v>
       </c>
       <c r="D55" t="n">
-        <v>93.31999969482422</v>
+        <v>94.45999908447266</v>
       </c>
       <c r="E55" t="n">
-        <v>94.56999969482422</v>
+        <v>94.79000091552734</v>
       </c>
       <c r="F55" t="n">
-        <v>34265000</v>
+        <v>50472800</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
@@ -1873,22 +1873,22 @@
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
-        <v>46008</v>
+        <v>46009</v>
       </c>
       <c r="B56" t="n">
-        <v>95.98000335693359</v>
+        <v>95.01999664306641</v>
       </c>
       <c r="C56" t="n">
-        <v>97.33000183105469</v>
+        <v>95.80999755859375</v>
       </c>
       <c r="D56" t="n">
-        <v>94.45999908447266</v>
+        <v>93.58999633789062</v>
       </c>
       <c r="E56" t="n">
-        <v>94.79000091552734</v>
+        <v>94</v>
       </c>
       <c r="F56" t="n">
-        <v>50472800</v>
+        <v>37244700</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
@@ -1899,22 +1899,22 @@
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
-        <v>46009</v>
+        <v>46010</v>
       </c>
       <c r="B57" t="n">
-        <v>95.01999664306641</v>
+        <v>93.56999969482422</v>
       </c>
       <c r="C57" t="n">
-        <v>95.80999755859375</v>
+        <v>95.54000091552734</v>
       </c>
       <c r="D57" t="n">
-        <v>93.58999633789062</v>
+        <v>93.44999694824219</v>
       </c>
       <c r="E57" t="n">
-        <v>94</v>
+        <v>94.38999938964844</v>
       </c>
       <c r="F57" t="n">
-        <v>37244700</v>
+        <v>78990200</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
@@ -1925,22 +1925,22 @@
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
-        <v>46010</v>
+        <v>46013</v>
       </c>
       <c r="B58" t="n">
-        <v>93.56999969482422</v>
+        <v>94.70999908447266</v>
       </c>
       <c r="C58" t="n">
-        <v>95.54000091552734</v>
+        <v>94.70999908447266</v>
       </c>
       <c r="D58" t="n">
-        <v>93.44999694824219</v>
+        <v>92.91000366210938</v>
       </c>
       <c r="E58" t="n">
-        <v>94.38999938964844</v>
+        <v>93.23000335693359</v>
       </c>
       <c r="F58" t="n">
-        <v>78990200</v>
+        <v>39484800</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
@@ -1951,22 +1951,22 @@
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
-        <v>46013</v>
+        <v>46014</v>
       </c>
       <c r="B59" t="n">
-        <v>94.70999908447266</v>
+        <v>93.40000152587891</v>
       </c>
       <c r="C59" t="n">
-        <v>94.70999908447266</v>
+        <v>93.80999755859375</v>
       </c>
       <c r="D59" t="n">
-        <v>92.91000366210938</v>
+        <v>91.33000183105469</v>
       </c>
       <c r="E59" t="n">
-        <v>93.23000335693359</v>
+        <v>93.5</v>
       </c>
       <c r="F59" t="n">
-        <v>39484800</v>
+        <v>25896200</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
@@ -1977,22 +1977,22 @@
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
-        <v>46014</v>
+        <v>46015</v>
       </c>
       <c r="B60" t="n">
-        <v>93.40000152587891</v>
+        <v>93.11000061035156</v>
       </c>
       <c r="C60" t="n">
-        <v>93.80999755859375</v>
+        <v>93.68000030517578</v>
       </c>
       <c r="D60" t="n">
-        <v>91.33000183105469</v>
+        <v>92.66999816894531</v>
       </c>
       <c r="E60" t="n">
-        <v>93.5</v>
+        <v>93.63999938964844</v>
       </c>
       <c r="F60" t="n">
-        <v>25896200</v>
+        <v>12427900</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
@@ -2003,22 +2003,22 @@
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
-        <v>46015</v>
+        <v>46017</v>
       </c>
       <c r="B61" t="n">
-        <v>93.11000061035156</v>
+        <v>93.48000335693359</v>
       </c>
       <c r="C61" t="n">
-        <v>93.68000030517578</v>
+        <v>94.69000244140625</v>
       </c>
       <c r="D61" t="n">
-        <v>92.66999816894531</v>
+        <v>93.26999664306641</v>
       </c>
       <c r="E61" t="n">
-        <v>93.63999938964844</v>
+        <v>94.47000122070312</v>
       </c>
       <c r="F61" t="n">
-        <v>12427900</v>
+        <v>22068300</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
@@ -2029,22 +2029,22 @@
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
-        <v>46017</v>
+        <v>46020</v>
       </c>
       <c r="B62" t="n">
-        <v>93.48000335693359</v>
+        <v>93.98999786376953</v>
       </c>
       <c r="C62" t="n">
-        <v>94.69000244140625</v>
+        <v>94.97000122070312</v>
       </c>
       <c r="D62" t="n">
-        <v>93.26999664306641</v>
+        <v>93.62999725341797</v>
       </c>
       <c r="E62" t="n">
-        <v>94.47000122070312</v>
+        <v>94.15000152587891</v>
       </c>
       <c r="F62" t="n">
-        <v>22068300</v>
+        <v>24493700</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
@@ -2055,22 +2055,22 @@
     </row>
     <row r="63">
       <c r="A63" s="1" t="n">
-        <v>46020</v>
+        <v>46021</v>
       </c>
       <c r="B63" t="n">
+        <v>93.51999664306641</v>
+      </c>
+      <c r="C63" t="n">
         <v>93.98999786376953</v>
       </c>
-      <c r="C63" t="n">
-        <v>94.97000122070312</v>
-      </c>
       <c r="D63" t="n">
-        <v>93.62999725341797</v>
+        <v>93.33999633789062</v>
       </c>
       <c r="E63" t="n">
-        <v>94.15000152587891</v>
+        <v>93.77999877929688</v>
       </c>
       <c r="F63" t="n">
-        <v>24493700</v>
+        <v>23422000</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
@@ -2081,22 +2081,22 @@
     </row>
     <row r="64">
       <c r="A64" s="1" t="n">
-        <v>46021</v>
+        <v>46022</v>
       </c>
       <c r="B64" t="n">
-        <v>93.51999664306641</v>
+        <v>93.59999847412109</v>
       </c>
       <c r="C64" t="n">
-        <v>93.98999786376953</v>
+        <v>94.30999755859375</v>
       </c>
       <c r="D64" t="n">
-        <v>93.33999633789062</v>
+        <v>93.19999694824219</v>
       </c>
       <c r="E64" t="n">
-        <v>93.77999877929688</v>
+        <v>93.76000213623047</v>
       </c>
       <c r="F64" t="n">
-        <v>23422000</v>
+        <v>23495200</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
@@ -2107,22 +2107,22 @@
     </row>
     <row r="65">
       <c r="A65" s="1" t="n">
-        <v>46022</v>
+        <v>46024</v>
       </c>
       <c r="B65" t="n">
-        <v>93.59999847412109</v>
+        <v>94.12999725341797</v>
       </c>
       <c r="C65" t="n">
-        <v>94.30999755859375</v>
+        <v>94.12999725341797</v>
       </c>
       <c r="D65" t="n">
-        <v>93.19999694824219</v>
+        <v>90.80999755859375</v>
       </c>
       <c r="E65" t="n">
-        <v>93.76000213623047</v>
+        <v>90.98999786376953</v>
       </c>
       <c r="F65" t="n">
-        <v>23495200</v>
+        <v>41155400</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
@@ -2133,22 +2133,22 @@
     </row>
     <row r="66">
       <c r="A66" s="1" t="n">
-        <v>46024</v>
+        <v>46027</v>
       </c>
       <c r="B66" t="n">
-        <v>94.12999725341797</v>
+        <v>90.91999816894531</v>
       </c>
       <c r="C66" t="n">
-        <v>94.12999725341797</v>
+        <v>92.62999725341797</v>
       </c>
       <c r="D66" t="n">
-        <v>90.80999755859375</v>
+        <v>90.83999633789062</v>
       </c>
       <c r="E66" t="n">
-        <v>90.98999786376953</v>
+        <v>91.45999908447266</v>
       </c>
       <c r="F66" t="n">
-        <v>41155400</v>
+        <v>39183300</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
@@ -2159,22 +2159,22 @@
     </row>
     <row r="67">
       <c r="A67" s="1" t="n">
-        <v>46027</v>
+        <v>46028</v>
       </c>
       <c r="B67" t="n">
-        <v>90.91999816894531</v>
+        <v>91.54000091552734</v>
       </c>
       <c r="C67" t="n">
-        <v>92.62999725341797</v>
+        <v>91.63999938964844</v>
       </c>
       <c r="D67" t="n">
-        <v>90.83999633789062</v>
+        <v>89.73999786376953</v>
       </c>
       <c r="E67" t="n">
-        <v>91.45999908447266</v>
+        <v>90.65000152587891</v>
       </c>
       <c r="F67" t="n">
-        <v>39183300</v>
+        <v>43331000</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
@@ -2185,22 +2185,22 @@
     </row>
     <row r="68">
       <c r="A68" s="1" t="n">
-        <v>46028</v>
+        <v>46029</v>
       </c>
       <c r="B68" t="n">
-        <v>91.54000091552734</v>
+        <v>91.55999755859375</v>
       </c>
       <c r="C68" t="n">
-        <v>91.63999938964844</v>
+        <v>92.41999816894531</v>
       </c>
       <c r="D68" t="n">
-        <v>89.73999786376953</v>
+        <v>90.05999755859375</v>
       </c>
       <c r="E68" t="n">
-        <v>90.65000152587891</v>
+        <v>90.73000335693359</v>
       </c>
       <c r="F68" t="n">
-        <v>43331000</v>
+        <v>36525700</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
@@ -2211,22 +2211,22 @@
     </row>
     <row r="69">
       <c r="A69" s="1" t="n">
-        <v>46029</v>
+        <v>46030</v>
       </c>
       <c r="B69" t="n">
-        <v>91.55999755859375</v>
+        <v>90.44999694824219</v>
       </c>
       <c r="C69" t="n">
-        <v>92.41999816894531</v>
+        <v>91.25</v>
       </c>
       <c r="D69" t="n">
-        <v>90.05999755859375</v>
+        <v>89.58000183105469</v>
       </c>
       <c r="E69" t="n">
-        <v>90.73000335693359</v>
+        <v>90.52999877929688</v>
       </c>
       <c r="F69" t="n">
-        <v>36525700</v>
+        <v>40068700</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
@@ -2237,22 +2237,22 @@
     </row>
     <row r="70">
       <c r="A70" s="1" t="n">
-        <v>46030</v>
+        <v>46031</v>
       </c>
       <c r="B70" t="n">
-        <v>90.44999694824219</v>
+        <v>90.02999877929688</v>
       </c>
       <c r="C70" t="n">
-        <v>91.25</v>
+        <v>90.05000305175781</v>
       </c>
       <c r="D70" t="n">
-        <v>89.58000183105469</v>
+        <v>88.31999969482422</v>
       </c>
       <c r="E70" t="n">
-        <v>90.52999877929688</v>
+        <v>89.45999908447266</v>
       </c>
       <c r="F70" t="n">
-        <v>40068700</v>
+        <v>55579500</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
@@ -2263,22 +2263,22 @@
     </row>
     <row r="71">
       <c r="A71" s="1" t="n">
-        <v>46031</v>
+        <v>46034</v>
       </c>
       <c r="B71" t="n">
-        <v>90.02999877929688</v>
+        <v>89.69000244140625</v>
       </c>
       <c r="C71" t="n">
-        <v>90.05000305175781</v>
+        <v>90.33999633789062</v>
       </c>
       <c r="D71" t="n">
-        <v>88.31999969482422</v>
+        <v>89.33000183105469</v>
       </c>
       <c r="E71" t="n">
-        <v>89.45999908447266</v>
+        <v>89.41000366210938</v>
       </c>
       <c r="F71" t="n">
-        <v>55579500</v>
+        <v>36290600</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
@@ -2289,22 +2289,22 @@
     </row>
     <row r="72">
       <c r="A72" s="1" t="n">
-        <v>46034</v>
+        <v>46035</v>
       </c>
       <c r="B72" t="n">
-        <v>89.69000244140625</v>
+        <v>89.44000244140625</v>
       </c>
       <c r="C72" t="n">
-        <v>90.33999633789062</v>
+        <v>91.15000152587891</v>
       </c>
       <c r="D72" t="n">
-        <v>89.33000183105469</v>
+        <v>89.06999969482422</v>
       </c>
       <c r="E72" t="n">
-        <v>89.41000366210938</v>
+        <v>90.31999969482422</v>
       </c>
       <c r="F72" t="n">
-        <v>36290600</v>
+        <v>45221100</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
@@ -2315,22 +2315,22 @@
     </row>
     <row r="73">
       <c r="A73" s="1" t="n">
-        <v>46035</v>
+        <v>46036</v>
       </c>
       <c r="B73" t="n">
-        <v>89.44000244140625</v>
+        <v>91.23999786376953</v>
       </c>
       <c r="C73" t="n">
-        <v>91.15000152587891</v>
+        <v>91.58000183105469</v>
       </c>
       <c r="D73" t="n">
-        <v>89.06999969482422</v>
+        <v>87.94999694824219</v>
       </c>
       <c r="E73" t="n">
-        <v>90.31999969482422</v>
+        <v>88.55000305175781</v>
       </c>
       <c r="F73" t="n">
-        <v>45221100</v>
+        <v>49737700</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
@@ -2341,22 +2341,22 @@
     </row>
     <row r="74">
       <c r="A74" s="1" t="n">
-        <v>46036</v>
+        <v>46037</v>
       </c>
       <c r="B74" t="n">
-        <v>91.23999786376953</v>
+        <v>89.01999664306641</v>
       </c>
       <c r="C74" t="n">
-        <v>91.58000183105469</v>
+        <v>89.88999938964844</v>
       </c>
       <c r="D74" t="n">
-        <v>87.94999694824219</v>
+        <v>87.81999969482422</v>
       </c>
       <c r="E74" t="n">
-        <v>88.55000305175781</v>
+        <v>88.05000305175781</v>
       </c>
       <c r="F74" t="n">
-        <v>49737700</v>
+        <v>36945100</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
@@ -2367,22 +2367,22 @@
     </row>
     <row r="75">
       <c r="A75" s="1" t="n">
-        <v>46037</v>
+        <v>46038</v>
       </c>
       <c r="B75" t="n">
-        <v>89.01999664306641</v>
+        <v>88.33999633789062</v>
       </c>
       <c r="C75" t="n">
-        <v>89.88999938964844</v>
+        <v>88.51000213623047</v>
       </c>
       <c r="D75" t="n">
-        <v>87.81999969482422</v>
+        <v>87.77999877929688</v>
       </c>
       <c r="E75" t="n">
-        <v>88.05000305175781</v>
+        <v>88</v>
       </c>
       <c r="F75" t="n">
-        <v>36945100</v>
+        <v>48130500</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
@@ -2393,22 +2393,22 @@
     </row>
     <row r="76">
       <c r="A76" s="1" t="n">
-        <v>46038</v>
+        <v>46042</v>
       </c>
       <c r="B76" t="n">
-        <v>88.33999633789062</v>
+        <v>88.97000122070312</v>
       </c>
       <c r="C76" t="n">
-        <v>88.51000213623047</v>
+        <v>89.90000152587891</v>
       </c>
       <c r="D76" t="n">
-        <v>87.77999877929688</v>
+        <v>87.01999664306641</v>
       </c>
       <c r="E76" t="n">
-        <v>88</v>
+        <v>87.26000213623047</v>
       </c>
       <c r="F76" t="n">
-        <v>48130500</v>
+        <v>109729700</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
@@ -2419,22 +2419,22 @@
     </row>
     <row r="77">
       <c r="A77" s="1" t="n">
-        <v>46042</v>
+        <v>46043</v>
       </c>
       <c r="B77" t="n">
-        <v>88.97000122070312</v>
+        <v>82.51999664306641</v>
       </c>
       <c r="C77" t="n">
-        <v>89.90000152587891</v>
+        <v>86</v>
       </c>
       <c r="D77" t="n">
-        <v>87.01999664306641</v>
+        <v>81.93000030517578</v>
       </c>
       <c r="E77" t="n">
-        <v>87.26000213623047</v>
+        <v>85.36000061035156</v>
       </c>
       <c r="F77" t="n">
-        <v>109729700</v>
+        <v>127940700</v>
       </c>
       <c r="G77" t="n">
         <v>0</v>
@@ -2445,22 +2445,22 @@
     </row>
     <row r="78">
       <c r="A78" s="1" t="n">
-        <v>46043</v>
+        <v>46044</v>
       </c>
       <c r="B78" t="n">
-        <v>82.51999664306641</v>
+        <v>85.01999664306641</v>
       </c>
       <c r="C78" t="n">
-        <v>86</v>
+        <v>85.09999847412109</v>
       </c>
       <c r="D78" t="n">
-        <v>81.93000030517578</v>
+        <v>82.98000335693359</v>
       </c>
       <c r="E78" t="n">
-        <v>85.36000061035156</v>
+        <v>83.54000091552734</v>
       </c>
       <c r="F78" t="n">
-        <v>127940700</v>
+        <v>69113300</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
@@ -2471,22 +2471,22 @@
     </row>
     <row r="79">
       <c r="A79" s="1" t="n">
-        <v>46044</v>
+        <v>46045</v>
       </c>
       <c r="B79" t="n">
-        <v>85.01999664306641</v>
+        <v>83.43000030517578</v>
       </c>
       <c r="C79" t="n">
-        <v>85.09999847412109</v>
+        <v>86.30000305175781</v>
       </c>
       <c r="D79" t="n">
-        <v>82.98000335693359</v>
+        <v>83.27999877929688</v>
       </c>
       <c r="E79" t="n">
-        <v>83.54000091552734</v>
+        <v>86.12000274658203</v>
       </c>
       <c r="F79" t="n">
-        <v>69113300</v>
+        <v>64520400</v>
       </c>
       <c r="G79" t="n">
         <v>0</v>
@@ -2497,22 +2497,22 @@
     </row>
     <row r="80">
       <c r="A80" s="1" t="n">
-        <v>46045</v>
+        <v>46048</v>
       </c>
       <c r="B80" t="n">
-        <v>83.43000030517578</v>
+        <v>86.91999816894531</v>
       </c>
       <c r="C80" t="n">
-        <v>86.30000305175781</v>
+        <v>86.94000244140625</v>
       </c>
       <c r="D80" t="n">
-        <v>83.27999877929688</v>
+        <v>85.34999847412109</v>
       </c>
       <c r="E80" t="n">
-        <v>86.12000274658203</v>
+        <v>85.69999694824219</v>
       </c>
       <c r="F80" t="n">
-        <v>64520400</v>
+        <v>40941900</v>
       </c>
       <c r="G80" t="n">
         <v>0</v>
@@ -2523,22 +2523,22 @@
     </row>
     <row r="81">
       <c r="A81" s="1" t="n">
-        <v>46048</v>
+        <v>46049</v>
       </c>
       <c r="B81" t="n">
-        <v>86.91999816894531</v>
+        <v>85.27999877929688</v>
       </c>
       <c r="C81" t="n">
-        <v>86.94000244140625</v>
+        <v>85.59999847412109</v>
       </c>
       <c r="D81" t="n">
-        <v>85.34999847412109</v>
+        <v>83.87999725341797</v>
       </c>
       <c r="E81" t="n">
-        <v>85.69999694824219</v>
+        <v>85.58000183105469</v>
       </c>
       <c r="F81" t="n">
-        <v>40941900</v>
+        <v>37790800</v>
       </c>
       <c r="G81" t="n">
         <v>0</v>
@@ -2549,22 +2549,22 @@
     </row>
     <row r="82">
       <c r="A82" s="1" t="n">
-        <v>46049</v>
+        <v>46050</v>
       </c>
       <c r="B82" t="n">
-        <v>85.27999877929688</v>
+        <v>85.62999725341797</v>
       </c>
       <c r="C82" t="n">
-        <v>85.59999847412109</v>
+        <v>86.47000122070312</v>
       </c>
       <c r="D82" t="n">
-        <v>83.87999725341797</v>
+        <v>84.30000305175781</v>
       </c>
       <c r="E82" t="n">
-        <v>85.58000183105469</v>
+        <v>84.63999938964844</v>
       </c>
       <c r="F82" t="n">
-        <v>37790800</v>
+        <v>37762600</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
@@ -2575,22 +2575,22 @@
     </row>
     <row r="83">
       <c r="A83" s="1" t="n">
-        <v>46050</v>
+        <v>46051</v>
       </c>
       <c r="B83" t="n">
-        <v>85.62999725341797</v>
+        <v>84.30999755859375</v>
       </c>
       <c r="C83" t="n">
-        <v>86.47000122070312</v>
+        <v>84.37999725341797</v>
       </c>
       <c r="D83" t="n">
-        <v>84.30000305175781</v>
+        <v>82.34999847412109</v>
       </c>
       <c r="E83" t="n">
-        <v>84.63999938964844</v>
+        <v>83.16000366210938</v>
       </c>
       <c r="F83" t="n">
-        <v>37762600</v>
+        <v>42278100</v>
       </c>
       <c r="G83" t="n">
         <v>0</v>
@@ -2601,22 +2601,22 @@
     </row>
     <row r="84">
       <c r="A84" s="1" t="n">
-        <v>46051</v>
+        <v>46052</v>
       </c>
       <c r="B84" t="n">
-        <v>84.30999755859375</v>
+        <v>83.09999847412109</v>
       </c>
       <c r="C84" t="n">
-        <v>84.37999725341797</v>
+        <v>84.05999755859375</v>
       </c>
       <c r="D84" t="n">
-        <v>82.34999847412109</v>
+        <v>82.77999877929688</v>
       </c>
       <c r="E84" t="n">
-        <v>83.16000366210938</v>
+        <v>83.48999786376953</v>
       </c>
       <c r="F84" t="n">
-        <v>42278100</v>
+        <v>45755000</v>
       </c>
       <c r="G84" t="n">
         <v>0</v>
@@ -2627,22 +2627,22 @@
     </row>
     <row r="85">
       <c r="A85" s="1" t="n">
-        <v>46052</v>
+        <v>46055</v>
       </c>
       <c r="B85" t="n">
-        <v>83.09999847412109</v>
+        <v>83.52999877929688</v>
       </c>
       <c r="C85" t="n">
-        <v>84.05999755859375</v>
+        <v>85.26999664306641</v>
       </c>
       <c r="D85" t="n">
-        <v>82.77999877929688</v>
+        <v>82.72000122070312</v>
       </c>
       <c r="E85" t="n">
-        <v>83.48999786376953</v>
+        <v>82.76000213623047</v>
       </c>
       <c r="F85" t="n">
-        <v>45755000</v>
+        <v>41445300</v>
       </c>
       <c r="G85" t="n">
         <v>0</v>
@@ -2653,22 +2653,22 @@
     </row>
     <row r="86">
       <c r="A86" s="1" t="n">
-        <v>46055</v>
+        <v>46056</v>
       </c>
       <c r="B86" t="n">
-        <v>83.52999877929688</v>
+        <v>82.23000335693359</v>
       </c>
       <c r="C86" t="n">
-        <v>85.26999664306641</v>
+        <v>82.44999694824219</v>
       </c>
       <c r="D86" t="n">
-        <v>82.72000122070312</v>
+        <v>79.62000274658203</v>
       </c>
       <c r="E86" t="n">
-        <v>82.76000213623047</v>
+        <v>79.94000244140625</v>
       </c>
       <c r="F86" t="n">
-        <v>41445300</v>
+        <v>49789000</v>
       </c>
       <c r="G86" t="n">
         <v>0</v>
@@ -2679,22 +2679,22 @@
     </row>
     <row r="87">
       <c r="A87" s="1" t="n">
-        <v>46056</v>
+        <v>46057</v>
       </c>
       <c r="B87" t="n">
-        <v>82.23000335693359</v>
+        <v>79.98999786376953</v>
       </c>
       <c r="C87" t="n">
-        <v>82.44999694824219</v>
+        <v>81.44000244140625</v>
       </c>
       <c r="D87" t="n">
-        <v>79.62000274658203</v>
+        <v>79.23000335693359</v>
       </c>
       <c r="E87" t="n">
-        <v>79.94000244140625</v>
+        <v>80.16000366210938</v>
       </c>
       <c r="F87" t="n">
-        <v>49789000</v>
+        <v>48963200</v>
       </c>
       <c r="G87" t="n">
         <v>0</v>
@@ -2705,22 +2705,22 @@
     </row>
     <row r="88">
       <c r="A88" s="1" t="n">
-        <v>46057</v>
+        <v>46058</v>
       </c>
       <c r="B88" t="n">
-        <v>79.98999786376953</v>
+        <v>81.48999786376953</v>
       </c>
       <c r="C88" t="n">
-        <v>81.44000244140625</v>
+        <v>83.30000305175781</v>
       </c>
       <c r="D88" t="n">
-        <v>79.23000335693359</v>
+        <v>80.54000091552734</v>
       </c>
       <c r="E88" t="n">
-        <v>80.16000366210938</v>
+        <v>80.87000274658203</v>
       </c>
       <c r="F88" t="n">
-        <v>48963200</v>
+        <v>54805700</v>
       </c>
       <c r="G88" t="n">
         <v>0</v>
@@ -2731,22 +2731,22 @@
     </row>
     <row r="89">
       <c r="A89" s="1" t="n">
-        <v>46058</v>
+        <v>46059</v>
       </c>
       <c r="B89" t="n">
-        <v>81.48999786376953</v>
+        <v>81.01999664306641</v>
       </c>
       <c r="C89" t="n">
-        <v>83.30000305175781</v>
+        <v>82.48999786376953</v>
       </c>
       <c r="D89" t="n">
-        <v>80.54000091552734</v>
+        <v>80.65000152587891</v>
       </c>
       <c r="E89" t="n">
-        <v>80.87000274658203</v>
+        <v>82.19999694824219</v>
       </c>
       <c r="F89" t="n">
-        <v>54805700</v>
+        <v>46154100</v>
       </c>
       <c r="G89" t="n">
         <v>0</v>
@@ -2757,22 +2757,22 @@
     </row>
     <row r="90">
       <c r="A90" s="1" t="n">
-        <v>46059</v>
+        <v>46062</v>
       </c>
       <c r="B90" t="n">
-        <v>81.01999664306641</v>
+        <v>82.18000030517578</v>
       </c>
       <c r="C90" t="n">
-        <v>82.48999786376953</v>
+        <v>82.20999908447266</v>
       </c>
       <c r="D90" t="n">
-        <v>80.65000152587891</v>
+        <v>79.87000274658203</v>
       </c>
       <c r="E90" t="n">
-        <v>82.19999694824219</v>
+        <v>81.47000122070312</v>
       </c>
       <c r="F90" t="n">
-        <v>46154100</v>
+        <v>42200200</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
@@ -2783,22 +2783,22 @@
     </row>
     <row r="91">
       <c r="A91" s="1" t="n">
-        <v>46062</v>
+        <v>46063</v>
       </c>
       <c r="B91" t="n">
-        <v>82.18000030517578</v>
+        <v>82.72000122070312</v>
       </c>
       <c r="C91" t="n">
+        <v>84.66000366210938</v>
+      </c>
+      <c r="D91" t="n">
+        <v>82.08999633789062</v>
+      </c>
+      <c r="E91" t="n">
         <v>82.20999908447266</v>
       </c>
-      <c r="D91" t="n">
-        <v>79.87000274658203</v>
-      </c>
-      <c r="E91" t="n">
-        <v>81.47000122070312</v>
-      </c>
       <c r="F91" t="n">
-        <v>42200200</v>
+        <v>43595800</v>
       </c>
       <c r="G91" t="n">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="92">
       <c r="A92" s="1" t="n">
-        <v>46063</v>
+        <v>46064</v>
       </c>
       <c r="B92" t="n">
-        <v>82.72000122070312</v>
+        <v>81.95999908447266</v>
       </c>
       <c r="C92" t="n">
-        <v>84.66000366210938</v>
+        <v>82.48000335693359</v>
       </c>
       <c r="D92" t="n">
-        <v>82.08999633789062</v>
+        <v>79.44999694824219</v>
       </c>
       <c r="E92" t="n">
-        <v>82.20999908447266</v>
+        <v>79.62000274658203</v>
       </c>
       <c r="F92" t="n">
-        <v>43595800</v>
+        <v>40840300</v>
       </c>
       <c r="G92" t="n">
         <v>0</v>
@@ -2835,22 +2835,22 @@
     </row>
     <row r="93">
       <c r="A93" s="1" t="n">
-        <v>46064</v>
+        <v>46065</v>
       </c>
       <c r="B93" t="n">
-        <v>81.95999908447266</v>
+        <v>79.11000061035156</v>
       </c>
       <c r="C93" t="n">
-        <v>82.48000335693359</v>
+        <v>79.15000152587891</v>
       </c>
       <c r="D93" t="n">
-        <v>79.44999694824219</v>
+        <v>75.23000335693359</v>
       </c>
       <c r="E93" t="n">
-        <v>79.62000274658203</v>
+        <v>75.86000061035156</v>
       </c>
       <c r="F93" t="n">
-        <v>40840300</v>
+        <v>73516100</v>
       </c>
       <c r="G93" t="n">
         <v>0</v>
@@ -2861,22 +2861,22 @@
     </row>
     <row r="94">
       <c r="A94" s="1" t="n">
-        <v>46065</v>
+        <v>46066</v>
       </c>
       <c r="B94" t="n">
-        <v>79.11000061035156</v>
+        <v>76.13999938964844</v>
       </c>
       <c r="C94" t="n">
-        <v>79.15000152587891</v>
+        <v>77.18000030517578</v>
       </c>
       <c r="D94" t="n">
-        <v>75.23000335693359</v>
+        <v>75.52999877929688</v>
       </c>
       <c r="E94" t="n">
-        <v>75.86000061035156</v>
+        <v>76.87000274658203</v>
       </c>
       <c r="F94" t="n">
-        <v>73516100</v>
+        <v>42292100</v>
       </c>
       <c r="G94" t="n">
         <v>0</v>
@@ -2887,22 +2887,22 @@
     </row>
     <row r="95">
       <c r="A95" s="1" t="n">
-        <v>46066</v>
+        <v>46070</v>
       </c>
       <c r="B95" t="n">
-        <v>76.13999938964844</v>
+        <v>76.91999816894531</v>
       </c>
       <c r="C95" t="n">
-        <v>77.18000030517578</v>
+        <v>77.87000274658203</v>
       </c>
       <c r="D95" t="n">
-        <v>75.52999877929688</v>
+        <v>75.30000305175781</v>
       </c>
       <c r="E95" t="n">
-        <v>76.87000274658203</v>
+        <v>77</v>
       </c>
       <c r="F95" t="n">
-        <v>42292100</v>
+        <v>35961500</v>
       </c>
       <c r="G95" t="n">
         <v>0</v>
@@ -2913,22 +2913,22 @@
     </row>
     <row r="96">
       <c r="A96" s="1" t="n">
-        <v>46070</v>
+        <v>46071</v>
       </c>
       <c r="B96" t="n">
-        <v>76.91999816894531</v>
+        <v>77.31999969482422</v>
       </c>
       <c r="C96" t="n">
-        <v>77.87000274658203</v>
+        <v>78.31999969482422</v>
       </c>
       <c r="D96" t="n">
-        <v>75.30000305175781</v>
+        <v>76.27999877929688</v>
       </c>
       <c r="E96" t="n">
-        <v>77</v>
+        <v>77.98999786376953</v>
       </c>
       <c r="F96" t="n">
-        <v>35961500</v>
+        <v>29883100</v>
       </c>
       <c r="G96" t="n">
         <v>0</v>
@@ -2939,22 +2939,22 @@
     </row>
     <row r="97">
       <c r="A97" s="1" t="n">
-        <v>46071</v>
+        <v>46072</v>
       </c>
       <c r="B97" t="n">
-        <v>77.31999969482422</v>
+        <v>77.75</v>
       </c>
       <c r="C97" t="n">
-        <v>78.31999969482422</v>
+        <v>78.69999694824219</v>
       </c>
       <c r="D97" t="n">
-        <v>76.27999877929688</v>
+        <v>76.58999633789062</v>
       </c>
       <c r="E97" t="n">
-        <v>77.98999786376953</v>
+        <v>77</v>
       </c>
       <c r="F97" t="n">
-        <v>29883100</v>
+        <v>30139200</v>
       </c>
       <c r="G97" t="n">
         <v>0</v>
@@ -2965,22 +2965,22 @@
     </row>
     <row r="98">
       <c r="A98" s="1" t="n">
-        <v>46072</v>
+        <v>46073</v>
       </c>
       <c r="B98" t="n">
-        <v>77.75</v>
+        <v>76.61000061035156</v>
       </c>
       <c r="C98" t="n">
-        <v>78.69999694824219</v>
+        <v>78.84999847412109</v>
       </c>
       <c r="D98" t="n">
-        <v>76.58999633789062</v>
+        <v>76.40000152587891</v>
       </c>
       <c r="E98" t="n">
-        <v>77</v>
+        <v>78.66999816894531</v>
       </c>
       <c r="F98" t="n">
-        <v>30139200</v>
+        <v>32411300</v>
       </c>
       <c r="G98" t="n">
         <v>0</v>
@@ -2991,22 +2991,22 @@
     </row>
     <row r="99">
       <c r="A99" s="1" t="n">
-        <v>46073</v>
+        <v>46076</v>
       </c>
       <c r="B99" t="n">
-        <v>76.61000061035156</v>
+        <v>77.79000091552734</v>
       </c>
       <c r="C99" t="n">
-        <v>78.84999847412109</v>
+        <v>77.83000183105469</v>
       </c>
       <c r="D99" t="n">
-        <v>76.40000152587891</v>
+        <v>75.01000213623047</v>
       </c>
       <c r="E99" t="n">
-        <v>78.66999816894531</v>
+        <v>76.01999664306641</v>
       </c>
       <c r="F99" t="n">
-        <v>32411300</v>
+        <v>38363000</v>
       </c>
       <c r="G99" t="n">
         <v>0</v>
@@ -3017,22 +3017,22 @@
     </row>
     <row r="100">
       <c r="A100" s="1" t="n">
-        <v>46076</v>
+        <v>46077</v>
       </c>
       <c r="B100" t="n">
-        <v>77.79000091552734</v>
+        <v>75.73000335693359</v>
       </c>
       <c r="C100" t="n">
-        <v>77.83000183105469</v>
+        <v>78.12000274658203</v>
       </c>
       <c r="D100" t="n">
-        <v>75.01000213623047</v>
+        <v>75.20999908447266</v>
       </c>
       <c r="E100" t="n">
-        <v>76.01999664306641</v>
+        <v>78.04000091552734</v>
       </c>
       <c r="F100" t="n">
-        <v>38363000</v>
+        <v>33079100</v>
       </c>
       <c r="G100" t="n">
         <v>0</v>
@@ -3043,22 +3043,22 @@
     </row>
     <row r="101">
       <c r="A101" s="1" t="n">
-        <v>46077</v>
+        <v>46078</v>
       </c>
       <c r="B101" t="n">
-        <v>75.73000335693359</v>
+        <v>79.43000030517578</v>
       </c>
       <c r="C101" t="n">
-        <v>78.12000274658203</v>
+        <v>83.12000274658203</v>
       </c>
       <c r="D101" t="n">
-        <v>75.20999908447266</v>
+        <v>79.25</v>
       </c>
       <c r="E101" t="n">
-        <v>78.04000091552734</v>
+        <v>82.69999694824219</v>
       </c>
       <c r="F101" t="n">
-        <v>33079100</v>
+        <v>69319300</v>
       </c>
       <c r="G101" t="n">
         <v>0</v>
@@ -3069,22 +3069,22 @@
     </row>
     <row r="102">
       <c r="A102" s="1" t="n">
-        <v>46078</v>
+        <v>46079</v>
       </c>
       <c r="B102" t="n">
-        <v>79.43000030517578</v>
+        <v>83.19999694824219</v>
       </c>
       <c r="C102" t="n">
-        <v>83.12000274658203</v>
+        <v>86.5</v>
       </c>
       <c r="D102" t="n">
-        <v>79.25</v>
+        <v>82.80000305175781</v>
       </c>
       <c r="E102" t="n">
-        <v>82.69999694824219</v>
+        <v>84.58999633789062</v>
       </c>
       <c r="F102" t="n">
-        <v>69319300</v>
+        <v>85642500</v>
       </c>
       <c r="G102" t="n">
         <v>0</v>
@@ -3095,22 +3095,22 @@
     </row>
     <row r="103">
       <c r="A103" s="1" t="n">
-        <v>46079</v>
+        <v>46080</v>
       </c>
       <c r="B103" t="n">
-        <v>83.19999694824219</v>
+        <v>94.30000305175781</v>
       </c>
       <c r="C103" t="n">
-        <v>86.5</v>
+        <v>96.75</v>
       </c>
       <c r="D103" t="n">
-        <v>82.80000305175781</v>
+        <v>90.58000183105469</v>
       </c>
       <c r="E103" t="n">
-        <v>84.58999633789062</v>
+        <v>96.23999786376953</v>
       </c>
       <c r="F103" t="n">
-        <v>85642500</v>
+        <v>200767000</v>
       </c>
       <c r="G103" t="n">
         <v>0</v>
@@ -3121,22 +3121,22 @@
     </row>
     <row r="104">
       <c r="A104" s="1" t="n">
-        <v>46080</v>
+        <v>46083</v>
       </c>
       <c r="B104" t="n">
-        <v>94.30000305175781</v>
+        <v>95.26000213623047</v>
       </c>
       <c r="C104" t="n">
-        <v>96.75</v>
+        <v>98.06999969482422</v>
       </c>
       <c r="D104" t="n">
-        <v>90.58000183105469</v>
+        <v>95.19999694824219</v>
       </c>
       <c r="E104" t="n">
-        <v>96.23999786376953</v>
+        <v>97.08999633789062</v>
       </c>
       <c r="F104" t="n">
-        <v>200767000</v>
+        <v>79915400</v>
       </c>
       <c r="G104" t="n">
         <v>0</v>
@@ -3147,22 +3147,22 @@
     </row>
     <row r="105">
       <c r="A105" s="1" t="n">
-        <v>46083</v>
+        <v>46084</v>
       </c>
       <c r="B105" t="n">
-        <v>95.26000213623047</v>
+        <v>96.01000213623047</v>
       </c>
       <c r="C105" t="n">
-        <v>98.06999969482422</v>
+        <v>98.45999908447266</v>
       </c>
       <c r="D105" t="n">
-        <v>95.19999694824219</v>
+        <v>95.33000183105469</v>
       </c>
       <c r="E105" t="n">
-        <v>97.08999633789062</v>
+        <v>97.69999694824219</v>
       </c>
       <c r="F105" t="n">
-        <v>79915400</v>
+        <v>59149000</v>
       </c>
       <c r="G105" t="n">
         <v>0</v>
@@ -3173,22 +3173,22 @@
     </row>
     <row r="106">
       <c r="A106" s="1" t="n">
-        <v>46084</v>
+        <v>46085</v>
       </c>
       <c r="B106" t="n">
-        <v>96.01000213623047</v>
+        <v>97.11000061035156</v>
       </c>
       <c r="C106" t="n">
-        <v>98.45999908447266</v>
+        <v>99.75</v>
       </c>
       <c r="D106" t="n">
-        <v>95.33000183105469</v>
+        <v>96.98999786376953</v>
       </c>
       <c r="E106" t="n">
-        <v>97.69999694824219</v>
+        <v>98.66000366210938</v>
       </c>
       <c r="F106" t="n">
-        <v>59149000</v>
+        <v>52604300</v>
       </c>
       <c r="G106" t="n">
         <v>0</v>
@@ -3199,22 +3199,22 @@
     </row>
     <row r="107">
       <c r="A107" s="1" t="n">
-        <v>46085</v>
+        <v>46086</v>
       </c>
       <c r="B107" t="n">
-        <v>97.11000061035156</v>
+        <v>98.5</v>
       </c>
       <c r="C107" t="n">
-        <v>99.75</v>
+        <v>100.1900024414062</v>
       </c>
       <c r="D107" t="n">
-        <v>96.98999786376953</v>
+        <v>98.09999847412109</v>
       </c>
       <c r="E107" t="n">
-        <v>98.66000366210938</v>
+        <v>99.16999816894531</v>
       </c>
       <c r="F107" t="n">
-        <v>52604300</v>
+        <v>53403000</v>
       </c>
       <c r="G107" t="n">
         <v>0</v>
@@ -3225,22 +3225,22 @@
     </row>
     <row r="108">
       <c r="A108" s="1" t="n">
-        <v>46086</v>
+        <v>46087</v>
       </c>
       <c r="B108" t="n">
-        <v>98.5</v>
+        <v>99.33000183105469</v>
       </c>
       <c r="C108" t="n">
-        <v>100.1900024414062</v>
+        <v>99.87999725341797</v>
       </c>
       <c r="D108" t="n">
-        <v>98.09999847412109</v>
+        <v>97.40000152587891</v>
       </c>
       <c r="E108" t="n">
-        <v>99.16999816894531</v>
+        <v>99.01999664306641</v>
       </c>
       <c r="F108" t="n">
-        <v>53403000</v>
+        <v>41196300</v>
       </c>
       <c r="G108" t="n">
         <v>0</v>
@@ -3251,22 +3251,22 @@
     </row>
     <row r="109">
       <c r="A109" s="1" t="n">
-        <v>46087</v>
+        <v>46090</v>
       </c>
       <c r="B109" t="n">
-        <v>99.33000183105469</v>
+        <v>97.69999694824219</v>
       </c>
       <c r="C109" t="n">
-        <v>99.87999725341797</v>
+        <v>98.94000244140625</v>
       </c>
       <c r="D109" t="n">
-        <v>97.40000152587891</v>
+        <v>96.58000183105469</v>
       </c>
       <c r="E109" t="n">
-        <v>99.01999664306641</v>
+        <v>98.31999969482422</v>
       </c>
       <c r="F109" t="n">
-        <v>41196300</v>
+        <v>48589000</v>
       </c>
       <c r="G109" t="n">
         <v>0</v>
@@ -3277,22 +3277,22 @@
     </row>
     <row r="110">
       <c r="A110" s="1" t="n">
-        <v>46090</v>
+        <v>46091</v>
       </c>
       <c r="B110" t="n">
-        <v>97.69999694824219</v>
+        <v>97.80999755859375</v>
       </c>
       <c r="C110" t="n">
-        <v>98.94000244140625</v>
+        <v>98.48999786376953</v>
       </c>
       <c r="D110" t="n">
-        <v>96.58000183105469</v>
+        <v>96.29000091552734</v>
       </c>
       <c r="E110" t="n">
-        <v>98.31999969482422</v>
+        <v>96.94000244140625</v>
       </c>
       <c r="F110" t="n">
-        <v>48589000</v>
+        <v>41027200</v>
       </c>
       <c r="G110" t="n">
         <v>0</v>
@@ -3303,22 +3303,22 @@
     </row>
     <row r="111">
       <c r="A111" s="1" t="n">
-        <v>46091</v>
+        <v>46092</v>
       </c>
       <c r="B111" t="n">
-        <v>97.80999755859375</v>
+        <v>97.41000366210938</v>
       </c>
       <c r="C111" t="n">
-        <v>98.48999786376953</v>
+        <v>98</v>
       </c>
       <c r="D111" t="n">
-        <v>96.29000091552734</v>
+        <v>94.69000244140625</v>
       </c>
       <c r="E111" t="n">
-        <v>96.94000244140625</v>
+        <v>94.88999938964844</v>
       </c>
       <c r="F111" t="n">
-        <v>41027200</v>
+        <v>33962900</v>
       </c>
       <c r="G111" t="n">
         <v>0</v>
@@ -3329,22 +3329,22 @@
     </row>
     <row r="112">
       <c r="A112" s="1" t="n">
-        <v>46092</v>
+        <v>46093</v>
       </c>
       <c r="B112" t="n">
-        <v>97.41000366210938</v>
+        <v>94.86000061035156</v>
       </c>
       <c r="C112" t="n">
-        <v>98</v>
+        <v>95.40000152587891</v>
       </c>
       <c r="D112" t="n">
-        <v>94.69000244140625</v>
+        <v>93.87000274658203</v>
       </c>
       <c r="E112" t="n">
-        <v>94.88999938964844</v>
+        <v>94.30999755859375</v>
       </c>
       <c r="F112" t="n">
-        <v>33962900</v>
+        <v>34206900</v>
       </c>
       <c r="G112" t="n">
         <v>0</v>
@@ -3355,22 +3355,22 @@
     </row>
     <row r="113">
       <c r="A113" s="1" t="n">
-        <v>46093</v>
+        <v>46094</v>
       </c>
       <c r="B113" t="n">
-        <v>94.86000061035156</v>
+        <v>94.63999938964844</v>
       </c>
       <c r="C113" t="n">
-        <v>95.40000152587891</v>
+        <v>95.68000030517578</v>
       </c>
       <c r="D113" t="n">
-        <v>93.87000274658203</v>
+        <v>94.23999786376953</v>
       </c>
       <c r="E113" t="n">
-        <v>94.30999755859375</v>
+        <v>95.30999755859375</v>
       </c>
       <c r="F113" t="n">
-        <v>34206900</v>
+        <v>29876700</v>
       </c>
       <c r="G113" t="n">
         <v>0</v>
@@ -3381,22 +3381,22 @@
     </row>
     <row r="114">
       <c r="A114" s="1" t="n">
-        <v>46094</v>
+        <v>46097</v>
       </c>
       <c r="B114" t="n">
-        <v>94.63999938964844</v>
+        <v>95.58000183105469</v>
       </c>
       <c r="C114" t="n">
-        <v>95.68000030517578</v>
+        <v>96.09999847412109</v>
       </c>
       <c r="D114" t="n">
-        <v>94.23999786376953</v>
+        <v>94.36000061035156</v>
       </c>
       <c r="E114" t="n">
-        <v>95.30999755859375</v>
+        <v>95.19999694824219</v>
       </c>
       <c r="F114" t="n">
-        <v>29876700</v>
+        <v>34931800</v>
       </c>
       <c r="G114" t="n">
         <v>0</v>
@@ -3407,22 +3407,22 @@
     </row>
     <row r="115">
       <c r="A115" s="1" t="n">
-        <v>46097</v>
+        <v>46098</v>
       </c>
       <c r="B115" t="n">
-        <v>95.58000183105469</v>
+        <v>95.30000305175781</v>
       </c>
       <c r="C115" t="n">
-        <v>96.09999847412109</v>
+        <v>96.33999633789062</v>
       </c>
       <c r="D115" t="n">
+        <v>94.01000213623047</v>
+      </c>
+      <c r="E115" t="n">
         <v>94.36000061035156</v>
       </c>
-      <c r="E115" t="n">
-        <v>95.19999694824219</v>
-      </c>
       <c r="F115" t="n">
-        <v>34931800</v>
+        <v>26434500</v>
       </c>
       <c r="G115" t="n">
         <v>0</v>
@@ -3433,22 +3433,22 @@
     </row>
     <row r="116">
       <c r="A116" s="1" t="n">
-        <v>46098</v>
+        <v>46099</v>
       </c>
       <c r="B116" t="n">
-        <v>95.30000305175781</v>
+        <v>94.44999694824219</v>
       </c>
       <c r="C116" t="n">
-        <v>96.33999633789062</v>
+        <v>95.33999633789062</v>
       </c>
       <c r="D116" t="n">
-        <v>94.01000213623047</v>
+        <v>93.61000061035156</v>
       </c>
       <c r="E116" t="n">
-        <v>94.36000061035156</v>
+        <v>94.69999694824219</v>
       </c>
       <c r="F116" t="n">
-        <v>26434500</v>
+        <v>27878300</v>
       </c>
       <c r="G116" t="n">
         <v>0</v>
@@ -3459,22 +3459,22 @@
     </row>
     <row r="117">
       <c r="A117" s="1" t="n">
-        <v>46099</v>
+        <v>46100</v>
       </c>
       <c r="B117" t="n">
-        <v>94.44999694824219</v>
+        <v>94.30999755859375</v>
       </c>
       <c r="C117" t="n">
-        <v>95.33999633789062</v>
+        <v>95.75</v>
       </c>
       <c r="D117" t="n">
-        <v>93.61000061035156</v>
+        <v>90.77999877929688</v>
       </c>
       <c r="E117" t="n">
-        <v>94.69999694824219</v>
+        <v>91.73999786376953</v>
       </c>
       <c r="F117" t="n">
-        <v>27878300</v>
+        <v>40169300</v>
       </c>
       <c r="G117" t="n">
         <v>0</v>
@@ -3485,22 +3485,22 @@
     </row>
     <row r="118">
       <c r="A118" s="1" t="n">
-        <v>46100</v>
+        <v>46101</v>
       </c>
       <c r="B118" t="n">
-        <v>94.30999755859375</v>
+        <v>91.30999755859375</v>
       </c>
       <c r="C118" t="n">
-        <v>95.75</v>
+        <v>91.87999725341797</v>
       </c>
       <c r="D118" t="n">
-        <v>90.77999877929688</v>
+        <v>90.69000244140625</v>
       </c>
       <c r="E118" t="n">
-        <v>91.73999786376953</v>
+        <v>91.81999969482422</v>
       </c>
       <c r="F118" t="n">
-        <v>40169300</v>
+        <v>61678000</v>
       </c>
       <c r="G118" t="n">
         <v>0</v>
@@ -3511,22 +3511,22 @@
     </row>
     <row r="119">
       <c r="A119" s="1" t="n">
-        <v>46101</v>
+        <v>46104</v>
       </c>
       <c r="B119" t="n">
-        <v>91.30999755859375</v>
+        <v>92.04000091552734</v>
       </c>
       <c r="C119" t="n">
-        <v>91.87999725341797</v>
+        <v>93.98000335693359</v>
       </c>
       <c r="D119" t="n">
-        <v>90.69000244140625</v>
+        <v>91.86000061035156</v>
       </c>
       <c r="E119" t="n">
-        <v>91.81999969482422</v>
+        <v>93.37999725341797</v>
       </c>
       <c r="F119" t="n">
-        <v>61678000</v>
+        <v>34315900</v>
       </c>
       <c r="G119" t="n">
         <v>0</v>
@@ -3537,22 +3537,22 @@
     </row>
     <row r="120">
       <c r="A120" s="1" t="n">
-        <v>46104</v>
+        <v>46105</v>
       </c>
       <c r="B120" t="n">
-        <v>92.04000091552734</v>
+        <v>92.79000091552734</v>
       </c>
       <c r="C120" t="n">
-        <v>93.98000335693359</v>
+        <v>93.73999786376953</v>
       </c>
       <c r="D120" t="n">
-        <v>91.86000061035156</v>
+        <v>90.81999969482422</v>
       </c>
       <c r="E120" t="n">
-        <v>93.37999725341797</v>
+        <v>90.91999816894531</v>
       </c>
       <c r="F120" t="n">
-        <v>34315900</v>
+        <v>28938000</v>
       </c>
       <c r="G120" t="n">
         <v>0</v>
@@ -3563,22 +3563,22 @@
     </row>
     <row r="121">
       <c r="A121" s="1" t="n">
-        <v>46105</v>
+        <v>46106</v>
       </c>
       <c r="B121" t="n">
-        <v>92.79000091552734</v>
+        <v>91.70999908447266</v>
       </c>
       <c r="C121" t="n">
-        <v>93.73999786376953</v>
+        <v>92.51999664306641</v>
       </c>
       <c r="D121" t="n">
-        <v>90.81999969482422</v>
+        <v>91.23999786376953</v>
       </c>
       <c r="E121" t="n">
-        <v>90.91999816894531</v>
+        <v>92.27999877929688</v>
       </c>
       <c r="F121" t="n">
-        <v>28938000</v>
+        <v>29545600</v>
       </c>
       <c r="G121" t="n">
         <v>0</v>
@@ -3589,22 +3589,22 @@
     </row>
     <row r="122">
       <c r="A122" s="1" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B122" t="n">
-        <v>91.70999908447266</v>
+        <v>91.51999664306641</v>
       </c>
       <c r="C122" t="n">
-        <v>92.51999664306641</v>
+        <v>95.86000061035156</v>
       </c>
       <c r="D122" t="n">
-        <v>91.23999786376953</v>
+        <v>91.01000213623047</v>
       </c>
       <c r="E122" t="n">
-        <v>92.27999877929688</v>
+        <v>93.31999969482422</v>
       </c>
       <c r="F122" t="n">
-        <v>29545600</v>
+        <v>59522000</v>
       </c>
       <c r="G122" t="n">
         <v>0</v>
@@ -3615,22 +3615,22 @@
     </row>
     <row r="123">
       <c r="A123" s="1" t="n">
-        <v>46107</v>
+        <v>46108</v>
       </c>
       <c r="B123" t="n">
-        <v>91.51999664306641</v>
+        <v>94.56999969482422</v>
       </c>
       <c r="C123" t="n">
-        <v>95.86000061035156</v>
+        <v>95.58000183105469</v>
       </c>
       <c r="D123" t="n">
-        <v>91.01000213623047</v>
+        <v>92.73999786376953</v>
       </c>
       <c r="E123" t="n">
-        <v>93.31999969482422</v>
+        <v>93.43000030517578</v>
       </c>
       <c r="F123" t="n">
-        <v>59522000</v>
+        <v>44590700</v>
       </c>
       <c r="G123" t="n">
         <v>0</v>
@@ -3641,22 +3641,22 @@
     </row>
     <row r="124">
       <c r="A124" s="1" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B124" t="n">
-        <v>94.56999969482422</v>
+        <v>92.75</v>
       </c>
       <c r="C124" t="n">
-        <v>95.58000183105469</v>
+        <v>94.48999786376953</v>
       </c>
       <c r="D124" t="n">
-        <v>92.73999786376953</v>
+        <v>92.22000122070312</v>
       </c>
       <c r="E124" t="n">
-        <v>93.43000030517578</v>
+        <v>92.97000122070312</v>
       </c>
       <c r="F124" t="n">
-        <v>44590700</v>
+        <v>32375100</v>
       </c>
       <c r="G124" t="n">
         <v>0</v>
@@ -3667,22 +3667,22 @@
     </row>
     <row r="125">
       <c r="A125" s="1" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B125" t="n">
-        <v>92.75</v>
+        <v>93.02999877929688</v>
       </c>
       <c r="C125" t="n">
-        <v>94.48999786376953</v>
+        <v>96.26000213623047</v>
       </c>
       <c r="D125" t="n">
-        <v>92.22000122070312</v>
+        <v>93.02999877929688</v>
       </c>
       <c r="E125" t="n">
-        <v>92.97000122070312</v>
+        <v>96.15000152587891</v>
       </c>
       <c r="F125" t="n">
-        <v>32375100</v>
+        <v>54270000</v>
       </c>
       <c r="G125" t="n">
         <v>0</v>
@@ -3693,22 +3693,22 @@
     </row>
     <row r="126">
       <c r="A126" s="1" t="n">
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="B126" t="n">
-        <v>93.02999877929688</v>
+        <v>96.47000122070312</v>
       </c>
       <c r="C126" t="n">
-        <v>96.26000213623047</v>
+        <v>97.19999694824219</v>
       </c>
       <c r="D126" t="n">
-        <v>93.02999877929688</v>
+        <v>94.26000213623047</v>
       </c>
       <c r="E126" t="n">
-        <v>96.15000152587891</v>
+        <v>95.55000305175781</v>
       </c>
       <c r="F126" t="n">
-        <v>54270000</v>
+        <v>30439300</v>
       </c>
       <c r="G126" t="n">
         <v>0</v>
@@ -3719,22 +3719,22 @@
     </row>
     <row r="127">
       <c r="A127" s="1" t="n">
-        <v>46113</v>
+        <v>46114</v>
       </c>
       <c r="B127" t="n">
-        <v>96.47000122070312</v>
+        <v>95.26999664306641</v>
       </c>
       <c r="C127" t="n">
-        <v>97.19999694824219</v>
+        <v>98.70999908447266</v>
       </c>
       <c r="D127" t="n">
-        <v>94.26000213623047</v>
+        <v>95.16999816894531</v>
       </c>
       <c r="E127" t="n">
-        <v>95.55000305175781</v>
+        <v>98.66000366210938</v>
       </c>
       <c r="F127" t="n">
-        <v>30439300</v>
+        <v>37068000</v>
       </c>
       <c r="G127" t="n">
         <v>0</v>
@@ -3745,22 +3745,22 @@
     </row>
     <row r="128">
       <c r="A128" s="1" t="n">
-        <v>46114</v>
+        <v>46118</v>
       </c>
       <c r="B128" t="n">
-        <v>95.26999664306641</v>
+        <v>100.9599990844727</v>
       </c>
       <c r="C128" t="n">
-        <v>98.70999908447266</v>
+        <v>102.6900024414062</v>
       </c>
       <c r="D128" t="n">
-        <v>95.16999816894531</v>
+        <v>97.97000122070312</v>
       </c>
       <c r="E128" t="n">
-        <v>98.66000366210938</v>
+        <v>98.93000030517578</v>
       </c>
       <c r="F128" t="n">
-        <v>37068000</v>
+        <v>37029300</v>
       </c>
       <c r="G128" t="n">
         <v>0</v>
@@ -3771,22 +3771,22 @@
     </row>
     <row r="129">
       <c r="A129" s="1" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B129" t="n">
-        <v>100.9599990844727</v>
+        <v>98.55000305175781</v>
       </c>
       <c r="C129" t="n">
-        <v>102.6900024414062</v>
+        <v>99.87999725341797</v>
       </c>
       <c r="D129" t="n">
-        <v>97.97000122070312</v>
+        <v>98.25</v>
       </c>
       <c r="E129" t="n">
-        <v>98.93000030517578</v>
+        <v>98.81999969482422</v>
       </c>
       <c r="F129" t="n">
-        <v>37029300</v>
+        <v>25016700</v>
       </c>
       <c r="G129" t="n">
         <v>0</v>
@@ -3797,22 +3797,22 @@
     </row>
     <row r="130">
       <c r="A130" s="1" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B130" t="n">
-        <v>98.55000305175781</v>
+        <v>100.3199996948242</v>
       </c>
       <c r="C130" t="n">
-        <v>99.87999725341797</v>
+        <v>100.4000015258789</v>
       </c>
       <c r="D130" t="n">
-        <v>98.25</v>
+        <v>97.44000244140625</v>
       </c>
       <c r="E130" t="n">
-        <v>98.81999969482422</v>
+        <v>99.38999938964844</v>
       </c>
       <c r="F130" t="n">
-        <v>25016700</v>
+        <v>30957600</v>
       </c>
       <c r="G130" t="n">
         <v>0</v>
@@ -3823,22 +3823,22 @@
     </row>
     <row r="131">
       <c r="A131" s="1" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B131" t="n">
-        <v>100.3199996948242</v>
+        <v>99.62999725341797</v>
       </c>
       <c r="C131" t="n">
-        <v>100.4000015258789</v>
+        <v>102.3399963378906</v>
       </c>
       <c r="D131" t="n">
-        <v>97.44000244140625</v>
+        <v>99.08000183105469</v>
       </c>
       <c r="E131" t="n">
-        <v>99.38999938964844</v>
+        <v>102.0500030517578</v>
       </c>
       <c r="F131" t="n">
-        <v>30957600</v>
+        <v>35087800</v>
       </c>
       <c r="G131" t="n">
         <v>0</v>
@@ -3849,22 +3849,22 @@
     </row>
     <row r="132">
       <c r="A132" s="1" t="n">
-        <v>46121</v>
+        <v>46122</v>
       </c>
       <c r="B132" t="n">
-        <v>99.62999725341797</v>
+        <v>102.4700012207031</v>
       </c>
       <c r="C132" t="n">
-        <v>102.3399963378906</v>
+        <v>103.0800018310547</v>
       </c>
       <c r="D132" t="n">
-        <v>99.08000183105469</v>
+        <v>101.4599990844727</v>
       </c>
       <c r="E132" t="n">
-        <v>102.0500030517578</v>
+        <v>103.0100021362305</v>
       </c>
       <c r="F132" t="n">
-        <v>35087800</v>
+        <v>25769900</v>
       </c>
       <c r="G132" t="n">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="133">
       <c r="A133" s="1" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B133" t="n">
-        <v>102.4700012207031</v>
+        <v>103.0299987792969</v>
       </c>
       <c r="C133" t="n">
-        <v>103.0800018310547</v>
+        <v>103.6699981689453</v>
       </c>
       <c r="D133" t="n">
-        <v>101.4599990844727</v>
+        <v>102.0599975585938</v>
       </c>
       <c r="E133" t="n">
-        <v>103.0100021362305</v>
+        <v>103.1600036621094</v>
       </c>
       <c r="F133" t="n">
-        <v>25769900</v>
+        <v>26042800</v>
       </c>
       <c r="G133" t="n">
         <v>0</v>
@@ -3901,22 +3901,22 @@
     </row>
     <row r="134">
       <c r="A134" s="1" t="n">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="B134" t="n">
-        <v>103.0299987792969</v>
+        <v>103.120002746582</v>
       </c>
       <c r="C134" t="n">
-        <v>103.6699981689453</v>
+        <v>106.5699996948242</v>
       </c>
       <c r="D134" t="n">
-        <v>102.0599975585938</v>
+        <v>103.0400009155273</v>
       </c>
       <c r="E134" t="n">
-        <v>103.1600036621094</v>
+        <v>106.2799987792969</v>
       </c>
       <c r="F134" t="n">
-        <v>26042800</v>
+        <v>40534900</v>
       </c>
       <c r="G134" t="n">
         <v>0</v>
@@ -3927,22 +3927,22 @@
     </row>
     <row r="135">
       <c r="A135" s="1" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B135" t="n">
-        <v>103.120002746582</v>
+        <v>105.9800033569336</v>
       </c>
       <c r="C135" t="n">
-        <v>106.5699996948242</v>
+        <v>107.8499984741211</v>
       </c>
       <c r="D135" t="n">
-        <v>103.0400009155273</v>
+        <v>105.0400009155273</v>
       </c>
       <c r="E135" t="n">
-        <v>106.2799987792969</v>
+        <v>107.7099990844727</v>
       </c>
       <c r="F135" t="n">
-        <v>40534900</v>
+        <v>38023700</v>
       </c>
       <c r="G135" t="n">
         <v>0</v>
@@ -3953,22 +3953,22 @@
     </row>
     <row r="136">
       <c r="A136" s="1" t="n">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c r="B136" t="n">
-        <v>105.9800033569336</v>
+        <v>107.4700012207031</v>
       </c>
       <c r="C136" t="n">
-        <v>107.8499984741211</v>
+        <v>108.9499969482422</v>
       </c>
       <c r="D136" t="n">
-        <v>105.0400009155273</v>
+        <v>106.620002746582</v>
       </c>
       <c r="E136" t="n">
-        <v>107.7099990844727</v>
+        <v>107.7900009155273</v>
       </c>
       <c r="F136" t="n">
-        <v>38023700</v>
+        <v>64928300</v>
       </c>
       <c r="G136" t="n">
         <v>0</v>
@@ -3979,22 +3979,22 @@
     </row>
     <row r="137">
       <c r="A137" s="1" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B137" t="n">
-        <v>107.4700012207031</v>
+        <v>96.37000274658203</v>
       </c>
       <c r="C137" t="n">
-        <v>108.9499969482422</v>
+        <v>98.73999786376953</v>
       </c>
       <c r="D137" t="n">
-        <v>106.620002746582</v>
+        <v>95.09999847412109</v>
       </c>
       <c r="E137" t="n">
-        <v>107.7900009155273</v>
+        <v>97.30999755859375</v>
       </c>
       <c r="F137" t="n">
-        <v>64928300</v>
+        <v>125958700</v>
       </c>
       <c r="G137" t="n">
         <v>0</v>
@@ -4005,22 +4005,22 @@
     </row>
     <row r="138">
       <c r="A138" s="1" t="n">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c r="B138" t="n">
-        <v>96.37000274658203</v>
+        <v>97.13999938964844</v>
       </c>
       <c r="C138" t="n">
-        <v>98.73999786376953</v>
+        <v>97.59999847412109</v>
       </c>
       <c r="D138" t="n">
-        <v>95.09999847412109</v>
+        <v>93.54000091552734</v>
       </c>
       <c r="E138" t="n">
-        <v>97.30999755859375</v>
+        <v>94.83000183105469</v>
       </c>
       <c r="F138" t="n">
-        <v>125958700</v>
+        <v>63298300</v>
       </c>
       <c r="G138" t="n">
         <v>0</v>
@@ -4031,22 +4031,22 @@
     </row>
     <row r="139">
       <c r="A139" s="1" t="n">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="B139" t="n">
-        <v>97.13999938964844</v>
+        <v>94</v>
       </c>
       <c r="C139" t="n">
-        <v>97.59999847412109</v>
+        <v>94.65000152587891</v>
       </c>
       <c r="D139" t="n">
-        <v>93.54000091552734</v>
+        <v>92.37000274658203</v>
       </c>
       <c r="E139" t="n">
-        <v>94.83000183105469</v>
+        <v>92.58000183105469</v>
       </c>
       <c r="F139" t="n">
-        <v>63298300</v>
+        <v>61962300</v>
       </c>
       <c r="G139" t="n">
         <v>0</v>
@@ -4057,22 +4057,22 @@
     </row>
     <row r="140">
       <c r="A140" s="1" t="n">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="B140" t="n">
-        <v>94</v>
+        <v>93.05999755859375</v>
       </c>
       <c r="C140" t="n">
-        <v>94.65000152587891</v>
+        <v>93.84999847412109</v>
       </c>
       <c r="D140" t="n">
-        <v>92.37000274658203</v>
+        <v>92.76999664306641</v>
       </c>
       <c r="E140" t="n">
-        <v>92.58000183105469</v>
+        <v>93.23999786376953</v>
       </c>
       <c r="F140" t="n">
-        <v>61962300</v>
+        <v>33694300</v>
       </c>
       <c r="G140" t="n">
         <v>0</v>
@@ -4083,22 +4083,22 @@
     </row>
     <row r="141">
       <c r="A141" s="1" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B141" t="n">
-        <v>93.05999755859375</v>
+        <v>94.05999755859375</v>
       </c>
       <c r="C141" t="n">
-        <v>93.84999847412109</v>
+        <v>94.63999938964844</v>
       </c>
       <c r="D141" t="n">
-        <v>92.76999664306641</v>
+        <v>92.06999969482422</v>
       </c>
       <c r="E141" t="n">
-        <v>93.23999786376953</v>
+        <v>92.81999969482422</v>
       </c>
       <c r="F141" t="n">
-        <v>33694300</v>
+        <v>36851700</v>
       </c>
       <c r="G141" t="n">
         <v>0</v>
@@ -4109,22 +4109,22 @@
     </row>
     <row r="142">
       <c r="A142" s="1" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B142" t="n">
-        <v>94.05999755859375</v>
+        <v>92.56999969482422</v>
       </c>
       <c r="C142" t="n">
-        <v>94.63999938964844</v>
+        <v>93.27999877929688</v>
       </c>
       <c r="D142" t="n">
-        <v>92.06999969482422</v>
+        <v>91.80000305175781</v>
       </c>
       <c r="E142" t="n">
-        <v>92.81999969482422</v>
+        <v>92.44000244140625</v>
       </c>
       <c r="F142" t="n">
-        <v>36851700</v>
+        <v>32553200</v>
       </c>
       <c r="G142" t="n">
         <v>0</v>
@@ -4135,22 +4135,22 @@
     </row>
     <row r="143">
       <c r="A143" s="1" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B143" t="n">
-        <v>92.56999969482422</v>
+        <v>92.05000305175781</v>
       </c>
       <c r="C143" t="n">
-        <v>93.27999877929688</v>
+        <v>92.83999633789062</v>
       </c>
       <c r="D143" t="n">
-        <v>91.80000305175781</v>
+        <v>91.30000305175781</v>
       </c>
       <c r="E143" t="n">
-        <v>92.44000244140625</v>
+        <v>91.37000274658203</v>
       </c>
       <c r="F143" t="n">
-        <v>32553200</v>
+        <v>29707400</v>
       </c>
       <c r="G143" t="n">
         <v>0</v>
@@ -4161,22 +4161,22 @@
     </row>
     <row r="144">
       <c r="A144" s="1" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B144" t="n">
-        <v>92.05000305175781</v>
+        <v>91.5</v>
       </c>
       <c r="C144" t="n">
-        <v>92.83999633789062</v>
+        <v>92.33999633789062</v>
       </c>
       <c r="D144" t="n">
-        <v>91.30000305175781</v>
+        <v>90.01999664306641</v>
       </c>
       <c r="E144" t="n">
-        <v>91.37000274658203</v>
+        <v>92.26999664306641</v>
       </c>
       <c r="F144" t="n">
-        <v>29707400</v>
+        <v>33418100</v>
       </c>
       <c r="G144" t="n">
         <v>0</v>
@@ -4187,22 +4187,22 @@
     </row>
     <row r="145">
       <c r="A145" s="1" t="n">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="B145" t="n">
-        <v>91.5</v>
+        <v>91.23000335693359</v>
       </c>
       <c r="C145" t="n">
-        <v>92.33999633789062</v>
+        <v>92.86000061035156</v>
       </c>
       <c r="D145" t="n">
-        <v>90.01999664306641</v>
+        <v>90.86000061035156</v>
       </c>
       <c r="E145" t="n">
-        <v>92.26999664306641</v>
+        <v>92.12000274658203</v>
       </c>
       <c r="F145" t="n">
-        <v>33418100</v>
+        <v>26122100</v>
       </c>
       <c r="G145" t="n">
         <v>0</v>
@@ -4213,22 +4213,22 @@
     </row>
     <row r="146">
       <c r="A146" s="1" t="n">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="B146" t="n">
-        <v>91.23000335693359</v>
+        <v>91.34999847412109</v>
       </c>
       <c r="C146" t="n">
-        <v>92.86000061035156</v>
+        <v>94.22000122070312</v>
       </c>
       <c r="D146" t="n">
-        <v>90.86000061035156</v>
+        <v>90.76999664306641</v>
       </c>
       <c r="E146" t="n">
-        <v>92.12000274658203</v>
+        <v>93.61000061035156</v>
       </c>
       <c r="F146" t="n">
-        <v>26122100</v>
+        <v>40923000</v>
       </c>
       <c r="G146" t="n">
         <v>0</v>
@@ -4239,22 +4239,22 @@
     </row>
     <row r="147">
       <c r="A147" s="1" t="n">
-        <v>46142</v>
+        <v>46143</v>
       </c>
       <c r="B147" t="n">
-        <v>91.34999847412109</v>
+        <v>94.41999816894531</v>
       </c>
       <c r="C147" t="n">
-        <v>94.22000122070312</v>
+        <v>94.69999694824219</v>
       </c>
       <c r="D147" t="n">
-        <v>90.76999664306641</v>
+        <v>91.90000152587891</v>
       </c>
       <c r="E147" t="n">
-        <v>93.61000061035156</v>
+        <v>92.05999755859375</v>
       </c>
       <c r="F147" t="n">
-        <v>40923000</v>
+        <v>30406900</v>
       </c>
       <c r="G147" t="n">
         <v>0</v>
@@ -4265,22 +4265,22 @@
     </row>
     <row r="148">
       <c r="A148" s="1" t="n">
-        <v>46143</v>
+        <v>46146</v>
       </c>
       <c r="B148" t="n">
-        <v>94.41999816894531</v>
+        <v>92.09999847412109</v>
       </c>
       <c r="C148" t="n">
-        <v>94.69999694824219</v>
+        <v>92.33000183105469</v>
       </c>
       <c r="D148" t="n">
-        <v>91.90000152587891</v>
+        <v>90.88999938964844</v>
       </c>
       <c r="E148" t="n">
-        <v>92.05999755859375</v>
+        <v>91.01999664306641</v>
       </c>
       <c r="F148" t="n">
-        <v>30406900</v>
+        <v>25928800</v>
       </c>
       <c r="G148" t="n">
         <v>0</v>
@@ -4291,22 +4291,22 @@
     </row>
     <row r="149">
       <c r="A149" s="1" t="n">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="B149" t="n">
-        <v>92.09999847412109</v>
+        <v>91.18000030517578</v>
       </c>
       <c r="C149" t="n">
-        <v>92.33000183105469</v>
+        <v>91.27999877929688</v>
       </c>
       <c r="D149" t="n">
-        <v>90.88999938964844</v>
+        <v>87.56999969482422</v>
       </c>
       <c r="E149" t="n">
-        <v>91.01999664306641</v>
+        <v>87.88999938964844</v>
       </c>
       <c r="F149" t="n">
-        <v>25928800</v>
+        <v>51961300</v>
       </c>
       <c r="G149" t="n">
         <v>0</v>
@@ -4317,22 +4317,22 @@
     </row>
     <row r="150">
       <c r="A150" s="1" t="n">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="B150" t="n">
-        <v>91.18000030517578</v>
+        <v>87.15000152587891</v>
       </c>
       <c r="C150" t="n">
-        <v>91.27999877929688</v>
+        <v>88.55000305175781</v>
       </c>
       <c r="D150" t="n">
-        <v>87.56999969482422</v>
+        <v>86.72000122070312</v>
       </c>
       <c r="E150" t="n">
-        <v>87.88999938964844</v>
+        <v>88.26999664306641</v>
       </c>
       <c r="F150" t="n">
-        <v>51961300</v>
+        <v>41932400</v>
       </c>
       <c r="G150" t="n">
         <v>0</v>
@@ -4343,22 +4343,22 @@
     </row>
     <row r="151">
       <c r="A151" s="1" t="n">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="B151" t="n">
-        <v>87.15000152587891</v>
+        <v>88.19999694824219</v>
       </c>
       <c r="C151" t="n">
-        <v>88.55000305175781</v>
+        <v>89.40000152587891</v>
       </c>
       <c r="D151" t="n">
-        <v>86.72000122070312</v>
+        <v>88.12999725341797</v>
       </c>
       <c r="E151" t="n">
-        <v>88.26999664306641</v>
+        <v>88.25</v>
       </c>
       <c r="F151" t="n">
-        <v>41932400</v>
+        <v>30627600</v>
       </c>
       <c r="G151" t="n">
         <v>0</v>
@@ -4369,22 +4369,22 @@
     </row>
     <row r="152">
       <c r="A152" s="1" t="n">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="B152" t="n">
-        <v>88.19999694824219</v>
+        <v>87.70999908447266</v>
       </c>
       <c r="C152" t="n">
-        <v>89.40000152587891</v>
+        <v>88.04000091552734</v>
       </c>
       <c r="D152" t="n">
-        <v>88.12999725341797</v>
+        <v>87.20999908447266</v>
       </c>
       <c r="E152" t="n">
-        <v>88.25</v>
+        <v>87.48999786376953</v>
       </c>
       <c r="F152" t="n">
-        <v>30627600</v>
+        <v>36215100</v>
       </c>
       <c r="G152" t="n">
         <v>0</v>
@@ -4395,22 +4395,22 @@
     </row>
     <row r="153">
       <c r="A153" s="1" t="n">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="B153" t="n">
-        <v>87.70999908447266</v>
+        <v>86.52999877929688</v>
       </c>
       <c r="C153" t="n">
-        <v>88.04000091552734</v>
+        <v>87.33999633789062</v>
       </c>
       <c r="D153" t="n">
-        <v>87.20999908447266</v>
+        <v>85.09999847412109</v>
       </c>
       <c r="E153" t="n">
-        <v>87.48999786376953</v>
+        <v>85.44999694824219</v>
       </c>
       <c r="F153" t="n">
-        <v>36215100</v>
+        <v>40556500</v>
       </c>
       <c r="G153" t="n">
         <v>0</v>
@@ -4421,22 +4421,22 @@
     </row>
     <row r="154">
       <c r="A154" s="1" t="n">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="B154" t="n">
-        <v>86.52999877929688</v>
+        <v>85.91000366210938</v>
       </c>
       <c r="C154" t="n">
-        <v>87.33999633789062</v>
+        <v>89.16999816894531</v>
       </c>
       <c r="D154" t="n">
-        <v>85.09999847412109</v>
+        <v>85.80999755859375</v>
       </c>
       <c r="E154" t="n">
-        <v>85.44999694824219</v>
+        <v>87.66000366210938</v>
       </c>
       <c r="F154" t="n">
-        <v>40556500</v>
+        <v>43556600</v>
       </c>
       <c r="G154" t="n">
         <v>0</v>
@@ -4447,22 +4447,22 @@
     </row>
     <row r="155">
       <c r="A155" s="1" t="n">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="B155" t="n">
-        <v>85.91000366210938</v>
+        <v>86.56999969482422</v>
       </c>
       <c r="C155" t="n">
-        <v>89.16999816894531</v>
+        <v>88.62000274658203</v>
       </c>
       <c r="D155" t="n">
-        <v>85.80999755859375</v>
+        <v>86.27999877929688</v>
       </c>
       <c r="E155" t="n">
-        <v>87.66000366210938</v>
+        <v>87.55999755859375</v>
       </c>
       <c r="F155" t="n">
-        <v>43556600</v>
+        <v>30823500</v>
       </c>
       <c r="G155" t="n">
         <v>0</v>
@@ -4473,22 +4473,22 @@
     </row>
     <row r="156">
       <c r="A156" s="1" t="n">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="B156" t="n">
-        <v>86.56999969482422</v>
+        <v>87.62000274658203</v>
       </c>
       <c r="C156" t="n">
-        <v>88.62000274658203</v>
+        <v>88.5</v>
       </c>
       <c r="D156" t="n">
-        <v>86.27999877929688</v>
+        <v>86.65000152587891</v>
       </c>
       <c r="E156" t="n">
-        <v>87.55999755859375</v>
+        <v>86.94000244140625</v>
       </c>
       <c r="F156" t="n">
-        <v>30823500</v>
+        <v>29408300</v>
       </c>
       <c r="G156" t="n">
         <v>0</v>
@@ -4499,22 +4499,22 @@
     </row>
     <row r="157">
       <c r="A157" s="1" t="n">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="B157" t="n">
-        <v>87.62000274658203</v>
+        <v>87.69000244140625</v>
       </c>
       <c r="C157" t="n">
-        <v>88.5</v>
+        <v>89.48999786376953</v>
       </c>
       <c r="D157" t="n">
-        <v>86.65000152587891</v>
+        <v>86.69000244140625</v>
       </c>
       <c r="E157" t="n">
-        <v>86.94000244140625</v>
+        <v>87.01999664306641</v>
       </c>
       <c r="F157" t="n">
-        <v>29408300</v>
+        <v>32335700</v>
       </c>
       <c r="G157" t="n">
         <v>0</v>
@@ -4525,22 +4525,22 @@
     </row>
     <row r="158">
       <c r="A158" s="1" t="n">
-        <v>46157</v>
+        <v>46160</v>
       </c>
       <c r="B158" t="n">
-        <v>87.69000244140625</v>
+        <v>86.5</v>
       </c>
       <c r="C158" t="n">
-        <v>89.48999786376953</v>
+        <v>89.81999969482422</v>
       </c>
       <c r="D158" t="n">
-        <v>86.69000244140625</v>
+        <v>86.33000183105469</v>
       </c>
       <c r="E158" t="n">
-        <v>87.01999664306641</v>
+        <v>89.65000152587891</v>
       </c>
       <c r="F158" t="n">
-        <v>32335700</v>
+        <v>35800500</v>
       </c>
       <c r="G158" t="n">
         <v>0</v>
@@ -4551,22 +4551,22 @@
     </row>
     <row r="159">
       <c r="A159" s="1" t="n">
-        <v>46160</v>
+        <v>46161</v>
       </c>
       <c r="B159" t="n">
-        <v>86.5</v>
+        <v>90.13999938964844</v>
       </c>
       <c r="C159" t="n">
-        <v>89.81999969482422</v>
+        <v>91.48000335693359</v>
       </c>
       <c r="D159" t="n">
-        <v>86.33000183105469</v>
+        <v>88.69000244140625</v>
       </c>
       <c r="E159" t="n">
-        <v>89.65000152587891</v>
+        <v>89.33000183105469</v>
       </c>
       <c r="F159" t="n">
-        <v>35800500</v>
+        <v>34545700</v>
       </c>
       <c r="G159" t="n">
         <v>0</v>
@@ -4577,22 +4577,22 @@
     </row>
     <row r="160">
       <c r="A160" s="1" t="n">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="B160" t="n">
-        <v>90.13999938964844</v>
+        <v>88.51999664306641</v>
       </c>
       <c r="C160" t="n">
-        <v>91.48000335693359</v>
+        <v>88.55000305175781</v>
       </c>
       <c r="D160" t="n">
-        <v>88.69000244140625</v>
+        <v>87.5</v>
       </c>
       <c r="E160" t="n">
-        <v>89.33000183105469</v>
+        <v>88.08999633789062</v>
       </c>
       <c r="F160" t="n">
-        <v>34545700</v>
+        <v>23463400</v>
       </c>
       <c r="G160" t="n">
         <v>0</v>
@@ -4603,22 +4603,22 @@
     </row>
     <row r="161">
       <c r="A161" s="1" t="n">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="B161" t="n">
-        <v>88.51999664306641</v>
+        <v>88.02999877929688</v>
       </c>
       <c r="C161" t="n">
-        <v>88.55000305175781</v>
+        <v>90.37000274658203</v>
       </c>
       <c r="D161" t="n">
-        <v>87.5</v>
+        <v>87.51999664306641</v>
       </c>
       <c r="E161" t="n">
-        <v>88.08999633789062</v>
+        <v>89.30000305175781</v>
       </c>
       <c r="F161" t="n">
-        <v>23463400</v>
+        <v>28613900</v>
       </c>
       <c r="G161" t="n">
         <v>0</v>
@@ -4629,22 +4629,22 @@
     </row>
     <row r="162">
       <c r="A162" s="1" t="n">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="B162" t="n">
-        <v>88.02999877929688</v>
+        <v>89.09999847412109</v>
       </c>
       <c r="C162" t="n">
-        <v>90.37000274658203</v>
+        <v>89.97000122070312</v>
       </c>
       <c r="D162" t="n">
-        <v>87.51999664306641</v>
+        <v>88.16999816894531</v>
       </c>
       <c r="E162" t="n">
-        <v>89.30000305175781</v>
+        <v>88.59999847412109</v>
       </c>
       <c r="F162" t="n">
-        <v>28613900</v>
+        <v>23847200</v>
       </c>
       <c r="G162" t="n">
         <v>0</v>
@@ -4655,22 +4655,22 @@
     </row>
     <row r="163">
       <c r="A163" s="1" t="n">
-        <v>46164</v>
+        <v>46168</v>
       </c>
       <c r="B163" t="n">
-        <v>89.09999847412109</v>
+        <v>88.40000152587891</v>
       </c>
       <c r="C163" t="n">
-        <v>89.97000122070312</v>
+        <v>88.73000335693359</v>
       </c>
       <c r="D163" t="n">
-        <v>88.16999816894531</v>
+        <v>87.25</v>
       </c>
       <c r="E163" t="n">
-        <v>88.59999847412109</v>
+        <v>87.68000030517578</v>
       </c>
       <c r="F163" t="n">
-        <v>23847200</v>
+        <v>24014500</v>
       </c>
       <c r="G163" t="n">
         <v>0</v>
@@ -4681,22 +4681,22 @@
     </row>
     <row r="164">
       <c r="A164" s="1" t="n">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="B164" t="n">
-        <v>88.40000152587891</v>
+        <v>87.05000305175781</v>
       </c>
       <c r="C164" t="n">
-        <v>88.73000335693359</v>
+        <v>88.5</v>
       </c>
       <c r="D164" t="n">
-        <v>87.25</v>
+        <v>86.81999969482422</v>
       </c>
       <c r="E164" t="n">
-        <v>87.68000030517578</v>
+        <v>87.34999847412109</v>
       </c>
       <c r="F164" t="n">
-        <v>24014500</v>
+        <v>22569500</v>
       </c>
       <c r="G164" t="n">
         <v>0</v>
@@ -4707,22 +4707,22 @@
     </row>
     <row r="165">
       <c r="A165" s="1" t="n">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="B165" t="n">
-        <v>87.05000305175781</v>
+        <v>86.90000152587891</v>
       </c>
       <c r="C165" t="n">
-        <v>88.5</v>
+        <v>87.04000091552734</v>
       </c>
       <c r="D165" t="n">
-        <v>86.81999969482422</v>
+        <v>85.58999633789062</v>
       </c>
       <c r="E165" t="n">
-        <v>87.34999847412109</v>
+        <v>86.36000061035156</v>
       </c>
       <c r="F165" t="n">
-        <v>22569500</v>
+        <v>38803800</v>
       </c>
       <c r="G165" t="n">
         <v>0</v>
@@ -4733,22 +4733,22 @@
     </row>
     <row r="166">
       <c r="A166" s="1" t="n">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="B166" t="n">
-        <v>86.90000152587891</v>
+        <v>86.19999694824219</v>
       </c>
       <c r="C166" t="n">
-        <v>87.04000091552734</v>
+        <v>86.66999816894531</v>
       </c>
       <c r="D166" t="n">
-        <v>85.58999633789062</v>
+        <v>85.66000366210938</v>
       </c>
       <c r="E166" t="n">
-        <v>86.36000061035156</v>
+        <v>86.01999664306641</v>
       </c>
       <c r="F166" t="n">
-        <v>38803800</v>
+        <v>39793600</v>
       </c>
       <c r="G166" t="n">
         <v>0</v>
@@ -4759,22 +4759,22 @@
     </row>
     <row r="167">
       <c r="A167" s="1" t="n">
-        <v>46171</v>
+        <v>46174</v>
       </c>
       <c r="B167" t="n">
-        <v>86.19999694824219</v>
+        <v>85.73000335693359</v>
       </c>
       <c r="C167" t="n">
-        <v>86.66999816894531</v>
+        <v>87.23000335693359</v>
       </c>
       <c r="D167" t="n">
-        <v>85.66000366210938</v>
+        <v>85.31999969482422</v>
       </c>
       <c r="E167" t="n">
-        <v>86.01999664306641</v>
+        <v>85.84999847412109</v>
       </c>
       <c r="F167" t="n">
-        <v>39793600</v>
+        <v>32747200</v>
       </c>
       <c r="G167" t="n">
         <v>0</v>
@@ -4785,22 +4785,22 @@
     </row>
     <row r="168">
       <c r="A168" s="1" t="n">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="B168" t="n">
-        <v>85.73000335693359</v>
+        <v>85.61000061035156</v>
       </c>
       <c r="C168" t="n">
-        <v>87.23000335693359</v>
+        <v>85.98000335693359</v>
       </c>
       <c r="D168" t="n">
-        <v>85.31999969482422</v>
+        <v>83.29000091552734</v>
       </c>
       <c r="E168" t="n">
-        <v>85.84999847412109</v>
+        <v>83.33000183105469</v>
       </c>
       <c r="F168" t="n">
-        <v>32747200</v>
+        <v>42947200</v>
       </c>
       <c r="G168" t="n">
         <v>0</v>
@@ -4811,22 +4811,22 @@
     </row>
     <row r="169">
       <c r="A169" s="1" t="n">
-        <v>46175</v>
+        <v>46176</v>
       </c>
       <c r="B169" t="n">
-        <v>85.61000061035156</v>
+        <v>82.91000366210938</v>
       </c>
       <c r="C169" t="n">
-        <v>85.98000335693359</v>
+        <v>83.30999755859375</v>
       </c>
       <c r="D169" t="n">
-        <v>83.29000091552734</v>
+        <v>81.09999847412109</v>
       </c>
       <c r="E169" t="n">
-        <v>83.33000183105469</v>
+        <v>81.51999664306641</v>
       </c>
       <c r="F169" t="n">
-        <v>42947200</v>
+        <v>36714700</v>
       </c>
       <c r="G169" t="n">
         <v>0</v>
@@ -4837,22 +4837,22 @@
     </row>
     <row r="170">
       <c r="A170" s="1" t="n">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="B170" t="n">
-        <v>82.91000366210938</v>
+        <v>83.19000244140625</v>
       </c>
       <c r="C170" t="n">
-        <v>83.30999755859375</v>
+        <v>83.69999694824219</v>
       </c>
       <c r="D170" t="n">
-        <v>81.09999847412109</v>
+        <v>81.37000274658203</v>
       </c>
       <c r="E170" t="n">
-        <v>81.51999664306641</v>
+        <v>81.55999755859375</v>
       </c>
       <c r="F170" t="n">
-        <v>36714700</v>
+        <v>39338800</v>
       </c>
       <c r="G170" t="n">
         <v>0</v>
@@ -4863,22 +4863,22 @@
     </row>
     <row r="171">
       <c r="A171" s="1" t="n">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="B171" t="n">
-        <v>83.19000244140625</v>
+        <v>82.33000183105469</v>
       </c>
       <c r="C171" t="n">
-        <v>83.69999694824219</v>
+        <v>82.75</v>
       </c>
       <c r="D171" t="n">
-        <v>81.37000274658203</v>
+        <v>81</v>
       </c>
       <c r="E171" t="n">
-        <v>81.55999755859375</v>
+        <v>82.18000030517578</v>
       </c>
       <c r="F171" t="n">
-        <v>39338800</v>
+        <v>43474100</v>
       </c>
       <c r="G171" t="n">
         <v>0</v>
@@ -4889,22 +4889,22 @@
     </row>
     <row r="172">
       <c r="A172" s="1" t="n">
-        <v>46178</v>
+        <v>46181</v>
       </c>
       <c r="B172" t="n">
-        <v>82.33000183105469</v>
+        <v>81.66000366210938</v>
       </c>
       <c r="C172" t="n">
-        <v>82.75</v>
+        <v>83.08000183105469</v>
       </c>
       <c r="D172" t="n">
-        <v>81</v>
+        <v>81.33999633789062</v>
       </c>
       <c r="E172" t="n">
-        <v>82.18000030517578</v>
+        <v>82.63999938964844</v>
       </c>
       <c r="F172" t="n">
-        <v>43474100</v>
+        <v>33056700</v>
       </c>
       <c r="G172" t="n">
         <v>0</v>
@@ -4915,22 +4915,22 @@
     </row>
     <row r="173">
       <c r="A173" s="1" t="n">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="B173" t="n">
-        <v>81.66000366210938</v>
+        <v>82.12999725341797</v>
       </c>
       <c r="C173" t="n">
-        <v>83.08000183105469</v>
+        <v>82.33999633789062</v>
       </c>
       <c r="D173" t="n">
         <v>81.33999633789062</v>
       </c>
       <c r="E173" t="n">
-        <v>82.63999938964844</v>
+        <v>81.41000366210938</v>
       </c>
       <c r="F173" t="n">
-        <v>33056700</v>
+        <v>34787200</v>
       </c>
       <c r="G173" t="n">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="174">
       <c r="A174" s="1" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="B174" t="n">
-        <v>82.12999725341797</v>
+        <v>81.70999908447266</v>
       </c>
       <c r="C174" t="n">
-        <v>82.33999633789062</v>
+        <v>82.75</v>
       </c>
       <c r="D174" t="n">
-        <v>81.33999633789062</v>
+        <v>80.98000335693359</v>
       </c>
       <c r="E174" t="n">
-        <v>81.41000366210938</v>
+        <v>82</v>
       </c>
       <c r="F174" t="n">
-        <v>34787200</v>
+        <v>36304600</v>
       </c>
       <c r="G174" t="n">
         <v>0</v>
@@ -4967,22 +4967,22 @@
     </row>
     <row r="175">
       <c r="A175" s="1" t="n">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="B175" t="n">
-        <v>81.70999908447266</v>
+        <v>81.87000274658203</v>
       </c>
       <c r="C175" t="n">
-        <v>82.75</v>
+        <v>82.09999847412109</v>
       </c>
       <c r="D175" t="n">
-        <v>80.98000335693359</v>
+        <v>80.08999633789062</v>
       </c>
       <c r="E175" t="n">
-        <v>82</v>
+        <v>81.26999664306641</v>
       </c>
       <c r="F175" t="n">
-        <v>36304600</v>
+        <v>33417600</v>
       </c>
       <c r="G175" t="n">
         <v>0</v>
@@ -4993,22 +4993,22 @@
     </row>
     <row r="176">
       <c r="A176" s="1" t="n">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="B176" t="n">
-        <v>81.87000274658203</v>
+        <v>81.58000183105469</v>
       </c>
       <c r="C176" t="n">
-        <v>82.09999847412109</v>
+        <v>82</v>
       </c>
       <c r="D176" t="n">
-        <v>80.08999633789062</v>
+        <v>79.27999877929688</v>
       </c>
       <c r="E176" t="n">
-        <v>81.26999664306641</v>
+        <v>80.33999633789062</v>
       </c>
       <c r="F176" t="n">
-        <v>33417600</v>
+        <v>35309700</v>
       </c>
       <c r="G176" t="n">
         <v>0</v>
@@ -5019,22 +5019,22 @@
     </row>
     <row r="177">
       <c r="A177" s="1" t="n">
-        <v>46185</v>
+        <v>46188</v>
       </c>
       <c r="B177" t="n">
-        <v>81.58000183105469</v>
+        <v>80.62000274658203</v>
       </c>
       <c r="C177" t="n">
-        <v>82</v>
+        <v>81.70999908447266</v>
       </c>
       <c r="D177" t="n">
-        <v>79.27999877929688</v>
+        <v>80.45999908447266</v>
       </c>
       <c r="E177" t="n">
-        <v>80.33999633789062</v>
+        <v>81.66999816894531</v>
       </c>
       <c r="F177" t="n">
-        <v>35309700</v>
+        <v>36430800</v>
       </c>
       <c r="G177" t="n">
         <v>0</v>
@@ -5045,22 +5045,22 @@
     </row>
     <row r="178">
       <c r="A178" s="1" t="n">
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="B178" t="n">
-        <v>80.62000274658203</v>
+        <v>81.90000152587891</v>
       </c>
       <c r="C178" t="n">
-        <v>81.70999908447266</v>
+        <v>81.93000030517578</v>
       </c>
       <c r="D178" t="n">
-        <v>80.45999908447266</v>
+        <v>77.70999908447266</v>
       </c>
       <c r="E178" t="n">
-        <v>81.66999816894531</v>
+        <v>78.72000122070312</v>
       </c>
       <c r="F178" t="n">
-        <v>36430800</v>
+        <v>65054000</v>
       </c>
       <c r="G178" t="n">
         <v>0</v>
@@ -5071,22 +5071,22 @@
     </row>
     <row r="179">
       <c r="A179" s="1" t="n">
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="B179" t="n">
-        <v>81.90000152587891</v>
+        <v>78.09999847412109</v>
       </c>
       <c r="C179" t="n">
-        <v>81.93000030517578</v>
+        <v>78.44999694824219</v>
       </c>
       <c r="D179" t="n">
-        <v>77.70999908447266</v>
+        <v>76.76000213623047</v>
       </c>
       <c r="E179" t="n">
-        <v>78.72000122070312</v>
+        <v>76.95999908447266</v>
       </c>
       <c r="F179" t="n">
-        <v>65054000</v>
+        <v>50338800</v>
       </c>
       <c r="G179" t="n">
         <v>0</v>
@@ -5097,22 +5097,22 @@
     </row>
     <row r="180">
       <c r="A180" s="1" t="n">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="B180" t="n">
-        <v>78.09999847412109</v>
+        <v>76.93000030517578</v>
       </c>
       <c r="C180" t="n">
-        <v>78.44999694824219</v>
+        <v>78.23999786376953</v>
       </c>
       <c r="D180" t="n">
-        <v>76.76000213623047</v>
+        <v>76.12000274658203</v>
       </c>
       <c r="E180" t="n">
-        <v>76.95999908447266</v>
+        <v>77.37999725341797</v>
       </c>
       <c r="F180" t="n">
-        <v>50338800</v>
+        <v>91920400</v>
       </c>
       <c r="G180" t="n">
         <v>0</v>
@@ -5123,22 +5123,22 @@
     </row>
     <row r="181">
       <c r="A181" s="1" t="n">
-        <v>46191</v>
+        <v>46195</v>
       </c>
       <c r="B181" t="n">
-        <v>76.93000030517578</v>
+        <v>76.13999938964844</v>
       </c>
       <c r="C181" t="n">
-        <v>78.23999786376953</v>
+        <v>77.08999633789062</v>
       </c>
       <c r="D181" t="n">
-        <v>76.12000274658203</v>
+        <v>71.80999755859375</v>
       </c>
       <c r="E181" t="n">
-        <v>77.37999725341797</v>
+        <v>72.87999725341797</v>
       </c>
       <c r="F181" t="n">
-        <v>91920400</v>
+        <v>82203300</v>
       </c>
       <c r="G181" t="n">
         <v>0</v>
@@ -5149,22 +5149,22 @@
     </row>
     <row r="182">
       <c r="A182" s="1" t="n">
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="B182" t="n">
-        <v>76.13999938964844</v>
+        <v>73.26000213623047</v>
       </c>
       <c r="C182" t="n">
-        <v>77.08999633789062</v>
+        <v>73.95999908447266</v>
       </c>
       <c r="D182" t="n">
-        <v>71.80999755859375</v>
+        <v>72.62999725341797</v>
       </c>
       <c r="E182" t="n">
-        <v>72.87999725341797</v>
+        <v>72.81999969482422</v>
       </c>
       <c r="F182" t="n">
-        <v>82203300</v>
+        <v>50806800</v>
       </c>
       <c r="G182" t="n">
         <v>0</v>
@@ -5175,22 +5175,22 @@
     </row>
     <row r="183">
       <c r="A183" s="1" t="n">
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="B183" t="n">
-        <v>73.26000213623047</v>
+        <v>72.69000244140625</v>
       </c>
       <c r="C183" t="n">
-        <v>73.95999908447266</v>
+        <v>73.44999694824219</v>
       </c>
       <c r="D183" t="n">
-        <v>72.62999725341797</v>
+        <v>71.62999725341797</v>
       </c>
       <c r="E183" t="n">
-        <v>72.81999969482422</v>
+        <v>71.83999633789062</v>
       </c>
       <c r="F183" t="n">
-        <v>50806800</v>
+        <v>48001500</v>
       </c>
       <c r="G183" t="n">
         <v>0</v>
@@ -5201,22 +5201,22 @@
     </row>
     <row r="184">
       <c r="A184" s="1" t="n">
-        <v>46197</v>
+        <v>46198</v>
       </c>
       <c r="B184" t="n">
-        <v>72.69000244140625</v>
+        <v>71.33000183105469</v>
       </c>
       <c r="C184" t="n">
-        <v>73.44999694824219</v>
+        <v>72.94000244140625</v>
       </c>
       <c r="D184" t="n">
-        <v>71.62999725341797</v>
+        <v>70.86000061035156</v>
       </c>
       <c r="E184" t="n">
-        <v>71.83999633789062</v>
+        <v>70.90000152587891</v>
       </c>
       <c r="F184" t="n">
-        <v>48001500</v>
+        <v>44446900</v>
       </c>
       <c r="G184" t="n">
         <v>0</v>
@@ -5227,22 +5227,22 @@
     </row>
     <row r="185">
       <c r="A185" s="1" t="n">
-        <v>46198</v>
+        <v>46199</v>
       </c>
       <c r="B185" t="n">
-        <v>71.33000183105469</v>
+        <v>71.69000244140625</v>
       </c>
       <c r="C185" t="n">
-        <v>72.94000244140625</v>
+        <v>75.19999694824219</v>
       </c>
       <c r="D185" t="n">
-        <v>70.86000061035156</v>
+        <v>71.52999877929688</v>
       </c>
       <c r="E185" t="n">
-        <v>70.90000152587891</v>
+        <v>73.80999755859375</v>
       </c>
       <c r="F185" t="n">
-        <v>44446900</v>
+        <v>74990300</v>
       </c>
       <c r="G185" t="n">
         <v>0</v>
@@ -5253,22 +5253,22 @@
     </row>
     <row r="186">
       <c r="A186" s="1" t="n">
-        <v>46199</v>
+        <v>46202</v>
       </c>
       <c r="B186" t="n">
-        <v>71.69000244140625</v>
+        <v>74.62000274658203</v>
       </c>
       <c r="C186" t="n">
-        <v>75.19999694824219</v>
+        <v>76.06999969482422</v>
       </c>
       <c r="D186" t="n">
-        <v>71.52999877929688</v>
+        <v>73.73000335693359</v>
       </c>
       <c r="E186" t="n">
-        <v>73.80999755859375</v>
+        <v>73.77999877929688</v>
       </c>
       <c r="F186" t="n">
-        <v>74990300</v>
+        <v>42429600</v>
       </c>
       <c r="G186" t="n">
         <v>0</v>
@@ -5279,22 +5279,22 @@
     </row>
     <row r="187">
       <c r="A187" s="1" t="n">
-        <v>46202</v>
+        <v>46203</v>
       </c>
       <c r="B187" t="n">
-        <v>74.62000274658203</v>
+        <v>73.58999633789062</v>
       </c>
       <c r="C187" t="n">
-        <v>76.06999969482422</v>
+        <v>73.75</v>
       </c>
       <c r="D187" t="n">
-        <v>73.73000335693359</v>
+        <v>71</v>
       </c>
       <c r="E187" t="n">
-        <v>73.77999877929688</v>
+        <v>71.40000152587891</v>
       </c>
       <c r="F187" t="n">
-        <v>42429600</v>
+        <v>49240900</v>
       </c>
       <c r="G187" t="n">
         <v>0</v>
@@ -5305,22 +5305,22 @@
     </row>
     <row r="188">
       <c r="A188" s="1" t="n">
-        <v>46203</v>
+        <v>46204</v>
       </c>
       <c r="B188" t="n">
-        <v>73.58999633789062</v>
+        <v>72.58999633789062</v>
       </c>
       <c r="C188" t="n">
-        <v>73.75</v>
+        <v>74.36000061035156</v>
       </c>
       <c r="D188" t="n">
-        <v>71</v>
+        <v>72.33000183105469</v>
       </c>
       <c r="E188" t="n">
-        <v>71.40000152587891</v>
+        <v>74.19000244140625</v>
       </c>
       <c r="F188" t="n">
-        <v>49240900</v>
+        <v>43841800</v>
       </c>
       <c r="G188" t="n">
         <v>0</v>
@@ -5331,22 +5331,22 @@
     </row>
     <row r="189">
       <c r="A189" s="1" t="n">
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="B189" t="n">
-        <v>72.58999633789062</v>
+        <v>75.08999633789062</v>
       </c>
       <c r="C189" t="n">
-        <v>74.36000061035156</v>
+        <v>78.44000244140625</v>
       </c>
       <c r="D189" t="n">
-        <v>72.33000183105469</v>
+        <v>74.91000366210938</v>
       </c>
       <c r="E189" t="n">
-        <v>74.19000244140625</v>
+        <v>77.65000152587891</v>
       </c>
       <c r="F189" t="n">
-        <v>43841800</v>
+        <v>55456500</v>
       </c>
       <c r="G189" t="n">
         <v>0</v>
@@ -5357,22 +5357,22 @@
     </row>
     <row r="190">
       <c r="A190" s="1" t="n">
-        <v>46205</v>
+        <v>46209</v>
       </c>
       <c r="B190" t="n">
-        <v>75.08999633789062</v>
+        <v>77.08000183105469</v>
       </c>
       <c r="C190" t="n">
-        <v>78.44000244140625</v>
+        <v>77.83999633789062</v>
       </c>
       <c r="D190" t="n">
-        <v>74.91000366210938</v>
+        <v>75.70999908447266</v>
       </c>
       <c r="E190" t="n">
-        <v>77.65000152587891</v>
+        <v>76.01999664306641</v>
       </c>
       <c r="F190" t="n">
-        <v>55456500</v>
+        <v>45056600</v>
       </c>
       <c r="G190" t="n">
         <v>0</v>
@@ -5383,22 +5383,22 @@
     </row>
     <row r="191">
       <c r="A191" s="1" t="n">
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="B191" t="n">
-        <v>77.08000183105469</v>
+        <v>77.87999725341797</v>
       </c>
       <c r="C191" t="n">
-        <v>77.83999633789062</v>
+        <v>78.19000244140625</v>
       </c>
       <c r="D191" t="n">
-        <v>75.70999908447266</v>
+        <v>76.09999847412109</v>
       </c>
       <c r="E191" t="n">
-        <v>76.01999664306641</v>
+        <v>76.18000030517578</v>
       </c>
       <c r="F191" t="n">
-        <v>45056600</v>
+        <v>33257300</v>
       </c>
       <c r="G191" t="n">
         <v>0</v>
@@ -5409,22 +5409,22 @@
     </row>
     <row r="192">
       <c r="A192" s="1" t="n">
-        <v>46210</v>
+        <v>46211</v>
       </c>
       <c r="B192" t="n">
-        <v>77.87999725341797</v>
+        <v>76.26999664306641</v>
       </c>
       <c r="C192" t="n">
-        <v>78.19000244140625</v>
+        <v>76.63999938964844</v>
       </c>
       <c r="D192" t="n">
-        <v>76.09999847412109</v>
+        <v>74.88999938964844</v>
       </c>
       <c r="E192" t="n">
-        <v>76.18000030517578</v>
+        <v>75.58999633789062</v>
       </c>
       <c r="F192" t="n">
-        <v>33257300</v>
+        <v>34373500</v>
       </c>
       <c r="G192" t="n">
         <v>0</v>
@@ -5435,22 +5435,22 @@
     </row>
     <row r="193">
       <c r="A193" s="1" t="n">
-        <v>46211</v>
+        <v>46212</v>
       </c>
       <c r="B193" t="n">
-        <v>76.26999664306641</v>
+        <v>74.30000305175781</v>
       </c>
       <c r="C193" t="n">
-        <v>76.63999938964844</v>
+        <v>75.55000305175781</v>
       </c>
       <c r="D193" t="n">
-        <v>74.88999938964844</v>
+        <v>74.01999664306641</v>
       </c>
       <c r="E193" t="n">
-        <v>75.58999633789062</v>
+        <v>75.47000122070312</v>
       </c>
       <c r="F193" t="n">
-        <v>34373500</v>
+        <v>36305700</v>
       </c>
       <c r="G193" t="n">
         <v>0</v>
@@ -5461,22 +5461,22 @@
     </row>
     <row r="194">
       <c r="A194" s="1" t="n">
-        <v>46212</v>
+        <v>46213</v>
       </c>
       <c r="B194" t="n">
-        <v>74.30000305175781</v>
+        <v>75.44000244140625</v>
       </c>
       <c r="C194" t="n">
-        <v>75.55000305175781</v>
+        <v>75.69999694824219</v>
       </c>
       <c r="D194" t="n">
-        <v>74.01999664306641</v>
+        <v>72.51000213623047</v>
       </c>
       <c r="E194" t="n">
-        <v>75.47000122070312</v>
+        <v>73.37000274658203</v>
       </c>
       <c r="F194" t="n">
-        <v>36305700</v>
+        <v>46713900</v>
       </c>
       <c r="G194" t="n">
         <v>0</v>
@@ -5487,22 +5487,22 @@
     </row>
     <row r="195">
       <c r="A195" s="1" t="n">
-        <v>46213</v>
+        <v>46216</v>
       </c>
       <c r="B195" t="n">
-        <v>75.44000244140625</v>
+        <v>73.90000152587891</v>
       </c>
       <c r="C195" t="n">
-        <v>75.69999694824219</v>
+        <v>75.44999694824219</v>
       </c>
       <c r="D195" t="n">
-        <v>72.51000213623047</v>
+        <v>73.70999908447266</v>
       </c>
       <c r="E195" t="n">
-        <v>73.37000274658203</v>
+        <v>73.83000183105469</v>
       </c>
       <c r="F195" t="n">
-        <v>46713900</v>
+        <v>35101800</v>
       </c>
       <c r="G195" t="n">
         <v>0</v>
@@ -5513,22 +5513,22 @@
     </row>
     <row r="196">
       <c r="A196" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="B196" t="n">
-        <v>73.90000152587891</v>
+        <v>72.63999938964844</v>
       </c>
       <c r="C196" t="n">
-        <v>75.44999694824219</v>
+        <v>74.01000213623047</v>
       </c>
       <c r="D196" t="n">
-        <v>73.70999908447266</v>
+        <v>72.27999877929688</v>
       </c>
       <c r="E196" t="n">
-        <v>73.83000183105469</v>
+        <v>73.52999877929688</v>
       </c>
       <c r="F196" t="n">
-        <v>35101800</v>
+        <v>33312100</v>
       </c>
       <c r="G196" t="n">
         <v>0</v>
@@ -5539,22 +5539,22 @@
     </row>
     <row r="197">
       <c r="A197" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="B197" t="n">
-        <v>72.63999938964844</v>
+        <v>73.79000091552734</v>
       </c>
       <c r="C197" t="n">
-        <v>74.01000213623047</v>
+        <v>75.05999755859375</v>
       </c>
       <c r="D197" t="n">
-        <v>72.27999877929688</v>
+        <v>73.12999725341797</v>
       </c>
       <c r="E197" t="n">
-        <v>73.52999877929688</v>
+        <v>73.68000030517578</v>
       </c>
       <c r="F197" t="n">
-        <v>33312100</v>
+        <v>32854300</v>
       </c>
       <c r="G197" t="n">
         <v>0</v>
@@ -5565,22 +5565,22 @@
     </row>
     <row r="198">
       <c r="A198" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="B198" t="n">
-        <v>73.79000091552734</v>
+        <v>73.94999694824219</v>
       </c>
       <c r="C198" t="n">
-        <v>75.05999755859375</v>
+        <v>74.68000030517578</v>
       </c>
       <c r="D198" t="n">
-        <v>73.12999725341797</v>
+        <v>72.94000244140625</v>
       </c>
       <c r="E198" t="n">
-        <v>73.68000030517578</v>
+        <v>74.34999847412109</v>
       </c>
       <c r="F198" t="n">
-        <v>32854300</v>
+        <v>77505200</v>
       </c>
       <c r="G198" t="n">
         <v>0</v>
@@ -5591,22 +5591,22 @@
     </row>
     <row r="199">
       <c r="A199" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="B199" t="n">
-        <v>73.94999694824219</v>
+        <v>65.48000335693359</v>
       </c>
       <c r="C199" t="n">
-        <v>74.68000030517578</v>
+        <v>69.48999786376953</v>
       </c>
       <c r="D199" t="n">
-        <v>72.94000244140625</v>
+        <v>65.08000183105469</v>
       </c>
       <c r="E199" t="n">
-        <v>74.34999847412109</v>
+        <v>68.94999694824219</v>
       </c>
       <c r="F199" t="n">
-        <v>77505200</v>
+        <v>142029200</v>
       </c>
       <c r="G199" t="n">
         <v>0</v>
@@ -5617,22 +5617,22 @@
     </row>
     <row r="200">
       <c r="A200" s="1" t="n">
-        <v>46220</v>
+        <v>46223</v>
       </c>
       <c r="B200" t="n">
-        <v>65.48000335693359</v>
+        <v>68.31999969482422</v>
       </c>
       <c r="C200" t="n">
-        <v>69.48999786376953</v>
+        <v>68.37999725341797</v>
       </c>
       <c r="D200" t="n">
-        <v>65.08000183105469</v>
+        <v>66.69000244140625</v>
       </c>
       <c r="E200" t="n">
-        <v>68.94999694824219</v>
+        <v>67.59999847412109</v>
       </c>
       <c r="F200" t="n">
-        <v>142029200</v>
+        <v>60669100</v>
       </c>
       <c r="G200" t="n">
         <v>0</v>
@@ -5643,22 +5643,22 @@
     </row>
     <row r="201">
       <c r="A201" s="1" t="n">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="B201" t="n">
-        <v>68.31999969482422</v>
+        <v>67.41999816894531</v>
       </c>
       <c r="C201" t="n">
-        <v>68.37999725341797</v>
+        <v>68.75</v>
       </c>
       <c r="D201" t="n">
-        <v>66.69000244140625</v>
+        <v>66.73000335693359</v>
       </c>
       <c r="E201" t="n">
-        <v>67.59999847412109</v>
+        <v>68.66999816894531</v>
       </c>
       <c r="F201" t="n">
-        <v>60669100</v>
+        <v>56565800</v>
       </c>
       <c r="G201" t="n">
         <v>0</v>
@@ -5669,22 +5669,22 @@
     </row>
     <row r="202">
       <c r="A202" s="1" t="n">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="B202" t="n">
-        <v>67.41999816894531</v>
+        <v>69.37000274658203</v>
       </c>
       <c r="C202" t="n">
-        <v>68.75</v>
+        <v>70.56999969482422</v>
       </c>
       <c r="D202" t="n">
-        <v>66.73000335693359</v>
+        <v>68.34999847412109</v>
       </c>
       <c r="E202" t="n">
-        <v>68.66999816894531</v>
+        <v>68.52999877929688</v>
       </c>
       <c r="F202" t="n">
-        <v>56565800</v>
+        <v>44947300</v>
       </c>
       <c r="G202" t="n">
         <v>0</v>
@@ -5695,22 +5695,22 @@
     </row>
     <row r="203">
       <c r="A203" s="1" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="B203" t="n">
-        <v>69.37000274658203</v>
+        <v>68.56999969482422</v>
       </c>
       <c r="C203" t="n">
-        <v>70.56999969482422</v>
+        <v>69.36000061035156</v>
       </c>
       <c r="D203" t="n">
-        <v>68.34999847412109</v>
+        <v>67.66999816894531</v>
       </c>
       <c r="E203" t="n">
-        <v>68.52999877929688</v>
+        <v>68.88999938964844</v>
       </c>
       <c r="F203" t="n">
-        <v>44947300</v>
+        <v>45029100</v>
       </c>
       <c r="G203" t="n">
         <v>0</v>
@@ -5721,22 +5721,22 @@
     </row>
     <row r="204">
       <c r="A204" s="1" t="n">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="B204" t="n">
-        <v>68.56999969482422</v>
+        <v>69.29000091552734</v>
       </c>
       <c r="C204" t="n">
-        <v>69.36000061035156</v>
+        <v>70.68000030517578</v>
       </c>
       <c r="D204" t="n">
-        <v>67.66999816894531</v>
+        <v>67.97000122070312</v>
       </c>
       <c r="E204" t="n">
-        <v>68.88999938964844</v>
+        <v>70.08999633789062</v>
       </c>
       <c r="F204" t="n">
-        <v>45029100</v>
+        <v>37593500</v>
       </c>
       <c r="G204" t="n">
         <v>0</v>
@@ -5747,22 +5747,22 @@
     </row>
     <row r="205">
       <c r="A205" s="1" t="n">
-        <v>46227</v>
+        <v>46230</v>
       </c>
       <c r="B205" t="n">
-        <v>69.29000091552734</v>
+        <v>70.58999633789062</v>
       </c>
       <c r="C205" t="n">
-        <v>70.68000030517578</v>
+        <v>71.65000152587891</v>
       </c>
       <c r="D205" t="n">
-        <v>67.97000122070312</v>
+        <v>69.86000061035156</v>
       </c>
       <c r="E205" t="n">
-        <v>70.08999633789062</v>
+        <v>70.40000152587891</v>
       </c>
       <c r="F205" t="n">
-        <v>37593500</v>
+        <v>39090800</v>
       </c>
       <c r="G205" t="n">
         <v>0</v>
@@ -5773,22 +5773,22 @@
     </row>
     <row r="206">
       <c r="A206" s="1" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="B206" t="n">
-        <v>70.58999633789062</v>
+        <v>72.06999969482422</v>
       </c>
       <c r="C206" t="n">
-        <v>71.65000152587891</v>
+        <v>73.76000213623047</v>
       </c>
       <c r="D206" t="n">
-        <v>69.86000061035156</v>
+        <v>71.23000335693359</v>
       </c>
       <c r="E206" t="n">
-        <v>70.40000152587891</v>
+        <v>72.38999938964844</v>
       </c>
       <c r="F206" t="n">
-        <v>39090800</v>
+        <v>47160200</v>
       </c>
       <c r="G206" t="n">
         <v>0</v>
@@ -5799,22 +5799,22 @@
     </row>
     <row r="207">
       <c r="A207" s="1" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="B207" t="n">
-        <v>72.06999969482422</v>
+        <v>72.19000244140625</v>
       </c>
       <c r="C207" t="n">
-        <v>73.76000213623047</v>
+        <v>73.73999786376953</v>
       </c>
       <c r="D207" t="n">
-        <v>71.23000335693359</v>
+        <v>71.75</v>
       </c>
       <c r="E207" t="n">
-        <v>72.38999938964844</v>
+        <v>73.62999725341797</v>
       </c>
       <c r="F207" t="n">
-        <v>47160200</v>
+        <v>43737600</v>
       </c>
       <c r="G207" t="n">
         <v>0</v>
@@ -5825,22 +5825,22 @@
     </row>
     <row r="208">
       <c r="A208" s="1" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="B208" t="n">
-        <v>72.19000244140625</v>
+        <v>71.48000335693359</v>
       </c>
       <c r="C208" t="n">
-        <v>73.73999786376953</v>
+        <v>73.31999969482422</v>
       </c>
       <c r="D208" t="n">
-        <v>71.75</v>
+        <v>70.55000305175781</v>
       </c>
       <c r="E208" t="n">
-        <v>73.62999725341797</v>
+        <v>73.16999816894531</v>
       </c>
       <c r="F208" t="n">
-        <v>43737600</v>
+        <v>54261000</v>
       </c>
       <c r="G208" t="n">
         <v>0</v>
@@ -5851,22 +5851,22 @@
     </row>
     <row r="209">
       <c r="A209" s="1" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="B209" t="n">
-        <v>71.48000335693359</v>
+        <v>71.97000122070312</v>
       </c>
       <c r="C209" t="n">
-        <v>73.31999969482422</v>
+        <v>72.75</v>
       </c>
       <c r="D209" t="n">
-        <v>70.55000305175781</v>
+        <v>71.11000061035156</v>
       </c>
       <c r="E209" t="n">
-        <v>73.16999816894531</v>
+        <v>71.70999908447266</v>
       </c>
       <c r="F209" t="n">
-        <v>54261000</v>
+        <v>35847500</v>
       </c>
       <c r="G209" t="n">
         <v>0</v>
@@ -5877,22 +5877,22 @@
     </row>
     <row r="210">
       <c r="A210" s="1" t="n">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="B210" t="n">
-        <v>71.97000122070312</v>
+        <v>72.76999664306641</v>
       </c>
       <c r="C210" t="n">
-        <v>72.75</v>
+        <v>73.94999694824219</v>
       </c>
       <c r="D210" t="n">
-        <v>71.11000061035156</v>
+        <v>72.18000030517578</v>
       </c>
       <c r="E210" t="n">
-        <v>71.70999908447266</v>
+        <v>73.33000183105469</v>
       </c>
       <c r="F210" t="n">
-        <v>35847500</v>
+        <v>33922300</v>
       </c>
       <c r="G210" t="n">
         <v>0</v>
@@ -5903,22 +5903,22 @@
     </row>
     <row r="211">
       <c r="A211" s="1" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="B211" t="n">
-        <v>72.76999664306641</v>
+        <v>72.51000213623047</v>
       </c>
       <c r="C211" t="n">
-        <v>73.94999694824219</v>
+        <v>73.75</v>
       </c>
       <c r="D211" t="n">
-        <v>72.18000030517578</v>
+        <v>72.30000305175781</v>
       </c>
       <c r="E211" t="n">
-        <v>73.33000183105469</v>
+        <v>73.56999969482422</v>
       </c>
       <c r="F211" t="n">
-        <v>33922300</v>
+        <v>42877900</v>
       </c>
       <c r="G211" t="n">
         <v>0</v>
@@ -5929,22 +5929,22 @@
     </row>
     <row r="212">
       <c r="A212" s="1" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="B212" t="n">
-        <v>72.51000213623047</v>
+        <v>75.11000061035156</v>
       </c>
       <c r="C212" t="n">
-        <v>73.75</v>
+        <v>75.30000305175781</v>
       </c>
       <c r="D212" t="n">
-        <v>72.30000305175781</v>
+        <v>73.16000366210938</v>
       </c>
       <c r="E212" t="n">
-        <v>73.56999969482422</v>
+        <v>74.19999694824219</v>
       </c>
       <c r="F212" t="n">
-        <v>42877900</v>
+        <v>28969400</v>
       </c>
       <c r="G212" t="n">
         <v>0</v>
@@ -5955,22 +5955,22 @@
     </row>
     <row r="213">
       <c r="A213" s="1" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="B213" t="n">
-        <v>75.11000061035156</v>
+        <v>75.13999938964844</v>
       </c>
       <c r="C213" t="n">
-        <v>75.30000305175781</v>
+        <v>75.20999908447266</v>
       </c>
       <c r="D213" t="n">
-        <v>73.16000366210938</v>
+        <v>73.09999847412109</v>
       </c>
       <c r="E213" t="n">
-        <v>74.19999694824219</v>
+        <v>73.69000244140625</v>
       </c>
       <c r="F213" t="n">
-        <v>28969400</v>
+        <v>28892700</v>
       </c>
       <c r="G213" t="n">
         <v>0</v>
@@ -5981,22 +5981,22 @@
     </row>
     <row r="214">
       <c r="A214" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="B214" t="n">
-        <v>75.13999938964844</v>
+        <v>73.12000274658203</v>
       </c>
       <c r="C214" t="n">
-        <v>75.20999908447266</v>
+        <v>74.5</v>
       </c>
       <c r="D214" t="n">
-        <v>73.09999847412109</v>
+        <v>73.08000183105469</v>
       </c>
       <c r="E214" t="n">
-        <v>73.69000244140625</v>
+        <v>74.13999938964844</v>
       </c>
       <c r="F214" t="n">
-        <v>28892700</v>
+        <v>24819000</v>
       </c>
       <c r="G214" t="n">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="215">
       <c r="A215" s="1" t="n">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="B215" t="n">
-        <v>73.12000274658203</v>
+        <v>73.80000305175781</v>
       </c>
       <c r="C215" t="n">
-        <v>74.5</v>
+        <v>76.31999969482422</v>
       </c>
       <c r="D215" t="n">
-        <v>73.08000183105469</v>
+        <v>73.56999969482422</v>
       </c>
       <c r="E215" t="n">
-        <v>74.13999938964844</v>
+        <v>76.29000091552734</v>
       </c>
       <c r="F215" t="n">
-        <v>24819000</v>
+        <v>26959900</v>
       </c>
       <c r="G215" t="n">
         <v>0</v>
@@ -6033,22 +6033,22 @@
     </row>
     <row r="216">
       <c r="A216" s="1" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="B216" t="n">
-        <v>73.80000305175781</v>
+        <v>76.19999694824219</v>
       </c>
       <c r="C216" t="n">
-        <v>76.31999969482422</v>
+        <v>76.90000152587891</v>
       </c>
       <c r="D216" t="n">
-        <v>73.56999969482422</v>
+        <v>74.48000335693359</v>
       </c>
       <c r="E216" t="n">
-        <v>76.29000091552734</v>
+        <v>74.79000091552734</v>
       </c>
       <c r="F216" t="n">
-        <v>26959900</v>
+        <v>27840500</v>
       </c>
       <c r="G216" t="n">
         <v>0</v>
@@ -6059,22 +6059,22 @@
     </row>
     <row r="217">
       <c r="A217" s="1" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="B217" t="n">
-        <v>76.19999694824219</v>
+        <v>74.34999847412109</v>
       </c>
       <c r="C217" t="n">
-        <v>76.90000152587891</v>
+        <v>74.66999816894531</v>
       </c>
       <c r="D217" t="n">
-        <v>74.48000335693359</v>
+        <v>73.56999969482422</v>
       </c>
       <c r="E217" t="n">
-        <v>74.79000091552734</v>
+        <v>74.20999908447266</v>
       </c>
       <c r="F217" t="n">
-        <v>27840500</v>
+        <v>20773100</v>
       </c>
       <c r="G217" t="n">
         <v>0</v>
@@ -6085,22 +6085,22 @@
     </row>
     <row r="218">
       <c r="A218" s="1" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="B218" t="n">
-        <v>74.34999847412109</v>
+        <v>76.01000213623047</v>
       </c>
       <c r="C218" t="n">
-        <v>74.66999816894531</v>
+        <v>78.40000152587891</v>
       </c>
       <c r="D218" t="n">
-        <v>73.56999969482422</v>
+        <v>75.44000244140625</v>
       </c>
       <c r="E218" t="n">
-        <v>74.20999908447266</v>
+        <v>78.23999786376953</v>
       </c>
       <c r="F218" t="n">
-        <v>20773100</v>
+        <v>41452900</v>
       </c>
       <c r="G218" t="n">
         <v>0</v>
@@ -6111,22 +6111,22 @@
     </row>
     <row r="219">
       <c r="A219" s="1" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="B219" t="n">
-        <v>76.01000213623047</v>
+        <v>78.48000335693359</v>
       </c>
       <c r="C219" t="n">
-        <v>78.40000152587891</v>
+        <v>78.73000335693359</v>
       </c>
       <c r="D219" t="n">
-        <v>75.44000244140625</v>
+        <v>77.76000213623047</v>
       </c>
       <c r="E219" t="n">
-        <v>78.23999786376953</v>
+        <v>78.16000366210938</v>
       </c>
       <c r="F219" t="n">
-        <v>41452900</v>
+        <v>26751000</v>
       </c>
       <c r="G219" t="n">
         <v>0</v>
@@ -6137,22 +6137,22 @@
     </row>
     <row r="220">
       <c r="A220" s="1" t="n">
-        <v>46248</v>
+        <v>46251</v>
       </c>
       <c r="B220" t="n">
-        <v>78.48000335693359</v>
+        <v>77.80000305175781</v>
       </c>
       <c r="C220" t="n">
-        <v>78.73000335693359</v>
+        <v>78.52999877929688</v>
       </c>
       <c r="D220" t="n">
-        <v>77.76000213623047</v>
+        <v>75.47000122070312</v>
       </c>
       <c r="E220" t="n">
-        <v>78.16000366210938</v>
+        <v>76.01999664306641</v>
       </c>
       <c r="F220" t="n">
-        <v>26751000</v>
+        <v>30753000</v>
       </c>
       <c r="G220" t="n">
         <v>0</v>
@@ -6163,22 +6163,22 @@
     </row>
     <row r="221">
       <c r="A221" s="1" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="B221" t="n">
-        <v>77.80000305175781</v>
+        <v>77.43000030517578</v>
       </c>
       <c r="C221" t="n">
-        <v>78.52999877929688</v>
+        <v>79.09999847412109</v>
       </c>
       <c r="D221" t="n">
-        <v>75.47000122070312</v>
+        <v>76.33999633789062</v>
       </c>
       <c r="E221" t="n">
-        <v>76.01999664306641</v>
+        <v>77.76999664306641</v>
       </c>
       <c r="F221" t="n">
-        <v>30753000</v>
+        <v>36151300</v>
       </c>
       <c r="G221" t="n">
         <v>0</v>
@@ -6189,22 +6189,22 @@
     </row>
     <row r="222">
       <c r="A222" s="1" t="n">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="B222" t="n">
-        <v>77.43000030517578</v>
+        <v>78.25</v>
       </c>
       <c r="C222" t="n">
-        <v>79.09999847412109</v>
+        <v>81.16000366210938</v>
       </c>
       <c r="D222" t="n">
-        <v>76.33999633789062</v>
+        <v>78.09999847412109</v>
       </c>
       <c r="E222" t="n">
-        <v>77.76999664306641</v>
+        <v>80.22000122070312</v>
       </c>
       <c r="F222" t="n">
-        <v>36151300</v>
+        <v>31461800</v>
       </c>
       <c r="G222" t="n">
         <v>0</v>
@@ -6215,22 +6215,22 @@
     </row>
     <row r="223">
       <c r="A223" s="1" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="B223" t="n">
-        <v>78.25</v>
+        <v>80.13999938964844</v>
       </c>
       <c r="C223" t="n">
-        <v>81.16000366210938</v>
+        <v>81.08000183105469</v>
       </c>
       <c r="D223" t="n">
-        <v>78.09999847412109</v>
+        <v>79.58999633789062</v>
       </c>
       <c r="E223" t="n">
-        <v>80.22000122070312</v>
+        <v>80.13999938964844</v>
       </c>
       <c r="F223" t="n">
-        <v>31461800</v>
+        <v>27118400</v>
       </c>
       <c r="G223" t="n">
         <v>0</v>
@@ -6241,22 +6241,22 @@
     </row>
     <row r="224">
       <c r="A224" s="1" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="B224" t="n">
-        <v>80.13999938964844</v>
+        <v>80.29000091552734</v>
       </c>
       <c r="C224" t="n">
-        <v>81.08000183105469</v>
+        <v>80.48999786376953</v>
       </c>
       <c r="D224" t="n">
+        <v>79.16999816894531</v>
+      </c>
+      <c r="E224" t="n">
         <v>79.58999633789062</v>
       </c>
-      <c r="E224" t="n">
-        <v>80.13999938964844</v>
-      </c>
       <c r="F224" t="n">
-        <v>27118400</v>
+        <v>23773800</v>
       </c>
       <c r="G224" t="n">
         <v>0</v>
@@ -6267,22 +6267,22 @@
     </row>
     <row r="225">
       <c r="A225" s="1" t="n">
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="B225" t="n">
-        <v>80.29000091552734</v>
+        <v>79.94000244140625</v>
       </c>
       <c r="C225" t="n">
-        <v>80.48999786376953</v>
+        <v>80.62000274658203</v>
       </c>
       <c r="D225" t="n">
-        <v>79.16999816894531</v>
+        <v>79.01999664306641</v>
       </c>
       <c r="E225" t="n">
-        <v>79.58999633789062</v>
+        <v>80.01000213623047</v>
       </c>
       <c r="F225" t="n">
-        <v>23773800</v>
+        <v>21085300</v>
       </c>
       <c r="G225" t="n">
         <v>0</v>
@@ -6293,22 +6293,22 @@
     </row>
     <row r="226">
       <c r="A226" s="1" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="B226" t="n">
-        <v>79.94000244140625</v>
+        <v>79.65000152587891</v>
       </c>
       <c r="C226" t="n">
-        <v>80.62000274658203</v>
+        <v>82.45999908447266</v>
       </c>
       <c r="D226" t="n">
-        <v>79.01999664306641</v>
+        <v>79.40000152587891</v>
       </c>
       <c r="E226" t="n">
-        <v>80.01000213623047</v>
+        <v>82.23000335693359</v>
       </c>
       <c r="F226" t="n">
-        <v>21085300</v>
+        <v>29462000</v>
       </c>
       <c r="G226" t="n">
         <v>0</v>
@@ -6319,22 +6319,22 @@
     </row>
     <row r="227">
       <c r="A227" s="1" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="B227" t="n">
-        <v>79.65000152587891</v>
+        <v>82.05000305175781</v>
       </c>
       <c r="C227" t="n">
-        <v>82.45999908447266</v>
+        <v>82.41999816894531</v>
       </c>
       <c r="D227" t="n">
-        <v>79.40000152587891</v>
+        <v>81.30000305175781</v>
       </c>
       <c r="E227" t="n">
-        <v>82.23000335693359</v>
+        <v>81.45999908447266</v>
       </c>
       <c r="F227" t="n">
-        <v>29462000</v>
+        <v>22874900</v>
       </c>
       <c r="G227" t="n">
         <v>0</v>
@@ -6345,22 +6345,22 @@
     </row>
     <row r="228">
       <c r="A228" s="1" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="B228" t="n">
-        <v>82.05000305175781</v>
+        <v>81.06999969482422</v>
       </c>
       <c r="C228" t="n">
-        <v>82.41999816894531</v>
+        <v>81.15000152587891</v>
       </c>
       <c r="D228" t="n">
-        <v>81.30000305175781</v>
+        <v>79.27999877929688</v>
       </c>
       <c r="E228" t="n">
-        <v>81.45999908447266</v>
+        <v>79.83999633789062</v>
       </c>
       <c r="F228" t="n">
-        <v>22874900</v>
+        <v>27174400</v>
       </c>
       <c r="G228" t="n">
         <v>0</v>
@@ -6371,22 +6371,22 @@
     </row>
     <row r="229">
       <c r="A229" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="B229" t="n">
-        <v>81.06999969482422</v>
+        <v>80.36000061035156</v>
       </c>
       <c r="C229" t="n">
-        <v>81.15000152587891</v>
+        <v>82.34999847412109</v>
       </c>
       <c r="D229" t="n">
-        <v>79.27999877929688</v>
+        <v>79.94999694824219</v>
       </c>
       <c r="E229" t="n">
-        <v>79.83999633789062</v>
+        <v>81.72000122070312</v>
       </c>
       <c r="F229" t="n">
-        <v>27174400</v>
+        <v>29092700</v>
       </c>
       <c r="G229" t="n">
         <v>0</v>
@@ -6397,22 +6397,22 @@
     </row>
     <row r="230">
       <c r="A230" s="1" t="n">
-        <v>46262</v>
+        <v>46265</v>
       </c>
       <c r="B230" t="n">
-        <v>80.36000061035156</v>
+        <v>81</v>
       </c>
       <c r="C230" t="n">
-        <v>82.34999847412109</v>
+        <v>81.73000335693359</v>
       </c>
       <c r="D230" t="n">
-        <v>79.94999694824219</v>
+        <v>80.65000152587891</v>
       </c>
       <c r="E230" t="n">
-        <v>81.72000122070312</v>
+        <v>81.05000305175781</v>
       </c>
       <c r="F230" t="n">
-        <v>29092700</v>
+        <v>30740800</v>
       </c>
       <c r="G230" t="n">
         <v>0</v>
@@ -6423,22 +6423,22 @@
     </row>
     <row r="231">
       <c r="A231" s="1" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="B231" t="n">
-        <v>81</v>
+        <v>80.16999816894531</v>
       </c>
       <c r="C231" t="n">
-        <v>81.73000335693359</v>
+        <v>82.12999725341797</v>
       </c>
       <c r="D231" t="n">
-        <v>80.65000152587891</v>
+        <v>79.59999847412109</v>
       </c>
       <c r="E231" t="n">
-        <v>81.05000305175781</v>
+        <v>80.80999755859375</v>
       </c>
       <c r="F231" t="n">
-        <v>30740800</v>
+        <v>21164900</v>
       </c>
       <c r="G231" t="n">
         <v>0</v>
@@ -6449,22 +6449,22 @@
     </row>
     <row r="232">
       <c r="A232" s="1" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="B232" t="n">
-        <v>80.16999816894531</v>
+        <v>80.55000305175781</v>
       </c>
       <c r="C232" t="n">
-        <v>82.12999725341797</v>
+        <v>83.12000274658203</v>
       </c>
       <c r="D232" t="n">
-        <v>79.59999847412109</v>
+        <v>80.30000305175781</v>
       </c>
       <c r="E232" t="n">
-        <v>80.80999755859375</v>
+        <v>82.73000335693359</v>
       </c>
       <c r="F232" t="n">
-        <v>21164900</v>
+        <v>22077800</v>
       </c>
       <c r="G232" t="n">
         <v>0</v>
@@ -6475,22 +6475,22 @@
     </row>
     <row r="233">
       <c r="A233" s="1" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="B233" t="n">
-        <v>80.55000305175781</v>
+        <v>83.18000030517578</v>
       </c>
       <c r="C233" t="n">
-        <v>83.12000274658203</v>
+        <v>83.59999847412109</v>
       </c>
       <c r="D233" t="n">
-        <v>80.30000305175781</v>
+        <v>81.62999725341797</v>
       </c>
       <c r="E233" t="n">
-        <v>82.73000335693359</v>
+        <v>82.66999816894531</v>
       </c>
       <c r="F233" t="n">
-        <v>22077800</v>
+        <v>24006400</v>
       </c>
       <c r="G233" t="n">
         <v>0</v>
@@ -6501,22 +6501,22 @@
     </row>
     <row r="234">
       <c r="A234" s="1" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B234" t="n">
-        <v>83.18000030517578</v>
+        <v>82.16999816894531</v>
       </c>
       <c r="C234" t="n">
-        <v>83.59999847412109</v>
+        <v>82.69000244140625</v>
       </c>
       <c r="D234" t="n">
-        <v>81.62999725341797</v>
+        <v>78.23000335693359</v>
       </c>
       <c r="E234" t="n">
-        <v>82.66999816894531</v>
+        <v>78.25</v>
       </c>
       <c r="F234" t="n">
-        <v>24006400</v>
+        <v>40190000</v>
       </c>
       <c r="G234" t="n">
         <v>0</v>
@@ -6527,22 +6527,22 @@
     </row>
     <row r="235">
       <c r="A235" s="1" t="n">
-        <v>46269</v>
+        <v>46273</v>
       </c>
       <c r="B235" t="n">
-        <v>82.16999816894531</v>
+        <v>77.55000305175781</v>
       </c>
       <c r="C235" t="n">
-        <v>82.69000244140625</v>
+        <v>77.73000335693359</v>
       </c>
       <c r="D235" t="n">
-        <v>78.23000335693359</v>
+        <v>75.91999816894531</v>
       </c>
       <c r="E235" t="n">
-        <v>78.25</v>
+        <v>76.76999664306641</v>
       </c>
       <c r="F235" t="n">
-        <v>40190000</v>
+        <v>33865500</v>
       </c>
       <c r="G235" t="n">
         <v>0</v>
@@ -6553,22 +6553,22 @@
     </row>
     <row r="236">
       <c r="A236" s="1" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B236" t="n">
-        <v>77.55000305175781</v>
+        <v>76.33999633789062</v>
       </c>
       <c r="C236" t="n">
-        <v>77.73000335693359</v>
+        <v>76.72000122070312</v>
       </c>
       <c r="D236" t="n">
-        <v>75.91999816894531</v>
+        <v>75.87000274658203</v>
       </c>
       <c r="E236" t="n">
-        <v>76.76999664306641</v>
+        <v>76.02999877929688</v>
       </c>
       <c r="F236" t="n">
-        <v>33865500</v>
+        <v>22779600</v>
       </c>
       <c r="G236" t="n">
         <v>0</v>
@@ -6579,22 +6579,22 @@
     </row>
     <row r="237">
       <c r="A237" s="1" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="B237" t="n">
-        <v>76.33999633789062</v>
+        <v>75.33000183105469</v>
       </c>
       <c r="C237" t="n">
-        <v>76.72000122070312</v>
+        <v>76.30000305175781</v>
       </c>
       <c r="D237" t="n">
-        <v>75.87000274658203</v>
+        <v>75.02999877929688</v>
       </c>
       <c r="E237" t="n">
-        <v>76.02999877929688</v>
+        <v>76.01000213623047</v>
       </c>
       <c r="F237" t="n">
-        <v>22779600</v>
+        <v>20049000</v>
       </c>
       <c r="G237" t="n">
         <v>0</v>
@@ -6605,22 +6605,22 @@
     </row>
     <row r="238">
       <c r="A238" s="1" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="B238" t="n">
-        <v>75.33000183105469</v>
+        <v>76.63999938964844</v>
       </c>
       <c r="C238" t="n">
-        <v>76.30000305175781</v>
+        <v>77.56999969482422</v>
       </c>
       <c r="D238" t="n">
-        <v>75.02999877929688</v>
+        <v>76.15000152587891</v>
       </c>
       <c r="E238" t="n">
-        <v>76.01000213623047</v>
+        <v>77.40000152587891</v>
       </c>
       <c r="F238" t="n">
-        <v>20049000</v>
+        <v>22237800</v>
       </c>
       <c r="G238" t="n">
         <v>0</v>
@@ -6631,22 +6631,22 @@
     </row>
     <row r="239">
       <c r="A239" s="1" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="B239" t="n">
-        <v>76.63999938964844</v>
+        <v>78.97000122070312</v>
       </c>
       <c r="C239" t="n">
-        <v>77.56999969482422</v>
+        <v>81.01999664306641</v>
       </c>
       <c r="D239" t="n">
-        <v>76.15000152587891</v>
+        <v>78.48999786376953</v>
       </c>
       <c r="E239" t="n">
-        <v>77.40000152587891</v>
+        <v>80.31999969482422</v>
       </c>
       <c r="F239" t="n">
-        <v>22237800</v>
+        <v>30945100</v>
       </c>
       <c r="G239" t="n">
         <v>0</v>
@@ -6657,22 +6657,22 @@
     </row>
     <row r="240">
       <c r="A240" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="B240" t="n">
-        <v>78.97000122070312</v>
+        <v>79.37999725341797</v>
       </c>
       <c r="C240" t="n">
-        <v>81.01999664306641</v>
+        <v>79.48000335693359</v>
       </c>
       <c r="D240" t="n">
-        <v>78.48999786376953</v>
+        <v>77.45999908447266</v>
       </c>
       <c r="E240" t="n">
-        <v>80.31999969482422</v>
+        <v>77.90000152587891</v>
       </c>
       <c r="F240" t="n">
-        <v>30945100</v>
+        <v>28027400</v>
       </c>
       <c r="G240" t="n">
         <v>0</v>
@@ -6683,22 +6683,22 @@
     </row>
     <row r="241">
       <c r="A241" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="B241" t="n">
-        <v>79.37999725341797</v>
+        <v>77.73000335693359</v>
       </c>
       <c r="C241" t="n">
-        <v>79.48000335693359</v>
+        <v>77.80000305175781</v>
       </c>
       <c r="D241" t="n">
-        <v>77.45999908447266</v>
+        <v>76.30999755859375</v>
       </c>
       <c r="E241" t="n">
-        <v>77.90000152587891</v>
+        <v>76.41000366210938</v>
       </c>
       <c r="F241" t="n">
-        <v>28027400</v>
+        <v>25376300</v>
       </c>
       <c r="G241" t="n">
         <v>0</v>
@@ -6709,22 +6709,22 @@
     </row>
     <row r="242">
       <c r="A242" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="B242" t="n">
-        <v>77.73000335693359</v>
+        <v>76.91000366210938</v>
       </c>
       <c r="C242" t="n">
-        <v>77.80000305175781</v>
+        <v>76.95999908447266</v>
       </c>
       <c r="D242" t="n">
-        <v>76.30999755859375</v>
+        <v>75.30000305175781</v>
       </c>
       <c r="E242" t="n">
-        <v>76.41000366210938</v>
+        <v>75.30999755859375</v>
       </c>
       <c r="F242" t="n">
-        <v>25376300</v>
+        <v>28167600</v>
       </c>
       <c r="G242" t="n">
         <v>0</v>
@@ -6735,22 +6735,22 @@
     </row>
     <row r="243">
       <c r="A243" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="B243" t="n">
-        <v>76.91000366210938</v>
+        <v>71.26999664306641</v>
       </c>
       <c r="C243" t="n">
-        <v>76.95999908447266</v>
+        <v>72.37999725341797</v>
       </c>
       <c r="D243" t="n">
-        <v>75.30000305175781</v>
+        <v>70.11000061035156</v>
       </c>
       <c r="E243" t="n">
-        <v>75.30999755859375</v>
+        <v>71.79000091552734</v>
       </c>
       <c r="F243" t="n">
-        <v>28167600</v>
+        <v>114413500</v>
       </c>
       <c r="G243" t="n">
         <v>0</v>
@@ -6761,22 +6761,22 @@
     </row>
     <row r="244">
       <c r="A244" s="1" t="n">
-        <v>46283</v>
+        <v>46286</v>
       </c>
       <c r="B244" t="n">
-        <v>71.26999664306641</v>
+        <v>71.81999969482422</v>
       </c>
       <c r="C244" t="n">
-        <v>72.37999725341797</v>
+        <v>73.87000274658203</v>
       </c>
       <c r="D244" t="n">
-        <v>70.11000061035156</v>
+        <v>71.79000091552734</v>
       </c>
       <c r="E244" t="n">
-        <v>71.79000091552734</v>
+        <v>73.36000061035156</v>
       </c>
       <c r="F244" t="n">
-        <v>114413500</v>
+        <v>36948000</v>
       </c>
       <c r="G244" t="n">
         <v>0</v>
@@ -6787,22 +6787,22 @@
     </row>
     <row r="245">
       <c r="A245" s="1" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="B245" t="n">
-        <v>71.81999969482422</v>
+        <v>73.69000244140625</v>
       </c>
       <c r="C245" t="n">
-        <v>73.87000274658203</v>
+        <v>73.76000213623047</v>
       </c>
       <c r="D245" t="n">
-        <v>71.79000091552734</v>
+        <v>71.58000183105469</v>
       </c>
       <c r="E245" t="n">
-        <v>73.36000061035156</v>
+        <v>72.16000366210938</v>
       </c>
       <c r="F245" t="n">
-        <v>36948000</v>
+        <v>34372500</v>
       </c>
       <c r="G245" t="n">
         <v>0</v>
@@ -6813,22 +6813,22 @@
     </row>
     <row r="246">
       <c r="A246" s="1" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="B246" t="n">
-        <v>73.69000244140625</v>
+        <v>72.08000183105469</v>
       </c>
       <c r="C246" t="n">
-        <v>73.76000213623047</v>
+        <v>72.37000274658203</v>
       </c>
       <c r="D246" t="n">
-        <v>71.58000183105469</v>
+        <v>71.06999969482422</v>
       </c>
       <c r="E246" t="n">
-        <v>72.16000366210938</v>
+        <v>71.36000061035156</v>
       </c>
       <c r="F246" t="n">
-        <v>34372500</v>
+        <v>32807500</v>
       </c>
       <c r="G246" t="n">
         <v>0</v>
@@ -6839,22 +6839,22 @@
     </row>
     <row r="247">
       <c r="A247" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="B247" t="n">
-        <v>72.08000183105469</v>
+        <v>71.62000274658203</v>
       </c>
       <c r="C247" t="n">
-        <v>72.37000274658203</v>
+        <v>72.04000091552734</v>
       </c>
       <c r="D247" t="n">
-        <v>71.06999969482422</v>
+        <v>71.20999908447266</v>
       </c>
       <c r="E247" t="n">
-        <v>71.36000061035156</v>
+        <v>71.72000122070312</v>
       </c>
       <c r="F247" t="n">
-        <v>32807500</v>
+        <v>28223900</v>
       </c>
       <c r="G247" t="n">
         <v>0</v>
@@ -6865,22 +6865,22 @@
     </row>
     <row r="248">
       <c r="A248" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="B248" t="n">
-        <v>71.62000274658203</v>
+        <v>71.62999725341797</v>
       </c>
       <c r="C248" t="n">
-        <v>72.04000091552734</v>
+        <v>71.83999633789062</v>
       </c>
       <c r="D248" t="n">
-        <v>71.20999908447266</v>
+        <v>70.98000335693359</v>
       </c>
       <c r="E248" t="n">
-        <v>71.72000122070312</v>
+        <v>71.15000152587891</v>
       </c>
       <c r="F248" t="n">
-        <v>28223900</v>
+        <v>23203100</v>
       </c>
       <c r="G248" t="n">
         <v>0</v>
@@ -6891,22 +6891,22 @@
     </row>
     <row r="249">
       <c r="A249" s="1" t="n">
-        <v>46290</v>
+        <v>46293</v>
       </c>
       <c r="B249" t="n">
-        <v>71.62999725341797</v>
+        <v>71.55000305175781</v>
       </c>
       <c r="C249" t="n">
-        <v>71.83999633789062</v>
+        <v>71.65000152587891</v>
       </c>
       <c r="D249" t="n">
-        <v>70.98000335693359</v>
+        <v>68.87999725341797</v>
       </c>
       <c r="E249" t="n">
-        <v>71.15000152587891</v>
+        <v>69.23000335693359</v>
       </c>
       <c r="F249" t="n">
-        <v>23203100</v>
+        <v>43366300</v>
       </c>
       <c r="G249" t="n">
         <v>0</v>
@@ -6917,22 +6917,22 @@
     </row>
     <row r="250">
       <c r="A250" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="B250" t="n">
-        <v>71.55000305175781</v>
+        <v>70.33000183105469</v>
       </c>
       <c r="C250" t="n">
-        <v>71.65000152587891</v>
+        <v>71.36000061035156</v>
       </c>
       <c r="D250" t="n">
-        <v>68.87999725341797</v>
+        <v>70.15000152587891</v>
       </c>
       <c r="E250" t="n">
-        <v>69.23000335693359</v>
+        <v>70.30000305175781</v>
       </c>
       <c r="F250" t="n">
-        <v>43366300</v>
+        <v>34550800</v>
       </c>
       <c r="G250" t="n">
         <v>0</v>
@@ -6943,22 +6943,22 @@
     </row>
     <row r="251">
       <c r="A251" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="B251" t="n">
-        <v>70.33000183105469</v>
+        <v>70.19999694824219</v>
       </c>
       <c r="C251" t="n">
-        <v>71.36000061035156</v>
+        <v>70.30000305175781</v>
       </c>
       <c r="D251" t="n">
-        <v>70.15000152587891</v>
+        <v>69.51000213623047</v>
       </c>
       <c r="E251" t="n">
-        <v>70.30000305175781</v>
+        <v>69.58000183105469</v>
       </c>
       <c r="F251" t="n">
-        <v>34550800</v>
+        <v>36416600</v>
       </c>
       <c r="G251" t="n">
         <v>0</v>
@@ -6969,22 +6969,22 @@
     </row>
     <row r="252">
       <c r="A252" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="B252" t="n">
-        <v>70.19999694824219</v>
+        <v>69.41000366210938</v>
       </c>
       <c r="C252" t="n">
-        <v>70.30000305175781</v>
+        <v>69.66000366210938</v>
       </c>
       <c r="D252" t="n">
-        <v>69.51000213623047</v>
+        <v>67.79000091552734</v>
       </c>
       <c r="E252" t="n">
-        <v>69.58000183105469</v>
+        <v>67.84999847412109</v>
       </c>
       <c r="F252" t="n">
-        <v>36350700</v>
+        <v>41403300</v>
       </c>
       <c r="G252" t="n">
         <v>0</v>
@@ -10434,34 +10434,34 @@
         </is>
       </c>
       <c r="C2" t="n">
+        <v>67.84999999999999</v>
+      </c>
+      <c r="D2" t="n">
         <v>69.58</v>
       </c>
-      <c r="D2" t="n">
-        <v>70.3</v>
-      </c>
       <c r="E2" t="n">
-        <v>70.13500000000001</v>
+        <v>69.34399999999999</v>
       </c>
       <c r="F2" t="n">
-        <v>70.3</v>
+        <v>69.66</v>
       </c>
       <c r="G2" t="n">
-        <v>69.51000000000001</v>
+        <v>67.79000000000001</v>
       </c>
       <c r="H2" t="n">
-        <v>34574416</v>
+        <v>40467844</v>
       </c>
       <c r="I2" t="n">
-        <v>37364324</v>
+        <v>37126214</v>
       </c>
       <c r="J2" t="n">
-        <v>289726922752</v>
+        <v>282523303936</v>
       </c>
       <c r="K2" t="n">
-        <v>21.880503</v>
+        <v>21.336477</v>
       </c>
       <c r="L2" t="n">
-        <v>18.250301</v>
+        <v>17.787018</v>
       </c>
       <c r="M2" t="n">
         <v>3.18</v>
@@ -10502,7 +10502,7 @@
         <v>7.241</v>
       </c>
       <c r="Y2" t="n">
-        <v>9.609170000000001</v>
+        <v>9.370253</v>
       </c>
       <c r="Z2" t="n">
         <v>0.111</v>
@@ -10514,7 +10514,7 @@
         <v>48370765824</v>
       </c>
       <c r="AC2" t="n">
-        <v>297253666816</v>
+        <v>290050048000</v>
       </c>
       <c r="AD2" t="n">
         <v>14726931456</v>
@@ -10541,7 +10541,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>2026-10-01 17:03:07</t>
+          <t>2026-10-02 19:38:49</t>
         </is>
       </c>
     </row>

--- a/data/NFLX_data.xlsx
+++ b/data/NFLX_data.xlsx
@@ -469,22 +469,22 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45932</v>
+        <v>45933</v>
       </c>
       <c r="B2" t="n">
-        <v>116.1500015258789</v>
+        <v>116.5</v>
       </c>
       <c r="C2" t="n">
-        <v>116.3330001831055</v>
+        <v>116.8000030517578</v>
       </c>
       <c r="D2" t="n">
-        <v>113.4000015258789</v>
+        <v>114.3219985961914</v>
       </c>
       <c r="E2" t="n">
-        <v>116.2529983520508</v>
+        <v>115.3320007324219</v>
       </c>
       <c r="F2" t="n">
-        <v>46855000</v>
+        <v>31374000</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -495,22 +495,22 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45933</v>
+        <v>45936</v>
       </c>
       <c r="B3" t="n">
-        <v>116.5</v>
+        <v>116.0370025634766</v>
       </c>
       <c r="C3" t="n">
-        <v>116.8000030517578</v>
+        <v>116.3580017089844</v>
       </c>
       <c r="D3" t="n">
-        <v>114.3219985961914</v>
+        <v>114.5449981689453</v>
       </c>
       <c r="E3" t="n">
-        <v>115.3320007324219</v>
+        <v>116.3310012817383</v>
       </c>
       <c r="F3" t="n">
-        <v>31374000</v>
+        <v>29686000</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -521,22 +521,22 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>45936</v>
+        <v>45937</v>
       </c>
       <c r="B4" t="n">
-        <v>116.0370025634766</v>
+        <v>117.7789993286133</v>
       </c>
       <c r="C4" t="n">
-        <v>116.3580017089844</v>
+        <v>120.1370010375977</v>
       </c>
       <c r="D4" t="n">
-        <v>114.5449981689453</v>
+        <v>117.7460021972656</v>
       </c>
       <c r="E4" t="n">
-        <v>116.3310012817383</v>
+        <v>119.1060028076172</v>
       </c>
       <c r="F4" t="n">
-        <v>29686000</v>
+        <v>33091000</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -547,22 +547,22 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>45937</v>
+        <v>45938</v>
       </c>
       <c r="B5" t="n">
-        <v>117.7789993286133</v>
+        <v>119.7109985351562</v>
       </c>
       <c r="C5" t="n">
-        <v>120.1370010375977</v>
+        <v>121.7389984130859</v>
       </c>
       <c r="D5" t="n">
-        <v>117.7460021972656</v>
+        <v>119.1999969482422</v>
       </c>
       <c r="E5" t="n">
-        <v>119.1060028076172</v>
+        <v>121.4250030517578</v>
       </c>
       <c r="F5" t="n">
-        <v>33091000</v>
+        <v>28514000</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -573,22 +573,22 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>45938</v>
+        <v>45939</v>
       </c>
       <c r="B6" t="n">
-        <v>119.7109985351562</v>
+        <v>121.4250030517578</v>
       </c>
       <c r="C6" t="n">
-        <v>121.7389984130859</v>
+        <v>123.75</v>
       </c>
       <c r="D6" t="n">
-        <v>119.1999969482422</v>
+        <v>121.181999206543</v>
       </c>
       <c r="E6" t="n">
-        <v>121.4250030517578</v>
+        <v>123.1070022583008</v>
       </c>
       <c r="F6" t="n">
-        <v>28514000</v>
+        <v>28241000</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -599,22 +599,22 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>45939</v>
+        <v>45940</v>
       </c>
       <c r="B7" t="n">
-        <v>121.4250030517578</v>
+        <v>122.9000015258789</v>
       </c>
       <c r="C7" t="n">
-        <v>123.75</v>
+        <v>124.6999969482422</v>
       </c>
       <c r="D7" t="n">
-        <v>121.181999206543</v>
+        <v>121.9100036621094</v>
       </c>
       <c r="E7" t="n">
-        <v>123.1070022583008</v>
+        <v>122.0080032348633</v>
       </c>
       <c r="F7" t="n">
-        <v>28241000</v>
+        <v>42798000</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -625,22 +625,22 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>45940</v>
+        <v>45943</v>
       </c>
       <c r="B8" t="n">
-        <v>122.9000015258789</v>
+        <v>122.1350021362305</v>
       </c>
       <c r="C8" t="n">
-        <v>124.6999969482422</v>
+        <v>123.1119995117188</v>
       </c>
       <c r="D8" t="n">
-        <v>121.9100036621094</v>
+        <v>120.6809997558594</v>
       </c>
       <c r="E8" t="n">
-        <v>122.0080032348633</v>
+        <v>121.9029998779297</v>
       </c>
       <c r="F8" t="n">
-        <v>42798000</v>
+        <v>24608000</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -651,22 +651,22 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>45943</v>
+        <v>45944</v>
       </c>
       <c r="B9" t="n">
-        <v>122.1350021362305</v>
+        <v>121.4749984741211</v>
       </c>
       <c r="C9" t="n">
-        <v>123.1119995117188</v>
+        <v>122.4290008544922</v>
       </c>
       <c r="D9" t="n">
-        <v>120.6809997558594</v>
+        <v>120.3099975585938</v>
       </c>
       <c r="E9" t="n">
-        <v>121.9029998779297</v>
+        <v>121.5350036621094</v>
       </c>
       <c r="F9" t="n">
-        <v>24608000</v>
+        <v>23624000</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -677,22 +677,22 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>45944</v>
+        <v>45945</v>
       </c>
       <c r="B10" t="n">
-        <v>121.4749984741211</v>
+        <v>121.3010025024414</v>
       </c>
       <c r="C10" t="n">
-        <v>122.4290008544922</v>
+        <v>121.9619979858398</v>
       </c>
       <c r="D10" t="n">
-        <v>120.3099975585938</v>
+        <v>120.161003112793</v>
       </c>
       <c r="E10" t="n">
-        <v>121.5350036621094</v>
+        <v>120.3290023803711</v>
       </c>
       <c r="F10" t="n">
-        <v>23624000</v>
+        <v>20252000</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -703,22 +703,22 @@
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>45945</v>
+        <v>45946</v>
       </c>
       <c r="B11" t="n">
-        <v>121.3010025024414</v>
+        <v>121.2149963378906</v>
       </c>
       <c r="C11" t="n">
-        <v>121.9619979858398</v>
+        <v>121.6709976196289</v>
       </c>
       <c r="D11" t="n">
-        <v>120.161003112793</v>
+        <v>117.5999984741211</v>
       </c>
       <c r="E11" t="n">
-        <v>120.3290023803711</v>
+        <v>118.359001159668</v>
       </c>
       <c r="F11" t="n">
-        <v>20252000</v>
+        <v>28326000</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -729,22 +729,22 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>45946</v>
+        <v>45947</v>
       </c>
       <c r="B12" t="n">
-        <v>121.2149963378906</v>
+        <v>118.3600006103516</v>
       </c>
       <c r="C12" t="n">
-        <v>121.6709976196289</v>
+        <v>120.3119964599609</v>
       </c>
       <c r="D12" t="n">
-        <v>117.5999984741211</v>
+        <v>117.8949966430664</v>
       </c>
       <c r="E12" t="n">
-        <v>118.359001159668</v>
+        <v>119.9359970092773</v>
       </c>
       <c r="F12" t="n">
-        <v>28326000</v>
+        <v>29571000</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -755,22 +755,22 @@
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>45947</v>
+        <v>45950</v>
       </c>
       <c r="B13" t="n">
-        <v>118.3600006103516</v>
+        <v>120.7880020141602</v>
       </c>
       <c r="C13" t="n">
-        <v>120.3119964599609</v>
+        <v>124.7760009765625</v>
       </c>
       <c r="D13" t="n">
-        <v>117.8949966430664</v>
+        <v>120.6900024414062</v>
       </c>
       <c r="E13" t="n">
-        <v>119.9359970092773</v>
+        <v>123.8560028076172</v>
       </c>
       <c r="F13" t="n">
-        <v>29571000</v>
+        <v>39862000</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -781,22 +781,22 @@
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>45950</v>
+        <v>45951</v>
       </c>
       <c r="B14" t="n">
-        <v>120.7880020141602</v>
+        <v>124.2829971313477</v>
       </c>
       <c r="C14" t="n">
-        <v>124.7760009765625</v>
+        <v>124.8600006103516</v>
       </c>
       <c r="D14" t="n">
-        <v>120.6900024414062</v>
+        <v>123.1760025024414</v>
       </c>
       <c r="E14" t="n">
-        <v>123.8560028076172</v>
+        <v>124.1350021362305</v>
       </c>
       <c r="F14" t="n">
-        <v>39862000</v>
+        <v>65082000</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -807,22 +807,22 @@
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>45951</v>
+        <v>45952</v>
       </c>
       <c r="B15" t="n">
-        <v>124.2829971313477</v>
+        <v>114.2900009155273</v>
       </c>
       <c r="C15" t="n">
-        <v>124.8600006103516</v>
+        <v>115.7600021362305</v>
       </c>
       <c r="D15" t="n">
-        <v>123.1760025024414</v>
+        <v>111.2509994506836</v>
       </c>
       <c r="E15" t="n">
-        <v>124.1350021362305</v>
+        <v>111.6370010375977</v>
       </c>
       <c r="F15" t="n">
-        <v>65082000</v>
+        <v>147890000</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -833,22 +833,22 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>45952</v>
+        <v>45953</v>
       </c>
       <c r="B16" t="n">
-        <v>114.2900009155273</v>
+        <v>112.6900024414062</v>
       </c>
       <c r="C16" t="n">
-        <v>115.7600021362305</v>
+        <v>112.7829971313477</v>
       </c>
       <c r="D16" t="n">
-        <v>111.2509994506836</v>
+        <v>109.9729995727539</v>
       </c>
       <c r="E16" t="n">
-        <v>111.6370010375977</v>
+        <v>111.359001159668</v>
       </c>
       <c r="F16" t="n">
-        <v>147890000</v>
+        <v>68497000</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -859,22 +859,22 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>45953</v>
+        <v>45954</v>
       </c>
       <c r="B17" t="n">
-        <v>112.6900024414062</v>
+        <v>111.0999984741211</v>
       </c>
       <c r="C17" t="n">
-        <v>112.7829971313477</v>
+        <v>111.4509963989258</v>
       </c>
       <c r="D17" t="n">
-        <v>109.9729995727539</v>
+        <v>109.4410018920898</v>
       </c>
       <c r="E17" t="n">
-        <v>111.359001159668</v>
+        <v>109.4690017700195</v>
       </c>
       <c r="F17" t="n">
-        <v>68497000</v>
+        <v>60280000</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -885,22 +885,22 @@
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>45954</v>
+        <v>45957</v>
       </c>
       <c r="B18" t="n">
-        <v>111.0999984741211</v>
+        <v>110.0670013427734</v>
       </c>
       <c r="C18" t="n">
-        <v>111.4509963989258</v>
+        <v>110.2279968261719</v>
       </c>
       <c r="D18" t="n">
-        <v>109.4410018920898</v>
+        <v>108.7300033569336</v>
       </c>
       <c r="E18" t="n">
-        <v>109.4690017700195</v>
+        <v>109.4560012817383</v>
       </c>
       <c r="F18" t="n">
-        <v>60280000</v>
+        <v>46911000</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -911,22 +911,22 @@
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>45957</v>
+        <v>45958</v>
       </c>
       <c r="B19" t="n">
-        <v>110.0670013427734</v>
+        <v>109.4000015258789</v>
       </c>
       <c r="C19" t="n">
-        <v>110.2279968261719</v>
+        <v>111.697998046875</v>
       </c>
       <c r="D19" t="n">
-        <v>108.7300033569336</v>
+        <v>109.3010025024414</v>
       </c>
       <c r="E19" t="n">
-        <v>109.4560012817383</v>
+        <v>110.25</v>
       </c>
       <c r="F19" t="n">
-        <v>46911000</v>
+        <v>40209000</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -937,22 +937,22 @@
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>45958</v>
+        <v>45959</v>
       </c>
       <c r="B20" t="n">
-        <v>109.4000015258789</v>
+        <v>109.984001159668</v>
       </c>
       <c r="C20" t="n">
-        <v>111.697998046875</v>
+        <v>110.8550033569336</v>
       </c>
       <c r="D20" t="n">
-        <v>109.3010025024414</v>
+        <v>109.5999984741211</v>
       </c>
       <c r="E20" t="n">
-        <v>110.25</v>
+        <v>110.0410003662109</v>
       </c>
       <c r="F20" t="n">
-        <v>40209000</v>
+        <v>33995000</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -963,22 +963,22 @@
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>45959</v>
+        <v>45960</v>
       </c>
       <c r="B21" t="n">
-        <v>109.984001159668</v>
+        <v>109.4400024414062</v>
       </c>
       <c r="C21" t="n">
-        <v>110.8550033569336</v>
+        <v>110.6159973144531</v>
       </c>
       <c r="D21" t="n">
-        <v>109.5999984741211</v>
+        <v>108.8109970092773</v>
       </c>
       <c r="E21" t="n">
-        <v>110.0410003662109</v>
+        <v>108.9000015258789</v>
       </c>
       <c r="F21" t="n">
-        <v>33995000</v>
+        <v>41581000</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -989,22 +989,22 @@
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>45960</v>
+        <v>45961</v>
       </c>
       <c r="B22" t="n">
-        <v>109.4400024414062</v>
+        <v>110.5390014648438</v>
       </c>
       <c r="C22" t="n">
-        <v>110.6159973144531</v>
+        <v>113.4879989624023</v>
       </c>
       <c r="D22" t="n">
-        <v>108.8109970092773</v>
+        <v>110.197998046875</v>
       </c>
       <c r="E22" t="n">
-        <v>108.9000015258789</v>
+        <v>111.8860015869141</v>
       </c>
       <c r="F22" t="n">
-        <v>41581000</v>
+        <v>68665000</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -1015,22 +1015,22 @@
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>45961</v>
+        <v>45964</v>
       </c>
       <c r="B23" t="n">
-        <v>110.5390014648438</v>
+        <v>113.3239974975586</v>
       </c>
       <c r="C23" t="n">
-        <v>113.4879989624023</v>
+        <v>113.3499984741211</v>
       </c>
       <c r="D23" t="n">
-        <v>110.197998046875</v>
+        <v>107.5149993896484</v>
       </c>
       <c r="E23" t="n">
-        <v>111.8860015869141</v>
+        <v>110.0090026855469</v>
       </c>
       <c r="F23" t="n">
-        <v>68665000</v>
+        <v>58634000</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -1041,22 +1041,22 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>45964</v>
+        <v>45965</v>
       </c>
       <c r="B24" t="n">
-        <v>113.3239974975586</v>
+        <v>109.9990005493164</v>
       </c>
       <c r="C24" t="n">
-        <v>113.3499984741211</v>
+        <v>110.4599990844727</v>
       </c>
       <c r="D24" t="n">
-        <v>107.5149993896484</v>
+        <v>108.6679992675781</v>
       </c>
       <c r="E24" t="n">
-        <v>110.0090026855469</v>
+        <v>109.2959976196289</v>
       </c>
       <c r="F24" t="n">
-        <v>58634000</v>
+        <v>38718000</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -1067,22 +1067,22 @@
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>45965</v>
+        <v>45966</v>
       </c>
       <c r="B25" t="n">
-        <v>109.9990005493164</v>
+        <v>108.5</v>
       </c>
       <c r="C25" t="n">
-        <v>110.4599990844727</v>
+        <v>110.0849990844727</v>
       </c>
       <c r="D25" t="n">
-        <v>108.6679992675781</v>
+        <v>107.3369979858398</v>
       </c>
       <c r="E25" t="n">
-        <v>109.2959976196289</v>
+        <v>109.8460006713867</v>
       </c>
       <c r="F25" t="n">
-        <v>38718000</v>
+        <v>35539000</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -1093,22 +1093,22 @@
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>45966</v>
+        <v>45967</v>
       </c>
       <c r="B26" t="n">
-        <v>108.5</v>
+        <v>109.4580001831055</v>
       </c>
       <c r="C26" t="n">
-        <v>110.0849990844727</v>
+        <v>110.370002746582</v>
       </c>
       <c r="D26" t="n">
-        <v>107.3369979858398</v>
+        <v>108.5130004882812</v>
       </c>
       <c r="E26" t="n">
-        <v>109.8460006713867</v>
+        <v>109.7020034790039</v>
       </c>
       <c r="F26" t="n">
-        <v>35539000</v>
+        <v>36532000</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -1119,22 +1119,22 @@
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>45967</v>
+        <v>45968</v>
       </c>
       <c r="B27" t="n">
-        <v>109.4580001831055</v>
+        <v>109.4179992675781</v>
       </c>
       <c r="C27" t="n">
-        <v>110.370002746582</v>
+        <v>110.8219985961914</v>
       </c>
       <c r="D27" t="n">
-        <v>108.5130004882812</v>
+        <v>108.75</v>
       </c>
       <c r="E27" t="n">
-        <v>109.7020034790039</v>
+        <v>110.3659973144531</v>
       </c>
       <c r="F27" t="n">
-        <v>36532000</v>
+        <v>44125000</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -1145,22 +1145,22 @@
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>45968</v>
+        <v>45971</v>
       </c>
       <c r="B28" t="n">
-        <v>109.4179992675781</v>
+        <v>110.6719970703125</v>
       </c>
       <c r="C28" t="n">
-        <v>110.8219985961914</v>
+        <v>112.8199996948242</v>
       </c>
       <c r="D28" t="n">
-        <v>108.75</v>
+        <v>110.4049987792969</v>
       </c>
       <c r="E28" t="n">
-        <v>110.3659973144531</v>
+        <v>112.0070037841797</v>
       </c>
       <c r="F28" t="n">
-        <v>44125000</v>
+        <v>36929000</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
@@ -1171,22 +1171,22 @@
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>45971</v>
+        <v>45972</v>
       </c>
       <c r="B29" t="n">
-        <v>110.6719970703125</v>
+        <v>111.7600021362305</v>
       </c>
       <c r="C29" t="n">
-        <v>112.8199996948242</v>
+        <v>113.9219970703125</v>
       </c>
       <c r="D29" t="n">
-        <v>110.4049987792969</v>
+        <v>111.2799987792969</v>
       </c>
       <c r="E29" t="n">
-        <v>112.0070037841797</v>
+        <v>113.6439971923828</v>
       </c>
       <c r="F29" t="n">
-        <v>36929000</v>
+        <v>27966000</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -1197,22 +1197,22 @@
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>45972</v>
+        <v>45973</v>
       </c>
       <c r="B30" t="n">
-        <v>111.7600021362305</v>
+        <v>113.8170013427734</v>
       </c>
       <c r="C30" t="n">
-        <v>113.9219970703125</v>
+        <v>116.4339981079102</v>
       </c>
       <c r="D30" t="n">
-        <v>111.2799987792969</v>
+        <v>112.8259963989258</v>
       </c>
       <c r="E30" t="n">
-        <v>113.6439971923828</v>
+        <v>115.75</v>
       </c>
       <c r="F30" t="n">
-        <v>27966000</v>
+        <v>39221000</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -1223,22 +1223,22 @@
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>45973</v>
+        <v>45974</v>
       </c>
       <c r="B31" t="n">
-        <v>113.8170013427734</v>
+        <v>115.8499984741211</v>
       </c>
       <c r="C31" t="n">
-        <v>116.4339981079102</v>
+        <v>116.7330017089844</v>
       </c>
       <c r="D31" t="n">
-        <v>112.8259963989258</v>
+        <v>114.5690002441406</v>
       </c>
       <c r="E31" t="n">
-        <v>115.75</v>
+        <v>115.4229965209961</v>
       </c>
       <c r="F31" t="n">
-        <v>39221000</v>
+        <v>40144000</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -1249,22 +1249,22 @@
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>45974</v>
+        <v>45975</v>
       </c>
       <c r="B32" t="n">
-        <v>115.8499984741211</v>
+        <v>114.2730026245117</v>
       </c>
       <c r="C32" t="n">
-        <v>116.7330017089844</v>
+        <v>114.2730026245117</v>
       </c>
       <c r="D32" t="n">
-        <v>114.5690002441406</v>
+        <v>110.7210006713867</v>
       </c>
       <c r="E32" t="n">
-        <v>115.4229965209961</v>
+        <v>111.2170028686523</v>
       </c>
       <c r="F32" t="n">
-        <v>40144000</v>
+        <v>47607000</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
@@ -1275,74 +1275,74 @@
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>45975</v>
+        <v>45978</v>
       </c>
       <c r="B33" t="n">
-        <v>114.2730026245117</v>
+        <v>110.75</v>
       </c>
       <c r="C33" t="n">
-        <v>114.2730026245117</v>
+        <v>111.8499984741211</v>
       </c>
       <c r="D33" t="n">
-        <v>110.7210006713867</v>
+        <v>109.5500030517578</v>
       </c>
       <c r="E33" t="n">
-        <v>111.2170028686523</v>
+        <v>110.2900009155273</v>
       </c>
       <c r="F33" t="n">
-        <v>47607000</v>
+        <v>26082700</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>45978</v>
+        <v>45979</v>
       </c>
       <c r="B34" t="n">
-        <v>110.75</v>
+        <v>110.2900009155273</v>
       </c>
       <c r="C34" t="n">
-        <v>111.8499984741211</v>
+        <v>115.25</v>
       </c>
       <c r="D34" t="n">
-        <v>109.5500030517578</v>
+        <v>109.1999969482422</v>
       </c>
       <c r="E34" t="n">
-        <v>110.2900009155273</v>
+        <v>114.0899963378906</v>
       </c>
       <c r="F34" t="n">
-        <v>26082700</v>
+        <v>43440600</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>45979</v>
+        <v>45980</v>
       </c>
       <c r="B35" t="n">
-        <v>110.2900009155273</v>
+        <v>113</v>
       </c>
       <c r="C35" t="n">
-        <v>115.25</v>
+        <v>113.3399963378906</v>
       </c>
       <c r="D35" t="n">
-        <v>109.1999969482422</v>
+        <v>108.6100006103516</v>
       </c>
       <c r="E35" t="n">
-        <v>114.0899963378906</v>
+        <v>110</v>
       </c>
       <c r="F35" t="n">
-        <v>43440600</v>
+        <v>31868100</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
@@ -1353,22 +1353,22 @@
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>45980</v>
+        <v>45981</v>
       </c>
       <c r="B36" t="n">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C36" t="n">
-        <v>113.3399963378906</v>
+        <v>111.0999984741211</v>
       </c>
       <c r="D36" t="n">
-        <v>108.6100006103516</v>
+        <v>105.3899993896484</v>
       </c>
       <c r="E36" t="n">
-        <v>110</v>
+        <v>105.6699981689453</v>
       </c>
       <c r="F36" t="n">
-        <v>31868100</v>
+        <v>36918500</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -1379,22 +1379,22 @@
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>45981</v>
+        <v>45982</v>
       </c>
       <c r="B37" t="n">
-        <v>111</v>
+        <v>105.129997253418</v>
       </c>
       <c r="C37" t="n">
-        <v>111.0999984741211</v>
+        <v>106.5299987792969</v>
       </c>
       <c r="D37" t="n">
-        <v>105.3899993896484</v>
+        <v>103.8099975585938</v>
       </c>
       <c r="E37" t="n">
-        <v>105.6699981689453</v>
+        <v>104.3099975585938</v>
       </c>
       <c r="F37" t="n">
-        <v>36918500</v>
+        <v>41232700</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
@@ -1405,22 +1405,22 @@
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>45982</v>
+        <v>45985</v>
       </c>
       <c r="B38" t="n">
-        <v>105.129997253418</v>
+        <v>104.25</v>
       </c>
       <c r="C38" t="n">
-        <v>106.5299987792969</v>
+        <v>108.0400009155273</v>
       </c>
       <c r="D38" t="n">
-        <v>103.8099975585938</v>
+        <v>103.3199996948242</v>
       </c>
       <c r="E38" t="n">
-        <v>104.3099975585938</v>
+        <v>106.9700012207031</v>
       </c>
       <c r="F38" t="n">
-        <v>41232700</v>
+        <v>62918300</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
@@ -1431,22 +1431,22 @@
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>45985</v>
+        <v>45986</v>
       </c>
       <c r="B39" t="n">
-        <v>104.25</v>
+        <v>106.120002746582</v>
       </c>
       <c r="C39" t="n">
-        <v>108.0400009155273</v>
+        <v>106.3000030517578</v>
       </c>
       <c r="D39" t="n">
-        <v>103.3199996948242</v>
+        <v>103.8199996948242</v>
       </c>
       <c r="E39" t="n">
-        <v>106.9700012207031</v>
+        <v>104.4000015258789</v>
       </c>
       <c r="F39" t="n">
-        <v>62918300</v>
+        <v>35122600</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
@@ -1457,22 +1457,22 @@
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>45986</v>
+        <v>45987</v>
       </c>
       <c r="B40" t="n">
-        <v>106.120002746582</v>
+        <v>105.7399978637695</v>
       </c>
       <c r="C40" t="n">
-        <v>106.3000030517578</v>
+        <v>106.9499969482422</v>
       </c>
       <c r="D40" t="n">
-        <v>103.8199996948242</v>
+        <v>105.2200012207031</v>
       </c>
       <c r="E40" t="n">
-        <v>104.4000015258789</v>
+        <v>106.1399993896484</v>
       </c>
       <c r="F40" t="n">
-        <v>35122600</v>
+        <v>27951000</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
@@ -1483,22 +1483,22 @@
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>45987</v>
+        <v>45989</v>
       </c>
       <c r="B41" t="n">
-        <v>105.7399978637695</v>
+        <v>106.4400024414062</v>
       </c>
       <c r="C41" t="n">
-        <v>106.9499969482422</v>
+        <v>107.9400024414062</v>
       </c>
       <c r="D41" t="n">
-        <v>105.2200012207031</v>
+        <v>106.2399978637695</v>
       </c>
       <c r="E41" t="n">
-        <v>106.1399993896484</v>
+        <v>107.5800018310547</v>
       </c>
       <c r="F41" t="n">
-        <v>27951000</v>
+        <v>15021600</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
@@ -1509,22 +1509,22 @@
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>45989</v>
+        <v>45992</v>
       </c>
       <c r="B42" t="n">
-        <v>106.4400024414062</v>
+        <v>106.5100021362305</v>
       </c>
       <c r="C42" t="n">
-        <v>107.9400024414062</v>
+        <v>109.3399963378906</v>
       </c>
       <c r="D42" t="n">
-        <v>106.2399978637695</v>
+        <v>106.3099975585938</v>
       </c>
       <c r="E42" t="n">
-        <v>107.5800018310547</v>
+        <v>109.129997253418</v>
       </c>
       <c r="F42" t="n">
-        <v>15021600</v>
+        <v>24873400</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
@@ -1535,22 +1535,22 @@
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>45992</v>
+        <v>45993</v>
       </c>
       <c r="B43" t="n">
-        <v>106.5100021362305</v>
+        <v>109.2099990844727</v>
       </c>
       <c r="C43" t="n">
-        <v>109.3399963378906</v>
+        <v>109.7300033569336</v>
       </c>
       <c r="D43" t="n">
-        <v>106.3099975585938</v>
+        <v>107.5199966430664</v>
       </c>
       <c r="E43" t="n">
-        <v>109.129997253418</v>
+        <v>109.3499984741211</v>
       </c>
       <c r="F43" t="n">
-        <v>24873400</v>
+        <v>25763000</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
@@ -1561,22 +1561,22 @@
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
-        <v>45993</v>
+        <v>45994</v>
       </c>
       <c r="B44" t="n">
-        <v>109.2099990844727</v>
+        <v>106.5899963378906</v>
       </c>
       <c r="C44" t="n">
-        <v>109.7300033569336</v>
+        <v>106.870002746582</v>
       </c>
       <c r="D44" t="n">
-        <v>107.5199966430664</v>
+        <v>102.0299987792969</v>
       </c>
       <c r="E44" t="n">
-        <v>109.3499984741211</v>
+        <v>103.9599990844727</v>
       </c>
       <c r="F44" t="n">
-        <v>25763000</v>
+        <v>53593400</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
@@ -1587,22 +1587,22 @@
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
-        <v>45994</v>
+        <v>45995</v>
       </c>
       <c r="B45" t="n">
-        <v>106.5899963378906</v>
+        <v>103.5699996948242</v>
       </c>
       <c r="C45" t="n">
-        <v>106.870002746582</v>
+        <v>103.8000030517578</v>
       </c>
       <c r="D45" t="n">
-        <v>102.0299987792969</v>
+        <v>101.7699966430664</v>
       </c>
       <c r="E45" t="n">
-        <v>103.9599990844727</v>
+        <v>103.2200012207031</v>
       </c>
       <c r="F45" t="n">
-        <v>53593400</v>
+        <v>51779100</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
@@ -1613,22 +1613,22 @@
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
-        <v>45995</v>
+        <v>45996</v>
       </c>
       <c r="B46" t="n">
-        <v>103.5699996948242</v>
+        <v>98.77999877929688</v>
       </c>
       <c r="C46" t="n">
-        <v>103.8000030517578</v>
+        <v>104.7900009155273</v>
       </c>
       <c r="D46" t="n">
-        <v>101.7699966430664</v>
+        <v>97.73999786376953</v>
       </c>
       <c r="E46" t="n">
-        <v>103.2200012207031</v>
+        <v>100.2399978637695</v>
       </c>
       <c r="F46" t="n">
-        <v>51779100</v>
+        <v>133363600</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
@@ -1639,22 +1639,22 @@
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
-        <v>45996</v>
+        <v>45999</v>
       </c>
       <c r="B47" t="n">
-        <v>98.77999877929688</v>
+        <v>99.87000274658203</v>
       </c>
       <c r="C47" t="n">
-        <v>104.7900009155273</v>
+        <v>99.88999938964844</v>
       </c>
       <c r="D47" t="n">
-        <v>97.73999786376953</v>
+        <v>95.30000305175781</v>
       </c>
       <c r="E47" t="n">
-        <v>100.2399978637695</v>
+        <v>96.79000091552734</v>
       </c>
       <c r="F47" t="n">
-        <v>133363600</v>
+        <v>100906300</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
@@ -1665,22 +1665,22 @@
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
-        <v>45999</v>
+        <v>46000</v>
       </c>
       <c r="B48" t="n">
-        <v>99.87000274658203</v>
+        <v>97.02999877929688</v>
       </c>
       <c r="C48" t="n">
-        <v>99.88999938964844</v>
+        <v>97.23999786376953</v>
       </c>
       <c r="D48" t="n">
-        <v>95.30000305175781</v>
+        <v>95.44999694824219</v>
       </c>
       <c r="E48" t="n">
-        <v>96.79000091552734</v>
+        <v>96.70999908447266</v>
       </c>
       <c r="F48" t="n">
-        <v>100906300</v>
+        <v>51745600</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
@@ -1691,22 +1691,22 @@
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>46000</v>
+        <v>46001</v>
       </c>
       <c r="B49" t="n">
-        <v>97.02999877929688</v>
+        <v>96.73999786376953</v>
       </c>
       <c r="C49" t="n">
-        <v>97.23999786376953</v>
+        <v>96.97000122070312</v>
       </c>
       <c r="D49" t="n">
-        <v>95.44999694824219</v>
+        <v>92.34999847412109</v>
       </c>
       <c r="E49" t="n">
-        <v>96.70999908447266</v>
+        <v>92.70999908447266</v>
       </c>
       <c r="F49" t="n">
-        <v>51745600</v>
+        <v>74129300</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
@@ -1717,22 +1717,22 @@
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>46001</v>
+        <v>46002</v>
       </c>
       <c r="B50" t="n">
-        <v>96.73999786376953</v>
+        <v>93.90000152587891</v>
       </c>
       <c r="C50" t="n">
-        <v>96.97000122070312</v>
+        <v>94.81999969482422</v>
       </c>
       <c r="D50" t="n">
-        <v>92.34999847412109</v>
+        <v>92.76000213623047</v>
       </c>
       <c r="E50" t="n">
-        <v>92.70999908447266</v>
+        <v>94.08999633789062</v>
       </c>
       <c r="F50" t="n">
-        <v>74129300</v>
+        <v>43949000</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
-        <v>46002</v>
+        <v>46003</v>
       </c>
       <c r="B51" t="n">
-        <v>93.90000152587891</v>
+        <v>95.5</v>
       </c>
       <c r="C51" t="n">
-        <v>94.81999969482422</v>
+        <v>96.91999816894531</v>
       </c>
       <c r="D51" t="n">
-        <v>92.76000213623047</v>
+        <v>94.65000152587891</v>
       </c>
       <c r="E51" t="n">
-        <v>94.08999633789062</v>
+        <v>95.19000244140625</v>
       </c>
       <c r="F51" t="n">
-        <v>43949000</v>
+        <v>49323100</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
@@ -1769,22 +1769,22 @@
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
-        <v>46003</v>
+        <v>46006</v>
       </c>
       <c r="B52" t="n">
-        <v>95.5</v>
+        <v>96.01999664306641</v>
       </c>
       <c r="C52" t="n">
-        <v>96.91999816894531</v>
+        <v>96.37000274658203</v>
       </c>
       <c r="D52" t="n">
-        <v>94.65000152587891</v>
+        <v>93.52999877929688</v>
       </c>
       <c r="E52" t="n">
-        <v>95.19000244140625</v>
+        <v>93.76999664306641</v>
       </c>
       <c r="F52" t="n">
-        <v>49323100</v>
+        <v>40016500</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
@@ -1795,22 +1795,22 @@
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
-        <v>46006</v>
+        <v>46007</v>
       </c>
       <c r="B53" t="n">
-        <v>96.01999664306641</v>
+        <v>93.87999725341797</v>
       </c>
       <c r="C53" t="n">
-        <v>96.37000274658203</v>
+        <v>94.93000030517578</v>
       </c>
       <c r="D53" t="n">
-        <v>93.52999877929688</v>
+        <v>93.31999969482422</v>
       </c>
       <c r="E53" t="n">
-        <v>93.76999664306641</v>
+        <v>94.56999969482422</v>
       </c>
       <c r="F53" t="n">
-        <v>40016500</v>
+        <v>34265000</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
@@ -1821,22 +1821,22 @@
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
-        <v>46007</v>
+        <v>46008</v>
       </c>
       <c r="B54" t="n">
-        <v>93.87999725341797</v>
+        <v>95.98000335693359</v>
       </c>
       <c r="C54" t="n">
-        <v>94.93000030517578</v>
+        <v>97.33000183105469</v>
       </c>
       <c r="D54" t="n">
-        <v>93.31999969482422</v>
+        <v>94.45999908447266</v>
       </c>
       <c r="E54" t="n">
-        <v>94.56999969482422</v>
+        <v>94.79000091552734</v>
       </c>
       <c r="F54" t="n">
-        <v>34265000</v>
+        <v>50472800</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
@@ -1847,22 +1847,22 @@
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
-        <v>46008</v>
+        <v>46009</v>
       </c>
       <c r="B55" t="n">
-        <v>95.98000335693359</v>
+        <v>95.01999664306641</v>
       </c>
       <c r="C55" t="n">
-        <v>97.33000183105469</v>
+        <v>95.80999755859375</v>
       </c>
       <c r="D55" t="n">
-        <v>94.45999908447266</v>
+        <v>93.58999633789062</v>
       </c>
       <c r="E55" t="n">
-        <v>94.79000091552734</v>
+        <v>94</v>
       </c>
       <c r="F55" t="n">
-        <v>50472800</v>
+        <v>37244700</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
@@ -1873,22 +1873,22 @@
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
-        <v>46009</v>
+        <v>46010</v>
       </c>
       <c r="B56" t="n">
-        <v>95.01999664306641</v>
+        <v>93.56999969482422</v>
       </c>
       <c r="C56" t="n">
-        <v>95.80999755859375</v>
+        <v>95.54000091552734</v>
       </c>
       <c r="D56" t="n">
-        <v>93.58999633789062</v>
+        <v>93.44999694824219</v>
       </c>
       <c r="E56" t="n">
-        <v>94</v>
+        <v>94.38999938964844</v>
       </c>
       <c r="F56" t="n">
-        <v>37244700</v>
+        <v>78990200</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
@@ -1899,22 +1899,22 @@
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
-        <v>46010</v>
+        <v>46013</v>
       </c>
       <c r="B57" t="n">
-        <v>93.56999969482422</v>
+        <v>94.70999908447266</v>
       </c>
       <c r="C57" t="n">
-        <v>95.54000091552734</v>
+        <v>94.70999908447266</v>
       </c>
       <c r="D57" t="n">
-        <v>93.44999694824219</v>
+        <v>92.91000366210938</v>
       </c>
       <c r="E57" t="n">
-        <v>94.38999938964844</v>
+        <v>93.23000335693359</v>
       </c>
       <c r="F57" t="n">
-        <v>78990200</v>
+        <v>39484800</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
@@ -1925,22 +1925,22 @@
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
-        <v>46013</v>
+        <v>46014</v>
       </c>
       <c r="B58" t="n">
-        <v>94.70999908447266</v>
+        <v>93.40000152587891</v>
       </c>
       <c r="C58" t="n">
-        <v>94.70999908447266</v>
+        <v>93.80999755859375</v>
       </c>
       <c r="D58" t="n">
-        <v>92.91000366210938</v>
+        <v>91.33000183105469</v>
       </c>
       <c r="E58" t="n">
-        <v>93.23000335693359</v>
+        <v>93.5</v>
       </c>
       <c r="F58" t="n">
-        <v>39484800</v>
+        <v>25896200</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
@@ -1951,22 +1951,22 @@
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
-        <v>46014</v>
+        <v>46015</v>
       </c>
       <c r="B59" t="n">
-        <v>93.40000152587891</v>
+        <v>93.11000061035156</v>
       </c>
       <c r="C59" t="n">
-        <v>93.80999755859375</v>
+        <v>93.68000030517578</v>
       </c>
       <c r="D59" t="n">
-        <v>91.33000183105469</v>
+        <v>92.66999816894531</v>
       </c>
       <c r="E59" t="n">
-        <v>93.5</v>
+        <v>93.63999938964844</v>
       </c>
       <c r="F59" t="n">
-        <v>25896200</v>
+        <v>12427900</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
@@ -1977,22 +1977,22 @@
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
-        <v>46015</v>
+        <v>46017</v>
       </c>
       <c r="B60" t="n">
-        <v>93.11000061035156</v>
+        <v>93.48000335693359</v>
       </c>
       <c r="C60" t="n">
-        <v>93.68000030517578</v>
+        <v>94.69000244140625</v>
       </c>
       <c r="D60" t="n">
-        <v>92.66999816894531</v>
+        <v>93.26999664306641</v>
       </c>
       <c r="E60" t="n">
-        <v>93.63999938964844</v>
+        <v>94.47000122070312</v>
       </c>
       <c r="F60" t="n">
-        <v>12427900</v>
+        <v>22068300</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
@@ -2003,22 +2003,22 @@
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
-        <v>46017</v>
+        <v>46020</v>
       </c>
       <c r="B61" t="n">
-        <v>93.48000335693359</v>
+        <v>93.98999786376953</v>
       </c>
       <c r="C61" t="n">
-        <v>94.69000244140625</v>
+        <v>94.97000122070312</v>
       </c>
       <c r="D61" t="n">
-        <v>93.26999664306641</v>
+        <v>93.62999725341797</v>
       </c>
       <c r="E61" t="n">
-        <v>94.47000122070312</v>
+        <v>94.15000152587891</v>
       </c>
       <c r="F61" t="n">
-        <v>22068300</v>
+        <v>24493700</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
@@ -2029,22 +2029,22 @@
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
-        <v>46020</v>
+        <v>46021</v>
       </c>
       <c r="B62" t="n">
+        <v>93.51999664306641</v>
+      </c>
+      <c r="C62" t="n">
         <v>93.98999786376953</v>
       </c>
-      <c r="C62" t="n">
-        <v>94.97000122070312</v>
-      </c>
       <c r="D62" t="n">
-        <v>93.62999725341797</v>
+        <v>93.33999633789062</v>
       </c>
       <c r="E62" t="n">
-        <v>94.15000152587891</v>
+        <v>93.77999877929688</v>
       </c>
       <c r="F62" t="n">
-        <v>24493700</v>
+        <v>23422000</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
@@ -2055,22 +2055,22 @@
     </row>
     <row r="63">
       <c r="A63" s="1" t="n">
-        <v>46021</v>
+        <v>46022</v>
       </c>
       <c r="B63" t="n">
-        <v>93.51999664306641</v>
+        <v>93.59999847412109</v>
       </c>
       <c r="C63" t="n">
-        <v>93.98999786376953</v>
+        <v>94.30999755859375</v>
       </c>
       <c r="D63" t="n">
-        <v>93.33999633789062</v>
+        <v>93.19999694824219</v>
       </c>
       <c r="E63" t="n">
-        <v>93.77999877929688</v>
+        <v>93.76000213623047</v>
       </c>
       <c r="F63" t="n">
-        <v>23422000</v>
+        <v>23495200</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
@@ -2081,22 +2081,22 @@
     </row>
     <row r="64">
       <c r="A64" s="1" t="n">
-        <v>46022</v>
+        <v>46024</v>
       </c>
       <c r="B64" t="n">
-        <v>93.59999847412109</v>
+        <v>94.12999725341797</v>
       </c>
       <c r="C64" t="n">
-        <v>94.30999755859375</v>
+        <v>94.12999725341797</v>
       </c>
       <c r="D64" t="n">
-        <v>93.19999694824219</v>
+        <v>90.80999755859375</v>
       </c>
       <c r="E64" t="n">
-        <v>93.76000213623047</v>
+        <v>90.98999786376953</v>
       </c>
       <c r="F64" t="n">
-        <v>23495200</v>
+        <v>41155400</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
@@ -2107,22 +2107,22 @@
     </row>
     <row r="65">
       <c r="A65" s="1" t="n">
-        <v>46024</v>
+        <v>46027</v>
       </c>
       <c r="B65" t="n">
-        <v>94.12999725341797</v>
+        <v>90.91999816894531</v>
       </c>
       <c r="C65" t="n">
-        <v>94.12999725341797</v>
+        <v>92.62999725341797</v>
       </c>
       <c r="D65" t="n">
-        <v>90.80999755859375</v>
+        <v>90.83999633789062</v>
       </c>
       <c r="E65" t="n">
-        <v>90.98999786376953</v>
+        <v>91.45999908447266</v>
       </c>
       <c r="F65" t="n">
-        <v>41155400</v>
+        <v>39183300</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
@@ -2133,22 +2133,22 @@
     </row>
     <row r="66">
       <c r="A66" s="1" t="n">
-        <v>46027</v>
+        <v>46028</v>
       </c>
       <c r="B66" t="n">
-        <v>90.91999816894531</v>
+        <v>91.54000091552734</v>
       </c>
       <c r="C66" t="n">
-        <v>92.62999725341797</v>
+        <v>91.63999938964844</v>
       </c>
       <c r="D66" t="n">
-        <v>90.83999633789062</v>
+        <v>89.73999786376953</v>
       </c>
       <c r="E66" t="n">
-        <v>91.45999908447266</v>
+        <v>90.65000152587891</v>
       </c>
       <c r="F66" t="n">
-        <v>39183300</v>
+        <v>43331000</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
@@ -2159,22 +2159,22 @@
     </row>
     <row r="67">
       <c r="A67" s="1" t="n">
-        <v>46028</v>
+        <v>46029</v>
       </c>
       <c r="B67" t="n">
-        <v>91.54000091552734</v>
+        <v>91.55999755859375</v>
       </c>
       <c r="C67" t="n">
-        <v>91.63999938964844</v>
+        <v>92.41999816894531</v>
       </c>
       <c r="D67" t="n">
-        <v>89.73999786376953</v>
+        <v>90.05999755859375</v>
       </c>
       <c r="E67" t="n">
-        <v>90.65000152587891</v>
+        <v>90.73000335693359</v>
       </c>
       <c r="F67" t="n">
-        <v>43331000</v>
+        <v>36525700</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
@@ -2185,22 +2185,22 @@
     </row>
     <row r="68">
       <c r="A68" s="1" t="n">
-        <v>46029</v>
+        <v>46030</v>
       </c>
       <c r="B68" t="n">
-        <v>91.55999755859375</v>
+        <v>90.44999694824219</v>
       </c>
       <c r="C68" t="n">
-        <v>92.41999816894531</v>
+        <v>91.25</v>
       </c>
       <c r="D68" t="n">
-        <v>90.05999755859375</v>
+        <v>89.58000183105469</v>
       </c>
       <c r="E68" t="n">
-        <v>90.73000335693359</v>
+        <v>90.52999877929688</v>
       </c>
       <c r="F68" t="n">
-        <v>36525700</v>
+        <v>40068700</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
@@ -2211,22 +2211,22 @@
     </row>
     <row r="69">
       <c r="A69" s="1" t="n">
-        <v>46030</v>
+        <v>46031</v>
       </c>
       <c r="B69" t="n">
-        <v>90.44999694824219</v>
+        <v>90.02999877929688</v>
       </c>
       <c r="C69" t="n">
-        <v>91.25</v>
+        <v>90.05000305175781</v>
       </c>
       <c r="D69" t="n">
-        <v>89.58000183105469</v>
+        <v>88.31999969482422</v>
       </c>
       <c r="E69" t="n">
-        <v>90.52999877929688</v>
+        <v>89.45999908447266</v>
       </c>
       <c r="F69" t="n">
-        <v>40068700</v>
+        <v>55579500</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
@@ -2237,22 +2237,22 @@
     </row>
     <row r="70">
       <c r="A70" s="1" t="n">
-        <v>46031</v>
+        <v>46034</v>
       </c>
       <c r="B70" t="n">
-        <v>90.02999877929688</v>
+        <v>89.69000244140625</v>
       </c>
       <c r="C70" t="n">
-        <v>90.05000305175781</v>
+        <v>90.33999633789062</v>
       </c>
       <c r="D70" t="n">
-        <v>88.31999969482422</v>
+        <v>89.33000183105469</v>
       </c>
       <c r="E70" t="n">
-        <v>89.45999908447266</v>
+        <v>89.41000366210938</v>
       </c>
       <c r="F70" t="n">
-        <v>55579500</v>
+        <v>36290600</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
@@ -2263,22 +2263,22 @@
     </row>
     <row r="71">
       <c r="A71" s="1" t="n">
-        <v>46034</v>
+        <v>46035</v>
       </c>
       <c r="B71" t="n">
-        <v>89.69000244140625</v>
+        <v>89.44000244140625</v>
       </c>
       <c r="C71" t="n">
-        <v>90.33999633789062</v>
+        <v>91.15000152587891</v>
       </c>
       <c r="D71" t="n">
-        <v>89.33000183105469</v>
+        <v>89.06999969482422</v>
       </c>
       <c r="E71" t="n">
-        <v>89.41000366210938</v>
+        <v>90.31999969482422</v>
       </c>
       <c r="F71" t="n">
-        <v>36290600</v>
+        <v>45221100</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
@@ -2289,22 +2289,22 @@
     </row>
     <row r="72">
       <c r="A72" s="1" t="n">
-        <v>46035</v>
+        <v>46036</v>
       </c>
       <c r="B72" t="n">
-        <v>89.44000244140625</v>
+        <v>91.23999786376953</v>
       </c>
       <c r="C72" t="n">
-        <v>91.15000152587891</v>
+        <v>91.58000183105469</v>
       </c>
       <c r="D72" t="n">
-        <v>89.06999969482422</v>
+        <v>87.94999694824219</v>
       </c>
       <c r="E72" t="n">
-        <v>90.31999969482422</v>
+        <v>88.55000305175781</v>
       </c>
       <c r="F72" t="n">
-        <v>45221100</v>
+        <v>49737700</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
@@ -2315,22 +2315,22 @@
     </row>
     <row r="73">
       <c r="A73" s="1" t="n">
-        <v>46036</v>
+        <v>46037</v>
       </c>
       <c r="B73" t="n">
-        <v>91.23999786376953</v>
+        <v>89.01999664306641</v>
       </c>
       <c r="C73" t="n">
-        <v>91.58000183105469</v>
+        <v>89.88999938964844</v>
       </c>
       <c r="D73" t="n">
-        <v>87.94999694824219</v>
+        <v>87.81999969482422</v>
       </c>
       <c r="E73" t="n">
-        <v>88.55000305175781</v>
+        <v>88.05000305175781</v>
       </c>
       <c r="F73" t="n">
-        <v>49737700</v>
+        <v>36945100</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
@@ -2341,22 +2341,22 @@
     </row>
     <row r="74">
       <c r="A74" s="1" t="n">
-        <v>46037</v>
+        <v>46038</v>
       </c>
       <c r="B74" t="n">
-        <v>89.01999664306641</v>
+        <v>88.33999633789062</v>
       </c>
       <c r="C74" t="n">
-        <v>89.88999938964844</v>
+        <v>88.51000213623047</v>
       </c>
       <c r="D74" t="n">
-        <v>87.81999969482422</v>
+        <v>87.77999877929688</v>
       </c>
       <c r="E74" t="n">
-        <v>88.05000305175781</v>
+        <v>88</v>
       </c>
       <c r="F74" t="n">
-        <v>36945100</v>
+        <v>48130500</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
@@ -2367,22 +2367,22 @@
     </row>
     <row r="75">
       <c r="A75" s="1" t="n">
-        <v>46038</v>
+        <v>46042</v>
       </c>
       <c r="B75" t="n">
-        <v>88.33999633789062</v>
+        <v>88.97000122070312</v>
       </c>
       <c r="C75" t="n">
-        <v>88.51000213623047</v>
+        <v>89.90000152587891</v>
       </c>
       <c r="D75" t="n">
-        <v>87.77999877929688</v>
+        <v>87.01999664306641</v>
       </c>
       <c r="E75" t="n">
-        <v>88</v>
+        <v>87.26000213623047</v>
       </c>
       <c r="F75" t="n">
-        <v>48130500</v>
+        <v>109729700</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
@@ -2393,22 +2393,22 @@
     </row>
     <row r="76">
       <c r="A76" s="1" t="n">
-        <v>46042</v>
+        <v>46043</v>
       </c>
       <c r="B76" t="n">
-        <v>88.97000122070312</v>
+        <v>82.51999664306641</v>
       </c>
       <c r="C76" t="n">
-        <v>89.90000152587891</v>
+        <v>86</v>
       </c>
       <c r="D76" t="n">
-        <v>87.01999664306641</v>
+        <v>81.93000030517578</v>
       </c>
       <c r="E76" t="n">
-        <v>87.26000213623047</v>
+        <v>85.36000061035156</v>
       </c>
       <c r="F76" t="n">
-        <v>109729700</v>
+        <v>127940700</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
@@ -2419,22 +2419,22 @@
     </row>
     <row r="77">
       <c r="A77" s="1" t="n">
-        <v>46043</v>
+        <v>46044</v>
       </c>
       <c r="B77" t="n">
-        <v>82.51999664306641</v>
+        <v>85.01999664306641</v>
       </c>
       <c r="C77" t="n">
-        <v>86</v>
+        <v>85.09999847412109</v>
       </c>
       <c r="D77" t="n">
-        <v>81.93000030517578</v>
+        <v>82.98000335693359</v>
       </c>
       <c r="E77" t="n">
-        <v>85.36000061035156</v>
+        <v>83.54000091552734</v>
       </c>
       <c r="F77" t="n">
-        <v>127940700</v>
+        <v>69113300</v>
       </c>
       <c r="G77" t="n">
         <v>0</v>
@@ -2445,22 +2445,22 @@
     </row>
     <row r="78">
       <c r="A78" s="1" t="n">
-        <v>46044</v>
+        <v>46045</v>
       </c>
       <c r="B78" t="n">
-        <v>85.01999664306641</v>
+        <v>83.43000030517578</v>
       </c>
       <c r="C78" t="n">
-        <v>85.09999847412109</v>
+        <v>86.30000305175781</v>
       </c>
       <c r="D78" t="n">
-        <v>82.98000335693359</v>
+        <v>83.27999877929688</v>
       </c>
       <c r="E78" t="n">
-        <v>83.54000091552734</v>
+        <v>86.12000274658203</v>
       </c>
       <c r="F78" t="n">
-        <v>69113300</v>
+        <v>64520400</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
@@ -2471,22 +2471,22 @@
     </row>
     <row r="79">
       <c r="A79" s="1" t="n">
-        <v>46045</v>
+        <v>46048</v>
       </c>
       <c r="B79" t="n">
-        <v>83.43000030517578</v>
+        <v>86.91999816894531</v>
       </c>
       <c r="C79" t="n">
-        <v>86.30000305175781</v>
+        <v>86.94000244140625</v>
       </c>
       <c r="D79" t="n">
-        <v>83.27999877929688</v>
+        <v>85.34999847412109</v>
       </c>
       <c r="E79" t="n">
-        <v>86.12000274658203</v>
+        <v>85.69999694824219</v>
       </c>
       <c r="F79" t="n">
-        <v>64520400</v>
+        <v>40941900</v>
       </c>
       <c r="G79" t="n">
         <v>0</v>
@@ -2497,22 +2497,22 @@
     </row>
     <row r="80">
       <c r="A80" s="1" t="n">
-        <v>46048</v>
+        <v>46049</v>
       </c>
       <c r="B80" t="n">
-        <v>86.91999816894531</v>
+        <v>85.27999877929688</v>
       </c>
       <c r="C80" t="n">
-        <v>86.94000244140625</v>
+        <v>85.59999847412109</v>
       </c>
       <c r="D80" t="n">
-        <v>85.34999847412109</v>
+        <v>83.87999725341797</v>
       </c>
       <c r="E80" t="n">
-        <v>85.69999694824219</v>
+        <v>85.58000183105469</v>
       </c>
       <c r="F80" t="n">
-        <v>40941900</v>
+        <v>37790800</v>
       </c>
       <c r="G80" t="n">
         <v>0</v>
@@ -2523,22 +2523,22 @@
     </row>
     <row r="81">
       <c r="A81" s="1" t="n">
-        <v>46049</v>
+        <v>46050</v>
       </c>
       <c r="B81" t="n">
-        <v>85.27999877929688</v>
+        <v>85.62999725341797</v>
       </c>
       <c r="C81" t="n">
-        <v>85.59999847412109</v>
+        <v>86.47000122070312</v>
       </c>
       <c r="D81" t="n">
-        <v>83.87999725341797</v>
+        <v>84.30000305175781</v>
       </c>
       <c r="E81" t="n">
-        <v>85.58000183105469</v>
+        <v>84.63999938964844</v>
       </c>
       <c r="F81" t="n">
-        <v>37790800</v>
+        <v>37762600</v>
       </c>
       <c r="G81" t="n">
         <v>0</v>
@@ -2549,22 +2549,22 @@
     </row>
     <row r="82">
       <c r="A82" s="1" t="n">
-        <v>46050</v>
+        <v>46051</v>
       </c>
       <c r="B82" t="n">
-        <v>85.62999725341797</v>
+        <v>84.30999755859375</v>
       </c>
       <c r="C82" t="n">
-        <v>86.47000122070312</v>
+        <v>84.37999725341797</v>
       </c>
       <c r="D82" t="n">
-        <v>84.30000305175781</v>
+        <v>82.34999847412109</v>
       </c>
       <c r="E82" t="n">
-        <v>84.63999938964844</v>
+        <v>83.16000366210938</v>
       </c>
       <c r="F82" t="n">
-        <v>37762600</v>
+        <v>42278100</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
@@ -2575,22 +2575,22 @@
     </row>
     <row r="83">
       <c r="A83" s="1" t="n">
-        <v>46051</v>
+        <v>46052</v>
       </c>
       <c r="B83" t="n">
-        <v>84.30999755859375</v>
+        <v>83.09999847412109</v>
       </c>
       <c r="C83" t="n">
-        <v>84.37999725341797</v>
+        <v>84.05999755859375</v>
       </c>
       <c r="D83" t="n">
-        <v>82.34999847412109</v>
+        <v>82.77999877929688</v>
       </c>
       <c r="E83" t="n">
-        <v>83.16000366210938</v>
+        <v>83.48999786376953</v>
       </c>
       <c r="F83" t="n">
-        <v>42278100</v>
+        <v>45755000</v>
       </c>
       <c r="G83" t="n">
         <v>0</v>
@@ -2601,22 +2601,22 @@
     </row>
     <row r="84">
       <c r="A84" s="1" t="n">
-        <v>46052</v>
+        <v>46055</v>
       </c>
       <c r="B84" t="n">
-        <v>83.09999847412109</v>
+        <v>83.52999877929688</v>
       </c>
       <c r="C84" t="n">
-        <v>84.05999755859375</v>
+        <v>85.26999664306641</v>
       </c>
       <c r="D84" t="n">
-        <v>82.77999877929688</v>
+        <v>82.72000122070312</v>
       </c>
       <c r="E84" t="n">
-        <v>83.48999786376953</v>
+        <v>82.76000213623047</v>
       </c>
       <c r="F84" t="n">
-        <v>45755000</v>
+        <v>41445300</v>
       </c>
       <c r="G84" t="n">
         <v>0</v>
@@ -2627,22 +2627,22 @@
     </row>
     <row r="85">
       <c r="A85" s="1" t="n">
-        <v>46055</v>
+        <v>46056</v>
       </c>
       <c r="B85" t="n">
-        <v>83.52999877929688</v>
+        <v>82.23000335693359</v>
       </c>
       <c r="C85" t="n">
-        <v>85.26999664306641</v>
+        <v>82.44999694824219</v>
       </c>
       <c r="D85" t="n">
-        <v>82.72000122070312</v>
+        <v>79.62000274658203</v>
       </c>
       <c r="E85" t="n">
-        <v>82.76000213623047</v>
+        <v>79.94000244140625</v>
       </c>
       <c r="F85" t="n">
-        <v>41445300</v>
+        <v>49789000</v>
       </c>
       <c r="G85" t="n">
         <v>0</v>
@@ -2653,22 +2653,22 @@
     </row>
     <row r="86">
       <c r="A86" s="1" t="n">
-        <v>46056</v>
+        <v>46057</v>
       </c>
       <c r="B86" t="n">
-        <v>82.23000335693359</v>
+        <v>79.98999786376953</v>
       </c>
       <c r="C86" t="n">
-        <v>82.44999694824219</v>
+        <v>81.44000244140625</v>
       </c>
       <c r="D86" t="n">
-        <v>79.62000274658203</v>
+        <v>79.23000335693359</v>
       </c>
       <c r="E86" t="n">
-        <v>79.94000244140625</v>
+        <v>80.16000366210938</v>
       </c>
       <c r="F86" t="n">
-        <v>49789000</v>
+        <v>48963200</v>
       </c>
       <c r="G86" t="n">
         <v>0</v>
@@ -2679,22 +2679,22 @@
     </row>
     <row r="87">
       <c r="A87" s="1" t="n">
-        <v>46057</v>
+        <v>46058</v>
       </c>
       <c r="B87" t="n">
-        <v>79.98999786376953</v>
+        <v>81.48999786376953</v>
       </c>
       <c r="C87" t="n">
-        <v>81.44000244140625</v>
+        <v>83.30000305175781</v>
       </c>
       <c r="D87" t="n">
-        <v>79.23000335693359</v>
+        <v>80.54000091552734</v>
       </c>
       <c r="E87" t="n">
-        <v>80.16000366210938</v>
+        <v>80.87000274658203</v>
       </c>
       <c r="F87" t="n">
-        <v>48963200</v>
+        <v>54805700</v>
       </c>
       <c r="G87" t="n">
         <v>0</v>
@@ -2705,22 +2705,22 @@
     </row>
     <row r="88">
       <c r="A88" s="1" t="n">
-        <v>46058</v>
+        <v>46059</v>
       </c>
       <c r="B88" t="n">
-        <v>81.48999786376953</v>
+        <v>81.01999664306641</v>
       </c>
       <c r="C88" t="n">
-        <v>83.30000305175781</v>
+        <v>82.48999786376953</v>
       </c>
       <c r="D88" t="n">
-        <v>80.54000091552734</v>
+        <v>80.65000152587891</v>
       </c>
       <c r="E88" t="n">
-        <v>80.87000274658203</v>
+        <v>82.19999694824219</v>
       </c>
       <c r="F88" t="n">
-        <v>54805700</v>
+        <v>46154100</v>
       </c>
       <c r="G88" t="n">
         <v>0</v>
@@ -2731,22 +2731,22 @@
     </row>
     <row r="89">
       <c r="A89" s="1" t="n">
-        <v>46059</v>
+        <v>46062</v>
       </c>
       <c r="B89" t="n">
-        <v>81.01999664306641</v>
+        <v>82.18000030517578</v>
       </c>
       <c r="C89" t="n">
-        <v>82.48999786376953</v>
+        <v>82.20999908447266</v>
       </c>
       <c r="D89" t="n">
-        <v>80.65000152587891</v>
+        <v>79.87000274658203</v>
       </c>
       <c r="E89" t="n">
-        <v>82.19999694824219</v>
+        <v>81.47000122070312</v>
       </c>
       <c r="F89" t="n">
-        <v>46154100</v>
+        <v>42200200</v>
       </c>
       <c r="G89" t="n">
         <v>0</v>
@@ -2757,22 +2757,22 @@
     </row>
     <row r="90">
       <c r="A90" s="1" t="n">
-        <v>46062</v>
+        <v>46063</v>
       </c>
       <c r="B90" t="n">
-        <v>82.18000030517578</v>
+        <v>82.72000122070312</v>
       </c>
       <c r="C90" t="n">
+        <v>84.66000366210938</v>
+      </c>
+      <c r="D90" t="n">
+        <v>82.08999633789062</v>
+      </c>
+      <c r="E90" t="n">
         <v>82.20999908447266</v>
       </c>
-      <c r="D90" t="n">
-        <v>79.87000274658203</v>
-      </c>
-      <c r="E90" t="n">
-        <v>81.47000122070312</v>
-      </c>
       <c r="F90" t="n">
-        <v>42200200</v>
+        <v>43595800</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
@@ -2783,22 +2783,22 @@
     </row>
     <row r="91">
       <c r="A91" s="1" t="n">
-        <v>46063</v>
+        <v>46064</v>
       </c>
       <c r="B91" t="n">
-        <v>82.72000122070312</v>
+        <v>81.95999908447266</v>
       </c>
       <c r="C91" t="n">
-        <v>84.66000366210938</v>
+        <v>82.48000335693359</v>
       </c>
       <c r="D91" t="n">
-        <v>82.08999633789062</v>
+        <v>79.44999694824219</v>
       </c>
       <c r="E91" t="n">
-        <v>82.20999908447266</v>
+        <v>79.62000274658203</v>
       </c>
       <c r="F91" t="n">
-        <v>43595800</v>
+        <v>40840300</v>
       </c>
       <c r="G91" t="n">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="92">
       <c r="A92" s="1" t="n">
-        <v>46064</v>
+        <v>46065</v>
       </c>
       <c r="B92" t="n">
-        <v>81.95999908447266</v>
+        <v>79.11000061035156</v>
       </c>
       <c r="C92" t="n">
-        <v>82.48000335693359</v>
+        <v>79.15000152587891</v>
       </c>
       <c r="D92" t="n">
-        <v>79.44999694824219</v>
+        <v>75.23000335693359</v>
       </c>
       <c r="E92" t="n">
-        <v>79.62000274658203</v>
+        <v>75.86000061035156</v>
       </c>
       <c r="F92" t="n">
-        <v>40840300</v>
+        <v>73516100</v>
       </c>
       <c r="G92" t="n">
         <v>0</v>
@@ -2835,22 +2835,22 @@
     </row>
     <row r="93">
       <c r="A93" s="1" t="n">
-        <v>46065</v>
+        <v>46066</v>
       </c>
       <c r="B93" t="n">
-        <v>79.11000061035156</v>
+        <v>76.13999938964844</v>
       </c>
       <c r="C93" t="n">
-        <v>79.15000152587891</v>
+        <v>77.18000030517578</v>
       </c>
       <c r="D93" t="n">
-        <v>75.23000335693359</v>
+        <v>75.52999877929688</v>
       </c>
       <c r="E93" t="n">
-        <v>75.86000061035156</v>
+        <v>76.87000274658203</v>
       </c>
       <c r="F93" t="n">
-        <v>73516100</v>
+        <v>42292100</v>
       </c>
       <c r="G93" t="n">
         <v>0</v>
@@ -2861,22 +2861,22 @@
     </row>
     <row r="94">
       <c r="A94" s="1" t="n">
-        <v>46066</v>
+        <v>46070</v>
       </c>
       <c r="B94" t="n">
-        <v>76.13999938964844</v>
+        <v>76.91999816894531</v>
       </c>
       <c r="C94" t="n">
-        <v>77.18000030517578</v>
+        <v>77.87000274658203</v>
       </c>
       <c r="D94" t="n">
-        <v>75.52999877929688</v>
+        <v>75.30000305175781</v>
       </c>
       <c r="E94" t="n">
-        <v>76.87000274658203</v>
+        <v>77</v>
       </c>
       <c r="F94" t="n">
-        <v>42292100</v>
+        <v>35961500</v>
       </c>
       <c r="G94" t="n">
         <v>0</v>
@@ -2887,22 +2887,22 @@
     </row>
     <row r="95">
       <c r="A95" s="1" t="n">
-        <v>46070</v>
+        <v>46071</v>
       </c>
       <c r="B95" t="n">
-        <v>76.91999816894531</v>
+        <v>77.31999969482422</v>
       </c>
       <c r="C95" t="n">
-        <v>77.87000274658203</v>
+        <v>78.31999969482422</v>
       </c>
       <c r="D95" t="n">
-        <v>75.30000305175781</v>
+        <v>76.27999877929688</v>
       </c>
       <c r="E95" t="n">
-        <v>77</v>
+        <v>77.98999786376953</v>
       </c>
       <c r="F95" t="n">
-        <v>35961500</v>
+        <v>29883100</v>
       </c>
       <c r="G95" t="n">
         <v>0</v>
@@ -2913,22 +2913,22 @@
     </row>
     <row r="96">
       <c r="A96" s="1" t="n">
-        <v>46071</v>
+        <v>46072</v>
       </c>
       <c r="B96" t="n">
-        <v>77.31999969482422</v>
+        <v>77.75</v>
       </c>
       <c r="C96" t="n">
-        <v>78.31999969482422</v>
+        <v>78.69999694824219</v>
       </c>
       <c r="D96" t="n">
-        <v>76.27999877929688</v>
+        <v>76.58999633789062</v>
       </c>
       <c r="E96" t="n">
-        <v>77.98999786376953</v>
+        <v>77</v>
       </c>
       <c r="F96" t="n">
-        <v>29883100</v>
+        <v>30139200</v>
       </c>
       <c r="G96" t="n">
         <v>0</v>
@@ -2939,22 +2939,22 @@
     </row>
     <row r="97">
       <c r="A97" s="1" t="n">
-        <v>46072</v>
+        <v>46073</v>
       </c>
       <c r="B97" t="n">
-        <v>77.75</v>
+        <v>76.61000061035156</v>
       </c>
       <c r="C97" t="n">
-        <v>78.69999694824219</v>
+        <v>78.84999847412109</v>
       </c>
       <c r="D97" t="n">
-        <v>76.58999633789062</v>
+        <v>76.40000152587891</v>
       </c>
       <c r="E97" t="n">
-        <v>77</v>
+        <v>78.66999816894531</v>
       </c>
       <c r="F97" t="n">
-        <v>30139200</v>
+        <v>32411300</v>
       </c>
       <c r="G97" t="n">
         <v>0</v>
@@ -2965,22 +2965,22 @@
     </row>
     <row r="98">
       <c r="A98" s="1" t="n">
-        <v>46073</v>
+        <v>46076</v>
       </c>
       <c r="B98" t="n">
-        <v>76.61000061035156</v>
+        <v>77.79000091552734</v>
       </c>
       <c r="C98" t="n">
-        <v>78.84999847412109</v>
+        <v>77.83000183105469</v>
       </c>
       <c r="D98" t="n">
-        <v>76.40000152587891</v>
+        <v>75.01000213623047</v>
       </c>
       <c r="E98" t="n">
-        <v>78.66999816894531</v>
+        <v>76.01999664306641</v>
       </c>
       <c r="F98" t="n">
-        <v>32411300</v>
+        <v>38363000</v>
       </c>
       <c r="G98" t="n">
         <v>0</v>
@@ -2991,22 +2991,22 @@
     </row>
     <row r="99">
       <c r="A99" s="1" t="n">
-        <v>46076</v>
+        <v>46077</v>
       </c>
       <c r="B99" t="n">
-        <v>77.79000091552734</v>
+        <v>75.73000335693359</v>
       </c>
       <c r="C99" t="n">
-        <v>77.83000183105469</v>
+        <v>78.12000274658203</v>
       </c>
       <c r="D99" t="n">
-        <v>75.01000213623047</v>
+        <v>75.20999908447266</v>
       </c>
       <c r="E99" t="n">
-        <v>76.01999664306641</v>
+        <v>78.04000091552734</v>
       </c>
       <c r="F99" t="n">
-        <v>38363000</v>
+        <v>33079100</v>
       </c>
       <c r="G99" t="n">
         <v>0</v>
@@ -3017,22 +3017,22 @@
     </row>
     <row r="100">
       <c r="A100" s="1" t="n">
-        <v>46077</v>
+        <v>46078</v>
       </c>
       <c r="B100" t="n">
-        <v>75.73000335693359</v>
+        <v>79.43000030517578</v>
       </c>
       <c r="C100" t="n">
-        <v>78.12000274658203</v>
+        <v>83.12000274658203</v>
       </c>
       <c r="D100" t="n">
-        <v>75.20999908447266</v>
+        <v>79.25</v>
       </c>
       <c r="E100" t="n">
-        <v>78.04000091552734</v>
+        <v>82.69999694824219</v>
       </c>
       <c r="F100" t="n">
-        <v>33079100</v>
+        <v>69319300</v>
       </c>
       <c r="G100" t="n">
         <v>0</v>
@@ -3043,22 +3043,22 @@
     </row>
     <row r="101">
       <c r="A101" s="1" t="n">
-        <v>46078</v>
+        <v>46079</v>
       </c>
       <c r="B101" t="n">
-        <v>79.43000030517578</v>
+        <v>83.19999694824219</v>
       </c>
       <c r="C101" t="n">
-        <v>83.12000274658203</v>
+        <v>86.5</v>
       </c>
       <c r="D101" t="n">
-        <v>79.25</v>
+        <v>82.80000305175781</v>
       </c>
       <c r="E101" t="n">
-        <v>82.69999694824219</v>
+        <v>84.58999633789062</v>
       </c>
       <c r="F101" t="n">
-        <v>69319300</v>
+        <v>85642500</v>
       </c>
       <c r="G101" t="n">
         <v>0</v>
@@ -3069,22 +3069,22 @@
     </row>
     <row r="102">
       <c r="A102" s="1" t="n">
-        <v>46079</v>
+        <v>46080</v>
       </c>
       <c r="B102" t="n">
-        <v>83.19999694824219</v>
+        <v>94.30000305175781</v>
       </c>
       <c r="C102" t="n">
-        <v>86.5</v>
+        <v>96.75</v>
       </c>
       <c r="D102" t="n">
-        <v>82.80000305175781</v>
+        <v>90.58000183105469</v>
       </c>
       <c r="E102" t="n">
-        <v>84.58999633789062</v>
+        <v>96.23999786376953</v>
       </c>
       <c r="F102" t="n">
-        <v>85642500</v>
+        <v>200767000</v>
       </c>
       <c r="G102" t="n">
         <v>0</v>
@@ -3095,22 +3095,22 @@
     </row>
     <row r="103">
       <c r="A103" s="1" t="n">
-        <v>46080</v>
+        <v>46083</v>
       </c>
       <c r="B103" t="n">
-        <v>94.30000305175781</v>
+        <v>95.26000213623047</v>
       </c>
       <c r="C103" t="n">
-        <v>96.75</v>
+        <v>98.06999969482422</v>
       </c>
       <c r="D103" t="n">
-        <v>90.58000183105469</v>
+        <v>95.19999694824219</v>
       </c>
       <c r="E103" t="n">
-        <v>96.23999786376953</v>
+        <v>97.08999633789062</v>
       </c>
       <c r="F103" t="n">
-        <v>200767000</v>
+        <v>79915400</v>
       </c>
       <c r="G103" t="n">
         <v>0</v>
@@ -3121,22 +3121,22 @@
     </row>
     <row r="104">
       <c r="A104" s="1" t="n">
-        <v>46083</v>
+        <v>46084</v>
       </c>
       <c r="B104" t="n">
-        <v>95.26000213623047</v>
+        <v>96.01000213623047</v>
       </c>
       <c r="C104" t="n">
-        <v>98.06999969482422</v>
+        <v>98.45999908447266</v>
       </c>
       <c r="D104" t="n">
-        <v>95.19999694824219</v>
+        <v>95.33000183105469</v>
       </c>
       <c r="E104" t="n">
-        <v>97.08999633789062</v>
+        <v>97.69999694824219</v>
       </c>
       <c r="F104" t="n">
-        <v>79915400</v>
+        <v>59149000</v>
       </c>
       <c r="G104" t="n">
         <v>0</v>
@@ -3147,22 +3147,22 @@
     </row>
     <row r="105">
       <c r="A105" s="1" t="n">
-        <v>46084</v>
+        <v>46085</v>
       </c>
       <c r="B105" t="n">
-        <v>96.01000213623047</v>
+        <v>97.11000061035156</v>
       </c>
       <c r="C105" t="n">
-        <v>98.45999908447266</v>
+        <v>99.75</v>
       </c>
       <c r="D105" t="n">
-        <v>95.33000183105469</v>
+        <v>96.98999786376953</v>
       </c>
       <c r="E105" t="n">
-        <v>97.69999694824219</v>
+        <v>98.66000366210938</v>
       </c>
       <c r="F105" t="n">
-        <v>59149000</v>
+        <v>52604300</v>
       </c>
       <c r="G105" t="n">
         <v>0</v>
@@ -3173,22 +3173,22 @@
     </row>
     <row r="106">
       <c r="A106" s="1" t="n">
-        <v>46085</v>
+        <v>46086</v>
       </c>
       <c r="B106" t="n">
-        <v>97.11000061035156</v>
+        <v>98.5</v>
       </c>
       <c r="C106" t="n">
-        <v>99.75</v>
+        <v>100.1900024414062</v>
       </c>
       <c r="D106" t="n">
-        <v>96.98999786376953</v>
+        <v>98.09999847412109</v>
       </c>
       <c r="E106" t="n">
-        <v>98.66000366210938</v>
+        <v>99.16999816894531</v>
       </c>
       <c r="F106" t="n">
-        <v>52604300</v>
+        <v>53403000</v>
       </c>
       <c r="G106" t="n">
         <v>0</v>
@@ -3199,22 +3199,22 @@
     </row>
     <row r="107">
       <c r="A107" s="1" t="n">
-        <v>46086</v>
+        <v>46087</v>
       </c>
       <c r="B107" t="n">
-        <v>98.5</v>
+        <v>99.33000183105469</v>
       </c>
       <c r="C107" t="n">
-        <v>100.1900024414062</v>
+        <v>99.87999725341797</v>
       </c>
       <c r="D107" t="n">
-        <v>98.09999847412109</v>
+        <v>97.40000152587891</v>
       </c>
       <c r="E107" t="n">
-        <v>99.16999816894531</v>
+        <v>99.01999664306641</v>
       </c>
       <c r="F107" t="n">
-        <v>53403000</v>
+        <v>41196300</v>
       </c>
       <c r="G107" t="n">
         <v>0</v>
@@ -3225,22 +3225,22 @@
     </row>
     <row r="108">
       <c r="A108" s="1" t="n">
-        <v>46087</v>
+        <v>46090</v>
       </c>
       <c r="B108" t="n">
-        <v>99.33000183105469</v>
+        <v>97.69999694824219</v>
       </c>
       <c r="C108" t="n">
-        <v>99.87999725341797</v>
+        <v>98.94000244140625</v>
       </c>
       <c r="D108" t="n">
-        <v>97.40000152587891</v>
+        <v>96.58000183105469</v>
       </c>
       <c r="E108" t="n">
-        <v>99.01999664306641</v>
+        <v>98.31999969482422</v>
       </c>
       <c r="F108" t="n">
-        <v>41196300</v>
+        <v>48589000</v>
       </c>
       <c r="G108" t="n">
         <v>0</v>
@@ -3251,22 +3251,22 @@
     </row>
     <row r="109">
       <c r="A109" s="1" t="n">
-        <v>46090</v>
+        <v>46091</v>
       </c>
       <c r="B109" t="n">
-        <v>97.69999694824219</v>
+        <v>97.80999755859375</v>
       </c>
       <c r="C109" t="n">
-        <v>98.94000244140625</v>
+        <v>98.48999786376953</v>
       </c>
       <c r="D109" t="n">
-        <v>96.58000183105469</v>
+        <v>96.29000091552734</v>
       </c>
       <c r="E109" t="n">
-        <v>98.31999969482422</v>
+        <v>96.94000244140625</v>
       </c>
       <c r="F109" t="n">
-        <v>48589000</v>
+        <v>41027200</v>
       </c>
       <c r="G109" t="n">
         <v>0</v>
@@ -3277,22 +3277,22 @@
     </row>
     <row r="110">
       <c r="A110" s="1" t="n">
-        <v>46091</v>
+        <v>46092</v>
       </c>
       <c r="B110" t="n">
-        <v>97.80999755859375</v>
+        <v>97.41000366210938</v>
       </c>
       <c r="C110" t="n">
-        <v>98.48999786376953</v>
+        <v>98</v>
       </c>
       <c r="D110" t="n">
-        <v>96.29000091552734</v>
+        <v>94.69000244140625</v>
       </c>
       <c r="E110" t="n">
-        <v>96.94000244140625</v>
+        <v>94.88999938964844</v>
       </c>
       <c r="F110" t="n">
-        <v>41027200</v>
+        <v>33962900</v>
       </c>
       <c r="G110" t="n">
         <v>0</v>
@@ -3303,22 +3303,22 @@
     </row>
     <row r="111">
       <c r="A111" s="1" t="n">
-        <v>46092</v>
+        <v>46093</v>
       </c>
       <c r="B111" t="n">
-        <v>97.41000366210938</v>
+        <v>94.86000061035156</v>
       </c>
       <c r="C111" t="n">
-        <v>98</v>
+        <v>95.40000152587891</v>
       </c>
       <c r="D111" t="n">
-        <v>94.69000244140625</v>
+        <v>93.87000274658203</v>
       </c>
       <c r="E111" t="n">
-        <v>94.88999938964844</v>
+        <v>94.30999755859375</v>
       </c>
       <c r="F111" t="n">
-        <v>33962900</v>
+        <v>34206900</v>
       </c>
       <c r="G111" t="n">
         <v>0</v>
@@ -3329,22 +3329,22 @@
     </row>
     <row r="112">
       <c r="A112" s="1" t="n">
-        <v>46093</v>
+        <v>46094</v>
       </c>
       <c r="B112" t="n">
-        <v>94.86000061035156</v>
+        <v>94.63999938964844</v>
       </c>
       <c r="C112" t="n">
-        <v>95.40000152587891</v>
+        <v>95.68000030517578</v>
       </c>
       <c r="D112" t="n">
-        <v>93.87000274658203</v>
+        <v>94.23999786376953</v>
       </c>
       <c r="E112" t="n">
-        <v>94.30999755859375</v>
+        <v>95.30999755859375</v>
       </c>
       <c r="F112" t="n">
-        <v>34206900</v>
+        <v>29876700</v>
       </c>
       <c r="G112" t="n">
         <v>0</v>
@@ -3355,22 +3355,22 @@
     </row>
     <row r="113">
       <c r="A113" s="1" t="n">
-        <v>46094</v>
+        <v>46097</v>
       </c>
       <c r="B113" t="n">
-        <v>94.63999938964844</v>
+        <v>95.58000183105469</v>
       </c>
       <c r="C113" t="n">
-        <v>95.68000030517578</v>
+        <v>96.09999847412109</v>
       </c>
       <c r="D113" t="n">
-        <v>94.23999786376953</v>
+        <v>94.36000061035156</v>
       </c>
       <c r="E113" t="n">
-        <v>95.30999755859375</v>
+        <v>95.19999694824219</v>
       </c>
       <c r="F113" t="n">
-        <v>29876700</v>
+        <v>34931800</v>
       </c>
       <c r="G113" t="n">
         <v>0</v>
@@ -3381,22 +3381,22 @@
     </row>
     <row r="114">
       <c r="A114" s="1" t="n">
-        <v>46097</v>
+        <v>46098</v>
       </c>
       <c r="B114" t="n">
-        <v>95.58000183105469</v>
+        <v>95.30000305175781</v>
       </c>
       <c r="C114" t="n">
-        <v>96.09999847412109</v>
+        <v>96.33999633789062</v>
       </c>
       <c r="D114" t="n">
+        <v>94.01000213623047</v>
+      </c>
+      <c r="E114" t="n">
         <v>94.36000061035156</v>
       </c>
-      <c r="E114" t="n">
-        <v>95.19999694824219</v>
-      </c>
       <c r="F114" t="n">
-        <v>34931800</v>
+        <v>26434500</v>
       </c>
       <c r="G114" t="n">
         <v>0</v>
@@ -3407,22 +3407,22 @@
     </row>
     <row r="115">
       <c r="A115" s="1" t="n">
-        <v>46098</v>
+        <v>46099</v>
       </c>
       <c r="B115" t="n">
-        <v>95.30000305175781</v>
+        <v>94.44999694824219</v>
       </c>
       <c r="C115" t="n">
-        <v>96.33999633789062</v>
+        <v>95.33999633789062</v>
       </c>
       <c r="D115" t="n">
-        <v>94.01000213623047</v>
+        <v>93.61000061035156</v>
       </c>
       <c r="E115" t="n">
-        <v>94.36000061035156</v>
+        <v>94.69999694824219</v>
       </c>
       <c r="F115" t="n">
-        <v>26434500</v>
+        <v>27878300</v>
       </c>
       <c r="G115" t="n">
         <v>0</v>
@@ -3433,22 +3433,22 @@
     </row>
     <row r="116">
       <c r="A116" s="1" t="n">
-        <v>46099</v>
+        <v>46100</v>
       </c>
       <c r="B116" t="n">
-        <v>94.44999694824219</v>
+        <v>94.30999755859375</v>
       </c>
       <c r="C116" t="n">
-        <v>95.33999633789062</v>
+        <v>95.75</v>
       </c>
       <c r="D116" t="n">
-        <v>93.61000061035156</v>
+        <v>90.77999877929688</v>
       </c>
       <c r="E116" t="n">
-        <v>94.69999694824219</v>
+        <v>91.73999786376953</v>
       </c>
       <c r="F116" t="n">
-        <v>27878300</v>
+        <v>40169300</v>
       </c>
       <c r="G116" t="n">
         <v>0</v>
@@ -3459,22 +3459,22 @@
     </row>
     <row r="117">
       <c r="A117" s="1" t="n">
-        <v>46100</v>
+        <v>46101</v>
       </c>
       <c r="B117" t="n">
-        <v>94.30999755859375</v>
+        <v>91.30999755859375</v>
       </c>
       <c r="C117" t="n">
-        <v>95.75</v>
+        <v>91.87999725341797</v>
       </c>
       <c r="D117" t="n">
-        <v>90.77999877929688</v>
+        <v>90.69000244140625</v>
       </c>
       <c r="E117" t="n">
-        <v>91.73999786376953</v>
+        <v>91.81999969482422</v>
       </c>
       <c r="F117" t="n">
-        <v>40169300</v>
+        <v>61678000</v>
       </c>
       <c r="G117" t="n">
         <v>0</v>
@@ -3485,22 +3485,22 @@
     </row>
     <row r="118">
       <c r="A118" s="1" t="n">
-        <v>46101</v>
+        <v>46104</v>
       </c>
       <c r="B118" t="n">
-        <v>91.30999755859375</v>
+        <v>92.04000091552734</v>
       </c>
       <c r="C118" t="n">
-        <v>91.87999725341797</v>
+        <v>93.98000335693359</v>
       </c>
       <c r="D118" t="n">
-        <v>90.69000244140625</v>
+        <v>91.86000061035156</v>
       </c>
       <c r="E118" t="n">
-        <v>91.81999969482422</v>
+        <v>93.37999725341797</v>
       </c>
       <c r="F118" t="n">
-        <v>61678000</v>
+        <v>34315900</v>
       </c>
       <c r="G118" t="n">
         <v>0</v>
@@ -3511,22 +3511,22 @@
     </row>
     <row r="119">
       <c r="A119" s="1" t="n">
-        <v>46104</v>
+        <v>46105</v>
       </c>
       <c r="B119" t="n">
-        <v>92.04000091552734</v>
+        <v>92.79000091552734</v>
       </c>
       <c r="C119" t="n">
-        <v>93.98000335693359</v>
+        <v>93.73999786376953</v>
       </c>
       <c r="D119" t="n">
-        <v>91.86000061035156</v>
+        <v>90.81999969482422</v>
       </c>
       <c r="E119" t="n">
-        <v>93.37999725341797</v>
+        <v>90.91999816894531</v>
       </c>
       <c r="F119" t="n">
-        <v>34315900</v>
+        <v>28938000</v>
       </c>
       <c r="G119" t="n">
         <v>0</v>
@@ -3537,22 +3537,22 @@
     </row>
     <row r="120">
       <c r="A120" s="1" t="n">
-        <v>46105</v>
+        <v>46106</v>
       </c>
       <c r="B120" t="n">
-        <v>92.79000091552734</v>
+        <v>91.70999908447266</v>
       </c>
       <c r="C120" t="n">
-        <v>93.73999786376953</v>
+        <v>92.51999664306641</v>
       </c>
       <c r="D120" t="n">
-        <v>90.81999969482422</v>
+        <v>91.23999786376953</v>
       </c>
       <c r="E120" t="n">
-        <v>90.91999816894531</v>
+        <v>92.27999877929688</v>
       </c>
       <c r="F120" t="n">
-        <v>28938000</v>
+        <v>29545600</v>
       </c>
       <c r="G120" t="n">
         <v>0</v>
@@ -3563,22 +3563,22 @@
     </row>
     <row r="121">
       <c r="A121" s="1" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B121" t="n">
-        <v>91.70999908447266</v>
+        <v>91.51999664306641</v>
       </c>
       <c r="C121" t="n">
-        <v>92.51999664306641</v>
+        <v>95.86000061035156</v>
       </c>
       <c r="D121" t="n">
-        <v>91.23999786376953</v>
+        <v>91.01000213623047</v>
       </c>
       <c r="E121" t="n">
-        <v>92.27999877929688</v>
+        <v>93.31999969482422</v>
       </c>
       <c r="F121" t="n">
-        <v>29545600</v>
+        <v>59522000</v>
       </c>
       <c r="G121" t="n">
         <v>0</v>
@@ -3589,22 +3589,22 @@
     </row>
     <row r="122">
       <c r="A122" s="1" t="n">
-        <v>46107</v>
+        <v>46108</v>
       </c>
       <c r="B122" t="n">
-        <v>91.51999664306641</v>
+        <v>94.56999969482422</v>
       </c>
       <c r="C122" t="n">
-        <v>95.86000061035156</v>
+        <v>95.58000183105469</v>
       </c>
       <c r="D122" t="n">
-        <v>91.01000213623047</v>
+        <v>92.73999786376953</v>
       </c>
       <c r="E122" t="n">
-        <v>93.31999969482422</v>
+        <v>93.43000030517578</v>
       </c>
       <c r="F122" t="n">
-        <v>59522000</v>
+        <v>44590700</v>
       </c>
       <c r="G122" t="n">
         <v>0</v>
@@ -3615,22 +3615,22 @@
     </row>
     <row r="123">
       <c r="A123" s="1" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B123" t="n">
-        <v>94.56999969482422</v>
+        <v>92.75</v>
       </c>
       <c r="C123" t="n">
-        <v>95.58000183105469</v>
+        <v>94.48999786376953</v>
       </c>
       <c r="D123" t="n">
-        <v>92.73999786376953</v>
+        <v>92.22000122070312</v>
       </c>
       <c r="E123" t="n">
-        <v>93.43000030517578</v>
+        <v>92.97000122070312</v>
       </c>
       <c r="F123" t="n">
-        <v>44590700</v>
+        <v>32375100</v>
       </c>
       <c r="G123" t="n">
         <v>0</v>
@@ -3641,22 +3641,22 @@
     </row>
     <row r="124">
       <c r="A124" s="1" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B124" t="n">
-        <v>92.75</v>
+        <v>93.02999877929688</v>
       </c>
       <c r="C124" t="n">
-        <v>94.48999786376953</v>
+        <v>96.26000213623047</v>
       </c>
       <c r="D124" t="n">
-        <v>92.22000122070312</v>
+        <v>93.02999877929688</v>
       </c>
       <c r="E124" t="n">
-        <v>92.97000122070312</v>
+        <v>96.15000152587891</v>
       </c>
       <c r="F124" t="n">
-        <v>32375100</v>
+        <v>54270000</v>
       </c>
       <c r="G124" t="n">
         <v>0</v>
@@ -3667,22 +3667,22 @@
     </row>
     <row r="125">
       <c r="A125" s="1" t="n">
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="B125" t="n">
-        <v>93.02999877929688</v>
+        <v>96.47000122070312</v>
       </c>
       <c r="C125" t="n">
-        <v>96.26000213623047</v>
+        <v>97.19999694824219</v>
       </c>
       <c r="D125" t="n">
-        <v>93.02999877929688</v>
+        <v>94.26000213623047</v>
       </c>
       <c r="E125" t="n">
-        <v>96.15000152587891</v>
+        <v>95.55000305175781</v>
       </c>
       <c r="F125" t="n">
-        <v>54270000</v>
+        <v>30439300</v>
       </c>
       <c r="G125" t="n">
         <v>0</v>
@@ -3693,22 +3693,22 @@
     </row>
     <row r="126">
       <c r="A126" s="1" t="n">
-        <v>46113</v>
+        <v>46114</v>
       </c>
       <c r="B126" t="n">
-        <v>96.47000122070312</v>
+        <v>95.26999664306641</v>
       </c>
       <c r="C126" t="n">
-        <v>97.19999694824219</v>
+        <v>98.70999908447266</v>
       </c>
       <c r="D126" t="n">
-        <v>94.26000213623047</v>
+        <v>95.16999816894531</v>
       </c>
       <c r="E126" t="n">
-        <v>95.55000305175781</v>
+        <v>98.66000366210938</v>
       </c>
       <c r="F126" t="n">
-        <v>30439300</v>
+        <v>37068000</v>
       </c>
       <c r="G126" t="n">
         <v>0</v>
@@ -3719,22 +3719,22 @@
     </row>
     <row r="127">
       <c r="A127" s="1" t="n">
-        <v>46114</v>
+        <v>46118</v>
       </c>
       <c r="B127" t="n">
-        <v>95.26999664306641</v>
+        <v>100.9599990844727</v>
       </c>
       <c r="C127" t="n">
-        <v>98.70999908447266</v>
+        <v>102.6900024414062</v>
       </c>
       <c r="D127" t="n">
-        <v>95.16999816894531</v>
+        <v>97.97000122070312</v>
       </c>
       <c r="E127" t="n">
-        <v>98.66000366210938</v>
+        <v>98.93000030517578</v>
       </c>
       <c r="F127" t="n">
-        <v>37068000</v>
+        <v>37029300</v>
       </c>
       <c r="G127" t="n">
         <v>0</v>
@@ -3745,22 +3745,22 @@
     </row>
     <row r="128">
       <c r="A128" s="1" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B128" t="n">
-        <v>100.9599990844727</v>
+        <v>98.55000305175781</v>
       </c>
       <c r="C128" t="n">
-        <v>102.6900024414062</v>
+        <v>99.87999725341797</v>
       </c>
       <c r="D128" t="n">
-        <v>97.97000122070312</v>
+        <v>98.25</v>
       </c>
       <c r="E128" t="n">
-        <v>98.93000030517578</v>
+        <v>98.81999969482422</v>
       </c>
       <c r="F128" t="n">
-        <v>37029300</v>
+        <v>25016700</v>
       </c>
       <c r="G128" t="n">
         <v>0</v>
@@ -3771,22 +3771,22 @@
     </row>
     <row r="129">
       <c r="A129" s="1" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B129" t="n">
-        <v>98.55000305175781</v>
+        <v>100.3199996948242</v>
       </c>
       <c r="C129" t="n">
-        <v>99.87999725341797</v>
+        <v>100.4000015258789</v>
       </c>
       <c r="D129" t="n">
-        <v>98.25</v>
+        <v>97.44000244140625</v>
       </c>
       <c r="E129" t="n">
-        <v>98.81999969482422</v>
+        <v>99.38999938964844</v>
       </c>
       <c r="F129" t="n">
-        <v>25016700</v>
+        <v>30957600</v>
       </c>
       <c r="G129" t="n">
         <v>0</v>
@@ -3797,22 +3797,22 @@
     </row>
     <row r="130">
       <c r="A130" s="1" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B130" t="n">
-        <v>100.3199996948242</v>
+        <v>99.62999725341797</v>
       </c>
       <c r="C130" t="n">
-        <v>100.4000015258789</v>
+        <v>102.3399963378906</v>
       </c>
       <c r="D130" t="n">
-        <v>97.44000244140625</v>
+        <v>99.08000183105469</v>
       </c>
       <c r="E130" t="n">
-        <v>99.38999938964844</v>
+        <v>102.0500030517578</v>
       </c>
       <c r="F130" t="n">
-        <v>30957600</v>
+        <v>35087800</v>
       </c>
       <c r="G130" t="n">
         <v>0</v>
@@ -3823,22 +3823,22 @@
     </row>
     <row r="131">
       <c r="A131" s="1" t="n">
-        <v>46121</v>
+        <v>46122</v>
       </c>
       <c r="B131" t="n">
-        <v>99.62999725341797</v>
+        <v>102.4700012207031</v>
       </c>
       <c r="C131" t="n">
-        <v>102.3399963378906</v>
+        <v>103.0800018310547</v>
       </c>
       <c r="D131" t="n">
-        <v>99.08000183105469</v>
+        <v>101.4599990844727</v>
       </c>
       <c r="E131" t="n">
-        <v>102.0500030517578</v>
+        <v>103.0100021362305</v>
       </c>
       <c r="F131" t="n">
-        <v>35087800</v>
+        <v>25769900</v>
       </c>
       <c r="G131" t="n">
         <v>0</v>
@@ -3849,22 +3849,22 @@
     </row>
     <row r="132">
       <c r="A132" s="1" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B132" t="n">
-        <v>102.4700012207031</v>
+        <v>103.0299987792969</v>
       </c>
       <c r="C132" t="n">
-        <v>103.0800018310547</v>
+        <v>103.6699981689453</v>
       </c>
       <c r="D132" t="n">
-        <v>101.4599990844727</v>
+        <v>102.0599975585938</v>
       </c>
       <c r="E132" t="n">
-        <v>103.0100021362305</v>
+        <v>103.1600036621094</v>
       </c>
       <c r="F132" t="n">
-        <v>25769900</v>
+        <v>26042800</v>
       </c>
       <c r="G132" t="n">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="133">
       <c r="A133" s="1" t="n">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="B133" t="n">
-        <v>103.0299987792969</v>
+        <v>103.120002746582</v>
       </c>
       <c r="C133" t="n">
-        <v>103.6699981689453</v>
+        <v>106.5699996948242</v>
       </c>
       <c r="D133" t="n">
-        <v>102.0599975585938</v>
+        <v>103.0400009155273</v>
       </c>
       <c r="E133" t="n">
-        <v>103.1600036621094</v>
+        <v>106.2799987792969</v>
       </c>
       <c r="F133" t="n">
-        <v>26042800</v>
+        <v>40534900</v>
       </c>
       <c r="G133" t="n">
         <v>0</v>
@@ -3901,22 +3901,22 @@
     </row>
     <row r="134">
       <c r="A134" s="1" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B134" t="n">
-        <v>103.120002746582</v>
+        <v>105.9800033569336</v>
       </c>
       <c r="C134" t="n">
-        <v>106.5699996948242</v>
+        <v>107.8499984741211</v>
       </c>
       <c r="D134" t="n">
-        <v>103.0400009155273</v>
+        <v>105.0400009155273</v>
       </c>
       <c r="E134" t="n">
-        <v>106.2799987792969</v>
+        <v>107.7099990844727</v>
       </c>
       <c r="F134" t="n">
-        <v>40534900</v>
+        <v>38023700</v>
       </c>
       <c r="G134" t="n">
         <v>0</v>
@@ -3927,22 +3927,22 @@
     </row>
     <row r="135">
       <c r="A135" s="1" t="n">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c r="B135" t="n">
-        <v>105.9800033569336</v>
+        <v>107.4700012207031</v>
       </c>
       <c r="C135" t="n">
-        <v>107.8499984741211</v>
+        <v>108.9499969482422</v>
       </c>
       <c r="D135" t="n">
-        <v>105.0400009155273</v>
+        <v>106.620002746582</v>
       </c>
       <c r="E135" t="n">
-        <v>107.7099990844727</v>
+        <v>107.7900009155273</v>
       </c>
       <c r="F135" t="n">
-        <v>38023700</v>
+        <v>64928300</v>
       </c>
       <c r="G135" t="n">
         <v>0</v>
@@ -3953,22 +3953,22 @@
     </row>
     <row r="136">
       <c r="A136" s="1" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B136" t="n">
-        <v>107.4700012207031</v>
+        <v>96.37000274658203</v>
       </c>
       <c r="C136" t="n">
-        <v>108.9499969482422</v>
+        <v>98.73999786376953</v>
       </c>
       <c r="D136" t="n">
-        <v>106.620002746582</v>
+        <v>95.09999847412109</v>
       </c>
       <c r="E136" t="n">
-        <v>107.7900009155273</v>
+        <v>97.30999755859375</v>
       </c>
       <c r="F136" t="n">
-        <v>64928300</v>
+        <v>125958700</v>
       </c>
       <c r="G136" t="n">
         <v>0</v>
@@ -3979,22 +3979,22 @@
     </row>
     <row r="137">
       <c r="A137" s="1" t="n">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c r="B137" t="n">
-        <v>96.37000274658203</v>
+        <v>97.13999938964844</v>
       </c>
       <c r="C137" t="n">
-        <v>98.73999786376953</v>
+        <v>97.59999847412109</v>
       </c>
       <c r="D137" t="n">
-        <v>95.09999847412109</v>
+        <v>93.54000091552734</v>
       </c>
       <c r="E137" t="n">
-        <v>97.30999755859375</v>
+        <v>94.83000183105469</v>
       </c>
       <c r="F137" t="n">
-        <v>125958700</v>
+        <v>63298300</v>
       </c>
       <c r="G137" t="n">
         <v>0</v>
@@ -4005,22 +4005,22 @@
     </row>
     <row r="138">
       <c r="A138" s="1" t="n">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="B138" t="n">
-        <v>97.13999938964844</v>
+        <v>94</v>
       </c>
       <c r="C138" t="n">
-        <v>97.59999847412109</v>
+        <v>94.65000152587891</v>
       </c>
       <c r="D138" t="n">
-        <v>93.54000091552734</v>
+        <v>92.37000274658203</v>
       </c>
       <c r="E138" t="n">
-        <v>94.83000183105469</v>
+        <v>92.58000183105469</v>
       </c>
       <c r="F138" t="n">
-        <v>63298300</v>
+        <v>61962300</v>
       </c>
       <c r="G138" t="n">
         <v>0</v>
@@ -4031,22 +4031,22 @@
     </row>
     <row r="139">
       <c r="A139" s="1" t="n">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="B139" t="n">
-        <v>94</v>
+        <v>93.05999755859375</v>
       </c>
       <c r="C139" t="n">
-        <v>94.65000152587891</v>
+        <v>93.84999847412109</v>
       </c>
       <c r="D139" t="n">
-        <v>92.37000274658203</v>
+        <v>92.76999664306641</v>
       </c>
       <c r="E139" t="n">
-        <v>92.58000183105469</v>
+        <v>93.23999786376953</v>
       </c>
       <c r="F139" t="n">
-        <v>61962300</v>
+        <v>33694300</v>
       </c>
       <c r="G139" t="n">
         <v>0</v>
@@ -4057,22 +4057,22 @@
     </row>
     <row r="140">
       <c r="A140" s="1" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B140" t="n">
-        <v>93.05999755859375</v>
+        <v>94.05999755859375</v>
       </c>
       <c r="C140" t="n">
-        <v>93.84999847412109</v>
+        <v>94.63999938964844</v>
       </c>
       <c r="D140" t="n">
-        <v>92.76999664306641</v>
+        <v>92.06999969482422</v>
       </c>
       <c r="E140" t="n">
-        <v>93.23999786376953</v>
+        <v>92.81999969482422</v>
       </c>
       <c r="F140" t="n">
-        <v>33694300</v>
+        <v>36851700</v>
       </c>
       <c r="G140" t="n">
         <v>0</v>
@@ -4083,22 +4083,22 @@
     </row>
     <row r="141">
       <c r="A141" s="1" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B141" t="n">
-        <v>94.05999755859375</v>
+        <v>92.56999969482422</v>
       </c>
       <c r="C141" t="n">
-        <v>94.63999938964844</v>
+        <v>93.27999877929688</v>
       </c>
       <c r="D141" t="n">
-        <v>92.06999969482422</v>
+        <v>91.80000305175781</v>
       </c>
       <c r="E141" t="n">
-        <v>92.81999969482422</v>
+        <v>92.44000244140625</v>
       </c>
       <c r="F141" t="n">
-        <v>36851700</v>
+        <v>32553200</v>
       </c>
       <c r="G141" t="n">
         <v>0</v>
@@ -4109,22 +4109,22 @@
     </row>
     <row r="142">
       <c r="A142" s="1" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B142" t="n">
-        <v>92.56999969482422</v>
+        <v>92.05000305175781</v>
       </c>
       <c r="C142" t="n">
-        <v>93.27999877929688</v>
+        <v>92.83999633789062</v>
       </c>
       <c r="D142" t="n">
-        <v>91.80000305175781</v>
+        <v>91.30000305175781</v>
       </c>
       <c r="E142" t="n">
-        <v>92.44000244140625</v>
+        <v>91.37000274658203</v>
       </c>
       <c r="F142" t="n">
-        <v>32553200</v>
+        <v>29707400</v>
       </c>
       <c r="G142" t="n">
         <v>0</v>
@@ -4135,22 +4135,22 @@
     </row>
     <row r="143">
       <c r="A143" s="1" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B143" t="n">
-        <v>92.05000305175781</v>
+        <v>91.5</v>
       </c>
       <c r="C143" t="n">
-        <v>92.83999633789062</v>
+        <v>92.33999633789062</v>
       </c>
       <c r="D143" t="n">
-        <v>91.30000305175781</v>
+        <v>90.01999664306641</v>
       </c>
       <c r="E143" t="n">
-        <v>91.37000274658203</v>
+        <v>92.26999664306641</v>
       </c>
       <c r="F143" t="n">
-        <v>29707400</v>
+        <v>33418100</v>
       </c>
       <c r="G143" t="n">
         <v>0</v>
@@ -4161,22 +4161,22 @@
     </row>
     <row r="144">
       <c r="A144" s="1" t="n">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="B144" t="n">
-        <v>91.5</v>
+        <v>91.23000335693359</v>
       </c>
       <c r="C144" t="n">
-        <v>92.33999633789062</v>
+        <v>92.86000061035156</v>
       </c>
       <c r="D144" t="n">
-        <v>90.01999664306641</v>
+        <v>90.86000061035156</v>
       </c>
       <c r="E144" t="n">
-        <v>92.26999664306641</v>
+        <v>92.12000274658203</v>
       </c>
       <c r="F144" t="n">
-        <v>33418100</v>
+        <v>26122100</v>
       </c>
       <c r="G144" t="n">
         <v>0</v>
@@ -4187,22 +4187,22 @@
     </row>
     <row r="145">
       <c r="A145" s="1" t="n">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="B145" t="n">
-        <v>91.23000335693359</v>
+        <v>91.34999847412109</v>
       </c>
       <c r="C145" t="n">
-        <v>92.86000061035156</v>
+        <v>94.22000122070312</v>
       </c>
       <c r="D145" t="n">
-        <v>90.86000061035156</v>
+        <v>90.76999664306641</v>
       </c>
       <c r="E145" t="n">
-        <v>92.12000274658203</v>
+        <v>93.61000061035156</v>
       </c>
       <c r="F145" t="n">
-        <v>26122100</v>
+        <v>40923000</v>
       </c>
       <c r="G145" t="n">
         <v>0</v>
@@ -4213,22 +4213,22 @@
     </row>
     <row r="146">
       <c r="A146" s="1" t="n">
-        <v>46142</v>
+        <v>46143</v>
       </c>
       <c r="B146" t="n">
-        <v>91.34999847412109</v>
+        <v>94.41999816894531</v>
       </c>
       <c r="C146" t="n">
-        <v>94.22000122070312</v>
+        <v>94.69999694824219</v>
       </c>
       <c r="D146" t="n">
-        <v>90.76999664306641</v>
+        <v>91.90000152587891</v>
       </c>
       <c r="E146" t="n">
-        <v>93.61000061035156</v>
+        <v>92.05999755859375</v>
       </c>
       <c r="F146" t="n">
-        <v>40923000</v>
+        <v>30406900</v>
       </c>
       <c r="G146" t="n">
         <v>0</v>
@@ -4239,22 +4239,22 @@
     </row>
     <row r="147">
       <c r="A147" s="1" t="n">
-        <v>46143</v>
+        <v>46146</v>
       </c>
       <c r="B147" t="n">
-        <v>94.41999816894531</v>
+        <v>92.09999847412109</v>
       </c>
       <c r="C147" t="n">
-        <v>94.69999694824219</v>
+        <v>92.33000183105469</v>
       </c>
       <c r="D147" t="n">
-        <v>91.90000152587891</v>
+        <v>90.88999938964844</v>
       </c>
       <c r="E147" t="n">
-        <v>92.05999755859375</v>
+        <v>91.01999664306641</v>
       </c>
       <c r="F147" t="n">
-        <v>30406900</v>
+        <v>25928800</v>
       </c>
       <c r="G147" t="n">
         <v>0</v>
@@ -4265,22 +4265,22 @@
     </row>
     <row r="148">
       <c r="A148" s="1" t="n">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="B148" t="n">
-        <v>92.09999847412109</v>
+        <v>91.18000030517578</v>
       </c>
       <c r="C148" t="n">
-        <v>92.33000183105469</v>
+        <v>91.27999877929688</v>
       </c>
       <c r="D148" t="n">
-        <v>90.88999938964844</v>
+        <v>87.56999969482422</v>
       </c>
       <c r="E148" t="n">
-        <v>91.01999664306641</v>
+        <v>87.88999938964844</v>
       </c>
       <c r="F148" t="n">
-        <v>25928800</v>
+        <v>51961300</v>
       </c>
       <c r="G148" t="n">
         <v>0</v>
@@ -4291,22 +4291,22 @@
     </row>
     <row r="149">
       <c r="A149" s="1" t="n">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="B149" t="n">
-        <v>91.18000030517578</v>
+        <v>87.15000152587891</v>
       </c>
       <c r="C149" t="n">
-        <v>91.27999877929688</v>
+        <v>88.55000305175781</v>
       </c>
       <c r="D149" t="n">
-        <v>87.56999969482422</v>
+        <v>86.72000122070312</v>
       </c>
       <c r="E149" t="n">
-        <v>87.88999938964844</v>
+        <v>88.26999664306641</v>
       </c>
       <c r="F149" t="n">
-        <v>51961300</v>
+        <v>41932400</v>
       </c>
       <c r="G149" t="n">
         <v>0</v>
@@ -4317,22 +4317,22 @@
     </row>
     <row r="150">
       <c r="A150" s="1" t="n">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="B150" t="n">
-        <v>87.15000152587891</v>
+        <v>88.19999694824219</v>
       </c>
       <c r="C150" t="n">
-        <v>88.55000305175781</v>
+        <v>89.40000152587891</v>
       </c>
       <c r="D150" t="n">
-        <v>86.72000122070312</v>
+        <v>88.12999725341797</v>
       </c>
       <c r="E150" t="n">
-        <v>88.26999664306641</v>
+        <v>88.25</v>
       </c>
       <c r="F150" t="n">
-        <v>41932400</v>
+        <v>30627600</v>
       </c>
       <c r="G150" t="n">
         <v>0</v>
@@ -4343,22 +4343,22 @@
     </row>
     <row r="151">
       <c r="A151" s="1" t="n">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="B151" t="n">
-        <v>88.19999694824219</v>
+        <v>87.70999908447266</v>
       </c>
       <c r="C151" t="n">
-        <v>89.40000152587891</v>
+        <v>88.04000091552734</v>
       </c>
       <c r="D151" t="n">
-        <v>88.12999725341797</v>
+        <v>87.20999908447266</v>
       </c>
       <c r="E151" t="n">
-        <v>88.25</v>
+        <v>87.48999786376953</v>
       </c>
       <c r="F151" t="n">
-        <v>30627600</v>
+        <v>36215100</v>
       </c>
       <c r="G151" t="n">
         <v>0</v>
@@ -4369,22 +4369,22 @@
     </row>
     <row r="152">
       <c r="A152" s="1" t="n">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="B152" t="n">
-        <v>87.70999908447266</v>
+        <v>86.52999877929688</v>
       </c>
       <c r="C152" t="n">
-        <v>88.04000091552734</v>
+        <v>87.33999633789062</v>
       </c>
       <c r="D152" t="n">
-        <v>87.20999908447266</v>
+        <v>85.09999847412109</v>
       </c>
       <c r="E152" t="n">
-        <v>87.48999786376953</v>
+        <v>85.44999694824219</v>
       </c>
       <c r="F152" t="n">
-        <v>36215100</v>
+        <v>40556500</v>
       </c>
       <c r="G152" t="n">
         <v>0</v>
@@ -4395,22 +4395,22 @@
     </row>
     <row r="153">
       <c r="A153" s="1" t="n">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="B153" t="n">
-        <v>86.52999877929688</v>
+        <v>85.91000366210938</v>
       </c>
       <c r="C153" t="n">
-        <v>87.33999633789062</v>
+        <v>89.16999816894531</v>
       </c>
       <c r="D153" t="n">
-        <v>85.09999847412109</v>
+        <v>85.80999755859375</v>
       </c>
       <c r="E153" t="n">
-        <v>85.44999694824219</v>
+        <v>87.66000366210938</v>
       </c>
       <c r="F153" t="n">
-        <v>40556500</v>
+        <v>43556600</v>
       </c>
       <c r="G153" t="n">
         <v>0</v>
@@ -4421,22 +4421,22 @@
     </row>
     <row r="154">
       <c r="A154" s="1" t="n">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="B154" t="n">
-        <v>85.91000366210938</v>
+        <v>86.56999969482422</v>
       </c>
       <c r="C154" t="n">
-        <v>89.16999816894531</v>
+        <v>88.62000274658203</v>
       </c>
       <c r="D154" t="n">
-        <v>85.80999755859375</v>
+        <v>86.27999877929688</v>
       </c>
       <c r="E154" t="n">
-        <v>87.66000366210938</v>
+        <v>87.55999755859375</v>
       </c>
       <c r="F154" t="n">
-        <v>43556600</v>
+        <v>30823500</v>
       </c>
       <c r="G154" t="n">
         <v>0</v>
@@ -4447,22 +4447,22 @@
     </row>
     <row r="155">
       <c r="A155" s="1" t="n">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="B155" t="n">
-        <v>86.56999969482422</v>
+        <v>87.62000274658203</v>
       </c>
       <c r="C155" t="n">
-        <v>88.62000274658203</v>
+        <v>88.5</v>
       </c>
       <c r="D155" t="n">
-        <v>86.27999877929688</v>
+        <v>86.65000152587891</v>
       </c>
       <c r="E155" t="n">
-        <v>87.55999755859375</v>
+        <v>86.94000244140625</v>
       </c>
       <c r="F155" t="n">
-        <v>30823500</v>
+        <v>29408300</v>
       </c>
       <c r="G155" t="n">
         <v>0</v>
@@ -4473,22 +4473,22 @@
     </row>
     <row r="156">
       <c r="A156" s="1" t="n">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="B156" t="n">
-        <v>87.62000274658203</v>
+        <v>87.69000244140625</v>
       </c>
       <c r="C156" t="n">
-        <v>88.5</v>
+        <v>89.48999786376953</v>
       </c>
       <c r="D156" t="n">
-        <v>86.65000152587891</v>
+        <v>86.69000244140625</v>
       </c>
       <c r="E156" t="n">
-        <v>86.94000244140625</v>
+        <v>87.01999664306641</v>
       </c>
       <c r="F156" t="n">
-        <v>29408300</v>
+        <v>32335700</v>
       </c>
       <c r="G156" t="n">
         <v>0</v>
@@ -4499,22 +4499,22 @@
     </row>
     <row r="157">
       <c r="A157" s="1" t="n">
-        <v>46157</v>
+        <v>46160</v>
       </c>
       <c r="B157" t="n">
-        <v>87.69000244140625</v>
+        <v>86.5</v>
       </c>
       <c r="C157" t="n">
-        <v>89.48999786376953</v>
+        <v>89.81999969482422</v>
       </c>
       <c r="D157" t="n">
-        <v>86.69000244140625</v>
+        <v>86.33000183105469</v>
       </c>
       <c r="E157" t="n">
-        <v>87.01999664306641</v>
+        <v>89.65000152587891</v>
       </c>
       <c r="F157" t="n">
-        <v>32335700</v>
+        <v>35800500</v>
       </c>
       <c r="G157" t="n">
         <v>0</v>
@@ -4525,22 +4525,22 @@
     </row>
     <row r="158">
       <c r="A158" s="1" t="n">
-        <v>46160</v>
+        <v>46161</v>
       </c>
       <c r="B158" t="n">
-        <v>86.5</v>
+        <v>90.13999938964844</v>
       </c>
       <c r="C158" t="n">
-        <v>89.81999969482422</v>
+        <v>91.48000335693359</v>
       </c>
       <c r="D158" t="n">
-        <v>86.33000183105469</v>
+        <v>88.69000244140625</v>
       </c>
       <c r="E158" t="n">
-        <v>89.65000152587891</v>
+        <v>89.33000183105469</v>
       </c>
       <c r="F158" t="n">
-        <v>35800500</v>
+        <v>34545700</v>
       </c>
       <c r="G158" t="n">
         <v>0</v>
@@ -4551,22 +4551,22 @@
     </row>
     <row r="159">
       <c r="A159" s="1" t="n">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="B159" t="n">
-        <v>90.13999938964844</v>
+        <v>88.51999664306641</v>
       </c>
       <c r="C159" t="n">
-        <v>91.48000335693359</v>
+        <v>88.55000305175781</v>
       </c>
       <c r="D159" t="n">
-        <v>88.69000244140625</v>
+        <v>87.5</v>
       </c>
       <c r="E159" t="n">
-        <v>89.33000183105469</v>
+        <v>88.08999633789062</v>
       </c>
       <c r="F159" t="n">
-        <v>34545700</v>
+        <v>23463400</v>
       </c>
       <c r="G159" t="n">
         <v>0</v>
@@ -4577,22 +4577,22 @@
     </row>
     <row r="160">
       <c r="A160" s="1" t="n">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="B160" t="n">
-        <v>88.51999664306641</v>
+        <v>88.02999877929688</v>
       </c>
       <c r="C160" t="n">
-        <v>88.55000305175781</v>
+        <v>90.37000274658203</v>
       </c>
       <c r="D160" t="n">
-        <v>87.5</v>
+        <v>87.51999664306641</v>
       </c>
       <c r="E160" t="n">
-        <v>88.08999633789062</v>
+        <v>89.30000305175781</v>
       </c>
       <c r="F160" t="n">
-        <v>23463400</v>
+        <v>28613900</v>
       </c>
       <c r="G160" t="n">
         <v>0</v>
@@ -4603,22 +4603,22 @@
     </row>
     <row r="161">
       <c r="A161" s="1" t="n">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="B161" t="n">
-        <v>88.02999877929688</v>
+        <v>89.09999847412109</v>
       </c>
       <c r="C161" t="n">
-        <v>90.37000274658203</v>
+        <v>89.97000122070312</v>
       </c>
       <c r="D161" t="n">
-        <v>87.51999664306641</v>
+        <v>88.16999816894531</v>
       </c>
       <c r="E161" t="n">
-        <v>89.30000305175781</v>
+        <v>88.59999847412109</v>
       </c>
       <c r="F161" t="n">
-        <v>28613900</v>
+        <v>23847200</v>
       </c>
       <c r="G161" t="n">
         <v>0</v>
@@ -4629,22 +4629,22 @@
     </row>
     <row r="162">
       <c r="A162" s="1" t="n">
-        <v>46164</v>
+        <v>46168</v>
       </c>
       <c r="B162" t="n">
-        <v>89.09999847412109</v>
+        <v>88.40000152587891</v>
       </c>
       <c r="C162" t="n">
-        <v>89.97000122070312</v>
+        <v>88.73000335693359</v>
       </c>
       <c r="D162" t="n">
-        <v>88.16999816894531</v>
+        <v>87.25</v>
       </c>
       <c r="E162" t="n">
-        <v>88.59999847412109</v>
+        <v>87.68000030517578</v>
       </c>
       <c r="F162" t="n">
-        <v>23847200</v>
+        <v>24014500</v>
       </c>
       <c r="G162" t="n">
         <v>0</v>
@@ -4655,22 +4655,22 @@
     </row>
     <row r="163">
       <c r="A163" s="1" t="n">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="B163" t="n">
-        <v>88.40000152587891</v>
+        <v>87.05000305175781</v>
       </c>
       <c r="C163" t="n">
-        <v>88.73000335693359</v>
+        <v>88.5</v>
       </c>
       <c r="D163" t="n">
-        <v>87.25</v>
+        <v>86.81999969482422</v>
       </c>
       <c r="E163" t="n">
-        <v>87.68000030517578</v>
+        <v>87.34999847412109</v>
       </c>
       <c r="F163" t="n">
-        <v>24014500</v>
+        <v>22569500</v>
       </c>
       <c r="G163" t="n">
         <v>0</v>
@@ -4681,22 +4681,22 @@
     </row>
     <row r="164">
       <c r="A164" s="1" t="n">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="B164" t="n">
-        <v>87.05000305175781</v>
+        <v>86.90000152587891</v>
       </c>
       <c r="C164" t="n">
-        <v>88.5</v>
+        <v>87.04000091552734</v>
       </c>
       <c r="D164" t="n">
-        <v>86.81999969482422</v>
+        <v>85.58999633789062</v>
       </c>
       <c r="E164" t="n">
-        <v>87.34999847412109</v>
+        <v>86.36000061035156</v>
       </c>
       <c r="F164" t="n">
-        <v>22569500</v>
+        <v>38803800</v>
       </c>
       <c r="G164" t="n">
         <v>0</v>
@@ -4707,22 +4707,22 @@
     </row>
     <row r="165">
       <c r="A165" s="1" t="n">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="B165" t="n">
-        <v>86.90000152587891</v>
+        <v>86.19999694824219</v>
       </c>
       <c r="C165" t="n">
-        <v>87.04000091552734</v>
+        <v>86.66999816894531</v>
       </c>
       <c r="D165" t="n">
-        <v>85.58999633789062</v>
+        <v>85.66000366210938</v>
       </c>
       <c r="E165" t="n">
-        <v>86.36000061035156</v>
+        <v>86.01999664306641</v>
       </c>
       <c r="F165" t="n">
-        <v>38803800</v>
+        <v>39793600</v>
       </c>
       <c r="G165" t="n">
         <v>0</v>
@@ -4733,22 +4733,22 @@
     </row>
     <row r="166">
       <c r="A166" s="1" t="n">
-        <v>46171</v>
+        <v>46174</v>
       </c>
       <c r="B166" t="n">
-        <v>86.19999694824219</v>
+        <v>85.73000335693359</v>
       </c>
       <c r="C166" t="n">
-        <v>86.66999816894531</v>
+        <v>87.23000335693359</v>
       </c>
       <c r="D166" t="n">
-        <v>85.66000366210938</v>
+        <v>85.31999969482422</v>
       </c>
       <c r="E166" t="n">
-        <v>86.01999664306641</v>
+        <v>85.84999847412109</v>
       </c>
       <c r="F166" t="n">
-        <v>39793600</v>
+        <v>32747200</v>
       </c>
       <c r="G166" t="n">
         <v>0</v>
@@ -4759,22 +4759,22 @@
     </row>
     <row r="167">
       <c r="A167" s="1" t="n">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="B167" t="n">
-        <v>85.73000335693359</v>
+        <v>85.61000061035156</v>
       </c>
       <c r="C167" t="n">
-        <v>87.23000335693359</v>
+        <v>85.98000335693359</v>
       </c>
       <c r="D167" t="n">
-        <v>85.31999969482422</v>
+        <v>83.29000091552734</v>
       </c>
       <c r="E167" t="n">
-        <v>85.84999847412109</v>
+        <v>83.33000183105469</v>
       </c>
       <c r="F167" t="n">
-        <v>32747200</v>
+        <v>42947200</v>
       </c>
       <c r="G167" t="n">
         <v>0</v>
@@ -4785,22 +4785,22 @@
     </row>
     <row r="168">
       <c r="A168" s="1" t="n">
-        <v>46175</v>
+        <v>46176</v>
       </c>
       <c r="B168" t="n">
-        <v>85.61000061035156</v>
+        <v>82.91000366210938</v>
       </c>
       <c r="C168" t="n">
-        <v>85.98000335693359</v>
+        <v>83.30999755859375</v>
       </c>
       <c r="D168" t="n">
-        <v>83.29000091552734</v>
+        <v>81.09999847412109</v>
       </c>
       <c r="E168" t="n">
-        <v>83.33000183105469</v>
+        <v>81.51999664306641</v>
       </c>
       <c r="F168" t="n">
-        <v>42947200</v>
+        <v>36714700</v>
       </c>
       <c r="G168" t="n">
         <v>0</v>
@@ -4811,22 +4811,22 @@
     </row>
     <row r="169">
       <c r="A169" s="1" t="n">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="B169" t="n">
-        <v>82.91000366210938</v>
+        <v>83.19000244140625</v>
       </c>
       <c r="C169" t="n">
-        <v>83.30999755859375</v>
+        <v>83.69999694824219</v>
       </c>
       <c r="D169" t="n">
-        <v>81.09999847412109</v>
+        <v>81.37000274658203</v>
       </c>
       <c r="E169" t="n">
-        <v>81.51999664306641</v>
+        <v>81.55999755859375</v>
       </c>
       <c r="F169" t="n">
-        <v>36714700</v>
+        <v>39338800</v>
       </c>
       <c r="G169" t="n">
         <v>0</v>
@@ -4837,22 +4837,22 @@
     </row>
     <row r="170">
       <c r="A170" s="1" t="n">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="B170" t="n">
-        <v>83.19000244140625</v>
+        <v>82.33000183105469</v>
       </c>
       <c r="C170" t="n">
-        <v>83.69999694824219</v>
+        <v>82.75</v>
       </c>
       <c r="D170" t="n">
-        <v>81.37000274658203</v>
+        <v>81</v>
       </c>
       <c r="E170" t="n">
-        <v>81.55999755859375</v>
+        <v>82.18000030517578</v>
       </c>
       <c r="F170" t="n">
-        <v>39338800</v>
+        <v>43474100</v>
       </c>
       <c r="G170" t="n">
         <v>0</v>
@@ -4863,22 +4863,22 @@
     </row>
     <row r="171">
       <c r="A171" s="1" t="n">
-        <v>46178</v>
+        <v>46181</v>
       </c>
       <c r="B171" t="n">
-        <v>82.33000183105469</v>
+        <v>81.66000366210938</v>
       </c>
       <c r="C171" t="n">
-        <v>82.75</v>
+        <v>83.08000183105469</v>
       </c>
       <c r="D171" t="n">
-        <v>81</v>
+        <v>81.33999633789062</v>
       </c>
       <c r="E171" t="n">
-        <v>82.18000030517578</v>
+        <v>82.63999938964844</v>
       </c>
       <c r="F171" t="n">
-        <v>43474100</v>
+        <v>33056700</v>
       </c>
       <c r="G171" t="n">
         <v>0</v>
@@ -4889,22 +4889,22 @@
     </row>
     <row r="172">
       <c r="A172" s="1" t="n">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="B172" t="n">
-        <v>81.66000366210938</v>
+        <v>82.12999725341797</v>
       </c>
       <c r="C172" t="n">
-        <v>83.08000183105469</v>
+        <v>82.33999633789062</v>
       </c>
       <c r="D172" t="n">
         <v>81.33999633789062</v>
       </c>
       <c r="E172" t="n">
-        <v>82.63999938964844</v>
+        <v>81.41000366210938</v>
       </c>
       <c r="F172" t="n">
-        <v>33056700</v>
+        <v>34787200</v>
       </c>
       <c r="G172" t="n">
         <v>0</v>
@@ -4915,22 +4915,22 @@
     </row>
     <row r="173">
       <c r="A173" s="1" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="B173" t="n">
-        <v>82.12999725341797</v>
+        <v>81.70999908447266</v>
       </c>
       <c r="C173" t="n">
-        <v>82.33999633789062</v>
+        <v>82.75</v>
       </c>
       <c r="D173" t="n">
-        <v>81.33999633789062</v>
+        <v>80.98000335693359</v>
       </c>
       <c r="E173" t="n">
-        <v>81.41000366210938</v>
+        <v>82</v>
       </c>
       <c r="F173" t="n">
-        <v>34787200</v>
+        <v>36304600</v>
       </c>
       <c r="G173" t="n">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="174">
       <c r="A174" s="1" t="n">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="B174" t="n">
-        <v>81.70999908447266</v>
+        <v>81.87000274658203</v>
       </c>
       <c r="C174" t="n">
-        <v>82.75</v>
+        <v>82.09999847412109</v>
       </c>
       <c r="D174" t="n">
-        <v>80.98000335693359</v>
+        <v>80.08999633789062</v>
       </c>
       <c r="E174" t="n">
-        <v>82</v>
+        <v>81.26999664306641</v>
       </c>
       <c r="F174" t="n">
-        <v>36304600</v>
+        <v>33417600</v>
       </c>
       <c r="G174" t="n">
         <v>0</v>
@@ -4967,22 +4967,22 @@
     </row>
     <row r="175">
       <c r="A175" s="1" t="n">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="B175" t="n">
-        <v>81.87000274658203</v>
+        <v>81.58000183105469</v>
       </c>
       <c r="C175" t="n">
-        <v>82.09999847412109</v>
+        <v>82</v>
       </c>
       <c r="D175" t="n">
-        <v>80.08999633789062</v>
+        <v>79.27999877929688</v>
       </c>
       <c r="E175" t="n">
-        <v>81.26999664306641</v>
+        <v>80.33999633789062</v>
       </c>
       <c r="F175" t="n">
-        <v>33417600</v>
+        <v>35309700</v>
       </c>
       <c r="G175" t="n">
         <v>0</v>
@@ -4993,22 +4993,22 @@
     </row>
     <row r="176">
       <c r="A176" s="1" t="n">
-        <v>46185</v>
+        <v>46188</v>
       </c>
       <c r="B176" t="n">
-        <v>81.58000183105469</v>
+        <v>80.62000274658203</v>
       </c>
       <c r="C176" t="n">
-        <v>82</v>
+        <v>81.70999908447266</v>
       </c>
       <c r="D176" t="n">
-        <v>79.27999877929688</v>
+        <v>80.45999908447266</v>
       </c>
       <c r="E176" t="n">
-        <v>80.33999633789062</v>
+        <v>81.66999816894531</v>
       </c>
       <c r="F176" t="n">
-        <v>35309700</v>
+        <v>36430800</v>
       </c>
       <c r="G176" t="n">
         <v>0</v>
@@ -5019,22 +5019,22 @@
     </row>
     <row r="177">
       <c r="A177" s="1" t="n">
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="B177" t="n">
-        <v>80.62000274658203</v>
+        <v>81.90000152587891</v>
       </c>
       <c r="C177" t="n">
-        <v>81.70999908447266</v>
+        <v>81.93000030517578</v>
       </c>
       <c r="D177" t="n">
-        <v>80.45999908447266</v>
+        <v>77.70999908447266</v>
       </c>
       <c r="E177" t="n">
-        <v>81.66999816894531</v>
+        <v>78.72000122070312</v>
       </c>
       <c r="F177" t="n">
-        <v>36430800</v>
+        <v>65054000</v>
       </c>
       <c r="G177" t="n">
         <v>0</v>
@@ -5045,22 +5045,22 @@
     </row>
     <row r="178">
       <c r="A178" s="1" t="n">
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="B178" t="n">
-        <v>81.90000152587891</v>
+        <v>78.09999847412109</v>
       </c>
       <c r="C178" t="n">
-        <v>81.93000030517578</v>
+        <v>78.44999694824219</v>
       </c>
       <c r="D178" t="n">
-        <v>77.70999908447266</v>
+        <v>76.76000213623047</v>
       </c>
       <c r="E178" t="n">
-        <v>78.72000122070312</v>
+        <v>76.95999908447266</v>
       </c>
       <c r="F178" t="n">
-        <v>65054000</v>
+        <v>50338800</v>
       </c>
       <c r="G178" t="n">
         <v>0</v>
@@ -5071,22 +5071,22 @@
     </row>
     <row r="179">
       <c r="A179" s="1" t="n">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="B179" t="n">
-        <v>78.09999847412109</v>
+        <v>76.93000030517578</v>
       </c>
       <c r="C179" t="n">
-        <v>78.44999694824219</v>
+        <v>78.23999786376953</v>
       </c>
       <c r="D179" t="n">
-        <v>76.76000213623047</v>
+        <v>76.12000274658203</v>
       </c>
       <c r="E179" t="n">
-        <v>76.95999908447266</v>
+        <v>77.37999725341797</v>
       </c>
       <c r="F179" t="n">
-        <v>50338800</v>
+        <v>91920400</v>
       </c>
       <c r="G179" t="n">
         <v>0</v>
@@ -5097,22 +5097,22 @@
     </row>
     <row r="180">
       <c r="A180" s="1" t="n">
-        <v>46191</v>
+        <v>46195</v>
       </c>
       <c r="B180" t="n">
-        <v>76.93000030517578</v>
+        <v>76.13999938964844</v>
       </c>
       <c r="C180" t="n">
-        <v>78.23999786376953</v>
+        <v>77.08999633789062</v>
       </c>
       <c r="D180" t="n">
-        <v>76.12000274658203</v>
+        <v>71.80999755859375</v>
       </c>
       <c r="E180" t="n">
-        <v>77.37999725341797</v>
+        <v>72.87999725341797</v>
       </c>
       <c r="F180" t="n">
-        <v>91920400</v>
+        <v>82203300</v>
       </c>
       <c r="G180" t="n">
         <v>0</v>
@@ -5123,22 +5123,22 @@
     </row>
     <row r="181">
       <c r="A181" s="1" t="n">
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="B181" t="n">
-        <v>76.13999938964844</v>
+        <v>73.26000213623047</v>
       </c>
       <c r="C181" t="n">
-        <v>77.08999633789062</v>
+        <v>73.95999908447266</v>
       </c>
       <c r="D181" t="n">
-        <v>71.80999755859375</v>
+        <v>72.62999725341797</v>
       </c>
       <c r="E181" t="n">
-        <v>72.87999725341797</v>
+        <v>72.81999969482422</v>
       </c>
       <c r="F181" t="n">
-        <v>82203300</v>
+        <v>50806800</v>
       </c>
       <c r="G181" t="n">
         <v>0</v>
@@ -5149,22 +5149,22 @@
     </row>
     <row r="182">
       <c r="A182" s="1" t="n">
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="B182" t="n">
-        <v>73.26000213623047</v>
+        <v>72.69000244140625</v>
       </c>
       <c r="C182" t="n">
-        <v>73.95999908447266</v>
+        <v>73.44999694824219</v>
       </c>
       <c r="D182" t="n">
-        <v>72.62999725341797</v>
+        <v>71.62999725341797</v>
       </c>
       <c r="E182" t="n">
-        <v>72.81999969482422</v>
+        <v>71.83999633789062</v>
       </c>
       <c r="F182" t="n">
-        <v>50806800</v>
+        <v>48001500</v>
       </c>
       <c r="G182" t="n">
         <v>0</v>
@@ -5175,22 +5175,22 @@
     </row>
     <row r="183">
       <c r="A183" s="1" t="n">
-        <v>46197</v>
+        <v>46198</v>
       </c>
       <c r="B183" t="n">
-        <v>72.69000244140625</v>
+        <v>71.33000183105469</v>
       </c>
       <c r="C183" t="n">
-        <v>73.44999694824219</v>
+        <v>72.94000244140625</v>
       </c>
       <c r="D183" t="n">
-        <v>71.62999725341797</v>
+        <v>70.86000061035156</v>
       </c>
       <c r="E183" t="n">
-        <v>71.83999633789062</v>
+        <v>70.90000152587891</v>
       </c>
       <c r="F183" t="n">
-        <v>48001500</v>
+        <v>44446900</v>
       </c>
       <c r="G183" t="n">
         <v>0</v>
@@ -5201,22 +5201,22 @@
     </row>
     <row r="184">
       <c r="A184" s="1" t="n">
-        <v>46198</v>
+        <v>46199</v>
       </c>
       <c r="B184" t="n">
-        <v>71.33000183105469</v>
+        <v>71.69000244140625</v>
       </c>
       <c r="C184" t="n">
-        <v>72.94000244140625</v>
+        <v>75.19999694824219</v>
       </c>
       <c r="D184" t="n">
-        <v>70.86000061035156</v>
+        <v>71.52999877929688</v>
       </c>
       <c r="E184" t="n">
-        <v>70.90000152587891</v>
+        <v>73.80999755859375</v>
       </c>
       <c r="F184" t="n">
-        <v>44446900</v>
+        <v>74990300</v>
       </c>
       <c r="G184" t="n">
         <v>0</v>
@@ -5227,22 +5227,22 @@
     </row>
     <row r="185">
       <c r="A185" s="1" t="n">
-        <v>46199</v>
+        <v>46202</v>
       </c>
       <c r="B185" t="n">
-        <v>71.69000244140625</v>
+        <v>74.62000274658203</v>
       </c>
       <c r="C185" t="n">
-        <v>75.19999694824219</v>
+        <v>76.06999969482422</v>
       </c>
       <c r="D185" t="n">
-        <v>71.52999877929688</v>
+        <v>73.73000335693359</v>
       </c>
       <c r="E185" t="n">
-        <v>73.80999755859375</v>
+        <v>73.77999877929688</v>
       </c>
       <c r="F185" t="n">
-        <v>74990300</v>
+        <v>42429600</v>
       </c>
       <c r="G185" t="n">
         <v>0</v>
@@ -5253,22 +5253,22 @@
     </row>
     <row r="186">
       <c r="A186" s="1" t="n">
-        <v>46202</v>
+        <v>46203</v>
       </c>
       <c r="B186" t="n">
-        <v>74.62000274658203</v>
+        <v>73.58999633789062</v>
       </c>
       <c r="C186" t="n">
-        <v>76.06999969482422</v>
+        <v>73.75</v>
       </c>
       <c r="D186" t="n">
-        <v>73.73000335693359</v>
+        <v>71</v>
       </c>
       <c r="E186" t="n">
-        <v>73.77999877929688</v>
+        <v>71.40000152587891</v>
       </c>
       <c r="F186" t="n">
-        <v>42429600</v>
+        <v>49240900</v>
       </c>
       <c r="G186" t="n">
         <v>0</v>
@@ -5279,22 +5279,22 @@
     </row>
     <row r="187">
       <c r="A187" s="1" t="n">
-        <v>46203</v>
+        <v>46204</v>
       </c>
       <c r="B187" t="n">
-        <v>73.58999633789062</v>
+        <v>72.58999633789062</v>
       </c>
       <c r="C187" t="n">
-        <v>73.75</v>
+        <v>74.36000061035156</v>
       </c>
       <c r="D187" t="n">
-        <v>71</v>
+        <v>72.33000183105469</v>
       </c>
       <c r="E187" t="n">
-        <v>71.40000152587891</v>
+        <v>74.19000244140625</v>
       </c>
       <c r="F187" t="n">
-        <v>49240900</v>
+        <v>43841800</v>
       </c>
       <c r="G187" t="n">
         <v>0</v>
@@ -5305,22 +5305,22 @@
     </row>
     <row r="188">
       <c r="A188" s="1" t="n">
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="B188" t="n">
-        <v>72.58999633789062</v>
+        <v>75.08999633789062</v>
       </c>
       <c r="C188" t="n">
-        <v>74.36000061035156</v>
+        <v>78.44000244140625</v>
       </c>
       <c r="D188" t="n">
-        <v>72.33000183105469</v>
+        <v>74.91000366210938</v>
       </c>
       <c r="E188" t="n">
-        <v>74.19000244140625</v>
+        <v>77.65000152587891</v>
       </c>
       <c r="F188" t="n">
-        <v>43841800</v>
+        <v>55456500</v>
       </c>
       <c r="G188" t="n">
         <v>0</v>
@@ -5331,22 +5331,22 @@
     </row>
     <row r="189">
       <c r="A189" s="1" t="n">
-        <v>46205</v>
+        <v>46209</v>
       </c>
       <c r="B189" t="n">
-        <v>75.08999633789062</v>
+        <v>77.08000183105469</v>
       </c>
       <c r="C189" t="n">
-        <v>78.44000244140625</v>
+        <v>77.83999633789062</v>
       </c>
       <c r="D189" t="n">
-        <v>74.91000366210938</v>
+        <v>75.70999908447266</v>
       </c>
       <c r="E189" t="n">
-        <v>77.65000152587891</v>
+        <v>76.01999664306641</v>
       </c>
       <c r="F189" t="n">
-        <v>55456500</v>
+        <v>45056600</v>
       </c>
       <c r="G189" t="n">
         <v>0</v>
@@ -5357,22 +5357,22 @@
     </row>
     <row r="190">
       <c r="A190" s="1" t="n">
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="B190" t="n">
-        <v>77.08000183105469</v>
+        <v>77.87999725341797</v>
       </c>
       <c r="C190" t="n">
-        <v>77.83999633789062</v>
+        <v>78.19000244140625</v>
       </c>
       <c r="D190" t="n">
-        <v>75.70999908447266</v>
+        <v>76.09999847412109</v>
       </c>
       <c r="E190" t="n">
-        <v>76.01999664306641</v>
+        <v>76.18000030517578</v>
       </c>
       <c r="F190" t="n">
-        <v>45056600</v>
+        <v>33257300</v>
       </c>
       <c r="G190" t="n">
         <v>0</v>
@@ -5383,22 +5383,22 @@
     </row>
     <row r="191">
       <c r="A191" s="1" t="n">
-        <v>46210</v>
+        <v>46211</v>
       </c>
       <c r="B191" t="n">
-        <v>77.87999725341797</v>
+        <v>76.26999664306641</v>
       </c>
       <c r="C191" t="n">
-        <v>78.19000244140625</v>
+        <v>76.63999938964844</v>
       </c>
       <c r="D191" t="n">
-        <v>76.09999847412109</v>
+        <v>74.88999938964844</v>
       </c>
       <c r="E191" t="n">
-        <v>76.18000030517578</v>
+        <v>75.58999633789062</v>
       </c>
       <c r="F191" t="n">
-        <v>33257300</v>
+        <v>34373500</v>
       </c>
       <c r="G191" t="n">
         <v>0</v>
@@ -5409,22 +5409,22 @@
     </row>
     <row r="192">
       <c r="A192" s="1" t="n">
-        <v>46211</v>
+        <v>46212</v>
       </c>
       <c r="B192" t="n">
-        <v>76.26999664306641</v>
+        <v>74.30000305175781</v>
       </c>
       <c r="C192" t="n">
-        <v>76.63999938964844</v>
+        <v>75.55000305175781</v>
       </c>
       <c r="D192" t="n">
-        <v>74.88999938964844</v>
+        <v>74.01999664306641</v>
       </c>
       <c r="E192" t="n">
-        <v>75.58999633789062</v>
+        <v>75.47000122070312</v>
       </c>
       <c r="F192" t="n">
-        <v>34373500</v>
+        <v>36305700</v>
       </c>
       <c r="G192" t="n">
         <v>0</v>
@@ -5435,22 +5435,22 @@
     </row>
     <row r="193">
       <c r="A193" s="1" t="n">
-        <v>46212</v>
+        <v>46213</v>
       </c>
       <c r="B193" t="n">
-        <v>74.30000305175781</v>
+        <v>75.44000244140625</v>
       </c>
       <c r="C193" t="n">
-        <v>75.55000305175781</v>
+        <v>75.69999694824219</v>
       </c>
       <c r="D193" t="n">
-        <v>74.01999664306641</v>
+        <v>72.51000213623047</v>
       </c>
       <c r="E193" t="n">
-        <v>75.47000122070312</v>
+        <v>73.37000274658203</v>
       </c>
       <c r="F193" t="n">
-        <v>36305700</v>
+        <v>46713900</v>
       </c>
       <c r="G193" t="n">
         <v>0</v>
@@ -5461,22 +5461,22 @@
     </row>
     <row r="194">
       <c r="A194" s="1" t="n">
-        <v>46213</v>
+        <v>46216</v>
       </c>
       <c r="B194" t="n">
-        <v>75.44000244140625</v>
+        <v>73.90000152587891</v>
       </c>
       <c r="C194" t="n">
-        <v>75.69999694824219</v>
+        <v>75.44999694824219</v>
       </c>
       <c r="D194" t="n">
-        <v>72.51000213623047</v>
+        <v>73.70999908447266</v>
       </c>
       <c r="E194" t="n">
-        <v>73.37000274658203</v>
+        <v>73.83000183105469</v>
       </c>
       <c r="F194" t="n">
-        <v>46713900</v>
+        <v>35101800</v>
       </c>
       <c r="G194" t="n">
         <v>0</v>
@@ -5487,22 +5487,22 @@
     </row>
     <row r="195">
       <c r="A195" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="B195" t="n">
-        <v>73.90000152587891</v>
+        <v>72.63999938964844</v>
       </c>
       <c r="C195" t="n">
-        <v>75.44999694824219</v>
+        <v>74.01000213623047</v>
       </c>
       <c r="D195" t="n">
-        <v>73.70999908447266</v>
+        <v>72.27999877929688</v>
       </c>
       <c r="E195" t="n">
-        <v>73.83000183105469</v>
+        <v>73.52999877929688</v>
       </c>
       <c r="F195" t="n">
-        <v>35101800</v>
+        <v>33312100</v>
       </c>
       <c r="G195" t="n">
         <v>0</v>
@@ -5513,22 +5513,22 @@
     </row>
     <row r="196">
       <c r="A196" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="B196" t="n">
-        <v>72.63999938964844</v>
+        <v>73.79000091552734</v>
       </c>
       <c r="C196" t="n">
-        <v>74.01000213623047</v>
+        <v>75.05999755859375</v>
       </c>
       <c r="D196" t="n">
-        <v>72.27999877929688</v>
+        <v>73.12999725341797</v>
       </c>
       <c r="E196" t="n">
-        <v>73.52999877929688</v>
+        <v>73.68000030517578</v>
       </c>
       <c r="F196" t="n">
-        <v>33312100</v>
+        <v>32854300</v>
       </c>
       <c r="G196" t="n">
         <v>0</v>
@@ -5539,22 +5539,22 @@
     </row>
     <row r="197">
       <c r="A197" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="B197" t="n">
-        <v>73.79000091552734</v>
+        <v>73.94999694824219</v>
       </c>
       <c r="C197" t="n">
-        <v>75.05999755859375</v>
+        <v>74.68000030517578</v>
       </c>
       <c r="D197" t="n">
-        <v>73.12999725341797</v>
+        <v>72.94000244140625</v>
       </c>
       <c r="E197" t="n">
-        <v>73.68000030517578</v>
+        <v>74.34999847412109</v>
       </c>
       <c r="F197" t="n">
-        <v>32854300</v>
+        <v>77505200</v>
       </c>
       <c r="G197" t="n">
         <v>0</v>
@@ -5565,22 +5565,22 @@
     </row>
     <row r="198">
       <c r="A198" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="B198" t="n">
-        <v>73.94999694824219</v>
+        <v>65.48000335693359</v>
       </c>
       <c r="C198" t="n">
-        <v>74.68000030517578</v>
+        <v>69.48999786376953</v>
       </c>
       <c r="D198" t="n">
-        <v>72.94000244140625</v>
+        <v>65.08000183105469</v>
       </c>
       <c r="E198" t="n">
-        <v>74.34999847412109</v>
+        <v>68.94999694824219</v>
       </c>
       <c r="F198" t="n">
-        <v>77505200</v>
+        <v>142029200</v>
       </c>
       <c r="G198" t="n">
         <v>0</v>
@@ -5591,22 +5591,22 @@
     </row>
     <row r="199">
       <c r="A199" s="1" t="n">
-        <v>46220</v>
+        <v>46223</v>
       </c>
       <c r="B199" t="n">
-        <v>65.48000335693359</v>
+        <v>68.31999969482422</v>
       </c>
       <c r="C199" t="n">
-        <v>69.48999786376953</v>
+        <v>68.37999725341797</v>
       </c>
       <c r="D199" t="n">
-        <v>65.08000183105469</v>
+        <v>66.69000244140625</v>
       </c>
       <c r="E199" t="n">
-        <v>68.94999694824219</v>
+        <v>67.59999847412109</v>
       </c>
       <c r="F199" t="n">
-        <v>142029200</v>
+        <v>60669100</v>
       </c>
       <c r="G199" t="n">
         <v>0</v>
@@ -5617,22 +5617,22 @@
     </row>
     <row r="200">
       <c r="A200" s="1" t="n">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="B200" t="n">
-        <v>68.31999969482422</v>
+        <v>67.41999816894531</v>
       </c>
       <c r="C200" t="n">
-        <v>68.37999725341797</v>
+        <v>68.75</v>
       </c>
       <c r="D200" t="n">
-        <v>66.69000244140625</v>
+        <v>66.73000335693359</v>
       </c>
       <c r="E200" t="n">
-        <v>67.59999847412109</v>
+        <v>68.66999816894531</v>
       </c>
       <c r="F200" t="n">
-        <v>60669100</v>
+        <v>56565800</v>
       </c>
       <c r="G200" t="n">
         <v>0</v>
@@ -5643,22 +5643,22 @@
     </row>
     <row r="201">
       <c r="A201" s="1" t="n">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="B201" t="n">
-        <v>67.41999816894531</v>
+        <v>69.37000274658203</v>
       </c>
       <c r="C201" t="n">
-        <v>68.75</v>
+        <v>70.56999969482422</v>
       </c>
       <c r="D201" t="n">
-        <v>66.73000335693359</v>
+        <v>68.34999847412109</v>
       </c>
       <c r="E201" t="n">
-        <v>68.66999816894531</v>
+        <v>68.52999877929688</v>
       </c>
       <c r="F201" t="n">
-        <v>56565800</v>
+        <v>44947300</v>
       </c>
       <c r="G201" t="n">
         <v>0</v>
@@ -5669,22 +5669,22 @@
     </row>
     <row r="202">
       <c r="A202" s="1" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="B202" t="n">
-        <v>69.37000274658203</v>
+        <v>68.56999969482422</v>
       </c>
       <c r="C202" t="n">
-        <v>70.56999969482422</v>
+        <v>69.36000061035156</v>
       </c>
       <c r="D202" t="n">
-        <v>68.34999847412109</v>
+        <v>67.66999816894531</v>
       </c>
       <c r="E202" t="n">
-        <v>68.52999877929688</v>
+        <v>68.88999938964844</v>
       </c>
       <c r="F202" t="n">
-        <v>44947300</v>
+        <v>45029100</v>
       </c>
       <c r="G202" t="n">
         <v>0</v>
@@ -5695,22 +5695,22 @@
     </row>
     <row r="203">
       <c r="A203" s="1" t="n">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="B203" t="n">
-        <v>68.56999969482422</v>
+        <v>69.29000091552734</v>
       </c>
       <c r="C203" t="n">
-        <v>69.36000061035156</v>
+        <v>70.68000030517578</v>
       </c>
       <c r="D203" t="n">
-        <v>67.66999816894531</v>
+        <v>67.97000122070312</v>
       </c>
       <c r="E203" t="n">
-        <v>68.88999938964844</v>
+        <v>70.08999633789062</v>
       </c>
       <c r="F203" t="n">
-        <v>45029100</v>
+        <v>37593500</v>
       </c>
       <c r="G203" t="n">
         <v>0</v>
@@ -5721,22 +5721,22 @@
     </row>
     <row r="204">
       <c r="A204" s="1" t="n">
-        <v>46227</v>
+        <v>46230</v>
       </c>
       <c r="B204" t="n">
-        <v>69.29000091552734</v>
+        <v>70.58999633789062</v>
       </c>
       <c r="C204" t="n">
-        <v>70.68000030517578</v>
+        <v>71.65000152587891</v>
       </c>
       <c r="D204" t="n">
-        <v>67.97000122070312</v>
+        <v>69.86000061035156</v>
       </c>
       <c r="E204" t="n">
-        <v>70.08999633789062</v>
+        <v>70.40000152587891</v>
       </c>
       <c r="F204" t="n">
-        <v>37593500</v>
+        <v>39090800</v>
       </c>
       <c r="G204" t="n">
         <v>0</v>
@@ -5747,22 +5747,22 @@
     </row>
     <row r="205">
       <c r="A205" s="1" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="B205" t="n">
-        <v>70.58999633789062</v>
+        <v>72.06999969482422</v>
       </c>
       <c r="C205" t="n">
-        <v>71.65000152587891</v>
+        <v>73.76000213623047</v>
       </c>
       <c r="D205" t="n">
-        <v>69.86000061035156</v>
+        <v>71.23000335693359</v>
       </c>
       <c r="E205" t="n">
-        <v>70.40000152587891</v>
+        <v>72.38999938964844</v>
       </c>
       <c r="F205" t="n">
-        <v>39090800</v>
+        <v>47160200</v>
       </c>
       <c r="G205" t="n">
         <v>0</v>
@@ -5773,22 +5773,22 @@
     </row>
     <row r="206">
       <c r="A206" s="1" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="B206" t="n">
-        <v>72.06999969482422</v>
+        <v>72.19000244140625</v>
       </c>
       <c r="C206" t="n">
-        <v>73.76000213623047</v>
+        <v>73.73999786376953</v>
       </c>
       <c r="D206" t="n">
-        <v>71.23000335693359</v>
+        <v>71.75</v>
       </c>
       <c r="E206" t="n">
-        <v>72.38999938964844</v>
+        <v>73.62999725341797</v>
       </c>
       <c r="F206" t="n">
-        <v>47160200</v>
+        <v>43737600</v>
       </c>
       <c r="G206" t="n">
         <v>0</v>
@@ -5799,22 +5799,22 @@
     </row>
     <row r="207">
       <c r="A207" s="1" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="B207" t="n">
-        <v>72.19000244140625</v>
+        <v>71.48000335693359</v>
       </c>
       <c r="C207" t="n">
-        <v>73.73999786376953</v>
+        <v>73.31999969482422</v>
       </c>
       <c r="D207" t="n">
-        <v>71.75</v>
+        <v>70.55000305175781</v>
       </c>
       <c r="E207" t="n">
-        <v>73.62999725341797</v>
+        <v>73.16999816894531</v>
       </c>
       <c r="F207" t="n">
-        <v>43737600</v>
+        <v>54261000</v>
       </c>
       <c r="G207" t="n">
         <v>0</v>
@@ -5825,22 +5825,22 @@
     </row>
     <row r="208">
       <c r="A208" s="1" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="B208" t="n">
-        <v>71.48000335693359</v>
+        <v>71.97000122070312</v>
       </c>
       <c r="C208" t="n">
-        <v>73.31999969482422</v>
+        <v>72.75</v>
       </c>
       <c r="D208" t="n">
-        <v>70.55000305175781</v>
+        <v>71.11000061035156</v>
       </c>
       <c r="E208" t="n">
-        <v>73.16999816894531</v>
+        <v>71.70999908447266</v>
       </c>
       <c r="F208" t="n">
-        <v>54261000</v>
+        <v>35847500</v>
       </c>
       <c r="G208" t="n">
         <v>0</v>
@@ -5851,22 +5851,22 @@
     </row>
     <row r="209">
       <c r="A209" s="1" t="n">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="B209" t="n">
-        <v>71.97000122070312</v>
+        <v>72.76999664306641</v>
       </c>
       <c r="C209" t="n">
-        <v>72.75</v>
+        <v>73.94999694824219</v>
       </c>
       <c r="D209" t="n">
-        <v>71.11000061035156</v>
+        <v>72.18000030517578</v>
       </c>
       <c r="E209" t="n">
-        <v>71.70999908447266</v>
+        <v>73.33000183105469</v>
       </c>
       <c r="F209" t="n">
-        <v>35847500</v>
+        <v>33922300</v>
       </c>
       <c r="G209" t="n">
         <v>0</v>
@@ -5877,22 +5877,22 @@
     </row>
     <row r="210">
       <c r="A210" s="1" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="B210" t="n">
-        <v>72.76999664306641</v>
+        <v>72.51000213623047</v>
       </c>
       <c r="C210" t="n">
-        <v>73.94999694824219</v>
+        <v>73.75</v>
       </c>
       <c r="D210" t="n">
-        <v>72.18000030517578</v>
+        <v>72.30000305175781</v>
       </c>
       <c r="E210" t="n">
-        <v>73.33000183105469</v>
+        <v>73.56999969482422</v>
       </c>
       <c r="F210" t="n">
-        <v>33922300</v>
+        <v>42877900</v>
       </c>
       <c r="G210" t="n">
         <v>0</v>
@@ -5903,22 +5903,22 @@
     </row>
     <row r="211">
       <c r="A211" s="1" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="B211" t="n">
-        <v>72.51000213623047</v>
+        <v>75.11000061035156</v>
       </c>
       <c r="C211" t="n">
-        <v>73.75</v>
+        <v>75.30000305175781</v>
       </c>
       <c r="D211" t="n">
-        <v>72.30000305175781</v>
+        <v>73.16000366210938</v>
       </c>
       <c r="E211" t="n">
-        <v>73.56999969482422</v>
+        <v>74.19999694824219</v>
       </c>
       <c r="F211" t="n">
-        <v>42877900</v>
+        <v>28969400</v>
       </c>
       <c r="G211" t="n">
         <v>0</v>
@@ -5929,22 +5929,22 @@
     </row>
     <row r="212">
       <c r="A212" s="1" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="B212" t="n">
-        <v>75.11000061035156</v>
+        <v>75.13999938964844</v>
       </c>
       <c r="C212" t="n">
-        <v>75.30000305175781</v>
+        <v>75.20999908447266</v>
       </c>
       <c r="D212" t="n">
-        <v>73.16000366210938</v>
+        <v>73.09999847412109</v>
       </c>
       <c r="E212" t="n">
-        <v>74.19999694824219</v>
+        <v>73.69000244140625</v>
       </c>
       <c r="F212" t="n">
-        <v>28969400</v>
+        <v>28892700</v>
       </c>
       <c r="G212" t="n">
         <v>0</v>
@@ -5955,22 +5955,22 @@
     </row>
     <row r="213">
       <c r="A213" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="B213" t="n">
-        <v>75.13999938964844</v>
+        <v>73.12000274658203</v>
       </c>
       <c r="C213" t="n">
-        <v>75.20999908447266</v>
+        <v>74.5</v>
       </c>
       <c r="D213" t="n">
-        <v>73.09999847412109</v>
+        <v>73.08000183105469</v>
       </c>
       <c r="E213" t="n">
-        <v>73.69000244140625</v>
+        <v>74.13999938964844</v>
       </c>
       <c r="F213" t="n">
-        <v>28892700</v>
+        <v>24819000</v>
       </c>
       <c r="G213" t="n">
         <v>0</v>
@@ -5981,22 +5981,22 @@
     </row>
     <row r="214">
       <c r="A214" s="1" t="n">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="B214" t="n">
-        <v>73.12000274658203</v>
+        <v>73.80000305175781</v>
       </c>
       <c r="C214" t="n">
-        <v>74.5</v>
+        <v>76.31999969482422</v>
       </c>
       <c r="D214" t="n">
-        <v>73.08000183105469</v>
+        <v>73.56999969482422</v>
       </c>
       <c r="E214" t="n">
-        <v>74.13999938964844</v>
+        <v>76.29000091552734</v>
       </c>
       <c r="F214" t="n">
-        <v>24819000</v>
+        <v>26959900</v>
       </c>
       <c r="G214" t="n">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="215">
       <c r="A215" s="1" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="B215" t="n">
-        <v>73.80000305175781</v>
+        <v>76.19999694824219</v>
       </c>
       <c r="C215" t="n">
-        <v>76.31999969482422</v>
+        <v>76.90000152587891</v>
       </c>
       <c r="D215" t="n">
-        <v>73.56999969482422</v>
+        <v>74.48000335693359</v>
       </c>
       <c r="E215" t="n">
-        <v>76.29000091552734</v>
+        <v>74.79000091552734</v>
       </c>
       <c r="F215" t="n">
-        <v>26959900</v>
+        <v>27840500</v>
       </c>
       <c r="G215" t="n">
         <v>0</v>
@@ -6033,22 +6033,22 @@
     </row>
     <row r="216">
       <c r="A216" s="1" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="B216" t="n">
-        <v>76.19999694824219</v>
+        <v>74.34999847412109</v>
       </c>
       <c r="C216" t="n">
-        <v>76.90000152587891</v>
+        <v>74.66999816894531</v>
       </c>
       <c r="D216" t="n">
-        <v>74.48000335693359</v>
+        <v>73.56999969482422</v>
       </c>
       <c r="E216" t="n">
-        <v>74.79000091552734</v>
+        <v>74.20999908447266</v>
       </c>
       <c r="F216" t="n">
-        <v>27840500</v>
+        <v>20773100</v>
       </c>
       <c r="G216" t="n">
         <v>0</v>
@@ -6059,22 +6059,22 @@
     </row>
     <row r="217">
       <c r="A217" s="1" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="B217" t="n">
-        <v>74.34999847412109</v>
+        <v>76.01000213623047</v>
       </c>
       <c r="C217" t="n">
-        <v>74.66999816894531</v>
+        <v>78.40000152587891</v>
       </c>
       <c r="D217" t="n">
-        <v>73.56999969482422</v>
+        <v>75.44000244140625</v>
       </c>
       <c r="E217" t="n">
-        <v>74.20999908447266</v>
+        <v>78.23999786376953</v>
       </c>
       <c r="F217" t="n">
-        <v>20773100</v>
+        <v>41452900</v>
       </c>
       <c r="G217" t="n">
         <v>0</v>
@@ -6085,22 +6085,22 @@
     </row>
     <row r="218">
       <c r="A218" s="1" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="B218" t="n">
-        <v>76.01000213623047</v>
+        <v>78.48000335693359</v>
       </c>
       <c r="C218" t="n">
-        <v>78.40000152587891</v>
+        <v>78.73000335693359</v>
       </c>
       <c r="D218" t="n">
-        <v>75.44000244140625</v>
+        <v>77.76000213623047</v>
       </c>
       <c r="E218" t="n">
-        <v>78.23999786376953</v>
+        <v>78.16000366210938</v>
       </c>
       <c r="F218" t="n">
-        <v>41452900</v>
+        <v>26751000</v>
       </c>
       <c r="G218" t="n">
         <v>0</v>
@@ -6111,22 +6111,22 @@
     </row>
     <row r="219">
       <c r="A219" s="1" t="n">
-        <v>46248</v>
+        <v>46251</v>
       </c>
       <c r="B219" t="n">
-        <v>78.48000335693359</v>
+        <v>77.80000305175781</v>
       </c>
       <c r="C219" t="n">
-        <v>78.73000335693359</v>
+        <v>78.52999877929688</v>
       </c>
       <c r="D219" t="n">
-        <v>77.76000213623047</v>
+        <v>75.47000122070312</v>
       </c>
       <c r="E219" t="n">
-        <v>78.16000366210938</v>
+        <v>76.01999664306641</v>
       </c>
       <c r="F219" t="n">
-        <v>26751000</v>
+        <v>30753000</v>
       </c>
       <c r="G219" t="n">
         <v>0</v>
@@ -6137,22 +6137,22 @@
     </row>
     <row r="220">
       <c r="A220" s="1" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="B220" t="n">
-        <v>77.80000305175781</v>
+        <v>77.43000030517578</v>
       </c>
       <c r="C220" t="n">
-        <v>78.52999877929688</v>
+        <v>79.09999847412109</v>
       </c>
       <c r="D220" t="n">
-        <v>75.47000122070312</v>
+        <v>76.33999633789062</v>
       </c>
       <c r="E220" t="n">
-        <v>76.01999664306641</v>
+        <v>77.76999664306641</v>
       </c>
       <c r="F220" t="n">
-        <v>30753000</v>
+        <v>36151300</v>
       </c>
       <c r="G220" t="n">
         <v>0</v>
@@ -6163,22 +6163,22 @@
     </row>
     <row r="221">
       <c r="A221" s="1" t="n">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="B221" t="n">
-        <v>77.43000030517578</v>
+        <v>78.25</v>
       </c>
       <c r="C221" t="n">
-        <v>79.09999847412109</v>
+        <v>81.16000366210938</v>
       </c>
       <c r="D221" t="n">
-        <v>76.33999633789062</v>
+        <v>78.09999847412109</v>
       </c>
       <c r="E221" t="n">
-        <v>77.76999664306641</v>
+        <v>80.22000122070312</v>
       </c>
       <c r="F221" t="n">
-        <v>36151300</v>
+        <v>31461800</v>
       </c>
       <c r="G221" t="n">
         <v>0</v>
@@ -6189,22 +6189,22 @@
     </row>
     <row r="222">
       <c r="A222" s="1" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="B222" t="n">
-        <v>78.25</v>
+        <v>80.13999938964844</v>
       </c>
       <c r="C222" t="n">
-        <v>81.16000366210938</v>
+        <v>81.08000183105469</v>
       </c>
       <c r="D222" t="n">
-        <v>78.09999847412109</v>
+        <v>79.58999633789062</v>
       </c>
       <c r="E222" t="n">
-        <v>80.22000122070312</v>
+        <v>80.13999938964844</v>
       </c>
       <c r="F222" t="n">
-        <v>31461800</v>
+        <v>27118400</v>
       </c>
       <c r="G222" t="n">
         <v>0</v>
@@ -6215,22 +6215,22 @@
     </row>
     <row r="223">
       <c r="A223" s="1" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="B223" t="n">
-        <v>80.13999938964844</v>
+        <v>80.29000091552734</v>
       </c>
       <c r="C223" t="n">
-        <v>81.08000183105469</v>
+        <v>80.48999786376953</v>
       </c>
       <c r="D223" t="n">
+        <v>79.16999816894531</v>
+      </c>
+      <c r="E223" t="n">
         <v>79.58999633789062</v>
       </c>
-      <c r="E223" t="n">
-        <v>80.13999938964844</v>
-      </c>
       <c r="F223" t="n">
-        <v>27118400</v>
+        <v>23773800</v>
       </c>
       <c r="G223" t="n">
         <v>0</v>
@@ -6241,22 +6241,22 @@
     </row>
     <row r="224">
       <c r="A224" s="1" t="n">
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="B224" t="n">
-        <v>80.29000091552734</v>
+        <v>79.94000244140625</v>
       </c>
       <c r="C224" t="n">
-        <v>80.48999786376953</v>
+        <v>80.62000274658203</v>
       </c>
       <c r="D224" t="n">
-        <v>79.16999816894531</v>
+        <v>79.01999664306641</v>
       </c>
       <c r="E224" t="n">
-        <v>79.58999633789062</v>
+        <v>80.01000213623047</v>
       </c>
       <c r="F224" t="n">
-        <v>23773800</v>
+        <v>21085300</v>
       </c>
       <c r="G224" t="n">
         <v>0</v>
@@ -6267,22 +6267,22 @@
     </row>
     <row r="225">
       <c r="A225" s="1" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="B225" t="n">
-        <v>79.94000244140625</v>
+        <v>79.65000152587891</v>
       </c>
       <c r="C225" t="n">
-        <v>80.62000274658203</v>
+        <v>82.45999908447266</v>
       </c>
       <c r="D225" t="n">
-        <v>79.01999664306641</v>
+        <v>79.40000152587891</v>
       </c>
       <c r="E225" t="n">
-        <v>80.01000213623047</v>
+        <v>82.23000335693359</v>
       </c>
       <c r="F225" t="n">
-        <v>21085300</v>
+        <v>29462000</v>
       </c>
       <c r="G225" t="n">
         <v>0</v>
@@ -6293,22 +6293,22 @@
     </row>
     <row r="226">
       <c r="A226" s="1" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="B226" t="n">
-        <v>79.65000152587891</v>
+        <v>82.05000305175781</v>
       </c>
       <c r="C226" t="n">
-        <v>82.45999908447266</v>
+        <v>82.41999816894531</v>
       </c>
       <c r="D226" t="n">
-        <v>79.40000152587891</v>
+        <v>81.30000305175781</v>
       </c>
       <c r="E226" t="n">
-        <v>82.23000335693359</v>
+        <v>81.45999908447266</v>
       </c>
       <c r="F226" t="n">
-        <v>29462000</v>
+        <v>22874900</v>
       </c>
       <c r="G226" t="n">
         <v>0</v>
@@ -6319,22 +6319,22 @@
     </row>
     <row r="227">
       <c r="A227" s="1" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="B227" t="n">
-        <v>82.05000305175781</v>
+        <v>81.06999969482422</v>
       </c>
       <c r="C227" t="n">
-        <v>82.41999816894531</v>
+        <v>81.15000152587891</v>
       </c>
       <c r="D227" t="n">
-        <v>81.30000305175781</v>
+        <v>79.27999877929688</v>
       </c>
       <c r="E227" t="n">
-        <v>81.45999908447266</v>
+        <v>79.83999633789062</v>
       </c>
       <c r="F227" t="n">
-        <v>22874900</v>
+        <v>27174400</v>
       </c>
       <c r="G227" t="n">
         <v>0</v>
@@ -6345,22 +6345,22 @@
     </row>
     <row r="228">
       <c r="A228" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="B228" t="n">
-        <v>81.06999969482422</v>
+        <v>80.36000061035156</v>
       </c>
       <c r="C228" t="n">
-        <v>81.15000152587891</v>
+        <v>82.34999847412109</v>
       </c>
       <c r="D228" t="n">
-        <v>79.27999877929688</v>
+        <v>79.94999694824219</v>
       </c>
       <c r="E228" t="n">
-        <v>79.83999633789062</v>
+        <v>81.72000122070312</v>
       </c>
       <c r="F228" t="n">
-        <v>27174400</v>
+        <v>29092700</v>
       </c>
       <c r="G228" t="n">
         <v>0</v>
@@ -6371,22 +6371,22 @@
     </row>
     <row r="229">
       <c r="A229" s="1" t="n">
-        <v>46262</v>
+        <v>46265</v>
       </c>
       <c r="B229" t="n">
-        <v>80.36000061035156</v>
+        <v>81</v>
       </c>
       <c r="C229" t="n">
-        <v>82.34999847412109</v>
+        <v>81.73000335693359</v>
       </c>
       <c r="D229" t="n">
-        <v>79.94999694824219</v>
+        <v>80.65000152587891</v>
       </c>
       <c r="E229" t="n">
-        <v>81.72000122070312</v>
+        <v>81.05000305175781</v>
       </c>
       <c r="F229" t="n">
-        <v>29092700</v>
+        <v>30740800</v>
       </c>
       <c r="G229" t="n">
         <v>0</v>
@@ -6397,22 +6397,22 @@
     </row>
     <row r="230">
       <c r="A230" s="1" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="B230" t="n">
-        <v>81</v>
+        <v>80.16999816894531</v>
       </c>
       <c r="C230" t="n">
-        <v>81.73000335693359</v>
+        <v>82.12999725341797</v>
       </c>
       <c r="D230" t="n">
-        <v>80.65000152587891</v>
+        <v>79.59999847412109</v>
       </c>
       <c r="E230" t="n">
-        <v>81.05000305175781</v>
+        <v>80.80999755859375</v>
       </c>
       <c r="F230" t="n">
-        <v>30740800</v>
+        <v>21164900</v>
       </c>
       <c r="G230" t="n">
         <v>0</v>
@@ -6423,22 +6423,22 @@
     </row>
     <row r="231">
       <c r="A231" s="1" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="B231" t="n">
-        <v>80.16999816894531</v>
+        <v>80.55000305175781</v>
       </c>
       <c r="C231" t="n">
-        <v>82.12999725341797</v>
+        <v>83.12000274658203</v>
       </c>
       <c r="D231" t="n">
-        <v>79.59999847412109</v>
+        <v>80.30000305175781</v>
       </c>
       <c r="E231" t="n">
-        <v>80.80999755859375</v>
+        <v>82.73000335693359</v>
       </c>
       <c r="F231" t="n">
-        <v>21164900</v>
+        <v>22077800</v>
       </c>
       <c r="G231" t="n">
         <v>0</v>
@@ -6449,22 +6449,22 @@
     </row>
     <row r="232">
       <c r="A232" s="1" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="B232" t="n">
-        <v>80.55000305175781</v>
+        <v>83.18000030517578</v>
       </c>
       <c r="C232" t="n">
-        <v>83.12000274658203</v>
+        <v>83.59999847412109</v>
       </c>
       <c r="D232" t="n">
-        <v>80.30000305175781</v>
+        <v>81.62999725341797</v>
       </c>
       <c r="E232" t="n">
-        <v>82.73000335693359</v>
+        <v>82.66999816894531</v>
       </c>
       <c r="F232" t="n">
-        <v>22077800</v>
+        <v>24006400</v>
       </c>
       <c r="G232" t="n">
         <v>0</v>
@@ -6475,22 +6475,22 @@
     </row>
     <row r="233">
       <c r="A233" s="1" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B233" t="n">
-        <v>83.18000030517578</v>
+        <v>82.16999816894531</v>
       </c>
       <c r="C233" t="n">
-        <v>83.59999847412109</v>
+        <v>82.69000244140625</v>
       </c>
       <c r="D233" t="n">
-        <v>81.62999725341797</v>
+        <v>78.23000335693359</v>
       </c>
       <c r="E233" t="n">
-        <v>82.66999816894531</v>
+        <v>78.25</v>
       </c>
       <c r="F233" t="n">
-        <v>24006400</v>
+        <v>40190000</v>
       </c>
       <c r="G233" t="n">
         <v>0</v>
@@ -6501,22 +6501,22 @@
     </row>
     <row r="234">
       <c r="A234" s="1" t="n">
-        <v>46269</v>
+        <v>46273</v>
       </c>
       <c r="B234" t="n">
-        <v>82.16999816894531</v>
+        <v>77.55000305175781</v>
       </c>
       <c r="C234" t="n">
-        <v>82.69000244140625</v>
+        <v>77.73000335693359</v>
       </c>
       <c r="D234" t="n">
-        <v>78.23000335693359</v>
+        <v>75.91999816894531</v>
       </c>
       <c r="E234" t="n">
-        <v>78.25</v>
+        <v>76.76999664306641</v>
       </c>
       <c r="F234" t="n">
-        <v>40190000</v>
+        <v>33865500</v>
       </c>
       <c r="G234" t="n">
         <v>0</v>
@@ -6527,22 +6527,22 @@
     </row>
     <row r="235">
       <c r="A235" s="1" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B235" t="n">
-        <v>77.55000305175781</v>
+        <v>76.33999633789062</v>
       </c>
       <c r="C235" t="n">
-        <v>77.73000335693359</v>
+        <v>76.72000122070312</v>
       </c>
       <c r="D235" t="n">
-        <v>75.91999816894531</v>
+        <v>75.87000274658203</v>
       </c>
       <c r="E235" t="n">
-        <v>76.76999664306641</v>
+        <v>76.02999877929688</v>
       </c>
       <c r="F235" t="n">
-        <v>33865500</v>
+        <v>22779600</v>
       </c>
       <c r="G235" t="n">
         <v>0</v>
@@ -6553,22 +6553,22 @@
     </row>
     <row r="236">
       <c r="A236" s="1" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="B236" t="n">
-        <v>76.33999633789062</v>
+        <v>75.33000183105469</v>
       </c>
       <c r="C236" t="n">
-        <v>76.72000122070312</v>
+        <v>76.30000305175781</v>
       </c>
       <c r="D236" t="n">
-        <v>75.87000274658203</v>
+        <v>75.02999877929688</v>
       </c>
       <c r="E236" t="n">
-        <v>76.02999877929688</v>
+        <v>76.01000213623047</v>
       </c>
       <c r="F236" t="n">
-        <v>22779600</v>
+        <v>20049000</v>
       </c>
       <c r="G236" t="n">
         <v>0</v>
@@ -6579,22 +6579,22 @@
     </row>
     <row r="237">
       <c r="A237" s="1" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="B237" t="n">
-        <v>75.33000183105469</v>
+        <v>76.63999938964844</v>
       </c>
       <c r="C237" t="n">
-        <v>76.30000305175781</v>
+        <v>77.56999969482422</v>
       </c>
       <c r="D237" t="n">
-        <v>75.02999877929688</v>
+        <v>76.15000152587891</v>
       </c>
       <c r="E237" t="n">
-        <v>76.01000213623047</v>
+        <v>77.40000152587891</v>
       </c>
       <c r="F237" t="n">
-        <v>20049000</v>
+        <v>22237800</v>
       </c>
       <c r="G237" t="n">
         <v>0</v>
@@ -6605,22 +6605,22 @@
     </row>
     <row r="238">
       <c r="A238" s="1" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="B238" t="n">
-        <v>76.63999938964844</v>
+        <v>78.97000122070312</v>
       </c>
       <c r="C238" t="n">
-        <v>77.56999969482422</v>
+        <v>81.01999664306641</v>
       </c>
       <c r="D238" t="n">
-        <v>76.15000152587891</v>
+        <v>78.48999786376953</v>
       </c>
       <c r="E238" t="n">
-        <v>77.40000152587891</v>
+        <v>80.31999969482422</v>
       </c>
       <c r="F238" t="n">
-        <v>22237800</v>
+        <v>30945100</v>
       </c>
       <c r="G238" t="n">
         <v>0</v>
@@ -6631,22 +6631,22 @@
     </row>
     <row r="239">
       <c r="A239" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="B239" t="n">
-        <v>78.97000122070312</v>
+        <v>79.37999725341797</v>
       </c>
       <c r="C239" t="n">
-        <v>81.01999664306641</v>
+        <v>79.48000335693359</v>
       </c>
       <c r="D239" t="n">
-        <v>78.48999786376953</v>
+        <v>77.45999908447266</v>
       </c>
       <c r="E239" t="n">
-        <v>80.31999969482422</v>
+        <v>77.90000152587891</v>
       </c>
       <c r="F239" t="n">
-        <v>30945100</v>
+        <v>28027400</v>
       </c>
       <c r="G239" t="n">
         <v>0</v>
@@ -6657,22 +6657,22 @@
     </row>
     <row r="240">
       <c r="A240" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="B240" t="n">
-        <v>79.37999725341797</v>
+        <v>77.73000335693359</v>
       </c>
       <c r="C240" t="n">
-        <v>79.48000335693359</v>
+        <v>77.80000305175781</v>
       </c>
       <c r="D240" t="n">
-        <v>77.45999908447266</v>
+        <v>76.30999755859375</v>
       </c>
       <c r="E240" t="n">
-        <v>77.90000152587891</v>
+        <v>76.41000366210938</v>
       </c>
       <c r="F240" t="n">
-        <v>28027400</v>
+        <v>25376300</v>
       </c>
       <c r="G240" t="n">
         <v>0</v>
@@ -6683,22 +6683,22 @@
     </row>
     <row r="241">
       <c r="A241" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="B241" t="n">
-        <v>77.73000335693359</v>
+        <v>76.91000366210938</v>
       </c>
       <c r="C241" t="n">
-        <v>77.80000305175781</v>
+        <v>76.95999908447266</v>
       </c>
       <c r="D241" t="n">
-        <v>76.30999755859375</v>
+        <v>75.30000305175781</v>
       </c>
       <c r="E241" t="n">
-        <v>76.41000366210938</v>
+        <v>75.30999755859375</v>
       </c>
       <c r="F241" t="n">
-        <v>25376300</v>
+        <v>28167600</v>
       </c>
       <c r="G241" t="n">
         <v>0</v>
@@ -6709,22 +6709,22 @@
     </row>
     <row r="242">
       <c r="A242" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="B242" t="n">
-        <v>76.91000366210938</v>
+        <v>71.26999664306641</v>
       </c>
       <c r="C242" t="n">
-        <v>76.95999908447266</v>
+        <v>72.37999725341797</v>
       </c>
       <c r="D242" t="n">
-        <v>75.30000305175781</v>
+        <v>70.11000061035156</v>
       </c>
       <c r="E242" t="n">
-        <v>75.30999755859375</v>
+        <v>71.79000091552734</v>
       </c>
       <c r="F242" t="n">
-        <v>28167600</v>
+        <v>114413500</v>
       </c>
       <c r="G242" t="n">
         <v>0</v>
@@ -6735,22 +6735,22 @@
     </row>
     <row r="243">
       <c r="A243" s="1" t="n">
-        <v>46283</v>
+        <v>46286</v>
       </c>
       <c r="B243" t="n">
-        <v>71.26999664306641</v>
+        <v>71.81999969482422</v>
       </c>
       <c r="C243" t="n">
-        <v>72.37999725341797</v>
+        <v>73.87000274658203</v>
       </c>
       <c r="D243" t="n">
-        <v>70.11000061035156</v>
+        <v>71.79000091552734</v>
       </c>
       <c r="E243" t="n">
-        <v>71.79000091552734</v>
+        <v>73.36000061035156</v>
       </c>
       <c r="F243" t="n">
-        <v>114413500</v>
+        <v>36948000</v>
       </c>
       <c r="G243" t="n">
         <v>0</v>
@@ -6761,22 +6761,22 @@
     </row>
     <row r="244">
       <c r="A244" s="1" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="B244" t="n">
-        <v>71.81999969482422</v>
+        <v>73.69000244140625</v>
       </c>
       <c r="C244" t="n">
-        <v>73.87000274658203</v>
+        <v>73.76000213623047</v>
       </c>
       <c r="D244" t="n">
-        <v>71.79000091552734</v>
+        <v>71.58000183105469</v>
       </c>
       <c r="E244" t="n">
-        <v>73.36000061035156</v>
+        <v>72.16000366210938</v>
       </c>
       <c r="F244" t="n">
-        <v>36948000</v>
+        <v>34372500</v>
       </c>
       <c r="G244" t="n">
         <v>0</v>
@@ -6787,22 +6787,22 @@
     </row>
     <row r="245">
       <c r="A245" s="1" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="B245" t="n">
-        <v>73.69000244140625</v>
+        <v>72.08000183105469</v>
       </c>
       <c r="C245" t="n">
-        <v>73.76000213623047</v>
+        <v>72.37000274658203</v>
       </c>
       <c r="D245" t="n">
-        <v>71.58000183105469</v>
+        <v>71.06999969482422</v>
       </c>
       <c r="E245" t="n">
-        <v>72.16000366210938</v>
+        <v>71.36000061035156</v>
       </c>
       <c r="F245" t="n">
-        <v>34372500</v>
+        <v>32807500</v>
       </c>
       <c r="G245" t="n">
         <v>0</v>
@@ -6813,22 +6813,22 @@
     </row>
     <row r="246">
       <c r="A246" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="B246" t="n">
-        <v>72.08000183105469</v>
+        <v>71.62000274658203</v>
       </c>
       <c r="C246" t="n">
-        <v>72.37000274658203</v>
+        <v>72.04000091552734</v>
       </c>
       <c r="D246" t="n">
-        <v>71.06999969482422</v>
+        <v>71.20999908447266</v>
       </c>
       <c r="E246" t="n">
-        <v>71.36000061035156</v>
+        <v>71.72000122070312</v>
       </c>
       <c r="F246" t="n">
-        <v>32807500</v>
+        <v>28223900</v>
       </c>
       <c r="G246" t="n">
         <v>0</v>
@@ -6839,22 +6839,22 @@
     </row>
     <row r="247">
       <c r="A247" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="B247" t="n">
-        <v>71.62000274658203</v>
+        <v>71.62999725341797</v>
       </c>
       <c r="C247" t="n">
-        <v>72.04000091552734</v>
+        <v>71.83999633789062</v>
       </c>
       <c r="D247" t="n">
-        <v>71.20999908447266</v>
+        <v>70.98000335693359</v>
       </c>
       <c r="E247" t="n">
-        <v>71.72000122070312</v>
+        <v>71.15000152587891</v>
       </c>
       <c r="F247" t="n">
-        <v>28223900</v>
+        <v>23203100</v>
       </c>
       <c r="G247" t="n">
         <v>0</v>
@@ -6865,22 +6865,22 @@
     </row>
     <row r="248">
       <c r="A248" s="1" t="n">
-        <v>46290</v>
+        <v>46293</v>
       </c>
       <c r="B248" t="n">
-        <v>71.62999725341797</v>
+        <v>71.55000305175781</v>
       </c>
       <c r="C248" t="n">
-        <v>71.83999633789062</v>
+        <v>71.65000152587891</v>
       </c>
       <c r="D248" t="n">
-        <v>70.98000335693359</v>
+        <v>68.87999725341797</v>
       </c>
       <c r="E248" t="n">
-        <v>71.15000152587891</v>
+        <v>69.23000335693359</v>
       </c>
       <c r="F248" t="n">
-        <v>23203100</v>
+        <v>43366300</v>
       </c>
       <c r="G248" t="n">
         <v>0</v>
@@ -6891,22 +6891,22 @@
     </row>
     <row r="249">
       <c r="A249" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="B249" t="n">
-        <v>71.55000305175781</v>
+        <v>70.33000183105469</v>
       </c>
       <c r="C249" t="n">
-        <v>71.65000152587891</v>
+        <v>71.36000061035156</v>
       </c>
       <c r="D249" t="n">
-        <v>68.87999725341797</v>
+        <v>70.15000152587891</v>
       </c>
       <c r="E249" t="n">
-        <v>69.23000335693359</v>
+        <v>70.30000305175781</v>
       </c>
       <c r="F249" t="n">
-        <v>43366300</v>
+        <v>34550800</v>
       </c>
       <c r="G249" t="n">
         <v>0</v>
@@ -6917,22 +6917,22 @@
     </row>
     <row r="250">
       <c r="A250" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="B250" t="n">
-        <v>70.33000183105469</v>
+        <v>70.19999694824219</v>
       </c>
       <c r="C250" t="n">
-        <v>71.36000061035156</v>
+        <v>70.30000305175781</v>
       </c>
       <c r="D250" t="n">
-        <v>70.15000152587891</v>
+        <v>69.51000213623047</v>
       </c>
       <c r="E250" t="n">
-        <v>70.30000305175781</v>
+        <v>69.58000183105469</v>
       </c>
       <c r="F250" t="n">
-        <v>34550800</v>
+        <v>36416600</v>
       </c>
       <c r="G250" t="n">
         <v>0</v>
@@ -6943,22 +6943,22 @@
     </row>
     <row r="251">
       <c r="A251" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="B251" t="n">
-        <v>70.19999694824219</v>
+        <v>69.41000366210938</v>
       </c>
       <c r="C251" t="n">
-        <v>70.30000305175781</v>
+        <v>69.66000366210938</v>
       </c>
       <c r="D251" t="n">
-        <v>69.51000213623047</v>
+        <v>67.79000091552734</v>
       </c>
       <c r="E251" t="n">
-        <v>69.58000183105469</v>
+        <v>67.84999847412109</v>
       </c>
       <c r="F251" t="n">
-        <v>36416600</v>
+        <v>41584700</v>
       </c>
       <c r="G251" t="n">
         <v>0</v>
@@ -6969,22 +6969,22 @@
     </row>
     <row r="252">
       <c r="A252" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="B252" t="n">
-        <v>69.41000366210938</v>
+        <v>67.65000152587891</v>
       </c>
       <c r="C252" t="n">
-        <v>69.66000366210938</v>
+        <v>67.87000274658203</v>
       </c>
       <c r="D252" t="n">
-        <v>67.79000091552734</v>
+        <v>66.74500274658203</v>
       </c>
       <c r="E252" t="n">
-        <v>67.84999847412109</v>
+        <v>67.05999755859375</v>
       </c>
       <c r="F252" t="n">
-        <v>41403300</v>
+        <v>38312283</v>
       </c>
       <c r="G252" t="n">
         <v>0</v>
@@ -10434,34 +10434,34 @@
         </is>
       </c>
       <c r="C2" t="n">
+        <v>67.06</v>
+      </c>
+      <c r="D2" t="n">
         <v>67.84999999999999</v>
       </c>
-      <c r="D2" t="n">
-        <v>69.58</v>
-      </c>
       <c r="E2" t="n">
-        <v>69.34399999999999</v>
+        <v>67.65000000000001</v>
       </c>
       <c r="F2" t="n">
-        <v>69.66</v>
+        <v>67.87</v>
       </c>
       <c r="G2" t="n">
-        <v>67.79000000000001</v>
+        <v>66.745</v>
       </c>
       <c r="H2" t="n">
-        <v>40467844</v>
+        <v>38312283</v>
       </c>
       <c r="I2" t="n">
         <v>37126214</v>
       </c>
       <c r="J2" t="n">
-        <v>282523303936</v>
+        <v>279233789952</v>
       </c>
       <c r="K2" t="n">
-        <v>21.336477</v>
+        <v>21.088049</v>
       </c>
       <c r="L2" t="n">
-        <v>17.787018</v>
+        <v>17.579916</v>
       </c>
       <c r="M2" t="n">
         <v>3.18</v>
@@ -10502,7 +10502,7 @@
         <v>7.241</v>
       </c>
       <c r="Y2" t="n">
-        <v>9.370253</v>
+        <v>9.261151</v>
       </c>
       <c r="Z2" t="n">
         <v>0.111</v>
@@ -10541,7 +10541,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>2026-10-02 19:38:49</t>
+          <t>2026-10-03 05:34:52</t>
         </is>
       </c>
     </row>

--- a/data/NFLX_data.xlsx
+++ b/data/NFLX_data.xlsx
@@ -469,22 +469,22 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45933</v>
+        <v>45936</v>
       </c>
       <c r="B2" t="n">
-        <v>116.5</v>
+        <v>116.0370025634766</v>
       </c>
       <c r="C2" t="n">
-        <v>116.8000030517578</v>
+        <v>116.3580017089844</v>
       </c>
       <c r="D2" t="n">
-        <v>114.3219985961914</v>
+        <v>114.5449981689453</v>
       </c>
       <c r="E2" t="n">
-        <v>115.3320007324219</v>
+        <v>116.3310012817383</v>
       </c>
       <c r="F2" t="n">
-        <v>31374000</v>
+        <v>29686000</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -495,22 +495,22 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45936</v>
+        <v>45937</v>
       </c>
       <c r="B3" t="n">
-        <v>116.0370025634766</v>
+        <v>117.7789993286133</v>
       </c>
       <c r="C3" t="n">
-        <v>116.3580017089844</v>
+        <v>120.1370010375977</v>
       </c>
       <c r="D3" t="n">
-        <v>114.5449981689453</v>
+        <v>117.7460021972656</v>
       </c>
       <c r="E3" t="n">
-        <v>116.3310012817383</v>
+        <v>119.1060028076172</v>
       </c>
       <c r="F3" t="n">
-        <v>29686000</v>
+        <v>33091000</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -521,22 +521,22 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>45937</v>
+        <v>45938</v>
       </c>
       <c r="B4" t="n">
-        <v>117.7789993286133</v>
+        <v>119.7109985351562</v>
       </c>
       <c r="C4" t="n">
-        <v>120.1370010375977</v>
+        <v>121.7389984130859</v>
       </c>
       <c r="D4" t="n">
-        <v>117.7460021972656</v>
+        <v>119.1999969482422</v>
       </c>
       <c r="E4" t="n">
-        <v>119.1060028076172</v>
+        <v>121.4250030517578</v>
       </c>
       <c r="F4" t="n">
-        <v>33091000</v>
+        <v>28514000</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -547,22 +547,22 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>45938</v>
+        <v>45939</v>
       </c>
       <c r="B5" t="n">
-        <v>119.7109985351562</v>
+        <v>121.4250030517578</v>
       </c>
       <c r="C5" t="n">
-        <v>121.7389984130859</v>
+        <v>123.75</v>
       </c>
       <c r="D5" t="n">
-        <v>119.1999969482422</v>
+        <v>121.181999206543</v>
       </c>
       <c r="E5" t="n">
-        <v>121.4250030517578</v>
+        <v>123.1070022583008</v>
       </c>
       <c r="F5" t="n">
-        <v>28514000</v>
+        <v>28241000</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -573,22 +573,22 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>45939</v>
+        <v>45940</v>
       </c>
       <c r="B6" t="n">
-        <v>121.4250030517578</v>
+        <v>122.9000015258789</v>
       </c>
       <c r="C6" t="n">
-        <v>123.75</v>
+        <v>124.6999969482422</v>
       </c>
       <c r="D6" t="n">
-        <v>121.181999206543</v>
+        <v>121.9100036621094</v>
       </c>
       <c r="E6" t="n">
-        <v>123.1070022583008</v>
+        <v>122.0080032348633</v>
       </c>
       <c r="F6" t="n">
-        <v>28241000</v>
+        <v>42798000</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -599,22 +599,22 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>45940</v>
+        <v>45943</v>
       </c>
       <c r="B7" t="n">
-        <v>122.9000015258789</v>
+        <v>122.1350021362305</v>
       </c>
       <c r="C7" t="n">
-        <v>124.6999969482422</v>
+        <v>123.1119995117188</v>
       </c>
       <c r="D7" t="n">
-        <v>121.9100036621094</v>
+        <v>120.6809997558594</v>
       </c>
       <c r="E7" t="n">
-        <v>122.0080032348633</v>
+        <v>121.9029998779297</v>
       </c>
       <c r="F7" t="n">
-        <v>42798000</v>
+        <v>24608000</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -625,22 +625,22 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>45943</v>
+        <v>45944</v>
       </c>
       <c r="B8" t="n">
-        <v>122.1350021362305</v>
+        <v>121.4749984741211</v>
       </c>
       <c r="C8" t="n">
-        <v>123.1119995117188</v>
+        <v>122.4290008544922</v>
       </c>
       <c r="D8" t="n">
-        <v>120.6809997558594</v>
+        <v>120.3099975585938</v>
       </c>
       <c r="E8" t="n">
-        <v>121.9029998779297</v>
+        <v>121.5350036621094</v>
       </c>
       <c r="F8" t="n">
-        <v>24608000</v>
+        <v>23624000</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -651,22 +651,22 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>45944</v>
+        <v>45945</v>
       </c>
       <c r="B9" t="n">
-        <v>121.4749984741211</v>
+        <v>121.3010025024414</v>
       </c>
       <c r="C9" t="n">
-        <v>122.4290008544922</v>
+        <v>121.9619979858398</v>
       </c>
       <c r="D9" t="n">
-        <v>120.3099975585938</v>
+        <v>120.161003112793</v>
       </c>
       <c r="E9" t="n">
-        <v>121.5350036621094</v>
+        <v>120.3290023803711</v>
       </c>
       <c r="F9" t="n">
-        <v>23624000</v>
+        <v>20252000</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -677,22 +677,22 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>45945</v>
+        <v>45946</v>
       </c>
       <c r="B10" t="n">
-        <v>121.3010025024414</v>
+        <v>121.2149963378906</v>
       </c>
       <c r="C10" t="n">
-        <v>121.9619979858398</v>
+        <v>121.6709976196289</v>
       </c>
       <c r="D10" t="n">
-        <v>120.161003112793</v>
+        <v>117.5999984741211</v>
       </c>
       <c r="E10" t="n">
-        <v>120.3290023803711</v>
+        <v>118.359001159668</v>
       </c>
       <c r="F10" t="n">
-        <v>20252000</v>
+        <v>28326000</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -703,22 +703,22 @@
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>45946</v>
+        <v>45947</v>
       </c>
       <c r="B11" t="n">
-        <v>121.2149963378906</v>
+        <v>118.3600006103516</v>
       </c>
       <c r="C11" t="n">
-        <v>121.6709976196289</v>
+        <v>120.3119964599609</v>
       </c>
       <c r="D11" t="n">
-        <v>117.5999984741211</v>
+        <v>117.8949966430664</v>
       </c>
       <c r="E11" t="n">
-        <v>118.359001159668</v>
+        <v>119.9359970092773</v>
       </c>
       <c r="F11" t="n">
-        <v>28326000</v>
+        <v>29571000</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -729,22 +729,22 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>45947</v>
+        <v>45950</v>
       </c>
       <c r="B12" t="n">
-        <v>118.3600006103516</v>
+        <v>120.7880020141602</v>
       </c>
       <c r="C12" t="n">
-        <v>120.3119964599609</v>
+        <v>124.7760009765625</v>
       </c>
       <c r="D12" t="n">
-        <v>117.8949966430664</v>
+        <v>120.6900024414062</v>
       </c>
       <c r="E12" t="n">
-        <v>119.9359970092773</v>
+        <v>123.8560028076172</v>
       </c>
       <c r="F12" t="n">
-        <v>29571000</v>
+        <v>39862000</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -755,22 +755,22 @@
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>45950</v>
+        <v>45951</v>
       </c>
       <c r="B13" t="n">
-        <v>120.7880020141602</v>
+        <v>124.2829971313477</v>
       </c>
       <c r="C13" t="n">
-        <v>124.7760009765625</v>
+        <v>124.8600006103516</v>
       </c>
       <c r="D13" t="n">
-        <v>120.6900024414062</v>
+        <v>123.1760025024414</v>
       </c>
       <c r="E13" t="n">
-        <v>123.8560028076172</v>
+        <v>124.1350021362305</v>
       </c>
       <c r="F13" t="n">
-        <v>39862000</v>
+        <v>65082000</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -781,22 +781,22 @@
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>45951</v>
+        <v>45952</v>
       </c>
       <c r="B14" t="n">
-        <v>124.2829971313477</v>
+        <v>114.2900009155273</v>
       </c>
       <c r="C14" t="n">
-        <v>124.8600006103516</v>
+        <v>115.7600021362305</v>
       </c>
       <c r="D14" t="n">
-        <v>123.1760025024414</v>
+        <v>111.2509994506836</v>
       </c>
       <c r="E14" t="n">
-        <v>124.1350021362305</v>
+        <v>111.6370010375977</v>
       </c>
       <c r="F14" t="n">
-        <v>65082000</v>
+        <v>147890000</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -807,22 +807,22 @@
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>45952</v>
+        <v>45953</v>
       </c>
       <c r="B15" t="n">
-        <v>114.2900009155273</v>
+        <v>112.6900024414062</v>
       </c>
       <c r="C15" t="n">
-        <v>115.7600021362305</v>
+        <v>112.7829971313477</v>
       </c>
       <c r="D15" t="n">
-        <v>111.2509994506836</v>
+        <v>109.9729995727539</v>
       </c>
       <c r="E15" t="n">
-        <v>111.6370010375977</v>
+        <v>111.359001159668</v>
       </c>
       <c r="F15" t="n">
-        <v>147890000</v>
+        <v>68497000</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -833,22 +833,22 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>45953</v>
+        <v>45954</v>
       </c>
       <c r="B16" t="n">
-        <v>112.6900024414062</v>
+        <v>111.0999984741211</v>
       </c>
       <c r="C16" t="n">
-        <v>112.7829971313477</v>
+        <v>111.4509963989258</v>
       </c>
       <c r="D16" t="n">
-        <v>109.9729995727539</v>
+        <v>109.4410018920898</v>
       </c>
       <c r="E16" t="n">
-        <v>111.359001159668</v>
+        <v>109.4690017700195</v>
       </c>
       <c r="F16" t="n">
-        <v>68497000</v>
+        <v>60280000</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -859,22 +859,22 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>45954</v>
+        <v>45957</v>
       </c>
       <c r="B17" t="n">
-        <v>111.0999984741211</v>
+        <v>110.0670013427734</v>
       </c>
       <c r="C17" t="n">
-        <v>111.4509963989258</v>
+        <v>110.2279968261719</v>
       </c>
       <c r="D17" t="n">
-        <v>109.4410018920898</v>
+        <v>108.7300033569336</v>
       </c>
       <c r="E17" t="n">
-        <v>109.4690017700195</v>
+        <v>109.4560012817383</v>
       </c>
       <c r="F17" t="n">
-        <v>60280000</v>
+        <v>46911000</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -885,22 +885,22 @@
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>45957</v>
+        <v>45958</v>
       </c>
       <c r="B18" t="n">
-        <v>110.0670013427734</v>
+        <v>109.4000015258789</v>
       </c>
       <c r="C18" t="n">
-        <v>110.2279968261719</v>
+        <v>111.697998046875</v>
       </c>
       <c r="D18" t="n">
-        <v>108.7300033569336</v>
+        <v>109.3010025024414</v>
       </c>
       <c r="E18" t="n">
-        <v>109.4560012817383</v>
+        <v>110.25</v>
       </c>
       <c r="F18" t="n">
-        <v>46911000</v>
+        <v>40209000</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -911,22 +911,22 @@
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>45958</v>
+        <v>45959</v>
       </c>
       <c r="B19" t="n">
-        <v>109.4000015258789</v>
+        <v>109.984001159668</v>
       </c>
       <c r="C19" t="n">
-        <v>111.697998046875</v>
+        <v>110.8550033569336</v>
       </c>
       <c r="D19" t="n">
-        <v>109.3010025024414</v>
+        <v>109.5999984741211</v>
       </c>
       <c r="E19" t="n">
-        <v>110.25</v>
+        <v>110.0410003662109</v>
       </c>
       <c r="F19" t="n">
-        <v>40209000</v>
+        <v>33995000</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -937,22 +937,22 @@
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>45959</v>
+        <v>45960</v>
       </c>
       <c r="B20" t="n">
-        <v>109.984001159668</v>
+        <v>109.4400024414062</v>
       </c>
       <c r="C20" t="n">
-        <v>110.8550033569336</v>
+        <v>110.6159973144531</v>
       </c>
       <c r="D20" t="n">
-        <v>109.5999984741211</v>
+        <v>108.8109970092773</v>
       </c>
       <c r="E20" t="n">
-        <v>110.0410003662109</v>
+        <v>108.9000015258789</v>
       </c>
       <c r="F20" t="n">
-        <v>33995000</v>
+        <v>41581000</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -963,22 +963,22 @@
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>45960</v>
+        <v>45961</v>
       </c>
       <c r="B21" t="n">
-        <v>109.4400024414062</v>
+        <v>110.5390014648438</v>
       </c>
       <c r="C21" t="n">
-        <v>110.6159973144531</v>
+        <v>113.4879989624023</v>
       </c>
       <c r="D21" t="n">
-        <v>108.8109970092773</v>
+        <v>110.197998046875</v>
       </c>
       <c r="E21" t="n">
-        <v>108.9000015258789</v>
+        <v>111.8860015869141</v>
       </c>
       <c r="F21" t="n">
-        <v>41581000</v>
+        <v>68665000</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -989,22 +989,22 @@
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>45961</v>
+        <v>45964</v>
       </c>
       <c r="B22" t="n">
-        <v>110.5390014648438</v>
+        <v>113.3239974975586</v>
       </c>
       <c r="C22" t="n">
-        <v>113.4879989624023</v>
+        <v>113.3499984741211</v>
       </c>
       <c r="D22" t="n">
-        <v>110.197998046875</v>
+        <v>107.5149993896484</v>
       </c>
       <c r="E22" t="n">
-        <v>111.8860015869141</v>
+        <v>110.0090026855469</v>
       </c>
       <c r="F22" t="n">
-        <v>68665000</v>
+        <v>58634000</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -1015,22 +1015,22 @@
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>45964</v>
+        <v>45965</v>
       </c>
       <c r="B23" t="n">
-        <v>113.3239974975586</v>
+        <v>109.9990005493164</v>
       </c>
       <c r="C23" t="n">
-        <v>113.3499984741211</v>
+        <v>110.4599990844727</v>
       </c>
       <c r="D23" t="n">
-        <v>107.5149993896484</v>
+        <v>108.6679992675781</v>
       </c>
       <c r="E23" t="n">
-        <v>110.0090026855469</v>
+        <v>109.2959976196289</v>
       </c>
       <c r="F23" t="n">
-        <v>58634000</v>
+        <v>38718000</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -1041,22 +1041,22 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>45965</v>
+        <v>45966</v>
       </c>
       <c r="B24" t="n">
-        <v>109.9990005493164</v>
+        <v>108.5</v>
       </c>
       <c r="C24" t="n">
-        <v>110.4599990844727</v>
+        <v>110.0849990844727</v>
       </c>
       <c r="D24" t="n">
-        <v>108.6679992675781</v>
+        <v>107.3369979858398</v>
       </c>
       <c r="E24" t="n">
-        <v>109.2959976196289</v>
+        <v>109.8460006713867</v>
       </c>
       <c r="F24" t="n">
-        <v>38718000</v>
+        <v>35539000</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -1067,22 +1067,22 @@
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>45966</v>
+        <v>45967</v>
       </c>
       <c r="B25" t="n">
-        <v>108.5</v>
+        <v>109.4580001831055</v>
       </c>
       <c r="C25" t="n">
-        <v>110.0849990844727</v>
+        <v>110.370002746582</v>
       </c>
       <c r="D25" t="n">
-        <v>107.3369979858398</v>
+        <v>108.5130004882812</v>
       </c>
       <c r="E25" t="n">
-        <v>109.8460006713867</v>
+        <v>109.7020034790039</v>
       </c>
       <c r="F25" t="n">
-        <v>35539000</v>
+        <v>36532000</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -1093,22 +1093,22 @@
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>45967</v>
+        <v>45968</v>
       </c>
       <c r="B26" t="n">
-        <v>109.4580001831055</v>
+        <v>109.4179992675781</v>
       </c>
       <c r="C26" t="n">
-        <v>110.370002746582</v>
+        <v>110.8219985961914</v>
       </c>
       <c r="D26" t="n">
-        <v>108.5130004882812</v>
+        <v>108.75</v>
       </c>
       <c r="E26" t="n">
-        <v>109.7020034790039</v>
+        <v>110.3659973144531</v>
       </c>
       <c r="F26" t="n">
-        <v>36532000</v>
+        <v>44125000</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -1119,22 +1119,22 @@
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>45968</v>
+        <v>45971</v>
       </c>
       <c r="B27" t="n">
-        <v>109.4179992675781</v>
+        <v>110.6719970703125</v>
       </c>
       <c r="C27" t="n">
-        <v>110.8219985961914</v>
+        <v>112.8199996948242</v>
       </c>
       <c r="D27" t="n">
-        <v>108.75</v>
+        <v>110.4049987792969</v>
       </c>
       <c r="E27" t="n">
-        <v>110.3659973144531</v>
+        <v>112.0070037841797</v>
       </c>
       <c r="F27" t="n">
-        <v>44125000</v>
+        <v>36929000</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -1145,22 +1145,22 @@
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>45971</v>
+        <v>45972</v>
       </c>
       <c r="B28" t="n">
-        <v>110.6719970703125</v>
+        <v>111.7600021362305</v>
       </c>
       <c r="C28" t="n">
-        <v>112.8199996948242</v>
+        <v>113.9219970703125</v>
       </c>
       <c r="D28" t="n">
-        <v>110.4049987792969</v>
+        <v>111.2799987792969</v>
       </c>
       <c r="E28" t="n">
-        <v>112.0070037841797</v>
+        <v>113.6439971923828</v>
       </c>
       <c r="F28" t="n">
-        <v>36929000</v>
+        <v>27966000</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
@@ -1171,22 +1171,22 @@
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>45972</v>
+        <v>45973</v>
       </c>
       <c r="B29" t="n">
-        <v>111.7600021362305</v>
+        <v>113.8170013427734</v>
       </c>
       <c r="C29" t="n">
-        <v>113.9219970703125</v>
+        <v>116.4339981079102</v>
       </c>
       <c r="D29" t="n">
-        <v>111.2799987792969</v>
+        <v>112.8259963989258</v>
       </c>
       <c r="E29" t="n">
-        <v>113.6439971923828</v>
+        <v>115.75</v>
       </c>
       <c r="F29" t="n">
-        <v>27966000</v>
+        <v>39221000</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -1197,22 +1197,22 @@
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>45973</v>
+        <v>45974</v>
       </c>
       <c r="B30" t="n">
-        <v>113.8170013427734</v>
+        <v>115.8499984741211</v>
       </c>
       <c r="C30" t="n">
-        <v>116.4339981079102</v>
+        <v>116.7330017089844</v>
       </c>
       <c r="D30" t="n">
-        <v>112.8259963989258</v>
+        <v>114.5690002441406</v>
       </c>
       <c r="E30" t="n">
-        <v>115.75</v>
+        <v>115.4229965209961</v>
       </c>
       <c r="F30" t="n">
-        <v>39221000</v>
+        <v>40144000</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -1223,22 +1223,22 @@
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>45974</v>
+        <v>45975</v>
       </c>
       <c r="B31" t="n">
-        <v>115.8499984741211</v>
+        <v>114.2730026245117</v>
       </c>
       <c r="C31" t="n">
-        <v>116.7330017089844</v>
+        <v>114.2730026245117</v>
       </c>
       <c r="D31" t="n">
-        <v>114.5690002441406</v>
+        <v>110.7210006713867</v>
       </c>
       <c r="E31" t="n">
-        <v>115.4229965209961</v>
+        <v>111.2170028686523</v>
       </c>
       <c r="F31" t="n">
-        <v>40144000</v>
+        <v>47607000</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -1249,74 +1249,74 @@
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>45975</v>
+        <v>45978</v>
       </c>
       <c r="B32" t="n">
-        <v>114.2730026245117</v>
+        <v>110.75</v>
       </c>
       <c r="C32" t="n">
-        <v>114.2730026245117</v>
+        <v>111.8499984741211</v>
       </c>
       <c r="D32" t="n">
-        <v>110.7210006713867</v>
+        <v>109.5500030517578</v>
       </c>
       <c r="E32" t="n">
-        <v>111.2170028686523</v>
+        <v>110.2900009155273</v>
       </c>
       <c r="F32" t="n">
-        <v>47607000</v>
+        <v>26082700</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>45978</v>
+        <v>45979</v>
       </c>
       <c r="B33" t="n">
-        <v>110.75</v>
+        <v>110.2900009155273</v>
       </c>
       <c r="C33" t="n">
-        <v>111.8499984741211</v>
+        <v>115.25</v>
       </c>
       <c r="D33" t="n">
-        <v>109.5500030517578</v>
+        <v>109.1999969482422</v>
       </c>
       <c r="E33" t="n">
-        <v>110.2900009155273</v>
+        <v>114.0899963378906</v>
       </c>
       <c r="F33" t="n">
-        <v>26082700</v>
+        <v>43440600</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>45979</v>
+        <v>45980</v>
       </c>
       <c r="B34" t="n">
-        <v>110.2900009155273</v>
+        <v>113</v>
       </c>
       <c r="C34" t="n">
-        <v>115.25</v>
+        <v>113.3399963378906</v>
       </c>
       <c r="D34" t="n">
-        <v>109.1999969482422</v>
+        <v>108.6100006103516</v>
       </c>
       <c r="E34" t="n">
-        <v>114.0899963378906</v>
+        <v>110</v>
       </c>
       <c r="F34" t="n">
-        <v>43440600</v>
+        <v>31868100</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
@@ -1327,22 +1327,22 @@
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>45980</v>
+        <v>45981</v>
       </c>
       <c r="B35" t="n">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C35" t="n">
-        <v>113.3399963378906</v>
+        <v>111.0999984741211</v>
       </c>
       <c r="D35" t="n">
-        <v>108.6100006103516</v>
+        <v>105.3899993896484</v>
       </c>
       <c r="E35" t="n">
-        <v>110</v>
+        <v>105.6699981689453</v>
       </c>
       <c r="F35" t="n">
-        <v>31868100</v>
+        <v>36918500</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
@@ -1353,22 +1353,22 @@
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>45981</v>
+        <v>45982</v>
       </c>
       <c r="B36" t="n">
-        <v>111</v>
+        <v>105.129997253418</v>
       </c>
       <c r="C36" t="n">
-        <v>111.0999984741211</v>
+        <v>106.5299987792969</v>
       </c>
       <c r="D36" t="n">
-        <v>105.3899993896484</v>
+        <v>103.8099975585938</v>
       </c>
       <c r="E36" t="n">
-        <v>105.6699981689453</v>
+        <v>104.3099975585938</v>
       </c>
       <c r="F36" t="n">
-        <v>36918500</v>
+        <v>41232700</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -1379,22 +1379,22 @@
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>45982</v>
+        <v>45985</v>
       </c>
       <c r="B37" t="n">
-        <v>105.129997253418</v>
+        <v>104.25</v>
       </c>
       <c r="C37" t="n">
-        <v>106.5299987792969</v>
+        <v>108.0400009155273</v>
       </c>
       <c r="D37" t="n">
-        <v>103.8099975585938</v>
+        <v>103.3199996948242</v>
       </c>
       <c r="E37" t="n">
-        <v>104.3099975585938</v>
+        <v>106.9700012207031</v>
       </c>
       <c r="F37" t="n">
-        <v>41232700</v>
+        <v>62918300</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
@@ -1405,22 +1405,22 @@
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>45985</v>
+        <v>45986</v>
       </c>
       <c r="B38" t="n">
-        <v>104.25</v>
+        <v>106.120002746582</v>
       </c>
       <c r="C38" t="n">
-        <v>108.0400009155273</v>
+        <v>106.3000030517578</v>
       </c>
       <c r="D38" t="n">
-        <v>103.3199996948242</v>
+        <v>103.8199996948242</v>
       </c>
       <c r="E38" t="n">
-        <v>106.9700012207031</v>
+        <v>104.4000015258789</v>
       </c>
       <c r="F38" t="n">
-        <v>62918300</v>
+        <v>35122600</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
@@ -1431,22 +1431,22 @@
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>45986</v>
+        <v>45987</v>
       </c>
       <c r="B39" t="n">
-        <v>106.120002746582</v>
+        <v>105.7399978637695</v>
       </c>
       <c r="C39" t="n">
-        <v>106.3000030517578</v>
+        <v>106.9499969482422</v>
       </c>
       <c r="D39" t="n">
-        <v>103.8199996948242</v>
+        <v>105.2200012207031</v>
       </c>
       <c r="E39" t="n">
-        <v>104.4000015258789</v>
+        <v>106.1399993896484</v>
       </c>
       <c r="F39" t="n">
-        <v>35122600</v>
+        <v>27951000</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
@@ -1457,22 +1457,22 @@
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>45987</v>
+        <v>45989</v>
       </c>
       <c r="B40" t="n">
-        <v>105.7399978637695</v>
+        <v>106.4400024414062</v>
       </c>
       <c r="C40" t="n">
-        <v>106.9499969482422</v>
+        <v>107.9400024414062</v>
       </c>
       <c r="D40" t="n">
-        <v>105.2200012207031</v>
+        <v>106.2399978637695</v>
       </c>
       <c r="E40" t="n">
-        <v>106.1399993896484</v>
+        <v>107.5800018310547</v>
       </c>
       <c r="F40" t="n">
-        <v>27951000</v>
+        <v>15021600</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
@@ -1483,22 +1483,22 @@
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>45989</v>
+        <v>45992</v>
       </c>
       <c r="B41" t="n">
-        <v>106.4400024414062</v>
+        <v>106.5100021362305</v>
       </c>
       <c r="C41" t="n">
-        <v>107.9400024414062</v>
+        <v>109.3399963378906</v>
       </c>
       <c r="D41" t="n">
-        <v>106.2399978637695</v>
+        <v>106.3099975585938</v>
       </c>
       <c r="E41" t="n">
-        <v>107.5800018310547</v>
+        <v>109.129997253418</v>
       </c>
       <c r="F41" t="n">
-        <v>15021600</v>
+        <v>24873400</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
@@ -1509,22 +1509,22 @@
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>45992</v>
+        <v>45993</v>
       </c>
       <c r="B42" t="n">
-        <v>106.5100021362305</v>
+        <v>109.2099990844727</v>
       </c>
       <c r="C42" t="n">
-        <v>109.3399963378906</v>
+        <v>109.7300033569336</v>
       </c>
       <c r="D42" t="n">
-        <v>106.3099975585938</v>
+        <v>107.5199966430664</v>
       </c>
       <c r="E42" t="n">
-        <v>109.129997253418</v>
+        <v>109.3499984741211</v>
       </c>
       <c r="F42" t="n">
-        <v>24873400</v>
+        <v>25763000</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
@@ -1535,22 +1535,22 @@
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>45993</v>
+        <v>45994</v>
       </c>
       <c r="B43" t="n">
-        <v>109.2099990844727</v>
+        <v>106.5899963378906</v>
       </c>
       <c r="C43" t="n">
-        <v>109.7300033569336</v>
+        <v>106.870002746582</v>
       </c>
       <c r="D43" t="n">
-        <v>107.5199966430664</v>
+        <v>102.0299987792969</v>
       </c>
       <c r="E43" t="n">
-        <v>109.3499984741211</v>
+        <v>103.9599990844727</v>
       </c>
       <c r="F43" t="n">
-        <v>25763000</v>
+        <v>53593400</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
@@ -1561,22 +1561,22 @@
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
-        <v>45994</v>
+        <v>45995</v>
       </c>
       <c r="B44" t="n">
-        <v>106.5899963378906</v>
+        <v>103.5699996948242</v>
       </c>
       <c r="C44" t="n">
-        <v>106.870002746582</v>
+        <v>103.8000030517578</v>
       </c>
       <c r="D44" t="n">
-        <v>102.0299987792969</v>
+        <v>101.7699966430664</v>
       </c>
       <c r="E44" t="n">
-        <v>103.9599990844727</v>
+        <v>103.2200012207031</v>
       </c>
       <c r="F44" t="n">
-        <v>53593400</v>
+        <v>51779100</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
@@ -1587,22 +1587,22 @@
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
-        <v>45995</v>
+        <v>45996</v>
       </c>
       <c r="B45" t="n">
-        <v>103.5699996948242</v>
+        <v>98.77999877929688</v>
       </c>
       <c r="C45" t="n">
-        <v>103.8000030517578</v>
+        <v>104.7900009155273</v>
       </c>
       <c r="D45" t="n">
-        <v>101.7699966430664</v>
+        <v>97.73999786376953</v>
       </c>
       <c r="E45" t="n">
-        <v>103.2200012207031</v>
+        <v>100.2399978637695</v>
       </c>
       <c r="F45" t="n">
-        <v>51779100</v>
+        <v>133363600</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
@@ -1613,22 +1613,22 @@
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
-        <v>45996</v>
+        <v>45999</v>
       </c>
       <c r="B46" t="n">
-        <v>98.77999877929688</v>
+        <v>99.87000274658203</v>
       </c>
       <c r="C46" t="n">
-        <v>104.7900009155273</v>
+        <v>99.88999938964844</v>
       </c>
       <c r="D46" t="n">
-        <v>97.73999786376953</v>
+        <v>95.30000305175781</v>
       </c>
       <c r="E46" t="n">
-        <v>100.2399978637695</v>
+        <v>96.79000091552734</v>
       </c>
       <c r="F46" t="n">
-        <v>133363600</v>
+        <v>100906300</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
@@ -1639,22 +1639,22 @@
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
-        <v>45999</v>
+        <v>46000</v>
       </c>
       <c r="B47" t="n">
-        <v>99.87000274658203</v>
+        <v>97.02999877929688</v>
       </c>
       <c r="C47" t="n">
-        <v>99.88999938964844</v>
+        <v>97.23999786376953</v>
       </c>
       <c r="D47" t="n">
-        <v>95.30000305175781</v>
+        <v>95.44999694824219</v>
       </c>
       <c r="E47" t="n">
-        <v>96.79000091552734</v>
+        <v>96.70999908447266</v>
       </c>
       <c r="F47" t="n">
-        <v>100906300</v>
+        <v>51745600</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
@@ -1665,22 +1665,22 @@
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
-        <v>46000</v>
+        <v>46001</v>
       </c>
       <c r="B48" t="n">
-        <v>97.02999877929688</v>
+        <v>96.73999786376953</v>
       </c>
       <c r="C48" t="n">
-        <v>97.23999786376953</v>
+        <v>96.97000122070312</v>
       </c>
       <c r="D48" t="n">
-        <v>95.44999694824219</v>
+        <v>92.34999847412109</v>
       </c>
       <c r="E48" t="n">
-        <v>96.70999908447266</v>
+        <v>92.70999908447266</v>
       </c>
       <c r="F48" t="n">
-        <v>51745600</v>
+        <v>74129300</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
@@ -1691,22 +1691,22 @@
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>46001</v>
+        <v>46002</v>
       </c>
       <c r="B49" t="n">
-        <v>96.73999786376953</v>
+        <v>93.90000152587891</v>
       </c>
       <c r="C49" t="n">
-        <v>96.97000122070312</v>
+        <v>94.81999969482422</v>
       </c>
       <c r="D49" t="n">
-        <v>92.34999847412109</v>
+        <v>92.76000213623047</v>
       </c>
       <c r="E49" t="n">
-        <v>92.70999908447266</v>
+        <v>94.08999633789062</v>
       </c>
       <c r="F49" t="n">
-        <v>74129300</v>
+        <v>43949000</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
@@ -1717,22 +1717,22 @@
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>46002</v>
+        <v>46003</v>
       </c>
       <c r="B50" t="n">
-        <v>93.90000152587891</v>
+        <v>95.5</v>
       </c>
       <c r="C50" t="n">
-        <v>94.81999969482422</v>
+        <v>96.91999816894531</v>
       </c>
       <c r="D50" t="n">
-        <v>92.76000213623047</v>
+        <v>94.65000152587891</v>
       </c>
       <c r="E50" t="n">
-        <v>94.08999633789062</v>
+        <v>95.19000244140625</v>
       </c>
       <c r="F50" t="n">
-        <v>43949000</v>
+        <v>49323100</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
-        <v>46003</v>
+        <v>46006</v>
       </c>
       <c r="B51" t="n">
-        <v>95.5</v>
+        <v>96.01999664306641</v>
       </c>
       <c r="C51" t="n">
-        <v>96.91999816894531</v>
+        <v>96.37000274658203</v>
       </c>
       <c r="D51" t="n">
-        <v>94.65000152587891</v>
+        <v>93.52999877929688</v>
       </c>
       <c r="E51" t="n">
-        <v>95.19000244140625</v>
+        <v>93.76999664306641</v>
       </c>
       <c r="F51" t="n">
-        <v>49323100</v>
+        <v>40016500</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
@@ -1769,22 +1769,22 @@
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
-        <v>46006</v>
+        <v>46007</v>
       </c>
       <c r="B52" t="n">
-        <v>96.01999664306641</v>
+        <v>93.87999725341797</v>
       </c>
       <c r="C52" t="n">
-        <v>96.37000274658203</v>
+        <v>94.93000030517578</v>
       </c>
       <c r="D52" t="n">
-        <v>93.52999877929688</v>
+        <v>93.31999969482422</v>
       </c>
       <c r="E52" t="n">
-        <v>93.76999664306641</v>
+        <v>94.56999969482422</v>
       </c>
       <c r="F52" t="n">
-        <v>40016500</v>
+        <v>34265000</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
@@ -1795,22 +1795,22 @@
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
-        <v>46007</v>
+        <v>46008</v>
       </c>
       <c r="B53" t="n">
-        <v>93.87999725341797</v>
+        <v>95.98000335693359</v>
       </c>
       <c r="C53" t="n">
-        <v>94.93000030517578</v>
+        <v>97.33000183105469</v>
       </c>
       <c r="D53" t="n">
-        <v>93.31999969482422</v>
+        <v>94.45999908447266</v>
       </c>
       <c r="E53" t="n">
-        <v>94.56999969482422</v>
+        <v>94.79000091552734</v>
       </c>
       <c r="F53" t="n">
-        <v>34265000</v>
+        <v>50472800</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
@@ -1821,22 +1821,22 @@
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
-        <v>46008</v>
+        <v>46009</v>
       </c>
       <c r="B54" t="n">
-        <v>95.98000335693359</v>
+        <v>95.01999664306641</v>
       </c>
       <c r="C54" t="n">
-        <v>97.33000183105469</v>
+        <v>95.80999755859375</v>
       </c>
       <c r="D54" t="n">
-        <v>94.45999908447266</v>
+        <v>93.58999633789062</v>
       </c>
       <c r="E54" t="n">
-        <v>94.79000091552734</v>
+        <v>94</v>
       </c>
       <c r="F54" t="n">
-        <v>50472800</v>
+        <v>37244700</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
@@ -1847,22 +1847,22 @@
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
-        <v>46009</v>
+        <v>46010</v>
       </c>
       <c r="B55" t="n">
-        <v>95.01999664306641</v>
+        <v>93.56999969482422</v>
       </c>
       <c r="C55" t="n">
-        <v>95.80999755859375</v>
+        <v>95.54000091552734</v>
       </c>
       <c r="D55" t="n">
-        <v>93.58999633789062</v>
+        <v>93.44999694824219</v>
       </c>
       <c r="E55" t="n">
-        <v>94</v>
+        <v>94.38999938964844</v>
       </c>
       <c r="F55" t="n">
-        <v>37244700</v>
+        <v>78990200</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
@@ -1873,22 +1873,22 @@
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
-        <v>46010</v>
+        <v>46013</v>
       </c>
       <c r="B56" t="n">
-        <v>93.56999969482422</v>
+        <v>94.70999908447266</v>
       </c>
       <c r="C56" t="n">
-        <v>95.54000091552734</v>
+        <v>94.70999908447266</v>
       </c>
       <c r="D56" t="n">
-        <v>93.44999694824219</v>
+        <v>92.91000366210938</v>
       </c>
       <c r="E56" t="n">
-        <v>94.38999938964844</v>
+        <v>93.23000335693359</v>
       </c>
       <c r="F56" t="n">
-        <v>78990200</v>
+        <v>39484800</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
@@ -1899,22 +1899,22 @@
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
-        <v>46013</v>
+        <v>46014</v>
       </c>
       <c r="B57" t="n">
-        <v>94.70999908447266</v>
+        <v>93.40000152587891</v>
       </c>
       <c r="C57" t="n">
-        <v>94.70999908447266</v>
+        <v>93.80999755859375</v>
       </c>
       <c r="D57" t="n">
-        <v>92.91000366210938</v>
+        <v>91.33000183105469</v>
       </c>
       <c r="E57" t="n">
-        <v>93.23000335693359</v>
+        <v>93.5</v>
       </c>
       <c r="F57" t="n">
-        <v>39484800</v>
+        <v>25896200</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
@@ -1925,22 +1925,22 @@
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
-        <v>46014</v>
+        <v>46015</v>
       </c>
       <c r="B58" t="n">
-        <v>93.40000152587891</v>
+        <v>93.11000061035156</v>
       </c>
       <c r="C58" t="n">
-        <v>93.80999755859375</v>
+        <v>93.68000030517578</v>
       </c>
       <c r="D58" t="n">
-        <v>91.33000183105469</v>
+        <v>92.66999816894531</v>
       </c>
       <c r="E58" t="n">
-        <v>93.5</v>
+        <v>93.63999938964844</v>
       </c>
       <c r="F58" t="n">
-        <v>25896200</v>
+        <v>12427900</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
@@ -1951,22 +1951,22 @@
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
-        <v>46015</v>
+        <v>46017</v>
       </c>
       <c r="B59" t="n">
-        <v>93.11000061035156</v>
+        <v>93.48000335693359</v>
       </c>
       <c r="C59" t="n">
-        <v>93.68000030517578</v>
+        <v>94.69000244140625</v>
       </c>
       <c r="D59" t="n">
-        <v>92.66999816894531</v>
+        <v>93.26999664306641</v>
       </c>
       <c r="E59" t="n">
-        <v>93.63999938964844</v>
+        <v>94.47000122070312</v>
       </c>
       <c r="F59" t="n">
-        <v>12427900</v>
+        <v>22068300</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
@@ -1977,22 +1977,22 @@
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
-        <v>46017</v>
+        <v>46020</v>
       </c>
       <c r="B60" t="n">
-        <v>93.48000335693359</v>
+        <v>93.98999786376953</v>
       </c>
       <c r="C60" t="n">
-        <v>94.69000244140625</v>
+        <v>94.97000122070312</v>
       </c>
       <c r="D60" t="n">
-        <v>93.26999664306641</v>
+        <v>93.62999725341797</v>
       </c>
       <c r="E60" t="n">
-        <v>94.47000122070312</v>
+        <v>94.15000152587891</v>
       </c>
       <c r="F60" t="n">
-        <v>22068300</v>
+        <v>24493700</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
@@ -2003,22 +2003,22 @@
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
-        <v>46020</v>
+        <v>46021</v>
       </c>
       <c r="B61" t="n">
+        <v>93.51999664306641</v>
+      </c>
+      <c r="C61" t="n">
         <v>93.98999786376953</v>
       </c>
-      <c r="C61" t="n">
-        <v>94.97000122070312</v>
-      </c>
       <c r="D61" t="n">
-        <v>93.62999725341797</v>
+        <v>93.33999633789062</v>
       </c>
       <c r="E61" t="n">
-        <v>94.15000152587891</v>
+        <v>93.77999877929688</v>
       </c>
       <c r="F61" t="n">
-        <v>24493700</v>
+        <v>23422000</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
@@ -2029,22 +2029,22 @@
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
-        <v>46021</v>
+        <v>46022</v>
       </c>
       <c r="B62" t="n">
-        <v>93.51999664306641</v>
+        <v>93.59999847412109</v>
       </c>
       <c r="C62" t="n">
-        <v>93.98999786376953</v>
+        <v>94.30999755859375</v>
       </c>
       <c r="D62" t="n">
-        <v>93.33999633789062</v>
+        <v>93.19999694824219</v>
       </c>
       <c r="E62" t="n">
-        <v>93.77999877929688</v>
+        <v>93.76000213623047</v>
       </c>
       <c r="F62" t="n">
-        <v>23422000</v>
+        <v>23495200</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
@@ -2055,22 +2055,22 @@
     </row>
     <row r="63">
       <c r="A63" s="1" t="n">
-        <v>46022</v>
+        <v>46024</v>
       </c>
       <c r="B63" t="n">
-        <v>93.59999847412109</v>
+        <v>94.12999725341797</v>
       </c>
       <c r="C63" t="n">
-        <v>94.30999755859375</v>
+        <v>94.12999725341797</v>
       </c>
       <c r="D63" t="n">
-        <v>93.19999694824219</v>
+        <v>90.80999755859375</v>
       </c>
       <c r="E63" t="n">
-        <v>93.76000213623047</v>
+        <v>90.98999786376953</v>
       </c>
       <c r="F63" t="n">
-        <v>23495200</v>
+        <v>41155400</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
@@ -2081,22 +2081,22 @@
     </row>
     <row r="64">
       <c r="A64" s="1" t="n">
-        <v>46024</v>
+        <v>46027</v>
       </c>
       <c r="B64" t="n">
-        <v>94.12999725341797</v>
+        <v>90.91999816894531</v>
       </c>
       <c r="C64" t="n">
-        <v>94.12999725341797</v>
+        <v>92.62999725341797</v>
       </c>
       <c r="D64" t="n">
-        <v>90.80999755859375</v>
+        <v>90.83999633789062</v>
       </c>
       <c r="E64" t="n">
-        <v>90.98999786376953</v>
+        <v>91.45999908447266</v>
       </c>
       <c r="F64" t="n">
-        <v>41155400</v>
+        <v>39183300</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
@@ -2107,22 +2107,22 @@
     </row>
     <row r="65">
       <c r="A65" s="1" t="n">
-        <v>46027</v>
+        <v>46028</v>
       </c>
       <c r="B65" t="n">
-        <v>90.91999816894531</v>
+        <v>91.54000091552734</v>
       </c>
       <c r="C65" t="n">
-        <v>92.62999725341797</v>
+        <v>91.63999938964844</v>
       </c>
       <c r="D65" t="n">
-        <v>90.83999633789062</v>
+        <v>89.73999786376953</v>
       </c>
       <c r="E65" t="n">
-        <v>91.45999908447266</v>
+        <v>90.65000152587891</v>
       </c>
       <c r="F65" t="n">
-        <v>39183300</v>
+        <v>43331000</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
@@ -2133,22 +2133,22 @@
     </row>
     <row r="66">
       <c r="A66" s="1" t="n">
-        <v>46028</v>
+        <v>46029</v>
       </c>
       <c r="B66" t="n">
-        <v>91.54000091552734</v>
+        <v>91.55999755859375</v>
       </c>
       <c r="C66" t="n">
-        <v>91.63999938964844</v>
+        <v>92.41999816894531</v>
       </c>
       <c r="D66" t="n">
-        <v>89.73999786376953</v>
+        <v>90.05999755859375</v>
       </c>
       <c r="E66" t="n">
-        <v>90.65000152587891</v>
+        <v>90.73000335693359</v>
       </c>
       <c r="F66" t="n">
-        <v>43331000</v>
+        <v>36525700</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
@@ -2159,22 +2159,22 @@
     </row>
     <row r="67">
       <c r="A67" s="1" t="n">
-        <v>46029</v>
+        <v>46030</v>
       </c>
       <c r="B67" t="n">
-        <v>91.55999755859375</v>
+        <v>90.44999694824219</v>
       </c>
       <c r="C67" t="n">
-        <v>92.41999816894531</v>
+        <v>91.25</v>
       </c>
       <c r="D67" t="n">
-        <v>90.05999755859375</v>
+        <v>89.58000183105469</v>
       </c>
       <c r="E67" t="n">
-        <v>90.73000335693359</v>
+        <v>90.52999877929688</v>
       </c>
       <c r="F67" t="n">
-        <v>36525700</v>
+        <v>40068700</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
@@ -2185,22 +2185,22 @@
     </row>
     <row r="68">
       <c r="A68" s="1" t="n">
-        <v>46030</v>
+        <v>46031</v>
       </c>
       <c r="B68" t="n">
-        <v>90.44999694824219</v>
+        <v>90.02999877929688</v>
       </c>
       <c r="C68" t="n">
-        <v>91.25</v>
+        <v>90.05000305175781</v>
       </c>
       <c r="D68" t="n">
-        <v>89.58000183105469</v>
+        <v>88.31999969482422</v>
       </c>
       <c r="E68" t="n">
-        <v>90.52999877929688</v>
+        <v>89.45999908447266</v>
       </c>
       <c r="F68" t="n">
-        <v>40068700</v>
+        <v>55579500</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
@@ -2211,22 +2211,22 @@
     </row>
     <row r="69">
       <c r="A69" s="1" t="n">
-        <v>46031</v>
+        <v>46034</v>
       </c>
       <c r="B69" t="n">
-        <v>90.02999877929688</v>
+        <v>89.69000244140625</v>
       </c>
       <c r="C69" t="n">
-        <v>90.05000305175781</v>
+        <v>90.33999633789062</v>
       </c>
       <c r="D69" t="n">
-        <v>88.31999969482422</v>
+        <v>89.33000183105469</v>
       </c>
       <c r="E69" t="n">
-        <v>89.45999908447266</v>
+        <v>89.41000366210938</v>
       </c>
       <c r="F69" t="n">
-        <v>55579500</v>
+        <v>36290600</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
@@ -2237,22 +2237,22 @@
     </row>
     <row r="70">
       <c r="A70" s="1" t="n">
-        <v>46034</v>
+        <v>46035</v>
       </c>
       <c r="B70" t="n">
-        <v>89.69000244140625</v>
+        <v>89.44000244140625</v>
       </c>
       <c r="C70" t="n">
-        <v>90.33999633789062</v>
+        <v>91.15000152587891</v>
       </c>
       <c r="D70" t="n">
-        <v>89.33000183105469</v>
+        <v>89.06999969482422</v>
       </c>
       <c r="E70" t="n">
-        <v>89.41000366210938</v>
+        <v>90.31999969482422</v>
       </c>
       <c r="F70" t="n">
-        <v>36290600</v>
+        <v>45221100</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
@@ -2263,22 +2263,22 @@
     </row>
     <row r="71">
       <c r="A71" s="1" t="n">
-        <v>46035</v>
+        <v>46036</v>
       </c>
       <c r="B71" t="n">
-        <v>89.44000244140625</v>
+        <v>91.23999786376953</v>
       </c>
       <c r="C71" t="n">
-        <v>91.15000152587891</v>
+        <v>91.58000183105469</v>
       </c>
       <c r="D71" t="n">
-        <v>89.06999969482422</v>
+        <v>87.94999694824219</v>
       </c>
       <c r="E71" t="n">
-        <v>90.31999969482422</v>
+        <v>88.55000305175781</v>
       </c>
       <c r="F71" t="n">
-        <v>45221100</v>
+        <v>49737700</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
@@ -2289,22 +2289,22 @@
     </row>
     <row r="72">
       <c r="A72" s="1" t="n">
-        <v>46036</v>
+        <v>46037</v>
       </c>
       <c r="B72" t="n">
-        <v>91.23999786376953</v>
+        <v>89.01999664306641</v>
       </c>
       <c r="C72" t="n">
-        <v>91.58000183105469</v>
+        <v>89.88999938964844</v>
       </c>
       <c r="D72" t="n">
-        <v>87.94999694824219</v>
+        <v>87.81999969482422</v>
       </c>
       <c r="E72" t="n">
-        <v>88.55000305175781</v>
+        <v>88.05000305175781</v>
       </c>
       <c r="F72" t="n">
-        <v>49737700</v>
+        <v>36945100</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
@@ -2315,22 +2315,22 @@
     </row>
     <row r="73">
       <c r="A73" s="1" t="n">
-        <v>46037</v>
+        <v>46038</v>
       </c>
       <c r="B73" t="n">
-        <v>89.01999664306641</v>
+        <v>88.33999633789062</v>
       </c>
       <c r="C73" t="n">
-        <v>89.88999938964844</v>
+        <v>88.51000213623047</v>
       </c>
       <c r="D73" t="n">
-        <v>87.81999969482422</v>
+        <v>87.77999877929688</v>
       </c>
       <c r="E73" t="n">
-        <v>88.05000305175781</v>
+        <v>88</v>
       </c>
       <c r="F73" t="n">
-        <v>36945100</v>
+        <v>48130500</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
@@ -2341,22 +2341,22 @@
     </row>
     <row r="74">
       <c r="A74" s="1" t="n">
-        <v>46038</v>
+        <v>46042</v>
       </c>
       <c r="B74" t="n">
-        <v>88.33999633789062</v>
+        <v>88.97000122070312</v>
       </c>
       <c r="C74" t="n">
-        <v>88.51000213623047</v>
+        <v>89.90000152587891</v>
       </c>
       <c r="D74" t="n">
-        <v>87.77999877929688</v>
+        <v>87.01999664306641</v>
       </c>
       <c r="E74" t="n">
-        <v>88</v>
+        <v>87.26000213623047</v>
       </c>
       <c r="F74" t="n">
-        <v>48130500</v>
+        <v>109729700</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
@@ -2367,22 +2367,22 @@
     </row>
     <row r="75">
       <c r="A75" s="1" t="n">
-        <v>46042</v>
+        <v>46043</v>
       </c>
       <c r="B75" t="n">
-        <v>88.97000122070312</v>
+        <v>82.51999664306641</v>
       </c>
       <c r="C75" t="n">
-        <v>89.90000152587891</v>
+        <v>86</v>
       </c>
       <c r="D75" t="n">
-        <v>87.01999664306641</v>
+        <v>81.93000030517578</v>
       </c>
       <c r="E75" t="n">
-        <v>87.26000213623047</v>
+        <v>85.36000061035156</v>
       </c>
       <c r="F75" t="n">
-        <v>109729700</v>
+        <v>127940700</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
@@ -2393,22 +2393,22 @@
     </row>
     <row r="76">
       <c r="A76" s="1" t="n">
-        <v>46043</v>
+        <v>46044</v>
       </c>
       <c r="B76" t="n">
-        <v>82.51999664306641</v>
+        <v>85.01999664306641</v>
       </c>
       <c r="C76" t="n">
-        <v>86</v>
+        <v>85.09999847412109</v>
       </c>
       <c r="D76" t="n">
-        <v>81.93000030517578</v>
+        <v>82.98000335693359</v>
       </c>
       <c r="E76" t="n">
-        <v>85.36000061035156</v>
+        <v>83.54000091552734</v>
       </c>
       <c r="F76" t="n">
-        <v>127940700</v>
+        <v>69113300</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
@@ -2419,22 +2419,22 @@
     </row>
     <row r="77">
       <c r="A77" s="1" t="n">
-        <v>46044</v>
+        <v>46045</v>
       </c>
       <c r="B77" t="n">
-        <v>85.01999664306641</v>
+        <v>83.43000030517578</v>
       </c>
       <c r="C77" t="n">
-        <v>85.09999847412109</v>
+        <v>86.30000305175781</v>
       </c>
       <c r="D77" t="n">
-        <v>82.98000335693359</v>
+        <v>83.27999877929688</v>
       </c>
       <c r="E77" t="n">
-        <v>83.54000091552734</v>
+        <v>86.12000274658203</v>
       </c>
       <c r="F77" t="n">
-        <v>69113300</v>
+        <v>64520400</v>
       </c>
       <c r="G77" t="n">
         <v>0</v>
@@ -2445,22 +2445,22 @@
     </row>
     <row r="78">
       <c r="A78" s="1" t="n">
-        <v>46045</v>
+        <v>46048</v>
       </c>
       <c r="B78" t="n">
-        <v>83.43000030517578</v>
+        <v>86.91999816894531</v>
       </c>
       <c r="C78" t="n">
-        <v>86.30000305175781</v>
+        <v>86.94000244140625</v>
       </c>
       <c r="D78" t="n">
-        <v>83.27999877929688</v>
+        <v>85.34999847412109</v>
       </c>
       <c r="E78" t="n">
-        <v>86.12000274658203</v>
+        <v>85.69999694824219</v>
       </c>
       <c r="F78" t="n">
-        <v>64520400</v>
+        <v>40941900</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
@@ -2471,22 +2471,22 @@
     </row>
     <row r="79">
       <c r="A79" s="1" t="n">
-        <v>46048</v>
+        <v>46049</v>
       </c>
       <c r="B79" t="n">
-        <v>86.91999816894531</v>
+        <v>85.27999877929688</v>
       </c>
       <c r="C79" t="n">
-        <v>86.94000244140625</v>
+        <v>85.59999847412109</v>
       </c>
       <c r="D79" t="n">
-        <v>85.34999847412109</v>
+        <v>83.87999725341797</v>
       </c>
       <c r="E79" t="n">
-        <v>85.69999694824219</v>
+        <v>85.58000183105469</v>
       </c>
       <c r="F79" t="n">
-        <v>40941900</v>
+        <v>37790800</v>
       </c>
       <c r="G79" t="n">
         <v>0</v>
@@ -2497,22 +2497,22 @@
     </row>
     <row r="80">
       <c r="A80" s="1" t="n">
-        <v>46049</v>
+        <v>46050</v>
       </c>
       <c r="B80" t="n">
-        <v>85.27999877929688</v>
+        <v>85.62999725341797</v>
       </c>
       <c r="C80" t="n">
-        <v>85.59999847412109</v>
+        <v>86.47000122070312</v>
       </c>
       <c r="D80" t="n">
-        <v>83.87999725341797</v>
+        <v>84.30000305175781</v>
       </c>
       <c r="E80" t="n">
-        <v>85.58000183105469</v>
+        <v>84.63999938964844</v>
       </c>
       <c r="F80" t="n">
-        <v>37790800</v>
+        <v>37762600</v>
       </c>
       <c r="G80" t="n">
         <v>0</v>
@@ -2523,22 +2523,22 @@
     </row>
     <row r="81">
       <c r="A81" s="1" t="n">
-        <v>46050</v>
+        <v>46051</v>
       </c>
       <c r="B81" t="n">
-        <v>85.62999725341797</v>
+        <v>84.30999755859375</v>
       </c>
       <c r="C81" t="n">
-        <v>86.47000122070312</v>
+        <v>84.37999725341797</v>
       </c>
       <c r="D81" t="n">
-        <v>84.30000305175781</v>
+        <v>82.34999847412109</v>
       </c>
       <c r="E81" t="n">
-        <v>84.63999938964844</v>
+        <v>83.16000366210938</v>
       </c>
       <c r="F81" t="n">
-        <v>37762600</v>
+        <v>42278100</v>
       </c>
       <c r="G81" t="n">
         <v>0</v>
@@ -2549,22 +2549,22 @@
     </row>
     <row r="82">
       <c r="A82" s="1" t="n">
-        <v>46051</v>
+        <v>46052</v>
       </c>
       <c r="B82" t="n">
-        <v>84.30999755859375</v>
+        <v>83.09999847412109</v>
       </c>
       <c r="C82" t="n">
-        <v>84.37999725341797</v>
+        <v>84.05999755859375</v>
       </c>
       <c r="D82" t="n">
-        <v>82.34999847412109</v>
+        <v>82.77999877929688</v>
       </c>
       <c r="E82" t="n">
-        <v>83.16000366210938</v>
+        <v>83.48999786376953</v>
       </c>
       <c r="F82" t="n">
-        <v>42278100</v>
+        <v>45755000</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
@@ -2575,22 +2575,22 @@
     </row>
     <row r="83">
       <c r="A83" s="1" t="n">
-        <v>46052</v>
+        <v>46055</v>
       </c>
       <c r="B83" t="n">
-        <v>83.09999847412109</v>
+        <v>83.52999877929688</v>
       </c>
       <c r="C83" t="n">
-        <v>84.05999755859375</v>
+        <v>85.26999664306641</v>
       </c>
       <c r="D83" t="n">
-        <v>82.77999877929688</v>
+        <v>82.72000122070312</v>
       </c>
       <c r="E83" t="n">
-        <v>83.48999786376953</v>
+        <v>82.76000213623047</v>
       </c>
       <c r="F83" t="n">
-        <v>45755000</v>
+        <v>41445300</v>
       </c>
       <c r="G83" t="n">
         <v>0</v>
@@ -2601,22 +2601,22 @@
     </row>
     <row r="84">
       <c r="A84" s="1" t="n">
-        <v>46055</v>
+        <v>46056</v>
       </c>
       <c r="B84" t="n">
-        <v>83.52999877929688</v>
+        <v>82.23000335693359</v>
       </c>
       <c r="C84" t="n">
-        <v>85.26999664306641</v>
+        <v>82.44999694824219</v>
       </c>
       <c r="D84" t="n">
-        <v>82.72000122070312</v>
+        <v>79.62000274658203</v>
       </c>
       <c r="E84" t="n">
-        <v>82.76000213623047</v>
+        <v>79.94000244140625</v>
       </c>
       <c r="F84" t="n">
-        <v>41445300</v>
+        <v>49789000</v>
       </c>
       <c r="G84" t="n">
         <v>0</v>
@@ -2627,22 +2627,22 @@
     </row>
     <row r="85">
       <c r="A85" s="1" t="n">
-        <v>46056</v>
+        <v>46057</v>
       </c>
       <c r="B85" t="n">
-        <v>82.23000335693359</v>
+        <v>79.98999786376953</v>
       </c>
       <c r="C85" t="n">
-        <v>82.44999694824219</v>
+        <v>81.44000244140625</v>
       </c>
       <c r="D85" t="n">
-        <v>79.62000274658203</v>
+        <v>79.23000335693359</v>
       </c>
       <c r="E85" t="n">
-        <v>79.94000244140625</v>
+        <v>80.16000366210938</v>
       </c>
       <c r="F85" t="n">
-        <v>49789000</v>
+        <v>48963200</v>
       </c>
       <c r="G85" t="n">
         <v>0</v>
@@ -2653,22 +2653,22 @@
     </row>
     <row r="86">
       <c r="A86" s="1" t="n">
-        <v>46057</v>
+        <v>46058</v>
       </c>
       <c r="B86" t="n">
-        <v>79.98999786376953</v>
+        <v>81.48999786376953</v>
       </c>
       <c r="C86" t="n">
-        <v>81.44000244140625</v>
+        <v>83.30000305175781</v>
       </c>
       <c r="D86" t="n">
-        <v>79.23000335693359</v>
+        <v>80.54000091552734</v>
       </c>
       <c r="E86" t="n">
-        <v>80.16000366210938</v>
+        <v>80.87000274658203</v>
       </c>
       <c r="F86" t="n">
-        <v>48963200</v>
+        <v>54805700</v>
       </c>
       <c r="G86" t="n">
         <v>0</v>
@@ -2679,22 +2679,22 @@
     </row>
     <row r="87">
       <c r="A87" s="1" t="n">
-        <v>46058</v>
+        <v>46059</v>
       </c>
       <c r="B87" t="n">
-        <v>81.48999786376953</v>
+        <v>81.01999664306641</v>
       </c>
       <c r="C87" t="n">
-        <v>83.30000305175781</v>
+        <v>82.48999786376953</v>
       </c>
       <c r="D87" t="n">
-        <v>80.54000091552734</v>
+        <v>80.65000152587891</v>
       </c>
       <c r="E87" t="n">
-        <v>80.87000274658203</v>
+        <v>82.19999694824219</v>
       </c>
       <c r="F87" t="n">
-        <v>54805700</v>
+        <v>46154100</v>
       </c>
       <c r="G87" t="n">
         <v>0</v>
@@ -2705,22 +2705,22 @@
     </row>
     <row r="88">
       <c r="A88" s="1" t="n">
-        <v>46059</v>
+        <v>46062</v>
       </c>
       <c r="B88" t="n">
-        <v>81.01999664306641</v>
+        <v>82.18000030517578</v>
       </c>
       <c r="C88" t="n">
-        <v>82.48999786376953</v>
+        <v>82.20999908447266</v>
       </c>
       <c r="D88" t="n">
-        <v>80.65000152587891</v>
+        <v>79.87000274658203</v>
       </c>
       <c r="E88" t="n">
-        <v>82.19999694824219</v>
+        <v>81.47000122070312</v>
       </c>
       <c r="F88" t="n">
-        <v>46154100</v>
+        <v>42200200</v>
       </c>
       <c r="G88" t="n">
         <v>0</v>
@@ -2731,22 +2731,22 @@
     </row>
     <row r="89">
       <c r="A89" s="1" t="n">
-        <v>46062</v>
+        <v>46063</v>
       </c>
       <c r="B89" t="n">
-        <v>82.18000030517578</v>
+        <v>82.72000122070312</v>
       </c>
       <c r="C89" t="n">
+        <v>84.66000366210938</v>
+      </c>
+      <c r="D89" t="n">
+        <v>82.08999633789062</v>
+      </c>
+      <c r="E89" t="n">
         <v>82.20999908447266</v>
       </c>
-      <c r="D89" t="n">
-        <v>79.87000274658203</v>
-      </c>
-      <c r="E89" t="n">
-        <v>81.47000122070312</v>
-      </c>
       <c r="F89" t="n">
-        <v>42200200</v>
+        <v>43595800</v>
       </c>
       <c r="G89" t="n">
         <v>0</v>
@@ -2757,22 +2757,22 @@
     </row>
     <row r="90">
       <c r="A90" s="1" t="n">
-        <v>46063</v>
+        <v>46064</v>
       </c>
       <c r="B90" t="n">
-        <v>82.72000122070312</v>
+        <v>81.95999908447266</v>
       </c>
       <c r="C90" t="n">
-        <v>84.66000366210938</v>
+        <v>82.48000335693359</v>
       </c>
       <c r="D90" t="n">
-        <v>82.08999633789062</v>
+        <v>79.44999694824219</v>
       </c>
       <c r="E90" t="n">
-        <v>82.20999908447266</v>
+        <v>79.62000274658203</v>
       </c>
       <c r="F90" t="n">
-        <v>43595800</v>
+        <v>40840300</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
@@ -2783,22 +2783,22 @@
     </row>
     <row r="91">
       <c r="A91" s="1" t="n">
-        <v>46064</v>
+        <v>46065</v>
       </c>
       <c r="B91" t="n">
-        <v>81.95999908447266</v>
+        <v>79.11000061035156</v>
       </c>
       <c r="C91" t="n">
-        <v>82.48000335693359</v>
+        <v>79.15000152587891</v>
       </c>
       <c r="D91" t="n">
-        <v>79.44999694824219</v>
+        <v>75.23000335693359</v>
       </c>
       <c r="E91" t="n">
-        <v>79.62000274658203</v>
+        <v>75.86000061035156</v>
       </c>
       <c r="F91" t="n">
-        <v>40840300</v>
+        <v>73516100</v>
       </c>
       <c r="G91" t="n">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="92">
       <c r="A92" s="1" t="n">
-        <v>46065</v>
+        <v>46066</v>
       </c>
       <c r="B92" t="n">
-        <v>79.11000061035156</v>
+        <v>76.13999938964844</v>
       </c>
       <c r="C92" t="n">
-        <v>79.15000152587891</v>
+        <v>77.18000030517578</v>
       </c>
       <c r="D92" t="n">
-        <v>75.23000335693359</v>
+        <v>75.52999877929688</v>
       </c>
       <c r="E92" t="n">
-        <v>75.86000061035156</v>
+        <v>76.87000274658203</v>
       </c>
       <c r="F92" t="n">
-        <v>73516100</v>
+        <v>42292100</v>
       </c>
       <c r="G92" t="n">
         <v>0</v>
@@ -2835,22 +2835,22 @@
     </row>
     <row r="93">
       <c r="A93" s="1" t="n">
-        <v>46066</v>
+        <v>46070</v>
       </c>
       <c r="B93" t="n">
-        <v>76.13999938964844</v>
+        <v>76.91999816894531</v>
       </c>
       <c r="C93" t="n">
-        <v>77.18000030517578</v>
+        <v>77.87000274658203</v>
       </c>
       <c r="D93" t="n">
-        <v>75.52999877929688</v>
+        <v>75.30000305175781</v>
       </c>
       <c r="E93" t="n">
-        <v>76.87000274658203</v>
+        <v>77</v>
       </c>
       <c r="F93" t="n">
-        <v>42292100</v>
+        <v>35961500</v>
       </c>
       <c r="G93" t="n">
         <v>0</v>
@@ -2861,22 +2861,22 @@
     </row>
     <row r="94">
       <c r="A94" s="1" t="n">
-        <v>46070</v>
+        <v>46071</v>
       </c>
       <c r="B94" t="n">
-        <v>76.91999816894531</v>
+        <v>77.31999969482422</v>
       </c>
       <c r="C94" t="n">
-        <v>77.87000274658203</v>
+        <v>78.31999969482422</v>
       </c>
       <c r="D94" t="n">
-        <v>75.30000305175781</v>
+        <v>76.27999877929688</v>
       </c>
       <c r="E94" t="n">
-        <v>77</v>
+        <v>77.98999786376953</v>
       </c>
       <c r="F94" t="n">
-        <v>35961500</v>
+        <v>29883100</v>
       </c>
       <c r="G94" t="n">
         <v>0</v>
@@ -2887,22 +2887,22 @@
     </row>
     <row r="95">
       <c r="A95" s="1" t="n">
-        <v>46071</v>
+        <v>46072</v>
       </c>
       <c r="B95" t="n">
-        <v>77.31999969482422</v>
+        <v>77.75</v>
       </c>
       <c r="C95" t="n">
-        <v>78.31999969482422</v>
+        <v>78.69999694824219</v>
       </c>
       <c r="D95" t="n">
-        <v>76.27999877929688</v>
+        <v>76.58999633789062</v>
       </c>
       <c r="E95" t="n">
-        <v>77.98999786376953</v>
+        <v>77</v>
       </c>
       <c r="F95" t="n">
-        <v>29883100</v>
+        <v>30139200</v>
       </c>
       <c r="G95" t="n">
         <v>0</v>
@@ -2913,22 +2913,22 @@
     </row>
     <row r="96">
       <c r="A96" s="1" t="n">
-        <v>46072</v>
+        <v>46073</v>
       </c>
       <c r="B96" t="n">
-        <v>77.75</v>
+        <v>76.61000061035156</v>
       </c>
       <c r="C96" t="n">
-        <v>78.69999694824219</v>
+        <v>78.84999847412109</v>
       </c>
       <c r="D96" t="n">
-        <v>76.58999633789062</v>
+        <v>76.40000152587891</v>
       </c>
       <c r="E96" t="n">
-        <v>77</v>
+        <v>78.66999816894531</v>
       </c>
       <c r="F96" t="n">
-        <v>30139200</v>
+        <v>32411300</v>
       </c>
       <c r="G96" t="n">
         <v>0</v>
@@ -2939,22 +2939,22 @@
     </row>
     <row r="97">
       <c r="A97" s="1" t="n">
-        <v>46073</v>
+        <v>46076</v>
       </c>
       <c r="B97" t="n">
-        <v>76.61000061035156</v>
+        <v>77.79000091552734</v>
       </c>
       <c r="C97" t="n">
-        <v>78.84999847412109</v>
+        <v>77.83000183105469</v>
       </c>
       <c r="D97" t="n">
-        <v>76.40000152587891</v>
+        <v>75.01000213623047</v>
       </c>
       <c r="E97" t="n">
-        <v>78.66999816894531</v>
+        <v>76.01999664306641</v>
       </c>
       <c r="F97" t="n">
-        <v>32411300</v>
+        <v>38363000</v>
       </c>
       <c r="G97" t="n">
         <v>0</v>
@@ -2965,22 +2965,22 @@
     </row>
     <row r="98">
       <c r="A98" s="1" t="n">
-        <v>46076</v>
+        <v>46077</v>
       </c>
       <c r="B98" t="n">
-        <v>77.79000091552734</v>
+        <v>75.73000335693359</v>
       </c>
       <c r="C98" t="n">
-        <v>77.83000183105469</v>
+        <v>78.12000274658203</v>
       </c>
       <c r="D98" t="n">
-        <v>75.01000213623047</v>
+        <v>75.20999908447266</v>
       </c>
       <c r="E98" t="n">
-        <v>76.01999664306641</v>
+        <v>78.04000091552734</v>
       </c>
       <c r="F98" t="n">
-        <v>38363000</v>
+        <v>33079100</v>
       </c>
       <c r="G98" t="n">
         <v>0</v>
@@ -2991,22 +2991,22 @@
     </row>
     <row r="99">
       <c r="A99" s="1" t="n">
-        <v>46077</v>
+        <v>46078</v>
       </c>
       <c r="B99" t="n">
-        <v>75.73000335693359</v>
+        <v>79.43000030517578</v>
       </c>
       <c r="C99" t="n">
-        <v>78.12000274658203</v>
+        <v>83.12000274658203</v>
       </c>
       <c r="D99" t="n">
-        <v>75.20999908447266</v>
+        <v>79.25</v>
       </c>
       <c r="E99" t="n">
-        <v>78.04000091552734</v>
+        <v>82.69999694824219</v>
       </c>
       <c r="F99" t="n">
-        <v>33079100</v>
+        <v>69319300</v>
       </c>
       <c r="G99" t="n">
         <v>0</v>
@@ -3017,22 +3017,22 @@
     </row>
     <row r="100">
       <c r="A100" s="1" t="n">
-        <v>46078</v>
+        <v>46079</v>
       </c>
       <c r="B100" t="n">
-        <v>79.43000030517578</v>
+        <v>83.19999694824219</v>
       </c>
       <c r="C100" t="n">
-        <v>83.12000274658203</v>
+        <v>86.5</v>
       </c>
       <c r="D100" t="n">
-        <v>79.25</v>
+        <v>82.80000305175781</v>
       </c>
       <c r="E100" t="n">
-        <v>82.69999694824219</v>
+        <v>84.58999633789062</v>
       </c>
       <c r="F100" t="n">
-        <v>69319300</v>
+        <v>85642500</v>
       </c>
       <c r="G100" t="n">
         <v>0</v>
@@ -3043,22 +3043,22 @@
     </row>
     <row r="101">
       <c r="A101" s="1" t="n">
-        <v>46079</v>
+        <v>46080</v>
       </c>
       <c r="B101" t="n">
-        <v>83.19999694824219</v>
+        <v>94.30000305175781</v>
       </c>
       <c r="C101" t="n">
-        <v>86.5</v>
+        <v>96.75</v>
       </c>
       <c r="D101" t="n">
-        <v>82.80000305175781</v>
+        <v>90.58000183105469</v>
       </c>
       <c r="E101" t="n">
-        <v>84.58999633789062</v>
+        <v>96.23999786376953</v>
       </c>
       <c r="F101" t="n">
-        <v>85642500</v>
+        <v>200767000</v>
       </c>
       <c r="G101" t="n">
         <v>0</v>
@@ -3069,22 +3069,22 @@
     </row>
     <row r="102">
       <c r="A102" s="1" t="n">
-        <v>46080</v>
+        <v>46083</v>
       </c>
       <c r="B102" t="n">
-        <v>94.30000305175781</v>
+        <v>95.26000213623047</v>
       </c>
       <c r="C102" t="n">
-        <v>96.75</v>
+        <v>98.06999969482422</v>
       </c>
       <c r="D102" t="n">
-        <v>90.58000183105469</v>
+        <v>95.19999694824219</v>
       </c>
       <c r="E102" t="n">
-        <v>96.23999786376953</v>
+        <v>97.08999633789062</v>
       </c>
       <c r="F102" t="n">
-        <v>200767000</v>
+        <v>79915400</v>
       </c>
       <c r="G102" t="n">
         <v>0</v>
@@ -3095,22 +3095,22 @@
     </row>
     <row r="103">
       <c r="A103" s="1" t="n">
-        <v>46083</v>
+        <v>46084</v>
       </c>
       <c r="B103" t="n">
-        <v>95.26000213623047</v>
+        <v>96.01000213623047</v>
       </c>
       <c r="C103" t="n">
-        <v>98.06999969482422</v>
+        <v>98.45999908447266</v>
       </c>
       <c r="D103" t="n">
-        <v>95.19999694824219</v>
+        <v>95.33000183105469</v>
       </c>
       <c r="E103" t="n">
-        <v>97.08999633789062</v>
+        <v>97.69999694824219</v>
       </c>
       <c r="F103" t="n">
-        <v>79915400</v>
+        <v>59149000</v>
       </c>
       <c r="G103" t="n">
         <v>0</v>
@@ -3121,22 +3121,22 @@
     </row>
     <row r="104">
       <c r="A104" s="1" t="n">
-        <v>46084</v>
+        <v>46085</v>
       </c>
       <c r="B104" t="n">
-        <v>96.01000213623047</v>
+        <v>97.11000061035156</v>
       </c>
       <c r="C104" t="n">
-        <v>98.45999908447266</v>
+        <v>99.75</v>
       </c>
       <c r="D104" t="n">
-        <v>95.33000183105469</v>
+        <v>96.98999786376953</v>
       </c>
       <c r="E104" t="n">
-        <v>97.69999694824219</v>
+        <v>98.66000366210938</v>
       </c>
       <c r="F104" t="n">
-        <v>59149000</v>
+        <v>52604300</v>
       </c>
       <c r="G104" t="n">
         <v>0</v>
@@ -3147,22 +3147,22 @@
     </row>
     <row r="1